--- a/data/daily/topic_feeds_daily.xlsx
+++ b/data/daily/topic_feeds_daily.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G91"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,354 +470,354 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ETS Nigeria Conflict Situation Report #109: January 2026 - ReliefWeb</t>
+          <t>Enhanced Free Trade Agreement with Switzerland round update - GOV.UK</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 09:33:09 GMT</t>
+          <t>Mon, 02 Feb 2026 18:05:45 GMT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOY2RLR1BHd1ZqN1d2c05HS0luYXYyUTB2ZGVhaFp6WFhmVW1yekJtY29oakx1OXc4VjA4bjVNUVdMX09YSldURkVOTjdPaWlmZE02S0xpWVVQVlRHUDZXd0VoYXZtZTFoU0V0VHV1SXBIRnM4aV94UUd2VkdOMGJfTGFBTV9pdDRWMldEcW5HNDl6UXV3b0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPNm9tY21mV1p0R0tWX29YZXpfaU1tOGdWWnd3Q2IxMDJKdFdCNklhOEZnVnlydVZEWHNVNTJWN3c0Y2Y1WVVzd1VCaXdPZkh1N2UxNkloTVduV0U0aThIOUlYQ2V1S3kyc3ZwYXhDMzcxQW5YbkljVkw4RGEyOEZvMFFGR09KNFhCRTQtcjhPQUt4cVVCYzlPdF9R?oc=5</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>46055.39802083333</v>
+        <v>46055.75399305556</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Logistics Manager Magazine February 2026 - Logistics Manager</t>
+          <t>Fox Williams cited in Treasury Select Committee report on AI regulation - Fox Williams</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 12:00:25 GMT</t>
+          <t>Mon, 02 Feb 2026 15:59:28 GMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE5WM3c1Um9FY0RtamoxcENreVJvWUpQbWl0ODFqb0VUX0tqTk8xTVM4SmRkc21FLWJJV3pnNVhUcDlUbU5CRHpNWGhNcjRidTVHZ0Qxd09zaWFZV3NIc01mWlpYQ1ZVZ2dYTUtiMEt5ZGRCWVc3dTl2c1pNZ3ozVEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxONUticHMyRF85OV9QcFRDQm5LV0YwTDc2c2RjZjRFcnpmUXJIcXRVWlIwSWpEdXNpbkp5eUMyZWh2UHNXbHFZcHlIZDJBWkJoQl96ZDAtdUtSc0xodUVGSzh6Q1pDTFdlal9RTmlEUVRZcjRMWXo4TE1feVlCaFJ6RExTR1ZYWHJZRllZMzZJaFhKTy0ydmVIX201Y2pPcHdIZUtVV3BzYm03YzIwbUQzYg?oc=5</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>46055.50028935185</v>
+        <v>46055.66629629629</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>UK manufacturers recalibrate trade strategies as tariffs bite - Relocate magazine</t>
+          <t>US jobs report delayed again amid government shutdown - The Guardian</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 10:43:42 GMT</t>
+          <t>Mon, 02 Feb 2026 19:46:00 GMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPNVhoOENKNGhOeVEtZTU1RlB5ZVZ3Zm1Obkw3Xzg3MVFXUnFkZ1ozZmJKZUZKSGhyNmNtMGZfTjRsOHFkLUxUTWMyUzRBbGx3RTRFZU5DQ1ZCODdZSXRTa0V6WmdyeUVqSHA4amw2NEtHNXNmVG1wdEFqOWRPSWlDei1Zcm10a1BvbzQwUi1kb3F6ZWdZeFNXbmV4RS1Gcm9YSkpmUmZBcUw4QnM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQX1ZZelJzVEM5Q2gyb1dsa1dfSjdScEdlRTA0azlsdVU1N3FXNDdmWVd5b3E2eDFYMFpISXYtVEV6azA4b1JBTjJacFViai1SYWlCcWxLZ3hYQmNhMEU4MnpwQXRscWlacVRaWXJnbGNua0RFc2ZBWDFqbVk5cmUzWGwwQUUtbnY5bUp6TDB0WFV0dXkxYUE?oc=5</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>46055.44701388889</v>
+        <v>46055.82361111111</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Services - GIMA Day Conference 2026: the future of the supply chain for garden products - gardenforum.co.uk</t>
+          <t>Briefing: asylum seeker social care costs in local authorities - The TaxPayers' Alliance</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 12:04:40 GMT</t>
+          <t>Mon, 02 Feb 2026 07:52:30 GMT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPU3VFMUNRR1duajV0UmZPN3VTeklQYUF6VXlmbmc0RmdXOXpseW5Cd1FTdnBLNS1nQmoxbGNOQjEwWkp2RThUQUZLUlUyYVJwVnhKUFpzV1RPUkZwUDJHYTlpSnltdFNUaXlwT1cwMUpRVnFiVVhLcHFmczVMRUNmV19vbUZPWlg1SllsSTAzQm5HeG05X0NXWk1UVjlDQTd2NUlzaExVU2tLTlpYaHIzM2ZLLXpEQndfQmM4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPWGdja0oxNFNLVHVRc09JckljX182MU42Y0d3eGczU0xnM2hsNUUzd1c4Ykd2SkNzQmVzY1VQcmtEVHIxUWljelRpMXlzbUVLbFVQdkcxZHFjWnZlcnZaNkh2X0MxS3JtX2k2UGV3aXU5MWZpUzNnZElPdFEwQVU3czhwRmNnamJYRXRjNW9fN013b3Z6N0tF?oc=5</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>46055.50324074074</v>
+        <v>46055.328125</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Price of consumer goods could surge as shipping costs soar, industry body says - The Guardian</t>
+          <t>New report finds quarter of young Scots fear they will fail in life - Daily Record</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sun, 01 Feb 2026 13:00:00 GMT</t>
+          <t>Tue, 03 Feb 2026 04:30:00 GMT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNM2ZMdGRNWlRFaVVqVHg2Q0Q3X0c1Um5uRFEzRnJselR5czM5OXJZdHdCOVpnUGxtbXo3VUlTekowNkZMaEgyeEtBeDVDUEZfSXhyZG80NlQ4bFp1cnFwTVdCdURyRnk5Zzc0N2doM1BqSFBIY25Jb2dMdUhCclVTZV93XzNsQm9VN1R3VFY3ejB6eVQ4M1ZGRmI4SV9FdEhCcXI0VEdIQVAzVjV6bHBDdmNwZzlzd2c5OVpuNmVaa09vWmdFcjBKQkJn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNd0pXZ1JVcVQwQVpsUGIyYWgwbXJXRTVVVF9IYTlrenMtRzJkci0wczJURllGeFdJc2Q5NUpYVUFpUG5UYWNwZEhmNVZCLWh5TEp2Y1lwTV9sZHZIbkxoMmJPY1hMTDRNOUotSVdMOUFKZk1xX3BVQ3JNcDhWQ3psTjNJTno2bjA4VjFnVnhBMG5jUdIBlwFBVV95cUxNN3FBR1hkWWhVZk01aWlsTGIxd3V5V2FkTTRlMGlULTNMOHlzMlFWZjJWbG5DU0tUbl9LVVBHMFhDX0NwUkl3cng1YWNWMG5XZGZCWm1fU0xIeG1PZWFwY01ENEJKLWY0X2poOUtpU0lqM2lqMVhKMndXVjUyNGZmak51ZEExeDNCUmNGWFpFN2xudkxGTi0w?oc=5</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>46054.54166666666</v>
+        <v>46056.1875</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China cuts tariffs on Scotch whisky - The Drinks Business</t>
+          <t>Opinion: The report the government didn't want you to read about climate decline - Eastern Daily Press</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 10:56:37 GMT</t>
+          <t>Tue, 03 Feb 2026 06:00:00 GMT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxPblMwMm5fMVJQejYzOWRYQ1BWWDhud0tfeTlIdnEzUEZYanRMbWdhQlhVNnprRGs0SVdjNjJtb2p4SUN1emU2ZnZBdl9HTVV6aFFvSUV4bWtsYTVnWjMyNzM3N0xQcVRWelpObUVQb0tUaE0tdkR5SGduMGhXWnpZWWF6SXU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNUGZ6R240am5jMWlPN2t6N0k0cVVZQU1rVmVMUDJaWEJuSDdXV2c1UWU1UUoxNTVwc0RtLWE3eVJTdDNzSW5WQmVxVUsxcjdaQ1JNcFIyQ2Z5UlRsZ0VZb2hxY1RPOFJHNzhxSV9yNFluRlRvenptbU9NWEVOUWtlRFdHTnBxUzFKa0pWcDFR?oc=5</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>46055.4559837963</v>
+        <v>46056.25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NPA host Agricultural Supply Chain Adjudicator in Lincolnshire - National Pig Association</t>
+          <t>Thriving Kids Advisory Group Final Report - MBS Online</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 10:49:27 GMT</t>
+          <t>Mon, 02 Feb 2026 22:47:12 GMT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQOFBxVjc5ZFRKY2h4WHFMcmhnbWVBckZHNlpfVk9PVUhhREtMUldwMzd6c1hJUnZPZVRRRklRa1hHek14SHVvWGo0YmdVM1hxQ2g4cWFoNVo0Q2tRc0FUeUNsSnFFc3hXcnRqU2oxMTB4RmU4QkVWSFIxN2kyWjFhLVhPQk4xS3Q2Qk0wd1hXeVFxN1ZLVkxBbmhvVHZFTzJxV2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQSU55MTVrdlV5c3kyTDhpTlBoM1J4UVlXSzZ1ajFiV2FFRmdtZEV1TGV3eUZvSWxNTFdRMjRiY1Jreko5WWZDVmQ1X09ndjEyUmZxQ19EWU1zXzlxdkZ5T0VjMnd2YnNLbEFMWWtjNC13MlN4ajVTM09KY0pjdHJVdlBkMXlhN2xMY0VHTnZ6cDlzYjJ5R2VCbEhmREk3UnZ2SkpEYw?oc=5</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>46055.45100694444</v>
+        <v>46055.94944444444</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Columbia Group appoints Prevention at Sea as compliance partner and rolls out MORSE platform across the fleet - shipmanagementinternational.com</t>
+          <t>Migrant encounters at the U.S.-Mexico border are at their lowest level in more than 50 years - Pew Research Center</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 10:34:37 GMT</t>
+          <t>Mon, 02 Feb 2026 18:55:15 GMT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxObWwwd0JPOVh6Rkp0cmFwckNxZ25TSThzZWtyS0N1dkRGOUV2ODBpUl82djNtZDROVVlmYUNibnpRUW5Cb2pvYnBWRGlLZk1xb2p6YVVqNXdsSWRRRTBFdDdPMWNpZ3JERDlvQzBkQy1qYU0tb2Q0MjQxcm9XZUlpdTc5aWR0OUxnbWV5QS13VDNxdkRMZ00wWm8wVlJENTBRdmZBR0k2dlVnSmNiRnVmZHFzRVktaTNXaU9FZWZ5YkthVHFkUndmWERXdFFYWjk3WU8zUXVFM2NPSlU2OWdDU2FLYXk3Y3NaekE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQcXUzZzRjaHZIb2g5VVJLZ1RvYktBWm1rdXBWTm45ZlBkbWNOdTRWOFlvWVlBQ1JYV1dXVkVIRWVwY0tmZ29LN0tWdUxEQktDZUlLRHcyaXN2QUFxZ3RRejUtR1NWMHJuX1dBalM2Q1VXMmFfMlUwYUwzTWItYTdRbkxyY2tiVVB4T2c2blR5X1hGWXBKbUttNjhYQUhnOGVhLWlEb091ZDBjcVZMVTg3a3IxSjBwVndTX1E2U0hrcFFFT2laWGdfNE9WeFpfR3ZjeWdKZjhhdktiQQ?oc=5</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>46055.44070601852</v>
+        <v>46055.78836805555</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>The North East’s Green Super Port: 18 months on, the opportunity remains vast - North East Bylines</t>
+          <t>Government report highlights artificial intelligence gains in Kazakhstan - IntelliNews</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 08:12:00 GMT</t>
+          <t>Mon, 02 Feb 2026 15:37:20 GMT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOamgxNERESWJlUy11VUpyMHBVazQzM0tMUXpNRzY3UTk5bXBoV0x2bVZUMkxaUFl1YUFrS3NldGFfY2xuNy1jcjB0amc2UFR0cGlqWWlyQTFpVEVadkY4akJuU2FTeEF1M0FfMXgxejlrbVJvZDhpVFZEcVlVY1N4MFpBaGZnMm5ObmtxemxDWk41V0h4STExZ00wbEhuVWtJQkpha0pHLTI1VG9EdG5wXzBqbm5zY3E4dmpzbUlRekY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxORGNzMl93aTlJdnFiczhjYnJNOXZMd3pNQlotRFRmS2RBd3hibUhieGlQTHR1MHY1eVpPQUtlVGEzM01KclZERFBPTkl5YU45X1JGTkNOaUZCTlhYdEVwT09OZFB5RURoUjN0TWxnbXk5V2J0dHJaQkc4VGVaZmttcGFwUWN2M3dUT2xYUGQyaFVYX0piM3J1NVFxWTZsWmtickt5dWJwMUpNWEZl?oc=5</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>46055.34166666667</v>
+        <v>46055.65092592593</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mapletree on how European logistics is gaining momentum - Private Equity Real Estate | PERE</t>
+          <t>Economy update: Seven Labubu stores to open in Britain after Keir Starmer's China visit - GB News</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 02:02:52 GMT</t>
+          <t>Mon, 02 Feb 2026 14:01:53 GMT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQbF9UQXJKSXljNU5GeW9JZmpVZ0ZobUNnTFF5bVFxanRIam4xX2lNMENFeTVJT1Z2WHF1bXI3WHphYXhfd0VQNWx1Z25UVy1WNkFKY0ZmY3hfYTAyYVhJanRnSW44M09CZ2lOcmRIc2czTnY2OVc3UlhFWjc5VGtSYng4QzNxbExj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE1kbUtPWWFJNVlGT2YyTU9OWEl0Y3F0SDQwWE9ELS1EXy1fd2xTQ3JNZEhiN0RENWg2RGxDZ2J6bGxBRGZ2NldxUkFUMFdRRlctMXZoY2R0UnB2RjhGSlM3cEJtOHB5TVBLRUhpbTlNdkhWNzA4SEtB?oc=5</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>46055.08532407408</v>
+        <v>46055.58464120371</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Geopolitics is rewriting freight rules - Air Cargo Week</t>
+          <t>UK’s former US ambassador faces scrutiny over Epstein ties, leaked briefing - South China Morning Post</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 12:50:44 GMT</t>
+          <t>Mon, 02 Feb 2026 15:59:12 GMT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTFBCSGVRWDFSV3p6eDNUb05PME9ieHF4TkJ2azVoNFUxcDU5WDhFemd3S0xEWmVadXY4R3M1OXdVR0RyQUo1cGhmTlRyN19idnlCbHNUY194My11ZUNKcHhoWnBfRkRNTVprbGZLc1pqLUpsdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPUkp2RzlBQ1hqN3RUY1RpS21EZlRoakx3ZXlaZWlxS2ZUMTdfZ0RDQnZkNm9oT3lwYzBYMUJLNl95Q3JWOVFxa080eEVpcUFheV9SSlVGWFUwbFhnTVczSWFKMUt0bk9mc21rbDZfVF9jWVcxU2hxRnU2dEVyN1hUc1J3NkJwbDd1OTExa0c4NkJjZ2VpbWlKZWYtM3BIYmczVnZuNXVrb0N1QVVkNlJkS0xlZGZFZHVVUGx3TE5zLUFHOV9pampaTFVn0gHKAUFVX3lxTFBVSElBNWxvdHZQSVZvNGt6eWJ4TnRRMW5OcEpITlVRZEJQZjE1eWJDVEppTW9pdHlZY1VpWkxjQlMtemJVWTN3SzZielBrcE5LU3JDVkt4NVA0aVdBLUl3d0c0SzRJUkt4ODJkRHBWMFRTaWY2TUV6ZF9BOXh4b2d5cDJxWUlBei1jeXBIYXBnUEF3YXlhUlRlaU44YXFIZXB2VkJkLUJsMmw2LWhveUp0WURTVGU0cGZJNHlIWklYc0tEOEJMeDVBRnc?oc=5</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>46055.53523148148</v>
+        <v>46055.66611111111</v>
       </c>
     </row>
     <row r="13">
@@ -833,24 +833,24 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Apollo appoints Valor as asset manager for logistics portfolio - Logistics Manager</t>
+          <t>Hope and uncertainty as India and US strike long-delayed trade deal - BBC</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 10:21:00 GMT</t>
+          <t>Tue, 03 Feb 2026 06:29:43 GMT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOUUx3a255dUZramdIYndNZmxSMGkwVS1fSy12dW5FWUY5d1ltV0RGbF9jRjdBdldRVXA5RW1SVm9sWUF3emNaYW5QLU1hOWpfZlluX2dPZkxGQTZGdHMwVEJ1LW9WeWk1dHlZOHhsWkk3bTI1alhXRjkzUmlZdDJlaE56R1hrX2FHQ2VXTll2N3BzOElsSTk4alhrZng?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBoRHZ3eDU2UERBbkZfcHFSSFdicTdPTFdCM2pMQjJORmV6TGFhT3poR2hzamVwN1V1QlF4UDIwMTFDT0gwZUJwb2EyX05Kd1VINnhEdU9fVDIyZw?oc=5</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>1</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>46055.43125</v>
+        <v>46056.27063657407</v>
       </c>
     </row>
     <row r="14">
@@ -866,24 +866,24 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Clarion acquires Mountpark Chartres 2 - Logistics Manager</t>
+          <t>US agrees to drop tariffs after India stops Russian oil purchases - BBC</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 10:31:48 GMT</t>
+          <t>Mon, 02 Feb 2026 17:55:54 GMT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE9tY2V5UFFHU0pfb0hCa25JNHk5S0JWbXZadk5kU1ZKSWV3QzQtN05HRk5CeHBVeHpQYTdFSVR3UVVIcGVzczJxR2ZEa1dlWjlXcFNaT1E2enVuM0UyUldUai1iU25xSk1PT2NqLUFNWUpUTzI2a043ZHdSYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE1OYXl3VnhHNkQ4QTZEUmpXS0JobDlJeGQ4MTRxbW9xanZvZ2xnY01veXpXNjhBNDR5bWZUUjVoMmdzTHd4dWxxbk1XclNmek9QUzdFTU9sNDIzLVBz?oc=5</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>1</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>46055.43875</v>
+        <v>46055.74715277777</v>
       </c>
     </row>
     <row r="15">
@@ -899,24 +899,24 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Wallenius Wilhelmsen starts operating car terminal at Port of Gothenburg - Logistics Manager</t>
+          <t>Modi liberalises Indian tariffs much to chagrin of the left - thecanary.co</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 09:24:18 GMT</t>
+          <t>Mon, 02 Feb 2026 21:23:15 GMT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOMzBjYXdWRGJ3QUN4QlgxWjJUeWUtVUxVSzhFbnRDOThwWFRySkJIZjNqUzNMRENVU0gxMzFlVUZqM1Y1dFFJQW9nbTlBQzdxVFdjazJ3XzdxWmgyZEVnblF5NnpscTZueVpuVnotU0Q0aUZTUW81aUM3dkFBSVNSMlMxQnduRUJZekxISnFmRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNQ05aX2phLTUtaURXdDB6UlZuZU9EWlJXX0s3MTFacURQZnZIdF9tRTI2T0MyOGhIdXJNVC1TbGJNcFBZZkw1T3FrSWtXaHgzcEtIWGJIVW01VTd3dXd5Z3NSbEJKZjQ0M1BEU3A4VXZDaGxOd2JsYzFrNndlV01oQnlqcWlwRzBkTTBkWHRiekxPTFZK?oc=5</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>46055.391875</v>
+        <v>46055.89114583333</v>
       </c>
     </row>
     <row r="16">
@@ -932,24 +932,24 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Why AI-native execution is the next step for supply chains - Logistics Manager</t>
+          <t>MP asks government about freight-only line amid 'closure by stealth' concerns - Rail Magazine</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 09:00:55 GMT</t>
+          <t>Tue, 03 Feb 2026 05:02:02 GMT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOSVEzSlZlTWE4QV9yZlM4QzVlN2pheHJsSjhVSlowVDJUUk9jaGRGT2psZ29OTUdpSENLNkE0VFQ4NjNvdFU4SjFlbXA2WU01M241WEhpMFBTSkxPSmJxTkxHU1pFN3A5SjJ2OEdvNHZRZV91RkZ3bjdDOUYyX2NyLUVaR3NDY3R0UjdtOWlPTDBROFZFZWVN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPc2NSUVZaTlRTVXJBNDNTUFZsazBhdFcxZlI0dXZkSGwzbVBvQ19ybndNamd1Y1NwSXpXTUhJTUNVYllvTzJtWXpLdjNkRmxWdk9uS2hGMlFWSkloLWszM29tdEp4RW5LbmZoS21hb3ZXN05tQnNJcDJHOEp3OXZ5aGJRWERva19HelJJb0RTUUptUklyS2FDZ0xrUm1Yd09Ra0JWQmVObzRKYVFK?oc=5</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>1</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>46055.37563657408</v>
+        <v>46056.20974537037</v>
       </c>
     </row>
     <row r="17">
@@ -965,24 +965,24 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>General Mills: Future-Proofing Sweet Corn Supply Chains - Supply Chain Digital Magazine</t>
+          <t>Grade II listed bridge could reconnect Port Talbot communities - Wales 247</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 10:36:53 GMT</t>
+          <t>Tue, 03 Feb 2026 06:27:57 GMT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPSDNHaERCRzBmS2xTYWNEMUQ3UVdfejZycGRHcExYWHVOZm5LSllMVUE0ZElpcEhkd2czakpfbU5BbnowTFFKN1gyZzBZbkVxdWpVVVEzSFU3UFVfUUNnbERBTUF3VmM3Y2oxMG9KLUp5OUtHQU50alNTTmFCQ0ExVXBfcTNiSDR2eHM1X0JZbXFpQ3dN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOT1JCUC1SQkRNbkhnY2x3RFRsVFFkekI3N2lqaGVLZHY3b2dfUzY5SlpKWnQ4TUpNWHdxeU5hUUtVV2h3eEFDamZCOHZ4anc3bXZ3TFFxVmNZR2NzVjNTb28xODlkbG1BSmZYenFKcTllanhOSXdmUzc1WE1pcUc1aXNILWFUY3JTbkdMRUFFeHkzQ1E?oc=5</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>46055.44228009259</v>
+        <v>46056.26940972222</v>
       </c>
     </row>
     <row r="18">
@@ -998,24 +998,24 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cargo outlook cools in 2026 as supply chain pressures persist - Air Cargo Week</t>
+          <t>People 'avoid St Peter Port' because of accessibility issues - BBC</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 11:42:00 GMT</t>
+          <t>Tue, 03 Feb 2026 06:15:03 GMT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPdEo1Y2NzWUg1YW5pbXZqSUFfSC1WX3NCdTIwOS1HUnBCR01XNGIzVmJoZ1hMMWhydnhTeW1JRC01RFZEY2RoMGFHOGV0SmZDVF9IUW5kSGNYRXJsLUVGc05YSW1BYVY0bHktT0NTRGI4QWpxTFZNbXplaEtvT09veUFMT1phTDBXSmw1TExhMGo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTFA5QlNNU2t0Q1JSdmItVU4wUzhEZ2JldGZWbFZLTEVlTG9vM0s0YmRqVndycGJ6RFg5R1pUbXRwT2dXSkg0NXJGZDI3SlM0SXl6RnNSRnczckVsOVdO0gFiQVVfeXFMTVBBOHRyZC1DajNSMUlkLVpma3haLW9vNkg1dW5scHJ5YXNFQ1F5NzVJaGl1YWg3Y3lEcEZDOHZoRlh4UU4xTWNQQmdOcHBYbjRoN21oRnZJdXNaYndaTmJPV1E?oc=5</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>1</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>46055.4875</v>
+        <v>46056.26045138889</v>
       </c>
     </row>
     <row r="19">
@@ -1031,24 +1031,24 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Gold in the age of sanctions: How the Russia-Ukraine war reshaped the global bullion market - New Eastern Europe</t>
+          <t>How Investors Are Reacting To Realty Income (O) Expanding Into Global Logistics With GIC Partnership - Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 12:49:35 GMT</t>
+          <t>Tue, 03 Feb 2026 07:09:00 GMT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNRTNnYlFDLVFLdGtpM3pQR0d6TEtJczFsRlZrVEVZa0pKcnBuZXVuNGU4X2Q3a0hackJvYnExOTFfZzFXVTJRcGdRakVoUEV5RGpCNk5zalpUNjRSSXNhTmd4aWd2RTBiTWk3YUpXbVpMZW5GanZaRlJqYWJmbHpmemItZEdvbWhfaHhISmFxNVZRWkxXeEdYMkU3YWlxUDlZRG9FNGJ5WEhDdTd2U25VY3p1djFkazU4aXFYdmQ0d1BabFRHOUxTZlBR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOYVBjTlNZa2pDYS1iQ1pKXzVZYy10UkFZX2FqbWszNGloMlpRSEdoSDRXMUNaY21BeDRvWTlwNkx3ZXFTWVYtcnR4V05BSl9uY1J2X2YxUndPYktIZFNObGg1ekN5dXAtRUJrNmVrUmFINWZYaVo3bFJxQjZJb3VSMEItRlNURURhZnNz?oc=5</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>1</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>46055.53443287037</v>
+        <v>46056.29791666667</v>
       </c>
     </row>
     <row r="20">
@@ -1064,24 +1064,24 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>How AMP8 digital compliance is shaping the water industry - Water Magazine</t>
+          <t>India’s Rupee, Stocks to Get Tariff-Truce Boost, Investors Say - Bloomberg.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 05:05:04 GMT</t>
+          <t>Tue, 03 Feb 2026 07:06:00 GMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNT2RfQVZPS1FHeHRURDhWalhPQU43d0RkOGFTTzRxd19BclVwRGtQMlJfUFB5TW5fY294SG13ajVWand6S2Z6a2FCaHFNcTFrQVNJQ0xIbWFOdkRhN2cxbGJ3aVRmVi1tNWt3WUxqUkxuUS1pYk8tWFh6N2ctbXlEYVRQUWd2SFhVNXZiMFVlclgzdkZUU2ZLSEpjdmpuVXpZV2dV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOemVlVDhuUDN6WHNuSGdnZnVfaTRTdXJUQkN6OE16M1lsa2dwRTlNZjhFMkUwbndRZDhCblpSVEc4ZTZFZEk3cjZrUTNNcGd5Q0pQeFV0Y0Q4U21OOXhVQ2dERWJ4NVZGLWpvd2pVMGhDdTBOOWpjWDZtR1ZrclJ6WTZJMGxQTWVuTVdRYWduRUJ0MjJteTNwdUotazJ2amUzOWExenJCeTRTSUhhaEJBSA?oc=5</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>1</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>46055.21185185185</v>
+        <v>46056.29583333333</v>
       </c>
     </row>
     <row r="21">
@@ -1097,24 +1097,24 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>EU ready to impose sanctions on Kyrgyzstan — report - Eurasianet</t>
+          <t>South Africa bemoans slow BRICS progress - Fruitnet</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 09:56:19 GMT</t>
+          <t>Tue, 03 Feb 2026 07:16:45 GMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTFBWb0tFRFFEc3BtZVhkUV94MWt2MUVzcGNMYmp3eGZHSmk4QmlyTC01U1VjU1JCQU9aM2dsVmMwYzMza1NfRmdHaEJKaGZiOXozMXM5bXVtRVJwb3JmbVhBaF9rRnQ3eTVLQ2lNUVgzcjB2NEI2U3dDX1VXazI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOZ2NHTzE3Znp2OFVmZmgxOXNJSnFpUS1CLTcwVHlnQW5DY2p1NjkxZFBtUnA3cTNDamttWXBjMkljaFFKVXRMbEozeTJNOWRJOEhFQTJBUGRMU2lfVko3WlZtNTJYSUdpSVc4ZlU1MlcxaDI1SnN0eS1OZmdTYzRlNnFGNF84M1BQSkRLaXYtenU1aFIy?oc=5</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>46055.4141087963</v>
+        <v>46056.30329861111</v>
       </c>
     </row>
     <row r="22">
@@ -1130,24 +1130,24 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Port of Tyne appoints new Direct of Innovation - porttechnology.org</t>
+          <t>Diana Shipping secures higher charter rate in extension with Cobelfret - Tradewinds News</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 11:45:34 GMT</t>
+          <t>Tue, 03 Feb 2026 07:12:31 GMT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNN05iX2doRUpwajRNSDFMVW1MUnU0d2VsOW1fbTdjR0V5Q1VkRzNHWlZwN1BkbV9SLXlYNF9ZNm1wb09YOUR0MU5jNXRTZHpnbWx0bkpsZWZfdTNiUDBOaW9CbWxxcWotZ3M4b2UtM0lseU1IdUpWaWpDaWpYTFRLeENqNjZhcEp4RzBj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNRlJqZnpUd01zNE52eDRkcGhIZDJhS0lqVVJGNG1ST2c1WVgyUDVWblM1OS0zNWNBbGwweXYtd05NZHFiZHAzUnlzUWdJUmlaWWlxX3NxRlZXeWxDUl9TQVlYV280WUZLNDBUS1BfaXZfaEJNcWZzajBUNk1lTFJ5T0txRHhfZjVTNE1tbEtKci0yZ19qd1ozVkgwMHljMmI1ZklNY05lNlUybjcxdWw0alRmdjRvSzZFeG41ZXR3?oc=5</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>1</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>46055.48997685185</v>
+        <v>46056.3003587963</v>
       </c>
     </row>
     <row r="23">
@@ -1163,24 +1163,24 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Health and Safety at Scale - Logistics Business</t>
+          <t>Andre Gray is a Valiant! - Port Vale Football Club</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 11:15:24 GMT</t>
+          <t>Mon, 02 Feb 2026 19:18:57 GMT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQZVY5dHhMNlBKYnlkVmRxV1RlZ3hfdDV3T0FzQ1lTajZjaDAtSVV2RVlleUYxZWIxUDR2dXFhSEFtS1VGVy0yTnJQNVgtOERlNTJoWm5fVkFoaVJVajZiVXFhdS1WOFV2bFZKVl9IYjJkWURkWkxyWmxrM3BTQll2aHpn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTFBmTTI3Q01qcGdCYjR1Qklwa3JNNTNNUlJ0c0VNeGhQMTdVVmVYbGg0aEgxT0x2VDdlcnNLOEYtMDg0THU4MHlCcmRObDNfcnhabjJBTXQzNFdqVm5wWnNfUA?oc=5</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>1</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>46055.46902777778</v>
+        <v>46055.80482638889</v>
       </c>
     </row>
     <row r="24">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>THIS WEEK: Russian sanctions, Ukrainian loan and US trade deal - EUobserver</t>
+          <t>MPC Capital and Morten Astrup roll out new shipping investment platform - Splash247</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 06:00:55 GMT</t>
+          <t>Tue, 03 Feb 2026 07:31:43 GMT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPZ0RuX1EzcDI4OVJDVTRMbmJMdTRuR3I0X3lDX1NYX3NBcUZDdEZIckxMMDhnYTNDMjhJM3A5UDE0UVpIUnV6clFYWkNOS1J5V3p2a1JkUGt6X19xWE5kZXcxeDB4QlZpNHBVRlJ2TTQ1Vmd2UF9qV1VybEhuME1HdnNMd0pNOVQ5cHlsV2hOUzVVVm9STGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPTE0wcTV6QlhtSEtqaHZWWHZhY0dHNS1BOUJjU0UtQXNLblQydVVycUxFT2xoLWhHb0Z1cDVTYnMySmNBVFhBUUtkdGJkWE1DUTlJUFJ1emgxSmZVai1MQ19XUWtpQXZ1LWNKQ2F2c0ZWblR6OENXOXdRSmdIZmtDTkQyR1NrM2QwLW1qM2o1bmlGYzZPSm5HcEFn?oc=5</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>1</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>46055.25063657408</v>
+        <v>46056.31369212963</v>
       </c>
     </row>
     <row r="25">
@@ -1229,24 +1229,24 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Net zero readiness in Hospitality, FMCG, Manufacturing, Logistics and Retail - theenergyst.com</t>
+          <t>Targeted sanctions in response to brutal repression of protests in Iran - Australian Minister for Foreign Affairs</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 10:46:56 GMT</t>
+          <t>Mon, 02 Feb 2026 18:53:57 GMT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPcENJelBLS2dmNFotWm5CLVpnY2h1dFhPbTlGYkJNZlRVSnVhNHJBZDFNU3lOMVNxWDRHc2NSYVpzZENlcEJaclRYNTB4TGhSNEM3b2RKMlA3TWxtN3NtMzFKaTNxWVNHUlowaVBGaTFHWnpQTlRSLS1SLW5tdTVJYjV5WjFtQnRodlg1R2V5dnNMWTJnNWlqT1o2al9pVUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQNF8xXzhtOG5yYXRXYk9Ydm9WSEdfd3NibzRuSmdtS2ozWFAycldxWHlNWVNoV29MTU94T0RuOVdYaHB1MXNDV3B2R1RfVXc0Y0tjc0xYOWlpV2dNWWxaaGxFQ3dwN2VGci1UTVRMLXV1aXpmNGxpTklXNWp2UW0zdGNIX2h2eVJHeGJkakRjWFpHTm5YR1VsTXlOd3FiN0NZdmFtZG12djR4MWRvYnlhc0I1elhqbEI3QXNMazlMeU1MOTFhRXNz?oc=5</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>1</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>46055.44925925926</v>
+        <v>46055.78746527778</v>
       </c>
     </row>
     <row r="26">
@@ -1262,24 +1262,24 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lamb welfare measures will be an “added cost” to supply chain, says NFU - Meat Management</t>
+          <t>AD Ports Group to help develop multi-purpose terminal in DR Congo - Baird Maritime</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 11:56:09 GMT</t>
+          <t>Tue, 03 Feb 2026 05:16:42 GMT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNYUVBWXIzNWlWWGRsbk1lVXE2RnVqMEtNbG9KR0YzbWlVTGJJNnpDaFN3YnRzMExRZlBESGxRem9mSXkxSEgySVpsSkxqM3pLSDFjNHdnckNmN2JtRGxFUWJYVTNYci00ZFdHbnE0bU5ZYUNVMmNGOEgxelc3cDJ4bXBVOGJGMlhOUlVhcGFWTkxLZjFUZU9wT2hOdk16Sl9XSmtpTkZYeXN6S0hDMVhSQzJrbW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQMzZZT0Z3ejBobWptOGdwTG9CemNtNFdyaDA5dkVEX0NXb0NhTzNFa0FYdUV5QjdjM1pyaXFtZGZOR0VnOFViR0hiazZSZUcycFIwYkxTUGxkU29DTkxXV1VrYmVYWUpIN3JTTlhZT0hqbDlUZ1l2ZHpzTzVwSjRmTE1mNHgyb3F4SG5tYjNPUERsRFBRSk5xbHRBWmpQNzdCdmJFQnZicnlUdEFJWGVr0gG8AUFVX3lxTE9OS0VYNnhRUHFXQmFkTmtLNUdIaW1RNlJKVmpLbzhxV0hqNXJfQmgwY1VjSVBDZnhWSUFOdDZoTHNUT0xqQW9vWWhVX05hLTI1NXNCbXoyN2Q3OVZtRFdNMjNQVkFkTlpJUTlwUHJyM2NxS2hSVFVqTTdGemtYb1RGc0dnT2NoSUVkZnlBRU15bF9mR0t3N0JDbnpJUE14U1p4ZG43bFpvQVhMcTQ2N25rQVhyY2VkTkYzYzY0?oc=5</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>1</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>46055.49732638889</v>
+        <v>46056.21993055556</v>
       </c>
     </row>
     <row r="27">
@@ -1295,24 +1295,24 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>The Compliance Inflection Point: Why Mid-Market US Insurers Are Feeling the Strain - Insurance Edge</t>
+          <t>The Clean Energy Supply Chain Europe Still Doesn't Control - Crude Oil Prices Today | OilPrice.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 09:02:57 GMT</t>
+          <t>Mon, 02 Feb 2026 21:00:00 GMT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOemlwSW5xR0c5TXk5ZXJtak96NktuWmpaUFRYcDZKWl9XMlg3dmJPLVZwOFVWQ0VuNFFUSWVSMEViZjhOZEpWbTZieXNVWjVwUW9QTGpucmVfQ2xDck55NEhsSzFhc2ItbjNmQkYzdkh4UE0xV05QLVFjM3hvc3BfTUZ3OGZsc1huVmFDVnhVWUVqVWFUc3NRUHN1VVZtRUZlcFZBcW9yTk9XU0l1aDBqX1JkNWRBYnJweW91MQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxONWNkWW5kTzhjYW1mT0ZXcXUwdVQtNW1GVzRFWTNwT0ZydzJxdlZJNDR6MnBpLXIwVDg1ZWF4ZlhmVnh3TG5FTkZJeDFGTk9yY1ZCSndWNVlFdWp2RWNjbUQzRmxTbDVBanFqVjBabXZ0SnlJcGZWc3d5NkdEdFFnYXVhNE55Q2ZRaUt5em4tWk5Vbi01TjJHQTN1NFNhTVpMNF9rY0lKR0HSAa4BQVVfeXFMTkNsSGJ6T2dMWXRKYmQ4M2tYbXNNR3NsRjVCQnV5TWJQRzVINWQ5ajlPY3A1Z1paWlhCakpaQTBQa0tvYmNJN24yLVlfdDRpZGpPV1pTWklPb0IyOHN1RU5qNFowd1F0Um1peU40RnF3RnZGc05paGF0TDVKdkQwazNxeXRDNERWaXNlempoSERvand2TEZnbHV1VzB4LV9yMGQwYjVHY29hbm5qY2RR?oc=5</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>1</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>46055.37704861111</v>
+        <v>46055.875</v>
       </c>
     </row>
     <row r="28">
@@ -1328,24 +1328,24 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Verdion plans €69m Greater Copenhagen urban logistics facility - Green Street News</t>
+          <t>Global Mobility Lawyer: A Focus on Compliance Means Clients Often Miss the Strategic Risk - Fragomen</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 07:45:57 GMT</t>
+          <t>Mon, 02 Feb 2026 22:35:06 GMT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOWU1GQkF6aWxiaWs2RjVoWTliVE9UcDRBOTE1aWJENE82amxXQXlmcTFpMERCUlUzckluZzA0N2paT09VeWhtVTU4YlpNZkticm8wWWs3UzZ1Q1BRcXA5bzVQd0tJRGJzVHUxdmdhMW4yOE5XNm1vclU3UUIydkkxdG11VDZmVnk3ak1ZZzNBdTNTeXBQTjhwcC1QMV9sMXJX?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOb2xYMHdGQWIyV092NjNUWUdCWWtUYzNxTmplb2RVT1FQOS0tQzloQ1RtQkZEOE1DYmN6VXBqUnU2MDMxbWlDRFI1T3h4Ynducmt4LXROdmpaTmZfMW1QcVc5TVdQOTBuc2QzRU1MV21QRmVCWFp5YlFPX0t4MEVvLTdmTUI3S3liUnFSc09uUnVtdk5IWUhkeERzQUhFZzVudWUtQ1RFZ285S0VrTVFybldjZ090Zk5sR0oxLWxxcnkyYlFISGc?oc=5</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>1</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>46055.32357638889</v>
+        <v>46055.94104166667</v>
       </c>
     </row>
     <row r="29">
@@ -1361,24 +1361,24 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Clarion Partners Europe acquires French logistics facility from Affinius - IPE Real Assets</t>
+          <t>Trump’s tariffs are keeping inflation from going lower, report finds - The Independent</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 11:33:47 GMT</t>
+          <t>Mon, 02 Feb 2026 17:29:00 GMT</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOS1g5VWhPM2VtR3lQSC1sVFRDNmhEVl9IdzYzWUw5QS1sVXgxZHhWc2o0bkR2WUtNTnlsUm45VnZiUV9ZVnlIeGdWbW1jbXhOYzViQlRxSEZtaHJoODQ1ZW96NHFHSWJtUGNqZC1xM1NVWnk4clcyT2VQSVhaRUtWRjdUQnlfWnZLOXM2dlFyaFNtWUQyYndCcDZTWHZXVnFLNWlRdV81NFdfWnUxcHVzMm1lb005R0FsM2g4aFJB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPOE5VQ0ZELW0zcHZyQ2JYdzdOQWJ3ZzNheTB5Nm1FRHk4aHBOQ3BOWlhYOEhBSEo1Y09GYjRsM3hqWnA4dzh4Rlk4ZHM5cG9lcjVQeExack1mMTUwRW9GWDJfQW5EQk8xTkJQdHBXUnRySEdGckFWVG9XR3RhQWQySFlOVWZFcGxtdTh4NURHSFJwWmE4QzlKRXpqdEw2YktYT0MzcXlFc0I5NzdjdTFNSmxiNlZPUzQ5MVJ3NmhEbw?oc=5</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>1</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>46055.48179398148</v>
+        <v>46055.72847222222</v>
       </c>
     </row>
     <row r="30">
@@ -1394,24 +1394,24 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CEO of World’s Largest Container Shipping Company Says ‘No’ to Arctic Shipping - High North News</t>
+          <t>Asia’s SITC extends container ship order tally in China - Shipping Telegraph</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 10:50:10 GMT</t>
+          <t>Tue, 03 Feb 2026 02:01:12 GMT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQU1ZCNTRWdUhWN2VyUzZQbmlwSDFFNFlwckhWWVhMazdIR1lFQmhieUxBYjJzLWFUTmdsRkVXdFdndXlVWWtoSDNTUjFhUHBQMmQ0a2RVcVhwR0VmM0tpN1ZVTVlWNE5tV1RHVEZmdjNXa3JqQ3lRbmdOVnFGNndTM1FuX1lnU2p1alBuVTBxT1ppSmwtT2NUX1NETk1PVVN6M3dlSlFLNnMwdGVqWFU0elQxYWc4Z3lWVGVCQm9WQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPdkd1NDR3ZnRtVXdmSDNSNDktd0F1aDM3d3lRZFdQWVVFcWtFS1lQTnZ0QjVJb3dFVkF1bHMxdnhKU1IydFVyMDQ3WFRURjgxZHNlZXljX0pkSGFNcklyZ3pGandDcnhWa0xwWDljWTg0SXpaOEphbnVjZjJLU09tc1VLaFViRFUyMnh1bkxxTmRwNVJTLXhDMFdRRGhWc0dfWVE?oc=5</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>1</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>46055.45150462963</v>
+        <v>46056.08416666667</v>
       </c>
     </row>
     <row r="31">
@@ -1427,24 +1427,24 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Skarv Shipping AS selects Oceanly Performance Plus to support automated data integration and digital fleet operations - shipmanagementinternational.com</t>
+          <t>Tariffs are reshaping Canadian manufacturing, but not all workers are being impacted the same way - The Conversation</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 10:34:37 GMT</t>
+          <t>Mon, 02 Feb 2026 19:08:28 GMT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQM2RvOWNMZ0JQblZOSjV3NHN3eldnckFLNldOaVc2cmU2YXRvakdmM2NhSlFXVmpmVnN3MFdrUjJqMGJxaWlXZFM4YVBPY2xBeXVETmVJYm9aMFNJdklfNmlkclNSbjc4X1BxcGluM1NVel9PN3R5VGNQVWJYVWw5T3ZfbjdhQ0UzdFI4QjFOOUs1M0JfNkY5cXVFN2hCNExaMTVBZG5XaW1rQ29MUG5waGdfQUs2OTV3TE9wVmdBeXN1VTUxSnd6NnNPOXBwYlNJS1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOaldJdHBoSHA2cmtTcUNIVXpxWGlvZk9RMGFKNjBDS3RlQmtqRS11b3pUZjlVX2JiUTZnNkcxRHdzTHFkZF9oa0V5R1JjY3hSS3JqR0xrQU15ZE92SU9kbmp5X1ZESXJ4dFFWMFJyREkxOXJ2QUJFREtIYkxJVl9IZGJ6UE1WQm9obUxQbUxlUGYyQlF6U01yT0VkYVhELTYtT1p4TXBCWE1yMTJKWV9GTUVtajVhYWd4bFJ1UDBXTGw4cG4yRHA2a3dMUQ?oc=5</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>1</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>46055.44070601852</v>
+        <v>46055.79754629629</v>
       </c>
     </row>
     <row r="32">
@@ -1460,24 +1460,24 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Shipping investor J Lauritzen hires new head of research - Tradewinds News</t>
+          <t>What Is a Supply Chain Risk Management Framework? - Z2Data</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 11:03:44 GMT</t>
+          <t>Mon, 02 Feb 2026 20:01:15 GMT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPNFZvNVlOdXhWeEVPakxtRTVVVkppb1ZmUjJmRW5mcGNsWkM3OWhpNW1IQldqVmx0VE9WSVlvc2N0TmloNDhHUUlQVlpPN1hzaGx0dkE2dmhqVURaNjU2U3ZyR1l5cnlfcHBCRVRzY0tiZEF1b2x1MjZQYXVDa25GdkVhZmhBOXEzUllVMHU5d0I5Ynl6WkJleWZQQ2ZjYUlhWk5qSHZTd2hRdWs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNck5ocEx0V0ttWmJuV3VMel8xZE5DZFNONU0xbS1fYlpwQ2taa2NiTjZTdl80TkpWZzFBcXE5MjR5UTBTSFZGUnlIZmtmTFNyR0k4cjJCek9Nb1ZtdmNITnhzczY0Q180Qy0zTld3MHN3QUtYVjhUY3BocXJ4cUZaNk1jMUI?oc=5</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>1</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>46055.46092592592</v>
+        <v>46055.83420138889</v>
       </c>
     </row>
     <row r="33">
@@ -1493,24 +1493,24 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Abuja Pushes for a Modern Logistics Architecture - Air Cargo Week</t>
+          <t>Columbia selects Prevention at Sea as its compliance partner - Splash247</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 12:13:26 GMT</t>
+          <t>Tue, 03 Feb 2026 04:22:43 GMT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1BZENaWFpKQldCdHo0UFpwTFZLdnBLYU5aZFc1TlhSaERkZGNrYVdXVk9KX0ppX0haX01lWUdRQjljV2pCVWFxamlnTmhpbWZTUGNyOGdRSUxWVTN4VlRUQXdYX3IxR2FIQkVrUHJoRzJQMXIxYTZNQTBwOV8wNGs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOMXpnenB6VVpjMWltS3d5OGhIS2x0a25LYndtVzVHS2FzRmp6WG1mUkd4WVp5MFdVXzQ1MWpNUXBKcFNSZkQ2UTBDN1dGQUFQb1JudjcyOEtGMkNlaVJLVVd0eHNTRDdacHc1NUVHdlo0cHctejBYMXA5dm1YeHNHWTFXRjJKaFgtNnlJ?oc=5</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>1</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>46055.5093287037</v>
+        <v>46056.18244212963</v>
       </c>
     </row>
     <row r="34">
@@ -1526,24 +1526,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Panama Canal's new ports and pipeline tender processes begin - Seatrade Maritime News</t>
+          <t>Epstein helped Dubai businessman lobby Mandelson over £1.8bn British port deal - The Telegraph</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 12:18:55 GMT</t>
+          <t>Mon, 02 Feb 2026 18:07:00 GMT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOTC1BSEZJYVZRVk1qSTNOS3VGbDlnTmpRWnFCVkUxQ2FYYklBajIwVGhfaDZ0dHRaTXMxWEZtR0lGSG9qMXRYU0JjanF1dlZPQ1FHQ29hNkJHYU5fTFhqNE5iS1JFNGVKUTZCd1VURUk2NDRTZEluS045ZVlPdkhoX0w0RmJBZEpXTUFndHdwWW9HdHlTbEozVjJJM0pOV1ZFeVhIc005TGNWS1c0Nkdz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNT3RtdThCZHJ6TV9ydks0ZnFVRWE2elh1V0w5WU1zTm9oSWFZQU92bnJGQ1FZZTV4Ql9UMFVzbXZubnlGMVFIZHRmNk5LOVZYSUdmcGFKaFFDS25FZGtYOG1fLVVoeXdIb3kwMTdfV2RTNTVvY3lDcklqN2J3ODUwV0dCMmpCUHRrbWlxVWUxTm5XcDdJR0xNVVhtSGZZUQ?oc=5</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>1</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>46055.51313657407</v>
+        <v>46055.75486111111</v>
       </c>
     </row>
     <row r="35">
@@ -1559,24 +1559,24 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norwegian court rules sanctions against Russian fishing firm Norebo are valid - SeafoodSource</t>
+          <t>Martin Sherif is a Valiant! - Port Vale Football Club</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 10:51:44 GMT</t>
+          <t>Mon, 02 Feb 2026 16:09:02 GMT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQY3FfUTVqdHJrN0VGdXMtWjFmUE9UYWtLTzhabFlfLUw3OHRYMzlrZ1JOaWh6NC11LWxGSXk3QlZvb3lzVnBzNmlQVmdBNjZCeEsyeVV5VWNoUWR3dG5qNmNiNUFHeThrOEZkOUNtVGNEZjItTG1QT2xUN2VOYzJ0Vk1kQ2VpMGFqUF9DZTh6bUZhU1NzSVhTdkR4a3NNNFhEYkNEUnNPbW5nc3pvQ3FoRXRpd1lqQ3M1QXdIRUZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE9ydllkZXd6Tld2X0VoYlhjZEJtQUliTEhYQncyTVpBZXpsaU9FTEVyU3F2RllYSUxONFZyd0lzZFMtWHFHeHQ0c0NFTDItclJOYW5lT1VvYnJHMnlWeUNHRzZTdFU?oc=5</t>
         </is>
       </c>
       <c r="F35" t="n">
         <v>1</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>46055.45259259259</v>
+        <v>46055.67293981482</v>
       </c>
     </row>
     <row r="36">
@@ -1592,24 +1592,24 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>APMT open to temporary operation of Panama ports - porttechnology.org</t>
+          <t>Vale confirm first-ever Hall of Fame inductees - Port Vale Football Club</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 09:55:34 GMT</t>
+          <t>Mon, 02 Feb 2026 15:09:03 GMT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxPYWNPVU9TXzUtb21BS2tJdEZPUkhfNFR5T29XRXBaX3llTkhwYVpQNFZPY0w3YUQ5NDktdVdPajNyc1F1Q1c2QTFOc1lqSlZpZWs2c1N2YmpDU1lTT3ZUeENDWnVrcmxnaDI4SzM4NGNEMGdVQ2paV21jLXg2NHIyMzlEZkdSVzZLTUdLZmFR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQX2ZjaVBpdkF0aHlpTlhRcXQ1QWJLLWxiN0YzZEFmMmlEdHpuS181YzMyMk1KRjZpdXA1QzctclF0V2pMN2xvdTJTNElXcFJzQjNqeGFhb0lMdUdpRTBPSlpxOEdfU19xWWdkQUxzUFo5SDRvaGNyMzNRQUkzcm51OUZB?oc=5</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>1</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>46055.41358796296</v>
+        <v>46055.63128472222</v>
       </c>
     </row>
     <row r="37">
@@ -1625,90 +1625,90 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Transport NorthLink warns of seven days of disruption as freight sailings cancelled - Shetland News</t>
+          <t>Tanker stocks off to blazing start to 2026 as sanctions trade continues - Tradewinds News</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 09:31:32 GMT</t>
+          <t>Mon, 02 Feb 2026 19:16:41 GMT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxNTUJsLUljdDNSNEx4SEFZWTc4TEFkaFFMZzg1ZUlJVEkyMGt0bXNIamlZcXlzSXk3YWVBMkZSZW1Na3hHaWxkVnRCNHVvVmlfV3RndkdxSGswaVcxVV9waWxCVlBTZmFQMlRrZ3R6UkphZHpycUdMQWpQYUpFaVZUU1pR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPb2lRMExjOXNsWFVhQU4ybGNoTXpOMS13WUE2MGxLVzd5Q0JqRGxLczBmbFpiOUJGSGxVZ2l3dGxzZXpHYlZjdVBRSE9Yak5tenh6ZE1MaDNFV1JLTlJMMHNNR0NCWUk1TUFGT0NkbjQxSlZqWlJBalJSS0JaUG4zaWFTYkQ3R3lPdWJKTWZGdE1INGxCc2VuSjhXZDhaclROTi1ubTRkSERHVWNXTGpkVVBnclpjZ0UxLTc0cDdFdw?oc=5</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>1</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>46055.39689814814</v>
+        <v>46055.80325231481</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Crystal International unveils advanced logistics hub in China - Just Style</t>
+          <t>Russia resumes strikes on freezing Ukrainian capital - The Times of Israel</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 10:57:30 GMT</t>
+          <t>Tue, 03 Feb 2026 05:08:37 GMT</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFBTLVJYX3pEcmhvNzAwR2tNVUZjQmJGbk54SVpwLVhxOGVrQ1A3NmtfY2NlTFY1Z0Jwdzd6QzhQN19QTnI5Y1h6N3RHUWZNczFDNlVCZXdaQVlSRXhsaTN5N0VSMjY3QUxtWWh3cDA1djRROVd2ME5nQWZjb2dUUVU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNem9RZ0trLWpVZTdfQjVUS0s2eWRBOTg4djdzaHZWbGxSLUR2NGFmVm1EM0lkWWpXUl9GRkRobnVwSDVvTGIxa01PVEVrLWo1RVBsdUFFYnB1TDhwa1BvVDlPbXRUdnMwUXZrc01lQy1iMDBONWFvYWswT0FRZTd5ZHpsQ2pTczJ4cVl5UXBWSlpIVDZtMU1qX04yT3UyU1E?oc=5</t>
         </is>
       </c>
       <c r="F38" t="n">
         <v>1</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>46055.45659722222</v>
+        <v>46056.21431712963</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Freightliner acquisition by CMA CGM completed - porttechnology.org</t>
+          <t>Iranian police detain four unspecified foreigners over unrest - Yahoo News UK</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 10:45:34 GMT</t>
+          <t>Mon, 02 Feb 2026 11:28:46 GMT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxONmpqaUtvSnJHMGhhWUlBQ1hXdjJ4V25yTUZGMElZQ0NmNGdUODBFYmE0NThjUnl3UG1lbEZ2RVcxRDVlV0hvcmxPS3F1dDlFZExSY25lUkIyejBJTlRvSjFVZmU4R21zTHRaamRIY0c2ZHdMdzJfM3pqQWpkYTNHdEdUdmtBOXJ2ZXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPekRjSmNra0R3WlRGV2hzZDRMWjNkWEJiNE9Jb1RfOWx2WG45cE15cGwxMXMzMm1FclVYeTlBeE1WQ2cyQkVVQ0kzSDkzUUR2TVhzM0psZEtyOUxVWUxhakllLXhEWXY2U2dJaDNmeF9pTWE0Z3pKMFJtaEhqOVJya0JIY0FBZw?oc=5</t>
         </is>
       </c>
       <c r="F39" t="n">
         <v>1</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>46055.44831018519</v>
+        <v>46055.47831018519</v>
       </c>
     </row>
     <row r="40">
@@ -1724,24 +1724,24 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Update after police called to convenience store - Cambs Times</t>
+          <t>Police statement as flag-waving protesters march on Hanley - Stoke-on-Trent Live</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 11:04:00 GMT</t>
+          <t>Mon, 02 Feb 2026 17:30:00 GMT</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxORnRnWW9xTkxDMVVISlZvNjZVS0RfZGhhLUU4RFBNZVNsbmExOEJZZHVBZ1IzelZXVl9nOGZFZGQwcTFfaE1YZjlUODVJWExsXzNiVm5DMnpQNGM4RHplZXZRZG5HMHNjaE1VY0VjOGdpd194cU1rUmMzQ3NXV0QyWXBoQkYzMEVVM1A2eFU3VlpkYTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPT1otX0VCaWwyTFVjMkhPU0habVRyTlZTWl9mYzRJX1RvcUZoTTBFbmd2NENQNVJOcW5aajZkLVFRZlZpUVM2MERmUDFCOWp3bFdkX2lseWg3eHByak9HUmlnV29OSlViX1ByNnExQllBQXdXeHRzNU9hc3RlMEY0d3otTjhkTXc0czZ5QVpYckJhNHpCajV5NWJuNG15SEt5NkNuSGNwR23SAa4BQVVfeXFMT29GZ3RWV0xJczVuSG91dVpCS0dXREVJNG0wQUhkU21sYTY4MVItR2pocTdpMC1obWRKeENHNFdkazgyZnpVdzRvZFotcnRpb1lxWk4tbW1hdkxmZ2duTkUyTGcyN2pGWG5iRE9KclhHeVdUUzg0UVVyR1pha2lKdUlYMTViQmF4b1lfc0ZGMlVZNTdEU2NoQU5rb2N0M0p5dGZDVG1USzdCWXJhdmhn?oc=5</t>
         </is>
       </c>
       <c r="F40" t="n">
         <v>1</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>46055.46111111111</v>
+        <v>46055.72916666666</v>
       </c>
     </row>
     <row r="41">
@@ -1757,24 +1757,24 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Iranian police detain four unspecified foreigners over unrest - Reuters</t>
+          <t>Update after police called to convenience store - Cambs Times</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 11:29:03 GMT</t>
+          <t>Mon, 02 Feb 2026 11:04:00 GMT</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQbEFYWUliVTVUN0ZCdEdQYVNQQWl2VUJqakF3S19nbG1BMjE2M2xDa1NLRXI3U1pjVFRsWGZhRUFfMnQ5cjdPTmF3VFlpcENfenhkOTFWOXhMckdETkVINWNaY3RCMWxwTElDVzg0U2xLamVuSXlVQXJ0RmpNb25taUp1aEFJc19IRXdhZk9DZHE5OVQzSnR5LVM5QmdhZFNHT2dPY2ZvNDVPSlhTdVRLdjJZMldiZkZaTzFsSA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxORnRnWW9xTkxDMVVISlZvNjZVS0RfZGhhLUU4RFBNZVNsbmExOEJZZHVBZ1IzelZXVl9nOGZFZGQwcTFfaE1YZjlUODVJWExsXzNiVm5DMnpQNGM4RHplZXZRZG5HMHNjaE1VY0VjOGdpd194cU1rUmMzQ3NXV0QyWXBoQkYzMEVVM1A2eFU3VlpkYTA?oc=5</t>
         </is>
       </c>
       <c r="F41" t="n">
         <v>1</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>46055.47850694445</v>
+        <v>46055.46111111111</v>
       </c>
     </row>
     <row r="42">
@@ -1790,24 +1790,24 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Another e-scooter taken into police possession - Fenland Citizen</t>
+          <t>Ukraine's capital of Kyiv, other cities under Russian attack, officials say - Reuters</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 11:33:00 GMT</t>
+          <t>Mon, 02 Feb 2026 23:23:20 GMT</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQY0xxNnhKTTZwdUtJdVZNZXBSQ0lwUlpxMDhCUWxhUFBFLXpUaDJMNmF2OW1YY2hWSTJ5Zm1Vbk9mcDl5UjZpWm1Jd1FPYW1mVk5sZV9xc3dlYktqRWlOQTFaUDBBU0JGMVhQZnRkSkMwYV9QWnpsY0RQU1VtRlhWWnJDb0o5WkIyWlZNcTVoTHZvM25keS1BRg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNVlBuNklvRHU5MVg4THZMa2VRMmlRZVpEb2FmX0pNNlJCNXNHbS1CWW5NaG5pbUNLZG05ZDlhcHgwQUV4Tm1mbXVuV2cyaXp5ZGZyNnJkeEJPdC0xR0NYYU8tOWVTX3NXSmNPUHhWSEg2dWlDZEFEYWhCOGdPdWFsMlM1SXYxU1Q1NlhTcFRfLVB0SDM4OGRYVDQxNVNpd0g3?oc=5</t>
         </is>
       </c>
       <c r="F42" t="n">
         <v>1</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>46055.48125</v>
+        <v>46055.97453703704</v>
       </c>
     </row>
     <row r="43">
@@ -1823,24 +1823,24 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Police probe launched after jewellery thieves strike at vulnerable Smethwick woman's home - Express &amp; Star</t>
+          <t>Police Urge NLC To Shelve Tuesday’s FCT Protest Over Security Concerns, Rights Group Pushes Back - Arise News</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 08:11:04 GMT</t>
+          <t>Tue, 03 Feb 2026 06:13:14 GMT</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxNSGdYOGR4YWRSQ0pFc0VxSUdoc3RNUkZ3bXRvdDBuVDBBWWhYLS0td1lPVmtDUWYwZGpqbVZ5RkxrMWQ4SkRqWHhBSkFjWll4QU11cnZKMEtRWTRmNi1xOWRsWTlnSmtkSXN6MVZRT2hCZHBnR2dlbmV1NzZBcWJ5SnJZcDJWNWtENVFkdVNKa2wyRTFkLVJRWDJTSHg2MlZUUDNWY0xOcFBuTkpWUUdRZG0xZzkyeGstTkdVMHF0UGo0UVlzYmNfdGQzMFVKNUtvMHF3UlpRSmJhR211YWFJQTdZVFFXSDJRU1lWNXQwQmxFQjNFMHk0VnFB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPdkNxV2FzejFFR0dsLTNlU0JSMDRocE4wZ2hyNzU5dGVuSnd6M3JOQ0lLSkZWYloxXzFub2VGcjFJcjFscWZxSHlRRXJTdkF6RmJjell2T1ItQk1CQTlFRzZiMGFhYTRYV3dIUWFKV3FpcFNJNXEzT0lWUjVrc0hwZHhLeVVYTHRVZmdXZWdGOWc5YmgyemdRNGRoZWhlbDZuS19rZlZNY1oxcmxYQXJQX2VYdVFGazA?oc=5</t>
         </is>
       </c>
       <c r="F43" t="n">
         <v>1</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>46055.34101851852</v>
+        <v>46056.25918981482</v>
       </c>
     </row>
     <row r="44">
@@ -1856,24 +1856,24 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Police and crime commissioner storms out of hearing after being censured for joining anti-migrant protests in Crowborough - GB News</t>
+          <t>Spokane police chief apologizes for officers wearing masks at protest - The Spokesman-Review</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Sun, 01 Feb 2026 15:14:07 GMT</t>
+          <t>Tue, 03 Feb 2026 05:50:11 GMT</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxPNzRfSWt4cFdoY3NpZmJoN3JicjVvcThEaHRCWTdtZW9CUWxNOEVNMURnV05DQ2hGUmJlbUwzbTg1OVZBTkJJaHBZc3dRMUNqTm5rQXBQeDQyMWFIQnh5bHJNWURBeTBJd1Q3OWJzMmNNeVZtbFg4NnZlX0QzQVRNZTdxUThmcjZONG4yaUU0SQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOZHRHU2VfME5sVTVoQkpLMmpoVUhPN1lnZzdCSm44cVRfZ3k2NFNIVVdMSTh3cXIwU0RFUFNfZ1NMdXhrR0FXVEx0NXNadWsxWEp5WVU4cHBoNkgzV09GcEVtSEpwcG1jdkZWR2h4bjd6QWhfQTRtazA4ck14VXFvaVBDcmlKdDJSVHk0TkZacW5XTTFjQ1dMYmI1Y3VoQQ?oc=5</t>
         </is>
       </c>
       <c r="F44" t="n">
         <v>1</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>46054.63480324074</v>
+        <v>46056.24318287037</v>
       </c>
     </row>
     <row r="45">
@@ -1889,24 +1889,24 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Eight Arrests made at Demonstration, including Three for Assaulting Police, Queen Street West and Bay Street area (Mahnoor Mohyuddin, Jennifer Vong, Kyle Stephens, Woodrow Fraser-Boychuk, Abe Berglas, Darcy Belanger, Bryn Williams &amp; Charles Kaake - Reddit</t>
+          <t>Another e-scooter taken into police possession - Fenland Citizen</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 12:33:10 GMT</t>
+          <t>Mon, 02 Feb 2026 11:33:00 GMT</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPYlA1UmFxRnlZNXpJODk5X0hOWldUOElDdG1mVXhndl93LUhackpTa1FYZDBjRWR1dmFhc2xrYXMzMFo4WV94OEtZb0ZpYTljNlJYb0RVd1llS0RuWmRHRlA4QUFJaG5QTzBzaDRKUFBBUWNDR1pDdklZUXBvdnVqMmJiMVZydUp1Q0hVV2IydDZQY0F6eGtYdXB1M0w5QU8weWVEag?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQY0xxNnhKTTZwdUtJdVZNZXBSQ0lwUlpxMDhCUWxhUFBFLXpUaDJMNmF2OW1YY2hWSTJ5Zm1Vbk9mcDl5UjZpWm1Jd1FPYW1mVk5sZV9xc3dlYktqRWlOQTFaUDBBU0JGMVhQZnRkSkMwYV9QWnpsY0RQU1VtRlhWWnJDb0o5WkIyWlZNcTVoTHZvM25keS1BRg?oc=5</t>
         </is>
       </c>
       <c r="F45" t="n">
         <v>1</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>46055.52303240741</v>
+        <v>46055.48125</v>
       </c>
     </row>
     <row r="46">
@@ -1922,24 +1922,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Clime Capital Announces March Quarter Dividend Guidance Of 1.35 AU Cents Per Share - TradingView</t>
+          <t>Hungary Raises Alarm after Slovak Police Arrest Politician over Beneš Decrees - Hungarian Conservative</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 01:59:00 GMT</t>
+          <t>Mon, 02 Feb 2026 14:09:31 GMT</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxPaERFNTN6UzRGZkxwdHJpTzVWdm0yOEgzM083aFUwVnZXbEpYbFg2cTFndjF5a2xSX1lFdzBkb3h1TGhIODRfcWh6dUIxdnJJbTFURTQ5dnJxVjFOVHhoZk41dHlrd1VDMi00VWpuSURqaWVQYVBZTHhrV1BFMVBnMkM4NEJVNExLenEycGUwYVBMU0ZldGE3Z2x3SGd2UUtOLXJDX01VYmpJYmNDMTJBcmNuWk9GUnphbHRranNOWWVfbGd1VlZBb1U4cWFmRXJVQWpWdDBEQXd2RVFrN2pTbTNhU2NXXzA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOSGNwRENjNUNNeDMxSWhEWndpNk9OQnpBV0EzazV3b1FSbzlic1lTUTFxTDQyY19UckVZYzB2cy0yZUhYNFF0dHJ1WEtXRDNSQ2VjY1B5WXZiNVA0UEJNLUo1SmxScmhEYS1NQUtoX1pFWjU5dUdqeXg1d3EycFZTZFFkSDlsRFptSHQ4X2lBenowTnZMNmtwRHh3bGQ4ODdzTlVRRzZEeE91ZUl6M2lFSDZoZ2Y?oc=5</t>
         </is>
       </c>
       <c r="F46" t="n">
         <v>1</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>46055.08263888889</v>
+        <v>46055.58994212963</v>
       </c>
     </row>
     <row r="47">
@@ -1955,24 +1955,24 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Police Urges NLC To Cancel Tuesday’s Planned Solidarity Protest - TVC News</t>
+          <t>NSW protest restrictions extended ahead of Israel president's visit - Australian Broadcasting Corporation</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 12:51:00 GMT</t>
+          <t>Tue, 03 Feb 2026 03:21:47 GMT</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQUzc5Q3FUNzJteVlSUEJQekViSS1GRnJ6NFlmd3NVTXRmRzhCVWJfVXNsMk5ENjQ4MDJoOHR0MXZYSzZHbGdQTXlQVGR1dkU1eklxS2wwZFBXbkVybEV2cTl4LVRPNkFXdjE2Z1lySDJEdWdIX0lybnp3R2s5VjlzQkJQVmhubjQxMDBnMmhaUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOR25CYWQ2V3BfQnRxMmVBSEFDY1RzSzdhaThTcVU0RWdLX0Zyc3IyS19yck1YZHhiQ3R1OVdkc195bzYtR0V5UXlLb2Fta1JkaldFOU9QYjJpajFrczNQWHBTeGZQRi1jMXIxcXA2Ql9BQm5jOUVyZ2ZxcktENTBoY010OXcwZ3VjRXZ2TXIybVJ1dHZBT21NdlVSMW9Ea3RjQ3UzcUpMWTNxQUZEQXc?oc=5</t>
         </is>
       </c>
       <c r="F47" t="n">
         <v>1</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>46055.53541666667</v>
+        <v>46056.14012731481</v>
       </c>
     </row>
     <row r="48">
@@ -1988,288 +1988,288 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Clashes in Turin Injure Over 100 Police During Social Center Eviction Protest - mezha.net</t>
+          <t>Reno police confirm battery report, citations after anti-ICE protests - Reno Gazette Journal</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 01:44:25 GMT</t>
+          <t>Tue, 03 Feb 2026 00:14:00 GMT</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOSVlDdkdjV3ItWWNVWENjVFlDcjFZb19jREVfb1FHVUtvTGZyeHdMY3l5WkMtVFI1MjlCNS13VnNidksxdU0xSk9sRUFwU0IzeTJVRTRmLVBFeXgzZGNsMEhnNTgtb00zUnp3eDVkRWN5aTFMVU4xMTZlUDNMd0d3OU5sNUpXMFRpamhhY2NVOGpmT1M1NEtMcDdlNWwwdHNYNGs2MWJsRFlSd9IBrwFBVV95cUxPa2NMbGltVmNON1BvS1lQMnZ3cFFzWFVtT240Vnl4QkhiN2UwUFhkTGp1Z1ZpRHRkTlhOZjdaVTg5MElzbjV1d1FlYnV6Ym92RG5YMHFja2p6WjFXVzNzb2EtanVmcS1rTUlWcS1peWRfS3dMWjN0ZTdrMWxBX0FDU2tfWWc4bzFjWVFFZXl2cUlOdUV6ZjNfNkZoOEswc1h2UzR6S1RDVUU1WDdjWEtB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOYVFWYkdQSUEwVkstQUVseXZ5TV9uTGtqbFFadjRwcXozcWJfaF9GQ2xsUXZHdXFyaVVFMXNmYnhUR05PbFJLa3UzN0lVUEIyX0J5RWM5VlRLR2VpRE5raGdMSE5DaFlaZW92blRuZEl5WUlEQW1aZW4zUE1CY0t5ekY4NlFuazU0cHFTSjN0bTlwT3p1Z29vbTJfcTB3R0p0THliSzNPN0NQODdoZGgtMHY4d25vUUNST1pSM0tPTQ?oc=5</t>
         </is>
       </c>
       <c r="F48" t="n">
         <v>1</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>46055.07251157407</v>
+        <v>46056.00972222222</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dow to replace 4,500 jobs with automation and AI as shares decline - Packaging Europe</t>
+          <t>“Everyone Stick Together": Eugene Mayor Kaarin Knudson on Protest and Community - NPR for Oregonians</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 11:08:32 GMT</t>
+          <t>Mon, 02 Feb 2026 22:40:00 GMT</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPUG85LWpVTTB1ajhzU3dMMEtCa3NkMDRxbmpjZTV4RmlvZ1dpSlh2VmZZSW40VEV2QzcwTDVaQVltdnpKT0gya19GT3I1VnJFUGNjRkNGNUtobGFCS0RjV2x1NmV5YTQ3bzlYUWxHRl81dnpLVk1vVHlEemtUU0JDeDk0SVhDYXBsSG9pMXBJdnJfOWpPQ3U4NjNVWm1IeEhCT1l6aWUxQ09EaGg0czl5MXh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxPaDRwdTVIc2RfTE1LVXJLanlzbjFxTFlHVzBlY3BFaXZRRF8xQWJySFQ2eG9TV0s4b19MOFNZNlhvTTZTMDBMSlF6SmdvOENVTDN0NDRIbFk5R0s4ZGlQSEhvNHlObFN3Sm1MY0t5UHFudzNpSEV4TFpWblNZWEhmU2xwRG8xWHVRU0xDZTRFbFB4V1hfdncxVmlNM1VxcW5QOTI0Q0hPeGpOYXlwUUZtYlFpOGdLcFVWOUk1ODI2a1FRX2w3OTFKTzR2OUEyX0lsQlpN?oc=5</t>
         </is>
       </c>
       <c r="F49" t="n">
         <v>1</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46055.46425925926</v>
+        <v>46055.94444444445</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Technology and human rights - Amnesty International UK</t>
+          <t>Ferndale Police answer questions regarding Friday student protest march - Whatcom News</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 10:19:47 GMT</t>
+          <t>Tue, 03 Feb 2026 00:17:16 GMT</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPNHlIOVVoNVd4VmE2V3B1b0JLemxfMTcyYXQxakg2Q0dLekxWLW1nS3Myb3BnNk1TUm9Va1BzR3dSdE93SlRmV2gxN1ZoNmFKSm1YSGF3NUVQOG5qMi1mdnp4WHVBeXJ1MTlrWE42ZkhCaHp1cmhXQlMwMkd4czhaczJXWmxMT0Raa1JKbjhSZy1uUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPbzk1cHEtbWI4VjhaVXBCSXA2Y3MtaEhZWXAxYk0zMkl5SUVvcmh3d2JycHRiMTh1dEZrdGRqVDhwR0Z3UjJoX0JhSE1kUk9MVkVEbzZqUl9OcWY0N0ZRZFdJQ2FUQUFrWFhxUVk4clNFV2o4R0dMa1JBaVpFVjdyVDFraVBEbkR5TFc3VmZUQmNxazNhNlZiSGI5RTZnWnN2TVVGWk9zQQ?oc=5</t>
         </is>
       </c>
       <c r="F50" t="n">
         <v>1</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46055.43040509259</v>
+        <v>46056.01199074074</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>The Telecoms.com Podcast: Ericsson, AI and Nokia - Telecoms</t>
+          <t>Police probe launched after jewellery thieves strike at vulnerable Smethwick woman's home - Express &amp; Star</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 12:28:13 GMT</t>
+          <t>Mon, 02 Feb 2026 08:11:04 GMT</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPTHhsYVpnTHdHNkNEQXR5YTVXeEdDSFh2dE9YLTJsdVdFbDV6MkxuQzJ5Q0xTdEZFb2VaMjlESi1JZDU1QWJpekR4ZExxY196ekhkZ2lJUDZzMnp5MjFrS250eDh5OGRSckRLczFKdjJKYVcyQlhmdEtSWTA2R0VLTTZUa1dhV2dlYXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxNSGdYOGR4YWRSQ0pFc0VxSUdoc3RNUkZ3bXRvdDBuVDBBWWhYLS0td1lPVmtDUWYwZGpqbVZ5RkxrMWQ4SkRqWHhBSkFjWll4QU11cnZKMEtRWTRmNi1xOWRsWTlnSmtkSXN6MVZRT2hCZHBnR2dlbmV1NzZBcWJ5SnJZcDJWNWtENVFkdVNKa2wyRTFkLVJRWDJTSHg2MlZUUDNWY0xOcFBuTkpWUUdRZG0xZzkyeGstTkdVMHF0UGo0UVlzYmNfdGQzMFVKNUtvMHF3UlpRSmJhR211YWFJQTdZVFFXSDJRU1lWNXQwQmxFQjNFMHk0VnFB?oc=5</t>
         </is>
       </c>
       <c r="F51" t="n">
         <v>1</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46055.5195949074</v>
+        <v>46055.34101851852</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NHS trials AI and robotics to speed up lung cancer diagnosis - UKAuthority</t>
+          <t>Alderpeople Say COPA Should Investigate Chicago Police Conduct During Immigration Raids, Protests - WTTW</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 08:01:03 GMT</t>
+          <t>Tue, 03 Feb 2026 01:02:00 GMT</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNVW9sb25UeG1CVzdNOGVXWFRsT1ZBYWhwYkVTYkRZT0E3SURaNHdxeko1ejh5S2xnQThQaWp3TjRrOHM1TE1GcmxXcWFvMWZleFpRZVRNeWpQZW9fZXdBOVZjZTVJTjlUb01YTkRsZWZEQmdheTJ5d2ItdUt4b0JPX3RvZGZWc2JWZU5NRjVSbzNzQlF1Q0JabXRtemtYQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPN2xkVWx4dWpnd25XYVhTLXF3cXRJOGRSUDZIMFJaTGRpa3dEeVEzOUdKSzA4ajZWVk95XzF1aS1WdFlBT3ZVR3lBaTZMZDE2U0pvZWlON2xNZ0taeWxnTlJNU0NDdkdabUxyVGZnS0JZTk1KcG0xMkhVWU5QWWZqMXpWRkJGT1R1WENRZWpvMkNJV09RUlM1NjdhQmV3VnhOUkNrTE55Y2U4NS10ZGNSel9MbFlwUHYxd0lkMw?oc=5</t>
         </is>
       </c>
       <c r="F52" t="n">
         <v>1</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46055.3340625</v>
+        <v>46056.04305555556</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Why banks shouldn’t wait for AI to fix the Gen problem - Retail Banker International</t>
+          <t>‘Significant animosity’ to Israeli president prompts further protest ban - AFR</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 09:28:04 GMT</t>
+          <t>Tue, 03 Feb 2026 04:31:00 GMT</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPNkJaSEM4djg2STlSalNWM0c3MmhmS1ZNS1c5MG14VUREZzNha25fVXp3VXF0YUczMkRlMEwtVldORHU4TFA1dEtLY3dfeXpmcW5UbHJLR09mX3FYZlFwbmtCbU1GZ3lsMFBUZmhpU2ZHMzlVZUxkSG0wNkRCeFcwQkk1OW5ZUlVaNXFPVktQb1g0djI5ZkQzU0ZKTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOM3VBTUx1czNTbG5CVmlqcnF4bk13aWpUbnIySGRLbmZiSEtWUnE3RU1LVG5HcTJuSE1fVEJsSTVkNm5XemVYQjVwbk1TZWFKcGtYTVJRVUg4WkhhSzlqX2dqMFhjZXJ4N3hQQnAtdEVXQUlzTlNfdnVQZEVOeTRlUkJmMWFtVGxxajU2WGtEdTFFTmFuWWJwb1NxaDhWZElhYXVQZVdJSEhRbHJGeTdGNm1nb0FGZw?oc=5</t>
         </is>
       </c>
       <c r="F53" t="n">
         <v>1</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46055.39449074074</v>
+        <v>46056.18819444445</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AI and tech adoption in treasury - Private Funds CFO</t>
+          <t>Police extend Sydney protest ban again in city’s east - dailytelegraph.com.au</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 02:00:49 GMT</t>
+          <t>Tue, 03 Feb 2026 03:01:48 GMT</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE9HX2wxTWg4OXVDNHpST0Z0MGZsRVJZVkVRSHJyWVJKMmk2QVN1Rk9LQmdfSjF1a0h1Vy1tSEpyREJpajlEcWRjZFdYRlZiT1ltYk0wb3hHUm1GejByQ183dTJWMlFXQmVOdDdyVGpjU2lVOFU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxNUkkyMUZaR29JbkkxOGZHSFF1YmRFYUxNYU5RVENDbHhmU2h2anF3bzAxVFhDc1AwRGFTVDluWVJvNEI1QnViR05GTU1YOS1JbzhQS3ZOUGJicFpmR3J5WlBwM0VDbVZlUGwxc0NqNkx3YnNVaGFvaWlpcFBXN2dibi1YMGJJQkpHbmNMWl9tWmNSMzFPdkVZY0pwOFdlcFFDZG1aMDB0ejNiN0dNenVUM2FKZ2F5a2E2UU5CNl9tdEtiWmt2cnU5N3RBbktEelRoaHBhUnNrdUtUYWdMcEw1NUZsYWgwRXM0WnUycksyYnhSbjDSAfgBQVVfeXFMTkNJUVUxVkp6UXFlZzcwVTVmYUl2RVUwZVc1NTM1ZU9XeHVBXzRFNG4zTFZTZHZnWThnQWViWkd0WlgzZXVkMlhGZ21NVHZWb0JyWnU2TUpDZHNLeDIyX0kxa2VIMmJIQlI3ZGNVQjE0c3pLYWJobTV4Q1lCS3hxaVRUR2FsanZ2M2V6azNydDV3Ym5KdXQyZFNuY3NDRjhkQXV0VUk3djBkbmx6YWg4eEhQb3lzTHZYVDVtM2JiRDVfR0RaMlRPVEJsZnVTRjVmNlo0U3NOSU5VaEtOZ2RXUnFaSjlKLWpabXpmSDl0SHlUcDlvVEdCNW8?oc=5</t>
         </is>
       </c>
       <c r="F54" t="n">
         <v>1</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46055.08390046296</v>
+        <v>46056.12625</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>IFR position paper on AI in robotics released - International Federation of Robotics</t>
+          <t>Eight Arrests made at Demonstration, including Three for Assaulting Police, Queen Street West and Bay Street area (Mahnoor Mohyuddin, Jennifer Vong, Kyle Stephens, Woodrow Fraser-Boychuk, Abe Berglas, Darcy Belanger, Bryn Williams &amp; Charles Kaake - Reddit</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 09:50:47 GMT</t>
+          <t>Mon, 02 Feb 2026 12:33:10 GMT</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE1uM2Vnek8zdm5IV1hWem9CYWl1S0czMEJLd3lhNHNlLURxajlQZy1ISzdSd28yblRfeUpKV3ZsYWlPYlJsNGdDalFWMUQyOTVqSmQxMzNqV1Y2SE9UbzRxcjc3RzVRcTc0NG9tYV9JbU5fWVAzemRVMTVhV1o?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPYlA1UmFxRnlZNXpJODk5X0hOWldUOElDdG1mVXhndl93LUhackpTa1FYZDBjRWR1dmFhc2xrYXMzMFo4WV94OEtZb0ZpYTljNlJYb0RVd1llS0RuWmRHRlA4QUFJaG5QTzBzaDRKUFBBUWNDR1pDdklZUXBvdnVqMmJiMVZydUp1Q0hVV2IydDZQY0F6eGtYdXB1M0w5QU8weWVEag?oc=5</t>
         </is>
       </c>
       <c r="F55" t="n">
         <v>1</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46055.4102662037</v>
+        <v>46055.52303240741</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>How sustainable funds are navigating AI, defence and financials - Trustnet</t>
+          <t>ATN International Board Calls March EGM to Consider Capital Reduction - TipRanks</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 11:01:33 GMT</t>
+          <t>Mon, 02 Feb 2026 18:07:35 GMT</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPRktGQTJJdXpHeldsX3E3NEl3ckx2QjkxU2tIb3lPUF84dEI0a2ZfQjVjbTNMeHpZUFZjdkR2bldWTnpMRmNjMnBkNFZ5Rk05dW5xeEpsTWo1YkRXUjhpYkdEYS1od0dPSmhScjZPRjZsYVBxTzlUbXh1QlVrbVhwaFRyNTB4aEk4V2I3b1dhV1J4VC1vRUdsMmdTUEFFeElqbE1J?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNSEh4dktnUVA3TF9rTkJIUXZ2cFFkN3puZWpIN2dYTU9kRmtiRmtGUGFNWS1ieS1XQVc1QlJCcTdWZmx6U0RLRVhJU1hybXlDSTN5dkU5VmUtMVJKcFVYanF5WEdtUlN5Yk1USUhpYVp5eVA2M3MydWtKdHhwcV9FY2lSQUVueGRkaWRTNFYxemIxZkY3bnRBVlpzZTVoTUJPcUN6R1hoc1d5dkxzNE5NbzJaWjF6Qm5hTlEzQ2xn?oc=5</t>
         </is>
       </c>
       <c r="F56" t="n">
         <v>1</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46055.45940972222</v>
+        <v>46055.75526620371</v>
       </c>
     </row>
     <row r="57">
@@ -2285,24 +2285,24 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Vera van der Burg puts AI and ceramics into "reflective" feedback loop - Dezeen</t>
+          <t>Technology and AI - Freeths</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 09:00:00 GMT</t>
+          <t>Tue, 03 Feb 2026 07:37:01 GMT</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiSEFVX3lxTE5RNF82VUc5cDNNTzhsdHpwbXB6TDBhNW80M2k2Y0NRbFlRYzdoV21GTDNEcko5UDdjbmxIVkgyeHhNWkRCLVJ0SQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTFBWa1dVRGdpcEZHemc2aURfM0tWNDlnRXJBRTRNa0F3Z25xMENnNHFmWC1henR2SkNXdnVYZ2VHa0lIcGo3UDFJb1hUWnI2R1c4ZDlpWkFIQlNPaGJBZTNGZUF4S2xnRl9qdG9wNGpGMV90aVpXdGc?oc=5</t>
         </is>
       </c>
       <c r="F57" t="n">
         <v>1</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46055.375</v>
+        <v>46056.31737268518</v>
       </c>
     </row>
     <row r="58">
@@ -2318,24 +2318,24 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AI 'slop' is transforming social media - and there's a backlash - BBC</t>
+          <t>CURE-ND brings together experts in AI and machine learning - UK DRI</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 06:54:06 GMT</t>
+          <t>Mon, 02 Feb 2026 13:45:51 GMT</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE9wNDA2bFFUbmx5aDlVcjdxaWE1c1JHZDZTcmxnampFRW5PN19EejRhQklPMkJmeDNYZnlMczE3MWl0M0h2UkhpZUN5b0hoX0RRZzExcTBZUmV3d9IBX0FVX3lxTE9LZjR2U0dKMjJ1WktUTy1JaWFWUkluMWYtSmJBQ0J4QmVuTVhhTUZTUGN5eUZ5UDdGMFZLeHN2TWNPaHZPSGk4LUtlYkpuYVA1Vk9Gd0p3RThuWTNrYXM4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQQUxpOEJSX3VYSW04MTVNYkd1TnJJMXJKUjc2eEpZQ1I3M0hsSTA0dEdaWEc4dUpGQUpvYjRqbFM3akdkZHdzZlhpdmhhcnQ2VnpWb2otYjZjeF9JZ0h3ZTY0SjhDOTBrMVhJVTVXNUQtREczX2xMejB1Q0JKRDNkamFfSGVZMGp2U2t3N3VEaEFZaU1XR2xhQzFYY3RlT3B0OVhZX3RESzI4ZTQyVDZ6T1FxMHZiUQ?oc=5</t>
         </is>
       </c>
       <c r="F58" t="n">
         <v>1</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46055.28756944444</v>
+        <v>46055.57350694444</v>
       </c>
     </row>
     <row r="59">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>“A cloud-enabled, digitally resilient Europe transforms the protection of its citizens, infrastructure and strategic interests” - Thales Group</t>
+          <t>Alphabet Q4 2025 earnings preview: cloud and AI to sustain valuation - ig.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 09:08:42 GMT</t>
+          <t>Tue, 03 Feb 2026 05:21:31 GMT</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQc3lvdXNHRWx4aTVFNFlPbGUyTjB5UlVaN3dhSUhvbXQ5dmF1Tk91REd1QTU4R2VPbGc0b0VEbTZrRlE0cHJWaXVFYmlXaDFDMDhqM3BUOWtNZzJLb0FBSEh3T2pwLWEyTE5ycEpEX19mSmJ4TG40UTIzRVdZTk1IdEpFaWpfVmtoZFRTaXRBREk1YzdNdk1NOVJFRHpzdTJPemlFYmZiWGtuWEJJWVgyaVlDSDBsRjFoaVVUU2tjLU9ZUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQcnY4a2J0bWRPZnJxSGRHeVYtc05FaUY1MXgzQ3NEVkNJYjVIM1BCT0lFblVJN0xkUi1jZ0ZMQTZnQS1IYVB5Tm95cXJfSDFJWnBFd2gwbnVVcXg0SUMzVnRhRXZld3lTdHhYbU9lS1lwOXB4SGFZa1JHc3diTzZjZF82OUlwYlFSVzE5YjdjWW1PeGsxLTFtLTBiMEFycVFxa1hsalpwWnlGYVlkN0ltbnFUcVlqM3U2ak91M3FKWC1NZw?oc=5</t>
         </is>
       </c>
       <c r="F59" t="n">
         <v>1</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46055.38104166667</v>
+        <v>46056.22327546297</v>
       </c>
     </row>
     <row r="60">
@@ -2384,24 +2384,24 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AI deepfakes are reshaping cyber risk – and insurance must keep pace - Insurance Business</t>
+          <t>How trade shapes the winners and losers of AI boom - Oxford Economics</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 11:25:07 GMT</t>
+          <t>Mon, 02 Feb 2026 23:33:39 GMT</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNd0JwN0R2S2lhZk02UGFIVWlwODVoZ0NQZTMxZzFURWZURExNbmpXRFlfemNZTWpwNXFidktkSDlSek1EYzlmZzlRSGxoN1dxeG9vcmZYbS1PNU5qTld2RVNQZUNwMXlKcnROQUFXYmtmQUdoVUxxNmV2VlVDRnBSMEZtam1MUzFnd09sRG5IWkVlcW9JNXBzb25qUVo2WjVvRXdxdUt3VnZjbk5vN1hsNVpMTUNQMkUtOVR4QUc3M05NVUZKU2xzNmVn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxORDcwTnZjQkprcmdaR1dMYWE0TTlSZUJ5ZEVqOHJCZDhYT21QdG5veEJpa3lOWUE1QzRpaVN2TGQtcHR1dGtlV2xkc1lQSkFabUIweFhqVWIxWXNORVh2T1ZTVlJFbFlBbGNVRWdwZFQtMDh5MmIwUmdCUWU3cjFPZmRhTVhfZzBOZWlqcURqSTFQRm1XRHZV?oc=5</t>
         </is>
       </c>
       <c r="F60" t="n">
         <v>1</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46055.47577546296</v>
+        <v>46055.98170138889</v>
       </c>
     </row>
     <row r="61">
@@ -2417,24 +2417,24 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>One Identity names Gihan Munasinghe chief technology officer - IT Brief UK</t>
+          <t>Publicis deepens AI push, saying rivals have yet to make it pay - Financial Times</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 12:00:00 GMT</t>
+          <t>Tue, 03 Feb 2026 06:30:20 GMT</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOcnhlcVU0RWd5WDI4R0s5d0lvQmdaVHZQeW9QblFnTV8tYmJ2UjlWY1NCckNEWmZiR1lGc19GV3k3ZmMzaF9XV0IwQXBNSEp1N0hTQkhmcW1Wa2ozVmZGUDYzSHh4bFo4UzMwc2FzMmNLTXMzRWw2Y3ZkVHRxYWo4N214NThWRUhHRzN4eHRZbTB1UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE05aFZudWF4Qno5cmZiX19mOXg2YWZvdlFIUVNjNHhsZGFfNWVxeEYzQmlxT0xud0hkYzdxSU1PRElxZHpOQ3o3Yng0aWYtS3FLdHhFcTJobU5oYTllaXI4eHNQS2ZncTNJeEJmd1loZ2Q?oc=5</t>
         </is>
       </c>
       <c r="F61" t="n">
         <v>1</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46055.5</v>
+        <v>46056.27106481481</v>
       </c>
     </row>
     <row r="62">
@@ -2450,24 +2450,24 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Breakthrough Power Module Aims to Ease Energy Strain from AI and Data Centers - Telecom Review Africa</t>
+          <t>Europe Today: European leaders in Dubai to discuss global trade and AI - Euronews.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 05:11:38 GMT</t>
+          <t>Tue, 03 Feb 2026 06:49:08 GMT</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxOQ293QzEtcl9tQWc2dlJOUG1MSWJwZm1pQXdxVnhiWHo4NEo3TU5YR1hzVXBGRXlQcFY4cDdfTjZPdXZBR3d1UDhXTkVtR1UybFotXzBPOUtDY3FkYndxbU9kODVOQ2RvcVYtM2FEeG80T2xLN1EwUVNZRTJkbzFBOXV5ZGRwRUJXcndkeUpfcDNLRnRxRWkxUHhiRjB6R0k2Zm9KRE1ENVh3TWZkcU5SYU1ja2NTZnJKOG52cndlYVdlN0REY2locnVVaHJLMnkwbXhERkROWTFFMzh3c3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQeVpwc3ZyM2dISHFvMjNObW9wX2FCbDU1VXBNWGdkUTZXTW8yN0xQRlVGYldQaHNBRlNlSDVsa3dVS0V2c1Nkckdqa1RtQnBwWGRXVnRMVjBLVi0xcVlqemlJaVg1bW53VnhPay1kczBCVllFVW9vWXg3NDJub2M0bUJoQ1JzN0dRbUZaUGRaUDRBaHZxOXoteU9jc2s2Y0hkRnY2VGVkNThHVGFCVlB1akJwQmpxSE5DelY5MFpuQVA2WUxQOXc?oc=5</t>
         </is>
       </c>
       <c r="F62" t="n">
         <v>1</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46055.21641203704</v>
+        <v>46056.28412037037</v>
       </c>
     </row>
     <row r="63">
@@ -2483,24 +2483,24 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>EU Selects SUPREME Consortium to Develop The Union’s Superconducting Technology - The Quantum Insider</t>
+          <t>Large RIAs step up AI and data spending: Cerulli - Structured Retail Products</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 09:24:45 GMT</t>
+          <t>Mon, 02 Feb 2026 16:11:33 GMT</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNaUNORlkxWXBCMW5YVjZIdHFFck9Yc2VhbGxWMElvaTI2RW01azg1cDBJTWlaclpXZENadEVsNXZiRnNpdUt3QjE5UkVkclByTTNEVXowa1VlTGZ0RlVIaWVIVkwzcjB6b1RVeTlkcjlWMXJrU2psMnNCbm1Fdkg0cW9faGpkVjFZNk1UVE1WejhXTjRfaHdaSUstY0k0UWZjeXNLYWJkbF9SUFRTWm9ZZTNXQ2VaQThROXlFXw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPcFBPNGFHby05c3dkYV9CNVZtRDc1eVdFRmhmSWdJVHQ1cE5GamVNaElKVnoxcHRSRFFFQnFyUDE2M3dzVW9MbmRCUmJVZnJsWXVLb1dMZ2xVa0VxUVNOaXJSNklRdW1oWE9RUEtabUt5MHJiQ2FrZHIxUGc1d21XOXAxeXJXZFFiLUtVeDJ1Uzl4VlJZV1VQczVJTzZ6d1dyUTdRX0xB?oc=5</t>
         </is>
       </c>
       <c r="F63" t="n">
         <v>1</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46055.3921875</v>
+        <v>46055.6746875</v>
       </c>
     </row>
     <row r="64">
@@ -2516,24 +2516,24 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Betting blind on AI and the scientific mind - The Transmitter</t>
+          <t>Barton Peveril case study - Google Cloud</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 05:00:58 GMT</t>
+          <t>Tue, 03 Feb 2026 05:13:05 GMT</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNdWJUT1lZS2tZZEVHXzlBbUJOaVl3Y2VLa3dXblRNcmxsci16YnBrWENIanhRRHFoY1k5VmkyenF6VzdXaGEtRW9WVFlwSXhtTFVHLTdLb1RGVTY0Y2dhZ3dWOHdPZDB1SWFNZnZoR0UyN05TNzQxYmx6eG9QRHROZERYX24tRVg0d0NKTm1OT1RRNU1WUTE0b21zT09UTW04?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE4xSjkwTjBsTk1qeWV5WGhJTFNIUEdKZkRXLUpGaFRUQXEzYVNNaUxkUEpDcmU1cFFJNjlCOVlkU2l4RTV1RmZsc19Sa0VaNXphVjJ3NFNMY1lmQThs?oc=5</t>
         </is>
       </c>
       <c r="F64" t="n">
         <v>1</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46055.20900462963</v>
+        <v>46056.21741898148</v>
       </c>
     </row>
     <row r="65">
@@ -2549,24 +2549,24 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>UPS Resets Network To Favour Automation And Higher Margin Deliveries - Yahoo Finance UK</t>
+          <t>The Telecoms.com Podcast: Ericsson, AI and Nokia - Telecoms</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 01:06:00 GMT</t>
+          <t>Mon, 02 Feb 2026 12:28:13 GMT</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNaVo5eHdfOGZhUjJoM0RQeTBpbWNDb0NkdnZKclhQcWtCc2NJUGFmTVBZQmNwcFdibW9QY2JfVjVMTDRiMjNWRkxaU1VPd2hYOWlZSS1GUlJjWFlGMjBfVWZETUVBaUNsUENXVkJ4eDVBNVN6Y2dkNFRVSzBPQXc4dkFqZXNPR2d3QVV4SWRB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPTHhsYVpnTHdHNkNEQXR5YTVXeEdDSFh2dE9YLTJsdVdFbDV6MkxuQzJ5Q0xTdEZFb2VaMjlESi1JZDU1QWJpekR4ZExxY196ekhkZ2lJUDZzMnp5MjFrS250eDh5OGRSckRLczFKdjJKYVcyQlhmdEtSWTA2R0VLTTZUa1dhV2dlYXc?oc=5</t>
         </is>
       </c>
       <c r="F65" t="n">
         <v>1</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46055.04583333333</v>
+        <v>46055.5195949074</v>
       </c>
     </row>
     <row r="66">
@@ -2582,24 +2582,24 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tarabut acquires Servable to add financial AI capabilities - Retail Banker International</t>
+          <t>Dow to replace 4,500 jobs with automation and AI as shares decline - Packaging Europe</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 11:43:07 GMT</t>
+          <t>Mon, 02 Feb 2026 11:08:32 GMT</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE4zbkhCOEtya20wSGRvRG1UNHkwTGN0NmlmWFNXdUMzOThtTVdaUGhDeFh0T0YtdzlDa2dCdXFHYUkzdUJjb2d5dngySGY2aWl2Vko4Z0s1dUFJbHBUeFZVRGpOR1I3SHVMLTREeUJnS0VDR2NUTXpLbm9BdXBJZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPUG85LWpVTTB1ajhzU3dMMEtCa3NkMDRxbmpjZTV4RmlvZ1dpSlh2VmZZSW40VEV2QzcwTDVaQVltdnpKT0gya19GT3I1VnJFUGNjRkNGNUtobGFCS0RjV2x1NmV5YTQ3bzlYUWxHRl81dnpLVk1vVHlEemtUU0JDeDk0SVhDYXBsSG9pMXBJdnJfOWpPQ3U4NjNVWm1IeEhCT1l6aWUxQ09EaGg0czl5MXh3?oc=5</t>
         </is>
       </c>
       <c r="F66" t="n">
         <v>1</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46055.48827546297</v>
+        <v>46055.46425925926</v>
       </c>
     </row>
     <row r="67">
@@ -2615,24 +2615,24 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Microsoft Q2 2026 Earnings: Can AI and Cloud Keep CX Ahead of the Curve? - CX Today</t>
+          <t>SpaceX absorbs xAI as Musk consolidates AI and aerospace ventures - Proactive Investors</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 10:46:47 GMT</t>
+          <t>Tue, 03 Feb 2026 07:19:00 GMT</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNUC1EZDJEcjROV0lVNzhneHVKWXk5NEcxZHk3OVZ5ellocGZJUnpTbHI2ZmNBbDVYY19SbS1XWGotdC1ISzE1S3RiT3dqWEFBY0JpUzlndDRCRlJ5SmdfZ2JhSlZQMUJsLUQ5UHA4NGZ3dlVKYmlRbnN6akZKSWZMbWxPWGtOOEVfZ24tMHBNMmZCam5ZeFhlRkkxd001SS1qanpXanNWM2xQQjNVaTRaV2Rvb0hLQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxOSktJdXEtMGNPWVJnb0ExNU9kLTNOVkhMei1sX0NVVjVuNXJYLWt3dVJaTXNwdzlaaERFemlOOTk1d1Y3d3oyQkJlQ2tEWHFFSnRIcDYzYVhIOE1JTkFXQ1J2b0NWRjRpVl81REJNUVlEeUhSb3VwYldETlFSUDBmdHRmd3R6N0FkWV9WVDV5TEw1YmkyWXhNNkNZREJVS09lVEhQRGM3SnBtdnVKbC12WHdselRoUnNtUV9BRkZXVmNBN0ctVjJWMGg1VmY2RWxaOWlVbw?oc=5</t>
         </is>
       </c>
       <c r="F67" t="n">
         <v>1</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46055.4491550926</v>
+        <v>46056.30486111111</v>
       </c>
     </row>
     <row r="68">
@@ -2648,24 +2648,24 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Why are women more sceptical of AI than men? New study sheds light - Euronews.com</t>
+          <t>SDAIA Launches National AI and Data Curriculum for All Saudi University Students - BABL AI</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 08:30:46 GMT</t>
+          <t>Tue, 03 Feb 2026 00:16:24 GMT</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPd285WTNKeFhFUUFjOW1qekVOX1dVeFBuZ1I4aGtZdjhsMFcwck00SGdRdHFkRmk5ZTM1Xzd1MDFtVkZYX29qRVR4RFY0Z21NTDhBRmhaZmV2azI5Uy1oTW9VbDRUS2thS0RYQWtLZDFIXzFiMGNNVjc3LXJNRk5CcTEzalNFQjNPUU1hbmRfcGJlRzZEd2I3c0FBMHFHVWltRDV3aHJBSnRZdWhPbVBfVmhKQVluQ1VCT1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOeTl0aUM3cjYtMFAzZ3IzU3VYRlJtWUVoX2ktMVJlLWxSMlpRcHVuWHdjNkdZNFh3cE56dXNvWjhXbEdNMGdTaE5PWHh1TFNwbjNCQzFWd044c1g0SmFFNHRzRWZwRmRuTG1FQUFtVUNHYWtISXdNWm03SlNDd1lWREtxel9RTHBicDQzVG9KMmZNUXBKVExBT0NCaHEydw?oc=5</t>
         </is>
       </c>
       <c r="F68" t="n">
         <v>1</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46055.35469907407</v>
+        <v>46056.01138888889</v>
       </c>
     </row>
     <row r="69">
@@ -2681,24 +2681,24 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>CANSO Says Greater Airspace Capacity Requires Automation and Strategy - Aviation Week Network</t>
+          <t>IFR position paper on AI in robotics released - International Federation of Robotics</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 12:39:01 GMT</t>
+          <t>Mon, 02 Feb 2026 09:50:47 GMT</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQeEpFajRYUjU3cDhISm9odXVmaF9BU01aZFZxNndTd3AyUnJyZWV1MVdsbjQ5SEt4UlZ4LTJTTFkxdW9lR0xITzY2TFpWQmJiRDhYTzNyQnJhWDNhY3g3bTQwdHVXd3J5ekFtdnlJZ3M4ODU0NWE0VFllMHRBTEpUbTh5OWJBT3cwcllYWHdlZ00yUFNOX3lSNGtKZk40aXpBVzNSVllCeUFmeDkwaVdSM1pFMTZsbEp5SFkwOFpfbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE1uM2Vnek8zdm5IV1hWem9CYWl1S0czMEJLd3lhNHNlLURxajlQZy1ISzdSd28yblRfeUpKV3ZsYWlPYlJsNGdDalFWMUQyOTVqSmQxMzNqV1Y2SE9UbzRxcjc3RzVRcTc0NG9tYV9JbU5fWVAzemRVMTVhV1o?oc=5</t>
         </is>
       </c>
       <c r="F69" t="n">
         <v>1</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46055.5270949074</v>
+        <v>46055.4102662037</v>
       </c>
     </row>
     <row r="70">
@@ -2714,24 +2714,24 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Maxio Report suggests B2B SaaS and AI growth remains strong but has become more selective - Enterprise Times</t>
+          <t>AI in 2026: From Promise to Pressure - Teneo</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 07:14:23 GMT</t>
+          <t>Mon, 02 Feb 2026 20:55:49 GMT</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQS1Y4c09NU1JsSUlBMjFudjlEUGlkX19mdWR6Wm5pZ3VpV0NMd0JFTjY4YmtPd1VqWjRzb2E3aGNyMjlxSlBUVm5aMnl5Z1RabC1rNEZpcW1mSURYaUZVVko5dUNkQ2kzekltTDR4dHpTQS1uZFFHN2hWYS0zYnl1NEp5UERRczJwU2pKUnkzakN3c3RZaXM2R3EwX0tXZWgxcUlVRmRwOTc4OGxacmRWbjM3WXNQaUNYcnhwOXptTXpHU2RpRWpNaVEwUEU1UzZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOLXVwemdRYk1qT1FqeUh0VnVrQ3dZWVNmWU1jWDJFaHVRRWlUcW5ZbGowSXN4MFBaSGwyb3lkMEF5aHg4VXdpRWtrNng4b0dIWldJdUJBRl9MNkNoRndQMGQxVVpub1p1VmRUekJodHYxNnpZV1M5NFV5REJiaU5fMERPQnlkTEZ4NUVKcFA1QUxXYTA?oc=5</t>
         </is>
       </c>
       <c r="F70" t="n">
         <v>1</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46055.30165509259</v>
+        <v>46055.8720949074</v>
       </c>
     </row>
     <row r="71">
@@ -2747,24 +2747,24 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Grok, AI and “free speech” – Starmer vs Musk - palatinate.org.uk</t>
+          <t>UK-Bulgaria: connecting semiconductor expertise for growth - GOV.UK</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Sun, 01 Feb 2026 20:30:01 GMT</t>
+          <t>Mon, 02 Feb 2026 13:59:31 GMT</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE9Qa2J6bG5BUjIzZ2k0Zkl6Ynk4a0x3dl9Hbm1yenJMNE1iUFM1cVY4d0hUcmdwYk5XRTB5a3ZjN0h6eldTVU41TkdWV185ZzFLQ0VCZkdkVU9keFZubF9kV0ZsQUdteE5jdDlKdHRpdUdjNXRacVpwMDR3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPUHdYRDVQYWVLZjR4MnFna1dPMEJYd25Bc3VvdllKVGJ3OXAzcGIzUy1zX3hQUHhfZVdlZExSZWVkVUc1dGF0OG5ncVRpNkp3YlNaaFBKZjczUm1ET3hBMVlRR00xbi1oVTZtS3REQ2tjek42Y1lKQUdTclFzT2dobGhIdE55QjVsVzFqTUJ3U01aZGVISTU0?oc=5</t>
         </is>
       </c>
       <c r="F71" t="n">
         <v>1</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46054.85417824074</v>
+        <v>46055.58299768518</v>
       </c>
     </row>
     <row r="72">
@@ -2780,24 +2780,24 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Can agtech fulfill its promise? World Agri-Tech explores opportunities, challenges for the future - AgTechNavigator.com</t>
+          <t>MediaTek Accelerates AI Development With an AI Factory - NVIDIA</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 10:06:00 GMT</t>
+          <t>Tue, 03 Feb 2026 06:16:43 GMT</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNWFFRQ2RucW80azhrWVJ4Y2J2enBFdDJHOTVlcXhnNWtDTmJsOWdadnQ0cUVHNzRXSGhlUGZweUI4RlZGWHA2cFRRRUl6YVhxNzNFYVd1d3dMMFU0LVJXbTA5Zk80ME14ZGhoVjdpVzRXUFZtV0pWb010Z2kwZWliVXV6Z0FkYlBqSmN1b3F6YklmTWxVWWtpVzh0RnhCYWZ3Qm9KLTlrUEFJUnBtdkNrVVpR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE1EY3BvY0lNOWlaSGhoYWRHOFl2ZVBVZ281bDRzMXJtT0FTUzhxYkRmMU1WaEJkWnpGN0kzYzdPZjBqeV9qQ3hQdXpEUUlNRU51a0llSWRpLURiLXVxbHpfTWxKNUpxWV8yYS1tNkdHSQ?oc=5</t>
         </is>
       </c>
       <c r="F72" t="n">
         <v>1</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46055.42083333333</v>
+        <v>46056.2616087963</v>
       </c>
     </row>
     <row r="73">
@@ -2813,24 +2813,24 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tesla Recasts Identity As Robotics And AI Platform With Merger Potential - Yahoo Finance UK</t>
+          <t>The Balance Between Rules and Learning in Robotics - Telecoms</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Sun, 01 Feb 2026 17:10:27 GMT</t>
+          <t>Mon, 02 Feb 2026 16:52:45 GMT</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOenZGbUM3RXE4U3Q5RUU5bmZoOC1MelduTGw2Nkl5dWpLZVY1UmNPWnpxQU9Pam1IWGtaYndOcUZWSGt3amdtZk1MQ2hOXzQxeFRETlRFWDd3UkxienlDSWhhTHN2c0hSblNnckdBaUg4V0JOQnlYdjU1VjliMF9aZ3gzNXpvQ3p0RVFR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxQVGNhZGZTZzZjUkl0NlJQWmpWSmFOTGlRTm9DZ1VDbXl1ZUs1TVBIT2ItbHdyV19ULUJDMWZfTkFGS0tuYWFyMGxTMEtFTEhFSXNYeUxYNGdvcmYxcGZ3ajdJYzVYcTVDQ3RlQTlwOHVkekljNUtOYWloN0hEZ2lfMmgtRm0?oc=5</t>
         </is>
       </c>
       <c r="F73" t="n">
         <v>1</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46054.71559027778</v>
+        <v>46055.70329861111</v>
       </c>
     </row>
     <row r="74">
@@ -2846,24 +2846,24 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Managing the Load: AI and Cognitive Load in Education - Faculty Focus</t>
+          <t>30,000 at Web Summit Qatar for AI, quantum and creator economy - Euronews.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 04:07:18 GMT</t>
+          <t>Mon, 02 Feb 2026 14:58:41 GMT</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNNUhwYkZCLS1OQk5FMnVLNThFcE05TGx2M1lEbld3bEdyT3dYdER5b0dwMnJZZW83YlBGRDIxYTRWRXp5eTJHRlRnZ0JwS0FzTHFRV3ZQRV9ZNGVqendFYmN0ekE2REVEblRMX0xWTGlUXzVsWGJLYXFjSkcyaEh4ZGt4SHZXQUU5bUFsWDgtelExVEV5bklDaHZTNk43RDkzNWNTcWwtOGZNYWlLTnY2SXhXNmtPNk9tMVpqWG1n?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPUEx0MTRuaVlMOHV3YkdXb182cC1BZE5OMVFMekFxWVQzX1l4UkpJTFBtWFdVYnU5UDVnUTlTelR6ZzFnd3prVVR0cXlScThjV2Z0TGswU3RoeXA2TUhfdjB3alhVRllMTDBIa3d3ZjhISGxrbWNJVjl5M29YbTFjTmpFSndVWHRPZEpJVWhTN0VGWWM0WnlCX3hNcHV0QXB1QWpqaGE5dWsybWFGV3dOMw?oc=5</t>
         </is>
       </c>
       <c r="F74" t="n">
         <v>1</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46055.17173611111</v>
+        <v>46055.62408564815</v>
       </c>
     </row>
     <row r="75">
@@ -2879,24 +2879,24 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>C-suite poses greatest AI risk to businesses, not entry-level - Personnel Today</t>
+          <t>Electronic Design Automation Software Market Size to Lead USD 34.71 Billion by 2035 Driven by AI, Cloud, and Advanced Chip Design - Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 05:00:58 GMT</t>
+          <t>Mon, 02 Feb 2026 15:02:00 GMT</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTFBhS2t1cTV0UkhxRmkxdkM0ZmU3eU1JUVR3WG5wY1lkMm1lNGZUZm85VDVYUEFJQnZmVGhKY0dfQkhGWjQ3bDk2bWdZSXRHM3U5ekc4LV9NNGs5MUc1R2owQWwtRlRUSlYwSXluN2VBTVZpS3M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQNUtvZDlhS1BqSDdfeFVBY1ZaVFNMd2ZOX3QyQk02UGtkNDFidHNkV3dLRXlVdEI4R0JjYkI5MzZiR242TVg1bTRJam4wakR6UUdJbzNXZmYzYUZhcC1JOV9EaTM5dWh4Smp0czlIaWJKYjRMNkNJQVlyMzN1V3QxUy1HbEhxRmF3QzUzMW8zaFJHSzB4Z0RJVw?oc=5</t>
         </is>
       </c>
       <c r="F75" t="n">
         <v>1</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46055.20900462963</v>
+        <v>46055.62638888889</v>
       </c>
     </row>
     <row r="76">
@@ -2912,24 +2912,24 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AI’s ongoing evolution in corporate travel - PhocusWire</t>
+          <t>The power of putting AI governance into practice - Global Government Forum</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 06:04:25 GMT</t>
+          <t>Mon, 02 Feb 2026 17:11:25 GMT</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQNnRpVmpSMDE0TWZYaXlNalhkMHN6VzdTWGJtbGtXdnd4bUhzZWpQS3dDUFVZaDdteGJxNGUySnBwMkJuemQ0U1ZVVF9XX2U2bktCa3BxcFdKQjBIOVZiUlhldm52YWNBOWpneWpQQWZXMlZvOFRiYXVJTTAxVndtdA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQWGllM2ZaRVR4MDZreC01cWFWUTNoTW5fMWc3bGVxTVVkSjVzNXR2cmp1UTlWM2ZDQjZHckNkVTIxdTVnQXZXc1JsTWhXSW0xWDB2dEtFWUNNNjE4emNveHN2dk1hMHR3VlJVWkVzSXRHMmd5Z0d3NUhQTFpGQlJTVGNFZXZvaDZnTkU4R3RqbmI?oc=5</t>
         </is>
       </c>
       <c r="F76" t="n">
         <v>1</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46055.25306712963</v>
+        <v>46055.71626157407</v>
       </c>
     </row>
     <row r="77">
@@ -2945,24 +2945,24 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Deezer opens AI detection tool to rivals - Digital Watch Observatory</t>
+          <t>Christian Klein Bets SAP’s Future on AI and Data with 5-Point Growth Plan - Cloud Wars</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 08:05:00 GMT</t>
+          <t>Mon, 02 Feb 2026 16:00:00 GMT</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE9ackFocUVZY1ltM2ZxaVpSQWFCcmdGTGVmRkN4WW10LXZJZlVFckQzQnc5RElZWmNvbzhPTEZVbFFLOGdwNm5RcE5ncmt3UkxoUXRRVzluTnlRMndvcXNYNmVQY01XOFpZeVlzck4tSF9TZTIy?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQU3d6S1RPNFdFbzJkR0Jfd25KTmZ4dW9lQkozcVlCS0ZPa2xOc05WWmhTMGJYbHlFVy12d2hnb2h2cU1XSmlrWC0tNkpHSEtpcENPRElUYlkyWXE5ZXd3Z2M3OGVXd3FRUDdWaldfNGtfc2FsMk94WmNqdnRONnVEY1k2dEpTeWViTmxyUjdYN1ItcEhuMHVZN2Y2OW53eUJrWXZGcEJ0cS1sSzNXS29qZnlXNnlmVHZO?oc=5</t>
         </is>
       </c>
       <c r="F77" t="n">
         <v>1</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46055.33680555555</v>
+        <v>46055.66666666666</v>
       </c>
     </row>
     <row r="78">
@@ -2978,24 +2978,24 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Kazakhstan to Introduce AI in Water Sector by May, PM Bektenov Says - The Astana Times</t>
+          <t>Forfusion Partners with Stellium Data Centres to Accelerate AI-Driven Innovation in the North East Growth Zone - TECHNOLOGY RESELLER</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 12:37:49 GMT</t>
+          <t>Mon, 02 Feb 2026 21:07:25 GMT</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNT2JBTHhOTmhnTTBtcWQ5NTVCR05aeW5oZnlxNTlyQzVYbllIWHdXX010Y3R5amFnUEN6U3d6Q1R4NVZZMnVhUVJiM3pmWVUyRzl3UTh4WUhwQjV4LUlRZ0k2TmlzUWx5QkhWdl9UbTNvUmRwNUM2VE91a3dCZEpmQlBqMVdSSlNpdnF1RHZKcTZ2UjRBcmRiWjR2ZWV2TFdu?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQc3VIdlFiZkpoWTlVLW41UW5aaU9Jb0ZzZTFCOURUSm9maU9Sd3hyWmpkZVROdFB5RFF3UjJEUHVia1FWdFNzdUhYczFFeUlGeXk1Zkw4WE5DSkp2dkNEc1ZOT2ZlWjFXZHlVMFhSMzRubVFjempHQmU1M2tuaWZvUEhmUjBKSVBpT0FfalRta0JfQnR2MDlJdUlhUWtrMnZ3bElJM2hnUlotZDdFd0xOZEdDX0FiMUNhMFplM0pmQ2ZObENSQkRqclAwSkE3SHpVcm4yUU43WEY?oc=5</t>
         </is>
       </c>
       <c r="F78" t="n">
         <v>1</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46055.52626157407</v>
+        <v>46055.88015046297</v>
       </c>
     </row>
     <row r="79">
@@ -3011,24 +3011,24 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>China, AI and the West’s Free Speech Crackdown | Ash Sarkar Meets Ai Weiwei - Novara Media</t>
+          <t>NEWS: NHS Tests AI and Robotics to Speed Up Lung Cancer Diagnosis - Practice Business</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Sun, 01 Feb 2026 15:03:30 GMT</t>
+          <t>Mon, 02 Feb 2026 08:38:49 GMT</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxQVlRxZHhhcHV0NGFidnJRcWZkQnc3WWZLQkNiR1M0T0JSZU9MaGc3VkprNWVvWkZfUVpaaHFxUVFHdkpjdUNWSWRiYno0cXhpOXZNWWF5LWJCV3NzRVJCM1lhbkc1YkFmNUg4ZG9FZ3p4RTJEZUNKeUtIVkh1cDVzTzdMQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNV2k0ell3bnhNOFBMM29oU3ZHenZTNkFvX0lDc01hSjN0QmZFM053cndMN3pPNDlPOGRxNUVVMjBuSDEtc3hSSXRzNkhwdkdMWlFvUzBGc08yWVM3S2tvaW9fd09heU83T3ZKVzF2NGpPc3VRamZzbUVMZXdqbUJtMm8tcDI1d1ZrM2RXTDU2VUZ4OUFMV0hkbEY4WQ?oc=5</t>
         </is>
       </c>
       <c r="F79" t="n">
         <v>1</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46054.62743055556</v>
+        <v>46055.36028935185</v>
       </c>
     </row>
     <row r="80">
@@ -3044,24 +3044,24 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>KPMG warns of gaps between AI ambition and returns - Digital Watch Observatory</t>
+          <t>Energy, healthcare and utilities: how to tap into AI in the real economy - MoneyWeek</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 09:00:00 GMT</t>
+          <t>Mon, 02 Feb 2026 15:58:55 GMT</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxPa0NUQkc4cm94QjhSZ1ppc1Bmb19FUW9RTGNjWDdGUHJncnFpeXNFdkJYS09LTHk2dGRQVUkzb2ZyMGxYOVJyeXlXSzJyMGwyTkdQOVpjX2NDVHMwalNMTkpoWTdPbm1NR1dRRDNKQ1pGbnBBZ1pzOVlRalJCM3dDQ1p3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE1xc2lydjV1aDZXaXliWnM3UHJDcncwYVF4Sm5QMWNxM2ZHb1J4OXNYYzJhSnZ1a2wzSDlBQ2UwWFpGWUlESkRQeV9PME1TUDRlOVhLZTVOSjdpU0Z0UUlWMXBYS05UZDZ1UmVtN2NqTlFwaXV5bEE?oc=5</t>
         </is>
       </c>
       <c r="F80" t="n">
         <v>1</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46055.375</v>
+        <v>46055.66591435186</v>
       </c>
     </row>
     <row r="81">
@@ -3077,24 +3077,24 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Venture Investment in AI Rises Fivefold in Two Years, Says Latest Report - The Astana Times</t>
+          <t>Answers to key questions about AI in IT security - Computer Weekly</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 04:52:40 GMT</t>
+          <t>Mon, 02 Feb 2026 16:59:23 GMT</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPVHdSRUZ1LTFkVDJ0VE9td2pIY0xHaThneU82YXFyN2Ric2JQSWpjTHY4WjR5ZDlDbXVMZHpVbTRvLWlTQnl3WlZYYTltYjh2ZGJuYTRkbkNoa0N6ZFV2MEU2RVNNZ0x6b3NoU1ZvdGRiX3QyVmpPNG0wREpJVEZ3VmZ1QS1VRWI3NWN6UXg1em96UTVkdjJVUTZSOXl1ZFF2MHE0ZTFwVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQenRxTzlpYTV3NW5xVEVqcFpNRDhZT1ZQbUFVdjQ1WFA3Y09MenRmUUd1MTJlX2NSTy11VUN5YzhmQkNyUnZCMG5kQTFYYTJ5aUtjcjlQLVJmQVZxbDUtSzliY1lLaVFfTzlzSTVLSHpKYk5DbzdzMG5DaUU3X0VYWklOemd6NmZ5M0JpaEF2SFk?oc=5</t>
         </is>
       </c>
       <c r="F81" t="n">
         <v>1</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>46055.20324074074</v>
+        <v>46055.70790509259</v>
       </c>
     </row>
     <row r="82">
@@ -3110,24 +3110,24 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Who Answers When We Ask AI About God? - EWTN Vatican</t>
+          <t>Why banks shouldn’t wait for AI to fix the Gen problem - Retail Banker International</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 08:26:40 GMT</t>
+          <t>Mon, 02 Feb 2026 09:28:04 GMT</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFB5NklNUjczbU81ZU1UdzdnaGdKak80OFJseVEyX2hKbUY2VVN4VUJBSGtBcUo2NGtTYkIxMDVsUHE0TlRfNlI1ekRScDExMjNDbHdUeVpVbkI4TTBPV3Z2NHpoakN5OVB0LWgzVlBlS0txeGJIN2RqemZfVmlkdDg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPNkJaSEM4djg2STlSalNWM0c3MmhmS1ZNS1c5MG14VUREZzNha25fVXp3VXF0YUczMkRlMEwtVldORHU4TFA1dEtLY3dfeXpmcW5UbHJLR09mX3FYZlFwbmtCbU1GZ3lsMFBUZmhpU2ZHMzlVZUxkSG0wNkRCeFcwQkk1OW5ZUlVaNXFPVktQb1g0djI5ZkQzU0ZKTQ?oc=5</t>
         </is>
       </c>
       <c r="F82" t="n">
         <v>1</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>46055.35185185185</v>
+        <v>46055.39449074074</v>
       </c>
     </row>
     <row r="83">
@@ -3143,24 +3143,24 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Opinion | Where Is A.I. Taking Us? Eight Leading Thinkers Share Their Visions. - The New York Times</t>
+          <t>Year in Review: 2025 Artificial Intelligence-Privacy Litigation Trends - WilmerHale</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 10:03:00 GMT</t>
+          <t>Mon, 02 Feb 2026 18:05:23 GMT</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPXy1tbFc5V2p0NVlhcHJUc2FQeFZkS21UMjQ5NXdkcUZib2VndHZOenBpTW5uOGZvYTRoUUZSN2tZT1c3M19XbDEtbkpVY1pPbWJmdmp5RDZuVFZtWDkyb0ZhbExleXl1NnBCVTJWSktzRHhicldUMnFOSmpLOXdLck5waWpnTUktenh4WmRsZExTdkNELXFwVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9wFBVV95cUxNelJqZWo1aVZoN2ZxMjJvckNuZW85ZzJzWTNhaFowc2swaTZLc3dzRWJ2Si1Ya3NXSDBfeXJLOG1NVjVVV1FHV21TZXB4clFKX3ZUTnEwbTIyN1pDblVSQnRSYTdUdmNvQmZWR21BRDdfQmVJd1J1VEQ4a3VmVVZlQm40XzZQZXlEVEJuZ25QemoyVnJlVWtBUkVUSTVJUEQ1RXpYN3VHZHhmTmtCZlIydmhZRzBWM1RwOE9nWGZRanc0WjNUaXdBdWg0UjJXUUZNbW1wcXFJOXNHbVVCUE1YLVNZTGItd0VwR3hLeExudzlpNThYaHJN?oc=5</t>
         </is>
       </c>
       <c r="F83" t="n">
         <v>1</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>46055.41875</v>
+        <v>46055.75373842593</v>
       </c>
     </row>
     <row r="84">
@@ -3176,24 +3176,24 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>How AI is Revolutionizing Life-Saving Drug Discovery - Pharmaceutical Executive</t>
+          <t>How sustainable funds are navigating AI, defence and financials - Trustnet</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 11:06:40 GMT</t>
+          <t>Mon, 02 Feb 2026 11:01:33 GMT</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxOZlkyRDlhc3RUM0EteE5ObTBkSE9IUmZGMzBjX3VYYmZ3bW9oN0x5aWRFYWZfMTdpRmNMZGxYYmNLZjhLZEZLNlNRck8tdXR3X3Y5T3BDV0hubWwwMlE4NFV2Tm9OM0wtcUowUDdpcG5aUVF0TW53QkQ5M1BZLUJVVjJrbEo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPRktGQTJJdXpHeldsX3E3NEl3ckx2QjkxU2tIb3lPUF84dEI0a2ZfQjVjbTNMeHpZUFZjdkR2bldWTnpMRmNjMnBkNFZ5Rk05dW5xeEpsTWo1YkRXUjhpYkdEYS1od0dPSmhScjZPRjZsYVBxTzlUbXh1QlVrbVhwaFRyNTB4aEk4V2I3b1dhV1J4VC1vRUdsMmdTUEFFeElqbE1J?oc=5</t>
         </is>
       </c>
       <c r="F84" t="n">
         <v>1</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>46055.46296296296</v>
+        <v>46055.45940972222</v>
       </c>
     </row>
     <row r="85">
@@ -3209,24 +3209,24 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Starbucks bets on robots to brew a turnaround and win customers - BBC</t>
+          <t>Yaspa Becomes Founding Member of UNLV’s AI Research Hub to Advance Responsible AI Adoption in the Gambling Industry - FF News | Fintech Finance</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 00:11:06 GMT</t>
+          <t>Mon, 02 Feb 2026 15:09:39 GMT</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5nSFI2ZTA2QTdDc3FqelRieW9rT0N4OXU1Mmc3YmtLd2V0Si04SmtQdlVqOG50ZEJKR1NnXzA5YmVjQUk0elRaeXZuZi15cl9zYTV0VUFRc1pMQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxQX0k2RTd2eVNGVVlxZTEzYnJKZUR4QmJtMjdTVHNmb2tha0pVbVFpOVduV2dWWFVha183MGRuRjRnc1NCVGZvcGcxYnBRUnZrd2RrVlAtMmpjbnU3MzFIYW5NUUxqbnJSQkdab2M4akJVMERVQVliRGZGZmtvT0FhTFVwZlVLMWlhTDFDRDI5bzNPbzh0cjlfemh4Y1pvZC13ZGI5cU9OMEhUT1kzZmd6QVktRWN2QVpUd2Zla295cm5TZzR4Uk5SMENPSU9PRG81MjdNd3podUxlVmUteWdRTjhKaXNibmNmeFE?oc=5</t>
         </is>
       </c>
       <c r="F85" t="n">
         <v>1</v>
       </c>
       <c r="G85" s="1" t="n">
-        <v>46055.00770833333</v>
+        <v>46055.63170138889</v>
       </c>
     </row>
     <row r="86">
@@ -3242,24 +3242,24 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Is AI killing productivity? - InfoWorld</t>
+          <t>From Ideathon to Pilots - Updates on AI and XR Medical Education Projects - Yale School of Medicine</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 09:04:02 GMT</t>
+          <t>Mon, 02 Feb 2026 13:35:17 GMT</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTFB1VTZOQWpQSWhQbjRZQWZyS0pCbkxuWi1EVHhQSWtKV0RmSTAyeENSVGVrcklaZnJLTUxuaGVBSHJwTnYtWXU5VVlFcGJPVC1qdWQzNzRsUXJram1GdHJCQzVHalV0ZFhZd1ptaWhabUtrd1RoRlNVUFoxZ1V2dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQLUdWWXRPYW84MkNFNmV2c2s1RllLSXh1azlkbWhHVjdpM1RkbzBHUTdINWNQckdDVWNEdmxGaVZhczRHLVh1SEVMNWgtV3NNOEIzaXh4WENHNEN3djRwbU5ZVDF5VkpwY1VrOUI1dVJHaENlQmlqVjh1SXVQNmpXWklBZjROZ0tpVU84b25R?oc=5</t>
         </is>
       </c>
       <c r="F86" t="n">
         <v>1</v>
       </c>
       <c r="G86" s="1" t="n">
-        <v>46055.37780092593</v>
+        <v>46055.56616898148</v>
       </c>
     </row>
     <row r="87">
@@ -3275,24 +3275,24 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>How technology can help bank Africa’s informal economy - The World Economic Forum</t>
+          <t>Policy in a Strange Land - felixonline.co.uk</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 08:00:00 GMT</t>
+          <t>Mon, 02 Feb 2026 19:27:01 GMT</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQY2VyZW5aLWxNNlhIajNPWXJfN0ZCSXh2T0xWSTdpX01yeUxoMGYxVl9tQ0xZdXhZMWJnX3JYMHg3YUkwZXdDdHJRTlNGLWtDM2doendjWTJKZVNmZjFxejlSbEYtalVKX0o0MVVUYjJIZVhNMkZFelIxem5DXzhzemZ2b0QtcHY2ckxrZG0zQ3ZLSnAzbkozOXhkZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE9KSXF2Z0M1YUtkQUJLOGN1RTU1MmVrbkc3cFpSS3BiU3RzTXhWUW9FZjNEYTJJVUx0elRZaHhfdGhNN09YOHJLN1Ytc2VEeGwwU1FKSnczRXp2dkVTZ0JpVGVwaFlNb05lOFZodQ?oc=5</t>
         </is>
       </c>
       <c r="F87" t="n">
         <v>1</v>
       </c>
       <c r="G87" s="1" t="n">
-        <v>46055.33333333334</v>
+        <v>46055.81042824074</v>
       </c>
     </row>
     <row r="88">
@@ -3308,24 +3308,24 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Did artificial intelligence really drive layoffs at Amazon and other firms? It can be hard to tell - ABC News</t>
+          <t>What is the 'social media network for AI' Moltbook? - BBC</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 08:27:13 GMT</t>
+          <t>Mon, 02 Feb 2026 13:59:14 GMT</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOUnd4UzhaZlNjTEVyRDVIbVgtMFJJcExLR1psMVdtWUxYcktJX05BUkFISUJLdW11Z09DYkg4UHhNVXdPc1NzdVI4VTdDWTBVNE5qSFVWRmU2YUtSSDFSWTJRM0pZWTd6YVRnQTRfcF9lUTE0VHVqX0N4TjFYS0FTSGdfQmxkU0IyekVEdnJjaXlLb2FaMHpLb3pKclJFbkktX3MtTmtlRDdzRWVHYlHSAbMBQVVfeXFMT0lRTjhydFNjTllyUF9qalVtbW8zSVdvSUpJcS1fMlY0a3dFb2VhZWtzZXhXMzdXeXVYUHd5TzNBTDRWcmRHM0l2d21yVkdhZEVLWFA0cGJHWG5hYkNTOHpMNFRhZkpIcktLVnUwUExqSlN0X1BkOHQ4dk1oWGdFS01kOXlKVWxYWGdVMkRnNHlVV2IzWUJVVDE3LXRDWXF3NWViTm9OOXlWOGV6aFVEb0pHOWM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFB3OWtDak5HWnlsTlhORjhSSEp3cGdyUzJaUU05cmdlTlZSTUZYclByUUFaWDh6OGdoMXRkYk9KRmFmbEp6SEpYd29uaEtWY25HQktwdFVTbzhMZw?oc=5</t>
         </is>
       </c>
       <c r="F88" t="n">
         <v>1</v>
       </c>
       <c r="G88" s="1" t="n">
-        <v>46055.35223379629</v>
+        <v>46055.58280092593</v>
       </c>
     </row>
     <row r="89">
@@ -3341,24 +3341,24 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>SPIE Photonics West 2026: AI Everywhere | Business | Jan 2026 - Photonics Spectra</t>
+          <t>“A cloud-enabled, digitally resilient Europe transforms the protection of its citizens, infrastructure and strategic interests” - Thales Group</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 10:28:00 GMT</t>
+          <t>Mon, 02 Feb 2026 12:00:00 GMT</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOVER5ekZJMjhVaG1QdWFaMlNMU3R5QjY0U2RkY1JqQllOVDhOcUJQaHJOOEswMks5dmdRWHB0ZlNjV1dRa3BxRlZ0SVgyeXYxaTBQQmRpWEx1M1NfZlh2bmoxaUF3YzkyZnJXWlhDX2o0QlZ0bGdHY0NhNnlvRUZrWFJDR0hkaU5aRnBN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQc3lvdXNHRWx4aTVFNFlPbGUyTjB5UlVaN3dhSUhvbXQ5dmF1Tk91REd1QTU4R2VPbGc0b0VEbTZrRlE0cHJWaXVFYmlXaDFDMDhqM3BUOWtNZzJLb0FBSEh3T2pwLWEyTE5ycEpEX19mSmJ4TG40UTIzRVdZTk1IdEpFaWpfVmtoZFRTaXRBREk1YzdNdk1NOVJFRHpzdTJPemlFYmZiWGtuWEJJWVgyaVlDSDBsRjFoaVVUU2tjLU9ZUQ?oc=5</t>
         </is>
       </c>
       <c r="F89" t="n">
         <v>1</v>
       </c>
       <c r="G89" s="1" t="n">
-        <v>46055.43611111111</v>
+        <v>46055.5</v>
       </c>
     </row>
     <row r="90">
@@ -3374,57 +3374,288 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>How AI Is Changing the Storied McKinsey Interview - Business Insider</t>
+          <t>Confronting AI: The Future of AI Regulation and Your Path to a Career in the AI and Tech Legal Fields. - UC Law San Francisco</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 10:31:00 GMT</t>
+          <t>Mon, 02 Feb 2026 17:23:12 GMT</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPTGQyZlRzS3c2MDdEQ1JKaWIzYlFkOHZEY1JKZWx2bkRfRTBLQW9mTGM5ZWk2dmFXQnpVcHA2dEJ3QTBQRkVRQnVJMjhSejFKdTBXbHh3VGlRSGMtcEh1S0hhNnktem5VLWZFTEJGdUI5SXpDUTBHdEF3a0NoUVhSMXJyMk5ac1U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNbm01cEhkZjg5ajd6M1lsYUZFbEFHMkRDZEwzYVQ2N2xoalN6S1FZSm9QZU1CS3YyUGg3cVZuTEt3UWVQYVFkeXN2Y2U2bGI1R0pqVExjRGdqTFJGcm9GdFpQdkdCN1dWZDQtaG9hQzhrLVJ4TFFBNlNPYndWRWlGRUh5WXAxeDFzdU5WYmJlTnZPWGlDeUZ3ZjJWSVV1TWdIOE9Rbkx2amFjekpzY2FhZTA4dXVzc2xZSnZFakFwd0JEanRvbngyMldnYw?oc=5</t>
         </is>
       </c>
       <c r="F90" t="n">
         <v>1</v>
       </c>
       <c r="G90" s="1" t="n">
-        <v>46055.43819444445</v>
+        <v>46055.72444444444</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>From Performance to Purpose: Lombard Odier on Intergenerational Wealth, Intelligent Technology and Enduring Partnerships in Asia - Hubbis</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Mon, 02 Feb 2026 16:04:12 GMT</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxQS2puWGNpajlmcGtCMnhvcUo4MHBxRWJiMXlBRjFjLW5XZkRUY1o1MkkyV25mV0Z0bkYwcDY0anFmR29qa0NnWDAxZVc3MkczZTgySG1rQWx0OFVEbWtxd1d4UlRfTk1fZDdGRHJVQkowcVZsZTNLUDN4YlFYcE5RSnhEMDhvT3hqby1ESXJ6R0ZXS1ZxMklPVU9aYXFpeDVUTzBWcUFCTEtDYUJVWDhCYnJNVHhrdDY1RUxFa3ZDTFUzUUpnMFV2OFdqSzVFaWU0aTZNM0VKZTJ5dF9ZUXhHanVESzFFdTdqX2Vyd2ln?oc=5</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" s="1" t="n">
+        <v>46055.66958333334</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>AI deepfakes are reshaping cyber risk – and insurance must keep pace - Insurance Business</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Mon, 02 Feb 2026 11:25:07 GMT</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNd0JwN0R2S2lhZk02UGFIVWlwODVoZ0NQZTMxZzFURWZURExNbmpXRFlfemNZTWpwNXFidktkSDlSek1EYzlmZzlRSGxoN1dxeG9vcmZYbS1PNU5qTld2RVNQZUNwMXlKcnROQUFXYmtmQUdoVUxxNmV2VlVDRnBSMEZtam1MUzFnd09sRG5IWkVlcW9JNXBzb25qUVo2WjVvRXdxdUt3VnZjbk5vN1hsNVpMTUNQMkUtOVR4QUc3M05NVUZKU2xzNmVn?oc=5</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" s="1" t="n">
+        <v>46055.47577546296</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Whether it’s Valentine’s Day notes or emails to loved ones, using AI to write leaves people feeling crummy about themselves - The Conversation</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Mon, 02 Feb 2026 19:05:03 GMT</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxObU1UcmpiWm5TdXBWNGtVV2JaODBFWUZhamtxaHFYU1M5YlhPUHBCdDgtX0I3NDR0TzNFYXFiZWdaT0x2ekxVSC00eVBhT1J5ZC12ZlZXb0dkVGU0YTBrelFMNHJKWWRuZ2tVdDVqdkFHVFAzU3hNM0NoczBkV1NtNzgxVHZRLWNialIxUEx3a0ZEREdQSE56MXhYY3RVSlp5Q1AwT2Jiekpya3ZQYzd2eHAwVG9wYWpMSUM5WVROYWJGaWNEMHg2MXYxdmcyLUVQV011NGdzOElKZ1BLQkp0RjB3cjVhNUlLV2Zv?oc=5</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" s="1" t="n">
+        <v>46055.79517361111</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Palantir beats fourth-quarter estimates on the strength of AI and defense demand - CNBC</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Mon, 02 Feb 2026 21:06:32 GMT</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE52amFPRG1pR1dBclY2VlpPYU85dWNkaFFHRGw4REVNT0hqM2o0NVJhR1BHWHlLNFFpUVA1dVZJN2dpZEIzcGRuVE1pdkxqazRjZGtSNkMtWGdIZ1MxWXl4VGZueHBHTDRmMFQwR0JVdThvTTVmOVHSAXtBVV95cUxOWnpvU2RBSG1qVkdDLVY2MGpoU0thN0prd3VIc0puMllkX3VfdE51RW9GampfcVdmTnVaLTFHSlg3R0xFd081S0hxdy1uXzEtZlBPY0l2dnF5amMwWnlxQm9pM19YeHpzOTAxdVBfSzF1NHpKUGVMcXpfNTQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" s="1" t="n">
+        <v>46055.87953703704</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
           <t>Fraud_Scam</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>(fraud OR scam OR phishing OR smishing OR vishing OR "identity theft" OR impersonation OR spoofing OR "account takeover" OR "payment fraud" OR "invoice fraud" OR "wire fraud" OR "business email compromise" OR BEC OR "fake invoice" OR "supplier fraud" OR "procurement fraud" OR "social engineering" OR extortion OR blackmail)AND (company OR business OR enterprise OR customer OR client OR employee OR bank OR financial OR payment OR transaction)</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Scam emails claiming to be from Okotoks Oilers still circulating - OkotoksOnline</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Mon, 02 Feb 2026 12:06:07 GMT</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNQ0txZE1iWXdHNlJjNVRKQ3g2SEN3YmJBdWNLTjd6RDJYbFMzYV9lYTJsZ1NUY1pCbmJ2REJ2YUxXQ1FtNXhCa3VCNDJfUmpGMGM4dnlaTTFvMnFXbF9VTlR0NzgxcWxYcGphclFISDFJZi1EVDUwd3BaWmY0NkY4V09wa0dzQ211TXpEV19uY1JSOWFxQlMxQjZ4SG41SjBY?oc=5</t>
-        </is>
-      </c>
-      <c r="F91" t="n">
-        <v>1</v>
-      </c>
-      <c r="G91" s="1" t="n">
-        <v>46055.50424768519</v>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Syncro Marketplace Now Offering IRONSCALES Email Security Services to MSPs - ChannelE2E</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Mon, 02 Feb 2026 14:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNUVYzWi1sSDk4QUF6TGFDa2QwTXl4SlNoT0dnajh3SmF4OEJud0NTRF8ySkk1NmNRVE1DT3d2UEZJNGltTGpjWEUxT0xJTXBvTktjb2lPd1pRZnk2RVJfYWhnSkZxRF9vOGRVUHpmNVNTLXJodEx6WWo2cXFBdmdTcE81bnlJZGtqWmtSVUp1cGN6LTc5NHBjTmJnVXM4UnZnc21ieXNDcmZ6UQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" s="1" t="n">
+        <v>46055.58333333334</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR smishing OR vishing OR "identity theft" OR impersonation OR spoofing OR "account takeover" OR "payment fraud" OR "invoice fraud" OR "wire fraud" OR "business email compromise" OR BEC OR "fake invoice" OR "supplier fraud" OR "procurement fraud" OR "social engineering" OR extortion OR blackmail)AND (company OR business OR enterprise OR customer OR client OR employee OR bank OR financial OR payment OR transaction)</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Scam Alert: Muscatine warns of planning and zoning impersonation - KWQC</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Mon, 02 Feb 2026 20:48:00 GMT</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNVlJDQlRHWi14dHpfMWhEaVVjdU1vSGpoa3V1S2FCRnprTUNQZE1fRVZlMmFvNEp3RVgzanQwc2hCOFpoNk5QaVBFMmNkOGJxMy00WkV6VGZOYjhCMG94MG5fSVJSdU5IWXhhODlWVjVhV1JYUFlPZmJWNm1wQlcxVTBOZl93WDhibXJqQUNDczZ1ejjSAacBQVVfeXFMTlhDV1ZnMzQwcExSeWswVURrTm9fVW9uSnRGdVpON0RZYjl4bUduaUFGN29NMUdCOTVKQlJDTzRMQ25OazVvYnI1OURmaTNQNElRMjZtX1NnSlUwZGVuWm9aSnluT0lqVW1ucUl4dGVkR0FQWjFYaEZKeUY5cS13bmZ0UVZpLU5YbWV6bjdWTXdvQXN2SEV6UXpJbVBiaUxpV3ZoaEY5dms?oc=5</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" s="1" t="n">
+        <v>46055.86666666667</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR smishing OR vishing OR "identity theft" OR impersonation OR spoofing OR "account takeover" OR "payment fraud" OR "invoice fraud" OR "wire fraud" OR "business email compromise" OR BEC OR "fake invoice" OR "supplier fraud" OR "procurement fraud" OR "social engineering" OR extortion OR blackmail)AND (company OR business OR enterprise OR customer OR client OR employee OR bank OR financial OR payment OR transaction)</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Phishing Scam Uses Clean Emails and PDFs to Steal Dropbox Logins - Hackread</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Mon, 02 Feb 2026 19:31:17 GMT</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTFBmQ3hleDhQc3dBbEFOWUNxdC1MbG9Gb1RWaUwydUp6M1hXOTFyUENQbEpZVWVxNEtGcmVJRDlsVWI4QjFLT3lYNUtSbmtHVjFMdVdFcFBvbkxMcllWeEQtdHB0ZjYwclR3Smc4QU5MOWxWVTBOQnZv?oc=5</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" s="1" t="n">
+        <v>46055.8133912037</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR smishing OR vishing OR "identity theft" OR impersonation OR spoofing OR "account takeover" OR "payment fraud" OR "invoice fraud" OR "wire fraud" OR "business email compromise" OR BEC OR "fake invoice" OR "supplier fraud" OR "procurement fraud" OR "social engineering" OR extortion OR blackmail)AND (company OR business OR enterprise OR customer OR client OR employee OR bank OR financial OR payment OR transaction)</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Scam emails claiming to be from Okotoks Oilers still circulating - HighRiverOnline</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Mon, 02 Feb 2026 12:03:44 GMT</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOaXFHaERNMEctdnA5ZWloTUlKdWxheW1Yd0R1cWdLVVMxNlhjWFRVQm8xVXBzaVJqbHl6SlhGZTJONXctcDJPVXpuclNyR0R4dGpnZXJPSGR0TTd4ZlZsRjZHeFJzOURiUkNDNVFVNDVhZkwwVkZGcmhxLXpNSE43NzcwVTFwLXBxaEwybWNIZTR5ZW9qQVdsVEZqQWhPVjJteHNZ?oc=5</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>1</v>
+      </c>
+      <c r="G98" s="1" t="n">
+        <v>46055.50259259259</v>
       </c>
     </row>
   </sheetData>

--- a/data/daily/topic_feeds_daily.xlsx
+++ b/data/daily/topic_feeds_daily.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,24 +470,24 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Enhanced Free Trade Agreement with Switzerland round update - GOV.UK</t>
+          <t>Fox Williams cited in Treasury Select Committee report on AI regulation - Fox Williams</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 18:05:45 GMT</t>
+          <t>Mon, 02 Feb 2026 15:59:28 GMT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPNm9tY21mV1p0R0tWX29YZXpfaU1tOGdWWnd3Q2IxMDJKdFdCNklhOEZnVnlydVZEWHNVNTJWN3c0Y2Y1WVVzd1VCaXdPZkh1N2UxNkloTVduV0U0aThIOUlYQ2V1S3kyc3ZwYXhDMzcxQW5YbkljVkw4RGEyOEZvMFFGR09KNFhCRTQtcjhPQUt4cVVCYzlPdF9R?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxONUticHMyRF85OV9QcFRDQm5LV0YwTDc2c2RjZjRFcnpmUXJIcXRVWlIwSWpEdXNpbkp5eUMyZWh2UHNXbHFZcHlIZDJBWkJoQl96ZDAtdUtSc0xodUVGSzh6Q1pDTFdlal9RTmlEUVRZcjRMWXo4TE1feVlCaFJ6RExTR1ZYWHJZRllZMzZJaFhKTy0ydmVIX201Y2pPcHdIZUtVV3BzYm03YzIwbUQzYg?oc=5</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>46055.75399305556</v>
+        <v>46055.66629629629</v>
       </c>
     </row>
     <row r="3">
@@ -503,24 +503,24 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Fox Williams cited in Treasury Select Committee report on AI regulation - Fox Williams</t>
+          <t>Opinion: The report the government didn't want you to read about climate decline - Eastern Daily Press</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 15:59:28 GMT</t>
+          <t>Tue, 03 Feb 2026 06:00:00 GMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxONUticHMyRF85OV9QcFRDQm5LV0YwTDc2c2RjZjRFcnpmUXJIcXRVWlIwSWpEdXNpbkp5eUMyZWh2UHNXbHFZcHlIZDJBWkJoQl96ZDAtdUtSc0xodUVGSzh6Q1pDTFdlal9RTmlEUVRZcjRMWXo4TE1feVlCaFJ6RExTR1ZYWHJZRllZMzZJaFhKTy0ydmVIX201Y2pPcHdIZUtVV3BzYm03YzIwbUQzYg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNUGZ6R240am5jMWlPN2t6N0k0cVVZQU1rVmVMUDJaWEJuSDdXV2c1UWU1UUoxNTVwc0RtLWE3eVJTdDNzSW5WQmVxVUsxcjdaQ1JNcFIyQ2Z5UlRsZ0VZb2hxY1RPOFJHNzhxSV9yNFluRlRvenptbU9NWEVOUWtlRFdHTnBxUzFKa0pWcDFR?oc=5</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>46055.66629629629</v>
+        <v>46056.25</v>
       </c>
     </row>
     <row r="4">
@@ -536,24 +536,24 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US jobs report delayed again amid government shutdown - The Guardian</t>
+          <t>Government update could see more families save 'up to £450 per year' from April 2026 - Essex Live</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 19:46:00 GMT</t>
+          <t>Tue, 03 Feb 2026 04:47:41 GMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQX1ZZelJzVEM5Q2gyb1dsa1dfSjdScEdlRTA0azlsdVU1N3FXNDdmWVd5b3E2eDFYMFpISXYtVEV6azA4b1JBTjJacFViai1SYWlCcWxLZ3hYQmNhMEU4MnpwQXRscWlacVRaWXJnbGNua0RFc2ZBWDFqbVk5cmUzWGwwQUUtbnY5bUp6TDB0WFV0dXkxYUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNSnJldm5BUGh1aTJxd2p3dkk0cFFkdTdrelJPUWdaX2R1UnZ0QnNYcWVDX3d2M2xCOHNfdFVGUmJPRUhVT0psNGp3NVVPVFcwOHgxb1kzbG9vMFgxODJvN2pVcFNxODAxenRmOXFMTGd6UjdQNGVUZWNUc25Tbk5KaEZSMHNfWW5wSVk4eDJva3dwZw?oc=5</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>46055.82361111111</v>
+        <v>46056.19978009259</v>
       </c>
     </row>
     <row r="5">
@@ -569,24 +569,24 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Briefing: asylum seeker social care costs in local authorities - The TaxPayers' Alliance</t>
+          <t>Thriving Kids Advisory Group Final Report - MBS Online</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 07:52:30 GMT</t>
+          <t>Mon, 02 Feb 2026 22:47:12 GMT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPWGdja0oxNFNLVHVRc09JckljX182MU42Y0d3eGczU0xnM2hsNUUzd1c4Ykd2SkNzQmVzY1VQcmtEVHIxUWljelRpMXlzbUVLbFVQdkcxZHFjWnZlcnZaNkh2X0MxS3JtX2k2UGV3aXU5MWZpUzNnZElPdFEwQVU3czhwRmNnamJYRXRjNW9fN013b3Z6N0tF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQSU55MTVrdlV5c3kyTDhpTlBoM1J4UVlXSzZ1ajFiV2FFRmdtZEV1TGV3eUZvSWxNTFdRMjRiY1Jreko5WWZDVmQ1X09ndjEyUmZxQ19EWU1zXzlxdkZ5T0VjMnd2YnNLbEFMWWtjNC13MlN4ajVTM09KY0pjdHJVdlBkMXlhN2xMY0VHTnZ6cDlzYjJ5R2VCbEhmREk3UnZ2SkpEYw?oc=5</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>46055.328125</v>
+        <v>46055.94944444444</v>
       </c>
     </row>
     <row r="6">
@@ -602,24 +602,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New report finds quarter of young Scots fear they will fail in life - Daily Record</t>
+          <t>REC Clarifies On Report "Government Considering Merger Of State-Run Entities PFC and REC" - TradingView</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 04:30:00 GMT</t>
+          <t>Tue, 03 Feb 2026 10:25:11 GMT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNd0pXZ1JVcVQwQVpsUGIyYWgwbXJXRTVVVF9IYTlrenMtRzJkci0wczJURllGeFdJc2Q5NUpYVUFpUG5UYWNwZEhmNVZCLWh5TEp2Y1lwTV9sZHZIbkxoMmJPY1hMTDRNOUotSVdMOUFKZk1xX3BVQ3JNcDhWQ3psTjNJTno2bjA4VjFnVnhBMG5jUdIBlwFBVV95cUxNN3FBR1hkWWhVZk01aWlsTGIxd3V5V2FkTTRlMGlULTNMOHlzMlFWZjJWbG5DU0tUbl9LVVBHMFhDX0NwUkl3cng1YWNWMG5XZGZCWm1fU0xIeG1PZWFwY01ENEJKLWY0X2poOUtpU0lqM2lqMVhKMndXVjUyNGZmak51ZEExeDNCUmNGWFpFN2xudkxGTi0w?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxPZmtoXzg2VFNiNzVjVk1PSlJQSjB4TTBYbml0M0EwWkpLOWxtQUthcjBLU243Q2dXOXpQM3lONzE4RExHQU9qMFV6eGJrdDBvYzBNcUE3N0pGUzBKeEZvczFLV25ZZUg0YmlncjhCdFMxQ3A2UkpJcGZvZ29NbVNET3hMS0xZeHh5WDA4dEJnT0IzcDAyZXBWdDc5MWs2SWJoRTRFUVFXM0JKaWdXNTlNVktCTGJ4bXczVExDTmUyOUhiOEpJY3M5TGdFR3VBTmN2T01fTWczVzZyTUQ1YWZTVFlQUnhhcG9hQUJvT0FR?oc=5</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>46056.1875</v>
+        <v>46056.43415509259</v>
       </c>
     </row>
     <row r="7">
@@ -635,24 +635,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Opinion: The report the government didn't want you to read about climate decline - Eastern Daily Press</t>
+          <t>Friday's jobs report will be delayed because of the partial government shutdown - CNBC</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 06:00:00 GMT</t>
+          <t>Mon, 02 Feb 2026 17:38:14 GMT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNUGZ6R240am5jMWlPN2t6N0k0cVVZQU1rVmVMUDJaWEJuSDdXV2c1UWU1UUoxNTVwc0RtLWE3eVJTdDNzSW5WQmVxVUsxcjdaQ1JNcFIyQ2Z5UlRsZ0VZb2hxY1RPOFJHNzhxSV9yNFluRlRvenptbU9NWEVOUWtlRFdHTnBxUzFKa0pWcDFR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQb0k3ZUp6dmt3Q19RZDlUNG5hTVM5SjFpUlRLSXFyWlllWmlDMTdkeGs4VTdMaUJuMW9aeDllOEkwLXFXdTNzSlZpTV9NcFNocWl2UXRjUDJOWmJpOS0xR3BLajZyeW9nRzRxZThPaTUwM1NLYVdJZlVQY0pTaDdLVEVrb3V6WWgySjJJYklzQ2c0TzdTbWR1Z0trLXJqRXcyRzRzZHdJaFFLZ2JWcnp3cVFVRjJnZ9IBuwFBVV95cUxPT1NnRm0tYmVtdWgwZFhobzlZajhUYi1rUWtTa210VVJQbFpzWXJEWnU4NTMzdTZzUFNUaGpwVVRFc3VYTG4wanhIeWlsV3ZHRE0wdThVOVYyRXE2dU1mbnFyc2RhMVRjUkRnYWNMWnNXTXZFNDdEbUl2d0s3ZW56UTZ5aUFIa0Mtd0RRN2lzalZsUnJ6Tm4zYXlnQjFkQVRvX1JOY1FGVlJ3aFlZZDR0dnpzQWtzUGpwUFNN?oc=5</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>46056.25</v>
+        <v>46055.73488425926</v>
       </c>
     </row>
     <row r="8">
@@ -668,24 +668,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thriving Kids Advisory Group Final Report - MBS Online</t>
+          <t>Migrant encounters at the U.S.-Mexico border are at their lowest level in more than 50 years - Pew Research Center</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 22:47:12 GMT</t>
+          <t>Mon, 02 Feb 2026 18:55:15 GMT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQSU55MTVrdlV5c3kyTDhpTlBoM1J4UVlXSzZ1ajFiV2FFRmdtZEV1TGV3eUZvSWxNTFdRMjRiY1Jreko5WWZDVmQ1X09ndjEyUmZxQ19EWU1zXzlxdkZ5T0VjMnd2YnNLbEFMWWtjNC13MlN4ajVTM09KY0pjdHJVdlBkMXlhN2xMY0VHTnZ6cDlzYjJ5R2VCbEhmREk3UnZ2SkpEYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQcXUzZzRjaHZIb2g5VVJLZ1RvYktBWm1rdXBWTm45ZlBkbWNOdTRWOFlvWVlBQ1JYV1dXVkVIRWVwY0tmZ29LN0tWdUxEQktDZUlLRHcyaXN2QUFxZ3RRejUtR1NWMHJuX1dBalM2Q1VXMmFfMlUwYUwzTWItYTdRbkxyY2tiVVB4T2c2blR5X1hGWXBKbUttNjhYQUhnOGVhLWlEb091ZDBjcVZMVTg3a3IxSjBwVndTX1E2U0hrcFFFT2laWGdfNE9WeFpfR3ZjeWdKZjhhdktiQQ?oc=5</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>46055.94944444444</v>
+        <v>46055.78836805555</v>
       </c>
     </row>
     <row r="9">
@@ -701,24 +701,24 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Migrant encounters at the U.S.-Mexico border are at their lowest level in more than 50 years - Pew Research Center</t>
+          <t>Government report highlights artificial intelligence gains in Kazakhstan - IntelliNews</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 18:55:15 GMT</t>
+          <t>Mon, 02 Feb 2026 15:37:20 GMT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQcXUzZzRjaHZIb2g5VVJLZ1RvYktBWm1rdXBWTm45ZlBkbWNOdTRWOFlvWVlBQ1JYV1dXVkVIRWVwY0tmZ29LN0tWdUxEQktDZUlLRHcyaXN2QUFxZ3RRejUtR1NWMHJuX1dBalM2Q1VXMmFfMlUwYUwzTWItYTdRbkxyY2tiVVB4T2c2blR5X1hGWXBKbUttNjhYQUhnOGVhLWlEb091ZDBjcVZMVTg3a3IxSjBwVndTX1E2U0hrcFFFT2laWGdfNE9WeFpfR3ZjeWdKZjhhdktiQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxORGNzMl93aTlJdnFiczhjYnJNOXZMd3pNQlotRFRmS2RBd3hibUhieGlQTHR1MHY1eVpPQUtlVGEzM01KclZERFBPTkl5YU45X1JGTkNOaUZCTlhYdEVwT09OZFB5RURoUjN0TWxnbXk5V2J0dHJaQkc4VGVaZmttcGFwUWN2M3dUT2xYUGQyaFVYX0piM3J1NVFxWTZsWmtickt5dWJwMUpNWEZl?oc=5</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>46055.78836805555</v>
+        <v>46055.65092592593</v>
       </c>
     </row>
     <row r="10">
@@ -734,24 +734,24 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Government report highlights artificial intelligence gains in Kazakhstan - IntelliNews</t>
+          <t>J.P. Morgan Private Bank Releases 2026 Global Family Office Report - PR Newswire</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 15:37:20 GMT</t>
+          <t>Mon, 02 Feb 2026 13:00:00 GMT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxORGNzMl93aTlJdnFiczhjYnJNOXZMd3pNQlotRFRmS2RBd3hibUhieGlQTHR1MHY1eVpPQUtlVGEzM01KclZERFBPTkl5YU45X1JGTkNOaUZCTlhYdEVwT09OZFB5RURoUjN0TWxnbXk5V2J0dHJaQkc4VGVaZmttcGFwUWN2M3dUT2xYUGQyaFVYX0piM3J1NVFxWTZsWmtickt5dWJwMUpNWEZl?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNNlVHdUt5N3NqaTY3UE1MNy1OWEhrQmxrREJBdGxORmtkU3g1U2E1Nl95UmhaaG8zRlhVRTZRTEgyd1JEVmZJRm1yUGgwcmt5ZWF0OWd6UHBqekdIdVEtZThXLTlRY0Z2SUo2R185OXJHWUNZMTdqNVhubHQwVXlZbHkwVjNnTThhTVRNTk1XbEFhbGttV0Q0SWZ6b205SGlxTFdLYnV2eGtxdVB5eGcybGNCbXpLcTdVUkMwMQ?oc=5</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>46055.65092592593</v>
+        <v>46055.54166666666</v>
       </c>
     </row>
     <row r="11">
@@ -800,24 +800,24 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>UK’s former US ambassador faces scrutiny over Epstein ties, leaked briefing - South China Morning Post</t>
+          <t>Trump Live Updates: India Trade Deal, Partial Government Shutdown and More News - The New York Times</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 15:59:12 GMT</t>
+          <t>Tue, 03 Feb 2026 00:36:17 GMT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPUkp2RzlBQ1hqN3RUY1RpS21EZlRoakx3ZXlaZWlxS2ZUMTdfZ0RDQnZkNm9oT3lwYzBYMUJLNl95Q3JWOVFxa080eEVpcUFheV9SSlVGWFUwbFhnTVczSWFKMUt0bk9mc21rbDZfVF9jWVcxU2hxRnU2dEVyN1hUc1J3NkJwbDd1OTExa0c4NkJjZ2VpbWlKZWYtM3BIYmczVnZuNXVrb0N1QVVkNlJkS0xlZGZFZHVVUGx3TE5zLUFHOV9pampaTFVn0gHKAUFVX3lxTFBVSElBNWxvdHZQSVZvNGt6eWJ4TnRRMW5OcEpITlVRZEJQZjE1eWJDVEppTW9pdHlZY1VpWkxjQlMtemJVWTN3SzZielBrcE5LU3JDVkt4NVA0aVdBLUl3d0c0SzRJUkt4ODJkRHBWMFRTaWY2TUV6ZF9BOXh4b2d5cDJxWUlBei1jeXBIYXBnUEF3YXlhUlRlaU44YXFIZXB2VkJkLUJsMmw2LWhveUp0WURTVGU0cGZJNHlIWklYc0tEOEJMeDVBRnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTE5EMXltcWRCdDFqc2owNmdaWVRqZTZhNDlod0hJeUdjdTJmb2M4cjR1dGpUQXZKNzBaYzFkNmFSR2p1TnNhTGp5bUNUS0lFSUk3ZncwZi1zT3ZaVWlrTW45YTVYSQ?oc=5</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>46055.66611111111</v>
+        <v>46056.02519675926</v>
       </c>
     </row>
     <row r="13">
@@ -866,24 +866,24 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US agrees to drop tariffs after India stops Russian oil purchases - BBC</t>
+          <t>Verdion extends €69m Danish development pipeline - Logistics Manager</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 17:55:54 GMT</t>
+          <t>Tue, 03 Feb 2026 10:38:14 GMT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE1OYXl3VnhHNkQ4QTZEUmpXS0JobDlJeGQ4MTRxbW9xanZvZ2xnY01veXpXNjhBNDR5bWZUUjVoMmdzTHd4dWxxbk1XclNmek9QUzdFTU9sNDIzLVBz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxORXZqU0V4V0wtZ3dmMTBaVG5wTjg5OGwyT0F3Y0pVbTc3a3Nsdm82cFNpakxIMmNoYmpEMGUyNGpzbVg4QWhWT0RfRjFFS1RsT19RVUl2aTRNS1FxcGFsekd0U1p0RGlBZTNUSEhKRVQ4cmtJeHFvMzBwZXF0ZEJFUExMVzg1bDhfcEE?oc=5</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>1</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>46055.74715277777</v>
+        <v>46056.44321759259</v>
       </c>
     </row>
     <row r="15">
@@ -899,24 +899,24 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Modi liberalises Indian tariffs much to chagrin of the left - thecanary.co</t>
+          <t>AWS to Lead Supply Chain Intelligence Workshop at Procurement and Supply Chain LIVE: The Net Zero Summit 2026 - Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 21:23:15 GMT</t>
+          <t>Tue, 03 Feb 2026 10:18:00 GMT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNQ05aX2phLTUtaURXdDB6UlZuZU9EWlJXX0s3MTFacURQZnZIdF9tRTI2T0MyOGhIdXJNVC1TbGJNcFBZZkw1T3FrSWtXaHgzcEtIWGJIVW01VTd3dXd5Z3NSbEJKZjQ0M1BEU3A4VXZDaGxOd2JsYzFrNndlV01oQnlqcWlwRzBkTTBkWHRiekxPTFZK?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQejBXZE80cXk3ekVEZGpNc1pkRHFscHdJQ3RYam04d0phWk11c2h2R1k0R0VWbzdVZGlZLVZVMVZ6S3ZzdUpmcFNKeVVHNHNqbm8xTV9SZ3dIVEJldGpMcDhKdXpZT2NEU0M2bmZwVlpoQUdfaDBSdXdJSEFSVF9kQ3VLa0ZPeVNHdUZF?oc=5</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>46055.89114583333</v>
+        <v>46056.42916666667</v>
       </c>
     </row>
     <row r="16">
@@ -932,24 +932,24 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MP asks government about freight-only line amid 'closure by stealth' concerns - Rail Magazine</t>
+          <t>How NVIDIA is Mitigating Climate Based Supply Chain Risks - Supply Chain Digital Magazine</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 05:02:02 GMT</t>
+          <t>Tue, 03 Feb 2026 10:13:24 GMT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPc2NSUVZaTlRTVXJBNDNTUFZsazBhdFcxZlI0dXZkSGwzbVBvQ19ybndNamd1Y1NwSXpXTUhJTUNVYllvTzJtWXpLdjNkRmxWdk9uS2hGMlFWSkloLWszM29tdEp4RW5LbmZoS21hb3ZXN05tQnNJcDJHOEp3OXZ5aGJRWERva19HelJJb0RTUUptUklyS2FDZ0xrUm1Yd09Ra0JWQmVObzRKYVFK?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOdUx2RzlMcFRaU2JNUjRwMDUyTWZac3VhSVNGbVB6NkNjeFBaSTItRmxpd1V0ajRHSFR1N2wycnAwNkFKX0Q3dTVCT3pxczlQNnFpZXFGRFlvbkJLUFhJLXFIN0Nvd0tkbXhKcm5ScFdxbkZ4UFhpa2g5Q2VpcnRSZlVRZklPZw?oc=5</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>1</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>46056.20974537037</v>
+        <v>46056.42597222222</v>
       </c>
     </row>
     <row r="17">
@@ -965,24 +965,24 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Grade II listed bridge could reconnect Port Talbot communities - Wales 247</t>
+          <t>NWSA volumes fall 5.5 per cent as tariffs disrupt trade flows - porttechnology.org</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 06:27:57 GMT</t>
+          <t>Tue, 03 Feb 2026 09:30:37 GMT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOT1JCUC1SQkRNbkhnY2x3RFRsVFFkekI3N2lqaGVLZHY3b2dfUzY5SlpKWnQ4TUpNWHdxeU5hUUtVV2h3eEFDamZCOHZ4anc3bXZ3TFFxVmNZR2NzVjNTb28xODlkbG1BSmZYenFKcTllanhOSXdmUzc1WE1pcUc1aXNILWFUY3JTbkdMRUFFeHkzQ1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNMHdleGpacGdmZC1vMWNsbXhteVpEb1JpVzNmYXFPcTBQTjVfQ3BpWjE3WXRZVFVqLWNHMEUwRW5qWHB2UDFYbE9rdThWMUhiZGNVRlRuSHBBNEpSajVYN1ZteU93UFNpbkd4T1BPcUxkdkFGM1FXTlc5NVBsazBMUVFqUU1DYjAxVldZeUJCcjBCLVRRQllHWHgxcm9RcTQ?oc=5</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>46056.26940972222</v>
+        <v>46056.39626157407</v>
       </c>
     </row>
     <row r="18">
@@ -998,24 +998,24 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>People 'avoid St Peter Port' because of accessibility issues - BBC</t>
+          <t>Solar PV Supply Chain Cost Tool: Methodology, results and analysis - International Renewable Energy Agency (IRENA)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 06:15:03 GMT</t>
+          <t>Tue, 03 Feb 2026 10:37:30 GMT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTFA5QlNNU2t0Q1JSdmItVU4wUzhEZ2JldGZWbFZLTEVlTG9vM0s0YmRqVndycGJ6RFg5R1pUbXRwT2dXSkg0NXJGZDI3SlM0SXl6RnNSRnczckVsOVdO0gFiQVVfeXFMTVBBOHRyZC1DajNSMUlkLVpma3haLW9vNkg1dW5scHJ5YXNFQ1F5NzVJaGl1YWg3Y3lEcEZDOHZoRlh4UU4xTWNQQmdOcHBYbjRoN21oRnZJdXNaYndaTmJPV1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPMFRPNHhwTDdjcGpGSkZFMTg1Wjd4OTBUeWtxWGVGNzFFN2FvQTI5ei1ZbDZzdV9fMWRnTTJYWlJWa1duX1UtOXo1YlFVTGxkNlRyaFZaOEJKc3VFaHJaZFJBTlExbzdQRVYyUWxmQ0NyVmczNFFnQzZXSXFfYU5tS3lQYkx3dlowVTdnWlc5c1FjcHF3SFdreHNneHV5R2x5MHhuSXI3LXFTVVFj?oc=5</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>1</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>46056.26045138889</v>
+        <v>46056.44270833334</v>
       </c>
     </row>
     <row r="19">
@@ -1031,24 +1031,24 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>How Investors Are Reacting To Realty Income (O) Expanding Into Global Logistics With GIC Partnership - Yahoo Finance UK</t>
+          <t>CLIP Group – The New Logistics: Interview with CEO, Agnieszka Hipś - businessfocusmagazine.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 07:09:00 GMT</t>
+          <t>Tue, 03 Feb 2026 09:58:48 GMT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOYVBjTlNZa2pDYS1iQ1pKXzVZYy10UkFZX2FqbWszNGloMlpRSEdoSDRXMUNaY21BeDRvWTlwNkx3ZXFTWVYtcnR4V05BSl9uY1J2X2YxUndPYktIZFNObGg1ekN5dXAtRUJrNmVrUmFINWZYaVo3bFJxQjZJb3VSMEItRlNURURhZnNz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPcjNqLTBRbjVqQXNVTmRGanZhdE1kLUxYdU82VzNiRnNJNy1ZU2JoRGhqdGdCTGFXZUUzc05xWFFQeHRTYkRvZEd1eTBPWkE5UWxLMUNxcGdDem9YQmJpRTdGb2pEb0RTcklnS1Q3eWp2RGpHRTBkUEh5Y1RYcU9jbGh6enFUQjVTRG45RXBITnZpbEd4TmU5anNHOF9ZQjdvVkkyOXk0eXFlWEwz?oc=5</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>1</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>46056.29791666667</v>
+        <v>46056.41583333333</v>
       </c>
     </row>
     <row r="20">
@@ -1064,24 +1064,24 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>India’s Rupee, Stocks to Get Tariff-Truce Boost, Investors Say - Bloomberg.com</t>
+          <t>Luton Airport to Open Consolidation Centre - Logistics Business</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 07:06:00 GMT</t>
+          <t>Tue, 03 Feb 2026 09:46:19 GMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOemVlVDhuUDN6WHNuSGdnZnVfaTRTdXJUQkN6OE16M1lsa2dwRTlNZjhFMkUwbndRZDhCblpSVEc4ZTZFZEk3cjZrUTNNcGd5Q0pQeFV0Y0Q4U21OOXhVQ2dERWJ4NVZGLWpvd2pVMGhDdTBOOWpjWDZtR1ZrclJ6WTZJMGxQTWVuTVdRYWduRUJ0MjJteTNwdUotazJ2amUzOWExenJCeTRTSUhhaEJBSA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPOXZQMk1HcDBzU19JWU91YjdaQk5heFJWekR2WEFyNGFpSVNzOFRXT2lfSHQzaHI0RmUxRjZnVHR4aTlfQTI4OTdwVXJsaWtmQ3RHY1U4cWtQdC1yRy1uOVpmRGVONkVJWEtoS21fM2oxN1hJeWF2dmFjcnFYV0llM215Y0ZXY1lXbzNjdHZkbzhBd2VNOEdwMDFpZS1HZTE3N054V0xON2Z4QQ?oc=5</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>1</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>46056.29583333333</v>
+        <v>46056.40716435185</v>
       </c>
     </row>
     <row r="21">
@@ -1097,24 +1097,24 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South Africa bemoans slow BRICS progress - Fruitnet</t>
+          <t>People 'avoid St Peter Port' because of accessibility issues - BBC</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 07:16:45 GMT</t>
+          <t>Tue, 03 Feb 2026 06:15:03 GMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOZ2NHTzE3Znp2OFVmZmgxOXNJSnFpUS1CLTcwVHlnQW5DY2p1NjkxZFBtUnA3cTNDamttWXBjMkljaFFKVXRMbEozeTJNOWRJOEhFQTJBUGRMU2lfVko3WlZtNTJYSUdpSVc4ZlU1MlcxaDI1SnN0eS1OZmdTYzRlNnFGNF84M1BQSkRLaXYtenU1aFIy?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTFA5QlNNU2t0Q1JSdmItVU4wUzhEZ2JldGZWbFZLTEVlTG9vM0s0YmRqVndycGJ6RFg5R1pUbXRwT2dXSkg0NXJGZDI3SlM0SXl6RnNSRnczckVsOVdO0gFiQVVfeXFMTVBBOHRyZC1DajNSMUlkLVpma3haLW9vNkg1dW5scHJ5YXNFQ1F5NzVJaGl1YWg3Y3lEcEZDOHZoRlh4UU4xTWNQQmdOcHBYbjRoN21oRnZJdXNaYndaTmJPV1E?oc=5</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>46056.30329861111</v>
+        <v>46056.26045138889</v>
       </c>
     </row>
     <row r="22">
@@ -1130,24 +1130,24 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Diana Shipping secures higher charter rate in extension with Cobelfret - Tradewinds News</t>
+          <t>Pharma strategies shift amid tariffs, pricing reforms, and US manufacturing pressure - itij.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 07:12:31 GMT</t>
+          <t>Tue, 03 Feb 2026 08:06:18 GMT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNRlJqZnpUd01zNE52eDRkcGhIZDJhS0lqVVJGNG1ST2c1WVgyUDVWblM1OS0zNWNBbGwweXYtd05NZHFiZHAzUnlzUWdJUmlaWWlxX3NxRlZXeWxDUl9TQVlYV280WUZLNDBUS1BfaXZfaEJNcWZzajBUNk1lTFJ5T0txRHhfZjVTNE1tbEtKci0yZ19qd1ozVkgwMHljMmI1ZklNY05lNlUybjcxdWw0alRmdjRvSzZFeG41ZXR3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNbWJCbjhfbUZDanY0Si1vMHZ1Q0NOMTdLcUFOaFNNRXVua1lLdU1GY1BvaTVEYzY1WXRiZ2c4b3NuOERISDFlLWpwLTFkNGttajBUekVXTjBFQnBHdUF1NkQyQ25HOU1QQnBOVXhhSTcyWDVkMWxfckVOSE95WWRQM1V2RGFRU2tQZVBSVU03YTNZUFZELTVPS2FCNUpVQU9fSFFxREg5d1JmU2lXZTYyRmkwNHhxQQ?oc=5</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>1</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>46056.3003587963</v>
+        <v>46056.33770833333</v>
       </c>
     </row>
     <row r="23">
@@ -1163,24 +1163,24 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Andre Gray is a Valiant! - Port Vale Football Club</t>
+          <t>Freight and ferries cancelled for bad weather and tides - Shetland Times</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 19:18:57 GMT</t>
+          <t>Tue, 03 Feb 2026 09:31:00 GMT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTFBmTTI3Q01qcGdCYjR1Qklwa3JNNTNNUlJ0c0VNeGhQMTdVVmVYbGg0aEgxT0x2VDdlcnNLOEYtMDg0THU4MHlCcmRObDNfcnhabjJBTXQzNFdqVm5wWnNfUA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNeGZQd1V5TVJnMW1BZWFpSjdUSElTNjYtWmZuN2JfVDVRSTB6NThsUk5ISTIwZ2JhMVdfR2JVa2YzQVMzTWFNNGI5d0c0MmtqTVNZTExMRjJzVTdRNE93bUs3YWU2Y01Kb1Z5aXlWc09oNEFndEJ2REhoa0JvcnZZcjNfMFpuMXpmaW01SElqWFNsMEpzd3EwM0hTRWl4c19kbEE?oc=5</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>1</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>46055.80482638889</v>
+        <v>46056.39652777778</v>
       </c>
     </row>
     <row r="24">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MPC Capital and Morten Astrup roll out new shipping investment platform - Splash247</t>
+          <t>Posidonia turns into a month-long shipping marathon - Splash247</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 07:31:43 GMT</t>
+          <t>Tue, 03 Feb 2026 09:57:45 GMT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPTE0wcTV6QlhtSEtqaHZWWHZhY0dHNS1BOUJjU0UtQXNLblQydVVycUxFT2xoLWhHb0Z1cDVTYnMySmNBVFhBUUtkdGJkWE1DUTlJUFJ1emgxSmZVai1MQ19XUWtpQXZ1LWNKQ2F2c0ZWblR6OENXOXdRSmdIZmtDTkQyR1NrM2QwLW1qM2o1bmlGYzZPSm5HcEFn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFBFYTFaZ2VIMFNPR3R0bnJjWFZUWHpwWmwydWItM0Z1T09ESy1iN1ZINF9iNzlncE84VmpwYmhWaUxhV0NYTlAwX2pHaWVrMWhkVG9yUFdWekZwUFVEZmlSc1h4MVhnVEpaRjB5RzVJTVF5bHJ0cENmRDVGLXVqTDg?oc=5</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>1</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>46056.31369212963</v>
+        <v>46056.41510416667</v>
       </c>
     </row>
     <row r="25">
@@ -1229,24 +1229,24 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Targeted sanctions in response to brutal repression of protests in Iran - Australian Minister for Foreign Affairs</t>
+          <t>Port of Rotterdam biofuels review and outlook for year ahead - Biofuels International</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 18:53:57 GMT</t>
+          <t>Tue, 03 Feb 2026 09:13:00 GMT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQNF8xXzhtOG5yYXRXYk9Ydm9WSEdfd3NibzRuSmdtS2ozWFAycldxWHlNWVNoV29MTU94T0RuOVdYaHB1MXNDV3B2R1RfVXc0Y0tjc0xYOWlpV2dNWWxaaGxFQ3dwN2VGci1UTVRMLXV1aXpmNGxpTklXNWp2UW0zdGNIX2h2eVJHeGJkakRjWFpHTm5YR1VsTXlOd3FiN0NZdmFtZG12djR4MWRvYnlhc0I1elhqbEI3QXNMazlMeU1MOTFhRXNz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNLW85M09HVGJMTHN6VW9qVnptdFJQTjdOb1A3b3JjTHNqNk5PYXBvenR1TEl5WGJGd1o5ODdpcmo0cFJuOXRlQjZCQjN1ZG9zTjBQRTU1TDVpLWM3MHZreHNNVVp4aHl1VzcyVEUydEE0SzJWTGZncjg3MWNpNHBiM09lZUwzU1hnSFFMbDFFRzA4Tm9uY0xR?oc=5</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>1</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>46055.78746527778</v>
+        <v>46056.38402777778</v>
       </c>
     </row>
     <row r="26">
@@ -1262,24 +1262,24 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AD Ports Group to help develop multi-purpose terminal in DR Congo - Baird Maritime</t>
+          <t>Arvato opens new bonded warehouse in Türkiye - Logistics Manager</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 05:16:42 GMT</t>
+          <t>Tue, 03 Feb 2026 10:20:12 GMT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQMzZZT0Z3ejBobWptOGdwTG9CemNtNFdyaDA5dkVEX0NXb0NhTzNFa0FYdUV5QjdjM1pyaXFtZGZOR0VnOFViR0hiazZSZUcycFIwYkxTUGxkU29DTkxXV1VrYmVYWUpIN3JTTlhZT0hqbDlUZ1l2ZHpzTzVwSjRmTE1mNHgyb3F4SG5tYjNPUERsRFBRSk5xbHRBWmpQNzdCdmJFQnZicnlUdEFJWGVr0gG8AUFVX3lxTE9OS0VYNnhRUHFXQmFkTmtLNUdIaW1RNlJKVmpLbzhxV0hqNXJfQmgwY1VjSVBDZnhWSUFOdDZoTHNUT0xqQW9vWWhVX05hLTI1NXNCbXoyN2Q3OVZtRFdNMjNQVkFkTlpJUTlwUHJyM2NxS2hSVFVqTTdGemtYb1RGc0dnT2NoSUVkZnlBRU15bF9mR0t3N0JDbnpJUE14U1p4ZG43bFpvQVhMcTQ2N25rQVhyY2VkTkYzYzY0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxPR19kY2ZmQkxUbmZDTWxVMnBoZHdkVXdsMGZVWmNwOVdNNHpCYWlsR1RPakthMGRpRWV1aWE3aXA5Unl0c0loRml2X08wNlNveGJzSGdNcVVQSkhQb3YwaF9YeU0xUjEyYTFPVDd3aGp2cVB4eWIwMVRrWWlVYmU5RUhaMGM?oc=5</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>1</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>46056.21993055556</v>
+        <v>46056.43069444445</v>
       </c>
     </row>
     <row r="27">
@@ -1295,24 +1295,24 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>The Clean Energy Supply Chain Europe Still Doesn't Control - Crude Oil Prices Today | OilPrice.com</t>
+          <t>One Month to Go: Sustainability LIVE and Procurement &amp; Supply Chain LIVE 2026 - Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 21:00:00 GMT</t>
+          <t>Tue, 03 Feb 2026 09:15:00 GMT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxONWNkWW5kTzhjYW1mT0ZXcXUwdVQtNW1GVzRFWTNwT0ZydzJxdlZJNDR6MnBpLXIwVDg1ZWF4ZlhmVnh3TG5FTkZJeDFGTk9yY1ZCSndWNVlFdWp2RWNjbUQzRmxTbDVBanFqVjBabXZ0SnlJcGZWc3d5NkdEdFFnYXVhNE55Q2ZRaUt5em4tWk5Vbi01TjJHQTN1NFNhTVpMNF9rY0lKR0HSAa4BQVVfeXFMTkNsSGJ6T2dMWXRKYmQ4M2tYbXNNR3NsRjVCQnV5TWJQRzVINWQ5ajlPY3A1Z1paWlhCakpaQTBQa0tvYmNJN24yLVlfdDRpZGpPV1pTWklPb0IyOHN1RU5qNFowd1F0Um1peU40RnF3RnZGc05paGF0TDVKdkQwazNxeXRDNERWaXNlempoSERvand2TEZnbHV1VzB4LV9yMGQwYjVHY29hbm5qY2RR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNMlpfR21lMDBXRUh6bGE0YWplU1kzRnpqNlh1ejZYVTVTSnBmenpBTHgxcW10bktxMkY5Vmw0MmNabl9MaGNaVWh6cGdkQ3Q3eFZFY1drOXo2UEVZTFVNX3JDYW5uNmxKZmNyTU1yN0pCbXNrajYwV3JDbkF4RWd0M1RYdnhEa1lQYnJ3UjdNMDFNX1dl?oc=5</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>1</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>46055.875</v>
+        <v>46056.38541666666</v>
       </c>
     </row>
     <row r="28">
@@ -1328,24 +1328,24 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Global Mobility Lawyer: A Focus on Compliance Means Clients Often Miss the Strategic Risk - Fragomen</t>
+          <t>Mexico’s busiest container port Contecon Manzanillo surpasses 12M TEUs — SMI DIGITAL - shipmanagementinternational.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 22:35:06 GMT</t>
+          <t>Tue, 03 Feb 2026 10:27:25 GMT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOb2xYMHdGQWIyV092NjNUWUdCWWtUYzNxTmplb2RVT1FQOS0tQzloQ1RtQkZEOE1DYmN6VXBqUnU2MDMxbWlDRFI1T3h4Ynducmt4LXROdmpaTmZfMW1QcVc5TVdQOTBuc2QzRU1MV21QRmVCWFp5YlFPX0t4MEVvLTdmTUI3S3liUnFSc09uUnVtdk5IWUhkeERzQUhFZzVudWUtQ1RFZ285S0VrTVFybldjZ090Zk5sR0oxLWxxcnkyYlFISGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxQdFBlTlFaRmxScmowY2wwM2RMYXE5WmpCNkUwSWR3MnVUOUVvUWlFMzZGR0ZSRmgtWVVLYVRkcmFwZnB2TFVYeklPcUZTUU1RRWtGVTRPc2JzU3Myd05Ua25iZ1Ayemt6QUlMQ1ZycnBDSDVEYjVUZ0hieGZDd3ptZzZjRVFiUWRIM09CQ2JVcHpwb1JxTUs3Yy12Y1E0bFZGWXdfSEVleWdjOVBvenB3bXdfMFgxNFVYNE1sajFLTm51S0Ryd0JhTDNYUDJSMGJwLUk1clFLRnVrZ05KcTBrTC00MnZwWGFkaklLOElacUJJLXRnLS02MkgwMUl6QWU1UUE?oc=5</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>1</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>46055.94104166667</v>
+        <v>46056.43570601852</v>
       </c>
     </row>
     <row r="29">
@@ -1361,24 +1361,24 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Trump’s tariffs are keeping inflation from going lower, report finds - The Independent</t>
+          <t>Switzerland seeks EU exemption from new steel tariffs - EUROMETAL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 17:29:00 GMT</t>
+          <t>Tue, 03 Feb 2026 07:23:51 GMT</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPOE5VQ0ZELW0zcHZyQ2JYdzdOQWJ3ZzNheTB5Nm1FRHk4aHBOQ3BOWlhYOEhBSEo1Y09GYjRsM3hqWnA4dzh4Rlk4ZHM5cG9lcjVQeExack1mMTUwRW9GWDJfQW5EQk8xTkJQdHBXUnRySEdGckFWVG9XR3RhQWQySFlOVWZFcGxtdTh4NURHSFJwWmE4QzlKRXpqdEw2YktYT0MzcXlFc0I5NzdjdTFNSmxiNlZPUzQ5MVJ3NmhEbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQQWc0d1hRVWZ0dHFHYkR6bTlIa09BNDRyUXNoR2RtN3A3RndyZmR3R09laWVEWVg2dkNGSHUyWEVhUEdJb0F5UWFpdDFCcWNfQkMzSnFpQkRaUEFwODhteE90N1Q5UzRpMS1GMjlCNXRqOEpST04zS3JqSzZQWFpIY0dR?oc=5</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>1</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>46055.72847222222</v>
+        <v>46056.30822916667</v>
       </c>
     </row>
     <row r="30">
@@ -1394,24 +1394,24 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Asia’s SITC extends container ship order tally in China - Shipping Telegraph</t>
+          <t>Modi liberalises Indian tariffs much to chagrin of the left - thecanary.co</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 02:01:12 GMT</t>
+          <t>Mon, 02 Feb 2026 21:23:15 GMT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPdkd1NDR3ZnRtVXdmSDNSNDktd0F1aDM3d3lRZFdQWVVFcWtFS1lQTnZ0QjVJb3dFVkF1bHMxdnhKU1IydFVyMDQ3WFRURjgxZHNlZXljX0pkSGFNcklyZ3pGandDcnhWa0xwWDljWTg0SXpaOEphbnVjZjJLU09tc1VLaFViRFUyMnh1bkxxTmRwNVJTLXhDMFdRRGhWc0dfWVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNQ05aX2phLTUtaURXdDB6UlZuZU9EWlJXX0s3MTFacURQZnZIdF9tRTI2T0MyOGhIdXJNVC1TbGJNcFBZZkw1T3FrSWtXaHgzcEtIWGJIVW01VTd3dXd5Z3NSbEJKZjQ0M1BEU3A4VXZDaGxOd2JsYzFrNndlV01oQnlqcWlwRzBkTTBkWHRiekxPTFZK?oc=5</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>1</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>46056.08416666667</v>
+        <v>46055.89114583333</v>
       </c>
     </row>
     <row r="31">
@@ -1427,24 +1427,24 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tariffs are reshaping Canadian manufacturing, but not all workers are being impacted the same way - The Conversation</t>
+          <t>MP asks government about freight-only line amid 'closure by stealth' concerns - Rail Magazine</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 19:08:28 GMT</t>
+          <t>Tue, 03 Feb 2026 05:02:02 GMT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOaldJdHBoSHA2cmtTcUNIVXpxWGlvZk9RMGFKNjBDS3RlQmtqRS11b3pUZjlVX2JiUTZnNkcxRHdzTHFkZF9oa0V5R1JjY3hSS3JqR0xrQU15ZE92SU9kbmp5X1ZESXJ4dFFWMFJyREkxOXJ2QUJFREtIYkxJVl9IZGJ6UE1WQm9obUxQbUxlUGYyQlF6U01yT0VkYVhELTYtT1p4TXBCWE1yMTJKWV9GTUVtajVhYWd4bFJ1UDBXTGw4cG4yRHA2a3dMUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPc2NSUVZaTlRTVXJBNDNTUFZsazBhdFcxZlI0dXZkSGwzbVBvQ19ybndNamd1Y1NwSXpXTUhJTUNVYllvTzJtWXpLdjNkRmxWdk9uS2hGMlFWSkloLWszM29tdEp4RW5LbmZoS21hb3ZXN05tQnNJcDJHOEp3OXZ5aGJRWERva19HelJJb0RTUUptUklyS2FDZ0xrUm1Yd09Ra0JWQmVObzRKYVFK?oc=5</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>1</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>46055.79754629629</v>
+        <v>46056.20974537037</v>
       </c>
     </row>
     <row r="32">
@@ -1460,24 +1460,24 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>What Is a Supply Chain Risk Management Framework? - Z2Data</t>
+          <t>WARE deploys new WMS at Knowsley distribution centre - Logistics Manager</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 20:01:15 GMT</t>
+          <t>Tue, 03 Feb 2026 09:14:34 GMT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNck5ocEx0V0ttWmJuV3VMel8xZE5DZFNONU0xbS1fYlpwQ2taa2NiTjZTdl80TkpWZzFBcXE5MjR5UTBTSFZGUnlIZmtmTFNyR0k4cjJCek9Nb1ZtdmNITnhzczY0Q180Qy0zTld3MHN3QUtYVjhUY3BocXJ4cUZaNk1jMUI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxObllXbnMtNWFYUlljSXpZZ0psUDNsSnVTZ2FKUmk3R3FnMXNINmdCLU1YLXpDS1JHbHhrLTZkNUF4VS1fUjFBazdzSWt0Y0Y3bWg3REFJRXZ5R0tzMkRQZE9FWktBM2Z4cWhrOFA2bHFzNGlDSXVwV1FibDRkR0NpdjNQakI0ME9ITGVv?oc=5</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>1</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>46055.83420138889</v>
+        <v>46056.38511574074</v>
       </c>
     </row>
     <row r="33">
@@ -1493,24 +1493,24 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Columbia selects Prevention at Sea as its compliance partner - Splash247</t>
+          <t>Klaipėda Port launches first phase of southern expansion - porttechnology.org</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 04:22:43 GMT</t>
+          <t>Tue, 03 Feb 2026 10:00:37 GMT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOMXpnenB6VVpjMWltS3d5OGhIS2x0a25LYndtVzVHS2FzRmp6WG1mUkd4WVp5MFdVXzQ1MWpNUXBKcFNSZkQ2UTBDN1dGQUFQb1JudjcyOEtGMkNlaVJLVVd0eHNTRDdacHc1NUVHdlo0cHctejBYMXA5dm1YeHNHWTFXRjJKaFgtNnlJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQUXZma1hCdHQxU20zRVFsUDU1UVBmYlBVMU5qZm5Pb0NxNzNtSnl0Q0dSMGp1NDJlbzdqRUxUT201UTFfRTd4RmhKU1paV0lPN2FFUTBkTEpCNkxlcFR2QUhRS3hRM2w1SjE1WmRCRjRXWUhmeUNKVWxpWmhQR0hodkNZemdwWWhLaWVYZWJuYk01dXVnWkVvNw?oc=5</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>1</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>46056.18244212963</v>
+        <v>46056.41709490741</v>
       </c>
     </row>
     <row r="34">
@@ -1526,24 +1526,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Epstein helped Dubai businessman lobby Mandelson over £1.8bn British port deal - The Telegraph</t>
+          <t>How Investors Are Reacting To Realty Income (O) Expanding Into Global Logistics With GIC Partnership - Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 18:07:00 GMT</t>
+          <t>Tue, 03 Feb 2026 07:09:00 GMT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNT3RtdThCZHJ6TV9ydks0ZnFVRWE2elh1V0w5WU1zTm9oSWFZQU92bnJGQ1FZZTV4Ql9UMFVzbXZubnlGMVFIZHRmNk5LOVZYSUdmcGFKaFFDS25FZGtYOG1fLVVoeXdIb3kwMTdfV2RTNTVvY3lDcklqN2J3ODUwV0dCMmpCUHRrbWlxVWUxTm5XcDdJR0xNVVhtSGZZUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOYVBjTlNZa2pDYS1iQ1pKXzVZYy10UkFZX2FqbWszNGloMlpRSEdoSDRXMUNaY21BeDRvWTlwNkx3ZXFTWVYtcnR4V05BSl9uY1J2X2YxUndPYktIZFNObGg1ekN5dXAtRUJrNmVrUmFINWZYaVo3bFJxQjZJb3VSMEItRlNURURhZnNz?oc=5</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>1</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>46055.75486111111</v>
+        <v>46056.29791666667</v>
       </c>
     </row>
     <row r="35">
@@ -1559,24 +1559,24 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Martin Sherif is a Valiant! - Port Vale Football Club</t>
+          <t>Port of Gothenburg posts record 934,000 TEUs in 2025 - porttechnology.org</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 16:09:02 GMT</t>
+          <t>Tue, 03 Feb 2026 09:15:36 GMT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE9ydllkZXd6Tld2X0VoYlhjZEJtQUliTEhYQncyTVpBZXpsaU9FTEVyU3F2RllYSUxONFZyd0lzZFMtWHFHeHQ0c0NFTDItclJOYW5lT1VvYnJHMnlWeUNHRzZTdFU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPVktIaHp6aUtXU01MQ2R1YjBhTDcyUEx1dmRGOVZ5NDNsQTNTYUdkQU5VUERNdHdvUk1JX2hZQkplTDJISUpxUXZjNFh5d1ZicXVIRWRObXh1UEp5ZE1qYkthT2xHQkJwcDYwQlh2OXZsbGh2OUZzTkJ6Y0I5VWIxUW5yTTJHdjJ3T0pOdUxmeUJIdw?oc=5</t>
         </is>
       </c>
       <c r="F35" t="n">
         <v>1</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>46055.67293981482</v>
+        <v>46056.38583333333</v>
       </c>
     </row>
     <row r="36">
@@ -1592,24 +1592,24 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Vale confirm first-ever Hall of Fame inductees - Port Vale Football Club</t>
+          <t>AD Ports signs HoT to develop Matadi Port terminal - porttechnology.org</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 15:09:03 GMT</t>
+          <t>Tue, 03 Feb 2026 09:51:01 GMT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQX2ZjaVBpdkF0aHlpTlhRcXQ1QWJLLWxiN0YzZEFmMmlEdHpuS181YzMyMk1KRjZpdXA1QzctclF0V2pMN2xvdTJTNElXcFJzQjNqeGFhb0lMdUdpRTBPSlpxOEdfU19xWWdkQUxzUFo5SDRvaGNyMzNRQUkzcm51OUZB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOOFdZTTdISXBhRUZwNU1fSVlpdUJkUmpGOU9oR2hHTkhoN2lMdTJRSVF5QTNKTlhNQXJ4MVVlVUs5UWNmQTdwNkRIWlNPTElfaTFYZVVpemprYXhkYUdjNW5xZm05NFFXa3BjUUVwSFI3QzlIZGlBUzdmVWNQM2ZaTmw4U3dkYmNhU3BzM3h4Q2o?oc=5</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>1</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>46055.63128472222</v>
+        <v>46056.41042824074</v>
       </c>
     </row>
     <row r="37">
@@ -1625,420 +1625,420 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tanker stocks off to blazing start to 2026 as sanctions trade continues - Tradewinds News</t>
+          <t>INTERCARGO Annual Review: Key trends shaping dry bulk shipping in 2025 - safety4sea</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 19:16:41 GMT</t>
+          <t>Tue, 03 Feb 2026 10:12:14 GMT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPb2lRMExjOXNsWFVhQU4ybGNoTXpOMS13WUE2MGxLVzd5Q0JqRGxLczBmbFpiOUJGSGxVZ2l3dGxzZXpHYlZjdVBRSE9Yak5tenh6ZE1MaDNFV1JLTlJMMHNNR0NCWUk1TUFGT0NkbjQxSlZqWlJBalJSS0JaUG4zaWFTYkQ3R3lPdWJKTWZGdE1INGxCc2VuSjhXZDhaclROTi1ubTRkSERHVWNXTGpkVVBnclpjZ0UxLTc0cDdFdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPdjJnUjk5RjgyMXBlMmFPSDF1MTBQQ1ZaMnhQSHl3SnJGNVdVTnVTMkxMa0ZRc2ViVkRCQ040RFM1VVlrNDVPbDlnTmN4aUtpcHE5M2FaekJpSTk5cFRGQlFCc3RMS2VsQ0lHMkdDcTNmeXVzbjV6MGNhWlZpSUY5Tnp1aEk5ZkxlV2FfQkk2cVdvY2pELXF3Ng?oc=5</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>1</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>46055.80325231481</v>
+        <v>46056.42516203703</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Russia resumes strikes on freezing Ukrainian capital - The Times of Israel</t>
+          <t>Dublin SafePort shortlisted for Innovation in Safety Award - porttechnology.org</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 05:08:37 GMT</t>
+          <t>Tue, 03 Feb 2026 08:50:36 GMT</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNem9RZ0trLWpVZTdfQjVUS0s2eWRBOTg4djdzaHZWbGxSLUR2NGFmVm1EM0lkWWpXUl9GRkRobnVwSDVvTGIxa01PVEVrLWo1RVBsdUFFYnB1TDhwa1BvVDlPbXRUdnMwUXZrc01lQy1iMDBONWFvYWswT0FRZTd5ZHpsQ2pTczJ4cVl5UXBWSlpIVDZtMU1qX04yT3UyU1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPd0kyWGdZdWxZUjBZZVRKTS1Wc3ZZMnpManRFamg5RVpKTVZ1WnhmYk01NENSMXBmZHI2MUs0M1RiUm1OTHhxbEF1bzFYM01iVkp6cXc4OHdNSzFya05LX3hLc00yRkRqb0d5Yi1uMHhuMWFmNnZuUzdsZFJkWExTTlRCbkpqZXRqcHltYjhvcGdyQnhmVGxyR0t1aw?oc=5</t>
         </is>
       </c>
       <c r="F38" t="n">
         <v>1</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>46056.21431712963</v>
+        <v>46056.36847222222</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Iranian police detain four unspecified foreigners over unrest - Yahoo News UK</t>
+          <t>Count down to CMA Shipping 2026 - Seatrade Maritime News</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 11:28:46 GMT</t>
+          <t>Tue, 03 Feb 2026 10:24:11 GMT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPekRjSmNra0R3WlRGV2hzZDRMWjNkWEJiNE9Jb1RfOWx2WG45cE15cGwxMXMzMm1FclVYeTlBeE1WQ2cyQkVVQ0kzSDkzUUR2TVhzM0psZEtyOUxVWUxhakllLXhEWXY2U2dJaDNmeF9pTWE0Z3pKMFJtaEhqOVJya0JIY0FBZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPcmJlZ2FvT0JMU0VVU3RPUDVVTGVZY3RoOFFYZXdHSUpubVFraGx6TEdZdnAyQWlXaHlrV3FjVmVmTVZEYVJpdXVMa09LS1lnMzZldlRmdDlyTlBEamlkYXd0Sm5UNlY0SEpVY29ValpxSjJFNHNsXzQ0cW11azY0S0EtMW5xUEtFZTcyWFcwMTdsZ3lhRlEtWUNLMmxuOFE5cy1QNnV3dzJ6U3pJUEo2WlRmVDM5M04xSXAtWmxXbHQ4LWhaVUE?oc=5</t>
         </is>
       </c>
       <c r="F39" t="n">
         <v>1</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>46055.47831018519</v>
+        <v>46056.43346064815</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Police statement as flag-waving protesters march on Hanley - Stoke-on-Trent Live</t>
+          <t>Saudi’s Viero Raises USD 1.2M to Scale Fleet &amp; Logistics Platform - waya.media</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 17:30:00 GMT</t>
+          <t>Tue, 03 Feb 2026 10:28:06 GMT</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPT1otX0VCaWwyTFVjMkhPU0habVRyTlZTWl9mYzRJX1RvcUZoTTBFbmd2NENQNVJOcW5aajZkLVFRZlZpUVM2MERmUDFCOWp3bFdkX2lseWg3eHByak9HUmlnV29OSlViX1ByNnExQllBQXdXeHRzNU9hc3RlMEY0d3otTjhkTXc0czZ5QVpYckJhNHpCajV5NWJuNG15SEt5NkNuSGNwR23SAa4BQVVfeXFMT29GZ3RWV0xJczVuSG91dVpCS0dXREVJNG0wQUhkU21sYTY4MVItR2pocTdpMC1obWRKeENHNFdkazgyZnpVdzRvZFotcnRpb1lxWk4tbW1hdkxmZ2duTkUyTGcyN2pGWG5iRE9KclhHeVdUUzg0UVVyR1pha2lKdUlYMTViQmF4b1lfc0ZGMlVZNTdEU2NoQU5rb2N0M0p5dGZDVG1USzdCWXJhdmhn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOckwySXljUHRGZTZLdW94SU9Rd1JMajFtMWZtSWxkeWpWcEx3b2h4UGRMZkNXcmpVTEF4azRsUWR0dUNDSS1hUjVFdU5hQUxydlFFRVJ1MTRqYk51dC1waFQ0cDhQUzR5UkV5bHFUc3hzZ2ZweXUwOTNfWHYzTDVnMEljeVA2amZqUlE?oc=5</t>
         </is>
       </c>
       <c r="F40" t="n">
         <v>1</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>46055.72916666666</v>
+        <v>46056.43618055555</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Update after police called to convenience store - Cambs Times</t>
+          <t>Stephenson Harwood LLP advises Hellenic Dry Bulk Ventures on the sale of vessels to Bangladesh Shipping Corporation - Stephenson Harwood</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 11:04:00 GMT</t>
+          <t>Tue, 03 Feb 2026 08:12:07 GMT</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxORnRnWW9xTkxDMVVISlZvNjZVS0RfZGhhLUU4RFBNZVNsbmExOEJZZHVBZ1IzelZXVl9nOGZFZGQwcTFfaE1YZjlUODVJWExsXzNiVm5DMnpQNGM4RHplZXZRZG5HMHNjaE1VY0VjOGdpd194cU1rUmMzQ3NXV0QyWXBoQkYzMEVVM1A2eFU3VlpkYTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxPYnAxMFVPemZlVHJNWFo3SWQ4QWFSTGMxYmpERnRpUmNHZk1GZDBPRnFHVGM5VFROWDc2M29ERWNZRkN0Y1EtcGlvNUFlZEdEN1BKS090UGtFSks1TGp3OVFBeEhYczQyRE5oNDBHREZqQVA3R3VkamR3ZUE1azh2TVRfOHdhNzJjaUlKdEdtSmtWWmRNd05rY3NEcHBUY3pJaWFkZ0FDS2pHQkRnQk9PaXVKMTM1cU5HaWNBMnJFQUd1TmVCZFVHU1NyNnk4WWRfYXYyZl9wY3J0eVFldDc4VUY3bS1zREI0Q09N?oc=5</t>
         </is>
       </c>
       <c r="F41" t="n">
         <v>1</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>46055.46111111111</v>
+        <v>46056.34174768518</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ukraine's capital of Kyiv, other cities under Russian attack, officials say - Reuters</t>
+          <t>Grade II listed bridge could reconnect Port Talbot communities - Wales 247</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 23:23:20 GMT</t>
+          <t>Tue, 03 Feb 2026 06:27:57 GMT</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNVlBuNklvRHU5MVg4THZMa2VRMmlRZVpEb2FmX0pNNlJCNXNHbS1CWW5NaG5pbUNLZG05ZDlhcHgwQUV4Tm1mbXVuV2cyaXp5ZGZyNnJkeEJPdC0xR0NYYU8tOWVTX3NXSmNPUHhWSEg2dWlDZEFEYWhCOGdPdWFsMlM1SXYxU1Q1NlhTcFRfLVB0SDM4OGRYVDQxNVNpd0g3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOT1JCUC1SQkRNbkhnY2x3RFRsVFFkekI3N2lqaGVLZHY3b2dfUzY5SlpKWnQ4TUpNWHdxeU5hUUtVV2h3eEFDamZCOHZ4anc3bXZ3TFFxVmNZR2NzVjNTb28xODlkbG1BSmZYenFKcTllanhOSXdmUzc1WE1pcUc1aXNILWFUY3JTbkdMRUFFeHkzQ1E?oc=5</t>
         </is>
       </c>
       <c r="F42" t="n">
         <v>1</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>46055.97453703704</v>
+        <v>46056.26940972222</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Police Urge NLC To Shelve Tuesday’s FCT Protest Over Security Concerns, Rights Group Pushes Back - Arise News</t>
+          <t>EXCLUSIVE: UK refuses to consider Israel sanctions despite mounting evidence of killings of Palestinians and ceasefire violations - Muslim News UK - The Muslim News</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 06:13:14 GMT</t>
+          <t>Tue, 03 Feb 2026 09:43:37 GMT</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPdkNxV2FzejFFR0dsLTNlU0JSMDRocE4wZ2hyNzU5dGVuSnd6M3JOQ0lLSkZWYloxXzFub2VGcjFJcjFscWZxSHlRRXJTdkF6RmJjell2T1ItQk1CQTlFRzZiMGFhYTRYV3dIUWFKV3FpcFNJNXEzT0lWUjVrc0hwZHhLeVVYTHRVZmdXZWdGOWc5YmgyemdRNGRoZWhlbDZuS19rZlZNY1oxcmxYQXJQX2VYdVFGazA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxPU0dJVG5aMEpCdWVseXY1Y1EzczNWR05fdWJLdzl0Qlg0LWhPY3pETXpiTXg4em5kZEdkT1l0anhSX0Nyb1M2bUpCa2xiNmkwSzlUTWNBWGRtempPdnZkaFZZRTRXaDJkUlozdDBmUHk4RXNRUW9IczlUTl91NjJyZ1BFa2RsMXVFRDR5c0VzQ1dibWJibF9iak5Ca1VZbUxrU3lDODdhcEN6OTNoZ0lkeHQ2LXJydF9PbjZkYWdIYlVRM3NuaHlOVzUzOFJzREtRa1Z1TVJCQkhHYTBSZlZXQjlzczcxWmVsbEE1MXAxSW5jVnRwUXMwTFVpckd5RDJnNkRVZlN0T3hPQQ?oc=5</t>
         </is>
       </c>
       <c r="F43" t="n">
         <v>1</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>46056.25918981482</v>
+        <v>46056.40528935185</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spokane police chief apologizes for officers wearing masks at protest - The Spokesman-Review</t>
+          <t>EV rollout accelerates but councils face funding and grid hurdles - AirQualityNews</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 05:50:11 GMT</t>
+          <t>Tue, 03 Feb 2026 10:10:01 GMT</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOZHRHU2VfME5sVTVoQkpLMmpoVUhPN1lnZzdCSm44cVRfZ3k2NFNIVVdMSTh3cXIwU0RFUFNfZ1NMdXhrR0FXVEx0NXNadWsxWEp5WVU4cHBoNkgzV09GcEVtSEpwcG1jdkZWR2h4bjd6QWhfQTRtazA4ck14VXFvaVBDcmlKdDJSVHk0TkZacW5XTTFjQ1dMYmI1Y3VoQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPVHpDRjJYbG1yendmcXBLRXp5c3VjME5wLVM1bm1QdG9IbWdRcXN5T0h6WVJrZXRUbHF2cEpnTHQ0c1B4eklxMG03OTdGWm8wc1VyZklmaUhBMm5tbnVfdzMwNkZYeVZqUkNLVG1BY2E1T1JFbE1SNXdZaEV5dGEzdmVLNklpSWlKeDBqMDNfZ1BOM2M0bjVGeUJzN0w3ZGFpempoZVB4T1l4WDRELTJkc0pCSERMQ2M?oc=5</t>
         </is>
       </c>
       <c r="F44" t="n">
         <v>1</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>46056.24318287037</v>
+        <v>46056.42362268519</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Another e-scooter taken into police possession - Fenland Citizen</t>
+          <t>Columbia Group deepens digital compliance drive with Prevention at Sea - Digital Ship</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 11:33:00 GMT</t>
+          <t>Tue, 03 Feb 2026 04:20:34 GMT</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQY0xxNnhKTTZwdUtJdVZNZXBSQ0lwUlpxMDhCUWxhUFBFLXpUaDJMNmF2OW1YY2hWSTJ5Zm1Vbk9mcDl5UjZpWm1Jd1FPYW1mVk5sZV9xc3dlYktqRWlOQTFaUDBBU0JGMVhQZnRkSkMwYV9QWnpsY0RQU1VtRlhWWnJDb0o5WkIyWlZNcTVoTHZvM25keS1BRg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOMmtyZTBYOTZkVzBFSkxFTnoxVGNlVFUtdDM0ZGxoZ21nQjFYRW9RazVOc2FnYzRuTk5TLWh0ajQ5R0Z3RkRQSjNQdUFyQjRXWGFLSEw1VjlMaWtZZzFiTVFzcUd6RXB3eFU0V19pblUwMkR6c2RjWVUxSUwxbVdId0tsVG81UnVtSlZYQnpuRnUtbWU3TTNQWGN2eTNzbWkySWwxSjhWWmtQODlKaDRvc3ZGT0JPcEJKeDlzQURn?oc=5</t>
         </is>
       </c>
       <c r="F45" t="n">
         <v>1</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>46055.48125</v>
+        <v>46056.18094907407</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hungary Raises Alarm after Slovak Police Arrest Politician over Beneš Decrees - Hungarian Conservative</t>
+          <t>How carbon capture could open up a new shipping market at the expense of pipelines - Tradewinds News</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 14:09:31 GMT</t>
+          <t>Tue, 03 Feb 2026 08:52:51 GMT</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOSGNwRENjNUNNeDMxSWhEWndpNk9OQnpBV0EzazV3b1FSbzlic1lTUTFxTDQyY19UckVZYzB2cy0yZUhYNFF0dHJ1WEtXRDNSQ2VjY1B5WXZiNVA0UEJNLUo1SmxScmhEYS1NQUtoX1pFWjU5dUdqeXg1d3EycFZTZFFkSDlsRFptSHQ4X2lBenowTnZMNmtwRHh3bGQ4ODdzTlVRRzZEeE91ZUl6M2lFSDZoZ2Y?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxNYU5iYU43SFJlcE81eXVpV2g2U0wzUnBvY2ZsZ2tvbGcxNGtkQkxHX0ptenBjMWpXZFlQNXctOGd1TmEtcndWR2ktWnA1MVJxdy1LT3djYVBZSmhzUElDakh3OVpXT0pFOW84blNoVUpDbFNMTDdkY2F0T1Y0YjFSaTZMcHVUTlFVWUlmRjlBbENYVTNwNTBfT0JMRDluRHN3MFBySWIwWW1NYnNJdEZjM01qQUtWMWVqTVRkMUJWS1R4aHFTeEp4V2pTWFg2QQ?oc=5</t>
         </is>
       </c>
       <c r="F46" t="n">
         <v>1</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>46055.58994212963</v>
+        <v>46056.37003472223</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>NSW protest restrictions extended ahead of Israel president's visit - Australian Broadcasting Corporation</t>
+          <t>NetSuite 2025.2 Enhances Supply Chain Agility Amid Growing Operational Pressures - ERP Today</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 03:21:47 GMT</t>
+          <t>Tue, 03 Feb 2026 10:13:08 GMT</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOR25CYWQ2V3BfQnRxMmVBSEFDY1RzSzdhaThTcVU0RWdLX0Zyc3IyS19yck1YZHhiQ3R1OVdkc195bzYtR0V5UXlLb2Fta1JkaldFOU9QYjJpajFrczNQWHBTeGZQRi1jMXIxcXA2Ql9BQm5jOUVyZ2ZxcktENTBoY010OXcwZ3VjRXZ2TXIybVJ1dHZBT21NdlVSMW9Ea3RjQ3UzcUpMWTNxQUZEQXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQWEE2Z2ozZFI0RW1jWFVXMVk1dUFFZGlYZlNPT2hqdlJVMUNBSGlWSVhIYll0RXZFQXh0WFRGcGtNSFN3T01nWURVd2hhMUFuUHBhRm9XTnBMcHF2a0hId3JlX2UyaFJJa3ctTXI5a1hQaEU1Y3BGTXZlRnpmU0lqZW44ekhXOWNGcllwbGtlUTA4Z09OZDc4eGlDNy10MVlG?oc=5</t>
         </is>
       </c>
       <c r="F47" t="n">
         <v>1</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>46056.14012731481</v>
+        <v>46056.42578703703</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Reno police confirm battery report, citations after anti-ICE protests - Reno Gazette Journal</t>
+          <t>MPC Capital and Morten Astrup roll out new shipping investment platform - Splash247</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 00:14:00 GMT</t>
+          <t>Tue, 03 Feb 2026 07:31:43 GMT</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOYVFWYkdQSUEwVkstQUVseXZ5TV9uTGtqbFFadjRwcXozcWJfaF9GQ2xsUXZHdXFyaVVFMXNmYnhUR05PbFJLa3UzN0lVUEIyX0J5RWM5VlRLR2VpRE5raGdMSE5DaFlaZW92blRuZEl5WUlEQW1aZW4zUE1CY0t5ekY4NlFuazU0cHFTSjN0bTlwT3p1Z29vbTJfcTB3R0p0THliSzNPN0NQODdoZGgtMHY4d25vUUNST1pSM0tPTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPTE0wcTV6QlhtSEtqaHZWWHZhY0dHNS1BOUJjU0UtQXNLblQydVVycUxFT2xoLWhHb0Z1cDVTYnMySmNBVFhBUUtkdGJkWE1DUTlJUFJ1emgxSmZVai1MQ19XUWtpQXZ1LWNKQ2F2c0ZWblR6OENXOXdRSmdIZmtDTkQyR1NrM2QwLW1qM2o1bmlGYzZPSm5HcEFn?oc=5</t>
         </is>
       </c>
       <c r="F48" t="n">
         <v>1</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>46056.00972222222</v>
+        <v>46056.31369212963</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>“Everyone Stick Together": Eugene Mayor Kaarin Knudson on Protest and Community - NPR for Oregonians</t>
+          <t>Politics latest: Police review after €500bn leak claim - as 'well hung young man' email emerges - Sky News</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 22:40:00 GMT</t>
+          <t>Tue, 03 Feb 2026 10:29:14 GMT</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxPaDRwdTVIc2RfTE1LVXJLanlzbjFxTFlHVzBlY3BFaXZRRF8xQWJySFQ2eG9TV0s4b19MOFNZNlhvTTZTMDBMSlF6SmdvOENVTDN0NDRIbFk5R0s4ZGlQSEhvNHlObFN3Sm1MY0t5UHFudzNpSEV4TFpWblNZWEhmU2xwRG8xWHVRU0xDZTRFbFB4V1hfdncxVmlNM1VxcW5QOTI0Q0hPeGpOYXlwUUZtYlFpOGdLcFVWOUk1ODI2a1FRX2w3OTFKTzR2OUEyX0lsQlpN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQWXI1a3lTS01RY1ZneTVDeTN5OWFBMTA5TE9fTzVxRWV3M1BaVmNSdVVheVZCbWxEeWlZWWJ1Z3V2RFozbUR0T2ppMXc1TXUzQUdQTEs3aDk4Ykwxb3RBbDBJd0ZrNUwzaEdJeHFJUWxhZV9LcDlmcGhFOXM5VlJNdklnVHl2QkozNmRTaVBKZ25aZElfSDFTbTAyYmhMeXJfeU5VSTVmdGF0QTczOWRBZnozT3E3V2FvOUtkcksySjgzTGM0Z3hQVDNBMUNndFk?oc=5</t>
         </is>
       </c>
       <c r="F49" t="n">
         <v>1</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46055.94444444445</v>
+        <v>46056.43696759259</v>
       </c>
     </row>
     <row r="50">
@@ -2054,24 +2054,24 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ferndale Police answer questions regarding Friday student protest march - Whatcom News</t>
+          <t>Russia resumes strikes on freezing Ukrainian capital ahead of talks - France 24</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 00:17:16 GMT</t>
+          <t>Tue, 03 Feb 2026 09:46:52 GMT</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPbzk1cHEtbWI4VjhaVXBCSXA2Y3MtaEhZWXAxYk0zMkl5SUVvcmh3d2JycHRiMTh1dEZrdGRqVDhwR0Z3UjJoX0JhSE1kUk9MVkVEbzZqUl9OcWY0N0ZRZFdJQ2FUQUFrWFhxUVk4clNFV2o4R0dMa1JBaVpFVjdyVDFraVBEbkR5TFc3VmZUQmNxazNhNlZiSGI5RTZnWnN2TVVGWk9zQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPN01uSVNackgwMjE1enhnOVdUWnJQOXZaYkJXQzBscXFaX0tmVkRrb0ZSNjhFTXR4NTJmOE0yQk5TNHZndHV1dkxyRldjZFlDNDhEbW5LMVNzcjdEOGg0VWVsbE5GOTVEZVV1VzZQSGdTLXZEMGREeWg4LUw1MnRIaDNMRjd1eG1BSUs5S2VORE1NTFVRVkI5bnlzZw?oc=5</t>
         </is>
       </c>
       <c r="F50" t="n">
         <v>1</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46056.01199074074</v>
+        <v>46056.40754629629</v>
       </c>
     </row>
     <row r="51">
@@ -2087,24 +2087,24 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Police probe launched after jewellery thieves strike at vulnerable Smethwick woman's home - Express &amp; Star</t>
+          <t>Police statement as flag-waving protesters march on Hanley - Stoke-on-Trent Live</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 08:11:04 GMT</t>
+          <t>Mon, 02 Feb 2026 17:30:00 GMT</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxNSGdYOGR4YWRSQ0pFc0VxSUdoc3RNUkZ3bXRvdDBuVDBBWWhYLS0td1lPVmtDUWYwZGpqbVZ5RkxrMWQ4SkRqWHhBSkFjWll4QU11cnZKMEtRWTRmNi1xOWRsWTlnSmtkSXN6MVZRT2hCZHBnR2dlbmV1NzZBcWJ5SnJZcDJWNWtENVFkdVNKa2wyRTFkLVJRWDJTSHg2MlZUUDNWY0xOcFBuTkpWUUdRZG0xZzkyeGstTkdVMHF0UGo0UVlzYmNfdGQzMFVKNUtvMHF3UlpRSmJhR211YWFJQTdZVFFXSDJRU1lWNXQwQmxFQjNFMHk0VnFB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPT1otX0VCaWwyTFVjMkhPU0habVRyTlZTWl9mYzRJX1RvcUZoTTBFbmd2NENQNVJOcW5aajZkLVFRZlZpUVM2MERmUDFCOWp3bFdkX2lseWg3eHByak9HUmlnV29OSlViX1ByNnExQllBQXdXeHRzNU9hc3RlMEY0d3otTjhkTXc0czZ5QVpYckJhNHpCajV5NWJuNG15SEt5NkNuSGNwR23SAa4BQVVfeXFMT29GZ3RWV0xJczVuSG91dVpCS0dXREVJNG0wQUhkU21sYTY4MVItR2pocTdpMC1obWRKeENHNFdkazgyZnpVdzRvZFotcnRpb1lxWk4tbW1hdkxmZ2duTkUyTGcyN2pGWG5iRE9KclhHeVdUUzg0UVVyR1pha2lKdUlYMTViQmF4b1lfc0ZGMlVZNTdEU2NoQU5rb2N0M0p5dGZDVG1USzdCWXJhdmhn?oc=5</t>
         </is>
       </c>
       <c r="F51" t="n">
         <v>1</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46055.34101851852</v>
+        <v>46055.72916666666</v>
       </c>
     </row>
     <row r="52">
@@ -2120,24 +2120,24 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Alderpeople Say COPA Should Investigate Chicago Police Conduct During Immigration Raids, Protests - WTTW</t>
+          <t>Iranian police detain four unspecified foreigners over unrest - AL-Monitor</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 01:02:00 GMT</t>
+          <t>Mon, 02 Feb 2026 11:29:32 GMT</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPN2xkVWx4dWpnd25XYVhTLXF3cXRJOGRSUDZIMFJaTGRpa3dEeVEzOUdKSzA4ajZWVk95XzF1aS1WdFlBT3ZVR3lBaTZMZDE2U0pvZWlON2xNZ0taeWxnTlJNU0NDdkdabUxyVGZnS0JZTk1KcG0xMkhVWU5QWWZqMXpWRkJGT1R1WENRZWpvMkNJV09RUlM1NjdhQmV3VnhOUkNrTE55Y2U4NS10ZGNSel9MbFlwUHYxd0lkMw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPcTMzQ2JESWJVYndqSFdxbUVheG12M2RWR29uUTNWWWZmR01XajUwb1dtU3VtNC1Wakk4VmYyWlJ2aVhhM2M3MmZZYkZ4V1R4RmFIUkpwUUk2WXBmcmFXcFQzUDRSRnEzdHB6LXhVSklxWTd3b2FBVlc5YnAta0RDdzVnNWU5QS1pZUc2UW11dmVfa3hsOHRpRnhHZGNNeTRoZDB2TDVFWk1DQQ?oc=5</t>
         </is>
       </c>
       <c r="F52" t="n">
         <v>1</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46056.04305555556</v>
+        <v>46055.47884259259</v>
       </c>
     </row>
     <row r="53">
@@ -2153,24 +2153,24 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>‘Significant animosity’ to Israeli president prompts further protest ban - AFR</t>
+          <t>Spokane police chief apologizes for officers wearing masks at protest - The Spokesman-Review</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 04:31:00 GMT</t>
+          <t>Tue, 03 Feb 2026 05:50:11 GMT</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOM3VBTUx1czNTbG5CVmlqcnF4bk13aWpUbnIySGRLbmZiSEtWUnE3RU1LVG5HcTJuSE1fVEJsSTVkNm5XemVYQjVwbk1TZWFKcGtYTVJRVUg4WkhhSzlqX2dqMFhjZXJ4N3hQQnAtdEVXQUlzTlNfdnVQZEVOeTRlUkJmMWFtVGxxajU2WGtEdTFFTmFuWWJwb1NxaDhWZElhYXVQZVdJSEhRbHJGeTdGNm1nb0FGZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOZHRHU2VfME5sVTVoQkpLMmpoVUhPN1lnZzdCSm44cVRfZ3k2NFNIVVdMSTh3cXIwU0RFUFNfZ1NMdXhrR0FXVEx0NXNadWsxWEp5WVU4cHBoNkgzV09GcEVtSEpwcG1jdkZWR2h4bjd6QWhfQTRtazA4ck14VXFvaVBDcmlKdDJSVHk0TkZacW5XTTFjQ1dMYmI1Y3VoQQ?oc=5</t>
         </is>
       </c>
       <c r="F53" t="n">
         <v>1</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46056.18819444445</v>
+        <v>46056.24318287037</v>
       </c>
     </row>
     <row r="54">
@@ -2186,24 +2186,24 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Police extend Sydney protest ban again in city’s east - dailytelegraph.com.au</t>
+          <t>Ukraine's capital of Kyiv, other cities under Russian attack, officials say - Reuters</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 03:01:48 GMT</t>
+          <t>Mon, 02 Feb 2026 23:23:20 GMT</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxNUkkyMUZaR29JbkkxOGZHSFF1YmRFYUxNYU5RVENDbHhmU2h2anF3bzAxVFhDc1AwRGFTVDluWVJvNEI1QnViR05GTU1YOS1JbzhQS3ZOUGJicFpmR3J5WlBwM0VDbVZlUGwxc0NqNkx3YnNVaGFvaWlpcFBXN2dibi1YMGJJQkpHbmNMWl9tWmNSMzFPdkVZY0pwOFdlcFFDZG1aMDB0ejNiN0dNenVUM2FKZ2F5a2E2UU5CNl9tdEtiWmt2cnU5N3RBbktEelRoaHBhUnNrdUtUYWdMcEw1NUZsYWgwRXM0WnUycksyYnhSbjDSAfgBQVVfeXFMTkNJUVUxVkp6UXFlZzcwVTVmYUl2RVUwZVc1NTM1ZU9XeHVBXzRFNG4zTFZTZHZnWThnQWViWkd0WlgzZXVkMlhGZ21NVHZWb0JyWnU2TUpDZHNLeDIyX0kxa2VIMmJIQlI3ZGNVQjE0c3pLYWJobTV4Q1lCS3hxaVRUR2FsanZ2M2V6azNydDV3Ym5KdXQyZFNuY3NDRjhkQXV0VUk3djBkbmx6YWg4eEhQb3lzTHZYVDVtM2JiRDVfR0RaMlRPVEJsZnVTRjVmNlo0U3NOSU5VaEtOZ2RXUnFaSjlKLWpabXpmSDl0SHlUcDlvVEdCNW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNVlBuNklvRHU5MVg4THZMa2VRMmlRZVpEb2FmX0pNNlJCNXNHbS1CWW5NaG5pbUNLZG05ZDlhcHgwQUV4Tm1mbXVuV2cyaXp5ZGZyNnJkeEJPdC0xR0NYYU8tOWVTX3NXSmNPUHhWSEg2dWlDZEFEYWhCOGdPdWFsMlM1SXYxU1Q1NlhTcFRfLVB0SDM4OGRYVDQxNVNpd0g3?oc=5</t>
         </is>
       </c>
       <c r="F54" t="n">
         <v>1</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46056.12625</v>
+        <v>46055.97453703704</v>
       </c>
     </row>
     <row r="55">
@@ -2219,24 +2219,24 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Eight Arrests made at Demonstration, including Three for Assaulting Police, Queen Street West and Bay Street area (Mahnoor Mohyuddin, Jennifer Vong, Kyle Stephens, Woodrow Fraser-Boychuk, Abe Berglas, Darcy Belanger, Bryn Williams &amp; Charles Kaake - Reddit</t>
+          <t>Gunfire strikes trolleybus in Kaunas, Lithuania: Police investigate - Caliber.Az</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 12:33:10 GMT</t>
+          <t>Tue, 03 Feb 2026 09:46:04 GMT</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPYlA1UmFxRnlZNXpJODk5X0hOWldUOElDdG1mVXhndl93LUhackpTa1FYZDBjRWR1dmFhc2xrYXMzMFo4WV94OEtZb0ZpYTljNlJYb0RVd1llS0RuWmRHRlA4QUFJaG5QTzBzaDRKUFBBUWNDR1pDdklZUXBvdnVqMmJiMVZydUp1Q0hVV2IydDZQY0F6eGtYdXB1M0w5QU8weWVEag?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOaGx5Zk1zN0ZWN3Rzbjh4SUk4WGlaem53MHQ5dTgweEY4M3ZVM2FOay1laW9UZlVFRmxpY0ZYNTkzcDN2OE1DdWhOTmdqbUJhY01XU2Q2SUd5eGdxUHZ3N0NDMElwY3Q4b2RJRXdSdm1uOWNCcGs0TnNXWHJnVGR0V1hNLU1FS2IwckxtNGctSEwwRkl6WjNv?oc=5</t>
         </is>
       </c>
       <c r="F55" t="n">
         <v>1</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46055.52303240741</v>
+        <v>46056.40699074074</v>
       </c>
     </row>
     <row r="56">
@@ -2252,288 +2252,288 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ATN International Board Calls March EGM to Consider Capital Reduction - TipRanks</t>
+          <t>Another e-scooter taken into police possession - Fenland Citizen</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 18:07:35 GMT</t>
+          <t>Mon, 02 Feb 2026 11:33:00 GMT</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNSEh4dktnUVA3TF9rTkJIUXZ2cFFkN3puZWpIN2dYTU9kRmtiRmtGUGFNWS1ieS1XQVc1QlJCcTdWZmx6U0RLRVhJU1hybXlDSTN5dkU5VmUtMVJKcFVYanF5WEdtUlN5Yk1USUhpYVp5eVA2M3MydWtKdHhwcV9FY2lSQUVueGRkaWRTNFYxemIxZkY3bnRBVlpzZTVoTUJPcUN6R1hoc1d5dkxzNE5NbzJaWjF6Qm5hTlEzQ2xn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQY0xxNnhKTTZwdUtJdVZNZXBSQ0lwUlpxMDhCUWxhUFBFLXpUaDJMNmF2OW1YY2hWSTJ5Zm1Vbk9mcDl5UjZpWm1Jd1FPYW1mVk5sZV9xc3dlYktqRWlOQTFaUDBBU0JGMVhQZnRkSkMwYV9QWnpsY0RQU1VtRlhWWnJDb0o5WkIyWlZNcTVoTHZvM25keS1BRg?oc=5</t>
         </is>
       </c>
       <c r="F56" t="n">
         <v>1</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46055.75526620371</v>
+        <v>46055.48125</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Technology and AI - Freeths</t>
+          <t>Hungary Raises Alarm after Slovak Police Arrest Politician over Beneš Decrees - Hungarian Conservative</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 07:37:01 GMT</t>
+          <t>Mon, 02 Feb 2026 14:09:31 GMT</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTFBWa1dVRGdpcEZHemc2aURfM0tWNDlnRXJBRTRNa0F3Z25xMENnNHFmWC1henR2SkNXdnVYZ2VHa0lIcGo3UDFJb1hUWnI2R1c4ZDlpWkFIQlNPaGJBZTNGZUF4S2xnRl9qdG9wNGpGMV90aVpXdGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOSGNwRENjNUNNeDMxSWhEWndpNk9OQnpBV0EzazV3b1FSbzlic1lTUTFxTDQyY19UckVZYzB2cy0yZUhYNFF0dHJ1WEtXRDNSQ2VjY1B5WXZiNVA0UEJNLUo1SmxScmhEYS1NQUtoX1pFWjU5dUdqeXg1d3EycFZTZFFkSDlsRFptSHQ4X2lBenowTnZMNmtwRHh3bGQ4ODdzTlVRRzZEeE91ZUl6M2lFSDZoZ2Y?oc=5</t>
         </is>
       </c>
       <c r="F57" t="n">
         <v>1</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46056.31737268518</v>
+        <v>46055.58994212963</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CURE-ND brings together experts in AI and machine learning - UK DRI</t>
+          <t>Reno police confirm battery report, citations after anti-ICE protests - Reno Gazette Journal</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 13:45:51 GMT</t>
+          <t>Tue, 03 Feb 2026 00:14:00 GMT</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQQUxpOEJSX3VYSW04MTVNYkd1TnJJMXJKUjc2eEpZQ1I3M0hsSTA0dEdaWEc4dUpGQUpvYjRqbFM3akdkZHdzZlhpdmhhcnQ2VnpWb2otYjZjeF9JZ0h3ZTY0SjhDOTBrMVhJVTVXNUQtREczX2xMejB1Q0JKRDNkamFfSGVZMGp2U2t3N3VEaEFZaU1XR2xhQzFYY3RlT3B0OVhZX3RESzI4ZTQyVDZ6T1FxMHZiUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOYVFWYkdQSUEwVkstQUVseXZ5TV9uTGtqbFFadjRwcXozcWJfaF9GQ2xsUXZHdXFyaVVFMXNmYnhUR05PbFJLa3UzN0lVUEIyX0J5RWM5VlRLR2VpRE5raGdMSE5DaFlaZW92blRuZEl5WUlEQW1aZW4zUE1CY0t5ekY4NlFuazU0cHFTSjN0bTlwT3p1Z29vbTJfcTB3R0p0THliSzNPN0NQODdoZGgtMHY4d25vUUNST1pSM0tPTQ?oc=5</t>
         </is>
       </c>
       <c r="F58" t="n">
         <v>1</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46055.57350694444</v>
+        <v>46056.00972222222</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Alphabet Q4 2025 earnings preview: cloud and AI to sustain valuation - ig.com</t>
+          <t>Ferndale Police answer questions regarding Friday student protest march - Whatcom News</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 05:21:31 GMT</t>
+          <t>Tue, 03 Feb 2026 00:17:16 GMT</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQcnY4a2J0bWRPZnJxSGRHeVYtc05FaUY1MXgzQ3NEVkNJYjVIM1BCT0lFblVJN0xkUi1jZ0ZMQTZnQS1IYVB5Tm95cXJfSDFJWnBFd2gwbnVVcXg0SUMzVnRhRXZld3lTdHhYbU9lS1lwOXB4SGFZa1JHc3diTzZjZF82OUlwYlFSVzE5YjdjWW1PeGsxLTFtLTBiMEFycVFxa1hsalpwWnlGYVlkN0ltbnFUcVlqM3U2ak91M3FKWC1NZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPbzk1cHEtbWI4VjhaVXBCSXA2Y3MtaEhZWXAxYk0zMkl5SUVvcmh3d2JycHRiMTh1dEZrdGRqVDhwR0Z3UjJoX0JhSE1kUk9MVkVEbzZqUl9OcWY0N0ZRZFdJQ2FUQUFrWFhxUVk4clNFV2o4R0dMa1JBaVpFVjdyVDFraVBEbkR5TFc3VmZUQmNxazNhNlZiSGI5RTZnWnN2TVVGWk9zQQ?oc=5</t>
         </is>
       </c>
       <c r="F59" t="n">
         <v>1</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46056.22327546297</v>
+        <v>46056.01199074074</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>How trade shapes the winners and losers of AI boom - Oxford Economics</t>
+          <t>NSW protest restrictions extended ahead of Israel president's visit - Australian Broadcasting Corporation</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 23:33:39 GMT</t>
+          <t>Tue, 03 Feb 2026 03:21:47 GMT</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxORDcwTnZjQkprcmdaR1dMYWE0TTlSZUJ5ZEVqOHJCZDhYT21QdG5veEJpa3lOWUE1QzRpaVN2TGQtcHR1dGtlV2xkc1lQSkFabUIweFhqVWIxWXNORVh2T1ZTVlJFbFlBbGNVRWdwZFQtMDh5MmIwUmdCUWU3cjFPZmRhTVhfZzBOZWlqcURqSTFQRm1XRHZV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOR25CYWQ2V3BfQnRxMmVBSEFDY1RzSzdhaThTcVU0RWdLX0Zyc3IyS19yck1YZHhiQ3R1OVdkc195bzYtR0V5UXlLb2Fta1JkaldFOU9QYjJpajFrczNQWHBTeGZQRi1jMXIxcXA2Ql9BQm5jOUVyZ2ZxcktENTBoY010OXcwZ3VjRXZ2TXIybVJ1dHZBT21NdlVSMW9Ea3RjQ3UzcUpMWTNxQUZEQXc?oc=5</t>
         </is>
       </c>
       <c r="F60" t="n">
         <v>1</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46055.98170138889</v>
+        <v>46056.14012731481</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Publicis deepens AI push, saying rivals have yet to make it pay - Financial Times</t>
+          <t>Alderpeople Say COPA Should Investigate Chicago Police Conduct During Immigration Raids, Protests - WTTW</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 06:30:20 GMT</t>
+          <t>Tue, 03 Feb 2026 01:02:00 GMT</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE05aFZudWF4Qno5cmZiX19mOXg2YWZvdlFIUVNjNHhsZGFfNWVxeEYzQmlxT0xud0hkYzdxSU1PRElxZHpOQ3o3Yng0aWYtS3FLdHhFcTJobU5oYTllaXI4eHNQS2ZncTNJeEJmd1loZ2Q?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPN2xkVWx4dWpnd25XYVhTLXF3cXRJOGRSUDZIMFJaTGRpa3dEeVEzOUdKSzA4ajZWVk95XzF1aS1WdFlBT3ZVR3lBaTZMZDE2U0pvZWlON2xNZ0taeWxnTlJNU0NDdkdabUxyVGZnS0JZTk1KcG0xMkhVWU5QWWZqMXpWRkJGT1R1WENRZWpvMkNJV09RUlM1NjdhQmV3VnhOUkNrTE55Y2U4NS10ZGNSel9MbFlwUHYxd0lkMw?oc=5</t>
         </is>
       </c>
       <c r="F61" t="n">
         <v>1</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46056.27106481481</v>
+        <v>46056.04305555556</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Europe Today: European leaders in Dubai to discuss global trade and AI - Euronews.com</t>
+          <t>‘Significant animosity’ to Israeli president prompts further protest ban - AFR</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 06:49:08 GMT</t>
+          <t>Tue, 03 Feb 2026 04:31:00 GMT</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQeVpwc3ZyM2dISHFvMjNObW9wX2FCbDU1VXBNWGdkUTZXTW8yN0xQRlVGYldQaHNBRlNlSDVsa3dVS0V2c1Nkckdqa1RtQnBwWGRXVnRMVjBLVi0xcVlqemlJaVg1bW53VnhPay1kczBCVllFVW9vWXg3NDJub2M0bUJoQ1JzN0dRbUZaUGRaUDRBaHZxOXoteU9jc2s2Y0hkRnY2VGVkNThHVGFCVlB1akJwQmpxSE5DelY5MFpuQVA2WUxQOXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOM3VBTUx1czNTbG5CVmlqcnF4bk13aWpUbnIySGRLbmZiSEtWUnE3RU1LVG5HcTJuSE1fVEJsSTVkNm5XemVYQjVwbk1TZWFKcGtYTVJRVUg4WkhhSzlqX2dqMFhjZXJ4N3hQQnAtdEVXQUlzTlNfdnVQZEVOeTRlUkJmMWFtVGxxajU2WGtEdTFFTmFuWWJwb1NxaDhWZElhYXVQZVdJSEhRbHJGeTdGNm1nb0FGZw?oc=5</t>
         </is>
       </c>
       <c r="F62" t="n">
         <v>1</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46056.28412037037</v>
+        <v>46056.18819444445</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Large RIAs step up AI and data spending: Cerulli - Structured Retail Products</t>
+          <t>National Tax Service Sets March 3 Deadline for Stock Capital Gains Tax - 조선일보</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 16:11:33 GMT</t>
+          <t>Tue, 03 Feb 2026 04:38:27 GMT</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPcFBPNGFHby05c3dkYV9CNVZtRDc1eVdFRmhmSWdJVHQ1cE5GamVNaElKVnoxcHRSRFFFQnFyUDE2M3dzVW9MbmRCUmJVZnJsWXVLb1dMZ2xVa0VxUVNOaXJSNklRdW1oWE9RUEtabUt5MHJiQ2FrZHIxUGc1d21XOXAxeXJXZFFiLUtVeDJ1Uzl4VlJZV1VQczVJTzZ6d1dyUTdRX0xB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOXzdGdHcyWHBCYXVUektpN0RGcWpDLWlmQ0M2Y3ZCX1JHcTEtalByTjk5cUp4MExzOGhEbU5ZUkJscFNha2ZXcjNtVTRvTGd0QTJVbVE2OVdMVnlGY1BoNWQxMHQxbnBFTUZYT3lIbHEzSzlDdTVPeTN3VUF3UUNuOWlaeE9DbWp3QnV1T2ln?oc=5</t>
         </is>
       </c>
       <c r="F63" t="n">
         <v>1</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46055.6746875</v>
+        <v>46056.19336805555</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Barton Peveril case study - Google Cloud</t>
+          <t>Why NLC should shelve today’s planned protest, by police - The Nation Newspaper</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 05:13:05 GMT</t>
+          <t>Tue, 03 Feb 2026 04:26:57 GMT</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE4xSjkwTjBsTk1qeWV5WGhJTFNIUEdKZkRXLUpGaFRUQXEzYVNNaUxkUEpDcmU1cFFJNjlCOVlkU2l4RTV1RmZsc19Sa0VaNXphVjJ3NFNMY1lmQThs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQaVJGdmRRUTF6SXJZU21JYk0yb3FyaXR5aVNiZ3RfVDhzdWp5RUlOM2pzdGQ1ZW55NHN6Smg0eDM1TEV2dVpKZGp3d3VJdHFOSTU3Ykwzc3lPanFYUjAtcHVhaW1HVnQwcGtobTZ3WkVmWVl1cDVMMDdxck1TT1VIbGhiSU1DSEhJbDdieHB30gGTAUFVX3lxTE9aNlN2WmN4aXVkbThzV0E4SmtBQkdPVmJnQjR2TllCWWVhN213Zno0UlF3OEtqOTYyWW9abWx0ajBzVG5yVkNGQXp5cDJ2bkpLeWV3c0VScDd0VzZVSzZxZFdGc0ZHX205aHJGRFZOQ2pITmVWRzlVU2EwNXF5T0hvYmtYc25GVTRQQ3J5YUJlTFVwVQ?oc=5</t>
         </is>
       </c>
       <c r="F64" t="n">
         <v>1</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46056.21741898148</v>
+        <v>46056.18538194444</v>
       </c>
     </row>
     <row r="65">
@@ -2549,24 +2549,24 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>The Telecoms.com Podcast: Ericsson, AI and Nokia - Telecoms</t>
+          <t>Technology and AI - Freeths</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 12:28:13 GMT</t>
+          <t>Tue, 03 Feb 2026 07:37:01 GMT</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPTHhsYVpnTHdHNkNEQXR5YTVXeEdDSFh2dE9YLTJsdVdFbDV6MkxuQzJ5Q0xTdEZFb2VaMjlESi1JZDU1QWJpekR4ZExxY196ekhkZ2lJUDZzMnp5MjFrS250eDh5OGRSckRLczFKdjJKYVcyQlhmdEtSWTA2R0VLTTZUa1dhV2dlYXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTFBWa1dVRGdpcEZHemc2aURfM0tWNDlnRXJBRTRNa0F3Z25xMENnNHFmWC1henR2SkNXdnVYZ2VHa0lIcGo3UDFJb1hUWnI2R1c4ZDlpWkFIQlNPaGJBZTNGZUF4S2xnRl9qdG9wNGpGMV90aVpXdGc?oc=5</t>
         </is>
       </c>
       <c r="F65" t="n">
         <v>1</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46055.5195949074</v>
+        <v>46056.31737268518</v>
       </c>
     </row>
     <row r="66">
@@ -2582,24 +2582,24 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dow to replace 4,500 jobs with automation and AI as shares decline - Packaging Europe</t>
+          <t>New robot swabbing technology trialled for the first time at Sellafield - GOV.UK</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 11:08:32 GMT</t>
+          <t>Tue, 03 Feb 2026 10:06:27 GMT</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPUG85LWpVTTB1ajhzU3dMMEtCa3NkMDRxbmpjZTV4RmlvZ1dpSlh2VmZZSW40VEV2QzcwTDVaQVltdnpKT0gya19GT3I1VnJFUGNjRkNGNUtobGFCS0RjV2x1NmV5YTQ3bzlYUWxHRl81dnpLVk1vVHlEemtUU0JDeDk0SVhDYXBsSG9pMXBJdnJfOWpPQ3U4NjNVWm1IeEhCT1l6aWUxQ09EaGg0czl5MXh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOd3FSVUNTenVpSFhtWjdBV3JYX2JNRWFhTWZCR2U1Y1FsWlVQQ1FhUjRMVmVwWnlZM2FOMUxJYVgxTk1maEY3RkJpMk9EZjk4Wks5em00UzJBbzRwbUdKUGVkUC1ybkJNc1J1WmtMNGxjMjhiREhzX29JTWQweHZfQ1ZhejluQjdSSzRmVVBGdDNWU0syUUhEd04zMWYyV1IxUWhETlRCejVldw?oc=5</t>
         </is>
       </c>
       <c r="F66" t="n">
         <v>1</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46055.46425925926</v>
+        <v>46056.42114583333</v>
       </c>
     </row>
     <row r="67">
@@ -2615,24 +2615,24 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SpaceX absorbs xAI as Musk consolidates AI and aerospace ventures - Proactive Investors</t>
+          <t>PhD students secure second place in global UN AI sustainability competition - University of Aberdeen</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 07:19:00 GMT</t>
+          <t>Tue, 03 Feb 2026 10:18:29 GMT</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxOSktJdXEtMGNPWVJnb0ExNU9kLTNOVkhMei1sX0NVVjVuNXJYLWt3dVJaTXNwdzlaaERFemlOOTk1d1Y3d3oyQkJlQ2tEWHFFSnRIcDYzYVhIOE1JTkFXQ1J2b0NWRjRpVl81REJNUVlEeUhSb3VwYldETlFSUDBmdHRmd3R6N0FkWV9WVDV5TEw1YmkyWXhNNkNZREJVS09lVEhQRGM3SnBtdnVKbC12WHdselRoUnNtUV9BRkZXVmNBN0ctVjJWMGg1VmY2RWxaOWlVbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiSkFVX3lxTE9QNnVZSlE1Tko5ZUNISnRFdzRUMm9GMjFjdW5RbElkRnpRVVBzbXFqX21SNW9jbzhFbEhQV3gtWWQteUwwVHBpV01R?oc=5</t>
         </is>
       </c>
       <c r="F67" t="n">
         <v>1</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46056.30486111111</v>
+        <v>46056.42950231482</v>
       </c>
     </row>
     <row r="68">
@@ -2648,24 +2648,24 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SDAIA Launches National AI and Data Curriculum for All Saudi University Students - BABL AI</t>
+          <t>CURE-ND brings together experts in AI and machine learning - UK DRI</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 00:16:24 GMT</t>
+          <t>Mon, 02 Feb 2026 13:45:51 GMT</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOeTl0aUM3cjYtMFAzZ3IzU3VYRlJtWUVoX2ktMVJlLWxSMlpRcHVuWHdjNkdZNFh3cE56dXNvWjhXbEdNMGdTaE5PWHh1TFNwbjNCQzFWd044c1g0SmFFNHRzRWZwRmRuTG1FQUFtVUNHYWtISXdNWm03SlNDd1lWREtxel9RTHBicDQzVG9KMmZNUXBKVExBT0NCaHEydw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQQUxpOEJSX3VYSW04MTVNYkd1TnJJMXJKUjc2eEpZQ1I3M0hsSTA0dEdaWEc4dUpGQUpvYjRqbFM3akdkZHdzZlhpdmhhcnQ2VnpWb2otYjZjeF9JZ0h3ZTY0SjhDOTBrMVhJVTVXNUQtREczX2xMejB1Q0JKRDNkamFfSGVZMGp2U2t3N3VEaEFZaU1XR2xhQzFYY3RlT3B0OVhZX3RESzI4ZTQyVDZ6T1FxMHZiUQ?oc=5</t>
         </is>
       </c>
       <c r="F68" t="n">
         <v>1</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46056.01138888889</v>
+        <v>46055.57350694444</v>
       </c>
     </row>
     <row r="69">
@@ -2681,24 +2681,24 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>IFR position paper on AI in robotics released - International Federation of Robotics</t>
+          <t>Publicis deepens AI push, saying rivals have yet to make it pay - Financial Times</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 09:50:47 GMT</t>
+          <t>Tue, 03 Feb 2026 06:30:20 GMT</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE1uM2Vnek8zdm5IV1hWem9CYWl1S0czMEJLd3lhNHNlLURxajlQZy1ISzdSd28yblRfeUpKV3ZsYWlPYlJsNGdDalFWMUQyOTVqSmQxMzNqV1Y2SE9UbzRxcjc3RzVRcTc0NG9tYV9JbU5fWVAzemRVMTVhV1o?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE05aFZudWF4Qno5cmZiX19mOXg2YWZvdlFIUVNjNHhsZGFfNWVxeEYzQmlxT0xud0hkYzdxSU1PRElxZHpOQ3o3Yng0aWYtS3FLdHhFcTJobU5oYTllaXI4eHNQS2ZncTNJeEJmd1loZ2Q?oc=5</t>
         </is>
       </c>
       <c r="F69" t="n">
         <v>1</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46055.4102662037</v>
+        <v>46056.27106481481</v>
       </c>
     </row>
     <row r="70">
@@ -2714,24 +2714,24 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AI in 2026: From Promise to Pressure - Teneo</t>
+          <t>Agentic AI audit platform Fieldguide raises $75m in Series C funding - International Accounting Bulletin</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 20:55:49 GMT</t>
+          <t>Tue, 03 Feb 2026 09:53:23 GMT</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOLXVwemdRYk1qT1FqeUh0VnVrQ3dZWVNmWU1jWDJFaHVRRWlUcW5ZbGowSXN4MFBaSGwyb3lkMEF5aHg4VXdpRWtrNng4b0dIWldJdUJBRl9MNkNoRndQMGQxVVpub1p1VmRUekJodHYxNnpZV1M5NFV5REJiaU5fMERPQnlkTEZ4NUVKcFA1QUxXYTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOR3BTVEVxMWUtS2hRMmpNOUNlaW9OR0trdDdlMEhEdzhBM0N2Z3FFWHpqRDItbXMzYndHbkhaaXhPWTBkZnhmZVBTdGZ6bXM3N19tWDRxc3JESEt3aDhOeURnR0wteU1XNFpmaC1qWlBsT1F3VWJVdkpsdy1iUHJudUhUb0JlVmVPN29XQjdwRUJXcHB2?oc=5</t>
         </is>
       </c>
       <c r="F70" t="n">
         <v>1</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46055.8720949074</v>
+        <v>46056.41207175926</v>
       </c>
     </row>
     <row r="71">
@@ -2747,24 +2747,24 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>UK-Bulgaria: connecting semiconductor expertise for growth - GOV.UK</t>
+          <t>How trade shapes the winners and losers of AI boom - Oxford Economics</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 13:59:31 GMT</t>
+          <t>Mon, 02 Feb 2026 23:33:39 GMT</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPUHdYRDVQYWVLZjR4MnFna1dPMEJYd25Bc3VvdllKVGJ3OXAzcGIzUy1zX3hQUHhfZVdlZExSZWVkVUc1dGF0OG5ncVRpNkp3YlNaaFBKZjczUm1ET3hBMVlRR00xbi1oVTZtS3REQ2tjek42Y1lKQUdTclFzT2dobGhIdE55QjVsVzFqTUJ3U01aZGVISTU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxORDcwTnZjQkprcmdaR1dMYWE0TTlSZUJ5ZEVqOHJCZDhYT21QdG5veEJpa3lOWUE1QzRpaVN2TGQtcHR1dGtlV2xkc1lQSkFabUIweFhqVWIxWXNORVh2T1ZTVlJFbFlBbGNVRWdwZFQtMDh5MmIwUmdCUWU3cjFPZmRhTVhfZzBOZWlqcURqSTFQRm1XRHZV?oc=5</t>
         </is>
       </c>
       <c r="F71" t="n">
         <v>1</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46055.58299768518</v>
+        <v>46055.98170138889</v>
       </c>
     </row>
     <row r="72">
@@ -2780,24 +2780,24 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MediaTek Accelerates AI Development With an AI Factory - NVIDIA</t>
+          <t>Opinion: What should artificial intelligence mean for fleets? - Fleet News</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 06:16:43 GMT</t>
+          <t>Tue, 03 Feb 2026 09:35:37 GMT</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE1EY3BvY0lNOWlaSGhoYWRHOFl2ZVBVZ281bDRzMXJtT0FTUzhxYkRmMU1WaEJkWnpGN0kzYzdPZjBqeV9qQ3hQdXpEUUlNRU51a0llSWRpLURiLXVxbHpfTWxKNUpxWV8yYS1tNkdHSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE1ZWEpUMkZKUFFMV2VuUTFUMzNBRDRZSGhaMWN5LTVjZEJ3SF8xcXowd2lydHBUcUpsZDhYcEVFTVpSQXprSU1qTmVhTTlSdHNUaUFFa3hrdTU4ay1IZXVPMlNNWWVMRV9YSTV1d0o2WHF2ZDZfcG55V0xxSQ?oc=5</t>
         </is>
       </c>
       <c r="F72" t="n">
         <v>1</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46056.2616087963</v>
+        <v>46056.39973379629</v>
       </c>
     </row>
     <row r="73">
@@ -2813,24 +2813,24 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>The Balance Between Rules and Learning in Robotics - Telecoms</t>
+          <t>AI and its impact on work: how companies are being transformed - Orange.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 16:52:45 GMT</t>
+          <t>Tue, 03 Feb 2026 06:01:08 GMT</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxQVGNhZGZTZzZjUkl0NlJQWmpWSmFOTGlRTm9DZ1VDbXl1ZUs1TVBIT2ItbHdyV19ULUJDMWZfTkFGS0tuYWFyMGxTMEtFTEhFSXNYeUxYNGdvcmYxcGZ3ajdJYzVYcTVDQ3RlQTlwOHVkekljNUtOYWloN0hEZ2lfMmgtRm0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPbWFwTmNLZ1VEOTNZLWpSMEFCNzhpWGpybHhfd0lJSVM0MWFEdXN2Q3hCc0VubzZlalJSbW5zcVJNMTRtMmt6ZEZyMnlWcFRBTE9BdG82Q0ZLZ1hfUDdTa1ctSUNTYU11TTM0QnhTa3E1ZVZKclplc2hJbTFHWXljWlR3V2tSSVZf?oc=5</t>
         </is>
       </c>
       <c r="F73" t="n">
         <v>1</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46055.70329861111</v>
+        <v>46056.25078703704</v>
       </c>
     </row>
     <row r="74">
@@ -2846,24 +2846,24 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>30,000 at Web Summit Qatar for AI, quantum and creator economy - Euronews.com</t>
+          <t>Liberty Global signs five-year AI and cloud deal with Google - Proactive Investors</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 14:58:41 GMT</t>
+          <t>Tue, 03 Feb 2026 07:55:00 GMT</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPUEx0MTRuaVlMOHV3YkdXb182cC1BZE5OMVFMekFxWVQzX1l4UkpJTFBtWFdVYnU5UDVnUTlTelR6ZzFnd3prVVR0cXlScThjV2Z0TGswU3RoeXA2TUhfdjB3alhVRllMTDBIa3d3ZjhISGxrbWNJVjl5M29YbTFjTmpFSndVWHRPZEpJVWhTN0VGWWM0WnlCX3hNcHV0QXB1QWpqaGE5dWsybWFGV3dOMw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQeVJhOWFLVVRlcWlmOGVfdnRuQ0V6Tl9xdkZsYnVvOFlrc0w1UTFTRzZrdTNfNXVyRFRFNzNRV0RUcmVUa0JLbjN6cVBBeGpZMWx3U09VbGVWR1pkRXJYQ0VCVXRmV25jdnZwX25lTWVJdlEzZFMyOXdtVm9QN0p2LXRqM3VEQUlkMDJKcXQ0amZTMlFVaFVFeDg1Tkp2Y05fN3UtckM0QlVBOXZOTTJNZHdoS21KSjRaZy1fNGtaS0pZZDNMVjlkb1p0U3R6Zw?oc=5</t>
         </is>
       </c>
       <c r="F74" t="n">
         <v>1</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46055.62408564815</v>
+        <v>46056.32986111111</v>
       </c>
     </row>
     <row r="75">
@@ -2879,24 +2879,24 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Electronic Design Automation Software Market Size to Lead USD 34.71 Billion by 2035 Driven by AI, Cloud, and Advanced Chip Design - Yahoo Finance UK</t>
+          <t>HAQQ Legal AI bags $3m to digitise legal work globally - FinTech Global</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 15:02:00 GMT</t>
+          <t>Tue, 03 Feb 2026 09:25:27 GMT</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQNUtvZDlhS1BqSDdfeFVBY1ZaVFNMd2ZOX3QyQk02UGtkNDFidHNkV3dLRXlVdEI4R0JjYkI5MzZiR242TVg1bTRJam4wakR6UUdJbzNXZmYzYUZhcC1JOV9EaTM5dWh4Smp0czlIaWJKYjRMNkNJQVlyMzN1V3QxUy1HbEhxRmF3QzUzMW8zaFJHSzB4Z0RJVw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQNV9ub1NnS016MkJZdGJLd05RV1JTdGlBbGp4Mmd3UGN1TGdOMm9tcmY4MFJfbUhNQjRPX2JmakIzcFV6N2tZc2VYNENOY1JrUlphdmJ2a08yZjdXQmwyTTdPb1RrVFZEMklaVVY2dUZIcjNmWDRBaXJHeU5faWlqSXlFSTFJWnBWMWVuT3lKU1Zydw?oc=5</t>
         </is>
       </c>
       <c r="F75" t="n">
         <v>1</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46055.62638888889</v>
+        <v>46056.39267361111</v>
       </c>
     </row>
     <row r="76">
@@ -2912,24 +2912,24 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>The power of putting AI governance into practice - Global Government Forum</t>
+          <t>Alphabet Q4 2025 earnings preview: cloud and AI to sustain valuation - ig.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 17:11:25 GMT</t>
+          <t>Tue, 03 Feb 2026 05:21:31 GMT</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQWGllM2ZaRVR4MDZreC01cWFWUTNoTW5fMWc3bGVxTVVkSjVzNXR2cmp1UTlWM2ZDQjZHckNkVTIxdTVnQXZXc1JsTWhXSW0xWDB2dEtFWUNNNjE4emNveHN2dk1hMHR3VlJVWkVzSXRHMmd5Z0d3NUhQTFpGQlJTVGNFZXZvaDZnTkU4R3RqbmI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQcnY4a2J0bWRPZnJxSGRHeVYtc05FaUY1MXgzQ3NEVkNJYjVIM1BCT0lFblVJN0xkUi1jZ0ZMQTZnQS1IYVB5Tm95cXJfSDFJWnBFd2gwbnVVcXg0SUMzVnRhRXZld3lTdHhYbU9lS1lwOXB4SGFZa1JHc3diTzZjZF82OUlwYlFSVzE5YjdjWW1PeGsxLTFtLTBiMEFycVFxa1hsalpwWnlGYVlkN0ltbnFUcVlqM3U2ak91M3FKWC1NZw?oc=5</t>
         </is>
       </c>
       <c r="F76" t="n">
         <v>1</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46055.71626157407</v>
+        <v>46056.22327546297</v>
       </c>
     </row>
     <row r="77">
@@ -2945,24 +2945,24 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Christian Klein Bets SAP’s Future on AI and Data with 5-Point Growth Plan - Cloud Wars</t>
+          <t>SkedGo unveils TripGo Mobility AI for smarter travel - IT Brief UK</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 16:00:00 GMT</t>
+          <t>Tue, 03 Feb 2026 08:00:00 GMT</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQU3d6S1RPNFdFbzJkR0Jfd25KTmZ4dW9lQkozcVlCS0ZPa2xOc05WWmhTMGJYbHlFVy12d2hnb2h2cU1XSmlrWC0tNkpHSEtpcENPRElUYlkyWXE5ZXd3Z2M3OGVXd3FRUDdWaldfNGtfc2FsMk94WmNqdnRONnVEY1k2dEpTeWViTmxyUjdYN1ItcEhuMHVZN2Y2OW53eUJrWXZGcEJ0cS1sSzNXS29qZnlXNnlmVHZO?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPbE9KYW8zbThNc3hzaWxSQWtpN1NDSlJhVVlMdWpjUzRESXJoWTJ1MzhSSHVaSHVYLXNrSzZ1OXJqeGFJd3M5VnFkYjNtMXVwT19tV2Z0c0tkaTRqQTZMcW1IM0V4eWxnWEdkQXVtZk94bEtIUzlOSTFEbUlYeGZkMUg3aEdTSnc?oc=5</t>
         </is>
       </c>
       <c r="F77" t="n">
         <v>1</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46055.66666666666</v>
+        <v>46056.33333333334</v>
       </c>
     </row>
     <row r="78">
@@ -2978,24 +2978,24 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Forfusion Partners with Stellium Data Centres to Accelerate AI-Driven Innovation in the North East Growth Zone - TECHNOLOGY RESELLER</t>
+          <t>UK and Japan strengthen science and technology ties - GOV.UK</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 21:07:25 GMT</t>
+          <t>Tue, 03 Feb 2026 09:04:44 GMT</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQc3VIdlFiZkpoWTlVLW41UW5aaU9Jb0ZzZTFCOURUSm9maU9Sd3hyWmpkZVROdFB5RFF3UjJEUHVia1FWdFNzdUhYczFFeUlGeXk1Zkw4WE5DSkp2dkNEc1ZOT2ZlWjFXZHlVMFhSMzRubVFjempHQmU1M2tuaWZvUEhmUjBKSVBpT0FfalRta0JfQnR2MDlJdUlhUWtrMnZ3bElJM2hnUlotZDdFd0xOZEdDX0FiMUNhMFplM0pmQ2ZObENSQkRqclAwSkE3SHpVcm4yUU43WEY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOQkZQLVZCX0pweG43Y0N0dWNXUXFGaGNsWUN0b0JBb1FFek5FREd3cnJXR0dFRGY4TGloaGlaRlFvMGo5SmxpZmFwVHpxbVdxX1RBTHN2T3dFc0M5Zk1uOTRDU0ktQ2NfRDdPN2xQVmpuanhLRHFIWjhPaHNJRDV1Rm1zVVQ1WlRBOEZrNlRsYw?oc=5</t>
         </is>
       </c>
       <c r="F78" t="n">
         <v>1</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46055.88015046297</v>
+        <v>46056.37828703703</v>
       </c>
     </row>
     <row r="79">
@@ -3011,24 +3011,24 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>NEWS: NHS Tests AI and Robotics to Speed Up Lung Cancer Diagnosis - Practice Business</t>
+          <t>Musk's SpaceX and xAI merge to make world's most valuable private company - BBC</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 08:38:49 GMT</t>
+          <t>Tue, 03 Feb 2026 09:31:06 GMT</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNV2k0ell3bnhNOFBMM29oU3ZHenZTNkFvX0lDc01hSjN0QmZFM053cndMN3pPNDlPOGRxNUVVMjBuSDEtc3hSSXRzNkhwdkdMWlFvUzBGc08yWVM3S2tvaW9fd09heU83T3ZKVzF2NGpPc3VRamZzbUVMZXdqbUJtMm8tcDI1d1ZrM2RXTDU2VUZ4OUFMV0hkbEY4WQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFAzc09Ibzl2eWJ1OEQ0VTkxakNQV1hxOERGX01GOTNYUW5RNlRwNnVNbzdzSGR3TXJnaTNYTUdkT1doUXdwTko3ZTNJOWxNeXJTampQUVhSRDZlQQ?oc=5</t>
         </is>
       </c>
       <c r="F79" t="n">
         <v>1</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46055.36028935185</v>
+        <v>46056.39659722222</v>
       </c>
     </row>
     <row r="80">
@@ -3044,24 +3044,24 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Energy, healthcare and utilities: how to tap into AI in the real economy - MoneyWeek</t>
+          <t>UK-Bulgaria: connecting semiconductor expertise for growth - GOV.UK</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 15:58:55 GMT</t>
+          <t>Mon, 02 Feb 2026 13:59:31 GMT</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE1xc2lydjV1aDZXaXliWnM3UHJDcncwYVF4Sm5QMWNxM2ZHb1J4OXNYYzJhSnZ1a2wzSDlBQ2UwWFpGWUlESkRQeV9PME1TUDRlOVhLZTVOSjdpU0Z0UUlWMXBYS05UZDZ1UmVtN2NqTlFwaXV5bEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPUHdYRDVQYWVLZjR4MnFna1dPMEJYd25Bc3VvdllKVGJ3OXAzcGIzUy1zX3hQUHhfZVdlZExSZWVkVUc1dGF0OG5ncVRpNkp3YlNaaFBKZjczUm1ET3hBMVlRR00xbi1oVTZtS3REQ2tjek42Y1lKQUdTclFzT2dobGhIdE55QjVsVzFqTUJ3U01aZGVISTU0?oc=5</t>
         </is>
       </c>
       <c r="F80" t="n">
         <v>1</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46055.66591435186</v>
+        <v>46055.58299768518</v>
       </c>
     </row>
     <row r="81">
@@ -3077,24 +3077,24 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Answers to key questions about AI in IT security - Computer Weekly</t>
+          <t>Large RIAs step up AI and data spending: Cerulli - Structured Retail Products</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 16:59:23 GMT</t>
+          <t>Mon, 02 Feb 2026 16:11:33 GMT</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQenRxTzlpYTV3NW5xVEVqcFpNRDhZT1ZQbUFVdjQ1WFA3Y09MenRmUUd1MTJlX2NSTy11VUN5YzhmQkNyUnZCMG5kQTFYYTJ5aUtjcjlQLVJmQVZxbDUtSzliY1lLaVFfTzlzSTVLSHpKYk5DbzdzMG5DaUU3X0VYWklOemd6NmZ5M0JpaEF2SFk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPcFBPNGFHby05c3dkYV9CNVZtRDc1eVdFRmhmSWdJVHQ1cE5GamVNaElKVnoxcHRSRFFFQnFyUDE2M3dzVW9MbmRCUmJVZnJsWXVLb1dMZ2xVa0VxUVNOaXJSNklRdW1oWE9RUEtabUt5MHJiQ2FrZHIxUGc1d21XOXAxeXJXZFFiLUtVeDJ1Uzl4VlJZV1VQczVJTzZ6d1dyUTdRX0xB?oc=5</t>
         </is>
       </c>
       <c r="F81" t="n">
         <v>1</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>46055.70790509259</v>
+        <v>46055.6746875</v>
       </c>
     </row>
     <row r="82">
@@ -3110,24 +3110,24 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Why banks shouldn’t wait for AI to fix the Gen problem - Retail Banker International</t>
+          <t>Barton Peveril case study - Google Cloud</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 09:28:04 GMT</t>
+          <t>Tue, 03 Feb 2026 05:13:05 GMT</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPNkJaSEM4djg2STlSalNWM0c3MmhmS1ZNS1c5MG14VUREZzNha25fVXp3VXF0YUczMkRlMEwtVldORHU4TFA1dEtLY3dfeXpmcW5UbHJLR09mX3FYZlFwbmtCbU1GZ3lsMFBUZmhpU2ZHMzlVZUxkSG0wNkRCeFcwQkk1OW5ZUlVaNXFPVktQb1g0djI5ZkQzU0ZKTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE4xSjkwTjBsTk1qeWV5WGhJTFNIUEdKZkRXLUpGaFRUQXEzYVNNaUxkUEpDcmU1cFFJNjlCOVlkU2l4RTV1RmZsc19Sa0VaNXphVjJ3NFNMY1lmQThs?oc=5</t>
         </is>
       </c>
       <c r="F82" t="n">
         <v>1</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>46055.39449074074</v>
+        <v>46056.21741898148</v>
       </c>
     </row>
     <row r="83">
@@ -3143,24 +3143,24 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Year in Review: 2025 Artificial Intelligence-Privacy Litigation Trends - WilmerHale</t>
+          <t>IT consultancy enters data centre partnership to support North East AI Growth Zone infrastructure and service needs - Prolific North</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 18:05:23 GMT</t>
+          <t>Tue, 03 Feb 2026 09:52:17 GMT</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9wFBVV95cUxNelJqZWo1aVZoN2ZxMjJvckNuZW85ZzJzWTNhaFowc2swaTZLc3dzRWJ2Si1Ya3NXSDBfeXJLOG1NVjVVV1FHV21TZXB4clFKX3ZUTnEwbTIyN1pDblVSQnRSYTdUdmNvQmZWR21BRDdfQmVJd1J1VEQ4a3VmVVZlQm40XzZQZXlEVEJuZ25QemoyVnJlVWtBUkVUSTVJUEQ1RXpYN3VHZHhmTmtCZlIydmhZRzBWM1RwOE9nWGZRanc0WjNUaXdBdWg0UjJXUUZNbW1wcXFJOXNHbVVCUE1YLVNZTGItd0VwR3hLeExudzlpNThYaHJN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQMm1QcjlSdmRjLXpWUGhqM0NpbHpTVkdZdU00OXZZV3lIWkxnUzhvQVEzcmpqampEN2pFSEtrb1hYcWptRFFkT1N0SENqMmRPSXVnWHNlclRjeU4tRU1Uc19hNkwtdU82OGJBUmZ0OGV2Tkd5WUhVZVFBc1daSkdsLTlVdVRVY2ZNMGtzaXR3YThubHgwU29pRVRGdWpOV1d2Z1hDNzF4X1J4NUFkM3ROQzhTcmZYajhONG1xcHhVUHZyT2x5U2VINDUtMnNoX0MwMVpuVjVRQ2lJVW1sa1RZZXl6VmhlcXpr?oc=5</t>
         </is>
       </c>
       <c r="F83" t="n">
         <v>1</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>46055.75373842593</v>
+        <v>46056.41130787037</v>
       </c>
     </row>
     <row r="84">
@@ -3176,24 +3176,24 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>How sustainable funds are navigating AI, defence and financials - Trustnet</t>
+          <t>Opinion | Where Is A.I. Taking Us? Eight Leading Thinkers Share Their Visions. - The New York Times</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 11:01:33 GMT</t>
+          <t>Tue, 03 Feb 2026 10:03:01 GMT</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPRktGQTJJdXpHeldsX3E3NEl3ckx2QjkxU2tIb3lPUF84dEI0a2ZfQjVjbTNMeHpZUFZjdkR2bldWTnpMRmNjMnBkNFZ5Rk05dW5xeEpsTWo1YkRXUjhpYkdEYS1od0dPSmhScjZPRjZsYVBxTzlUbXh1QlVrbVhwaFRyNTB4aEk4V2I3b1dhV1J4VC1vRUdsMmdTUEFFeElqbE1J?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPXy1tbFc5V2p0NVlhcHJUc2FQeFZkS21UMjQ5NXdkcUZib2VndHZOenBpTW5uOGZvYTRoUUZSN2tZT1c3M19XbDEtbkpVY1pPbWJmdmp5RDZuVFZtWDkyb0ZhbExleXl1NnBCVTJWSktzRHhicldUMnFOSmpLOXdLck5waWpnTUktenh4WmRsZExTdkNELXFwVQ?oc=5</t>
         </is>
       </c>
       <c r="F84" t="n">
         <v>1</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>46055.45940972222</v>
+        <v>46056.41876157407</v>
       </c>
     </row>
     <row r="85">
@@ -3209,24 +3209,24 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Yaspa Becomes Founding Member of UNLV’s AI Research Hub to Advance Responsible AI Adoption in the Gambling Industry - FF News | Fintech Finance</t>
+          <t>VivaTech 2026 Confidence Barometer: A paradox revealing tensions between technology adoption, sovereignty, and cybersecurity in a fragmented geopolitical context - PR Newswire UK</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 15:09:39 GMT</t>
+          <t>Tue, 03 Feb 2026 08:00:00 GMT</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxQX0k2RTd2eVNGVVlxZTEzYnJKZUR4QmJtMjdTVHNmb2tha0pVbVFpOVduV2dWWFVha183MGRuRjRnc1NCVGZvcGcxYnBRUnZrd2RrVlAtMmpjbnU3MzFIYW5NUUxqbnJSQkdab2M4akJVMERVQVliRGZGZmtvT0FhTFVwZlVLMWlhTDFDRDI5bzNPbzh0cjlfemh4Y1pvZC13ZGI5cU9OMEhUT1kzZmd6QVktRWN2QVpUd2Zla295cm5TZzR4Uk5SMENPSU9PRG81MjdNd3podUxlVmUteWdRTjhKaXNibmNmeFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAJBVV95cUxPOGpDN3dqWlRvWW84MDgzaXlDaFpmcmJ5enpnUmpBZldDX2JCU1RiTlpUOGdudDhWcm92VG5rOGhfZlJIWjRPX2tSOG96TTVtcHNpUXRadklXdEV2T1V6WFdmeHFndnlTRmpfTjU2MFp1MmRXSGJJZE1nNDBlbmxFamZQb2x2bTBHVkxDUlg3WExYMWZTNGpqTjlicHdVTS1peENtbzJEOUhsT21OQVhNa21NMXJsRnVDdWg2ekE1U25zWUxSa2NNZmVaT0FBb1pjWDBhdmpEc1RIblVDVlNjUDFDeklldU5lcXFhdFhURTBGTnhZYWdFdXUtdlp2M2NKS1JobHF5aXRNdjJMQ19qV3ItRGF4WTBISExVS2N0ajJ2SW9XQXI0U0duWDVvUGQ3QjJWYkpORXNVbVZD?oc=5</t>
         </is>
       </c>
       <c r="F85" t="n">
         <v>1</v>
       </c>
       <c r="G85" s="1" t="n">
-        <v>46055.63170138889</v>
+        <v>46056.33333333334</v>
       </c>
     </row>
     <row r="86">
@@ -3242,24 +3242,24 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>From Ideathon to Pilots - Updates on AI and XR Medical Education Projects - Yale School of Medicine</t>
+          <t>Stronger sales at LadBible owner amid generative AI growth - Welwyn Hatfield Times</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 13:35:17 GMT</t>
+          <t>Tue, 03 Feb 2026 09:25:54 GMT</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQLUdWWXRPYW84MkNFNmV2c2s1RllLSXh1azlkbWhHVjdpM1RkbzBHUTdINWNQckdDVWNEdmxGaVZhczRHLVh1SEVMNWgtV3NNOEIzaXh4WENHNEN3djRwbU5ZVDF5VkpwY1VrOUI1dVJHaENlQmlqVjh1SXVQNmpXWklBZjROZ0tpVU84b25R?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPNlVfREVpaUlFbU5XN2lWTTRRWTRHN280dGd6RlRBc2sxbnBrcHotOFE4UjdzMXJ3NUc3dlAydXRhLVB0Z0VoQjFEanZQZkdPbC1YOHJtYTdDOHNONk9aMjBvdHVrS2JYRThoOFoweUV3UVpUeWN0VDZiOHhZU0llbnBEWFJ6WFdrekFHT2ZhQlFvZm5HN0t4RmoyTmY4WXBma1oxV3JYUng?oc=5</t>
         </is>
       </c>
       <c r="F86" t="n">
         <v>1</v>
       </c>
       <c r="G86" s="1" t="n">
-        <v>46055.56616898148</v>
+        <v>46056.39298611111</v>
       </c>
     </row>
     <row r="87">
@@ -3275,24 +3275,24 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Policy in a Strange Land - felixonline.co.uk</t>
+          <t>SDAIA Launches National AI and Data Curriculum for All Saudi University Students - BABL AI</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 19:27:01 GMT</t>
+          <t>Tue, 03 Feb 2026 00:16:24 GMT</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE9KSXF2Z0M1YUtkQUJLOGN1RTU1MmVrbkc3cFpSS3BiU3RzTXhWUW9FZjNEYTJJVUx0elRZaHhfdGhNN09YOHJLN1Ytc2VEeGwwU1FKSnczRXp2dkVTZ0JpVGVwaFlNb05lOFZodQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOeTl0aUM3cjYtMFAzZ3IzU3VYRlJtWUVoX2ktMVJlLWxSMlpRcHVuWHdjNkdZNFh3cE56dXNvWjhXbEdNMGdTaE5PWHh1TFNwbjNCQzFWd044c1g0SmFFNHRzRWZwRmRuTG1FQUFtVUNHYWtISXdNWm03SlNDd1lWREtxel9RTHBicDQzVG9KMmZNUXBKVExBT0NCaHEydw?oc=5</t>
         </is>
       </c>
       <c r="F87" t="n">
         <v>1</v>
       </c>
       <c r="G87" s="1" t="n">
-        <v>46055.81042824074</v>
+        <v>46056.01138888889</v>
       </c>
     </row>
     <row r="88">
@@ -3308,24 +3308,24 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>What is the 'social media network for AI' Moltbook? - BBC</t>
+          <t>01 Quantum Launches Quantum-Resistant Blockchain Migration Toolkit - The Quantum Insider</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 13:59:14 GMT</t>
+          <t>Tue, 03 Feb 2026 10:25:04 GMT</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFB3OWtDak5HWnlsTlhORjhSSEp3cGdyUzJaUU05cmdlTlZSTUZYclByUUFaWDh6OGdoMXRkYk9KRmFmbEp6SEpYd29uaEtWY25HQktwdFVTbzhMZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxORWpicmVnSVI2T1RYamIwVm5aVVFoTXphMGlrSXRoWlREb0p4OE1SYWxiYmRwVEVXN2o5WU55QVp2TjJZNWJSRnJCOWl2Q1duQVFIRlJfdXphdGNUTi0xbi1JbVp5VUJfS0xjTDlHRFU1ZTZ5bmhOdWE5TjhYZ00ydnJEWGFiT085SXBqY0M2ZUNOLUE?oc=5</t>
         </is>
       </c>
       <c r="F88" t="n">
         <v>1</v>
       </c>
       <c r="G88" s="1" t="n">
-        <v>46055.58280092593</v>
+        <v>46056.43407407407</v>
       </c>
     </row>
     <row r="89">
@@ -3341,24 +3341,24 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>“A cloud-enabled, digitally resilient Europe transforms the protection of its citizens, infrastructure and strategic interests” - Thales Group</t>
+          <t>AI in 2026: From Promise to Pressure - Teneo</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 12:00:00 GMT</t>
+          <t>Mon, 02 Feb 2026 20:55:49 GMT</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQc3lvdXNHRWx4aTVFNFlPbGUyTjB5UlVaN3dhSUhvbXQ5dmF1Tk91REd1QTU4R2VPbGc0b0VEbTZrRlE0cHJWaXVFYmlXaDFDMDhqM3BUOWtNZzJLb0FBSEh3T2pwLWEyTE5ycEpEX19mSmJ4TG40UTIzRVdZTk1IdEpFaWpfVmtoZFRTaXRBREk1YzdNdk1NOVJFRHpzdTJPemlFYmZiWGtuWEJJWVgyaVlDSDBsRjFoaVVUU2tjLU9ZUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOLXVwemdRYk1qT1FqeUh0VnVrQ3dZWVNmWU1jWDJFaHVRRWlUcW5ZbGowSXN4MFBaSGwyb3lkMEF5aHg4VXdpRWtrNng4b0dIWldJdUJBRl9MNkNoRndQMGQxVVpub1p1VmRUekJodHYxNnpZV1M5NFV5REJiaU5fMERPQnlkTEZ4NUVKcFA1QUxXYTA?oc=5</t>
         </is>
       </c>
       <c r="F89" t="n">
         <v>1</v>
       </c>
       <c r="G89" s="1" t="n">
-        <v>46055.5</v>
+        <v>46055.8720949074</v>
       </c>
     </row>
     <row r="90">
@@ -3374,24 +3374,24 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Confronting AI: The Future of AI Regulation and Your Path to a Career in the AI and Tech Legal Fields. - UC Law San Francisco</t>
+          <t>4 signals from the front lines of AI investment - PhocusWire</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 17:23:12 GMT</t>
+          <t>Tue, 03 Feb 2026 08:04:27 GMT</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNbm01cEhkZjg5ajd6M1lsYUZFbEFHMkRDZEwzYVQ2N2xoalN6S1FZSm9QZU1CS3YyUGg3cVZuTEt3UWVQYVFkeXN2Y2U2bGI1R0pqVExjRGdqTFJGcm9GdFpQdkdCN1dWZDQtaG9hQzhrLVJ4TFFBNlNPYndWRWlGRUh5WXAxeDFzdU5WYmJlTnZPWGlDeUZ3ZjJWSVV1TWdIOE9Rbkx2amFjekpzY2FhZTA4dXVzc2xZSnZFakFwd0JEanRvbngyMldnYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOZjlVTXNNMjJidTVkdzYzc3NwX1pVZzFXN09JZkprUnZ6a29NVTcxOHhhWTZZbDdKWENLNDltTEtLQjNMQkZpaEs3T25aMVBaQXlSaHBaOUU1RWUyc1JjOWU0UjVkRXpoWFlSbUtFV0d2eVBoT2R4ZlRpbDl2Zk4zN3F0OFkzT19PYTlRZnFZakNxZw?oc=5</t>
         </is>
       </c>
       <c r="F90" t="n">
         <v>1</v>
       </c>
       <c r="G90" s="1" t="n">
-        <v>46055.72444444444</v>
+        <v>46056.33642361111</v>
       </c>
     </row>
     <row r="91">
@@ -3407,24 +3407,24 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>From Performance to Purpose: Lombard Odier on Intergenerational Wealth, Intelligent Technology and Enduring Partnerships in Asia - Hubbis</t>
+          <t>Dow to replace 4,500 jobs with automation and AI as shares decline - Packaging Europe</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 16:04:12 GMT</t>
+          <t>Mon, 02 Feb 2026 11:08:32 GMT</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxQS2puWGNpajlmcGtCMnhvcUo4MHBxRWJiMXlBRjFjLW5XZkRUY1o1MkkyV25mV0Z0bkYwcDY0anFmR29qa0NnWDAxZVc3MkczZTgySG1rQWx0OFVEbWtxd1d4UlRfTk1fZDdGRHJVQkowcVZsZTNLUDN4YlFYcE5RSnhEMDhvT3hqby1ESXJ6R0ZXS1ZxMklPVU9aYXFpeDVUTzBWcUFCTEtDYUJVWDhCYnJNVHhrdDY1RUxFa3ZDTFUzUUpnMFV2OFdqSzVFaWU0aTZNM0VKZTJ5dF9ZUXhHanVESzFFdTdqX2Vyd2ln?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPUG85LWpVTTB1ajhzU3dMMEtCa3NkMDRxbmpjZTV4RmlvZ1dpSlh2VmZZSW40VEV2QzcwTDVaQVltdnpKT0gya19GT3I1VnJFUGNjRkNGNUtobGFCS0RjV2x1NmV5YTQ3bzlYUWxHRl81dnpLVk1vVHlEemtUU0JDeDk0SVhDYXBsSG9pMXBJdnJfOWpPQ3U4NjNVWm1IeEhCT1l6aWUxQ09EaGg0czl5MXh3?oc=5</t>
         </is>
       </c>
       <c r="F91" t="n">
         <v>1</v>
       </c>
       <c r="G91" s="1" t="n">
-        <v>46055.66958333334</v>
+        <v>46055.46425925926</v>
       </c>
     </row>
     <row r="92">
@@ -3440,24 +3440,24 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>AI deepfakes are reshaping cyber risk – and insurance must keep pace - Insurance Business</t>
+          <t>30,000 at Web Summit Qatar for AI, quantum and creator economy - Euronews.com</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 11:25:07 GMT</t>
+          <t>Mon, 02 Feb 2026 14:58:41 GMT</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNd0JwN0R2S2lhZk02UGFIVWlwODVoZ0NQZTMxZzFURWZURExNbmpXRFlfemNZTWpwNXFidktkSDlSek1EYzlmZzlRSGxoN1dxeG9vcmZYbS1PNU5qTld2RVNQZUNwMXlKcnROQUFXYmtmQUdoVUxxNmV2VlVDRnBSMEZtam1MUzFnd09sRG5IWkVlcW9JNXBzb25qUVo2WjVvRXdxdUt3VnZjbk5vN1hsNVpMTUNQMkUtOVR4QUc3M05NVUZKU2xzNmVn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPUEx0MTRuaVlMOHV3YkdXb182cC1BZE5OMVFMekFxWVQzX1l4UkpJTFBtWFdVYnU5UDVnUTlTelR6ZzFnd3prVVR0cXlScThjV2Z0TGswU3RoeXA2TUhfdjB3alhVRllMTDBIa3d3ZjhISGxrbWNJVjl5M29YbTFjTmpFSndVWHRPZEpJVWhTN0VGWWM0WnlCX3hNcHV0QXB1QWpqaGE5dWsybWFGV3dOMw?oc=5</t>
         </is>
       </c>
       <c r="F92" t="n">
         <v>1</v>
       </c>
       <c r="G92" s="1" t="n">
-        <v>46055.47577546296</v>
+        <v>46055.62408564815</v>
       </c>
     </row>
     <row r="93">
@@ -3473,24 +3473,24 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Whether it’s Valentine’s Day notes or emails to loved ones, using AI to write leaves people feeling crummy about themselves - The Conversation</t>
+          <t>Cortex Code - Snowflake</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 19:05:03 GMT</t>
+          <t>Tue, 03 Feb 2026 08:25:58 GMT</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxObU1UcmpiWm5TdXBWNGtVV2JaODBFWUZhamtxaHFYU1M5YlhPUHBCdDgtX0I3NDR0TzNFYXFiZWdaT0x2ekxVSC00eVBhT1J5ZC12ZlZXb0dkVGU0YTBrelFMNHJKWWRuZ2tVdDVqdkFHVFAzU3hNM0NoczBkV1NtNzgxVHZRLWNialIxUEx3a0ZEREdQSE56MXhYY3RVSlp5Q1AwT2Jiekpya3ZQYzd2eHAwVG9wYWpMSUM5WVROYWJGaWNEMHg2MXYxdmcyLUVQV011NGdzOElKZ1BLQkp0RjB3cjVhNUlLV2Zv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE56Vk5yZEJiZDdMbG9vclhSa0cwLVNKTGh4c3Q2QnZ2QnRDOS1vdVR5QVZvVDJBcTlHWGZQLWVXblBkSmxrMl9CeUhKRFlJZ2xvQ184Nm9peFlGbmc2ckd4MDRNRUJ3QlZ6OFE?oc=5</t>
         </is>
       </c>
       <c r="F93" t="n">
         <v>1</v>
       </c>
       <c r="G93" s="1" t="n">
-        <v>46055.79517361111</v>
+        <v>46056.35136574074</v>
       </c>
     </row>
     <row r="94">
@@ -3506,156 +3506,189 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Palantir beats fourth-quarter estimates on the strength of AI and defense demand - CNBC</t>
+          <t>Electronic Design Automation Software Market Size to Lead USD 34.71 Billion by 2035 Driven by AI, Cloud, and Advanced Chip Design - Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 21:06:32 GMT</t>
+          <t>Mon, 02 Feb 2026 15:02:00 GMT</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE52amFPRG1pR1dBclY2VlpPYU85dWNkaFFHRGw4REVNT0hqM2o0NVJhR1BHWHlLNFFpUVA1dVZJN2dpZEIzcGRuVE1pdkxqazRjZGtSNkMtWGdIZ1MxWXl4VGZueHBHTDRmMFQwR0JVdThvTTVmOVHSAXtBVV95cUxOWnpvU2RBSG1qVkdDLVY2MGpoU0thN0prd3VIc0puMllkX3VfdE51RW9GampfcVdmTnVaLTFHSlg3R0xFd081S0hxdy1uXzEtZlBPY0l2dnF5amMwWnlxQm9pM19YeHpzOTAxdVBfSzF1NHpKUGVMcXpfNTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQNUtvZDlhS1BqSDdfeFVBY1ZaVFNMd2ZOX3QyQk02UGtkNDFidHNkV3dLRXlVdEI4R0JjYkI5MzZiR242TVg1bTRJam4wakR6UUdJbzNXZmYzYUZhcC1JOV9EaTM5dWh4Smp0czlIaWJKYjRMNkNJQVlyMzN1V3QxUy1HbEhxRmF3QzUzMW8zaFJHSzB4Z0RJVw?oc=5</t>
         </is>
       </c>
       <c r="F94" t="n">
         <v>1</v>
       </c>
       <c r="G94" s="1" t="n">
-        <v>46055.87953703704</v>
+        <v>46055.62638888889</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>(fraud OR scam OR phishing OR smishing OR vishing OR "identity theft" OR impersonation OR spoofing OR "account takeover" OR "payment fraud" OR "invoice fraud" OR "wire fraud" OR "business email compromise" OR BEC OR "fake invoice" OR "supplier fraud" OR "procurement fraud" OR "social engineering" OR extortion OR blackmail)AND (company OR business OR enterprise OR customer OR client OR employee OR bank OR financial OR payment OR transaction)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Syncro Marketplace Now Offering IRONSCALES Email Security Services to MSPs - ChannelE2E</t>
+          <t>The Quantum Era Is Here—and It Looks Different Than Expected - American Enterprise Institute - AEI</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 14:00:00 GMT</t>
+          <t>Tue, 03 Feb 2026 10:35:56 GMT</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNUVYzWi1sSDk4QUF6TGFDa2QwTXl4SlNoT0dnajh3SmF4OEJud0NTRF8ySkk1NmNRVE1DT3d2UEZJNGltTGpjWEUxT0xJTXBvTktjb2lPd1pRZnk2RVJfYWhnSkZxRF9vOGRVUHpmNVNTLXJodEx6WWo2cXFBdmdTcE81bnlJZGtqWmtSVUp1cGN6LTc5NHBjTmJnVXM4UnZnc21ieXNDcmZ6UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNUkhYYW83TXNhSWlyMjBVQWdhVEdZUVNhcE9RdEd6aXNVNjF5V2NfOTUyYmZPZndiTURueTI4VGVzSlhZdVlZajdxb1lhN2FJeGhucDJOU0NpWDYySmViaFUxTk85VnZTLTQtOGlSZUhXU2dtVy1va2M4T2xTZTdDRXZUSHp0cUlRQjlKZlhpTEJ3d0F0TExwaUxYUzBtbmFQTXFSb2JZemd3b3c?oc=5</t>
         </is>
       </c>
       <c r="F95" t="n">
         <v>1</v>
       </c>
       <c r="G95" s="1" t="n">
-        <v>46055.58333333334</v>
+        <v>46056.44162037037</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>(fraud OR scam OR phishing OR smishing OR vishing OR "identity theft" OR impersonation OR spoofing OR "account takeover" OR "payment fraud" OR "invoice fraud" OR "wire fraud" OR "business email compromise" OR BEC OR "fake invoice" OR "supplier fraud" OR "procurement fraud" OR "social engineering" OR extortion OR blackmail)AND (company OR business OR enterprise OR customer OR client OR employee OR bank OR financial OR payment OR transaction)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Scam Alert: Muscatine warns of planning and zoning impersonation - KWQC</t>
+          <t>Microsoft and Software Survival - Stratechery by Ben Thompson</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 20:48:00 GMT</t>
+          <t>Tue, 03 Feb 2026 11:00:00 GMT</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNVlJDQlRHWi14dHpfMWhEaVVjdU1vSGpoa3V1S2FCRnprTUNQZE1fRVZlMmFvNEp3RVgzanQwc2hCOFpoNk5QaVBFMmNkOGJxMy00WkV6VGZOYjhCMG94MG5fSVJSdU5IWXhhODlWVjVhV1JYUFlPZmJWNm1wQlcxVTBOZl93WDhibXJqQUNDczZ1ejjSAacBQVVfeXFMTlhDV1ZnMzQwcExSeWswVURrTm9fVW9uSnRGdVpON0RZYjl4bUduaUFGN29NMUdCOTVKQlJDTzRMQ25OazVvYnI1OURmaTNQNElRMjZtX1NnSlUwZGVuWm9aSnluT0lqVW1ucUl4dGVkR0FQWjFYaEZKeUY5cS13bmZ0UVZpLU5YbWV6bjdWTXdvQXN2SEV6UXpJbVBiaUxpV3ZoaEY5dms?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE1ya2NoUTJ4OG5GTlY5N3JITkNGWV9rZEVDc1RFaGNjWUxBZ09ocmJGRGNVVm5ra3lyYkYtT2ZmYWFCSlBRMHhTVkNXdEFnT09HZ3lZYjN0MDRjakVaYnZkakptZkMzdU9Hdml5MlBn?oc=5</t>
         </is>
       </c>
       <c r="F96" t="n">
         <v>1</v>
       </c>
       <c r="G96" s="1" t="n">
-        <v>46055.86666666667</v>
+        <v>46056.45833333334</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>(fraud OR scam OR phishing OR smishing OR vishing OR "identity theft" OR impersonation OR spoofing OR "account takeover" OR "payment fraud" OR "invoice fraud" OR "wire fraud" OR "business email compromise" OR BEC OR "fake invoice" OR "supplier fraud" OR "procurement fraud" OR "social engineering" OR extortion OR blackmail)AND (company OR business OR enterprise OR customer OR client OR employee OR bank OR financial OR payment OR transaction)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Phishing Scam Uses Clean Emails and PDFs to Steal Dropbox Logins - Hackread</t>
+          <t>Christopher Nolan Wants to Know Where All the Hollywood Jobs Are, Too - The Hollywood Reporter</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 19:31:17 GMT</t>
+          <t>Tue, 03 Feb 2026 09:01:06 GMT</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTFBmQ3hleDhQc3dBbEFOWUNxdC1MbG9Gb1RWaUwydUp6M1hXOTFyUENQbEpZVWVxNEtGcmVJRDlsVWI4QjFLT3lYNUtSbmtHVjFMdVdFcFBvbkxMcllWeEQtdHB0ZjYwclR3Smc4QU5MOWxWVTBOQnZv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOTEx5U1hxTlJrbERXNnVVbnk3WVl0RjVKRUJ0aVNXNFN1eERPQVI0Z09mcnVDa0Zob3NvSWw2VjEzd0hGZFh6c1VxeEVOYWwzSVVaTlJoZ1cwMVh5YU51eUE2RHBCVjlKUFB4Q2txMnBqUUVYeDhwQm1VS0NLT1JKdXRPZVdBY1NEV0JnNy1RazhFVC0wdy1mMTNuTjZJMDBkT2N5LUhCbjBGNGpBVjg5RThQSW1PU1g4cHFlYzlKWQ?oc=5</t>
         </is>
       </c>
       <c r="F97" t="n">
         <v>1</v>
       </c>
       <c r="G97" s="1" t="n">
-        <v>46055.8133912037</v>
+        <v>46056.37576388889</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>(fraud OR scam OR phishing OR smishing OR vishing OR "identity theft" OR impersonation OR spoofing OR "account takeover" OR "payment fraud" OR "invoice fraud" OR "wire fraud" OR "business email compromise" OR BEC OR "fake invoice" OR "supplier fraud" OR "procurement fraud" OR "social engineering" OR extortion OR blackmail)AND (company OR business OR enterprise OR customer OR client OR employee OR bank OR financial OR payment OR transaction)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Scam emails claiming to be from Okotoks Oilers still circulating - HighRiverOnline</t>
+          <t>Christian Klein Bets SAP’s Future on AI and Data with 5-Point Growth Plan - Cloud Wars</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 12:03:44 GMT</t>
+          <t>Mon, 02 Feb 2026 16:00:00 GMT</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOaXFHaERNMEctdnA5ZWloTUlKdWxheW1Yd0R1cWdLVVMxNlhjWFRVQm8xVXBzaVJqbHl6SlhGZTJONXctcDJPVXpuclNyR0R4dGpnZXJPSGR0TTd4ZlZsRjZHeFJzOURiUkNDNVFVNDVhZkwwVkZGcmhxLXpNSE43NzcwVTFwLXBxaEwybWNIZTR5ZW9qQVdsVEZqQWhPVjJteHNZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQU3d6S1RPNFdFbzJkR0Jfd25KTmZ4dW9lQkozcVlCS0ZPa2xOc05WWmhTMGJYbHlFVy12d2hnb2h2cU1XSmlrWC0tNkpHSEtpcENPRElUYlkyWXE5ZXd3Z2M3OGVXd3FRUDdWaldfNGtfc2FsMk94WmNqdnRONnVEY1k2dEpTeWViTmxyUjdYN1ItcEhuMHVZN2Y2OW53eUJrWXZGcEJ0cS1sSzNXS29qZnlXNnlmVHZO?oc=5</t>
         </is>
       </c>
       <c r="F98" t="n">
         <v>1</v>
       </c>
       <c r="G98" s="1" t="n">
-        <v>46055.50259259259</v>
+        <v>46055.66666666666</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Wales Taking Decisive Steps to Utilise Artificial Intelligence Technology - newsfromwales.co.uk</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Tue, 03 Feb 2026 09:40:07 GMT</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQdXBNVWhudzFuTjNGRHd2a0VwZ2FtdExDQVhFTnQ3ekRtSF83OHhHaXFVRkh2LUNpbGNwN0J0OS1sZ1JDUC1JZGY3LWlPWFNSRW9TbHpOUC1DclRTNVFPMVVtbGdMZU9JNTU3T3A4MUJJcks5UlhVNmR2ZFY5bHhCTVFPcFo2ZVBHVDFqck5CWDIzMkZ0YWdyVFp5bHcyYVNhRGwzdQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" s="1" t="n">
+        <v>46056.4028587963</v>
       </c>
     </row>
   </sheetData>

--- a/data/daily/topic_feeds_daily.xlsx
+++ b/data/daily/topic_feeds_daily.xlsx
@@ -16,10 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -49,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G99"/>
+  <dimension ref="A1:F91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,11 +447,6 @@
           <t>past_days</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>published_dt_utc</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -470,24 +461,21 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Fox Williams cited in Treasury Select Committee report on AI regulation - Fox Williams</t>
+          <t>National children’s report to Government influenced by local experiences - North East Lincolnshire Council</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 15:59:28 GMT</t>
+          <t>Tue, 03 Feb 2026 11:08:00 GMT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxONUticHMyRF85OV9QcFRDQm5LV0YwTDc2c2RjZjRFcnpmUXJIcXRVWlIwSWpEdXNpbkp5eUMyZWh2UHNXbHFZcHlIZDJBWkJoQl96ZDAtdUtSc0xodUVGSzh6Q1pDTFdlal9RTmlEUVRZcjRMWXo4TE1feVlCaFJ6RExTR1ZYWHJZRllZMzZJaFhKTy0ydmVIX201Y2pPcHdIZUtVV3BzYm03YzIwbUQzYg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPNmItNlgyTnhIUkppVk84b1RfMFh2N3FIRS1BS3ZyRktScGp0VlJqYmttdF9HeGgtVlFDekpOS1RXanJrZlZ5YTI1ZTBTQ1NkaC1qbHF3cUNKZkpOTWZhYklMNzR5WWFOT2xHSDJVcmh0cDRZbmRlMEtZODBQZ1MzNlg3WlA4NW5NSmFpaExlVFpMSXNlejlNaWhfc1laMjBB?oc=5</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>1</v>
-      </c>
-      <c r="G2" s="1" t="n">
-        <v>46055.66629629629</v>
       </c>
     </row>
     <row r="3">
@@ -503,24 +491,21 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Opinion: The report the government didn't want you to read about climate decline - Eastern Daily Press</t>
+          <t>Sudan, conflict - ETC Situation Report #36 (Reporting period: January 2026) - ReliefWeb</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 06:00:00 GMT</t>
+          <t>Wed, 04 Feb 2026 06:33:07 GMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNUGZ6R240am5jMWlPN2t6N0k0cVVZQU1rVmVMUDJaWEJuSDdXV2c1UWU1UUoxNTVwc0RtLWE3eVJTdDNzSW5WQmVxVUsxcjdaQ1JNcFIyQ2Z5UlRsZ0VZb2hxY1RPOFJHNzhxSV9yNFluRlRvenptbU9NWEVOUWtlRFdHTnBxUzFKa0pWcDFR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNX2haNFB0Y21DelpXNTZhMGQyVWxrYzlKVkJhUWFROEJ4WWhZSUNvbjRSb1FMR2NNV3g1VGtyVE53RUxSNVg3a2cxeDBXR1hoNHFTTWNoc3RhYUxHQWQ3X2R6cnBuQy1xUW1sTmE4SXN2Mm5hSGZ0TnJ5VTdKOTRjUi1rc2NlbVNmVEdnX2E5OFdNYml5MTJZNXd5M0JLaFpuQzFlRm9n?oc=5</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>1</v>
-      </c>
-      <c r="G3" s="1" t="n">
-        <v>46056.25</v>
       </c>
     </row>
     <row r="4">
@@ -536,24 +521,21 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Government update could see more families save 'up to £450 per year' from April 2026 - Essex Live</t>
+          <t>Government report warns Ireland lacks access to key EU border-security databases - VisaHQ</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 04:47:41 GMT</t>
+          <t>Tue, 03 Feb 2026 20:52:20 GMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNSnJldm5BUGh1aTJxd2p3dkk0cFFkdTdrelJPUWdaX2R1UnZ0QnNYcWVDX3d2M2xCOHNfdFVGUmJPRUhVT0psNGp3NVVPVFcwOHgxb1kzbG9vMFgxODJvN2pVcFNxODAxenRmOXFMTGd6UjdQNGVUZWNUc25Tbk5KaEZSMHNfWW5wSVk4eDJva3dwZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQNks4THV6akVUNEIwUjNXVVJ6VEN1aTNDanU1Y0QwalplRVNSSmwxaDhqdWFFb1EwMERKcWxlUk03X2ViNzQwZkRIbEVxOUZBeXZ2UVBDX1c0ZkRJS29UX1JYTzFSQ25hT2pvSWpEek10WGxwcllDNnloWlFXbGs4QnRScmw5Q1lFc3ZDM3ZFZ2tkdEJVWXBsWDAxT0I1cDdqQTA2VHZBNWg0Y1JmMlQ5bW1walQzSjRwaHM1b095NXA?oc=5</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>1</v>
-      </c>
-      <c r="G4" s="1" t="n">
-        <v>46056.19978009259</v>
       </c>
     </row>
     <row r="5">
@@ -569,24 +551,21 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Thriving Kids Advisory Group Final Report - MBS Online</t>
+          <t>Thriving Kids Advisory Group Delivers Final Report - MBS Online</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 22:47:12 GMT</t>
+          <t>Wed, 04 Feb 2026 04:20:18 GMT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQSU55MTVrdlV5c3kyTDhpTlBoM1J4UVlXSzZ1ajFiV2FFRmdtZEV1TGV3eUZvSWxNTFdRMjRiY1Jreko5WWZDVmQ1X09ndjEyUmZxQ19EWU1zXzlxdkZ5T0VjMnd2YnNLbEFMWWtjNC13MlN4ajVTM09KY0pjdHJVdlBkMXlhN2xMY0VHTnZ6cDlzYjJ5R2VCbEhmREk3UnZ2SkpEYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPQ1lvX0FNbDhia2hlbVhlMnhSb2tKM1l4NlZ3RmZvLV82QzhnWmppcDZCU1dUNjNweE1DUlZOb21fVGlDZE5VaGdmUDE3WnNWNzlFQkktTDZpXy1nX0pFN2RqVXp4clNRdFZpQThsNHk5UVdzaE9tQ1hFblVnX1VkMmJSYjhEenFB?oc=5</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>1</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>46055.94944444444</v>
       </c>
     </row>
     <row r="6">
@@ -602,24 +581,21 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>REC Clarifies On Report "Government Considering Merger Of State-Run Entities PFC and REC" - TradingView</t>
+          <t>Policy analysis: Prospective changes to prevailing wage levels and impacts on international hiring - AIP.ORG</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 10:25:11 GMT</t>
+          <t>Tue, 03 Feb 2026 20:36:56 GMT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxPZmtoXzg2VFNiNzVjVk1PSlJQSjB4TTBYbml0M0EwWkpLOWxtQUthcjBLU243Q2dXOXpQM3lONzE4RExHQU9qMFV6eGJrdDBvYzBNcUE3N0pGUzBKeEZvczFLV25ZZUg0YmlncjhCdFMxQ3A2UkpJcGZvZ29NbVNET3hMS0xZeHh5WDA4dEJnT0IzcDAyZXBWdDc5MWs2SWJoRTRFUVFXM0JKaWdXNTlNVktCTGJ4bXczVExDTmUyOUhiOEpJY3M5TGdFR3VBTmN2T01fTWczVzZyTUQ1YWZTVFlQUnhhcG9hQUJvT0FR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNVFZfVmlvaDZhVXNZMjBKSU9aUFFydWxKTFlyRFZ0eU1FOEg4WDY4eGdDQm9FdkJtUVJNQmw3am9DZDRqZHVBeVpMNjlaelo4TWhiR3h0RDBCcUU2V3U3TmVUWVh0bzJvdnpISC1fWE9kSE5fVmhWYmtCS293UXltMnJYWHFaOEhlME1BTW5jVTRfOHNMNl9iMS12clFHSnkzYjVzUFlUR2MwNG12T2FaYWtoMmxfcU9BaVJRdzNGcmZTa2JV?oc=5</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>1</v>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>46056.43415509259</v>
       </c>
     </row>
     <row r="7">
@@ -635,189 +611,171 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Friday's jobs report will be delayed because of the partial government shutdown - CNBC</t>
+          <t>BetMGM explicitly bans harassment of athletes in policy update - Yogonet</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 17:38:14 GMT</t>
+          <t>Tue, 03 Feb 2026 13:12:32 GMT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQb0k3ZUp6dmt3Q19RZDlUNG5hTVM5SjFpUlRLSXFyWlllWmlDMTdkeGs4VTdMaUJuMW9aeDllOEkwLXFXdTNzSlZpTV9NcFNocWl2UXRjUDJOWmJpOS0xR3BLajZyeW9nRzRxZThPaTUwM1NLYVdJZlVQY0pTaDdLVEVrb3V6WWgySjJJYklzQ2c0TzdTbWR1Z0trLXJqRXcyRzRzZHdJaFFLZ2JWcnp3cVFVRjJnZ9IBuwFBVV95cUxPT1NnRm0tYmVtdWgwZFhobzlZajhUYi1rUWtTa210VVJQbFpzWXJEWnU4NTMzdTZzUFNUaGpwVVRFc3VYTG4wanhIeWlsV3ZHRE0wdThVOVYyRXE2dU1mbnFyc2RhMVRjUkRnYWNMWnNXTXZFNDdEbUl2d0s3ZW56UTZ5aUFIa0Mtd0RRN2lzalZsUnJ6Tm4zYXlnQjFkQVRvX1JOY1FGVlJ3aFlZZDR0dnpzQWtzUGpwUFNN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxORjZNV0FPbUxXU2tKM1lqamYtXzJNV2dSU2djb3hSOF8zVzJUbHJ3UGE2eEV3aGNpNHJUZTJEUlFpNnhHVmFIWm93QThIcUJnSW5QMHhPbFA2Yk9zX0FweGhYR0VZRDI3V20wWkRta1BvZVlkZGNJb3I2dmFpZVQ4TlFjYzhJMFdRZjd4ZDFXZ283T1RqLWhKeDFLcHY1eDIwZlhSRzVZeHhPejJKZ3FiMExjUjhTQU96YnlodjV2aHE?oc=5</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>1</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>46055.73488425926</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Current_Affairs</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Migrant encounters at the U.S.-Mexico border are at their lowest level in more than 50 years - Pew Research Center</t>
+          <t>UK investigating first suspected breach of cyber sanctions - The Record from Recorded Future News</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 18:55:15 GMT</t>
+          <t>Tue, 03 Feb 2026 16:46:57 GMT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQcXUzZzRjaHZIb2g5VVJLZ1RvYktBWm1rdXBWTm45ZlBkbWNOdTRWOFlvWVlBQ1JYV1dXVkVIRWVwY0tmZ29LN0tWdUxEQktDZUlLRHcyaXN2QUFxZ3RRejUtR1NWMHJuX1dBalM2Q1VXMmFfMlUwYUwzTWItYTdRbkxyY2tiVVB4T2c2blR5X1hGWXBKbUttNjhYQUhnOGVhLWlEb091ZDBjcVZMVTg3a3IxSjBwVndTX1E2U0hrcFFFT2laWGdfNE9WeFpfR3ZjeWdKZjhhdktiQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQLVYxb29zZ3JfTnpfTHl1TGp3emJHQjNrR2ljZk9Zb2RsRG5mOFJGV0w3dnQxdW5BTjFlRzRnUEhmUjk0SFphWVBSeUo0bWZ4bWRzY3Z4R191QXY2QU1hTmJ1cGthVGwzM201TUtRc2NreUd5Q01HbnZjcHR5alNUQQ?oc=5</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>1</v>
-      </c>
-      <c r="G8" s="1" t="n">
-        <v>46055.78836805555</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Current_Affairs</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Government report highlights artificial intelligence gains in Kazakhstan - IntelliNews</t>
+          <t>Vale's transfer window round-up - Port Vale</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 15:37:20 GMT</t>
+          <t>Tue, 03 Feb 2026 20:02:05 GMT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxORGNzMl93aTlJdnFiczhjYnJNOXZMd3pNQlotRFRmS2RBd3hibUhieGlQTHR1MHY1eVpPQUtlVGEzM01KclZERFBPTkl5YU45X1JGTkNOaUZCTlhYdEVwT09OZFB5RURoUjN0TWxnbXk5V2J0dHJaQkc4VGVaZmttcGFwUWN2M3dUT2xYUGQyaFVYX0piM3J1NVFxWTZsWmtickt5dWJwMUpNWEZl?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE1QTGtyOVQ4Mm9Nc3NxZ3lfRGpxN3diUktMS2Fnc2RhYmdrRl9adEN1N0Q0c3dRUjhrQjVaZU5MOFF1RzFPRi1mYnFBTG8tQVlfYWdRVXh4R3FqQ3ZYVG1sSE5fWlVyUzNsWWdPeQ?oc=5</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>1</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>46055.65092592593</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Current_Affairs</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>J.P. Morgan Private Bank Releases 2026 Global Family Office Report - PR Newswire</t>
+          <t>Disco Bingo, exclusive port tours and a mini circus – what’s not to like about Love Immingham! - North East Lincolnshire Council</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 13:00:00 GMT</t>
+          <t>Tue, 03 Feb 2026 15:00:00 GMT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNNlVHdUt5N3NqaTY3UE1MNy1OWEhrQmxrREJBdGxORmtkU3g1U2E1Nl95UmhaaG8zRlhVRTZRTEgyd1JEVmZJRm1yUGgwcmt5ZWF0OWd6UHBqekdIdVEtZThXLTlRY0Z2SUo2R185OXJHWUNZMTdqNVhubHQwVXlZbHkwVjNnTThhTVRNTk1XbEFhbGttV0Q0SWZ6b205SGlxTFdLYnV2eGtxdVB5eGcybGNCbXpLcTdVUkMwMQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOZDNwUmkxbGNOdFpTdEFhaWNxa2Vmb2ZfcFZHZjBnZVc4OEZxRlkwN2hnTDlKQ2RqdW5VUEdLRm5na2dQeF9BSlZuRW5wTmlGNTBmQk0zeHlRbEZCVjh0bWJNU1dYWlZOSU9IT3ZWQmYzb0MwVVRYdXM1NHhnc0R6eXZnMWxKN190MU9DWGNnZUtJZ2l4YTdhdU42UTdZWHN6ODZLd3BZVXNPcE15YkZZQ0t4ZXpRVFo2?oc=5</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>1</v>
-      </c>
-      <c r="G10" s="1" t="n">
-        <v>46055.54166666666</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Current_Affairs</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Economy update: Seven Labubu stores to open in Britain after Keir Starmer's China visit - GB News</t>
+          <t>Tribunal upholds FCA sanctions against Banque Havilland but slashes fine - Funds Europe</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 14:01:53 GMT</t>
+          <t>Tue, 03 Feb 2026 16:07:30 GMT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE1kbUtPWWFJNVlGT2YyTU9OWEl0Y3F0SDQwWE9ELS1EXy1fd2xTQ3JNZEhiN0RENWg2RGxDZ2J6bGxBRGZ2NldxUkFUMFdRRlctMXZoY2R0UnB2RjhGSlM3cEJtOHB5TVBLRUhpbTlNdkhWNzA4SEtB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNZGpzd005RFUtY0tMaWRyWV9PdU1MWkJreDRKZ21lbi1yTUItSGItRXE5VDJLNURDQUNqUGpoTEVaaGtiWVMxUjJ0VV9NZFJha0s3aFdjOXlweUR5ckxlR29mUExKUzVydEU4VmJBMWtJb0E4eTdfbXBUYmFobzdHdDgtanp3R2gtZU9mUHdXMlZqdlpVNWRfZHU0ZUZEWGM?oc=5</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>1</v>
-      </c>
-      <c r="G11" s="1" t="n">
-        <v>46055.58464120371</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Current_Affairs</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Trump Live Updates: India Trade Deal, Partial Government Shutdown and More News - The New York Times</t>
+          <t>Fortinet: How to Build a Secure Digital Supply Chain - Supply Chain Digital</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 00:36:17 GMT</t>
+          <t>Tue, 03 Feb 2026 21:08:30 GMT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTE5EMXltcWRCdDFqc2owNmdaWVRqZTZhNDlod0hJeUdjdTJmb2M4cjR1dGpUQXZKNzBaYzFkNmFSR2p1TnNhTGp5bUNUS0lFSUk3ZncwZi1zT3ZaVWlrTW45YTVYSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNUmVQOFVwRTZ6MmdWTE5JdVhZZ1lWQV9hWHdDR3FTbzFWWEs2X1JOMDNzMjdfQkNpNndFQ0psSmVMbS1CNENOQXllbUk2MGJDUjRxVVpYb1lWdUZMcVVwdDFSalpLRVVXVklmUm9xTDJ6TXlpdTJ3MXRrSjdObnpseXRDWXo?oc=5</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>1</v>
-      </c>
-      <c r="G12" s="1" t="n">
-        <v>46056.02519675926</v>
       </c>
     </row>
     <row r="13">
@@ -833,24 +791,21 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hope and uncertainty as India and US strike long-delayed trade deal - BBC</t>
+          <t>Canada faces ICSID claim over Russia sanctions - Global Arbitration Review</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 06:29:43 GMT</t>
+          <t>Tue, 03 Feb 2026 22:09:45 GMT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBoRHZ3eDU2UERBbkZfcHFSSFdicTdPTFdCM2pMQjJORmV6TGFhT3poR2hzamVwN1V1QlF4UDIwMTFDT0gwZUJwb2EyX05Kd1VINnhEdU9fVDIyZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPSzRidXRjaDhZbF9wQmxWYkhYMEJkZlQxRkd6bUIxWHI1dEtZWFhNb29DR0c0VmFKaWo4Tm1tQy1uczAyMlV3YXJfVEc1c3FidXZKWGVwdGpCWlphUThEcUJ1cUZ5a2RBT1FfQ3pmeGtVbVhqUUNENDcwa25rN2NJUXRYZi1hWUNfQm9yUHNKZU83d1p4?oc=5</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>1</v>
-      </c>
-      <c r="G13" s="1" t="n">
-        <v>46056.27063657407</v>
       </c>
     </row>
     <row r="14">
@@ -866,24 +821,21 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Verdion extends €69m Danish development pipeline - Logistics Manager</t>
+          <t>Op Chirk: Over thirty arrested in Swansea and Neath Port Talbot - south-wales.police.uk</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 10:38:14 GMT</t>
+          <t>Tue, 03 Feb 2026 15:00:00 GMT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxORXZqU0V4V0wtZ3dmMTBaVG5wTjg5OGwyT0F3Y0pVbTc3a3Nsdm82cFNpakxIMmNoYmpEMGUyNGpzbVg4QWhWT0RfRjFFS1RsT19RVUl2aTRNS1FxcGFsekd0U1p0RGlBZTNUSEhKRVQ4cmtJeHFvMzBwZXF0ZEJFUExMVzg1bDhfcEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOeHByb0hvOHcySzBpb2liZl9zeUZGdmJLMTl2d0NIRnRYdnhpelNmV0Y5Y2NYS0VBQ1RhMXBrNFVTMXBqZTVaYUExb0pqR3h2NDZuSjFrRDlTZ0lZVmNpSVVlWWhieHFNVGU2em5tbU1QajBONmVQYzROdHFDR2ktWmxfbkZhemFEbFNzbGJzeTlZRzBnOUJiT1dFLUI0YVRLTjlha0xxcmROblpLOW9zT1NxSF9SQjQ1Vm5PWEIya3YwVGd6OHFHZU5ocFRXdw?oc=5</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>1</v>
-      </c>
-      <c r="G14" s="1" t="n">
-        <v>46056.44321759259</v>
       </c>
     </row>
     <row r="15">
@@ -899,24 +851,21 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AWS to Lead Supply Chain Intelligence Workshop at Procurement and Supply Chain LIVE: The Net Zero Summit 2026 - Yahoo Finance UK</t>
+          <t>What channel is Port Vale v AFC Wimbledon League One match on? TV coverage, live stream and kick-off time - Radio Times</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 10:18:00 GMT</t>
+          <t>Tue, 03 Feb 2026 14:50:13 GMT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQejBXZE80cXk3ekVEZGpNc1pkRHFscHdJQ3RYam04d0phWk11c2h2R1k0R0VWbzdVZGlZLVZVMVZ6S3ZzdUpmcFNKeVVHNHNqbm8xTV9SZ3dIVEJldGpMcDhKdXpZT2NEU0M2bmZwVlpoQUdfaDBSdXdJSEFSVF9kQ3VLa0ZPeVNHdUZF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNQm45aDF4R01VeW1FTDdRbS1Wb3pTWC1UcUNKdF94aHlWSU83ZEFtcjJKakRudkV6MnBtWEhCTmVCb2UxUkxBa0d1UXlUM2RReVNjNUZwQlZsRnJTaklMdE9tblBCVjB0QlFUODVwWjl2c0lWMWhVQ1hwNERwd1g2VDd3YUYtalk3UGpkeUJ5UExtNE52QmpQR19rZGo?oc=5</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>1</v>
-      </c>
-      <c r="G15" s="1" t="n">
-        <v>46056.42916666667</v>
       </c>
     </row>
     <row r="16">
@@ -932,24 +881,21 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>How NVIDIA is Mitigating Climate Based Supply Chain Risks - Supply Chain Digital Magazine</t>
+          <t>Deadline extended for 2026 Everywoman in Transport &amp; Logistics Awards - Fleet News</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 10:13:24 GMT</t>
+          <t>Tue, 03 Feb 2026 13:05:44 GMT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOdUx2RzlMcFRaU2JNUjRwMDUyTWZac3VhSVNGbVB6NkNjeFBaSTItRmxpd1V0ajRHSFR1N2wycnAwNkFKX0Q3dTVCT3pxczlQNnFpZXFGRFlvbkJLUFhJLXFIN0Nvd0tkbXhKcm5ScFdxbkZ4UFhpa2g5Q2VpcnRSZlVRZklPZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOSVk5MHZuNTRobjd2dWdXd2NtNFREXzcwbk9reklJRnRBNnp5RDBVUElzUnpFRTU0ZDF5aGp5WVktUmY0d2V5NlYzZmpqb0JjS05HQjZTRk05ZjhjczhDSXdjTHllR3pteWZXU2ljaHZQdUNDamFvV3ZKdHlyS2JROU5sZ1A0S2dmRVFVVEZUQzNySTNmaklIaDdRUllkN21FbEp4cHBxbw?oc=5</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>1</v>
-      </c>
-      <c r="G16" s="1" t="n">
-        <v>46056.42597222222</v>
       </c>
     </row>
     <row r="17">
@@ -965,24 +911,21 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NWSA volumes fall 5.5 per cent as tariffs disrupt trade flows - porttechnology.org</t>
+          <t>Report: Late Maycock winner seals three points at Port Vale - AFC Wimbledon</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 09:30:37 GMT</t>
+          <t>Tue, 03 Feb 2026 17:06:53 GMT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNMHdleGpacGdmZC1vMWNsbXhteVpEb1JpVzNmYXFPcTBQTjVfQ3BpWjE3WXRZVFVqLWNHMEUwRW5qWHB2UDFYbE9rdThWMUhiZGNVRlRuSHBBNEpSajVYN1ZteU93UFNpbkd4T1BPcUxkdkFGM1FXTlc5NVBsazBMUVFqUU1DYjAxVldZeUJCcjBCLVRRQllHWHgxcm9RcTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQWklEWlZuQmxKQjdwbndIRS1peE8tdEJDVkRqZVZkWWNmUUFPSGUybDNsRFRnSEVpTFhYeVpJZUxSQk5LM2hucnRwUFdnNE9sVlJjOUZpQmRsVmRrbENUR0FpX2hCbFRuZ3NMWnJGT2xocjhzX0ZGMGJXMnhmclc2bXdWY0tjd3E4NDFYeTF1TmpFRkh4VktSMUVzOWdBNzljUHI1WTFZcHpGVkdpRzA5dWItZU91TDQ?oc=5</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>1</v>
-      </c>
-      <c r="G17" s="1" t="n">
-        <v>46056.39626157407</v>
       </c>
     </row>
     <row r="18">
@@ -998,24 +941,21 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Solar PV Supply Chain Cost Tool: Methodology, results and analysis - International Renewable Energy Agency (IRENA)</t>
+          <t>How The Old Dominion Freight Line ODFL Story Is Shifting As Analysts Rework Expectations - Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 10:37:30 GMT</t>
+          <t>Wed, 04 Feb 2026 05:12:00 GMT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPMFRPNHhwTDdjcGpGSkZFMTg1Wjd4OTBUeWtxWGVGNzFFN2FvQTI5ei1ZbDZzdV9fMWRnTTJYWlJWa1duX1UtOXo1YlFVTGxkNlRyaFZaOEJKc3VFaHJaZFJBTlExbzdQRVYyUWxmQ0NyVmczNFFnQzZXSXFfYU5tS3lQYkx3dlowVTdnWlc5c1FjcHF3SFdreHNneHV5R2x5MHhuSXI3LXFTVVFj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOeC1zTXRDb1BBSElUMzhrNVEwSWZzemI3S2Vwd2NmaTNZSHk5cGc0NDh2UXR3M0I0WUdwZzBOOWY5eWxUdGFQc0gxX1F6ZmxVeTdlRU9sRC1nSVdXRlp2NWpXcmd0cWRBaHNPUVlsRG5WTkxvNEJreW42VHZYY1VhSE1lOHhSUQ?oc=5</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>1</v>
-      </c>
-      <c r="G18" s="1" t="n">
-        <v>46056.44270833334</v>
       </c>
     </row>
     <row r="19">
@@ -1031,24 +971,21 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CLIP Group – The New Logistics: Interview with CEO, Agnieszka Hipś - businessfocusmagazine.com</t>
+          <t>DNB shipping loan book rises in fourth quarter - Tradewinds News</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 09:58:48 GMT</t>
+          <t>Wed, 04 Feb 2026 07:06:25 GMT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPcjNqLTBRbjVqQXNVTmRGanZhdE1kLUxYdU82VzNiRnNJNy1ZU2JoRGhqdGdCTGFXZUUzc05xWFFQeHRTYkRvZEd1eTBPWkE5UWxLMUNxcGdDem9YQmJpRTdGb2pEb0RTcklnS1Q3eWp2RGpHRTBkUEh5Y1RYcU9jbGh6enFUQjVTRG45RXBITnZpbEd4TmU5anNHOF9ZQjdvVkkyOXk0eXFlWEwz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQajdGNldSRzk1V2E1cHVXM3J5NmdVRU9zcFp1NkRxdHYxQ3czUzVpZHY3RmhsNWh3aHZibUcxaGt6Y200c205QXJUUmZDUHhvNU1wN1ZjUXliQnZ4dm5DMV8zaGFQenlyV29PYzF6djJ2NzZjY2YwWTE1RzFXUHN4d29HTERSU3Y4UkZzMkQxeENtVEJsYk83aU9LcjZlZw?oc=5</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>1</v>
-      </c>
-      <c r="G19" s="1" t="n">
-        <v>46056.41583333333</v>
       </c>
     </row>
     <row r="20">
@@ -1064,24 +1001,21 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Luton Airport to Open Consolidation Centre - Logistics Business</t>
+          <t>Andre Gray is a Valiant! - Port Vale</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 09:46:19 GMT</t>
+          <t>Tue, 03 Feb 2026 08:36:50 GMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPOXZQMk1HcDBzU19JWU91YjdaQk5heFJWekR2WEFyNGFpSVNzOFRXT2lfSHQzaHI0RmUxRjZnVHR4aTlfQTI4OTdwVXJsaWtmQ3RHY1U4cWtQdC1yRy1uOVpmRGVONkVJWEtoS21fM2oxN1hJeWF2dmFjcnFYV0llM215Y0ZXY1lXbzNjdHZkbzhBd2VNOEdwMDFpZS1HZTE3N054V0xON2Z4QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTFBmTTI3Q01qcGdCYjR1Qklwa3JNNTNNUlJ0c0VNeGhQMTdVVmVYbGg0aEgxT0x2VDdlcnNLOEYtMDg0THU4MHlCcmRObDNfcnhabjJBTXQzNFdqVm5wWnNfUA?oc=5</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>1</v>
-      </c>
-      <c r="G20" s="1" t="n">
-        <v>46056.40716435185</v>
       </c>
     </row>
     <row r="21">
@@ -1097,24 +1031,21 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>People 'avoid St Peter Port' because of accessibility issues - BBC</t>
+          <t>What do EVITA Trials Mean for DP World's Decarbonisation? - Supply Chain Digital</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 06:15:03 GMT</t>
+          <t>Tue, 03 Feb 2026 20:36:12 GMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTFA5QlNNU2t0Q1JSdmItVU4wUzhEZ2JldGZWbFZLTEVlTG9vM0s0YmRqVndycGJ6RFg5R1pUbXRwT2dXSkg0NXJGZDI3SlM0SXl6RnNSRnczckVsOVdO0gFiQVVfeXFMTVBBOHRyZC1DajNSMUlkLVpma3haLW9vNkg1dW5scHJ5YXNFQ1F5NzVJaGl1YWg3Y3lEcEZDOHZoRlh4UU4xTWNQQmdOcHBYbjRoN21oRnZJdXNaYndaTmJPV1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9tRW4wWlhVWlQwdzRYcUpRdS1OSkwtUWh5VFBiN3F3cURlU1BiTjliMFFUVWx1eG5jclBKSE5Ibk1GRFZEaks2VGd0VVdaLXRzeUNleGRqMWZTbUJfcDZxQUp3WjA1a1pVd2lKSjlwSG1CM3lJSWpFVk80Snhadw?oc=5</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>1</v>
-      </c>
-      <c r="G21" s="1" t="n">
-        <v>46056.26045138889</v>
       </c>
     </row>
     <row r="22">
@@ -1130,24 +1061,21 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pharma strategies shift amid tariffs, pricing reforms, and US manufacturing pressure - itij.com</t>
+          <t>Will Cheaper LNG Reshape Europe's Supply Chain Strategy? - Supply Chain Digital</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 08:06:18 GMT</t>
+          <t>Tue, 03 Feb 2026 16:59:23 GMT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNbWJCbjhfbUZDanY0Si1vMHZ1Q0NOMTdLcUFOaFNNRXVua1lLdU1GY1BvaTVEYzY1WXRiZ2c4b3NuOERISDFlLWpwLTFkNGttajBUekVXTjBFQnBHdUF1NkQyQ25HOU1QQnBOVXhhSTcyWDVkMWxfckVOSE95WWRQM1V2RGFRU2tQZVBSVU03YTNZUFZELTVPS2FCNUpVQU9fSFFxREg5d1JmU2lXZTYyRmkwNHhxQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOSTFGNkZPaGZVMXlYWFh3NEw0UXdvaWhGMWZ6UjJkdFM0bll1Tmd1OEZ4Y094NDdMLUt2dGdHQVdCY0s4WkFaREVZS2JSdzcxTmNLSHNPNEFidW4wWWhoU3djVXF3WnNaU2k4MjNvYVdLRWZoUjdGdURlSDNzY3NMZFhpVENXem8zUjlCSFl3?oc=5</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>1</v>
-      </c>
-      <c r="G22" s="1" t="n">
-        <v>46056.33770833333</v>
       </c>
     </row>
     <row r="23">
@@ -1163,24 +1091,21 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Freight and ferries cancelled for bad weather and tides - Shetland Times</t>
+          <t>Sumsub Partners with Fireblocks to Ensure Travel Rule Compliance - Finovate</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 09:31:00 GMT</t>
+          <t>Tue, 03 Feb 2026 22:27:00 GMT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNeGZQd1V5TVJnMW1BZWFpSjdUSElTNjYtWmZuN2JfVDVRSTB6NThsUk5ISTIwZ2JhMVdfR2JVa2YzQVMzTWFNNGI5d0c0MmtqTVNZTExMRjJzVTdRNE93bUs3YWU2Y01Kb1Z5aXlWc09oNEFndEJ2REhoa0JvcnZZcjNfMFpuMXpmaW01SElqWFNsMEpzd3EwM0hTRWl4c19kbEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQOUtVbXppa0hOcUhPTmR4Nm5RWDJtdWRaVnNyTERVdjkwT0NnRE9ObDl5aWRtQnhIZ1JxaG4tOUhPMFhrLXg3d21Ga1pZaE80SVZXdEl0MHViYUNiLXVCYTM5U2pDSmxUOFFad01yZkstSTA0S2Y4czEwSGx3dEQxT3Z3aFRiVGlQcWZxd3lnUQ?oc=5</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>1</v>
-      </c>
-      <c r="G23" s="1" t="n">
-        <v>46056.39652777778</v>
       </c>
     </row>
     <row r="24">
@@ -1196,24 +1121,21 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Posidonia turns into a month-long shipping marathon - Splash247</t>
+          <t>Stiffening European sanctions against the Russian oil trade - Brookings</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 09:57:45 GMT</t>
+          <t>Tue, 03 Feb 2026 16:57:39 GMT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFBFYTFaZ2VIMFNPR3R0bnJjWFZUWHpwWmwydWItM0Z1T09ESy1iN1ZINF9iNzlncE84VmpwYmhWaUxhV0NYTlAwX2pHaWVrMWhkVG9yUFdWekZwUFVEZmlSc1h4MVhnVEpaRjB5RzVJTVF5bHJ0cENmRDVGLXVqTDg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQWlNPcHQ3bkY1alBCeDF6V2FKTzgyZlY5dVNiZjdja2Fnb0RoZThSUHpDaDRKRVQxaTY1U0pKbWU2UHBCU2NnQXd1NVFWRHpmQ1JpWTdhb0w5RVJLN0VPMGFJRU5xclhVaEt3OUNuY1hzRk50bDlXMmVIZ0VTWHAwM2I0Z1ZwM2hIaGl3OEJsUlJVLUVoekhuNl8wYw?oc=5</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>1</v>
-      </c>
-      <c r="G24" s="1" t="n">
-        <v>46056.41510416667</v>
       </c>
     </row>
     <row r="25">
@@ -1229,24 +1151,21 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Port of Rotterdam biofuels review and outlook for year ahead - Biofuels International</t>
+          <t>P&amp;O Cruises says port fee commission shift brings it 'in line with industry practice' - Travel Weekly - Home</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 09:13:00 GMT</t>
+          <t>Tue, 03 Feb 2026 15:39:00 GMT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNLW85M09HVGJMTHN6VW9qVnptdFJQTjdOb1A3b3JjTHNqNk5PYXBvenR1TEl5WGJGd1o5ODdpcmo0cFJuOXRlQjZCQjN1ZG9zTjBQRTU1TDVpLWM3MHZreHNNVVp4aHl1VzcyVEUydEE0SzJWTGZncjg3MWNpNHBiM09lZUwzU1hnSFFMbDFFRzA4Tm9uY0xR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNRjA0bjhCMDZERDZCSjBzNWc5N2dHWFN0eFI0b2ZVcm5fZE9sOU5PWWpnOFJYQjJqdUZEZGU2ZGtzWE9jWFhPdFpRa2lHa0RPVE9OdTNiR1FqNjdLVl9MaVZxb0dCQW95dmN5QVFKVk9Mdkd5MmNXNGs5dkFRWXJlVklkQS0teFpQTWd3dFhDUWpqa3UyLVFIVE9JS0JuM0l0OXNhejF3YjhnaXNJN205Tlg0ZXo?oc=5</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>1</v>
-      </c>
-      <c r="G25" s="1" t="n">
-        <v>46056.38402777778</v>
       </c>
     </row>
     <row r="26">
@@ -1262,24 +1181,21 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Arvato opens new bonded warehouse in Türkiye - Logistics Manager</t>
+          <t>DP World's EVITA Trial: Decarbonising Logistics with Trucks - Sustainability Magazine</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 10:20:12 GMT</t>
+          <t>Tue, 03 Feb 2026 17:38:03 GMT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxPR19kY2ZmQkxUbmZDTWxVMnBoZHdkVXdsMGZVWmNwOVdNNHpCYWlsR1RPakthMGRpRWV1aWE3aXA5Unl0c0loRml2X08wNlNveGJzSGdNcVVQSkhQb3YwaF9YeU0xUjEyYTFPVDd3aGp2cVB4eWIwMVRrWWlVYmU5RUhaMGM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNSjF0OVBpMWVsWkFoUDZwdUhIYk9HWmVlUmM0ZHgzTnlqQWdCc1BYWi1aaDd3MW16cUpsVXc3RnMxdkJSMEprcEpTbUpzVzdyZFdIOHVySmVrZzE3My0tMlkySHU5Ym80SWhGRGlTTTFZVmdSeHYtcFdNOFZHeHd6SE01LXI2cFRuX1FtemxwMA?oc=5</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>1</v>
-      </c>
-      <c r="G26" s="1" t="n">
-        <v>46056.43069444445</v>
       </c>
     </row>
     <row r="27">
@@ -1295,24 +1211,21 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>One Month to Go: Sustainability LIVE and Procurement &amp; Supply Chain LIVE 2026 - Yahoo Finance UK</t>
+          <t>WADA provides update on the compliance status of the Comité National Lutte Antidopage de Côte d'Ivoire - World Anti Doping Agency</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 09:15:00 GMT</t>
+          <t>Tue, 03 Feb 2026 19:28:29 GMT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNMlpfR21lMDBXRUh6bGE0YWplU1kzRnpqNlh1ejZYVTVTSnBmenpBTHgxcW10bktxMkY5Vmw0MmNabl9MaGNaVWh6cGdkQ3Q3eFZFY1drOXo2UEVZTFVNX3JDYW5uNmxKZmNyTU1yN0pCbXNrajYwV3JDbkF4RWd0M1RYdnhEa1lQYnJ3UjdNMDFNX1dl?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNRG1BOFVWVGdHVHZVY3AyUTNIejFZTm1ORUlyWFRIdUhmTmZvc19TTTZVS3B5RDJ3X3VDb095ZWRvMXBjWF9FWmhQUEI3LW1hTkUyN1NjS0ZWYjdXRlZHaU5ialNodkxJUGUwMmhCLVhySTY0MkFrQi1aM21UaFpaRS1mZGNCQy13aVB4ZTVleFlyZVZpdGN5U1E2eHpCTE5sWWhEM2JPYWQ4V0x2R1dVZFNhZ1ZKY0FrLUYzWg?oc=5</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>1</v>
-      </c>
-      <c r="G27" s="1" t="n">
-        <v>46056.38541666666</v>
       </c>
     </row>
     <row r="28">
@@ -1328,24 +1241,21 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Mexico’s busiest container port Contecon Manzanillo surpasses 12M TEUs — SMI DIGITAL - shipmanagementinternational.com</t>
+          <t>The Myth That Foreigners Pay Our Tariffs - The Daily Economy</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 10:27:25 GMT</t>
+          <t>Tue, 03 Feb 2026 11:31:00 GMT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxQdFBlTlFaRmxScmowY2wwM2RMYXE5WmpCNkUwSWR3MnVUOUVvUWlFMzZGR0ZSRmgtWVVLYVRkcmFwZnB2TFVYeklPcUZTUU1RRWtGVTRPc2JzU3Myd05Ua25iZ1Ayemt6QUlMQ1ZycnBDSDVEYjVUZ0hieGZDd3ptZzZjRVFiUWRIM09CQ2JVcHpwb1JxTUs3Yy12Y1E0bFZGWXdfSEVleWdjOVBvenB3bXdfMFgxNFVYNE1sajFLTm51S0Ryd0JhTDNYUDJSMGJwLUk1clFLRnVrZ05KcTBrTC00MnZwWGFkaklLOElacUJJLXRnLS02MkgwMUl6QWU1UUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxOSWNTSWVzOWxGeHJfTGkyaTgxcy03dEM3VTJMZ2g2d1F2ckZGQkwwSlJ4NXBHcHZvWHZFaUwxM0hyZC16X3ZYSVdoU3hNX1gxMkUxa1NqRFo1X3YzMFVmUEhpMC1jOTVjZnJobUw3dUxPcUpoLWNGN0lfUWZTMGg0S010Yw?oc=5</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>1</v>
-      </c>
-      <c r="G28" s="1" t="n">
-        <v>46056.43570601852</v>
       </c>
     </row>
     <row r="29">
@@ -1361,24 +1271,21 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Switzerland seeks EU exemption from new steel tariffs - EUROMETAL</t>
+          <t>CUBA: Oil sanctions will hit the poorest and weakest warn bishops | Aid to the Church in Need - Aid to the Church in Need</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 07:23:51 GMT</t>
+          <t>Tue, 03 Feb 2026 16:29:29 GMT</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQQWc0d1hRVWZ0dHFHYkR6bTlIa09BNDRyUXNoR2RtN3A3RndyZmR3R09laWVEWVg2dkNGSHUyWEVhUEdJb0F5UWFpdDFCcWNfQkMzSnFpQkRaUEFwODhteE90N1Q5UzRpMS1GMjlCNXRqOEpST04zS3JqSzZQWFpIY0dR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQWlhkWkN4dzFMUjdOaU5FOURSaEpyQnBhQURFZjV2MmdtLXdUdVljaXRnOGloVnYxMm1iYTZrcG9xMlhKdXZrMVdyWHFiNGhlN3VlZDJvSFN6bHppNEc5OGVqRXlYX3dKckdoWVJtZjBVZ1dleTFOczB4MnNNWGl4TEU3eDByRXYzNF9IekFKRHhzdGpFcHF5dFJn?oc=5</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>1</v>
-      </c>
-      <c r="G29" s="1" t="n">
-        <v>46056.30822916667</v>
       </c>
     </row>
     <row r="30">
@@ -1394,24 +1301,21 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Modi liberalises Indian tariffs much to chagrin of the left - thecanary.co</t>
+          <t>Massive Parkside regeneration scheme approved - business-live.co.uk</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 21:23:15 GMT</t>
+          <t>Wed, 04 Feb 2026 07:21:00 GMT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNQ05aX2phLTUtaURXdDB6UlZuZU9EWlJXX0s3MTFacURQZnZIdF9tRTI2T0MyOGhIdXJNVC1TbGJNcFBZZkw1T3FrSWtXaHgzcEtIWGJIVW01VTd3dXd5Z3NSbEJKZjQ0M1BEU3A4VXZDaGxOd2JsYzFrNndlV01oQnlqcWlwRzBkTTBkWHRiekxPTFZK?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOLW1wZ2pQdDJPR0lRWWJBSTNzbDlOdXNNUGdxdE9Lc1FoczRNY0Frcl92TGxMQW4wOTdFSjNKMVhQQTBZcS1YZ3hfblZFTWdvd29Tb0xCdExUSXdiakRXYmp3VVJkcDIyWG1oTzFfSHpndlkyVDVCZ01VTFlBSjYwZ0pnRmRhVGVfd3FQQ3pPM01ybHd1TnhJX3BfdTdXZ9IBowFBVV95cUxOU3pxeEx5WTdVNmExVEhXeTQ4alNXYS1OUkNQWFJDUW8waVJQNVRTQ3hudjNNTUtubW5sMWtPVV9VbkQzN3o3X0dFelZveG5leVlkZm1YQkZjb2RoLUY0S19tR1k3SUdmUGZvck9ZNFlyU28xek5YQXlEZWRrSWJZNEtJdHVfeUlDSjc5OW44MDNJX1M1NTFKUTNHZnBkTjVOS1JV?oc=5</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>1</v>
-      </c>
-      <c r="G30" s="1" t="n">
-        <v>46055.89114583333</v>
       </c>
     </row>
     <row r="31">
@@ -1427,24 +1331,21 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MP asks government about freight-only line amid 'closure by stealth' concerns - Rail Magazine</t>
+          <t>Two arrested over attempted sabotage of German naval vessels - BBC</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 05:02:02 GMT</t>
+          <t>Tue, 03 Feb 2026 16:30:11 GMT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPc2NSUVZaTlRTVXJBNDNTUFZsazBhdFcxZlI0dXZkSGwzbVBvQ19ybndNamd1Y1NwSXpXTUhJTUNVYllvTzJtWXpLdjNkRmxWdk9uS2hGMlFWSkloLWszM29tdEp4RW5LbmZoS21hb3ZXN05tQnNJcDJHOEp3OXZ5aGJRWERva19HelJJb0RTUUptUklyS2FDZ0xrUm1Yd09Ra0JWQmVObzRKYVFK?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5vUVFxb0Q0Sm9Zdzh4NllUVW9VRllRSEZZVGlSNzZFbzlrUmgtWEpQYnpOeHZHSVZxbnBuNzNjWHU0ZDlpR3I2bzRkenNPMXU1X0ZhaFdFQ0MtZw?oc=5</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>1</v>
-      </c>
-      <c r="G31" s="1" t="n">
-        <v>46056.20974537037</v>
       </c>
     </row>
     <row r="32">
@@ -1460,24 +1361,21 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>WARE deploys new WMS at Knowsley distribution centre - Logistics Manager</t>
+          <t>CK Hutchison launches arbitration over Panama Canal ports contract ruling - Reuters</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 09:14:34 GMT</t>
+          <t>Wed, 04 Feb 2026 00:41:00 GMT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxObllXbnMtNWFYUlljSXpZZ0psUDNsSnVTZ2FKUmk3R3FnMXNINmdCLU1YLXpDS1JHbHhrLTZkNUF4VS1fUjFBazdzSWt0Y0Y3bWg3REFJRXZ5R0tzMkRQZE9FWktBM2Z4cWhrOFA2bHFzNGlDSXVwV1FibDRkR0NpdjNQakI0ME9ITGVv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNZzBvWW5tSmtDbmZ5MG5RY0xNZ05lRHh0R1VLeF95VTVPbTNNQUhmcXQ1QjN4NEVYMGJra1pXcFZaR0FUYWNhSjNqMHg5TVJtc3RHak9WSldydkNpQ2Q0c0MzcVpMLWtYZk5PemlEZHZEalJqS2d1cUtOdzNqQkM4WWhad2FiNzVrMW80NmozT2lnaTJuSnM1M0twY3NnYU00UFJLWU1mdEg0VFdlRlNvbFBhdGp4bWNNRVBpR19MaGswaFU?oc=5</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>1</v>
-      </c>
-      <c r="G32" s="1" t="n">
-        <v>46056.38511574074</v>
       </c>
     </row>
     <row r="33">
@@ -1493,24 +1391,21 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Klaipėda Port launches first phase of southern expansion - porttechnology.org</t>
+          <t>Johnnie Jackson on Port Vale, Osman Foyo &amp; our supporters - AFC Wimbledon</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 10:00:37 GMT</t>
+          <t>Tue, 03 Feb 2026 11:23:13 GMT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQUXZma1hCdHQxU20zRVFsUDU1UVBmYlBVMU5qZm5Pb0NxNzNtSnl0Q0dSMGp1NDJlbzdqRUxUT201UTFfRTd4RmhKU1paV0lPN2FFUTBkTEpCNkxlcFR2QUhRS3hRM2w1SjE1WmRCRjRXWUhmeUNKVWxpWmhQR0hodkNZemdwWWhLaWVYZWJuYk01dXVnWkVvNw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNV09XdFc4SjRBREhVS3E0SVN4elRlNlZacVVvU3hjRE5zTEVuUzllUm9tY29KanpoSHRkWEluLVNOMGRqX3NwTUE3WTRKazUyUVRDS1Bfd2VqNmtYSTZZdURUV1Z6ZU1LYlNUYTBOc1hKVTVqbndHSlFHZU5kUU5TSEdqTGQwRm1vYkFhTXM2RXlQOG11VjFVcWM3SkZvNzlzeHcybmlZOVpkX2p5WEhKTVNB?oc=5</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>1</v>
-      </c>
-      <c r="G33" s="1" t="n">
-        <v>46056.41709490741</v>
       </c>
     </row>
     <row r="34">
@@ -1526,24 +1421,21 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>How Investors Are Reacting To Realty Income (O) Expanding Into Global Logistics With GIC Partnership - Yahoo Finance UK</t>
+          <t>The Trump-Modi Trade Deal Won’t Magically Restore U.S.-India Trust - Carnegie Endowment for International Peace</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 07:09:00 GMT</t>
+          <t>Tue, 03 Feb 2026 21:24:07 GMT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOYVBjTlNZa2pDYS1iQ1pKXzVZYy10UkFZX2FqbWszNGloMlpRSEdoSDRXMUNaY21BeDRvWTlwNkx3ZXFTWVYtcnR4V05BSl9uY1J2X2YxUndPYktIZFNObGg1ekN5dXAtRUJrNmVrUmFINWZYaVo3bFJxQjZJb3VSMEItRlNURURhZnNz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQOXNLeDh5cmFqWjlfSUNmTEVwOTA5THBMSjRmcmc3TEoxN2lnaWk3Vk13WEFsWGZDTmlXLVB6OXZiMjVxYm90YVlNSnBNbGFUMm05V3l1VXJkeHlkTkdWNlh3bXA5bzVDZXNndEpqRmM0VkRVLWZUenVlN0dwVzFaQVlTcVRmUzJtUXItR2VhM0xKdG5yT0RUelJBeDNfd2c?oc=5</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>1</v>
-      </c>
-      <c r="G34" s="1" t="n">
-        <v>46056.29791666667</v>
       </c>
     </row>
     <row r="35">
@@ -1559,24 +1451,21 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Port of Gothenburg posts record 934,000 TEUs in 2025 - porttechnology.org</t>
+          <t>Around 100 flats on 'prime' Port Glasgow site to be demolished after delays - Yahoo News UK</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 09:15:36 GMT</t>
+          <t>Wed, 04 Feb 2026 06:30:00 GMT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPVktIaHp6aUtXU01MQ2R1YjBhTDcyUEx1dmRGOVZ5NDNsQTNTYUdkQU5VUERNdHdvUk1JX2hZQkplTDJISUpxUXZjNFh5d1ZicXVIRWRObXh1UEp5ZE1qYkthT2xHQkJwcDYwQlh2OXZsbGh2OUZzTkJ6Y0I5VWIxUW5yTTJHdjJ3T0pOdUxmeUJIdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE92WE44aFUzbURfbkF0d3Iwd0J3WUx1LXlRc3ZOenhTZ2xRVTlnTE12SXl3VlZKQnlQUUZ5VWttLUxzZlpjZjZhUDRGWGdOemZYQ1l3M0VKekNiZ216Nkg2Q2tvS0FiQTlyUXI0bU5HQzMwd0ZNQnNR?oc=5</t>
         </is>
       </c>
       <c r="F35" t="n">
         <v>1</v>
-      </c>
-      <c r="G35" s="1" t="n">
-        <v>46056.38583333333</v>
       </c>
     </row>
     <row r="36">
@@ -1592,24 +1481,21 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AD Ports signs HoT to develop Matadi Port terminal - porttechnology.org</t>
+          <t>Yusen Logistics and AGL Establish Strategic Joint Venture in Kenya - LM - Logistics Manager</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 09:51:01 GMT</t>
+          <t>Wed, 04 Feb 2026 07:44:04 GMT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOOFdZTTdISXBhRUZwNU1fSVlpdUJkUmpGOU9oR2hHTkhoN2lMdTJRSVF5QTNKTlhNQXJ4MVVlVUs5UWNmQTdwNkRIWlNPTElfaTFYZVVpemprYXhkYUdjNW5xZm05NFFXa3BjUUVwSFI3QzlIZGlBUzdmVWNQM2ZaTmw4U3dkYmNhU3BzM3h4Q2o?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOc2JUNGw5NGF1dC1TbWE4ZnpfZWVrSmhDeG5nWWpIcDdlck9pTlBaaGJyYlNNN3dKWHo4T2x4dV90WXItTzl2emZfZEd2QU5oLWhYeVlONDg3QWpvdEVrNUhYUENFQTlfQTZOZjRpWG9TNDRmVTBJVERlQUNmc09hWnRxbVRaQVJiYmVNTFk3RFpFSUk0RE1fV2JLVHZ3UQ?oc=5</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>1</v>
-      </c>
-      <c r="G36" s="1" t="n">
-        <v>46056.41042824074</v>
       </c>
     </row>
     <row r="37">
@@ -1625,24 +1511,21 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>INTERCARGO Annual Review: Key trends shaping dry bulk shipping in 2025 - safety4sea</t>
+          <t>Five critical compliance deadlines food and beverage businesses must prioritise - Lexology</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 10:12:14 GMT</t>
+          <t>Wed, 04 Feb 2026 03:31:22 GMT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPdjJnUjk5RjgyMXBlMmFPSDF1MTBQQ1ZaMnhQSHl3SnJGNVdVTnVTMkxMa0ZRc2ViVkRCQ040RFM1VVlrNDVPbDlnTmN4aUtpcHE5M2FaekJpSTk5cFRGQlFCc3RMS2VsQ0lHMkdDcTNmeXVzbjV6MGNhWlZpSUY5Tnp1aEk5ZkxlV2FfQkk2cVdvY2pELXF3Ng?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOd2lPX3RCV25scjFGMmNhcHRwUEU1VUVkeFFqNkJhQk10cU9aREI3U0VleFMxNi1lZnl0SEN6dDFpakRpZlFoV2hWcWZNM1phejBNSlpYcnpzOV9QZFFFTG52SWFLVEhGZFlzTWlKSVVXaWI4RV8yYjlxbnhXRmNoenZpelVIdGU0R2NWcENXRVZqcDdXd3k4Z1pxd3A1TmF3dmR1TllUTlpLREZjZHRPTWRFalJFV0E?oc=5</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>1</v>
-      </c>
-      <c r="G37" s="1" t="n">
-        <v>46056.42516203703</v>
       </c>
     </row>
     <row r="38">
@@ -1658,24 +1541,21 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dublin SafePort shortlisted for Innovation in Safety Award - porttechnology.org</t>
+          <t>Shipping Firms Face Tough 2026 as Reopening of Red Sea Looms - Bloomberg.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 08:50:36 GMT</t>
+          <t>Wed, 04 Feb 2026 05:25:00 GMT</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPd0kyWGdZdWxZUjBZZVRKTS1Wc3ZZMnpManRFamg5RVpKTVZ1WnhmYk01NENSMXBmZHI2MUs0M1RiUm1OTHhxbEF1bzFYM01iVkp6cXc4OHdNSzFya05LX3hLc00yRkRqb0d5Yi1uMHhuMWFmNnZuUzdsZFJkWExTTlRCbkpqZXRqcHltYjhvcGdyQnhmVGxyR0t1aw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQb0M3ZUhwNzNlN0JLODhUMUdFd1ZIa05OSzlXMndOWTBlREZIdmRHeF9NM0pEOHJEQlp1VXpQNVU3MEJJMnV6dm1LaXNER0dtSXJVYWhqd0hHc2QxRFdKZVJSckRDQmhJWjk4SmFtZW53MEVzRXZMV0h1aGJpckd2bjJFUHJWalc3SFNqQUtJRVVVZEgxYU1SWW9SQVBXQVp4eDI1ZUxSTEVOd2t4R21YRg?oc=5</t>
         </is>
       </c>
       <c r="F38" t="n">
         <v>1</v>
-      </c>
-      <c r="G38" s="1" t="n">
-        <v>46056.36847222222</v>
       </c>
     </row>
     <row r="39">
@@ -1691,24 +1571,21 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Count down to CMA Shipping 2026 - Seatrade Maritime News</t>
+          <t>AD Ports Group secures $115m financing for terminal development in Egypt - Baird Maritime</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 10:24:11 GMT</t>
+          <t>Wed, 04 Feb 2026 05:20:30 GMT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPcmJlZ2FvT0JMU0VVU3RPUDVVTGVZY3RoOFFYZXdHSUpubVFraGx6TEdZdnAyQWlXaHlrV3FjVmVmTVZEYVJpdXVMa09LS1lnMzZldlRmdDlyTlBEamlkYXd0Sm5UNlY0SEpVY29ValpxSjJFNHNsXzQ0cW11azY0S0EtMW5xUEtFZTcyWFcwMTdsZ3lhRlEtWUNLMmxuOFE5cy1QNnV3dzJ6U3pJUEo2WlRmVDM5M04xSXAtWmxXbHQ4LWhaVUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPMFZzd3VmSldrcTZ4aHlicmtXOGR2QnN1dHhxSGVYcUZrV2hSdXBoMmdHWUxZTXlSU2djZzRVTTQyODZtY3JIN0FEckFtd3dsSzBjbHhuMTlfUl9tQUxOYjZNS1ZPaWJsSXExQUJaVlltYTl5QzJBTVRLSEF4TVVCV2JnMDREWlI5T0xDVjd2SE5aeUVObTZRSXdKZDBkdmYxSTJ5bXNhdWpYYWc0UEszb0dDamhvZWPSAcQBQVVfeXFMT3U1djFaZS0xbE12cU9rN3lPUHdnWXdyRlBqWkltRXpkY2NzWHY2WlZQeW4wWVFjQktqbm5PZlRSamJPZWpXVHZYZkFXUERZN1psaUJ1dGJ0STM5SGxLOWkwNkVnMEt3dGE1bVVmR2RLMW9MbGRBVnFSTEplcjNIQjk1V1B0bm5LV3AtX3B1N2o4OWpkbE01eWs5OVNNNTMzRWJZMVJ3QjdOWnlCQ0RqV2pCY2lzN2t3NXcwSmJBQzB4VWN4Zg?oc=5</t>
         </is>
       </c>
       <c r="F39" t="n">
         <v>1</v>
-      </c>
-      <c r="G39" s="1" t="n">
-        <v>46056.43346064815</v>
       </c>
     </row>
     <row r="40">
@@ -1724,24 +1601,21 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Saudi’s Viero Raises USD 1.2M to Scale Fleet &amp; Logistics Platform - waya.media</t>
+          <t>GXO Logistics (GXO) Expected to Beat Earnings Estimates: Should You Buy? - Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 10:28:06 GMT</t>
+          <t>Tue, 03 Feb 2026 15:00:06 GMT</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOckwySXljUHRGZTZLdW94SU9Rd1JMajFtMWZtSWxkeWpWcEx3b2h4UGRMZkNXcmpVTEF4azRsUWR0dUNDSS1hUjVFdU5hQUxydlFFRVJ1MTRqYk51dC1waFQ0cDhQUzR5UkV5bHFUc3hzZ2ZweXUwOTNfWHYzTDVnMEljeVA2amZqUlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxOMGZacEpxT1BRYVZZWHJhZVAyMFFqSEhqOUJEQlAwcTcwRXVETm9tQmpsZG1XaGZyMV9TQ0dZREV2VF92VWc0OHJqMVJBRllRODZlTzlIS2hkdzVoZURjS2Z3T0ItNVBCaU4wNHE1eTRidGd6SVZMLWlJb1BpMHZjbUNPU3NwOWc?oc=5</t>
         </is>
       </c>
       <c r="F40" t="n">
         <v>1</v>
-      </c>
-      <c r="G40" s="1" t="n">
-        <v>46056.43618055555</v>
       </c>
     </row>
     <row r="41">
@@ -1757,24 +1631,21 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Stephenson Harwood LLP advises Hellenic Dry Bulk Ventures on the sale of vessels to Bangladesh Shipping Corporation - Stephenson Harwood</t>
+          <t>HighBrook agrees recap of €300m Dutch logistics portfolio - Green Street News</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 08:12:07 GMT</t>
+          <t>Tue, 03 Feb 2026 15:19:06 GMT</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxPYnAxMFVPemZlVHJNWFo3SWQ4QWFSTGMxYmpERnRpUmNHZk1GZDBPRnFHVGM5VFROWDc2M29ERWNZRkN0Y1EtcGlvNUFlZEdEN1BKS090UGtFSks1TGp3OVFBeEhYczQyRE5oNDBHREZqQVA3R3VkamR3ZUE1azh2TVRfOHdhNzJjaUlKdEdtSmtWWmRNd05rY3NEcHBUY3pJaWFkZ0FDS2pHQkRnQk9PaXVKMTM1cU5HaWNBMnJFQUd1TmVCZFVHU1NyNnk4WWRfYXYyZl9wY3J0eVFldDc4VUY3bS1zREI0Q09N?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPNi1ISjBfR0ozQWl0VGY0REZOUUU0Z0ZYQzRUeGZ6ZV9FSktlWjdwcVROMkRjQXI0Wmc0Q2xvYXRkd3BLck83cWZIWGVGOWxMWU40VENwb0w0R1Zpb1E4SHNtLThKa2dkOUVXRkRaMGJ3b24tU2huY05iWXlmSlNBVWg4LWtiRWdwcWg3U0ZEUkxnY1R6bDFLaTB3?oc=5</t>
         </is>
       </c>
       <c r="F41" t="n">
         <v>1</v>
-      </c>
-      <c r="G41" s="1" t="n">
-        <v>46056.34174768518</v>
       </c>
     </row>
     <row r="42">
@@ -1790,24 +1661,21 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Grade II listed bridge could reconnect Port Talbot communities - Wales 247</t>
+          <t>What’s next: your complete guide to logistics trends for 2026 - Maersk</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 06:27:57 GMT</t>
+          <t>Tue, 03 Feb 2026 13:38:45 GMT</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOT1JCUC1SQkRNbkhnY2x3RFRsVFFkekI3N2lqaGVLZHY3b2dfUzY5SlpKWnQ4TUpNWHdxeU5hUUtVV2h3eEFDamZCOHZ4anc3bXZ3TFFxVmNZR2NzVjNTb28xODlkbG1BSmZYenFKcTllanhOSXdmUzc1WE1pcUc1aXNILWFUY3JTbkdMRUFFeHkzQ1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQX044eGlSSEpLTFJpbUdhdlVaaWlmS3BUaXI1VWpKMnU1MXNjMDlVRHZBXzJwOEwwSi00WUE0NnJMX21CbEp2b3RMVkd5WUNiX2N5U0xSUmJXVkR4SGhBb0V5Uzl2YTc5SnY0S3JjWXR6UHBYcDJuMkh0T1dpdDJXRWVEbEhfNXM2VEFGZ2NCMTRaZFNwOEpscno4T3VCWlltTUxRU3pwWnNvSzg?oc=5</t>
         </is>
       </c>
       <c r="F42" t="n">
         <v>1</v>
-      </c>
-      <c r="G42" s="1" t="n">
-        <v>46056.26940972222</v>
       </c>
     </row>
     <row r="43">
@@ -1823,222 +1691,201 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>EXCLUSIVE: UK refuses to consider Israel sanctions despite mounting evidence of killings of Palestinians and ceasefire violations - Muslim News UK - The Muslim News</t>
+          <t>Haskoning acquires port planning and simulation experts - WorldCargo News</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 09:43:37 GMT</t>
+          <t>Wed, 04 Feb 2026 00:22:31 GMT</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxPU0dJVG5aMEpCdWVseXY1Y1EzczNWR05fdWJLdzl0Qlg0LWhPY3pETXpiTXg4em5kZEdkT1l0anhSX0Nyb1M2bUpCa2xiNmkwSzlUTWNBWGRtempPdnZkaFZZRTRXaDJkUlozdDBmUHk4RXNRUW9IczlUTl91NjJyZ1BFa2RsMXVFRDR5c0VzQ1dibWJibF9iak5Ca1VZbUxrU3lDODdhcEN6OTNoZ0lkeHQ2LXJydF9PbjZkYWdIYlVRM3NuaHlOVzUzOFJzREtRa1Z1TVJCQkhHYTBSZlZXQjlzczcxWmVsbEE1MXAxSW5jVnRwUXMwTFVpckd5RDJnNkRVZlN0T3hPQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQRklmQVJSd3dyaDFSRF9FWW5jQnYtcEdITW1QM0Q0RktiMTB3UDhwM19xbHNIS3RvOTlkN2dZX25rM01aTW5kRTRXZk9rdTdTaG1GdlhNeEhJWjlHLXM0S0h3ZFM3WUdPaUdRS2llcnZsd0RldDd0Q001R21OcW8taVBMaXVYQWIzVGRRNXZXX0RNT0pOVHBDYW1UNldkYW01T0E?oc=5</t>
         </is>
       </c>
       <c r="F43" t="n">
         <v>1</v>
-      </c>
-      <c r="G43" s="1" t="n">
-        <v>46056.40528935185</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>EV rollout accelerates but councils face funding and grid hurdles - AirQualityNews</t>
+          <t>Police and Crime Commissioner censured for supporting anti-migrant protests - Searchlight Magazine</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 10:10:01 GMT</t>
+          <t>Tue, 03 Feb 2026 11:34:16 GMT</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPVHpDRjJYbG1yendmcXBLRXp5c3VjME5wLVM1bm1QdG9IbWdRcXN5T0h6WVJrZXRUbHF2cEpnTHQ0c1B4eklxMG03OTdGWm8wc1VyZklmaUhBMm5tbnVfdzMwNkZYeVZqUkNLVG1BY2E1T1JFbE1SNXdZaEV5dGEzdmVLNklpSWlKeDBqMDNfZ1BOM2M0bjVGeUJzN0w3ZGFpempoZVB4T1l4WDRELTJkc0pCSERMQ2M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQM2M4R2FWQzBlbHpIelJhMVpsQkE4V095dmNlMjFDNHMxOEd3V0g1RTM5SWotbE1IeEpNd1plOWNBSTZ6bWNiV2xzMy1KNjZJVlhoR2ZDSTVBMjJTS1I1NUhNWjhYcEh2RzRUak5nYllpT3lRTk5BMml3OWsyTHR2Rm5hTTJFdTc4X3NFTkJLU0U2bVZlU0NCcUhVU1otS3FxRWtreFE3VjF6d19LeGxRZ0kxUlhvSUU?oc=5</t>
         </is>
       </c>
       <c r="F44" t="n">
         <v>1</v>
-      </c>
-      <c r="G44" s="1" t="n">
-        <v>46056.42362268519</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Columbia Group deepens digital compliance drive with Prevention at Sea - Digital Ship</t>
+          <t>Iran police say 139 foreign nationals arrested over protests in Yazd - ایران اینترنشنال</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 04:20:34 GMT</t>
+          <t>Tue, 03 Feb 2026 10:11:32 GMT</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOMmtyZTBYOTZkVzBFSkxFTnoxVGNlVFUtdDM0ZGxoZ21nQjFYRW9RazVOc2FnYzRuTk5TLWh0ajQ5R0Z3RkRQSjNQdUFyQjRXWGFLSEw1VjlMaWtZZzFiTVFzcUd6RXB3eFU0V19pblUwMkR6c2RjWVUxSUwxbVdId0tsVG81UnVtSlZYQnpuRnUtbWU3TTNQWGN2eTNzbWkySWwxSjhWWmtQODlKaDRvc3ZGT0JPcEJKeDlzQURn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUkFVX3lxTE5OLVNjX1hqdFk0NllxYU5uSGN5TmRXTERJSDh1bktUeHZvNC1BaDBzWDVtaUhJbmlWX2Jpekl5WklaZzUzSkhBY1d6VXhmUU5acHc?oc=5</t>
         </is>
       </c>
       <c r="F45" t="n">
         <v>1</v>
-      </c>
-      <c r="G45" s="1" t="n">
-        <v>46056.18094907407</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>How carbon capture could open up a new shipping market at the expense of pipelines - Tradewinds News</t>
+          <t>Russia resumes strikes on freezing Ukrainian capital ahead of talks - France 24</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 08:52:51 GMT</t>
+          <t>Tue, 03 Feb 2026 09:46:52 GMT</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxNYU5iYU43SFJlcE81eXVpV2g2U0wzUnBvY2ZsZ2tvbGcxNGtkQkxHX0ptenBjMWpXZFlQNXctOGd1TmEtcndWR2ktWnA1MVJxdy1LT3djYVBZSmhzUElDakh3OVpXT0pFOW84blNoVUpDbFNMTDdkY2F0T1Y0YjFSaTZMcHVUTlFVWUlmRjlBbENYVTNwNTBfT0JMRDluRHN3MFBySWIwWW1NYnNJdEZjM01qQUtWMWVqTVRkMUJWS1R4aHFTeEp4V2pTWFg2QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPN01uSVNackgwMjE1enhnOVdUWnJQOXZaYkJXQzBscXFaX0tmVkRrb0ZSNjhFTXR4NTJmOE0yQk5TNHZndHV1dkxyRldjZFlDNDhEbW5LMVNzcjdEOGg0VWVsbE5GOTVEZVV1VzZQSGdTLXZEMGREeWg4LUw1MnRIaDNMRjd1eG1BSUs5S2VORE1NTFVRVkI5bnlzZw?oc=5</t>
         </is>
       </c>
       <c r="F46" t="n">
         <v>1</v>
-      </c>
-      <c r="G46" s="1" t="n">
-        <v>46056.37003472223</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>NetSuite 2025.2 Enhances Supply Chain Agility Amid Growing Operational Pressures - ERP Today</t>
+          <t>Man arrested in connection with physical altercation during Buda high school student walkout, police say - KSAT</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 10:13:08 GMT</t>
+          <t>Wed, 04 Feb 2026 04:41:03 GMT</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQWEE2Z2ozZFI0RW1jWFVXMVk1dUFFZGlYZlNPT2hqdlJVMUNBSGlWSVhIYll0RXZFQXh0WFRGcGtNSFN3T01nWURVd2hhMUFuUHBhRm9XTnBMcHF2a0hId3JlX2UyaFJJa3ctTXI5a1hQaEU1Y3BGTXZlRnpmU0lqZW44ekhXOWNGcllwbGtlUTA4Z09OZDc4eGlDNy10MVlG?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxNS1VuTHpOWGU3M3BEZTVzWU5LbDNILWEwWmJMbGFYdVVraVBMTUI5bXFBRXR6THdDUmd2SHhuQ0dVTTVXbnNQM2NyVnIyamtlMElvMHZJSTBfTnJ3cC05S1ZsMWVSeTY5TnRBSUJCYncwclhMOXdtYXQ1YTB2YVd4Z2R4TW1MNkoxOFpqNjdTdjdPVlpxVTFoM2xqeWtWb0RJZDZYWXdyTnZvUHU3cEN1R0hQaW5aX2NuVTktTXJ5T3BScjN1UWYxcTNtVzY2V3dxRTVlbHJ1SHhjQlNYdUdyXw?oc=5</t>
         </is>
       </c>
       <c r="F47" t="n">
         <v>1</v>
-      </c>
-      <c r="G47" s="1" t="n">
-        <v>46056.42578703703</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MPC Capital and Morten Astrup roll out new shipping investment platform - Splash247</t>
+          <t>Palestine Action Group plans march against Isaac Herzog’s visit despite protest restrictions - The Guardian</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 07:31:43 GMT</t>
+          <t>Tue, 03 Feb 2026 10:02:00 GMT</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPTE0wcTV6QlhtSEtqaHZWWHZhY0dHNS1BOUJjU0UtQXNLblQydVVycUxFT2xoLWhHb0Z1cDVTYnMySmNBVFhBUUtkdGJkWE1DUTlJUFJ1emgxSmZVai1MQ19XUWtpQXZ1LWNKQ2F2c0ZWblR6OENXOXdRSmdIZmtDTkQyR1NrM2QwLW1qM2o1bmlGYzZPSm5HcEFn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPNlhyVnR2VUlxTWpRY2J5M3c4MkpZcGkzNk5iWG5Wajc5QmlvVDVEcDRwd2lVbTJpaFBjR051RERCNmd4dXhibWJtdmJQZjNNT05kMF9vWDRkM0V6X2Z1R0ZEb1ZIOGN5anI4NHFCM0ViQlN6N1BNbXFzZ2tMakZscFg2Y0xseXIwYWxLb0tnSGthaUl5dThmWklCSzdKMi03Y01EUnZn?oc=5</t>
         </is>
       </c>
       <c r="F48" t="n">
         <v>1</v>
-      </c>
-      <c r="G48" s="1" t="n">
-        <v>46056.31369212963</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Politics latest: Police review after €500bn leak claim - as 'well hung young man' email emerges - Sky News</t>
+          <t>Islamophobia in Europe: Dutch police assault on Muslim women sparks protests, highlights growing crisis - Muslim Network TV</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 10:29:14 GMT</t>
+          <t>Tue, 03 Feb 2026 15:14:40 GMT</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQWXI1a3lTS01RY1ZneTVDeTN5OWFBMTA5TE9fTzVxRWV3M1BaVmNSdVVheVZCbWxEeWlZWWJ1Z3V2RFozbUR0T2ppMXc1TXUzQUdQTEs3aDk4Ykwxb3RBbDBJd0ZrNUwzaEdJeHFJUWxhZV9LcDlmcGhFOXM5VlJNdklnVHl2QkozNmRTaVBKZ25aZElfSDFTbTAyYmhMeXJfeU5VSTVmdGF0QTczOWRBZnozT3E3V2FvOUtkcksySjgzTGM0Z3hQVDNBMUNndFk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNaDVlX294ZEx2MWpIaTc2RUtuM00xbXFNV2xBWWZhUmY5TmVjaXZiYXBXZ1kyQVFrMlNpNldFY0hiVmdrQXNlMnJkeUhnVkdEQWFINS1EdHhrOC1GTGVpeXBqb29MVDZqV2ZMS2xQT05ibFBYS0ZxNHRBWnFVOE5GLVJBaTlOVTdfM0xYaHdURVhYTGVKc2JFVzd2LVhqZGNiZE8xcnZNWlN0MlY2NkYtMWlWWU9CVmJHVkpadlpONHVLMGdYbWU1OFlPSQ?oc=5</t>
         </is>
       </c>
       <c r="F49" t="n">
         <v>1</v>
-      </c>
-      <c r="G49" s="1" t="n">
-        <v>46056.43696759259</v>
       </c>
     </row>
     <row r="50">
@@ -2054,24 +1901,21 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Russia resumes strikes on freezing Ukrainian capital ahead of talks - France 24</t>
+          <t>NTUCB Cries Foul After Police Deny Protest Permit - Greater Belize Media</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 09:46:52 GMT</t>
+          <t>Wed, 04 Feb 2026 01:51:29 GMT</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPN01uSVNackgwMjE1enhnOVdUWnJQOXZaYkJXQzBscXFaX0tmVkRrb0ZSNjhFTXR4NTJmOE0yQk5TNHZndHV1dkxyRldjZFlDNDhEbW5LMVNzcjdEOGg0VWVsbE5GOTVEZVV1VzZQSGdTLXZEMGREeWg4LUw1MnRIaDNMRjd1eG1BSUs5S2VORE1NTFVRVkI5bnlzZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxNMnZiTGxNZjVlM24tYnBTbEV3OC1oc3JvMEE3b1RvY1JTcTNkMEp5Q0xsc3R1MzAtRXZfWGZqb2hnZXRvWjVxVGZzc05kbUE1OXp4bFhWSE9IQmE2SHZvRlkwV2daUUFPTDlsRlcyT2RNUncwWjVkWGx3Nnl2enBFdHQyM2s0OFk?oc=5</t>
         </is>
       </c>
       <c r="F50" t="n">
         <v>1</v>
-      </c>
-      <c r="G50" s="1" t="n">
-        <v>46056.40754629629</v>
       </c>
     </row>
     <row r="51">
@@ -2087,24 +1931,21 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Police statement as flag-waving protesters march on Hanley - Stoke-on-Trent Live</t>
+          <t>Maple Grove Police Chief Addresses ICE Enforcement and Recent Protest Arrests - CCX Media -</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 17:30:00 GMT</t>
+          <t>Wed, 04 Feb 2026 00:32:02 GMT</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPT1otX0VCaWwyTFVjMkhPU0habVRyTlZTWl9mYzRJX1RvcUZoTTBFbmd2NENQNVJOcW5aajZkLVFRZlZpUVM2MERmUDFCOWp3bFdkX2lseWg3eHByak9HUmlnV29OSlViX1ByNnExQllBQXdXeHRzNU9hc3RlMEY0d3otTjhkTXc0czZ5QVpYckJhNHpCajV5NWJuNG15SEt5NkNuSGNwR23SAa4BQVVfeXFMT29GZ3RWV0xJczVuSG91dVpCS0dXREVJNG0wQUhkU21sYTY4MVItR2pocTdpMC1obWRKeENHNFdkazgyZnpVdzRvZFotcnRpb1lxWk4tbW1hdkxmZ2duTkUyTGcyN2pGWG5iRE9KclhHeVdUUzg0UVVyR1pha2lKdUlYMTViQmF4b1lfc0ZGMlVZNTdEU2NoQU5rb2N0M0p5dGZDVG1USzdCWXJhdmhn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOZXN2UHBVaTBoNHljclNnSThxSnhFd1hhWWFBQ191V0s1eFVzdV9EMGE2dzZGT0xqaDlsaHlQRDNVdVhWM25PMzQydGQ2RTdOZXo4X3ZFMXYxMndrYktNSHIycGhxUVY4ZU82RFdKY3JUR1dRaExOWmVfNmVhQURoMkE3X1VzaXBXTVdwcnZXSDlUQkRvNlNnMjBFb0ZZd3RfQ1JRTmphTQ?oc=5</t>
         </is>
       </c>
       <c r="F51" t="n">
         <v>1</v>
-      </c>
-      <c r="G51" s="1" t="n">
-        <v>46055.72916666666</v>
       </c>
     </row>
     <row r="52">
@@ -2120,24 +1961,21 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Iranian police detain four unspecified foreigners over unrest - AL-Monitor</t>
+          <t>ICE-Out Protests in LA w/ LA Times' Gustavo Arellano, plus Capital B's Adam Mahoney on Impact of Freezing Temps - KPFA</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 11:29:32 GMT</t>
+          <t>Tue, 03 Feb 2026 16:00:00 GMT</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPcTMzQ2JESWJVYndqSFdxbUVheG12M2RWR29uUTNWWWZmR01XajUwb1dtU3VtNC1Wakk4VmYyWlJ2aVhhM2M3MmZZYkZ4V1R4RmFIUkpwUUk2WXBmcmFXcFQzUDRSRnEzdHB6LXhVSklxWTd3b2FBVlc5YnAta0RDdzVnNWU5QS1pZUc2UW11dmVfa3hsOHRpRnhHZGNNeTRoZDB2TDVFWk1DQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE11MmFBVWRiMlpkdzd3SFU0aTQ1YnZBd2RJSDhtNWJZZW5XaVhKczVWTG1LUDVkRHVmaXFkWVc1dC1XMXMyMzM5bmZpWXJzNVlPQlVsTU9FYkdZTHhSdml6aS1McDQ?oc=5</t>
         </is>
       </c>
       <c r="F52" t="n">
         <v>1</v>
-      </c>
-      <c r="G52" s="1" t="n">
-        <v>46055.47884259259</v>
       </c>
     </row>
     <row r="53">
@@ -2153,387 +1991,351 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spokane police chief apologizes for officers wearing masks at protest - The Spokesman-Review</t>
+          <t>Spokane police chief apologizes for officers wearing masks at protest - The Seattle Times</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 05:50:11 GMT</t>
+          <t>Tue, 03 Feb 2026 19:00:02 GMT</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOZHRHU2VfME5sVTVoQkpLMmpoVUhPN1lnZzdCSm44cVRfZ3k2NFNIVVdMSTh3cXIwU0RFUFNfZ1NMdXhrR0FXVEx0NXNadWsxWEp5WVU4cHBoNkgzV09GcEVtSEpwcG1jdkZWR2h4bjd6QWhfQTRtazA4ck14VXFvaVBDcmlKdDJSVHk0TkZacW5XTTFjQ1dMYmI1Y3VoQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPZHVEUEY5SVQyb3FseU83enJMeHd1S1dzc1NsUUR2aWpPRHBRQ05zQ20zZTBmM1MwYmc1emlYQW05VDg3T2l4bXFNS3k2aHlvOFl6cTctcS1vQnU1dFVGRVFucnVLd3VZbVR5eThXT015cUJLaHIzaWtETlJfUU9rbllnTFdfeU84cXpXdVFuT3Z0UmtGdzVlNWhYS2RCeE5pVV9RVTdXMVkwSFcwSjhFUlZqRUU4QTFYR1ExQWJocw?oc=5</t>
         </is>
       </c>
       <c r="F53" t="n">
         <v>1</v>
-      </c>
-      <c r="G53" s="1" t="n">
-        <v>46056.24318287037</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ukraine's capital of Kyiv, other cities under Russian attack, officials say - Reuters</t>
+          <t>US stocks drop on fears AI will hit software and analytics groups - Financial Times</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 23:23:20 GMT</t>
+          <t>Tue, 03 Feb 2026 15:51:54 GMT</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNVlBuNklvRHU5MVg4THZMa2VRMmlRZVpEb2FmX0pNNlJCNXNHbS1CWW5NaG5pbUNLZG05ZDlhcHgwQUV4Tm1mbXVuV2cyaXp5ZGZyNnJkeEJPdC0xR0NYYU8tOWVTX3NXSmNPUHhWSEg2dWlDZEFEYWhCOGdPdWFsMlM1SXYxU1Q1NlhTcFRfLVB0SDM4OGRYVDQxNVNpd0g3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5uQzVsUF85MERrc09IUk83T0piRjgtQUFvZ2R4c0VyVmxzTlJ2R3BkelNLMWw4eHYxcGMwc3hjSmJsN0tTbGhsNEVQYlJmcWVkaXhxaTk4NW14WDBDbjFFZml4SVFyaGNVbXhqb3licHc?oc=5</t>
         </is>
       </c>
       <c r="F54" t="n">
         <v>1</v>
-      </c>
-      <c r="G54" s="1" t="n">
-        <v>46055.97453703704</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Gunfire strikes trolleybus in Kaunas, Lithuania: Police investigate - Caliber.Az</t>
+          <t>NHS launches AI and robotic pilot to speed up cancer diagnoses - PublicTechnology</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 09:46:04 GMT</t>
+          <t>Wed, 04 Feb 2026 01:08:48 GMT</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOaGx5Zk1zN0ZWN3Rzbjh4SUk4WGlaem53MHQ5dTgweEY4M3ZVM2FOay1laW9UZlVFRmxpY0ZYNTkzcDN2OE1DdWhOTmdqbUJhY01XU2Q2SUd5eGdxUHZ3N0NDMElwY3Q4b2RJRXdSdm1uOWNCcGs0TnNXWHJnVGR0V1hNLU1FS2IwckxtNGctSEwwRkl6WjNv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNYm04ZWFpSkZ1UmgwOTlXVU5TRkJBWjBQeU9PbFNfbDBVVmNpN0ZpT081RUdHemQyVEwwZmJrZXIwYzJSLTJsSGpNcFBmWjJROUVQQlRNaUZrUU90MmphQTQzYi05TV96dGtrT2VFa0hPY1l4YU1pYXlmZ3FrdUdtbmhGQ2xMQkNMU1Y1a2hYc3ZFODZDQVVaSnhhTjJXVTdnMWlIVHFhZlRhYjlPYmJuWHpQeEwwbGotd3JWSTNDZTIzSXAzMURiNDR3?oc=5</t>
         </is>
       </c>
       <c r="F55" t="n">
         <v>1</v>
-      </c>
-      <c r="G55" s="1" t="n">
-        <v>46056.40699074074</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Another e-scooter taken into police possession - Fenland Citizen</t>
+          <t>King's robotics and AI specialist helps government upgrade public services - King's College London</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 11:33:00 GMT</t>
+          <t>Tue, 03 Feb 2026 12:59:31 GMT</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQY0xxNnhKTTZwdUtJdVZNZXBSQ0lwUlpxMDhCUWxhUFBFLXpUaDJMNmF2OW1YY2hWSTJ5Zm1Vbk9mcDl5UjZpWm1Jd1FPYW1mVk5sZV9xc3dlYktqRWlOQTFaUDBBU0JGMVhQZnRkSkMwYV9QWnpsY0RQU1VtRlhWWnJDb0o5WkIyWlZNcTVoTHZvM25keS1BRg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQQVJBNEtMQjhaaXJZb25qLUpPZnFHYkpkeVJtdWcwME5NdmlJdG1nWU5sYUZuYVFEMzJsTWItU0kxelRkckI4eVE4dkVoOUtWbkNJaWszYV9VV1FENGphSjhtVU5OcnJnSGtJNFFUYVVYN3ZsTXo2UGhBNGxublktUUV0YzNMdzF1amZkSk05NjRWcVNDa0RUMld3cVZ4WE1DbXc?oc=5</t>
         </is>
       </c>
       <c r="F56" t="n">
         <v>1</v>
-      </c>
-      <c r="G56" s="1" t="n">
-        <v>46055.48125</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Hungary Raises Alarm after Slovak Police Arrest Politician over Beneš Decrees - Hungarian Conservative</t>
+          <t>‘Technology must enhance, not replace, real-world learning’ - The Hull Story</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 14:09:31 GMT</t>
+          <t>Wed, 04 Feb 2026 06:37:50 GMT</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOSGNwRENjNUNNeDMxSWhEWndpNk9OQnpBV0EzazV3b1FSbzlic1lTUTFxTDQyY19UckVZYzB2cy0yZUhYNFF0dHJ1WEtXRDNSQ2VjY1B5WXZiNVA0UEJNLUo1SmxScmhEYS1NQUtoX1pFWjU5dUdqeXg1d3EycFZTZFFkSDlsRFptSHQ4X2lBenowTnZMNmtwRHh3bGQ4ODdzTlVRRzZEeE91ZUl6M2lFSDZoZ2Y?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQNm1XOWJDUDBSc09mbEZ0VUFaQ2JwNEdMd0w5a0wxVXczc0RMb09pUlY3ZFB2T3haWHBaR2FTSlB2OEJBN09rRFprMlFfXzBOREtkMkMwb3RGV1I0S3YzenBjOXRUYUdXU2xKS3RIaHZ0T2FMcnIzUmxwdlVYVjJLUGxLcl9BelZldklsNFBqbWNGbFZPNVFQclBGaVA?oc=5</t>
         </is>
       </c>
       <c r="F57" t="n">
         <v>1</v>
-      </c>
-      <c r="G57" s="1" t="n">
-        <v>46055.58994212963</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Reno police confirm battery report, citations after anti-ICE protests - Reno Gazette Journal</t>
+          <t>UK and Japan strengthen science and technology ties - GOV.UK</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 00:14:00 GMT</t>
+          <t>Tue, 03 Feb 2026 09:04:44 GMT</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOYVFWYkdQSUEwVkstQUVseXZ5TV9uTGtqbFFadjRwcXozcWJfaF9GQ2xsUXZHdXFyaVVFMXNmYnhUR05PbFJLa3UzN0lVUEIyX0J5RWM5VlRLR2VpRE5raGdMSE5DaFlaZW92blRuZEl5WUlEQW1aZW4zUE1CY0t5ekY4NlFuazU0cHFTSjN0bTlwT3p1Z29vbTJfcTB3R0p0THliSzNPN0NQODdoZGgtMHY4d25vUUNST1pSM0tPTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOQkZQLVZCX0pweG43Y0N0dWNXUXFGaGNsWUN0b0JBb1FFek5FREd3cnJXR0dFRGY4TGloaGlaRlFvMGo5SmxpZmFwVHpxbVdxX1RBTHN2T3dFc0M5Zk1uOTRDU0ktQ2NfRDdPN2xQVmpuanhLRHFIWjhPaHNJRDV1Rm1zVVQ1WlRBOEZrNlRsYw?oc=5</t>
         </is>
       </c>
       <c r="F58" t="n">
         <v>1</v>
-      </c>
-      <c r="G58" s="1" t="n">
-        <v>46056.00972222222</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Ferndale Police answer questions regarding Friday student protest march - Whatcom News</t>
+          <t>Women in tech and finance at higher risk from AI job losses, report says - The Guardian</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 00:17:16 GMT</t>
+          <t>Wed, 04 Feb 2026 00:03:00 GMT</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPbzk1cHEtbWI4VjhaVXBCSXA2Y3MtaEhZWXAxYk0zMkl5SUVvcmh3d2JycHRiMTh1dEZrdGRqVDhwR0Z3UjJoX0JhSE1kUk9MVkVEbzZqUl9OcWY0N0ZRZFdJQ2FUQUFrWFhxUVk4clNFV2o4R0dMa1JBaVpFVjdyVDFraVBEbkR5TFc3VmZUQmNxazNhNlZiSGI5RTZnWnN2TVVGWk9zQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNakRQMFJ4NFJDWEU1UnRoVG55QzZjWnl0WW1Kd2czUDgyM1hXVzlNYXM1S2ZtRlRmeTFXMUdMWWhad2taWGpCZUF4UER2ZGRpa3R5aTFycUhyNjZKN0ZzenQ4XzA0ZDdpX2xnaUt1d0I4TkV1VjdadFNQa0ZaNlQ3Qm9QN0hKQ1Vnd1Viamc0anA2UGdQLUQ0S0I1Q3pYXzRnOGc?oc=5</t>
         </is>
       </c>
       <c r="F59" t="n">
         <v>1</v>
-      </c>
-      <c r="G59" s="1" t="n">
-        <v>46056.01199074074</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>NSW protest restrictions extended ahead of Israel president's visit - Australian Broadcasting Corporation</t>
+          <t>Industry suffers lack of joined up AI and digital skills - DecisionMarketing</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 03:21:47 GMT</t>
+          <t>Tue, 03 Feb 2026 13:49:00 GMT</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOR25CYWQ2V3BfQnRxMmVBSEFDY1RzSzdhaThTcVU0RWdLX0Zyc3IyS19yck1YZHhiQ3R1OVdkc195bzYtR0V5UXlLb2Fta1JkaldFOU9QYjJpajFrczNQWHBTeGZQRi1jMXIxcXA2Ql9BQm5jOUVyZ2ZxcktENTBoY010OXcwZ3VjRXZ2TXIybVJ1dHZBT21NdlVSMW9Ea3RjQ3UzcUpMWTNxQUZEQXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPOEw4RTlNUGI2WDlXMEVBUkJMMlBZZ2VWNnAwbFZIdkJHTEhPbTMyQllzZzZlek5JX2pMQzNxWXQ3a2lTbEdxN253ZEFVM0JNdHZ1dTJrd0UwTWRJNl82YS0wYzlrc2ZPbjl4TkF1bDd6RVc0aWVEWjFhUlp2dHd0VjFNbU9qM3dmYUVKY1VBeXgzMVROd1gtVjY0TGRGdw?oc=5</t>
         </is>
       </c>
       <c r="F60" t="n">
         <v>1</v>
-      </c>
-      <c r="G60" s="1" t="n">
-        <v>46056.14012731481</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Alderpeople Say COPA Should Investigate Chicago Police Conduct During Immigration Raids, Protests - WTTW</t>
+          <t>Nottingham receives funding to develop quantum sensors to improve precision and read-out speed - University of Nottingham</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 01:02:00 GMT</t>
+          <t>Tue, 03 Feb 2026 16:30:50 GMT</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPN2xkVWx4dWpnd25XYVhTLXF3cXRJOGRSUDZIMFJaTGRpa3dEeVEzOUdKSzA4ajZWVk95XzF1aS1WdFlBT3ZVR3lBaTZMZDE2U0pvZWlON2xNZ0taeWxnTlJNU0NDdkdabUxyVGZnS0JZTk1KcG0xMkhVWU5QWWZqMXpWRkJGT1R1WENRZWpvMkNJV09RUlM1NjdhQmV3VnhOUkNrTE55Y2U4NS10ZGNSel9MbFlwUHYxd0lkMw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNaEF1YTRSWm4xM1NnTWJnU0NRVDRVYVlkdTFWRXlJdUY1RWh5QWVQT095VTBzMHFnbkxlbmlqRU5Ha2g0ejJ5ZzFTUE5PMllGUkJyQXRPdzYyNl9MLURSWG50cEYyYUZhN2UyTGFOYlBXRE1lLXU3U1BDYnBaNmJQbDVpV1lLTXJhLVRNTE1BZUktTVF2c01EY3FBNHdXV0pPQWo0R19MOEFZczRqZXpRQk5wZnFqa1lLWlMweDNuR3ZLTEZUYUtV?oc=5</t>
         </is>
       </c>
       <c r="F61" t="n">
         <v>1</v>
-      </c>
-      <c r="G61" s="1" t="n">
-        <v>46056.04305555556</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>‘Significant animosity’ to Israeli president prompts further protest ban - AFR</t>
+          <t>Why High-Stakes Decisions Demand a Different Kind of AI - IT Brief UK</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 04:31:00 GMT</t>
+          <t>Tue, 03 Feb 2026 23:35:05 GMT</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOM3VBTUx1czNTbG5CVmlqcnF4bk13aWpUbnIySGRLbmZiSEtWUnE3RU1LVG5HcTJuSE1fVEJsSTVkNm5XemVYQjVwbk1TZWFKcGtYTVJRVUg4WkhhSzlqX2dqMFhjZXJ4N3hQQnAtdEVXQUlzTlNfdnVQZEVOeTRlUkJmMWFtVGxxajU2WGtEdTFFTmFuWWJwb1NxaDhWZElhYXVQZVdJSEhRbHJGeTdGNm1nb0FGZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOYUY4VU01Q0ZDQVF3TnZMN2I2ckMyeXpjRlktczhyS2M5S0Q0YUlOaFNqbDhDQWpTTkUwNlJITlQtaFZ0aTBkSDhwc1d3c00wTXk0ZjRXSDJJb1czVk5PeVQ3eHFTNW84a1hha1V3QndMTDhUeXBZaks5RmwzbTVyeVNDa2F1bDV0NEIw?oc=5</t>
         </is>
       </c>
       <c r="F62" t="n">
         <v>1</v>
-      </c>
-      <c r="G62" s="1" t="n">
-        <v>46056.18819444445</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>National Tax Service Sets March 3 Deadline for Stock Capital Gains Tax - 조선일보</t>
+          <t>How agentic AI is transforming financial services - Impact Economist</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 04:38:27 GMT</t>
+          <t>Wed, 04 Feb 2026 02:29:43 GMT</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOXzdGdHcyWHBCYXVUektpN0RGcWpDLWlmQ0M2Y3ZCX1JHcTEtalByTjk5cUp4MExzOGhEbU5ZUkJscFNha2ZXcjNtVTRvTGd0QTJVbVE2OVdMVnlGY1BoNWQxMHQxbnBFTUZYT3lIbHEzSzlDdTVPeTN3VUF3UUNuOWlaeE9DbWp3QnV1T2ln?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxQdk5tYWV3M0t0aEtZRHhmVnI1STNPLXFBTTZPLXFXZENUbkdxMDdSaGE5dUh2dmRkOWpRYnpScHdmeE51SEV2WG91ajZJbUZPaFJLODloZUFtMFAxQkNfN0U1dEVqUUZ6YTFqRnhQZm1SWFRKRk9COUpRWmlTMWRVUWJUamhmdWJ0bUNPMw?oc=5</t>
         </is>
       </c>
       <c r="F63" t="n">
         <v>1</v>
-      </c>
-      <c r="G63" s="1" t="n">
-        <v>46056.19336805555</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Why NLC should shelve today’s planned protest, by police - The Nation Newspaper</t>
+          <t>Liberty Global and Google Cloud strike five-year AI deal - Mobile Europe</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 04:26:57 GMT</t>
+          <t>Wed, 04 Feb 2026 00:15:55 GMT</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQaVJGdmRRUTF6SXJZU21JYk0yb3FyaXR5aVNiZ3RfVDhzdWp5RUlOM2pzdGQ1ZW55NHN6Smg0eDM1TEV2dVpKZGp3d3VJdHFOSTU3Ykwzc3lPanFYUjAtcHVhaW1HVnQwcGtobTZ3WkVmWVl1cDVMMDdxck1TT1VIbGhiSU1DSEhJbDdieHB30gGTAUFVX3lxTE9aNlN2WmN4aXVkbThzV0E4SmtBQkdPVmJnQjR2TllCWWVhN213Zno0UlF3OEtqOTYyWW9abWx0ajBzVG5yVkNGQXp5cDJ2bkpLeWV3c0VScDd0VzZVSzZxZFdGc0ZHX205aHJGRFZOQ2pITmVWRzlVU2EwNXF5T0hvYmtYc25GVTRQQ3J5YUJlTFVwVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNY0RJU1NmOVNBNzdrOXdTXzdfZWF1QXpPdlg4ZHFKRU5tUWV3MndBR2lrcl91bHFVZlJtUFRPYmZBX01YeU9FUXhITWtVQXVkc3J5TVpxTWRMY3Z2cjhyZ3dZTVBqZWxkTXA3eEREemRsblBQYi12aGVWZWloVkY5a0lUNll1NzdmdjZ6VzVpS1ZqQQ?oc=5</t>
         </is>
       </c>
       <c r="F64" t="n">
         <v>1</v>
-      </c>
-      <c r="G64" s="1" t="n">
-        <v>46056.18538194444</v>
       </c>
     </row>
     <row r="65">
@@ -2549,24 +2351,21 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Technology and AI - Freeths</t>
+          <t>Amazon, Prosus Reach AI, Cloud Deal for Double-Digit Cost Saving - Bloomberg.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 07:37:01 GMT</t>
+          <t>Wed, 04 Feb 2026 04:30:00 GMT</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTFBWa1dVRGdpcEZHemc2aURfM0tWNDlnRXJBRTRNa0F3Z25xMENnNHFmWC1henR2SkNXdnVYZ2VHa0lIcGo3UDFJb1hUWnI2R1c4ZDlpWkFIQlNPaGJBZTNGZUF4S2xnRl9qdG9wNGpGMV90aVpXdGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQYlpGRFV0SVRkU0VuQnBMaTRKaUp3VDlGOUswRmNuQmFCVEdnbkNRcFE1NVdKbjdrMmRSanU0M2NxUDVRQjJEZkVJeGtKLVVEYXZwdlJFb0RWaDVRUWhRbGtZbWFsSk4tTmJpNm11UF9PYTdCY0FXc3Jwcl9XRkRCQmIySElkdDNMQThmYnFpbzBYUVgzNjFNTEh4Y3YtTS0wX3BFTjNVWnltMWdHT0laa2xXdw?oc=5</t>
         </is>
       </c>
       <c r="F65" t="n">
         <v>1</v>
-      </c>
-      <c r="G65" s="1" t="n">
-        <v>46056.31737268518</v>
       </c>
     </row>
     <row r="66">
@@ -2582,24 +2381,21 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New robot swabbing technology trialled for the first time at Sellafield - GOV.UK</t>
+          <t>Use more AI and video hearings to fix English courts system, report says - Financial Times</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 10:06:27 GMT</t>
+          <t>Wed, 04 Feb 2026 00:01:01 GMT</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOd3FSVUNTenVpSFhtWjdBV3JYX2JNRWFhTWZCR2U1Y1FsWlVQQ1FhUjRMVmVwWnlZM2FOMUxJYVgxTk1maEY3RkJpMk9EZjk4Wks5em00UzJBbzRwbUdKUGVkUC1ybkJNc1J1WmtMNGxjMjhiREhzX29JTWQweHZfQ1ZhejluQjdSSzRmVVBGdDNWU0syUUhEd04zMWYyV1IxUWhETlRCejVldw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1zU2RFeUxERWhId3lMWDFVbmJTMl96NVhHdndqRkt0VW1JQ2ZSYjJtYWhYS1J4cHc2RHQ0X2tzOVp4ZnoyNDE1eE5Eb0ZJVzdsbjdCdjh5M2pUak1WU1pZbTU3Y000ZlV3QWV0dGh1clA?oc=5</t>
         </is>
       </c>
       <c r="F66" t="n">
         <v>1</v>
-      </c>
-      <c r="G66" s="1" t="n">
-        <v>46056.42114583333</v>
       </c>
     </row>
     <row r="67">
@@ -2615,24 +2411,21 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>PhD students secure second place in global UN AI sustainability competition - University of Aberdeen</t>
+          <t>New robot swabbing technology trialled for the first time at Sellafield - GOV.UK</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 10:18:29 GMT</t>
+          <t>Tue, 03 Feb 2026 10:41:15 GMT</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiSkFVX3lxTE9QNnVZSlE1Tko5ZUNISnRFdzRUMm9GMjFjdW5RbElkRnpRVVBzbXFqX21SNW9jbzhFbEhQV3gtWWQteUwwVHBpV01R?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOd3FSVUNTenVpSFhtWjdBV3JYX2JNRWFhTWZCR2U1Y1FsWlVQQ1FhUjRMVmVwWnlZM2FOMUxJYVgxTk1maEY3RkJpMk9EZjk4Wks5em00UzJBbzRwbUdKUGVkUC1ybkJNc1J1WmtMNGxjMjhiREhzX29JTWQweHZfQ1ZhejluQjdSSzRmVVBGdDNWU0syUUhEd04zMWYyV1IxUWhETlRCejVldw?oc=5</t>
         </is>
       </c>
       <c r="F67" t="n">
         <v>1</v>
-      </c>
-      <c r="G67" s="1" t="n">
-        <v>46056.42950231482</v>
       </c>
     </row>
     <row r="68">
@@ -2648,24 +2441,21 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CURE-ND brings together experts in AI and machine learning - UK DRI</t>
+          <t>01.ai's Kai-Fu Lee: Why China will beat the US in consumer AI - Financial Times</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 13:45:51 GMT</t>
+          <t>Wed, 04 Feb 2026 05:00:06 GMT</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQQUxpOEJSX3VYSW04MTVNYkd1TnJJMXJKUjc2eEpZQ1I3M0hsSTA0dEdaWEc4dUpGQUpvYjRqbFM3akdkZHdzZlhpdmhhcnQ2VnpWb2otYjZjeF9JZ0h3ZTY0SjhDOTBrMVhJVTVXNUQtREczX2xMejB1Q0JKRDNkamFfSGVZMGp2U2t3N3VEaEFZaU1XR2xhQzFYY3RlT3B0OVhZX3RESzI4ZTQyVDZ6T1FxMHZiUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE91ZF8xa2FhUFN1cnNHR2lzWlloQTg0TDltLXA3WjVnNktxUWtCaWpFcXlSS2ZrRVJUVGlxOUtOOVkzMGFjMjNWY3lWaGx3MlJSQ25DRHdOX1FzVUwwQzk0SkI1QXJOQVY0dk85MXNhUlY?oc=5</t>
         </is>
       </c>
       <c r="F68" t="n">
         <v>1</v>
-      </c>
-      <c r="G68" s="1" t="n">
-        <v>46055.57350694444</v>
       </c>
     </row>
     <row r="69">
@@ -2681,24 +2471,21 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Publicis deepens AI push, saying rivals have yet to make it pay - Financial Times</t>
+          <t>The trillion-dollar question for AI business models - GIS Reports</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 06:30:20 GMT</t>
+          <t>Wed, 04 Feb 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE05aFZudWF4Qno5cmZiX19mOXg2YWZvdlFIUVNjNHhsZGFfNWVxeEYzQmlxT0xud0hkYzdxSU1PRElxZHpOQ3o3Yng0aWYtS3FLdHhFcTJobU5oYTllaXI4eHNQS2ZncTNJeEJmd1loZ2Q?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE94cUluRXhZMVo3ZjhYeHc0N25PUVN0cUl4RDdGeGtuRWVDaEI1dzJUc01pVjJNZnlyTDB4QU5iZ1YtZUtXRGpLbVNuLUU3cktEajkySzR5WGdueDBCMUVmT2p5LTI?oc=5</t>
         </is>
       </c>
       <c r="F69" t="n">
         <v>1</v>
-      </c>
-      <c r="G69" s="1" t="n">
-        <v>46056.27106481481</v>
       </c>
     </row>
     <row r="70">
@@ -2714,24 +2501,21 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Agentic AI audit platform Fieldguide raises $75m in Series C funding - International Accounting Bulletin</t>
+          <t>Tech Secretary: Barnsley can blaze a trail as UK's first Tech Town - GOV.UK</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 09:53:23 GMT</t>
+          <t>Tue, 03 Feb 2026 12:31:33 GMT</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOR3BTVEVxMWUtS2hRMmpNOUNlaW9OR0trdDdlMEhEdzhBM0N2Z3FFWHpqRDItbXMzYndHbkhaaXhPWTBkZnhmZVBTdGZ6bXM3N19tWDRxc3JESEt3aDhOeURnR0wteU1XNFpmaC1qWlBsT1F3VWJVdkpsdy1iUHJudUhUb0JlVmVPN29XQjdwRUJXcHB2?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPd0luMnF3ZHJGUFQyMV9VaXM1OENiNjFWVDRQbjRkRWlCeVBvaGxoYmo3Szkxdk04aVlpOEpsazZCZlZMRlNPMk10TnpOeWZOWXViNjNtODZtU3NTWHFZeHRJSnlpaE90Wk1UYXhmeEFwbTRqVmdNWXMwZFVTYmJrRUVUdWN6MDNZY1pwTFVNdjZab2xTMnpZTGNPN1ZhR0pZ?oc=5</t>
         </is>
       </c>
       <c r="F70" t="n">
         <v>1</v>
-      </c>
-      <c r="G70" s="1" t="n">
-        <v>46056.41207175926</v>
       </c>
     </row>
     <row r="71">
@@ -2747,24 +2531,21 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>How trade shapes the winners and losers of AI boom - Oxford Economics</t>
+          <t>Are jobs getting better? “AI has the potential for a massive productivity uplift” - The London School of Economics and Political Science</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 23:33:39 GMT</t>
+          <t>Tue, 03 Feb 2026 12:55:05 GMT</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxORDcwTnZjQkprcmdaR1dMYWE0TTlSZUJ5ZEVqOHJCZDhYT21QdG5veEJpa3lOWUE1QzRpaVN2TGQtcHR1dGtlV2xkc1lQSkFabUIweFhqVWIxWXNORVh2T1ZTVlJFbFlBbGNVRWdwZFQtMDh5MmIwUmdCUWU3cjFPZmRhTVhfZzBOZWlqcURqSTFQRm1XRHZV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPeE1EZV9iRnpHTVVPZTR5MDRrOHpKVHI3OEdpN0VobFpEOWlfdFVNQUpqZVN6N1gxS1R6V0J3R29YM2s2LW1meXZ5V2hRbE82Y1lyd0JpY0N2b2RWdFFWcFptNVF3ak4tWmVQUDh1Ym9kZEpqZG1VODF4Q2ktQzBzWXJlakhSQ1Nyc2tqbGxib0xZM19fazMtMW1WM2J5Z0tFUG53X19RaTB1Mm56ZU1hX2g2OGhsYzRnQUtOUlF5VkRndEl2T2FvRw?oc=5</t>
         </is>
       </c>
       <c r="F71" t="n">
         <v>1</v>
-      </c>
-      <c r="G71" s="1" t="n">
-        <v>46055.98170138889</v>
       </c>
     </row>
     <row r="72">
@@ -2780,24 +2561,21 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Opinion: What should artificial intelligence mean for fleets? - Fleet News</t>
+          <t>From ‘nerdy’ Gemini to ‘edgy’ Grok: how developers are shaping AI behaviours - The Guardian</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 09:35:37 GMT</t>
+          <t>Tue, 03 Feb 2026 20:36:00 GMT</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE1ZWEpUMkZKUFFMV2VuUTFUMzNBRDRZSGhaMWN5LTVjZEJ3SF8xcXowd2lydHBUcUpsZDhYcEVFTVpSQXprSU1qTmVhTTlSdHNUaUFFa3hrdTU4ay1IZXVPMlNNWWVMRV9YSTV1d0o2WHF2ZDZfcG55V0xxSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNaFZVa3liZzhLa1dvUk5RVFc3d3h4MDVqbEkzY3lJOUZ0bzN6b0ZQZDVVLUdLTGF3RnFzZHA4aTFwN0Fja0I2WlhoTFYtTmhZa1BJYU9JSldfQ29Cd1B3WktreDR5alJSdUtCU2RRZTB3VGFocDl6eFhINHdIaEJ1VFpqTk1yeHlZZmp5Mk9QUk82dmtRVG5YZktURGx1UjVmZFpSY1BxVlduc0hNRlZJ?oc=5</t>
         </is>
       </c>
       <c r="F72" t="n">
         <v>1</v>
-      </c>
-      <c r="G72" s="1" t="n">
-        <v>46056.39973379629</v>
       </c>
     </row>
     <row r="73">
@@ -2813,24 +2591,21 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AI and its impact on work: how companies are being transformed - Orange.com</t>
+          <t>9 indirect tax filing challenges technology can solve - Thomson Reuters tax</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 06:01:08 GMT</t>
+          <t>Wed, 04 Feb 2026 03:30:35 GMT</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPbWFwTmNLZ1VEOTNZLWpSMEFCNzhpWGpybHhfd0lJSVM0MWFEdXN2Q3hCc0VubzZlalJSbW5zcVJNMTRtMmt6ZEZyMnlWcFRBTE9BdG82Q0ZLZ1hfUDdTa1ctSUNTYU11TTM0QnhTa3E1ZVZKclplc2hJbTFHWXljWlR3V2tSSVZf?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOMXB2MnJybjVnVGVlR09Rak5vakU1NEs4QmZXWEM0WndUTjRfUTBlb3hVaUxEYVR4ZWpuQ0d2SlVvcnFNN0NXY2swYmV5RHJrSktGZkg5UFM4UFVTTlhUTFVRUmNKNTlpdGZRb0dxZ2pyV0JqaWpPMzItX2RBb1pUZnA3SGk3SEZqNVM0cw?oc=5</t>
         </is>
       </c>
       <c r="F73" t="n">
         <v>1</v>
-      </c>
-      <c r="G73" s="1" t="n">
-        <v>46056.25078703704</v>
       </c>
     </row>
     <row r="74">
@@ -2846,24 +2621,21 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Liberty Global signs five-year AI and cloud deal with Google - Proactive Investors</t>
+          <t>Aberdeen Science Centre steps into world of AI with new theme - Aberdeen &amp; Grampian Chamber of Commerce</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 07:55:00 GMT</t>
+          <t>Tue, 03 Feb 2026 15:11:50 GMT</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQeVJhOWFLVVRlcWlmOGVfdnRuQ0V6Tl9xdkZsYnVvOFlrc0w1UTFTRzZrdTNfNXVyRFRFNzNRV0RUcmVUa0JLbjN6cVBBeGpZMWx3U09VbGVWR1pkRXJYQ0VCVXRmV25jdnZwX25lTWVJdlEzZFMyOXdtVm9QN0p2LXRqM3VEQUlkMDJKcXQ0amZTMlFVaFVFeDg1Tkp2Y05fN3UtckM0QlVBOXZOTTJNZHdoS21KSjRaZy1fNGtaS0pZZDNMVjlkb1p0U3R6Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNalo5Y3l4UTZST3JaSGp3c2t3cTZZYzNhVUxOMDA4TFFja0QtT21LSHlnZW5vd3VpM3RiN1JEQkFJRFhQZ1FBdHJGOW41c2xlX015aEdYQzZ1ZGdVUEJGYzA1WEZzOEJhWlp4UXhYR2pvTnVWQnNvbnJXMjYzLTg0SG52OWVxRnR2WFVCTEJnWkhSSlB5MnRRbGVaU1haUQ?oc=5</t>
         </is>
       </c>
       <c r="F74" t="n">
         <v>1</v>
-      </c>
-      <c r="G74" s="1" t="n">
-        <v>46056.32986111111</v>
       </c>
     </row>
     <row r="75">
@@ -2879,24 +2651,21 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>HAQQ Legal AI bags $3m to digitise legal work globally - FinTech Global</t>
+          <t>Alphabet (GOOGL) Q4 Earnings Preview: Can AI and cloud momentum sustain the $4 trillion valuation? - marketpulse.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 09:25:27 GMT</t>
+          <t>Tue, 03 Feb 2026 23:04:00 GMT</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQNV9ub1NnS016MkJZdGJLd05RV1JTdGlBbGp4Mmd3UGN1TGdOMm9tcmY4MFJfbUhNQjRPX2JmakIzcFV6N2tZc2VYNENOY1JrUlphdmJ2a08yZjdXQmwyTTdPb1RrVFZEMklaVVY2dUZIcjNmWDRBaXJHeU5faWlqSXlFSTFJWnBWMWVuT3lKU1Zydw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPUnl1S1J3dFVvMG9CMEdqcEphckNVTHVkSFFMMmNDb0JaUWhNMFNMM3pvRWZoRng1RmxBSG5UX3VRNFlFdTRjTDA1dngwRXl1OTUxSGhHUlNuelZMWmx3Tzg2YTBvYjFOSEpTMlpZeHU3eDJFWmprZmMzZjdHUDEzOFNhTkFhRkJnQ0JlVzVKWUh5NzJDSk1JSlpELVZyRkVTMW9tdlpuTkZ2akxnYndVbGJvZG16M2VYSWpqNVF5RUhoSzNYTk9qa25n?oc=5</t>
         </is>
       </c>
       <c r="F75" t="n">
         <v>1</v>
-      </c>
-      <c r="G75" s="1" t="n">
-        <v>46056.39267361111</v>
       </c>
     </row>
     <row r="76">
@@ -2912,24 +2681,21 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Alphabet Q4 2025 earnings preview: cloud and AI to sustain valuation - ig.com</t>
+          <t>Leveraging AI for Optimal Clinical Trial Design in Oncology - OncLive</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 05:21:31 GMT</t>
+          <t>Wed, 04 Feb 2026 00:27:01 GMT</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQcnY4a2J0bWRPZnJxSGRHeVYtc05FaUY1MXgzQ3NEVkNJYjVIM1BCT0lFblVJN0xkUi1jZ0ZMQTZnQS1IYVB5Tm95cXJfSDFJWnBFd2gwbnVVcXg0SUMzVnRhRXZld3lTdHhYbU9lS1lwOXB4SGFZa1JHc3diTzZjZF82OUlwYlFSVzE5YjdjWW1PeGsxLTFtLTBiMEFycVFxa1hsalpwWnlGYVlkN0ltbnFUcVlqM3U2ak91M3FKWC1NZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPd29OejkxVVNVblpFcUpvbFdIQzAtd1FZaE5GemJURU1jUk9XSUtsbkxTTzNleVFNQmdlTWNtSjhPLTVrTXIxeXVDWHRlNzBBM1NYVTNCYTRCaHI4TlRPRE9UcVJUc3dSUm9QR2R0akU4Um1tWC11bks4X29UVFFCQWdZenhlYzM3NmRlWWk2RzhZdw?oc=5</t>
         </is>
       </c>
       <c r="F76" t="n">
         <v>1</v>
-      </c>
-      <c r="G76" s="1" t="n">
-        <v>46056.22327546297</v>
       </c>
     </row>
     <row r="77">
@@ -2945,24 +2711,21 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SkedGo unveils TripGo Mobility AI for smarter travel - IT Brief UK</t>
+          <t>Hospitality Tech360 launches programmes tackling leadership, AI and the future of hospitality - hotel magazine</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 08:00:00 GMT</t>
+          <t>Tue, 03 Feb 2026 11:48:24 GMT</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPbE9KYW8zbThNc3hzaWxSQWtpN1NDSlJhVVlMdWpjUzRESXJoWTJ1MzhSSHVaSHVYLXNrSzZ1OXJqeGFJd3M5VnFkYjNtMXVwT19tV2Z0c0tkaTRqQTZMcW1IM0V4eWxnWEdkQXVtZk94bEtIUzlOSTFEbUlYeGZkMUg3aEdTSnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOTUloLWxxbENQaVVhU1hEcjFNLTdGMWZWSTBNdU81c1o4ZzA3SEZXaWo5aGEySDVZVnJ0cnQ4QkFnWUJXVjZJWndzTGdPQ2hEVlh5MDZrS3IyS0ZYUEZ0MTQ5dmRMSDJuYkEzdzAwVktYOVJqeU1LZmdfNkcxb3ZIYzl6ekNwcmlHU3EzWE0wbnpLb2VIYUVJLW44QmFtQnVqSTNEVWNuX1BXclJhUjhRT1pfbnh4MVozMzFwTUFQckJwdw?oc=5</t>
         </is>
       </c>
       <c r="F77" t="n">
         <v>1</v>
-      </c>
-      <c r="G77" s="1" t="n">
-        <v>46056.33333333334</v>
       </c>
     </row>
     <row r="78">
@@ -2978,24 +2741,21 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>UK and Japan strengthen science and technology ties - GOV.UK</t>
+          <t>Musk's SpaceX and xAI merge to make world's most valuable private company - BBC</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 09:04:44 GMT</t>
+          <t>Tue, 03 Feb 2026 09:31:06 GMT</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOQkZQLVZCX0pweG43Y0N0dWNXUXFGaGNsWUN0b0JBb1FFek5FREd3cnJXR0dFRGY4TGloaGlaRlFvMGo5SmxpZmFwVHpxbVdxX1RBTHN2T3dFc0M5Zk1uOTRDU0ktQ2NfRDdPN2xQVmpuanhLRHFIWjhPaHNJRDV1Rm1zVVQ1WlRBOEZrNlRsYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFAzc09Ibzl2eWJ1OEQ0VTkxakNQV1hxOERGX01GOTNYUW5RNlRwNnVNbzdzSGR3TXJnaTNYTUdkT1doUXdwTko3ZTNJOWxNeXJTampQUVhSRDZlQQ?oc=5</t>
         </is>
       </c>
       <c r="F78" t="n">
         <v>1</v>
-      </c>
-      <c r="G78" s="1" t="n">
-        <v>46056.37828703703</v>
       </c>
     </row>
     <row r="79">
@@ -3011,24 +2771,21 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Musk's SpaceX and xAI merge to make world's most valuable private company - BBC</t>
+          <t>enclaive secures €4.1m to scale confidential computing across multi-cloud - FinTech Global</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 09:31:06 GMT</t>
+          <t>Tue, 03 Feb 2026 15:22:02 GMT</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFAzc09Ibzl2eWJ1OEQ0VTkxakNQV1hxOERGX01GOTNYUW5RNlRwNnVNbzdzSGR3TXJnaTNYTUdkT1doUXdwTko3ZTNJOWxNeXJTampQUVhSRDZlQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOQmFLR3ItVk1aSW10TjRZWG9wSjk4d05tVHlLekNNVzdGeW1uanh3bGpJRlVoZnVvejY4Umdmelpya0tLMm02QnlrWXpsRDgwZHBPckdTclY5M2tySEVPS29qRVlrT0NucXZoZDV6LWlHci0xeVZMY19CRWlPUDB5OFEwajU5ekJZWWVDelZuaHFMSWFMNDhiM1lCV2E3Q3VDNHpYX3Jsc1dNQnM1?oc=5</t>
         </is>
       </c>
       <c r="F79" t="n">
         <v>1</v>
-      </c>
-      <c r="G79" s="1" t="n">
-        <v>46056.39659722222</v>
       </c>
     </row>
     <row r="80">
@@ -3044,24 +2801,21 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>UK-Bulgaria: connecting semiconductor expertise for growth - GOV.UK</t>
+          <t>Perseverance: Nasa's rover makes history with AI-planned trip - BBC</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 13:59:31 GMT</t>
+          <t>Tue, 03 Feb 2026 14:21:14 GMT</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPUHdYRDVQYWVLZjR4MnFna1dPMEJYd25Bc3VvdllKVGJ3OXAzcGIzUy1zX3hQUHhfZVdlZExSZWVkVUc1dGF0OG5ncVRpNkp3YlNaaFBKZjczUm1ET3hBMVlRR00xbi1oVTZtS3REQ2tjek42Y1lKQUdTclFzT2dobGhIdE55QjVsVzFqTUJ3U01aZGVISTU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTFB5aXNmSUoxVDhEZjdEZ1l3WG84WGYzX2pwbDd2UFRsZFczWDhqRk9aMmZ1bENhZEFPVDFwaWtyV1Q1VVZndjNMVzBDTVlzZ1ZCZDc1QTd4VFZKQzBUVjA3ak5mTdIBaEFVX3lxTE1VOUNha0wtSkpOMV9icjRyeVBqWU4xZ3dWbTlsVnlwcjItOF91VkpITjV5UlFRaE9MT0xCcDU0akJKTm1ZWHB4U01qR29nS3pVMUtabF9XWVIxQ19ZbVdjZXNOVzRHNVRa?oc=5</t>
         </is>
       </c>
       <c r="F80" t="n">
         <v>1</v>
-      </c>
-      <c r="G80" s="1" t="n">
-        <v>46055.58299768518</v>
       </c>
     </row>
     <row r="81">
@@ -3077,24 +2831,21 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Large RIAs step up AI and data spending: Cerulli - Structured Retail Products</t>
+          <t>How Do Workers Develop Good Judgment in the AI Era? - Harvard Business Review</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 16:11:33 GMT</t>
+          <t>Tue, 03 Feb 2026 13:44:19 GMT</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPcFBPNGFHby05c3dkYV9CNVZtRDc1eVdFRmhmSWdJVHQ1cE5GamVNaElKVnoxcHRSRFFFQnFyUDE2M3dzVW9MbmRCUmJVZnJsWXVLb1dMZ2xVa0VxUVNOaXJSNklRdW1oWE9RUEtabUt5MHJiQ2FrZHIxUGc1d21XOXAxeXJXZFFiLUtVeDJ1Uzl4VlJZV1VQczVJTzZ6d1dyUTdRX0xB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1TcXg3M1ljSGhzb2kxLUVYejNnMjdhYVpKeEZUV0F3aV9EOV9pV21MTmpEWE9JR2RQUUFQSVJJZDVxNnZBQ1ZIRDlKOU9Jb25QYVVIX2ZEcGZOWXEtOHZBMXZIV3U4a092VG1UU0hheGpNcl9OZG8weXl0Rm84REk?oc=5</t>
         </is>
       </c>
       <c r="F81" t="n">
         <v>1</v>
-      </c>
-      <c r="G81" s="1" t="n">
-        <v>46055.6746875</v>
       </c>
     </row>
     <row r="82">
@@ -3110,24 +2861,21 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Barton Peveril case study - Google Cloud</t>
+          <t>CNBC Daily Open: Nvidia denies rift with OpenAI, while software and asset management stocks plunge - CNBC</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 05:13:05 GMT</t>
+          <t>Wed, 04 Feb 2026 01:21:00 GMT</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE4xSjkwTjBsTk1qeWV5WGhJTFNIUEdKZkRXLUpGaFRUQXEzYVNNaUxkUEpDcmU1cFFJNjlCOVlkU2l4RTV1RmZsc19Sa0VaNXphVjJ3NFNMY1lmQThs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQNHpZWElCTU8zN3VlSnNoeUhTZ2tPNWJyQzNzWDZOUldkTlkxcXZSdUZjWEswY3FVbmRCSjV2enRFY0IwVWU1S1JFMG9HV1JfOWtKN2Nla1lEVUtzZFlLb3Y1enowRkhrTlM0LTRDNlFacDZzclp1MGI5a2dmcUdOcjEwek5fREFTdHdnZzZ2M3NqSTAyQVpPMjhUV1pHaUduZ25QZEJ2V29qWmt5aDBhMGZlN3d1dTJEUWlUbjRUckxPVFQwd3Y2Zndib1Qxd9IB0wFBVV95cUxNZzlCQ3JZMnlJMEdPTTB0TThqM29fR3R2S3JTenFIX05YSTZFNlNzQW9RWDRzSU1uM0Jfdk83aWtXVlJsQ2lWTTdXYTh6U0ZPWE4zZHhvOXhxNURSUFVzdlgtUGFNcXJtcWd0U21GamdTbExFMERtVm0xVDZrS1E1VzdkVExPTm5MelQwelB0WmdlaHB2STkzQTEzZ2hsZFZ1M09IMkdORHNHLXdJYjJod205dUpPMC1XU0RQVGZ4M0x2YmtWUjdCbmFLVHZGUGhObE1J?oc=5</t>
         </is>
       </c>
       <c r="F82" t="n">
         <v>1</v>
-      </c>
-      <c r="G82" s="1" t="n">
-        <v>46056.21741898148</v>
       </c>
     </row>
     <row r="83">
@@ -3143,24 +2891,21 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>IT consultancy enters data centre partnership to support North East AI Growth Zone infrastructure and service needs - Prolific North</t>
+          <t>Dassault Systèmes and NVIDIA Partner to Build Industrial AI Platform Powering Virtual Twins - Dassault Systèmes</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 09:52:17 GMT</t>
+          <t>Tue, 03 Feb 2026 10:31:12 GMT</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQMm1QcjlSdmRjLXpWUGhqM0NpbHpTVkdZdU00OXZZV3lIWkxnUzhvQVEzcmpqampEN2pFSEtrb1hYcWptRFFkT1N0SENqMmRPSXVnWHNlclRjeU4tRU1Uc19hNkwtdU82OGJBUmZ0OGV2Tkd5WUhVZVFBc1daSkdsLTlVdVRVY2ZNMGtzaXR3YThubHgwU29pRVRGdWpOV1d2Z1hDNzF4X1J4NUFkM3ROQzhTcmZYajhONG1xcHhVUHZyT2x5U2VINDUtMnNoX0MwMVpuVjVRQ2lJVW1sa1RZZXl6VmhlcXpr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOb1BjODQ2T1lSRWZJUWFXV2laMjl6dElWODlZa0Y1M295UENQS09BMHR6VHJUTlpRcmFsUmhXclU4bnoxd2NBaHRTQjUtMDRmNG1Ob0QwTkgtaEtiNUFLbUtIUmVZWXFkVFBHUVVPSUF6UWw5N1hyWHJMQ29zeFlHZFduMEUwdjd1UXBFUTFKLXctOWNJWi0zSldSV1ZOTW5EZGJHelUwMFprSUlKLW9XY25kRjBMallKeTI4b0U0amRuYzlyTzhCNjlqS1U?oc=5</t>
         </is>
       </c>
       <c r="F83" t="n">
         <v>1</v>
-      </c>
-      <c r="G83" s="1" t="n">
-        <v>46056.41130787037</v>
       </c>
     </row>
     <row r="84">
@@ -3176,519 +2921,231 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Opinion | Where Is A.I. Taking Us? Eight Leading Thinkers Share Their Visions. - The New York Times</t>
+          <t>FormationQ, Cambridge, and IonQ Collaborate on Applied Quantum Work - The Quantum Insider</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 10:03:01 GMT</t>
+          <t>Tue, 03 Feb 2026 16:30:00 GMT</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPXy1tbFc5V2p0NVlhcHJUc2FQeFZkS21UMjQ5NXdkcUZib2VndHZOenBpTW5uOGZvYTRoUUZSN2tZT1c3M19XbDEtbkpVY1pPbWJmdmp5RDZuVFZtWDkyb0ZhbExleXl1NnBCVTJWSktzRHhicldUMnFOSmpLOXdLck5waWpnTUktenh4WmRsZExTdkNELXFwVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPS0xHRF9WcnY4VkFOSDFLd2RYdFpBVjdfbUJnd1FWRWRDb2JrbjkwbWdLUzc0bkpLc2c5T1pJbnFFc2NZcDRUd0ZKSmNEN3V3dXFFRGVrcXl3NGttZjh5VXJUZ0ZsLXp1dFJiRWJOZWlhREJLaFFTd1RsbGUzby1WTHh4cklCdnlkMXBvWlNDV2lwc2s?oc=5</t>
         </is>
       </c>
       <c r="F84" t="n">
         <v>1</v>
-      </c>
-      <c r="G84" s="1" t="n">
-        <v>46056.41876157407</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>VivaTech 2026 Confidence Barometer: A paradox revealing tensions between technology adoption, sovereignty, and cybersecurity in a fragmented geopolitical context - PR Newswire UK</t>
+          <t>Managing insider threats across the organization - Barracuda Networks Blog</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 08:00:00 GMT</t>
+          <t>Tue, 03 Feb 2026 18:22:09 GMT</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAJBVV95cUxPOGpDN3dqWlRvWW84MDgzaXlDaFpmcmJ5enpnUmpBZldDX2JCU1RiTlpUOGdudDhWcm92VG5rOGhfZlJIWjRPX2tSOG96TTVtcHNpUXRadklXdEV2T1V6WFdmeHFndnlTRmpfTjU2MFp1MmRXSGJJZE1nNDBlbmxFamZQb2x2bTBHVkxDUlg3WExYMWZTNGpqTjlicHdVTS1peENtbzJEOUhsT21OQVhNa21NMXJsRnVDdWg2ekE1U25zWUxSa2NNZmVaT0FBb1pjWDBhdmpEc1RIblVDVlNjUDFDeklldU5lcXFhdFhURTBGTnhZYWdFdXUtdlp2M2NKS1JobHF5aXRNdjJMQ19qV3ItRGF4WTBISExVS2N0ajJ2SW9XQXI0U0duWDVvUGQ3QjJWYkpORXNVbVZD?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxPaHVQWllJV0VIT2dJaEtVekhZTWQ3SF9BMTRpeDRGZG13OWR0V0pSSmtHdWtEOXByTTQwNS1yNEJLTi00cXV2eDJ2dzVqSk1KcUhjTFRfT1YzaGVHdTBWcGNWLVUxbGhsTm13MGNzaTRPcndGbTc5b29fWGh6WUg4MVhrdGxkYWJLa0xLdFlKUQ?oc=5</t>
         </is>
       </c>
       <c r="F85" t="n">
         <v>1</v>
-      </c>
-      <c r="G85" s="1" t="n">
-        <v>46056.33333333334</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Stronger sales at LadBible owner amid generative AI growth - Welwyn Hatfield Times</t>
+          <t>Prudential Of Japan Implements Voluntary 90-Day Suspension Of New Sales To Address Previously Disclosed Employee Misconduct - TradingView</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 09:25:54 GMT</t>
+          <t>Tue, 03 Feb 2026 21:17:23 GMT</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPNlVfREVpaUlFbU5XN2lWTTRRWTRHN280dGd6RlRBc2sxbnBrcHotOFE4UjdzMXJ3NUc3dlAydXRhLVB0Z0VoQjFEanZQZkdPbC1YOHJtYTdDOHNONk9aMjBvdHVrS2JYRThoOFoweUV3UVpUeWN0VDZiOHhZU0llbnBEWFJ6WFdrekFHT2ZhQlFvZm5HN0t4RmoyTmY4WXBma1oxV3JYUng?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAJBVV95cUxObUF6ZkV6bk03bUlPb0dRR0hsdkZpYm4tM2Y0SU1LaktjWnhHeFBCNzdnSkFsQ0xZTU5ORG1lRDk5elhodjlVV0VmTkxyWE5YWUpuUnpRMndmeVR2NWtDdkM1Tmc2VEtOdEhlT1VNM2ZLdnpHM1NzTUJUaFJtbldJUm0xbzdxV0pjYXpwOFB6MzhLWWlTNkNRbHk4dUtvRWhIdkM4RkE4ajBKNV9jc2pBV1RpY2dJNVJzVmFmNHVURnpvSVpGb055Wk5yS2pLdG43aWpjZFdtR01kbVVxX0k1emg4eXE0U2FBamkwMTIzWldETlVFbWd5UDhjcWZTU1FBTDhsdXhLWVg0UGFOUUs3QTNmY1dEYXBoMEZRUQ?oc=5</t>
         </is>
       </c>
       <c r="F86" t="n">
         <v>1</v>
-      </c>
-      <c r="G86" s="1" t="n">
-        <v>46056.39298611111</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>SDAIA Launches National AI and Data Curriculum for All Saudi University Students - BABL AI</t>
+          <t>News - North West council starts crackdown on housing fraud with launch of key amnesty - Inside Housing</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 00:16:24 GMT</t>
+          <t>Tue, 03 Feb 2026 16:30:00 GMT</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOeTl0aUM3cjYtMFAzZ3IzU3VYRlJtWUVoX2ktMVJlLWxSMlpRcHVuWHdjNkdZNFh3cE56dXNvWjhXbEdNMGdTaE5PWHh1TFNwbjNCQzFWd044c1g0SmFFNHRzRWZwRmRuTG1FQUFtVUNHYWtISXdNWm03SlNDd1lWREtxel9RTHBicDQzVG9KMmZNUXBKVExBT0NCaHEydw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNdGROQm16bWJmc1kzMUg4NkdDVjRLN241ZlNRZGRyZVJQUVdXcUFEN29teVNuZ2pjZVJPX1RUNUNsamxVUElhbXkxUUYxcGdYcEttTjJtR2pxMVdkU0Y4VGV2aFd2YV85Wi1uSXNaZ3ltYUpUTkxPd2sxUzBINTdpYjJhT2tIbElTUHZzbldFZmxrR0diRHI2VUVKdFVfZE1zSGcxSGZrM2NOLUo3V3VqRTRma0xiVWJYLWR4YkNlQQ?oc=5</t>
         </is>
       </c>
       <c r="F87" t="n">
         <v>1</v>
-      </c>
-      <c r="G87" s="1" t="n">
-        <v>46056.01138888889</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>01 Quantum Launches Quantum-Resistant Blockchain Migration Toolkit - The Quantum Insider</t>
+          <t>State adding staff to review nearly 6,000 Medicaid providers in Minnesota for potential fraud - MPR News</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 10:25:04 GMT</t>
+          <t>Tue, 03 Feb 2026 17:32:00 GMT</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxORWpicmVnSVI2T1RYamIwVm5aVVFoTXphMGlrSXRoWlREb0p4OE1SYWxiYmRwVEVXN2o5WU55QVp2TjJZNWJSRnJCOWl2Q1duQVFIRlJfdXphdGNUTi0xbi1JbVp5VUJfS0xjTDlHRFU1ZTZ5bmhOdWE5TjhYZ00ydnJEWGFiT085SXBqY0M2ZUNOLUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNUGlSc0lpXzN2X3VPbTFXazZ0cF93WTRYMURlNW1YQlB1bFYtbGZveS1aN1BpVWxfWVM3T05UckE4eEJVRU40STNtV3FCdjdrZEdpVWdXa0JkeGpSSVhGTUlJRWhYZWRXeG9XTk5wRndmZXQtY0R6bzVITlN5YnhyNWFoQ21oMldRcDdiaVBRN1JjOHhINTVWZ2dHYzVSUUIweTE4Z2ZneDZUeWFIYVd2YQ?oc=5</t>
         </is>
       </c>
       <c r="F88" t="n">
         <v>1</v>
-      </c>
-      <c r="G88" s="1" t="n">
-        <v>46056.43407407407</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>AI in 2026: From Promise to Pressure - Teneo</t>
+          <t>Man used social media in Gaffney property listing scam: Police - wspa.com</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 20:55:49 GMT</t>
+          <t>Wed, 04 Feb 2026 01:07:14 GMT</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOLXVwemdRYk1qT1FqeUh0VnVrQ3dZWVNmWU1jWDJFaHVRRWlUcW5ZbGowSXN4MFBaSGwyb3lkMEF5aHg4VXdpRWtrNng4b0dIWldJdUJBRl9MNkNoRndQMGQxVVpub1p1VmRUekJodHYxNnpZV1M5NFV5REJiaU5fMERPQnlkTEZ4NUVKcFA1QUxXYTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE02c0VSLXZKdFlTZDVjRmdHYUZiZVdpMXNfYzZXc1h3Wk54Wk9UZkM2bjFwX0tCNnpfcEc1ZUNZeUZsNmQyR2V1Nks4YnhvXzZObC03UUI4eXRyUVM0OVBsT05kbkR3YlFNWUxhSWxB0gFzQVVfeXFMTVpsZE8xWTBvTTFfanFtY2dob3BSWHlYWlZ4UWJuTVVnME9SYzI0eEo5RUJoSnJMOWxxRVE0Sk45cktocTVxSnpvODAtZmJhT2l0dHJEM3FVTzkybEptZGVYYXpUS2RLUnlWMG83aTlFNWtXQQ?oc=5</t>
         </is>
       </c>
       <c r="F89" t="n">
         <v>1</v>
-      </c>
-      <c r="G89" s="1" t="n">
-        <v>46055.8720949074</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>4 signals from the front lines of AI investment - PhocusWire</t>
+          <t>CNAS denies the information about the granting of 5000 lei from the social fund: It is a scam - ipn.md</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 08:04:27 GMT</t>
+          <t>Tue, 03 Feb 2026 10:46:59 GMT</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOZjlVTXNNMjJidTVkdzYzc3NwX1pVZzFXN09JZkprUnZ6a29NVTcxOHhhWTZZbDdKWENLNDltTEtLQjNMQkZpaEs3T25aMVBaQXlSaHBaOUU1RWUyc1JjOWU0UjVkRXpoWFlSbUtFV0d2eVBoT2R4ZlRpbDl2Zk4zN3F0OFkzT19PYTlRZnFZakNxZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQeUtTOTY5c2w1MjBkLWxRUHRacllZN0x5MlNuNDBJMmZJWW9CZEVPaEdBTzhIUDJIRUhEX1g3bThnYTFXRERpM1FwV1dxei16ZWVPaWhBUld1NlRrRXFRRVQydlRFZkdhMnJvbk0wR2R1Q0RfLWRNb1VxT005eHVkbWJlTDFtcjg2TG5Dd0dmWjZhb21Gdjg0Q2pXMG44LTh6U2ZyTnlZUXJfaXRCdG5mbA?oc=5</t>
         </is>
       </c>
       <c r="F90" t="n">
         <v>1</v>
-      </c>
-      <c r="G90" s="1" t="n">
-        <v>46056.33642361111</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Dow to replace 4,500 jobs with automation and AI as shares decline - Packaging Europe</t>
+          <t>Scam Alert! Social Media Page Claiming to Be Famous Krabi Hotel Was Found Fake - Thai PBS</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Mon, 02 Feb 2026 11:08:32 GMT</t>
+          <t>Tue, 03 Feb 2026 10:31:00 GMT</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPUG85LWpVTTB1ajhzU3dMMEtCa3NkMDRxbmpjZTV4RmlvZ1dpSlh2VmZZSW40VEV2QzcwTDVaQVltdnpKT0gya19GT3I1VnJFUGNjRkNGNUtobGFCS0RjV2x1NmV5YTQ3bzlYUWxHRl81dnpLVk1vVHlEemtUU0JDeDk0SVhDYXBsSG9pMXBJdnJfOWpPQ3U4NjNVWm1IeEhCT1l6aWUxQ09EaGg0czl5MXh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE9DeG8wQ20zZHhlcFdCQ2JSRmJHeEdBcjBqalAyQ2g1SGJId2pnWTY5Qjk1dmZkZDJXNDlsb29HWnFOTkpKQnFFSklTNEs2NlZuSTR3QXZWM1F2bGYy?oc=5</t>
         </is>
       </c>
       <c r="F91" t="n">
         <v>1</v>
-      </c>
-      <c r="G91" s="1" t="n">
-        <v>46055.46425925926</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>30,000 at Web Summit Qatar for AI, quantum and creator economy - Euronews.com</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Mon, 02 Feb 2026 14:58:41 GMT</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPUEx0MTRuaVlMOHV3YkdXb182cC1BZE5OMVFMekFxWVQzX1l4UkpJTFBtWFdVYnU5UDVnUTlTelR6ZzFnd3prVVR0cXlScThjV2Z0TGswU3RoeXA2TUhfdjB3alhVRllMTDBIa3d3ZjhISGxrbWNJVjl5M29YbTFjTmpFSndVWHRPZEpJVWhTN0VGWWM0WnlCX3hNcHV0QXB1QWpqaGE5dWsybWFGV3dOMw?oc=5</t>
-        </is>
-      </c>
-      <c r="F92" t="n">
-        <v>1</v>
-      </c>
-      <c r="G92" s="1" t="n">
-        <v>46055.62408564815</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Cortex Code - Snowflake</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Tue, 03 Feb 2026 08:25:58 GMT</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE56Vk5yZEJiZDdMbG9vclhSa0cwLVNKTGh4c3Q2QnZ2QnRDOS1vdVR5QVZvVDJBcTlHWGZQLWVXblBkSmxrMl9CeUhKRFlJZ2xvQ184Nm9peFlGbmc2ckd4MDRNRUJ3QlZ6OFE?oc=5</t>
-        </is>
-      </c>
-      <c r="F93" t="n">
-        <v>1</v>
-      </c>
-      <c r="G93" s="1" t="n">
-        <v>46056.35136574074</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Electronic Design Automation Software Market Size to Lead USD 34.71 Billion by 2035 Driven by AI, Cloud, and Advanced Chip Design - Yahoo Finance UK</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Mon, 02 Feb 2026 15:02:00 GMT</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQNUtvZDlhS1BqSDdfeFVBY1ZaVFNMd2ZOX3QyQk02UGtkNDFidHNkV3dLRXlVdEI4R0JjYkI5MzZiR242TVg1bTRJam4wakR6UUdJbzNXZmYzYUZhcC1JOV9EaTM5dWh4Smp0czlIaWJKYjRMNkNJQVlyMzN1V3QxUy1HbEhxRmF3QzUzMW8zaFJHSzB4Z0RJVw?oc=5</t>
-        </is>
-      </c>
-      <c r="F94" t="n">
-        <v>1</v>
-      </c>
-      <c r="G94" s="1" t="n">
-        <v>46055.62638888889</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>The Quantum Era Is Here—and It Looks Different Than Expected - American Enterprise Institute - AEI</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Tue, 03 Feb 2026 10:35:56 GMT</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNUkhYYW83TXNhSWlyMjBVQWdhVEdZUVNhcE9RdEd6aXNVNjF5V2NfOTUyYmZPZndiTURueTI4VGVzSlhZdVlZajdxb1lhN2FJeGhucDJOU0NpWDYySmViaFUxTk85VnZTLTQtOGlSZUhXU2dtVy1va2M4T2xTZTdDRXZUSHp0cUlRQjlKZlhpTEJ3d0F0TExwaUxYUzBtbmFQTXFSb2JZemd3b3c?oc=5</t>
-        </is>
-      </c>
-      <c r="F95" t="n">
-        <v>1</v>
-      </c>
-      <c r="G95" s="1" t="n">
-        <v>46056.44162037037</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Microsoft and Software Survival - Stratechery by Ben Thompson</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Tue, 03 Feb 2026 11:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE1ya2NoUTJ4OG5GTlY5N3JITkNGWV9rZEVDc1RFaGNjWUxBZ09ocmJGRGNVVm5ra3lyYkYtT2ZmYWFCSlBRMHhTVkNXdEFnT09HZ3lZYjN0MDRjakVaYnZkakptZkMzdU9Hdml5MlBn?oc=5</t>
-        </is>
-      </c>
-      <c r="F96" t="n">
-        <v>1</v>
-      </c>
-      <c r="G96" s="1" t="n">
-        <v>46056.45833333334</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Christopher Nolan Wants to Know Where All the Hollywood Jobs Are, Too - The Hollywood Reporter</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Tue, 03 Feb 2026 09:01:06 GMT</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOTEx5U1hxTlJrbERXNnVVbnk3WVl0RjVKRUJ0aVNXNFN1eERPQVI0Z09mcnVDa0Zob3NvSWw2VjEzd0hGZFh6c1VxeEVOYWwzSVVaTlJoZ1cwMVh5YU51eUE2RHBCVjlKUFB4Q2txMnBqUUVYeDhwQm1VS0NLT1JKdXRPZVdBY1NEV0JnNy1RazhFVC0wdy1mMTNuTjZJMDBkT2N5LUhCbjBGNGpBVjg5RThQSW1PU1g4cHFlYzlKWQ?oc=5</t>
-        </is>
-      </c>
-      <c r="F97" t="n">
-        <v>1</v>
-      </c>
-      <c r="G97" s="1" t="n">
-        <v>46056.37576388889</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Christian Klein Bets SAP’s Future on AI and Data with 5-Point Growth Plan - Cloud Wars</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Mon, 02 Feb 2026 16:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQU3d6S1RPNFdFbzJkR0Jfd25KTmZ4dW9lQkozcVlCS0ZPa2xOc05WWmhTMGJYbHlFVy12d2hnb2h2cU1XSmlrWC0tNkpHSEtpcENPRElUYlkyWXE5ZXd3Z2M3OGVXd3FRUDdWaldfNGtfc2FsMk94WmNqdnRONnVEY1k2dEpTeWViTmxyUjdYN1ItcEhuMHVZN2Y2OW53eUJrWXZGcEJ0cS1sSzNXS29qZnlXNnlmVHZO?oc=5</t>
-        </is>
-      </c>
-      <c r="F98" t="n">
-        <v>1</v>
-      </c>
-      <c r="G98" s="1" t="n">
-        <v>46055.66666666666</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Wales Taking Decisive Steps to Utilise Artificial Intelligence Technology - newsfromwales.co.uk</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Tue, 03 Feb 2026 09:40:07 GMT</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQdXBNVWhudzFuTjNGRHd2a0VwZ2FtdExDQVhFTnQ3ekRtSF83OHhHaXFVRkh2LUNpbGNwN0J0OS1sZ1JDUC1JZGY3LWlPWFNSRW9TbHpOUC1DclRTNVFPMVVtbGdMZU9JNTU3T3A4MUJJcks5UlhVNmR2ZFY5bHhCTVFPcFo2ZVBHVDFqck5CWDIzMkZ0YWdyVFp5bHcyYVNhRGwzdQ?oc=5</t>
-        </is>
-      </c>
-      <c r="F99" t="n">
-        <v>1</v>
-      </c>
-      <c r="G99" s="1" t="n">
-        <v>46056.4028587963</v>
       </c>
     </row>
   </sheetData>

--- a/data/daily/topic_feeds_daily.xlsx
+++ b/data/daily/topic_feeds_daily.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F91"/>
+  <dimension ref="A1:F107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,17 +461,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>National children’s report to Government influenced by local experiences - North East Lincolnshire Council</t>
+          <t>Vulnerabilities in Government Bond-backed Repo Markets - Financial Stability Board</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 11:08:00 GMT</t>
+          <t>Wed, 04 Feb 2026 09:03:43 GMT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPNmItNlgyTnhIUkppVk84b1RfMFh2N3FIRS1BS3ZyRktScGp0VlJqYmttdF9HeGgtVlFDekpOS1RXanJrZlZ5YTI1ZTBTQ1NkaC1qbHF3cUNKZkpOTWZhYklMNzR5WWFOT2xHSDJVcmh0cDRZbmRlMEtZODBQZ1MzNlg3WlA4NW5NSmFpaExlVFpMSXNlejlNaWhfc1laMjBB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNZ3FOQ0VSNVlhUkRKekRlTmpHRGRiNmN5MjZ3M00xNmxuQURwbEVfSU5iS29OX3BZNXNFcWtpQlZPMWtXRFV6S3k2Z1BLeGZlQ1FDX0N3T0V2NTVkbHljZG90X1J4RHFKLVgwMlFBOHJOam5nQ1lKZFFfTERScVctTWhQLXlrY2tjWnBN?oc=5</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -491,17 +491,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sudan, conflict - ETC Situation Report #36 (Reporting period: January 2026) - ReliefWeb</t>
+          <t>UK government must get its hands dirty on security, report says - Computer Weekly</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 06:33:07 GMT</t>
+          <t>Wed, 04 Feb 2026 20:56:45 GMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNX2haNFB0Y21DelpXNTZhMGQyVWxrYzlKVkJhUWFROEJ4WWhZSUNvbjRSb1FMR2NNV3g1VGtyVE53RUxSNVg3a2cxeDBXR1hoNHFTTWNoc3RhYUxHQWQ3X2R6cnBuQy1xUW1sTmE4SXN2Mm5hSGZ0TnJ5VTdKOTRjUi1rc2NlbVNmVEdnX2E5OFdNYml5MTJZNXd5M0JLaFpuQzFlRm9n?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNckVZV0N2d3d3ekRWMzBadWtLZW1zNzNNTHRSeWY3MTRIM0dfam02WTJWemI5QmJsTFhJa0ROcjZKTXlyTldDbEFoUFRtSEd6dmdpN0FISS00OGpuQUN4WXFlc25yTUlfbV9OQ19scVFUX1NYeHluQTFQb0JPSGZsMURhck1TYnA3cGp5bUJfeUN1R0NtLTJNS183V0FyYmdHSHJnRHJyR3RoLWVJ?oc=5</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -521,17 +521,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Government report warns Ireland lacks access to key EU border-security databases - VisaHQ</t>
+          <t>Marsh Report Flags Policy Gaps That Could Undermine European CCS Funding - Carbon Herald</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 20:52:20 GMT</t>
+          <t>Wed, 04 Feb 2026 11:50:15 GMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQNks4THV6akVUNEIwUjNXVVJ6VEN1aTNDanU1Y0QwalplRVNSSmwxaDhqdWFFb1EwMERKcWxlUk03X2ViNzQwZkRIbEVxOUZBeXZ2UVBDX1c0ZkRJS29UX1JYTzFSQ25hT2pvSWpEek10WGxwcllDNnloWlFXbGs4QnRScmw5Q1lFc3ZDM3ZFZ2tkdEJVWXBsWDAxT0I1cDdqQTA2VHZBNWg0Y1JmMlQ5bW1walQzSjRwaHM1b095NXA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPWXZyejNHNW9TNGp4ZC16MVNTVDhDV1FwdVpnalhFdG5JOFY3N0JOeUI2OHFYQ3JBOGwwbzRQVGF2YzVWRWVtZnhPQTJHV2t2TzZTR0tSQjFQV0RqdWhDazVRVEpUNnU2ajQ1X3FyZFo2QnRrMVgzRnZ6dkRmRGJRZjhJcGk4MWhJNE1abFppOWFSeEhOSWQ5YllCYURWTzQ?oc=5</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -551,17 +551,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Thriving Kids Advisory Group Delivers Final Report - MBS Online</t>
+          <t>Inflation and regulation among factors reshaping convenience, report shows - Talking Retail</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 04:20:18 GMT</t>
+          <t>Wed, 04 Feb 2026 12:10:09 GMT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPQ1lvX0FNbDhia2hlbVhlMnhSb2tKM1l4NlZ3RmZvLV82QzhnWmppcDZCU1dUNjNweE1DUlZOb21fVGlDZE5VaGdmUDE3WnNWNzlFQkktTDZpXy1nX0pFN2RqVXp4clNRdFZpQThsNHk5UVdzaE9tQ1hFblVnX1VkMmJSYjhEenFB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQNFp2RjBiNkE4ZEMwTlBEbmpUT09qdVRPOS1yb1RYZFFjLVY1MjJzNEFfTHgtOW9TNExCR19ZTkdVZGR3LWVlU3FFUjZoazFpYXFDbWd1XzA1XzQxTzhzak96aWpJRVlwNy1GTUhzY19keGtxaTlZb2NqYWxSRzI2bVo1YWlFd2syMmxFZWdaZVdWeDNZZjI5NFlGeHUwNEpjd1RQX2hSSzBoZTBSUjgzNWJhMmZyRnM2Y2NObjhpWkd4dw?oc=5</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -581,17 +581,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Policy analysis: Prospective changes to prevailing wage levels and impacts on international hiring - AIP.ORG</t>
+          <t>January jobs report will be released on Feb. 11 after shutdown delay - CNBC</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 20:36:56 GMT</t>
+          <t>Wed, 04 Feb 2026 17:01:40 GMT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNVFZfVmlvaDZhVXNZMjBKSU9aUFFydWxKTFlyRFZ0eU1FOEg4WDY4eGdDQm9FdkJtUVJNQmw3am9DZDRqZHVBeVpMNjlaelo4TWhiR3h0RDBCcUU2V3U3TmVUWVh0bzJvdnpISC1fWE9kSE5fVmhWYmtCS293UXltMnJYWHFaOEhlME1BTW5jVTRfOHNMNl9iMS12clFHSnkzYjVzUFlUR2MwNG12T2FaYWtoMmxfcU9BaVJRdzNGcmZTa2JV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxOTklhTHVoaVpUaW94b3k2N0lyS0VOa0tma252bDR0dlRZdFR1OW1vQnN6eWwwLUI1ZFp5eG1fRFY4S3RXd0F0bS1aeTJrd1dmWHdNNnhIQkhjd0FJbWVZaldCS3BmTTRCX21kLWRLUUt1Rk1GWjRjaDlPUEhSV0xBTGNn0gGHAUFVX3lxTE9uOUg5eDcwdThtWi1JWHhqUkhIVk9qaUtuQlM3OW9IZlFKQVB6TDVNNFg2X284Q1RwOEx1cUhoVW0yWlRUdWFFRURoaTVrVUNLeUFFaVZGZG9GOGxRQzg4R25fTTlFOW1GbV9ySEpQcmhsYTJKOVJxMzZNdXNndDRsYXBnY2h0dw?oc=5</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -611,17 +611,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BetMGM explicitly bans harassment of athletes in policy update - Yogonet</t>
+          <t>A rights report calls on the Syrian government for comprehensive accountability for violations - Enab Baladi - Enab Baladi</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 13:12:32 GMT</t>
+          <t>Wed, 04 Feb 2026 19:44:06 GMT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxORjZNV0FPbUxXU2tKM1lqamYtXzJNV2dSU2djb3hSOF8zVzJUbHJ3UGE2eEV3aGNpNHJUZTJEUlFpNnhHVmFIWm93QThIcUJnSW5QMHhPbFA2Yk9zX0FweGhYR0VZRDI3V20wWkRta1BvZVlkZGNJb3I2dmFpZVQ4TlFjYzhJMFdRZjd4ZDFXZ283T1RqLWhKeDFLcHY1eDIwZlhSRzVZeHhPejJKZ3FiMExjUjhTQU96YnlodjV2aHE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPT0p1c2lMcWJaOVdDWG9UQ2dzSGdXT2Q1dDdBTjZnNGg2LWI4NG9ZXzE4N1ZVTkJmVV9HVTNZcXh5V1RWZjJEdWc4ZjltNHg3N3o1T0JIMTRrYzlTUTdfakRVZ2hsaEdCeDROMm9lME9XWmpmbnU4ZjVFVENNMDFJUUpjN3VOVEMtN2FGa2ZqcDRnZW5DYjRiTFJDZ2pBa3ZrX0lHNDJEbWlqSGpMOWVvQ0pDRWZfaG9xd0ZybGx4ZDNabkxfZXNENHlB0gHPAUFVX3lxTE9FZ1Q2cUN0NjM1S3hZa0tCVUdjVVpOWEpYX1hZcjZKWkxaRzlPYWFCbExnUXVjaFFOaUtYXzI3a0pYamdEbE5KRVlZU01hYm1uVmxkQ3huNzFBZERZck9HNXZiRVJoMmpHa0pQYjFzT1M5WFFjcjg2cTYtNEEtWkE5eFlPMWFNYUxMbkdpbndtbWg0aWZpSWxOQ2lCVmpzN3l4dEdSWmkxRFJQdjNiRWNZek9lcXVSMlhzdnY5RWN6R2o0UFI4TEJJYUNYY3dqVQ?oc=5</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -631,27 +631,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>UK investigating first suspected breach of cyber sanctions - The Record from Recorded Future News</t>
+          <t>Dorset housing allocation policy update - Bournemouth One</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 16:46:57 GMT</t>
+          <t>Wed, 04 Feb 2026 13:00:38 GMT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQLVYxb29zZ3JfTnpfTHl1TGp3emJHQjNrR2ljZk9Zb2RsRG5mOFJGV0w3dnQxdW5BTjFlRzRnUEhmUjk0SFphWVBSeUo0bWZ4bWRzY3Z4R191QXY2QU1hTmJ1cGthVGwzM201TUtRc2NreUd5Q01HbnZjcHR5alNUQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE9sM01xMUlseXVoY1gxeHhueS1sM05USnhvUHpRTHdhYWVXU0RZU1NjVV8wd3lZQkVkdVpIMUNCS1V3RzJXVEwwQ2RPTUFvNEU?oc=5</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -661,27 +661,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vale's transfer window round-up - Port Vale</t>
+          <t>Government update issued on drivers reporting 'collisions with cats' in the UK - Daily Express</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 20:02:05 GMT</t>
+          <t>Wed, 04 Feb 2026 11:35:00 GMT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE1QTGtyOVQ4Mm9Nc3NxZ3lfRGpxN3diUktMS2Fnc2RhYmdrRl9adEN1N0Q0c3dRUjhrQjVaZU5MOFF1RzFPRi1mYnFBTG8tQVlfYWdRVXh4R3FqQ3ZYVG1sSE5fWlVyUzNsWWdPeQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPdHp0ZGhrS3dwVmJSNjRJZElBMi1yOXJXSnFUNVRYUmVxNUhPMVU5TmtDZnJUMDRySS1OSWRzaTdIMEFVZ2F4UnF5d3ZWb05KcHhlU1JzMEI0UG4yQWNnRVpHY2tHVFpxQ1JObkpwUTB0WTctVFB3RmJ3V0FxOTZOZHI4YTlKSlBvRHNrSlZfZ3RFQkFiR0hrUnBTWHVfQnJFM2cw0gGoAUFVX3lxTFB6b0tiekxTemV5VVZpSVNWOUJRN1pveEJac2dGdHhXR3BNUTdIN3ZCLXA0WHc2QlNrX0pYcDhHUngyYWcwVHNIMkE3OTh5dUd0MEZVTlZMZEZ2T1dVMGxlNTlOVUFhd3R2NVU2bVFYanJNSEJOZmtMNEY5ei1sRThpcnBQbE1nYUpma00wbzVpOEpLTUM4UzB3RWcxYlEzZ05KVy1sTmF4RA?oc=5</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -701,17 +701,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Disco Bingo, exclusive port tours and a mini circus – what’s not to like about Love Immingham! - North East Lincolnshire Council</t>
+          <t>Sanctions having ‘significant impact’ on Russian economy, says EU special envoy - The Guardian</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 15:00:00 GMT</t>
+          <t>Thu, 05 Feb 2026 05:00:00 GMT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOZDNwUmkxbGNOdFpTdEFhaWNxa2Vmb2ZfcFZHZjBnZVc4OEZxRlkwN2hnTDlKQ2RqdW5VUEdLRm5na2dQeF9BSlZuRW5wTmlGNTBmQk0zeHlRbEZCVjh0bWJNU1dYWlZOSU9IT3ZWQmYzb0MwVVRYdXM1NHhnc0R6eXZnMWxKN190MU9DWGNnZUtJZ2l4YTdhdU42UTdZWHN6ODZLd3BZVXNPcE15YkZZQ0t4ZXpRVFo2?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPSDR2eHdnRHNIdF9vVG9Na1NqSm80X2dkMHZuNi1pbER0anFsYUJtZl96RVNadHRRa2F0LTNIN1BtelYzRGIwMldCYUx2bk05MGhXcF91TUdzUE5RWE9TUFVpdFNkQ0pZQ19PQXoza1ZBUTBQZXBNMDJzTEpJOEczRXJfRzZSSnlBU0xXUVNoS1BqbjNJSFpDdEQyenBxVWVuYVIzeEpuSUZsLW4xTDR4My1CQ0xqcGRzRms2dFVycU9CNzdmUlZnd2xQNzY2Zw?oc=5</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -731,17 +731,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tribunal upholds FCA sanctions against Banque Havilland but slashes fine - Funds Europe</t>
+          <t>Canadian pension funds to exit UK’s biggest port operator in £10bn deal - Financial Times</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 16:07:30 GMT</t>
+          <t>Thu, 05 Feb 2026 05:00:49 GMT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNZGpzd005RFUtY0tMaWRyWV9PdU1MWkJreDRKZ21lbi1yTUItSGItRXE5VDJLNURDQUNqUGpoTEVaaGtiWVMxUjJ0VV9NZFJha0s3aFdjOXlweUR5ckxlR29mUExKUzVydEU4VmJBMWtJb0E4eTdfbXBUYmFobzdHdDgtanp3R2gtZU9mUHdXMlZqdlpVNWRfZHU0ZUZEWGM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE8wOS1JVzF0WVl4Zk1LQmlIcExQVFNTWkFWbWk1TGE1cG0wVFdlY1FhUS1tVF96LUZ2MkdBNWZzZEF4R1c0akJ5ZVlDODg4TFdPU2JDQ1NVSTF0RHBjZi1icFVvLS1YUVg2b2dFcUUzR2I?oc=5</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -761,17 +761,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fortinet: How to Build a Secure Digital Supply Chain - Supply Chain Digital</t>
+          <t>Maersk Q4 meets forecasts, falling freight rates to weigh on 2026 profits - Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 21:08:30 GMT</t>
+          <t>Thu, 05 Feb 2026 07:16:00 GMT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNUmVQOFVwRTZ6MmdWTE5JdVhZZ1lWQV9hWHdDR3FTbzFWWEs2X1JOMDNzMjdfQkNpNndFQ0psSmVMbS1CNENOQXllbUk2MGJDUjRxVVpYb1lWdUZMcVVwdDFSalpLRVVXVklmUm9xTDJ6TXlpdTJ3MXRrSjdObnpseXRDWXo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxObnVhWHJkZVV1T3ZlWkVndGFOSnZXbjFpREdEbnEzOTIyYkJ6WGI0VEhXUmh5MHRhOGlCM1N0MXRFcmJZM0lYSGdDeTlwbFNpZUd0TXlsNDhhRzMyeEpHRV8yZUVOTU82RFdEVm1UektFYmt2UGpUcXJrLTdBWm1VRXE1QW5NZS10UlE?oc=5</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -791,17 +791,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Canada faces ICSID claim over Russia sanctions - Global Arbitration Review</t>
+          <t>What are key themes for the European logistics market this year? - Savills</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 22:09:45 GMT</t>
+          <t>Wed, 04 Feb 2026 21:03:29 GMT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPSzRidXRjaDhZbF9wQmxWYkhYMEJkZlQxRkd6bUIxWHI1dEtZWFhNb29DR0c0VmFKaWo4Tm1tQy1uczAyMlV3YXJfVEc1c3FidXZKWGVwdGpCWlphUThEcUJ1cUZ5a2RBT1FfQ3pmeGtVbVhqUUNENDcwa25rN2NJUXRYZi1hWUNfQm9yUHNKZU83d1p4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxORzFEcEdlM2JYRVZwQjRZdjhUelFuVjB1TGgwSHdWemdKbGU1WHo5a0hCcUVzVFB1ZHNZS0pabFhOXzF4MWw3X1BmUm8wRGZlMmY5c2dnTjdRVFZ0OUVGc2cxekFpb0g4TnIxTDF2aUVzWThiblV2d1BNWXNnb3Nqc2NDTDhwc3FMVS16RUwtRmdPR2gyZUlhQlFjcUptMlZPeG9iMS1GT0JSZTNsM0JUYlRXSGF0dzc0YlJERzFWR0YxdnNPbGZ1QzBncWNuX18x?oc=5</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -821,17 +821,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Op Chirk: Over thirty arrested in Swansea and Neath Port Talbot - south-wales.police.uk</t>
+          <t>Pre-CNY sea freight reliability is breaking down at origin - Metro Global</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 15:00:00 GMT</t>
+          <t>Thu, 05 Feb 2026 07:15:15 GMT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOeHByb0hvOHcySzBpb2liZl9zeUZGdmJLMTl2d0NIRnRYdnhpelNmV0Y5Y2NYS0VBQ1RhMXBrNFVTMXBqZTVaYUExb0pqR3h2NDZuSjFrRDlTZ0lZVmNpSVVlWWhieHFNVGU2em5tbU1QajBONmVQYzROdHFDR2ktWmxfbkZhemFEbFNzbGJzeTlZRzBnOUJiT1dFLUI0YVRLTjlha0xxcmROblpLOW9zT1NxSF9SQjQ1Vm5PWEIya3YwVGd6OHFHZU5ocFRXdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPTUg0U2IySHNSX3R5cHdybEZHUVNiVldrNmdOV2V6SVdZT0xFclhVWlFWakxKYjN1OTlnRTNadjZUR2syLXJCTi1uOXJOQm9pSUt4VUJETGRkSkdCb3dMV1cyVkpySXMxWl84Ukd2SkZnb09Gb3o0MzR5ZVFiWTh5dHdvR0pJNWdGSUtSX0dMUFR4QjJNeVE?oc=5</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -851,17 +851,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>What channel is Port Vale v AFC Wimbledon League One match on? TV coverage, live stream and kick-off time - Radio Times</t>
+          <t>Charge Forward! Innovating across the Battery Supply Chain - Natixis CIB | Natixis Corporate &amp; Investment Banking</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 14:50:13 GMT</t>
+          <t>Thu, 05 Feb 2026 06:56:15 GMT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNQm45aDF4R01VeW1FTDdRbS1Wb3pTWC1UcUNKdF94aHlWSU83ZEFtcjJKakRudkV6MnBtWEhCTmVCb2UxUkxBa0d1UXlUM2RReVNjNUZwQlZsRnJTaklMdE9tblBCVjB0QlFUODVwWjl2c0lWMWhVQ1hwNERwd1g2VDd3YUYtalk3UGpkeUJ5UExtNE52QmpQR19rZGo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQVEpZOXlRR3NrSVhla1hUZ2xmRXg3Y1RLdmxLT2FseUROMEdyZUd2Vy0yT3QzdG5yMHdENEptdjBkUmJxODA5bTItWEpvME1wSndua1V0dlFYMEpvUU5Jd2ZGLWdwVU1mbHlNbXp3LWZwUzg4OEJNWmdOY1JKT2ZVMnNZQnNERFFpQUZNR0praWl0aGhNdk5DYTNzYw?oc=5</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -881,17 +881,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Deadline extended for 2026 Everywoman in Transport &amp; Logistics Awards - Fleet News</t>
+          <t>UK agencies launch joint operation on crypto-based sanctions threats - Pinsent Masons</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 13:05:44 GMT</t>
+          <t>Wed, 04 Feb 2026 16:04:39 GMT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOSVk5MHZuNTRobjd2dWdXd2NtNFREXzcwbk9reklJRnRBNnp5RDBVUElzUnpFRTU0ZDF5aGp5WVktUmY0d2V5NlYzZmpqb0JjS05HQjZTRk05ZjhjczhDSXdjTHllR3pteWZXU2ljaHZQdUNDamFvV3ZKdHlyS2JROU5sZ1A0S2dmRVFVVEZUQzNySTNmaklIaDdRUllkN21FbEp4cHBxbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQT2V0ZHY1dFpvQ2JGTGdCdGJRY3JfaUVBSUE1T3JCaVJKaTY1dzI5eXVvZGJEMjhxaDRMNzBJT3ZqbjdSOFdCYzQ0WXJXR1hoVmtVdVJMRkNMZHdfWldNUVo2dUJMTlhJa1FmT2M0UWNCMEZQb3BQX3lEV0U1YnJISllvUGZ5NFNFdWhIdXBsNDdVUUlYdHo5VXQ4aHFRLV9sMjMzN1ZabTMwdmFBUlJDaQ?oc=5</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -911,17 +911,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Report: Late Maycock winner seals three points at Port Vale - AFC Wimbledon</t>
+          <t>Miller’s CLC Risk &amp; Compliance Conference sees industry leaders gather in City of London - Today's Conveyancer</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 17:06:53 GMT</t>
+          <t>Thu, 05 Feb 2026 04:51:32 GMT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQWklEWlZuQmxKQjdwbndIRS1peE8tdEJDVkRqZVZkWWNmUUFPSGUybDNsRFRnSEVpTFhYeVpJZUxSQk5LM2hucnRwUFdnNE9sVlJjOUZpQmRsVmRrbENUR0FpX2hCbFRuZ3NMWnJGT2xocjhzX0ZGMGJXMnhmclc2bXdWY0tjd3E4NDFYeTF1TmpFRkh4VktSMUVzOWdBNzljUHI1WTFZcHpGVkdpRzA5dWItZU91TDQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNT2xWeE85VFFtajN6X3J0b2VWR1lsVmZ0RFRjdFkxcW91RFd4TmFONTQxSEpoWkNUc2g3MmR6eTQwUWV0bUpWd2U5b2JwdHh6UldZM1RtTEJISGwtaF9VVEtWOFpxWVFOZjgzTzN2V2xWT0w0QWFxVmNMdENHRFoyQnRBQUFJUUdOUjE5WGNyMElHdTNCMkRkOW9zUVR6N0RSV0lCQml3ZVZIUG1GbGJCU3o1NzlxQXdLcFE?oc=5</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>How The Old Dominion Freight Line ODFL Story Is Shifting As Analysts Rework Expectations - Yahoo Finance UK</t>
+          <t>Dave Clark's supply chain technology startup Auger bags Meta Reality Labs as a customer - Retail Technology Innovation Hub</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 05:12:00 GMT</t>
+          <t>Thu, 05 Feb 2026 05:32:24 GMT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOeC1zTXRDb1BBSElUMzhrNVEwSWZzemI3S2Vwd2NmaTNZSHk5cGc0NDh2UXR3M0I0WUdwZzBOOWY5eWxUdGFQc0gxX1F6ZmxVeTdlRU9sRC1nSVdXRlp2NWpXcmd0cWRBaHNPUVlsRG5WTkxvNEJreW42VHZYY1VhSE1lOHhSUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNRUNnUHNTSWtTTGtuSHRjZUZBUk01N056Wkk0UlJ3dlBORHItbUpOMlk5TFB3bTM2eWYxSTZwRzlVQWpTTnFZc3RWaE5ldHRiNURGeVIwVVctSHhwUkxGZjJudkYtVjNocHFQM3ZxWDlGTHljT1BPeW9QQjBsLUdybVRBOE5BWldqXzRnWjhiS1VxX2VXY3B2endaQzF5dEhkbTlBbVg5RXVnOXNjRDI4b2Z1QjBxOC1iSjJBM2dGVkoxeU5XcUtpU2JkM2kzazR3bmc?oc=5</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -971,17 +971,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DNB shipping loan book rises in fourth quarter - Tradewinds News</t>
+          <t>Divided EU urged to sink its green shipping plan amid US pressure - Euractiv</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 07:06:25 GMT</t>
+          <t>Thu, 05 Feb 2026 05:01:56 GMT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQajdGNldSRzk1V2E1cHVXM3J5NmdVRU9zcFp1NkRxdHYxQ3czUzVpZHY3RmhsNWh3aHZibUcxaGt6Y200c205QXJUUmZDUHhvNU1wN1ZjUXliQnZ4dm5DMV8zaGFQenlyV29PYzF6djJ2NzZjY2YwWTE1RzFXUHN4d29HTERSU3Y4UkZzMkQxeENtVEJsYk83aU9LcjZlZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQRUtlNjJIMnlFVG5HYWhwV3N2OHFnajNEWS01cmdSN0YzU1lzaFNRdEZ6VHhhT1cxdnBPdFFXYTBYdHZPc2d5WUEwRWZJNi03dXNJVkFnMUpFODhxdlFTak4zSGxOdXJFSTVDcmhKdWVhR3hYdWYwTTU0eWY4Rl83V2JLMUczaVp0M1oyUy1abnA1Y2owNnFVZmwyejE?oc=5</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Andre Gray is a Valiant! - Port Vale</t>
+          <t>Kreios partners with BVI for improved operational fund compliance in Germany - Funds Europe</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 08:36:50 GMT</t>
+          <t>Wed, 04 Feb 2026 16:06:04 GMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTFBmTTI3Q01qcGdCYjR1Qklwa3JNNTNNUlJ0c0VNeGhQMTdVVmVYbGg0aEgxT0x2VDdlcnNLOEYtMDg0THU4MHlCcmRObDNfcnhabjJBTXQzNFdqVm5wWnNfUA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNQ0tzZGVaLUxLVzI4M0M1b0l6V0lOaXNFWW01UmhTUHpCc2xxTks1OUVDZHdSV25UQ0dYX0VwYnBYMnJZVl84cTczN0YtczAwZGVYQ2V4SkllbjFTc3JYX05QalRvM1dmTE01VXdkTzZXRDhrVVh4bGNvQmtSQllsQjRZcjhySzdsMjgtbldueFUwdllUYjBqOFJQNFAzMVVLTE1uVA?oc=5</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1031,17 +1031,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>What do EVITA Trials Mean for DP World's Decarbonisation? - Supply Chain Digital</t>
+          <t>Learn how NHS Supply Chain is accelerating Scope 3 decarbonisation - Logistics Manager</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 20:36:12 GMT</t>
+          <t>Wed, 04 Feb 2026 10:00:57 GMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9tRW4wWlhVWlQwdzRYcUpRdS1OSkwtUWh5VFBiN3F3cURlU1BiTjliMFFUVWx1eG5jclBKSE5Ibk1GRFZEaks2VGd0VVdaLXRzeUNleGRqMWZTbUJfcDZxQUp3WjA1a1pVd2lKSjlwSG1CM3lJSWpFVk80Snhadw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQOVZMY2ZpblBTNmNndGFMYk9SbGV1d0RsZC11MTdscTZXWmd4WlZ5U2dHbXo5eU52dmdVSjQtSkZlZWxyX3k1d0xIUmpJanNNOF9fNDFLd1JiQjAzNVAycXp0akdUeWtBc1ZzUkkzdE9QQ08zMEtYZi11SDR0czZ0X2ItRnhZMGZicVFmRDRfSVQ?oc=5</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1061,17 +1061,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Will Cheaper LNG Reshape Europe's Supply Chain Strategy? - Supply Chain Digital</t>
+          <t>Can a sweeping statement about tech compliance help deter the dark fleet in North Europe? - Tradewinds News</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 16:59:23 GMT</t>
+          <t>Thu, 05 Feb 2026 07:22:56 GMT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOSTFGNkZPaGZVMXlYWFh3NEw0UXdvaWhGMWZ6UjJkdFM0bll1Tmd1OEZ4Y094NDdMLUt2dGdHQVdCY0s4WkFaREVZS2JSdzcxTmNLSHNPNEFidW4wWWhoU3djVXF3WnNaU2k4MjNvYVdLRWZoUjdGdURlSDNzY3NMZFhpVENXem8zUjlCSFl3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQczQ3UTlNY0hIYTZwVWNFRUNrc2tOZ21fVHJFNFhwVHE4UE1wZURRcHlvbC1tZzNkNFVkR2drUkhsd3lVOUVEWEhfVXRfdWppOXFJcFBsMjhlNDFPdlZ4b3R1a0xrVjNKbkdGT1BUVzkzWEpwVUpGTEcyX2JkZXZSdjZCR3o5cnJTRFVTdDAwbDRYMi0tSVNNRTNaNW9QbjFFSndmZjZnYXhpSDdxUTZMN1FZb0Roak1YLWc5S2huTEVUc3RDRTUtQlczeFBYcDN6Y2d3cDBJVQ?oc=5</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sumsub Partners with Fireblocks to Ensure Travel Rule Compliance - Finovate</t>
+          <t>Port Talbot is a crucible: Jon Doyle on writing faith, masculinity and the weight of a place - Nation.Cymru</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 22:27:00 GMT</t>
+          <t>Wed, 04 Feb 2026 21:00:14 GMT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQOUtVbXppa0hOcUhPTmR4Nm5RWDJtdWRaVnNyTERVdjkwT0NnRE9ObDl5aWRtQnhIZ1JxaG4tOUhPMFhrLXg3d21Ga1pZaE80SVZXdEl0MHViYUNiLXVCYTM5U2pDSmxUOFFad01yZkstSTA0S2Y4czEwSGx3dEQxT3Z3aFRiVGlQcWZxd3lnUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQRWc4Z0dXSkVETjE1OFgxajZpSGNZbFFIUVZONnlMVzdEemhNMzlQR0NBTGF0clp6Y1BCbWJpeVBvWXM5bDN1Smx4OWFXNXR0UEE0cXhLcnA0Um1waElMZ0VUQWJNT25uaHV3Q0N3Ty13OUxRS01KUW5pZ3RrQW5ucUlOMjdNUWhsYk5kVDh6eGJmQ3RSamFJODBnSnpEZ05LYTZIaS1pb3EtZHFnQXY1d01TZGtZWDBDd29QRQ?oc=5</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1121,17 +1121,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Stiffening European sanctions against the Russian oil trade - Brookings</t>
+          <t>Opinion: What the government’s new approach to sanctions and export controls enforcement means for you - Chartered Institute of Export &amp; International Trade</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 16:57:39 GMT</t>
+          <t>Wed, 04 Feb 2026 10:20:24 GMT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQWlNPcHQ3bkY1alBCeDF6V2FKTzgyZlY5dVNiZjdja2Fnb0RoZThSUHpDaDRKRVQxaTY1U0pKbWU2UHBCU2NnQXd1NVFWRHpmQ1JpWTdhb0w5RVJLN0VPMGFJRU5xclhVaEt3OUNuY1hzRk50bDlXMmVIZ0VTWHAwM2I0Z1ZwM2hIaGl3OEJsUlJVLUVoekhuNl8wYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNU1JoRlR0Ql8tbi1JSllTaV9qaGc5MXl1S2lYYXFnalZxemlCVllQSVlDdldkVEZvRGJjYUgxY2RHTm02ckQ3U1hVczRZMWhUWGh3bHE3Wkc5OTVrZmJVYkFqSl9XY2RTN0hZdUM2cFRrbWFwRklzc29yWWdHZ3o1c0hFN2ozTFR5ZkJ2UUZWQ18tVTEwcGwxRlhjVVhzNTVIUE9WQTY0cmRrcVlyMlJvUkxUSmkwRVpUQWpHc0VDRmJTUHN5N3lfNkpIVW50c1Q5NkFicC10dWwtS1haRnc?oc=5</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>P&amp;O Cruises says port fee commission shift brings it 'in line with industry practice' - Travel Weekly - Home</t>
+          <t>Sterling strength becomes a supply-chain variable - Metro Global</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 15:39:00 GMT</t>
+          <t>Wed, 04 Feb 2026 20:15:00 GMT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNRjA0bjhCMDZERDZCSjBzNWc5N2dHWFN0eFI0b2ZVcm5fZE9sOU5PWWpnOFJYQjJqdUZEZGU2ZGtzWE9jWFhPdFpRa2lHa0RPVE9OdTNiR1FqNjdLVl9MaVZxb0dCQW95dmN5QVFKVk9Mdkd5MmNXNGs5dkFRWXJlVklkQS0teFpQTWd3dFhDUWpqa3UyLVFIVE9JS0JuM0l0OXNhejF3YjhnaXNJN205Tlg0ZXo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNdkpDUXdPdDR3d2hFQkVBREVMVUkxSUZJYmoxeldUNWxzQ1g5Q3R0eU5wbkRYZkJsNDMzNXNPRXVkS1g1X1k5Q0x2NG5HNXZ6SUt4S043c3llUG83ZVBRdFdEZ1Zka3pyeVpXSUQ0MGdwN2MzZlE0VmktbTJpdGVPWk9TYS1iU2w3LVE?oc=5</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>DP World's EVITA Trial: Decarbonising Logistics with Trucks - Sustainability Magazine</t>
+          <t>CEVA Logistics and HAECO Group sign global air freight deal - Logistics Manager</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 17:38:03 GMT</t>
+          <t>Wed, 04 Feb 2026 14:00:46 GMT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNSjF0OVBpMWVsWkFoUDZwdUhIYk9HWmVlUmM0ZHgzTnlqQWdCc1BYWi1aaDd3MW16cUpsVXc3RnMxdkJSMEprcEpTbUpzVzdyZFdIOHVySmVrZzE3My0tMlkySHU5Ym80SWhGRGlTTTFZVmdSeHYtcFdNOFZHeHd6SE01LXI2cFRuX1FtemxwMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPZmQ3MzJxVTdKdndReENmRFBxTWEwWGtzOGxZS2thb1hfZjRUUE8yN3JMZy1DcnQyMU5jcVRpekhYMVVCZG1yZ0hIUk9SX2Q0dUxmTDgwTXlnWlZRWEdEdjFNZjV4eDVZV1JYZExtZnB2S0U1dW1EWlgyeXczeUEtWTVTOTBpVS13cXpRQ2hQdGEzVjdjU0tOYg?oc=5</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1211,17 +1211,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>WADA provides update on the compliance status of the Comité National Lutte Antidopage de Côte d'Ivoire - World Anti Doping Agency</t>
+          <t>Air freight markets firm as Chinese New Year front-loading reshapes early-year demand - Metro Global</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 19:28:29 GMT</t>
+          <t>Thu, 05 Feb 2026 07:15:15 GMT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNRG1BOFVWVGdHVHZVY3AyUTNIejFZTm1ORUlyWFRIdUhmTmZvc19TTTZVS3B5RDJ3X3VDb095ZWRvMXBjWF9FWmhQUEI3LW1hTkUyN1NjS0ZWYjdXRlZHaU5ialNodkxJUGUwMmhCLVhySTY0MkFrQi1aM21UaFpaRS1mZGNCQy13aVB4ZTVleFlyZVZpdGN5U1E2eHpCTE5sWWhEM2JPYWQ4V0x2R1dVZFNhZ1ZKY0FrLUYzWg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQekYzUlJhdXYzVTZSamdjM0RwZFJsOF9FcVpNRmJkblhLQ0d4ckNrRFZlWThMSWlmQ01QUUZKMjBCejg0ODlaQUJGRXU0NFAxbVdrRGtWRGZTSmRMNURwajFWclBCcV8tSnZvc21xbVZSanRkWHBRV0RMd284NWJrMVlxQjV0X0h0X1lFWklEX0NvcTV2VjBoR2cxaFhXVTFPT19QMWlEeldQUkNKaFUyaTQ0S0ZkOTJkTlE?oc=5</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1241,17 +1241,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>The Myth That Foreigners Pay Our Tariffs - The Daily Economy</t>
+          <t>Port operator brings ICC claim against Panama - Global Arbitration Review</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 11:31:00 GMT</t>
+          <t>Wed, 04 Feb 2026 22:18:17 GMT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxOSWNTSWVzOWxGeHJfTGkyaTgxcy03dEM3VTJMZ2g2d1F2ckZGQkwwSlJ4NXBHcHZvWHZFaUwxM0hyZC16X3ZYSVdoU3hNX1gxMkUxa1NqRFo1X3YzMFVmUEhpMC1jOTVjZnJobUw3dUxPcUpoLWNGN0lfUWZTMGg0S010Yw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNbWpTM3JlRHZ1Z3Y1RGh4b1BSc2VPWVZOLVNCeEFEaWlWUmN3ZGFqSzBUOGNRWXEybEZFQ0JFcXZBd0gxdGpBVFRXNFdpV3o0d2tGXy1zZ05OS2hGNzFGVVVHM2JQR3VNU2VFMEFkbUt0VHNPMHNvbmdrWlVjelNlRG4yckNwNEZ3TXZyeXhCeWRnYkU?oc=5</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CUBA: Oil sanctions will hit the poorest and weakest warn bishops | Aid to the Church in Need - Aid to the Church in Need</t>
+          <t>Port of Barcelona posts slight profit drop in 2025 amid higher revenues - Baird Maritime</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 16:29:29 GMT</t>
+          <t>Thu, 05 Feb 2026 05:18:16 GMT</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQWlhkWkN4dzFMUjdOaU5FOURSaEpyQnBhQURFZjV2MmdtLXdUdVljaXRnOGloVnYxMm1iYTZrcG9xMlhKdXZrMVdyWHFiNGhlN3VlZDJvSFN6bHppNEc5OGVqRXlYX3dKckdoWVJtZjBVZ1dleTFOczB4MnNNWGl4TEU3eDByRXYzNF9IekFKRHhzdGpFcHF5dFJn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQZmlkQkNYTkJzUGpBU1ItN19rdlhKNXhJR3BoYUhKeGt5dmdPOER0dWFfSFNlMFJZdDdYM3RFUEVjSUdBT25LUWpzeV9SeXM2LUlBamJCUDVYU0x2Y3dIN09TSnRYckdlSFdZcG5rVG04emxSYkV1cUdPaDZ5OUdvV28tcVlXMTV0eXVQWWZNWDFHSUVGcmFuYU90cHpHTklFYThIa21nNGx5bkgxeFJUVTc0dHI4eGPSAcQBQVVfeXFMTlI0SkxnckdmUjlnLVNldzdyUkZQY3lHd1k4NFdmQnVYLV8yb1pDdWJXbFFENm9CSjkteHRobUFGWHVxejI4LWN6SVM3dm5vODVValIzZ01vNUg2alc4cGNFdTFocGlyWWd0X2hKN0R0a3d1TU5JTXVEdnhsbF85eHNNWWY0LWxGNURLUF9CS0lVcG1iQ3hvQ3dDNENkQURJZDhveEZ1QWtWYXloVEtlSGk5dU1Sc0VsWXNHWktWV19uNzVTRQ?oc=5</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Massive Parkside regeneration scheme approved - business-live.co.uk</t>
+          <t>ArcelorMittal Sees European Steel Tariffs Restoring Profits - Bloomberg.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 07:21:00 GMT</t>
+          <t>Thu, 05 Feb 2026 06:35:00 GMT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOLW1wZ2pQdDJPR0lRWWJBSTNzbDlOdXNNUGdxdE9Lc1FoczRNY0Frcl92TGxMQW4wOTdFSjNKMVhQQTBZcS1YZ3hfblZFTWdvd29Tb0xCdExUSXdiakRXYmp3VVJkcDIyWG1oTzFfSHpndlkyVDVCZ01VTFlBSjYwZ0pnRmRhVGVfd3FQQ3pPM01ybHd1TnhJX3BfdTdXZ9IBowFBVV95cUxOU3pxeEx5WTdVNmExVEhXeTQ4alNXYS1OUkNQWFJDUW8waVJQNVRTQ3hudjNNTUtubW5sMWtPVV9VbkQzN3o3X0dFelZveG5leVlkZm1YQkZjb2RoLUY0S19tR1k3SUdmUGZvck9ZNFlyU28xek5YQXlEZWRrSWJZNEtJdHVfeUlDSjc5OW44MDNJX1M1NTFKUTNHZnBkTjVOS1JV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQNTRHdW5FUlRvaFd0NXpzZWtBbmdtaU1IM0V3UGVyUVZBcGJ2X0ZLZnhXNW5DY2h6MlRUUkNqcDh1WkZibTJEWG9wYllYelVkV1hUMUpLVjY5d2U0cFRLY3JKMW52REV4d0FreEk3ek96VmdwX1pnUEdJZ19VWnNrQTNiT0ZtUlVjcnhiME5WT0Q2dlVybGxXRGdBYXNpbHVVbnc4RmFGQVZZRGhjLUszQ3RVbTc?oc=5</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1331,17 +1331,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Two arrested over attempted sabotage of German naval vessels - BBC</t>
+          <t>What are the Logistics Behind Super Bowl LX? - Supply Chain Digital Magazine</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 16:30:11 GMT</t>
+          <t>Wed, 04 Feb 2026 17:57:03 GMT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5vUVFxb0Q0Sm9Zdzh4NllUVW9VRllRSEZZVGlSNzZFbzlrUmgtWEpQYnpOeHZHSVZxbnBuNzNjWHU0ZDlpR3I2bzRkenNPMXU1X0ZhaFdFQ0MtZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE1qaG9LN3VCVGxGNXgxZHljZUtKcXlKUkx6bWJ4R01Sc05lZGZaa0ZBQ1AtZE55NWNIU0hjTEJEdEFYRVZ3WE1OWjZNQXc0cDhrYkVna1F6bUsyWk1hdm45bFc5ZGRMQjAzc08w?oc=5</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CK Hutchison launches arbitration over Panama Canal ports contract ruling - Reuters</t>
+          <t>US to reduce tariffs on India once it stops buying Russian oil - Sky News</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 00:41:00 GMT</t>
+          <t>Wed, 04 Feb 2026 12:59:29 GMT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNZzBvWW5tSmtDbmZ5MG5RY0xNZ05lRHh0R1VLeF95VTVPbTNNQUhmcXQ1QjN4NEVYMGJra1pXcFZaR0FUYWNhSjNqMHg5TVJtc3RHak9WSldydkNpQ2Q0c0MzcVpMLWtYZk5PemlEZHZEalJqS2d1cUtOdzNqQkM4WWhad2FiNzVrMW80NmozT2lnaTJuSnM1M0twY3NnYU00UFJLWU1mdEg0VFdlRlNvbFBhdGp4bWNNRVBpR19MaGswaFU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNMkhaaDZaMnY5enZjZUhhNm4xQ25JNHIwTzVqbTU5T29HbVEwOUFwTTFaajRMZW5NSFFzOTFHNklGZWZ2cW9KMGlvYUNwSmlSVjdUTUVTUklnV3ZPOWxpRzJKS3VhaTB0WUdVck9mOFlBdWlJSkNuMk5ITi01VUhpMlRQREs2RnN2NXV5c2ZIUXQ1Y2duelFGMjRqTmlqWHM?oc=5</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1391,17 +1391,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Johnnie Jackson on Port Vale, Osman Foyo &amp; our supporters - AFC Wimbledon</t>
+          <t>Curio Water puts out call to all ozone producers as new UK REACH compliance enters crucial registration phase - Water Magazine</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 11:23:13 GMT</t>
+          <t>Thu, 05 Feb 2026 04:00:14 GMT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNV09XdFc4SjRBREhVS3E0SVN4elRlNlZacVVvU3hjRE5zTEVuUzllUm9tY29KanpoSHRkWEluLVNOMGRqX3NwTUE3WTRKazUyUVRDS1Bfd2VqNmtYSTZZdURUV1Z6ZU1LYlNUYTBOc1hKVTVqbndHSlFHZU5kUU5TSEdqTGQwRm1vYkFhTXM2RXlQOG11VjFVcWM3SkZvNzlzeHcybmlZOVpkX2p5WEhKTVNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxNTnM1Q0huRzZRTnFfQUJYWnplTjl6REtFdVN5elVheGN5LVpCZ0Q5b1lPWXZZaVVUZ2dQNWN2RnhLWlhqcG9RdGFrMDVPVXpHTGlkZHRHaWozUzlYNW5wZldnUGkwMjZWdld5WkExSWxhd3NIRHRvOWExVnBhdEplVW5SOEhFNXFQZWV3SlNycm1MWlE0VldCQlBHS3FCdUtaQVdVLWdNQVNvNG1HZ1JEWFMteS1ZajRCcVh3MzkycGkwTFBHcURGV0ZTbUxOazRMWEFYcy1WZ0lmNHZnQnRRekM4QmpHUTJ3?oc=5</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1421,17 +1421,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>The Trump-Modi Trade Deal Won’t Magically Restore U.S.-India Trust - Carnegie Endowment for International Peace</t>
+          <t>Port Talbot RNLI volunteer reaches training milestone - RNLI</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 21:24:07 GMT</t>
+          <t>Wed, 04 Feb 2026 10:35:02 GMT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQOXNLeDh5cmFqWjlfSUNmTEVwOTA5THBMSjRmcmc3TEoxN2lnaWk3Vk13WEFsWGZDTmlXLVB6OXZiMjVxYm90YVlNSnBNbGFUMm05V3l1VXJkeHlkTkdWNlh3bXA5bzVDZXNndEpqRmM0VkRVLWZUenVlN0dwVzFaQVlTcVRmUzJtUXItR2VhM0xKdG5yT0RUelJBeDNfd2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQZXdxUXpvMDgwZHZkdWZKZWRUU2xOTllzeWtteWtITzJhSENKbFJSNUhXSTJldGpuUXhWQjJtY1VlRmlvMUVvVGY5M0o3QThPd1ZKd2FXV3ZsWVp1YVM5WnZCOGJzX0RtSnBvSDFuTW5EajU4eTNRX3A2b1EtdFVDa2J1WE85Tl9IeXd6cnB1VVo5cEYxeEU0SW5iWDVUWTB0UndxdQ?oc=5</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1451,17 +1451,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Around 100 flats on 'prime' Port Glasgow site to be demolished after delays - Yahoo News UK</t>
+          <t>Danish Pelagic Fleet Goes Green at Nation’s Largest Fishing Port - The Fishing Daily</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 06:30:00 GMT</t>
+          <t>Wed, 04 Feb 2026 15:29:50 GMT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE92WE44aFUzbURfbkF0d3Iwd0J3WUx1LXlRc3ZOenhTZ2xRVTlnTE12SXl3VlZKQnlQUUZ5VWttLUxzZlpjZjZhUDRGWGdOemZYQ1l3M0VKekNiZ216Nkg2Q2tvS0FiQTlyUXI0bU5HQzMwd0ZNQnNR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNTlVicHFwTHhjM081YXdUeHcwcWcybHRyNVd1QmpKN29KTGJ5c3pXaWU0a29Ha1dERWZFXzZOUWJpcVBMMTBaOElPYnRUUlFuU003aVBjOXNsNDhaeGV0NUk2MVdtUlRnV2RqazNUQUZXSTVHNk1mUjNWLW5ITWVHX0NFZ1d1eVl1SzdaU1ktZjdkQ0lETjRFUGtZV0dZQVRXdDRWRzlNSWZ4WWZudnB5WGZVVWg3MTNMRUU1d3hR?oc=5</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Yusen Logistics and AGL Establish Strategic Joint Venture in Kenya - LM - Logistics Manager</t>
+          <t>China Has A Plan To Avoid European Tariffs: Team Up With Ford - Motor1.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 07:44:04 GMT</t>
+          <t>Thu, 05 Feb 2026 04:15:25 GMT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOc2JUNGw5NGF1dC1TbWE4ZnpfZWVrSmhDeG5nWWpIcDdlck9pTlBaaGJyYlNNN3dKWHo4T2x4dV90WXItTzl2emZfZEd2QU5oLWhYeVlONDg3QWpvdEVrNUhYUENFQTlfQTZOZjRpWG9TNDRmVTBJVERlQUNmc09hWnRxbVRaQVJiYmVNTFk3RFpFSUk0RE1fV2JLVHZ3UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE1jZG0xaU1xSG84TmU0WXhuaUoxNFM0TDY4MVZ5aURjdjZjQXU0MHZleExZUTZpOU9Xbm9kVmhUTEZrUW9tVTlKckZRNlhMVzg2elYydnVBU1Bra0k3T2MxMlRWNk1qemkyc2NDS0t3?oc=5</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1511,17 +1511,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Five critical compliance deadlines food and beverage businesses must prioritise - Lexology</t>
+          <t>Inside the World’s First AI-Powered Shoppable Runway - Supply Chain Digital Magazine</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 03:31:22 GMT</t>
+          <t>Wed, 04 Feb 2026 14:32:56 GMT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOd2lPX3RCV25scjFGMmNhcHRwUEU1VUVkeFFqNkJhQk10cU9aREI3U0VleFMxNi1lZnl0SEN6dDFpakRpZlFoV2hWcWZNM1phejBNSlpYcnpzOV9QZFFFTG52SWFLVEhGZFlzTWlKSVVXaWI4RV8yYjlxbnhXRmNoenZpelVIdGU0R2NWcENXRVZqcDdXd3k4Z1pxd3A1TmF3dmR1TllUTlpLREZjZHRPTWRFalJFV0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOa2k2QTE1dDVZZ0JUdmpWaUM2Y0h1eGpWbFFTQUdveXUwdWVmSmFQeVVsejdJTjBPRGZjeFRCOHp3TDZDOEZwWHplRnl0WUI0aDZMZFRRY3YxNnlRQ2c4bjJOOUR5bWx5dTZFaXdaTE9QN2U4a1ROSVN6d1NhZ19MX2pFT0VLOVVxNkE?oc=5</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1541,17 +1541,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Shipping Firms Face Tough 2026 as Reopening of Red Sea Looms - Bloomberg.com</t>
+          <t>‘Timing is critical’: UK has five years to secure the energy supply chain, regulator warns - Energy Voice</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 05:25:00 GMT</t>
+          <t>Wed, 04 Feb 2026 14:26:29 GMT</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQb0M3ZUhwNzNlN0JLODhUMUdFd1ZIa05OSzlXMndOWTBlREZIdmRHeF9NM0pEOHJEQlp1VXpQNVU3MEJJMnV6dm1LaXNER0dtSXJVYWhqd0hHc2QxRFdKZVJSckRDQmhJWjk4SmFtZW53MEVzRXZMV0h1aGJpckd2bjJFUHJWalc3SFNqQUtJRVVVZEgxYU1SWW9SQVBXQVp4eDI1ZUxSTEVOd2t4R21YRg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNVkp5ZEFyUkNZcU9nNWFEVHpSS2hDa1FlMnFYdlNlbGl1OGFZQnU0c0h4ZkI1WEE0ZWdvREdxclQ1QUkybDNiWDNrS1FNclVSa3JEdDVpVXhPd2JpZGlMX0RzNVR6YlphTGJ1OHVCNU9RekdTaTNRNGVYZ3J1VndIY0lOMHJadGFQZ1pfcWpkVzFIYWpP?oc=5</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AD Ports Group secures $115m financing for terminal development in Egypt - Baird Maritime</t>
+          <t>Tony's Chocolonely: Sales Surge Despite Cocoa Supply Concern - Supply Chain Digital Magazine</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 05:20:30 GMT</t>
+          <t>Wed, 04 Feb 2026 17:13:35 GMT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPMFZzd3VmSldrcTZ4aHlicmtXOGR2QnN1dHhxSGVYcUZrV2hSdXBoMmdHWUxZTXlSU2djZzRVTTQyODZtY3JIN0FEckFtd3dsSzBjbHhuMTlfUl9tQUxOYjZNS1ZPaWJsSXExQUJaVlltYTl5QzJBTVRLSEF4TVVCV2JnMDREWlI5T0xDVjd2SE5aeUVObTZRSXdKZDBkdmYxSTJ5bXNhdWpYYWc0UEszb0dDamhvZWPSAcQBQVVfeXFMT3U1djFaZS0xbE12cU9rN3lPUHdnWXdyRlBqWkltRXpkY2NzWHY2WlZQeW4wWVFjQktqbm5PZlRSamJPZWpXVHZYZkFXUERZN1psaUJ1dGJ0STM5SGxLOWkwNkVnMEt3dGE1bVVmR2RLMW9MbGRBVnFSTEplcjNIQjk1V1B0bm5LV3AtX3B1N2o4OWpkbE01eWs5OVNNNTMzRWJZMVJ3QjdOWnlCQ0RqV2pCY2lzN2t3NXcwSmJBQzB4VWN4Zg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxQeW5IUFFqd2tZb3JFUWNaenhjSVA3SjZ5RW93LVBIYnFnM3A4ZmFJb016RGJlaTA0ckpGdUdnVHVmQ3hFTjNUc1MzbFhQbUpLVlVkSzVEUUtmQ3JIRnR0NVJNazVDVTFmVWNwS056QUxXOEVZQ3NmTHNnV0NtbGdLM1BBVm4?oc=5</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -1601,17 +1601,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>GXO Logistics (GXO) Expected to Beat Earnings Estimates: Should You Buy? - Yahoo Finance UK</t>
+          <t>How Does Orion's Acquisition Impact Mineral Supply Chains? - Supply Chain Digital Magazine</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 15:00:06 GMT</t>
+          <t>Wed, 04 Feb 2026 17:05:00 GMT</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxOMGZacEpxT1BRYVZZWHJhZVAyMFFqSEhqOUJEQlAwcTcwRXVETm9tQmpsZG1XaGZyMV9TQ0dZREV2VF92VWc0OHJqMVJBRllRODZlTzlIS2hkdzVoZURjS2Z3T0ItNVBCaU4wNHE1eTRidGd6SVZMLWlJb1BpMHZjbUNPU3NwOWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNSklKTzd4Vmd0enhKNXRTcVVMV3pIRnhnbzlya2gxOU0wWUV5UXlZSzhJOGkzUWMwRks0dzFvVFU5ZDdVMUZJU0owRmhBVVQ4R1Rrbk15X09XOUxGYkx2OFBvVVZlcnlnTWtDZ2o3TWFGZGk4X1puOXNYYWZYVm1aWg?oc=5</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>HighBrook agrees recap of €300m Dutch logistics portfolio - Green Street News</t>
+          <t>Toyota expected to post third straight quarterly profit drop as costs, tariffs bite - Reuters</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 15:19:06 GMT</t>
+          <t>Thu, 05 Feb 2026 04:52:04 GMT</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPNi1ISjBfR0ozQWl0VGY0REZOUUU0Z0ZYQzRUeGZ6ZV9FSktlWjdwcVROMkRjQXI0Wmc0Q2xvYXRkd3BLck83cWZIWGVGOWxMWU40VENwb0w0R1Zpb1E4SHNtLThKa2dkOUVXRkRaMGJ3b24tU2huY05iWXlmSlNBVWg4LWtiRWdwcWg3U0ZEUkxnY1R6bDFLaTB3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxOU0JtVUdXRnkyZWg1VGNrWkxzbWREYnA4U3VHcHctb2ZLdjJfYlgyNWRPVE1DXzZ0a2I1QnAzQ2xCTHJZcVVEZER2bXV5S2hZVEdvbUJjWWFQUHFtQkppTmZkX2VuSUtjRWxjS05fZzZ5ZTlLaE11SlFJNXdzRGllNExJaDktdnZqdzNZSEVpRHlQVWNsbjBtX1JkWnF5eTBOcnRQcU44QnVBOGFMa094c1F1RUFkT2tQTDdaWHYzVVI4UFFqNEdBVmhzU0hOLV9yWEJnYnM4UFdzTEpuaXJJUzRUaDZjbF9lY016Q0RB?oc=5</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1661,17 +1661,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>What’s next: your complete guide to logistics trends for 2026 - Maersk</t>
+          <t>Top 10: Supply Chain Leaders - Supply Chain Digital Magazine</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 13:38:45 GMT</t>
+          <t>Wed, 04 Feb 2026 15:56:57 GMT</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQX044eGlSSEpLTFJpbUdhdlVaaWlmS3BUaXI1VWpKMnU1MXNjMDlVRHZBXzJwOEwwSi00WUE0NnJMX21CbEp2b3RMVkd5WUNiX2N5U0xSUmJXVkR4SGhBb0V5Uzl2YTc5SnY0S3JjWXR6UHBYcDJuMkh0T1dpdDJXRWVEbEhfNXM2VEFGZ2NCMTRaZFNwOEpscno4T3VCWlltTUxRU3pwWnNvSzg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE0temVHbHYyVmZMYlIzdmpRS1JLMW5nTUxfSU5LdjhwVGRHeGVnSklkQmlUOWMwdF9sM2FrVVlFQ3ZnRWdrd04tak5mNkxuQjVUakQ5MVFUaFlSV2k3V3hTN0FIbXJjVzVMOG8zOWlEVXNPM3N5UHJTdg?oc=5</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1691,17 +1691,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Haskoning acquires port planning and simulation experts - WorldCargo News</t>
+          <t>US Treasury's Bessent says he was wrong when he said tariffs could be inflationary - Reuters</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 00:22:31 GMT</t>
+          <t>Wed, 04 Feb 2026 17:55:40 GMT</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQRklmQVJSd3dyaDFSRF9FWW5jQnYtcEdITW1QM0Q0RktiMTB3UDhwM19xbHNIS3RvOTlkN2dZX25rM01aTW5kRTRXZk9rdTdTaG1GdlhNeEhJWjlHLXM0S0h3ZFM3WUdPaUdRS2llcnZsd0RldDd0Q001R21OcW8taVBMaXVYQWIzVGRRNXZXX0RNT0pOVHBDYW1UNldkYW01T0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNVy1nWVVrck11VkQzTnRyMHFRaFlHZnhWS0ZjbG1vcXRVQzRyb1poek9MTGtqY3JPQ3p1SDM1dHAwT1I5c1VnekUzTmdqMkRENXB6SHg2Z2YxUjJXMEpQdERwbkJsLW9pSEpBdnUzUmNLem9RWTFldmFVbTUzYXY3eUZBZFBHSENka2pnS2o1Zk4tdHptRDkzWnJKSmh1RllXYTAwVDBkdVdSckRUQU0tVVVhY3BhUjZLNHR0TjRXVVBDcWd3?oc=5</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1711,27 +1711,27 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Police and Crime Commissioner censured for supporting anti-migrant protests - Searchlight Magazine</t>
+          <t>It’s a kind of MAGIC: uncovering the origins of chromosomal instability - Nature</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 11:34:16 GMT</t>
+          <t>Thu, 05 Feb 2026 00:51:34 GMT</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQM2M4R2FWQzBlbHpIelJhMVpsQkE4V095dmNlMjFDNHMxOEd3V0g1RTM5SWotbE1IeEpNd1plOWNBSTZ6bWNiV2xzMy1KNjZJVlhoR2ZDSTVBMjJTS1I1NUhNWjhYcEh2RzRUak5nYllpT3lRTk5BMml3OWsyTHR2Rm5hTTJFdTc4X3NFTkJLU0U2bVZlU0NCcUhVU1otS3FxRWtreFE3VjF6d19LeGxRZ0kxUlhvSUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE5vNVJiNG14SWdKSkR2WlZjbFdwcGFSSHczOFF6bmlfNi1zVzhONEpPQjROUEw4TlRaNE1CbGhtd093MDR2SndzSnZsTE0xdlFGTXBORFZSdkh2bHdlMVNr?oc=5</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1741,27 +1741,27 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Iran police say 139 foreign nationals arrested over protests in Yazd - ایران اینترنشنال</t>
+          <t>AI Contributes to Surge in Cargo Theft and Freight Fraud - The Maritime Executive</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 10:11:32 GMT</t>
+          <t>Wed, 04 Feb 2026 22:55:44 GMT</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUkFVX3lxTE5OLVNjX1hqdFk0NllxYU5uSGN5TmRXTERJSDh1bktUeHZvNC1BaDBzWDVtaUhJbmlWX2Jpekl5WklaZzUzSkhBY1d6VXhmUU5acHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOVngtbWx1Q3RXLWZTMndsTWpWd1hJbWo5emxKN01mQXROZHhQVjN2S0lielN4dHZPZkNQSlBLZXF6WU9kWk1iRDFRWmp2V0FaZ3E5THc4NWJBUkRnWHltbmNZWmtwd2xkZnVhOHctVHBnSW1haVF6SnFybnRfMEY5dHNQaDRLOUR3OEUwSjhFUmpOTGdjR3k2b2FTVQ?oc=5</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1771,27 +1771,27 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Russia resumes strikes on freezing Ukrainian capital ahead of talks - France 24</t>
+          <t>EU AI Office Establishes Signatory Taskforce to Guide Compliance with General-Purpose AI Rules - BABL AI</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 09:46:52 GMT</t>
+          <t>Wed, 04 Feb 2026 22:29:52 GMT</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPN01uSVNackgwMjE1enhnOVdUWnJQOXZaYkJXQzBscXFaX0tmVkRrb0ZSNjhFTXR4NTJmOE0yQk5TNHZndHV1dkxyRldjZFlDNDhEbW5LMVNzcjdEOGg0VWVsbE5GOTVEZVV1VzZQSGdTLXZEMGREeWg4LUw1MnRIaDNMRjd1eG1BSUs5S2VORE1NTFVRVkI5bnlzZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPVHJhX3ZmaXRuQWoyeFNJVndmQk5JT0w3NXQ3SkZGa1JfRTNRbWpaeF9wME1PX2UwSkJxZTdiZjBsWWZQeTdPOFM5Ty1tcFJXXzhoOFNfbDNzYzJvSkh0NnIxM1RJMnpxLUpSWWY0TUx6bTBoM0JvdF9kQk92SFF1MHJ6Z3M1UlJmVFJlSnFtd2ZpeVVlOG5sZEltNGRRWHlOOUc3Z2RFRFRQZE0ycFFYTg?oc=5</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1801,27 +1801,27 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Man arrested in connection with physical altercation during Buda high school student walkout, police say - KSAT</t>
+          <t>Two arrested over attempted sabotage of German navy ships - Shipping Telegraph</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 04:41:03 GMT</t>
+          <t>Thu, 05 Feb 2026 02:02:21 GMT</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxNS1VuTHpOWGU3M3BEZTVzWU5LbDNILWEwWmJMbGFYdVVraVBMTUI5bXFBRXR6THdDUmd2SHhuQ0dVTTVXbnNQM2NyVnIyamtlMElvMHZJSTBfTnJ3cC05S1ZsMWVSeTY5TnRBSUJCYncwclhMOXdtYXQ1YTB2YVd4Z2R4TW1MNkoxOFpqNjdTdjdPVlpxVTFoM2xqeWtWb0RJZDZYWXdyTnZvUHU3cEN1R0hQaW5aX2NuVTktTXJ5T3BScjN1UWYxcTNtVzY2V3dxRTVlbHJ1SHhjQlNYdUdyXw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPS0MtaTJIRFA2d291SzdsYmdRQ2d0TENUejhBQkZld1JRM05rUDF1VlhKbnFxUWtYLWp5NkoweUh6Z2x0b0lwZ3JmR2xBZS1QQjltNk4yOHVUVy1ySTJwNlNPVTQyNVptRnlrVktMMEJuZWcxQXc4TzBVdkg3NkdlVTN4UTFYSlFaXzYteEtGUTBBdDdoaUhVSm9tVVNaVVk?oc=5</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -1831,27 +1831,27 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Palestine Action Group plans march against Isaac Herzog’s visit despite protest restrictions - The Guardian</t>
+          <t>Port of Mombasa hits 2.1 million TEUs in 2025 - porttechnology.org</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 10:02:00 GMT</t>
+          <t>Wed, 04 Feb 2026 15:27:22 GMT</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPNlhyVnR2VUlxTWpRY2J5M3c4MkpZcGkzNk5iWG5Wajc5QmlvVDVEcDRwd2lVbTJpaFBjR051RERCNmd4dXhibWJtdmJQZjNNT05kMF9vWDRkM0V6X2Z1R0ZEb1ZIOGN5anI4NHFCM0ViQlN6N1BNbXFzZ2tMakZscFg2Y0xseXIwYWxLb0tnSGthaUl5dThmWklCSzdKMi03Y01EUnZn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOU1NoejczMGNrVERINU9uZ05kRFNjTFlOOW1ValR2SkNzUWwxXzJiajFVYi1TOUpsbkplVk91UXZ5eV9ScGluR29pUVFOS19OVElpcWNyYndoVUFCZHpuNGIxLWg5d0h3ZEhHNEhWWWVnYXJqSlNfbmxOZ2tJa0lLN2xOYUZKU3FCc3c?oc=5</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -1861,27 +1861,27 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Islamophobia in Europe: Dutch police assault on Muslim women sparks protests, highlights growing crisis - Muslim Network TV</t>
+          <t>Measuring Epigenetic Instability May Improve Early Cancer Detection - Inside Precision Medicine</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 15:14:40 GMT</t>
+          <t>Wed, 04 Feb 2026 18:22:53 GMT</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNaDVlX294ZEx2MWpIaTc2RUtuM00xbXFNV2xBWWZhUmY5TmVjaXZiYXBXZ1kyQVFrMlNpNldFY0hiVmdrQXNlMnJkeUhnVkdEQWFINS1EdHhrOC1GTGVpeXBqb29MVDZqV2ZMS2xQT05ibFBYS0ZxNHRBWnFVOE5GLVJBaTlOVTdfM0xYaHdURVhYTGVKc2JFVzd2LVhqZGNiZE8xcnZNWlN0MlY2NkYtMWlWWU9CVmJHVkpadlpONHVLMGdYbWU1OFlPSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQYWo0dUhXZElFSGdrRGh4UmM3eUtvbHFTRFZZeHJMVzdnOUdFMVdHM1NuLThLS05vdldNLW1JaUVUOWxvb3hkTVNvNHZfdk1sZGZMb3g3dUQwaVBfLXJaU1hKeGFROWxuei14bVJZaGgwSEl5T0pzUGVTVC0xMFgyM2JqUS1KZjkzNEZoeVZ5WTdHNWdNUXNSZlktTTJlSHRxS3VwcF9hTldVdGlaNExpZUxPZUdfd21PYkg5MVdPUEdSQQ?oc=5</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -1891,27 +1891,27 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>NTUCB Cries Foul After Police Deny Protest Permit - Greater Belize Media</t>
+          <t>Zhonggu Logistics boosts orderbook with two post-panamax container ships - Tradewinds News</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 01:51:29 GMT</t>
+          <t>Thu, 05 Feb 2026 04:01:05 GMT</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxNMnZiTGxNZjVlM24tYnBTbEV3OC1oc3JvMEE3b1RvY1JTcTNkMEp5Q0xsc3R1MzAtRXZfWGZqb2hnZXRvWjVxVGZzc05kbUE1OXp4bFhWSE9IQmE2SHZvRlkwV2daUUFPTDlsRlcyT2RNUncwWjVkWGx3Nnl2enBFdHQyM2s0OFk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxONUR2eEFtVy1HVnczN3FFaGFDcEJsYWI1OWJ0TER5aW9iMC1FNlRIX0twM19kV3dQX3VhWlVKcFVPemRSTk9xVHd5clpXMVRfOXpheGZQSmVqbWZtS01zSkpIbkI2SkJKNmF2TWFZZzg3bTBrYjgyYXhGc0lxWDRrM2VrLWZIVmZQQl9tMldiUHRKdmhJSUVfY0UyWjV2aWVsMjdsYWdkZnNJX2FTUlR0aVBDV0xIdFl3eVRVM3ZLb0VNN2JG?oc=5</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -1931,17 +1931,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Maple Grove Police Chief Addresses ICE Enforcement and Recent Protest Arrests - CCX Media -</t>
+          <t>UK: Council reported disabilities drama group to police over Gaza genocide protest - Middle East Eye</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 00:32:02 GMT</t>
+          <t>Wed, 04 Feb 2026 19:39:00 GMT</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOZXN2UHBVaTBoNHljclNnSThxSnhFd1hhWWFBQ191V0s1eFVzdV9EMGE2dzZGT0xqaDlsaHlQRDNVdVhWM25PMzQydGQ2RTdOZXo4X3ZFMXYxMndrYktNSHIycGhxUVY4ZU82RFdKY3JUR1dRaExOWmVfNmVhQURoMkE3X1VzaXBXTVdwcnZXSDlUQkRvNlNnMjBFb0ZZd3RfQ1JRTmphTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNTF9qY2hmNG5MV2JGNHpyZXpoLVltRDkxc0tJTEJWdXR1clRFQzBKampvUTA0a1ljNzVpUnNsZ3luRVhHM1JBd19LQXh1MUR2c253b2drQW13NEhqTXJLQXNFeGpNdkszcEFKVUIycGphUzlUbVc4SVROdlpKdDZmRmdrODg2Vks4emhPczBlZDByRHFBbWlnOGZwbktjZ1E0UGtNbEJfZ1BwWFhlWWw1UkNZZ0JiWllQb0prRw?oc=5</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -1961,17 +1961,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ICE-Out Protests in LA w/ LA Times' Gustavo Arellano, plus Capital B's Adam Mahoney on Impact of Freezing Temps - KPFA</t>
+          <t>Women told police they had been on 'wonderful escapade' after Norwich paint protest - Eastern Daily Press</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 16:00:00 GMT</t>
+          <t>Wed, 04 Feb 2026 14:00:00 GMT</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE11MmFBVWRiMlpkdzd3SFU0aTQ1YnZBd2RJSDhtNWJZZW5XaVhKczVWTG1LUDVkRHVmaXFkWVc1dC1XMXMyMzM5bmZpWXJzNVlPQlVsTU9FYkdZTHhSdml6aS1McDQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPbktmV2xVWERDeV9nV0pfOS1FbWxjVHEzZXdGQmI5cFo5REVmcFkzWlpLYW84NmJQMDF0dUlWdHNxYW84UVJzTlRlVzV2a3Foc29FZEkwZ1kxekJYRzJrX0J2a2FDemlqdE9DcU01Z1VZa2FFcndUMkwyNllwX0J5eEVOcVVqaXJRc09lSVV5dWNBWG1rVS1JRQ?oc=5</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spokane police chief apologizes for officers wearing masks at protest - The Seattle Times</t>
+          <t>Police warn of disruption ahead of Enniskillen demonstration - The Impartial Reporter</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 19:00:02 GMT</t>
+          <t>Wed, 04 Feb 2026 19:39:46 GMT</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPZHVEUEY5SVQyb3FseU83enJMeHd1S1dzc1NsUUR2aWpPRHBRQ05zQ20zZTBmM1MwYmc1emlYQW05VDg3T2l4bXFNS3k2aHlvOFl6cTctcS1vQnU1dFVGRVFucnVLd3VZbVR5eThXT015cUJLaHIzaWtETlJfUU9rbllnTFdfeU84cXpXdVFuT3Z0UmtGdzVlNWhYS2RCeE5pVV9RVTdXMVkwSFcwSjhFUlZqRUU4QTFYR1ExQWJocw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOcFdGU1VKalFHMlZOenI2dGk2dWdzOVEyc2s2dk5HSUQyVFc4d21lazFaNEJRbVBnWUZiLVo4WDVIai05S2RhMVFGemR0aFBva25KUHdpdzV4VHlqOHc0Qmc0em5ROUJHOTlHTkVmWVRUdnV0SVM3SkE5dHRrdUFZcjNhc3ROdG95SF9Xcnp2eGphTWk4ck5KdHMzZlZaWkRZSE9vaUtB?oc=5</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2011,27 +2011,27 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US stocks drop on fears AI will hit software and analytics groups - Financial Times</t>
+          <t>Police issue six citations after hit-and-run at Fremont protest - Nebraska Public Media</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 15:51:54 GMT</t>
+          <t>Wed, 04 Feb 2026 17:44:59 GMT</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5uQzVsUF85MERrc09IUk83T0piRjgtQUFvZ2R4c0VyVmxzTlJ2R3BkelNLMWw4eHYxcGMwc3hjSmJsN0tTbGhsNEVQYlJmcWVkaXhxaTk4NW14WDBDbjFFZml4SVFyaGNVbXhqb3licHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQeWxwdF9xRVBlWG1DbVVjRE5wUkYyVmVaaE4xLVUtWXE0YmdOWFJ1ZHlHZzRING13TGdadDl6TU5oT2p3TmZfVXBNZnEySk1YT3RnX01VY183X25uUGt6aGprek1LOTVWd2dLYnRBSjBDbmJQdkFfTjdCekZaRFBRR1VHdWd2QV9Ha1VmaGtoVnRLQ3lDSFRackNVMENGMnNrUUpuSzN1bUFjS1RJbV9uWUwtT01OZzV1NHc?oc=5</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2041,27 +2041,27 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>NHS launches AI and robotic pilot to speed up cancer diagnoses - PublicTechnology</t>
+          <t>Police Detain ‘Yellowman’ Ahead of Protest, Motive Disputed - Greater Belize Media</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 01:08:48 GMT</t>
+          <t>Thu, 05 Feb 2026 01:39:30 GMT</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNYm04ZWFpSkZ1UmgwOTlXVU5TRkJBWjBQeU9PbFNfbDBVVmNpN0ZpT081RUdHemQyVEwwZmJrZXIwYzJSLTJsSGpNcFBmWjJROUVQQlRNaUZrUU90MmphQTQzYi05TV96dGtrT2VFa0hPY1l4YU1pYXlmZ3FrdUdtbmhGQ2xMQkNMU1Y1a2hYc3ZFODZDQVVaSnhhTjJXVTdnMWlIVHFhZlRhYjlPYmJuWHpQeEwwbGotd3JWSTNDZTIzSXAzMURiNDR3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgJBVV95cUxOZjJhWVM1VFpQRW01UFVIZXRMV3BCYnprUW1nX2hFZmdSQjNuRmE1WDQ5MGtkOG9VbDVDMWNXdzJsTUdUekpEbjFvTy1aeV9ZdTh6bmthMGx5NzE1cUxTdk56NWdiTkRKLU56SHBab3M5UFJabHptcEQtYTl5Z1I4MlpyWDdNeWg5a20zVE1vUHVuSGNVWndwS25QNnNBdVZURUlIRkFwUGw5Tk5uRV9yU2l4NXppYUh5cHpGX2gwb3BMd3F1emJ0VXVsRlo5cV9yS1hzcHFjVTZhWjFjNV9VaGNjMFNVNTRHVldzNExVQ2h0NzV0U0tWcGNoX2FEaUlrbTJDT3p0RW5QS3NDaTEyamhWZGtqdw?oc=5</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2071,27 +2071,27 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>King's robotics and AI specialist helps government upgrade public services - King's College London</t>
+          <t>HANZA invites you to its Capital Markets Day on March 10 - TradingView</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 12:59:31 GMT</t>
+          <t>Wed, 04 Feb 2026 08:12:00 GMT</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQQVJBNEtMQjhaaXJZb25qLUpPZnFHYkpkeVJtdWcwME5NdmlJdG1nWU5sYUZuYVFEMzJsTWItU0kxelRkckI4eVE4dkVoOUtWbkNJaWszYV9VV1FENGphSjhtVU5OcnJnSGtJNFFUYVVYN3ZsTXo2UGhBNGxublktUUV0YzNMdzF1amZkSk05NjRWcVNDa0RUMld3cVZ4WE1DbXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQVVRYUGw1b1cxTW5mN2ZMekw3Y1RUWWE1VWNzQURIa1lTTURnTzZIamk2X1FkdFZfeC1fSGRqUWpUV2lIQWRjOW12T0ZTWmo5MUpOWDd0Zlp0dWhTdWQ0bEhuVFU0ZWg5dUVqbUthYU04UkNxeGlNUUUya2pGdjBMSEowTjdsQkVlNnlXZlR1RTZUbnZqd2c2ZE9LVEY2WDRvdUhEU19SQmFPZXBwZnJXQlA0eUlqenJBcDJsWnBYUQ?oc=5</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2101,27 +2101,27 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>‘Technology must enhance, not replace, real-world learning’ - The Hull Story</t>
+          <t>Officer strikes naked man with police vehicle in Norristown - NBC10 Philadelphia</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 06:37:50 GMT</t>
+          <t>Thu, 05 Feb 2026 04:15:46 GMT</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQNm1XOWJDUDBSc09mbEZ0VUFaQ2JwNEdMd0w5a0wxVXczc0RMb09pUlY3ZFB2T3haWHBaR2FTSlB2OEJBN09rRFprMlFfXzBOREtkMkMwb3RGV1I0S3YzenBjOXRUYUdXU2xKS3RIaHZ0T2FMcnIzUmxwdlVYVjJLUGxLcl9BelZldklsNFBqbWNGbFZPNVFQclBGaVA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNQ0RndVl3Y2c5QXZoVHhvMkFwYTJjTW85RDZvbk1TTFJHRWVTcTB2d1RlanlacFJSNE1YYmx6bGFWeWt5RUZLa3JEWkdjaFQ2cUZ6bmc5Z3JWcnVKNnJHYnJPQTFrM3RYU3J2Q25VSEdLLVp6cGZ4bHhRTkRjb1NLQkhrTmlZVFpKZktlT0F4S3lESGxCQW1nbXIzczZ4Wm1sLVdHSnYwTlpYZ3NNcHJrNmZiNE15SmJG0gHAAUFVX3lxTFBzb1NYREUzRUlYbjdrZDZtVXRfUm5mZjh5NlF6cnhSUTFKRF9UTkR3cU40YVJFYkFWLUZkcHdWY2w4VGpLUW84bk5OTFBVdTN4YVlxMGViY1VXWmJVYUY3eE84SGxfa2JvRlJQREc3UkxWSTVieEg5Mmc2VVI3VFljblgxcXZKNE4ySWlrWHFVcGVJTmU3M21JR0xYbjhiaVpEZ0h6eTJxb1Bad3VIRmZmbDR3bFY0eEV4Rmx1TW5oSg?oc=5</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2131,27 +2131,27 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>UK and Japan strengthen science and technology ties - GOV.UK</t>
+          <t>Wis. man steals cruiser, strikes and injures 4 officers - Police1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 09:04:44 GMT</t>
+          <t>Wed, 04 Feb 2026 22:18:45 GMT</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOQkZQLVZCX0pweG43Y0N0dWNXUXFGaGNsWUN0b0JBb1FFek5FREd3cnJXR0dFRGY4TGloaGlaRlFvMGo5SmxpZmFwVHpxbVdxX1RBTHN2T3dFc0M5Zk1uOTRDU0ktQ2NfRDdPN2xQVmpuanhLRHFIWjhPaHNJRDV1Rm1zVVQ1WlRBOEZrNlRsYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOWTg4dXpSNjYzUTU3N3c1cWs4b0JZQTJ6OWwyVm1qMzVlQnFXNjYwY0poYzBHQnpWX05xTTFaN0FoSGRtSXlxTVJ5a2ZGQTUyNEJwSXpjeTJWQkdiT0loMms2TmFvcmc5ZEllMEVzSE55UVFTZ0dPNnVDelZaQkZ4b2hQZ3VKMzkzd3NZSDd1V3FJdjA4WndvbmlGRQ?oc=5</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2171,17 +2171,17 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Women in tech and finance at higher risk from AI job losses, report says - The Guardian</t>
+          <t>Dentistry in 2026: trends, technology and leadership - Dentistry.co.uk</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 00:03:00 GMT</t>
+          <t>Thu, 05 Feb 2026 06:31:45 GMT</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNakRQMFJ4NFJDWEU1UnRoVG55QzZjWnl0WW1Kd2czUDgyM1hXVzlNYXM1S2ZtRlRmeTFXMUdMWWhad2taWGpCZUF4UER2ZGRpa3R5aTFycUhyNjZKN0ZzenQ4XzA0ZDdpX2xnaUt1d0I4TkV1VjdadFNQa0ZaNlQ3Qm9QN0hKQ1Vnd1Viamc0anA2UGdQLUQ0S0I1Q3pYXzRnOGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQOUNQU0lTaEZOTm5Qa2lsMU5zQXZtazFhSGIzVFQzaUxUNHhxQVplVUFuYVpaSk5DWjIwd2k1aXRmV0NaRTZrSVVDN3RLVEhRaUVtRFdtUWlzSU9zWFFzRWJ2aXhCX3J6WVAyS3JYRGFfLXdKM2ViSFRQU3duaE1PUXZkZGpPOGdXUEZ1TXVlNA?oc=5</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2201,17 +2201,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Industry suffers lack of joined up AI and digital skills - DecisionMarketing</t>
+          <t>AI agents spark fresh security fears on Safer Internet Day - IT Brief UK</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 13:49:00 GMT</t>
+          <t>Thu, 05 Feb 2026 04:59:00 GMT</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPOEw4RTlNUGI2WDlXMEVBUkJMMlBZZ2VWNnAwbFZIdkJHTEhPbTMyQllzZzZlek5JX2pMQzNxWXQ3a2lTbEdxN253ZEFVM0JNdHZ1dTJrd0UwTWRJNl82YS0wYzlrc2ZPbjl4TkF1bDd6RVc0aWVEWjFhUlp2dHd0VjFNbU9qM3dmYUVKY1VBeXgzMVROd1gtVjY0TGRGdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQTkZ0RDVWVEhRbkNqUGpFZWdZWEJ4dUNEbFpFV3FlbGJOUTBGU29GU0R1UUwzZFdIRndYNWFWdTcyejc3QTFjLXRkMEpwNzUxUkZGbTlySGhyelNyZldIYzdfREtjaG43SWlJUWhXQlYyVkp4WVVrY1gzZ19OZzVvVnRWSlI2Rjd3cTAyTHZSWQ?oc=5</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2231,17 +2231,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Nottingham receives funding to develop quantum sensors to improve precision and read-out speed - University of Nottingham</t>
+          <t>AI to create “dividing line between innovative and conservative firms” - Legal Futures</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 16:30:50 GMT</t>
+          <t>Thu, 05 Feb 2026 00:13:58 GMT</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNaEF1YTRSWm4xM1NnTWJnU0NRVDRVYVlkdTFWRXlJdUY1RWh5QWVQT095VTBzMHFnbkxlbmlqRU5Ha2g0ejJ5ZzFTUE5PMllGUkJyQXRPdzYyNl9MLURSWG50cEYyYUZhN2UyTGFOYlBXRE1lLXU3U1BDYnBaNmJQbDVpV1lLTXJhLVRNTE1BZUktTVF2c01EY3FBNHdXV0pPQWo0R19MOEFZczRqZXpRQk5wZnFqa1lLWlMweDNuR3ZLTEZUYUtV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUkFVX3lxTE1KNDJrVENsRHRBdUY3VFRCc2NGWWhLVlEtM0tobm0zTUY4MHRFbVlndVVFaHNJUXlRbkpPTG5oTi1RTmF4ekFDR3FjZUxpRmxFQ2c?oc=5</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2261,17 +2261,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Why High-Stakes Decisions Demand a Different Kind of AI - IT Brief UK</t>
+          <t>TripStax adds AI and sustainability features to Analytics module - Business Travel News Europe</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 23:35:05 GMT</t>
+          <t>Wed, 04 Feb 2026 14:06:08 GMT</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOYUY4VU01Q0ZDQVF3TnZMN2I2ckMyeXpjRlktczhyS2M5S0Q0YUlOaFNqbDhDQWpTTkUwNlJITlQtaFZ0aTBkSDhwc1d3c00wTXk0ZjRXSDJJb1czVk5PeVQ3eHFTNW84a1hha1V3QndMTDhUeXBZaks5RmwzbTVyeVNDa2F1bDV0NEIw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPdDdFaE9uNm1ITUR3U2JvV1J6SDdYeloxTEJnTmJCbXNHYWtud3Y2bDVDT1lPMW56UHZ1cHFlZXBzUE9HMUhpb3BkS1hoc1ZEYk5jQ2VTeC14M1ZpajhHeGE3ZXY3Tk8zaHJKSVljWXNGTDI2alJ3bzJwYnZlZHNEWEw0OVluSWFIMkZsUTd4YkxRMXlsNGJEZHl3aHluUQ?oc=5</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2291,17 +2291,17 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>How agentic AI is transforming financial services - Impact Economist</t>
+          <t>Women in tech and finance at higher risk from AI job losses, report says - The Guardian</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 02:29:43 GMT</t>
+          <t>Wed, 04 Feb 2026 11:29:00 GMT</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxQdk5tYWV3M0t0aEtZRHhmVnI1STNPLXFBTTZPLXFXZENUbkdxMDdSaGE5dUh2dmRkOWpRYnpScHdmeE51SEV2WG91ajZJbUZPaFJLODloZUFtMFAxQkNfN0U1dEVqUUZ6YTFqRnhQZm1SWFRKRk9COUpRWmlTMWRVUWJUamhmdWJ0bUNPMw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNakRQMFJ4NFJDWEU1UnRoVG55QzZjWnl0WW1Kd2czUDgyM1hXVzlNYXM1S2ZtRlRmeTFXMUdMWWhad2taWGpCZUF4UER2ZGRpa3R5aTFycUhyNjZKN0ZzenQ4XzA0ZDdpX2xnaUt1d0I4TkV1VjdadFNQa0ZaNlQ3Qm9QN0hKQ1Vnd1Viamc0anA2UGdQLUQ0S0I1Q3pYXzRnOGc?oc=5</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2321,17 +2321,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Liberty Global and Google Cloud strike five-year AI deal - Mobile Europe</t>
+          <t>How the Met Office is exploring AI innovation - metoffice.gov.uk</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 00:15:55 GMT</t>
+          <t>Wed, 04 Feb 2026 14:00:00 GMT</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNY0RJU1NmOVNBNzdrOXdTXzdfZWF1QXpPdlg4ZHFKRU5tUWV3MndBR2lrcl91bHFVZlJtUFRPYmZBX01YeU9FUXhITWtVQXVkc3J5TVpxTWRMY3Z2cjhyZ3dZTVBqZWxkTXA3eEREemRsblBQYi12aGVWZWloVkY5a0lUNll1NzdmdjZ6VzVpS1ZqQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1NdzQ4Rk95YU1kQlJJeXN1RnkxYU5XN0RKTGgtenhKNDNTSmRPbHVwWHlwVVU4U05pSGx6MDZ1bXZwQ05FWC1sQVdnWmdSQkxZaWJ3ZWhrUkt4LXp0VWZIdmEzSE9ZVWp0OUVzdFZIckhRSWVGVi1scA?oc=5</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -2351,17 +2351,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Amazon, Prosus Reach AI, Cloud Deal for Double-Digit Cost Saving - Bloomberg.com</t>
+          <t>42 Technology and Synaptics partner to accelerate Edge AI adoption in manufacturing - New Electronics</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 04:30:00 GMT</t>
+          <t>Wed, 04 Feb 2026 23:27:45 GMT</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQYlpGRFV0SVRkU0VuQnBMaTRKaUp3VDlGOUswRmNuQmFCVEdnbkNRcFE1NVdKbjdrMmRSanU0M2NxUDVRQjJEZkVJeGtKLVVEYXZwdlJFb0RWaDVRUWhRbGtZbWFsSk4tTmJpNm11UF9PYTdCY0FXc3Jwcl9XRkRCQmIySElkdDNMQThmYnFpbzBYUVgzNjFNTEh4Y3YtTS0wX3BFTjNVWnltMWdHT0laa2xXdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNaThDVDY3WkFTTUVZdWpUNl90ZDU2NUlmMGZPOW93VGU5Tlk4bkxpMlZ3bjVQc2dSWWZOMHREaFRNbEJPS0hHaDZmZGFHY2VTU3NjU0FldnZyOGFlZVlRczhXZGRLcmlSNFZPWG9MQ3FaeUg1U3NIOU84OGtPR2xuWkxLRzNHbjdkSFdJUEFmbGE3OVUwUkJtWHlSaUc4QlJFMnJnUjlOY1VRV1dkUDlRaDdVZEZsZjdIRVZyVEpRVWdKd0s2bXRiMQ?oc=5</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -2381,17 +2381,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Use more AI and video hearings to fix English courts system, report says - Financial Times</t>
+          <t>AI 'slop' is transforming social media - and a backlash is brewing - BBC</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 00:01:01 GMT</t>
+          <t>Wed, 04 Feb 2026 11:29:30 GMT</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1zU2RFeUxERWhId3lMWDFVbmJTMl96NVhHdndqRkt0VW1JQ2ZSYjJtYWhYS1J4cHc2RHQ0X2tzOVp4ZnoyNDE1eE5Eb0ZJVzdsbjdCdjh5M2pUak1WU1pZbTU3Y000ZlV3QWV0dGh1clA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE9wNDA2bFFUbmx5aDlVcjdxaWE1c1JHZDZTcmxnampFRW5PN19EejRhQklPMkJmeDNYZnlMczE3MWl0M0h2UkhpZUN5b0hoX0RRZzExcTBZUmV3dw?oc=5</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -2411,17 +2411,17 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>New robot swabbing technology trialled for the first time at Sellafield - GOV.UK</t>
+          <t>How to lead with empathy in the age of AI - Home | Digital Health</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 10:41:15 GMT</t>
+          <t>Wed, 04 Feb 2026 13:55:11 GMT</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOd3FSVUNTenVpSFhtWjdBV3JYX2JNRWFhTWZCR2U1Y1FsWlVQQ1FhUjRMVmVwWnlZM2FOMUxJYVgxTk1maEY3RkJpMk9EZjk4Wks5em00UzJBbzRwbUdKUGVkUC1ybkJNc1J1WmtMNGxjMjhiREhzX29JTWQweHZfQ1ZhejluQjdSSzRmVVBGdDNWU0syUUhEd04zMWYyV1IxUWhETlRCejVldw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxNVm1KSkstZWh5MHNFYzdyRzFaaDFta3p1ZXZ5Ml9OYnRtZUladlp1ZTlXanBWMHZEdFBPb2IyN1dHX290ZjZZUlVtY1ZuZHpfNUp0WnJfb3Nna0kwR1FfemRCZVFFZU1VSXdpekg5bjljQ3J4NWFSWUUzMGYyY3RBdHAxSV9jSFU?oc=5</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>01.ai's Kai-Fu Lee: Why China will beat the US in consumer AI - Financial Times</t>
+          <t>Tech stocks plunge as AI fears take hold - The Telegraph</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 05:00:06 GMT</t>
+          <t>Wed, 04 Feb 2026 20:10:00 GMT</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE91ZF8xa2FhUFN1cnNHR2lzWlloQTg0TDltLXA3WjVnNktxUWtCaWpFcXlSS2ZrRVJUVGlxOUtOOVkzMGFjMjNWY3lWaGx3MlJSQ25DRHdOX1FzVUwwQzk0SkI1QXJOQVY0dk85MXNhUlY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPc2tvVTRXY1NJTW1TNEphOFJzMVZHZjlQLXdtT2FqTjY4cUl5ZDRGTklpcnBna1liU3dDdi1ORnVRU0h4bmh0YlczUDJOdHhVc3VzV2JqbVlxajhON0E0MGpmbUNSZ2VCLTJIVjNMUFRQa0ZIemExZXBqbFhnY19ySmdGWHlFVEVtLVJibzBkRF9uSmM?oc=5</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -2471,17 +2471,17 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>The trillion-dollar question for AI business models - GIS Reports</t>
+          <t>Web Summit Qatar startups raise $205 million as the summit wraps up - Euronews.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 07:00:00 GMT</t>
+          <t>Wed, 04 Feb 2026 17:07:48 GMT</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE94cUluRXhZMVo3ZjhYeHc0N25PUVN0cUl4RDdGeGtuRWVDaEI1dzJUc01pVjJNZnlyTDB4QU5iZ1YtZUtXRGpLbVNuLUU3cktEajkySzR5WGdueDBCMUVmT2p5LTI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQeUlsbVNiSl83b0dzU0k3Z2NoMlhBejJPNG9ZT3FVemxtUlE3MXdpdEJDVnRrbHdWV0JZVDBseFVaMm5VTkJKcXRtamNwdFpZWXlqeG5nWnJjenRWeWM2NFhrQnVWYTg3eTNWV3V2aW9iZE9zV05pVlN0NElCNjZfMnl5UXluX0RKSm9XbnBZODNoakExb2w4VHpqRXEtc2tlY1dKVTc3WWpPcjRhSjNOR243cENGQkJzbzBfNXhR?oc=5</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -2501,17 +2501,17 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tech Secretary: Barnsley can blaze a trail as UK's first Tech Town - GOV.UK</t>
+          <t>Lab AI and automation start-up raises $5.8 million - Chemical &amp; Engineering News</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 12:31:33 GMT</t>
+          <t>Wed, 04 Feb 2026 16:44:01 GMT</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPd0luMnF3ZHJGUFQyMV9VaXM1OENiNjFWVDRQbjRkRWlCeVBvaGxoYmo3Szkxdk04aVlpOEpsazZCZlZMRlNPMk10TnpOeWZOWXViNjNtODZtU3NTWHFZeHRJSnlpaE90Wk1UYXhmeEFwbTRqVmdNWXMwZFVTYmJrRUVUdWN6MDNZY1pwTFVNdjZab2xTMnpZTGNPN1ZhR0pZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPSVllLXFHZmR5aDJKaDhiRGpoNHA2TTIzWDYwbllkSHpTaGtxOG9vcmJ6dmkzRzFYQWJYcDBOSlNXYUNvZW9aUXlPN2g1akpuWjRFX3h5LVlVUGxla2tOR2RfOGcyWE9FQmVZY3RrZWZvTi1Kbmp5bVpoWkloMy1ZblpvN3NaRHpNNEtNN0xKZEY?oc=5</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -2531,17 +2531,17 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Are jobs getting better? “AI has the potential for a massive productivity uplift” - The London School of Economics and Political Science</t>
+          <t>DigitalOcean report finds widening gap between companies adopting agentic AI and those falling behind - Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 12:55:05 GMT</t>
+          <t>Wed, 04 Feb 2026 14:00:00 GMT</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPeE1EZV9iRnpHTVVPZTR5MDRrOHpKVHI3OEdpN0VobFpEOWlfdFVNQUpqZVN6N1gxS1R6V0J3R29YM2s2LW1meXZ5V2hRbE82Y1lyd0JpY0N2b2RWdFFWcFptNVF3ak4tWmVQUDh1Ym9kZEpqZG1VODF4Q2ktQzBzWXJlakhSQ1Nyc2tqbGxib0xZM19fazMtMW1WM2J5Z0tFUG53X19RaTB1Mm56ZU1hX2g2OGhsYzRnQUtOUlF5VkRndEl2T2FvRw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOVUVqUVRobjFLdmZHQk1peUc4bUljR29jN2FpUS05cEpDUEQ3NW1Ib18tS1pJaVcxejlTdks2QjNqUlV4MGc4ejJtRDVleEVRMnI5M3BTQVhyajJkVm1VbG4xWkc2bVFwTk5lWUdGVTZ6UUFSWlhCWXhLSjBmVnV4am8yeGEwNF81dURyY0EtRjY?oc=5</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -2561,17 +2561,17 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>From ‘nerdy’ Gemini to ‘edgy’ Grok: how developers are shaping AI behaviours - The Guardian</t>
+          <t>Energy and utilities cyber threats escalate as ransomware and APT activity rise, Cyfirma reports - Industrial Cyber</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 20:36:00 GMT</t>
+          <t>Wed, 04 Feb 2026 13:53:09 GMT</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNaFZVa3liZzhLa1dvUk5RVFc3d3h4MDVqbEkzY3lJOUZ0bzN6b0ZQZDVVLUdLTGF3RnFzZHA4aTFwN0Fja0I2WlhoTFYtTmhZa1BJYU9JSldfQ29Cd1B3WktreDR5alJSdUtCU2RRZTB3VGFocDl6eFhINHdIaEJ1VFpqTk1yeHlZZmp5Mk9QUk82dmtRVG5YZktURGx1UjVmZFpSY1BxVlduc0hNRlZJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxQNDFFcTU1U2tuV0FIQjdad012SUdtcmtKQkY4X3piR2J0UDVPVkF2NlZIdnVHMTM2UEg0Nmh4UGFPbnV1eXc0cjNmN2kyS0Zpb0ZzclFOMm4yRUV1ODg4VS15Y1lZUVhMa1ZnUHh0OWxNMThTOGY1SFo4UVQ4c0VsZlJjSHdHbWZOc3VKTHRsazJabzdWTWpVTWc1dExtRTd4cks0Uzd2UHdoa3pJZmdpRXl2eEdLRl96aklUakhwTmZ6cGxFUlBZZ2Zoc0lrb19hZENpN0lrbnloQk9TdW91TXVYMlRMQTNxWncxOEVqNA?oc=5</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -2591,17 +2591,17 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>9 indirect tax filing challenges technology can solve - Thomson Reuters tax</t>
+          <t>AI investment shows strong momentum beyond bubble fears - Digital Watch Observatory</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 03:30:35 GMT</t>
+          <t>Thu, 05 Feb 2026 07:45:00 GMT</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOMXB2MnJybjVnVGVlR09Rak5vakU1NEs4QmZXWEM0WndUTjRfUTBlb3hVaUxEYVR4ZWpuQ0d2SlVvcnFNN0NXY2swYmV5RHJrSktGZkg5UFM4UFVTTlhUTFVRUmNKNTlpdGZRb0dxZ2pyV0JqaWpPMzItX2RBb1pUZnA3SGk3SEZqNVM0cw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxNNlNjWFpPbDd1a3VxN3l3REEyOHVabFR5N2p0QnNPUmRrS1d3WjYyWmVUY2xrX2xzZzNQOE10RXhia19aR01JQjBsdHAwbEZkT2hpV0tzVS1TdXBUNllHVlMzNkJzZklEbk1OaXJkM0RaSmpuOENvQ1V2RHU2cmRSTDVpZWFDbjY0?oc=5</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Aberdeen Science Centre steps into world of AI with new theme - Aberdeen &amp; Grampian Chamber of Commerce</t>
+          <t>FirstFT: Google to double AI spending to $185bn - Financial Times</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 15:11:50 GMT</t>
+          <t>Wed, 04 Feb 2026 22:00:42 GMT</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNalo5Y3l4UTZST3JaSGp3c2t3cTZZYzNhVUxOMDA4TFFja0QtT21LSHlnZW5vd3VpM3RiN1JEQkFJRFhQZ1FBdHJGOW41c2xlX015aEdYQzZ1ZGdVUEJGYzA1WEZzOEJhWlp4UXhYR2pvTnVWQnNvbnJXMjYzLTg0SG52OWVxRnR2WFVCTEJnWkhSSlB5MnRRbGVaU1haUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE9xY3hZeENtWFpFdmZHTk8zT1FRTWxGNVVTMlVwVVFpSjlPeXg4WEY1aUFBNE1iZ0w3RkF6c2ZMWkxjZERMak5ENnlrU212QjdHMWl2Um05dEY5WUU0NW9OUW1QUEpUWXpCUGxidFlaY0k?oc=5</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -2651,17 +2651,17 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Alphabet (GOOGL) Q4 Earnings Preview: Can AI and cloud momentum sustain the $4 trillion valuation? - marketpulse.com</t>
+          <t>Cleaning up AI - New Electronics</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 23:04:00 GMT</t>
+          <t>Wed, 04 Feb 2026 23:27:45 GMT</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPUnl1S1J3dFVvMG9CMEdqcEphckNVTHVkSFFMMmNDb0JaUWhNMFNMM3pvRWZoRng1RmxBSG5UX3VRNFlFdTRjTDA1dngwRXl1OTUxSGhHUlNuelZMWmx3Tzg2YTBvYjFOSEpTMlpZeHU3eDJFWmprZmMzZjdHUDEzOFNhTkFhRkJnQ0JlVzVKWUh5NzJDSk1JSlpELVZyRkVTMW9tdlpuTkZ2akxnYndVbGJvZG16M2VYSWpqNVF5RUhoSzNYTk9qa25n?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTFB1MmFnVldNdlNKbU1Ocmp5dTdvdnBQd1JhX0pLYTBEbW1vNFA4aEMtZ0Z0MFNhaEpnRzRLS3pLLWl2LWdrY0VMYUVqMjlBbnRjSEdFQ2QzdVFEMjh2djQzeEhyT010WlhUZHE5ZFJXSTZ3cWkt?oc=5</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Leveraging AI for Optimal Clinical Trial Design in Oncology - OncLive</t>
+          <t>Germany's first AI factory for industry officially goes into operation in Munich - Deutsche Telekom</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 00:27:01 GMT</t>
+          <t>Wed, 04 Feb 2026 12:30:00 GMT</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPd29OejkxVVNVblpFcUpvbFdIQzAtd1FZaE5GemJURU1jUk9XSUtsbkxTTzNleVFNQmdlTWNtSjhPLTVrTXIxeXVDWHRlNzBBM1NYVTNCYTRCaHI4TlRPRE9UcVJUc3dSUm9QR2R0akU4Um1tWC11bks4X29UVFFCQWdZenhlYzM3NmRlWWk2RzhZdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPZHZHNk8wR1pCc2I3RTdESWRERllfaERRblZISzBHZXN4TV9PdmxNUHp0UEkzS2VpSlZZNWg5d3hIcWlVV05paGdiZjJIc1I0X1otRU9QQnRpMnJvNzR5ZDNGNVM4aDdWZ2JVSDFyMmVXY3JNS2FJUXFobkpHTDNtSjI5VEpfRmFwRF9kS3pSUG0ycGRmb1lfdVR2U3FybGlyM041QlNjd0RwQQ?oc=5</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -2711,17 +2711,17 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Hospitality Tech360 launches programmes tackling leadership, AI and the future of hospitality - hotel magazine</t>
+          <t>Alder Hey and Hartree Centre develop AI-powered NHS staff rota system - UKAuthority</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 11:48:24 GMT</t>
+          <t>Wed, 04 Feb 2026 16:17:58 GMT</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOTUloLWxxbENQaVVhU1hEcjFNLTdGMWZWSTBNdU81c1o4ZzA3SEZXaWo5aGEySDVZVnJ0cnQ4QkFnWUJXVjZJWndzTGdPQ2hEVlh5MDZrS3IyS0ZYUEZ0MTQ5dmRMSDJuYkEzdzAwVktYOVJqeU1LZmdfNkcxb3ZIYzl6ekNwcmlHU3EzWE0wbnpLb2VIYUVJLW44QmFtQnVqSTNEVWNuX1BXclJhUjhRT1pfbnh4MVozMzFwTUFQckJwdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNQUZVWEpMZThiMlNpMDdFS040cG1VTVhHSWIyb19yYmhmSTNlNno3MFY5emlXUlUwMFFacWJTa05UZVM0MHZYbGVMWlFhcGhfcEZWdlRGZ1VRVFc4OTd6ejJlZUpmOThod1ZDQ3R5Ni04N1QxZEJSUENFaGtSa2xsV2xkOUhVLVRYczFyeW56TDk4LVQyYzZ6WEIxNGIwYnZ5Nmh0S2JkMjBqZw?oc=5</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -2741,17 +2741,17 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Musk's SpaceX and xAI merge to make world's most valuable private company - BBC</t>
+          <t>Gangs use AI to clone pensioners’ voices and empty their bank accounts - The Telegraph</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 09:31:06 GMT</t>
+          <t>Thu, 05 Feb 2026 07:30:00 GMT</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFAzc09Ibzl2eWJ1OEQ0VTkxakNQV1hxOERGX01GOTNYUW5RNlRwNnVNbzdzSGR3TXJnaTNYTUdkT1doUXdwTko3ZTNJOWxNeXJTampQUVhSRDZlQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPLVBFYXd5VDFFQ2cyVTVDQ1BGMHBCWHlVdV90VTVvREdsdm5nY09CUkJIeFVrTkRzd09VcUJrbWQtYnp3Smo0cUxYWWRRc29tYUlGX3haYlduSkNZeWpXRnJxMDVBNW5VU2NzWWxzVlpmcVhUZHlKVmZhSmVtelR1bTZXbVZVcXpmOTJhLXpMYm5RR21wTlVQcGt5aE5GcGVu?oc=5</t>
         </is>
       </c>
       <c r="F78" t="n">
@@ -2771,17 +2771,17 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>enclaive secures €4.1m to scale confidential computing across multi-cloud - FinTech Global</t>
+          <t>Beyond bans: AI-resilient and creative HE assessment design - Times Higher Education</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 15:22:02 GMT</t>
+          <t>Thu, 05 Feb 2026 00:17:46 GMT</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOQmFLR3ItVk1aSW10TjRZWG9wSjk4d05tVHlLekNNVzdGeW1uanh3bGpJRlVoZnVvejY4Umdmelpya0tLMm02QnlrWXpsRDgwZHBPckdTclY5M2tySEVPS29qRVlrT0NucXZoZDV6LWlHci0xeVZMY19CRWlPUDB5OFEwajU5ekJZWWVDelZuaHFMSWFMNDhiM1lCV2E3Q3VDNHpYX3Jsc1dNQnM1?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPdk5WN1I0S0NjazItOGozejFBVGJsV2Zvb3pEanRpQnM4RnpKa0tRZHE3RmdlYnk1YXlqTS12RENVQXBRYW1jWmtmMEQ5QXF1RGtqS25hUFpkN0RRbTdkZjBodHdLQzh5RmNCdURxWjAtR1BzV0pKZUxtT0N0RWY4V2NQemtGVWlmeUN0TWhDNkI2RDc3NjRDUlBDQXlEMnRMNzg0?oc=5</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -2801,17 +2801,17 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Perseverance: Nasa's rover makes history with AI-planned trip - BBC</t>
+          <t>ElevenLabs raises $500m as telco AI use grows - Mobile Europe</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 14:21:14 GMT</t>
+          <t>Thu, 05 Feb 2026 00:30:05 GMT</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTFB5aXNmSUoxVDhEZjdEZ1l3WG84WGYzX2pwbDd2UFRsZFczWDhqRk9aMmZ1bENhZEFPVDFwaWtyV1Q1VVZndjNMVzBDTVlzZ1ZCZDc1QTd4VFZKQzBUVjA3ak5mTdIBaEFVX3lxTE1VOUNha0wtSkpOMV9icjRyeVBqWU4xZ3dWbTlsVnlwcjItOF91VkpITjV5UlFRaE9MT0xCcDU0akJKTm1ZWHB4U01qR29nS3pVMUtabF9XWVIxQ19ZbVdjZXNOVzRHNVRa?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxOaEVXN2NicTlCMXI0eG44OGhtQkpwTWlaajdoUE9lcjNpMjFzN21BMVVaNnBEUlRfZW83QWd3clVLZ3J6VTQtSkxnV0t1dm01UXdfdmZzMXdWSGpMS1RRWlVOQ0FsODk0ckNld2JZeEEzN3BCZjFlYVJCdlhkcUU4RGRn?oc=5</t>
         </is>
       </c>
       <c r="F80" t="n">
@@ -2831,17 +2831,17 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>How Do Workers Develop Good Judgment in the AI Era? - Harvard Business Review</t>
+          <t>Software and Legal Services Get Crushed. AI Panic Hits the Market. - Barron's</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 13:44:19 GMT</t>
+          <t>Wed, 04 Feb 2026 17:11:00 GMT</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1TcXg3M1ljSGhzb2kxLUVYejNnMjdhYVpKeEZUV0F3aV9EOV9pV21MTmpEWE9JR2RQUUFQSVJJZDVxNnZBQ1ZIRDlKOU9Jb25QYVVIX2ZEcGZOWXEtOHZBMXZIV3U4a092VG1UU0hheGpNcl9OZG8weXl0Rm84REk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihANBVV95cUxPZnNwZWdQMHRaLUNtZ2dRX19NbFNPSTVIVENCNkk1SVZvaTUtS21oZHFyVDNKTzhSa2RTR2p4cVBQNlo3amtVSktxa181Qy1xcXE3aDE0cVY1cUJJeUNYcENVYU9HeDMyZXlKTXpMbnlzTXhaR2RpMmtrZWdoQ2tOMVhTcWFFVzYyemdRTlB0dk5oNTRXVGJoTElId1FPSC1ZRVRkOHlMWTZEY1duVGZMY0pQaWJkUW1IdDN0YVowNnY3cEt3X1V4LVl2bG10TzhPMWxTNFJiX0FvcWp4QnI1U2I2VFJ4c2k4TGRWMHZ2RTlncjFtYUd1UU5YRjZMbmpYbE5iZ1Q5Z0c0NHYtQXlLS1hFUVl0alJNenBwR2U1QVZKck01VkJJQjU5b1VFbks1aXYyNG5fUGpiaHZ2cnMwSzJkTE9MalktTzZzWWFrX1BfcVJLcnFRVUZWbzE4RFVORndRMEZkWFBBbUN0Wmh3ZTlxbjB4REpidldqbVN5bzJTMTFv?oc=5</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -2861,17 +2861,17 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>CNBC Daily Open: Nvidia denies rift with OpenAI, while software and asset management stocks plunge - CNBC</t>
+          <t>Omnicom, WPP, Publicis and Havas share prices plummet amid AI sell-off - PRWeek</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 01:21:00 GMT</t>
+          <t>Wed, 04 Feb 2026 21:27:06 GMT</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQNHpZWElCTU8zN3VlSnNoeUhTZ2tPNWJyQzNzWDZOUldkTlkxcXZSdUZjWEswY3FVbmRCSjV2enRFY0IwVWU1S1JFMG9HV1JfOWtKN2Nla1lEVUtzZFlLb3Y1enowRkhrTlM0LTRDNlFacDZzclp1MGI5a2dmcUdOcjEwek5fREFTdHdnZzZ2M3NqSTAyQVpPMjhUV1pHaUduZ25QZEJ2V29qWmt5aDBhMGZlN3d1dTJEUWlUbjRUckxPVFQwd3Y2Zndib1Qxd9IB0wFBVV95cUxNZzlCQ3JZMnlJMEdPTTB0TThqM29fR3R2S3JTenFIX05YSTZFNlNzQW9RWDRzSU1uM0Jfdk83aWtXVlJsQ2lWTTdXYTh6U0ZPWE4zZHhvOXhxNURSUFVzdlgtUGFNcXJtcWd0U21GamdTbExFMERtVm0xVDZrS1E1VzdkVExPTm5MelQwelB0WmdlaHB2STkzQTEzZ2hsZFZ1M09IMkdORHNHLXdJYjJod205dUpPMC1XU0RQVGZ4M0x2YmtWUjdCbmFLVHZGUGhObE1J?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOMVNmNl9oTDRpeldHS3AxTFZsN3lJTDBaLUZFOUVYY2JYMlVwWUR4LTVFOFNsakZxOW96bExTV0FpNlRReUdZbnhWWmNoX3lFYktRV216Sjl4ZWxiOFU2eC1BQXdrQjFZUk1VU203XzhtSHhvY2Z0SnM0alpWQ1dNSzFBVjJLNTZQdGtjUFQwcUZQRkM2VWZjQlBWX2NOT095Q210Q0dB?oc=5</t>
         </is>
       </c>
       <c r="F82" t="n">
@@ -2891,17 +2891,17 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Dassault Systèmes and NVIDIA Partner to Build Industrial AI Platform Powering Virtual Twins - Dassault Systèmes</t>
+          <t>How to integrate artificial intelligence agents with operational work teams - telefonica.com</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 10:31:12 GMT</t>
+          <t>Wed, 04 Feb 2026 16:30:00 GMT</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOb1BjODQ2T1lSRWZJUWFXV2laMjl6dElWODlZa0Y1M295UENQS09BMHR6VHJUTlpRcmFsUmhXclU4bnoxd2NBaHRTQjUtMDRmNG1Ob0QwTkgtaEtiNUFLbUtIUmVZWXFkVFBHUVVPSUF6UWw5N1hyWHJMQ29zeFlHZFduMEUwdjd1UXBFUTFKLXctOWNJWi0zSldSV1ZOTW5EZGJHelUwMFprSUlKLW9XY25kRjBMallKeTI4b0U0amRuYzlyTzhCNjlqS1U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOZjJIaTN1SGtUcXlXZ0xmNUVPVS03TXVFTHZ0VzgwZU16ZVVMdmdiRkVvOS1ZbmRia2VRZTFGRDJSNTZoTzJUdk42MndtMnlTUXdFWW9USmxfYklHQVd6a2ttQ0dWSnlRRFhRWEdlbERrNjQ4RUZKM2luejVKMVQyMjFhbGNHQU9KVGhzbHNOZUZRUlo2UG9LdDlXazltLTBqMHNJeG5YYzR0b0o0enVHcHctY2FaR0JVNXR4cHBrbGFwNEE?oc=5</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>FormationQ, Cambridge, and IonQ Collaborate on Applied Quantum Work - The Quantum Insider</t>
+          <t>4 takeaways for finance teams as they implement AI - MIT Sloan</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 16:30:00 GMT</t>
+          <t>Wed, 04 Feb 2026 16:04:14 GMT</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPS0xHRF9WcnY4VkFOSDFLd2RYdFpBVjdfbUJnd1FWRWRDb2JrbjkwbWdLUzc0bkpLc2c5T1pJbnFFc2NZcDRUd0ZKSmNEN3V3dXFFRGVrcXl3NGttZjh5VXJUZ0ZsLXp1dFJiRWJOZWlhREJLaFFTd1RsbGUzby1WTHh4cklCdnlkMXBvWlNDV2lwc2s?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOZWxCZ3ZwZWZDWXJKeGJsUDdyb0ZiaWdCSzZfVGR6cDJDaGtqc3lXLVRUcV9lbVNhclZhb0lHakYtS3BGQl96UWh6QUQzZ3h2MXZIWEtkemhiemZUeUFyMFZqb0JfdUdFYmJGVUFBeXN0X2hkdTV3NGg5ZEZONVNGUEFSbVE3d2NFZTE3NllEQmp2Szg?oc=5</t>
         </is>
       </c>
       <c r="F84" t="n">
@@ -2941,27 +2941,27 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Managing insider threats across the organization - Barracuda Networks Blog</t>
+          <t>Why India’s Digital Public Infrastructure Will Democratize AI Usage - ICTworks</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 18:22:09 GMT</t>
+          <t>Thu, 05 Feb 2026 05:52:05 GMT</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxPaHVQWllJV0VIT2dJaEtVekhZTWQ3SF9BMTRpeDRGZG13OWR0V0pSSmtHdWtEOXByTTQwNS1yNEJLTi00cXV2eDJ2dzVqSk1KcUhjTFRfT1YzaGVHdTBWcGNWLVUxbGhsTm13MGNzaTRPcndGbTc5b29fWGh6WUg4MVhrdGxkYWJLa0xLdFlKUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOcklSUUJpQ0RwRTFGZm5HazZ3Q3RIalFIRTlEZ19DT3J5bC1XeTJJc2lfSTl3dzlNUE1DU3g0TmJfc1Fpci04dDZtMjdHZDZ2YkNqSElNeXlIdmpjcGlKYkQxUlZnTjdYX0ItSFlQb2swWWdSVUYwek9IZ2F4WmV0Vkc4TzJOMkVtY2ppMURlMktVQlV6ZjlV?oc=5</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -2971,27 +2971,27 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Prudential Of Japan Implements Voluntary 90-Day Suspension Of New Sales To Address Previously Disclosed Employee Misconduct - TradingView</t>
+          <t>Industrial Safety Market Poised for Strong Growth as Regulatory Compliance, Automation, and Workforce Protection Imperatives Accelerate: Verified Market Research® - PR Newswire UK</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 21:17:23 GMT</t>
+          <t>Wed, 04 Feb 2026 15:43:00 GMT</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAJBVV95cUxObUF6ZkV6bk03bUlPb0dRR0hsdkZpYm4tM2Y0SU1LaktjWnhHeFBCNzdnSkFsQ0xZTU5ORG1lRDk5elhodjlVV0VmTkxyWE5YWUpuUnpRMndmeVR2NWtDdkM1Tmc2VEtOdEhlT1VNM2ZLdnpHM1NzTUJUaFJtbldJUm0xbzdxV0pjYXpwOFB6MzhLWWlTNkNRbHk4dUtvRWhIdkM4RkE4ajBKNV9jc2pBV1RpY2dJNVJzVmFmNHVURnpvSVpGb055Wk5yS2pLdG43aWpjZFdtR01kbVVxX0k1emg4eXE0U2FBamkwMTIzWldETlVFbWd5UDhjcWZTU1FBTDhsdXhLWVg0UGFOUUs3QTNmY1dEYXBoMEZRUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAJBVV95cUxPNHFVWHJheEhhQXFLVkUtTXFveXRZeFBhMkRjZi1tV2hqN0VZRXRNY3hDR2I1NW05T3hJdVNnTkFXdURnTWpXSDc2STNfT3VCSVdzSnpzdG9Jb2xRaTk1bV9BSXc4LVZ3OG9vMERGNU5zZ1cybVhGbkVUVUVoRXRFY05nZUtBdXM0eVp6ME50RUxBQ3VCaUdnbmwybGVva1NNa3ZLcXpnWlhZTmNiZ1M3YnlKcUtQQlBTd21BNlRzS1VuTkJOdkg3QzJKTW9idnl0TVBqTE82cW9XZWJneG1hLXBCMDdLeUdRdE9oRnVWN2MwNWtOcVJsNkRzSm5wcUNpVVVuOEFrQ3c3cmdvNmV4eFpuMU5ROE9WY2NveHl0aDZFYjdIcHdOUkczbTBvZWJPQnlqOFFFM2pFN0Rk?oc=5</t>
         </is>
       </c>
       <c r="F86" t="n">
@@ -3001,27 +3001,27 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>News - North West council starts crackdown on housing fraud with launch of key amnesty - Inside Housing</t>
+          <t>MTC drives automation and robotics scale-up with new accelerator programme - Plant &amp; Works Engineering</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 16:30:00 GMT</t>
+          <t>Wed, 04 Feb 2026 09:44:43 GMT</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNdGROQm16bWJmc1kzMUg4NkdDVjRLN241ZlNRZGRyZVJQUVdXcUFEN29teVNuZ2pjZVJPX1RUNUNsamxVUElhbXkxUUYxcGdYcEttTjJtR2pxMVdkU0Y4VGV2aFd2YV85Wi1uSXNaZ3ltYUpUTkxPd2sxUzBINTdpYjJhT2tIbElTUHZzbldFZmxrR0diRHI2VUVKdFVfZE1zSGcxSGZrM2NOLUo3V3VqRTRma0xiVWJYLWR4YkNlQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPajdlZTNBbUNIblhpQzNDU0RmUlBhTUxKVEhSNUVrcUhzQ3RlSnBiV0xyYUl4UG44ajNSMFdDbG42Yk1KWjVwRmVzdERlUHdiWVNFVlFWNmJsS3VzdjJ4ZTZmQmV1aGFLMG9iamRMbEZ1bGxNTDc5R0ZWcnNBOF90dW80OXFPZ0VrLS1QeF9hYlR1aXhXNUZhZDB6MUU?oc=5</t>
         </is>
       </c>
       <c r="F87" t="n">
@@ -3031,27 +3031,27 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>State adding staff to review nearly 6,000 Medicaid providers in Minnesota for potential fraud - MPR News</t>
+          <t>Understanding Global AI Governance Through a Three-Layer Framework - Lawfare</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 17:32:00 GMT</t>
+          <t>Wed, 04 Feb 2026 16:30:00 GMT</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNUGlSc0lpXzN2X3VPbTFXazZ0cF93WTRYMURlNW1YQlB1bFYtbGZveS1aN1BpVWxfWVM3T05UckE4eEJVRU40STNtV3FCdjdrZEdpVWdXa0JkeGpSSVhGTUlJRWhYZWRXeG9XTk5wRndmZXQtY0R6bzVITlN5YnhyNWFoQ21oMldRcDdiaVBRN1JjOHhINTVWZ2dHYzVSUUIweTE4Z2ZneDZUeWFIYVd2YQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNbTBCUWN5N0tCVlNfMWtVU1BaSVh6VmtVS3lSWG1mVU90LXFZakw3TWpqYWhmajlVVFowNF81eG9UdFhhVEktS1JHUkM4dWh3MllMSFdzN1ZLalpEVUR4T29DSE8xREJjeE5YZTZJQlduNFR6a2dudUNwbFNwOTkzbFNkNlNCckdCbFlvNnFGaC1MVzEyOVRiSGNsclA5UXBKMm9SbXpR?oc=5</t>
         </is>
       </c>
       <c r="F88" t="n">
@@ -3061,27 +3061,27 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Man used social media in Gaffney property listing scam: Police - wspa.com</t>
+          <t>Smart AI Policy Means Examing Its Real Harms and Benefits - Electronic Frontier Foundation</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 01:07:14 GMT</t>
+          <t>Wed, 04 Feb 2026 22:40:34 GMT</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE02c0VSLXZKdFlTZDVjRmdHYUZiZVdpMXNfYzZXc1h3Wk54Wk9UZkM2bjFwX0tCNnpfcEc1ZUNZeUZsNmQyR2V1Nks4YnhvXzZObC03UUI4eXRyUVM0OVBsT05kbkR3YlFNWUxhSWxB0gFzQVVfeXFMTVpsZE8xWTBvTTFfanFtY2dob3BSWHlYWlZ4UWJuTVVnME9SYzI0eEo5RUJoSnJMOWxxRVE0Sk45cktocTVxSnpvODAtZmJhT2l0dHJEM3FVTzkybEptZGVYYXpUS2RLUnlWMG83aTlFNWtXQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPUlBmX1ZENzNYbk9KQld2eE1Zd1ZyZDltdGhER1UxbTRIbWlvNlNDQ05vZkNPejllb2o3amRPTEN4VEZlMVdJdE5HRWpnTVM4QVY4UXZHR1d2X2ppaGtkZVU2X0ZBc1A3ZnpoSDVKZ3QzS1hoM3U1T1lHMzJFeGtqY0hLWXVlVVVUajdIZmM2Uk9XdHFVVDBobVRIUVp5aGZZU2dr?oc=5</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -3091,27 +3091,27 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>CNAS denies the information about the granting of 5000 lei from the social fund: It is a scam - ipn.md</t>
+          <t>Telling your company’s story in an AI world - Daily Business Magazine</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Tue, 03 Feb 2026 10:46:59 GMT</t>
+          <t>Wed, 04 Feb 2026 19:51:31 GMT</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQeUtTOTY5c2w1MjBkLWxRUHRacllZN0x5MlNuNDBJMmZJWW9CZEVPaEdBTzhIUDJIRUhEX1g3bThnYTFXRERpM1FwV1dxei16ZWVPaWhBUld1NlRrRXFRRVQydlRFZkdhMnJvbk0wR2R1Q0RfLWRNb1VxT005eHVkbWJlTDFtcjg2TG5Dd0dmWjZhb21Gdjg0Q2pXMG44LTh6U2ZyTnlZUXJfaXRCdG5mbA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOZUZPX0xpcUE2a0ZMT1YtY1N0NERvczUyM2xyNlJFUXRDOWYxcWlrVG1wV0xGMklwLXZ1YUlxc2Ixd1M1NzJybUFKVTNSMEVLM0Fqc2hOU2U5X21ubnBCLTNvWXFDeFpCT3F2QUp4TzhBWTVBQnNSbHJXWFBGQWNURXhBZnpVZlU5UGJ5MUF3MmNHQUo0MURwS09FNlo?oc=5</t>
         </is>
       </c>
       <c r="F90" t="n">
@@ -3121,30 +3121,510 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Your Brain’s ‘Scaffolding’ Could Collapse—And It May Radically Alter the Way You Think - Popular Mechanics</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Wed, 04 Feb 2026 23:41:00 GMT</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxON0k0bHRXdXh3ZWlLUmU2V25Kc1ZIekp1UUJGN19zZlNpenhpNnFMQUFSLTJFdEpkREFLYWRJTk5sQ2tLU2lIUzlFdFZ2RU0tdy14WlJzWG8ybS1QX2dkTFJmN0FrUnNIV3MwdExfZTFJTm5fdUhMUzQ1RV84MjVfblB3?oc=5</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>"Moving Forward Responsibly”, the Dutch DPA's vision on Generative AI - Stibbe</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Wed, 04 Feb 2026 15:11:47 GMT</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOb1daTm1iTkZ6VTdIREZvVVFPUzB0bEx0Y1VtTXh1LVVmMHRqakI5R0tNdnNwV0dlOHlvMWlkcmlKSVoxclBfa21XbGpTX0hhdGdybXljN1d2enVoTnJ1ZWMzRlYwbE1OOF9MZVRnM2YzQzhqcUJKNHNXY3hXUnhud3ZTYXhKaV9FVDYxRk9BNUtGOFFVMW9lVlZmeVRmQVA1TnVKc3pVMTVyS0JTTDRUVW9XaHE?oc=5</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>IFS : How Industrial AI Is Shaping Construction - EME Outlook Magazine</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Wed, 04 Feb 2026 09:58:13 GMT</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxPNDJkTDI2d0huNUZTell3WktfbzM4ZUpHX1ZzQm1OSTdpalg2VHI1LWtHbEsxRXdIZWNnRDFCU1ZjMEpfZzJhSE1TQ3JKYWpqaHhPQm9qT19wbFI0Zi1tXy1MY3hDbmdfV1QzZkFfOEhOelRqMmpEM1FfSDVpRTZlZVJOa2t2UTNiVkY4MkRmMA?oc=5</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Developer’s Guide to Cisco Live EMEA 2026: AI, Automation, and Meraki - Cisco Blogs</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Wed, 04 Feb 2026 18:07:22 GMT</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE5hNWpDVmE5VDZ0YlhVcXJUVmFSMlVxdDdxejJvV1ROV2NYbV9KZlRYZExHU3Ixa25YeHN6dmtiSzZpejMxaXotdUdBd21ramdxWVctSFYyOXZNT1lqUUc1SHA4bzVHdlNyZmkwanhJdnFobU5hVm83ZEdn?oc=5</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>US Renewables in 2025; Supercomputing and AI; and Tighter European Sanctions on Refined Petroleum - S&amp;P Global</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Wed, 04 Feb 2026 11:35:16 GMT</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNak9XdUo0TC1JQUtVTTRjMEM5NW5iUTZtMjJBS0V2akpFU2FQckNxaHpIb0k2UWdReWtOZUgyU19LNEpHOFZsNG1tUDdlb2xLZTFzZHNrMkJRR1I4eXdJcDhQQk5xXzVoU1pXejJPeEdlSUNxaU1xd3RCTnFYVDR4MWFCOXloUjhabWFpRzFBUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Brightcove maps 2026 AI roadmap &amp; Video Cloud revamp - IT Brief UK</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Wed, 04 Feb 2026 10:27:00 GMT</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNS0tQTy1fZl9VQkxDMXJhM0Q3Qk0xMzNzWklVTVpfM3VUOXJhTXhCRW1MaERob3VtcVhGWlRmMjIwVUZJNVYtSVg3YUVtUm5fZ3I2MENtVDFRdEY2WEMzN0xRcTQzdTdkOEFZeDRMQVhlT3BneER4V1VpV3hsTHQ4LU55UEw?oc=5</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Workers worry about AI job loss amid enterprise adoption - CIO Dive</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Wed, 04 Feb 2026 20:49:52 GMT</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE4xQnU5MG04QzVBcWhmX3NfVWZmanJLLUZCTkszWUZiRE9UckNuTzRRVkpLOXp2U1VONkV3RENvTGYwaUlYVW43LWdnZVFoR29oY2o1U0s3WjZlQjEzQmpHMWtFS2E3ZXRoa2lJbXZqd2hlQVFSek5CR0dR?oc=5</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Anthropic president talks debut Super Bowl ad, future of AI and what it means for kids - ABC News</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Wed, 04 Feb 2026 20:48:45 GMT</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQV0tuU0o1OWVsMG1DVlZpUXViakRrdVotWU5tOVdUVFltdk1UVERlUC1mUzJQV1FhUHlTemNSdngwNk9uc1R6NjBZUW5yNzNhZXRScTVmRmlreFFsYUZTX1g1YzJDdGo2ZXAzcEktQkZqcjlOR3RDcGJ0QV9uMmJzUUQ0RDBndVZnWXVjQVNYQ1JXMExvdGxRTlRtQmRyUjdpMlFBdzU4SFlKUdIBrwFBVV95cUxNWEJXb1QzOG1qWGlBLXp3dk1zQnJwYlU5V1U5Zngxb3FNeHFPLVRxNmRaT1pmZjhBWmpITERMcE8xRy1kRzhrbGgxejV0RXpDRVdlZHlQcUZYZFdlbkRSQTZsRW5XYjV4QlE0cm5zcGNwZGktd2pXNGM1WktNNG1QVkstZkRkejRBX2Q4OUxFVXNvVEZRM0FFRlduOWtTU2hfU3dBblc3Uk0xQVRmSThB?oc=5</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Insider_Risk</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>CISA Guidance Emphasizes Insider Threat Readiness - RTO Insider</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Thu, 05 Feb 2026 00:27:09 GMT</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOZTdrdENmRVJPOUloY0tKMEt0N2JQT2hrZDJmQXZ1cWdlU2FhQTBYbm1USk4yT3JNQ3NieXZuZ3g2aVo2VUNPd2k2YTJ4UFpMSGZiR1dFYzU1TWhNbDNVNmQ2VlcxZ1QySDRRblZ2cHc0eHVRTUh2RWM4bzdPZlladUp5eEFwMkxMelowUw?oc=5</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Insider_Risk</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Insider threat cited in $22M Iowa bank fraud case - American Banker</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Wed, 04 Feb 2026 21:22:00 GMT</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNcUhMQm5HVzBqRjVKY2NoYlBDNnB4aTdJYnpnb1R1d1N6empJSHBHRGVGN0NqUVI1QmFackp2VWVub0hCR1EtQVNZOVJSQ3JyUzBqU0ppTWtyMl9STzd4SDFMdmJrZ1VkQkZBSlExTkpOa3JNRmotWkczQ2hsUW5EdWhDUUdVZHVBVFpjeQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Insider_Risk</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Allegations of assault and employee misconduct at Macomb supported living facility for people with intellectual disabilities - KHQA</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Thu, 05 Feb 2026 04:25:00 GMT</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgJBVV95cUxOUUo1N1lRVXB3VXRlRlFQT3Z0eE5PbUg4TUM0VzZ0ZHJVVDROQ01TVFBLQUx2OHU3WXNEd1R0NTRub0tpMjJJWnZmYUNxRGdhalNWbjNxMGVnd0lzS2FHT0kyREJ6cTk2NjRJZVFwVGpSQXFnbFE2SF9tOE9xQjRFXzFJWTJOeEszV3VRWTV2aTFVSXlOVWtQZFdTSjluem1zQlVBNEp0VHJ2UFdJNGotMEc5aG5hanpXQkdXVXFwUnFMRkhyeDFtOXQtd0diVkRTQVBfUnJ0M1VCMFdMSWM2Y095SDJCZVk3bXBUT21tMEVTek1JOU9tVXJyd01QQTBkMi0yajBGUVpueDV4NXBKYWFna2g5UQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
           <t>Fraud_Scam</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B102" t="inlineStr">
         <is>
           <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Scam Alert! Social Media Page Claiming to Be Famous Krabi Hotel Was Found Fake - Thai PBS</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Tue, 03 Feb 2026 10:31:00 GMT</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE9DeG8wQ20zZHhlcFdCQ2JSRmJHeEdBcjBqalAyQ2g1SGJId2pnWTY5Qjk1dmZkZDJXNDlsb29HWnFOTkpKQnFFSklTNEs2NlZuSTR3QXZWM1F2bGYy?oc=5</t>
-        </is>
-      </c>
-      <c r="F91" t="n">
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Council launches key amnesty to tackle social housing tenancy fraud - Property118</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Wed, 04 Feb 2026 09:09:47 GMT</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNVFkyOXYzcFVjVExkSVVGeEliZUNWenBKZ3Byd0Z4aTNqbXZhb2NteXlrRWFTbTFhX1p3bVBra3p3d1RneUR2QnhzQU9XTVl4YmNObmVSUnV0RW53QjFENno4MDhBMmZzMGI3MkRSNER4MEdoaEptbGhIVG9jVHdxZmd6eWgtLWloMXZyNjZNODdYcVZUbkRpOEo2Y1c?oc=5</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Exclusive: US Senators unveil bill to prevent scam ads on social media platforms - Reuters</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Wed, 04 Feb 2026 11:03:12 GMT</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOYmg5YVltOGVZSGNFajhSam5ET05SX2lqODVKdDRwOG5XbjhZV2x1NnNMX3hvc29VN2FYbVltWWJINWFsSEpfbHl4dlowUW1QdjVBa3RpNHFKQU9EXzBUdUdmZ3FvTGl6ZGd4UmtEMko0MXNSS184SS0yRXFrMFItbUU3eHpOZVlQLWJySTlJMDAtd0pwRXAtamNGOENBeU9hdDVOa0lPNUxMNEZ5RkFyX252S24xZ28?oc=5</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>'Too good to be true': Warning after counterfeit iPhones sold in social media scam - Lancashire Evening Post</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Wed, 04 Feb 2026 13:25:00 GMT</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOc2RDcndqdEJuVWp5bVBUbVJDMHBkTUhxOEVmTzdwWE9BRFVEb1RfbnhRbHB1T0dwYm5ESnFQRi1lb2hhNk1ocUUxU3JLay1CV3FzV1ZUQXo1bE1IcnliN2FkdnIwRF9zNnh6NDJ3Yk1McXNzRDQ2cnJXZlhDWDFWdGxpQktlU1NtdE5VSU9SSUZmRGMzdDNTdGRVWFpTV1VZYVdRVjRXUHpRa1R3N0RCNUVn?oc=5</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Being social media sober is a scam - The University Daily Kansan</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Wed, 04 Feb 2026 21:14:00 GMT</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOTENaR2pnSmpqTnA1YjBJNHJuLVFJeGk1Z0UyLU5TcDVjSjlSWkVUYjdBNWNvTXR3NDV2SDl0RmJWek9CSTAwQVI3Y3Jtc1V2MktsOWJpX2d2U0xuYk5lVENCVkRMYmJWRWN0cC1KT09aSm85V2I0R1NtUXg3Qjc5X3NaWmlUSUZVNFdITnJLYWEzQldEQzVoZGJndVEwd285VzV5bTBPZFRNRnRPMEliUHJGWmNwUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>”Phishing &amp; Social Engineering are the most Significant Risks for South African organizations” - IT News Africa</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Wed, 04 Feb 2026 14:00:03 GMT</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNcTd4VGhOaTIwc1VFc0w4Zk5obURrUWYtWngxVG9UTTRuWV9GQmZnU1RIT25oTkd6MGRncXhsWnp6OHBaRTV4LThoMDg1Ul85bzlvQndOeWxNRzZudWlUcE02NXc2V0sxYjIzc0x4QkdwbW9wblNmNUpCYjNlY0VPbmNBUTltV09oWG9vYnJ5akF3TllFbW01eDZVNjhhTS1VNV9IZmlheVFtekV3NmRUczhORmgydW5yVWozcjJkdV9JcTJRX2Zz?oc=5</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Indiana governor launches group to root out fraud, abuse in federal social safety net programs - Indiana Capital Chronicle</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Wed, 04 Feb 2026 12:04:15 GMT</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOY0FXOFBLTXh2Nk1sSWlUa0E2c1gxUkM1QUQ5X1ZydUxaVk4tNTRYT2dUcEZfQ0VfeXFQNUpNaUJWaEJKcWtTcTZDSjFDS1NBTmJ3T0lqckhGbXFQWFFlampjMVNVVHJwaHI1SzlxYVBzSVB4R05fTk50UF85NHp0UjIyay0tT1BkLTBNa1dUdHg5ZlZtTlgwRGNWd3NVcDk1YzZ5YmVXTVFnZGtpMDdTQWR6UkQ3cUxqbjZ0bDhDdHBFN0VYYWlsN3hWY0tjaE8xUFV4V1E2eEs?oc=5</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
         <v>1</v>
       </c>
     </row>

--- a/data/daily/topic_feeds_daily.xlsx
+++ b/data/daily/topic_feeds_daily.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F107"/>
+  <dimension ref="A1:F97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,17 +461,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Vulnerabilities in Government Bond-backed Repo Markets - Financial Stability Board</t>
+          <t>Report of the Cranston Inquiry - GOV.UK</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 09:03:43 GMT</t>
+          <t>Thu, 05 Feb 2026 11:35:23 GMT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNZ3FOQ0VSNVlhUkRKekRlTmpHRGRiNmN5MjZ3M00xNmxuQURwbEVfSU5iS29OX3BZNXNFcWtpQlZPMWtXRFV6S3k2Z1BLeGZlQ1FDX0N3T0V2NTVkbHljZG90X1J4RHFKLVgwMlFBOHJOam5nQ1lKZFFfTERScVctTWhQLXlrY2tjWnBN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTFBETG8xdDBhelhEVWRlbXZrUXVyaXNQTlNzNjhGOVRGRWh1Q3EtM2s1UGM3SkNSTS16RVRvcUdoZU84Zktud2VKYXgxVU5Fc2dSQWRHU3NoR01jZGZoY01aaEF6SW1KVUpEWHhybkNJbS1pckljdDJPQw?oc=5</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -491,17 +491,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>UK government must get its hands dirty on security, report says - Computer Weekly</t>
+          <t>Quarterly Mixed Migration Update: West Africa, Quarter 4, 2025 - ReliefWeb</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 20:56:45 GMT</t>
+          <t>Thu, 05 Feb 2026 12:48:01 GMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNckVZV0N2d3d3ekRWMzBadWtLZW1zNzNNTHRSeWY3MTRIM0dfam02WTJWemI5QmJsTFhJa0ROcjZKTXlyTldDbEFoUFRtSEd6dmdpN0FISS00OGpuQUN4WXFlc25yTUlfbV9OQ19scVFUX1NYeHluQTFQb0JPSGZsMURhck1TYnA3cGp5bUJfeUN1R0NtLTJNS183V0FyYmdHSHJnRHJyR3RoLWVJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNa01PLXBYSTI2cGMxR1lxLVNRLTZoODN3VGQ2OHlzY1IzWXBIc3FiMmpJTEYtN3lBNGM1cl9CYmhyMDUzZFFLS3JmOGVnQ1JtUnRQUFVrSkhlTGxheGVLaWU5YTZoT1JSaU1oNFBqdG1yNVJyV2FCaWhpcThCdVNSTDkyOEZsdlMtTm44bl9vWGJSVXc3eGUwRw?oc=5</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -521,17 +521,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Marsh Report Flags Policy Gaps That Could Undermine European CCS Funding - Carbon Herald</t>
+          <t>Why the Bank of England is holding rates despite a weakening economy | Phillip Inman - The Guardian</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 11:50:15 GMT</t>
+          <t>Thu, 05 Feb 2026 13:18:00 GMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPWXZyejNHNW9TNGp4ZC16MVNTVDhDV1FwdVpnalhFdG5JOFY3N0JOeUI2OHFYQ3JBOGwwbzRQVGF2YzVWRWVtZnhPQTJHV2t2TzZTR0tSQjFQV0RqdWhDazVRVEpUNnU2ajQ1X3FyZFo2QnRrMVgzRnZ6dkRmRGJRZjhJcGk4MWhJNE1abFppOWFSeEhOSWQ5YllCYURWTzQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOWkplWEZRV1d1M0loR1I5b0FKUkNLTm1qQWNsMTkwVzFmUnNhbG5YOGpxV2RKRWlWcE5JQjlOQ29SQm1GNHJrYnVFcG5mbFBESmVIVUxJUF9jbWRUNnNJNkQxVG04V2dWNlZiVGNvc05SaVphNld4bnppWmgwNFlhVWhLaVNzbTRtamdIdnRlaXIzVHFuZTZCbVJYY2N1YXF1VzR3dUZBQzJLUy1pLXMw?oc=5</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -551,17 +551,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Inflation and regulation among factors reshaping convenience, report shows - Talking Retail</t>
+          <t>Government update on 'biggest change in a generation' for Warwickshire councils - Coventry Telegraph</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 12:10:09 GMT</t>
+          <t>Fri, 06 Feb 2026 05:17:51 GMT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQNFp2RjBiNkE4ZEMwTlBEbmpUT09qdVRPOS1yb1RYZFFjLVY1MjJzNEFfTHgtOW9TNExCR19ZTkdVZGR3LWVlU3FFUjZoazFpYXFDbWd1XzA1XzQxTzhzak96aWpJRVlwNy1GTUhzY19keGtxaTlZb2NqYWxSRzI2bVo1YWlFd2syMmxFZWdaZVdWeDNZZjI5NFlGeHUwNEpjd1RQX2hSSzBoZTBSUjgzNWJhMmZyRnM2Y2NObjhpWkd4dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQXzdKUlc2RHRGNGc0anlISnNMbURhcVhiX1Y3Unl3VnplbUswSFZFWF9Cdkk4dlpXMnUwS1N0ZEJ0SThORzNKb0NHUVpGdGlSQkxKOFJJQjhyZHo4Sm42T2x0cmE1VnRBYjU5MmVydTQtVkdqSTNlSEV6VmhRZzNnaHBFaTJUcjgxeFlZaFY2R3g1Y2JIZVVkMHRPSlNVWXJGSzRIdtIBqgFBVV95cUxOU3pZRFdmOU1rekNuZ1JtdndDZmlaakhTTEZ2a0RPZHlHQlJlOHZUazFlc2xYLV9ZbGhZZk9VUnQtS3pZcEFWcDhROUptakVCaFROVEJCV1pSZUtDalAxXzZrZV9VNjd5aGQyNEpIY1R5dkVPRlJ3ckozZWxHazk4OV8xRWZEcTRzVEltMWE0ZE51blE2TEp2Yk5ESHN6bFVvOEc2ZXhmaHoydw?oc=5</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -581,17 +581,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>January jobs report will be released on Feb. 11 after shutdown delay - CNBC</t>
+          <t>Gender Balance on Government Boards – 2024–25 Annual Report - pmc.gov.au</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 17:01:40 GMT</t>
+          <t>Fri, 06 Feb 2026 00:27:18 GMT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxOTklhTHVoaVpUaW94b3k2N0lyS0VOa0tma252bDR0dlRZdFR1OW1vQnN6eWwwLUI1ZFp5eG1fRFY4S3RXd0F0bS1aeTJrd1dmWHdNNnhIQkhjd0FJbWVZaldCS3BmTTRCX21kLWRLUUt1Rk1GWjRjaDlPUEhSV0xBTGNn0gGHAUFVX3lxTE9uOUg5eDcwdThtWi1JWHhqUkhIVk9qaUtuQlM3OW9IZlFKQVB6TDVNNFg2X284Q1RwOEx1cUhoVW0yWlRUdWFFRURoaTVrVUNLeUFFaVZGZG9GOGxRQzg4R25fTTlFOW1GbV9ySEpQcmhsYTJKOVJxMzZNdXNndDRsYXBnY2h0dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOeUU1RFhoWEV6UXFlYjVVbGp4RFNreDNRSVNLZGV1TUVyOG45ekNvTGxhYkhVbEU0TVpjR01xY2xXVEM0Wm9WOVlkZTlxcW8zemVCTV9uM09kN1l6MHdIQ1BLNDR3YnVpb3lqYndCVTQtTnQtQ0NwbWFKVG9PUUZCMi1sNUVvQ2dpLWc?oc=5</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -611,17 +611,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>A rights report calls on the Syrian government for comprehensive accountability for violations - Enab Baladi - Enab Baladi</t>
+          <t>Bank of England Monetary Policy Report Press Conference - Reuters Connect</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 19:44:06 GMT</t>
+          <t>Thu, 05 Feb 2026 13:28:00 GMT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPT0p1c2lMcWJaOVdDWG9UQ2dzSGdXT2Q1dDdBTjZnNGg2LWI4NG9ZXzE4N1ZVTkJmVV9HVTNZcXh5V1RWZjJEdWc4ZjltNHg3N3o1T0JIMTRrYzlTUTdfakRVZ2hsaEdCeDROMm9lME9XWmpmbnU4ZjVFVENNMDFJUUpjN3VOVEMtN2FGa2ZqcDRnZW5DYjRiTFJDZ2pBa3ZrX0lHNDJEbWlqSGpMOWVvQ0pDRWZfaG9xd0ZybGx4ZDNabkxfZXNENHlB0gHPAUFVX3lxTE9FZ1Q2cUN0NjM1S3hZa0tCVUdjVVpOWEpYX1hZcjZKWkxaRzlPYWFCbExnUXVjaFFOaUtYXzI3a0pYamdEbE5KRVlZU01hYm1uVmxkQ3huNzFBZERZck9HNXZiRVJoMmpHa0pQYjFzT1M5WFFjcjg2cTYtNEEtWkE5eFlPMWFNYUxMbkdpbndtbWg0aWZpSWxOQ2lCVmpzN3l4dEdSWmkxRFJQdjNiRWNZek9lcXVSMlhzdnY5RWN6R2o0UFI4TEJJYUNYY3dqVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxQNGFQajM0ZmkwRFIzdi0yeUM3Q0FXRVJXNDNlUVVBeDdVajc5TzFaZ1BTYWN2cFhoSEd2aWpXVmNBbi12b3lvV0lzQ29VbFkxWWJfWTNKNzY3RnVYYWFValc4MHItZUtGblpwUm5vWHBXWWFXRlFCUHN4MC1nYTlvMWVaRThqYTZzZUw0RDYzaWE0RmlUalpuRW9mMjhfaGlIdGo4T2liMklJWVVnOThGY2NvRmx2NkN4cWNlR1VVa29rMWt4eUVGQzJNLVNFNE5ESGtyMU9TZ3RXQ3lpWDBJ?oc=5</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -641,17 +641,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dorset housing allocation policy update - Bournemouth One</t>
+          <t>CEO Innovation Policy Update 02.05.26 - Massachusetts Biotechnology Council</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 13:00:38 GMT</t>
+          <t>Thu, 05 Feb 2026 22:22:18 GMT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE9sM01xMUlseXVoY1gxeHhueS1sM05USnhvUHpRTHdhYWVXU0RZU1NjVV8wd3lZQkVkdVpIMUNCS1V3RzJXVEwwQ2RPTUFvNEU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxQTmphcXpjb3BVREItNjduWGdHdG03R1p2a0VKMVB4c2k0M3dsTy1RVzNuaUZDbGhfbVRpbkFCbzFMdmhZNVNVbUtrN2p6OTQySTVwcXEwTnF2YWhlLTNuWG16b1BrX3FEUDdFTldYbWRmaDhUQnpBeTl5Ty1rZW93dWp2NE00dw?oc=5</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Government update issued on drivers reporting 'collisions with cats' in the UK - Daily Express</t>
+          <t>'Stealth tax on jobs and wages': Damning report slams flexible working as damaging to productivity - GB News</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 11:35:00 GMT</t>
+          <t>Thu, 05 Feb 2026 22:33:03 GMT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPdHp0ZGhrS3dwVmJSNjRJZElBMi1yOXJXSnFUNVRYUmVxNUhPMVU5TmtDZnJUMDRySS1OSWRzaTdIMEFVZ2F4UnF5d3ZWb05KcHhlU1JzMEI0UG4yQWNnRVpHY2tHVFpxQ1JObkpwUTB0WTctVFB3RmJ3V0FxOTZOZHI4YTlKSlBvRHNrSlZfZ3RFQkFiR0hrUnBTWHVfQnJFM2cw0gGoAUFVX3lxTFB6b0tiekxTemV5VVZpSVNWOUJRN1pveEJac2dGdHhXR3BNUTdIN3ZCLXA0WHc2QlNrX0pYcDhHUngyYWcwVHNIMkE3OTh5dUd0MEZVTlZMZEZ2T1dVMGxlNTlOVUFhd3R2NVU2bVFYanJNSEJOZmtMNEY5ei1sRThpcnBQbE1nYUpma00wbzVpOEpLTUM4UzB3RWcxYlEzZ05KVy1sTmF4RA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE5xaW9nTUlRZGlobWVPajZEWWlnS29MTTQtUEhQS0YxamgxcklrNHUwUGtOc3paQU1HalVpeVQwU285djJwck9ORF9hVHM0MllJbC1YVW5nS0RpakViMFhnXzV1TWlNSS1GaU5VWUs2VFhKcjFzTG1zUGJvcUM?oc=5</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -691,27 +691,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sanctions having ‘significant impact’ on Russian economy, says EU special envoy - The Guardian</t>
+          <t>Bank of England governor speaks after close vote to hold rates - Reuters</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 05:00:00 GMT</t>
+          <t>Thu, 05 Feb 2026 12:57:41 GMT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPSDR2eHdnRHNIdF9vVG9Na1NqSm80X2dkMHZuNi1pbER0anFsYUJtZl96RVNadHRRa2F0LTNIN1BtelYzRGIwMldCYUx2bk05MGhXcF91TUdzUE5RWE9TUFVpdFNkQ0pZQ19PQXoza1ZBUTBQZXBNMDJzTEpJOEczRXJfRzZSSnlBU0xXUVNoS1BqbjNJSFpDdEQyenBxVWVuYVIzeEpuSUZsLW4xTDR4My1CQ0xqcGRzRms2dFVycU9CNzdmUlZnd2xQNzY2Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxObUtRb1ZVMUNaV1J3bzMtb0F5OEREYUtMY3NXbjJQbTNDVWxIcTY3cFdveWg2dndjNk81Y0d1YnZ3WVB4eUtBYVJWcjZMcW9xZHZkbjA1Q0VwT3lLc1QxTzlFaWpBVTczMnpUc0ZfS0NLSC0wMWhQcFJtM21LaVdGMUc3NTdvX1VfYlZpeG1GTUFZUEt5UTBpZzlVTE9SaXFkUWRZ?oc=5</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -721,27 +721,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Canadian pension funds to exit UK’s biggest port operator in £10bn deal - Financial Times</t>
+          <t>Well-managed EfW can complement circular economy, report says - ENDS Waste &amp; Bioenergy</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 05:00:49 GMT</t>
+          <t>Thu, 05 Feb 2026 17:36:24 GMT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE8wOS1JVzF0WVl4Zk1LQmlIcExQVFNTWkFWbWk1TGE1cG0wVFdlY1FhUS1tVF96LUZ2MkdBNWZzZEF4R1c0akJ5ZVlDODg4TFdPU2JDQ1NVSTF0RHBjZi1icFVvLS1YUVg2b2dFcUUzR2I?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPSktPNUcxTkhoSHdzQkU4Vmg0Vi1VdHJCN1FiS1pFNlJSYXVGaEFSdTllUmF2TGE2YUxCV29fUWZSTnpienlBSWFVbUN6endycHBaWm94RWNmclY2T1hVWEVMOGtIM1N2YlBLTF84OGxvTjJWSHJheUhrLVp6dVpYUmZ0SzJhWnE5TGVjWklJWGhqcjlhQ0Mza0haVDBjUmlpeDhoX3k4UGs1U0ctbkVB?oc=5</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -751,27 +751,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Maersk Q4 meets forecasts, falling freight rates to weigh on 2026 profits - Yahoo Finance UK</t>
+          <t>WEF Report Names AM in its New Supply Chain Policy Blueprint - 3D Printing Industry</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 07:16:00 GMT</t>
+          <t>Thu, 05 Feb 2026 10:42:35 GMT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxObnVhWHJkZVV1T3ZlWkVndGFOSnZXbjFpREdEbnEzOTIyYkJ6WGI0VEhXUmh5MHRhOGlCM1N0MXRFcmJZM0lYSGdDeTlwbFNpZUd0TXlsNDhhRzMyeEpHRV8yZUVOTU82RFdEVm1UektFYmt2UGpUcXJrLTdBWm1VRXE1QW5NZS10UlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQd21JSkl2cVRpS2ItTFplYUgtMTJ6aTVHUWRiMlNHZ2Q2b0x3TGo3c3k1T0w1d1ZRYVlGRGhpaDZHZVpIa19vQ1hIV3hFSkNoUlFSQkpWbGFIYWJvYUNCSGR3aVlRekloRWZNWk5DMDdBdmllbndoUWxaVmxCNjcwcldhcnRPcF92aWJIV09YX0k5VWhWRkM2aVRjaWpWaUc2Sm1HRDVLMA?oc=5</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -781,27 +781,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>What are key themes for the European logistics market this year? - Savills</t>
+          <t>US Treasury and IRS Release Proposed 45Z Regulation Update - ResourceWise</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 21:03:29 GMT</t>
+          <t>Thu, 05 Feb 2026 20:32:16 GMT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxORzFEcEdlM2JYRVZwQjRZdjhUelFuVjB1TGgwSHdWemdKbGU1WHo5a0hCcUVzVFB1ZHNZS0pabFhOXzF4MWw3X1BmUm8wRGZlMmY5c2dnTjdRVFZ0OUVGc2cxekFpb0g4TnIxTDF2aUVzWThiblV2d1BNWXNnb3Nqc2NDTDhwc3FMVS16RUwtRmdPR2gyZUlhQlFjcUptMlZPeG9iMS1GT0JSZTNsM0JUYlRXSGF0dzc0YlJERzFWR0YxdnNPbGZ1QzBncWNuX18x?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQak85MDh6N041c2pDSmdNbjhJaFRRMkRXNEVXZFRETUdWQXdLVU1pN3QweWVOdlpCQW50V2NpSVNxcC1KMDNXemNFM3Y0STBvTWpQZUJPYmx1X2ZLbHhkZ2hlMU9nQXJIekR0RENiWjR0VGpxTVBQZ0E2dGR3enEyZmoxOE5SOEJOWUhRbjh1eWFHaTdsX096ZS1yZEdkN3RyeWR0ZNIBpwFBVV95cUxOS0R2N19lanluODRsWlM3aThJSHVtWmoxQ0tUOEJSalpCbWJHR0FaV2VtWDhMbVBPY3JoamszZzZXQ0VXeUhTaTIybkVIa2hiZWVRS3RUOXlrUDExRU1TbUx4bnhVSnBaLTJ3MGs2dFNkbFl3LUl1SVdWZGFtM0VOV3lnNFpRNXUxY3VBdjh6YUc0akl3QkxQN1ZiUGxEY1hKX2E1Q0tqbw?oc=5</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -821,17 +821,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Pre-CNY sea freight reliability is breaking down at origin - Metro Global</t>
+          <t>Maersk fears first loss in a decade after rise in container shipping capacity - Financial Times</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 07:15:15 GMT</t>
+          <t>Thu, 05 Feb 2026 10:53:54 GMT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPTUg0U2IySHNSX3R5cHdybEZHUVNiVldrNmdOV2V6SVdZT0xFclhVWlFWakxKYjN1OTlnRTNadjZUR2syLXJCTi1uOXJOQm9pSUt4VUJETGRkSkdCb3dMV1cyVkpySXMxWl84Ukd2SkZnb09Gb3o0MzR5ZVFiWTh5dHdvR0pJNWdGSUtSX0dMUFR4QjJNeVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1fM3hrUW9DWE9DT0d4RVZCaDNXa29tUHVUVTUwLW51WDhnYnZJNXU4OWlXc1JkSHhIRTIwS29oRVpvSEI4Z214QXB3Yl80bW03LWxwWlZpczdjM1F0cFF1YXlHLXBTa1pSSER1eHZ1ZEg?oc=5</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -851,17 +851,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Charge Forward! Innovating across the Battery Supply Chain - Natixis CIB | Natixis Corporate &amp; Investment Banking</t>
+          <t>Port Vale clash postponed - Doncaster Rovers FC</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 06:56:15 GMT</t>
+          <t>Thu, 05 Feb 2026 16:35:09 GMT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQVEpZOXlRR3NrSVhla1hUZ2xmRXg3Y1RLdmxLT2FseUROMEdyZUd2Vy0yT3QzdG5yMHdENEptdjBkUmJxODA5bTItWEpvME1wSndua1V0dlFYMEpvUU5Jd2ZGLWdwVU1mbHlNbXp3LWZwUzg4OEJNWmdOY1JKT2ZVMnNZQnNERFFpQUZNR0praWl0aGhNdk5DYTNzYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOYTNEVlJVNkV2VGhkUmlFaUlySnE4dHltVno2Qm9LRHgzejhweHBPWi1uZ1Jlbkl3Tm0wUzZscDNsZlhQVjlLQjVDOHQwZ2h0QnJrb2o1c2JUc3NCbmxvY1M0QTA1R2xkLXFkZUVQbVZWTllyVlBqM1NDbnlEZ1ZUY2VOS3VoT1NXSkpMUQ?oc=5</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -881,17 +881,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UK agencies launch joint operation on crypto-based sanctions threats - Pinsent Masons</t>
+          <t>Kuehne+Nagel opens new Container Freight Station to meet India’s growing trade needs - Kuehne+Nagel</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 16:04:39 GMT</t>
+          <t>Fri, 06 Feb 2026 05:45:00 GMT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQT2V0ZHY1dFpvQ2JGTGdCdGJRY3JfaUVBSUE1T3JCaVJKaTY1dzI5eXVvZGJEMjhxaDRMNzBJT3ZqbjdSOFdCYzQ0WXJXR1hoVmtVdVJMRkNMZHdfWldNUVo2dUJMTlhJa1FmT2M0UWNCMEZQb3BQX3lEV0U1YnJISllvUGZ5NFNFdWhIdXBsNDdVUUlYdHo5VXQ4aHFRLV9sMjMzN1ZabTMwdmFBUlJDaQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQQ2JsRHBIUDlqdENrTnBOQnV0ZXpXWXdkQ2cxZTZzTDN5MFcwd1ZXX0xOaGVUY0pULXBZcUF5cW95YUdVbm1BdEVPdHM3UUhaVEdmRDM5a2I1ZlRDck9peWdITC1YS2FkRm5hNXBjOWh2eDk3Nm1TS3gtbDAxdzdobmIzSHdSLWt5NGw4S3FvOTc5MG9vb3BDcVV1VXFEVW9jUUFvZkd0RHhTbExnLUxvY3N2SlNHWXFX?oc=5</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -911,17 +911,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Miller’s CLC Risk &amp; Compliance Conference sees industry leaders gather in City of London - Today's Conveyancer</t>
+          <t>Establishment of the World’s First[1] Global Supply Chain to Introduce the Use of Renewable Plastics in Sony’s High-Performance Products - neste.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 04:51:32 GMT</t>
+          <t>Fri, 06 Feb 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNT2xWeE85VFFtajN6X3J0b2VWR1lsVmZ0RFRjdFkxcW91RFd4TmFONTQxSEpoWkNUc2g3MmR6eTQwUWV0bUpWd2U5b2JwdHh6UldZM1RtTEJISGwtaF9VVEtWOFpxWVFOZjgzTzN2V2xWT0w0QWFxVmNMdENHRFoyQnRBQUFJUUdOUjE5WGNyMElHdTNCMkRkOW9zUVR6N0RSV0lCQml3ZVZIUG1GbGJCU3o1NzlxQXdLcFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxNajNwREpaWmxVZFFjOXpBSUJXbVkyQVBoNVVmY3czX25ERmlmc1Q4N0g0d3UtOGxFeGtIc3ZLZXgzQVgxbUVPdTJOaHZYM2tvUV9fai1zTmwzNjhMY3FoVFo0UHpJX2dNYkhaanRxQkRzczVhczlQS2pZUEFzbEhJSFoweTRwaE9GVzZmdHZjQllOQ09MZ2FhNUFCSm05NDhuX2l4NmNYTXQycXZGWXZqbWJTLVJvdFRNRTlZeU8xN21GZXdXb3JYc1BSODZOa3ZMU3kwd3NVU25kMWtOcXJKc1g5TmhGaFdrZmF2TEVCUC0ydw?oc=5</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dave Clark's supply chain technology startup Auger bags Meta Reality Labs as a customer - Retail Technology Innovation Hub</t>
+          <t>Ferry firm's Jersey-Portsmouth freight sailing U-turn welcomed - BBC</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 05:32:24 GMT</t>
+          <t>Thu, 05 Feb 2026 15:26:51 GMT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNRUNnUHNTSWtTTGtuSHRjZUZBUk01N056Wkk0UlJ3dlBORHItbUpOMlk5TFB3bTM2eWYxSTZwRzlVQWpTTnFZc3RWaE5ldHRiNURGeVIwVVctSHhwUkxGZjJudkYtVjNocHFQM3ZxWDlGTHljT1BPeW9QQjBsLUdybVRBOE5BWldqXzRnWjhiS1VxX2VXY3B2endaQzF5dEhkbTlBbVg5RXVnOXNjRDI4b2Z1QjBxOC1iSjJBM2dGVkoxeU5XcUtpU2JkM2kzazR3bmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE4wTWJtdGFWeWZxNmdhbC1fcS1IZERUdEFzZXhNTndjMlNGWVJlblc4OVFWbC1UU1F3QXc0N1dxNTMzNlJoQ01lbmtBUDExSDRBd2xFMWk2OUIyUdIBX0FVX3lxTE56T2tIN0x3RU1CaHBqMlNhbk1EcVJPNmxyN2VqOElSbkhMTmtmbjdxZzNEb0pGYmVxbTcyMHR1Q3JwMk5zM1h3N2s4SkRjUGJZNDJNa0NJSHJDOGtpalAw?oc=5</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -971,17 +971,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Divided EU urged to sink its green shipping plan amid US pressure - Euractiv</t>
+          <t>Rob Montgomery: Driving Agility as Supply Chain EVP, Walmart - Supply Chain Digital</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 05:01:56 GMT</t>
+          <t>Thu, 05 Feb 2026 18:16:08 GMT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQRUtlNjJIMnlFVG5HYWhwV3N2OHFnajNEWS01cmdSN0YzU1lzaFNRdEZ6VHhhT1cxdnBPdFFXYTBYdHZPc2d5WUEwRWZJNi03dXNJVkFnMUpFODhxdlFTak4zSGxOdXJFSTVDcmhKdWVhR3hYdWYwTTU0eWY4Rl83V2JLMUczaVp0M1oyUy1abnA1Y2owNnFVZmwyejE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxPMHQyRUgtdmRfUFo1MmFCWlBXMlJTU2V2X1k5VS02WGJiSDJENkpjOWROaGxpRGN2cGhRQVYwY0RFa1p5a1JVMVdLVGZxZlNmcUQ0akJIcjc5ODJDLW9XT1R2VlNiRGdMS081UXZINDZIaGhxcFQ2a3JtRzB4OVZ3enV4RGNPYWg5eVRN?oc=5</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kreios partners with BVI for improved operational fund compliance in Germany - Funds Europe</t>
+          <t>Can blockchain help track and reduce global supply chain emissions? - Impakter</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 16:06:04 GMT</t>
+          <t>Thu, 05 Feb 2026 22:52:39 GMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNQ0tzZGVaLUxLVzI4M0M1b0l6V0lOaXNFWW01UmhTUHpCc2xxTks1OUVDZHdSV25UQ0dYX0VwYnBYMnJZVl84cTczN0YtczAwZGVYQ2V4SkllbjFTc3JYX05QalRvM1dmTE01VXdkTzZXRDhrVVh4bGNvQmtSQllsQjRZcjhySzdsMjgtbldueFUwdllUYjBqOFJQNFAzMVVLTE1uVA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPSjhvZFlMVXlPUnhoUDlHVVNOOWk4djdXd2RlVGJ6dnhKNDJkb2dfalY5b21LT21ZWTBQNW1Bald6RzRzMkRJSWZHSXl4bHBkVFNnWElEVXpxNWc0TXBhZmxUaThCUjJwR2dJal9OMzE1bDBoMzJld1R0YUpYTm4wYURRaDBzalJsc1RMa0xMTmkzQQ?oc=5</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1031,17 +1031,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Learn how NHS Supply Chain is accelerating Scope 3 decarbonisation - Logistics Manager</t>
+          <t>INSIGHT: AMLA’s SPD reveals how it will transform EU compliance – here are the important dates - AML Intelligence</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 10:00:57 GMT</t>
+          <t>Fri, 06 Feb 2026 00:12:29 GMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQOVZMY2ZpblBTNmNndGFMYk9SbGV1d0RsZC11MTdscTZXWmd4WlZ5U2dHbXo5eU52dmdVSjQtSkZlZWxyX3k1d0xIUmpJanNNOF9fNDFLd1JiQjAzNVAycXp0akdUeWtBc1ZzUkkzdE9QQ08zMEtYZi11SDR0czZ0X2ItRnhZMGZicVFmRDRfSVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOTkJKNUtYTFVfX19tUUZEbzdpQzJQTkhVZ3hkUUlWX1NGS2RvbjlBbmJ5cUJhTzRFb2t4Yndhc3FNM2VVbU9ZaFBCblFpMzVhNGV0WGFwVzJreWZtVXFmczVvN0NKRFVQUlNBODA2SGp2OGZldFFjcy1OdExWdElBajBCQ2JzeENVU0IyUEt5clk4ekVPdkl0ZHFFRnBQTEl0alJHQXNveWQtNVNMenR6MDJrTVlKQ2trS2RmRXg1aU5lWG45Vk9qQjVfSQ?oc=5</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1061,17 +1061,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Can a sweeping statement about tech compliance help deter the dark fleet in North Europe? - Tradewinds News</t>
+          <t>Fragmented single market is ‘number one problem’ for EU research - Science|Business</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 07:22:56 GMT</t>
+          <t>Thu, 05 Feb 2026 17:59:27 GMT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQczQ3UTlNY0hIYTZwVWNFRUNrc2tOZ21fVHJFNFhwVHE4UE1wZURRcHlvbC1tZzNkNFVkR2drUkhsd3lVOUVEWEhfVXRfdWppOXFJcFBsMjhlNDFPdlZ4b3R1a0xrVjNKbkdGT1BUVzkzWEpwVUpGTEcyX2JkZXZSdjZCR3o5cnJTRFVTdDAwbDRYMi0tSVNNRTNaNW9QbjFFSndmZjZnYXhpSDdxUTZMN1FZb0Roak1YLWc5S2huTEVUc3RDRTUtQlczeFBYcDN6Y2d3cDBJVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOMXZjcGY2RjlLTHVMNEh0ZGJ5dlJZZ3h2MWFRRzJyNm5CbXN0cjFzNkFOMDdWdl9LUGVXeDlrZU9HNlBZVXRrdzVrOEZ2WWJPb3RuSW5MeFRXcV8zOUJtMkpuV0xsa1VZZ3JIWmJSSk5kbWw2WEFDZUlHVENabmJmeDhwaktLTGhqTHFKSGlVTmZuLTR1cV9zY1RBRHRlUVUtT0Jneg?oc=5</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Port Talbot is a crucible: Jon Doyle on writing faith, masculinity and the weight of a place - Nation.Cymru</t>
+          <t>Are index-based shipping contracts a trap for BCOs? - Splash247</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 21:00:14 GMT</t>
+          <t>Fri, 06 Feb 2026 06:00:09 GMT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQRWc4Z0dXSkVETjE1OFgxajZpSGNZbFFIUVZONnlMVzdEemhNMzlQR0NBTGF0clp6Y1BCbWJpeVBvWXM5bDN1Smx4OWFXNXR0UEE0cXhLcnA0Um1waElMZ0VUQWJNT25uaHV3Q0N3Ty13OUxRS01KUW5pZ3RrQW5ucUlOMjdNUWhsYk5kVDh6eGJmQ3RSamFJODBnSnpEZ05LYTZIaS1pb3EtZHFnQXY1d01TZGtZWDBDd29QRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE5tVG9zN0dpcnJPa3FtYjI3eVRhUnZ2a01SYWxYSU5TbmROWEtnWkZ6dXhEaVR0QkxjOE51THQ1Ti1ERzZSbnE3dk5fRHFSY1k2VDhWcExYSFUxa3A5Z1J2eFlSQjZESzdxU0lfVTlEelBGeE9IWFBGaHBabS1Qdw?oc=5</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1121,17 +1121,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Opinion: What the government’s new approach to sanctions and export controls enforcement means for you - Chartered Institute of Export &amp; International Trade</t>
+          <t>Three African countries agree to UK migrant returns after visa penalty threat - BBC</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 10:20:24 GMT</t>
+          <t>Fri, 06 Feb 2026 03:14:38 GMT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNU1JoRlR0Ql8tbi1JSllTaV9qaGc5MXl1S2lYYXFnalZxemlCVllQSVlDdldkVEZvRGJjYUgxY2RHTm02ckQ3U1hVczRZMWhUWGh3bHE3Wkc5OTVrZmJVYkFqSl9XY2RTN0hZdUM2cFRrbWFwRklzc29yWWdHZ3o1c0hFN2ozTFR5ZkJ2UUZWQ18tVTEwcGwxRlhjVVhzNTVIUE9WQTY0cmRrcVlyMlJvUkxUSmkwRVpUQWpHc0VDRmJTUHN5N3lfNkpIVW50c1Q5NkFicC10dWwtS1haRnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE4xRUlsYkQzMnRZdV9ubFZRV01IQUR4NUJLTk9qQ0tHRGpCWE9PcXpEZXhQRWs2U3BGQkxqSTBRUTBEMzl6VnUzZjlxb283dm52b2YybFVpZUtqQQ?oc=5</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sterling strength becomes a supply-chain variable - Metro Global</t>
+          <t>Flying through Freight: Scania’s Autonomous Push - Supply Chain Digital</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 20:15:00 GMT</t>
+          <t>Thu, 05 Feb 2026 16:21:40 GMT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNdkpDUXdPdDR3d2hFQkVBREVMVUkxSUZJYmoxeldUNWxzQ1g5Q3R0eU5wbkRYZkJsNDMzNXNPRXVkS1g1X1k5Q0x2NG5HNXZ6SUt4S043c3llUG83ZVBRdFdEZ1Zka3pyeVpXSUQ0MGdwN2MzZlE0VmktbTJpdGVPWk9TYS1iU2w3LVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxQdzdFV1h2czgzZnhZS2Q1ZUF0QzVBUHRSQVY5LXNQd3Q5MkgxSmwwOWNpX1Vrcl90czhTNk1JLUYwNnA3M29tcDFfN0lKZUhmTm5SdE1hU19JNldMZ05MM2Q0MnU4bnQxYVN6TTZQQk9zdjAwSy1IVkVRYlAzcG9YbmpndXlPbVdSeWc?oc=5</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CEVA Logistics and HAECO Group sign global air freight deal - Logistics Manager</t>
+          <t>Canada unveils auto industry plan in latest pivot away from US - BBC</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 14:00:46 GMT</t>
+          <t>Thu, 05 Feb 2026 23:07:21 GMT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPZmQ3MzJxVTdKdndReENmRFBxTWEwWGtzOGxZS2thb1hfZjRUUE8yN3JMZy1DcnQyMU5jcVRpekhYMVVCZG1yZ0hIUk9SX2Q0dUxmTDgwTXlnWlZRWEdEdjFNZjV4eDVZV1JYZExtZnB2S0U1dW1EWlgyeXczeUEtWTVTOTBpVS13cXpRQ2hQdGEzVjdjU0tOYg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFB3WVM4a2w2MlZoZDhmYTVwdkMydVZRM05zdEV6UGMzWVZSa1JUNWRiVTl1UkxRS0JmcnVlOExsWjlzaW92dExrQVU0Z1U2eVI4YURiZkxsekxyUQ?oc=5</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1211,17 +1211,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Air freight markets firm as Chinese New Year front-loading reshapes early-year demand - Metro Global</t>
+          <t>Gartner: Increasing Employee Retention With Gamification - Supply Chain Digital</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 07:15:15 GMT</t>
+          <t>Thu, 05 Feb 2026 15:23:54 GMT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQekYzUlJhdXYzVTZSamdjM0RwZFJsOF9FcVpNRmJkblhLQ0d4ckNrRFZlWThMSWlmQ01QUUZKMjBCejg0ODlaQUJGRXU0NFAxbVdrRGtWRGZTSmRMNURwajFWclBCcV8tSnZvc21xbVZSanRkWHBRV0RMd284NWJrMVlxQjV0X0h0X1lFWklEX0NvcTV2VjBoR2cxaFhXVTFPT19QMWlEeldQUkNKaFUyaTQ0S0ZkOTJkTlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPNUlpWmdqVTJWWHhaZmgyNEx6T2U0THlpd0FtYUlSQzRkZVA0OHFlQ2lRQVVwODRhZFU3bTlhYUl4ZnVEUGh3SHhCdzBHTTlMeS13dkNNMDdyd0Q1TVVWcWlFdkhYN3YyUGRDenN6U1NrUTZhbERHWDhWWnZqc2JRNmlaVkdqcmUydnJYOHV2Rlowd19scjJmZHln?oc=5</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1241,17 +1241,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Port operator brings ICC claim against Panama - Global Arbitration Review</t>
+          <t>Logistics growth driven by smart systems - China Daily</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 22:18:17 GMT</t>
+          <t>Fri, 06 Feb 2026 01:05:00 GMT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNbWpTM3JlRHZ1Z3Y1RGh4b1BSc2VPWVZOLVNCeEFEaWlWUmN3ZGFqSzBUOGNRWXEybEZFQ0JFcXZBd0gxdGpBVFRXNFdpV3o0d2tGXy1zZ05OS2hGNzFGVVVHM2JQR3VNU2VFMEFkbUt0VHNPMHNvbmdrWlVjelNlRG4yckNwNEZ3TXZyeXhCeWRnYkU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE5JLVFfSE5sQjQzTVRudm1sYUJBcnRGRm90WDZ6bmVHTzRta1BVQ2dJY3J6S1lnbUdDQ1RhWk1CT0QzdU15Mm52ZGNRMGFxRHZQOWNpRXc5eHpwMW1kaFVxLXRuUmR6Q3lqNmF3Sm9iUGxmbVNDb3YxUnh0M1FsQQ?oc=5</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Port of Barcelona posts slight profit drop in 2025 amid higher revenues - Baird Maritime</t>
+          <t>E.ON Next cuts EV tariff day rates to boost off-peak savings - Fleet News</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 05:18:16 GMT</t>
+          <t>Fri, 06 Feb 2026 03:00:54 GMT</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQZmlkQkNYTkJzUGpBU1ItN19rdlhKNXhJR3BoYUhKeGt5dmdPOER0dWFfSFNlMFJZdDdYM3RFUEVjSUdBT25LUWpzeV9SeXM2LUlBamJCUDVYU0x2Y3dIN09TSnRYckdlSFdZcG5rVG04emxSYkV1cUdPaDZ5OUdvV28tcVlXMTV0eXVQWWZNWDFHSUVGcmFuYU90cHpHTklFYThIa21nNGx5bkgxeFJUVTc0dHI4eGPSAcQBQVVfeXFMTlI0SkxnckdmUjlnLVNldzdyUkZQY3lHd1k4NFdmQnVYLV8yb1pDdWJXbFFENm9CSjkteHRobUFGWHVxejI4LWN6SVM3dm5vODVValIzZ01vNUg2alc4cGNFdTFocGlyWWd0X2hKN0R0a3d1TU5JTXVEdnhsbF85eHNNWWY0LWxGNURLUF9CS0lVcG1iQ3hvQ3dDNENkQURJZDhveEZ1QWtWYXloVEtlSGk5dU1Sc0VsWXNHWktWV19uNzVTRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQZ1dxaDRyeVQ5Qm9NS1daZTd2SE52MnpxdWFwWTREd1JSYi0yYmR4eGh0UnlDS3VERnNWTmdsWEZwaXA3WWZvV0JrQmNIOEdoUzFJdnFQdmFDSU43VHJfdjFHd0ZDdVFEY252di1Yc1BQRC12SENXMDQwSkY5NUprTGU3WUtMb3RjaHlyQlRicGQwcGFDMENF?oc=5</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ArcelorMittal Sees European Steel Tariffs Restoring Profits - Bloomberg.com</t>
+          <t>AD Ports Group to operate Aqaba Multipurpose Port in Jordan - Baird Maritime</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 06:35:00 GMT</t>
+          <t>Fri, 06 Feb 2026 01:55:27 GMT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQNTRHdW5FUlRvaFd0NXpzZWtBbmdtaU1IM0V3UGVyUVZBcGJ2X0ZLZnhXNW5DY2h6MlRUUkNqcDh1WkZibTJEWG9wYllYelVkV1hUMUpLVjY5d2U0cFRLY3JKMW52REV4d0FreEk3ek96VmdwX1pnUEdJZ19VWnNrQTNiT0ZtUlVjcnhiME5WT0Q2dlVybGxXRGdBYXNpbHVVbnc4RmFGQVZZRGhjLUszQ3RVbTc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPWnViTXJsVXZsUGZRalE4QVRPYjFpS1lTdHBfZkR0M2RGeGdOR0tENUU3a2YyWDJ6TGYyUEpwRVM5TGhvUUFqbGVFbWdtcEVEd2xPQzJuN0ZlVnVRQzlCZnN2U2lDcm5pS1pORVJBQVVDYklZV2NQTlY1UWN5dFJubmZkY0lwUWNUaDlWODdoSGVPaWVsSGItM1NlNWtDZFctdS1sODRTMNIBtAFBVV95cUxNZVg2eEE5WndVSDBBLU5BOFRVaEFKNTc3aWU5ZlQtMHhQRDBULThoNzdCZHhITHQ5ZGRiNjNuRWxFZThldXBldXZNakYtS2FNaElmNWRvTzhoT1Z0a0RIcGU4OFU1U0xxTmMyWEVxZ1JLQ1poalRSb2NFbmlhR3AxdmpOal9zMjdraXF5X2FKX0hrTG91SmVqd1RiMnVQQ015NmpVMkdQWTVta0Q5cXVsWENDaWM?oc=5</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1331,17 +1331,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>What are the Logistics Behind Super Bowl LX? - Supply Chain Digital Magazine</t>
+          <t>Supply chain chaos becomes aviation's 'new norm' as demand hits records - Reuters</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 17:57:03 GMT</t>
+          <t>Fri, 06 Feb 2026 05:09:00 GMT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE1qaG9LN3VCVGxGNXgxZHljZUtKcXlKUkx6bWJ4R01Sc05lZGZaa0ZBQ1AtZE55NWNIU0hjTEJEdEFYRVZ3WE1OWjZNQXc0cDhrYkVna1F6bUsyWk1hdm45bFc5ZGRMQjAzc08w?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOdXdCZ3ljN09qWFJxMVBMLTNXWVExeFlqZG5ubXg1MEwzalZ6Qmp1dkxxUExjeFlRWHNEVTlkVm0wb1lZdmJJQ0ZHWUhnLTFvTExrZWlZT1I2blZ1OWRRRVFZc0FBcHc5UlpkMmV6TkZLVWhKTlRaQW4yS0NHVWs3RTFwR2RSdmk0MUVNZ3o1cEZjNnZ0UE1DN0V0d3VlRDlLcEtoZnRpUXpzMl9lQ3BjWmZxTnVnel8ydm5LNy1PUjNmQmhiOUJv?oc=5</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US to reduce tariffs on India once it stops buying Russian oil - Sky News</t>
+          <t>Cuba open to dialogue with US after Washington tightens sanctions - Anadolu Ajansı</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 12:59:29 GMT</t>
+          <t>Fri, 06 Feb 2026 05:32:58 GMT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNMkhaaDZaMnY5enZjZUhhNm4xQ25JNHIwTzVqbTU5T29HbVEwOUFwTTFaajRMZW5NSFFzOTFHNklGZWZ2cW9KMGlvYUNwSmlSVjdUTUVTUklnV3ZPOWxpRzJKS3VhaTB0WUdVck9mOFlBdWlJSkNuMk5ITi01VUhpMlRQREs2RnN2NXV5c2ZIUXQ1Y2duelFGMjRqTmlqWHM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQdk5Ec1FTeUpmZ3Bra2dGVE52aUsxeHltQjJGakFmNGt1dDBWb3hXUmNsYnJPMjAzSTJrVmViNndTS1c2RldoR2FaMDQ2bWZxSVRwUkJEd0lvM2xPaEpnU2tjcS0wRVA3bVNLOFE1R2hTZHBCWmFEbmVhRDlqOUZDNk1icnVvTklqUEd6OFd3X004WXp4OXBDUnkxNlN0dHFfZFAzbEhDajU2Q2c?oc=5</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1391,17 +1391,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Curio Water puts out call to all ozone producers as new UK REACH compliance enters crucial registration phase - Water Magazine</t>
+          <t>Andreas Nyman Secures Aerospace Logistics at Kuehne+Nagel - Supply Chain Digital</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 04:00:14 GMT</t>
+          <t>Thu, 05 Feb 2026 14:08:53 GMT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxNTnM1Q0huRzZRTnFfQUJYWnplTjl6REtFdVN5elVheGN5LVpCZ0Q5b1lPWXZZaVVUZ2dQNWN2RnhLWlhqcG9RdGFrMDVPVXpHTGlkZHRHaWozUzlYNW5wZldnUGkwMjZWdld5WkExSWxhd3NIRHRvOWExVnBhdEplVW5SOEhFNXFQZWV3SlNycm1MWlE0VldCQlBHS3FCdUtaQVdVLWdNQVNvNG1HZ1JEWFMteS1ZajRCcVh3MzkycGkwTFBHcURGV0ZTbUxOazRMWEFYcy1WZ0lmNHZnQnRRekM4QmpHUTJ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNWm5ZVmxYb0hWeXpHYlcwZDFCcHhwc1B4SEg0TXJ6OWF6WC1qTU5SSEdQbll4cjBJM0s2bXhZc01CUjI3Wm9PZ2RLdHpuZ0FsYkRRNHY1TldpelloeEZaTkMwMXE1Y29GYWpWeDhJMU5tVWxyRlVFTEREaEM3VW13NTNFZ0tndEtYQ0xta0pETXFDNUk0OE9z?oc=5</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1421,17 +1421,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Port Talbot RNLI volunteer reaches training milestone - RNLI</t>
+          <t>Cargo ship runs aground near Sweden's Varberg Port - Baird Maritime</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 10:35:02 GMT</t>
+          <t>Fri, 06 Feb 2026 04:35:23 GMT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQZXdxUXpvMDgwZHZkdWZKZWRUU2xOTllzeWtteWtITzJhSENKbFJSNUhXSTJldGpuUXhWQjJtY1VlRmlvMUVvVGY5M0o3QThPd1ZKd2FXV3ZsWVp1YVM5WnZCOGJzX0RtSnBvSDFuTW5EajU4eTNRX3A2b1EtdFVDa2J1WE85Tl9IeXd6cnB1VVo5cEYxeEU0SW5iWDVUWTB0UndxdQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNOGtIT3Z6MTFDR2V3VzBGSXc0UDJuVlNGaHk4WkdGeVIwblpqdEVVY215U1dILXRBRThLaGhRSDl1M3RTalZ1WkktMFJXWVlKMEJTcno2N3JTR0FIRHNWVm90M2xqa2EyZUJ0ZXVkZ2lISDg0TGdJempNSjNMZHhFcGRmVzk5NFE4aGZYU29pa2lxeklOeXJPTjNPLWdZblkyNV91bE1TdGJOV0ND0gG6AUFVX3lxTFBFeHBSQktId3lZVkZUOTNZVGVORXotVUhFR2lNcHplN0szWVlhZjEwOEtOVzY2Sk9tQXI1ekRfeThycGprQUVCRVhuaVVQYzN1cWVucGxod2p6S0Frb2sxQlFYUTVjeFhUS2M4b002LUhZSW1wLVdaaUxZTkNYeFNZVDluamYwVDBhOEpPU21hSTNxOHRRczFDNVI3NnhvT3pJai1JVnBjR1lUbTZuM05vSFhCMnlaUUM1QQ?oc=5</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1451,17 +1451,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Danish Pelagic Fleet Goes Green at Nation’s Largest Fishing Port - The Fishing Daily</t>
+          <t>Trump's trade war creating economic 'mirage' with GDP forecasts, freight market disconnected: Shipping expert - CNBC</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 15:29:50 GMT</t>
+          <t>Thu, 05 Feb 2026 19:35:35 GMT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNTlVicHFwTHhjM081YXdUeHcwcWcybHRyNVd1QmpKN29KTGJ5c3pXaWU0a29Ha1dERWZFXzZOUWJpcVBMMTBaOElPYnRUUlFuU003aVBjOXNsNDhaeGV0NUk2MVdtUlRnV2RqazNUQUZXSTVHNk1mUjNWLW5ITWVHX0NFZ1d1eVl1SzdaU1ktZjdkQ0lETjRFUGtZV0dZQVRXdDRWRzlNSWZ4WWZudnB5WGZVVWg3MTNMRUU1d3hR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNX3R0RXFmcDZBUlBFVVN3aFpuLTZMc3BCTUpZWW8yVFpyLTlTVjZZUUhvS2hfS0l6aWRLTDFtWGRiZnB2cS11QlJzLXU1akdDZEgtSTB4bG5WUUNRUllWWmhRMmNhZFpRSUlWUVpuUi1PM21YZkNUYlVYY0piUFBISVYwdXZZSTFLMGhoY3kwUXBqWVZfZ0xURnJGZExwb2hLTkxJLVlTUVM5Wlc30gGyAUFVX3lxTE83R1psdTE1QnVCYm9qT1lMaE81aFlLUFlvN1JENkg0VG5zSEYwRlEtcWh6aVJJeldnSVN0eWVQZWdWWmhNMHhFRVN3eDBKZVZxblppd0NhaFhoajZ4Y2VxTHlUZ0k1YlpQbnNzRVZodWQ4T3ZFcW80QlBaejlpdFlsbUpGTjZvNTgycElXdmZKVHl1N3ktR3cxQ3pXaGJrNERDVzFiY0owUFBUb0cwekF1N1E?oc=5</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>China Has A Plan To Avoid European Tariffs: Team Up With Ford - Motor1.com</t>
+          <t>Supply Chain Disruptions - Robin J Brooks | Substack</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 04:15:25 GMT</t>
+          <t>Fri, 06 Feb 2026 06:00:54 GMT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE1jZG0xaU1xSG84TmU0WXhuaUoxNFM0TDY4MVZ5aURjdjZjQXU0MHZleExZUTZpOU9Xbm9kVmhUTEZrUW9tVTlKckZRNlhMVzg2elYydnVBU1Bra0k3T2MxMlRWNk1qemkyc2NDS0t3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE1uMHpMbTExNUdTaHZHMGptQUYySFRqTGJmZkxtRDVIdlJRLU5aUU55djBYblMyY1l3X1VhclhGX0xuNmZ6UnZUVjdaTG5YNHhQRHRPVC1XTHd5QlFkSlZuN1BMWVp5ekVQVXMxMQ?oc=5</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1511,17 +1511,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Inside the World’s First AI-Powered Shoppable Runway - Supply Chain Digital Magazine</t>
+          <t>Hostage families call for urgent clarity over PM’s Hamas sanctions pledge - Jewish News</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 14:32:56 GMT</t>
+          <t>Thu, 05 Feb 2026 16:31:00 GMT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOa2k2QTE1dDVZZ0JUdmpWaUM2Y0h1eGpWbFFTQUdveXUwdWVmSmFQeVVsejdJTjBPRGZjeFRCOHp3TDZDOEZwWHplRnl0WUI0aDZMZFRRY3YxNnlRQ2c4bjJOOUR5bWx5dTZFaXdaTE9QN2U4a1ROSVN6d1NhZ19MX2pFT0VLOVVxNkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNc01yUUFiLWRDYjdqek5XOVB1NmNCUHZQck9sNzEtTTM0ZWRzcUV3ZTRoU3RHdi1CMFVjbWtoOExQODk0dlFkcEcxYTBYWTNxbkppaVJJTWtSNHNyU0tfTDIyMTc0eVVpci1wREY3dThiYUNHOGp2MEtnOEplTmRxNmNramNQY0xFakZLbTc5V2w0QWZMVEQ1WktDSXBvZHhrMTRpV9IBqgFBVV95cUxPNlRnQkdZNTVTcDZnLVVBN1piZC1jZ1MzSWlaV0ZqelE0aS0weXQ2LVd0eWxQSjJmVHNoeFlQSUd4ekNBcWlMRlRRZmxuMk5zekxoRVFUT0czYU5JMk83QWpYTmJkRlAyQzVkSDlmRUpSWWVkYzRjMWNHZkVyMlU2MzU5bWxhelNNR3ZYeVBuWDFCcXRLMXpPQ0QwSkhxSVEwVmwwdHVhTGtodw?oc=5</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1541,17 +1541,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>‘Timing is critical’: UK has five years to secure the energy supply chain, regulator warns - Energy Voice</t>
+          <t>Freight train carrying liquid propane derails in Connecticut - Yahoo News UK</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 14:26:29 GMT</t>
+          <t>Thu, 05 Feb 2026 23:57:43 GMT</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNVkp5ZEFyUkNZcU9nNWFEVHpSS2hDa1FlMnFYdlNlbGl1OGFZQnU0c0h4ZkI1WEE0ZWdvREdxclQ1QUkybDNiWDNrS1FNclVSa3JEdDVpVXhPd2JpZGlMX0RzNVR6YlphTGJ1OHVCNU9RekdTaTNRNGVYZ3J1VndIY0lOMHJadGFQZ1pfcWpkVzFIYWpP?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxPYUU4QWRad2lrOUl1SnpXek9Fc2lhdnRUWHJGYzF4SkROd0FxRm1McXVMUnB2dVdlRjFjdnNCcXZOdW1feV90MHloZ2xLY1p3RHMtLUFfWWhLa0RZR0NNZmNqMTNmZllGbEtnLTdYcS1DS0U1ZWt0cUlqbjBsTG85eW5MWmI?oc=5</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tony's Chocolonely: Sales Surge Despite Cocoa Supply Concern - Supply Chain Digital Magazine</t>
+          <t>Panama port ruling threatens judicial integrity - China Daily - Global Edition</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 17:13:35 GMT</t>
+          <t>Fri, 06 Feb 2026 01:58:55 GMT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxQeW5IUFFqd2tZb3JFUWNaenhjSVA3SjZ5RW93LVBIYnFnM3A4ZmFJb016RGJlaTA0ckpGdUdnVHVmQ3hFTjNUc1MzbFhQbUpLVlVkSzVEUUtmQ3JIRnR0NVJNazVDVTFmVWNwS056QUxXOEVZQ3NmTHNnV0NtbGdLM1BBVm4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxNWmp1LUhzelUyYnFvaVdjNUc3WncyTWtWREFDWThFc05LNTlRSFJraU1NVTFQYUNSWGYwZmc2cXZRcnBkVlgycDRJekExRTh4bWp4d0dIUER6OGpuVjZDeVFpbXBrby1YRmdCN3VWY25pUmQ3RG02M1dSZzVFMDNUWEFn?oc=5</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -1601,17 +1601,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>How Does Orion's Acquisition Impact Mineral Supply Chains? - Supply Chain Digital Magazine</t>
+          <t>UK imposes sanctions on senior Sudanese army commander and five others over war atrocities - thenationalnews.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 17:05:00 GMT</t>
+          <t>Fri, 06 Feb 2026 06:11:15 GMT</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNSklKTzd4Vmd0enhKNXRTcVVMV3pIRnhnbzlya2gxOU0wWUV5UXlZSzhJOGkzUWMwRks0dzFvVFU5ZDdVMUZJU0owRmhBVVQ4R1Rrbk15X09XOUxGYkx2OFBvVVZlcnlnTWtDZ2o3TWFGZGk4X1puOXNYYWZYVm1aWg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxPLWJuMXJiUTJRTjdyT05aamR5TDZUZFZJZ2kwdy10Y2ZMTEhWcGppcTNkMTBJRDBzVG43WDdJc1ZYS2hNSDNvRjhzRC1aZnJlN09kS21ST1JZcUt6TDRpRjhDUnVXUm5XU0J4czJPMGxmeXMwWnFRWXlkaTlFSFdXLTRyUGhuWW5SUmhuVTRCZC1YbVg0YnNKSFF0ZXpKT2RlTEtGeUE1OFlrLVpYSURFN3hJMHdYb2NrN0pUWG9COGZWYWp4c1FjZlpjUUV5UktNZFNVYW9RU21zNDl4?oc=5</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Toyota expected to post third straight quarterly profit drop as costs, tariffs bite - Reuters</t>
+          <t>Cash Awards Strengthen Offshore Wind Supply Chain - Maritime Fairtrade</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 04:52:04 GMT</t>
+          <t>Fri, 06 Feb 2026 00:11:58 GMT</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxOU0JtVUdXRnkyZWg1VGNrWkxzbWREYnA4U3VHcHctb2ZLdjJfYlgyNWRPVE1DXzZ0a2I1QnAzQ2xCTHJZcVVEZER2bXV5S2hZVEdvbUJjWWFQUHFtQkppTmZkX2VuSUtjRWxjS05fZzZ5ZTlLaE11SlFJNXdzRGllNExJaDktdnZqdzNZSEVpRHlQVWNsbjBtX1JkWnF5eTBOcnRQcU44QnVBOGFMa094c1F1RUFkT2tQTDdaWHYzVVI4UFFqNEdBVmhzU0hOLV9yWEJnYnM4UFdzTEpuaXJJUzRUaDZjbF9lY016Q0RB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQUWpNQUdVQlFJRE1qNlR3YmNSby1aQlJTOW9jZno2cUhwZWpRRFVhNF9yeTdSTW42MG5lbjkxcFFNWEhTaHNoNGY4WUtyV3RFa2h5Vl92cUc3b1BzeG9vWjR4X014bV9yNFlYSmZhejNzTXNSX1ZQb1NZbDd4eGp3bVRnb00xa28?oc=5</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1661,17 +1661,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Top 10: Supply Chain Leaders - Supply Chain Digital Magazine</t>
+          <t>Shifting bond markets: Resilience amid fragmentation - S&amp;P Global</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 15:56:57 GMT</t>
+          <t>Thu, 05 Feb 2026 17:58:34 GMT</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE0temVHbHYyVmZMYlIzdmpRS1JLMW5nTUxfSU5LdjhwVGRHeGVnSklkQmlUOWMwdF9sM2FrVVlFQ3ZnRWdrd04tak5mNkxuQjVUakQ5MVFUaFlSV2k3V3hTN0FIbXJjVzVMOG8zOWlEVXNPM3N5UHJTdg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgJBVV95cUxPM1NkYVJwMmhpaHR2eTlEbFZ6TUpoc0pRVTVhYkQtODN3alZ3YnhkQklBeW92dGRGT2E0eVlNYzJ6bGhnTTNXUkdNZThvZGVuOU1qUFF6V25UQXNwNm0zODFRSDF4ZXF6VzlIS29ZSmwzLWJOV3VsSHF3bk1rUDhweEFtOXpmdzU0S2FRNDB4SF9UY2xuY1NGdWx3OUlIclZNQXdna3JfVlUyb0lXUVFTX3hCUVl3VFFhQTNhWUx5SVlfdVllQzZ1ZktFUFZEaGNXU242cFFablVuM0ZNNVFWejRnUVlTaFZhTkRocnF5dEV3QUd4Rm9PeGZTV0JkNnV6UXFESEcyZHl1dUNIOUVvRUpLMFNQdw?oc=5</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1691,17 +1691,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US Treasury's Bessent says he was wrong when he said tariffs could be inflationary - Reuters</t>
+          <t>EU renews efforts to advance US tariff deal after Trump reverses threats - Supply Chain Dive</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 17:55:40 GMT</t>
+          <t>Thu, 05 Feb 2026 19:12:16 GMT</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNVy1nWVVrck11VkQzTnRyMHFRaFlHZnhWS0ZjbG1vcXRVQzRyb1poek9MTGtqY3JPQ3p1SDM1dHAwT1I5c1VnekUzTmdqMkRENXB6SHg2Z2YxUjJXMEpQdERwbkJsLW9pSEpBdnUzUmNLem9RWTFldmFVbTUzYXY3eUZBZFBHSENka2pnS2o1Zk4tdHptRDkzWnJKSmh1RllXYTAwVDBkdVdSckRUQU0tVVVhY3BhUjZLNHR0TjRXVVBDcWd3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxOb3J3ZHhZMHVZLXBUR2NxRlJBSkVQQ0Q3MlNPZjZBNmpnclZhZG1SUUVCa1VuYl82WUIxekhYQkVjaHo0S1lQMi1UeUw2b1VqLWdBRzIwd25xaURDT25GNUdlMmdkQVlMR0RreTFhUU9kNjhRbXFPSTdoV0lFQ24ta3ByWQ?oc=5</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1721,17 +1721,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>It’s a kind of MAGIC: uncovering the origins of chromosomal instability - Nature</t>
+          <t>Polish border-guard IT failure slows passenger and freight flows on Ukrainian frontier - VisaHQ</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 00:51:34 GMT</t>
+          <t>Thu, 05 Feb 2026 22:53:50 GMT</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE5vNVJiNG14SWdKSkR2WlZjbFdwcGFSSHczOFF6bmlfNi1zVzhONEpPQjROUEw4TlRaNE1CbGhtd093MDR2SndzSnZsTE0xdlFGTXBORFZSdkh2bHdlMVNr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQSTV5WF90S0lEZXlobno5b0YzLS1nUElvMXVmNFFsVkp0SGpvWHdGN09Iak95VWFuYldyaXg3ZW83bDBWTzk1VDlIemU1WmgzWThkU213WUg4Y1lUMHY3MjJhSFhOc1JfVnJKcGtNNU1hUUZBNS1KVFVCa2t3emNfX245LWw5d1VaRmt3WUhxdHRVdGk4V2pQcVQtdDg4bHhiRjN4VEkyX2s5X2VkTVREZTRFdldwUVNkQW9lUVZueDZQV0RJdl9BZw?oc=5</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1751,17 +1751,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AI Contributes to Surge in Cargo Theft and Freight Fraud - The Maritime Executive</t>
+          <t>Sanctions Can’t Solve the Israeli Settlement Problem - The Century Foundation</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 22:55:44 GMT</t>
+          <t>Thu, 05 Feb 2026 19:00:00 GMT</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOVngtbWx1Q3RXLWZTMndsTWpWd1hJbWo5emxKN01mQXROZHhQVjN2S0lielN4dHZPZkNQSlBLZXF6WU9kWk1iRDFRWmp2V0FaZ3E5THc4NWJBUkRnWHltbmNZWmtwd2xkZnVhOHctVHBnSW1haVF6SnFybnRfMEY5dHNQaDRLOUR3OEUwSjhFUmpOTGdjR3k2b2FTVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQNEE5dVlHTkpyVHl3QzJ2TTQxYWt4Q0o4Tzl1UHJqVWkyeDhGQXM2VVQxQmp1cm1jeUo1dXJoc1lNVDlJZWNGcnoyOWtqVE5UeThIbzk0ZGlIQzF3cVhWa1d1bFp5SGtpVU5ySDd6TnVzbFZyZXRYbEUxMzBldUF5dElNRjl0RG5oNDhDdUpONDY?oc=5</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>EU AI Office Establishes Signatory Taskforce to Guide Compliance with General-Purpose AI Rules - BABL AI</t>
+          <t>Argentina Says It Signed US Trade Deal With Trump - bloomberg.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 22:29:52 GMT</t>
+          <t>Thu, 05 Feb 2026 21:34:50 GMT</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPVHJhX3ZmaXRuQWoyeFNJVndmQk5JT0w3NXQ3SkZGa1JfRTNRbWpaeF9wME1PX2UwSkJxZTdiZjBsWWZQeTdPOFM5Ty1tcFJXXzhoOFNfbDNzYzJvSkh0NnIxM1RJMnpxLUpSWWY0TUx6bTBoM0JvdF9kQk92SFF1MHJ6Z3M1UlJmVFJlSnFtd2ZpeVVlOG5sZEltNGRRWHlOOUc3Z2RFRFRQZE0ycFFYTg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPNU11Z180cm5YOUxGSUxiRFFfYmJfeGVJcDVMV1M1U0I0cVdyTDRuV1A5emRsUTY5MkxxMTdoOGFKcUZyUUMzZVdjNy1QUzZIMFpiRWRfOVZUMFpGOE1XM2c3VlhoVVpPeU14aVRRc3BmdFBVYkNySGpIYjN6Wmx2dTlkRGFROUMwSTAyN2k5OW1BeFBWSnhhcnpWcUlEMDY5VnZyMU1XRUY3ekl5RzZpUWV5cWpFZw?oc=5</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1811,17 +1811,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Two arrested over attempted sabotage of German navy ships - Shipping Telegraph</t>
+          <t>Spotlight: Al-Futtaim Logistics - Aviation Week Network</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 02:02:21 GMT</t>
+          <t>Thu, 05 Feb 2026 16:42:50 GMT</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPS0MtaTJIRFA2d291SzdsYmdRQ2d0TENUejhBQkZld1JRM05rUDF1VlhKbnFxUWtYLWp5NkoweUh6Z2x0b0lwZ3JmR2xBZS1QQjltNk4yOHVUVy1ySTJwNlNPVTQyNVptRnlrVktMMEJuZWcxQXc4TzBVdkg3NkdlVTN4UTFYSlFaXzYteEtGUTBBdDdoaUhVSm9tVVNaVVk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE1lR19aX0t5MEk0S1RvazBuMm1CVi1CSGVXUWI3eWN3RFFudVd6dV82SG0xbk5tSEhJb19fWWJwLWlZYjJqQVZrTVRERnp6NEJpaUROcnRLMjF4VVh0NFhzc2JPa1VzRWg1TUtxejdoWEZ0ZXozY3ZlZEV4X0E?oc=5</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -1841,17 +1841,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Port of Mombasa hits 2.1 million TEUs in 2025 - porttechnology.org</t>
+          <t>Pension firms look to sell stake in owner of Southampton port - Daily Echo</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 15:27:22 GMT</t>
+          <t>Thu, 05 Feb 2026 16:36:00 GMT</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOU1NoejczMGNrVERINU9uZ05kRFNjTFlOOW1ValR2SkNzUWwxXzJiajFVYi1TOUpsbkplVk91UXZ5eV9ScGluR29pUVFOS19OVElpcWNyYndoVUFCZHpuNGIxLWg5d0h3ZEhHNEhWWWVnYXJqSlNfbmxOZ2tJa0lLN2xOYUZKU3FCc3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOVWUwQ0lTUS1ETXhudFh2aGcxTEViZG1GZVd6SUNYM1d2OWJlNXdVX2lpUllwRUN1eFdGX0JBcFk0emZUeWdSU0gwN2hKcm1YamIwbHdSdHpWcHhoRnVvdkNzMFRCampvMlRIbm92R0xxOEN2WmdXRnpzdHFSLU5XbTRiRWMxSDBiVENpUEppZWJZeTF1ZTVieXU3THJDZGhG?oc=5</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -1871,17 +1871,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Measuring Epigenetic Instability May Improve Early Cancer Detection - Inside Precision Medicine</t>
+          <t>Hydrogen Technologies in Port Polska's Investment Plans - Fuel Cells Works</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 18:22:53 GMT</t>
+          <t>Thu, 05 Feb 2026 15:25:00 GMT</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQYWo0dUhXZElFSGdrRGh4UmM3eUtvbHFTRFZZeHJMVzdnOUdFMVdHM1NuLThLS05vdldNLW1JaUVUOWxvb3hkTVNvNHZfdk1sZGZMb3g3dUQwaVBfLXJaU1hKeGFROWxuei14bVJZaGgwSEl5T0pzUGVTVC0xMFgyM2JqUS1KZjkzNEZoeVZ5WTdHNWdNUXNSZlktTTJlSHRxS3VwcF9hTldVdGlaNExpZUxPZUdfd21PYkg5MVdPUEdSQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPVFNQWUVyYzdLeUMzc1lXYWpHSFo3M1l5UFc4OE1PRW5rTXNheHcwUmtBNE9iQzcwMmlCbVFMU3dhVWRHMjZnWEVGcWNsQVhzRjZKR2k1anpxWWR5b1o4ZDg5c3o4VmRGLWRiLXFxQWZPb3VtRHM3NzNpU2hLRDktWEU3VWliWG1Peko3YndIYmlxTks5RDktdHRLYThZZmhobFRiVHlEVUM2cE5uajBVQg?oc=5</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -1901,17 +1901,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Zhonggu Logistics boosts orderbook with two post-panamax container ships - Tradewinds News</t>
+          <t>Future Prospects for the Port of Churchill on Canada’s Hudson Bay - The Maritime Executive</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 04:01:05 GMT</t>
+          <t>Thu, 05 Feb 2026 20:54:00 GMT</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxONUR2eEFtVy1HVnczN3FFaGFDcEJsYWI1OWJ0TER5aW9iMC1FNlRIX0twM19kV3dQX3VhWlVKcFVPemRSTk9xVHd5clpXMVRfOXpheGZQSmVqbWZtS01zSkpIbkI2SkJKNmF2TWFZZzg3bTBrYjgyYXhGc0lxWDRrM2VrLWZIVmZQQl9tMldiUHRKdmhJSUVfY0UyWjV2aWVsMjdsYWdkZnNJX2FTUlR0aVBDV0xIdFl3eVRVM3ZLb0VNN2JG?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNWXJnVjg1eWFwR1V2OVg1d1M4QkJ6elRDeVl4ZmJWZ04xMzRoemxtcmI5SjRxWGY2aDFCLVIzUjhXa1NhQUtuT3NqQVVGYmdRbEtMRzZ4Z2UyTDdtdHh0YVU2Z2pvb3lGUk1fVTJtN1JialhoTnhfNXNlV0xlSEI0c0RzZTk3djNidHpCX2Z0T1ZRelA0d3ZWSlpIc3M3dDNaU3FYX2VVeXcxeHM?oc=5</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -1921,27 +1921,27 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>UK: Council reported disabilities drama group to police over Gaza genocide protest - Middle East Eye</t>
+          <t>Mitsubishi Motors Incurs Loss in April-Dec. on U.S. Tariffs - nippon.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 19:39:00 GMT</t>
+          <t>Fri, 06 Feb 2026 03:28:01 GMT</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNTF9qY2hmNG5MV2JGNHpyZXpoLVltRDkxc0tJTEJWdXR1clRFQzBKampvUTA0a1ljNzVpUnNsZ3luRVhHM1JBd19LQXh1MUR2c253b2drQW13NEhqTXJLQXNFeGpNdkszcEFKVUIycGphUzlUbVc4SVROdlpKdDZmRmdrODg2Vks4emhPczBlZDByRHFBbWlnOGZwbktjZ1E0UGtNbEJfZ1BwWFhlWWw1UkNZZ0JiWllQb0prRw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE1kNmtmUlRfc2UxeDlnNDl3TUFuOWhST09MQnJ3Yk1lOGZUSFpPNlpNY3VvNEcySWdqZmUweEtlX3hsZDBPbUpObHV4N0gtVnZIQ1YtUUVYNndVeGxr?oc=5</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -1961,17 +1961,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Women told police they had been on 'wonderful escapade' after Norwich paint protest - Eastern Daily Press</t>
+          <t>Demonstrators and police still in deadlock over Israeli president protest plans - SBS Australia</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 14:00:00 GMT</t>
+          <t>Fri, 06 Feb 2026 03:56:35 GMT</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPbktmV2xVWERDeV9nV0pfOS1FbWxjVHEzZXdGQmI5cFo5REVmcFkzWlpLYW84NmJQMDF0dUlWdHNxYW84UVJzTlRlVzV2a3Foc29FZEkwZ1kxekJYRzJrX0J2a2FDemlqdE9DcU01Z1VZa2FFcndUMkwyNllwX0J5eEVOcVVqaXJRc09lSVV5dWNBWG1rVS1JRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNN1c4b3dIaUswNGRvTk81c1Vvc2hvQkVfSjBEdUg4VjBUVS11M3ZSVXlGR1JoNXBuM1hFbzkwdWY3VHg0ei1YemhtNk52QmVPOGVYWXdNT2g4b21BRVBmbnVsMm5iV3Jua1FBY3VEb2tXRFZZN0pxdlpiTU44QUdnQkUzLVZ6RDMxam0zZmVRNWs3bnZQZ1dRMzI1WnM5UFhSWnUtNVpkN0lORGJkRFJsTFRCUzlzRDRmNjhJSHVkOTlORDNKcWpN?oc=5</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Police warn of disruption ahead of Enniskillen demonstration - The Impartial Reporter</t>
+          <t>In Pictures - Sri Lankan police attempt to block Batticaloa march as Tamils mark ‘Black Day’ - Tamil Guardian</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 19:39:46 GMT</t>
+          <t>Thu, 05 Feb 2026 16:45:53 GMT</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOcFdGU1VKalFHMlZOenI2dGk2dWdzOVEyc2s2dk5HSUQyVFc4d21lazFaNEJRbVBnWUZiLVo4WDVIai05S2RhMVFGemR0aFBva25KUHdpdzV4VHlqOHc0Qmc0em5ROUJHOTlHTkVmWVRUdnV0SVM3SkE5dHRrdUFZcjNhc3ROdG95SF9Xcnp2eGphTWk4ck5KdHMzZlZaWkRZSE9vaUtB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOa3gtbXVTRUdwWHo3SE5QaUdOMER6TnY1cXM0c29PRHQyVVFtTWRvR1YzeTVZbHQtaGFMYkZUZWFKUGxnc0VJLTVVWGF4Y1NwdkZ4UjdoaFd5TTE5cVlCR3lVVzdSV3BrOHpLR0RhR1dSaWNZTXYxNDYyQ1g1RXY0SVhlTDdNVzdkbHhlT0hubzNqUG9zZ3hXSjFWN0d4MU9NY0xVd3NJR0dRTkZJUU0yUUNwT0Ixc1FD?oc=5</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2021,17 +2021,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Police issue six citations after hit-and-run at Fremont protest - Nebraska Public Media</t>
+          <t>Norristown community demands answers after police officer strikes man with patrol vehicle - 6abc Philadelphia</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 17:44:59 GMT</t>
+          <t>Fri, 06 Feb 2026 04:38:15 GMT</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQeWxwdF9xRVBlWG1DbVVjRE5wUkYyVmVaaE4xLVUtWXE0YmdOWFJ1ZHlHZzRING13TGdadDl6TU5oT2p3TmZfVXBNZnEySk1YT3RnX01VY183X25uUGt6aGprek1LOTVWd2dLYnRBSjBDbmJQdkFfTjdCekZaRFBRR1VHdWd2QV9Ha1VmaGtoVnRLQ3lDSFRackNVMENGMnNrUUpuSzN1bUFjS1RJbV9uWUwtT01OZzV1NHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOa3p3bHpUenZCemw1OV9nckIwY1NaWmxVZHM5cVJjQjFCOVIwTlJkUU10Y0FBd2YzM0FOc08yaUpQTndCcW92dGNhalRNamQzejh3UEdtZE1zZlloZWVKcUVCcXpUV2s3MnBCYUk2dEdFYjdheTRfLWdyNV9vajh3YXVEQUNQRnV2SVl3Uk5oMEJuMnM4ampkalc1SGZrb2o2ZFl0Vkc2dUZEa3d3RFp30gG0AUFVX3lxTE9WNWc5NENieldvSkxzS3pJX2JrazN4a3h6M0p5dlRQVWs3SmFyR3VHWjh4aDItMDh3ZHNFckFtMm9RX2ZRZFJaTEtnT3BaQnNKSG0zWFFtWWNSWmFKdVcyS3ZuelRzMklGZjNMOXlRYV9EZF9QNzlaWWZUXzFicU5ncW81U0g5YjM0LU12dURBOS13MkRXLTlXUV92WEdoSzhOZW5iSXNlTHFOemhBbHZSdVB2NQ?oc=5</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2051,17 +2051,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Police Detain ‘Yellowman’ Ahead of Protest, Motive Disputed - Greater Belize Media</t>
+          <t>Catholic clergy protest police attack on priest in Sri Lanka - Herald Malaysia Online</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 01:39:30 GMT</t>
+          <t>Thu, 05 Feb 2026 12:00:49 GMT</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgJBVV95cUxOZjJhWVM1VFpQRW01UFVIZXRMV3BCYnprUW1nX2hFZmdSQjNuRmE1WDQ5MGtkOG9VbDVDMWNXdzJsTUdUekpEbjFvTy1aeV9ZdTh6bmthMGx5NzE1cUxTdk56NWdiTkRKLU56SHBab3M5UFJabHptcEQtYTl5Z1I4MlpyWDdNeWg5a20zVE1vUHVuSGNVWndwS25QNnNBdVZURUlIRkFwUGw5Tk5uRV9yU2l4NXppYUh5cHpGX2gwb3BMd3F1emJ0VXVsRlo5cV9yS1hzcHFjVTZhWjFjNV9VaGNjMFNVNTRHVldzNExVQ2h0NzV0U0tWcGNoX2FEaUlrbTJDT3p0RW5QS3NDaTEyamhWZGtqdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOVjRSSEtmdFhXczBjcVJVY2dsLXJ2WlJ4NlM2YVpRLVZqLS1UV1FGS001V3VpYkphS0ZJU3dWNUpkTTR6TzBvR1doVFRDX1NreHZjTXVyMGhVSWtLWDdZQ1NHaDVmeWRncVJzZmxBSVR6ZTVGRnB4OWxuM2JBV2pPY3R2V1R3Q3JBZHg0VXhrcmxxcjhlVkdGZE40T0FUUVFKYlR4WjYzTQ?oc=5</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2081,17 +2081,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>HANZA invites you to its Capital Markets Day on March 10 - TradingView</t>
+          <t>Reno Police prepare for anticipated ice protests - KOLO | 8 News Now</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 08:12:00 GMT</t>
+          <t>Fri, 06 Feb 2026 00:38:00 GMT</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQVVRYUGw1b1cxTW5mN2ZMekw3Y1RUWWE1VWNzQURIa1lTTURnTzZIamk2X1FkdFZfeC1fSGRqUWpUV2lIQWRjOW12T0ZTWmo5MUpOWDd0Zlp0dWhTdWQ0bEhuVFU0ZWg5dUVqbUthYU04UkNxeGlNUUUya2pGdjBMSEowTjdsQkVlNnlXZlR1RTZUbnZqd2c2ZE9LVEY2WDRvdUhEU19SQmFPZXBwZnJXQlA0eUlqenJBcDJsWnBYUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxQeEJJTTlIeVZWN2FNNUFVRTYxaDY3a29DdHJyT01FY0dtUl90RUZCSWUxZVhyOEhWVGY2LW53NXh6UXNmT0Nubm81UDRuZTdxYUJwWWQzUmpCcThIMFBRUC1YZFA3Z1p3bmQ5UTBiOW4zalZVRkllN2FNLUdGancyMzdFNW5kQdIBmgFBVV95cUxNeHZKOXZOZzdkM2pRY1hBeFRXNVpSSkxhLU0tWENyX19aZERxcUFxUFYzNUlxalNzSm9lVXVNc3pjeTcyRWt5SDNyV0Q5anF0dEVjbnNOUGZHZ0N1TEIxUVhKeUE4NnZUbDFZUGVROGZOd2JmNnRMd2Zya3pUT3NZQkZuTnNoN0VhTVJoZjgzM2duX0dIWEhUSFpB?oc=5</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2111,17 +2111,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Officer strikes naked man with police vehicle in Norristown - NBC10 Philadelphia</t>
+          <t>Labor’s radical dream of the “general strike” - Capital Research Center</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 04:15:46 GMT</t>
+          <t>Thu, 05 Feb 2026 13:30:00 GMT</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNQ0RndVl3Y2c5QXZoVHhvMkFwYTJjTW85RDZvbk1TTFJHRWVTcTB2d1RlanlacFJSNE1YYmx6bGFWeWt5RUZLa3JEWkdjaFQ2cUZ6bmc5Z3JWcnVKNnJHYnJPQTFrM3RYU3J2Q25VSEdLLVp6cGZ4bHhRTkRjb1NLQkhrTmlZVFpKZktlT0F4S3lESGxCQW1nbXIzczZ4Wm1sLVdHSnYwTlpYZ3NNcHJrNmZiNE15SmJG0gHAAUFVX3lxTFBzb1NYREUzRUlYbjdrZDZtVXRfUm5mZjh5NlF6cnhSUTFKRF9UTkR3cU40YVJFYkFWLUZkcHdWY2w4VGpLUW84bk5OTFBVdTN4YVlxMGViY1VXWmJVYUY3eE84SGxfa2JvRlJQREc3UkxWSTVieEg5Mmc2VVI3VFljblgxcXZKNE4ySWlrWHFVcGVJTmU3M21JR0xYbjhiaVpEZ0h6eTJxb1Bad3VIRmZmbDR3bFY0eEV4Rmx1TW5oSg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNSVA2SldrUjVQX1RjY25GcU1kazE0cmtBYmt1bXVXLXJ6UzR3QzZmd3BFa2REb0JGV3VMck56eGtUMDhHaEJtTDFwTV9LXzQxdVdXWXpsY3huRjJkRkgzem8tT05BczJvQVJmaVpROXU5NmdON0pFR0FPcnJjZEF3QXVCa2NuUQ?oc=5</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Wis. man steals cruiser, strikes and injures 4 officers - Police1</t>
+          <t>Itaú Unibanco Board Clears 2025 Accounts and Confirms March Interest-on-Capital Payout - TipRanks</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 22:18:45 GMT</t>
+          <t>Thu, 05 Feb 2026 18:36:59 GMT</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOWTg4dXpSNjYzUTU3N3c1cWs4b0JZQTJ6OWwyVm1qMzVlQnFXNjYwY0poYzBHQnpWX05xTTFaN0FoSGRtSXlxTVJ5a2ZGQTUyNEJwSXpjeTJWQkdiT0loMms2TmFvcmc5ZEllMEVzSE55UVFTZ0dPNnVDelZaQkZ4b2hQZ3VKMzkzd3NZSDd1V3FJdjA4WndvbmlGRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxQQzZfSFRNeFRFaUw3bUhBR19PZ1VPU21YcXN4V1FFallHNmNhSXA2SFFiTlg4eU1KNnhIMkY5dG90VHZiY0VadHBNSjdrZFBRSEd2V051alBRdmRDRnhpYjhSVFhJQjA0bGFvbkFBQXdiWmhfdWRDQTBlRVFSaWktX2JESDBvVDc3V0NJUFpKczVLWmVpaFFCbG9FcDBsbmVtRC0yUXBZZEtNSmtDRlJzUTNuRm1JaFJGdjZkYWR5TU5RUFBOa1pOMGJ5UmFRUnUxLUYycw?oc=5</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2161,27 +2161,27 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dentistry in 2026: trends, technology and leadership - Dentistry.co.uk</t>
+          <t>Attendo to Present Updated Financial Targets and Strategy at March Capital Markets Day 2026 - TipRanks</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 06:31:45 GMT</t>
+          <t>Thu, 05 Feb 2026 08:06:20 GMT</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQOUNQU0lTaEZOTm5Qa2lsMU5zQXZtazFhSGIzVFQzaUxUNHhxQVplVUFuYVpaSk5DWjIwd2k1aXRmV0NaRTZrSVVDN3RLVEhRaUVtRFdtUWlzSU9zWFFzRWJ2aXhCX3J6WVAyS3JYRGFfLXdKM2ViSFRQU3duaE1PUXZkZGpPOGdXUEZ1TXVlNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOMXRDeEhMcHNuVklmQ2dORFlRQ2pVdlpXOVJrMkl5dzhvTmt0enFEdDJuUW8wTXJBZWRtRkNKbHBYZGh1NWVLY21aX1U1NVBQS0R3YVY1YTVUSS1zQ1l2NEZUWGU1bEhuUG80bFJsbm13SGVzeTg5Zks4RFJrMUhCMElhM2ZWSE1DRk1sbFQtT0dDTWVoVFo2X3FsWTZSTmxKR01PZEVhRnlfdUVNdS1LWmwwMm9hcjNqejBZRS1kbDV2ZGdPdkdkYVNYaTZrOExFOUZuamlwdms3eFU?oc=5</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2191,27 +2191,27 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AI agents spark fresh security fears on Safer Internet Day - IT Brief UK</t>
+          <t>Cleary’s tenant charged after police raid - News.com.au</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 04:59:00 GMT</t>
+          <t>Fri, 06 Feb 2026 05:15:28 GMT</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQTkZ0RDVWVEhRbkNqUGpFZWdZWEJ4dUNEbFpFV3FlbGJOUTBGU29GU0R1UUwzZFdIRndYNWFWdTcyejc3QTFjLXRkMEpwNzUxUkZGbTlySGhyelNyZldIYzdfREtjaG43SWlJUWhXQlYyVkp4WVVrY1gzZ19OZzVvVnRWSlI2Rjd3cTAyTHZSWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOWjJ4aGM1NGVNa2N0RHhxaEFST3BSa1M3Um1HcDdHVFFGWkhVdzN4SkJTckUyYmtBYVhMM253NC1JczRoR09fRWE2VTFuZ3V1NTZNS2tZTVM5VlNnano3UHBMa3l3bnhMYjRCMHM4TXFEQlZHbUVkbzZIcE01TTBLTTlEc2U1M3d3Z3lLOFVZZVBqUldibmxJQ2NUeFB0NVNZTzJpdnBrWXFXQUw3NHBtQlVoZEZZMk5pMWhnbXpiRGI0OWlQd3JBU2JhbC1NMHZD0gHWAUFVX3lxTE82cTlSaXg1VGdKTmlSaElUUnJhZk9HaGdJcFdNUzJDX1R2VWFoVzIwRFNWS2VfclRETEZKWG9tb0l0X3R5MXR0M3JtUi16Q0RCN0ZaT29JYml2dldCM1VJLWhpMlIyaUFfLXZiQjdCOWRhWDA3X0ZMcl82QU1ybmZoMG93R0lXMU9RVU5JQmtRZ1hQamk2alppakNIYkFVMkYwdUx3bnJrcXRxZVA2bkpsTXJHcDBra3liYk5ubU5NOUk0a0lyRmNfbDNqdDY5OGFIczUtb2c?oc=5</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2231,17 +2231,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AI to create “dividing line between innovative and conservative firms” - Legal Futures</t>
+          <t>AI and GDPR Monthly Update - Dentons</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 00:13:58 GMT</t>
+          <t>Thu, 05 Feb 2026 20:13:43 GMT</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUkFVX3lxTE1KNDJrVENsRHRBdUY3VFRCc2NGWWhLVlEtM0tobm0zTUY4MHRFbVlndVVFaHNJUXlRbkpPTG5oTi1RTmF4ekFDR3FjZUxpRmxFQ2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgJBVV95cUxOdl9Ba0pDNzNFUnZsQ0NaUDJWOG5uaU9SUEJfOXJ3VXNtWVRZTS05ZzB2dC05R1R3clV4SG44OU0yU0FHcDVMXzJfbG4zS1FhZldKQ3hTNEF5bVdHRXJqYW9EeU9lRjJ1dHlMRE5nMXNsY1JwdUI1SkR0dzZGbE4wcUxJblNsckFsc05xUnNUQmxuS3JGZkQ5ME42Ymk1SnBFMTkxRVhla3pHZlFCVUhKaDJhYVJ5TjlpMXdrOWZFdUg0V0ZiMUpnT1g3R2hrN1R1NmtobUhoN1luTTVKNURMOGs0RkNic3ZDSEs4UlZ2bTRVSkV3TDJLWHZYbVdROEY3SGhBLXhoOC1OM1lmd3c?oc=5</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2261,17 +2261,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>TripStax adds AI and sustainability features to Analytics module - Business Travel News Europe</t>
+          <t>KPMG pressed its auditor to pass on AI cost savings - Financial Times</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 14:06:08 GMT</t>
+          <t>Fri, 06 Feb 2026 05:00:13 GMT</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPdDdFaE9uNm1ITUR3U2JvV1J6SDdYeloxTEJnTmJCbXNHYWtud3Y2bDVDT1lPMW56UHZ1cHFlZXBzUE9HMUhpb3BkS1hoc1ZEYk5jQ2VTeC14M1ZpajhHeGE3ZXY3Tk8zaHJKSVljWXNGTDI2alJ3bzJwYnZlZHNEWEw0OVluSWFIMkZsUTd4YkxRMXlsNGJEZHl3aHluUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1JcFJRMmdvcFYxNVhvQmdYNklVN3gtNWUtMEJ4Y2VTbWRUNEtIck9HdExUZFVPSFp1RWZ6NUlRQTRIc1MxeGhkVVBJakxuZnpMcFRneDRKdmoyTWFvWDlFdE9EMjUydDI1d1MzWjJXeHc?oc=5</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2291,17 +2291,17 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Women in tech and finance at higher risk from AI job losses, report says - The Guardian</t>
+          <t>Amazon shares tumble as it joins the Big Tech AI spending spree - BBC</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 11:29:00 GMT</t>
+          <t>Fri, 06 Feb 2026 00:06:56 GMT</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNakRQMFJ4NFJDWEU1UnRoVG55QzZjWnl0WW1Kd2czUDgyM1hXVzlNYXM1S2ZtRlRmeTFXMUdMWWhad2taWGpCZUF4UER2ZGRpa3R5aTFycUhyNjZKN0ZzenQ4XzA0ZDdpX2xnaUt1d0I4TkV1VjdadFNQa0ZaNlQ3Qm9QN0hKQ1Vnd1Viamc0anA2UGdQLUQ0S0I1Q3pYXzRnOGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1wZzJieWpQdW1JZ1ZfaGEyQkUtS3ZjUi1NOHZCY1ZMTXJZMFU3Ym4wUG0zaDhuYmsxSGNBbFpSbUszRW1HUUhwRkJZc2VDc0hpN2FaSFlfM015dw?oc=5</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2321,17 +2321,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>How the Met Office is exploring AI innovation - metoffice.gov.uk</t>
+          <t>Why comparisons between AI and human intelligence miss the point - The Conversation</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 14:00:00 GMT</t>
+          <t>Thu, 05 Feb 2026 22:54:46 GMT</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1NdzQ4Rk95YU1kQlJJeXN1RnkxYU5XN0RKTGgtenhKNDNTSmRPbHVwWHlwVVU4U05pSGx6MDZ1bXZwQ05FWC1sQVdnWmdSQkxZaWJ3ZWhrUkt4LXp0VWZIdmEzSE9ZVWp0OUVzdFZIckhRSWVGVi1scA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQUEZhTmltemh0R1RtT0R6SjB6dEcyM2c4VjdDa3hZNFY0R3JyMjFmT19TU05yN3FKeWR1aVNUYUtpMU04aDdHYmdpYlBHcUJiNjVVb0ZjU3g0YUlHd0FFamxLTmt0MS1hOWxyVUdZa3BKbnVSdVBSNFQtZlg0VVFtbkc5ZjdQVTRLY0VoY0lqd1JIcEQ2UEFCc2ZUSzFPLVhT?oc=5</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -2351,17 +2351,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>42 Technology and Synaptics partner to accelerate Edge AI adoption in manufacturing - New Electronics</t>
+          <t>Agri-tech and AI can help you break productivity plateau, farmers told - Eastern Daily Press</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 23:27:45 GMT</t>
+          <t>Fri, 06 Feb 2026 06:00:00 GMT</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNaThDVDY3WkFTTUVZdWpUNl90ZDU2NUlmMGZPOW93VGU5Tlk4bkxpMlZ3bjVQc2dSWWZOMHREaFRNbEJPS0hHaDZmZGFHY2VTU3NjU0FldnZyOGFlZVlRczhXZGRLcmlSNFZPWG9MQ3FaeUg1U3NIOU84OGtPR2xuWkxLRzNHbjdkSFdJUEFmbGE3OVUwUkJtWHlSaUc4QlJFMnJnUjlOY1VRV1dkUDlRaDdVZEZsZjdIRVZyVEpRVWdKd0s2bXRiMQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOM25yVWZFTm02OGc5alZPajl2b0xpZG83dWxzVmJQQzh4UkFyRVVqWVlpOEYtcW1fTFBTUjNscEozYV9QaG5HMXNTdmhidm5XaWxEQlhhMXpsWGFpeVNlLTUyOXVuQXdidVRodXAwdWhDY3h5RjV3VWZpOFVoVWVqc1hOc09aZER2MVlWWjJMTUhGTUY0OTNJ?oc=5</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -2381,17 +2381,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AI 'slop' is transforming social media - and a backlash is brewing - BBC</t>
+          <t>Microsoft Launches AI QuickStart Programme with Support from IMDA and UOB - Microsoft Source</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 11:29:30 GMT</t>
+          <t>Fri, 06 Feb 2026 07:41:09 GMT</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE9wNDA2bFFUbmx5aDlVcjdxaWE1c1JHZDZTcmxnampFRW5PN19EejRhQklPMkJmeDNYZnlMczE3MWl0M0h2UkhpZUN5b0hoX0RRZzExcTBZUmV3dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNd2ljT2pkVlFBMkc4VzBVSkFsZnR1RkNTb1lxSG9NTkVGOHdRWHVQMDZOT2hram0yZHRram45dFpCV3RvbE8zOXFyRDdoZFY4THhZVlhWYjdTMlhoY29oQkh2WDcwdlBfSUpZTEYwZnl2MGFLR0Zqel9KenNCSzNzM1pNYXpoSTJGSi04QlJRcnpwTFRTTGZ0aS0wX1ZBQlduOTNqTUN3dHlOSU1rdzlGWklFMGpKY2Y3ZGduWEsxV2o4dw?oc=5</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -2411,17 +2411,17 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>How to lead with empathy in the age of AI - Home | Digital Health</t>
+          <t>Safer Internet Day: Young people encouraged to use AI safely and responsibly - Warwickshire County Council</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 13:55:11 GMT</t>
+          <t>Thu, 05 Feb 2026 11:51:57 GMT</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxNVm1KSkstZWh5MHNFYzdyRzFaaDFta3p1ZXZ5Ml9OYnRtZUladlp1ZTlXanBWMHZEdFBPb2IyN1dHX290ZjZZUlVtY1ZuZHpfNUp0WnJfb3Nna0kwR1FfemRCZVFFZU1VSXdpekg5bjljQ3J4NWFSWUUzMGYyY3RBdHAxSV9jSFU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxORHllMEgydXVnS3pOTEQ4MEJBbDJCcnIxZy1VNzQ3eFdnd2FIQmg4emktR09uQXNZWFNvd0k3SEV0dlhoTFExWVpSM3dDT0pfUnFEWE9CZnh0LTEwS1RVQ1VteXhQbDAzV1J6U2dWbGdySzdZT25BWnY0V3dHS01zRGhsZlFHRTg3dmR4dHBfNlFlQWNRaVFLQnd2MV9mWkVPd2RCajJRenFxLWk1RF9SWkljX0V5ZGtzT3pSeENYS0NCYmM?oc=5</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tech stocks plunge as AI fears take hold - The Telegraph</t>
+          <t>Micron’s Singapore Fab Builds AI Memory Capacity While Valuation Stays Stretched - Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 20:10:00 GMT</t>
+          <t>Fri, 06 Feb 2026 07:05:00 GMT</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPc2tvVTRXY1NJTW1TNEphOFJzMVZHZjlQLXdtT2FqTjY4cUl5ZDRGTklpcnBna1liU3dDdi1ORnVRU0h4bmh0YlczUDJOdHhVc3VzV2JqbVlxajhON0E0MGpmbUNSZ2VCLTJIVjNMUFRQa0ZIemExZXBqbFhnY19ySmdGWHlFVEVtLVJibzBkRF9uSmM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxQRldMNDd3UHBqX3FaSWJWS1F5V2hsUkJhYk1NZGZTeDJmVXg0WFpsYUtVcGFVZEFwSTZRaFRGZzRDOWZ4TDRDdUt0SDNwdGIzRUJDdzNYN2Q2U3VSalVmQTc1QllPN1JYQXM0NDdrYjBUQkV3ejdVRnVySzY2TldHUnEwVFQ4QQ?oc=5</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -2471,17 +2471,17 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Web Summit Qatar startups raise $205 million as the summit wraps up - Euronews.com</t>
+          <t>NGMN sets out framework to simplify 5G network operations - Mobile Europe</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 17:07:48 GMT</t>
+          <t>Fri, 06 Feb 2026 00:35:19 GMT</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQeUlsbVNiSl83b0dzU0k3Z2NoMlhBejJPNG9ZT3FVemxtUlE3MXdpdEJDVnRrbHdWV0JZVDBseFVaMm5VTkJKcXRtamNwdFpZWXlqeG5nWnJjenRWeWM2NFhrQnVWYTg3eTNWV3V2aW9iZE9zV05pVlN0NElCNjZfMnl5UXluX0RKSm9XbnBZODNoakExb2w4VHpqRXEtc2tlY1dKVTc3WWpPcjRhSjNOR243cENGQkJzbzBfNXhR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQa3lZZWU2aGhDN0VuSmowSGUyZ1g0UkxGZmItTWEzVUl3RlRWT2JsRTlReVAydERUYlNIb2JQNkZ1QXhwNHRlTTFwSmstMG14a2dNcm8tZXZyWDZNTlBXSXlkQTJZcmZNS3FDNklBR1hDaXRVM2s3UGp5ejd5a05GLWJ1bEpRNGp2cUpKZ1FWZVFCUFk?oc=5</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -2501,17 +2501,17 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Lab AI and automation start-up raises $5.8 million - Chemical &amp; Engineering News</t>
+          <t>AI fears pummel software stocks: Is it 'illogical' panic or a SaaS apocalypse? - CNBC</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 16:44:01 GMT</t>
+          <t>Fri, 06 Feb 2026 04:20:00 GMT</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPSVllLXFHZmR5aDJKaDhiRGpoNHA2TTIzWDYwbllkSHpTaGtxOG9vcmJ6dmkzRzFYQWJYcDBOSlNXYUNvZW9aUXlPN2g1akpuWjRFX3h5LVlVUGxla2tOR2RfOGcyWE9FQmVZY3RrZWZvTi1Kbmp5bVpoWkloMy1ZblpvN3NaRHpNNEtNN0xKZEY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNdThQSFVQWWhleE1YV2MtOUhOTUFnYkd2aTNVaU1MZ2o4S3ZlOEtOeEd0Q0oyMTRaUVhwM1BmTjRiWlhyVFU1UW1GNGp4RURqakV6WVJWMlpoWFNCMzhLY3BuRDZETi12Mk5hV1BDMVFzbU5sUjFFM0pRSUlRN1JTNUYyQXI5eVNnaHFUX9IBkgFBVV95cUxOZWE2NFl0QWEyU1AtNUw4Y3l1V2FkUlpLc19DYVAxYUJveGNOa2hjRGZYdkNUYm5zWWFFMXRzeGhaTzhHbXJvRmdGa0kzczE5R2Y4OE1xbG5JTXMzZ3VPanFLNzFwUEV1czc0Vmo2bjd2Q29XWjNFM3VxaWdMQUhuWjg3WW1nZU80RXFZR283NXBCdw?oc=5</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -2531,17 +2531,17 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>DigitalOcean report finds widening gap between companies adopting agentic AI and those falling behind - Yahoo Finance UK</t>
+          <t>Alphabet results keep analysts bullish on AI and cloud outlook - Proactive Investors</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 14:00:00 GMT</t>
+          <t>Thu, 05 Feb 2026 18:34:00 GMT</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOVUVqUVRobjFLdmZHQk1peUc4bUljR29jN2FpUS05cEpDUEQ3NW1Ib18tS1pJaVcxejlTdks2QjNqUlV4MGc4ejJtRDVleEVRMnI5M3BTQVhyajJkVm1VbG4xWkc2bVFwTk5lWUdGVTZ6UUFSWlhCWXhLSjBmVnV4am8yeGEwNF81dURyY0EtRjY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxPSDI4XzI5Xzgzd2N4dTdjUUI4NmxocDFVX2E5ZDk4MGlsQ214UTNvdlY3MjdJelBhclI0U2wxdnppVGxneG9hQi02U1NoRTVlWHo5VkZJcHJiUlp6bzdMNzduNWNqRmF0Q1VPVk9nVzJObjJxcEN5OWRUdjhHLXFWMi0xX3RkVVlTbEVkOXJTVmJUNVYzNjROaHZIbC1Cc1dYMWlGUjExOUl1UThXVXJLdGFHV0RHV21uejY3TmdmNWpTbFBCaktjN0NjMlhzOHV3?oc=5</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -2561,17 +2561,17 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Energy and utilities cyber threats escalate as ransomware and APT activity rise, Cyfirma reports - Industrial Cyber</t>
+          <t>Ship Production Ready AI and Survive the Multimodal Frontier This February - Google Cloud</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 13:53:09 GMT</t>
+          <t>Thu, 05 Feb 2026 21:19:05 GMT</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxQNDFFcTU1U2tuV0FIQjdad012SUdtcmtKQkY4X3piR2J0UDVPVkF2NlZIdnVHMTM2UEg0Nmh4UGFPbnV1eXc0cjNmN2kyS0Zpb0ZzclFOMm4yRUV1ODg4VS15Y1lZUVhMa1ZnUHh0OWxNMThTOGY1SFo4UVQ4c0VsZlJjSHdHbWZOc3VKTHRsazJabzdWTWpVTWc1dExtRTd4cks0Uzd2UHdoa3pJZmdpRXl2eEdLRl96aklUakhwTmZ6cGxFUlBZZ2Zoc0lrb19hZENpN0lrbnloQk9TdW91TXVYMlRMQTNxWncxOEVqNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxPWTBKTXdPZlQ4WXVvWS1UcEcwcm5SM0xfN0JPTnpIY1gyZnNPSWxYZzFvRF9JVWNpNFBZTUNfdVo5YWpDd1ZiVGVMb2pYRnhvMEdMRnM3SWJsQmRkZHZyZE1xS05xUWY0RzNfRWRJNHRQSmlUOUZVREludzRuSlA1dWdSeWhwTVE5WXlGMFFPV1dJUkhGaXJubV95WllFXzkzRWptMnhTeEdnUXFsOXlxMDFQT1lpUWgzRTQwWlNJR0JhZXZCaW5jY3hYNEdZYVdQU1Fr?oc=5</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -2591,17 +2591,17 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AI investment shows strong momentum beyond bubble fears - Digital Watch Observatory</t>
+          <t>Latest NDAA Supports AI Safety, Innovation, and China Decoupling - Lawfare</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 07:45:00 GMT</t>
+          <t>Thu, 05 Feb 2026 19:19:19 GMT</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxNNlNjWFpPbDd1a3VxN3l3REEyOHVabFR5N2p0QnNPUmRrS1d3WjYyWmVUY2xrX2xzZzNQOE10RXhia19aR01JQjBsdHAwbEZkT2hpV0tzVS1TdXBUNllHVlMzNkJzZklEbk1OaXJkM0RaSmpuOENvQ1V2RHU2cmRSTDVpZWFDbjY0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOWnZGQjV5cWRzU1YwR2pmRkZSMXRWWW9YSUNsaHNCeC02d2ZIdWtqaDJjOF9uaWJDMkdMcHd4Q3NhYlI2ZVZILW9nc1U1MWhNam0wVmcwZVFYUmxsQmlmLWpScmFJYVhkMWhkRS1WVkhqejJ0NGprLUUtdDFfbUZ1MVU4TUpTYktHMGtRa3JrbG4wWVNPbURxcjhrQ1oyTXp3Tl9z?oc=5</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>FirstFT: Google to double AI spending to $185bn - Financial Times</t>
+          <t>Arista Networks (ANET) Is Down 13.1% After AI Data Center Hype Meets Pre-Earnings Reality - What's Changed - Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 22:00:42 GMT</t>
+          <t>Fri, 06 Feb 2026 07:06:00 GMT</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE9xY3hZeENtWFpFdmZHTk8zT1FRTWxGNVVTMlVwVVFpSjlPeXg4WEY1aUFBNE1iZ0w3RkF6c2ZMWkxjZERMak5ENnlrU212QjdHMWl2Um05dEY5WUU0NW9OUW1QUEpUWXpCUGxidFlaY0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxQcWd3ZENhS1I0NFZWampEdVdrQXowand5QmtzNm9nXzBRSUNTbjgxbUVlOVozUEpNZnFLNkRSNnFIaXQ0MGRhajIzZERPdW5Bdnd4Q3NPbFFONU1kcFhHM3RjVVJSRmF4MXhlRHpzbEdXcU1KNl9CWlVpOTM3LXVleDAySQ?oc=5</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -2651,17 +2651,17 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Cleaning up AI - New Electronics</t>
+          <t>FTSE and European firms worst hit by software sell-off - Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 23:27:45 GMT</t>
+          <t>Thu, 05 Feb 2026 15:59:36 GMT</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTFB1MmFnVldNdlNKbU1Ocmp5dTdvdnBQd1JhX0pLYTBEbW1vNFA4aEMtZ0Z0MFNhaEpnRzRLS3pLLWl2LWdrY0VMYUVqMjlBbnRjSEdFQ2QzdVFEMjh2djQzeEhyT010WlhUZHE5ZFJXSTZ3cWkt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQUlllM1AzbmNnckhQV0pMWUxkSUZrVnFVNndGeDBJbmVMcFFzZFl3NDhsT3VwUjFrUS04NXQ5NkhYLVFSZXJMMkd3YjZvbjRubWg2Y3pVcTN3SFpkandZTTYtNy1FZTZHN3pUUWdad0dOdDc3X3o3S29pVml0RHJTTkVIRkxtOGRuRFFqSHJLYXBsUQ?oc=5</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Germany's first AI factory for industry officially goes into operation in Munich - Deutsche Telekom</t>
+          <t>Lawmakers introduce bill to strengthen energy sector cybersecurity and threat analysis, boost resilience - Industrial Cyber</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 12:30:00 GMT</t>
+          <t>Thu, 05 Feb 2026 09:11:13 GMT</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPZHZHNk8wR1pCc2I3RTdESWRERllfaERRblZISzBHZXN4TV9PdmxNUHp0UEkzS2VpSlZZNWg5d3hIcWlVV05paGdiZjJIc1I0X1otRU9QQnRpMnJvNzR5ZDNGNVM4aDdWZ2JVSDFyMmVXY3JNS2FJUXFobkpHTDNtSjI5VEpfRmFwRF9kS3pSUG0ycGRmb1lfdVR2U3FybGlyM041QlNjd0RwQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxQWXZXbXdhVE56VjBmZVdCNVBzRlV6WWs0a3Y2R0NGSGpoYmdycjR3cTROLWg5NjVZenQwS2RPaEp3ckUxMGI5aHEtaWlnanJ3SGxTMF9RNnJUY0V0YmZKSlRadGpIeWlUNl82S05jajV2ZGJRcXZRWTRWYk44czlETHFYZzYybGxHU0MzUFQ3bUhnVzJuYVZ5Y3VkaXgwZ0FnRUZpbktwa0RvcVJHclJqSTNGaVpfeHpqUjBWS1dkWm1WLUl3VHk2YVdQeGNNQXFUZDhrb3RlS0Y1U053czBGeTNNTG93bEtwN1ZYSk1DWlA1eDBBLWxrVXhtRQ?oc=5</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -2711,17 +2711,17 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Alder Hey and Hartree Centre develop AI-powered NHS staff rota system - UKAuthority</t>
+          <t>Scandinavian Airlines CEO: AI can cut disruption response times - Euronews.com</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 16:17:58 GMT</t>
+          <t>Fri, 06 Feb 2026 06:30:04 GMT</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNQUZVWEpMZThiMlNpMDdFS040cG1VTVhHSWIyb19yYmhmSTNlNno3MFY5emlXUlUwMFFacWJTa05UZVM0MHZYbGVMWlFhcGhfcEZWdlRGZ1VRVFc4OTd6ejJlZUpmOThod1ZDQ3R5Ni04N1QxZEJSUENFaGtSa2xsV2xkOUhVLVRYczFyeW56TDk4LVQyYzZ6WEIxNGIwYnZ5Nmh0S2JkMjBqZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxObVpKNWFtSGh3RmVabEg0ZUxJZ1pyTlp4YmVSUEpjb0hHdGRmbzNYM01reU94UERQRjQxUGpRcDhBRmtjSnJKd1B3TjlvZ2F0Qm90Mk5MN28wWDZsTDBKZXB4WXNQVzV4Z2Z3UjZNTHRQV002ZmZvb2p2RkZFeHI0WkhvOTZVNW9pTGxHVEpybTdMNVgzUFMtRFhuTmREMmczTjJGcmlkREJlX0U?oc=5</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -2741,17 +2741,17 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Gangs use AI to clone pensioners’ voices and empty their bank accounts - The Telegraph</t>
+          <t>Kocho taps Zadara for sovereign AI cloud in VMware shift - IT Brief UK</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 07:30:00 GMT</t>
+          <t>Thu, 05 Feb 2026 17:15:00 GMT</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPLVBFYXd5VDFFQ2cyVTVDQ1BGMHBCWHlVdV90VTVvREdsdm5nY09CUkJIeFVrTkRzd09VcUJrbWQtYnp3Smo0cUxYWWRRc29tYUlGX3haYlduSkNZeWpXRnJxMDVBNW5VU2NzWWxzVlpmcVhUZHlKVmZhSmVtelR1bTZXbVZVcXpmOTJhLXpMYm5RR21wTlVQcGt5aE5GcGVu?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNMGRJRUNwRHFKdlZEZ09LMjloR1VlQlFuRGFzX1ZiaGlmdU5SSTJPYWJVVGV4NnRURjd5amQtbkZXMTJnZ1pkMmdVMVYzNGkwWHRNVThoWjdkNkRwVThoaFcxcUdEcm5qN0ZSZEoxcE4za1ZwQUF0VFRYQnI4ODhjSWs1eFZPT3FWcUM3Zg?oc=5</t>
         </is>
       </c>
       <c r="F78" t="n">
@@ -2771,17 +2771,17 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Beyond bans: AI-resilient and creative HE assessment design - Times Higher Education</t>
+          <t>Exclusive | Inside Elon Musk’s $1.25 Trillion AI and Space Megamerger - The Wall Street Journal</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 00:17:46 GMT</t>
+          <t>Fri, 06 Feb 2026 03:35:00 GMT</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPdk5WN1I0S0NjazItOGozejFBVGJsV2Zvb3pEanRpQnM4RnpKa0tRZHE3RmdlYnk1YXlqTS12RENVQXBRYW1jWmtmMEQ5QXF1RGtqS25hUFpkN0RRbTdkZjBodHdLQzh5RmNCdURxWjAtR1BzV0pKZUxtT0N0RWY4V2NQemtGVWlmeUN0TWhDNkI2RDc3NjRDUlBDQXlEMnRMNzg0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8wJBVV95cUxNOFEweUlkM3ZCT1F6Y2FyZ3A5UE9TYUlvbDhkTl9JYjg1bkN1NV9tblBrV0FRamR5c0hCcnRaVERCRGEtaE9RdUVPRGw3YnhsR2lJYVdscnNqZE1rNmRXZGVMeUpvQ3B4TmloSkJLWE15VGVrSHpWaHE5T2Z5M2wyeGFHUGN6cTVkQnZpSG5XV0pWUmR5T05mbDg1Y3piNG5kdE9EZnJ6cVFYM054MTBra2RUOWtmbjRZNmt5NUtSbE5Dc3ktc1ZtdGh6YkFkVDkwX1hTbTJOaXExdFZ5a1l6SHQ1QWlnMHowRXpjM1lENGE1aGxMM0g5QV80Q3BqQ0RPSWFxV0h6RzYwWGRxcWM1OGJObzNmaTlHVXItNWVyWWdpckc1SldDdElSdlhKcWNWRDkxcGVkdDRNb1h3cnRjVXFCVlh2M1IzLU5ET0ZCRkpyMkN1TEpBZEUtRlFqYTdPeHlSQ1hqOHo4Nmk0SDlORXRTcw?oc=5</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -2801,17 +2801,17 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ElevenLabs raises $500m as telco AI use grows - Mobile Europe</t>
+          <t>The AI Shift: Is this the ‘take off’ moment for AI agents? - Financial Times</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 00:30:05 GMT</t>
+          <t>Thu, 05 Feb 2026 12:30:07 GMT</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxOaEVXN2NicTlCMXI0eG44OGhtQkpwTWlaajdoUE9lcjNpMjFzN21BMVVaNnBEUlRfZW83QWd3clVLZ3J6VTQtSkxnV0t1dm01UXdfdmZzMXdWSGpMS1RRWlVOQ0FsODk0ckNld2JZeEEzN3BCZjFlYVJCdlhkcUU4RGRn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBHdE1JcXdQcnFhZ3VlM1hfSGF1NDVDemJfYmRSLVkyTFFZcmVEU2dabDBYYVA4ckRmZW1ySUI1ekhIalE2elg2ci15LW9tbFNydlBXYlNjb1c4RWpEb2hqTjFybTYxU24zZUhWQ3VMazY?oc=5</t>
         </is>
       </c>
       <c r="F80" t="n">
@@ -2831,17 +2831,17 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Software and Legal Services Get Crushed. AI Panic Hits the Market. - Barron's</t>
+          <t>Hospitality Tech360 programme to tackle leadership, AI and the future of hospitality - The Caterer</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 17:11:00 GMT</t>
+          <t>Thu, 05 Feb 2026 10:49:34 GMT</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihANBVV95cUxPZnNwZWdQMHRaLUNtZ2dRX19NbFNPSTVIVENCNkk1SVZvaTUtS21oZHFyVDNKTzhSa2RTR2p4cVBQNlo3amtVSktxa181Qy1xcXE3aDE0cVY1cUJJeUNYcENVYU9HeDMyZXlKTXpMbnlzTXhaR2RpMmtrZWdoQ2tOMVhTcWFFVzYyemdRTlB0dk5oNTRXVGJoTElId1FPSC1ZRVRkOHlMWTZEY1duVGZMY0pQaWJkUW1IdDN0YVowNnY3cEt3X1V4LVl2bG10TzhPMWxTNFJiX0FvcWp4QnI1U2I2VFJ4c2k4TGRWMHZ2RTlncjFtYUd1UU5YRjZMbmpYbE5iZ1Q5Z0c0NHYtQXlLS1hFUVl0alJNenBwR2U1QVZKck01VkJJQjU5b1VFbks1aXYyNG5fUGpiaHZ2cnMwSzJkTE9MalktTzZzWWFrX1BfcVJLcnFRVUZWbzE4RFVORndRMEZkWFBBbUN0Wmh3ZTlxbjB4REpidldqbVN5bzJTMTFv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxON3p4VWVUWWt4VnVYRVVsaFlQejBQM0o3R2RMWW40d2lEV0ZyTmw0aktNV1hJcldoV2RmRkhGOFNkWHUya2liQXoySmo5ZE1MV3VIZEREeHpnbUtGaTRMZTVvTDE5LW9TM25xTDF3Q0J5SmVyOGhGblE4WWRFZ0NMa0hZTktYZHJiQ0NNa0J1TUFwVHd3UWZOemdacTIyN1B3c0RoZHpJZFYzYWlhVDYtVG9kRFE3ZDF4WWhqWV8xdw?oc=5</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -2861,17 +2861,17 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Omnicom, WPP, Publicis and Havas share prices plummet amid AI sell-off - PRWeek</t>
+          <t>Transforming into an AI-first Frontier Firm in partnership with our works councils - Microsoft</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 21:27:06 GMT</t>
+          <t>Thu, 05 Feb 2026 17:05:00 GMT</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOMVNmNl9oTDRpeldHS3AxTFZsN3lJTDBaLUZFOUVYY2JYMlVwWUR4LTVFOFNsakZxOW96bExTV0FpNlRReUdZbnhWWmNoX3lFYktRV216Sjl4ZWxiOFU2eC1BQXdrQjFZUk1VU203XzhtSHhvY2Z0SnM0alpWQ1dNSzFBVjJLNTZQdGtjUFQwcUZQRkM2VWZjQlBWX2NOT095Q210Q0dB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxPa3c0RmJBTGcxLVRPR0lRVUNSNzBadGxXMm03M195cnZHdVp6X0Vob0ZvVWZFZzQ0aFQ0bEtSaFRsVlZNOTQ0UFhDYlhlNmRmNmNqdWpMaHJiM2F4VDRkQ0RCT25SUTJReTg1QXAzTW03SGpDbDlvV0ZTcGViZHZwWkxubjh4a2VpclRvQzBaeWVCZHMyOXFfWm5FQVZzYTlUT1NMNk1ZZ1A1bUhGMm14bE9aMUpwU0o3ZkhsX1RFLXdnRnFN?oc=5</t>
         </is>
       </c>
       <c r="F82" t="n">
@@ -2891,17 +2891,17 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>How to integrate artificial intelligence agents with operational work teams - telefonica.com</t>
+          <t>As WHO Debates Global AI Regulation, States Clash Over ‘Data Sovereignty’ - Health Policy Watch</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 16:30:00 GMT</t>
+          <t>Thu, 05 Feb 2026 15:54:17 GMT</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOZjJIaTN1SGtUcXlXZ0xmNUVPVS03TXVFTHZ0VzgwZU16ZVVMdmdiRkVvOS1ZbmRia2VRZTFGRDJSNTZoTzJUdk42MndtMnlTUXdFWW9USmxfYklHQVd6a2ttQ0dWSnlRRFhRWEdlbERrNjQ4RUZKM2luejVKMVQyMjFhbGNHQU9KVGhzbHNOZUZRUlo2UG9LdDlXazltLTBqMHNJeG5YYzR0b0o0enVHcHctY2FaR0JVNXR4cHBrbGFwNEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFBwYUZScUJFWHpudm4zcTN3YndZLWxVM3JLdFF3UXlXbFlhMDQxVGhfUHl3R1MyTHZjN053b3Vzd3BVY1RLMEpnRzJoRnF0R1pmYWZjejRSbVJhQkpiS0ZPRnUzaEpPV09mb2paVw?oc=5</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>4 takeaways for finance teams as they implement AI - MIT Sloan</t>
+          <t>AI and the Law: What Documentary Filmmakers Need to Know (March 2026) - International Documentary Association</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 16:04:14 GMT</t>
+          <t>Thu, 05 Feb 2026 22:53:40 GMT</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOZWxCZ3ZwZWZDWXJKeGJsUDdyb0ZiaWdCSzZfVGR6cDJDaGtqc3lXLVRUcV9lbVNhclZhb0lHakYtS3BGQl96UWh6QUQzZ3h2MXZIWEtkemhiemZUeUFyMFZqb0JfdUdFYmJGVUFBeXN0X2hkdTV3NGg5ZEZONVNGUEFSbVE3d2NFZTE3NllEQmp2Szg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxQUGQ1U0o0TERoSkwtcVoyc0RSWUpIM0hzTGs0dkJ5b1hIT1RORl96VGRRZm5haWpKSnlPTWx5TmFfdWNHYXVXRnpvUzQwV2pmYXplZ2JWMm9SSUlzM0RHYzJDN3FRSTJzUTZrS0xmSVBKYVpLWF9KeFVBYzFLT3BnYnJhN2ZQcTBnMnJsLQ?oc=5</t>
         </is>
       </c>
       <c r="F84" t="n">
@@ -2951,17 +2951,17 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Why India’s Digital Public Infrastructure Will Democratize AI Usage - ICTworks</t>
+          <t>Cloud cover: Forecasting digital disruption in a cybercrime climate - Slipcase</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 05:52:05 GMT</t>
+          <t>Thu, 05 Feb 2026 13:25:35 GMT</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOcklSUUJpQ0RwRTFGZm5HazZ3Q3RIalFIRTlEZ19DT3J5bC1XeTJJc2lfSTl3dzlNUE1DU3g0TmJfc1Fpci04dDZtMjdHZDZ2YkNqSElNeXlIdmpjcGlKYkQxUlZnTjdYX0ItSFlQb2swWWdSVUYwek9IZ2F4WmV0Vkc4TzJOMkVtY2ppMURlMktVQlV6ZjlV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQOG91WHZVSWFoZEc1THR0TEczWDYxWExxNXRCa0xfcmVaLUZxcG5KVUpULWp0aUUzdHAzakhLUExFVzBTLUNtYW43dlNWb2d5QTJ2MFFpX1ZIV1QwbmtuTy1hdVRMdDJKc2ZRZWVIdkpobUJuTWktMFhYUkJIMjhNRjZLSUVHbm9MZ2oyMVVyUS1XaUdUY0N6UlhwUzJjYkI2R1FxRktn?oc=5</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Industrial Safety Market Poised for Strong Growth as Regulatory Compliance, Automation, and Workforce Protection Imperatives Accelerate: Verified Market Research® - PR Newswire UK</t>
+          <t>Amazon reveals plans to spend $200bn in one year the day after Bezos guts Washington Post - The Guardian</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 15:43:00 GMT</t>
+          <t>Fri, 06 Feb 2026 00:55:00 GMT</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAJBVV95cUxPNHFVWHJheEhhQXFLVkUtTXFveXRZeFBhMkRjZi1tV2hqN0VZRXRNY3hDR2I1NW05T3hJdVNnTkFXdURnTWpXSDc2STNfT3VCSVdzSnpzdG9Jb2xRaTk1bV9BSXc4LVZ3OG9vMERGNU5zZ1cybVhGbkVUVUVoRXRFY05nZUtBdXM0eVp6ME50RUxBQ3VCaUdnbmwybGVva1NNa3ZLcXpnWlhZTmNiZ1M3YnlKcUtQQlBTd21BNlRzS1VuTkJOdkg3QzJKTW9idnl0TVBqTE82cW9XZWJneG1hLXBCMDdLeUdRdE9oRnVWN2MwNWtOcVJsNkRzSm5wcUNpVVVuOEFrQ3c3cmdvNmV4eFpuMU5ROE9WY2NveHl0aDZFYjdIcHdOUkczbTBvZWJPQnlqOFFFM2pFN0Rk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOOE93U3BaYmt3dEE1ZFgxOUhxczZURUgyTFpIX1B4WUlaeDE4clNGOTBNbDByNkdwcjFudTJIbmVSX19TeEVmaHAzMFBqRXoyYlFWbVpKNXhNbmd3Q0p3WWs2WmtlUWJneUpBeFVFODVLZ0JRZW5lQnNPV1BVbGROaWg1R0h1V0cxX3dvWjdiS1NFUDNxUkE?oc=5</t>
         </is>
       </c>
       <c r="F86" t="n">
@@ -3011,17 +3011,17 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>MTC drives automation and robotics scale-up with new accelerator programme - Plant &amp; Works Engineering</t>
+          <t>Savannah Guthrie's demand for mom's 'proof of life' is complicated in this era of AI and deepfakes - The Independent</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 09:44:43 GMT</t>
+          <t>Fri, 06 Feb 2026 05:01:00 GMT</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPajdlZTNBbUNIblhpQzNDU0RmUlBhTUxKVEhSNUVrcUhzQ3RlSnBiV0xyYUl4UG44ajNSMFdDbG42Yk1KWjVwRmVzdERlUHdiWVNFVlFWNmJsS3VzdjJ4ZTZmQmV1aGFLMG9iamRMbEZ1bGxNTDc5R0ZWcnNBOF90dW80OXFPZ0VrLS1QeF9hYlR1aXhXNUZhZDB6MUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPbFdpOWdDX3E2aXRvbk5yNzIxWEp3djBIZHJpbGNpVHk5bTBzY014aEY0Q2E5Qm5maGtzcTlkY0hYTjRuRUNDOU5HZ0pNSm5DQVp5eU5vaENRTUVjb0picjY3cTk5cFZxdXNXXzhBVzNLRjR5SzhyOWdPS2t0NnVJMnRLVXJHUmFZQ0k5ZHJTQ3JBV1l1MS1oeDBuaw?oc=5</t>
         </is>
       </c>
       <c r="F87" t="n">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Understanding Global AI Governance Through a Three-Layer Framework - Lawfare</t>
+          <t>WTF is the IAB’s AI Accountability for Publishers Act (and what happens next)? - Digiday</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 16:30:00 GMT</t>
+          <t>Fri, 06 Feb 2026 05:03:07 GMT</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNbTBCUWN5N0tCVlNfMWtVU1BaSVh6VmtVS3lSWG1mVU90LXFZakw3TWpqYWhmajlVVFowNF81eG9UdFhhVEktS1JHUkM4dWh3MllMSFdzN1ZLalpEVUR4T29DSE8xREJjeE5YZTZJQlduNFR6a2dudUNwbFNwOTkzbFNkNlNCckdCbFlvNnFGaC1MVzEyOVRiSGNsclA5UXBKMm9SbXpR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPeGdmWmJjZjlGWWY0SzZFQlkzZXFWa3JDTVMzM3ZRbTlmY2VJeU5jQnVaN1ZPNFpHTlhYMWFCSG9SV2tqaG1VWWRScWpCTUdxcmpPQzZsWXJHb1h6cFQ1NGRkY0o3bzVmd1NhbFN5VjJ3ZkJkTERkajBTS0p4cjlUVThENjZZT0d2TXBESkFMZ2RvejY4ZDN2NXlxU05fSldUWXlz?oc=5</t>
         </is>
       </c>
       <c r="F88" t="n">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Smart AI Policy Means Examing Its Real Harms and Benefits - Electronic Frontier Foundation</t>
+          <t>AI adoption accelerates as engineers across EMEA move into production, survey finds - New Electronics</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 22:40:34 GMT</t>
+          <t>Thu, 05 Feb 2026 22:27:38 GMT</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPUlBmX1ZENzNYbk9KQld2eE1Zd1ZyZDltdGhER1UxbTRIbWlvNlNDQ05vZkNPejllb2o3amRPTEN4VEZlMVdJdE5HRWpnTVM4QVY4UXZHR1d2X2ppaGtkZVU2X0ZBc1A3ZnpoSDVKZ3QzS1hoM3U1T1lHMzJFeGtqY0hLWXVlVVVUajdIZmM2Uk9XdHFVVDBobVRIUVp5aGZZU2dr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNSEl0eE9RdU1xSUtub18xOWtIaWJHRHc1Q2w1TXFCZWt2OFlwaEktUTMyS3pZQm1MVk9tQUNOcFc2TFAtTGVWdXRLT1V5X1Fvc1dyel9oMUNsU2tQNjNXRkxod1NEVUdfRG1qaHNxUGJjN3c2Z2QtNTZqRWRROUc4UHYxZTZBX3Q5SWhhbWRpWmt1QzFCazM4aGpQQ1hKbmNuNzZnMjdDS25ubk5mb2wxeGMzRjhaZ3dqNDdQZ3dxZkpPM25yVHNv?oc=5</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -3101,17 +3101,17 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Telling your company’s story in an AI world - Daily Business Magazine</t>
+          <t>Evri Group launches pilot AI and data apprenticeship programmes - Motor Transport</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 19:51:31 GMT</t>
+          <t>Thu, 05 Feb 2026 12:46:06 GMT</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOZUZPX0xpcUE2a0ZMT1YtY1N0NERvczUyM2xyNlJFUXRDOWYxcWlrVG1wV0xGMklwLXZ1YUlxc2Ixd1M1NzJybUFKVTNSMEVLM0Fqc2hOU2U5X21ubnBCLTNvWXFDeFpCT3F2QUp4TzhBWTVBQnNSbHJXWFBGQWNURXhBZnpVZlU5UGJ5MUF3MmNHQUo0MURwS09FNlo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQU3hVdDQ4ckhwY0UybElPNGhhTmxwQ25JVEVkUUh2d25FWjVMd0kzV3hxb3hEbVE4TmdQdzJzMGxhemdWQnIwdTV5Z3pDNHRnTHlmWGRqM1JFZGFwOEFoZXkydzQzQ0FsZUwzbmp1YWFWcVZvOXpIWFg1dWdMOWVPMUdXRGljcHZZTUVrODVDVWRsR0lRclgxUTdhUFZxN0FoN3dhdUg3S1JNR0szeFZSNnZQam5pT2JVbktVQQ?oc=5</t>
         </is>
       </c>
       <c r="F90" t="n">
@@ -3131,17 +3131,17 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Your Brain’s ‘Scaffolding’ Could Collapse—And It May Radically Alter the Way You Think - Popular Mechanics</t>
+          <t>UN secretary general discusses future of AI accountability - Jurist.org</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 23:41:00 GMT</t>
+          <t>Fri, 06 Feb 2026 01:56:48 GMT</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxON0k0bHRXdXh3ZWlLUmU2V25Kc1ZIekp1UUJGN19zZlNpenhpNnFMQUFSLTJFdEpkREFLYWRJTk5sQ2tLU2lIUzlFdFZ2RU0tdy14WlJzWG8ybS1QX2dkTFJmN0FrUnNIV3MwdExfZTFJTm5fdUhMUzQ1RV84MjVfblB3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPTlQ5ZUpTcC1EWVZkbXJGSHFEcWJpaDlaZlBfNVJaNjVmaXpqYUhZOTk5N09QSFN1U1M1TkcxaF92aEFMWEt1SXIwS1RtWndqYkV1RWR6UGQ4dHFRNk9Ud1NsenVpMGdJc1pVWDNwQzJSQUdsX3VLeS1tTFRneGtWaWljanUzdDg3WU1Cb3dJT04tNFM3NHA0QWMwVQ?oc=5</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -3161,17 +3161,17 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>"Moving Forward Responsibly”, the Dutch DPA's vision on Generative AI - Stibbe</t>
+          <t>Intelligent Infrastructure: How AI is Enhancing Terraform Automation - Atos</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 15:11:47 GMT</t>
+          <t>Thu, 05 Feb 2026 17:07:39 GMT</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOb1daTm1iTkZ6VTdIREZvVVFPUzB0bEx0Y1VtTXh1LVVmMHRqakI5R0tNdnNwV0dlOHlvMWlkcmlKSVoxclBfa21XbGpTX0hhdGdybXljN1d2enVoTnJ1ZWMzRlYwbE1OOF9MZVRnM2YzQzhqcUJKNHNXY3hXUnhud3ZTYXhKaV9FVDYxRk9BNUtGOFFVMW9lVlZmeVRmQVA1TnVKc3pVMTVyS0JTTDRUVW9XaHE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOdEljUmlBLUVMV3Y1b2VKZmMxZk5MWUhBSlR3Y2ZJTG9KaTJQM2UyVTVZcWNqSm9sSVJ2dHpCbWY3eFhrczNWQ3ZCVEZvQVRHd0dnVGxleGoxdUstbTFsM3hvWUYzaS0zNVotc3huc1B6MDJ4Qk5hLXdDQUtvbWE1WEJjZmgwQTZoRE4td0swNmhncGs4T29v?oc=5</t>
         </is>
       </c>
       <c r="F92" t="n">
@@ -3191,17 +3191,17 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>IFS : How Industrial AI Is Shaping Construction - EME Outlook Magazine</t>
+          <t>Insurance AML explained: red flags, AI and reporting - FinTech Global</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 09:58:13 GMT</t>
+          <t>Thu, 05 Feb 2026 10:09:21 GMT</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxPNDJkTDI2d0huNUZTell3WktfbzM4ZUpHX1ZzQm1OSTdpalg2VHI1LWtHbEsxRXdIZWNnRDFCU1ZjMEpfZzJhSE1TQ3JKYWpqaHhPQm9qT19wbFI0Zi1tXy1MY3hDbmdfV1QzZkFfOEhOelRqMmpEM1FfSDVpRTZlZVJOa2t2UTNiVkY4MkRmMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxPN0lEWDFzaWRLVEdMaURtVjdYQmJ4Y2puUFQ5TGV2VFVTWC1KcDNXbXE3ZXNMUlQ4VjEtSV9UVGFiLTJYU1JqUDM5QldrSlFMejFFY2tnZVBLMjFiNEZmT2o3Qzc3cmMzVW9JZHNrT3BBOG9WZ0RWLWR0SFgzM29mX2xVU3FfT24zQnU5WlJR?oc=5</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -3221,17 +3221,17 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Developer’s Guide to Cisco Live EMEA 2026: AI, Automation, and Meraki - Cisco Blogs</t>
+          <t>Alibaba Cloud deploys AI innovations for Milano Cortina 2026 - Broadcast</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 18:07:22 GMT</t>
+          <t>Thu, 05 Feb 2026 11:10:31 GMT</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE5hNWpDVmE5VDZ0YlhVcXJUVmFSMlVxdDdxejJvV1ROV2NYbV9KZlRYZExHU3Ixa25YeHN6dmtiSzZpejMxaXotdUdBd21ramdxWVctSFYyOXZNT1lqUUc1SHA4bzVHdlNyZmkwanhJdnFobU5hVm83ZEdn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNSTBLaDByblBiX0JtUUN6TXRUM1B1WHVqcHZPTGVnUmc5d2dGMkJfVlhlVWxpemZOUUt6MmlYdGNpYl9NQk5zM0MxRXFna1EyUkQ4WmNHeVVVUWJwdWpnUU0tamd4TURBaWx4ZGFkRVo0cTdJcHMyOWVtQk9XQ1dHYUNwWkxUbHcwMnhTbTVwaDhEclZVbUZhczctX01BaE1QSGdDcm5ieTloX3hJSmlRdGVfUzNHdTk4Y2djUFJMa2JBSS15OWc?oc=5</t>
         </is>
       </c>
       <c r="F94" t="n">
@@ -3251,17 +3251,17 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>US Renewables in 2025; Supercomputing and AI; and Tighter European Sanctions on Refined Petroleum - S&amp;P Global</t>
+          <t>Vexlum Secures EUR 10M to Expand Semiconductor Laser Manufacturing - The Quantum Insider</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 11:35:16 GMT</t>
+          <t>Thu, 05 Feb 2026 15:00:00 GMT</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNak9XdUo0TC1JQUtVTTRjMEM5NW5iUTZtMjJBS0V2akpFU2FQckNxaHpIb0k2UWdReWtOZUgyU19LNEpHOFZsNG1tUDdlb2xLZTFzZHNrMkJRR1I4eXdJcDhQQk5xXzVoU1pXejJPeEdlSUNxaU1xd3RCTnFYVDR4MWFCOXloUjhabWFpRzFBUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPUlAzRXphdURhcjN4X2lqaUpZUnhOWmZ1bVhRVjh0UkpQYUwzNm5GR3FvdkV3RFRXa3EzMGJEVlQ3TFRwWHJVVWtnbjdhRlFGdXViLTZFSFdTWVVqM25vNEdRcUpMU2tKNkN6MTRNUWMzcXpkQ3p4RmxzaERxNUxUM05MNl9vSXNWb3plWVdycUlkN1JJZU5iTDlISDI2bnBRTEpmdDVpTQ?oc=5</t>
         </is>
       </c>
       <c r="F95" t="n">
@@ -3271,27 +3271,27 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Brightcove maps 2026 AI roadmap &amp; Video Cloud revamp - IT Brief UK</t>
+          <t>Bipartisan bill to tackle social media scam ads introduced in US Senate - Biometric Update</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 10:27:00 GMT</t>
+          <t>Thu, 05 Feb 2026 17:16:00 GMT</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNS0tQTy1fZl9VQkxDMXJhM0Q3Qk0xMzNzWklVTVpfM3VUOXJhTXhCRW1MaERob3VtcVhGWlRmMjIwVUZJNVYtSVg3YUVtUm5fZ3I2MENtVDFRdEY2WEMzN0xRcTQzdTdkOEFZeDRMQVhlT3BneER4V1VpV3hsTHQ4LU55UEw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPa0k5QncxTVJRU1VrTE9WNzBkWEc0M0YwX2dOdThzZmlKaEw5MGEwNkkwMm9CZG93ZkotRzJ4dzJXaW9XRFlERHhPTXpkNElVczhQMnlJRDV3M0g2SFg5WmxZRl96NE03XzU4UmpoUWh4d2prd19lMXJyemdabVpVZ2EwcXpoUWhnSW11MFQ2MHNLeHJCLVZVMkgtT0VUaFIzU2ZzeGxHdmU5Q0c2RXNj?oc=5</t>
         </is>
       </c>
       <c r="F96" t="n">
@@ -3301,330 +3301,30 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Workers worry about AI job loss amid enterprise adoption - CIO Dive</t>
+          <t>Police Probe Social Media Scam After Nurse Loses Money Online - Love FM Belize</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Wed, 04 Feb 2026 20:49:52 GMT</t>
+          <t>Fri, 06 Feb 2026 02:01:04 GMT</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE4xQnU5MG04QzVBcWhmX3NfVWZmanJLLUZCTkszWUZiRE9UckNuTzRRVkpLOXp2U1VONkV3RENvTGYwaUlYVW43LWdnZVFoR29oY2o1U0s3WjZlQjEzQmpHMWtFS2E3ZXRoa2lJbXZqd2hlQVFSek5CR0dR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQZDRLZlotejFPUGkyLVJkcXdCUHVvWm5tc2d4S2psVExlTHhHc29pa2NIUDBCb3JtM242VFRVSnJDWmc0emRxTmd6cFBQZ3ZidXM1TlpHTXZYdGpzWmFkT3RiMjFSLVhhSndybXNfa3RYenY4Uk9oZmwtd1lFQjJaYThTXzVoZ25m?oc=5</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Anthropic president talks debut Super Bowl ad, future of AI and what it means for kids - ABC News</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Wed, 04 Feb 2026 20:48:45 GMT</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQV0tuU0o1OWVsMG1DVlZpUXViakRrdVotWU5tOVdUVFltdk1UVERlUC1mUzJQV1FhUHlTemNSdngwNk9uc1R6NjBZUW5yNzNhZXRScTVmRmlreFFsYUZTX1g1YzJDdGo2ZXAzcEktQkZqcjlOR3RDcGJ0QV9uMmJzUUQ0RDBndVZnWXVjQVNYQ1JXMExvdGxRTlRtQmRyUjdpMlFBdzU4SFlKUdIBrwFBVV95cUxNWEJXb1QzOG1qWGlBLXp3dk1zQnJwYlU5V1U5Zngxb3FNeHFPLVRxNmRaT1pmZjhBWmpITERMcE8xRy1kRzhrbGgxejV0RXpDRVdlZHlQcUZYZFdlbkRSQTZsRW5XYjV4QlE0cm5zcGNwZGktd2pXNGM1WktNNG1QVkstZkRkejRBX2Q4OUxFVXNvVEZRM0FFRlduOWtTU2hfU3dBblc3Uk0xQVRmSThB?oc=5</t>
-        </is>
-      </c>
-      <c r="F98" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Insider_Risk</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>CISA Guidance Emphasizes Insider Threat Readiness - RTO Insider</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Thu, 05 Feb 2026 00:27:09 GMT</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOZTdrdENmRVJPOUloY0tKMEt0N2JQT2hrZDJmQXZ1cWdlU2FhQTBYbm1USk4yT3JNQ3NieXZuZ3g2aVo2VUNPd2k2YTJ4UFpMSGZiR1dFYzU1TWhNbDNVNmQ2VlcxZ1QySDRRblZ2cHc0eHVRTUh2RWM4bzdPZlladUp5eEFwMkxMelowUw?oc=5</t>
-        </is>
-      </c>
-      <c r="F99" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Insider_Risk</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Insider threat cited in $22M Iowa bank fraud case - American Banker</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>Wed, 04 Feb 2026 21:22:00 GMT</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNcUhMQm5HVzBqRjVKY2NoYlBDNnB4aTdJYnpnb1R1d1N6empJSHBHRGVGN0NqUVI1QmFackp2VWVub0hCR1EtQVNZOVJSQ3JyUzBqU0ppTWtyMl9STzd4SDFMdmJrZ1VkQkZBSlExTkpOa3JNRmotWkczQ2hsUW5EdWhDUUdVZHVBVFpjeQ?oc=5</t>
-        </is>
-      </c>
-      <c r="F100" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Insider_Risk</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Allegations of assault and employee misconduct at Macomb supported living facility for people with intellectual disabilities - KHQA</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Thu, 05 Feb 2026 04:25:00 GMT</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMilgJBVV95cUxOUUo1N1lRVXB3VXRlRlFQT3Z0eE5PbUg4TUM0VzZ0ZHJVVDROQ01TVFBLQUx2OHU3WXNEd1R0NTRub0tpMjJJWnZmYUNxRGdhalNWbjNxMGVnd0lzS2FHT0kyREJ6cTk2NjRJZVFwVGpSQXFnbFE2SF9tOE9xQjRFXzFJWTJOeEszV3VRWTV2aTFVSXlOVWtQZFdTSjluem1zQlVBNEp0VHJ2UFdJNGotMEc5aG5hanpXQkdXVXFwUnFMRkhyeDFtOXQtd0diVkRTQVBfUnJ0M1VCMFdMSWM2Y095SDJCZVk3bXBUT21tMEVTek1JOU9tVXJyd01QQTBkMi0yajBGUVpueDV4NXBKYWFna2g5UQ?oc=5</t>
-        </is>
-      </c>
-      <c r="F101" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Fraud_Scam</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Council launches key amnesty to tackle social housing tenancy fraud - Property118</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>Wed, 04 Feb 2026 09:09:47 GMT</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNVFkyOXYzcFVjVExkSVVGeEliZUNWenBKZ3Byd0Z4aTNqbXZhb2NteXlrRWFTbTFhX1p3bVBra3p3d1RneUR2QnhzQU9XTVl4YmNObmVSUnV0RW53QjFENno4MDhBMmZzMGI3MkRSNER4MEdoaEptbGhIVG9jVHdxZmd6eWgtLWloMXZyNjZNODdYcVZUbkRpOEo2Y1c?oc=5</t>
-        </is>
-      </c>
-      <c r="F102" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Fraud_Scam</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Exclusive: US Senators unveil bill to prevent scam ads on social media platforms - Reuters</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>Wed, 04 Feb 2026 11:03:12 GMT</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOYmg5YVltOGVZSGNFajhSam5ET05SX2lqODVKdDRwOG5XbjhZV2x1NnNMX3hvc29VN2FYbVltWWJINWFsSEpfbHl4dlowUW1QdjVBa3RpNHFKQU9EXzBUdUdmZ3FvTGl6ZGd4UmtEMko0MXNSS184SS0yRXFrMFItbUU3eHpOZVlQLWJySTlJMDAtd0pwRXAtamNGOENBeU9hdDVOa0lPNUxMNEZ5RkFyX252S24xZ28?oc=5</t>
-        </is>
-      </c>
-      <c r="F103" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Fraud_Scam</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>'Too good to be true': Warning after counterfeit iPhones sold in social media scam - Lancashire Evening Post</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>Wed, 04 Feb 2026 13:25:00 GMT</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOc2RDcndqdEJuVWp5bVBUbVJDMHBkTUhxOEVmTzdwWE9BRFVEb1RfbnhRbHB1T0dwYm5ESnFQRi1lb2hhNk1ocUUxU3JLay1CV3FzV1ZUQXo1bE1IcnliN2FkdnIwRF9zNnh6NDJ3Yk1McXNzRDQ2cnJXZlhDWDFWdGxpQktlU1NtdE5VSU9SSUZmRGMzdDNTdGRVWFpTV1VZYVdRVjRXUHpRa1R3N0RCNUVn?oc=5</t>
-        </is>
-      </c>
-      <c r="F104" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Fraud_Scam</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Being social media sober is a scam - The University Daily Kansan</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>Wed, 04 Feb 2026 21:14:00 GMT</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOTENaR2pnSmpqTnA1YjBJNHJuLVFJeGk1Z0UyLU5TcDVjSjlSWkVUYjdBNWNvTXR3NDV2SDl0RmJWek9CSTAwQVI3Y3Jtc1V2MktsOWJpX2d2U0xuYk5lVENCVkRMYmJWRWN0cC1KT09aSm85V2I0R1NtUXg3Qjc5X3NaWmlUSUZVNFdITnJLYWEzQldEQzVoZGJndVEwd285VzV5bTBPZFRNRnRPMEliUHJGWmNwUQ?oc=5</t>
-        </is>
-      </c>
-      <c r="F105" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Fraud_Scam</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>”Phishing &amp; Social Engineering are the most Significant Risks for South African organizations” - IT News Africa</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>Wed, 04 Feb 2026 14:00:03 GMT</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNcTd4VGhOaTIwc1VFc0w4Zk5obURrUWYtWngxVG9UTTRuWV9GQmZnU1RIT25oTkd6MGRncXhsWnp6OHBaRTV4LThoMDg1Ul85bzlvQndOeWxNRzZudWlUcE02NXc2V0sxYjIzc0x4QkdwbW9wblNmNUpCYjNlY0VPbmNBUTltV09oWG9vYnJ5akF3TllFbW01eDZVNjhhTS1VNV9IZmlheVFtekV3NmRUczhORmgydW5yVWozcjJkdV9JcTJRX2Zz?oc=5</t>
-        </is>
-      </c>
-      <c r="F106" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Fraud_Scam</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Indiana governor launches group to root out fraud, abuse in federal social safety net programs - Indiana Capital Chronicle</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>Wed, 04 Feb 2026 12:04:15 GMT</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOY0FXOFBLTXh2Nk1sSWlUa0E2c1gxUkM1QUQ5X1ZydUxaVk4tNTRYT2dUcEZfQ0VfeXFQNUpNaUJWaEJKcWtTcTZDSjFDS1NBTmJ3T0lqckhGbXFQWFFlampjMVNVVHJwaHI1SzlxYVBzSVB4R05fTk50UF85NHp0UjIyay0tT1BkLTBNa1dUdHg5ZlZtTlgwRGNWd3NVcDk1YzZ5YmVXTVFnZGtpMDdTQWR6UkQ3cUxqbjZ0bDhDdHBFN0VYYWlsN3hWY0tjaE8xUFV4V1E2eEs?oc=5</t>
-        </is>
-      </c>
-      <c r="F107" t="n">
         <v>1</v>
       </c>
     </row>

--- a/data/daily/topic_feeds_daily.xlsx
+++ b/data/daily/topic_feeds_daily.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F97"/>
+  <dimension ref="A1:F86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,17 +461,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Report of the Cranston Inquiry - GOV.UK</t>
+          <t>Justice That Works: Report of the Scottish Sentencing and Penal Policy Commission - Wired-Gov</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 11:35:23 GMT</t>
+          <t>Fri, 06 Feb 2026 15:05:26 GMT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTFBETG8xdDBhelhEVWRlbXZrUXVyaXNQTlNzNjhGOVRGRWh1Q3EtM2s1UGM3SkNSTS16RVRvcUdoZU84Zktud2VKYXgxVU5Fc2dSQWRHU3NoR01jZGZoY01aaEF6SW1KVUpEWHhybkNJbS1pckljdDJPQw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxNWDVYOVI5S2hSWm1nM2VoVlNLS2pqYUxQUDA3SXQ1cDFtZllkbW1Zd1ItR2x4RWVzVnlRajEtbUNTa1JWelZaUFBwcHBWLXRCS19FS05EMnA5SXY3NWFsaUhqRHNGVHJ0SGRuWmZIcThuS3JPX1ZQMHh5dlZNVXNwbjI2TEpKQldSMHV2YktKQ3diWmdjSGtVekcwVWVqTWkxWGQxYnlVYUNEY192WHdCZ1FpWmhkN2J4cUoxc05PcEJnSDUyVmdYXzlnM043U2x5UkZ2dldYUG9rSlVFbUY3QQ?oc=5</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -491,17 +491,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Quarterly Mixed Migration Update: West Africa, Quarter 4, 2025 - ReliefWeb</t>
+          <t>US Policy in the Middle East in the First Year of Trump 2.0: A Report Card - Middle East Institute</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 12:48:01 GMT</t>
+          <t>Fri, 06 Feb 2026 22:14:06 GMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNa01PLXBYSTI2cGMxR1lxLVNRLTZoODN3VGQ2OHlzY1IzWXBIc3FiMmpJTEYtN3lBNGM1cl9CYmhyMDUzZFFLS3JmOGVnQ1JtUnRQUFVrSkhlTGxheGVLaWU5YTZoT1JSaU1oNFBqdG1yNVJyV2FCaWhpcThCdVNSTDkyOEZsdlMtTm44bl9vWGJSVXc3eGUwRw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOSWprdF9OVEdlZWNRT19MTm04QjZfV1FDUjN3TTMzbFlaOUZ6WVgtcTNBTnlGWG1XRkYweWRVUlB1NnJpc2x3ZjRXUzFZNnFzbEI4YVhrMzN2TXg5bmZ1T1RvT0djTkEyZ280dkZ4QXVHX2FRTFduMER0YUJiOUtnNWxPYUNLT2JSZUJOTElpcDVpSkx0ZFU0UUZXc29FQQ?oc=5</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -521,17 +521,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Why the Bank of England is holding rates despite a weakening economy | Phillip Inman - The Guardian</t>
+          <t>Maternal And Child Nutrition Backslides: WHO Report Reveals - Health Policy Watch</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 13:18:00 GMT</t>
+          <t>Fri, 06 Feb 2026 19:41:22 GMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOWkplWEZRV1d1M0loR1I5b0FKUkNLTm1qQWNsMTkwVzFmUnNhbG5YOGpxV2RKRWlWcE5JQjlOQ29SQm1GNHJrYnVFcG5mbFBESmVIVUxJUF9jbWRUNnNJNkQxVG04V2dWNlZiVGNvc05SaVphNld4bnppWmgwNFlhVWhLaVNzbTRtamdIdnRlaXIzVHFuZTZCbVJYY2N1YXF1VzR3dUZBQzJLUy1pLXMw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE5PRkhmSGNVS2F0VHhnYXdJMWxtVGpSREg5djNoaHdsdHl2UWNjSl9BWVBzLWdmbWxtTHBmT1ZDbXlpQ01ZQ2FlQ0hNLWVydE9qZlVlVkowYnRielhSb1RKcTR6Zk5uU29BSFpBc2hmNDl1MEN4SmpmVg?oc=5</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -551,17 +551,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Government update on 'biggest change in a generation' for Warwickshire councils - Coventry Telegraph</t>
+          <t>Welsh Government Provide Update on Menai Suspension Bridge Work - The Bangor Aye</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 05:17:51 GMT</t>
+          <t>Fri, 06 Feb 2026 14:52:16 GMT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQXzdKUlc2RHRGNGc0anlISnNMbURhcVhiX1Y3Unl3VnplbUswSFZFWF9Cdkk4dlpXMnUwS1N0ZEJ0SThORzNKb0NHUVpGdGlSQkxKOFJJQjhyZHo4Sm42T2x0cmE1VnRBYjU5MmVydTQtVkdqSTNlSEV6VmhRZzNnaHBFaTJUcjgxeFlZaFY2R3g1Y2JIZVVkMHRPSlNVWXJGSzRIdtIBqgFBVV95cUxOU3pZRFdmOU1rekNuZ1JtdndDZmlaakhTTEZ2a0RPZHlHQlJlOHZUazFlc2xYLV9ZbGhZZk9VUnQtS3pZcEFWcDhROUptakVCaFROVEJCV1pSZUtDalAxXzZrZV9VNjd5aGQyNEpIY1R5dkVPRlJ3ckozZWxHazk4OV8xRWZEcTRzVEltMWE0ZE51blE2TEp2Yk5ESHN6bFVvOEc2ZXhmaHoydw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOQW5mTHlZNDJoYld3al9LbV9IREZvMDdnV19Kb1FycjhZTF8xLWRkTnBLMGdLNTJXdmNkZGxOSFpDWHNvcW1jX1RwakZURGRmb3hscWdoQWREZjM4N205cmVmZzNhSmphWW9zZVpBWXpCc1o5UVBNNEtoRnNMZ2hpMzByeGI5U0xmUW11amVwVjBzZ3pzQXlaNQ?oc=5</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -581,17 +581,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Gender Balance on Government Boards – 2024–25 Annual Report - pmc.gov.au</t>
+          <t>Discover Core Update, AI Mode Ads &amp; Crawl Policy – SEO Pulse - Search Engine Journal</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 00:27:18 GMT</t>
+          <t>Fri, 06 Feb 2026 12:58:09 GMT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOeUU1RFhoWEV6UXFlYjVVbGp4RFNreDNRSVNLZGV1TUVyOG45ekNvTGxhYkhVbEU0TVpjR01xY2xXVEM0Wm9WOVlkZTlxcW8zemVCTV9uM09kN1l6MHdIQ1BLNDR3YnVpb3lqYndCVTQtTnQtQ0NwbWFKVG9PUUZCMi1sNUVvQ2dpLWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxORUFnNC1YMXZuTGNMYXdHWmplMzNfSHJ1b0REYnVWZUp4TGV3ZzhwSDQ0MHlBdjRPXzVLSHJKRDZKcUxnbnF0aDRQZDdvYzQxSEpkUTkwSE1HeFhpUFJUcWVjaGhITUtkVG1wV3hlSF8yM2lIY2ZibEVTd0QxSUZ3T1hFY20zLVFaUFZEWU4zOW5wMVdjd3pSR1E0WUxSTHI5?oc=5</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -611,17 +611,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bank of England Monetary Policy Report Press Conference - Reuters Connect</t>
+          <t>International report - Caught between conflict and crisis, Syria faces 'incredibly fragile moment' - RFI</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 13:28:00 GMT</t>
+          <t>Fri, 06 Feb 2026 10:12:57 GMT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxQNGFQajM0ZmkwRFIzdi0yeUM3Q0FXRVJXNDNlUVVBeDdVajc5TzFaZ1BTYWN2cFhoSEd2aWpXVmNBbi12b3lvV0lzQ29VbFkxWWJfWTNKNzY3RnVYYWFValc4MHItZUtGblpwUm5vWHBXWWFXRlFCUHN4MC1nYTlvMWVaRThqYTZzZUw0RDYzaWE0RmlUalpuRW9mMjhfaGlIdGo4T2liMklJWVVnOThGY2NvRmx2NkN4cWNlR1VVa29rMWt4eUVGQzJNLVNFNE5ESGtyMU9TZ3RXQ3lpWDBJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPdl96V0tOdUFfMEY3eXJyMEZ4enFIOTF0enVzWjloeFF2alNkXzdSY3RpaFZ3QmdLSnVxR1BVLTBQajc2bmZVSDB0N05SWWZsN1RKMjJ1aDJRNUtmZEZLRm1tN2FVeW9UNXY5V1g0bjBhQW5ZbjhMdjNDRXpSVzR1dnlIR0UyeTB2SE1INlFTazNGcm1MMGJRWU1BN3FaMG5VMmM5UXhvQUVjUEgteVpBaXMzU1k3UnNObjdfSWc3VTVyWXV0bGZIeTNfeUdxQQ?oc=5</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -631,27 +631,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Current_Affairs</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CEO Innovation Policy Update 02.05.26 - Massachusetts Biotechnology Council</t>
+          <t>Trump signs executive order threatening tariffs for countries trading with Iran - BBC</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 22:22:18 GMT</t>
+          <t>Sat, 07 Feb 2026 01:28:56 GMT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxQTmphcXpjb3BVREItNjduWGdHdG03R1p2a0VKMVB4c2k0M3dsTy1RVzNuaUZDbGhfbVRpbkFCbzFMdmhZNVNVbUtrN2p6OTQySTVwcXEwTnF2YWhlLTNuWG16b1BrX3FEUDdFTldYbWRmaDhUQnpBeTl5Ty1rZW93dWp2NE00dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE84aTZ3SE1iWEJEbWNNZFhMMjdob2hBaUN2bGVqQWx6azRuUE1YdktPX0ktMlVwNzl2X1JreWgtNERCcWN0VzFMdXB1Ul92eS1DOEpCQURpR2d4UdIBX0FVX3lxTE05d1E3NGFURFN3RG1fYVlwckFYLVZnYzVROFM4aE9HZjZfLWlJN01rOVhMS0VZdkh4QzFTRUdwbC1aeGU5TkNuOExScXhxeW4yY0ozYkpqcGtwaG9qd1FF?oc=5</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -661,27 +661,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Current_Affairs</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'Stealth tax on jobs and wages': Damning report slams flexible working as damaging to productivity - GB News</t>
+          <t>US imposes sanctions on ‘shadow fleet’ accused of transporting Iranian oil - Al Jazeera</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 22:33:03 GMT</t>
+          <t>Sat, 07 Feb 2026 01:36:16 GMT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE5xaW9nTUlRZGlobWVPajZEWWlnS29MTTQtUEhQS0YxamgxcklrNHUwUGtOc3paQU1HalVpeVQwU285djJwck9ORF9hVHM0MllJbC1YVW5nS0RpakViMFhnXzV1TWlNSS1GaU5VWUs2VFhKcjFzTG1zUGJvcUM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOQ1ppczJOc0FGTGloTzA1c0QybWotUXgtMGoxeW9UYVpzQkNxRWxObW5iSzJ5M2lEREgtcGsxTWhKS0NEYXJaeGVJTDNtVlM0QlNZVkVoSEE2c0NWRU1qS3JscDFHcEVyN21vQ09lOEtZdTVrQVgzZ0xSekxmc0dzZ2FfVm9HM2c1cDVVckZ3Zl9BX2lFQnNBcHIxcXNmYjU4T0hDN2FMeWlQeHlVMllqZHln0gG3AUFVX3lxTFBjR1l1cmpuczUwcXdnc185LV9XUmR5V0FTbm1nM2pmeUs3RGZRM0Fsb0M5SHdtUUo4Z2NjaDhpSm5SeThZYTF6ZW9BblUwTFVvRGRiNXlGc2FlbTgtWERpbi1UZVBZdFpIdF9PeU5rdXZGSmdGTEZ2bGp6Y0EzZmFLSFM1RGQwVjBCSGVTeU9nUEd0SkR0aVNXck1BTU9uOHNkMUNmZ0RPczZxb2trTy1CdWdoN002UQ?oc=5</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -691,27 +691,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Current_Affairs</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bank of England governor speaks after close vote to hold rates - Reuters</t>
+          <t>EU targets Russian energy, banks, goods and services in latest sanctions package - politico.eu</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 12:57:41 GMT</t>
+          <t>Fri, 06 Feb 2026 14:44:00 GMT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxObUtRb1ZVMUNaV1J3bzMtb0F5OEREYUtMY3NXbjJQbTNDVWxIcTY3cFdveWg2dndjNk81Y0d1YnZ3WVB4eUtBYVJWcjZMcW9xZHZkbjA1Q0VwT3lLc1QxTzlFaWpBVTczMnpUc0ZfS0NLSC0wMWhQcFJtM21LaVdGMUc3NTdvX1VfYlZpeG1GTUFZUEt5UTBpZzlVTE9SaXFkUWRZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNdUx5aUc0Rkl1Z0dPQllNbWdNOHA5RzJvSHFTLUl2WmtZRjY5dW9uaEhpejVmUmIxc3ZqUmYwMGlFSzZiQlp2bDhnN3h0blA5R0JuX01YZ0VwcFVMTjB5Q09MZnVhUVJBMWJ5S2VHNjhDVWJYcEZTWE54bTc3TUFMNEtWbmhMNFpJcDRSN05DdEN2Tm1XYWw3V0ZUbGljbzd2NngyaGpxMTFEVk1MckdHeg?oc=5</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -721,27 +721,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Current_Affairs</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Well-managed EfW can complement circular economy, report says - ENDS Waste &amp; Bioenergy</t>
+          <t>Commission rolls out new Russia sanctions package after delays - Euractiv</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 17:36:24 GMT</t>
+          <t>Fri, 06 Feb 2026 15:07:49 GMT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPSktPNUcxTkhoSHdzQkU4Vmg0Vi1VdHJCN1FiS1pFNlJSYXVGaEFSdTllUmF2TGE2YUxCV29fUWZSTnpienlBSWFVbUN6endycHBaWm94RWNmclY2T1hVWEVMOGtIM1N2YlBLTF84OGxvTjJWSHJheUhrLVp6dVpYUmZ0SzJhWnE5TGVjWklJWGhqcjlhQ0Mza0haVDBjUmlpeDhoX3k4UGs1U0ctbkVB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNcmxfMW5SbkItWVJnLS0yMktHbUI2WEZPdC1KYnc3TVhMMUd3UWY1aHhkTmdRc0d0MWtDOWtELVdCMnNIZWNQSERDWVpZQU5rMnRwRHkxeTlPZGx5cmtCTlFBMUZYYzY4TEpZd29ubkRpaDR6b3ZTaDRHR25MOUNXbjhaalNXcDFhd1I0WGQwMUlYcDNTbTZSUQ?oc=5</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -751,27 +751,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Current_Affairs</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>WEF Report Names AM in its New Supply Chain Policy Blueprint - 3D Printing Industry</t>
+          <t>American taste for champagne goes flat due to tariffs and weaker dollar - This is Money</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 10:42:35 GMT</t>
+          <t>Fri, 06 Feb 2026 21:50:21 GMT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQd21JSkl2cVRpS2ItTFplYUgtMTJ6aTVHUWRiMlNHZ2Q2b0x3TGo3c3k1T0w1d1ZRYVlGRGhpaDZHZVpIa19vQ1hIV3hFSkNoUlFSQkpWbGFIYWJvYUNCSGR3aVlRekloRWZNWk5DMDdBdmllbndoUWxaVmxCNjcwcldhcnRPcF92aWJIV09YX0k5VWhWRkM2aVRjaWpWaUc2Sm1HRDVLMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPZzBtN1pxRXhPMFFNZ1M3QllHTEZwM3FFQjktM29VbWdKaGVPelhrX1g3cGVFYnBPSjYtZ3pITzhydTZCek5Ndm81eHNvWnJzUk1mcmxoQ3FrOFl2NENmQldMRXltb1hIUEZ6R1hhdE9OZkhEclFycUl0S3g3ZXZ4UTBxUlJrV3N6X2ljT0pRb0JJbEtwWHpoVUVxRTlhY18zR0ZIU0pEdzNpWndicHhQNUdYUUhBUjZ6dmJMVFQta9IBxAFBVV95cUxPVWtXMldqc204bXdLb0djQW1LNzhOSl9WNTFDSkhQM2xQTGFKWlc3Nm9NeUdsUWtYc01wcmtpM0Zkc1FtNXRLUjBHYmpMTzRfRk5EZ0oyTjlVX2VWQ0NBRW9nWmFrSU1mWTdBMF90TFdISm0taGp4V3RUTU1uS2tFTWlHRy1MLXM3cjI4alc2UlEwZkd6bnZZNVNxbjhCbVVMLUpkeFBEVXVINnpqWUNhZHVmeXY5aktlR0gzdll4NXlBenRP?oc=5</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -781,27 +781,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Current_Affairs</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US Treasury and IRS Release Proposed 45Z Regulation Update - ResourceWise</t>
+          <t>Mitigating The Risk In Your Supply Chain - Construction Wave</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 20:32:16 GMT</t>
+          <t>Sat, 07 Feb 2026 07:07:07 GMT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQak85MDh6N041c2pDSmdNbjhJaFRRMkRXNEVXZFRETUdWQXdLVU1pN3QweWVOdlpCQW50V2NpSVNxcC1KMDNXemNFM3Y0STBvTWpQZUJPYmx1X2ZLbHhkZ2hlMU9nQXJIekR0RENiWjR0VGpxTVBQZ0E2dGR3enEyZmoxOE5SOEJOWUhRbjh1eWFHaTdsX096ZS1yZEdkN3RyeWR0ZNIBpwFBVV95cUxOS0R2N19lanluODRsWlM3aThJSHVtWmoxQ0tUOEJSalpCbWJHR0FaV2VtWDhMbVBPY3JoamszZzZXQ0VXeUhTaTIybkVIa2hiZWVRS3RUOXlrUDExRU1TbUx4bnhVSnBaLTJ3MGs2dFNkbFl3LUl1SVdWZGFtM0VOV3lnNFpRNXUxY3VBdjh6YUc0akl3QkxQN1ZiUGxEY1hKX2E1Q0tqbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE1oUkxwNlhzcktTSUJEUUE1WWM3S0Q1cWxLdlk1VXNRRUtYcWVYX0otNUNQQ3IzOXM2WVZMTkQzdndpOTVtTE9VYjJaczFhMGd3ckFHZHh4TDVXRGU3X3B6SVJXN1pXR2FwUHVuVlQ5bGRaVHVTNlgxdl91U1I?oc=5</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -821,17 +821,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Maersk fears first loss in a decade after rise in container shipping capacity - Financial Times</t>
+          <t>Visa-sanctions strategy pays off as Angola, Namibia and DRC agree to accept deportees - VisaHQ</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 10:53:54 GMT</t>
+          <t>Sat, 07 Feb 2026 00:14:21 GMT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1fM3hrUW9DWE9DT0d4RVZCaDNXa29tUHVUVTUwLW51WDhnYnZJNXU4OWlXc1JkSHhIRTIwS29oRVpvSEI4Z214QXB3Yl80bW03LWxwWlZpczdjM1F0cFF1YXlHLXBTa1pSSER1eHZ1ZEg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPWGNCTGw5NGktUy1IOGRvTHQxTTdVVGNWQzIxNEU1bWJ3ZmswdzFvWU1HSjBYc0hnOURHVHFOMkhuTDN0X2M0TTBXcTNhaFZ4dnEzLWZyZFpaTjRCcFVJTEtnb0pWN1lLbkQ4MkxYYTE0R1BrU1NZT3pGZlRkV24tczhJVWRtbjZzM3B2VHJaVk5aQU9lNDRIc0xNSjUydDQwWnpNNl9aSko0QlE2TkdpOGJOOGdOYW01QlBSdndmSndmTVl0d0E?oc=5</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -851,17 +851,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Port Vale clash postponed - Doncaster Rovers FC</t>
+          <t>M2i Global ships titanium, gallium in supply chain milestone – ICYMI - Proactive Investors</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 16:35:09 GMT</t>
+          <t>Sat, 07 Feb 2026 05:45:59 GMT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOYTNEVlJVNkV2VGhkUmlFaUlySnE4dHltVno2Qm9LRHgzejhweHBPWi1uZ1Jlbkl3Tm0wUzZscDNsZlhQVjlLQjVDOHQwZ2h0QnJrb2o1c2JUc3NCbmxvY1M0QTA1R2xkLXFkZUVQbVZWTllyVlBqM1NDbnlEZ1ZUY2VOS3VoT1NXSkpMUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxORXNpN2tTNi1DbjM1eGloNFF1SU5TRnVyOFFJMzZKTXBjU3I0X1RWRkMtbFNDWXVxS3p5NHh3dGtLemJqaTR5UWxCNVhvZUUwQmd4VXVPUTBLTjNNOF9qUWdiOHJ2aWFXdVBxZ284Q1NkTUVRY3pCUExZLTFLdXF2Z25XbWw3RDlPbXR0OFJWUnBrMmVqa0s3bEM2b2VpbVRsMTR5WEhocERCRVQ4SG9WS25KeExfcFJKVno0bzd4cEYtSGpiTE02eHhzeWdVUUNlS1NsdQ?oc=5</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -881,17 +881,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kuehne+Nagel opens new Container Freight Station to meet India’s growing trade needs - Kuehne+Nagel</t>
+          <t>Scottish football legend says Port Glasgow Juniors are 'in a fantastic place' - Greenock Telegraph</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 05:45:00 GMT</t>
+          <t>Sat, 07 Feb 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQQ2JsRHBIUDlqdENrTnBOQnV0ZXpXWXdkQ2cxZTZzTDN5MFcwd1ZXX0xOaGVUY0pULXBZcUF5cW95YUdVbm1BdEVPdHM3UUhaVEdmRDM5a2I1ZlRDck9peWdITC1YS2FkRm5hNXBjOWh2eDk3Nm1TS3gtbDAxdzdobmIzSHdSLWt5NGw4S3FvOTc5MG9vb3BDcVV1VXFEVW9jUUFvZkd0RHhTbExnLUxvY3N2SlNHWXFX?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNOGRuaXVrVVAyZDcxXzJkV1hfM0c2QUdNZnBQMUVRMVJiWmNWUXI4bjB2U1NJLXlYNWJOU1NYdTZLaWs2U0MyUXBpTEdlTFpoZXViRTRzQ3RORXhxX2kyd05SN0piX2E1NHhiY1VReUZiOGx3ZjYxT2YwYlo2WGYybC1xTXpaYUc0SkUtbjByRVlmcER2ZDBzY24weGxiNjN0MGJ1QU1IQ0g4bmVwMlctOUFjcGpia1pCSGc?oc=5</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -911,17 +911,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Establishment of the World’s First[1] Global Supply Chain to Introduce the Use of Renewable Plastics in Sony’s High-Performance Products - neste.com</t>
+          <t>Port Tennant storage unit break-in leaves items strewn on road - BBC</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 07:00:00 GMT</t>
+          <t>Fri, 06 Feb 2026 22:55:15 GMT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxNajNwREpaWmxVZFFjOXpBSUJXbVkyQVBoNVVmY3czX25ERmlmc1Q4N0g0d3UtOGxFeGtIc3ZLZXgzQVgxbUVPdTJOaHZYM2tvUV9fai1zTmwzNjhMY3FoVFo0UHpJX2dNYkhaanRxQkRzczVhczlQS2pZUEFzbEhJSFoweTRwaE9GVzZmdHZjQllOQ09MZ2FhNUFCSm05NDhuX2l4NmNYTXQycXZGWXZqbWJTLVJvdFRNRTlZeU8xN21GZXdXb3JYc1BSODZOa3ZMU3kwd3NVU25kMWtOcXJKc1g5TmhGaFdrZmF2TEVCUC0ydw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE9TWm1XdG9YN2FZWGdjc0VvaC0wZi13MVJYaFFGUWtESUZhbmFyLU1oaWpBbUJaQlpUQmpPMlNMdDdsZUlLbjExOUdLMjlkVHdWUzZRa2JmQVcwOTM5?oc=5</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ferry firm's Jersey-Portsmouth freight sailing U-turn welcomed - BBC</t>
+          <t>Port Vale: Jon Brady wants League One strugglers to make Burton game "our day" - BBC</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 15:26:51 GMT</t>
+          <t>Fri, 06 Feb 2026 18:10:13 GMT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE4wTWJtdGFWeWZxNmdhbC1fcS1IZERUdEFzZXhNTndjMlNGWVJlblc4OVFWbC1UU1F3QXc0N1dxNTMzNlJoQ01lbmtBUDExSDRBd2xFMWk2OUIyUdIBX0FVX3lxTE56T2tIN0x3RU1CaHBqMlNhbk1EcVJPNmxyN2VqOElSbkhMTmtmbjdxZzNEb0pGYmVxbTcyMHR1Q3JwMk5zM1h3N2s4SkRjUGJZNDJNa0NJSHJDOGtpalAw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE1ST013amVoYWowTHZiWllTbHdhTFNmWjhrRzdfZmVrVFlWQWw1aHlCNXVFR2w0QUF5TFFaZkJXMTVIbnR5Y085M2NyM2paeWhhMXcxc2ZVejc2eGM1Si1TQzZETWxIY2M?oc=5</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -971,17 +971,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Rob Montgomery: Driving Agility as Supply Chain EVP, Walmart - Supply Chain Digital</t>
+          <t>Port Talbot woman's journey from psychosis to mental health nurse - BBC</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 18:16:08 GMT</t>
+          <t>Fri, 06 Feb 2026 22:53:32 GMT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxPMHQyRUgtdmRfUFo1MmFCWlBXMlJTU2V2X1k5VS02WGJiSDJENkpjOWROaGxpRGN2cGhRQVYwY0RFa1p5a1JVMVdLVGZxZlNmcUQ0akJIcjc5ODJDLW9XT1R2VlNiRGdMS081UXZINDZIaGhxcFQ2a3JtRzB4OVZ3enV4RGNPYWg5eVRN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE9JbUNKMktJUDZFaE95XzctSFJ2R3lkMHMtSUdkbnhEZ2VBNXJBRjFDOEtNS0JvUzlGU1dMb0FEUnlTWFNCUWNqNzIwZGV6dTZuQ2NBc0FwaTM4dw?oc=5</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Can blockchain help track and reduce global supply chain emissions? - Impakter</t>
+          <t>Massive crude oil tanker sails into Dorset port - Dorset Echo</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 22:52:39 GMT</t>
+          <t>Sat, 07 Feb 2026 05:00:00 GMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPSjhvZFlMVXlPUnhoUDlHVVNOOWk4djdXd2RlVGJ6dnhKNDJkb2dfalY5b21LT21ZWTBQNW1Bald6RzRzMkRJSWZHSXl4bHBkVFNnWElEVXpxNWc0TXBhZmxUaThCUjJwR2dJal9OMzE1bDBoMzJld1R0YUpYTm4wYURRaDBzalJsc1RMa0xMTmkzQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPaGctQy04eGR4YUlEVzFHQVhDRnMyUnRhbnNUWE01MF9mV081TVk5NkNNLUh1LWR5QzRDU0xuczJEWnRHbVBCTkt1bUplNmZBenE2TkJ3Z2JWem9rS1dHZ3I3eGRneHpieGJWUU1qczI5bmZWWHc1ZXNUZ29BcTFwZ0x0UDUwcGtYVE9aRm12R2VhU1dUX3BDVTd4TVZPQQ?oc=5</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1031,17 +1031,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>INSIGHT: AMLA’s SPD reveals how it will transform EU compliance – here are the important dates - AML Intelligence</t>
+          <t>Maersk to cut 15% of corporate jobs as tariffs hit 2025 airfreight volumes - Air Cargo News</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 00:12:29 GMT</t>
+          <t>Fri, 06 Feb 2026 16:54:49 GMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOTkJKNUtYTFVfX19tUUZEbzdpQzJQTkhVZ3hkUUlWX1NGS2RvbjlBbmJ5cUJhTzRFb2t4Yndhc3FNM2VVbU9ZaFBCblFpMzVhNGV0WGFwVzJreWZtVXFmczVvN0NKRFVQUlNBODA2SGp2OGZldFFjcy1OdExWdElBajBCQ2JzeENVU0IyUEt5clk4ekVPdkl0ZHFFRnBQTEl0alJHQXNveWQtNVNMenR6MDJrTVlKQ2trS2RmRXg1aU5lWG45Vk9qQjVfSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPZHFlb3RpdVhRSm51MjJTa3NPNmViRUFtQzM5YXFfa0VGb0pBQ3FRWDdYS1BWMUc1RlRaMUMxWmRkTEdpYXhqUDI5ajF6UldVTmZMWVlyNjZHdHliRUZfSkd6eHZBZnkyaVRPWUJyMU9IVmFMTW9sM2ZsLTZqcWRNd0d1WHNuZEpEYkFkSVZRQUhzWHlFTE9NaTVDVmdtWmFzMHlQeC1VYkhkaERhSHNEbzB6aExTNkplOV9PZQ?oc=5</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1061,17 +1061,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Fragmented single market is ‘number one problem’ for EU research - Science|Business</t>
+          <t>EU hikes tariffs on Chinese ceramics to 79% to counter dumping - Reuters</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 17:59:27 GMT</t>
+          <t>Fri, 06 Feb 2026 15:33:47 GMT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOMXZjcGY2RjlLTHVMNEh0ZGJ5dlJZZ3h2MWFRRzJyNm5CbXN0cjFzNkFOMDdWdl9LUGVXeDlrZU9HNlBZVXRrdzVrOEZ2WWJPb3RuSW5MeFRXcV8zOUJtMkpuV0xsa1VZZ3JIWmJSSk5kbWw2WEFDZUlHVENabmJmeDhwaktLTGhqTHFKSGlVTmZuLTR1cV9zY1RBRHRlUVUtT0Jneg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPalM4UnI0YkpVNUU3Vlc5TDJXUUtTLXlmMWYwelRseEVlZnNJMTRlZW40cnFra1EtcTJ3Nl8tNXVsdnhyZkFUU0U4aXFnaGxYLWt0UHJGa1c5eTlrdEFTQUtzM0Z0NlcwM0xPTFZuWWIxV2FzTWVvXzRIMFUwUUNsSGt6VTlYNzBMSW1LcHBlV0ZkWXUzRlpQS2NscnNsMnBON0Q4TlFMZmJvVmFfbkI2NHFWTHRpSHFxVkRLSXd4TE1sWjQ3TEVZ?oc=5</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Are index-based shipping contracts a trap for BCOs? - Splash247</t>
+          <t>Russia Secretly Shipped $2.5 Billion in Cash to Iran to Bypass US Sanctions - UNITED24 Media</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 06:00:09 GMT</t>
+          <t>Fri, 06 Feb 2026 18:27:29 GMT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE5tVG9zN0dpcnJPa3FtYjI3eVRhUnZ2a01SYWxYSU5TbmROWEtnWkZ6dXhEaVR0QkxjOE51THQ1Ti1ERzZSbnE3dk5fRHFSY1k2VDhWcExYSFUxa3A5Z1J2eFlSQjZESzdxU0lfVTlEelBGeE9IWFBGaHBabS1Qdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNRWRXT0IydTBkRDNKZ2ZoSUJHMlpmVnhNbDh0eFdXZlNPUWlFMTNkRzdJVFpGWWJ1MkNlcDdIMEZ2RE9PUmJtcGtKbEZoMGk1d3BON0VUclpXMUtDdjBUcVdKa3I3a041MVI5X3NRc3ZJZHhQcmJHb2I1djlrLW56TUFxQlYzdlBlajZjOUdzV3Y2YUlTNmpOclZQb3otVnA2ZW1KYlJMS3N4QVI3OEx1WTA0VnJCMHJv?oc=5</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1121,17 +1121,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Three African countries agree to UK migrant returns after visa penalty threat - BBC</t>
+          <t>Russia’s Time as a Sporting Pariah May Be Coming to an End - The New York Times</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 03:14:38 GMT</t>
+          <t>Sat, 07 Feb 2026 05:01:06 GMT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE4xRUlsYkQzMnRZdV9ubFZRV01IQUR4NUJLTk9qQ0tHRGpCWE9PcXpEZXhQRWs2U3BGQkxqSTBRUTBEMzl6VnUzZjlxb283dm52b2YybFVpZUtqQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNUzJiLVJOQTZpSk9SdDhnYlRSRGJpUFFIVTFIWVlkRXUwMDUtR2NudWFUSWRLOVdWWk01NDJEcTlpeldWNGo3dFhyaEV0TzJaUHIxd2hkckFRXzlmeXVwZHpPSTAzZF9JNzU4V3h5WHFRSnV1TWdWbzRaZW5wcWJkWmFFYjdxbkFRWHhmVmY2cVNTczQtWk9SWA?oc=5</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Flying through Freight: Scania’s Autonomous Push - Supply Chain Digital</t>
+          <t>Experts say tariffs stall innovative development - China Daily</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 16:21:40 GMT</t>
+          <t>Sat, 07 Feb 2026 01:19:00 GMT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxQdzdFV1h2czgzZnhZS2Q1ZUF0QzVBUHRSQVY5LXNQd3Q5MkgxSmwwOWNpX1Vrcl90czhTNk1JLUYwNnA3M29tcDFfN0lKZUhmTm5SdE1hU19JNldMZ05MM2Q0MnU4bnQxYVN6TTZQQk9zdjAwSy1IVkVRYlAzcG9YbmpndXlPbVdSeWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTFB1aThMX2ctMEVnZEFqMU5ya005dTFuMUtjMEpvR0xpbWtYc2lsUE9XU0lkYWdYR09WTkZTSlgyUUF5VkIxWDlLX0lQVDVjcks3RFEwUDZlOVJxdlUtQTZfeHgxTi03amJWTVJSUVM5cWpXZ3JDSy05MGJGcEJOQQ?oc=5</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Canada unveils auto industry plan in latest pivot away from US - BBC</t>
+          <t>Engineering powerhouses launch North East Data Centre to propel regional supply chain - business-live.co.uk</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 23:07:21 GMT</t>
+          <t>Fri, 06 Feb 2026 16:45:00 GMT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFB3WVM4a2w2MlZoZDhmYTVwdkMydVZRM05zdEV6UGMzWVZSa1JUNWRiVTl1UkxRS0JmcnVlOExsWjlzaW92dExrQVU0Z1U2eVI4YURiZkxsekxyUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOdl82dUp0V2oxb1ZyNVZaUEpGbEVBNjlrelZ5eHk5TnZXMFpZQWZ3bmtGb1ExYVltV3NLZlNYcWRlWjNIa1NibnI2eS1mUHlJSFNIeXdMMmNLNkdMVUtTSmNXMlNUbWd6U2lMSHl6a0pLNkdNVUdtejRDMzJ1M0gwSXJqc0w2dmNMRkFfbV9sTlZ0UGFmcHY0dNIBngFBVV95cUxPZHhOUkxtZHVVV2FWZUhnemZXMzRGREpmUTgtY3BwTTJtempmQmIyUmVfOUJoUTB0bllWMXpCMzNadExlbzlTczluZ3dzbWFZaGxLNmdOQ3pJZTFRWkdfU1NwdEY1Mi1aWG9keVlFVU9Hby1hZGlPNWFZWV9IM2VKRDduRnNSRnVoZ2RLcXlmZTYwYm9GckZKSU1XTUtTQQ?oc=5</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1211,17 +1211,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Gartner: Increasing Employee Retention With Gamification - Supply Chain Digital</t>
+          <t>Dockworkers Disrupt Ports in Italy Protesting Alleged Arms Shipments - The Maritime Executive</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 15:23:54 GMT</t>
+          <t>Sat, 07 Feb 2026 01:12:48 GMT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPNUlpWmdqVTJWWHhaZmgyNEx6T2U0THlpd0FtYUlSQzRkZVA0OHFlQ2lRQVVwODRhZFU3bTlhYUl4ZnVEUGh3SHhCdzBHTTlMeS13dkNNMDdyd0Q1TVVWcWlFdkhYN3YyUGRDenN6U1NrUTZhbERHWDhWWnZqc2JRNmlaVkdqcmUydnJYOHV2Rlowd19scjJmZHln?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQZ3g0ei1VWVNTVkVITHc1UTJHOWtGeWlPRHVHYmh3T3k0VWpwT05zaVNGazB1RnFTOTFpNlpsd2FfbHNBM0x6cFBsdl92Ym53Y1JfdGMtX1B4dkpETEhtUDFiRzFPcGJ2cWVmZ2Z2V24teUZzUm1HN19qczJLX1lhN0Q0N2Q2b3EtbGIyM0NmYU9wRHU3aVBBT0xGdHZ3LUFaaEhnLWVVMGhuXzQ?oc=5</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1241,17 +1241,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Logistics growth driven by smart systems - China Daily</t>
+          <t>Energy Is No Longer an Overhead – It’s a Supply Chain Constraint - Logistics Viewpoints -</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 01:05:00 GMT</t>
+          <t>Fri, 06 Feb 2026 20:40:26 GMT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE5JLVFfSE5sQjQzTVRudm1sYUJBcnRGRm90WDZ6bmVHTzRta1BVQ2dJY3J6S1lnbUdDQ1RhWk1CT0QzdU15Mm52ZGNRMGFxRHZQOWNpRXc5eHpwMW1kaFVxLXRuUmR6Q3lqNmF3Sm9iUGxmbVNDb3YxUnh0M1FsQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPSF8xS1BLNlRWNDczX0NpS05GdFVKeFJkdS1GanNBYldfVVZUNVBEMWs4WFNfX2N0VXU1OC1KTmFmOHEwVUE0dl8xY3BMT3FDQXdLVU05aVJ6cml6dGxxWGVocXpVTWZmUVQ1b0hKVkJieVZHeHFxQnBxSkttc2p1TDZBTjV3YUNUdjRMbHNCVkFFaTdDSm9VTFVPN3FUOW5zclEyb1BHTlU?oc=5</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>E.ON Next cuts EV tariff day rates to boost off-peak savings - Fleet News</t>
+          <t>Mexico’s tariffs on India are a double whammy after US tariffs - Al Jazeera</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 03:00:54 GMT</t>
+          <t>Fri, 06 Feb 2026 08:48:45 GMT</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQZ1dxaDRyeVQ5Qm9NS1daZTd2SE52MnpxdWFwWTREd1JSYi0yYmR4eGh0UnlDS3VERnNWTmdsWEZwaXA3WWZvV0JrQmNIOEdoUzFJdnFQdmFDSU43VHJfdjFHd0ZDdVFEY252di1Yc1BQRC12SENXMDQwSkY5NUprTGU3WUtMb3RjaHlyQlRicGQwcGFDMENF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxONTVYYjRENmRLckFqU2JYNVBqcGFzTy1hYWNpWmtybnF0NnJCMEthOTl4bEx3bWNsaEsteGRxcC1HWWxHblQtbkw3eFI1clR2SHNhMmZWaGZmR01TWV9ONkxNVzlMcUpYRXlySlA1V1BhZ21zUzlNVXVBdzl5U213dGVpd0VBbFpvZWhQWG8wMW9rODY4akFZcERvUlNGbllnR1ByUjR4SdIBrAFBVV95cUxQbXRIazZFNW5fVWNuX19qb0pLWmczYms2dDQ0U01zbWhyNHZaWXdaY28teGlZX1IxdWtYMlh3VHRMUFFUQk1lZVk2NWpTb2lVZklwWnB6aFM5NTBqLUdISmdVTEJBNlowWEZSaUlKZUtRTXlQWWtuazBjaGJGWHpSTy02RlB0b3hZZXgxWDMyTHNsMG80VmIyODhFU0szSDRITklmLS05b2NNZGpI?oc=5</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AD Ports Group to operate Aqaba Multipurpose Port in Jordan - Baird Maritime</t>
+          <t>Neath Port Talbot Council leader wades into Ospreys row with blistering warning to WRU - Swansea Bay News</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 01:55:27 GMT</t>
+          <t>Fri, 06 Feb 2026 20:18:31 GMT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPWnViTXJsVXZsUGZRalE4QVRPYjFpS1lTdHBfZkR0M2RGeGdOR0tENUU3a2YyWDJ6TGYyUEpwRVM5TGhvUUFqbGVFbWdtcEVEd2xPQzJuN0ZlVnVRQzlCZnN2U2lDcm5pS1pORVJBQVVDYklZV2NQTlY1UWN5dFJubmZkY0lwUWNUaDlWODdoSGVPaWVsSGItM1NlNWtDZFctdS1sODRTMNIBtAFBVV95cUxNZVg2eEE5WndVSDBBLU5BOFRVaEFKNTc3aWU5ZlQtMHhQRDBULThoNzdCZHhITHQ5ZGRiNjNuRWxFZThldXBldXZNakYtS2FNaElmNWRvTzhoT1Z0a0RIcGU4OFU1U0xxTmMyWEVxZ1JLQ1poalRSb2NFbmlhR3AxdmpOal9zMjdraXF5X2FKX0hrTG91SmVqd1RiMnVQQ015NmpVMkdQWTVta0Q5cXVsWENDaWM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQc0dpdm5ZLWMzVXg0RVcyeVBXRTltWG1lcFpwRnNvMnZwLUJURzNraW5BZHZMUExQLXBkMWlxZWNiVFVfNWtheUJTRWpmRkJVNFlFV0FtYWFCYUZneU41QUZQVFV3ejhuck1QYzBmRWhDazlvNE9FWUpFRFpfQVVYNFYtWjVBVWRmeWZ0YUJvS2ZmYnRVUS1JbXJxVFlvMUQ3aXpPSVBmLUo5dEZMTUxLQThqZ1Q?oc=5</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1331,17 +1331,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Supply chain chaos becomes aviation's 'new norm' as demand hits records - Reuters</t>
+          <t>Tranmere Rovers Football Club - Tranmere Rovers Football Club</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 05:09:00 GMT</t>
+          <t>Fri, 06 Feb 2026 11:07:28 GMT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOdXdCZ3ljN09qWFJxMVBMLTNXWVExeFlqZG5ubXg1MEwzalZ6Qmp1dkxxUExjeFlRWHNEVTlkVm0wb1lZdmJJQ0ZHWUhnLTFvTExrZWlZT1I2blZ1OWRRRVFZc0FBcHc5UlpkMmV6TkZLVWhKTlRaQW4yS0NHVWs3RTFwR2RSdmk0MUVNZ3o1cEZjNnZ0UE1DN0V0d3VlRDlLcEtoZnRpUXpzMl9lQ3BjWmZxTnVnel8ydm5LNy1PUjNmQmhiOUJv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOc2hyVnlnOThyT296YXdEWEZJZVlleFBNRkdNWGFnMDZWV0FocWQ2R1hlMzRuWDI5dlpHaTA1VGZTeE51UEs0OXNtTFVCVFVnNnhpU09HMGs3cU1SUm1sTkQyMzdKNmswTWxoN1p5SjFLQWZ0UG1xME8tMGlXZDcxZGh4Q3ozX2EyaDQxaTdXZnpJb2NxTXRldmdVRUowQkdJVFdSSmtxZ0htY19BaldUZGJYUjV6YW1v?oc=5</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Cuba open to dialogue with US after Washington tightens sanctions - Anadolu Ajansı</t>
+          <t>In Trump’s war on global justice, court staff and U.N. face terrorist‑grade sanctions - Reuters</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 05:32:58 GMT</t>
+          <t>Fri, 06 Feb 2026 11:00:46 GMT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQdk5Ec1FTeUpmZ3Bra2dGVE52aUsxeHltQjJGakFmNGt1dDBWb3hXUmNsYnJPMjAzSTJrVmViNndTS1c2RldoR2FaMDQ2bWZxSVRwUkJEd0lvM2xPaEpnU2tjcS0wRVA3bVNLOFE1R2hTZHBCWmFEbmVhRDlqOUZDNk1icnVvTklqUEd6OFd3X004WXp4OXBDUnkxNlN0dHFfZFAzbEhDajU2Q2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPejQteDljMkdfXzk2bldndW5tZW5Rdi1GSVpzZ0ZLelhaa2puMmlMLVpQNDV4V0tud2djd0w2MFNtUVZpWi1VSWFaZHFHa25JMzhxRkNGcndXZU1GSzctNjVOaVhVcGw1WkZ6NGx4SThrTTBSaU1qTlFOTUpiV3VtNVZlZlhmMWpKZThpcVU3MGpnNWFQNFQ2Sk5jZG9XZVNxMEd0Yl9FelVDWVlGbGEtUG5fTzNHLUNoZklyajZR?oc=5</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1391,17 +1391,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Andreas Nyman Secures Aerospace Logistics at Kuehne+Nagel - Supply Chain Digital</t>
+          <t>One-minute clearance: Yunnan’s Mohan railway port showcases smart border for Spring-Festival peak - VisaHQ</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 14:08:53 GMT</t>
+          <t>Fri, 06 Feb 2026 20:10:52 GMT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNWm5ZVmxYb0hWeXpHYlcwZDFCcHhwc1B4SEg0TXJ6OWF6WC1qTU5SSEdQbll4cjBJM0s2bXhZc01CUjI3Wm9PZ2RLdHpuZ0FsYkRRNHY1TldpelloeEZaTkMwMXE1Y29GYWpWeDhJMU5tVWxyRlVFTEREaEM3VW13NTNFZ0tndEtYQ0xta0pETXFDNUk0OE9z?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxQbW9Gb2RlNGN4Qi1NQ1lRU2RmMXMxUXRpTmdCOW5LWFM4MThUZFd3elh1amtFbGZIWlVtNjRVT2JuOGlJS0NaZGhWVWw0VkdWRXBab0p1TnI4ejFxdHF2WHhCa2w4VkhkdGpoajg5RXRnbGJOVjRwYjIyX3BaRy1rX3pfUWRtMTVGMlVObC0zUDlMWHRXQ2NuV0pRVFdtQnRRbktTdHNHYmtjam5xcGZkeFZTZXpwNHZFY1pmbDRvLVBPcU5ycUpaZ0sxYmJXSFV3VS10TA?oc=5</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1421,17 +1421,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cargo ship runs aground near Sweden's Varberg Port - Baird Maritime</t>
+          <t>The Act Unpacked: Fundamentals of compliance under India’s Digital Personal Data Protection Act - IAPP</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 04:35:23 GMT</t>
+          <t>Fri, 06 Feb 2026 21:26:30 GMT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNOGtIT3Z6MTFDR2V3VzBGSXc0UDJuVlNGaHk4WkdGeVIwblpqdEVVY215U1dILXRBRThLaGhRSDl1M3RTalZ1WkktMFJXWVlKMEJTcno2N3JTR0FIRHNWVm90M2xqa2EyZUJ0ZXVkZ2lISDg0TGdJempNSjNMZHhFcGRmVzk5NFE4aGZYU29pa2lxeklOeXJPTjNPLWdZblkyNV91bE1TdGJOV0ND0gG6AUFVX3lxTFBFeHBSQktId3lZVkZUOTNZVGVORXotVUhFR2lNcHplN0szWVlhZjEwOEtOVzY2Sk9tQXI1ekRfeThycGprQUVCRVhuaVVQYzN1cWVucGxod2p6S0Frb2sxQlFYUTVjeFhUS2M4b002LUhZSW1wLVdaaUxZTkNYeFNZVDluamYwVDBhOEpPU21hSTNxOHRRczFDNVI3NnhvT3pJai1JVnBjR1lUbTZuM05vSFhCMnlaUUM1QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNZG5MSDhBRmpzczRjbkh2b1F3SFljbGl3VlEzMkFnYnZkNTJ4VTI4bkpuZmtSV3lqbTRiV3d6YWFmdnJTVS1sVklTcGM2U2NzQXBIV0pQWU9UZEYxQW15VEE5SWpLNGlfVXdqbWR3QzFaVU9lVXkxeHU3dGxYRTZRWGU1djh3c3VBQkx3WnduTlZpaElqM1ZYYzNtTEdJOGpybEZkbS1XZElzMWR6Z3BKd1hZcTFmNXl4b1d6VmRXd3hyWmxzOXB3?oc=5</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1451,17 +1451,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Trump's trade war creating economic 'mirage' with GDP forecasts, freight market disconnected: Shipping expert - CNBC</t>
+          <t>Teeny tots from Port Glasgow are this week's Scoop winners - Greenock Telegraph</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 19:35:35 GMT</t>
+          <t>Sat, 07 Feb 2026 06:30:00 GMT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNX3R0RXFmcDZBUlBFVVN3aFpuLTZMc3BCTUpZWW8yVFpyLTlTVjZZUUhvS2hfS0l6aWRLTDFtWGRiZnB2cS11QlJzLXU1akdDZEgtSTB4bG5WUUNRUllWWmhRMmNhZFpRSUlWUVpuUi1PM21YZkNUYlVYY0piUFBISVYwdXZZSTFLMGhoY3kwUXBqWVZfZ0xURnJGZExwb2hLTkxJLVlTUVM5Wlc30gGyAUFVX3lxTE83R1psdTE1QnVCYm9qT1lMaE81aFlLUFlvN1JENkg0VG5zSEYwRlEtcWh6aVJJeldnSVN0eWVQZWdWWmhNMHhFRVN3eDBKZVZxblppd0NhaFhoajZ4Y2VxTHlUZ0k1YlpQbnNzRVZodWQ4T3ZFcW80QlBaejlpdFlsbUpGTjZvNTgycElXdmZKVHl1N3ktR3cxQ3pXaGJrNERDVzFiY0owUFBUb0cwekF1N1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPWFVpUlpsSkJRdEJlbUI3Tzlwc19WZjYxSHoyQW9fWE5vYWQyZFkzRFdVOTBzQjh0UWk1QjJVOGYtODJxWVIwcS1uN01FNGtJY25IcHJzWWQtbTMwVWZRQ3lLVnFzZDFqcEhqcTNoMFlma05WVmhOVjk1WGpFQnRXOGU4M0JNQ3dUT1pIMUNpWUJJWm52TDhMWnNYaUkxQWp0OXo3WWlTVlFyODZMYjcyTzEwai14UQ?oc=5</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Supply Chain Disruptions - Robin J Brooks | Substack</t>
+          <t>Medical Device Manufacturers Redefine Quality Amid Digital, Regulatory and Supply Chain Pressures - Quality Magazine</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 06:00:54 GMT</t>
+          <t>Sat, 07 Feb 2026 05:00:00 GMT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE1uMHpMbTExNUdTaHZHMGptQUYySFRqTGJmZkxtRDVIdlJRLU5aUU55djBYblMyY1l3X1VhclhGX0xuNmZ6UnZUVjdaTG5YNHhQRHRPVC1XTHd5QlFkSlZuN1BMWVp5ekVQVXMxMQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxQV2xaNWFJZmR0NW1vOG83ckI4T0ZQYlFtOGJlQnZnMVg5aXF6TFZLVGNIY3dCQzRPZjdVU1VoQ0RIMkJNOWpQR0N4bWdDZjhoS1NFYzBaY0dXb0haNHBkdnJYUldiX0RIb0l3RzRETzN2YVBISGY5UmRSWTg2UkcyRmVNLWNwUTU4elUyQVZZOFZHUGpHZGZKRGJFc3haN1JzYTRNcW40azh5YzBYdjZRbkluSkNwdHJMaldDV0ZBS1N6eU5Ob3ZsV0R4MmF4Q1Z1aWY4LQ?oc=5</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1511,17 +1511,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hostage families call for urgent clarity over PM’s Hamas sanctions pledge - Jewish News</t>
+          <t>Did ‘America First’ tariffs work? - Brookings</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 16:31:00 GMT</t>
+          <t>Fri, 06 Feb 2026 21:51:12 GMT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNc01yUUFiLWRDYjdqek5XOVB1NmNCUHZQck9sNzEtTTM0ZWRzcUV3ZTRoU3RHdi1CMFVjbWtoOExQODk0dlFkcEcxYTBYWTNxbkppaVJJTWtSNHNyU0tfTDIyMTc0eVVpci1wREY3dThiYUNHOGp2MEtnOEplTmRxNmNramNQY0xFakZLbTc5V2w0QWZMVEQ1WktDSXBvZHhrMTRpV9IBqgFBVV95cUxPNlRnQkdZNTVTcDZnLVVBN1piZC1jZ1MzSWlaV0ZqelE0aS0weXQ2LVd0eWxQSjJmVHNoeFlQSUd4ekNBcWlMRlRRZmxuMk5zekxoRVFUT0czYU5JMk83QWpYTmJkRlAyQzVkSDlmRUpSWWVkYzRjMWNHZkVyMlU2MzU5bWxhelNNR3ZYeVBuWDFCcXRLMXpPQ0QwSkhxSVEwVmwwdHVhTGtodw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTFB5N3JlNXM1clBYR0daZENSSUpMd0ItUDliYjVuMW1Rcl9ES1JDZElDbC1VQlR3aW11OEtvZmJ2ajhLNUxUMDJMeFM1RHFqNVBma2tHX0JIQnVsWmxXT1pxWXF3a2V4alNoQjkyT0JQenJjbnBj?oc=5</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1541,17 +1541,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Freight train carrying liquid propane derails in Connecticut - Yahoo News UK</t>
+          <t>News: #UK sanctions six individuals over #Sudan war atrocities, mercenary recruitment Mekelle - #Britain has imposed sanctions on six individuals accused of committing atrocities during Sudan’s ongoing war or of fueling the conflict through the recruitment of - Facebook</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 23:57:43 GMT</t>
+          <t>Sat, 07 Feb 2026 05:30:03 GMT</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxPYUU4QWRad2lrOUl1SnpXek9Fc2lhdnRUWHJGYzF4SkROd0FxRm1McXVMUnB2dVdlRjFjdnNCcXZOdW1feV90MHloZ2xLY1p3RHMtLUFfWWhLa0RZR0NNZmNqMTNmZllGbEtnLTdYcS1DS0U1ZWt0cUlqbjBsTG85eW5MWmI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxQQkpwNXBPcDdfWk0tYk9VV25UYlgwcTBNUXpHWXV3Ul9RVjNNR2xXaUR5YWpZU3JQOTFBMEk1ejJmZEJTX3NrUU5Xa09EOEZkYU1Zclo2NjNTMExiTVBZVEJ0Rko1eFk0Q1Y4ZjFlLWt1OVQ0Yk1pU3RHdGxFSzFXeHpGRnN0d0k3VGhTRnVCZk5wUlU4eEFsOTNXQ3ZaUVFWRVptd1p5UFpZXzZEYVV6b1hJeXUwV21tUHZGdWYwU3p2RWJtZFM2R0J3cXp1aHVwMHg5RXBOck5NSjRFTmpXTQ?oc=5</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Panama port ruling threatens judicial integrity - China Daily - Global Edition</t>
+          <t>Three African countries agree to UK migrant returns after visa penalty threat - BBC</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 01:58:55 GMT</t>
+          <t>Fri, 06 Feb 2026 11:00:06 GMT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxNWmp1LUhzelUyYnFvaVdjNUc3WncyTWtWREFDWThFc05LNTlRSFJraU1NVTFQYUNSWGYwZmc2cXZRcnBkVlgycDRJekExRTh4bWp4d0dIUER6OGpuVjZDeVFpbXBrby1YRmdCN3VWY25pUmQ3RG02M1dSZzVFMDNUWEFn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE4xRUlsYkQzMnRZdV9ubFZRV01IQUR4NUJLTk9qQ0tHRGpCWE9PcXpEZXhQRWs2U3BGQkxqSTBRUTBEMzl6VnUzZjlxb283dm52b2YybFVpZUtqQQ?oc=5</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -1591,27 +1591,27 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>UK imposes sanctions on senior Sudanese army commander and five others over war atrocities - thenationalnews.com</t>
+          <t>Minns invokes special powers for NSW police to restrict protests during Israeli president’s visit - The Guardian</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 06:11:15 GMT</t>
+          <t>Sat, 07 Feb 2026 05:33:41 GMT</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxPLWJuMXJiUTJRTjdyT05aamR5TDZUZFZJZ2kwdy10Y2ZMTEhWcGppcTNkMTBJRDBzVG43WDdJc1ZYS2hNSDNvRjhzRC1aZnJlN09kS21ST1JZcUt6TDRpRjhDUnVXUm5XU0J4czJPMGxmeXMwWnFRWXlkaTlFSFdXLTRyUGhuWW5SUmhuVTRCZC1YbVg0YnNKSFF0ZXpKT2RlTEtGeUE1OFlrLVpYSURFN3hJMHdYb2NrN0pUWG9COGZWYWp4c1FjZlpjUUV5UktNZFNVYW9RU21zNDl4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOTDZhdUwzZDFOQ2pVTkNtYXBfRUhtUlhleEhQa2dQeUotX2JKOUEyVUFKNk9QVzV5UTRPcDRpQnhFTlpaWklFRndPX1JQUE5YcHBhUXpPVXdwbU5XTkI5alNsQmpwSU5paG8xMjdrUGRBejFyeThVeWdhVi1WblRVY0h6WFMxOUxWVlBuTV9CQU80ejJvMS1RX0R5c1VMZDB6dUl4dGp5M01mbUwxS1l6QXJoWWtXem5YSVpHR2NLbW0wUS0yMm9rSFNR?oc=5</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1621,27 +1621,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Cash Awards Strengthen Offshore Wind Supply Chain - Maritime Fairtrade</t>
+          <t>Police seek man over UDA banner display at Apprentice Boys' Relief of Derry demonstration - Derry Now</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 00:11:58 GMT</t>
+          <t>Fri, 06 Feb 2026 21:00:00 GMT</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQUWpNQUdVQlFJRE1qNlR3YmNSby1aQlJTOW9jZno2cUhwZWpRRFVhNF9yeTdSTW42MG5lbjkxcFFNWEhTaHNoNGY4WUtyV3RFa2h5Vl92cUc3b1BzeG9vWjR4X014bV9yNFlYSmZhejNzTXNSX1ZQb1NZbDd4eGp3bVRnb00xa28?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxOQTFveTdyN1F3alVXTmlUQ0ZLZW5CTDd6NFd1a1dxVDc1bmFzR3VnbGN3d2RLZlVZRnBQQ2dVTml0eWxFdl9mS1JJOG1Ea1NMd08xWUM1blhSY1llaGJfWHpoYnZJRXQ0SGJNZmVxZ093eFJhQXlmNmpydFI5UVc1bHZWVEJ2eUdHRWtDUmhGblpSclhLTXVrNnNGRW95Um8yVWlrdTgwS3dQcGhQQmFJdDI2WjdkVXlEOUNWUVl5VHhUdVBoNEdQSVR4eHJIaUZVYUpsRldxT0Fhb0EzbFln?oc=5</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1651,27 +1651,27 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Shifting bond markets: Resilience amid fragmentation - S&amp;P Global</t>
+          <t>Teen threatens Indiana school over protest, then pens apology, police say - IndyStar</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 17:58:34 GMT</t>
+          <t>Fri, 06 Feb 2026 21:59:00 GMT</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgJBVV95cUxPM1NkYVJwMmhpaHR2eTlEbFZ6TUpoc0pRVTVhYkQtODN3alZ3YnhkQklBeW92dGRGT2E0eVlNYzJ6bGhnTTNXUkdNZThvZGVuOU1qUFF6V25UQXNwNm0zODFRSDF4ZXF6VzlIS29ZSmwzLWJOV3VsSHF3bk1rUDhweEFtOXpmdzU0S2FRNDB4SF9UY2xuY1NGdWx3OUlIclZNQXdna3JfVlUyb0lXUVFTX3hCUVl3VFFhQTNhWUx5SVlfdVllQzZ1ZktFUFZEaGNXU242cFFablVuM0ZNNVFWejRnUVlTaFZhTkRocnF5dEV3QUd4Rm9PeGZTV0JkNnV6UXFESEcyZHl1dUNIOUVvRUpLMFNQdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxOZVFuOU5hdkpfTzdtM2NZV19FVkRNelVGREZfWlNOa01fellOU1phR1d2NWp4QkdCREExRG5JUE1udXFRV1pDVFpOeDMyNEtfZ0VHNWE0dU1LZ3NjWEFCYjEzb0NRT2lPeFR1b25Yc0pvOWJvcGVWY1M4eGRQOWdkS3hqTjZWZ2w1M00zMDJma19XZm5vSERUOFgybFVfRGFDckNyekljS1hCdWNOWkdWRVpIOF9yclYyR2VocnZfOVZlUC1SbVNaZHN5MjgwYTNLUC0tQXNnLXo4V3JfcC1VVnBkc0tta21xVVpmVVlkaTU4dl93QkRYMQ?oc=5</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1681,27 +1681,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>EU renews efforts to advance US tariff deal after Trump reverses threats - Supply Chain Dive</t>
+          <t>Fargo Police seek 3 suspects from Downtown protest incident - Valley News Live</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 19:12:16 GMT</t>
+          <t>Fri, 06 Feb 2026 23:06:00 GMT</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxOb3J3ZHhZMHVZLXBUR2NxRlJBSkVQQ0Q3MlNPZjZBNmpnclZhZG1SUUVCa1VuYl82WUIxekhYQkVjaHo0S1lQMi1UeUw2b1VqLWdBRzIwd25xaURDT25GNUdlMmdkQVlMR0RreTFhUU9kNjhRbXFPSTdoV0lFQ24ta3ByWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPT2JoUEdYdmRwdXNsemhjTW1WMVh0WnZ5bnZYUVROemgwMTNheF83RU5kTFBsLVhNemRLOUl0VUJxbFJSWGU1SEJlNmNTMnRvMWVwTnJRUWxWSVo5MDRkZHNYWjFYMlFmOU9MS0l0Yy1mS3VYV2hCeklsYVREbkxYVDF6WU1IQ1N2UGV4Q2dSd1dhMkdCVnZOVUl0cXVaUdIBsgFBVV95cUxPYnVtYlhIV3Q5MWQ3VXN3NWdYUWc2NkhwTzZoTW5iX3pjSHoyOWY3T0VnWDZLZk5jWndlQl9Fb2lZUS1sRkxXWmo1RXkwVnhoSk5FdmE0bGtWeDNkdjg3QUx3Ukk5REpXTVV0RjNCTmk5ZnMxZGxzZ09PcV9rYklWR1lOdEd4Qnl2RnBsd3dZRWFSU2xENUtlZEpwTWhXQ0dja2NkczNtUkJYRmRncndNdlN3?oc=5</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1711,27 +1711,27 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Polish border-guard IT failure slows passenger and freight flows on Ukrainian frontier - VisaHQ</t>
+          <t>Terror strikes capital for second time in less than three months - Dawn</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 22:53:50 GMT</t>
+          <t>Sat, 07 Feb 2026 00:29:21 GMT</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQSTV5WF90S0lEZXlobno5b0YzLS1nUElvMXVmNFFsVkp0SGpvWHdGN09Iak95VWFuYldyaXg3ZW83bDBWTzk1VDlIemU1WmgzWThkU213WUg4Y1lUMHY3MjJhSFhOc1JfVnJKcGtNNU1hUUZBNS1KVFVCa2t3emNfX245LWw5d1VaRmt3WUhxdHRVdGk4V2pQcVQtdDg4bHhiRjN4VEkyX2s5X2VkTVREZTRFdldwUVNkQW9lUVZueDZQV0RJdl9BZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiSEFVX3lxTE1OUHo0eXNCbWJQb29mamdNSXBlaG5MMWxqVHB1SDZzbkNENEJrN2x1Vkg3eEdEU1Q5MjI1QUpNWEN1YzNfQS1MY9IBTkFVX3lxTE1fVjdCTDRzRm9VLWpfNWJBT3Z5aWRFTXRqMGUwUnBhSThYWTVqNUMtdTZFTlh6WWxLa3lIc3ZaMEJQU2dpR2dMcDU3MHBuUQ?oc=5</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1741,27 +1741,27 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sanctions Can’t Solve the Israeli Settlement Problem - The Century Foundation</t>
+          <t>Austinites demand police, city leaders do more to resist ICE - KUT</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 19:00:00 GMT</t>
+          <t>Fri, 06 Feb 2026 17:06:00 GMT</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQNEE5dVlHTkpyVHl3QzJ2TTQxYWt4Q0o4Tzl1UHJqVWkyeDhGQXM2VVQxQmp1cm1jeUo1dXJoc1lNVDlJZWNGcnoyOWtqVE5UeThIbzk0ZGlIQzF3cVhWa1d1bFp5SGtpVU5ySDd6TnVzbFZyZXRYbEUxMzBldUF5dElNRjl0RG5oNDhDdUpONDY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOa0dnT0VaamhPZVJjQjVYZm0xN05YQkdpMGJDeklMRlVScG95Z0lYUGJQR21OT3dkOENZRlphbklqdUI2QXJyRVhaVi1ReHktQ2ZpSHZQMHdQdXR3X2lLb1lnSVdGeEZxQnctREpOcFNaZlRwYm1sX29wcUpzSnZZdHhtbTJNcm55OE9YUzdrMzY2NGZEdGN6RU9uMFMtbndlanFF?oc=5</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1771,27 +1771,27 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Argentina Says It Signed US Trade Deal With Trump - bloomberg.com</t>
+          <t>Ninth pay scale: Police use water cannon, tear gas to disperse protesters - The Daily Star</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 21:34:50 GMT</t>
+          <t>Fri, 06 Feb 2026 22:38:58 GMT</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPNU11Z180cm5YOUxGSUxiRFFfYmJfeGVJcDVMV1M1U0I0cVdyTDRuV1A5emRsUTY5MkxxMTdoOGFKcUZyUUMzZVdjNy1QUzZIMFpiRWRfOVZUMFpGOE1XM2c3VlhoVVpPeU14aVRRc3BmdFBVYkNySGpIYjN6Wmx2dTlkRGFROUMwSTAyN2k5OW1BeFBWSnhhcnpWcUlEMDY5VnZyMU1XRUY3ekl5RzZpUWV5cWpFZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQUFRSOHdzMkxieW5RRHJYeWdnNldxZWdRMV95TTZ1bXRkQTR1S05Na2VjVUE3TjhKTUtaZTRBM2NDZEtFOEsyZVBWM1d4RTZ2cjFNYlRlZ2hpeXBxRXgtUkdNQ2t1SGdFX2VlYkhid2xxbjBPdzZlVERPZmxTS21oYmpGLW5ILUlDVlBvQ25pb29fb3FhMEZZMEZmc0hkY2lOV21qeUNSYVdfeFBxaTFnNEdGcS1iS09faDJJVVl5bEpsZ1Bp?oc=5</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1801,27 +1801,27 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spotlight: Al-Futtaim Logistics - Aviation Week Network</t>
+          <t>Europe’s Style Forecast for 2026: Frugal Chic, Slow Fashion, AI, and a Wave of Individuality - strandmagazine.co.uk</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 16:42:50 GMT</t>
+          <t>Fri, 06 Feb 2026 21:30:35 GMT</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE1lR19aX0t5MEk0S1RvazBuMm1CVi1CSGVXUWI3eWN3RFFudVd6dV82SG0xbk5tSEhJb19fWWJwLWlZYjJqQVZrTVRERnp6NEJpaUROcnRLMjF4VVh0NFhzc2JPa1VzRWg1TUtxejdoWEZ0ZXozY3ZlZEV4X0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPTGEzYWh3aHdaZTJXNEZ1Y0ZYR2U4Y3RJeTNDbmtEcUowa09xdjd3M1VZNENsUUNjMmdocVBYdHg4RW9SbjB6TXNLNHByT3lpUjJPLVpNOEJ4U0t3Ym5UMDJfX2hFaDZjMnM1R1l4Wk81UGJ5V1NvMzh0MW9sWXF5R0dDMU53M05lUElSWEdRUnFQNkdzeDZ4SnJkLVZNNEpxU2ZWNVZPWjhFTHRTVmdmTlhEdVBpUjBuM2RXcFJoOTZEQVM5YmdjejZMc20tdw?oc=5</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -1831,27 +1831,27 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Pension firms look to sell stake in owner of Southampton port - Daily Echo</t>
+          <t>Amazon shares fall as it joins Big Tech AI spending spree - BBC</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 16:36:00 GMT</t>
+          <t>Fri, 06 Feb 2026 15:11:52 GMT</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOVWUwQ0lTUS1ETXhudFh2aGcxTEViZG1GZVd6SUNYM1d2OWJlNXdVX2lpUllwRUN1eFdGX0JBcFk0emZUeWdSU0gwN2hKcm1YamIwbHdSdHpWcHhoRnVvdkNzMFRCampvMlRIbm92R0xxOEN2WmdXRnpzdHFSLU5XbTRiRWMxSDBiVENpUEppZWJZeTF1ZTVieXU3THJDZGhG?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1wZzJieWpQdW1JZ1ZfaGEyQkUtS3ZjUi1NOHZCY1ZMTXJZMFU3Ym4wUG0zaDhuYmsxSGNBbFpSbUszRW1HUUhwRkJZc2VDc0hpN2FaSFlfM015dw?oc=5</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -1861,27 +1861,27 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Hydrogen Technologies in Port Polska's Investment Plans - Fuel Cells Works</t>
+          <t>Technology - haileybury.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 15:25:00 GMT</t>
+          <t>Fri, 06 Feb 2026 10:12:40 GMT</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPVFNQWUVyYzdLeUMzc1lXYWpHSFo3M1l5UFc4OE1PRW5rTXNheHcwUmtBNE9iQzcwMmlCbVFMU3dhVWRHMjZnWEVGcWNsQVhzRjZKR2k1anpxWWR5b1o4ZDg5c3o4VmRGLWRiLXFxQWZPb3VtRHM3NzNpU2hLRDktWEU3VWliWG1Peko3YndIYmlxTks5RDktdHRLYThZZmhobFRiVHlEVUM2cE5uajBVQg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFBzSHYySnd2eG9Pel9ZMjBmZjZObTM1cTVXZDEzY0RnQjFfc0ZrQW1vcUduRGdTTW1IZWFuaEVlWkxEY2t0YUViMU9PblZOZ1kxTGpYcnFoR0ZRaUk?oc=5</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -1891,27 +1891,27 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Future Prospects for the Port of Churchill on Canada’s Hudson Bay - The Maritime Executive</t>
+          <t>The Blake Brief: AI and Earth Observation: A New Lens on Our Planet - Wilson Sonsini</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 20:54:00 GMT</t>
+          <t>Sat, 07 Feb 2026 01:49:01 GMT</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNWXJnVjg1eWFwR1V2OVg1d1M4QkJ6elRDeVl4ZmJWZ04xMzRoemxtcmI5SjRxWGY2aDFCLVIzUjhXa1NhQUtuT3NqQVVGYmdRbEtMRzZ4Z2UyTDdtdHh0YVU2Z2pvb3lGUk1fVTJtN1JialhoTnhfNXNlV0xlSEI0c0RzZTk3djNidHpCX2Z0T1ZRelA0d3ZWSlpIc3M3dDNaU3FYX2VVeXcxeHM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQMEFlNWx2Y2JDRm9aWGhBTkhwWUhYZWRYN0RpVV9KS0FmTC1kUXVHc0pwdlJfSHpFSVdHOWhGVDM0OUVzVEo3LTQweVZtV2d1VXdYOFY5ZTBFNDRMc3pYQUJJWnZKWTduSndJMGVBUUY5aHNzUmZlSHhfSUZubmxXYlRqaXptaFlZaGI1T2ZablJnYzl0M1pKQUUzQmNGSWw3b2g1cnptTWhyb0hLUHllWDhOSU1VaFF5cFR6RkloUzVmMHdoeVE?oc=5</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -1921,27 +1921,27 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Mitsubishi Motors Incurs Loss in April-Dec. on U.S. Tariffs - nippon.com</t>
+          <t>Looking ahead - AI and business integration - New Electronics</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 03:28:01 GMT</t>
+          <t>Fri, 06 Feb 2026 14:33:28 GMT</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE1kNmtmUlRfc2UxeDlnNDl3TUFuOWhST09MQnJ3Yk1lOGZUSFpPNlpNY3VvNEcySWdqZmUweEtlX3hsZDBPbUpObHV4N0gtVnZIQ1YtUUVYNndVeGxr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOTGMxTU5OMkhDWDh4ZDZ3a3NtQ1BhYm5tWE9nLXgydWJoSHZpQmR6OE83bXpGTk05TDV2LUZwanpOWGlURVBGYm5zU2ZvOXBVV0R0U1g0dXJfMzFiZnFKbHZKRm13VDVvRlF5YktMOGFHR0E0WU9jamxpVXB5cWdPSlFINlZwWDdkRDhTV19kTHlhckxGZmc?oc=5</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -1951,27 +1951,27 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Demonstrators and police still in deadlock over Israeli president protest plans - SBS Australia</t>
+          <t>New study uses Neanderthals to demonstrate gap between generative AI and scholarly knowledge - Phys.org</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 03:56:35 GMT</t>
+          <t>Fri, 06 Feb 2026 20:40:01 GMT</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNN1c4b3dIaUswNGRvTk81c1Vvc2hvQkVfSjBEdUg4VjBUVS11M3ZSVXlGR1JoNXBuM1hFbzkwdWY3VHg0ei1YemhtNk52QmVPOGVYWXdNT2g4b21BRVBmbnVsMm5iV3Jua1FBY3VEb2tXRFZZN0pxdlpiTU44QUdnQkUzLVZ6RDMxam0zZmVRNWs3bnZQZ1dRMzI1WnM5UFhSWnUtNVpkN0lORGJkRFJsTFRCUzlzRDRmNjhJSHVkOTlORDNKcWpN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxOSXBscEFqU040cGdWU2dERjI1c3BVS056NnhCenp6b0VveXRYSmVVeGNTTGxiWU13YU9CZERybnE4VS1GWG5ZVXJoNS12dVJ0dHY4NW5tR3l2ZU1qdHdJUDFrbHJmVEpWbmRIZElhTHBzZU1OVWM1V1V5dEFmZVkwdA?oc=5</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -1981,27 +1981,27 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>In Pictures - Sri Lankan police attempt to block Batticaloa march as Tamils mark ‘Black Day’ - Tamil Guardian</t>
+          <t>How The Narrative Around UiPath (PATH) Is Shifting With AI Themes And New Index Adds - Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 16:45:53 GMT</t>
+          <t>Sat, 07 Feb 2026 05:05:00 GMT</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOa3gtbXVTRUdwWHo3SE5QaUdOMER6TnY1cXM0c29PRHQyVVFtTWRvR1YzeTVZbHQtaGFMYkZUZWFKUGxnc0VJLTVVWGF4Y1NwdkZ4UjdoaFd5TTE5cVlCR3lVVzdSV3BrOHpLR0RhR1dSaWNZTXYxNDYyQ1g1RXY0SVhlTDdNVzdkbHhlT0hubzNqUG9zZ3hXSjFWN0d4MU9NY0xVd3NJR0dRTkZJUU0yUUNwT0Ixc1FD?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxPeTJoVDd4Rkhwemp4VE9qWENRVnp2c0FQb1dKTEJBYmRwNUpmaUlSYTM1RFI2dlR5eGVpZVBDZWl6SVE2UTd4NnNDNU9EMUx0ZHA3WG1XSEIyajItV3d1SUdjOFF1eUtJZkl0V2xOc2kyUWxKTF9adnhCNnFDb25jNzNNWVZ2LTFGakh6RHpXUQ?oc=5</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2011,27 +2011,27 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Norristown community demands answers after police officer strikes man with patrol vehicle - 6abc Philadelphia</t>
+          <t>Strengthening AI capacity in the Arab States - unesco.org</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 04:38:15 GMT</t>
+          <t>Fri, 06 Feb 2026 15:48:05 GMT</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOa3p3bHpUenZCemw1OV9nckIwY1NaWmxVZHM5cVJjQjFCOVIwTlJkUU10Y0FBd2YzM0FOc08yaUpQTndCcW92dGNhalRNamQzejh3UEdtZE1zZlloZWVKcUVCcXpUV2s3MnBCYUk2dEdFYjdheTRfLWdyNV9vajh3YXVEQUNQRnV2SVl3Uk5oMEJuMnM4ampkalc1SGZrb2o2ZFl0Vkc2dUZEa3d3RFp30gG0AUFVX3lxTE9WNWc5NENieldvSkxzS3pJX2JrazN4a3h6M0p5dlRQVWs3SmFyR3VHWjh4aDItMDh3ZHNFckFtMm9RX2ZRZFJaTEtnT3BaQnNKSG0zWFFtWWNSWmFKdVcyS3ZuelRzMklGZjNMOXlRYV9EZF9QNzlaWWZUXzFicU5ncW81U0g5YjM0LU12dURBOS13MkRXLTlXUV92WEdoSzhOZW5iSXNlTHFOemhBbHZSdVB2NQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE5CbWVNVm5UTVBEa09xMWpWZTRyYlJZQzFsN2xxSGVWWjROR01jXzRQUXlnX09NVC00WWdxdlZiTkswUW5jYTZubENxTEY1ZmRvT29lbFZqVmxMLWlxajA5N2Vja3p1LVJFVFJ6OFQ3NXUtNkQ2MnQ5T2dzX18?oc=5</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2041,27 +2041,27 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Catholic clergy protest police attack on priest in Sri Lanka - Herald Malaysia Online</t>
+          <t>AI &amp; liability - does English law need to change? - Mishcon de Reya LLP</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 12:00:49 GMT</t>
+          <t>Fri, 06 Feb 2026 12:39:26 GMT</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOVjRSSEtmdFhXczBjcVJVY2dsLXJ2WlJ4NlM2YVpRLVZqLS1UV1FGS001V3VpYkphS0ZJU3dWNUpkTTR6TzBvR1doVFRDX1NreHZjTXVyMGhVSWtLWDdZQ1NHaDVmeWRncVJzZmxBSVR6ZTVGRnB4OWxuM2JBV2pPY3R2V1R3Q3JBZHg0VXhrcmxxcjhlVkdGZE40T0FUUVFKYlR4WjYzTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxNX2gwVllkdC0xYkV6eFpoMnhoS0xDVkRhbkpNWHVCOVFrV3dOekNDWmtsSnhqUmJETUJrVF82RW5MNk5ZdmlSdjdIRE5MbHh0N2pTaXl4ZGtWTU9ERWRDVWkydEJlaVlPS0liTjl5OTItS3ExaEpFWkdsN3gtb0U2akdQOA?oc=5</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2071,27 +2071,27 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Reno Police prepare for anticipated ice protests - KOLO | 8 News Now</t>
+          <t>Call for North East to embrace AI or 'be smashed' by it - BBC</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 00:38:00 GMT</t>
+          <t>Fri, 06 Feb 2026 19:33:35 GMT</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxQeEJJTTlIeVZWN2FNNUFVRTYxaDY3a29DdHJyT01FY0dtUl90RUZCSWUxZVhyOEhWVGY2LW53NXh6UXNmT0Nubm81UDRuZTdxYUJwWWQzUmpCcThIMFBRUC1YZFA3Z1p3bmQ5UTBiOW4zalZVRkllN2FNLUdGancyMzdFNW5kQdIBmgFBVV95cUxNeHZKOXZOZzdkM2pRY1hBeFRXNVpSSkxhLU0tWENyX19aZERxcUFxUFYzNUlxalNzSm9lVXVNc3pjeTcyRWt5SDNyV0Q5anF0dEVjbnNOUGZHZ0N1TEIxUVhKeUE4NnZUbDFZUGVROGZOd2JmNnRMd2Zya3pUT3NZQkZuTnNoN0VhTVJoZjgzM2duX0dIWEhUSFpB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1IdW5ISTNsbmVUeDRZaFNuVkd6WFBEVDJBZDQ0OUpfMTlETmUyWFdQYXZMNkU5V0g2MVdOdU54T0U0eGZYRWd5YXVkZF9RYmxFOHU3QTZIcFltdw?oc=5</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2101,27 +2101,27 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Labor’s radical dream of the “general strike” - Capital Research Center</t>
+          <t>FTSE and Wall Street rebound from week-long rout as traders reassess AI and Big Tech spending - Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 13:30:00 GMT</t>
+          <t>Fri, 06 Feb 2026 16:33:20 GMT</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNSVA2SldrUjVQX1RjY25GcU1kazE0cmtBYmt1bXVXLXJ6UzR3QzZmd3BFa2REb0JGV3VMck56eGtUMDhHaEJtTDFwTV9LXzQxdVdXWXpsY3huRjJkRkgzem8tT05BczJvQVJmaVpROXU5NmdON0pFR0FPcnJjZEF3QXVCa2NuUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPNDVBZEhnTkJ3eU4zX1NYbGdTMXRpOVBCM3NjOFVGRXFtX3FxZ0Z4dkpEejJ5LWt0SFA4TlppVkJVczZKVkJFVlROWnJZSGpoQ2RhVjZRSTRMM21zTW82ME9JRU0xWEp3ejRrcjFoVU5LMi1reFg1dlc3MC1ad1hJeGRNSXd1X1FTdUFSS3ZEa0paRVoxYTlTTW55ZWtmSUV1Q0VCQVlySktYdkU2YjVPMlZR?oc=5</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2131,27 +2131,27 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Itaú Unibanco Board Clears 2025 Accounts and Confirms March Interest-on-Capital Payout - TipRanks</t>
+          <t>Microsoft Launches AI QuickStart Programme with Support from IMDA and UOB - Microsoft Source</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 18:36:59 GMT</t>
+          <t>Fri, 06 Feb 2026 07:41:09 GMT</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxQQzZfSFRNeFRFaUw3bUhBR19PZ1VPU21YcXN4V1FFallHNmNhSXA2SFFiTlg4eU1KNnhIMkY5dG90VHZiY0VadHBNSjdrZFBRSEd2V051alBRdmRDRnhpYjhSVFhJQjA0bGFvbkFBQXdiWmhfdWRDQTBlRVFSaWktX2JESDBvVDc3V0NJUFpKczVLWmVpaFFCbG9FcDBsbmVtRC0yUXBZZEtNSmtDRlJzUTNuRm1JaFJGdjZkYWR5TU5RUFBOa1pOMGJ5UmFRUnUxLUYycw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNd2ljT2pkVlFBMkc4VzBVSkFsZnR1RkNTb1lxSG9NTkVGOHdRWHVQMDZOT2hram0yZHRram45dFpCV3RvbE8zOXFyRDdoZFY4THhZVlhWYjdTMlhoY29oQkh2WDcwdlBfSUpZTEYwZnl2MGFLR0Zqel9KenNCSzNzM1pNYXpoSTJGSi04QlJRcnpwTFRTTGZ0aS0wX1ZBQlduOTNqTUN3dHlOSU1rdzlGWklFMGpKY2Y3ZGduWEsxV2o4dw?oc=5</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2161,27 +2161,27 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Attendo to Present Updated Financial Targets and Strategy at March Capital Markets Day 2026 - TipRanks</t>
+          <t>HBS Short Intensive Program on AI and Climate Change Merges a Global Challenge with an Unprecedented Tool for Change - Harvard Business School</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 08:06:20 GMT</t>
+          <t>Fri, 06 Feb 2026 15:08:02 GMT</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOMXRDeEhMcHNuVklmQ2dORFlRQ2pVdlpXOVJrMkl5dzhvTmt0enFEdDJuUW8wTXJBZWRtRkNKbHBYZGh1NWVLY21aX1U1NVBQS0R3YVY1YTVUSS1zQ1l2NEZUWGU1bEhuUG80bFJsbm13SGVzeTg5Zks4RFJrMUhCMElhM2ZWSE1DRk1sbFQtT0dDTWVoVFo2X3FsWTZSTmxKR01PZEVhRnlfdUVNdS1LWmwwMm9hcjNqejBZRS1kbDV2ZGdPdkdkYVNYaTZrOExFOUZuamlwdms3eFU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE9CSjFaM21nUzAtY0hVZkY5SHZOMENBcnNMMHhXamFIcnhibEtOSTRhQXJaNUs1UFplejRsTEVWVEpSNksyRGotblpIUXFndnFDcVpJMHlsTjB3Y0xJdi1MR3BxbTlfYWhqMmdSSTdKUkVEV21o?oc=5</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2191,27 +2191,27 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Cleary’s tenant charged after police raid - News.com.au</t>
+          <t>Baker McKenzie to cut back office jobs, cites AI - Non-Billable</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 05:15:28 GMT</t>
+          <t>Fri, 06 Feb 2026 12:25:00 GMT</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOWjJ4aGM1NGVNa2N0RHhxaEFST3BSa1M3Um1HcDdHVFFGWkhVdzN4SkJTckUyYmtBYVhMM253NC1JczRoR09fRWE2VTFuZ3V1NTZNS2tZTVM5VlNnano3UHBMa3l3bnhMYjRCMHM4TXFEQlZHbUVkbzZIcE01TTBLTTlEc2U1M3d3Z3lLOFVZZVBqUldibmxJQ2NUeFB0NVNZTzJpdnBrWXFXQUw3NHBtQlVoZEZZMk5pMWhnbXpiRGI0OWlQd3JBU2JhbC1NMHZD0gHWAUFVX3lxTE82cTlSaXg1VGdKTmlSaElUUnJhZk9HaGdJcFdNUzJDX1R2VWFoVzIwRFNWS2VfclRETEZKWG9tb0l0X3R5MXR0M3JtUi16Q0RCN0ZaT29JYml2dldCM1VJLWhpMlIyaUFfLXZiQjdCOWRhWDA3X0ZMcl82QU1ybmZoMG93R0lXMU9RVU5JQmtRZ1hQamk2alppakNIYkFVMkYwdUx3bnJrcXRxZVA2bkpsTXJHcDBra3liYk5ubU5NOUk0a0lyRmNfbDNqdDY5OGFIczUtb2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE0zMlltTS1MNVZtY0dqV0Z6Q2lzM2Z1V3pETVAwbTVaenNXQm1mY3VKc1U0VTFWaHYxMGxGMXZ4WDNnMmhwZk0xdUY2eHJpRzVxMHczYllCX3A1UmFGSTJfZzdYR2QzLXNnSTFfMkdkUmJXTDU4YmdCT1F3bVhvZw?oc=5</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2231,17 +2231,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AI and GDPR Monthly Update - Dentons</t>
+          <t>AI hype meets software reality in bloody week for stocks - The Irish Times</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 20:13:43 GMT</t>
+          <t>Sat, 07 Feb 2026 06:00:14 GMT</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgJBVV95cUxOdl9Ba0pDNzNFUnZsQ0NaUDJWOG5uaU9SUEJfOXJ3VXNtWVRZTS05ZzB2dC05R1R3clV4SG44OU0yU0FHcDVMXzJfbG4zS1FhZldKQ3hTNEF5bVdHRXJqYW9EeU9lRjJ1dHlMRE5nMXNsY1JwdUI1SkR0dzZGbE4wcUxJblNsckFsc05xUnNUQmxuS3JGZkQ5ME42Ymk1SnBFMTkxRVhla3pHZlFCVUhKaDJhYVJ5TjlpMXdrOWZFdUg0V0ZiMUpnT1g3R2hrN1R1NmtobUhoN1luTTVKNURMOGs0RkNic3ZDSEs4UlZ2bTRVSkV3TDJLWHZYbVdROEY3SGhBLXhoOC1OM1lmd3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOQkpXb3c0RWFKWlh2R1FYR1N4eXBDdjBMLURXdGZzbGxJUUNZYWVqY2o4MjhLUmV6ekxVbFloUVV1cnY0LWJZeU5kWDNVMW9ZWXVodVBkWnZocWZSMGpWRDE1Tm9yQkh6Vkk0VHpqTGRQU3VLYndCZ2tUc0RmM2VqaldRbXF5c1JfZEhLcDM1ZzF4Sjc1MDc0dWRfZjU1NkVxTjJGeWxZTUJPdw?oc=5</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2261,17 +2261,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>KPMG pressed its auditor to pass on AI cost savings - Financial Times</t>
+          <t>Nothing About Us Without Us: Reclaiming power in an age of border technology - openDemocracy</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 05:00:13 GMT</t>
+          <t>Fri, 06 Feb 2026 17:41:11 GMT</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1JcFJRMmdvcFYxNVhvQmdYNklVN3gtNWUtMEJ4Y2VTbWRUNEtIck9HdExUZFVPSFp1RWZ6NUlRQTRIc1MxeGhkVVBJakxuZnpMcFRneDRKdmoyTWFvWDlFdE9EMjUydDI1d1MzWjJXeHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPYVJrSmk2VFZ3M041VHBVMF9TZVVyR2laZmRXby1BM3BKQVV3Q2huNU5GNWhYVHY5dVlPc1JoZW9RT2NrMlFFUnQtb2J3T19SMUJyZDZOOW5qbmk5V1l1ZTl0Z05jdFlCcmxKNzNMQm53eDlMeFZndU9vU0lrMjJjVjVQUUplZ2VHbnZfaFR3dGtoUEt0TGhWaUhxS0JKSFVZeVVVb2F0dW5YbDd1bl9tSmk0eHlHQ0k?oc=5</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2291,17 +2291,17 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Amazon shares tumble as it joins the Big Tech AI spending spree - BBC</t>
+          <t>Andrew Boyagi: 'AI alone is not a panacea’ - Computing UK</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 00:06:56 GMT</t>
+          <t>Fri, 06 Feb 2026 12:13:28 GMT</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1wZzJieWpQdW1JZ1ZfaGEyQkUtS3ZjUi1NOHZCY1ZMTXJZMFU3Ym4wUG0zaDhuYmsxSGNBbFpSbUszRW1HUUhwRkJZc2VDc0hpN2FaSFlfM015dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE5oQmRsYnhmSmc3Zmp6blpyM0lrZDlDdGRrZE1JRXFmdGVCUmxxME9ua19mcDJsbE5lV3BiN0E1VDdLdlZsMzM3RDNndDBCMXpyNzJwOHlfSWNRc0FFWEZDeTEza3pYeGZ0azFHLXVGN1dJdkNub0J0Z3BHSkRkQQ?oc=5</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2321,17 +2321,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Why comparisons between AI and human intelligence miss the point - The Conversation</t>
+          <t>Gas, power and AI’s role in the new age of energy addition - Al Jazeera</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 22:54:46 GMT</t>
+          <t>Fri, 06 Feb 2026 21:38:59 GMT</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQUEZhTmltemh0R1RtT0R6SjB6dEcyM2c4VjdDa3hZNFY0R3JyMjFmT19TU05yN3FKeWR1aVNUYUtpMU04aDdHYmdpYlBHcUJiNjVVb0ZjU3g0YUlHd0FFamxLTmt0MS1hOWxyVUdZa3BKbnVSdVBSNFQtZlg0VVFtbkc5ZjdQVTRLY0VoY0lqd1JIcEQ2UEFCc2ZUSzFPLVhT?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNSUd2c0tURE9DbkRINVpBSE9qOVNwTWloNHFmWkNsY3cxRmh4bnZfeU5fbzdqajVtbkFEUUpTdl9SQTZQeDRwZTNCR2ZYZm9XWXE2MTZhZjFHSm1jVW5GOXBLUkVjZzlJQl9PRHVGZW5jR0xwc25jbS0tZVpqWGNaX1J2cWxZLXBRR0d3MkJkajF6TmRkSHUxRFVyWDVvakpE0gGmAUFVX3lxTE9Ncmk3Um92ZDZyZXdGYXNUU1J6bUJDM09ubFNIOVpuYmdFN2JwaFBLem82VWF5UllQUnRWNUxjR01HV2g0RlFuQXc4UjlDUFMyYTlHdDNIaFBkMHZocVlDN2NVcElqczhJU0x3T2JQZkoxSVVFQ252ZXZSb1kwbEozTHJJa3lfUGlEeERRdTVrV3o2bzdjcmJvTjNUbVpHc2lDemNxb3c?oc=5</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -2351,17 +2351,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Agri-tech and AI can help you break productivity plateau, farmers told - Eastern Daily Press</t>
+          <t>Cybersecurity Information Sharing Act of 2015 Reauthorized Through September 2026 - Inside Privacy</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 06:00:00 GMT</t>
+          <t>Fri, 06 Feb 2026 19:32:43 GMT</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOM25yVWZFTm02OGc5alZPajl2b0xpZG83dWxzVmJQQzh4UkFyRVVqWVlpOEYtcW1fTFBTUjNscEozYV9QaG5HMXNTdmhidm5XaWxEQlhhMXpsWGFpeVNlLTUyOXVuQXdidVRodXAwdWhDY3h5RjV3VWZpOFVoVWVqc1hOc09aZER2MVlWWjJMTUhGTUY0OTNJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNSGVwV25WdXQyR2VzTENBbTRUQzFrWmJkeGsyZjZtZlFMUjhnSDBWckxMeUpwd1JkbWc1N0tlTEFFVUVwYm9CT0JEZlRVLUZwcV9oQjVZeWRVMmRJbEViN3ltQjE4ZEhITDlKVUxyS2tYZ0ZyRnk4QTBsRFAwMF9zV2JFOTZtT0JpeVYteE1DcWhfVi1IQjFKeW1DcGhILTdnQlRELThkQm5GYllWUUpmdDYwa3p6OGFWeXlYNXlVYmVJVkJ5aTFv?oc=5</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -2381,17 +2381,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Microsoft Launches AI QuickStart Programme with Support from IMDA and UOB - Microsoft Source</t>
+          <t>Bury Council ponders using AI for budget gains - LocalGov.co.uk</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 07:41:09 GMT</t>
+          <t>Fri, 06 Feb 2026 12:50:19 GMT</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNd2ljT2pkVlFBMkc4VzBVSkFsZnR1RkNTb1lxSG9NTkVGOHdRWHVQMDZOT2hram0yZHRram45dFpCV3RvbE8zOXFyRDdoZFY4THhZVlhWYjdTMlhoY29oQkh2WDcwdlBfSUpZTEYwZnl2MGFLR0Zqel9KenNCSzNzM1pNYXpoSTJGSi04QlJRcnpwTFRTTGZ0aS0wX1ZBQlduOTNqTUN3dHlOSU1rdzlGWklFMGpKY2Y3ZGduWEsxV2o4dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxQYlV1TVROd0E3RTZjRngxQlBQVGIxTF9jdVE4Y3Y4OGU5VHF1VkxIdXUwUjBNajBrWTZDWXpMdU45OE5xWGpnRDRnaFpzcFJoQ1dnMlJvZVNnNTA5dmZYUEREdVBtcHNkZjZWTkZ5Nlc5SGxPNnBKTXY3RHhWUFU3dWE4SjJSZw?oc=5</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -2411,17 +2411,17 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Safer Internet Day: Young people encouraged to use AI safely and responsibly - Warwickshire County Council</t>
+          <t>Which European country is the best and worst at AI adoption? - Euronews.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 11:51:57 GMT</t>
+          <t>Sat, 07 Feb 2026 07:01:40 GMT</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxORHllMEgydXVnS3pOTEQ4MEJBbDJCcnIxZy1VNzQ3eFdnd2FIQmg4emktR09uQXNZWFNvd0k3SEV0dlhoTFExWVpSM3dDT0pfUnFEWE9CZnh0LTEwS1RVQ1VteXhQbDAzV1J6U2dWbGdySzdZT25BWnY0V3dHS01zRGhsZlFHRTg3dmR4dHBfNlFlQWNRaVFLQnd2MV9mWkVPd2RCajJRenFxLWk1RF9SWkljX0V5ZGtzT3pSeENYS0NCYmM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOcHFRcHk5V3g0LTdBMHpRRjM3bzhlb1NWZlY5SDNfTEgyRXFUVjB6emZXWUQ3MUpFaERlbVFMSmtoQkR6cElOR1VvLWlPYXp1dHNGVUpmZkFKWWdESmVYaWNmVFU3Q2I4UjM0dkozeUExcVpma0ZZZ0pIOU03bWVmWjFIT0w2YUppcmZPS2dRZUJIVEpYN3hpYk1fWE9FQWdwYTQxbk5xZmVkOG1j?oc=5</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Micron’s Singapore Fab Builds AI Memory Capacity While Valuation Stays Stretched - Yahoo Finance UK</t>
+          <t>Alphabet Q4 FY 2025 Highlights Cloud Acceleration and Enterprise AI Momentum - The Futurum Group</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 07:05:00 GMT</t>
+          <t>Fri, 06 Feb 2026 15:06:09 GMT</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxQRldMNDd3UHBqX3FaSWJWS1F5V2hsUkJhYk1NZGZTeDJmVXg0WFpsYUtVcGFVZEFwSTZRaFRGZzRDOWZ4TDRDdUt0SDNwdGIzRUJDdzNYN2Q2U3VSalVmQTc1QllPN1JYQXM0NDdrYjBUQkV3ejdVRnVySzY2TldHUnEwVFQ4QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOVE1LYXVNOHJUVWdpQWxmSFlyc1ZMYXZlSTc4NVJaTGE1X0p1YWVkVFVsYTlEbk5qd2VXMXV3V3lsczNYbHYzcV9XY1FCOWdBckJDUW93bmtCNFhrcVpaRm5iNkQ3Mk9MMjhpT0xzbHRGTXAtcFM5QWZBVld4Y3J0OXFKVF9TVnE5YnMycmg3NWlLSVBSZ2xUaHFGOGp2eWhnY3M5OVR1cTA4U05ETTluag?oc=5</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -2471,17 +2471,17 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>NGMN sets out framework to simplify 5G network operations - Mobile Europe</t>
+          <t>From Jesuit Education to Career Success: A CTL Conversation on Generative Artificial Intelligence - Marquette Today</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 00:35:19 GMT</t>
+          <t>Sat, 07 Feb 2026 05:41:35 GMT</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQa3lZZWU2aGhDN0VuSmowSGUyZ1g0UkxGZmItTWEzVUl3RlRWT2JsRTlReVAydERUYlNIb2JQNkZ1QXhwNHRlTTFwSmstMG14a2dNcm8tZXZyWDZNTlBXSXlkQTJZcmZNS3FDNklBR1hDaXRVM2s3UGp5ejd5a05GLWJ1bEpRNGp2cUpKZ1FWZVFCUFk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPbkRFVEZZdm1HUndHaGhzeDFmeU10dmhQWGJmVE1rQ0ZxRFc0bVAxMExPbHhEUnVhQi1fWkdpR3FodDJfU3NZZDhRSkkwakg0Z3dIV0QyNWl6Vjk2U0cwYkcxZDlRSU05dXVKbXZ5dE50aVZFNGNWT2VsSjdUb1RZU3JSbFlPaG1EWDBrVlBNYUpXSUptYy1FaE1mWTM2OUFoNlUyNzZOZFB4NU5XV2NlNUtmRGhSbXVhcGN3MnR1NzJkLTJFMGE3dGVGXzRPM3M?oc=5</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -2501,17 +2501,17 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AI fears pummel software stocks: Is it 'illogical' panic or a SaaS apocalypse? - CNBC</t>
+          <t>How to adapt your lab leadership to an AI era - Dentistry UK</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 04:20:00 GMT</t>
+          <t>Fri, 06 Feb 2026 09:24:20 GMT</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNdThQSFVQWWhleE1YV2MtOUhOTUFnYkd2aTNVaU1MZ2o4S3ZlOEtOeEd0Q0oyMTRaUVhwM1BmTjRiWlhyVFU1UW1GNGp4RURqakV6WVJWMlpoWFNCMzhLY3BuRDZETi12Mk5hV1BDMVFzbU5sUjFFM0pRSUlRN1JTNUYyQXI5eVNnaHFUX9IBkgFBVV95cUxOZWE2NFl0QWEyU1AtNUw4Y3l1V2FkUlpLc19DYVAxYUJveGNOa2hjRGZYdkNUYm5zWWFFMXRzeGhaTzhHbXJvRmdGa0kzczE5R2Y4OE1xbG5JTXMzZ3VPanFLNzFwUEV1czc0Vmo2bjd2Q29XWjNFM3VxaWdMQUhuWjg3WW1nZU80RXFZR283NXBCdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQNXpScldvXzRYZnNDS19WeUFLNU9hZWtvVjdzdHl0VWZxc3QzRUl5TllWamNCbmxfWWk0VUE0S284eGR2VFRQNXN3M3VFdEViT3BtWVVvQXROV0dUVThUV001QzBENnZiYmstSEtCUmJJVkZqaldJWDJveFI3WGYtclk4WnpLQTA4?oc=5</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -2531,17 +2531,17 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Alphabet results keep analysts bullish on AI and cloud outlook - Proactive Investors</t>
+          <t>Beyond serendipity: rational design and AI’s expansion of the undruggable target landscape - Drug Target Review</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 18:34:00 GMT</t>
+          <t>Fri, 06 Feb 2026 09:05:22 GMT</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxPSDI4XzI5Xzgzd2N4dTdjUUI4NmxocDFVX2E5ZDk4MGlsQ214UTNvdlY3MjdJelBhclI0U2wxdnppVGxneG9hQi02U1NoRTVlWHo5VkZJcHJiUlp6bzdMNzduNWNqRmF0Q1VPVk9nVzJObjJxcEN5OWRUdjhHLXFWMi0xX3RkVVlTbEVkOXJTVmJUNVYzNjROaHZIbC1Cc1dYMWlGUjExOUl1UThXVXJLdGFHV0RHV21uejY3TmdmNWpTbFBCaktjN0NjMlhzOHV3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQZ28xQk1ObTFfeDJ2N0ZkTTEtajFtWEt1YXZaS1pqWnBraWtGNWRYbG9tUEUzME9iWTM4dlIycGhUeEpNSDlhSFpHRldjM285MWQ5SzhWV05NclZqaHFNTTRabzJlbTRaLVU5Y1haMGlXdU9DM0tYOGg0SWtBVGNQY04zcHAxdkpVTnh2REM2cm0xNjlncUZQWFBGekg4WUFqUklSdl9TQ3RYNEo2YTRnNmtjQ2pSM3V3b2hpTmZQTTFyLWdG?oc=5</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -2561,17 +2561,17 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Ship Production Ready AI and Survive the Multimodal Frontier This February - Google Cloud</t>
+          <t>A New Economic World Order May Be Based on Sovereign AI and Midsized Nation Alliances - Stanford HAI</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 21:19:05 GMT</t>
+          <t>Fri, 06 Feb 2026 17:38:05 GMT</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxPWTBKTXdPZlQ4WXVvWS1UcEcwcm5SM0xfN0JPTnpIY1gyZnNPSWxYZzFvRF9JVWNpNFBZTUNfdVo5YWpDd1ZiVGVMb2pYRnhvMEdMRnM3SWJsQmRkZHZyZE1xS05xUWY0RzNfRWRJNHRQSmlUOUZVREludzRuSlA1dWdSeWhwTVE5WXlGMFFPV1dJUkhGaXJubV95WllFXzkzRWptMnhTeEdnUXFsOXlxMDFQT1lpUWgzRTQwWlNJR0JhZXZCaW5jY3hYNEdZYVdQU1Fr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOcVVDZGxfaERySnFTNVRqSUxjU0M1bkVEUFQ0TFhkZV82LUxhRWtTWUlEVEV6cUtRUVhLTzdsY2J3ckZxSVN6QUo0cjdzSWlacmpTLXU1bzAyQU10aEQ1SXVkNHVOaTN3cEFxelFXcjExWHhja2xJN2hIS3cwQU9ZMGE2Wl9iVGt1X3hSUDl6UGV2bzUzZ2VvWTUxRVlxQm5MTjVIYWlZRmpZeXJIQUV5UnBpb2hsdw?oc=5</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -2591,17 +2591,17 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Latest NDAA Supports AI Safety, Innovation, and China Decoupling - Lawfare</t>
+          <t>Howmet Aerospace to Host Technology and Markets Day on March 10, 2026 - PR Newswire</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 19:19:19 GMT</t>
+          <t>Fri, 06 Feb 2026 13:00:00 GMT</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOWnZGQjV5cWRzU1YwR2pmRkZSMXRWWW9YSUNsaHNCeC02d2ZIdWtqaDJjOF9uaWJDMkdMcHd4Q3NhYlI2ZVZILW9nc1U1MWhNam0wVmcwZVFYUmxsQmlmLWpScmFJYVhkMWhkRS1WVkhqejJ0NGprLUUtdDFfbUZ1MVU4TUpTYktHMGtRa3JrbG4wWVNPbURxcjhrQ1oyTXp3Tl9z?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNZF9zZm5LbkZ1ZXVjNGdqT3JiX3I2X2FPX0s4V25ZOVZENjd5dmxHOTF2ekViX0FZTzhzd1EzcVYxYm5uaDRkaXZKc1gwbHJsR1R3R0pSN0NEZUtFWDJ0bm5kb1lvcUdjWEx6THhDajF6ODJKTFFBSVFvWDI5M1Y1SHd1aUNtVW9DVFFsSVBfWHVjNkJBcHFTSzFSOXV1QndBc0FQZ1R4MmZZX25pNy02S2hfc0xha2dkZmNzTm9iVFJWQQ?oc=5</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Arista Networks (ANET) Is Down 13.1% After AI Data Center Hype Meets Pre-Earnings Reality - What's Changed - Yahoo Finance UK</t>
+          <t>CC at the AI Impact Summit: Core Interventions for the Public Interest - creativecommons.org</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 07:06:00 GMT</t>
+          <t>Fri, 06 Feb 2026 17:27:46 GMT</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxQcWd3ZENhS1I0NFZWampEdVdrQXowand5QmtzNm9nXzBRSUNTbjgxbUVlOVozUEpNZnFLNkRSNnFIaXQ0MGRhajIzZERPdW5Bdnd4Q3NPbFFONU1kcFhHM3RjVVJSRmF4MXhlRHpzbEdXcU1KNl9CWlVpOTM3LXVleDAySQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTFBwVGJFRmVmTTRaaFotRU5UX1pTcjU1cGVlSnNVM05wa2hOUHFyYVpLNWdCb3ozR3R6ZnItQzVHZWItN3ZUWXRtUjVycmc0dUVpbFRfa2xfWDVrLTc4N2tNTmRxVDFPUXJ1ZTJlTEg5bUJMdmJOelFUcEpWSQ?oc=5</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -2651,17 +2651,17 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>FTSE and European firms worst hit by software sell-off - Yahoo Finance UK</t>
+          <t>Hail our new robot overlords! Amazon warehouse tour offers glimpse of future - The Guardian</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 15:59:36 GMT</t>
+          <t>Fri, 06 Feb 2026 12:01:00 GMT</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQUlllM1AzbmNnckhQV0pMWUxkSUZrVnFVNndGeDBJbmVMcFFzZFl3NDhsT3VwUjFrUS04NXQ5NkhYLVFSZXJMMkd3YjZvbjRubWg2Y3pVcTN3SFpkandZTTYtNy1FZTZHN3pUUWdad0dOdDc3X3o3S29pVml0RHJTTkVIRkxtOGRuRFFqSHJLYXBsUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPSVh1SWVWWUtkbHZURHFMYW5MLWZxZzIwWFFxM0wwbjM5aVZkX3BoaTBmVmlqeDNpQU5YZWRmUGJZOTA1MWpzZ0UtRnJEbk16NThua1lEVVM0U3Q2cDlVcVlMM0xnNmZ4YmJmeGxyWnhlclJTV3BkUG5ZVXRybERoSXItTXBTMERKT1NqNDd1MHQ?oc=5</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Lawmakers introduce bill to strengthen energy sector cybersecurity and threat analysis, boost resilience - Industrial Cyber</t>
+          <t>Google, Amazon, OpenAI and the race to find alternatives to Nvidia - EL PAÍS English</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 09:11:13 GMT</t>
+          <t>Sat, 07 Feb 2026 04:00:00 GMT</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxQWXZXbXdhVE56VjBmZVdCNVBzRlV6WWs0a3Y2R0NGSGpoYmdycjR3cTROLWg5NjVZenQwS2RPaEp3ckUxMGI5aHEtaWlnanJ3SGxTMF9RNnJUY0V0YmZKSlRadGpIeWlUNl82S05jajV2ZGJRcXZRWTRWYk44czlETHFYZzYybGxHU0MzUFQ3bUhnVzJuYVZ5Y3VkaXgwZ0FnRUZpbktwa0RvcVJHclJqSTNGaVpfeHpqUjBWS1dkWm1WLUl3VHk2YVdQeGNNQXFUZDhrb3RlS0Y1U053czBGeTNNTG93bEtwN1ZYSk1DWlA1eDBBLWxrVXhtRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQZEp0cTZld1RTR3lSSVFvWXdzQU1aX2ZXVnM1aHJ2UE80SWJsdmxuOEZ1SEljbkFwNUxVVlBmR3k2Z1RHTWxFYVVnRWlVemk5eEc4eE9zbTllcS1lYXhOQ0IyTWNfX2ZvU3dBT1h3SWQwUEdFeHVZQzd3NDVjUHphM1IwaVZnODlMYmdrNkN5Uk1JejYtSVE1bXVabHZyUUs0QWZTcmU3c0ExdEEyZmcybWh0a0JkUW92YWfSAc4BQVVfeXFMUE9wOVJMTk9zb1lGVEI4SWMycHNYM3Z2OXlhM0JlSjMxNEdSVnROSFhON2pWWFZGVUYzMmZVb01iYjZDNjc0MHljTFlSZnhUeGt5YjFFRDJ0aGEyLVJkbzM2TGpUU1BwemcxTXBOcHlFUFhJVXhCdVViZmVwYUhwc1ZBQ3hMaWNFeGZCc0tkTy1QY1dfRk9PUGVzV01tV0puVE42TnB2eEloNXpkQ2k1bmN1cUxCN1RES0pQYmxoZzhZQWpYcW9KaGVFNU0tWmc?oc=5</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -2711,17 +2711,17 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Scandinavian Airlines CEO: AI can cut disruption response times - Euronews.com</t>
+          <t>Open RAN Forecast Revised Up as Expectations for Future 5G and 6G Deployments Increase, According to Dell’Oro Group - Dell'Oro Group</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 06:30:04 GMT</t>
+          <t>Fri, 06 Feb 2026 13:00:11 GMT</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxObVpKNWFtSGh3RmVabEg0ZUxJZ1pyTlp4YmVSUEpjb0hHdGRmbzNYM01reU94UERQRjQxUGpRcDhBRmtjSnJKd1B3TjlvZ2F0Qm90Mk5MN28wWDZsTDBKZXB4WXNQVzV4Z2Z3UjZNTHRQV002ZmZvb2p2RkZFeHI0WkhvOTZVNW9pTGxHVEpybTdMNVgzUFMtRFhuTmREMmczTjJGcmlkREJlX0U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNNnlpMnlYTFg5SjhXT0xXOF8wbTFiUWhURDJmSjgwdWpMc0szWENSUDYzLXI2OWIyTHBtOXpTdHFQSzcwaGg3bFRJUFozcjBodjYtblhhOTN0ekF4MXYwZTVobDZWbmt6UUVBdUFoa2RNN1JDamRUSkxKcHRtcmpCTEZoTWNiQ2pvbjN2YTlaUEpNZkNSb1haZHRhbjNuazRaX20wUzBsU2RscjF2Y1RjS1RTQ0NDbjA?oc=5</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -2741,17 +2741,17 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Kocho taps Zadara for sovereign AI cloud in VMware shift - IT Brief UK</t>
+          <t>Kevin Frazier Joins the Cato Institute as Adjunct Research Fellow in Technology and AI - Cato Institute</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 17:15:00 GMT</t>
+          <t>Fri, 06 Feb 2026 19:16:46 GMT</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNMGRJRUNwRHFKdlZEZ09LMjloR1VlQlFuRGFzX1ZiaGlmdU5SSTJPYWJVVGV4NnRURjd5amQtbkZXMTJnZ1pkMmdVMVYzNGkwWHRNVThoWjdkNkRwVThoaFcxcUdEcm5qN0ZSZEoxcE4za1ZwQUF0VFRYQnI4ODhjSWs1eFZPT3FWcUM3Zg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOX0x5ZWhyeGppQWNaSVAwLU5IMXdBdDFPQlZJeFVycDhjbWtYNUl1YW11anozS2NVZFZjOFFxdkU3T21wNnhYOTNPOEJ0MjUxTTNLWW9PRC1fOFJJN3VScXg0VnNTV0dJRm80aWx5bHcwZEtFS3ZnYUt3UHVqYUpFbGY0MW9TU1V6cHRNSnYxM0doeUxEdXg3cDk3bzBIeVJMeDVNV2d5TWxwam8?oc=5</t>
         </is>
       </c>
       <c r="F78" t="n">
@@ -2761,27 +2761,27 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Exclusive | Inside Elon Musk’s $1.25 Trillion AI and Space Megamerger - The Wall Street Journal</t>
+          <t>Employee misconduct leads to over $16K loss for Lloyd Catholic school division - meadowlakeNOW</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 03:35:00 GMT</t>
+          <t>Fri, 06 Feb 2026 16:23:43 GMT</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8wJBVV95cUxNOFEweUlkM3ZCT1F6Y2FyZ3A5UE9TYUlvbDhkTl9JYjg1bkN1NV9tblBrV0FRamR5c0hCcnRaVERCRGEtaE9RdUVPRGw3YnhsR2lJYVdscnNqZE1rNmRXZGVMeUpvQ3B4TmloSkJLWE15VGVrSHpWaHE5T2Z5M2wyeGFHUGN6cTVkQnZpSG5XV0pWUmR5T05mbDg1Y3piNG5kdE9EZnJ6cVFYM054MTBra2RUOWtmbjRZNmt5NUtSbE5Dc3ktc1ZtdGh6YkFkVDkwX1hTbTJOaXExdFZ5a1l6SHQ1QWlnMHowRXpjM1lENGE1aGxMM0g5QV80Q3BqQ0RPSWFxV0h6RzYwWGRxcWM1OGJObzNmaTlHVXItNWVyWWdpckc1SldDdElSdlhKcWNWRDkxcGVkdDRNb1h3cnRjVXFCVlh2M1IzLU5ET0ZCRkpyMkN1TEpBZEUtRlFqYTdPeHlSQ1hqOHo4Nmk0SDlORXRTcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNVXdQUFo2RmRSeFc3clg5VWMxa2xqU1FyU0VjQkhUbWtTWW56QjY3Smw3SkVSZkxXZTV0TUJiWUJEM0lBTzhBVExYc3dmTHJ3aUlTWUNPWUlpLUwzTDJzQzhzOFgyRklpUURWRi0wc2Q4SXc5bEc2TEl3LWZtY0FjVUExQjZVZzRndW9zMk9BWXU3b3hYQnFxV19pZklBOUcxcElxU0ZNU21tVkg4SWEwOVUwRUsyUQ?oc=5</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -2791,27 +2791,27 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>The AI Shift: Is this the ‘take off’ moment for AI agents? - Financial Times</t>
+          <t>TSB warns romance fraud rising sharply across social media - FinTech Global</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 12:30:07 GMT</t>
+          <t>Fri, 06 Feb 2026 12:10:59 GMT</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBHdE1JcXdQcnFhZ3VlM1hfSGF1NDVDemJfYmRSLVkyTFFZcmVEU2dabDBYYVA4ckRmZW1ySUI1ekhIalE2elg2ci15LW9tbFNydlBXYlNjb1c4RWpEb2hqTjFybTYxU24zZUhWQ3VMazY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPaHhuZVdVNjhJM0xyLW45TTZMRndhemlvWXNKbzNmU3RGU0xNZlNhd1VTVURSbGRsXzVxZDVIR2lvVzdXbzAydklleUtOZWJ4WEgxeXRUdk9XLXdWX1pQVkFlcVBzZDUwRlREZC1QdG94YzI0Zm1XNFhUZEdqZlFWdHU0Z0o0TjZXbURJY0xQSDFObVlkLUU2dw?oc=5</t>
         </is>
       </c>
       <c r="F80" t="n">
@@ -2821,27 +2821,27 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Hospitality Tech360 programme to tackle leadership, AI and the future of hospitality - The Caterer</t>
+          <t>Oversight chair Comer requests wide range of business documents from Ilhan Omar’s husband - MinnPost</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 10:49:34 GMT</t>
+          <t>Fri, 06 Feb 2026 20:15:47 GMT</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxON3p4VWVUWWt4VnVYRVVsaFlQejBQM0o3R2RMWW40d2lEV0ZyTmw0aktNV1hJcldoV2RmRkhGOFNkWHUya2liQXoySmo5ZE1MV3VIZEREeHpnbUtGaTRMZTVvTDE5LW9TM25xTDF3Q0J5SmVyOGhGblE4WWRFZ0NMa0hZTktYZHJiQ0NNa0J1TUFwVHd3UWZOemdacTIyN1B3c0RoZHpJZFYzYWlhVDYtVG9kRFE3ZDF4WWhqWV8xdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOcXptUEdGY1NxSjF3d2U2emNXMFB3Nnl3ZWZCS0tmLVotbmVRcEtHTXJiV2NyYVI1LVBiN25XZ21iOW5RTmlKZm5KRzNPeHBjZFdOQnRpMU1JQjJlVU1VMzJoTGlWcDhITVNHMzdVNXlucXNsWEprX3UtN0RFdDZnMTloamNaMENoT3lzS2xEaVlSZ1E0V1BYMWg2MzExYlpHUEh3SmlsN0pNWTZuYy1LUUhBUDBGTVZjVHdIUkRVQkVpU3ZLSVFDdk4zeEJnQXRtWVlBSGpRRkczUQ?oc=5</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -2851,27 +2851,27 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Transforming into an AI-first Frontier Firm in partnership with our works councils - Microsoft</t>
+          <t>Trump shares video depicting Obamas as 'monkeys', also repeating election fraud claims - Anadolu Ajansı</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 17:05:00 GMT</t>
+          <t>Fri, 06 Feb 2026 10:12:47 GMT</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxPa3c0RmJBTGcxLVRPR0lRVUNSNzBadGxXMm03M195cnZHdVp6X0Vob0ZvVWZFZzQ0aFQ0bEtSaFRsVlZNOTQ0UFhDYlhlNmRmNmNqdWpMaHJiM2F4VDRkQ0RCT25SUTJReTg1QXAzTW03SGpDbDlvV0ZTcGViZHZwWkxubjh4a2VpclRvQzBaeWVCZHMyOXFfWm5FQVZzYTlUT1NMNk1ZZ1A1bUhGMm14bE9aMUpwU0o3ZkhsX1RFLXdnRnFN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQVVhSdXc2alE2elRWVEh3TTZhdTY0ai1vMFpPYWswRVFGY2p1V2NEMnQzOGxnMWIxQ2tLdDBzSGZuUlloRVZqVDR2N1pqLURJeUh4R3d2TEtPRHM1NTFPaVBCNEFqOWlpSVFiQTVlTUJSeWhEemtHdDNyZzJleFBQX3lHLUxKTkNidkl6a1NxYjlZdjRZRUl1ZTMzT1BheV9wN3hrMmxwQ0lMVlpCcG8yYXV5eEdCOW1xUm1zNWlLa2NlMkk?oc=5</t>
         </is>
       </c>
       <c r="F82" t="n">
@@ -2881,27 +2881,27 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>As WHO Debates Global AI Regulation, States Clash Over ‘Data Sovereignty’ - Health Policy Watch</t>
+          <t>Bernie Moreno introduces bipartisan bill to crack down on social media fraud - Cleveland.com</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 15:54:17 GMT</t>
+          <t>Fri, 06 Feb 2026 20:16:00 GMT</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFBwYUZScUJFWHpudm4zcTN3YndZLWxVM3JLdFF3UXlXbFlhMDQxVGhfUHl3R1MyTHZjN053b3Vzd3BVY1RLMEpnRzJoRnF0R1pmYWZjejRSbVJhQkpiS0ZPRnUzaEpPV09mb2paVw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNdWZNTmpoYzVXS1llQXE2d3ZpRHNMOWctWS1YaER2eVU4a0xsNXZpU2Jtay1qaUZSUGpvMU1ianFtQWpkR3pMWnBCRDIxdHJiRlNDYmZhQkxzYkpnSDB0bndSelk4Mk9DS3ZJaVZuYVBzMmUxUklHaXE3QkotVUtxdWl1Z3ItMHBJVVJvM1d2cG1SSDFSeEFOMDlHdHh3YXFRQ1RHczZTSUVqUENhR2FPcnhkQWw0NE9JSWZmT9IB0AFBVV95cUxPb1d5WXMtNVk3SFY4T0lHZVQxb1N3cE5USU1kX3VnVnNIQUxFbnN6YzZBMUpsNWI1V2J1OGJFZ1p2QWItdUZZTk5HLUx6ZmxsYjJFbHEzd25fa3RQMXpidGJKUDA4Y1lxWkpaQ1J1a1lyTWZTWGhzSkNaSDV0MXhWeFM1ajZ4ckxzMjQ0dGtMdWMwZGpWdzB2MWxVV0Y5NmRJRW5ZS1pYRnFjaVZyNURqdXU2amd4M1FzeGhQa0t1TlZfWU84b1NCLVNuaG8waU5N?oc=5</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -2911,27 +2911,27 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AI and the Law: What Documentary Filmmakers Need to Know (March 2026) - International Documentary Association</t>
+          <t>Trump’s racist ‘Truth Social’ post also included whopper on debunked Michigan election fraud theory - Michigan Advance</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 22:53:40 GMT</t>
+          <t>Fri, 06 Feb 2026 18:34:52 GMT</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxQUGQ1U0o0TERoSkwtcVoyc0RSWUpIM0hzTGs0dkJ5b1hIT1RORl96VGRRZm5haWpKSnlPTWx5TmFfdWNHYXVXRnpvUzQwV2pmYXplZ2JWMm9SSUlzM0RHYzJDN3FRSTJzUTZrS0xmSVBKYVpLWF9KeFVBYzFLT3BnYnJhN2ZQcTBnMnJsLQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNYlRuT0lWTUdvTkUxRDdycjZ0SWJ2cnZiZGxfWXV2MEk5R2N6ay1Eb2RfZmx4V2VsSDVtWVRjN3V4Rm1sMEtwOGk0RzdqT1ZISnlRVHdXTWozQlE3Rms0bUxaLUFKZk9TWmk4LUpkTmNRZW1zU0NDMlBmYU1EdUd3MG1mcjdrTWxXY1E2enJfY29NNUI4QjBxRGZYVXZZT1BJUmhlY1FTeDQzV3JlTjlEQ2lLdUdZVmxuQ3M0UEM3Wi1kVkFtcF9nR0lMU1FIbGVDdVE?oc=5</t>
         </is>
       </c>
       <c r="F84" t="n">
@@ -2941,27 +2941,27 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Cloud cover: Forecasting digital disruption in a cybercrime climate - Slipcase</t>
+          <t>Feds can't withhold social service funds from 5 Democratic states amid fraud claims, judge rules - Action News Now</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Thu, 05 Feb 2026 13:25:35 GMT</t>
+          <t>Sat, 07 Feb 2026 00:19:39 GMT</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQOG91WHZVSWFoZEc1THR0TEczWDYxWExxNXRCa0xfcmVaLUZxcG5KVUpULWp0aUUzdHAzakhLUExFVzBTLUNtYW43dlNWb2d5QTJ2MFFpX1ZIV1QwbmtuTy1hdVRMdDJKc2ZRZWVIdkpobUJuTWktMFhYUkJIMjhNRjZLSUVHbm9MZ2oyMVVyUS1XaUdUY0N6UlhwUzJjYkI2R1FxRktn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwJBVV95cUxPNjB4SURaaUJUUFRTRXA4a0VnQ1FUR04zbm8xVHVxWEUyaFJ2TzR2bVR0cS16ZEs3RkxObVZHY0l3enBzU3l1YlF0cWtGY0NMVWM3TktYb3gwQnI3bFVwQXlHQkhVWnROa1FaX0pLb2tTUWI0aXg0WWFxbjlhZEYtMjY1a1JyRXczTmpza1p6ZERZZzJ5eXluM2dFbmxoWERXNWcxLVVicmR0NDM3YmFPc3l4Z2hWenN2ZHNiYmY1cjVOTjdXZ3Z5cVBzdjJiWTBkNzdHanlZdzVhbUxwWmlETms0MXdFM0JNR1Q1YUhCd1lYdHVCQklUYXViNmxVRmZMaDNkcENsZVdPelk?oc=5</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -2971,360 +2971,30 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Amazon reveals plans to spend $200bn in one year the day after Bezos guts Washington Post - The Guardian</t>
+          <t>SASSA ramps up social grant reviews to ensure compliance and tackle fraud - Cape Town ETC</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 00:55:00 GMT</t>
+          <t>Fri, 06 Feb 2026 14:00:56 GMT</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOOE93U3BaYmt3dEE1ZFgxOUhxczZURUgyTFpIX1B4WUlaeDE4clNGOTBNbDByNkdwcjFudTJIbmVSX19TeEVmaHAzMFBqRXoyYlFWbVpKNXhNbmd3Q0p3WWs2WmtlUWJneUpBeFVFODVLZ0JRZW5lQnNPV1BVbGROaWg1R0h1V0cxX3dvWjdiS1NFUDNxUkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPWnUwNFFtSjNVeFdVZmNzenlWWmVIa1d5SFlBcjFPcXBXSHYyN2cwLXVfeXR5ZGNlVlE2NkN0NjJKVm9XdVUzem4zeVFqS2llSlAxU2l1YTlSd0ZZMEtweEtrUUFjQWZRYkswNDZneTVULUR5bW0zWm1ELWt1Vk9iejExdWFXU05BdUVMZTNZMVJ2aWxHU0V3ZGxjaVlMVkdxeld3WUVRTnJ2WVk?oc=5</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Savannah Guthrie's demand for mom's 'proof of life' is complicated in this era of AI and deepfakes - The Independent</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Fri, 06 Feb 2026 05:01:00 GMT</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPbFdpOWdDX3E2aXRvbk5yNzIxWEp3djBIZHJpbGNpVHk5bTBzY014aEY0Q2E5Qm5maGtzcTlkY0hYTjRuRUNDOU5HZ0pNSm5DQVp5eU5vaENRTUVjb0picjY3cTk5cFZxdXNXXzhBVzNLRjR5SzhyOWdPS2t0NnVJMnRLVXJHUmFZQ0k5ZHJTQ3JBV1l1MS1oeDBuaw?oc=5</t>
-        </is>
-      </c>
-      <c r="F87" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>WTF is the IAB’s AI Accountability for Publishers Act (and what happens next)? - Digiday</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Fri, 06 Feb 2026 05:03:07 GMT</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPeGdmWmJjZjlGWWY0SzZFQlkzZXFWa3JDTVMzM3ZRbTlmY2VJeU5jQnVaN1ZPNFpHTlhYMWFCSG9SV2tqaG1VWWRScWpCTUdxcmpPQzZsWXJHb1h6cFQ1NGRkY0o3bzVmd1NhbFN5VjJ3ZkJkTERkajBTS0p4cjlUVThENjZZT0d2TXBESkFMZ2RvejY4ZDN2NXlxU05fSldUWXlz?oc=5</t>
-        </is>
-      </c>
-      <c r="F88" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>AI adoption accelerates as engineers across EMEA move into production, survey finds - New Electronics</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Thu, 05 Feb 2026 22:27:38 GMT</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNSEl0eE9RdU1xSUtub18xOWtIaWJHRHc1Q2w1TXFCZWt2OFlwaEktUTMyS3pZQm1MVk9tQUNOcFc2TFAtTGVWdXRLT1V5X1Fvc1dyel9oMUNsU2tQNjNXRkxod1NEVUdfRG1qaHNxUGJjN3c2Z2QtNTZqRWRROUc4UHYxZTZBX3Q5SWhhbWRpWmt1QzFCazM4aGpQQ1hKbmNuNzZnMjdDS25ubk5mb2wxeGMzRjhaZ3dqNDdQZ3dxZkpPM25yVHNv?oc=5</t>
-        </is>
-      </c>
-      <c r="F89" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Evri Group launches pilot AI and data apprenticeship programmes - Motor Transport</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Thu, 05 Feb 2026 12:46:06 GMT</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQU3hVdDQ4ckhwY0UybElPNGhhTmxwQ25JVEVkUUh2d25FWjVMd0kzV3hxb3hEbVE4TmdQdzJzMGxhemdWQnIwdTV5Z3pDNHRnTHlmWGRqM1JFZGFwOEFoZXkydzQzQ0FsZUwzbmp1YWFWcVZvOXpIWFg1dWdMOWVPMUdXRGljcHZZTUVrODVDVWRsR0lRclgxUTdhUFZxN0FoN3dhdUg3S1JNR0szeFZSNnZQam5pT2JVbktVQQ?oc=5</t>
-        </is>
-      </c>
-      <c r="F90" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>UN secretary general discusses future of AI accountability - Jurist.org</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Fri, 06 Feb 2026 01:56:48 GMT</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPTlQ5ZUpTcC1EWVZkbXJGSHFEcWJpaDlaZlBfNVJaNjVmaXpqYUhZOTk5N09QSFN1U1M1TkcxaF92aEFMWEt1SXIwS1RtWndqYkV1RWR6UGQ4dHFRNk9Ud1NsenVpMGdJc1pVWDNwQzJSQUdsX3VLeS1tTFRneGtWaWljanUzdDg3WU1Cb3dJT04tNFM3NHA0QWMwVQ?oc=5</t>
-        </is>
-      </c>
-      <c r="F91" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Intelligent Infrastructure: How AI is Enhancing Terraform Automation - Atos</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Thu, 05 Feb 2026 17:07:39 GMT</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOdEljUmlBLUVMV3Y1b2VKZmMxZk5MWUhBSlR3Y2ZJTG9KaTJQM2UyVTVZcWNqSm9sSVJ2dHpCbWY3eFhrczNWQ3ZCVEZvQVRHd0dnVGxleGoxdUstbTFsM3hvWUYzaS0zNVotc3huc1B6MDJ4Qk5hLXdDQUtvbWE1WEJjZmgwQTZoRE4td0swNmhncGs4T29v?oc=5</t>
-        </is>
-      </c>
-      <c r="F92" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Insurance AML explained: red flags, AI and reporting - FinTech Global</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Thu, 05 Feb 2026 10:09:21 GMT</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxPN0lEWDFzaWRLVEdMaURtVjdYQmJ4Y2puUFQ5TGV2VFVTWC1KcDNXbXE3ZXNMUlQ4VjEtSV9UVGFiLTJYU1JqUDM5QldrSlFMejFFY2tnZVBLMjFiNEZmT2o3Qzc3cmMzVW9JZHNrT3BBOG9WZ0RWLWR0SFgzM29mX2xVU3FfT24zQnU5WlJR?oc=5</t>
-        </is>
-      </c>
-      <c r="F93" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Alibaba Cloud deploys AI innovations for Milano Cortina 2026 - Broadcast</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Thu, 05 Feb 2026 11:10:31 GMT</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNSTBLaDByblBiX0JtUUN6TXRUM1B1WHVqcHZPTGVnUmc5d2dGMkJfVlhlVWxpemZOUUt6MmlYdGNpYl9NQk5zM0MxRXFna1EyUkQ4WmNHeVVVUWJwdWpnUU0tamd4TURBaWx4ZGFkRVo0cTdJcHMyOWVtQk9XQ1dHYUNwWkxUbHcwMnhTbTVwaDhEclZVbUZhczctX01BaE1QSGdDcm5ieTloX3hJSmlRdGVfUzNHdTk4Y2djUFJMa2JBSS15OWc?oc=5</t>
-        </is>
-      </c>
-      <c r="F94" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Vexlum Secures EUR 10M to Expand Semiconductor Laser Manufacturing - The Quantum Insider</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Thu, 05 Feb 2026 15:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPUlAzRXphdURhcjN4X2lqaUpZUnhOWmZ1bVhRVjh0UkpQYUwzNm5GR3FvdkV3RFRXa3EzMGJEVlQ3TFRwWHJVVWtnbjdhRlFGdXViLTZFSFdTWVVqM25vNEdRcUpMU2tKNkN6MTRNUWMzcXpkQ3p4RmxzaERxNUxUM05MNl9vSXNWb3plWVdycUlkN1JJZU5iTDlISDI2bnBRTEpmdDVpTQ?oc=5</t>
-        </is>
-      </c>
-      <c r="F95" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Fraud_Scam</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Bipartisan bill to tackle social media scam ads introduced in US Senate - Biometric Update</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Thu, 05 Feb 2026 17:16:00 GMT</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPa0k5QncxTVJRU1VrTE9WNzBkWEc0M0YwX2dOdThzZmlKaEw5MGEwNkkwMm9CZG93ZkotRzJ4dzJXaW9XRFlERHhPTXpkNElVczhQMnlJRDV3M0g2SFg5WmxZRl96NE03XzU4UmpoUWh4d2prd19lMXJyemdabVpVZ2EwcXpoUWhnSW11MFQ2MHNLeHJCLVZVMkgtT0VUaFIzU2ZzeGxHdmU5Q0c2RXNj?oc=5</t>
-        </is>
-      </c>
-      <c r="F96" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Fraud_Scam</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Police Probe Social Media Scam After Nurse Loses Money Online - Love FM Belize</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Fri, 06 Feb 2026 02:01:04 GMT</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQZDRLZlotejFPUGkyLVJkcXdCUHVvWm5tc2d4S2psVExlTHhHc29pa2NIUDBCb3JtM242VFRVSnJDWmc0emRxTmd6cFBQZ3ZidXM1TlpHTXZYdGpzWmFkT3RiMjFSLVhhSndybXNfa3RYenY4Uk9oZmwtd1lFQjJaYThTXzVoZ25m?oc=5</t>
-        </is>
-      </c>
-      <c r="F97" t="n">
         <v>1</v>
       </c>
     </row>

--- a/data/daily/topic_feeds_daily.xlsx
+++ b/data/daily/topic_feeds_daily.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F86"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,17 +461,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Justice That Works: Report of the Scottish Sentencing and Penal Policy Commission - Wired-Gov</t>
+          <t>Treasury issues update on car tax 'structure' policy after MP query - North Wales Live</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 15:05:26 GMT</t>
+          <t>Sun, 08 Feb 2026 06:19:00 GMT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxNWDVYOVI5S2hSWm1nM2VoVlNLS2pqYUxQUDA3SXQ1cDFtZllkbW1Zd1ItR2x4RWVzVnlRajEtbUNTa1JWelZaUFBwcHBWLXRCS19FS05EMnA5SXY3NWFsaUhqRHNGVHJ0SGRuWmZIcThuS3JPX1ZQMHh5dlZNVXNwbjI2TEpKQldSMHV2YktKQ3diWmdjSGtVekcwVWVqTWkxWGQxYnlVYUNEY192WHdCZ1FpWmhkN2J4cUoxc05PcEJnSDUyVmdYXzlnM043U2x5UkZ2dldYUG9rSlVFbUY3QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPZHR4RmpfWkRiX043Y3JWYXJEOVdmZDBUUFJGR3pVQlp2eGRaSEY3Zl8tZmRsTGNnSTl4c0poT1l6a2J5a0l3UmdVUHJ5VU1ydnhNTTFiQk91WDNxU1k5azZpVzdqdFBzbHBkR0t4RzlFSG5JTzhrMXFDM0dfOGUwZTRLV2FZX3VnR3JXWlVrenk?oc=5</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -491,17 +491,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US Policy in the Middle East in the First Year of Trump 2.0: A Report Card - Middle East Institute</t>
+          <t>Herzog’s visit to Australia builds conflict not social cohesion - Asia Pacific Report</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 22:14:06 GMT</t>
+          <t>Sun, 08 Feb 2026 02:58:24 GMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOSWprdF9OVEdlZWNRT19MTm04QjZfV1FDUjN3TTMzbFlaOUZ6WVgtcTNBTnlGWG1XRkYweWRVUlB1NnJpc2x3ZjRXUzFZNnFzbEI4YVhrMzN2TXg5bmZ1T1RvT0djTkEyZ280dkZ4QXVHX2FRTFduMER0YUJiOUtnNWxPYUNLT2JSZUJOTElpcDVpSkx0ZFU0UUZXc29FQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQOV8tUW1CYVNtdnNpOG40WFYxOHg5aXlDTngxTmRYdzllZDl5S1Rla09ENkh6N21pMjlBZXF2T2toMlRpbC1mYlhhTmZNVzZFTzJWODFCZEI2azRGX0pkT3gzVDhaSHhlVlk3bUttSnBKOFA4bExMYVNMN2l4RmtwYXVxY253UnZxUzFlaHFKX0drYkI2WXMyM2p2NFRaRVlpQ1k3am93?oc=5</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -521,17 +521,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Maternal And Child Nutrition Backslides: WHO Report Reveals - Health Policy Watch</t>
+          <t>Internet, Cybercrime, And Politics – Analysis - Eurasia Review</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 19:41:22 GMT</t>
+          <t>Sun, 08 Feb 2026 01:05:40 GMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE5PRkhmSGNVS2F0VHhnYXdJMWxtVGpSREg5djNoaHdsdHl2UWNjSl9BWVBzLWdmbWxtTHBmT1ZDbXlpQ01ZQ2FlQ0hNLWVydE9qZlVlVkowYnRielhSb1RKcTR6Zk5uU29BSFpBc2hmNDl1MEN4SmpmVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOTktNanFySm5jVFRySkJKdmFQUDFsYU9fMU5RQWluV2g3UGVTdFIxZlFMVXJQWExuRlpuT3M0TXNpblBabGRreC1jdEdIMVA2dXdwdzJiblA4Qi1ZYS1BLTFHc055VGpkMDhGSEZyc3ItMVkxOUpsaExfd2N2SkNyQnJ4RTBrZUNu?oc=5</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -541,27 +541,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Current_Affairs</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Welsh Government Provide Update on Menai Suspension Bridge Work - The Bangor Aye</t>
+          <t>Port Vale 2-2 Burton Albion | League One highlights - Sky Sports</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 14:52:16 GMT</t>
+          <t>Sat, 07 Feb 2026 14:35:01 GMT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOQW5mTHlZNDJoYld3al9LbV9IREZvMDdnV19Kb1FycjhZTF8xLWRkTnBLMGdLNTJXdmNkZGxOSFpDWHNvcW1jX1RwakZURGRmb3hscWdoQWREZjM4N205cmVmZzNhSmphWW9zZVpBWXpCc1o5UVBNNEtoRnNMZ2hpMzByeGI5U0xmUW11amVwVjBzZ3pzQXlaNQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNSld6WEktOXhONmYwRF9WRVVMQm1Hd2w5bTlyT2ljUmxUUWdoYTJLcmFxQXpKOUpSWjFSeTdGYXZQMUpUVm45UTB3aVliU29KREdiNmVldkhGU0hQVUpYTEFUREV1VHF5NUp6RmxBSWJYamNMLU9LZ280OFpjUm4zbUZpVmF0dDdtWFpRU09BTUZfdVhXcGRoemVMQmVONUFfenkxV1A1ZE4?oc=5</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -571,27 +571,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Current_Affairs</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Discover Core Update, AI Mode Ads &amp; Crawl Policy – SEO Pulse - Search Engine Journal</t>
+          <t>Trump signs executive order threatening tariffs for countries trading with Iran - BBC</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 12:58:09 GMT</t>
+          <t>Sat, 07 Feb 2026 08:06:45 GMT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxORUFnNC1YMXZuTGNMYXdHWmplMzNfSHJ1b0REYnVWZUp4TGV3ZzhwSDQ0MHlBdjRPXzVLSHJKRDZKcUxnbnF0aDRQZDdvYzQxSEpkUTkwSE1HeFhpUFJUcWVjaGhITUtkVG1wV3hlSF8yM2lIY2ZibEVTd0QxSUZ3T1hFY20zLVFaUFZEWU4zOW5wMVdjd3pSR1E0WUxSTHI5?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE84aTZ3SE1iWEJEbWNNZFhMMjdob2hBaUN2bGVqQWx6azRuUE1YdktPX0ktMlVwNzl2X1JreWgtNERCcWN0VzFMdXB1Ul92eS1DOEpCQURpR2d4UdIBX0FVX3lxTE05d1E3NGFURFN3RG1fYVlwckFYLVZnYzVROFM4aE9HZjZfLWlJN01rOVhMS0VZdkh4QzFTRUdwbC1aeGU5TkNuOExScXhxeW4yY0ozYkpqcGtwaG9qd1FF?oc=5</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -601,27 +601,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Current_Affairs</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>International report - Caught between conflict and crisis, Syria faces 'incredibly fragile moment' - RFI</t>
+          <t>Iran Sanctions and European Energy Security: Compliance Considerations for Caspian Trade - The Times Of Central Asia</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 10:12:57 GMT</t>
+          <t>Sat, 07 Feb 2026 16:41:32 GMT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPdl96V0tOdUFfMEY3eXJyMEZ4enFIOTF0enVzWjloeFF2alNkXzdSY3RpaFZ3QmdLSnVxR1BVLTBQajc2bmZVSDB0N05SWWZsN1RKMjJ1aDJRNUtmZEZLRm1tN2FVeW9UNXY5V1g0bjBhQW5ZbjhMdjNDRXpSVzR1dnlIR0UyeTB2SE1INlFTazNGcm1MMGJRWU1BN3FaMG5VMmM5UXhvQUVjUEgteVpBaXMzU1k3UnNObjdfSWc3VTVyWXV0bGZIeTNfeUdxQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxON243MGVVY1ljc3JBeURzUll1bVpLamFRRjdicXVFbzBKMTdJamZyVFYwUDJoeklEVHNJeG9QMWlpUjg4cW1yLWpMVHhFQUxIRWFTaVRPM1JfeG1Ma3RWa1hVQXk3U09MeXRPVi1IVlo1ekZ1UW5qWjhlT2NHOThtVXk0eDVBWjFUdFBDTFd0SExhZ0hwQmxJOGw0Ykh2YzdWVUJ5Z0t4UE1YNlVi?oc=5</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -641,17 +641,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Trump signs executive order threatening tariffs for countries trading with Iran - BBC</t>
+          <t>Porthos: Decarbonizing Europe's largest industrial port - Air Liquide</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Sat, 07 Feb 2026 01:28:56 GMT</t>
+          <t>Sat, 07 Feb 2026 15:10:48 GMT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE84aTZ3SE1iWEJEbWNNZFhMMjdob2hBaUN2bGVqQWx6azRuUE1YdktPX0ktMlVwNzl2X1JreWgtNERCcWN0VzFMdXB1Ul92eS1DOEpCQURpR2d4UdIBX0FVX3lxTE05d1E3NGFURFN3RG1fYVlwckFYLVZnYzVROFM4aE9HZjZfLWlJN01rOVhMS0VZdkh4QzFTRUdwbC1aeGU5TkNuOExScXhxeW4yY0ozYkpqcGtwaG9qd1FF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxOUjZUN3NXTlBIal8zRDZxTnQ5cDFrbk1NYlVuMEVnclB1N09MazJTSlNncW40Umdkbk9FejJxUEZmLVZGUEN1aWQ1Y1hJU01hUHA4WlI1b2xJMXNLbVVjYjFvODZfQVo1ejVKVnYxOXA4bGpES2hUZWJjNnRaN3Q0ek8xMkNZWnM?oc=5</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US imposes sanctions on ‘shadow fleet’ accused of transporting Iranian oil - Al Jazeera</t>
+          <t>India embraces free(er) trade - Financial Times</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Sat, 07 Feb 2026 01:36:16 GMT</t>
+          <t>Sun, 08 Feb 2026 02:13:50 GMT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOQ1ppczJOc0FGTGloTzA1c0QybWotUXgtMGoxeW9UYVpzQkNxRWxObW5iSzJ5M2lEREgtcGsxTWhKS0NEYXJaeGVJTDNtVlM0QlNZVkVoSEE2c0NWRU1qS3JscDFHcEVyN21vQ09lOEtZdTVrQVgzZ0xSekxmc0dzZ2FfVm9HM2c1cDVVckZ3Zl9BX2lFQnNBcHIxcXNmYjU4T0hDN2FMeWlQeHlVMllqZHln0gG3AUFVX3lxTFBjR1l1cmpuczUwcXdnc185LV9XUmR5V0FTbm1nM2pmeUs3RGZRM0Fsb0M5SHdtUUo4Z2NjaDhpSm5SeThZYTF6ZW9BblUwTFVvRGRiNXlGc2FlbTgtWERpbi1UZVBZdFpIdF9PeU5rdXZGSmdGTEZ2bGp6Y0EzZmFLSFM1RGQwVjBCSGVTeU9nUEd0SkR0aVNXck1BTU9uOHNkMUNmZ0RPczZxb2trTy1CdWdoN002UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE41a3QzQTJMUlVQTGVXMm5maWVGTW83ajJzd2tWTDN1UlFxd2hpSzUxU2Vfa2ZzM1MteG0tTG1ocVY2ZGlMclAybzJsdTlIU1NCTFRPUllMcjN2dEs4Z04yYlBzRWxTeUp4MmtyQ0g5NnU?oc=5</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -701,17 +701,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>EU targets Russian energy, banks, goods and services in latest sanctions package - politico.eu</t>
+          <t>WATCH: All White Ben Waine finds scoresheet again for England’s Port Vale - Friends of Football</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 14:44:00 GMT</t>
+          <t>Sat, 07 Feb 2026 21:14:11 GMT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNdUx5aUc0Rkl1Z0dPQllNbWdNOHA5RzJvSHFTLUl2WmtZRjY5dW9uaEhpejVmUmIxc3ZqUmYwMGlFSzZiQlp2bDhnN3h0blA5R0JuX01YZ0VwcFVMTjB5Q09MZnVhUVJBMWJ5S2VHNjhDVWJYcEZTWE54bTc3TUFMNEtWbmhMNFpJcDRSN05DdEN2Tm1XYWw3V0ZUbGljbzd2NngyaGpxMTFEVk1MckdHeg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQZlhZeFFyOVVSSDV6cG1OdTBleTk0NVRVdVJyTUxlemJTX0cwdkgtV2ZVckN5OU1wRGExWC1RelpMUkpJdF95QnNtSVVaVERLWnZPS1VUNzhiUVVWZE1saDhndEkxUE4yVHNmZXhWMm1KWWktSHlKYldTeFh5dllJNHRwSjA4Rl83VXNpTWZNR2dWdXdhd2tPYXEyU1FFTW9OSUJpVkhMcXFGcWVHQnhLd3JuNmQzZWFjT2pv?oc=5</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -731,17 +731,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Commission rolls out new Russia sanctions package after delays - Euractiv</t>
+          <t>Genoa Port Strike Blocks Weapon-Carrying Vessel and Disrupts Mediterranean Supply Chains - VisaHQ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 15:07:49 GMT</t>
+          <t>Sat, 07 Feb 2026 20:41:18 GMT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNcmxfMW5SbkItWVJnLS0yMktHbUI2WEZPdC1KYnc3TVhMMUd3UWY1aHhkTmdRc0d0MWtDOWtELVdCMnNIZWNQSERDWVpZQU5rMnRwRHkxeTlPZGx5cmtCTlFBMUZYYzY4TEpZd29ubkRpaDR6b3ZTaDRHR25MOUNXbjhaalNXcDFhd1I0WGQwMUlYcDNTbTZSUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPeFNlTkFhbnZ3bWthOVdua01LYk9zVVFDZ2pRTWdDR2VVYXJzT2o1Nm1PZU1vZ05OTHB2WG91c0xQSGhNQWo1ZUJoRXVqN09TdkhmOGxZaGVWdmQzWVowdllCblRNR2ozQkZ3Z3ppUnl0QkY4THhrc1pHWFF4MWNxX1JBNjBfcDlvZHUtUkpTUDdSeDJURnRVMFcyNFZsOGprQjduTEtKUlpHNEV3cXpPX1EwZFh5V1lDWGl3WVVadWNoWWFvNENaUW5aWQ?oc=5</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -761,17 +761,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>American taste for champagne goes flat due to tariffs and weaker dollar - This is Money</t>
+          <t>Veezu Hull Switches from Metered Tariffs to Fixed Fares - DM News</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 21:50:21 GMT</t>
+          <t>Sun, 08 Feb 2026 07:41:14 GMT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPZzBtN1pxRXhPMFFNZ1M3QllHTEZwM3FFQjktM29VbWdKaGVPelhrX1g3cGVFYnBPSjYtZ3pITzhydTZCek5Ndm81eHNvWnJzUk1mcmxoQ3FrOFl2NENmQldMRXltb1hIUEZ6R1hhdE9OZkhEclFycUl0S3g3ZXZ4UTBxUlJrV3N6X2ljT0pRb0JJbEtwWHpoVUVxRTlhY18zR0ZIU0pEdzNpWndicHhQNUdYUUhBUjZ6dmJMVFQta9IBxAFBVV95cUxPVWtXMldqc204bXdLb0djQW1LNzhOSl9WNTFDSkhQM2xQTGFKWlc3Nm9NeUdsUWtYc01wcmtpM0Zkc1FtNXRLUjBHYmpMTzRfRk5EZ0oyTjlVX2VWQ0NBRW9nWmFrSU1mWTdBMF90TFdISm0taGp4V3RUTU1uS2tFTWlHRy1MLXM3cjI4alc2UlEwZkd6bnZZNVNxbjhCbVVMLUpkeFBEVXVINnpqWUNhZHVmeXY5aktlR0gzdll4NXlBenRP?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxNSk1ULXcyZlRrakJzejRGcjl1VFZPV2h1anVFSHRob3FzQ3Q1cjhDTFRISFVHTXdrSkNtajVuemU0QlRDTzhScG5pTGk1M0dpcWRtZmJFTVp2cm9oZW10ckVxaGM1ZXEzMUVXUE5ONHJOZlBpeHNZM1gzOWlNV0RKWGFqbw?oc=5</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -791,17 +791,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mitigating The Risk In Your Supply Chain - Construction Wave</t>
+          <t>Drug dealer jailed after creating group chats to share child abuse images - Greenock Telegraph</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Sat, 07 Feb 2026 07:07:07 GMT</t>
+          <t>Sun, 08 Feb 2026 06:30:00 GMT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE1oUkxwNlhzcktTSUJEUUE1WWM3S0Q1cWxLdlk1VXNRRUtYcWVYX0otNUNQQ3IzOXM2WVZMTkQzdndpOTVtTE9VYjJaczFhMGd3ckFHZHh4TDVXRGU3X3B6SVJXN1pXR2FwUHVuVlQ5bGRaVHVTNlgxdl91U1I?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQNWtRUnZBS0JpbjRzc1JUQUVOT1R5WVQ1WUJJeTlQY0pLNGQzS0Fxei1NcXFBa1QxQ0lWRzdweDBWX09kb0xwMEQ2eDd3RTB0dUZQbFNJeUZnd0dkOE9DYmp2OURET0tVbEpva1B2LXFnOFdwbXd0SFFlTFR4WVJYY1o2eU5MWnVwWGw5STA2OU5fNjhZX1hOZ1htdzVDWDM1VlE?oc=5</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -821,17 +821,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Visa-sanctions strategy pays off as Angola, Namibia and DRC agree to accept deportees - VisaHQ</t>
+          <t>'I don't believe it!' - fury as council say 'horror' waste site is compliant - The Worcester News</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Sat, 07 Feb 2026 00:14:21 GMT</t>
+          <t>Sun, 08 Feb 2026 05:00:00 GMT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPWGNCTGw5NGktUy1IOGRvTHQxTTdVVGNWQzIxNEU1bWJ3ZmswdzFvWU1HSjBYc0hnOURHVHFOMkhuTDN0X2M0TTBXcTNhaFZ4dnEzLWZyZFpaTjRCcFVJTEtnb0pWN1lLbkQ4MkxYYTE0R1BrU1NZT3pGZlRkV24tczhJVWRtbjZzM3B2VHJaVk5aQU9lNDRIc0xNSjUydDQwWnpNNl9aSko0QlE2TkdpOGJOOGdOYW01QlBSdndmSndmTVl0d0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQSjhVT25RWnRXbDZiWjBwS0ZCWFdjNDJWSmZlWUZYbnRJN0doODhxQ003d2dxSkFxb1hnZERuOXQwZmNtYVhLV0c0YkRfXzBxeFVoTFBkWnB2SzFyRkpUQnB4UlQ1d1RUbWZKalMwYVJfWXFlSTJBZkpXeUlHN1p0SFBJbkZ4ZU5SeDRoUWhWRWZVM1lJYzE0TU1nVnR4Y0U?oc=5</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -851,17 +851,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>M2i Global ships titanium, gallium in supply chain milestone – ICYMI - Proactive Investors</t>
+          <t>Somaliland leader says Israeli firm could be granted port access - middleeasteye.net</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Sat, 07 Feb 2026 05:45:59 GMT</t>
+          <t>Sat, 07 Feb 2026 23:22:00 GMT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxORXNpN2tTNi1DbjM1eGloNFF1SU5TRnVyOFFJMzZKTXBjU3I0X1RWRkMtbFNDWXVxS3p5NHh3dGtLemJqaTR5UWxCNVhvZUUwQmd4VXVPUTBLTjNNOF9qUWdiOHJ2aWFXdVBxZ284Q1NkTUVRY3pCUExZLTFLdXF2Z25XbWw3RDlPbXR0OFJWUnBrMmVqa0s3bEM2b2VpbVRsMTR5WEhocERCRVQ4SG9WS25KeExfcFJKVno0bzd4cEYtSGpiTE02eHhzeWdVUUNlS1NsdQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNamstcjJQNGl6NWVGenQzZFNVemZIMFBvcHVEalhBS3JJTHFJbWpiSlZiczdCQUdwRDZnMHRCRkRxUnpHNTI2dURtanZuRy1DbS1tcjVUVU1vRDV4c3NiSjRvd1M2UjRob3ZPRFBVYnRjUG0tdE1TVDlEZWxQM29pSnl6VlhFYlhEdG5vRFUzR0hzVmUzQXNCMlBiSDJoQTA0?oc=5</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -881,17 +881,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Scottish football legend says Port Glasgow Juniors are 'in a fantastic place' - Greenock Telegraph</t>
+          <t>COSCO SHIPPING Debuts "Budget-Friendly" Sea-Postal Link to Peru - LM - Logistics Manager</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sat, 07 Feb 2026 07:00:00 GMT</t>
+          <t>Sun, 08 Feb 2026 05:16:39 GMT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNOGRuaXVrVVAyZDcxXzJkV1hfM0c2QUdNZnBQMUVRMVJiWmNWUXI4bjB2U1NJLXlYNWJOU1NYdTZLaWs2U0MyUXBpTEdlTFpoZXViRTRzQ3RORXhxX2kyd05SN0piX2E1NHhiY1VReUZiOGx3ZjYxT2YwYlo2WGYybC1xTXpaYUc0SkUtbjByRVlmcER2ZDBzY24weGxiNjN0MGJ1QU1IQ0g4bmVwMlctOUFjcGpia1pCSGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOb1l1ZU1WbmJNV3ZFQ01WaVdQRUpSR1JYX1BJdk0tN0FzX090dktwNlQyZEJMWE5XV0xEQWtCSE9fNzVOS3hkTkx0eVJMZGZRZjgwT2dsT25vV0tlNHRTX1RRRC0yajBOY05RWTYyWkFkbndzUG13MlRBa1JSMnQxZUtiZzRxSmxDVkpDTWxIbUxYdFZyNWV3?oc=5</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -911,17 +911,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Port Tennant storage unit break-in leaves items strewn on road - BBC</t>
+          <t>Optical tissue monitoring predicts dialysis-related fluid instability - News-Medical</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 22:55:15 GMT</t>
+          <t>Sun, 08 Feb 2026 03:04:00 GMT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE9TWm1XdG9YN2FZWGdjc0VvaC0wZi13MVJYaFFGUWtESUZhbmFyLU1oaWpBbUJaQlpUQmpPMlNMdDdsZUlLbjExOUdLMjlkVHdWUzZRa2JmQVcwOTM5?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxORTFTdlo4bmZ0SnlNNWRpNGt6amZLakVyRFp3aERPcm1Zam9EMlp6QkJJUTdlTW5ra19qbEZWd0IxN3VaR0FZblhURFBSNXJ0TEVDZW5iRHlLV2ZvcTVMNWZGQkI1akNDVnRrVmROcGpRdENCTXM4R0NNR0t0dWhSdGlwQTVlSUlJR0tMSTJMWjlSS1NLVHZnUkh6YkJROG93ZXFsa3ZyY0xuS0VqOFp1UzhIaWIxTU92?oc=5</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Port Vale: Jon Brady wants League One strugglers to make Burton game "our day" - BBC</t>
+          <t>Thailand votes in three-way race as risk of instability looms - Reuters</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 18:10:13 GMT</t>
+          <t>Sun, 08 Feb 2026 01:02:55 GMT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE1ST013amVoYWowTHZiWllTbHdhTFNmWjhrRzdfZmVrVFlWQWw1aHlCNXVFR2w0QUF5TFFaZkJXMTVIbnR5Y085M2NyM2paeWhhMXcxc2ZVejc2eGM1Si1TQzZETWxIY2M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPRURUVDdMXy1PbHNYa1pFQVVoc2FGbzJwTlM1OENlNXkzbnl6WGd5eGg1UmJwemJ3SWtlcHQxbmdLTGlBeHBBeEh2aDE3WW56OExyZVY5ZHZKVWtPTEFSbHBoQ3RBYzdCUTNaZ0psaE1fRENiOTZDVl9BTkVfcXpMNnItb0dGSk1JTlJDbVlNaDBUU1dTVGdwQ25tRHpDQlJ4YXEySlBUa2lFWkE?oc=5</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -971,17 +971,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Port Talbot woman's journey from psychosis to mental health nurse - BBC</t>
+          <t>Algeria’s Russia Deal: How US Sanctions Can Halt a New Mediterranean Rogue State - The Times of Israel</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 22:53:32 GMT</t>
+          <t>Sun, 08 Feb 2026 01:47:00 GMT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE9JbUNKMktJUDZFaE95XzctSFJ2R3lkMHMtSUdkbnhEZ2VBNXJBRjFDOEtNS0JvUzlGU1dMb0FEUnlTWFNCUWNqNzIwZGV6dTZuQ2NBc0FwaTM4dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNcTlQS09KY1VPd3c4M3NiSVZTXzlfcENtTFp0UjR4N2JYMHUyUk83LXh6SFRyYzRpS0lkV3VpTDVfTkpCdE4ycXg4WURic2cwNGdFakgyUm90UVg0VlBsM1RhQkZIMjhrSTVsUkp6eGNyOGVkOV9QWmNhRFJaNW9SWVdYTFpYUzN2amZzRjFWSXVWblBUUVoxUkVWd3dHT3Ffb3BLa3c2LV9abzhackxHQg?oc=5</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Massive crude oil tanker sails into Dorset port - Dorset Echo</t>
+          <t>Former British commander Richard Kemp offers his assessment of the instability in Iran and weighs in on whether the ongoing unrest across the region could be drawing to a close. - Facebook</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Sat, 07 Feb 2026 05:00:00 GMT</t>
+          <t>Sun, 08 Feb 2026 01:13:15 GMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPaGctQy04eGR4YUlEVzFHQVhDRnMyUnRhbnNUWE01MF9mV081TVk5NkNNLUh1LWR5QzRDU0xuczJEWnRHbVBCTkt1bUplNmZBenE2TkJ3Z2JWem9rS1dHZ3I3eGRneHpieGJWUU1qczI5bmZWWHc1ZXNUZ29BcTFwZ0x0UDUwcGtYVE9aRm12R2VhU1dUX3BDVTd4TVZPQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxQN0NJQ0Q5Q0tpVjFwQzRlZjZ6LTNvZDdEN01XOWMxZ1lLcVU5NUotNWlOSWhsTWlyTnBIOTB6VmswaUtMSmEySmJQc1dBa08wRzQ1Ry1rcEtYWlo0NHZReXpxdkk4R25zanNpWDZEbGItdGl5aHZ1OWhQTmpOYm5LVTlHZGJrOE90d1ItNGZFZFJKRnVaOUxjQzFtRERhXzUxWVBkQ2MtWmtqN19hYkREaVlteE1EZXMtY08tUDJDamVlOHZsTlVDOGgyOFFhUURwZ2cxNzJ5MTIzYXQtUHBJ?oc=5</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1031,17 +1031,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Maersk to cut 15% of corporate jobs as tariffs hit 2025 airfreight volumes - Air Cargo News</t>
+          <t>BYD sues US government over tariffs; move sets precedent for Chinese firms to defend legitimate rights, interests: expert - Global Times</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 16:54:49 GMT</t>
+          <t>Sun, 08 Feb 2026 06:51:00 GMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPZHFlb3RpdVhRSm51MjJTa3NPNmViRUFtQzM5YXFfa0VGb0pBQ3FRWDdYS1BWMUc1RlRaMUMxWmRkTEdpYXhqUDI5ajF6UldVTmZMWVlyNjZHdHliRUZfSkd6eHZBZnkyaVRPWUJyMU9IVmFMTW9sM2ZsLTZqcWRNd0d1WHNuZEpEYkFkSVZRQUhzWHlFTE9NaTVDVmdtWmFzMHlQeC1VYkhkaERhSHNEbzB6aExTNkplOV9PZQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYkFVX3lxTE9NYXV1UlY3c3NvQUZSRm1GQ3QzYldadG5zSm81dnp0T0NBbVVWdkJrMFBaN3JPVC1SM1lVUThVXzFPY0k3eUtTNzNaTWQtTk5kazU0azdzbG1IeUZpMDhDLVBR?oc=5</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1061,17 +1061,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>EU hikes tariffs on Chinese ceramics to 79% to counter dumping - Reuters</t>
+          <t>Victoria International Container Terminal extends contract at Port of Melbourne to 2066 - container-news.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 15:33:47 GMT</t>
+          <t>Sun, 08 Feb 2026 06:00:23 GMT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPalM4UnI0YkpVNUU3Vlc5TDJXUUtTLXlmMWYwelRseEVlZnNJMTRlZW40cnFra1EtcTJ3Nl8tNXVsdnhyZkFUU0U4aXFnaGxYLWt0UHJGa1c5eTlrdEFTQUtzM0Z0NlcwM0xPTFZuWWIxV2FzTWVvXzRIMFUwUUNsSGt6VTlYNzBMSW1LcHBlV0ZkWXUzRlpQS2NscnNsMnBON0Q4TlFMZmJvVmFfbkI2NHFWTHRpSHFxVkRLSXd4TE1sWjQ3TEVZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQcXROdUd2LXR1VUlGUFVxRGVqRzVEaU0xaGRmTnA0T1dYWFdtaDNWa1lOOHVIM2xwSDFZR2VLM3pXMm54RlhOVU1hT3hXUkhjRVdwemJ1VnNPRXZTekNydnUxYjlJS1UwOUNPOHFHRkI2dmhYb0FQMHV6WEZHN0VkYkpwYVdhcnFOclZnMGJGUjNfaTFJTV9ucUtzT0lLcGl4dUQyTnh2N21tMEpfdFplOThDbFc1dw?oc=5</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia Secretly Shipped $2.5 Billion in Cash to Iran to Bypass US Sanctions - UNITED24 Media</t>
+          <t>Ukraine's Parliament Speaker Makes Sanctions Case On Capitol Hill, Warns Against Prolonged Talks - Radio Free Europe/Radio Liberty</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 18:27:29 GMT</t>
+          <t>Sat, 07 Feb 2026 13:04:36 GMT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNRWRXT0IydTBkRDNKZ2ZoSUJHMlpmVnhNbDh0eFdXZlNPUWlFMTNkRzdJVFpGWWJ1MkNlcDdIMEZ2RE9PUmJtcGtKbEZoMGk1d3BON0VUclpXMUtDdjBUcVdKa3I3a041MVI5X3NRc3ZJZHhQcmJHb2I1djlrLW56TUFxQlYzdlBlajZjOUdzV3Y2YUlTNmpOclZQb3otVnA2ZW1KYlJMS3N4QVI3OEx1WTA0VnJCMHJv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPX1FKSHkxLXp4R2xWYmtxS0pWXy13VUdTMWw1VDJETGtyZlhHZXdadEotM1lKZ0V4cWlNaUN0YnhsLXlCVEdrRnJsbUFHWTdTQUE4OF9GWlZfVTVwcEs3Y2hQeWFlUUVNSVdwWGhvWWNJVi1GS1lnWHRkZW1wUlI0RGdkRTQ4MkE4NjBMZmd0WmJOd0RMU3B3MjVRTVZxWjU2NGpIUNIBpwFBVV95cUxOTmVpWkl6VkZ2dGRZSEdzZk5MNm9udUNDOG9aY1k4Um9VZ2toU08zeGREd2tacG04MG03aXBCaXIxdkZiS2JtWmRYZFA5ZlJnZkNVc1MwNm9hWTJfajFZenhwZ0lEU1lQWURXVmtmd0E4M0xYMVd4YXcwTVlwU04zYm1NdlcwMFNCeWN1a1pVcXpOX09rdkxjeXJnSW8xM3ZPUTRWUnMzYw?oc=5</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1121,17 +1121,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia’s Time as a Sporting Pariah May Be Coming to an End - The New York Times</t>
+          <t>China's logistics costs-to-GDP ratio hits record low in 2025 - chinadailyasia.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Sat, 07 Feb 2026 05:01:06 GMT</t>
+          <t>Sun, 08 Feb 2026 01:59:49 GMT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNUzJiLVJOQTZpSk9SdDhnYlRSRGJpUFFIVTFIWVlkRXUwMDUtR2NudWFUSWRLOVdWWk01NDJEcTlpeldWNGo3dFhyaEV0TzJaUHIxd2hkckFRXzlmeXVwZHpPSTAzZF9JNzU4V3h5WHFRSnV1TWdWbzRaZW5wcWJkWmFFYjdxbkFRWHhmVmY2cVNTczQtWk9SWA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBuNGhVQ2JqbGhBN0VaSHZtYlBGY1JldThTc3RlT2R2eXBuSzQ0RThDZkRzSHRYdUstX2FJWUx1U0VNQkExclhMTWdVVUpQbV9pMmZSN2MwRmI?oc=5</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Experts say tariffs stall innovative development - China Daily</t>
+          <t>JORDAN WRIGHT IS THE EXILES' SPOT-KICK HERO AS PORT SECURE CRUCIAL REWARD //NEWPORT COUNTY 0 GRIMSBY TOWN 0 - Newport County</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Sat, 07 Feb 2026 01:19:00 GMT</t>
+          <t>Sat, 07 Feb 2026 10:34:30 GMT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTFB1aThMX2ctMEVnZEFqMU5ya005dTFuMUtjMEpvR0xpbWtYc2lsUE9XU0lkYWdYR09WTkZTSlgyUUF5VkIxWDlLX0lQVDVjcks3RFEwUDZlOVJxdlUtQTZfeHgxTi03amJWTVJSUVM5cWpXZ3JDSy05MGJGcEJOQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNaUJsUDFHUjFkbm9IbUJQN3UyMDZtTGdKRkpXc3FxSjdjWVk4WHlfWnNSSTZWN2ZVaHA2akJVMEYybTdZYU9GQ2Fhbi13V3h5WWhOaVVzalRQeEFLTEZrbHhrTGV4eTE2U2hVbTE3WEZpZThBZExmRmpaa3lRdFlHQ2FZbjJ3VmVYWi0xMExEYmhWcnBqbXp3Zzh5SnRPbElPTHBHZThOZmZOc3Nab0NsZVJLeHhUZS0xYUgzZXBScVg3d3VsSDhnR3dFNko?oc=5</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Engineering powerhouses launch North East Data Centre to propel regional supply chain - business-live.co.uk</t>
+          <t>As China intensifies offshore tax hunt, exporters struggle with compliance - South China Morning Post</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 16:45:00 GMT</t>
+          <t>Sun, 08 Feb 2026 02:00:14 GMT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOdl82dUp0V2oxb1ZyNVZaUEpGbEVBNjlrelZ5eHk5TnZXMFpZQWZ3bmtGb1ExYVltV3NLZlNYcWRlWjNIa1NibnI2eS1mUHlJSFNIeXdMMmNLNkdMVUtTSmNXMlNUbWd6U2lMSHl6a0pLNkdNVUdtejRDMzJ1M0gwSXJqc0w2dmNMRkFfbV9sTlZ0UGFmcHY0dNIBngFBVV95cUxPZHhOUkxtZHVVV2FWZUhnemZXMzRGREpmUTgtY3BwTTJtempmQmIyUmVfOUJoUTB0bllWMXpCMzNadExlbzlTczluZ3dzbWFZaGxLNmdOQ3pJZTFRWkdfU1NwdEY1Mi1aWG9keVlFVU9Hby1hZGlPNWFZWV9IM2VKRDduRnNSRnVoZ2RLcXlmZTYwYm9GckZKSU1XTUtTQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNUGdfSDc4ZlpwMk5oX1BjbmlrdU91UzNmUU9vSnVVbmJtblE4VmtaTG5KMUpRbGFvZ0tWbU9zeHZVSkJMOGZyLWZoeklwY2R4eDBpbjRfVWhFeTZRMXZfLVcwVVFBcXlIeTg3M0tJcldsT0F5TGtDY3hxS2d2eUVaQUlJVlMyb2JNSlAzZ1ZmTm44VTlkUUZrMVYyMG1jSURMcVhmMDFxU09PMUh0N0UzemxKRUpaeWc1MUpNaEhxbWdlQjjSAcMBQVVfeXFMTUdidFliVmMtbTRpdjZ2VUFrdGdnQTlwNmYyNnBvbnNmVmpZcFZuZFViWjI0VzZtbWpwMTlIWnZKa0YtSFRoc3k0cl8xR1pCcDhibXVWZkpwbDBWT1VmRk9lWGZpV1JXNHdaaEhRVHF4Mm5VWVhBYnhFOWNqanZLLUdIWDdac1VmbzFZNVlpQ2JNZmV4ME9lbF9pYkt1N1hCbHE2bDd6WV9uUzNmdXBuckU3Nm5VSFRVRmkwMlJyekxJdlhr?oc=5</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1211,17 +1211,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dockworkers Disrupt Ports in Italy Protesting Alleged Arms Shipments - The Maritime Executive</t>
+          <t>Stefanchuk discusses sanctions against Russia with U.S. Senate Ukraine Caucus - Ukrinform</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Sat, 07 Feb 2026 01:12:48 GMT</t>
+          <t>Sat, 07 Feb 2026 18:10:00 GMT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQZ3g0ei1VWVNTVkVITHc1UTJHOWtGeWlPRHVHYmh3T3k0VWpwT05zaVNGazB1RnFTOTFpNlpsd2FfbHNBM0x6cFBsdl92Ym53Y1JfdGMtX1B4dkpETEhtUDFiRzFPcGJ2cWVmZ2Z2V24teUZzUm1HN19qczJLX1lhN0Q0N2Q2b3EtbGIyM0NmYU9wRHU3aVBBT0xGdHZ3LUFaaEhnLWVVMGhuXzQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQTGVKMDNlYXpyU1lOenBBWnZobzhFa0lkZFZHYU9mZnNzRkg4NHJLNHktWkVsVnp3dGJLMEh3ZDFBT2sxeHdOM3NDOUJHTEZmS1N1SWtVdFJzUVM5WXA0UDZTREZvRjNWNjRvWEFYUXFyRUdwYXF1bVE5d0pTT3J4WTBVclk3el93M1VkLU11dkJqWDYtUk9lSXlNTC1ySFpXN1Y2bWVsN05ISzEzRS02WDJXWmYtLTFTdXRkZXhqWGJxeHNMb1E5Vjdn0gHPAUFVX3lxTE1QYlJPWFlhSzFkUjBKaFlpOGgxNzJsVHhZY1d3ejY1aWxpV0hybTg5NUYwQUFBTFlZZFZjcnlhMjlGWDJXVzRlVlR2bkhCQnFmX19lQ2FOeGFTQ3Q5WXMwWWZCT3EtMzNGT0I5b3Z3ZkFMZDhPcUJWajRJVGRzX3NXZnB6XzBQOFJpT0ZWLTlFREIxWFh5a1YzODV5UzJMeklzT0VwcXZvSFVaWkJsTjVWUFR2RFR5ZEZRZXRRYm40elNKSGtZWnYyZkNaUV9PSQ?oc=5</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1241,17 +1241,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Energy Is No Longer an Overhead – It’s a Supply Chain Constraint - Logistics Viewpoints -</t>
+          <t>Enjoy a perfect port in Porto with American’s new flights - Breaking Travel News</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 20:40:26 GMT</t>
+          <t>Sat, 07 Feb 2026 11:05:33 GMT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPSF8xS1BLNlRWNDczX0NpS05GdFVKeFJkdS1GanNBYldfVVZUNVBEMWs4WFNfX2N0VXU1OC1KTmFmOHEwVUE0dl8xY3BMT3FDQXdLVU05aVJ6cml6dGxxWGVocXpVTWZmUVQ1b0hKVkJieVZHeHFxQnBxSkttc2p1TDZBTjV3YUNUdjRMbHNCVkFFaTdDSm9VTFVPN3FUOW5zclEyb1BHTlU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQeFlmeTNpalYyZXlORGRyQi1RbUlRZXl6X1FENm5MbVhrd2tEY2g3UXJZVjdoRFlWQ3NTb0QxWUpLcGgyaVBOTVFWMnd0YXR6Y1hKRHdZQmQxQnJGc082d0dqalNxbGY0bmduRUV2Xy1aQThFbGVkQmt3SVhrTHJwSW5BYUlad0lWOWVvWjR1YWItU3BDai1IcS01dXZ2WVRwby12aWhPVnA?oc=5</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Mexico’s tariffs on India are a double whammy after US tariffs - Al Jazeera</t>
+          <t>EXILES' BOSS CHRISTIAN FUCHS SAYS RESILIENCE THE KEY AS PORT SHUT OUT THE MARINERS TO GRAB A CRUCIAL POINT - Newport County</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 08:48:45 GMT</t>
+          <t>Sat, 07 Feb 2026 10:04:19 GMT</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxONTVYYjRENmRLckFqU2JYNVBqcGFzTy1hYWNpWmtybnF0NnJCMEthOTl4bEx3bWNsaEsteGRxcC1HWWxHblQtbkw3eFI1clR2SHNhMmZWaGZmR01TWV9ONkxNVzlMcUpYRXlySlA1V1BhZ21zUzlNVXVBdzl5U213dGVpd0VBbFpvZWhQWG8wMW9rODY4akFZcERvUlNGbllnR1ByUjR4SdIBrAFBVV95cUxQbXRIazZFNW5fVWNuX19qb0pLWmczYms2dDQ0U01zbWhyNHZaWXdaY28teGlZX1IxdWtYMlh3VHRMUFFUQk1lZVk2NWpTb2lVZklwWnB6aFM5NTBqLUdISmdVTEJBNlowWEZSaUlKZUtRTXlQWWtuazBjaGJGWHpSTy02RlB0b3hZZXgxWDMyTHNsMG80VmIyODhFU0szSDRITklmLS05b2NNZGpI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxObVotVjFLcEYyLTF3cWZMSHpITV9OYnExNk9RNEtKLWtNXzQxcTNURnRsZ2hhbE42ZXMyNDRBaU5wRGJQeXlPdWYxSFROdVplbVY3MzVEOV8tOU9JQU9vM0NmMkpaemdMbzNMamdzRHgtT0pFZGQ1X0NlQW1TaHJUOGxOUmNHNWxfYUJYRzJGS3ZSODc4OWNfdGJURFNMeU5EcnYtc0xTUU1WOVpZblUyMW0tQmg0Z3hFQ2JZU1lkWkFUY0Njd3c?oc=5</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Neath Port Talbot Council leader wades into Ospreys row with blistering warning to WRU - Swansea Bay News</t>
+          <t>Shipping containers 'recovered or believed to have sunk', says coastguard agency - SussexWorld</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 20:18:31 GMT</t>
+          <t>Sat, 07 Feb 2026 14:39:00 GMT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQc0dpdm5ZLWMzVXg0RVcyeVBXRTltWG1lcFpwRnNvMnZwLUJURzNraW5BZHZMUExQLXBkMWlxZWNiVFVfNWtheUJTRWpmRkJVNFlFV0FtYWFCYUZneU41QUZQVFV3ejhuck1QYzBmRWhDazlvNE9FWUpFRFpfQVVYNFYtWjVBVWRmeWZ0YUJvS2ZmYnRVUS1JbXJxVFlvMUQ3aXpPSVBmLUo5dEZMTUxLQThqZ1Q?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNWkNWb0ZBdnlQZHVCeVQtWURpMEhnWElSVDRoRE9MOGZhZHY5c0xtQ3dDclAtN2hIVnF2OXR4NnB2cWgtQzdBRjZXVEc0SGVXOHVlcE5kd3lmTDNsTzRPWmxOQ2ItelZUNGwzQ2VpTzQ4R2ZQaW5nRDZob09YRkFqS1dJWnBERlh2SDhJVWhDMUU3RWdRTHIweTFCcUdEMHNwMkh4U0U4UGZXckRoQzM3SF80QVRlakpTeFpJZTNXdzc3TTRULWYxTDdSNllFSGlTRU85TWpmc2w?oc=5</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1331,17 +1331,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tranmere Rovers Football Club - Tranmere Rovers Football Club</t>
+          <t>Korean auto part exports to U.S. fall for first time in five years as Trump tariffs take hold - Korea JoongAng Daily</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 11:07:28 GMT</t>
+          <t>Sun, 08 Feb 2026 05:56:01 GMT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOc2hyVnlnOThyT296YXdEWEZJZVlleFBNRkdNWGFnMDZWV0FocWQ2R1hlMzRuWDI5dlpHaTA1VGZTeE51UEs0OXNtTFVCVFVnNnhpU09HMGs3cU1SUm1sTkQyMzdKNmswTWxoN1p5SjFLQWZ0UG1xME8tMGlXZDcxZGh4Q3ozX2EyaDQxaTdXZnpJb2NxTXRldmdVRUowQkdJVFdSSmtxZ0htY19BaldUZGJYUjV6YW1v?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_wFBVV95cUxPR3pEM3NvajdCelRPc19kY1U3MWszdkJyUjh6YTBtR3E1YXRBaVUyUl9kTGNmenR4UzBJT1lFUjZ6TWNrcnlOMkVoVkFQTTRxRmVfRklVVXAzTzRpckZIZ2tianh0N2FzMU9EWDM2V1ZxUWRqU0RyVGpldXRuV0xfaXp6RjlfbmJ6V0N2Z08wWmUyU29pRGlmcnRDQzhfcEFKX09xUTh5THF4QXBWOXdQd0t4c29HaFhEQU0yZzJVdmY1a0FESnkwTkxGQVRZMGw2VFEzS0pqYnpOTVdKYjM5Sm82WER2YkUzS0ZieVRqWURtbEFMWFJjS2c1TkZWME0?oc=5</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1351,27 +1351,27 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>In Trump’s war on global justice, court staff and U.N. face terrorist‑grade sanctions - Reuters</t>
+          <t>Minns invokes special powers for NSW police to restrict protests during Israeli president’s visit - The Guardian</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 11:00:46 GMT</t>
+          <t>Sun, 08 Feb 2026 00:13:00 GMT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPejQteDljMkdfXzk2bldndW5tZW5Rdi1GSVpzZ0ZLelhaa2puMmlMLVpQNDV4V0tud2djd0w2MFNtUVZpWi1VSWFaZHFHa25JMzhxRkNGcndXZU1GSzctNjVOaVhVcGw1WkZ6NGx4SThrTTBSaU1qTlFOTUpiV3VtNVZlZlhmMWpKZThpcVU3MGpnNWFQNFQ2Sk5jZG9XZVNxMEd0Yl9FelVDWVlGbGEtUG5fTzNHLUNoZklyajZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOTDZhdUwzZDFOQ2pVTkNtYXBfRUhtUlhleEhQa2dQeUotX2JKOUEyVUFKNk9QVzV5UTRPcDRpQnhFTlpaWklFRndPX1JQUE5YcHBhUXpPVXdwbU5XTkI5alNsQmpwSU5paG8xMjdrUGRBejFyeThVeWdhVi1WblRVY0h6WFMxOUxWVlBuTV9CQU80ejJvMS1RX0R5c1VMZDB6dUl4dGp5M01mbUwxS1l6QXJoWWtXem5YSVpHR2NLbW0wUS0yMm9rSFNR?oc=5</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1381,27 +1381,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>One-minute clearance: Yunnan’s Mohan railway port showcases smart border for Spring-Festival peak - VisaHQ</t>
+          <t>Video. Italian police fire tear gas as protesters clash near Winter Olympics venue - Euronews.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 20:10:52 GMT</t>
+          <t>Sat, 07 Feb 2026 20:15:57 GMT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxQbW9Gb2RlNGN4Qi1NQ1lRU2RmMXMxUXRpTmdCOW5LWFM4MThUZFd3elh1amtFbGZIWlVtNjRVT2JuOGlJS0NaZGhWVWw0VkdWRXBab0p1TnI4ejFxdHF2WHhCa2w4VkhkdGpoajg5RXRnbGJOVjRwYjIyX3BaRy1rX3pfUWRtMTVGMlVObC0zUDlMWHRXQ2NuV0pRVFdtQnRRbktTdHNHYmtjam5xcGZkeFZTZXpwNHZFY1pmbDRvLVBPcU5ycUpaZ0sxYmJXSFV3VS10TA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOYUZEQ2d6MkZuOTVEZVN4eE42YzBjbWhXb2prV2V3NnkzcXNDb042N2RqUGNxTlV1X0Vnc2FWWlV3RFZrd3V2SmpLb2xtd2o3aGJGTEVlNkpKNEJXLXVlaUpfNlN5NmtXTUduNENKVER4aklid3Y0Zmk1SEoxZEp0eE5ZRnp3UW12YXJqT3h3dVVnN0d1VWRTYXJTUEwzUW9PN1J4WWpuald4Uzc1bDRXckVHQXV2TjVR?oc=5</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1411,27 +1411,27 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>The Act Unpacked: Fundamentals of compliance under India’s Digital Personal Data Protection Act - IAPP</t>
+          <t>Garah: Protest organisers Zamri Vinoth, Tamim Dahri remanded as police release 18 on bail - The Vibes</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 21:26:30 GMT</t>
+          <t>Sun, 08 Feb 2026 01:27:00 GMT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNZG5MSDhBRmpzczRjbkh2b1F3SFljbGl3VlEzMkFnYnZkNTJ4VTI4bkpuZmtSV3lqbTRiV3d6YWFmdnJTVS1sVklTcGM2U2NzQXBIV0pQWU9UZEYxQW15VEE5SWpLNGlfVXdqbWR3QzFaVU9lVXkxeHU3dGxYRTZRWGU1djh3c3VBQkx3WnduTlZpaElqM1ZYYzNtTEdJOGpybEZkbS1XZElzMWR6Z3BKd1hZcTFmNXl4b1d6VmRXd3hyWmxzOXB3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOZmlFSUYzUGNycFo5MHRqNk10bkVhZDlvUGd6U3lreE1iS0syUGFFdV9qZjZydlB3a1RmcUlSd1p2eUhtOTNEMkJJdkJsM0xJMVVGRG80c0lhUnVxcDZFYkN2SVN1bnVEbm1uWE55dkdoajRnc1MtWUlrdlhxcjJiRDNOM0NYVjFtTmxBQjVydWNFaDNLTmU2M3VmdTdENWdVR2pXSy0tTW80TzNXSDBFT0ItX2tkeHhnck9HZVl3ODQwMklBa3d4MEpaeXg3TDROcE9Ya3hlOGIzMDZHYjFhYmNrRGlEOWUt?oc=5</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1441,27 +1441,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Teeny tots from Port Glasgow are this week's Scoop winners - Greenock Telegraph</t>
+          <t>Police arrest protesters at Minneapolis federal building on 1-month anniversary of woman's death - ABC News</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Sat, 07 Feb 2026 06:30:00 GMT</t>
+          <t>Sun, 08 Feb 2026 01:34:25 GMT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPWFVpUlpsSkJRdEJlbUI3Tzlwc19WZjYxSHoyQW9fWE5vYWQyZFkzRFdVOTBzQjh0UWk1QjJVOGYtODJxWVIwcS1uN01FNGtJY25IcHJzWWQtbTMwVWZRQ3lLVnFzZDFqcEhqcTNoMFlma05WVmhOVjk1WGpFQnRXOGU4M0JNQ3dUT1pIMUNpWUJJWm52TDhMWnNYaUkxQWp0OXo3WWlTVlFyODZMYjcyTzEwai14UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNcUVvcXhYOW5TU3dTUXJlSVdnQTdXblNlZGd6VFFxOVpaLWxwbnJpQW5qdHdyM1Z1LVRfWEFhd2k2Y1F4dHgtTDNIX0h6QzJoV3lBeTA5UzJKcnhhdDlzNk1obUtWUkt0QmEteE82OEZjc3VQRm1lMG5EcmU0NjJMaElGV1FIRTVBcElQWnM4VTd1akFhRGVsblEyUndBcXFQWEtYZlU4Z19SY0XSAbABQVVfeXFMTm1KbjF1djVicXNsNEVNbWtvRzIxU3AxNWJCX2ZzTXZuWmZDN2xiN0ZIMml6QkJNMVV4am9QaWV6X1pkeWpXN3dvRlRpX2lOeXh4SGQ4bUN1a3hNNi1aTEluczZSZXFobWZRdjNzVXFzT2V6WTRKaVlPWFR0b2xyZVJXNURTSXJxY2x5bHVzV2QwUlptX1J0MTU4b1BKX3NnZWJjMEZaR3J4dEc5MDJ2Z0g?oc=5</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1471,27 +1471,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Medical Device Manufacturers Redefine Quality Amid Digital, Regulatory and Supply Chain Pressures - Quality Magazine</t>
+          <t>Police Medal Awardee, Was To Retire In March: Cop Who Died At Surajkund Fair - NDTV</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Sat, 07 Feb 2026 05:00:00 GMT</t>
+          <t>Sun, 08 Feb 2026 04:52:16 GMT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxQV2xaNWFJZmR0NW1vOG83ckI4T0ZQYlFtOGJlQnZnMVg5aXF6TFZLVGNIY3dCQzRPZjdVU1VoQ0RIMkJNOWpQR0N4bWdDZjhoS1NFYzBaY0dXb0haNHBkdnJYUldiX0RIb0l3RzRETzN2YVBISGY5UmRSWTg2UkcyRmVNLWNwUTU4elUyQVZZOFZHUGpHZGZKRGJFc3haN1JzYTRNcW40azh5YzBYdjZRbkluSkNwdHJMaldDV0ZBS1N6eU5Ob3ZsV0R4MmF4Q1Z1aWY4LQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQZ1E2dndueWRjZHQ3VWV3OFBsdXFVY2hmbnRLc0ZpM2NnUDRLVC1jd2x2TWx6QVZCeV94QXZscEdUUDhOWHhHZE9kRUhCVWFvWXV4OWx0X3ZhSlVTbVpEMUZhaDlPdVlwTk1SVlo2OFNvUWw1M0gyd1poOFdtUjk5ZkljMURPOC1CUW0xZHpjQ1hycHpYZXNuYkN2UGFDV0Q5WFAzcVY3NGtPeHhZckltT0tyVUVmbFNaVDY3eXlwbzh1WUMx0gHMAUFVX3lxTE1kdEo0Y0lEN0NHOE91QngzYXljS3lydmdNUXd5OThON2lNU3o4VGVQbHhvcHQzNE1DS2FNZk5LMFBOUzE4RU1zNXQwcDY2UjA0Y3Y2bWh3Ty01X2JQenFIYUw1UURzTEZCUDlPanpTLTMxTHA3Y3N1Yy1qYmplMWpTYkFJY2dVS2hvbDJQX2FZTXlhYTlTdVhFVW5Hdm5PUm11V0VaVThRN09LQkwtd0gxaXNBVEg2UExnX0xCSFZNUlItdTVKUFNwcU83bA?oc=5</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1501,27 +1501,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Did ‘America First’ tariffs work? - Brookings</t>
+          <t>Police chief: Officer’s kick, baton strikes partly excessive in shopping center arrest - NL Times</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 21:51:12 GMT</t>
+          <t>Sat, 07 Feb 2026 12:05:00 GMT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTFB5N3JlNXM1clBYR0daZENSSUpMd0ItUDliYjVuMW1Rcl9ES1JDZElDbC1VQlR3aW11OEtvZmJ2ajhLNUxUMDJMeFM1RHFqNVBma2tHX0JIQnVsWmxXT1pxWXF3a2V4alNoQjkyT0JQenJjbnBj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPUUlIT0hoYjBNQVd6eGZJWk9RbnQ5ZVdCNGV2UmtmY01TOTJ0VTduQ0V0OWxEcnRIc1BpTHgwZXZVYUt6UjQ0cnRKU3VLTlIxYXREV3QwSXNYSnVCM2EtRERNZzQ0R0lOSV9pLXNSQUtObkMtM1dPbWttQWhYSldUS2RmUnF1QnYwSkxjbFY2Z3UwT0dxWkZuNEhQWmpIUlhWMXQ3dEdJZUpYV2VZVDRz?oc=5</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1531,27 +1531,27 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>News: #UK sanctions six individuals over #Sudan war atrocities, mercenary recruitment Mekelle - #Britain has imposed sanctions on six individuals accused of committing atrocities during Sudan’s ongoing war or of fueling the conflict through the recruitment of - Facebook</t>
+          <t>Barclays cuts dozens of jobs in AI and offshoring drive - The Telegraph</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Sat, 07 Feb 2026 05:30:03 GMT</t>
+          <t>Sun, 08 Feb 2026 06:30:00 GMT</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxQQkpwNXBPcDdfWk0tYk9VV25UYlgwcTBNUXpHWXV3Ul9RVjNNR2xXaUR5YWpZU3JQOTFBMEk1ejJmZEJTX3NrUU5Xa09EOEZkYU1Zclo2NjNTMExiTVBZVEJ0Rko1eFk0Q1Y4ZjFlLWt1OVQ0Yk1pU3RHdGxFSzFXeHpGRnN0d0k3VGhTRnVCZk5wUlU4eEFsOTNXQ3ZaUVFWRVptd1p5UFpZXzZEYVV6b1hJeXUwV21tUHZGdWYwU3p2RWJtZFM2R0J3cXp1aHVwMHg5RXBOck5NSjRFTmpXTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPUXJIZEU2M29pVG5MNEVDY2dSWkN0dW9xUGhMQm81NlJoSWdrQnRsUDlYYXpiclJQYWRGa0k2LTdCaVdHUjcyRDRvWHMtTTJtM1RiMzJEdEZVTzUycUU1Tk40VUlUTDhsdVM2WHV6M2F6Y0dKWUpBQVlCbHFyNmlydjNsa3VybDQ5Q0F5LTQwSGxqWUhqejlQUW9SeVVvclhGdmtDUXdEZw?oc=5</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1561,27 +1561,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Three African countries agree to UK migrant returns after visa penalty threat - BBC</t>
+          <t>Technology and treatment in eye disease - Association of Optometrists (AOP)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 11:00:06 GMT</t>
+          <t>Sun, 08 Feb 2026 07:05:43 GMT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE4xRUlsYkQzMnRZdV9ubFZRV01IQUR4NUJLTk9qQ0tHRGpCWE9PcXpEZXhQRWs2U3BGQkxqSTBRUTBEMzl6VnUzZjlxb283dm52b2YybFVpZUtqQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNdF93VDZ5TUdIN3JyTk9DNnhhU0Q0ZW9JcU1CTkdpcFo3MmJSdjNJTV90ZTk4NHhudkFULWtCUlF4Qzh1d3ZBWVpHTnc0WE9rbU1pMkhMT0FRNlBIUE84U2xVeEQxc1VyTjVvUmdzVkZGLTQyRWlnMkZmeVBIeVVWRllGRXJFMjJTaUtBX2t3?oc=5</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -1591,27 +1591,27 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Minns invokes special powers for NSW police to restrict protests during Israeli president’s visit - The Guardian</t>
+          <t>AI could boost Jersey economy with right funding, expert says - BBC</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Sat, 07 Feb 2026 05:33:41 GMT</t>
+          <t>Sat, 07 Feb 2026 11:53:05 GMT</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOTDZhdUwzZDFOQ2pVTkNtYXBfRUhtUlhleEhQa2dQeUotX2JKOUEyVUFKNk9QVzV5UTRPcDRpQnhFTlpaWklFRndPX1JQUE5YcHBhUXpPVXdwbU5XTkI5alNsQmpwSU5paG8xMjdrUGRBejFyeThVeWdhVi1WblRVY0h6WFMxOUxWVlBuTV9CQU80ejJvMS1RX0R5c1VMZDB6dUl4dGp5M01mbUwxS1l6QXJoWWtXem5YSVpHR2NLbW0wUS0yMm9rSFNR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE82cGUtS3ZHQUtJVjZMb3R2ZVVZUHB1cGVzWUcwa0JlNHpYZ3U1SWc2ckZOX0hCcDJQX25Oa1lfZGltVFk1d2lvN3VUUXk4Tzdyd2g0ckJEZXdYUdIBX0FVX3lxTE1HTnJ5NGR1TVp1Y29IN2pwalNadUd3NFZkVkZaTG00VFppTE1pV29qSkR1Q0RMSEZYRlo5WlNfcno2UC05eW8yWE9JUENvVzFETG4ycG96N3ZlNC1TRFI4?oc=5</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1621,27 +1621,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Police seek man over UDA banner display at Apprentice Boys' Relief of Derry demonstration - Derry Now</t>
+          <t>Dan Ives Says Software Selloff Is Worst He's Seen In 25 Years As Microsoft, Salesforce Face Brutal AI Reckoning - Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 21:00:00 GMT</t>
+          <t>Sun, 08 Feb 2026 00:31:00 GMT</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxOQTFveTdyN1F3alVXTmlUQ0ZLZW5CTDd6NFd1a1dxVDc1bmFzR3VnbGN3d2RLZlVZRnBQQ2dVTml0eWxFdl9mS1JJOG1Ea1NMd08xWUM1blhSY1llaGJfWHpoYnZJRXQ0SGJNZmVxZ093eFJhQXlmNmpydFI5UVc1bHZWVEJ2eUdHRWtDUmhGblpSclhLTXVrNnNGRW95Um8yVWlrdTgwS3dQcGhQQmFJdDI2WjdkVXlEOUNWUVl5VHhUdVBoNEdQSVR4eHJIaUZVYUpsRldxT0Fhb0EzbFln?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxORThiaDlTOXlGeVpiUXV4ZjE5Mk9POVA2YlI3YUtRVDU5czBEUlE1Y2llZnNvcjJ6Z1dMdUpmQldNMlVUdWFVYkk5Y09DTWNabThwOG80SFZUQjBUNFROSnNsdXFSbHpvNDJPd0phUmo2OTBSd1lmMWRhbk9NeDBOaFBIeXF2UQ?oc=5</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1651,27 +1651,27 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Teen threatens Indiana school over protest, then pens apology, police say - IndyStar</t>
+          <t>Sage chief: 'Ridiculous' to claim AI bots would destroy our business - This is Money</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 21:59:00 GMT</t>
+          <t>Sat, 07 Feb 2026 21:50:22 GMT</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxOZVFuOU5hdkpfTzdtM2NZV19FVkRNelVGREZfWlNOa01fellOU1phR1d2NWp4QkdCREExRG5JUE1udXFRV1pDVFpOeDMyNEtfZ0VHNWE0dU1LZ3NjWEFCYjEzb0NRT2lPeFR1b25Yc0pvOWJvcGVWY1M4eGRQOWdkS3hqTjZWZ2w1M00zMDJma19XZm5vSERUOFgybFVfRGFDckNyekljS1hCdWNOWkdWRVpIOF9yclYyR2VocnZfOVZlUC1SbVNaZHN5MjgwYTNLUC0tQXNnLXo4V3JfcC1VVnBkc0tta21xVVpmVVlkaTU4dl93QkRYMQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNU3VUZi1XZF80a3V4TmlxYk5tTzNwMVl4Smlob0l0Vlh4X3FPSXY4NlNGS29GYktiNWRhbWV5SEZBNGpXR2dnOEtCZnB4dDQ0Y1hxT2thZzBrN1hfMDBsYXZka3BoRTJTci1VZzBkV3VCWm5xRjNqR2RMWnp3VW12aWpwSjR5Nkx5YW5IOUEtS2FuS0Q0Um9UT2haZDJDX1JhYVI1QzBfUnhWMHFlUVFhWDJNZDlPbFg3RnfSAb8BQVVfeXFMUG5XY1BoeEc3UFRIeUt4ZUxyMnRla3gxZzdqM2dVb1VXalFjUVpya3FRTmdJSlhLaU9mY0FBYkx0ejUtdGF4M1lIdVRwalZxNHE3YmRHbVJ5Z1hkRXBLMjJvYnZCY1dCQjRkcVBFVmVJbFV6bEJlUW5XYWwyX1gzWDkyMU9DNVdkWnV1aXZhTHFjaVgyckxhMnF6T2lUaEVNMW1BN2NPVHp2cVdPRXNGZ2dvcXRwWnowTjVkekQxRWM?oc=5</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1681,27 +1681,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Fargo Police seek 3 suspects from Downtown protest incident - Valley News Live</t>
+          <t>Water Implications of AI-Driven Digital Infrastructure Expansion - TRENDS Research &amp; Advisory</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 23:06:00 GMT</t>
+          <t>Sun, 08 Feb 2026 06:00:54 GMT</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPT2JoUEdYdmRwdXNsemhjTW1WMVh0WnZ5bnZYUVROemgwMTNheF83RU5kTFBsLVhNemRLOUl0VUJxbFJSWGU1SEJlNmNTMnRvMWVwTnJRUWxWSVo5MDRkZHNYWjFYMlFmOU9MS0l0Yy1mS3VYV2hCeklsYVREbkxYVDF6WU1IQ1N2UGV4Q2dSd1dhMkdCVnZOVUl0cXVaUdIBsgFBVV95cUxPYnVtYlhIV3Q5MWQ3VXN3NWdYUWc2NkhwTzZoTW5iX3pjSHoyOWY3T0VnWDZLZk5jWndlQl9Fb2lZUS1sRkxXWmo1RXkwVnhoSk5FdmE0bGtWeDNkdjg3QUx3Ukk5REpXTVV0RjNCTmk5ZnMxZGxzZ09PcV9rYklWR1lOdEd4Qnl2RnBsd3dZRWFSU2xENUtlZEpwTWhXQ0dja2NkczNtUkJYRmRncndNdlN3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNQTh0UGNTbHp5YVl6ZFFWWlY2SnBFdko1RUlRWkJiZFZsRXNTMmI0bWtKaG9GNkdQX0NGUTFmc0l0VkhQR2FIc3VxVWp0S2c5amd0Z1VabVlGSEkwT0paUGxiXy1BQkpKWHFhdHRhclA2Nk5TU0xmQVpoVlo2c0VkXzRSd1JUbmxZTGZfSTJqMFlaRkh1eWVicWRyZEllYVp6aWc?oc=5</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1711,27 +1711,27 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Terror strikes capital for second time in less than three months - Dawn</t>
+          <t>When the Diaphragm Deceives: Subpulmonic Effusion Flagged by AI and Confirmed by Ultrasound - Cureus</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Sat, 07 Feb 2026 00:29:21 GMT</t>
+          <t>Sat, 07 Feb 2026 15:37:43 GMT</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiSEFVX3lxTE1OUHo0eXNCbWJQb29mamdNSXBlaG5MMWxqVHB1SDZzbkNENEJrN2x1Vkg3eEdEU1Q5MjI1QUpNWEN1YzNfQS1MY9IBTkFVX3lxTE1fVjdCTDRzRm9VLWpfNWJBT3Z5aWRFTXRqMGUwUnBhSThYWTVqNUMtdTZFTlh6WWxLa3lIc3ZaMEJQU2dpR2dMcDU3MHBuUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQSVdKTVhwWFA3MDRjd0JMbFg5WTZqMS1mb2tVVS1FaE5qZy1fWmNwQTJhMXJFZURvNG9iVnlCdE5VZmZnTUZLaWtPam8tdmg5U21ucTVnZlYwaHhSazc3UDFoQ3liTFUzZjV4aWk1V0k3QWFJNGpHM2JTdzFfSFBqMEFzU1J0WTRoZlhrTjRKV0w1NnJRSFkySm9IVXNFRktJN0FodW5OYTRsOWZhRnlvd3NXNEZ1TUpGOEdsMnVKVVR5T2QyY3M3UQ?oc=5</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1741,27 +1741,27 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austinites demand police, city leaders do more to resist ICE - KUT</t>
+          <t>Could CrowdStrike’s (CRWD) Aramco Pact Redefine Its Role In National‑Scale Cybersecurity Architectures? - Yahoo Finance Singapore</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 17:06:00 GMT</t>
+          <t>Sun, 08 Feb 2026 00:17:00 GMT</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOa0dnT0VaamhPZVJjQjVYZm0xN05YQkdpMGJDeklMRlVScG95Z0lYUGJQR21OT3dkOENZRlphbklqdUI2QXJyRVhaVi1ReHktQ2ZpSHZQMHdQdXR3X2lLb1lnSVdGeEZxQnctREpOcFNaZlRwYm1sX29wcUpzSnZZdHhtbTJNcm55OE9YUzdrMzY2NGZEdGN6RU9uMFMtbndlanFF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOLTg0TUVSa2p6Z3hlNlVkZGRZN254ZTVYd0xYOU1ONk5xWFh1TTE3eGNVSUhIYTZpalF2SUttYmdBeFdhMnN3cVduUW1mT0g5X0ljTzV5NE1tNWF5QmRSand3ZUIwLUQ4SEtyb0dvd2RaMHVCUXNKQ0w2RkVTclFkQ3JRcDZ5YThXUlI0?oc=5</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1771,27 +1771,27 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ninth pay scale: Police use water cannon, tear gas to disperse protesters - The Daily Star</t>
+          <t>Tanja Obradovic Shares Insights on AI and Drug Development for HopeAI - Oncodaily</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 22:38:58 GMT</t>
+          <t>Sat, 07 Feb 2026 17:32:04 GMT</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQUFRSOHdzMkxieW5RRHJYeWdnNldxZWdRMV95TTZ1bXRkQTR1S05Na2VjVUE3TjhKTUtaZTRBM2NDZEtFOEsyZVBWM1d4RTZ2cjFNYlRlZ2hpeXBxRXgtUkdNQ2t1SGdFX2VlYkhid2xxbjBPdzZlVERPZmxTS21oYmpGLW5ILUlDVlBvQ25pb29fb3FhMEZZMEZmc0hkY2lOV21qeUNSYVdfeFBxaTFnNEdGcS1iS09faDJJVVl5bEpsZ1Bp?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE85WS1veFBvaVBUMGw4LVRhalNkVkJ3Rnd1NU5TbVQyLUtFYTFDYTJPZlRBa1NuRi1JOUtpUFBxbjJpSm1aSFVKRnl1NFQxTG9FR3EzNF9naEtYY2xMOEg0Zg?oc=5</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1811,17 +1811,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Europe’s Style Forecast for 2026: Frugal Chic, Slow Fashion, AI, and a Wave of Individuality - strandmagazine.co.uk</t>
+          <t>Assessing Atlassian (TEAM) Valuation After First $1 Billion Cloud Quarter And Strong AI Momentum - Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 21:30:35 GMT</t>
+          <t>Sat, 07 Feb 2026 08:07:34 GMT</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPTGEzYWh3aHdaZTJXNEZ1Y0ZYR2U4Y3RJeTNDbmtEcUowa09xdjd3M1VZNENsUUNjMmdocVBYdHg4RW9SbjB6TXNLNHByT3lpUjJPLVpNOEJ4U0t3Ym5UMDJfX2hFaDZjMnM1R1l4Wk81UGJ5V1NvMzh0MW9sWXF5R0dDMU53M05lUElSWEdRUnFQNkdzeDZ4SnJkLVZNNEpxU2ZWNVZPWjhFTHRTVmdmTlhEdVBpUjBuM2RXcFJoOTZEQVM5YmdjejZMc20tdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOOTdhM0c4amRMZDBZR2dQdWlRTldVWlUtXzcyZHl4RVNLOVF2SkNnMzZDc2xhVjRKdFU5RFE5VDlwMXhHSE8waW5KSURCcE9Ea1F6dUZjRXRscnFSaHNGdHhocUVZcDI2WHNjc0NadElxNVgwZzVlekl0aFdGaXBCZW5yYnJodVRoS29Wbi1CS2VCbFE?oc=5</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -1841,17 +1841,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Amazon shares fall as it joins Big Tech AI spending spree - BBC</t>
+          <t>After Merging xAI and SpaceX, Elon Musk Hopes He Can Win Over Wall Street - The New York Times</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 15:11:52 GMT</t>
+          <t>Sun, 08 Feb 2026 01:27:03 GMT</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1wZzJieWpQdW1JZ1ZfaGEyQkUtS3ZjUi1NOHZCY1ZMTXJZMFU3Ym4wUG0zaDhuYmsxSGNBbFpSbUszRW1HUUhwRkJZc2VDc0hpN2FaSFlfM015dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE1MOVcwSmRCUlN1QXFrYjhjY1FNcXpBUmxBdXVUMUtqSUpocjNNTlF3RzcxMWhlN2VpLUNrNUlKcjVnYUZkcHlzWE52Tm9DbE5NY3F0cU1YN1RTUVgtaGhVZ19WUWNXazQ4dzBIUWZnaGduSVNHdlFIX1ZtQQ?oc=5</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -1861,27 +1861,27 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Technology - haileybury.com</t>
+          <t>Warning To Under-18s Over Social Media 'Jobs' Scam - West Yorkshire Police</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Fri, 06 Feb 2026 10:12:40 GMT</t>
+          <t>Sat, 07 Feb 2026 11:08:44 GMT</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFBzSHYySnd2eG9Pel9ZMjBmZjZObTM1cTVXZDEzY0RnQjFfc0ZrQW1vcUduRGdTTW1IZWFuaEVlWkxEY2t0YUViMU9PblZOZ1kxTGpYcnFoR0ZRaUk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQTHhVUEg2NUt1alJ3azBXbTN3dFNaZzk3YXIwM05PVENXZ2J6THByWHlwR2lybEJWblQ1VHJTRld5eWROQXdueE83SGVzUl9oTjVjUlJwYmt5YlRLa2lkZW42clJWSnVSZGtJdFYyMWc0d29tZXhUQUNVR2tiU2FVNy1kOG1NeksyRjlZd0JIOGJzbzYtc0VDQUFn?oc=5</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -1891,1110 +1891,30 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>The Blake Brief: AI and Earth Observation: A New Lens on Our Planet - Wilson Sonsini</t>
+          <t>Phishing and Social Engineering Still the Main Gaps of Digital Crimes - VOI.id</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Sat, 07 Feb 2026 01:49:01 GMT</t>
+          <t>Sun, 08 Feb 2026 07:11:16 GMT</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQMEFlNWx2Y2JDRm9aWGhBTkhwWUhYZWRYN0RpVV9KS0FmTC1kUXVHc0pwdlJfSHpFSVdHOWhGVDM0OUVzVEo3LTQweVZtV2d1VXdYOFY5ZTBFNDRMc3pYQUJJWnZKWTduSndJMGVBUUY5aHNzUmZlSHhfSUZubmxXYlRqaXptaFlZaGI1T2ZablJnYzl0M1pKQUUzQmNGSWw3b2g1cnptTWhyb0hLUHllWDhOSU1VaFF5cFR6RkloUzVmMHdoeVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiS0FVX3lxTE1jNHF3elRwdlRNZTduWXE2dDB4R3VLR05XQWh0RC1POFVLbXIyY19ZYTlQOEFseWZxUkh5WG1XUkxFQWR1djBhMDd0b9IBQkFVX3lxTE1pbWRoMjc5MkZ4WDMyQkxYY24wblhOZDMwTzRBTkZRRUdWU1JEYlo2Z2lJNUVHWHNSeDVmbmt4UXM3UQ?oc=5</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Looking ahead - AI and business integration - New Electronics</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Fri, 06 Feb 2026 14:33:28 GMT</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOTGMxTU5OMkhDWDh4ZDZ3a3NtQ1BhYm5tWE9nLXgydWJoSHZpQmR6OE83bXpGTk05TDV2LUZwanpOWGlURVBGYm5zU2ZvOXBVV0R0U1g0dXJfMzFiZnFKbHZKRm13VDVvRlF5YktMOGFHR0E0WU9jamxpVXB5cWdPSlFINlZwWDdkRDhTV19kTHlhckxGZmc?oc=5</t>
-        </is>
-      </c>
-      <c r="F51" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>New study uses Neanderthals to demonstrate gap between generative AI and scholarly knowledge - Phys.org</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Fri, 06 Feb 2026 20:40:01 GMT</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxOSXBscEFqU040cGdWU2dERjI1c3BVS056NnhCenp6b0VveXRYSmVVeGNTTGxiWU13YU9CZERybnE4VS1GWG5ZVXJoNS12dVJ0dHY4NW5tR3l2ZU1qdHdJUDFrbHJmVEpWbmRIZElhTHBzZU1OVWM1V1V5dEFmZVkwdA?oc=5</t>
-        </is>
-      </c>
-      <c r="F52" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>How The Narrative Around UiPath (PATH) Is Shifting With AI Themes And New Index Adds - Yahoo Finance UK</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Sat, 07 Feb 2026 05:05:00 GMT</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxPeTJoVDd4Rkhwemp4VE9qWENRVnp2c0FQb1dKTEJBYmRwNUpmaUlSYTM1RFI2dlR5eGVpZVBDZWl6SVE2UTd4NnNDNU9EMUx0ZHA3WG1XSEIyajItV3d1SUdjOFF1eUtJZkl0V2xOc2kyUWxKTF9adnhCNnFDb25jNzNNWVZ2LTFGakh6RHpXUQ?oc=5</t>
-        </is>
-      </c>
-      <c r="F53" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Strengthening AI capacity in the Arab States - unesco.org</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Fri, 06 Feb 2026 15:48:05 GMT</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE5CbWVNVm5UTVBEa09xMWpWZTRyYlJZQzFsN2xxSGVWWjROR01jXzRQUXlnX09NVC00WWdxdlZiTkswUW5jYTZubENxTEY1ZmRvT29lbFZqVmxMLWlxajA5N2Vja3p1LVJFVFJ6OFQ3NXUtNkQ2MnQ5T2dzX18?oc=5</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>AI &amp; liability - does English law need to change? - Mishcon de Reya LLP</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Fri, 06 Feb 2026 12:39:26 GMT</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxNX2gwVllkdC0xYkV6eFpoMnhoS0xDVkRhbkpNWHVCOVFrV3dOekNDWmtsSnhqUmJETUJrVF82RW5MNk5ZdmlSdjdIRE5MbHh0N2pTaXl4ZGtWTU9ERWRDVWkydEJlaVlPS0liTjl5OTItS3ExaEpFWkdsN3gtb0U2akdQOA?oc=5</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Call for North East to embrace AI or 'be smashed' by it - BBC</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Fri, 06 Feb 2026 19:33:35 GMT</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1IdW5ISTNsbmVUeDRZaFNuVkd6WFBEVDJBZDQ0OUpfMTlETmUyWFdQYXZMNkU5V0g2MVdOdU54T0U0eGZYRWd5YXVkZF9RYmxFOHU3QTZIcFltdw?oc=5</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>FTSE and Wall Street rebound from week-long rout as traders reassess AI and Big Tech spending - Yahoo Finance UK</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Fri, 06 Feb 2026 16:33:20 GMT</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPNDVBZEhnTkJ3eU4zX1NYbGdTMXRpOVBCM3NjOFVGRXFtX3FxZ0Z4dkpEejJ5LWt0SFA4TlppVkJVczZKVkJFVlROWnJZSGpoQ2RhVjZRSTRMM21zTW82ME9JRU0xWEp3ejRrcjFoVU5LMi1reFg1dlc3MC1ad1hJeGRNSXd1X1FTdUFSS3ZEa0paRVoxYTlTTW55ZWtmSUV1Q0VCQVlySktYdkU2YjVPMlZR?oc=5</t>
-        </is>
-      </c>
-      <c r="F57" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Microsoft Launches AI QuickStart Programme with Support from IMDA and UOB - Microsoft Source</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Fri, 06 Feb 2026 07:41:09 GMT</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNd2ljT2pkVlFBMkc4VzBVSkFsZnR1RkNTb1lxSG9NTkVGOHdRWHVQMDZOT2hram0yZHRram45dFpCV3RvbE8zOXFyRDdoZFY4THhZVlhWYjdTMlhoY29oQkh2WDcwdlBfSUpZTEYwZnl2MGFLR0Zqel9KenNCSzNzM1pNYXpoSTJGSi04QlJRcnpwTFRTTGZ0aS0wX1ZBQlduOTNqTUN3dHlOSU1rdzlGWklFMGpKY2Y3ZGduWEsxV2o4dw?oc=5</t>
-        </is>
-      </c>
-      <c r="F58" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>HBS Short Intensive Program on AI and Climate Change Merges a Global Challenge with an Unprecedented Tool for Change - Harvard Business School</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Fri, 06 Feb 2026 15:08:02 GMT</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE9CSjFaM21nUzAtY0hVZkY5SHZOMENBcnNMMHhXamFIcnhibEtOSTRhQXJaNUs1UFplejRsTEVWVEpSNksyRGotblpIUXFndnFDcVpJMHlsTjB3Y0xJdi1MR3BxbTlfYWhqMmdSSTdKUkVEV21o?oc=5</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Baker McKenzie to cut back office jobs, cites AI - Non-Billable</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Fri, 06 Feb 2026 12:25:00 GMT</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE0zMlltTS1MNVZtY0dqV0Z6Q2lzM2Z1V3pETVAwbTVaenNXQm1mY3VKc1U0VTFWaHYxMGxGMXZ4WDNnMmhwZk0xdUY2eHJpRzVxMHczYllCX3A1UmFGSTJfZzdYR2QzLXNnSTFfMkdkUmJXTDU4YmdCT1F3bVhvZw?oc=5</t>
-        </is>
-      </c>
-      <c r="F60" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>AI hype meets software reality in bloody week for stocks - The Irish Times</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Sat, 07 Feb 2026 06:00:14 GMT</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOQkpXb3c0RWFKWlh2R1FYR1N4eXBDdjBMLURXdGZzbGxJUUNZYWVqY2o4MjhLUmV6ekxVbFloUVV1cnY0LWJZeU5kWDNVMW9ZWXVodVBkWnZocWZSMGpWRDE1Tm9yQkh6Vkk0VHpqTGRQU3VLYndCZ2tUc0RmM2VqaldRbXF5c1JfZEhLcDM1ZzF4Sjc1MDc0dWRfZjU1NkVxTjJGeWxZTUJPdw?oc=5</t>
-        </is>
-      </c>
-      <c r="F61" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Nothing About Us Without Us: Reclaiming power in an age of border technology - openDemocracy</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Fri, 06 Feb 2026 17:41:11 GMT</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPYVJrSmk2VFZ3M041VHBVMF9TZVVyR2laZmRXby1BM3BKQVV3Q2huNU5GNWhYVHY5dVlPc1JoZW9RT2NrMlFFUnQtb2J3T19SMUJyZDZOOW5qbmk5V1l1ZTl0Z05jdFlCcmxKNzNMQm53eDlMeFZndU9vU0lrMjJjVjVQUUplZ2VHbnZfaFR3dGtoUEt0TGhWaUhxS0JKSFVZeVVVb2F0dW5YbDd1bl9tSmk0eHlHQ0k?oc=5</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Andrew Boyagi: 'AI alone is not a panacea’ - Computing UK</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Fri, 06 Feb 2026 12:13:28 GMT</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE5oQmRsYnhmSmc3Zmp6blpyM0lrZDlDdGRrZE1JRXFmdGVCUmxxME9ua19mcDJsbE5lV3BiN0E1VDdLdlZsMzM3RDNndDBCMXpyNzJwOHlfSWNRc0FFWEZDeTEza3pYeGZ0azFHLXVGN1dJdkNub0J0Z3BHSkRkQQ?oc=5</t>
-        </is>
-      </c>
-      <c r="F63" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Gas, power and AI’s role in the new age of energy addition - Al Jazeera</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Fri, 06 Feb 2026 21:38:59 GMT</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNSUd2c0tURE9DbkRINVpBSE9qOVNwTWloNHFmWkNsY3cxRmh4bnZfeU5fbzdqajVtbkFEUUpTdl9SQTZQeDRwZTNCR2ZYZm9XWXE2MTZhZjFHSm1jVW5GOXBLUkVjZzlJQl9PRHVGZW5jR0xwc25jbS0tZVpqWGNaX1J2cWxZLXBRR0d3MkJkajF6TmRkSHUxRFVyWDVvakpE0gGmAUFVX3lxTE9Ncmk3Um92ZDZyZXdGYXNUU1J6bUJDM09ubFNIOVpuYmdFN2JwaFBLem82VWF5UllQUnRWNUxjR01HV2g0RlFuQXc4UjlDUFMyYTlHdDNIaFBkMHZocVlDN2NVcElqczhJU0x3T2JQZkoxSVVFQ252ZXZSb1kwbEozTHJJa3lfUGlEeERRdTVrV3o2bzdjcmJvTjNUbVpHc2lDemNxb3c?oc=5</t>
-        </is>
-      </c>
-      <c r="F64" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Cybersecurity Information Sharing Act of 2015 Reauthorized Through September 2026 - Inside Privacy</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Fri, 06 Feb 2026 19:32:43 GMT</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNSGVwV25WdXQyR2VzTENBbTRUQzFrWmJkeGsyZjZtZlFMUjhnSDBWckxMeUpwd1JkbWc1N0tlTEFFVUVwYm9CT0JEZlRVLUZwcV9oQjVZeWRVMmRJbEViN3ltQjE4ZEhITDlKVUxyS2tYZ0ZyRnk4QTBsRFAwMF9zV2JFOTZtT0JpeVYteE1DcWhfVi1IQjFKeW1DcGhILTdnQlRELThkQm5GYllWUUpmdDYwa3p6OGFWeXlYNXlVYmVJVkJ5aTFv?oc=5</t>
-        </is>
-      </c>
-      <c r="F65" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Bury Council ponders using AI for budget gains - LocalGov.co.uk</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Fri, 06 Feb 2026 12:50:19 GMT</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxQYlV1TVROd0E3RTZjRngxQlBQVGIxTF9jdVE4Y3Y4OGU5VHF1VkxIdXUwUjBNajBrWTZDWXpMdU45OE5xWGpnRDRnaFpzcFJoQ1dnMlJvZVNnNTA5dmZYUEREdVBtcHNkZjZWTkZ5Nlc5SGxPNnBKTXY3RHhWUFU3dWE4SjJSZw?oc=5</t>
-        </is>
-      </c>
-      <c r="F66" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Which European country is the best and worst at AI adoption? - Euronews.com</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Sat, 07 Feb 2026 07:01:40 GMT</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOcHFRcHk5V3g0LTdBMHpRRjM3bzhlb1NWZlY5SDNfTEgyRXFUVjB6emZXWUQ3MUpFaERlbVFMSmtoQkR6cElOR1VvLWlPYXp1dHNGVUpmZkFKWWdESmVYaWNmVFU3Q2I4UjM0dkozeUExcVpma0ZZZ0pIOU03bWVmWjFIT0w2YUppcmZPS2dRZUJIVEpYN3hpYk1fWE9FQWdwYTQxbk5xZmVkOG1j?oc=5</t>
-        </is>
-      </c>
-      <c r="F67" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Alphabet Q4 FY 2025 Highlights Cloud Acceleration and Enterprise AI Momentum - The Futurum Group</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Fri, 06 Feb 2026 15:06:09 GMT</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOVE1LYXVNOHJUVWdpQWxmSFlyc1ZMYXZlSTc4NVJaTGE1X0p1YWVkVFVsYTlEbk5qd2VXMXV3V3lsczNYbHYzcV9XY1FCOWdBckJDUW93bmtCNFhrcVpaRm5iNkQ3Mk9MMjhpT0xzbHRGTXAtcFM5QWZBVld4Y3J0OXFKVF9TVnE5YnMycmg3NWlLSVBSZ2xUaHFGOGp2eWhnY3M5OVR1cTA4U05ETTluag?oc=5</t>
-        </is>
-      </c>
-      <c r="F68" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>From Jesuit Education to Career Success: A CTL Conversation on Generative Artificial Intelligence - Marquette Today</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Sat, 07 Feb 2026 05:41:35 GMT</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPbkRFVEZZdm1HUndHaGhzeDFmeU10dmhQWGJmVE1rQ0ZxRFc0bVAxMExPbHhEUnVhQi1fWkdpR3FodDJfU3NZZDhRSkkwakg0Z3dIV0QyNWl6Vjk2U0cwYkcxZDlRSU05dXVKbXZ5dE50aVZFNGNWT2VsSjdUb1RZU3JSbFlPaG1EWDBrVlBNYUpXSUptYy1FaE1mWTM2OUFoNlUyNzZOZFB4NU5XV2NlNUtmRGhSbXVhcGN3MnR1NzJkLTJFMGE3dGVGXzRPM3M?oc=5</t>
-        </is>
-      </c>
-      <c r="F69" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>How to adapt your lab leadership to an AI era - Dentistry UK</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Fri, 06 Feb 2026 09:24:20 GMT</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQNXpScldvXzRYZnNDS19WeUFLNU9hZWtvVjdzdHl0VWZxc3QzRUl5TllWamNCbmxfWWk0VUE0S284eGR2VFRQNXN3M3VFdEViT3BtWVVvQXROV0dUVThUV001QzBENnZiYmstSEtCUmJJVkZqaldJWDJveFI3WGYtclk4WnpLQTA4?oc=5</t>
-        </is>
-      </c>
-      <c r="F70" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Beyond serendipity: rational design and AI’s expansion of the undruggable target landscape - Drug Target Review</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Fri, 06 Feb 2026 09:05:22 GMT</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQZ28xQk1ObTFfeDJ2N0ZkTTEtajFtWEt1YXZaS1pqWnBraWtGNWRYbG9tUEUzME9iWTM4dlIycGhUeEpNSDlhSFpHRldjM285MWQ5SzhWV05NclZqaHFNTTRabzJlbTRaLVU5Y1haMGlXdU9DM0tYOGg0SWtBVGNQY04zcHAxdkpVTnh2REM2cm0xNjlncUZQWFBGekg4WUFqUklSdl9TQ3RYNEo2YTRnNmtjQ2pSM3V3b2hpTmZQTTFyLWdG?oc=5</t>
-        </is>
-      </c>
-      <c r="F71" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>A New Economic World Order May Be Based on Sovereign AI and Midsized Nation Alliances - Stanford HAI</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Fri, 06 Feb 2026 17:38:05 GMT</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOcVVDZGxfaERySnFTNVRqSUxjU0M1bkVEUFQ0TFhkZV82LUxhRWtTWUlEVEV6cUtRUVhLTzdsY2J3ckZxSVN6QUo0cjdzSWlacmpTLXU1bzAyQU10aEQ1SXVkNHVOaTN3cEFxelFXcjExWHhja2xJN2hIS3cwQU9ZMGE2Wl9iVGt1X3hSUDl6UGV2bzUzZ2VvWTUxRVlxQm5MTjVIYWlZRmpZeXJIQUV5UnBpb2hsdw?oc=5</t>
-        </is>
-      </c>
-      <c r="F72" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Howmet Aerospace to Host Technology and Markets Day on March 10, 2026 - PR Newswire</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Fri, 06 Feb 2026 13:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNZF9zZm5LbkZ1ZXVjNGdqT3JiX3I2X2FPX0s4V25ZOVZENjd5dmxHOTF2ekViX0FZTzhzd1EzcVYxYm5uaDRkaXZKc1gwbHJsR1R3R0pSN0NEZUtFWDJ0bm5kb1lvcUdjWEx6THhDajF6ODJKTFFBSVFvWDI5M1Y1SHd1aUNtVW9DVFFsSVBfWHVjNkJBcHFTSzFSOXV1QndBc0FQZ1R4MmZZX25pNy02S2hfc0xha2dkZmNzTm9iVFJWQQ?oc=5</t>
-        </is>
-      </c>
-      <c r="F73" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>CC at the AI Impact Summit: Core Interventions for the Public Interest - creativecommons.org</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Fri, 06 Feb 2026 17:27:46 GMT</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTFBwVGJFRmVmTTRaaFotRU5UX1pTcjU1cGVlSnNVM05wa2hOUHFyYVpLNWdCb3ozR3R6ZnItQzVHZWItN3ZUWXRtUjVycmc0dUVpbFRfa2xfWDVrLTc4N2tNTmRxVDFPUXJ1ZTJlTEg5bUJMdmJOelFUcEpWSQ?oc=5</t>
-        </is>
-      </c>
-      <c r="F74" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Hail our new robot overlords! Amazon warehouse tour offers glimpse of future - The Guardian</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Fri, 06 Feb 2026 12:01:00 GMT</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPSVh1SWVWWUtkbHZURHFMYW5MLWZxZzIwWFFxM0wwbjM5aVZkX3BoaTBmVmlqeDNpQU5YZWRmUGJZOTA1MWpzZ0UtRnJEbk16NThua1lEVVM0U3Q2cDlVcVlMM0xnNmZ4YmJmeGxyWnhlclJTV3BkUG5ZVXRybERoSXItTXBTMERKT1NqNDd1MHQ?oc=5</t>
-        </is>
-      </c>
-      <c r="F75" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Google, Amazon, OpenAI and the race to find alternatives to Nvidia - EL PAÍS English</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Sat, 07 Feb 2026 04:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQZEp0cTZld1RTR3lSSVFvWXdzQU1aX2ZXVnM1aHJ2UE80SWJsdmxuOEZ1SEljbkFwNUxVVlBmR3k2Z1RHTWxFYVVnRWlVemk5eEc4eE9zbTllcS1lYXhOQ0IyTWNfX2ZvU3dBT1h3SWQwUEdFeHVZQzd3NDVjUHphM1IwaVZnODlMYmdrNkN5Uk1JejYtSVE1bXVabHZyUUs0QWZTcmU3c0ExdEEyZmcybWh0a0JkUW92YWfSAc4BQVVfeXFMUE9wOVJMTk9zb1lGVEI4SWMycHNYM3Z2OXlhM0JlSjMxNEdSVnROSFhON2pWWFZGVUYzMmZVb01iYjZDNjc0MHljTFlSZnhUeGt5YjFFRDJ0aGEyLVJkbzM2TGpUU1BwemcxTXBOcHlFUFhJVXhCdVViZmVwYUhwc1ZBQ3hMaWNFeGZCc0tkTy1QY1dfRk9PUGVzV01tV0puVE42TnB2eEloNXpkQ2k1bmN1cUxCN1RES0pQYmxoZzhZQWpYcW9KaGVFNU0tWmc?oc=5</t>
-        </is>
-      </c>
-      <c r="F76" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Open RAN Forecast Revised Up as Expectations for Future 5G and 6G Deployments Increase, According to Dell’Oro Group - Dell'Oro Group</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Fri, 06 Feb 2026 13:00:11 GMT</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNNnlpMnlYTFg5SjhXT0xXOF8wbTFiUWhURDJmSjgwdWpMc0szWENSUDYzLXI2OWIyTHBtOXpTdHFQSzcwaGg3bFRJUFozcjBodjYtblhhOTN0ekF4MXYwZTVobDZWbmt6UUVBdUFoa2RNN1JDamRUSkxKcHRtcmpCTEZoTWNiQ2pvbjN2YTlaUEpNZkNSb1haZHRhbjNuazRaX20wUzBsU2RscjF2Y1RjS1RTQ0NDbjA?oc=5</t>
-        </is>
-      </c>
-      <c r="F77" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Kevin Frazier Joins the Cato Institute as Adjunct Research Fellow in Technology and AI - Cato Institute</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Fri, 06 Feb 2026 19:16:46 GMT</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOX0x5ZWhyeGppQWNaSVAwLU5IMXdBdDFPQlZJeFVycDhjbWtYNUl1YW11anozS2NVZFZjOFFxdkU3T21wNnhYOTNPOEJ0MjUxTTNLWW9PRC1fOFJJN3VScXg0VnNTV0dJRm80aWx5bHcwZEtFS3ZnYUt3UHVqYUpFbGY0MW9TU1V6cHRNSnYxM0doeUxEdXg3cDk3bzBIeVJMeDVNV2d5TWxwam8?oc=5</t>
-        </is>
-      </c>
-      <c r="F78" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Insider_Risk</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Employee misconduct leads to over $16K loss for Lloyd Catholic school division - meadowlakeNOW</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Fri, 06 Feb 2026 16:23:43 GMT</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNVXdQUFo2RmRSeFc3clg5VWMxa2xqU1FyU0VjQkhUbWtTWW56QjY3Smw3SkVSZkxXZTV0TUJiWUJEM0lBTzhBVExYc3dmTHJ3aUlTWUNPWUlpLUwzTDJzQzhzOFgyRklpUURWRi0wc2Q4SXc5bEc2TEl3LWZtY0FjVUExQjZVZzRndW9zMk9BWXU3b3hYQnFxV19pZklBOUcxcElxU0ZNU21tVkg4SWEwOVUwRUsyUQ?oc=5</t>
-        </is>
-      </c>
-      <c r="F79" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Fraud_Scam</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>TSB warns romance fraud rising sharply across social media - FinTech Global</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Fri, 06 Feb 2026 12:10:59 GMT</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPaHhuZVdVNjhJM0xyLW45TTZMRndhemlvWXNKbzNmU3RGU0xNZlNhd1VTVURSbGRsXzVxZDVIR2lvVzdXbzAydklleUtOZWJ4WEgxeXRUdk9XLXdWX1pQVkFlcVBzZDUwRlREZC1QdG94YzI0Zm1XNFhUZEdqZlFWdHU0Z0o0TjZXbURJY0xQSDFObVlkLUU2dw?oc=5</t>
-        </is>
-      </c>
-      <c r="F80" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Fraud_Scam</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Oversight chair Comer requests wide range of business documents from Ilhan Omar’s husband - MinnPost</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Fri, 06 Feb 2026 20:15:47 GMT</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOcXptUEdGY1NxSjF3d2U2emNXMFB3Nnl3ZWZCS0tmLVotbmVRcEtHTXJiV2NyYVI1LVBiN25XZ21iOW5RTmlKZm5KRzNPeHBjZFdOQnRpMU1JQjJlVU1VMzJoTGlWcDhITVNHMzdVNXlucXNsWEprX3UtN0RFdDZnMTloamNaMENoT3lzS2xEaVlSZ1E0V1BYMWg2MzExYlpHUEh3SmlsN0pNWTZuYy1LUUhBUDBGTVZjVHdIUkRVQkVpU3ZLSVFDdk4zeEJnQXRtWVlBSGpRRkczUQ?oc=5</t>
-        </is>
-      </c>
-      <c r="F81" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Fraud_Scam</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Trump shares video depicting Obamas as 'monkeys', also repeating election fraud claims - Anadolu Ajansı</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Fri, 06 Feb 2026 10:12:47 GMT</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQVVhSdXc2alE2elRWVEh3TTZhdTY0ai1vMFpPYWswRVFGY2p1V2NEMnQzOGxnMWIxQ2tLdDBzSGZuUlloRVZqVDR2N1pqLURJeUh4R3d2TEtPRHM1NTFPaVBCNEFqOWlpSVFiQTVlTUJSeWhEemtHdDNyZzJleFBQX3lHLUxKTkNidkl6a1NxYjlZdjRZRUl1ZTMzT1BheV9wN3hrMmxwQ0lMVlpCcG8yYXV5eEdCOW1xUm1zNWlLa2NlMkk?oc=5</t>
-        </is>
-      </c>
-      <c r="F82" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Fraud_Scam</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Bernie Moreno introduces bipartisan bill to crack down on social media fraud - Cleveland.com</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Fri, 06 Feb 2026 20:16:00 GMT</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNdWZNTmpoYzVXS1llQXE2d3ZpRHNMOWctWS1YaER2eVU4a0xsNXZpU2Jtay1qaUZSUGpvMU1ianFtQWpkR3pMWnBCRDIxdHJiRlNDYmZhQkxzYkpnSDB0bndSelk4Mk9DS3ZJaVZuYVBzMmUxUklHaXE3QkotVUtxdWl1Z3ItMHBJVVJvM1d2cG1SSDFSeEFOMDlHdHh3YXFRQ1RHczZTSUVqUENhR2FPcnhkQWw0NE9JSWZmT9IB0AFBVV95cUxPb1d5WXMtNVk3SFY4T0lHZVQxb1N3cE5USU1kX3VnVnNIQUxFbnN6YzZBMUpsNWI1V2J1OGJFZ1p2QWItdUZZTk5HLUx6ZmxsYjJFbHEzd25fa3RQMXpidGJKUDA4Y1lxWkpaQ1J1a1lyTWZTWGhzSkNaSDV0MXhWeFM1ajZ4ckxzMjQ0dGtMdWMwZGpWdzB2MWxVV0Y5NmRJRW5ZS1pYRnFjaVZyNURqdXU2amd4M1FzeGhQa0t1TlZfWU84b1NCLVNuaG8waU5N?oc=5</t>
-        </is>
-      </c>
-      <c r="F83" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Fraud_Scam</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Trump’s racist ‘Truth Social’ post also included whopper on debunked Michigan election fraud theory - Michigan Advance</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Fri, 06 Feb 2026 18:34:52 GMT</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNYlRuT0lWTUdvTkUxRDdycjZ0SWJ2cnZiZGxfWXV2MEk5R2N6ay1Eb2RfZmx4V2VsSDVtWVRjN3V4Rm1sMEtwOGk0RzdqT1ZISnlRVHdXTWozQlE3Rms0bUxaLUFKZk9TWmk4LUpkTmNRZW1zU0NDMlBmYU1EdUd3MG1mcjdrTWxXY1E2enJfY29NNUI4QjBxRGZYVXZZT1BJUmhlY1FTeDQzV3JlTjlEQ2lLdUdZVmxuQ3M0UEM3Wi1kVkFtcF9nR0lMU1FIbGVDdVE?oc=5</t>
-        </is>
-      </c>
-      <c r="F84" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Fraud_Scam</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Feds can't withhold social service funds from 5 Democratic states amid fraud claims, judge rules - Action News Now</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Sat, 07 Feb 2026 00:19:39 GMT</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiiwJBVV95cUxPNjB4SURaaUJUUFRTRXA4a0VnQ1FUR04zbm8xVHVxWEUyaFJ2TzR2bVR0cS16ZEs3RkxObVZHY0l3enBzU3l1YlF0cWtGY0NMVWM3TktYb3gwQnI3bFVwQXlHQkhVWnROa1FaX0pLb2tTUWI0aXg0WWFxbjlhZEYtMjY1a1JyRXczTmpza1p6ZERZZzJ5eXluM2dFbmxoWERXNWcxLVVicmR0NDM3YmFPc3l4Z2hWenN2ZHNiYmY1cjVOTjdXZ3Z5cVBzdjJiWTBkNzdHanlZdzVhbUxwWmlETms0MXdFM0JNR1Q1YUhCd1lYdHVCQklUYXViNmxVRmZMaDNkcENsZVdPelk?oc=5</t>
-        </is>
-      </c>
-      <c r="F85" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Fraud_Scam</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>SASSA ramps up social grant reviews to ensure compliance and tackle fraud - Cape Town ETC</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Fri, 06 Feb 2026 14:00:56 GMT</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPWnUwNFFtSjNVeFdVZmNzenlWWmVIa1d5SFlBcjFPcXBXSHYyN2cwLXVfeXR5ZGNlVlE2NkN0NjJKVm9XdVUzem4zeVFqS2llSlAxU2l1YTlSd0ZZMEtweEtrUUFjQWZRYkswNDZneTVULUR5bW0zWm1ELWt1Vk9iejExdWFXU05BdUVMZTNZMVJ2aWxHU0V3ZGxjaVlMVkdxeld3WUVRTnJ2WVk?oc=5</t>
-        </is>
-      </c>
-      <c r="F86" t="n">
         <v>1</v>
       </c>
     </row>

--- a/data/daily/topic_feeds_daily.xlsx
+++ b/data/daily/topic_feeds_daily.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,17 +461,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Treasury issues update on car tax 'structure' policy after MP query - North Wales Live</t>
+          <t>ANALYSIS: Understanding Geopolitics To Gain Wealth Edge - Wealth Briefing</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 06:19:00 GMT</t>
+          <t>Mon, 09 Feb 2026 07:24:00 GMT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPZHR4RmpfWkRiX043Y3JWYXJEOVdmZDBUUFJGR3pVQlp2eGRaSEY3Zl8tZmRsTGNnSTl4c0poT1l6a2J5a0l3UmdVUHJ5VU1ydnhNTTFiQk91WDNxU1k5azZpVzdqdFBzbHBkR0t4RzlFSG5JTzhrMXFDM0dfOGUwZTRLV2FZX3VnR3JXWlVrenk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPbm13a08yemRjZ0YxVFBmSThhaDNMSzUyckY3YWFyVmMtUzZmMU1wWHlKN3U1VDNYeDQ5UURSX1ZXbWtFeXF1REtNU1dXaTdQMXpvUVZnVWxkcEdKQm1yMEh6QVhrMU5VMmVlamR0SndBMkYwc1hFOWpNb183SnFVZ1VoUWd4UFgzajEwbkl1M2EyV3NnZS1rM041Rm42R3ZfV19MUlFfYXk?oc=5</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -491,17 +491,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Herzog’s visit to Australia builds conflict not social cohesion - Asia Pacific Report</t>
+          <t>Global Humanitarian Policy Forum 2025 - Protecting Principles, Norms and Values: Summary Report - ReliefWeb</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 02:58:24 GMT</t>
+          <t>Sun, 08 Feb 2026 23:25:19 GMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQOV8tUW1CYVNtdnNpOG40WFYxOHg5aXlDTngxTmRYdzllZDl5S1Rla09ENkh6N21pMjlBZXF2T2toMlRpbC1mYlhhTmZNVzZFTzJWODFCZEI2azRGX0pkT3gzVDhaSHhlVlk3bUttSnBKOFA4bExMYVNMN2l4RmtwYXVxY253UnZxUzFlaHFKX0drYkI2WXMyM2p2NFRaRVlpQ1k3am93?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxPNmpYUGpRU2x6eUZtWkpOMGc4QlNEZEVTdVE3NWVuSjF2V0pQMHRlcURkVUtUbDg4Q1RXMGtwWmdYaFVkaWtqclFWUF92QnJHNzBGQ1MyR1pMTXNoYmZ6VjdhNUpERy1ZZXpaN1hNb2ZacGVPLW1TOGNFSjZybkJoUHI3UDByTmJCTGpwZWUwQngxMk40ekJhNkc2REY2YzhWTi1TUXBuNHNxVXhaY0NkUGdjR3N3S0E2djhwbHI0dFAwNi1j?oc=5</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -521,17 +521,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Internet, Cybercrime, And Politics – Analysis - Eurasia Review</t>
+          <t>Review of Marketing of Infant Formula by Retailers Final Report - MBS Online</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 01:05:40 GMT</t>
+          <t>Mon, 09 Feb 2026 05:10:57 GMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOTktNanFySm5jVFRySkJKdmFQUDFsYU9fMU5RQWluV2g3UGVTdFIxZlFMVXJQWExuRlpuT3M0TXNpblBabGRreC1jdEdIMVA2dXdwdzJiblA4Qi1ZYS1BLTFHc055VGpkMDhGSEZyc3ItMVkxOUpsaExfd2N2SkNyQnJ4RTBrZUNu?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOM3ktUUhpREhicEs1MkNXY2h6Y3lUbFAtWTVuSEZoMkc2RTV5emdRbXV4ck8yQnRqVVdPcGN4bHl1MmxySFBLNWw3eXFRdGR1Q3BKNzUzbHpGUFhhSzk4RldIY25uR2pvR2ZIc3FBTi15dl82QjVkTnZsTVUxOVFxd1hwd045aFNxb3FfU2paY3hxaVRVZ1huZnl1cEYyb1p6bkd1b1BFVzRkdTRqNTJzZktKdEJWNloyd0kxanpFMm9aUQ?oc=5</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -541,27 +541,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Port Vale 2-2 Burton Albion | League One highlights - Sky Sports</t>
+          <t>UMSG addresses ICE ‘misinformation’ on campus, hears budget report - The Maine Campus</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sat, 07 Feb 2026 14:35:01 GMT</t>
+          <t>Mon, 09 Feb 2026 07:05:05 GMT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNSld6WEktOXhONmYwRF9WRVVMQm1Hd2w5bTlyT2ljUmxUUWdoYTJLcmFxQXpKOUpSWjFSeTdGYXZQMUpUVm45UTB3aVliU29KREdiNmVldkhGU0hQVUpYTEFUREV1VHF5NUp6RmxBSWJYamNMLU9LZ280OFpjUm4zbUZpVmF0dDdtWFpRU09BTUZfdVhXcGRoemVMQmVONUFfenkxV1A1ZE4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOTXBWbWRYSlpxYlJWVkRaTEFLSkdNSWpmQlhXbWFwY0dmb09nWVdpYjZkeVA1RFF1VjFja3cxekZYVkwwQllta2VfdXA2dXA2R1JFbWczcTUta3RqaVQ2R0ladWVoS3pycmlfRk1qNnVfSXRjUTZjYXBXU0RXeF82VUlyQ2F2alJwVEhuOWVtTG9sY2dSbmNVeE83NkpDbElKSlJQMW5LSjlvcWpUbHdv?oc=5</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -571,27 +571,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Trump signs executive order threatening tariffs for countries trading with Iran - BBC</t>
+          <t>TikTok US Explains Privacy Policy Update - Social Media Today</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sat, 07 Feb 2026 08:06:45 GMT</t>
+          <t>Sun, 08 Feb 2026 19:22:13 GMT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE84aTZ3SE1iWEJEbWNNZFhMMjdob2hBaUN2bGVqQWx6azRuUE1YdktPX0ktMlVwNzl2X1JreWgtNERCcWN0VzFMdXB1Ul92eS1DOEpCQURpR2d4UdIBX0FVX3lxTE05d1E3NGFURFN3RG1fYVlwckFYLVZnYzVROFM4aE9HZjZfLWlJN01rOVhMS0VZdkh4QzFTRUdwbC1aeGU5TkNuOExScXhxeW4yY0ozYkpqcGtwaG9qd1FF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOdUZzMzVvdzJubF93SDcwN2pET3lhLXViSG1sd0tHR0VtdDMwbzRMNFkwWTNxbVFIeWJURTNvRTc4WXFYWTRENGs5MGdYdTVpekh6M2lwSWNFN09fMHczcmRkNldUUmFnVG5JLW5fcFYyZGVpcFdZSk1xakNGVDFIbzhCV2o0dVlDOGtHR2RCcw?oc=5</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -601,27 +601,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Iran Sanctions and European Energy Security: Compliance Considerations for Caspian Trade - The Times Of Central Asia</t>
+          <t>Inflation, AI, Geopolitics To Impact Australian Economy : Analysis - Crowdfund Insider</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sat, 07 Feb 2026 16:41:32 GMT</t>
+          <t>Sun, 08 Feb 2026 15:42:41 GMT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxON243MGVVY1ljc3JBeURzUll1bVpLamFRRjdicXVFbzBKMTdJamZyVFYwUDJoeklEVHNJeG9QMWlpUjg4cW1yLWpMVHhFQUxIRWFTaVRPM1JfeG1Ma3RWa1hVQXk3U09MeXRPVi1IVlo1ekZ1UW5qWjhlT2NHOThtVXk0eDVBWjFUdFBDTFd0SExhZ0hwQmxJOGw0Ykh2YzdWVUJ5Z0t4UE1YNlVi?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQQVlmWVZyWlJLd2RxaHh0OE9obUEya1MzcXNrZFpneXpod3hhYVgzMXB4Y1BzaFp2Q0hrMkhtaVVMWENnRndNT0xGcEtNOEZoZjhDdUpKaVQxdlpPN1phS1BWeGZvVVZLMXotOXFRaEtTME5kMkxXcEhxNVEtRU5TemhQU1R3Vm1MTGlzVkd4OG5maHJXeDdQLWlGOVhjMnptUjFobkZLQWtUTnRqQ3BfQQ?oc=5</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -631,27 +631,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Porthos: Decarbonizing Europe's largest industrial port - Air Liquide</t>
+          <t>Russian officials are warning Putin that a financial crisis could arrive this summer, report says - Fortune</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Sat, 07 Feb 2026 15:10:48 GMT</t>
+          <t>Sun, 08 Feb 2026 21:14:00 GMT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxOUjZUN3NXTlBIal8zRDZxTnQ5cDFrbk1NYlVuMEVnclB1N09MazJTSlNncW40Umdkbk9FejJxUEZmLVZGUEN1aWQ1Y1hJU01hUHA4WlI1b2xJMXNLbVVjYjFvODZfQVo1ejVKVnYxOXA4bGpES2hUZWJjNnRaN3Q0ek8xMkNZWnM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQRTE1QWtyZmJHTlYwOHh5dXNra0tJQXBES21RYm1qZmxBMUtNS1RUMUlwdDd4MEFzM2lJemdOUlloa3pkTHNkWjdqdHZyby1ORkZOT2xUdnExTC00b1VZVGgwRzgtODZTWkJBQlRsUHVOdlR2QXhDXzBOMENLTUlFQkROSFFScGVLUGw2cUp0T1NKUHlrRGRoZG1BbUxCOW13al9FSTFmRlg0VUdiaFNvR1NrVQ?oc=5</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>India embraces free(er) trade - Financial Times</t>
+          <t>5 things to prevent supply chain disruption - - Enterprise Times</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 02:13:50 GMT</t>
+          <t>Mon, 09 Feb 2026 06:39:33 GMT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE41a3QzQTJMUlVQTGVXMm5maWVGTW83ajJzd2tWTDN1UlFxd2hpSzUxU2Vfa2ZzM1MteG0tTG1ocVY2ZGlMclAybzJsdTlIU1NCTFRPUllMcjN2dEs4Z04yYlBzRWxTeUp4MmtyQ0g5NnU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPWjhaT2M5c0hCdXhLczJMUHZnR1Y2Uk1ncGlQT180UFB6ZEpkSF93MVFNaF9sR2p5bjY2LXZhZERXSEVDRGFQSlFFZGcwZ1pjcktiNXg1Y0M3TkI5eVF1ZzZ6ZGRyWkl4OHA0TTR0WjFFVVBlTFhzOWU1cnVDSW1UWE0tZHEwbDQzUjNPSy1UQlpGcWc?oc=5</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -701,17 +701,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>WATCH: All White Ben Waine finds scoresheet again for England’s Port Vale - Friends of Football</t>
+          <t>Dining across the divide: ‘Tariffs are the one thing I agree with Donald Trump on’ - The Guardian</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Sat, 07 Feb 2026 21:14:11 GMT</t>
+          <t>Sun, 08 Feb 2026 12:00:00 GMT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQZlhZeFFyOVVSSDV6cG1OdTBleTk0NVRVdVJyTUxlemJTX0cwdkgtV2ZVckN5OU1wRGExWC1RelpMUkpJdF95QnNtSVVaVERLWnZPS1VUNzhiUVVWZE1saDhndEkxUE4yVHNmZXhWMm1KWWktSHlKYldTeFh5dllJNHRwSjA4Rl83VXNpTWZNR2dWdXdhd2tPYXEyU1FFTW9OSUJpVkhMcXFGcWVHQnhLd3JuNmQzZWFjT2pv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPVno1bmFoU0l3ZEhfWG5yckFyUE5PVVMzMnpGcHZDTVl4cEExS0ZNQnhDX2ZXTjFpX3V3bWpwcHQwQlVBWUpWSFBKZEpRM1VxRHlxdWRDUUNPOWp4NThyV0I4Y2dIanlsNHRuVXBlQjdtSF8tRGdNRVMyWXFUcXdaNHNaNkJaNEJUS0xfUTZWVjUzM3FSamg0MklpeXZobVdkRnZOVWVKbEZra0ZydHFmUWpHVWxOTVNzaE1HZldJQVFVYmRRRHdWM3lGaS0?oc=5</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -731,17 +731,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Genoa Port Strike Blocks Weapon-Carrying Vessel and Disrupts Mediterranean Supply Chains - VisaHQ</t>
+          <t>Last mile quickly becomes logistics investors’ first choice - Private Equity Real Estate | PERE</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Sat, 07 Feb 2026 20:41:18 GMT</t>
+          <t>Mon, 09 Feb 2026 02:00:39 GMT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPeFNlTkFhbnZ3bWthOVdua01LYk9zVVFDZ2pRTWdDR2VVYXJzT2o1Nm1PZU1vZ05OTHB2WG91c0xQSGhNQWo1ZUJoRXVqN09TdkhmOGxZaGVWdmQzWVowdllCblRNR2ozQkZ3Z3ppUnl0QkY4THhrc1pHWFF4MWNxX1JBNjBfcDlvZHUtUkpTUDdSeDJURnRVMFcyNFZsOGprQjduTEtKUlpHNEV3cXpPX1EwZFh5V1lDWGl3WVVadWNoWWFvNENaUW5aWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxQY0JTX2pwT3VzYjAtS3ozdHZqUzdYN3FfMmxNWFYtMTV3S1VhQzNNRE54WldqcWJXbWZmWWZhWVVuX1dtTzg5SWhUOFI1bzc5ZkhqWnZ6aUtuX1NIazE1cHdqd04zc19MVEJaVkU0bVBoWVpwX1BIUXZCSjF1dmhvWThoMTVLZDRHUnRLRQ?oc=5</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -761,17 +761,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Veezu Hull Switches from Metered Tariffs to Fixed Fares - DM News</t>
+          <t>EU targets marine insurers with proposed blanket ban on Russian oil shipping - Insurance Business</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 07:41:14 GMT</t>
+          <t>Mon, 09 Feb 2026 06:09:36 GMT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxNSk1ULXcyZlRrakJzejRGcjl1VFZPV2h1anVFSHRob3FzQ3Q1cjhDTFRISFVHTXdrSkNtajVuemU0QlRDTzhScG5pTGk1M0dpcWRtZmJFTVp2cm9oZW10ckVxaGM1ZXEzMUVXUE5ONHJOZlBpeHNZM1gzOWlNV0RKWGFqbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPZkdkTkRxckRUZktTSTJsLTkyLXhsbksxbUs4YjRDdmFKUGM4WEpUdXlTWWpPNVF5d1BpR2o5azh0T2JIeVhaX0VYakRzYk4tbzFkMjRxZ3RqaU1oc1AxaTRLR3piQW9rMzlRTGI5RThjbFdqZW02dl82X2FIZDhxeFRfYUszcm56T1BWRDFoWEZJY2NhVHJ1TEpNSHFPU2tXUU5faVVyN1JfcW5PVllHeWdtaUw1SmdZZ0ZVNUktTzhxR1dySFVnTW1nUk53cHBqd0ozUlB0cw?oc=5</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -791,17 +791,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Drug dealer jailed after creating group chats to share child abuse images - Greenock Telegraph</t>
+          <t>NBIM quantifies the portfolio threat of economic fragmentation - Top1000funds.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 06:30:00 GMT</t>
+          <t>Mon, 09 Feb 2026 06:01:24 GMT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQNWtRUnZBS0JpbjRzc1JUQUVOT1R5WVQ1WUJJeTlQY0pLNGQzS0Fxei1NcXFBa1QxQ0lWRzdweDBWX09kb0xwMEQ2eDd3RTB0dUZQbFNJeUZnd0dkOE9DYmp2OURET0tVbEpva1B2LXFnOFdwbXd0SFFlTFR4WVJYY1o2eU5MWnVwWGw5STA2OU5fNjhZX1hOZ1htdzVDWDM1VlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNRkRnTGpxcXJxTFpGSFBQWVlBM2JKbEZaMWJfczJNbWhwNDNXeHFUUVdrMkFXeDNjbXdmZUJVSDViM042LWp4MXZDSWdDZkdxTnFJLUFwNGsycUlUbWQ5alQ2RFRJZksyYzBhOGpOejBsZ1NSRUNGbDVDX1NVa00zdk5xMG1YeVEtdmdYSjdOZ1hvdS1nWkxQM2l6eUZ6RjV2UEE?oc=5</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -821,17 +821,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'I don't believe it!' - fury as council say 'horror' waste site is compliant - The Worcester News</t>
+          <t>New compliance manager for RSS - Vertikal</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 05:00:00 GMT</t>
+          <t>Sun, 08 Feb 2026 23:32:04 GMT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQSjhVT25RWnRXbDZiWjBwS0ZCWFdjNDJWSmZlWUZYbnRJN0doODhxQ003d2dxSkFxb1hnZERuOXQwZmNtYVhLV0c0YkRfXzBxeFVoTFBkWnB2SzFyRkpUQnB4UlQ1d1RUbWZKalMwYVJfWXFlSTJBZkpXeUlHN1p0SFBJbkZ4ZU5SeDRoUWhWRWZVM1lJYzE0TU1nVnR4Y0U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE45RVN5WWQ3bjdjWkRpOG9PMWo0RXhtcFhRSmRaNVJTV0J2Ml8xc1RUd1BXb1JGckMwZUtfS1RiUVk2V1hLT3dzYk5nR2xPUmpkRmFmWUY2UXpTbHJiVVZnbVBGMmwzek41SVNwUkZrRE9qVDlkX1N5ZnlyTQ?oc=5</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -851,17 +851,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Somaliland leader says Israeli firm could be granted port access - middleeasteye.net</t>
+          <t>Statement by President von der Leyen on the 20th package of sanctions against Russia - EU Reporter</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Sat, 07 Feb 2026 23:22:00 GMT</t>
+          <t>Mon, 09 Feb 2026 07:44:24 GMT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNamstcjJQNGl6NWVGenQzZFNVemZIMFBvcHVEalhBS3JJTHFJbWpiSlZiczdCQUdwRDZnMHRCRkRxUnpHNTI2dURtanZuRy1DbS1tcjVUVU1vRDV4c3NiSjRvd1M2UjRob3ZPRFBVYnRjUG0tdE1TVDlEZWxQM29pSnl6VlhFYlhEdG5vRFUzR0hzVmUzQXNCMlBiSDJoQTA0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQa2FNelBQcFg1Y3ZrLUl0Q1ZHNmk5SUlab0lvRm9rTEN2ZUU5QWlaMEJVSElZMTBwc3c1UVFNVFFWN1JBMFZybGx5cjRqUjZueGRwdHAteXU4WG14QjdFdkd1UXdwQjJTU0xUYi1ZLU42MUZYWVhFRHhaQWJ6Q3dVLUFuVG5NOHdXMVIzZXVIcDNkRENMOUJIeTZXY2tucFF0aU5xUFVuMTJ0OTRnZ1RlTGpBOUdhckxZREhQR0FfOW1YdllmSHBoeUZOeWtuZGZs?oc=5</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -881,17 +881,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>COSCO SHIPPING Debuts "Budget-Friendly" Sea-Postal Link to Peru - LM - Logistics Manager</t>
+          <t>Major Australian Iron Ore Port Reopens as Cyclone Risk Recedes - bloomberg.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 05:16:39 GMT</t>
+          <t>Mon, 09 Feb 2026 07:06:00 GMT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOb1l1ZU1WbmJNV3ZFQ01WaVdQRUpSR1JYX1BJdk0tN0FzX090dktwNlQyZEJMWE5XV0xEQWtCSE9fNzVOS3hkTkx0eVJMZGZRZjgwT2dsT25vV0tlNHRTX1RRRC0yajBOY05RWTYyWkFkbndzUG13MlRBa1JSMnQxZUtiZzRxSmxDVkpDTWxIbUxYdFZyNWV3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPWThaQV9FdHF3N2oyZDNXNmN4YVViejNJSThiWU1qcl9VRU5mem9DdGJLOEY1X3BKVkhReTNPZlFPa3JkRGNXQTNaSG16LXZMZWN4ZjJnNDRkc0VmOWV1RU0xRWw5RHZOaEZPTFRsV3JNNDNJVWt2TGgwTzJtVFQyR25MdEljX0ZYMmRRdmZCcHhYU2wtRWVMaUhpUGZCTUZXMGJKclZ0aFRZQUpIX1dWRXMtNA?oc=5</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -911,17 +911,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Optical tissue monitoring predicts dialysis-related fluid instability - News-Medical</t>
+          <t>Who will use OIC’s Scapa port? - The Orcadian Online</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 03:04:00 GMT</t>
+          <t>Sun, 08 Feb 2026 17:18:08 GMT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxORTFTdlo4bmZ0SnlNNWRpNGt6amZLakVyRFp3aERPcm1Zam9EMlp6QkJJUTdlTW5ra19qbEZWd0IxN3VaR0FZblhURFBSNXJ0TEVDZW5iRHlLV2ZvcTVMNWZGQkI1akNDVnRrVmROcGpRdENCTXM4R0NNR0t0dWhSdGlwQTVlSUlJR0tMSTJMWjlSS1NLVHZnUkh6YkJROG93ZXFsa3ZyY0xuS0VqOFp1UzhIaWIxTU92?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYkFVX3lxTE9DUU1hdDY4TFl4blgyamFiZkVmakFYQUwwOXRYYk5uTWFSZFVKdzVUTlZ3Y0stLVZraDNNREc3RlZMaHRPS1dueElRd0FLbXZQRVppTVhGZThrTUR6QVE2YU5R?oc=5</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Thailand votes in three-way race as risk of instability looms - Reuters</t>
+          <t>Record Order Intake for Witron - Logistics Business</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 01:02:55 GMT</t>
+          <t>Sun, 08 Feb 2026 15:38:20 GMT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPRURUVDdMXy1PbHNYa1pFQVVoc2FGbzJwTlM1OENlNXkzbnl6WGd5eGg1UmJwemJ3SWtlcHQxbmdLTGlBeHBBeEh2aDE3WW56OExyZVY5ZHZKVWtPTEFSbHBoQ3RBYzdCUTNaZ0psaE1fRENiOTZDVl9BTkVfcXpMNnItb0dGSk1JTlJDbVlNaDBUU1dTVGdwQ25tRHpDQlJ4YXEySlBUa2lFWkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNdGZ3X0VPOU5hOG9BbFpJMHotdVMwZzdKOGZCNktzcnc2M1FNS0RFaF9CVk51Q21MVkloUU0td3RZNENNWjE4YmhiNWZQNHdMTVl5TDhfWlVKcG5Iazg0LVlJS0o2QTBVcGJtSHpZRzJwZXpqMGkwY2R1WWlvVTFsVWhjaXo5Y2JLUllGOGZLQlR3M21EYmRLNG15YUVLQUROekpRVUMwSGRtYUlv?oc=5</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -971,17 +971,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria’s Russia Deal: How US Sanctions Can Halt a New Mediterranean Rogue State - The Times of Israel</t>
+          <t>Braving tariffs and uncertainty - eKathimerini.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 01:47:00 GMT</t>
+          <t>Mon, 09 Feb 2026 06:00:22 GMT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNcTlQS09KY1VPd3c4M3NiSVZTXzlfcENtTFp0UjR4N2JYMHUyUk83LXh6SFRyYzRpS0lkV3VpTDVfTkpCdE4ycXg4WURic2cwNGdFakgyUm90UVg0VlBsM1RhQkZIMjhrSTVsUkp6eGNyOGVkOV9QWmNhRFJaNW9SWVdYTFpYUzN2amZzRjFWSXVWblBUUVoxUkVWd3dHT3Ffb3BLa3c2LV9abzhackxHQg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxQR1lCNEZWR1pfNTR3b0Y5SnZBei1IeDNDWXhlejdTUHJqZFpsM0ZhOUxPR3djY2VMUC1TUnU1OFZFVEJXbWJaUjdfb0pzRk9weHNmRWNqNzljV1JkaTNsQnVRajJkcWFPTnV0eGw4d1MtUHVmUlBLQU9KRV9lV3ZQWjczMA?oc=5</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Former British commander Richard Kemp offers his assessment of the instability in Iran and weighs in on whether the ongoing unrest across the region could be drawing to a close. - Facebook</t>
+          <t>The shadowy world of abandoned oil tankers - BBC</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 01:13:15 GMT</t>
+          <t>Mon, 09 Feb 2026 00:09:30 GMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxQN0NJQ0Q5Q0tpVjFwQzRlZjZ6LTNvZDdEN01XOWMxZ1lLcVU5NUotNWlOSWhsTWlyTnBIOTB6VmswaUtMSmEySmJQc1dBa08wRzQ1Ry1rcEtYWlo0NHZReXpxdkk4R25zanNpWDZEbGItdGl5aHZ1OWhQTmpOYm5LVTlHZGJrOE90d1ItNGZFZFJKRnVaOUxjQzFtRERhXzUxWVBkQ2MtWmtqN19hYkREaVlteE1EZXMtY08tUDJDamVlOHZsTlVDOGgyOFFhUURwZ2cxNzJ5MTIzYXQtUHBJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE9zeHBlczJhQzR5bGNsQlV0cjhoMU1BcnEweU04eHg2U3VYQjNuNXdlRkQ2TkNTRFJ3Q1BzdjBlcEQ3a3ZQLWF6dWJlMTVtdEg5eTVZNEY2NWtZajEx?oc=5</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1031,17 +1031,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BYD sues US government over tariffs; move sets precedent for Chinese firms to defend legitimate rights, interests: expert - Global Times</t>
+          <t>WTI holds $63.00 as US sanctions offset easing US-Iran tensions - FXStreet</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 06:51:00 GMT</t>
+          <t>Mon, 09 Feb 2026 01:32:03 GMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiYkFVX3lxTE9NYXV1UlY3c3NvQUZSRm1GQ3QzYldadG5zSm81dnp0T0NBbVVWdkJrMFBaN3JPVC1SM1lVUThVXzFPY0k3eUtTNzNaTWQtTk5kazU0azdzbG1IeUZpMDhDLVBR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNYUU3YU9ja2tsR25tMmpBOHpJYjhtNDRWbk5uVTFWc0dBVTFrMVJKQ19lRVhyUEJOY292cFg5TmowTXVJM2hyNVhQUU93NzRRTk1BeGFOc3ZtcnpmY21MdHd2dHJ1V2ozdXNBOEFzYmVkSFZEZDB4ajRhNFRVYkhlSjM0czhPQlVwRmRhQ3NfN3E0dS1XZHBaZjZTaV9UWUJPX0U3UVc0S3BfNTFjVmRsY2o3aDBuUmRzZjMya1ptVEhLcDNnM09wYdIBzgFBVV95cUxNVjhnbkZBYzR3Y3lxc2RxM010NXFTQjd1NDc3ZFA2OXFLcU0tWElwYm9yeDNxeGJWbmEteUFlRW54NEYzbV9TaXVBUlJzcktEMDRrWi1LQndpWGNldXJ3N2tlU0ZQeWN0UmNlU0RKOUlMMmhVN1ZFWkstWkR1M05rQTBsODdWc3VKeEFhSUh0SFNodV9qdmNPMlJ2NG9ZNjgtbHprLWJFTERpOHRCeWhkdThBeVVLR0pkck52dzBaV21lenAxQ2ZvTmtMc0pMdw?oc=5</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1061,17 +1061,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Victoria International Container Terminal extends contract at Port of Melbourne to 2066 - container-news.com</t>
+          <t>Port Hedland resumes operations after tropical cyclone Mitchell - Mining Weekly</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 06:00:23 GMT</t>
+          <t>Mon, 09 Feb 2026 03:38:00 GMT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQcXROdUd2LXR1VUlGUFVxRGVqRzVEaU0xaGRmTnA0T1dYWFdtaDNWa1lOOHVIM2xwSDFZR2VLM3pXMm54RlhOVU1hT3hXUkhjRVdwemJ1VnNPRXZTekNydnUxYjlJS1UwOUNPOHFHRkI2dmhYb0FQMHV6WEZHN0VkYkpwYVdhcnFOclZnMGJGUjNfaTFJTV9ucUtzT0lLcGl4dUQyTnh2N21tMEpfdFplOThDbFc1dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNU21DRnd2dWJMV2hjeE8xUDRRaHQwb0Y1dmQzZDJkbnhsdDlxcGVPdlVfbDh1c0U3T18ycUJNejNkU1I1bXcwOW9mVVEyYWVtOGJmaWM5M1BnTmp6UXNSS2dzZUZjMUxnVnpiMl9NN2M4TUh6eWVrWnlCMUNfd25YUkxzbTZZOHRVVWxBTGtpYVVsT1NkY25ycE4xN3k4eDRwSGI2TnlWUHBOYVhFMGtDNg?oc=5</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ukraine's Parliament Speaker Makes Sanctions Case On Capitol Hill, Warns Against Prolonged Talks - Radio Free Europe/Radio Liberty</t>
+          <t>Travel platforms face cost and compliance impact of changing regulations - PhocusWire</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Sat, 07 Feb 2026 13:04:36 GMT</t>
+          <t>Mon, 09 Feb 2026 07:01:30 GMT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPX1FKSHkxLXp4R2xWYmtxS0pWXy13VUdTMWw1VDJETGtyZlhHZXdadEotM1lKZ0V4cWlNaUN0YnhsLXlCVEdrRnJsbUFHWTdTQUE4OF9GWlZfVTVwcEs3Y2hQeWFlUUVNSVdwWGhvWWNJVi1GS1lnWHRkZW1wUlI0RGdkRTQ4MkE4NjBMZmd0WmJOd0RMU3B3MjVRTVZxWjU2NGpIUNIBpwFBVV95cUxOTmVpWkl6VkZ2dGRZSEdzZk5MNm9udUNDOG9aY1k4Um9VZ2toU08zeGREd2tacG04MG03aXBCaXIxdkZiS2JtWmRYZFA5ZlJnZkNVc1MwNm9hWTJfajFZenhwZ0lEU1lQWURXVmtmd0E4M0xYMVd4YXcwTVlwU04zYm1NdlcwMFNCeWN1a1pVcXpOX09rdkxjeXJnSW8xM3ZPUTRWUnMzYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQZnpBekVUV0JaTXFJbm9iekkxbEZoWWk0OFlkWDAzeVZLWk5IaWZhdjEtdkFheTBSWDAyYklSelBRMGM4Uk9HX0tOaERLOG5pYVdJZWE3bHdQaUpfaFJsOEp0LVJkNkJUeXJxQTlBZkttZDZZcWhBUHdUSTlfNEpMMm5JV2tyaWkxMFpnVTR3RjVURjhRdGV5TA?oc=5</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1121,17 +1121,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>China's logistics costs-to-GDP ratio hits record low in 2025 - chinadailyasia.com</t>
+          <t>Embraer seeks expanded Indian supply chain role amid partnerships - FlightGlobal</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 01:59:49 GMT</t>
+          <t>Mon, 09 Feb 2026 04:56:46 GMT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBuNGhVQ2JqbGhBN0VaSHZtYlBGY1JldThTc3RlT2R2eXBuSzQ0RThDZkRzSHRYdUstX2FJWUx1U0VNQkExclhMTWdVVUpQbV9pMmZSN2MwRmI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQNDFFMjRvMHFwdmJzb3hmeWU2X0RPTkQ1S1dhMzJLY0hWalQyN09CMUY4ajdFMVdRZWdubkU1eURyVGdkVk45ZVFaNmtjVlZSSlF3UEVNM0luYmszb3dhb0ptbnNtdUxqMXlQR3VnbGowRXl5VWMtakJnU1QzYzNfTDRJRUwySERHeE5FZ3lHSVpobGFGNl9CUjJaU2M2ODNZeXhNNS1QS0xrMk03cndxTDRsVW1FcGxRX3pB?oc=5</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>JORDAN WRIGHT IS THE EXILES' SPOT-KICK HERO AS PORT SECURE CRUCIAL REWARD //NEWPORT COUNTY 0 GRIMSBY TOWN 0 - Newport County</t>
+          <t>China’s RWA tokenisation rules lift related stocks as compliance race begins - investingLive</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Sat, 07 Feb 2026 10:34:30 GMT</t>
+          <t>Mon, 09 Feb 2026 03:44:47 GMT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNaUJsUDFHUjFkbm9IbUJQN3UyMDZtTGdKRkpXc3FxSjdjWVk4WHlfWnNSSTZWN2ZVaHA2akJVMEYybTdZYU9GQ2Fhbi13V3h5WWhOaVVzalRQeEFLTEZrbHhrTGV4eTE2U2hVbTE3WEZpZThBZExmRmpaa3lRdFlHQ2FZbjJ3VmVYWi0xMExEYmhWcnBqbXp3Zzh5SnRPbElPTHBHZThOZmZOc3Nab0NsZVJLeHhUZS0xYUgzZXBScVg3d3VsSDhnR3dFNko?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNRTMtc204Q3E4Mk1QMHBhMW1QTjg2ZnlmV2ExWWVLZ0pTNnFTMno5d1dpV1puNUx3QUo5WUl3UkVwWUlVT1R4N2VzekNrdkdwcUJydUIwNzlkZlFpRzlQNjJoY1NVR2tvR3JaTTJRYURhaGMybERIZ3R0allQbzZwaldYbVJZWEJfbDBLeS16aTExcHZ0dW9nRngyMUVkQVFhVDNMZy1NX0pNdGdpQmtzS0x0MEV0aTBuMmdqSzRrVmdkaTZy0gHKAUFVX3lxTE5XVTRMOTNja21lY0JuNlpxSUFaZE1mb0FJRk5ERFNxZXpGYTNJbFdna1Q3aENYYks5LUhDZTdVd0ZuZk1MbU5jQ1dJbXZIOFFSY0g0NTZ3LWFRQnRWRkpXRzlTQ1FhNEw1dUU4a0tCQjk5RE93NU9ib1d4SmtXXzZZcUMxMFN3UmlQaFhEZVZoOEJsaFBqUUNKMWhoM1JiMjdnOHY4VmIyQU10clZuaE5iOWktYlZOQ3d5MTR2VXlfa0JDY3N3amFkNVE?oc=5</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>As China intensifies offshore tax hunt, exporters struggle with compliance - South China Morning Post</t>
+          <t>How a North East logistics firm is supporting major solar energy projects - The Northern Echo</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 02:00:14 GMT</t>
+          <t>Mon, 09 Feb 2026 06:00:00 GMT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNUGdfSDc4ZlpwMk5oX1BjbmlrdU91UzNmUU9vSnVVbmJtblE4VmtaTG5KMUpRbGFvZ0tWbU9zeHZVSkJMOGZyLWZoeklwY2R4eDBpbjRfVWhFeTZRMXZfLVcwVVFBcXlIeTg3M0tJcldsT0F5TGtDY3hxS2d2eUVaQUlJVlMyb2JNSlAzZ1ZmTm44VTlkUUZrMVYyMG1jSURMcVhmMDFxU09PMUh0N0UzemxKRUpaeWc1MUpNaEhxbWdlQjjSAcMBQVVfeXFMTUdidFliVmMtbTRpdjZ2VUFrdGdnQTlwNmYyNnBvbnNmVmpZcFZuZFViWjI0VzZtbWpwMTlIWnZKa0YtSFRoc3k0cl8xR1pCcDhibXVWZkpwbDBWT1VmRk9lWGZpV1JXNHdaaEhRVHF4Mm5VWVhBYnhFOWNqanZLLUdIWDdac1VmbzFZNVlpQ2JNZmV4ME9lbF9pYkt1N1hCbHE2bDd6WV9uUzNmdXBuckU3Nm5VSFRVRmkwMlJyekxJdlhr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPbXZ6N1l1bGZGR1ZVandIVGh2SHBrTFMxcFJLcnRSREhidUFHTk9xd01USENpaGF1Yi02Njk4NldTTFpYMnZDTm5KZHdldDVfUEl0aExrS214SWRVdjR5RWRQUHhFaFY5M2lFZVBLUmV6NEpETTNSMjRsY2lSNDZudThkNWRqRU5PdGJEZjdDcUc3eFBvUXVoM2FlWmFLSWk2amRHV053?oc=5</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1211,17 +1211,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Stefanchuk discusses sanctions against Russia with U.S. Senate Ukraine Caucus - Ukrinform</t>
+          <t>Europe’s shipping rules are not just Europe’s problem - 信德海事</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Sat, 07 Feb 2026 18:10:00 GMT</t>
+          <t>Mon, 09 Feb 2026 05:45:30 GMT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQTGVKMDNlYXpyU1lOenBBWnZobzhFa0lkZFZHYU9mZnNzRkg4NHJLNHktWkVsVnp3dGJLMEh3ZDFBT2sxeHdOM3NDOUJHTEZmS1N1SWtVdFJzUVM5WXA0UDZTREZvRjNWNjRvWEFYUXFyRUdwYXF1bVE5d0pTT3J4WTBVclk3el93M1VkLU11dkJqWDYtUk9lSXlNTC1ySFpXN1Y2bWVsN05ISzEzRS02WDJXWmYtLTFTdXRkZXhqWGJxeHNMb1E5Vjdn0gHPAUFVX3lxTE1QYlJPWFlhSzFkUjBKaFlpOGgxNzJsVHhZY1d3ejY1aWxpV0hybTg5NUYwQUFBTFlZZFZjcnlhMjlGWDJXVzRlVlR2bkhCQnFmX19lQ2FOeGFTQ3Q5WXMwWWZCT3EtMzNGT0I5b3Z3ZkFMZDhPcUJWajRJVGRzX3NXZnB6XzBQOFJpT0ZWLTlFREIxWFh5a1YzODV5UzJMeklzT0VwcXZvSFVaWkJsTjVWUFR2RFR5ZEZRZXRRYm40elNKSGtZWnYyZkNaUV9PSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE5nRURWN3BhMjNJalZxSUVIc0V6bnM2c3RpTDhtSEFOZkJISGdxWmFqLVc2NnVIUEhzdC1vLWFUYlRwNEROT05XZHpXZ2ptWWctM0dBZHlfVjNHYloyVFh4bklWLVdaZ1ZvcGItaGNLXzNOSkdoR0E?oc=5</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1241,17 +1241,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Enjoy a perfect port in Porto with American’s new flights - Breaking Travel News</t>
+          <t>Eskom Can Raise $3.4 Billion From Tariffs After Regulator Error - Energy Connects</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Sat, 07 Feb 2026 11:05:33 GMT</t>
+          <t>Mon, 09 Feb 2026 04:57:10 GMT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQeFlmeTNpalYyZXlORGRyQi1RbUlRZXl6X1FENm5MbVhrd2tEY2g3UXJZVjdoRFlWQ3NTb0QxWUpLcGgyaVBOTVFWMnd0YXR6Y1hKRHdZQmQxQnJGc082d0dqalNxbGY0bmduRUV2Xy1aQThFbGVkQmt3SVhrTHJwSW5BYUlad0lWOWVvWjR1YWItU3BDai1IcS01dXZ2WVRwby12aWhPVnA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPS0VaTnVrV3p2VWZ3VmVvTzhlUWpfN3YxQ3JoS3BMbV9aU29KQ2o0OHl3Sk9XWWhQdGV0YVQySG14VG4zOEtrcHdzQ1dSeVpmSXI0cFFlTEc1ajZNdkI0MkFWYW5HanNWYXlraURleTQwNGpSTjJqQU1iOGtxay1MZURqZ3ZDeFRRb3Jqb25FY3RYNVRFTG9WVWI2WFJlbXAzNkFuY2JYZGJJcUdnZXJLN3BKUmZjLVNob3FXblcxVQ?oc=5</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>EXILES' BOSS CHRISTIAN FUCHS SAYS RESILIENCE THE KEY AS PORT SHUT OUT THE MARINERS TO GRAB A CRUCIAL POINT - Newport County</t>
+          <t>Poland divided over pharmacy ad rules, Commission urges compliance - Euractiv</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sat, 07 Feb 2026 10:04:19 GMT</t>
+          <t>Mon, 09 Feb 2026 02:55:20 GMT</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxObVotVjFLcEYyLTF3cWZMSHpITV9OYnExNk9RNEtKLWtNXzQxcTNURnRsZ2hhbE42ZXMyNDRBaU5wRGJQeXlPdWYxSFROdVplbVY3MzVEOV8tOU9JQU9vM0NmMkpaemdMbzNMamdzRHgtT0pFZGQ1X0NlQW1TaHJUOGxOUmNHNWxfYUJYRzJGS3ZSODc4OWNfdGJURFNMeU5EcnYtc0xTUU1WOVpZblUyMW0tQmg0Z3hFQ2JZU1lkWkFUY0Njd3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOX3JUVzlqbzJSME1VTFpJR1NfSHRsUjRYajBoY1hDSmlWTTF1RGs2by1GM2ZQeTVEN0pOeEc0SUJuSi1IRkJGQi14VE1KRVlsWGdoWXBYQ0pWSTMzclNzRTJVbWVnSTFpNUVUMS14cmhtNFFxbE5wdVVDdThQNG9WaWlPbHRZLUFHUzZlZThQcGs4V3pfSFAtSmF6bVk?oc=5</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Shipping containers 'recovered or believed to have sunk', says coastguard agency - SussexWorld</t>
+          <t>Twice the compliance. Same old agency fees. Does that add up? - Property Industry Eye</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sat, 07 Feb 2026 14:39:00 GMT</t>
+          <t>Mon, 09 Feb 2026 03:50:12 GMT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNWkNWb0ZBdnlQZHVCeVQtWURpMEhnWElSVDRoRE9MOGZhZHY5c0xtQ3dDclAtN2hIVnF2OXR4NnB2cWgtQzdBRjZXVEc0SGVXOHVlcE5kd3lmTDNsTzRPWmxOQ2ItelZUNGwzQ2VpTzQ4R2ZQaW5nRDZob09YRkFqS1dJWnBERlh2SDhJVWhDMUU3RWdRTHIweTFCcUdEMHNwMkh4U0U4UGZXckRoQzM3SF80QVRlakpTeFpJZTNXdzc3TTRULWYxTDdSNllFSGlTRU85TWpmc2w?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPVGJyaTZEMG1VWUd4UFJYNjRSVTNWWFJaSFluSXg0Y1N4Q3BYeHllal9CRUc5S2NxTm05UFdnVUFyaW5Ta0o1ZGNKN3hnQ2MwYnFsSGU3U0lZS2RobU5PRkpZdFFVdHRSMlZTYmpqbzBua1VUa2pVcHBNNW1UVm9vVnZaeGtiV0UyTWU5cFEwczdRWXpGZnc?oc=5</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1331,17 +1331,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Korean auto part exports to U.S. fall for first time in five years as Trump tariffs take hold - Korea JoongAng Daily</t>
+          <t>Canada builds playbook for surviving lasting auto tariffs, in case USMCA talks go south - Automotive News</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 05:56:01 GMT</t>
+          <t>Mon, 09 Feb 2026 04:26:00 GMT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_wFBVV95cUxPR3pEM3NvajdCelRPc19kY1U3MWszdkJyUjh6YTBtR3E1YXRBaVUyUl9kTGNmenR4UzBJT1lFUjZ6TWNrcnlOMkVoVkFQTTRxRmVfRklVVXAzTzRpckZIZ2tianh0N2FzMU9EWDM2V1ZxUWRqU0RyVGpldXRuV0xfaXp6RjlfbmJ6V0N2Z08wWmUyU29pRGlmcnRDQzhfcEFKX09xUTh5THF4QXBWOXdQd0t4c29HaFhEQU0yZzJVdmY1a0FESnkwTkxGQVRZMGw2VFEzS0pqYnpOTVdKYjM5Sm82WER2YkUzS0ZieVRqWURtbEFMWFJjS2c1TkZWME0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNQTVka1ZZalZMVWM3WlNKYkNSTjAzcFVZenFERTVfcFA1TENya3dzckIyQmRRaUU0aF9YWnFtc1hudlVROU5XMi1MdXR5VU9LYTBMQ1lBOHpUR1VfZ0doaXJMQnIzVUxrMVB2TUxOQVdJenB0TWRTT0VpdEotLVlmdmhKeWJiSGczQm5fUkhn?oc=5</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1351,27 +1351,27 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Minns invokes special powers for NSW police to restrict protests during Israeli president’s visit - The Guardian</t>
+          <t>Duo to celebrate their 40th birthday with charity skydive - Newark Advertiser</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 00:13:00 GMT</t>
+          <t>Mon, 09 Feb 2026 05:00:00 GMT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOTDZhdUwzZDFOQ2pVTkNtYXBfRUhtUlhleEhQa2dQeUotX2JKOUEyVUFKNk9QVzV5UTRPcDRpQnhFTlpaWklFRndPX1JQUE5YcHBhUXpPVXdwbU5XTkI5alNsQmpwSU5paG8xMjdrUGRBejFyeThVeWdhVi1WblRVY0h6WFMxOUxWVlBuTV9CQU80ejJvMS1RX0R5c1VMZDB6dUl4dGp5M01mbUwxS1l6QXJoWWtXem5YSVpHR2NLbW0wUS0yMm9rSFNR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOaWg2OHItdV9iSjJOTjdXZm1GXzhHeVR2c2pqVXQ4TDE5YTVaS3VfZW8yQjlEYTl6SEM5Rm11RmkzTFNKTE12eDE1YXZKajR1S2FaX2liRzZPSnJPVmJhbUl2RlFfOGs4YkQ5NHVEeVc2Q3lZZzdlNkNFWUVHTTlRa3hNMlo0NGxXMG83M2pMN2ZJVDFyRG1Cd3ZoNWhmNWZwZ0ZUd3VZa1htdw?oc=5</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1381,27 +1381,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Video. Italian police fire tear gas as protesters clash near Winter Olympics venue - Euronews.com</t>
+          <t>U.S. sanctions Iran-linked ‘shadow fleet’ as nuclear talks resume - Shipping Telegraph</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Sat, 07 Feb 2026 20:15:57 GMT</t>
+          <t>Mon, 09 Feb 2026 01:52:25 GMT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOYUZEQ2d6MkZuOTVEZVN4eE42YzBjbWhXb2prV2V3NnkzcXNDb042N2RqUGNxTlV1X0Vnc2FWWlV3RFZrd3V2SmpLb2xtd2o3aGJGTEVlNkpKNEJXLXVlaUpfNlN5NmtXTUduNENKVER4aklid3Y0Zmk1SEoxZEp0eE5ZRnp3UW12YXJqT3h3dVVnN0d1VWRTYXJTUEwzUW9PN1J4WWpuald4Uzc1bDRXckVHQXV2TjVR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQQUZWUWt5TC1kQTZsMWJsTFRNTC15XzBPQjY5VUphNE1VdmJJOG1MNjIwdUhsdTlwM1pvSFZhV1dCR1ZMaFJLT28zRWtwRnh2Xzh1QkF1WlNHcWVWdnhIbk1JYVppTUJZdDl3czMxa01sQWJ5UE9JdVFwY3doOTN2bUlFQXE5bEk2LWZwYmk3eVNUTWlJdjluN3VIYTlLZFkyNDJ1NG9mNEt3YmZJdnhhU2IzRHBBYkFK?oc=5</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1411,27 +1411,27 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Garah: Protest organisers Zamri Vinoth, Tamim Dahri remanded as police release 18 on bail - The Vibes</t>
+          <t>Fujian Guohang Ocean Shipping takes delivery of Ultramax bulker - Baird Maritime</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 01:27:00 GMT</t>
+          <t>Mon, 09 Feb 2026 02:21:08 GMT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOZmlFSUYzUGNycFo5MHRqNk10bkVhZDlvUGd6U3lreE1iS0syUGFFdV9qZjZydlB3a1RmcUlSd1p2eUhtOTNEMkJJdkJsM0xJMVVGRG80c0lhUnVxcDZFYkN2SVN1bnVEbm1uWE55dkdoajRnc1MtWUlrdlhxcjJiRDNOM0NYVjFtTmxBQjVydWNFaDNLTmU2M3VmdTdENWdVR2pXSy0tTW80TzNXSDBFT0ItX2tkeHhnck9HZVl3ODQwMklBa3d4MEpaeXg3TDROcE9Ya3hlOGIzMDZHYjFhYmNrRGlEOWUt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNM3ZQV3l5MUYxWVZMajhJdlk2dUNPWnJtQ2VJRHBPakpqc0F5SjVFNV9keGlGYjBWZVNUNGJKWDVsbF95VWduNEROV3JkWUIyWTg3MkV4QlY0SU0wSi1JRFBZY1plMnVkZVRFeHFSeDNhZzVPUnhWd3JUczRpT3RqZUtNZV9vOWxmdnpiMThtU0U3Ny01RmFKZHBLV09BQXdqbnVVbHJ6WHBTZWJ5cWs4dEV5ak9paVJ1UGljZNIBygFBVV95cUxPOVMtc3ROUXlJVmMzUEFjaE52M0lUR25lMDFEaTFDdm1iZGI1ZU02cEFwNVRkMnhYN0hGMXNsMFAyTGM4d1pGZnhoeGpHZ3VnWlZ6aVdNLUhPRkRIWEhlbHM3NEh6MnB4azJDTDRQSXlIYkZIcE9rS0FhS2JIRy1Bc2QxbWhKZGZ1TTZHbUZkRFpSbjV1T0NxTGM1OWpYSFlxTWZhVUtjV3BIb041RkZfUFVkalk3c0pmSDBIY21MZjk5RDNzUXdlakZR?oc=5</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1441,27 +1441,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Police arrest protesters at Minneapolis federal building on 1-month anniversary of woman's death - ABC News</t>
+          <t>The Logistics Lens: Chaos Versus Control - Breakbulk Events &amp; Media</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 01:34:25 GMT</t>
+          <t>Sun, 08 Feb 2026 15:15:10 GMT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNcUVvcXhYOW5TU3dTUXJlSVdnQTdXblNlZGd6VFFxOVpaLWxwbnJpQW5qdHdyM1Z1LVRfWEFhd2k2Y1F4dHgtTDNIX0h6QzJoV3lBeTA5UzJKcnhhdDlzNk1obUtWUkt0QmEteE82OEZjc3VQRm1lMG5EcmU0NjJMaElGV1FIRTVBcElQWnM4VTd1akFhRGVsblEyUndBcXFQWEtYZlU4Z19SY0XSAbABQVVfeXFMTm1KbjF1djVicXNsNEVNbWtvRzIxU3AxNWJCX2ZzTXZuWmZDN2xiN0ZIMml6QkJNMVV4am9QaWV6X1pkeWpXN3dvRlRpX2lOeXh4SGQ4bUN1a3hNNi1aTEluczZSZXFobWZRdjNzVXFzT2V6WTRKaVlPWFR0b2xyZVJXNURTSXJxY2x5bHVzV2QwUlptX1J0MTU4b1BKX3NnZWJjMEZaR3J4dEc5MDJ2Z0g?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE5LMkVhekRZSEFmZm9Fc3FCeG11ZnZabEotUHhMNjhINTZPZzhRdXRweHEwM0s5YUE2Rk9lb2FzT2w3WHZKSUoyU01ySzlaZXczdU1vQ2RlNHRhVVpNbWZXeWF2Ujl2R1M1X1N6TWpHTzNMYmVjYmdpM09B?oc=5</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1471,27 +1471,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Police Medal Awardee, Was To Retire In March: Cop Who Died At Surajkund Fair - NDTV</t>
+          <t>UC Data Residency and Compliance in Global Collaboration Strategies: Finding a Safe Home for Data - UC Today</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 04:52:16 GMT</t>
+          <t>Mon, 09 Feb 2026 05:29:16 GMT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQZ1E2dndueWRjZHQ3VWV3OFBsdXFVY2hmbnRLc0ZpM2NnUDRLVC1jd2x2TWx6QVZCeV94QXZscEdUUDhOWHhHZE9kRUhCVWFvWXV4OWx0X3ZhSlVTbVpEMUZhaDlPdVlwTk1SVlo2OFNvUWw1M0gyd1poOFdtUjk5ZkljMURPOC1CUW0xZHpjQ1hycHpYZXNuYkN2UGFDV0Q5WFAzcVY3NGtPeHhZckltT0tyVUVmbFNaVDY3eXlwbzh1WUMx0gHMAUFVX3lxTE1kdEo0Y0lEN0NHOE91QngzYXljS3lydmdNUXd5OThON2lNU3o4VGVQbHhvcHQzNE1DS2FNZk5LMFBOUzE4RU1zNXQwcDY2UjA0Y3Y2bWh3Ty01X2JQenFIYUw1UURzTEZCUDlPanpTLTMxTHA3Y3N1Yy1qYmplMWpTYkFJY2dVS2hvbDJQX2FZTXlhYTlTdVhFVW5Hdm5PUm11V0VaVThRN09LQkwtd0gxaXNBVEg2UExnX0xCSFZNUlItdTVKUFNwcU83bA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE5YYlJSSFV2Z19wVzFia0pFby1FVVYtUlpfSW40aGxyTG9RV19OSllHcm13SDBGckFZNEFqcUtLVHZOOU5wVEtTZTRWcC1iQXRjMERTNXIxS01ZQzZVUjhUbGx1cWhEa2lBeVBTcndtUnpOQUhoTnc?oc=5</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1501,27 +1501,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Police chief: Officer’s kick, baton strikes partly excessive in shopping center arrest - NL Times</t>
+          <t>Morocco • The kingdom now knows its fate on US customs tariffs - Africa Intelligence</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Sat, 07 Feb 2026 12:05:00 GMT</t>
+          <t>Mon, 09 Feb 2026 06:01:36 GMT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPUUlIT0hoYjBNQVd6eGZJWk9RbnQ5ZVdCNGV2UmtmY01TOTJ0VTduQ0V0OWxEcnRIc1BpTHgwZXZVYUt6UjQ0cnRKU3VLTlIxYXREV3QwSXNYSnVCM2EtRERNZzQ0R0lOSV9pLXNSQUtObkMtM1dPbWttQWhYSldUS2RmUnF1QnYwSkxjbFY2Z3UwT0dxWkZuNEhQWmpIUlhWMXQ3dEdJZUpYV2VZVDRz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQeGVWbmN3czZlY0Y0Zk1vUS1qMjZWdW1ZNGFlTUpBenJLd180V3hZOVBYSEUzVlJnQi1SUmIwWXV1blI2YktDaFBSblZKdUhOZ1dtOHJqT0E2ZlF1a2EzYzdPOXdnMDNmdkI2SFMzX0dkc0F4WndmY0RtdXp5Z0hHY3Vnd094SVdheGV0LVpCekN5UHJTMmdnS3AzNG9HZHZjNF81eTZhR0o3c0dzUWticmk1QnhtTUM3c05mdkxQeFFYQzg?oc=5</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1531,27 +1531,27 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Barclays cuts dozens of jobs in AI and offshoring drive - The Telegraph</t>
+          <t>Ukraine imposes sanctions on foreign suppliers of components for Russian missiles - Reuters</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 06:30:00 GMT</t>
+          <t>Sun, 08 Feb 2026 09:30:44 GMT</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPUXJIZEU2M29pVG5MNEVDY2dSWkN0dW9xUGhMQm81NlJoSWdrQnRsUDlYYXpiclJQYWRGa0k2LTdCaVdHUjcyRDRvWHMtTTJtM1RiMzJEdEZVTzUycUU1Tk40VUlUTDhsdVM2WHV6M2F6Y0dKWUpBQVlCbHFyNmlydjNsa3VybDQ5Q0F5LTQwSGxqWUhqejlQUW9SeVVvclhGdmtDUXdEZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQLVdvSzVaY3dpRHFvWjN5dWJjYkNRZ1dwNlBMbUtkd3VmYWE0MkUzNTVoTE9FNzFwbmhxWl9rQlhBaXRLV28yYWlXNVhOU3ZreXNkMlpvQ216ekp6OHI3T0lpNVNiR1RMZzBLR2tzT1BwRzU4dFZUbGhtaXItOURyS0pfdmRjUjNTN19sVjNHT25QQUJfRnRLYTl3ZVltLTNrdVNTSDFKRTFkc29XaTY2TnBLMnRNSVJTSVlwVGdMbUtiZkQ4UnhLeDVwY3Itckk?oc=5</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1561,27 +1561,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Technology and treatment in eye disease - Association of Optometrists (AOP)</t>
+          <t>Could Algeria Back Away From russian Weapons, Including Su-57, Under Pressure of U.S. Sanctions? - Defense Express</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 07:05:43 GMT</t>
+          <t>Mon, 09 Feb 2026 05:05:40 GMT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNdF93VDZ5TUdIN3JyTk9DNnhhU0Q0ZW9JcU1CTkdpcFo3MmJSdjNJTV90ZTk4NHhudkFULWtCUlF4Qzh1d3ZBWVpHTnc0WE9rbU1pMkhMT0FRNlBIUE84U2xVeEQxc1VyTjVvUmdzVkZGLTQyRWlnMkZmeVBIeVVWRllGRXJFMjJTaUtBX2t3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPTE5NaWhVVnJkcU04b2hCcVNLZUFEMVdaMHNUdUUxWDI0bHpTYW01ZUZuTy1MRGd2V1lCRmZzeDQtV0dpU3I5NXRHSEd2bS1mVTJaZzl2WnNuTl9rdWlaRjBpY2RwalBLWGdKQ3Jaakx4aWc5TWNqampkUEVrY2FSSTNKSzYxYWljeVhkQnVILVAtSXhyYkhxeFVLQzRZcHo3QVNKZzlLQ2Jfa0k1V3Q2ZnhWUUFxM1dmaUpfVUY1dnJoOC13dXFEM1hyUGdSQQ?oc=5</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -1591,27 +1591,27 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AI could boost Jersey economy with right funding, expert says - BBC</t>
+          <t>Saudi Ports Authority seeks Suez Canal partnership for Jeddah port development - Dailynewsegypt</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Sat, 07 Feb 2026 11:53:05 GMT</t>
+          <t>Sun, 08 Feb 2026 18:35:20 GMT</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE82cGUtS3ZHQUtJVjZMb3R2ZVVZUHB1cGVzWUcwa0JlNHpYZ3U1SWc2ckZOX0hCcDJQX25Oa1lfZGltVFk1d2lvN3VUUXk4Tzdyd2g0ckJEZXdYUdIBX0FVX3lxTE1HTnJ5NGR1TVp1Y29IN2pwalNadUd3NFZkVkZaTG00VFppTE1pV29qSkR1Q0RMSEZYRlo5WlNfcno2UC05eW8yWE9JUENvVzFETG4ycG96N3ZlNC1TRFI4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxONlo0eEw1WnVJRHp2b1NQdXhlR2Vkd2FkOG5DQnFYd3RKVnZfY3pQUlVOOUM5dEcydzZBWWhyUXdOQVVVdmNHS21sdGg2c3gxdW05eldMdlFWNDk5MldKVUMwQ04zcDNRQ3ZhWjc5TEtna3BHRWowaWdDQ3VLQ2lzMF9sMGJSNVZLUUdJcGtYZ1hjanlWODczQWpaNHlfSElDeUdyTGZOYnN2Rm4tOERjcDJHUkI5Z2dRWW1ZM3VR?oc=5</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1621,27 +1621,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dan Ives Says Software Selloff Is Worst He's Seen In 25 Years As Microsoft, Salesforce Face Brutal AI Reckoning - Yahoo Finance UK</t>
+          <t>Namibia will not recognise TotalEnergies and Petrobras due to non-compliance with procedure - Offshore Engineer Magazine</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 00:31:00 GMT</t>
+          <t>Sun, 08 Feb 2026 22:58:14 GMT</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxORThiaDlTOXlGeVpiUXV4ZjE5Mk9POVA2YlI3YUtRVDU5czBEUlE1Y2llZnNvcjJ6Z1dMdUpmQldNMlVUdWFVYkk5Y09DTWNabThwOG80SFZUQjBUNFROSnNsdXFSbHpvNDJPd0phUmo2OTBSd1lmMWRhbk9NeDBOaFBIeXF2UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxORmRlTC0zSlYzcFVwNmwwVUFZblRCM0NOU2hSRXh4NWdRRDJHT1NZVGxzMEtMaTlHUVNER0dwM3dpLU8ydE9fYk1GeDl0ZWFRa3V1Z0JMNGs3SDFaSmJ6TnFYNHBNZUtkVGZ5dWY5aExYZG5RMEZVUHZFU2tjRjhYVmtmSmRwcVBfUURHbWRoVWpPbnJUbnZXWjhqYzVBRTlqQkpETnNWNXBPTUNwMDNyMW9vN25QZWtlSVdCOWdYVEVZU24xd1RJUQ?oc=5</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1651,27 +1651,27 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sage chief: 'Ridiculous' to claim AI bots would destroy our business - This is Money</t>
+          <t>Assembly to debate motion on tougher sanctions for ministers who breach code - The Irish News</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Sat, 07 Feb 2026 21:50:22 GMT</t>
+          <t>Sun, 08 Feb 2026 15:46:27 GMT</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNU3VUZi1XZF80a3V4TmlxYk5tTzNwMVl4Smlob0l0Vlh4X3FPSXY4NlNGS29GYktiNWRhbWV5SEZBNGpXR2dnOEtCZnB4dDQ0Y1hxT2thZzBrN1hfMDBsYXZka3BoRTJTci1VZzBkV3VCWm5xRjNqR2RMWnp3VW12aWpwSjR5Nkx5YW5IOUEtS2FuS0Q0Um9UT2haZDJDX1JhYVI1QzBfUnhWMHFlUVFhWDJNZDlPbFg3RnfSAb8BQVVfeXFMUG5XY1BoeEc3UFRIeUt4ZUxyMnRla3gxZzdqM2dVb1VXalFjUVpya3FRTmdJSlhLaU9mY0FBYkx0ejUtdGF4M1lIdVRwalZxNHE3YmRHbVJ5Z1hkRXBLMjJvYnZCY1dCQjRkcVBFVmVJbFV6bEJlUW5XYWwyX1gzWDkyMU9DNVdkWnV1aXZhTHFjaVgyckxhMnF6T2lUaEVNMW1BN2NPVHp2cVdPRXNGZ2dvcXRwWnowTjVkekQxRWM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxPcXlKSnBvZDkxb1RENXZCUW1xM2RFcUhvWFhVSjROM2ZXTXZCTUR1VjBpX2Mwekc0d1U0TTRSenN1Q3FBU1Zpb0lPUmtPS1B3OTZqTW52NENJWU9NS0djWmNEd1d6MmpyazhBZWRDb3FfdTdpUGJYMTdZa2R6X2U5Q1hBYXZLcHh2MTNFYlE2VFRCVGoxOE4tMERCSUhPVlN3RTdKdnN3QTRQdVNtWEZBUTdyQXlUWmo3UWlRcFlUTUlidjJKaXIzYUF2X0pGQmJYSUtTUDN6VDBHU3FxcVI0RWRqNm5HQWVQR2hKdVZR?oc=5</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1681,27 +1681,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Water Implications of AI-Driven Digital Infrastructure Expansion - TRENDS Research &amp; Advisory</t>
+          <t>Italian police arrest protesters after clash in Olympic host city Milan - BBC</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 06:00:54 GMT</t>
+          <t>Sun, 08 Feb 2026 13:02:35 GMT</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNQTh0UGNTbHp5YVl6ZFFWWlY2SnBFdko1RUlRWkJiZFZsRXNTMmI0bWtKaG9GNkdQX0NGUTFmc0l0VkhQR2FIc3VxVWp0S2c5amd0Z1VabVlGSEkwT0paUGxiXy1BQkpKWHFhdHRhclA2Nk5TU0xmQVpoVlo2c0VkXzRSd1JUbmxZTGZfSTJqMFlaRkh1eWVicWRyZEllYVp6aWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5yUTg3VmVQckk2WTF5N2d1VllTWUVpMnVvWVdQME1mRHdMYnpoNnRhQ0JPLUVVdDluNjc5WUhYcWRReldXYXBrSWJOZVlfVTdYWU5mQnhRam9OQQ?oc=5</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1711,27 +1711,27 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>When the Diaphragm Deceives: Subpulmonic Effusion Flagged by AI and Confirmed by Ultrasound - Cureus</t>
+          <t>Pro-Palestine group loses legal challenge against sweeping NSW police powers for Isaac Herzog’s visit - The Guardian</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Sat, 07 Feb 2026 15:37:43 GMT</t>
+          <t>Mon, 09 Feb 2026 04:52:00 GMT</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQSVdKTVhwWFA3MDRjd0JMbFg5WTZqMS1mb2tVVS1FaE5qZy1fWmNwQTJhMXJFZURvNG9iVnlCdE5VZmZnTUZLaWtPam8tdmg5U21ucTVnZlYwaHhSazc3UDFoQ3liTFUzZjV4aWk1V0k3QWFJNGpHM2JTdzFfSFBqMEFzU1J0WTRoZlhrTjRKV0w1NnJRSFkySm9IVXNFRktJN0FodW5OYTRsOWZhRnlvd3NXNEZ1TUpGOEdsMnVKVVR5T2QyY3M3UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPYTJrZF85VTg2Z0xPbmFlZ2NYVEJhaDktcnRXV2l5a0VpNU1acnRFOVZScDhvZjRFVWQ0S0pIZWNyeHhrTjE4SmlwRTMtMkVTUDJMaEtIS2N3bEJhZk9yQ1kzQ095M2ZRaVNxZi02bEtIYUxvN1BJc1hnZm55VDNyaU1famFvaVhIbS1sdVcwNm1PeldQNFI0QWNXbk5LdXRZd09KWlplUzlhSkJwbjJfNC1HakExSWla?oc=5</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1741,27 +1741,27 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Could CrowdStrike’s (CRWD) Aramco Pact Redefine Its Role In National‑Scale Cybersecurity Architectures? - Yahoo Finance Singapore</t>
+          <t>Italian police fired tear gas and a water cannon at dozens of protesters who threw firecrackers and tried to access a highway near a Winter Olympics venue on Saturday. The brief confrontation came at the end of a peaceful march by thousands against the envi - Facebook</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 00:17:00 GMT</t>
+          <t>Sun, 08 Feb 2026 08:56:21 GMT</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOLTg0TUVSa2p6Z3hlNlVkZGRZN254ZTVYd0xYOU1ONk5xWFh1TTE3eGNVSUhIYTZpalF2SUttYmdBeFdhMnN3cVduUW1mT0g5X0ljTzV5NE1tNWF5QmRSand3ZUIwLUQ4SEtyb0dvd2RaMHVCUXNKQ0w2RkVTclFkQ3JRcDZ5YThXUlI0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxNVmF3LTc4SHh5bktseUE3bTc3U0VLUE1pWkxMbndWeUNYVGR0ZzEwdlRDdkhwaGItU3dHdlduaDFOMW1tU3lzMDVxV3g2LWhubjVaajlVRDRRVVBacmxKLV9EOUJQNm1GTmNjYkRRN0xlVkxhWEM0NjQzXzhwai1oVG55bnZvSE12ZU1uQmlGQ2szUGZHUXVOdzItbGJTQjJhU2lWem52UWdTSlI2WEtfbkZ0azMyZjZ1OS02UUl1R0dwMjZuR1YtT3d6TTdiMkdVTk9pSHdsQ2FZN3NycVBn?oc=5</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1771,27 +1771,27 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tanja Obradovic Shares Insights on AI and Drug Development for HopeAI - Oncodaily</t>
+          <t>VIDEO: Heavy police presence at Sydney Town Hall as protesters gather - Australian Broadcasting Corporation</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Sat, 07 Feb 2026 17:32:04 GMT</t>
+          <t>Mon, 09 Feb 2026 07:02:48 GMT</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE85WS1veFBvaVBUMGw4LVRhalNkVkJ3Rnd1NU5TbVQyLUtFYTFDYTJPZlRBa1NuRi1JOUtpUFBxbjJpSm1aSFVKRnl1NFQxTG9FR3EzNF9naEtYY2xMOEg0Zg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOOG5WNHNqdWFOS010WlgtVUhxVm16YVBwb1VxVzhBMmMwcFJ4LTdlUVFIX0pXcjFKdU1aU3FzTm9mdHYyUFNjRC0tVlNodF9ubi1hREVkYXdfWGllM1lfd3hiNTJsZWlmYjFEREFZeE1YUG5ZSS0weDNBaHdwZmsyOXFtN3VkMHlzXzlvdUJ4M1lqRXRyX3FINjU4ZEZaaEhYdkluLU5SRER6bWEzRDZVWg?oc=5</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1811,17 +1811,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Assessing Atlassian (TEAM) Valuation After First $1 Billion Cloud Quarter And Strong AI Momentum - Yahoo Finance UK</t>
+          <t>Students deliver AI, automation and digital tools to factory floors - The Manufacturer</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Sat, 07 Feb 2026 08:07:34 GMT</t>
+          <t>Mon, 09 Feb 2026 06:36:11 GMT</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOOTdhM0c4amRMZDBZR2dQdWlRTldVWlUtXzcyZHl4RVNLOVF2SkNnMzZDc2xhVjRKdFU5RFE5VDlwMXhHSE8waW5KSURCcE9Ea1F6dUZjRXRscnFSaHNGdHhocUVZcDI2WHNjc0NadElxNVgwZzVlekl0aFdGaXBCZW5yYnJodVRoS29Wbi1CS2VCbFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOdnpkYlhIRHZSeEdwOEtnYzFYSHJUcVp0b3RHOXg0MXhSQ3Nhb0FYNUpNLW51OVRtcU50TzB2aEpFQWtUZGQzaS1rZnVCU3phWmhEdW82YWlya2hSaWNycUtlZTZ4Z1pLVmlnaFJ4azZaTWhlVTZFak56azNwaHZzY2JaR2l6clBsNFZEY2c3ZWRNYzc3eGpvZ3NZR0dVcl95ZE5EZ1o0aHdaTTlE?oc=5</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -1841,17 +1841,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>After Merging xAI and SpaceX, Elon Musk Hopes He Can Win Over Wall Street - The New York Times</t>
+          <t>What does authentic assessment mean in the context of AI? - Wonkhe</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 01:27:03 GMT</t>
+          <t>Mon, 09 Feb 2026 00:27:53 GMT</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE1MOVcwSmRCUlN1QXFrYjhjY1FNcXpBUmxBdXVUMUtqSUpocjNNTlF3RzcxMWhlN2VpLUNrNUlKcjVnYUZkcHlzWE52Tm9DbE5NY3F0cU1YN1RTUVgtaGhVZ19WUWNXazQ4dzBIUWZnaGduSVNHdlFIX1ZtQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOYUt4b2gzeWxKdksyNXo2OWp1MHcwX2pUWVFvUkZ3bW8zR3ViN3lYb1ZZUHRRdGJQNTZENWwwWHNFT0VMVW1nWm44aUdYeVREd2ZhdVRZdkNyT01nLWVZZ2I1dFJoa1doTFNkV2VjWWR6amtPQ05jWXh4aEhEbXZnbEVCTjJwVVhyNUE?oc=5</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -1861,27 +1861,27 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Warning To Under-18s Over Social Media 'Jobs' Scam - West Yorkshire Police</t>
+          <t>Sovereign‑ready cloud and AI innovation set to scale for European enterprises with Capgemini solutions on the AWS Sovereign Cloud - capgemini.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Sat, 07 Feb 2026 11:08:44 GMT</t>
+          <t>Mon, 09 Feb 2026 07:32:05 GMT</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQTHhVUEg2NUt1alJ3azBXbTN3dFNaZzk3YXIwM05PVENXZ2J6THByWHlwR2lybEJWblQ1VHJTRld5eWROQXdueE83SGVzUl9oTjVjUlJwYmt5YlRLa2lkZW42clJWSnVSZGtJdFYyMWc0d29tZXhUQUNVR2tiU2FVNy1kOG1NeksyRjlZd0JIOGJzbzYtc0VDQUFn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxObHljSDlRSjVGVVhBZFZhdU01RXBNdHlwVmwxSGZsN2VjWjl0LVktMDZiNUp6NU9IVjRwU2dRWlNiUFE3LUNZbVpyV1VSeFhIU250cEFXRnAzY2djZlNqRHdYS0h6cFU0SDBlWmY0elZhalRoWThaUDhBMl9xZGgzQ0VPQzJMSkVya2g5LWxSb3JENDY4ZVhPSGlfTUtNa0phcng2SEJOekRMLUZGR1ZabXh2YlBqamhkMDYwM0lpbXpBbzVsVDdTek52clBtS0ZlMTZMWDJ2bmVVdG5OYi1mcWJlSTd1LUN4Tnk4MEtoYnVRNUNzXy1HSkZNSER5UXA4Z0RTRkpn?oc=5</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -1891,30 +1891,840 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Software Leads AI-Driven Tech Rout—What Next? - nb.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Mon, 09 Feb 2026 01:22:02 GMT</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQZDBaUUlHdWlsYjMteGlIVUJhUWlYdlB2dHlOaWNZMWhoRlJoRmtSR0xaMnpueVoxcHkwZG85cHJyRHpDdkdlMFVGRUFtSmdudG85SmFtLXJ4eFNkUFlRRUxKRUQ4VmRjdHFJVXpXakpzbEdoQkpJRlpEd2QydXFNY3hNenJkR3MyVk1iLXdkRzMySmNHMXAwdWpvY2d6ZXJXdnFwQmxmMjVENjF5WHZZOURpNA?oc=5</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>In Q1, marketers pivot to spending backed by AI and measurement - Digiday</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Mon, 09 Feb 2026 05:01:53 GMT</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNQW90SENldlZTTUxkdEwzaDhHZXpMTkJEemFWaVc3S0FuNXdVTXdUNHdMbHZEaWJ1MkVRaHMzNksxQkgzbEZ2M3NRdmZGQkNPQ2lEYnFWSTRWTUJrdzBQV01uZkxQdkpLcUlRczhKSTFtdExRXzlHQnNleEZraTZUbjBPVVZIZW9KdGJFZC1fM1ZhbFN3WXN4LQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>From AI investment to GDP growth: An ecosystem view - CEPR</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Mon, 09 Feb 2026 00:05:04 GMT</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE1EUmJyajFkQUV0REF0R01UeFVaQnpiaGp0SVR0N0JkQTBjX2NXWmtpTXJkclhYdzZRR1pOMWRSNml4R1Zabi1FcTlQVFgzV3VQMjRLNmdyMmNlVmw4bXBMSm9NRTBHVDlJZGRCV3N4T3doeUkwRnFtaUJ3?oc=5</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Boomi hits 30,000 customers as AI integration surges - IT Brief UK</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Sun, 08 Feb 2026 21:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQSy1qeHo4VE9veEtHbURwVG9Edy1YdU1nTS1WcnhXb0hzeVFqZ1c2RlhTQ1Q1aTRkVDlvc2h1U2RLQzBWOW5EVmo5R2NjcTdTenJEUWg3Q0doUVpRYnZRUXdZVjBtQVFyZ1BPc2VMczNTUWNwVlZkX0pETFgzUkh5MlREdldXUVU?oc=5</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Private credit worries resurface in $3 trillion market as AI pressures software firms - CNBC</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Mon, 09 Feb 2026 04:41:00 GMT</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxOMnpYdGtaTlNFSGNpS2dQRGwwNERxTks5SE9YeFo4cTlnTHJvaUo2LVdvdGhqTWZ5MHJ2RUdIcV9vTWQxVzBEUThEZkZZXzk0dlY4V2R4TkIxRThnZUp6ZlA0ZVplUjZXNzJaaXg1aDNULVR6dEFkZ2hEUTFBb0hQWnV1QXBaUDTSAYwBQVVfeXFMTm9oQml3Z3c1QzJ1aXpEWlRHNzZQd2k4WXIwc0IyR1BGazFqRFZOYWFwZHJVcTRRMW9FX3hTTmtYejVhc29WdldkVGdrV2FXdjZoVzdOSWN5NXVOTEZaZTRZZVdkS0FyYThCNFpyWGZQeWpSVzdWeU11cWZncFRtWGJrdGs0ZjZJV1lPd18?oc=5</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Sage chief: 'Ridiculous' to claim AI bots would destroy our business - This is Money</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Sun, 08 Feb 2026 11:59:47 GMT</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNU3VUZi1XZF80a3V4TmlxYk5tTzNwMVl4Smlob0l0Vlh4X3FPSXY4NlNGS29GYktiNWRhbWV5SEZBNGpXR2dnOEtCZnB4dDQ0Y1hxT2thZzBrN1hfMDBsYXZka3BoRTJTci1VZzBkV3VCWm5xRjNqR2RMWnp3VW12aWpwSjR5Nkx5YW5IOUEtS2FuS0Q0Um9UT2haZDJDX1JhYVI1QzBfUnhWMHFlUVFhWDJNZDlPbFg3RnfSAb8BQVVfeXFMUG5XY1BoeEc3UFRIeUt4ZUxyMnRla3gxZzdqM2dVb1VXalFjUVpya3FRTmdJSlhLaU9mY0FBYkx0ejUtdGF4M1lIdVRwalZxNHE3YmRHbVJ5Z1hkRXBLMjJvYnZCY1dCQjRkcVBFVmVJbFV6bEJlUW5XYWwyX1gzWDkyMU9DNVdkWnV1aXZhTHFjaVgyckxhMnF6T2lUaEVNMW1BN2NPVHp2cVdPRXNGZ2dvcXRwWnowTjVkekQxRWM?oc=5</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>"How To AI" author Mims makes AI approachable for business leaders - SmartBrief</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Mon, 09 Feb 2026 06:33:46 GMT</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQbWVHRERiSHZLa2xELWxFRkFVaExWZEx4WVJidExPb284NndZYmJfaE9OSkh0U2pEY2kzcnVEQWt3T2g3aDk2T0dua1d3Sk5QbU1CamdOSUI0MVREdTdod1RITE5WNVVyTDZqOUI2aDZBaWVHU2R0LUlSS3N5ZXI3R0NUWmVTRmF2WjRRazZDX0p0M25vUzYyVXMyRm1fdHN6Tnc?oc=5</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>AI and energy: Behind the headlines at Davos 2026 - Mitsubishi Heavy Industries, Ltd.</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Sun, 08 Feb 2026 12:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE9FQ09UeVJzRXlzZlN2NW4waTA0T01QUWllVTFBanNiXzg4OFpQbUdvdFlBQUxXbEVmb2twU29haWt3SU9Da2lhQlowbDF0cjFTdktWanpFZEFCOGowc3BqQkM1SlNCSUFQYm9JOHVZTXJRQ21zRzVJeHUxMFI?oc=5</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Andrew Bailey: AI training is critical to future of UK job market - The Times</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Sun, 08 Feb 2026 14:52:31 GMT</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1ANBVV95cUxOTWU1bEViZmN3SDlaaVZkd25BcmJrempHcjJ2U0VNOGdaa1VoYTJOS0E3Vm9wOFJrbUthc2h3eTh2UWNQMVZfeHlnejdESFZmazZPamp4aWJQY3EtbXE3T0F2ei1zc0JqQTlISzlCMkhTRzNxWEh0ZUxtTHdyc3pzRmRaaXpNVEhkYVc2THNRWGI5VDdhb1VZeXJ4MDdKT3BsYmVvVVgwc1JSUVFneHlkdFRldlZRczNZTTBZaHFyX0RfNkZ1Xzk2QjA0bl9wTkVUSmd2NjhnbTd2VkEtSE5KZ1hrbVBSMDFyNnc0ZmlVUUVDUVQ3eGtwZUFxVUZNSGxlM1dSTjlobVBfbzFBeEVtUWxNRmJKdnpqUnhxQXNNM2RLcloxTzRBS3prTjZnVEFQUTBMdzNjQVRUZ3hyNjc3c3U4MDJWemhzSHpGOUF6WENxOUVhQVlnWHY0cUgwelRIZzRxU2RhdFQyXzFZVHp4M25uRzUteEpnNnY5c1dRTnpleTVUUTVza1JaVEVBWllDMl9tQWJQV1pNOGs1b3dXN0NnWFRWN0lWMHlucjJmSFNOdmZGcmozSXRYSUQtQ29OQ1QzbUxoVXpkRXB6S0hTLXRSWlk?oc=5</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>CompTIA and SGInnovate partner to bridge AI and cybersecurity talent gap in Singapore - PR Newswire</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Mon, 09 Feb 2026 03:05:00 GMT</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQUjYzZS16UEM3NlFFZWR5Y2VmQUQzWXZfclNzYWgxTFVwT2R0ZlVvbi04UlJzQjByM3ZkclZxcG1CdlNLWEhqdkJ6cDBUVEswNG5vZGl5Z3p1YWNOQjBGTkgzTGYwOGxCaVFOUmRwcjg0ZlhwbDFQRlhhVXNXdVc2NmViVE52Q3NsUVl1OXVfSTFmekdUQzZKU2k1R3dFeFczR21paEw3SkllMHVTWmJPWmRIT3VEeDRzYy1NVWRTZzYxNFNtWV8zQnctNnRJeEY4aER6Tll0dGM?oc=5</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>‘Major upgrade’ to Met Office system could help avoid flight delays - AOL.co.uk</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Mon, 09 Feb 2026 00:01:00 GMT</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxQRllWZXpObHlHb0t3ZWVjR3pTb0Z5VjZ6NERORjVuM25NbUNmVEZabUpXTHNaYXUtRFo0amRaa3g1UEFha1NMYXNrMnkxbWZGSm84eHFGd2RiYlBTbE0tLVJSUldzQnE5OTNCTktBNkV2Zlh2WXNLRUlkVS10enpGOHd5aw?oc=5</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Asia/Pacific CIO Agenda 2026: Five Predictions Defining the Shift to Agentic AI - International Data Corporation</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Mon, 09 Feb 2026 01:32:18 GMT</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQc25lUDdGME5BcXhGbkZ3bUwwWDUzUDdGODZKU3pjYWxqY2xCOGZ6bHBWamVCV0p2SzN2WEVyeWRMR0ZnYjFiOXJIdENvOEhlamhEbkt6V0hrTGJ5dFNlQkJsb3gwNHg5MU9PMmlmZWZyZXdrejQ1NzdwMThENGczcVRfS01FUlpETFZPbHdjN3k4Vkk3bHhEOQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ILO chief urges ‘human‑centred’ approach to AI and tech disruption - HRD America</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Mon, 09 Feb 2026 04:54:17 GMT</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPM2NzamQ0ZTBwZnI3Yl9tUVNrSjB1SG5qZ1F3RkI2dFU1eG1vbWo0SXY1NXo2cHNKaGNxNWxPbHlkUFhoVFlYYURxb1JRYnJWSlhBejIxVTVKckNRRlc0WUl2VmYyYm1qbEFRd1pSelpTcWpOTnJVVDZoSTVObnFQSllGWXJDZ2xaT21DR3VNamZhcHp4bXVvSTd4VkhZSEQxcERWbkRjTnk5T0M0YlE?oc=5</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Arm’s Record Q3 Puts AI And Data Center Shift In Focus - Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Sun, 08 Feb 2026 17:07:53 GMT</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE5QTUZtQjA1UUhVazVRNWxWQkM3dWFxeGRFS29OX3NvTUEzSmJqeWd1cTV3ZXA2aW5OVDNjSVFQUENQYXdfRTBpMFBmcDU5eGVhWjNVRmhmaEZQQXZucExrYl9ZbmZZczNsMVdDNG1ETTFUaDNZb0E?oc=5</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>STMicroelectronics expands strategic engagement with Amazon Web Services to enable new high performance compute infrastructure for cloud and AI data centers - Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Mon, 09 Feb 2026 06:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOVlJ1VXZBakdYWF92c0oxZXNpLUYwMDkzZXpZelBuNVpfM29ta3JzZnNjU1F5UDdSZE9td2Fqc3lOSEota2cyN1lzdThySGlzMklrUWR0UjNyRlRCelU0V0lUWUFCV1NSSV9vN1lDOEY0TVdER1ZoNnozWldjcmg4Sy1RcEUxS3kwREhLYkhCa2pMSkJ6WnNnZ1ZVc2drYk5RZUE?oc=5</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Apple Prepares to Kick Off 2026 With the iPhone 17e, New iPads and Macs - bloomberg.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Mon, 09 Feb 2026 05:10:30 GMT</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxQV0VaSUViVTlCVzBLbTAyMHZCaVVqbjYwOXRSYXhDSElBRUprMnFac0dvUWpDUXFZZ29LQVZFaE1ZeS1lR2xwYXljdS1oUEFDNkp4QjBSTVdRcWU0ZXlocjJCSVJCcHlrc2FLdEVDZnRhTVhBTHpzdm1sYlZ6NTFNLWViVjg4eGYwazhDWmZ5V05jcUV0akJGQWFuSUI3MkxPQnpPMDBSSU1RZ1FzQ1ZXRGZWcEU4UXZMZUhHUEY3ZG50WWhmMGhTWC1YRTJNWGdRWE1fcg?oc=5</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Chinese chip designer Montage Technology soars over 50% in Hong Kong debut - CNBC</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Mon, 09 Feb 2026 02:53:00 GMT</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPdVFNUDVPVGF3Ul8za0hZTUtvaWhRQjVLOXpfYzQ3VzVVazhPNEJpMGNFRWNSaExWaWd2OGZVWnlXeEZDTFJpQ0VXWGowU2ZuUEZLamVNcl93YkRmckU2U2ZxN255MzZaLUpETEw2RUcxZ2NOdzJQZ1JnWEl0Sm9BcHU3QTVXb0ZyR2p0T3ZfZFBDTjktdWZoQtIBngFBVV95cUxOTmVqSF9zWUplVnZrTlFpeHZtX2szSFBpY1g0TDc5a0dFaklWSjVVbndod290eHFSOHdhM3l4dFJ4UTNsWmlPSGU2ZHlmcjM4aWZEenRrZDUwS3AwNGhJckdsdDRGUVpsRGd6NWRqa2gtbDF3VFJMeE14anFXM2o3V3pqd2xiZm80Wmg2UEFtSk9UMFhRMF91LUhwa0RDdw?oc=5</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Alibaba’s ‘Wonder on Ice’ brings interactive AI showcase to Milano Cortina 2026 - Milano Cortina 2026</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Sun, 08 Feb 2026 10:48:48 GMT</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQMG9UNnZkSTZpRnJJSzd0SXdmNXdqeHZCUjhpUEZIdE1abndGaV80dDM0czRfWlc2dkdLamhJTWxqcjZaRU1DZ0p3SkQ3UWJ4X0VQeHA3T3hPTTNVOE44OVBqWS1aNE91ZXFCaXNhajU4M3l1Zkw3VkJ6OWhEaTVvUUI1b0RTaW9qZE42YTQ1dTc2UHRGYnRRWlZmZjl4SmI3bG9uMVNjYTRBUXc?oc=5</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>WISeKey's WISe.Art and GMA Once Again Revolutionize the Future of Art and Technology in an Extraordinary Event in Venice - Investing News Network</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Mon, 09 Feb 2026 06:48:51 GMT</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPQmxMbWhMaFZrVXpaU2hzWlBsbHRsVHU2VjYzOHNOS3hiT2VaVGJkd2hDZHBscE9MQnpFbzNwNjRHa0NFYThGQzVCQ0hLRUZKNndpVGZuZ2JSODFVQ0ZQaXZDNk5OVTVGRkVnNmlub3ZLdUtEUEd6T040R0NNUGNYblpEa0tCTEFaSkVqb2w3SXhkZzJVdWM4V2s4a1p1RlFmeGl0RUxKd1BzdEszRzlSVEJmcER5c1lJakZkcXFnZURhWGVLVzl6NXVLc0d4MWs5UlJtekJiYnpqYXM2UDZTVQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Worried AI means you won’t get a job when you graduate? Here’s what the research says - The Conversation</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Sun, 08 Feb 2026 19:16:45 GMT</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQWkFUbWo5bF9XaVBOdmE1S05KUzlQTnAzT3lCQXZfQzFvcy1oNUliVTF6UV9LUU5rX3lZT24tVDlERTFxMzEzbzd2V0NXc2JkZXkzVnp3clZSQnhibXhTVkNOMjQ3TVJORjdSVy1TLW4tdmxac21tb0hjSW13VmJMRHZtRE04YmItWXpXRldhYVRHcFN2ZUZUMFBzTDBaV29OdnRyR0JWRTVnQU9hV05hQlhHcDBNZWhf?oc=5</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>European tech strategy advances with Germany’s new AI factory - Digital Watch Observatory</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Sun, 08 Feb 2026 12:05:36 GMT</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE4yenZzTkg4QVNGc0ZBUXlYZTczWHdNMDZRRzlFdm5hTVo3RFdDc1IwVzdadzd4RnZ2VkVlOEZvN2I0Tjl0Wmo2ZjE2ZzVkVG0xMGFJUWJUWkUxbWlQN0p1VlJNQU9tNm4t?oc=5</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Pony.ai and Toyota Advance Robotaxi Commercialization with Mass-Produced bZ4X Robotaxis - Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Mon, 09 Feb 2026 05:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxONWk3Rm5kS1lDYWJabGh6Y2RhVEtoS1ZpRkhHUkhjM0ZucE1LaGc3MVFZNmhMZG11SG5TRDVtelh3ZDR1RFROVDZqb0tEclhTZ1FQOE9rVTlvcXA0MVZzNHJEcjd1dXc2UGNoUnRweUE2eGc4NU9fODJsUE5yOENNNGlfOA?oc=5</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Quantum Teleportation Was Performed Over The Internet For The First Time - ScienceAlert</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Sun, 08 Feb 2026 22:20:53 GMT</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNTFJxWTl1M1FGeEtCenQtU1BpSExHMXRCdjZaSXcySHdNS0NuVm5POG9XS1Y5dy1RNU9LRUcxZ1I2YUlucFI3WENEcFY4Q21WQ05lUENmVndfWll3T2RXZGRGSFUzOUlCM3RBazF4OVRBUG5XT3ZPMUNQVjIxdjRiZ0ZzYmdXSGhnMlk0UVlRNldUejdkd3lxbmJKam56VFJ6YlRF?oc=5</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>Fraud_Scam</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Phishing and Social Engineering Still the Main Gaps of Digital Crimes - VOI.id</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Sun, 08 Feb 2026 07:11:16 GMT</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiS0FVX3lxTE1jNHF3elRwdlRNZTduWXE2dDB4R3VLR05XQWh0RC1POFVLbXIyY19ZYTlQOEFseWZxUkh5WG1XUkxFQWR1djBhMDd0b9IBQkFVX3lxTE1pbWRoMjc5MkZ4WDMyQkxYY24wblhOZDMwTzRBTkZRRUdWU1JEYlo2Z2lJNUVHWHNSeDVmbmt4UXM3UQ?oc=5</t>
-        </is>
-      </c>
-      <c r="F50" t="n">
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Social platforms made €32m from scam ads on Irish users - RTE.ie</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Mon, 09 Feb 2026 07:00:20 GMT</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTFBoSWFOSC1STGRRb3NjUUMtZkQ1ck5zeFhIdmtJaV96azFnbDNPdVoyZHhRMjIwU29HblM5cjM2cDlUemx6UUVvc3o2UWQtdnpHMG9KOXAyaDEzVjM2Vk1DOWtERGNCVVhDREJZRWpPWnlWTUdTb2c?oc=5</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Student shares experience as social media scam victim at Internet Safety Day - The Vibes</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Sun, 08 Feb 2026 09:24:00 GMT</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNUWVBSU5WQWktc29LY0wxbFNZd0wyV3dWV1VWRm5NTlZYVDRfWTRJR2ZwRm51TlN0aFplSWxHVWRoX3g5aDJTNU1obTVrTkZ6cVNrUkx4YVdfaFhBb25XNnRhQy1uTGRjeGlIU1ZnOGVRS1ZHbzBKaE00QkdWODhZVlVBVFNMbU1LeU43TDQ1R0g4b3MyU1Q2V2MxV2V5bmhldTRTeUtBeTJaa2NrMWVPSEZHd1BvTWpzQS1DM3dUWQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Trump seeks crypto donations in Super Bowl pre-game show ‘AI’ ad; social media says: ‘scam’ | Hindustan Times - Hindustan Times</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Sun, 08 Feb 2026 22:54:45 GMT</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxOQ3lsVnpYaHp5bXZKR3RMalBKUVlHdTJyRXZpUklwdDNJcHJLa1FpUzJicGZWM3lZNlR2ODUxTHhPNjBLYlgtZmQtWnR1X2tsT1BLOEFlSVl2M1BRVXJ3Ti1Zc25JUFdqNEVrMGhNbW1Bd25ubVZ3cGNOUWNwWlA5N0dHaVU3T3Y0U1N2azZpeXVYM2cxcDgtbVlmNkJYeE9pb2ZPejFTa0M4cGpyWHE0Sk1IN2oybjEtbk1DamY3SjJ6bmFYQzY1N3RVeTRSQ3RmVzBQWjBRbllTNDBIVWd2SV83NUJKRmRpZXphYy1aTdIB9AFBVV95cUxPU05sa3pSSHczVFZPZWE4N2tZRXM4MEtRQTdZLWl3MjlVMjctRWROMlc3Z0xLRlNrZDROWm5FUmtRbjhxS3VqcG5BdlNleXpKcDY3MmxsSUVWb09qUUxhaFNtdUpyQmhtY1Y1NWhLaW1kUzVtN1pEdnhBNE55SDRJWXRBYW1FTTVfbVZ1RmsyZGZOR1V6Q1VjVnFNaVZlMm9acm5uRjIyMTZtamxyeUZFS1J5TldwTFpUSXg0aVNMR1lzSDRLVHZEcDVlRGJoSk81TmJhb1RObmdBb3NsQlFYSUFqYV9ZWlFJclhNTk5SUXNPZDhp?oc=5</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Oz alleges Maine ‘looks a lot like Minnesota’ regarding entitlement fraud - The Hill</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Sun, 08 Feb 2026 12:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxONlQyU3Z2b25RMk9UaDhXeUc5bm1oTHlNU0l5aDdubkJoU0hpQkVpbGxHNEVXOWFuWDhHYzdMYlY2dWJ2YmFjS1hyakRjekUzRmFsbTN1ZVZzTDZrRU5VLXVOMWdKQk9DRmJWUDJ5X1RXLWc4YlJ0NFJJU0didXl1RFJLZ9IBiAFBVV95cUxOU1h4b0JPdUhnR0RwTUFiUVVvaGtYVzhhVTJuMTR0d0o0bmdKLU5aX25iZFphQ2hRM19pRU1KX3ZYRW12SGdaMnF3dTVoa0tFZHhKeWRBajZneVhjdFBfZVg2bGs4OXdOYjdmN2xJMVRFR3BpNzZOZzU3di0tV1RvYUtRcG5DaG1I?oc=5</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Abu Dhabi court orders man to pay Dh194,000 for social media fraud - The Filipino Times</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Mon, 09 Feb 2026 03:40:17 GMT</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPZXcyOUZDbDloNWFVUVFIRjVaTzhVcDcxVmFxVWlkX09jLXNpRVV6NF85MVk1RTRjSzR0OUVuc25RUk8wUzlhUHo0WDU3ZFpnZEs3VVI0eWx4SWRhcWE3Y1VLZmZydTRCRDhXdGFFUEtSMUUwWHpjazAxVWpXS1RvZmR0cTU0bVY5RHlLNnV5cGFKSE50S0tucUJ2eFNWUE1lNXpkaFpVQnAyS2hYTFZ5cUtMYWh3Zw?oc=5</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
         <v>1</v>
       </c>
     </row>

--- a/data/daily/topic_feeds_daily.xlsx
+++ b/data/daily/topic_feeds_daily.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F77"/>
+  <dimension ref="A1:F95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,17 +461,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ANALYSIS: Understanding Geopolitics To Gain Wealth Edge - Wealth Briefing</t>
+          <t>Importance of Natural Capital to the Scottish Economy – Regional Analysis - The Scottish Government</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 07:24:00 GMT</t>
+          <t>Mon, 09 Feb 2026 09:01:39 GMT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPbm13a08yemRjZ0YxVFBmSThhaDNMSzUyckY3YWFyVmMtUzZmMU1wWHlKN3U1VDNYeDQ5UURSX1ZXbWtFeXF1REtNU1dXaTdQMXpvUVZnVWxkcEdKQm1yMEh6QVhrMU5VMmVlamR0SndBMkYwc1hFOWpNb183SnFVZ1VoUWd4UFgzajEwbkl1M2EyV3NnZS1rM041Rm42R3ZfV19MUlFfYXk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOTEJxbWVpdDlUUHY2c3hNa2huaENGUmtQQ1lfNTFaMDZfZ0xOWW5FaEhEemw2U3BqZS1PR2hMOURLWXNSanVNSEdXUGVNS0ZJcDlnVzlLYjZWYnFOeU9DMHVmQXZydGxKdzhKWmsxaXFxb0RHajMtY2N2YWhyaVdKZUVKcnFucWlOdFROczJyOXpiR3hvTW16RF9aZVg?oc=5</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -491,17 +491,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Global Humanitarian Policy Forum 2025 - Protecting Principles, Norms and Values: Summary Report - ReliefWeb</t>
+          <t>HCLG Committee report on social housing conditions: LGA statement - Local Government Association</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 23:25:19 GMT</t>
+          <t>Mon, 09 Feb 2026 08:46:43 GMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxPNmpYUGpRU2x6eUZtWkpOMGc4QlNEZEVTdVE3NWVuSjF2V0pQMHRlcURkVUtUbDg4Q1RXMGtwWmdYaFVkaWtqclFWUF92QnJHNzBGQ1MyR1pMTXNoYmZ6VjdhNUpERy1ZZXpaN1hNb2ZacGVPLW1TOGNFSjZybkJoUHI3UDByTmJCTGpwZWUwQngxMk40ekJhNkc2REY2YzhWTi1TUXBuNHNxVXhaY0NkUGdjR3N3S0E2djhwbHI0dFAwNi1j?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNNWxxSjhkQkF0WUZ3d3dzNUxCQ25Nam9rWkhzamg2MUhmRy1vWlpNbjhnRDRibE5aVnQxQ1NGQzJWQ0NaQ0JWX0FoMnlNcHNUbjZxZjdGSEsydWI4LU9PSlctVzBmWGVlSHlSVzYtazM1UXZHQWVNX1VWQnhoSjRBQzh1b3M2TDZjS01INFlaUGw3WU1DbDc4UzRLQ1pJZw?oc=5</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -521,17 +521,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Review of Marketing of Infant Formula by Retailers Final Report - MBS Online</t>
+          <t>Briefing: delayed elections and council tax rises - The TaxPayers' Alliance</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 05:10:57 GMT</t>
+          <t>Mon, 09 Feb 2026 08:28:40 GMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOM3ktUUhpREhicEs1MkNXY2h6Y3lUbFAtWTVuSEZoMkc2RTV5emdRbXV4ck8yQnRqVVdPcGN4bHl1MmxySFBLNWw3eXFRdGR1Q3BKNzUzbHpGUFhhSzk4RldIY25uR2pvR2ZIc3FBTi15dl82QjVkTnZsTVUxOVFxd1hwd045aFNxb3FfU2paY3hxaVRVZ1huZnl1cEYyb1p6bkd1b1BFVzRkdTRqNTJzZktKdEJWNloyd0kxanpFMm9aUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxQWnl2NTJwYm9oa2hsRHdsSXlYdFNGZ1RVME91dU1rSkk4RVVEQm1DUF81N2ZOcVRYMkNhcE5TdjZ5eVVBMWhGaWVkd3pfOVNhQzQzTG91S2ZRQzJWWTBSbExhbWVkZXRpcHNuVGR4QmdsbFNLcTNiZ2dWNmZIYm5XVlBnaS0xZw?oc=5</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -551,17 +551,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>UMSG addresses ICE ‘misinformation’ on campus, hears budget report - The Maine Campus</t>
+          <t>Villeroy's Exit: Minimal Effect on ECB Policy Direction Ahead - Global Banking &amp; Finance Review®</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 07:05:05 GMT</t>
+          <t>Mon, 09 Feb 2026 16:08:24 GMT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOTXBWbWRYSlpxYlJWVkRaTEFLSkdNSWpmQlhXbWFwY0dmb09nWVdpYjZkeVA1RFF1VjFja3cxekZYVkwwQllta2VfdXA2dXA2R1JFbWczcTUta3RqaVQ2R0ladWVoS3pycmlfRk1qNnVfSXRjUTZjYXBXU0RXeF82VUlyQ2F2alJwVEhuOWVtTG9sY2dSbmNVeE83NkpDbElKSlJQMW5LSjlvcWpUbHdv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNTG9uMGUzRHBLNVZzWjJiWjRnMEJGV3lRR0MzaE5Kb2xwbWR2eEVKcXRZY0pvbHBVN0VrMzhZQ050WHRYbS05ZlpJV3VCSjNiNi1OVzNsYjB6ejZSUVBSeVRYb2NEc052REU2OU0wV0JLbVY1QVRPdnQ4LWFBenVMU2FtX0VkMjNmemp4N3NpeFJ0Y0ZPUXdnQjhacDM5XzQ?oc=5</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -581,17 +581,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TikTok US Explains Privacy Policy Update - Social Media Today</t>
+          <t>The Government’s clinical negligence report looks in wrong places for cost-cutting - Jonathan Baker - Yorkshire Post</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 19:22:13 GMT</t>
+          <t>Tue, 10 Feb 2026 06:00:00 GMT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOdUZzMzVvdzJubF93SDcwN2pET3lhLXViSG1sd0tHR0VtdDMwbzRMNFkwWTNxbVFIeWJURTNvRTc4WXFYWTRENGs5MGdYdTVpekh6M2lwSWNFN09fMHczcmRkNldUUmFnVG5JLW5fcFYyZGVpcFdZSk1xakNGVDFIbzhCV2o0dVlDOGtHR2RCcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9wFBVV95cUxOZkp6NTU3U1hEWmtFVWhDYndTMkN1RkZxdjlfNzZhMm9Odm8wSUhYSkZEM2ZQb3F4emk1ZjBhVzhEM1hvbEtUN240bmdvcmdQNzl5bFVLaDY3RjMtV1hoYUZvUWpXMmdPVkVwbmxjUml0QkdxbEM0anFUeFBuQjBZckVRcnVybmM1ME5VYmdRQ212bzNmNmlodFd3ejJORThKdVlJWkRzQmZTOU9SUEpHM2YxajVyYkFza0RQcUZGV1pPNFQyX1Z6bFo3VzBfMWEtTElvSWNic0FzLWhLS0ExWGV4ZS11SVVjM29pQW05VmhqME5nSkpN?oc=5</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -611,17 +611,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Inflation, AI, Geopolitics To Impact Australian Economy : Analysis - Crowdfund Insider</t>
+          <t>Kuwait adds eight Lebanese hospitals to terrorism list, report says - Middle East Monitor</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 15:42:41 GMT</t>
+          <t>Mon, 09 Feb 2026 13:09:00 GMT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQQVlmWVZyWlJLd2RxaHh0OE9obUEya1MzcXNrZFpneXpod3hhYVgzMXB4Y1BzaFp2Q0hrMkhtaVVMWENnRndNT0xGcEtNOEZoZjhDdUpKaVQxdlpPN1phS1BWeGZvVVZLMXotOXFRaEtTME5kMkxXcEhxNVEtRU5TemhQU1R3Vm1MTGlzVkd4OG5maHJXeDdQLWlGOVhjMnptUjFobkZLQWtUTnRqQ3BfQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPLUVSRU95aml4WTBlMnlvU1JOejZnbzZON3V6aGhDUnlwQVVyR0dpNjlKdmV5NGJtVjNOUmFkaWxyeENaZGVoNzhreVlpUlZmekFabjdZRk95UXdhaDRBOXRGemhVR2c3YUV4aTFXRU1hQk9nSll3a09EYzFuWi1LUzJaUXlweUZzdVZKWGg5TjgxRXQ4UWNYdFdDblpTUXdpNWVJYnB3RU42NkF6ZFJz0gG0AUFVX3lxTFBsUXBPbDZQcnNwaGVOVnMyMXk3V3pMZzBDNzV1bjNHTjR3V1EzcUtTekdwcVBjM1lObmhNdjB5SWR4YXBocDRzNFdEUjRaczhWUjJfRlZ5Z1RSRkhnbExGZ2dOeVRrSjBNejl6UFVvNXhkOE5vV2VhbzNUay1GbjltZmFtaTA3ZG4ycnI3TUN1UlI2aVhzYVBvX3E3WEJ6ZmNlQUpLX21kVUM5eHdDaEtIZEtYVQ?oc=5</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -641,17 +641,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russian officials are warning Putin that a financial crisis could arrive this summer, report says - Fortune</t>
+          <t>What to look for in the delayed jobs, inflation data out this week - marketplace.org</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 21:14:00 GMT</t>
+          <t>Mon, 09 Feb 2026 23:32:59 GMT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQRTE1QWtyZmJHTlYwOHh5dXNra0tJQXBES21RYm1qZmxBMUtNS1RUMUlwdDd4MEFzM2lJemdOUlloa3pkTHNkWjdqdHZyby1ORkZOT2xUdnExTC00b1VZVGgwRzgtODZTWkJBQlRsUHVOdlR2QXhDXzBOMENLTUlFQkROSFFScGVLUGw2cUp0T1NKUHlrRGRoZG1BbUxCOW13al9FSTFmRlg0VUdiaFNvR1NrVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNdDZhNmhocXk5Sm15cHdyamdRMmlqMHdLZ0F2QW5sSTRtdWJLdkpoMVgtNXRZdHZBZkJrTE01VlJPejYycE1mbDhZSFVsN1VRMVNpXzVaTTRsZ2p3ZUFiMEt1M3hMY0xkZnpMS3c0M3lBWk10NTkwMDJsVXVJSE5wbjdVZ0RlaDdhSFdIaG55VEN2MlNJekxZUG5tejNzeVFmSHR3ME5xYnAxcjFNeUhZ?oc=5</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -661,27 +661,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>5 things to prevent supply chain disruption - - Enterprise Times</t>
+          <t>Indian migration boosts deployable skills for UK economy: Report - Deccan Herald</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 06:39:33 GMT</t>
+          <t>Mon, 09 Feb 2026 18:35:14 GMT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPWjhaT2M5c0hCdXhLczJMUHZnR1Y2Uk1ncGlQT180UFB6ZEpkSF93MVFNaF9sR2p5bjY2LXZhZERXSEVDRGFQSlFFZGcwZ1pjcktiNXg1Y0M3TkI5eVF1ZzZ6ZGRyWkl4OHA0TTR0WjFFVVBlTFhzOWU1cnVDSW1UWE0tZHEwbDQzUjNPSy1UQlpGcWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNWE12SXYzSHg4S3AwQjdaTi1NMkZoUm91YlZxVVlCaGRCYVZ3RDBJNWtqcWN3MWNxRzJXUzA5aExxS0RYaV9PRGRlLWlnMjc5REdsd0pjdmJSbWtOcThOdmhSRlJ5eWhSWnpaMXUzZmdzczVVd0E0TVBSRTJ6Ry1rT0xZLVkzaG4yLVVDbnc2c3laSGhnX2ZzTzdlc0R1QUJZM3o0d05zS1ZjZw?oc=5</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -691,27 +691,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dining across the divide: ‘Tariffs are the one thing I agree with Donald Trump on’ - The Guardian</t>
+          <t>Crime Report: February 9, 2026 - Arlington County</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 12:00:00 GMT</t>
+          <t>Mon, 09 Feb 2026 16:43:51 GMT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPVno1bmFoU0l3ZEhfWG5yckFyUE5PVVMzMnpGcHZDTVl4cEExS0ZNQnhDX2ZXTjFpX3V3bWpwcHQwQlVBWUpWSFBKZEpRM1VxRHlxdWRDUUNPOWp4NThyV0I4Y2dIanlsNHRuVXBlQjdtSF8tRGdNRVMyWXFUcXdaNHNaNkJaNEJUS0xfUTZWVjUzM3FSamg0MklpeXZobVdkRnZOVWVKbEZra0ZydHFmUWpHVWxOTVNzaE1HZldJQVFVYmRRRHdWM3lGaS0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOdTlaTUt3bzZDbE5sSFlFRzNIakJ0dEMxZlBjQU5reFhXZFlIVlBGVEpKUUM1TWpsQ29OV0czdzRHV0Vrd0JrWkhWRl9jOFlSUUp1YTBiaF9HZHdLUEpLdUM3LU0yU1BRUHliV1dZSFU2azdDbFZsU0N3aGNUMWZQUUhCTXR0SWt1YTlSMVFuY3dWc0tlc3F6b3ZB?oc=5</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -731,17 +731,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Last mile quickly becomes logistics investors’ first choice - Private Equity Real Estate | PERE</t>
+          <t>Bangladesh secures lower US tariffs and exemptions for clothing goods - BBC</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 02:00:39 GMT</t>
+          <t>Tue, 10 Feb 2026 03:26:05 GMT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxQY0JTX2pwT3VzYjAtS3ozdHZqUzdYN3FfMmxNWFYtMTV3S1VhQzNNRE54WldqcWJXbWZmWWZhWVVuX1dtTzg5SWhUOFI1bzc5ZkhqWnZ6aUtuX1NIazE1cHdqd04zc19MVEJaVkU0bVBoWVpwX1BIUXZCSjF1dmhvWThoMTVLZDRHUnRLRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE00RDA1ZHRVYXYtTkpxTXZoSTB0ZDRtSTB2VzdNdnVyMGR2NFBKV3JuYXhOang0ZlUzNS05c181WXpmQlNaeEpMUFpSMVdjWEZLNnlOeEtFSlpqdw?oc=5</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -761,17 +761,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>EU targets marine insurers with proposed blanket ban on Russian oil shipping - Insurance Business</t>
+          <t>US plans Big Tech carve-out from next wave of chip tariffs - Financial Times</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 06:09:36 GMT</t>
+          <t>Mon, 09 Feb 2026 23:27:26 GMT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPZkdkTkRxckRUZktTSTJsLTkyLXhsbksxbUs4YjRDdmFKUGM4WEpUdXlTWWpPNVF5d1BpR2o5azh0T2JIeVhaX0VYakRzYk4tbzFkMjRxZ3RqaU1oc1AxaTRLR3piQW9rMzlRTGI5RThjbFdqZW02dl82X2FIZDhxeFRfYUszcm56T1BWRDFoWEZJY2NhVHJ1TEpNSHFPU2tXUU5faVVyN1JfcW5PVllHeWdtaUw1SmdZZ0ZVNUktTzhxR1dySFVnTW1nUk53cHBqd0ozUlB0cw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE02QlNTMVdWQjVZR09sQ2NhdS13SWtXSmRETzhRdkV1Z3pLZFAzSmRqaTNZTWEwb0pMbUEyNkVfdFlDNVNkZXhfUTlyRkliWUsyZzZtTkcwNE5GUGZvbkQ3azNDRnE3UlZYSzUyLW91RWY?oc=5</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -791,17 +791,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NBIM quantifies the portfolio threat of economic fragmentation - Top1000funds.com</t>
+          <t>BELFAST HARBOUR REPORTS STEADY INCREASE IN PORT TRADE IN 2025 - Belfast Harbour</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 06:01:24 GMT</t>
+          <t>Tue, 10 Feb 2026 00:03:53 GMT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNRkRnTGpxcXJxTFpGSFBQWVlBM2JKbEZaMWJfczJNbWhwNDNXeHFUUVdrMkFXeDNjbXdmZUJVSDViM042LWp4MXZDSWdDZkdxTnFJLUFwNGsycUlUbWQ5alQ2RFRJZksyYzBhOGpOejBsZ1NSRUNGbDVDX1NVa00zdk5xMG1YeVEtdmdYSjdOZ1hvdS1nWkxQM2l6eUZ6RjV2UEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNR01kRDVpeVM5aGdKMVljSmtRZkdFUjFCRTRCTDhwclAtVGh0RGhLbnd0VGp5NWtZU2dlcWJfX2MxdlhnNW1ZeGw2NlNkbTl4TVpBMURPT0dFWEhvTG5BTG1hcV9henUxWmVCWERjWVQ5QXoxOTl2Wng0UXFFWmE1cGJmVHp2R0txSFNyRVpqRjBWTE5UcGo3NzNEenoyaXV1OGZZ?oc=5</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -821,17 +821,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New compliance manager for RSS - Vertikal</t>
+          <t>Cargo ship to be towed to shore after engine room fire - BBC</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 23:32:04 GMT</t>
+          <t>Tue, 10 Feb 2026 07:32:05 GMT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE45RVN5WWQ3bjdjWkRpOG9PMWo0RXhtcFhRSmRaNVJTV0J2Ml8xc1RUd1BXb1JGckMwZUtfS1RiUVk2V1hLT3dzYk5nR2xPUmpkRmFmWUY2UXpTbHJiVVZnbVBGMmwzek41SVNwUkZrRE9qVDlkX1N5ZnlyTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE1JdjZkYVdxc0tLMlhXcUFxUDBFd09BYVFGVkYwRU9VSXJoMVh2NWhpSDJXZnlmb1NHZURtWTdaQXd2XzZsN050VGVVZXgwajB2Uk41ZVVJeDc3RDBy?oc=5</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -851,17 +851,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Statement by President von der Leyen on the 20th package of sanctions against Russia - EU Reporter</t>
+          <t>In 2026, contract logistics is set to grow again - Trans.INFO</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 07:44:24 GMT</t>
+          <t>Tue, 10 Feb 2026 04:07:19 GMT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQa2FNelBQcFg1Y3ZrLUl0Q1ZHNmk5SUlab0lvRm9rTEN2ZUU5QWlaMEJVSElZMTBwc3c1UVFNVFFWN1JBMFZybGx5cjRqUjZueGRwdHAteXU4WG14QjdFdkd1UXdwQjJTU0xUYi1ZLU42MUZYWVhFRHhaQWJ6Q3dVLUFuVG5NOHdXMVIzZXVIcDNkRENMOUJIeTZXY2tucFF0aU5xUFVuMTJ0OTRnZ1RlTGpBOUdhckxZREhQR0FfOW1YdllmSHBoeUZOeWtuZGZs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYkFVX3lxTE5hS09jREZ1MEZwck5KX1NvRlpMMi1aSDB3RGR0cVg4R0JLM3huZ1lRczlFd3BWNTM4TFJ6SkVtVll1Z3pjcFoyTWw3Z21pVmd6UzhUM0ZrVUprMzFFb1BUSzlR?oc=5</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -881,17 +881,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Major Australian Iron Ore Port Reopens as Cyclone Risk Recedes - bloomberg.com</t>
+          <t>Match Officials | Port Vale (A) - Stockport County</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 07:06:00 GMT</t>
+          <t>Mon, 09 Feb 2026 17:18:08 GMT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPWThaQV9FdHF3N2oyZDNXNmN4YVViejNJSThiWU1qcl9VRU5mem9DdGJLOEY1X3BKVkhReTNPZlFPa3JkRGNXQTNaSG16LXZMZWN4ZjJnNDRkc0VmOWV1RU0xRWw5RHZOaEZPTFRsV3JNNDNJVWt2TGgwTzJtVFQyR25MdEljX0ZYMmRRdmZCcHhYU2wtRWVMaUhpUGZCTUZXMGJKclZ0aFRZQUpIX1dWRXMtNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNaXlGRzh0QUt2d1NKdGM1ZU5IbmZJYVZnOVJ0SU5jX2QtZ1hYbkRPREVadGZabG9xRkgzbFF5eDFrNmgtRGJsWnJoaWFCck1vUVRkeVhQb0p4YUtvMDA5bzBTZWNGdzVPcEpJYXl1NHVaT1FEdVUyNGc2UjlMbDdGcXpreHQ3QXotdlo2ekwyOA?oc=5</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -911,17 +911,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Who will use OIC’s Scapa port? - The Orcadian Online</t>
+          <t>Grant Ward is a Valiant! - Port Vale Football Club</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 17:18:08 GMT</t>
+          <t>Mon, 09 Feb 2026 15:54:38 GMT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiYkFVX3lxTE9DUU1hdDY4TFl4blgyamFiZkVmakFYQUwwOXRYYk5uTWFSZFVKdzVUTlZ3Y0stLVZraDNNREc3RlZMaHRPS1dueElRd0FLbXZQRVppTVhGZThrTUR6QVE2YU5R?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE1DZE1lMlpmTkRXVl9FZ2VhZnhzaDhCMHEyTFNxRGFfd2N4MUNWN0NlLUU1eHZ2RUtlU0lCdWZkdVdQT3RBeVVkX0JQT0xOQlljeXVDaFdGX0FqaEhCODE1Qw?oc=5</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Record Order Intake for Witron - Logistics Business</t>
+          <t>RLAM's 1m sq ft Leicester logistics scheme to be approved - Green Street News</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 15:38:20 GMT</t>
+          <t>Tue, 10 Feb 2026 07:12:32 GMT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNdGZ3X0VPOU5hOG9BbFpJMHotdVMwZzdKOGZCNktzcnc2M1FNS0RFaF9CVk51Q21MVkloUU0td3RZNENNWjE4YmhiNWZQNHdMTVl5TDhfWlVKcG5Iazg0LVlJS0o2QTBVcGJtSHpZRzJwZXpqMGkwY2R1WWlvVTFsVWhjaXo5Y2JLUllGOGZLQlR3M21EYmRLNG15YUVLQUROekpRVUMwSGRtYUlv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNX1pkamVkSlRCUWJZSFJvbGFmcUVkRUFsaWtaT1VuenpmOXBHVDJBOTNQOXR1d25CaUxLYV9fZkUtd0FHTW9jeHliOVhKSTRkUXlhZHZWSkNWbXNYOUREdS1FaUlDUVBVeldKblNqaXBZdk00bFo3ejk4WjU5eTdKb3R3YktjMkp1VkZFWjB4OWc0UHFuUXNvQg?oc=5</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -971,17 +971,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Braving tariffs and uncertainty - eKathimerini.com</t>
+          <t>Hiring delays worse than economic instability - The Global Recruiter</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 06:00:22 GMT</t>
+          <t>Tue, 10 Feb 2026 07:47:40 GMT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxQR1lCNEZWR1pfNTR3b0Y5SnZBei1IeDNDWXhlejdTUHJqZFpsM0ZhOUxPR3djY2VMUC1TUnU1OFZFVEJXbWJaUjdfb0pzRk9weHNmRWNqNzljV1JkaTNsQnVRajJkcWFPTnV0eGw4d1MtUHVmUlBLQU9KRV9lV3ZQWjczMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQemUydWYycU1rZUxUZGpvcVdPSWdPeEdjNXh2LU5xVVU4T2hUQkg2VUpuTUpQWkRQYnhOb0dQc2dGbmNkYkJLRHBxSWJobUJFSnZnTXRtdlBmVGllWnV5RVd2dkhrQVVSRHJFV0Jxd0Mzc3RmWWx3VE9WNkhKM0ZxZTFLNTY4UFlX?oc=5</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>The shadowy world of abandoned oil tankers - BBC</t>
+          <t>How Buy With Prime is Transforming Logistics and Fulfilment - Supply Chain Digital Magazine</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 00:09:30 GMT</t>
+          <t>Mon, 09 Feb 2026 16:01:13 GMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE9zeHBlczJhQzR5bGNsQlV0cjhoMU1BcnEweU04eHg2U3VYQjNuNXdlRkQ2TkNTRFJ3Q1BzdjBlcEQ3a3ZQLWF6dWJlMTVtdEg5eTVZNEY2NWtZajEx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOUktNZW53RmJzQ0RUZG50SndmTEhOT0d5X0ZoQkR3NENELTNqUDJUMFhSR2QwaDQ2VkV1dHJCb24xbTI0Z1ZxX2I1WVhnZVVaSjhIdnZmS2JhWm1kQWJqVWh6bmsyREVtbEczcG95Tnd1RlE1TmJBUHk4a0JUZmx3QUdMMmFQaXVUdXoyUlZUQV90QQ?oc=5</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1031,17 +1031,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>WTI holds $63.00 as US sanctions offset easing US-Iran tensions - FXStreet</t>
+          <t>Shipping giants have learned the right lessons from past storms - Financial Times</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 01:32:03 GMT</t>
+          <t>Mon, 09 Feb 2026 13:48:40 GMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNYUU3YU9ja2tsR25tMmpBOHpJYjhtNDRWbk5uVTFWc0dBVTFrMVJKQ19lRVhyUEJOY292cFg5TmowTXVJM2hyNVhQUU93NzRRTk1BeGFOc3ZtcnpmY21MdHd2dHJ1V2ozdXNBOEFzYmVkSFZEZDB4ajRhNFRVYkhlSjM0czhPQlVwRmRhQ3NfN3E0dS1XZHBaZjZTaV9UWUJPX0U3UVc0S3BfNTFjVmRsY2o3aDBuUmRzZjMya1ptVEhLcDNnM09wYdIBzgFBVV95cUxNVjhnbkZBYzR3Y3lxc2RxM010NXFTQjd1NDc3ZFA2OXFLcU0tWElwYm9yeDNxeGJWbmEteUFlRW54NEYzbV9TaXVBUlJzcktEMDRrWi1LQndpWGNldXJ3N2tlU0ZQeWN0UmNlU0RKOUlMMmhVN1ZFWkstWkR1M05rQTBsODdWc3VKeEFhSUh0SFNodV9qdmNPMlJ2NG9ZNjgtbHprLWJFTERpOHRCeWhkdThBeVVLR0pkck52dzBaV21lenAxQ2ZvTmtMc0pMdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE9SMGpTQ2M4Q3NuRTZDRVdqNFFHSGhqTUstSGM0WVdPamdKMnBfbXlIY2ZHUnNJYjVSekdDSGtmU2owVWdwYkkzLVRFRlNoQ3VDOUtLNGFLcEZkeTIwZnZlVWlrZFV6dUp2aDk0SkdqOXQ?oc=5</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1061,17 +1061,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Port Hedland resumes operations after tropical cyclone Mitchell - Mining Weekly</t>
+          <t>Shipping giant MSC facilitates trade from Israeli settlements through EU - Al Jazeera</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 03:38:00 GMT</t>
+          <t>Mon, 09 Feb 2026 10:02:46 GMT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNU21DRnd2dWJMV2hjeE8xUDRRaHQwb0Y1dmQzZDJkbnhsdDlxcGVPdlVfbDh1c0U3T18ycUJNejNkU1I1bXcwOW9mVVEyYWVtOGJmaWM5M1BnTmp6UXNSS2dzZUZjMUxnVnpiMl9NN2M4TUh6eWVrWnlCMUNfd25YUkxzbTZZOHRVVWxBTGtpYVVsT1NkY25ycE4xN3k4eDRwSGI2TnlWUHBOYVhFMGtDNg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOdXd5S1R0TS1hWW43U2ExSnpGcU9wWWxsMFFTbHlPT29oSWRzLWlyQjE2MDZ2ZjlLbXpqaXFfN2dESzRkWGNfVFZSaWlnMzhQbjRRZkJvdkRlQldnc3o1S3hfRHo0WHQybVcwaDFMdHVxT0dzeEo0VGtTMlFFak5JOVdqT0xSbTU3WjRObTlHODdJd19yN0FlYWx4WjRmZ1VUVF9ZaVNPSGw4TDZVVUpBM3VR0gG3AUFVX3lxTE8xaUpIZlg1T2hfU1BDOG9UakJWaGR1VVpNcVltbGxGUkVhTjE4OVFqNzVqbDVmdU10ZzN6Y0QxaUZhLXhka21CUmRYSkpoQmpLM1ZGRDl6UlBCMDBtekthb1NjaFIxTjF0cnpOcmFYWjlvWVFicUFQZzVaMGZaUzVERERISGRHUFVRblg0TTgzbElqWWN0WjdOM2llQ3Zyd2NhM2xPRk4yV0sydFVYT1g1eUx2WURTQQ?oc=5</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Travel platforms face cost and compliance impact of changing regulations - PhocusWire</t>
+          <t>EU proposes sanctions on Georgian, Indonesian ports for handling Russian oil - Reuters</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 07:01:30 GMT</t>
+          <t>Mon, 09 Feb 2026 16:59:37 GMT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQZnpBekVUV0JaTXFJbm9iekkxbEZoWWk0OFlkWDAzeVZLWk5IaWZhdjEtdkFheTBSWDAyYklSelBRMGM4Uk9HX0tOaERLOG5pYVdJZWE3bHdQaUpfaFJsOEp0LVJkNkJUeXJxQTlBZkttZDZZcWhBUHdUSTlfNEpMMm5JV2tyaWkxMFpnVTR3RjVURjhRdGV5TA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQSmF0YlpISU1LNm9adUVUOXdaemlFbG9hTzFHUnUxX3N4Rm5PYURNc1FSLVVHTm95bE9BSHlsZVJLZE9HazVWVG1CTk81NGh2eFpKeDh5bTdiYWtlRDh2ZjBfZ2JZcTV0ZDVGV2NOdU0wRG1HdzJ4WXBhRER0REZQMm5WSVdPSVlhbkRRa0p1ZUV0c0NXdnBaaDQ1cnpwVWxjejZ2ZkhHbThPSTQ?oc=5</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1121,17 +1121,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Embraer seeks expanded Indian supply chain role amid partnerships - FlightGlobal</t>
+          <t>Campaign to help tenants saw Port St Mary rent arrears fall 47% - BBC</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 04:56:46 GMT</t>
+          <t>Tue, 10 Feb 2026 06:39:08 GMT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQNDFFMjRvMHFwdmJzb3hmeWU2X0RPTkQ1S1dhMzJLY0hWalQyN09CMUY4ajdFMVdRZWdubkU1eURyVGdkVk45ZVFaNmtjVlZSSlF3UEVNM0luYmszb3dhb0ptbnNtdUxqMXlQR3VnbGowRXl5VWMtakJnU1QzYzNfTDRJRUwySERHeE5FZ3lHSVpobGFGNl9CUjJaU2M2ODNZeXhNNS1QS0xrMk03cndxTDRsVW1FcGxRX3pB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxOaVFYLXJXVU9sX0I4N3JHbVFObzFhTmJTYWxVcFJ6M2NrczRvd3hlRnFzUkhIellBMlFZOGp3YlR3RXpUQzFPSlVVV0ZQRExLMmZSZjlZSVY3ckpmYkx1czd0X2Y2TTV3YkFaSEFTNDBwbXFnd01VU0VoMW5ZQVU5Z0F0UXZFVktpM3Y5UUZrMlFENnpxN2tSb056NGoxaDlHN2xCUjdpRkx6ZkxDWUdsRjRFaUU0M1dzcnl2dWUwZ1pkV2N4a2RkVjJ2aENNVU8tQ0FESS1RRmFfZkJIMEF5TEJn?oc=5</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>China’s RWA tokenisation rules lift related stocks as compliance race begins - investingLive</t>
+          <t>More people travelling to and from Jersey, say ports - BBC</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 03:44:47 GMT</t>
+          <t>Tue, 10 Feb 2026 06:17:17 GMT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNRTMtc204Q3E4Mk1QMHBhMW1QTjg2ZnlmV2ExWWVLZ0pTNnFTMno5d1dpV1puNUx3QUo5WUl3UkVwWUlVT1R4N2VzekNrdkdwcUJydUIwNzlkZlFpRzlQNjJoY1NVR2tvR3JaTTJRYURhaGMybERIZ3R0allQbzZwaldYbVJZWEJfbDBLeS16aTExcHZ0dW9nRngyMUVkQVFhVDNMZy1NX0pNdGdpQmtzS0x0MEV0aTBuMmdqSzRrVmdkaTZy0gHKAUFVX3lxTE5XVTRMOTNja21lY0JuNlpxSUFaZE1mb0FJRk5ERFNxZXpGYTNJbFdna1Q3aENYYks5LUhDZTdVd0ZuZk1MbU5jQ1dJbXZIOFFSY0g0NTZ3LWFRQnRWRkpXRzlTQ1FhNEw1dUU4a0tCQjk5RE93NU9ib1d4SmtXXzZZcUMxMFN3UmlQaFhEZVZoOEJsaFBqUUNKMWhoM1JiMjdnOHY4VmIyQU10clZuaE5iOWktYlZOQ3d5MTR2VXlfa0JDY3N3amFkNVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTFBhWnVueEQyajRWRU9Xd09HM29jSVhOeGZXdU5uZVZlVndfYkFoeGVrYWR0RXlmWm9rT196bTRpdFRVdHNMclE3ZDdqeUhtUkljN1IxemtEa0hMVDB40gFiQVVfeXFMTzJTdHNBWFA1NU1EQ0NMZmM1MGVyYmxlalB4c1dpZFZGRjhlekQzU2ozcVYtNmNhblBwY2tuZmVkYzd3QVYyX3BaZXRoNkU3ZllxM2lvdVU4dmJQclJrbmxtN0E?oc=5</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>How a North East logistics firm is supporting major solar energy projects - The Northern Echo</t>
+          <t>Oil exports have been a cash cow for Russia. But revenues are dwindling, thanks to sanctions - The Independent</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 06:00:00 GMT</t>
+          <t>Tue, 10 Feb 2026 05:05:00 GMT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPbXZ6N1l1bGZGR1ZVandIVGh2SHBrTFMxcFJLcnRSREhidUFHTk9xd01USENpaGF1Yi02Njk4NldTTFpYMnZDTm5KZHdldDVfUEl0aExrS214SWRVdjR5RWRQUHhFaFY5M2lFZVBLUmV6NEpETTNSMjRsY2lSNDZudThkNWRqRU5PdGJEZjdDcUc3eFBvUXVoM2FlWmFLSWk2amRHV053?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPd1BtSzFYSHRlLUJwX215Tkw1NG1rN1RfSjZodW1ZVENxSHJRWkloWFlNT3M5bUhQX3JlamhDYndFUmNGaF81dVV5SGItMjVVdFl3OTQzckVmWG50WUpMak5HX0pXQ2pGTHBpQS1PTVNfYjN4MnBXYWM1OVNkbFZST1lxeUhqdkhWem9zOWV5WG03RlRnYUxwMWpMOGlTUXkxYkRFTXhzRDJmdw?oc=5</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1211,17 +1211,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Europe’s shipping rules are not just Europe’s problem - 信德海事</t>
+          <t>Port Vale MatchWornShirt auction now live! - AFC Wimbledon</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 05:45:30 GMT</t>
+          <t>Mon, 09 Feb 2026 18:06:11 GMT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE5nRURWN3BhMjNJalZxSUVIc0V6bnM2c3RpTDhtSEFOZkJISGdxWmFqLVc2NnVIUEhzdC1vLWFUYlRwNEROT05XZHpXZ2ptWWctM0dBZHlfVjNHYloyVFh4bklWLVdaZ1ZvcGItaGNLXzNOSkdoR0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPSmRDM1hpZVBoVVRWVTN3ajYwQ2sxOGRMR1QyRS0yUXpubFI5MkcyVzZLbEU5NkNWQ2NuZjc0amFuODVyLUNCR050WE5SUlJvZTN2ZWNyNS1LTEI4MlNwdE5ZS2RMVGpJcDhQS3VkQ2ZUbGhxU2FBR29yYmo1NG1EMmQyRUtYUTF5cVY2NG9OT2ZReE9heTBXM01xRlJyMHFzU1I4dmgzUTludy1MREE?oc=5</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1241,17 +1241,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Eskom Can Raise $3.4 Billion From Tariffs After Regulator Error - Energy Connects</t>
+          <t>Iran suggests it could dilute highly enriched uranium for sanctions relief - Al Jazeera</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 04:57:10 GMT</t>
+          <t>Mon, 09 Feb 2026 17:12:31 GMT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPS0VaTnVrV3p2VWZ3VmVvTzhlUWpfN3YxQ3JoS3BMbV9aU29KQ2o0OHl3Sk9XWWhQdGV0YVQySG14VG4zOEtrcHdzQ1dSeVpmSXI0cFFlTEc1ajZNdkI0MkFWYW5HanNWYXlraURleTQwNGpSTjJqQU1iOGtxay1MZURqZ3ZDeFRRb3Jqb25FY3RYNVRFTG9WVWI2WFJlbXAzNkFuY2JYZGJJcUdnZXJLN3BKUmZjLVNob3FXblcxVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQX0VYZ3JhZk9rUW80RmR3clZlQXFFVGtwcmtvUnZjN25MN1ZjWVQxRnBvSi1sT2E3SWhfQjFJWlNWQWV3cTNXenVFRmlwbjVycVZibTRpRm5sR3JyTzBMSERXcUY1VUxxOF9yRzdEMHowMjkyTldUUGtjeW1Ub25MLVAxUnhfTUk0aE0xU1RBbWRXbEJYaHctMWs4NFJNREZwX2NTeWlzcWRMOXlGTE5SVUs0YkHSAboBQVVfeXFMTlBYaTdfay1YY1JiMEJ0cllidTVFUmltY0c1SHNaNlpQM2JqdkNZeE5TMDlqUDN0WG13NjFTWlBUN09JVDh1TmVlOHdUbjdnLVc3MU10b2pJekFBSVBscVhNSTZhVDlfRTlzejdHUzFZeGhoZkRBZ080ckFabXVHRVFzMnVZVWhHWjhweU5pYjFodzMzQ3d5SW1KX2tQYnlGNm1nYzRiTjhORkFuVm9xcTBtWGlfX0pCM2dn?oc=5</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland divided over pharmacy ad rules, Commission urges compliance - Euractiv</t>
+          <t>Council set to approve shipping containers despite emergency service fears - Nwemail.co.uk</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 02:55:20 GMT</t>
+          <t>Tue, 10 Feb 2026 05:00:00 GMT</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOX3JUVzlqbzJSME1VTFpJR1NfSHRsUjRYajBoY1hDSmlWTTF1RGs2by1GM2ZQeTVEN0pOeEc0SUJuSi1IRkJGQi14VE1KRVlsWGdoWXBYQ0pWSTMzclNzRTJVbWVnSTFpNUVUMS14cmhtNFFxbE5wdVVDdThQNG9WaWlPbHRZLUFHUzZlZThQcGs4V3pfSFAtSmF6bVk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOdGxXVUtrRGpGSnIxWmE2dFRJa1VqT3cyam5UX3NoQXBReVdySjFwTE1fUU5fbFlRMlNKUEZWNl9RaUFoREhuQXZ6bjY0eEJ5QW0wNVkxLVA2LXNrMEp3VnhPYVRWako3UmFLOGhYSnYydXFaWk5ySjVnZlVsUnBmRDR5M3Nta3ZISDNMLXUxc1FlbmxKUFhmRVRvR0RuQmJQSFpfUUVn?oc=5</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Twice the compliance. Same old agency fees. Does that add up? - Property Industry Eye</t>
+          <t>House Republicans Move to Keep Putting Off Vote on Trump Tariffs - bloomberg.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 03:50:12 GMT</t>
+          <t>Tue, 10 Feb 2026 00:53:00 GMT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPVGJyaTZEMG1VWUd4UFJYNjRSVTNWWFJaSFluSXg0Y1N4Q3BYeHllal9CRUc5S2NxTm05UFdnVUFyaW5Ta0o1ZGNKN3hnQ2MwYnFsSGU3U0lZS2RobU5PRkpZdFFVdHRSMlZTYmpqbzBua1VUa2pVcHBNNW1UVm9vVnZaeGtiV0UyTWU5cFEwczdRWXpGZnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPYWJaVE00N3A4N3hHME5KTE0tQUF5MlRsRk9VX2UwSmpVRGZSRmRRNTB6YVdVQzlNQ2ZBVDBiNE5YRDJGTXRzZTFsb3NPTFVUVkJoeHhYWXRNUEx6WEJRczNBeThQbFJaTzd3MGhDQmxuYm1tNElBN2plWkp3SVFweWJqZHExSVQwSDlGWHZxeDRLeEJpX0xRd3BzRU5McWN5dkhxbXNRQWZ3cGJHRTE3bnhNa2JDdw?oc=5</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1331,17 +1331,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Canada builds playbook for surviving lasting auto tariffs, in case USMCA talks go south - Automotive News</t>
+          <t>BoE’s Mann says US Trump tariffs are pushing Chinese export prices higher for UK - investingLive</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 04:26:00 GMT</t>
+          <t>Tue, 10 Feb 2026 02:47:24 GMT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNQTVka1ZZalZMVWM3WlNKYkNSTjAzcFVZenFERTVfcFA1TENya3dzckIyQmRRaUU0aF9YWnFtc1hudlVROU5XMi1MdXR5VU9LYTBMQ1lBOHpUR1VfZ0doaXJMQnIzVUxrMVB2TUxOQVdJenB0TWRTT0VpdEotLVlmdmhKeWJiSGczQm5fUkhn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPX1lGMHVKZXJoS1p4RWlMLU1UU2RwcFhJU2hNRHZsS211Z1NreTlFemhTN19pRFhqYVh3ZWVZbmZELXRqZTY2M3c5ekVBV2wxN0UzZTV0ZUw1RllMd2FlYjRkQWxsaFA2amJBU0dpVFpMbWh6ejdHR0poMjRVUDUyY3NPVmZUbWUxejVETjJSc2xIcHJrTjhpN0JYMGc5cjZrTm44UHBYY2RxbVJJUzVHZTN0a19kVkh3eW45UUZ0QV9YTHVXcGfSAcsBQVVfeXFMT012VzJLVl9fNlI5d0xqRndUaUFZdkVQaExuNmIyaTM3Tlg1ME1fTnJHTU15bFJqRUxFVVVxbmRPa1F5aFc5cjdqLVRPc1ZkR2djQ0I5SmZPbnBuSFM3R2tOc0RqR1cyQWlielNSX1RwN0lvdDI4d28zb1dSRjN2cHQwNngtV2VjMi1lR2tndlVmX2NOWTlpYThHQkhzcS10Z0JWS01oMzF6VmZTMm1rTFhEclctTmprSllXNDFIS1hJUkVzY3dFMldqU1E?oc=5</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Duo to celebrate their 40th birthday with charity skydive - Newark Advertiser</t>
+          <t>US tariffs pushed French cosmetics exports into rare 2025 decline - Cosmetics Design Europe</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 05:00:00 GMT</t>
+          <t>Mon, 09 Feb 2026 18:25:22 GMT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOaWg2OHItdV9iSjJOTjdXZm1GXzhHeVR2c2pqVXQ4TDE5YTVaS3VfZW8yQjlEYTl6SEM5Rm11RmkzTFNKTE12eDE1YXZKajR1S2FaX2liRzZPSnJPVmJhbUl2RlFfOGs4YkQ5NHVEeVc2Q3lZZzdlNkNFWUVHTTlRa3hNMlo0NGxXMG83M2pMN2ZJVDFyRG1Cd3ZoNWhmNWZwZ0ZUd3VZa1htdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNVXR2bjlnaU9IODJJVGt0UDQ5UEFhMTZ0ZnN6ZXRVemQwdHY3NkNWUzJ1eXBoNS1kTElkVDhwdDhHT0J0NWROVkhub2RwcEp6OHlFRkVoVEFaSzJaNDJ0ZEJDWlhDUnlJVFhNWmF1TllYTk9KZEowU2p6bjBTYmY1di1xU0pMY0ZnRUpsZzJXTEpxTHRfQkNNLXRxd1NLbnpTX1hKeGFLbnIwbUhaUWVDbGZzZkZQV0x5THVIUGtHUQ?oc=5</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1391,17 +1391,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>U.S. sanctions Iran-linked ‘shadow fleet’ as nuclear talks resume - Shipping Telegraph</t>
+          <t>International compliance firm acquires VAT specialist SimplyVAT - Yahoo News UK</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 01:52:25 GMT</t>
+          <t>Tue, 10 Feb 2026 05:00:00 GMT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQQUZWUWt5TC1kQTZsMWJsTFRNTC15XzBPQjY5VUphNE1VdmJJOG1MNjIwdUhsdTlwM1pvSFZhV1dCR1ZMaFJLT28zRWtwRnh2Xzh1QkF1WlNHcWVWdnhIbk1JYVppTUJZdDl3czMxa01sQWJ5UE9JdVFwY3doOTN2bUlFQXE5bEk2LWZwYmk3eVNUTWlJdjluN3VIYTlLZFkyNDJ1NG9mNEt3YmZJdnhhU2IzRHBBYkFK?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxPbVhsVmN6RXBtZlA4My1VQXZVb2FlT0pjQzRMN1pTOXBEd2pOLUR5Q0FkUElkRFl5X0lENUx6d3JYR3pHYUpLY0NJQno1OUR2SzNQaS04dXFXcWMzeGRic0JMSXVqWWFUY2s4R2h6OUhudk9iWHVmNk55LTB6UlBEUUd5d1g2MW9xZENJ?oc=5</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1421,17 +1421,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Fujian Guohang Ocean Shipping takes delivery of Ultramax bulker - Baird Maritime</t>
+          <t>Logistics firm will run major Swindon factory - Yahoo News UK</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 02:21:08 GMT</t>
+          <t>Tue, 10 Feb 2026 05:00:00 GMT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNM3ZQV3l5MUYxWVZMajhJdlk2dUNPWnJtQ2VJRHBPakpqc0F5SjVFNV9keGlGYjBWZVNUNGJKWDVsbF95VWduNEROV3JkWUIyWTg3MkV4QlY0SU0wSi1JRFBZY1plMnVkZVRFeHFSeDNhZzVPUnhWd3JUczRpT3RqZUtNZV9vOWxmdnpiMThtU0U3Ny01RmFKZHBLV09BQXdqbnVVbHJ6WHBTZWJ5cWs4dEV5ak9paVJ1UGljZNIBygFBVV95cUxPOVMtc3ROUXlJVmMzUEFjaE52M0lUR25lMDFEaTFDdm1iZGI1ZU02cEFwNVRkMnhYN0hGMXNsMFAyTGM4d1pGZnhoeGpHZ3VnWlZ6aVdNLUhPRkRIWEhlbHM3NEh6MnB4azJDTDRQSXlIYkZIcE9rS0FhS2JIRy1Bc2QxbWhKZGZ1TTZHbUZkRFpSbjV1T0NxTGM1OWpYSFlxTWZhVUtjV3BIb041RkZfUFVkalk3c0pmSDBIY21MZjk5RDNzUXdlakZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9KdGloTGV0NmpMbUdtUDMzY3FIR05qZUJSODJXR3lHVW10X0F3SUljYkRSNk51UExPaTJ3Mm85UW1IWElaVC1Ta1NJVlJZSFFwX1VVaGZ5SXFIZ3J6R1lyWXFkNVkyNnpwTl9jY2l0Y1NTMnJUeDE4RFpBMkhVZw?oc=5</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1451,17 +1451,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>The Logistics Lens: Chaos Versus Control - Breakbulk Events &amp; Media</t>
+          <t>Top-Rated Logistics Software Development Companies Driving Efficiency in 2026 - Impakter</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 15:15:10 GMT</t>
+          <t>Mon, 09 Feb 2026 22:45:08 GMT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE5LMkVhekRZSEFmZm9Fc3FCeG11ZnZabEotUHhMNjhINTZPZzhRdXRweHEwM0s5YUE2Rk9lb2FzT2w3WHZKSUoyU01ySzlaZXczdU1vQ2RlNHRhVVpNbWZXeWF2Ujl2R1M1X1N6TWpHTzNMYmVjYmdpM09B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE9pTzU2eXhCRjhLUEYwdDhxVzVKMFFJMWd6c1hrdUlvWlpWd1ExNU9VZHFaT2hTSEc5Q3NNdUZZQU1odGlJV3NJTURLMUtGcDRRWFhMLXJZR2JEbHNtbkxLbnM4WC1NUjdzWm4tSWpkVnRXeXE2ZmxtZEJEYw?oc=5</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>UC Data Residency and Compliance in Global Collaboration Strategies: Finding a Safe Home for Data - UC Today</t>
+          <t>Pembrokeshire student cadets receive boost from port - Yahoo News UK</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 05:29:16 GMT</t>
+          <t>Tue, 10 Feb 2026 06:00:00 GMT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE5YYlJSSFV2Z19wVzFia0pFby1FVVYtUlpfSW40aGxyTG9RV19OSllHcm13SDBGckFZNEFqcUtLVHZOOU5wVEtTZTRWcC1iQXRjMERTNXIxS01ZQzZVUjhUbGx1cWhEa2lBeVBTcndtUnpOQUhoTnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOX0JXR0J1UnZEcF9RX2NrcVVtUklLUjh2b29GdnNlaWloT2JBb1l0TGZjcHFXT2RscWRPOU1zTWRLTUV6X0VzWkJ0VkNjMHdSNld5d0JvejNiUFRpUUR1Rk1mdkpaNTdjMmlzZDdXZlFoOVU5ZFdLS1JRUUZneTNFOV9HcFdJM2tGc1lR?oc=5</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1511,17 +1511,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Morocco • The kingdom now knows its fate on US customs tariffs - Africa Intelligence</t>
+          <t>Himalaya Shipping reports ‘strong’ trading performance in January - Tradewinds News</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 06:01:36 GMT</t>
+          <t>Tue, 10 Feb 2026 07:59:54 GMT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQeGVWbmN3czZlY0Y0Zk1vUS1qMjZWdW1ZNGFlTUpBenJLd180V3hZOVBYSEUzVlJnQi1SUmIwWXV1blI2YktDaFBSblZKdUhOZ1dtOHJqT0E2ZlF1a2EzYzdPOXdnMDNmdkI2SFMzX0dkc0F4WndmY0RtdXp5Z0hHY3Vnd094SVdheGV0LVpCekN5UHJTMmdnS3AzNG9HZHZjNF81eTZhR0o3c0dzUWticmk1QnhtTUM3c05mdkxQeFFYQzg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPQkxsOHAwa1EteDR3OV9mWE1HYUVGVW4yWmphSzg1aUhLT2JLTVJfMnY4a0duTHBFN0dpS01weTFjbXFZS2hzRjUwdEVkX0YwUVFneFh1ZmtxY2d0ZlY1ZURkd25pLUQtSzcxc1B5VjFyTW5sN1lSVkY4bmNKeXlaZ1gyYV9DTDF0bEtpUXRtXzd5TEJxaXFnTmk5blNrRWZXZVJMQlV5SlFhZTQtdjVLZUQ5S2E?oc=5</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1541,17 +1541,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ukraine imposes sanctions on foreign suppliers of components for Russian missiles - Reuters</t>
+          <t>Boeing sees aerospace aftermarket recovering from supply chain pressures - FlightGlobal</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 09:30:44 GMT</t>
+          <t>Tue, 10 Feb 2026 04:49:40 GMT</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQLVdvSzVaY3dpRHFvWjN5dWJjYkNRZ1dwNlBMbUtkd3VmYWE0MkUzNTVoTE9FNzFwbmhxWl9rQlhBaXRLV28yYWlXNVhOU3ZreXNkMlpvQ216ekp6OHI3T0lpNVNiR1RMZzBLR2tzT1BwRzU4dFZUbGhtaXItOURyS0pfdmRjUjNTN19sVjNHT25QQUJfRnRLYTl3ZVltLTNrdVNTSDFKRTFkc29XaTY2TnBLMnRNSVJTSVlwVGdMbUtiZkQ4UnhLeDVwY3Itckk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOZDd4UGNSWWlRMGdtbGpNOVpwSGVyV1RCY2p6VFhmNVhnX2FZdlhTWFp0eEM1SDc1cnB3M3JBcVZ5eGw5LVZWb0lsRzZHbFZ5NTRDelBHa2VLdHJ0ckhHdW5iMWh3Z0wyZjRuRFZQelI1cm04QkE0NkU1ZUw2M2xFMVZTQkI2cXJmaW9JRUZBZ0hJQmJ3VURuS1otZXBrTHRJUk1RVnpQMUtja2RPbklDb2h0Mk5sN2tUUGxBcnQ0b3VHOUls?oc=5</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Could Algeria Back Away From russian Weapons, Including Su-57, Under Pressure of U.S. Sanctions? - Defense Express</t>
+          <t>Changes to school funding could affect thousands of local parents - southwalesguardian.co.uk</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 05:05:40 GMT</t>
+          <t>Tue, 10 Feb 2026 06:00:00 GMT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPTE5NaWhVVnJkcU04b2hCcVNLZUFEMVdaMHNUdUUxWDI0bHpTYW01ZUZuTy1MRGd2V1lCRmZzeDQtV0dpU3I5NXRHSEd2bS1mVTJaZzl2WnNuTl9rdWlaRjBpY2RwalBLWGdKQ3Jaakx4aWc5TWNqampkUEVrY2FSSTNKSzYxYWljeVhkQnVILVAtSXhyYkhxeFVLQzRZcHo3QVNKZzlLQ2Jfa0k1V3Q2ZnhWUUFxM1dmaUpfVUY1dnJoOC13dXFEM1hyUGdSQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQT0lfaG5fR3FPUUVCUGlINHFhbWNHMUNobzZNWk5MaGNxaVNPT1d0OUR6dHlldnQzZnYxa3ZnMnBBWW5Ka0MwVk5DYy0xQjBGWlF2TlhFbVRPOTc5SUNwaTRsWER1WDZnbHRfcThvZldORFVpVkFNU2JNMHY5Qm83SjVXVnZ2cThGR0pOQ2FPV2NzN09qdklZbGpQVWVFWnZ5VG9jWW5YRHlRanM?oc=5</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -1601,17 +1601,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Saudi Ports Authority seeks Suez Canal partnership for Jeddah port development - Dailynewsegypt</t>
+          <t>Residents warned of drone activity around Radlett rail freight site - Herts Advertiser</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 18:35:20 GMT</t>
+          <t>Tue, 10 Feb 2026 06:01:00 GMT</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxONlo0eEw1WnVJRHp2b1NQdXhlR2Vkd2FkOG5DQnFYd3RKVnZfY3pQUlVOOUM5dEcydzZBWWhyUXdOQVVVdmNHS21sdGg2c3gxdW05eldMdlFWNDk5MldKVUMwQ04zcDNRQ3ZhWjc5TEtna3BHRWowaWdDQ3VLQ2lzMF9sMGJSNVZLUUdJcGtYZ1hjanlWODczQWpaNHlfSElDeUdyTGZOYnN2Rm4tOERjcDJHUkI5Z2dRWW1ZM3VR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQcDF6X19MUEt0S3U4YmY1ZVBaMEhGUlJ3SnFoUmFDMlBUSW1fM0lvZXRFMW9wb0diSmRtT0ZoUUtKU3JtdVc4bTFzdXBMT2Vna3RUUFQtLXo0RWZCb1loUjB5MG1oeTFSQzVobTBrTHpjblk2RUh0SnFBOVltOWd5dzlZdVE0V0xGdEVKMmpUMkxDS0NmOFBGZA?oc=5</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Namibia will not recognise TotalEnergies and Petrobras due to non-compliance with procedure - Offshore Engineer Magazine</t>
+          <t>Northfleet Hope – Gravesend Reach – Port of Tilbury: Dredging Operations - DredgeWire</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 22:58:14 GMT</t>
+          <t>Tue, 10 Feb 2026 00:26:59 GMT</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxORmRlTC0zSlYzcFVwNmwwVUFZblRCM0NOU2hSRXh4NWdRRDJHT1NZVGxzMEtMaTlHUVNER0dwM3dpLU8ydE9fYk1GeDl0ZWFRa3V1Z0JMNGs3SDFaSmJ6TnFYNHBNZUtkVGZ5dWY5aExYZG5RMEZVUHZFU2tjRjhYVmtmSmRwcVBfUURHbWRoVWpPbnJUbnZXWjhqYzVBRTlqQkpETnNWNXBPTUNwMDNyMW9vN25QZWtlSVdCOWdYVEVZU24xd1RJUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQZWFMM2Q2aUVpUURUTFFpYlJwTEMtQ2w5UnRKT01rSWptNGZNcVZNSmN2c3NFVWk2NkZOcnhmX2hLSGNLX0xFaGRXOEktcTdVZ1J4TFpaLWEwQmNYaXFwbVdvamtXVFEtZHB5NG1TTlpZczMtODlqOURQUGx4YnIwVnZFY01QQ0h0MTBoT3czbVlUb0RmRUE?oc=5</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1661,17 +1661,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Assembly to debate motion on tougher sanctions for ministers who breach code - The Irish News</t>
+          <t>How do CTV ad teams handle Pharma compliance? - Advanced Television</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 15:46:27 GMT</t>
+          <t>Mon, 09 Feb 2026 22:57:23 GMT</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxPcXlKSnBvZDkxb1RENXZCUW1xM2RFcUhvWFhVSjROM2ZXTXZCTUR1VjBpX2Mwekc0d1U0TTRSenN1Q3FBU1Zpb0lPUmtPS1B3OTZqTW52NENJWU9NS0djWmNEd1d6MmpyazhBZWRDb3FfdTdpUGJYMTdZa2R6X2U5Q1hBYXZLcHh2MTNFYlE2VFRCVGoxOE4tMERCSUhPVlN3RTdKdnN3QTRQdVNtWEZBUTdyQXlUWmo3UWlRcFlUTUlidjJKaXIzYUF2X0pGQmJYSUtTUDN6VDBHU3FxcVI0RWRqNm5HQWVQR2hKdVZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQbWdITTBWMVcxd2pPeHliUlUwYi1ma3Q5SkxxMVcwLXUzMFZXRTZDaFQ3bEJFNnJhSUE5Z0k5SDVMMmV2R0lHb2Jib0xJM2x2WjFnX3hNX2dSZVF6WDJZNzNON0lneW9sV0FRdTVUeHRqaVNLcFYyVUxXMEZpaHpVWk9WaDQ1ZWZMVmg0a2FVMnoybWJIeTZr?oc=5</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1681,27 +1681,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italian police arrest protesters after clash in Olympic host city Milan - BBC</t>
+          <t>Port expansion would have ‘extremely significant’ impact on historic fort - Inverness Courier</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 13:02:35 GMT</t>
+          <t>Mon, 09 Feb 2026 17:00:00 GMT</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5yUTg3VmVQckk2WTF5N2d1VllTWUVpMnVvWVdQME1mRHdMYnpoNnRhQ0JPLUVVdDluNjc5WUhYcWRReldXYXBrSWJOZVlfVTdYWU5mQnhRam9OQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOa2x0VTVJenF6RlhlVm82MUsxNDFHNlBKdUtWc0ZHZDBSb19nRWxYV1plbUROTUZPRV9UNjFHN3I2RGo1V19ZN2Vxdm9BZm1RX1BZSnpYTkt4RmhIZzBhbVJKNGFvY0s1cUtPekZnNDRBOUJvUGtKSTI4SWZaTWFPVlhOc1J6amE2a0RlMmExTEItOUR3eENJU3I5TFZmYjdxWEVIQ09renBHdw?oc=5</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1711,27 +1711,27 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Pro-Palestine group loses legal challenge against sweeping NSW police powers for Isaac Herzog’s visit - The Guardian</t>
+          <t>INTERVIEW: UAE’s AML chief Hamid AlZaabi reveals plans to maximize compliance effectiveness - AML Intelligence</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 04:52:00 GMT</t>
+          <t>Tue, 10 Feb 2026 02:04:19 GMT</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPYTJrZF85VTg2Z0xPbmFlZ2NYVEJhaDktcnRXV2l5a0VpNU1acnRFOVZScDhvZjRFVWQ0S0pIZWNyeHhrTjE4SmlwRTMtMkVTUDJMaEtIS2N3bEJhZk9yQ1kzQ095M2ZRaVNxZi02bEtIYUxvN1BJc1hnZm55VDNyaU1famFvaVhIbS1sdVcwNm1PeldQNFI0QWNXbk5LdXRZd09KWlplUzlhSkJwbjJfNC1HakExSWla?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQSjVQTDhWUmlJN1NsS0laT2VhUWxtTDgwUS1vcG1RWFlXVWd6cXNIdF80M3NqUmpKMG1FRVp0RVdkVFZyUFRoeFc4QjZtX25pcUJuWTA5LU81UWdpZEdPY3NzUWp2RkZfblk4TlFCRmNHckYzN1dsRDctZ0xOWDFaSFhXOTFVZWd3MGY3NDlNdVBJT0xIVS1iTk9XUzU3YlUxQVlOTFc4MmRDdExuMGFZVmJlSTNRbGZGcldDMEp3cDJJelFxTWpablZ3?oc=5</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1751,17 +1751,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italian police fired tear gas and a water cannon at dozens of protesters who threw firecrackers and tried to access a highway near a Winter Olympics venue on Saturday. The brief confrontation came at the end of a peaceful march by thousands against the envi - Facebook</t>
+          <t>Australia police defend actions after violence at protest over Israeli president visit - BBC</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 08:56:21 GMT</t>
+          <t>Tue, 10 Feb 2026 04:19:50 GMT</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxNVmF3LTc4SHh5bktseUE3bTc3U0VLUE1pWkxMbndWeUNYVGR0ZzEwdlRDdkhwaGItU3dHdlduaDFOMW1tU3lzMDVxV3g2LWhubjVaajlVRDRRVVBacmxKLV9EOUJQNm1GTmNjYkRRN0xlVkxhWEM0NjQzXzhwai1oVG55bnZvSE12ZU1uQmlGQ2szUGZHUXVOdzItbGJTQjJhU2lWem52UWdTSlI2WEtfbkZ0azMyZjZ1OS02UUl1R0dwMjZuR1YtT3d6TTdiMkdVTk9pSHdsQ2FZN3NycVBn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE55X3pEekVVX2xLYkhnZjg4VmdvLUlPRFFOUkMxekVsc0ptSXEyMDA0ZkNzS0pNM2lEeGVubWs2Q3JoU2Z6YU1qZzB1cGVVRXViSS1sdW96XzRadw?oc=5</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>VIDEO: Heavy police presence at Sydney Town Hall as protesters gather - Australian Broadcasting Corporation</t>
+          <t>Australia politics live: Ley allies demand Taylor backers put their names to spill petition; rally at Sydney police station after alleged brutality at Herzog protest - The Guardian</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 07:02:48 GMT</t>
+          <t>Tue, 10 Feb 2026 07:16:00 GMT</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOOG5WNHNqdWFOS010WlgtVUhxVm16YVBwb1VxVzhBMmMwcFJ4LTdlUVFIX0pXcjFKdU1aU3FzTm9mdHYyUFNjRC0tVlNodF9ubi1hREVkYXdfWGllM1lfd3hiNTJsZWlmYjFEREFZeE1YUG5ZSS0weDNBaHdwZmsyOXFtN3VkMHlzXzlvdUJ4M1lqRXRyX3FINjU4ZEZaaEhYdkluLU5SRER6bWEzRDZVWg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AJBVV95cUxOSmxaQUQxYks4b09OSVh3LTE5OWk4eTIydEZQUk5pZnphYUJ6SHF2d0NJSUVRSlJDakNhLU9sQXdpc2trMnprdkFqX0pSUXNkc3p2bEo1bXhZb2hGU28wWU5XeV93cUJabVhIWmxQSTNHX2xUWFZZM3pOTVNYZWdXMnNBbGl3VHVsZ0oySERDMzNCOE5YNW9ya05tVndyS1dCYWY5MEZFcWs5VXRtZjdEZWVOUXZwOUNiLXA5N2dNNnA2em0wUjlKb0dLU0VENW9pVzZxTEhadUVDMk1qRUZ2dGx0MzdpTDI3b0k2VDBaVTFCMlZOWk5iUjlWMWp0Z3phdmd3aU13QmJJVmVyemRzYi1UdHBaMmlndng5NWlTUnN5S1JSZTFURVdxdzhBbFk5Y0ZOZlVtYU5LQWo0akR3UWFPLWMxRzB4VTdHR1laTUpKSkZKZG9FbEZVNmEyd1c2?oc=5</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1801,27 +1801,27 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Students deliver AI, automation and digital tools to factory floors - The Manufacturer</t>
+          <t>Haredi protesters block highway, clash with police after suspected draft dodgers arrested - The Times of Israel</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 06:36:11 GMT</t>
+          <t>Mon, 09 Feb 2026 20:05:00 GMT</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOdnpkYlhIRHZSeEdwOEtnYzFYSHJUcVp0b3RHOXg0MXhSQ3Nhb0FYNUpNLW51OVRtcU50TzB2aEpFQWtUZGQzaS1rZnVCU3phWmhEdW82YWlya2hSaWNycUtlZTZ4Z1pLVmlnaFJ4azZaTWhlVTZFak56azNwaHZzY2JaR2l6clBsNFZEY2c3ZWRNYzc3eGpvZ3NZR0dVcl95ZE5EZ1o0aHdaTTlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOWWhoc1UteGE5TEVEUG5YOWV1aTAzenFITHBUMkZVcm1jREp5cno3OFJjbklpcDk3VEc0SVJZcFQ3dlhOWFk0OHpieUxYZkZGVTkydUFMc2lWcnNiWDAxTDI1QS16eU53elpERXV0ZWVESGN1eDdkcVkyZDdma1pHWXQzTzFNME4yX0tRcmpJVE1mRU9uNTJZank1YThfUWtxdURCX1A0bzNKU0k4VmZuSTlKcXlMNVp0ajhv0gHAAUFVX3lxTE9oSWZRbUZKWE1wNTBuM3FYdkVNSzVRNXQ5WjFYR0JkS29kTS02eDJDWEtNTVlYMEZTa2FDZ2NBYWh5dVFYazF5U3JFdG1CczlwY3dfNTJPQ1RMV2NxeHkySGtZOGw5ZjZrZFlWLXc2bldGdUtUVjlZSzNqUWVtbE40eUNuTVdoZkdzNFhLTXR6U01DWTFtN0JQVDJHT0Jxc2p6S3EyYVVZWlY5UXBqb0xKM09ETVBSS1ZTQklJRUNFeg?oc=5</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -1831,27 +1831,27 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>What does authentic assessment mean in the context of AI? - Wonkhe</t>
+          <t>Police update after rumours of 'man threatening people with belt' - Cambs Times</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 00:27:53 GMT</t>
+          <t>Mon, 09 Feb 2026 13:00:00 GMT</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOYUt4b2gzeWxKdksyNXo2OWp1MHcwX2pUWVFvUkZ3bW8zR3ViN3lYb1ZZUHRRdGJQNTZENWwwWHNFT0VMVW1nWm44aUdYeVREd2ZhdVRZdkNyT01nLWVZZ2I1dFJoa1doTFNkV2VjWWR6amtPQ05jWXh4aEhEbXZnbEVCTjJwVVhyNUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPemxoenFFcUN2YVFRQThSYzEyS1BtUDlmWnBGelNlWXhlNk0tVVhPaFdTcnZUOEFyTmpDUWhRdUZpTGFzMWhFY0N4V0hJYmZKQkRWUDh5d1hfdEZxRUZfTnl2ajNOQmZxR1BMYm5KVjQ0blp6UDNpVUtJenNGSGFmWnFXbFU0NE5pYllrTm1vNHJwQ0FNMlBtNTBrblA?oc=5</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -1861,27 +1861,27 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sovereign‑ready cloud and AI innovation set to scale for European enterprises with Capgemini solutions on the AWS Sovereign Cloud - capgemini.com</t>
+          <t>Latest News - NSW Police</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 07:32:05 GMT</t>
+          <t>Tue, 10 Feb 2026 03:54:43 GMT</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxObHljSDlRSjVGVVhBZFZhdU01RXBNdHlwVmwxSGZsN2VjWjl0LVktMDZiNUp6NU9IVjRwU2dRWlNiUFE3LUNZbVpyV1VSeFhIU250cEFXRnAzY2djZlNqRHdYS0h6cFU0SDBlWmY0elZhalRoWThaUDhBMl9xZGgzQ0VPQzJMSkVya2g5LWxSb3JENDY4ZVhPSGlfTUtNa0phcng2SEJOekRMLUZGR1ZabXh2YlBqamhkMDYwM0lpbXpBbzVsVDdTek52clBtS0ZlMTZMWDJ2bmVVdG5OYi1mcWJlSTd1LUN4Tnk4MEtoYnVRNUNzXy1HSkZNSER5UXA4Z0RTRkpn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxPQXQ3ZDc5MnpSYml4WG5Lc2JfUlFXcGdsZ29ITmdJOWFueVptR1dPN0wwOUZmNU52Y2tZazlCYkdDZUhEZFVTdjZidmE4akw1MTNqVWIxWlVlZUZkUFlhMGlkMmduS1U1Y01CV2xFc1psT3pjQjNmeGpZTk4tS2pBYXIxa1ZkZjd0SkdEWXhCaDZlbUpTSDFVdkJicFRwZ3h1blE4cC1IemlXeTl4Qkt1RVlKZGZrWF9SSzhWcW1rUldicFl5OWt0cU5GSGpmeElrX2s5X2dRNnlfX1JrbWM2UHZ3bjJvZmpGZUpkbg?oc=5</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -1891,27 +1891,27 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Software Leads AI-Driven Tech Rout—What Next? - nb.com</t>
+          <t>Significant police response ready for expected protests - ACT Policing</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 01:22:02 GMT</t>
+          <t>Tue, 10 Feb 2026 00:29:15 GMT</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQZDBaUUlHdWlsYjMteGlIVUJhUWlYdlB2dHlOaWNZMWhoRlJoRmtSR0xaMnpueVoxcHkwZG85cHJyRHpDdkdlMFVGRUFtSmdudG85SmFtLXJ4eFNkUFlRRUxKRUQ4VmRjdHFJVXpXakpzbEdoQkpJRlpEd2QydXFNY3hNenJkR3MyVk1iLXdkRzMySmNHMXAwdWpvY2d6ZXJXdnFwQmxmMjVENjF5WHZZOURpNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOYkEtSWFWQVkta05IaXBJN3BLTGM5MUNLblpZSXc0ekhxYnpMRm5oaXQzUnhuNk9WTmZ1SE1wcm1ueTlXSlBGMy11MFJnaFpIV0ZXWXRncWJBbzBKY0haMEpnSlpROWVUSjU3WWNwbFRiNlowM0haMGw2UE9TOENpX0I0STJaUmhUVzhZU3VxMTRUV2FRSmVHbU9yNjcyS0prdVoteU5Cajd3UGJUc190cEhPR3BoUQ?oc=5</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -1931,17 +1931,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>In Q1, marketers pivot to spending backed by AI and measurement - Digiday</t>
+          <t>Focus on AI and cyber attacks at business event - BBC</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 05:01:53 GMT</t>
+          <t>Tue, 10 Feb 2026 06:25:45 GMT</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNQW90SENldlZTTUxkdEwzaDhHZXpMTkJEemFWaVc3S0FuNXdVTXdUNHdMbHZEaWJ1MkVRaHMzNksxQkgzbEZ2M3NRdmZGQkNPQ2lEYnFWSTRWTUJrdzBQV01uZkxQdkpLcUlRczhKSTFtdExRXzlHQnNleEZraTZUbjBPVVZIZW9KdGJFZC1fM1ZhbFN3WXN4LQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE9SaXhSTzNIaDN2UzBYU1h6NURyYVFUZzhZWWk4eE5ySUJoWkxoVjl4ZnNCVG5VX1dvTGtueGJhVGxaeTlmNmVlV3g3enpvcERpVmoybzFQblpWQVNX?oc=5</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -1961,17 +1961,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>From AI investment to GDP growth: An ecosystem view - CEPR</t>
+          <t>Investors pour billions into Europe’s AI and defence start-ups - Financial Times</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 00:05:04 GMT</t>
+          <t>Tue, 10 Feb 2026 05:00:17 GMT</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE1EUmJyajFkQUV0REF0R01UeFVaQnpiaGp0SVR0N0JkQTBjX2NXWmtpTXJkclhYdzZRR1pOMWRSNml4R1Zabi1FcTlQVFgzV3VQMjRLNmdyMmNlVmw4bXBMSm9NRTBHVDlJZGRCV3N4T3doeUkwRnFtaUJ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5lS0NTQS1aNEdWbXJ0TzZCck4yU24yYkdIVEtoQ3hUSjJGTE8tbmxhVW1OSzk0a3g5UTJLaHNqSTRIa2JOZ1NkSUpXWkdPbmgyMHpYUDhyVTJYNV80N3F1NG9NMlJQc3lKWGE3SzVmTi0?oc=5</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Boomi hits 30,000 customers as AI integration surges - IT Brief UK</t>
+          <t>New National Cancer Plan with AI and robotics focus - UKAuthority</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 21:00:00 GMT</t>
+          <t>Tue, 10 Feb 2026 06:01:26 GMT</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQSy1qeHo4VE9veEtHbURwVG9Edy1YdU1nTS1WcnhXb0hzeVFqZ1c2RlhTQ1Q1aTRkVDlvc2h1U2RLQzBWOW5EVmo5R2NjcTdTenJEUWg3Q0doUVpRYnZRUXdZVjBtQVFyZ1BPc2VMczNTUWNwVlZkX0pETFgzUkh5MlREdldXUVU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPSGtUOGliT2gyd1FIdEQ3YXBOaGJnWk5MbWFNSTk3WURxWjE3SVBnS3Z0ckVORlNvMFVEVnU3TkdLV0EwLU1pbU9BeUg5cTJnXzNqai01SEFiQjZZZDVpNU11Nm0xakxzOWlwbjNZVE44X0dZMFBJTWQ2X3ZVbFlxY2NQcFJXOGZodm1iYXJESmpaZw?oc=5</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2021,17 +2021,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Private credit worries resurface in $3 trillion market as AI pressures software firms - CNBC</t>
+          <t>AI In Robotics - New Position Paper - IFR International Federation of Robotics</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 04:41:00 GMT</t>
+          <t>Tue, 10 Feb 2026 06:10:49 GMT</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxOMnpYdGtaTlNFSGNpS2dQRGwwNERxTks5SE9YeFo4cTlnTHJvaUo2LVdvdGhqTWZ5MHJ2RUdIcV9vTWQxVzBEUThEZkZZXzk0dlY4V2R4TkIxRThnZUp6ZlA0ZVplUjZXNzJaaXg1aDNULVR6dEFkZ2hEUTFBb0hQWnV1QXBaUDTSAYwBQVVfeXFMTm9oQml3Z3c1QzJ1aXpEWlRHNzZQd2k4WXIwc0IyR1BGazFqRFZOYWFwZHJVcTRRMW9FX3hTTmtYejVhc29WdldkVGdrV2FXdjZoVzdOSWN5NXVOTEZaZTRZZVdkS0FyYThCNFpyWGZQeWpSVzdWeU11cWZncFRtWGJrdGs0ZjZJV1lPd18?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1xNmVSVWNmVUV0cUZUeWF5c2llWVA4X2w3NG14NkNETm9xNkRoU1hySnlnTkdBQWNCSzJ5MXN2eUU2bWpZUU9iUjZFdTZEVHhBc0hULS1QYUJQcnJ0U3dvSElHSkxOeE9NR1pNMXlfaTE4VEhWa1VWbTF0QWJBdw?oc=5</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2051,17 +2051,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sage chief: 'Ridiculous' to claim AI bots would destroy our business - This is Money</t>
+          <t>Addison Lee partners with Multiverse to build AI and data capability across workforce - taxi-point.co.uk</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 11:59:47 GMT</t>
+          <t>Tue, 10 Feb 2026 07:09:05 GMT</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNU3VUZi1XZF80a3V4TmlxYk5tTzNwMVl4Smlob0l0Vlh4X3FPSXY4NlNGS29GYktiNWRhbWV5SEZBNGpXR2dnOEtCZnB4dDQ0Y1hxT2thZzBrN1hfMDBsYXZka3BoRTJTci1VZzBkV3VCWm5xRjNqR2RMWnp3VW12aWpwSjR5Nkx5YW5IOUEtS2FuS0Q0Um9UT2haZDJDX1JhYVI1QzBfUnhWMHFlUVFhWDJNZDlPbFg3RnfSAb8BQVVfeXFMUG5XY1BoeEc3UFRIeUt4ZUxyMnRla3gxZzdqM2dVb1VXalFjUVpya3FRTmdJSlhLaU9mY0FBYkx0ejUtdGF4M1lIdVRwalZxNHE3YmRHbVJ5Z1hkRXBLMjJvYnZCY1dCQjRkcVBFVmVJbFV6bEJlUW5XYWwyX1gzWDkyMU9DNVdkWnV1aXZhTHFjaVgyckxhMnF6T2lUaEVNMW1BN2NPVHp2cVdPRXNGZ2dvcXRwWnowTjVkekQxRWM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNNWszTkZqS2t5a0s4X3V4VkpROHNYQ0ZpU2d1UkZjTEpoaGlyREtDNFhCTHFieGlkaDBxWklyQlpWNmpEcG1JTEVrZW5mNk9Oa0ZEZHNOWmZlRHlXcjBleFlsQ1VvUGV3akY2cW44THlVZnlNNW1jSkhteFA0RW5wYzNIeV9uOWs3TmNFNWs3Zk1DaDZ5bmQ4R2xpTUxka1NKcjM5QmZoZEZmZ1haRUR2bU1rUDA3QU1VZWx3?oc=5</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2081,17 +2081,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>"How To AI" author Mims makes AI approachable for business leaders - SmartBrief</t>
+          <t>AI and the future of professional services - benews.co.uk</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 06:33:46 GMT</t>
+          <t>Mon, 09 Feb 2026 20:38:47 GMT</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQbWVHRERiSHZLa2xELWxFRkFVaExWZEx4WVJidExPb284NndZYmJfaE9OSkh0U2pEY2kzcnVEQWt3T2g3aDk2T0dua1d3Sk5QbU1CamdOSUI0MVREdTdod1RITE5WNVVyTDZqOUI2aDZBaWVHU2R0LUlSS3N5ZXI3R0NUWmVTRmF2WjRRazZDX0p0M25vUzYyVXMyRm1fdHN6Tnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE1Ya2FKbzlFemJrOFpLMURsUGlJb25iMXh2cnVQeXo2ZnRWUXpVMlZWMFVMUUhQNGFLZkkxOXVtemRyU3p0UkVjZHBuQ1dpbkhIR1lyQU5qWHhpNk8wRk0yRHA3Tk9KSl9lSExtYl82TEpteWFlS0FocWdMRmk?oc=5</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2111,17 +2111,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AI and energy: Behind the headlines at Davos 2026 - Mitsubishi Heavy Industries, Ltd.</t>
+          <t>Australian tribunal decision helps shape how businesses use facial recognition technology - Pinsent Masons</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 12:00:00 GMT</t>
+          <t>Tue, 10 Feb 2026 00:59:31 GMT</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE9FQ09UeVJzRXlzZlN2NW4waTA0T01QUWllVTFBanNiXzg4OFpQbUdvdFlBQUxXbEVmb2twU29haWt3SU9Da2lhQlowbDF0cjFTdktWanpFZEFCOGowc3BqQkM1SlNCSUFQYm9JOHVZTXJRQ21zRzVJeHUxMFI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTFAtTEc3RnRJT2hHOEQ1ZGN5bHJmY243OEEzNGR3eThKdGVGUGw5Nm03UmY0NG9xRnNFZmo5SFBzOU9UeWVQTlRRbUJFd2ExZ3VJR3F6Z3RsR2wwZlA3M29Kd25BTmgzaDhKd1J1TU5saEtpM2FySEZQWVFuRjk?oc=5</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Andrew Bailey: AI training is critical to future of UK job market - The Times</t>
+          <t>ABB Robotics brings AI-driven automation to life at SLAS 2026 - Drug Target Review</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 14:52:31 GMT</t>
+          <t>Mon, 09 Feb 2026 18:45:37 GMT</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1ANBVV95cUxOTWU1bEViZmN3SDlaaVZkd25BcmJrempHcjJ2U0VNOGdaa1VoYTJOS0E3Vm9wOFJrbUthc2h3eTh2UWNQMVZfeHlnejdESFZmazZPamp4aWJQY3EtbXE3T0F2ei1zc0JqQTlISzlCMkhTRzNxWEh0ZUxtTHdyc3pzRmRaaXpNVEhkYVc2THNRWGI5VDdhb1VZeXJ4MDdKT3BsYmVvVVgwc1JSUVFneHlkdFRldlZRczNZTTBZaHFyX0RfNkZ1Xzk2QjA0bl9wTkVUSmd2NjhnbTd2VkEtSE5KZ1hrbVBSMDFyNnc0ZmlVUUVDUVQ3eGtwZUFxVUZNSGxlM1dSTjlobVBfbzFBeEVtUWxNRmJKdnpqUnhxQXNNM2RLcloxTzRBS3prTjZnVEFQUTBMdzNjQVRUZ3hyNjc3c3U4MDJWemhzSHpGOUF6WENxOUVhQVlnWHY0cUgwelRIZzRxU2RhdFQyXzFZVHp4M25uRzUteEpnNnY5c1dRTnpleTVUUTVza1JaVEVBWllDMl9tQWJQV1pNOGs1b3dXN0NnWFRWN0lWMHlucjJmSFNOdmZGcmozSXRYSUQtQ29OQ1QzbUxoVXpkRXB6S0hTLXRSWlk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQZkRCbDgxMGVRNXE4WGJ6aTdwR180NGFyWVR4SGxYQ3hlVFlLVnVfTjhqTDdpc3duSERyb2oxQ2xCNTVDcU93UnduSkw3MGVxaF9MdHFVY29oS0k5NEpJRW9tWUlNLUE3bHFPZXJrdE9USlV1RjdMd0hBYTB5VVN3bEg5RFNzMGpLSVYydjl0R2JxMGVBT3dIaDN6WGgtSUhTZ2NjNHBtUVBZNkk?oc=5</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2171,17 +2171,17 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CompTIA and SGInnovate partner to bridge AI and cybersecurity talent gap in Singapore - PR Newswire</t>
+          <t>Should you believe the AI hype? Probably not - The London School of Economics and Political Science</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 03:05:00 GMT</t>
+          <t>Mon, 09 Feb 2026 18:33:40 GMT</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQUjYzZS16UEM3NlFFZWR5Y2VmQUQzWXZfclNzYWgxTFVwT2R0ZlVvbi04UlJzQjByM3ZkclZxcG1CdlNLWEhqdkJ6cDBUVEswNG5vZGl5Z3p1YWNOQjBGTkgzTGYwOGxCaVFOUmRwcjg0ZlhwbDFQRlhhVXNXdVc2NmViVE52Q3NsUVl1OXVfSTFmekdUQzZKU2k1R3dFeFczR21paEw3SkllMHVTWmJPWmRIT3VEeDRzYy1NVWRTZzYxNFNtWV8zQnctNnRJeEY4aER6Tll0dGM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxObTlrQ2lBMzVjbnF6SUU4dmVpZUwydVZpbk1JWG5CQ2Y1NV9GQlhpY2NuZ09COFpzaUxxTDJjNGFfeGtNLWs4aS12aHlVS3pwUTdocVhrb01Ma0E3YnlHejNBYXR3YVdIQ0M1YlFXQURxd2JFTnNSQk1tbnFibjB4bDRlQmxGcmdodng0VHdiNTJROEVaemVSRnhaWHJ2enVnQ2NV?oc=5</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2201,17 +2201,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>‘Major upgrade’ to Met Office system could help avoid flight delays - AOL.co.uk</t>
+          <t>Mainland China’s cloud infrastructure market accelerates to 24% growth in Q3 2025 - Omdia</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 00:01:00 GMT</t>
+          <t>Tue, 10 Feb 2026 06:51:46 GMT</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxQRllWZXpObHlHb0t3ZWVjR3pTb0Z5VjZ6NERORjVuM25NbUNmVEZabUpXTHNaYXUtRFo0amRaa3g1UEFha1NMYXNrMnkxbWZGSm84eHFGd2RiYlBTbE0tLVJSUldzQnE5OTNCTktBNkV2Zlh2WXNLRUlkVS10enpGOHd5aw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQOXpOUWI3UVUwSDRzdGRLOTZfdHJTdF9XUFctNVNnc25QaXBURWVoQ1gzckhkSzRtQlhrdEl4dDhrWWNudUJac1BNWkpaLUN1NTgtMGlKczBfVzVlblRaN2d0cUM2X0h5RWR2b2k3UFVEQXNvb2VqRXpzS2dpUVdDbXktdUNtVFo5TzU2VzR6U2pKaUgwQkFnTWVlVjdXcFNtQkY2QXptU3FJOUZxSkhmOU4wR0RleWRsek45Q3hyWVdMeTVUY0Q4Tw?oc=5</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2231,17 +2231,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Asia/Pacific CIO Agenda 2026: Five Predictions Defining the Shift to Agentic AI - International Data Corporation</t>
+          <t>Industrial Automation Market is Projected to Reach US$ 326.48 Billion by 2032, Driven by Smart Manufacturing and Predictive Maintenance, According to Maximize Market Research - prnewswire.co.uk</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 01:32:18 GMT</t>
+          <t>Tue, 10 Feb 2026 05:31:00 GMT</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQc25lUDdGME5BcXhGbkZ3bUwwWDUzUDdGODZKU3pjYWxqY2xCOGZ6bHBWamVCV0p2SzN2WEVyeWRMR0ZnYjFiOXJIdENvOEhlamhEbkt6V0hrTGJ5dFNlQkJsb3gwNHg5MU9PMmlmZWZyZXdrejQ1NzdwMThENGczcVRfS01FUlpETFZPbHdjN3k4Vkk3bHhEOQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwJBVV95cUxQanlHeEJQYlVqN0ZwQ2ZqeGJOMksxMlRsUlh5SEllOFhmX0NCLUpnMHFsWEV5dEZEeEI2VWZ1NU0zOGM1RVZweU1tcHkxQ2JSdGFHcmtWdUtLS05JdTBFcGpVU2Nzd3RnU0ZLTEVQSE9wYkNROHMzUmp3QzdGN1k1TDVjX01aZkdJeGdtWnZRdjZEZld1NDZiMHlsUmtiTHJfWFRYQklmaDNLb1VxTk9NRmpieWswWFlaM0djdVRNV05SemE2NnV0OWdPRTBneDdHYW5UVUVUWk93VkVLd3c1NTAyX2dyNUFQeXB6aGR6LTdLUWNEcGhjVG50ekFKZFhJenByQ053RGxUV1lCbkQxMGFtUGlFenZ4SVFrcEh0SzVjR192aXFsWjFILVhoOGgwX2NQZTFfbURhSEJOMFFzTmJVLXFQNGplT1lzM0RqUQ?oc=5</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2261,17 +2261,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ILO chief urges ‘human‑centred’ approach to AI and tech disruption - HRD America</t>
+          <t>How AI and automation are redefining legal practice - Today's Conveyancer</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 04:54:17 GMT</t>
+          <t>Mon, 09 Feb 2026 16:32:34 GMT</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPM2NzamQ0ZTBwZnI3Yl9tUVNrSjB1SG5qZ1F3RkI2dFU1eG1vbWo0SXY1NXo2cHNKaGNxNWxPbHlkUFhoVFlYYURxb1JRYnJWSlhBejIxVTVKckNRRlc0WUl2VmYyYm1qbEFRd1pSelpTcWpOTnJVVDZoSTVObnFQSllGWXJDZ2xaT21DR3VNamZhcHp4bXVvSTd4VkhZSEQxcERWbkRjTnk5T0M0YlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE5iSkhWdkxyZFNLeXQwTDlfbUk2MExjbFNfRktUUjhSU2tCWGZpd1NQVjhHMVU5eW5JQ2VTWEptOEs2dDdsUDR2a3JocENDR1ZhRUl6MHpkY005TGhpeEFONU5vaEJfNWdQbHBWb0pLamc5eWczQ3Vybnp6WTU?oc=5</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2291,17 +2291,17 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Arm’s Record Q3 Puts AI And Data Center Shift In Focus - Yahoo Finance</t>
+          <t>EU risks losing AI and space computing sovereignty amid Musk's plans - Euronews.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 17:07:53 GMT</t>
+          <t>Tue, 10 Feb 2026 05:30:26 GMT</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE5QTUZtQjA1UUhVazVRNWxWQkM3dWFxeGRFS29OX3NvTUEzSmJqeWd1cTV3ZXA2aW5OVDNjSVFQUENQYXdfRTBpMFBmcDU5eGVhWjNVRmhmaEZQQXZucExrYl9ZbmZZczNsMVdDNG1ETTFUaDNZb0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPN0FmN2NhWXJUUENlZVRDUWdJUVZwckszRDNBZEVlQzV2TGlxb2JGQ0ZqT1ExUFdpMlhKbzlXakhXMmtPZjVHS2JIQXpiXzhJSUhOaHFpQ2lFc2FZYnpjVHM5MnRXYk1ET0FfVmJKNDQyQUNWYjVrMV9uWmRxbG1vaDBDVzQ5QThOMVhETzZLVVozQ2RueXlfVHVVOEhQWGQ3UXFHWlBhRVpfTnRSek15Um44RlFJbE1neVZGcU5sTXhNWnhPVVloMDI1TQ?oc=5</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2321,17 +2321,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>STMicroelectronics expands strategic engagement with Amazon Web Services to enable new high performance compute infrastructure for cloud and AI data centers - Yahoo Finance</t>
+          <t>Council using AI technology to predict flooding and save social workers’ time - Hexham Courant</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 06:00:00 GMT</t>
+          <t>Tue, 10 Feb 2026 05:00:00 GMT</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOVlJ1VXZBakdYWF92c0oxZXNpLUYwMDkzZXpZelBuNVpfM29ta3JzZnNjU1F5UDdSZE9td2Fqc3lOSEota2cyN1lzdThySGlzMklrUWR0UjNyRlRCelU0V0lUWUFCV1NSSV9vN1lDOEY0TVdER1ZoNnozWldjcmg4Sy1RcEUxS3kwREhLYkhCa2pMSkJ6WnNnZ1ZVc2drYk5RZUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPMnhoay1PT3J2bkZDYlJ6YzkteC1lNVlOTno5YmRvOGh6VjlWUTViQnZmNXlIbmdiNnNhYUpVTjczUlNOanhLN2ljekZVMlM3aWxJUWdoRWxVa1JyTFVPUXBJVlFEVmwya2Uzc0hTT0IwNmZ3VEp6dVMwalNPaDM4SlRkV3hwN1VKcmxLMGFEOEdJTmJaWG1TdmttZVZHTy12OHdJ?oc=5</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -2351,17 +2351,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Apple Prepares to Kick Off 2026 With the iPhone 17e, New iPads and Macs - bloomberg.com</t>
+          <t>Technology and older people: bridging the digital divide with empathy, innovation and purpose - telefonica.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 05:10:30 GMT</t>
+          <t>Mon, 09 Feb 2026 16:30:00 GMT</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxQV0VaSUViVTlCVzBLbTAyMHZCaVVqbjYwOXRSYXhDSElBRUprMnFac0dvUWpDUXFZZ29LQVZFaE1ZeS1lR2xwYXljdS1oUEFDNkp4QjBSTVdRcWU0ZXlocjJCSVJCcHlrc2FLdEVDZnRhTVhBTHpzdm1sYlZ6NTFNLWViVjg4eGYwazhDWmZ5V05jcUV0akJGQWFuSUI3MkxPQnpPMDBSSU1RZ1FzQ1ZXRGZWcEU4UXZMZUhHUEY3ZG50WWhmMGhTWC1YRTJNWGdRWE1fcg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOSUxhWnJGSm5lTTVxZEszelg4NTlOYWdXYXBDLUxYWW1PUUZXN1A5UW9DV2JlbGRRQ3h5aDlHMDlmSXY2SElzS1JwZjJmRW4tSy1HMEt2X2QtMFFfcnBsLXY5WDFFMUdveUt3UW5RWW5qc21LUnNZWEZLd1dzZjJaejBNZzA2dktHbjFfQnhkQzRNTDNaOWNEN1Iyc2FzTWFYWHp0UmUtYWRfZw?oc=5</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -2381,17 +2381,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chinese chip designer Montage Technology soars over 50% in Hong Kong debut - CNBC</t>
+          <t>Students deliver AI, automation and digital tools to SMEs - Machinery Market</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 02:53:00 GMT</t>
+          <t>Mon, 09 Feb 2026 11:15:32 GMT</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPdVFNUDVPVGF3Ul8za0hZTUtvaWhRQjVLOXpfYzQ3VzVVazhPNEJpMGNFRWNSaExWaWd2OGZVWnlXeEZDTFJpQ0VXWGowU2ZuUEZLamVNcl93YkRmckU2U2ZxN255MzZaLUpETEw2RUcxZ2NOdzJQZ1JnWEl0Sm9BcHU3QTVXb0ZyR2p0T3ZfZFBDTjktdWZoQtIBngFBVV95cUxOTmVqSF9zWUplVnZrTlFpeHZtX2szSFBpY1g0TDc5a0dFaklWSjVVbndod290eHFSOHdhM3l4dFJ4UTNsWmlPSGU2ZHlmcjM4aWZEenRrZDUwS3AwNGhJckdsdDRGUVpsRGd6NWRqa2gtbDF3VFJMeE14anFXM2o3V3pqd2xiZm80Wmg2UEFtSk9UMFhRMF91LUhwa0RDdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPMG81OW9FeHBYQzVobXB0VDZyaUlQWDlNWEI2M0VGbUVaZmNUR1NZS0pQNEhYSWZWYkdpU0EzYkk0REF1MjVhcGV5SEtYbjI2MUtBYXUwdWZFWnduMGlfSUVxREd3TTdDcm1xcW1pY1FJdWsyS19uZGV2U3d0aHdKVGp1cUo4VnFXa1lmTVFCSVA0YXhSQ3c0ZlViR2FaeXlEYVlMMQ?oc=5</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -2411,17 +2411,17 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Alibaba’s ‘Wonder on Ice’ brings interactive AI showcase to Milano Cortina 2026 - Milano Cortina 2026</t>
+          <t>AI, edge and colo: Nokia’s Neutral Host Index redraws telecom’s $200bn shared-infra map - TelcoTitans.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 10:48:48 GMT</t>
+          <t>Tue, 10 Feb 2026 05:03:47 GMT</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQMG9UNnZkSTZpRnJJSzd0SXdmNXdqeHZCUjhpUEZIdE1abndGaV80dDM0czRfWlc2dkdLamhJTWxqcjZaRU1DZ0p3SkQ3UWJ4X0VQeHA3T3hPTTNVOE44OVBqWS1aNE91ZXFCaXNhajU4M3l1Zkw3VkJ6OWhEaTVvUUI1b0RTaW9qZE42YTQ1dTc2UHRGYnRRWlZmZjl4SmI3bG9uMVNjYTRBUXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOY0VjT243eU5FNXF5aUExcDlfR3lhRGd4NWxjbWRzbTZ4MWFuMk90TXpBb0s2SWs4UlNNNGxvczRYeW5qNDhYbnVyZFl1cXVkTXdhTktOZklVVlBscVJDY1lSU20yUjhKZ3h6eUVUUVhETm9xc1NlY2kxSUZBU29mMWZPaVlFT1o3UUdYVktjRFE5enR5cG4wdVF3cVdPUmFvS1JLTW5TWnF1bXdhT3JBeUVJQUlDalQyTmd2R2o2VDBzeFpLUGt5amltTEdxT0tn?oc=5</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>WISeKey's WISe.Art and GMA Once Again Revolutionize the Future of Art and Technology in an Extraordinary Event in Venice - Investing News Network</t>
+          <t>STMicroelectronics introduces the first automotive microcontroller with AI acceleration for edge intelligence - Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 06:48:51 GMT</t>
+          <t>Tue, 10 Feb 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPQmxMbWhMaFZrVXpaU2hzWlBsbHRsVHU2VjYzOHNOS3hiT2VaVGJkd2hDZHBscE9MQnpFbzNwNjRHa0NFYThGQzVCQ0hLRUZKNndpVGZuZ2JSODFVQ0ZQaXZDNk5OVTVGRkVnNmlub3ZLdUtEUEd6T040R0NNUGNYblpEa0tCTEFaSkVqb2w3SXhkZzJVdWM4V2s4a1p1RlFmeGl0RUxKd1BzdEszRzlSVEJmcER5c1lJakZkcXFnZURhWGVLVzl6NXVLc0d4MWs5UlJtekJiYnpqYXM2UDZTVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNMHVKaUo1Y0Q0TUVhMWZtZ3Q3bkJteUlPbFF0Smd1RktaZDVZb1dfOXR3Z0V1RnRmVjllb1k5SEI5dHp3N2ZSNlFJOUg4YVhwTG5vb3JfY1B3NXotZEZ4ai1KbkpMMUVESHFIX2VFYlBaYzRXYUw5WTNEeWxyb3pZNVFwVkhnMENWQUdGNWVuRkJmNXZwMF9zRmRNdHYyQkNiZVF0aFlsaUp5YWNOZGZJTg?oc=5</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -2471,17 +2471,17 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Worried AI means you won’t get a job when you graduate? Here’s what the research says - The Conversation</t>
+          <t>The AI Divide - Foreign Affairs</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 19:16:45 GMT</t>
+          <t>Tue, 10 Feb 2026 05:00:00 GMT</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQWkFUbWo5bF9XaVBOdmE1S05KUzlQTnAzT3lCQXZfQzFvcy1oNUliVTF6UV9LUU5rX3lZT24tVDlERTFxMzEzbzd2V0NXc2JkZXkzVnp3clZSQnhibXhTVkNOMjQ3TVJORjdSVy1TLW4tdmxac21tb0hjSW13VmJMRHZtRE04YmItWXpXRldhYVRHcFN2ZUZUMFBzTDBaV29OdnRyR0JWRTVnQU9hV05hQlhHcDBNZWhf?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTFAtd1A2ekhhSC11Ym9WZ3g4N1VhR0JSQ0h1Rk15ME5IYzh3MmVoQWl1THFhX2FuY1pUWDM1bDJUZVFZLVJtQ2F1dzB2akJxRVA0elVZSW9Yd3B3ajRVX3VXZmV5YjY?oc=5</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -2501,17 +2501,17 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>European tech strategy advances with Germany’s new AI factory - Digital Watch Observatory</t>
+          <t>AI experts warn of ‘zombie algorithm phenomenon’ impacting imaging - Radiology Business</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 12:05:36 GMT</t>
+          <t>Tue, 10 Feb 2026 06:05:29 GMT</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE4yenZzTkg4QVNGc0ZBUXlYZTczWHdNMDZRRzlFdm5hTVo3RFdDc1IwVzdadzd4RnZ2VkVlOEZvN2I0Tjl0Wmo2ZjE2ZzVkVG0xMGFJUWJUWkUxbWlQN0p1VlJNQU9tNm4t?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPOGFvMWNiTkRHcTR4UHNmaHRSWWlxb0pZcUpwVW16RG5aMjlhYnpCd29WS1NZQm8tdjQtTGNtSkZHYVlZLWVONjNia3BFWVF3a1lNN2Q5TUIwNVNTZjZ6ZFlQb1FRU3VpeDBSX3VjWVZrbTRoemwtMnJqVFM3UGVsc0MyUDZiY3JnelRiTDBnWlNfeWZ0eURTVmtwS3BJU1VRcUpyakpERG5rR0dkZHBxWVk4RFJ0eUtoZ3h3YmRYOA?oc=5</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -2531,17 +2531,17 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Pony.ai and Toyota Advance Robotaxi Commercialization with Mass-Produced bZ4X Robotaxis - Yahoo Finance</t>
+          <t>Google Cloud and Liberty Global sign 5 year deal - rcrwireless.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 05:00:00 GMT</t>
+          <t>Mon, 09 Feb 2026 18:37:10 GMT</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxONWk3Rm5kS1lDYWJabGh6Y2RhVEtoS1ZpRkhHUkhjM0ZucE1LaGc3MVFZNmhMZG11SG5TRDVtelh3ZDR1RFROVDZqb0tEclhTZ1FQOE9rVTlvcXA0MVZzNHJEcjd1dXc2UGNoUnRweUE2eGc4NU9fODJsUE5yOENNNGlfOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE9jRU54VVcweFpiSTlaMkJlWERhSERQeFhuM05jQkl3Vnl3Z25FR2xOdk1vVXNrWmNLaWNBOE1MS3FRdEdBN0R0VjFFQXpOU1EzVkY3TUQxYlZFcmltYXQ5U0ViNjh4ZEg3VWY4eVJFRnVQUTIwVEdVRGs2dHU?oc=5</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -2561,17 +2561,17 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Quantum Teleportation Was Performed Over The Internet For The First Time - ScienceAlert</t>
+          <t>AI model accelerates antibody production and clone selection - News-Medical</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 22:20:53 GMT</t>
+          <t>Tue, 10 Feb 2026 03:41:00 GMT</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNTFJxWTl1M1FGeEtCenQtU1BpSExHMXRCdjZaSXcySHdNS0NuVm5POG9XS1Y5dy1RNU9LRUcxZ1I2YUlucFI3WENEcFY4Q21WQ05lUENmVndfWll3T2RXZGRGSFUzOUlCM3RBazF4OVRBUG5XT3ZPMUNQVjIxdjRiZ0ZzYmdXSGhnMlk0UVlRNldUejdkd3lxbmJKam56VFJ6YlRF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNSlFXdTNWVktnZm5MWVBRcm5oaHMxc2l0U2ZwVTEwZGR1elctR0ViZ3p4dnQwcmp3MDdlN0FhcmE3SE95WkpQMk9sNHk1dVE3UVFaemNmUUJWSWNfVi1KM2RyUVpyVE1Ia2cwd3Fkb2hXZGs2c282b2FGc294WnluMTNzM19NcGszOHBHT1JKUllXcy1nTnowaV81OThnVzQtd1JocUJpRjFiNEhr?oc=5</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -2581,27 +2581,27 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Social platforms made €32m from scam ads on Irish users - RTE.ie</t>
+          <t>Special Issue: The World of Fluid Technology and Moving People - openDemocracy</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 07:00:20 GMT</t>
+          <t>Mon, 09 Feb 2026 11:35:13 GMT</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTFBoSWFOSC1STGRRb3NjUUMtZkQ1ck5zeFhIdmtJaV96azFnbDNPdVoyZHhRMjIwU29HblM5cjM2cDlUemx6UUVvc3o2UWQtdnpHMG9KOXAyaDEzVjM2Vk1DOWtERGNCVVhDREJZRWpPWnlWTUdTb2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE91SDYwWUFyN19MUmY3cXM1eWNkeUlhSnE4Y0U4ZGV5aF9FbW1JMjBOUlhDMjU2WlRxckticHFuZTVoZWRPaUxXaTFJWWwxcVY4RnQ4a0FjeURFa0hxTjdQX2RSckNkYk9KRGNQSkVIR3JEQQ?oc=5</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -2611,27 +2611,27 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Student shares experience as social media scam victim at Internet Safety Day - The Vibes</t>
+          <t>AI literacy and competency: The key to workforce readiness - Relocate magazine</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 09:24:00 GMT</t>
+          <t>Mon, 09 Feb 2026 15:02:04 GMT</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNUWVBSU5WQWktc29LY0wxbFNZd0wyV3dWV1VWRm5NTlZYVDRfWTRJR2ZwRm51TlN0aFplSWxHVWRoX3g5aDJTNU1obTVrTkZ6cVNrUkx4YVdfaFhBb25XNnRhQy1uTGRjeGlIU1ZnOGVRS1ZHbzBKaE00QkdWODhZVlVBVFNMbU1LeU43TDQ1R0g4b3MyU1Q2V2MxV2V5bmhldTRTeUtBeTJaa2NrMWVPSEZHd1BvTWpzQS1DM3dUWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQbEhZTGlqWktJNXBSd2dsTDJfSWhLOWJDbnpUcngteE15RUxDTklOTTJPNFNUVEhPT2pMYldVdE1feUhNVlhfWnRETzEtRk9PNTFENktTU2ZKSVBlMmY2WWNKZFk0UVZsRlR4VURQX3ZLemotLV91bEpQc2lSV21fUnlJQXJqYkU4bi1VVHdhejZxYzQwQXplS3VXaldIYTBOTTlBc0pKU1NkQ3JnakxkeXlyRHY5TEpQT1RtZzlTRUk0VUFNVVNTSg?oc=5</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -2641,27 +2641,27 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Trump seeks crypto donations in Super Bowl pre-game show ‘AI’ ad; social media says: ‘scam’ | Hindustan Times - Hindustan Times</t>
+          <t>Majority of young people worry AI will be used to make inappropriate images of them - The Independent</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 22:54:45 GMT</t>
+          <t>Tue, 10 Feb 2026 00:03:00 GMT</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxOQ3lsVnpYaHp5bXZKR3RMalBKUVlHdTJyRXZpUklwdDNJcHJLa1FpUzJicGZWM3lZNlR2ODUxTHhPNjBLYlgtZmQtWnR1X2tsT1BLOEFlSVl2M1BRVXJ3Ti1Zc25JUFdqNEVrMGhNbW1Bd25ubVZ3cGNOUWNwWlA5N0dHaVU3T3Y0U1N2azZpeXVYM2cxcDgtbVlmNkJYeE9pb2ZPejFTa0M4cGpyWHE0Sk1IN2oybjEtbk1DamY3SjJ6bmFYQzY1N3RVeTRSQ3RmVzBQWjBRbllTNDBIVWd2SV83NUJKRmRpZXphYy1aTdIB9AFBVV95cUxPU05sa3pSSHczVFZPZWE4N2tZRXM4MEtRQTdZLWl3MjlVMjctRWROMlc3Z0xLRlNrZDROWm5FUmtRbjhxS3VqcG5BdlNleXpKcDY3MmxsSUVWb09qUUxhaFNtdUpyQmhtY1Y1NWhLaW1kUzVtN1pEdnhBNE55SDRJWXRBYW1FTTVfbVZ1RmsyZGZOR1V6Q1VjVnFNaVZlMm9acm5uRjIyMTZtamxyeUZFS1J5TldwTFpUSXg0aVNMR1lzSDRLVHZEcDVlRGJoSk81TmJhb1RObmdBb3NsQlFYSUFqYV9ZWlFJclhNTk5SUXNPZDhp?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNZ3hhUXE3allXQkhlN0hOR2kzNXNIRnMwX3Bqczh4c1JuYm1vR1hkb2hxVEZXc3FoaGZQU01nM0ZySTExMFVqVHhOZkgwbnhqNV9KZFNCcVQ3alFuVXFkWkV6aS1lTFRFdC0xc0dnVlJPMmF4ajBMQ0Z5MU5yUnlNWUw4X3p1X3pNS2FyRjZSN2ZqSEZmV3FDNVo2VFZmUQ?oc=5</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -2671,27 +2671,27 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Oz alleges Maine ‘looks a lot like Minnesota’ regarding entitlement fraud - The Hill</t>
+          <t>Looking At The Alibaba Group Holding (NYSE:BABA) Narrative After Mixed Cloud And Retail Signals - Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Sun, 08 Feb 2026 12:00:00 GMT</t>
+          <t>Tue, 10 Feb 2026 01:11:00 GMT</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxONlQyU3Z2b25RMk9UaDhXeUc5bm1oTHlNU0l5aDdubkJoU0hpQkVpbGxHNEVXOWFuWDhHYzdMYlY2dWJ2YmFjS1hyakRjekUzRmFsbTN1ZVZzTDZrRU5VLXVOMWdKQk9DRmJWUDJ5X1RXLWc4YlJ0NFJJU0didXl1RFJLZ9IBiAFBVV95cUxOU1h4b0JPdUhnR0RwTUFiUVVvaGtYVzhhVTJuMTR0d0o0bmdKLU5aX25iZFphQ2hRM19pRU1KX3ZYRW12SGdaMnF3dTVoa0tFZHhKeWRBajZneVhjdFBfZVg2bGs4OXdOYjdmN2xJMVRFR3BpNzZOZzU3di0tV1RvYUtRcG5DaG1I?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQUG1ja2ZsRG9ZVDU4eklNTng2Unhna196ZDFheW9PVm9YQ3lBbmlDVXdQTkVaQloweGk2V0RJaERBdUM1dWFYa3pOYkI4eF9TR1VuOG9kNGExV3MwM0kzTlB5czJnODZaVVFMTnNyNEZvYnZQZkpySUtQXzV1djdRNmdEUG90b0RGbHNN?oc=5</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -2701,30 +2701,570 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>AI chatbots and competition law: A look into the Meta WhatsApp antitrust investigations | Insights - TLT LLP</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Mon, 09 Feb 2026 11:56:19 GMT</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPb2h2MFQwRHpQS3NuZG9ra1BZWVJtSEtXWGo1SVBaRFlzbWlGOURBZWxNYWNZMEdHZW9EMzRBU0FqTHBFRjB5T0xsTWhfQTJsZFFaVDdrekVSUUpwNGVxZ0JOQnpWWjAzY0x1UFgtM0RDNVBXT2NlRXF1Nl81c0JEZGNMTWJPWEZWTDVOR1ZGRkZUSXYtQVVRUXJFbU9VbEUtckNQbHQzT0NTQlU3cUR2VW85ay1wREVmOGljNC1oTkp6YW5zVEwxYkRDZVNFTjA?oc=5</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>’AI can be helpful for learning if it’s used in a safe way’ - The Mirror</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Tue, 10 Feb 2026 06:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxQMUFqZEVsTFFwUHZXdFlJTklQUnRDUTFQc0pMMWFESWxzLUxtMkFyTmVfS2cwNjJnUVVrN05taW5taFpWRnVCMWU4eUNMbXhfbmRBVmdTbExvRmFLVEFlWXkySW1UdzBIRDk1T3pkTFpINGdQc1h6TG9vUWVaMW9FZHJQQVrSAYoBQVVfeXFMUDRjU19CQXdSczhFY05JTGFxNjUydG1iSzRuNjlJOEp3WTlYWXhXUzl2al9VSUE4UTI0VGRNNmQ3OHctWmZvOEhMSURGX29GRUZYTVJXZ2NZYlR1ZXBuX2QxOHNEa1V1Nmd4Ui14NTczNlZWWGgxekZvMmd2RUVSVHJaUWVNRVduY3pB?oc=5</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2026 CreaTech Network Series: Creativity and AI - The University of Manchester</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Mon, 09 Feb 2026 10:41:31 GMT</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNeU5KWkxMT3h1MUxUUThXd292MElQcktjUDhNODh1RWl5V0JBM0R1bVlXQk9TZC1vSktuNHV3QzZqMjJuRUpNVWJLWjU1dlRISC1oV292ZXpDaVJicFRQaVBUYmI0NmVYUEE5aUZtOUNsODdFb2xGcGtVMXh3Y1lVWXprbWN4V2JBZ2Q1WXZldkc?oc=5</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>AI, homework and friendship: Why more children are opening up to chatbots - ITVX</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Mon, 09 Feb 2026 17:00:53 GMT</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQTU5BVUZ3dDNqNXBNN3ZjNmtDTXFQWXFYQ0M5X2NEdTEzVXlaR1BOdGZxLVlYX1N4eXI0aEJudzhHcTF0NVQ2WlFqR0RLQVNEbnlEeGR0OWFBVGI3QzRnQTh1dzBzZU9zcllzTm1rbDNySDJwNnR0b1V5MVFJY2dhMmF2RndnZW1PdjFzbnRUODNKRExpcF9nNVJWMGR5UnQ2WkEybEJTMUNBLVU?oc=5</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Academics moving away from outright bans of AI, study finds - Times Higher Education</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Tue, 10 Feb 2026 00:35:17 GMT</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPMzB1YzVsTUhjUzl6b2M5cC03TWlyRWdCaVhxeUJhZ1VuV1BjNlNET0VxU1dtUXdmR1dFNGJSeGVWZlNuOXV3MHBrbExzaGV1UWoySjBtYlFjQXF3TUpTLVRYTWFxTm9YRkNudGx6UEQ1cWxJTl9QbUF5RVhBdXd4SkdWTnB5b19hR1NQREh5M1QyM19lSEc4?oc=5</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>From Quantum Threat to AI Exposure: Why Security Is Converging Faster Than Enterprises Expect - The Quantum Insider</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Mon, 09 Feb 2026 13:36:09 GMT</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPeDJUSjh3RUhVOGc3eXhGRm1nbEVMRWMwNl94LXlKRkh0NjFDNmNOdHNySDBfUHg1MmRMOFBOVFBYRGVpU1Y3RGhWOXNvcVpvU29tVFZfblBjeXFBUXA1MWlTSTF1ZXVZUEJ2akNDNEYzNTZzbmJ6clMxaTVyYWw0a05Zb1hCU1k1cGNaWFR3d0dFVmJ5ZllmOWlNcEo2TktDVTJaNmpNOTZjSU1nd0YzNHVSTnpxT3VUdk5mT1h5NXQ1YUhWY0JFR0tSRkZUWFU?oc=5</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Datavault AI Sets Bold Revenue Targets With US$150m AI And Web3 Plan - Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Tue, 10 Feb 2026 04:28:00 GMT</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxOTVlKRjBLWi1nc1pPazNBX3lIUHBRT3kwNHZRQmEzYVBxUGFjTGhKbWZubkNFVnVxYlNEZFZ1U1VhZ0JaS3R6eHRNTDZuUjF2NjQ3SlJfc1JQMUcyNDJ1YV8yWS1tdjVmamhNdWpLZ3hVclhYSDk0eDJ1UGpRMnM1YllR?oc=5</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>US software stocks tumble sparks concerns that AI trade is reshaping markets - Reuters</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Mon, 09 Feb 2026 11:03:16 GMT</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQNWU2VDZkT1E5TmdpMXF5MkRqdU0yZ2VqN29iZ0dQRUlQZFRCMjVWTktEOU9kM3dhSDJUeFQ4NVZ3aGZrQ2RtSkRZYUE0MkJleEcxbnRQTDFFN0FCdEtJUTY1eUlKY3JFd2pJcmhHRjZ1N3c5aVJoRlI1LXF2RkNkaWQyc290X0tSMHpmQVlKbDZNZ1dISDRrcmZaSW01OTZYSmQ2SjZyamV4RFV5dkRYZ3lhMUFKbkp6Q3UzTDZzNmlUazZWYU9Ra29UZGoyamp6?oc=5</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>£10 million expansion to Milton Keynes data centre to support AI and advanced computing - Milton Keynes Citizen</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Mon, 09 Feb 2026 09:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPb3VqWks2ME96azdCVEdFVTVQbFpGU0hMMzliVEhiSEo5ZmZiOHJhdTBQZzBadEt2eURkcW5OQkR2TFA1Q2tHOUF2TWh6Vld2blFTQVRxUzB6OHFpNUFZUENqZnphaTlpQmQ2UE9GTjdDR3RyZzR1X1dna1JFdkJZVDdzTTFaWlRvNFM3ajFoU3J4NGJ6NElhc1VMRVpjekpTWGVIOEZEek1hTUM5cGo4NXVMeTI2Zjh3UkYzYVdFWTktSTJOMGVlRGRXbGdMa25ja0FVM19R?oc=5</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Science Minister says AI can bring stronger North East communities and renewed pride of place - Chronicle Live</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Tue, 10 Feb 2026 01:08:00 GMT</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNTVVFMDJWRVJKNG80cW1pX1FJSWFxZ1FqRlUwMmxoclhqQWJETjZTOGJ4dml0NUFya0hYcEtJcnRHV3JuQUVFMHU4ZkZhUWdXTFJhQUdhVlhqU19iMUwwZ0ZNZlhPNU9NcWM0TnFmbnNMdEpMVXctSS1IUFhVcU8ydGxvMnZva3ljWWlvc1h6aFBtRW050gGaAUFVX3lxTE1IQ3dSejV6V3h6eTZJQzl6MDlXVG8tckZ0bV84Z2ktNE1IUjFyU2gwSXhMLThGS2xadElDYlJ3VDV1d2xkYklKbGhyT0haWGtYalR0ak1XelB6X3BkUXI2TE9mZ09BZ2tPdWkxZ0s0UHVkQ3ZtUHJfc0xJTVlSRGNhaVJTNVdUbkJOUF94cEFpUlpMY0JHVDNTWVE?oc=5</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Experian caught in the AI crossfire, but fundamentals still standing, says UBS - Yahoo Finance UK</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Mon, 09 Feb 2026 14:12:00 GMT</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOTTJiQXQxY2RlcXdfSi1WdXVUVUpiV2I2czhyOVdFNktZWjVpLXdDd1lReFhINEFTMGFXYk5naHZzQXdTSDgzN0k5N0tRRGdBYmV3czc5T2VEQ1o0TWE5WXpDblBITHNmel9LNU5iQTl3ZnJRTEFIb0hteUg4X2llbWlGTUl4TkZLUnFPNUlwa2NORmd1?oc=5</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>As AI enters the operating room, reports arise of botched surgeries and misidentified body parts - Reuters</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Mon, 09 Feb 2026 11:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxPb0EwdkM3R2tVX2RwczFRZFRnUGFBYlRoWG1Yb0d1Ul9XVHNvRUZzVnU5VThqZ1ZUVDFhc05SWG0zWTBDa1ZKLW04TXA2M1JHOGs1elZISTBhaHhvd1pGR05xaldGQ0xtRzNZUElvZk9IU1BIOWlLVDBIV0FZZnZ3V0lickNVbWZ1TWtPcjJtMHpFQV92QjhoNk9jUWFRcWIzZjFmV1cwYmRZRGRFR3Y2TU5CXy1STmZ5SkU5LVpyUDNCbzk5?oc=5</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Intel’s AI And GPU Pivot Puts Valuation And Momentum In Focus - Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Tue, 10 Feb 2026 03:10:00 GMT</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1oUWF5Ny1CX2ZvVE9ldUZzal9ZRlc5dDFhTUowaUp5NUFyVVIyRXhyd280QmlwU3htbnBsMDJqM3RzRzZWZ21zQ215SU50NmZzOEtWODVYNFZhUlY5TGhGZ3YyNDdxVmd4OENuaEZwczFPUVg2dUNjQg?oc=5</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Insider_Risk</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>The Modern Insider Threat: Shadow IT, BYOD, and Trade Secrets - Seyfarth Shaw</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Mon, 09 Feb 2026 20:21:58 GMT</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQVXpXMVN1NDdoTk1QcldHSFlsWFVPa21BZ3JqeUltQVRzdDU4NlBGUlNLUk5EdEp3UWtJYjZDbVY3UE1CSVp3YTNqZzZiZWVIQ003NFNOcXZiMTlFZnRNUWxKdkJya1g5S09XeW1US09sWDl2cFpwenJHc3Vzb0F0NVBWMnFaWXF5cDNjV1Fnb1RHQUltYjhnZWdqU2ZGUFl0TnN1UQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Insider_Risk</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Inside employee misconduct rings: closing blind spots on fraud and theft - hcamag.com</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Mon, 09 Feb 2026 20:41:28 GMT</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQRUdUM0FQWkpUVnBkbE4wbzJGZzRCSlNrTDNfN05vZjE2RUktWWtVZ1VzTkhXODl5UnZzQUpObEllWVFDY1FQWGJOSzlzT1B4NExmWlFNSmhpZjVqNzRfU1BiUXQzZVZYNVhYNTRNSV94VTlTUTQwYlk3T05WMW1YQlN1VVM1SEhFTGJYNjA2ZG1ud05TSDRVak01Nm5HLVJfM0NZcXFrNnZLLWNia2pWZTd0MUh1OXliak5qTEZ3M2NyNjdmMlRMNDFIeVg3ZkU?oc=5</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Insider_Risk</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>SD Public Integrity Unit fields 47 complaints, 4 criminal charges - aberdeennews.com</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Mon, 09 Feb 2026 09:01:00 GMT</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxOZ0o1WjdvUzZQV2YtWTZDc2JMU3RjVWtPUVhvOTlKYUEtY0FzUHJXWUV0eFdtYlZzcTJXSzFNeEJiZjNHQTFvVEZyTkNFa1BVWUlSd2lOa2dkMW1OSUdaSU8zQnItSlk5dXN4T0FJb04zd1ozWHRXdENzTGcxTVp5cWo4MnFZbkxiLWpMc3pMbktGdXZLWVhFc2Q3bUkwc0tHQUE4WV9ZTHoybTFRLXBPaHVkbFVubUlnS09mam9ndEZwOE1fMnBUd180M19YbGZteS1IRGFjN1ZkMlVVOHA3SzhzcDJxa2pieFNYV2dsZVdTQTBfeEIwOF9zaw?oc=5</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
           <t>Fraud_Scam</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Abu Dhabi court orders man to pay Dh194,000 for social media fraud - The Filipino Times</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Mon, 09 Feb 2026 03:40:17 GMT</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPZXcyOUZDbDloNWFVUVFIRjVaTzhVcDcxVmFxVWlkX09jLXNpRVV6NF85MVk1RTRjSzR0OUVuc25RUk8wUzlhUHo0WDU3ZFpnZEs3VVI0eWx4SWRhcWE3Y1VLZmZydTRCRDhXdGFFUEtSMUUwWHpjazAxVWpXS1RvZmR0cTU0bVY5RHlLNnV5cGFKSE50S0tucUJ2eFNWUE1lNXpkaFpVQnAyS2hYTFZ5cUtMYWh3Zw?oc=5</t>
-        </is>
-      </c>
-      <c r="F77" t="n">
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>NEWS: Social media giants made €32m from scam ads aimed at Irish users - AML Intelligence</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Tue, 10 Feb 2026 01:59:17 GMT</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQMWNXbExxZUxfTlJ3SmlYVzVvcVRqMWNjbVV1N2F5bTJRdzZ6ZTBiY04wWHJhcjJkMVlqN1dDaC11eWxFekgyZmVCS2pSZ0dWeENMWngtYXZDYWY0WkhhQ0pPOGp3dUJxNnVpQ1oyZUk1YmNla2dxdUh1TzRQeDE5UUtvdHE5c24xSU5lNU9jX1NsNFp4RkFES2RlaG1lc3F0VXFvSV8zY2taMnBWN0Nr?oc=5</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>ESET Threat Report H2 2025: Phishing and Social Engineering pose biggest cybersecurity risks for South African organisations - ZAWYA</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Mon, 09 Feb 2026 10:50:43 GMT</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxOdlRIOHdKYXA3V0l4SWJCNXQyQmVYSUF5WXZmWG52cTRNcTI2cXJwQVoxMzNXd09VQzJYNzBUTldaVEd4cjhuX1cxRVlxM2VhckRINUp5a3JkSmExZXd2bUp4NzNxcEVRQnJ1VG8tblg3NDRGSnNscEc2NlJ1eUg3dFVLcF9wWklpVnVrRTlCa0NDczBveEQtSEk3c2xNSFdvT3VwVHRKU3RQanFpdEx2a1FOOGFhZE9VbnBtcHhLYmpMN29wajQ0UzZYYjVlZW1yZi1wUk1LSUpzclc4OHhkckF3TE9QcWtnaUJDRG9URm1aYmJHSVVZZWZtSHNIOFF0TWc?oc=5</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Hidalgo County warns of social media scam involving vehicle registration renewals - KRGV</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Tue, 10 Feb 2026 04:40:03 GMT</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQRVpvaFJKRlE5VjFOSC1PRUliTndNSkM0dVdudThnOFpYTkZkVERXcWpGVm5KdDR0LWVVUWhKS2ltSldLbGI4VS1XRGhDZGNGTjBlLXhWYWhNd1kwdVl2VWtUTE11ZVNvXzNhLS16OXFjSnJ5WThXbEg3ZzNkU0R4Q2w5Wk5KRUpkQjNsTWRLeGdNUVJEQzVNNGtCYk5wX3U4ZUZBbWpiUWszQ2No?oc=5</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
         <v>1</v>
       </c>
     </row>

--- a/data/daily/topic_feeds_daily.xlsx
+++ b/data/daily/topic_feeds_daily.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F95"/>
+  <dimension ref="A1:F101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,17 +461,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Importance of Natural Capital to the Scottish Economy – Regional Analysis - The Scottish Government</t>
+          <t>I got a copy of the Beveridge Report for my 80th birthday. Every government minister should read it - Big Issue</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 09:01:39 GMT</t>
+          <t>Wed, 11 Feb 2026 04:03:31 GMT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOTEJxbWVpdDlUUHY2c3hNa2huaENGUmtQQ1lfNTFaMDZfZ0xOWW5FaEhEemw2U3BqZS1PR2hMOURLWXNSanVNSEdXUGVNS0ZJcDlnVzlLYjZWYnFOeU9DMHVmQXZydGxKdzhKWmsxaXFxb0RHajMtY2N2YWhyaVdKZUVKcnFucWlOdFROczJyOXpiR3hvTW16RF9aZVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxNRTNGMzYxRFl6cVJCZXNhbWlPQ0ptbFhpdXpHSWJFMDVDTXlRcnZ2MlEta1l2c0poMG5od19neGJURDE3enVKVUdqdHdnUmthMjJ5dVUyWXQ1aExHeHlqMUxDb25QYnYxRFBFb0JjU2kzbFRhdXdydV9GamZCd0VieHpBSQ?oc=5</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -491,17 +491,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>HCLG Committee report on social housing conditions: LGA statement - Local Government Association</t>
+          <t>Policy report: Mapping the EU's long-term budget - The Parliament Magazine</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 08:46:43 GMT</t>
+          <t>Tue, 10 Feb 2026 16:54:05 GMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNNWxxSjhkQkF0WUZ3d3dzNUxCQ25Nam9rWkhzamg2MUhmRy1vWlpNbjhnRDRibE5aVnQxQ1NGQzJWQ0NaQ0JWX0FoMnlNcHNUbjZxZjdGSEsydWI4LU9PSlctVzBmWGVlSHlSVzYtazM1UXZHQWVNX1VWQnhoSjRBQzh1b3M2TDZjS01INFlaUGw3WU1DbDc4UzRLQ1pJZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNMGZ6b1RSQVkwOUVLQUFlYk5xM2wwMXA0ZXpqb3lTNm1hSm9jVUlqZDBSVmk0UVlpNXlxeFVEZ1A0WHlfTGdVU1JVVUlmdUtZRFdoWngtU0pnZmNXelJTRklfemVCbzRrNzRVT0tXMzJwcVJuNmw1YnRSaGVkcWtycmdValByeHNybWhVTEpGWE1qU1dib1o5TldkZ0tsVkU?oc=5</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -521,17 +521,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Briefing: delayed elections and council tax rises - The TaxPayers' Alliance</t>
+          <t>Situational Analysis Report for children in conflict with the law in Egypt - ReliefWeb</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 08:28:40 GMT</t>
+          <t>Tue, 10 Feb 2026 12:03:47 GMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxQWnl2NTJwYm9oa2hsRHdsSXlYdFNGZ1RVME91dU1rSkk4RVVEQm1DUF81N2ZOcVRYMkNhcE5TdjZ5eVVBMWhGaWVkd3pfOVNhQzQzTG91S2ZRQzJWWTBSbExhbWVkZXRpcHNuVGR4QmdsbFNLcTNiZ2dWNmZIYm5XVlBnaS0xZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOOG9HemJ4S244MjBJYm81WG9WUlZyU0lMME5qNzBOMHZ3dVBtSHhfRnhLcGF6b1ZVa3ZnSjMxZ0p5Qml2MkV5MFY1TDBQdW5nWFpTdDVBenhvRFNHazl3UE5hU0J4YUJXZHVQelJTZmxBTkk4SmpVNmZPOEhicFE4R0U1LWdOaUpuZ3VfVWdqSzVMUVdW?oc=5</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -551,17 +551,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Villeroy's Exit: Minimal Effect on ECB Policy Direction Ahead - Global Banking &amp; Finance Review®</t>
+          <t>Internal DOE Documents Confirm Climate Report Was Created to Justify Administration Policy - The Equation - Union of Concerned Scientists</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 16:08:24 GMT</t>
+          <t>Tue, 10 Feb 2026 14:18:01 GMT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNTG9uMGUzRHBLNVZzWjJiWjRnMEJGV3lRR0MzaE5Kb2xwbWR2eEVKcXRZY0pvbHBVN0VrMzhZQ050WHRYbS05ZlpJV3VCSjNiNi1OVzNsYjB6ejZSUVBSeVRYb2NEc052REU2OU0wV0JLbVY1QVRPdnQ4LWFBenVMU2FtX0VkMjNmemp4N3NpeFJ0Y0ZPUXdnQjhacDM5XzQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOTEVzMVN1MXlMSldHTkdWMnBvV0p5MkhuNXd5MU1aZ1R0c3QyenhYWm9CRFp3THdYYU5XXzJnV2I3S25tRWVfZk5jZmlvRXdfSTRsUThZcHRrUmtkVU9BMTVYenhmcE9mdWljaFBRM3hraC1VSTlZMmRZbWoyaTd1ZU1KN0lSM01hQXhlV2VIcFNUQjZ4NGpjaVFwdlhLSzNJVFZaM3V5QUpOSktad2g4UmpORk80bEMtSkkyNWNXYmgxZ0FtRkJB?oc=5</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -581,17 +581,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>The Government’s clinical negligence report looks in wrong places for cost-cutting - Jonathan Baker - Yorkshire Post</t>
+          <t>ICYMI - PBOC pledges loose policy, ample liquidity in Q4 report - investingLive</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 06:00:00 GMT</t>
+          <t>Wed, 11 Feb 2026 00:27:01 GMT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9wFBVV95cUxOZkp6NTU3U1hEWmtFVWhDYndTMkN1RkZxdjlfNzZhMm9Odm8wSUhYSkZEM2ZQb3F4emk1ZjBhVzhEM1hvbEtUN240bmdvcmdQNzl5bFVLaDY3RjMtV1hoYUZvUWpXMmdPVkVwbmxjUml0QkdxbEM0anFUeFBuQjBZckVRcnVybmM1ME5VYmdRQ212bzNmNmlodFd3ejJORThKdVlJWkRzQmZTOU9SUEpHM2YxajVyYkFza0RQcUZGV1pPNFQyX1Z6bFo3VzBfMWEtTElvSWNic0FzLWhLS0ExWGV4ZS11SVVjM29pQW05VmhqME5nSkpN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQV1Vvakx4ZHRXUlo2eUZScFhzNjl6emNQZGZoanNaOWZDbXl6Q0cwZzYxbUZGZEF4QUJnNWRUNjVURF9GVW9qSTBsbWs3QURyWWhPaXlWbUlDNGZ5blV1ZVM3SGI1MDF2NXo2dGFIZmoxRExoczBGUWVBUzk3QUJJWVo3cVo0a2Z5enBMM0oxVnRjSzJwU0FqLXNDN1Z5WGtaYzRKNjctYWI3M1Bw0gGyAUFVX3lxTE1nS0w5TVc3R0l4WV9MMDdjdEdzTTVNMjFIeC1DZHp1cWs5REdvdTRVSWxrczhzOWlPQ0VUdm11Q1VKanNINjBPcmJGdWZmZ0xfcUZTTWNqT0k5RnNOWmpaQ2czZFBnTnJZZjAxZ202eUI2Z01vRWZnMGFfRWY3SGJOUnIwU1hxUTlJd0VQUGlmUXg2UW9BM0JkVFJJSG50NXpSemJkdTd5ZjFvSDhZMWU3QWc?oc=5</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -611,17 +611,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kuwait adds eight Lebanese hospitals to terrorism list, report says - Middle East Monitor</t>
+          <t>OpenAI policy head exits after discrimination allegation: Report - Storyboard18</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 13:09:00 GMT</t>
+          <t>Wed, 11 Feb 2026 03:22:38 GMT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPLUVSRU95aml4WTBlMnlvU1JOejZnbzZON3V6aGhDUnlwQVVyR0dpNjlKdmV5NGJtVjNOUmFkaWxyeENaZGVoNzhreVlpUlZmekFabjdZRk95UXdhaDRBOXRGemhVR2c3YUV4aTFXRU1hQk9nSll3a09EYzFuWi1LUzJaUXlweUZzdVZKWGg5TjgxRXQ4UWNYdFdDblpTUXdpNWVJYnB3RU42NkF6ZFJz0gG0AUFVX3lxTFBsUXBPbDZQcnNwaGVOVnMyMXk3V3pMZzBDNzV1bjNHTjR3V1EzcUtTekdwcVBjM1lObmhNdjB5SWR4YXBocDRzNFdEUjRaczhWUjJfRlZ5Z1RSRkhnbExGZ2dOeVRrSjBNejl6UFVvNXhkOE5vV2VhbzNUay1GbjltZmFtaTA3ZG4ycnI3TUN1UlI2aVhzYVBvX3E3WEJ6ZmNlQUpLX21kVUM5eHdDaEtIZEtYVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPN2ZxVTVMR25DTWhUYy1xQTdhNkFJUFRMYWxaeElsWXhFMHd5X0VqekhrS3IyQWdYQ3RkS1NZX3FhdFM0ZkdsdlJlT2RjejBKdUdPamh3M3lhX2lxMFJvTDVQcDFjRU5vZEl4NUFpTFVJLS04WnF0dVFMdEZUdmpXVExENlJUZm9tS2w4NWZCN2VzSjJ2NXR1cUFRa0hhcWVpUnRkendxb05BZkZkQUhR0gG0AUFVX3lxTE43S19McW4xTWF4OXMwZG5LVUZtS0d4UGtDQ0ZOSHR6SjRFWERKSnpZbnVVb1paWUpjNTF3TndkUXVnV2otQUxuMWx1MzlObVZFbllGekdldXJuWXczRGFHUFJ6OW1mTDlCSUNWYnUwOHYtTm5KY2QtdjAyRmVIdE5YdE45VW41aTUzN25Bc0t0WE5Od1k3amRWS2xSaC1id1dUejRXM3lQdXpNNDY4eWtKbWdoWQ?oc=5</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -641,17 +641,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>What to look for in the delayed jobs, inflation data out this week - marketplace.org</t>
+          <t>Euna Solutions Releases “State of AI in the Public Sector” Report, Revealing Where Government Agencies Are Finding Real, Measurable Value from AI - Business Wire</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 23:32:59 GMT</t>
+          <t>Tue, 10 Feb 2026 15:54:00 GMT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNdDZhNmhocXk5Sm15cHdyamdRMmlqMHdLZ0F2QW5sSTRtdWJLdkpoMVgtNXRZdHZBZkJrTE01VlJPejYycE1mbDhZSFVsN1VRMVNpXzVaTTRsZ2p3ZUFiMEt1M3hMY0xkZnpMS3c0M3lBWk10NTkwMDJsVXVJSE5wbjdVZ0RlaDdhSFdIaG55VEN2MlNJekxZUG5tejNzeVFmSHR3ME5xYnAxcjFNeUhZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAJBVV95cUxNZFU4aHNKcDBXZDI2aTRQSGswZG1mdFRKM25xVDdqV1lyb2wtdXBVSkZuT2lWRjltY3VBT0ZaRE8xY0lKem5zRlh6Z1g5cF9VbFRORndCSVlRQXhXZUVKRFB1V2ttcF9DbG9NR29YSC1LTVFKTkg0eS11bkRfcTJSc253ZlM2Vjg4X3dhOVFRV3lTQmZERTYxUUdDeE15bXBrV3BQZHdaMnpmeVZjWXQtR1Z2aVF6T2V4OGpUN2JQWjd5aE5mcENwU3U4QjIwcE1aT2NrSE12WUlOX0wwUWl5Z2Y4ZWhvQWJjaFNXYm41M0huR1MxeVl5TVpBckVxRTVDMTZGd1F3RDhnM240a3FKbHFsS2N5X1BCNW5LTVBheXM2RHVH?oc=5</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indian migration boosts deployable skills for UK economy: Report - Deccan Herald</t>
+          <t>South Sudan: Conflict in Jonglei State - Flash Update No.6 (as of 10 February 2026) - ReliefWeb</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 18:35:14 GMT</t>
+          <t>Tue, 10 Feb 2026 15:50:57 GMT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNWE12SXYzSHg4S3AwQjdaTi1NMkZoUm91YlZxVVlCaGRCYVZ3RDBJNWtqcWN3MWNxRzJXUzA5aExxS0RYaV9PRGRlLWlnMjc5REdsd0pjdmJSbWtOcThOdmhSRlJ5eWhSWnpaMXUzZmdzczVVd0E0TVBSRTJ6Ry1rT0xZLVkzaG4yLVVDbnc2c3laSGhnX2ZzTzdlc0R1QUJZM3o0d05zS1ZjZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPLWFMYzUzOEt3a19BVzRLQThYZFZYM3FNVDZKelBweUhlbTFCcnl2aXkzcTltc3p5TjM1Ym5lWFFsbXJTbjc5Wl9rVThORm1NeGt6MmRCUXpzY3lhRkxEWDZEd0Vpa2FYYmFvYTBqWUxzbHFIa25ZZGxGeGMzOEtLUEFuN3ZxSUQxMzc4bHdqSXVBZDVuRFlHejRvS01oTDVwX3MtRFJFbktnbTROQkE?oc=5</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -691,27 +691,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Current_Affairs</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Crime Report: February 9, 2026 - Arlington County</t>
+          <t>Sanctions-busting shadow ships are increasing - the big question is what to do about them - BBC</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 16:43:51 GMT</t>
+          <t>Wed, 11 Feb 2026 00:17:37 GMT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOdTlaTUt3bzZDbE5sSFlFRzNIakJ0dEMxZlBjQU5reFhXZFlIVlBGVEpKUUM1TWpsQ29OV0czdzRHV0Vrd0JrWkhWRl9jOFlSUUp1YTBiaF9HZHdLUEpLdUM3LU0yU1BRUHliV1dZSFU2azdDbFZsU0N3aGNUMWZQUUhCTXR0SWt1YTlSMVFuY3dWc0tlc3F6b3ZB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE8tYnJWQ2piRzNBWlg0WUZQZ2NCWnM5VTMzNXJaSFowbUEycXZySGhmMElwSC11SThYU2FLdUxtaFRteFlsM01YTVZMOUtUVVgxX0s0Skkxd056Zw?oc=5</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -731,17 +731,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bangladesh secures lower US tariffs and exemptions for clothing goods - BBC</t>
+          <t>Tariffs and falling demand leave Scotch distillers under pressure - Business Matters</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 03:26:05 GMT</t>
+          <t>Wed, 11 Feb 2026 07:13:24 GMT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE00RDA1ZHRVYXYtTkpxTXZoSTB0ZDRtSTB2VzdNdnVyMGR2NFBKV3JuYXhOang0ZlUzNS05c181WXpmQlNaeEpMUFpSMVdjWEZLNnlOeEtFSlpqdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOVkYxY0JNREhERW5tdEo4U1FVS1ktUFJHMGZvRFlBLVU2cXpmLUxka0dncjM3MEpoMWdHZ3UyM0I4SE56R0N0TWZBb2xqWUE0NFdXWHFja21CTFdobUR2ZWJyOXU0bEhaWEhYcWQtR2tyeEVKWGZkX29UUW9UTUQ5NnFZaG1MdVpYY3BScDRMamV5dmsxZzNZ?oc=5</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -761,17 +761,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US plans Big Tech carve-out from next wave of chip tariffs - Financial Times</t>
+          <t>An Invitation Into the world of elevated luxury logistics - Air Cargo Week</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 23:27:26 GMT</t>
+          <t>Wed, 11 Feb 2026 07:30:23 GMT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE02QlNTMVdWQjVZR09sQ2NhdS13SWtXSmRETzhRdkV1Z3pLZFAzSmRqaTNZTWEwb0pMbUEyNkVfdFlDNVNkZXhfUTlyRkliWUsyZzZtTkcwNE5GUGZvbkQ3azNDRnE3UlZYSzUyLW91RWY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQWEtnY1F2bFNudGFMZ1I5WHJ6M195MXI5U1dSekxlcDREa2tDaDFiWkhaMEpfOGM0ZV9aNGVyd2NKajlYZC1heU5nRUF4TzdMZG1tOWlrcG5HS0ZiOGJTRkxYc2ZQWW9oeG1odVF4MlRlQTFlMklmbl9RaUJMNEFTakpSam9wRk9aeE9B?oc=5</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -791,17 +791,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BELFAST HARBOUR REPORTS STEADY INCREASE IN PORT TRADE IN 2025 - Belfast Harbour</t>
+          <t>US sanctions officials from Marshall Islands and Palau, citing China fears - Al Jazeera</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 00:03:53 GMT</t>
+          <t>Wed, 11 Feb 2026 02:44:59 GMT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNR01kRDVpeVM5aGdKMVljSmtRZkdFUjFCRTRCTDhwclAtVGh0RGhLbnd0VGp5NWtZU2dlcWJfX2MxdlhnNW1ZeGw2NlNkbTl4TVpBMURPT0dFWEhvTG5BTG1hcV9henUxWmVCWERjWVQ5QXoxOTl2Wng0UXFFWmE1cGJmVHp2R0txSFNyRVpqRjBWTE5UcGo3NzNEenoyaXV1OGZZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOZ09FUDJUdmZSc3dPc21lenByX3lSaTZicGZFMkdmMXRWSzE1WV9lQ05NMUotZVRKVUpKLWtpSEhsV21DaURxVEJxT2RVcnhNUlRCM3VGc0tyeUs5WENOSVR0NjNrc2dobmFiRVRZSDZkVFM3V2h0U3ZkdjBKbUZnUzlGMnBVaVJ2TGlPMEhQUlVqYjAtamZ3RUROa0U0bk40dS0xWkxaRVhJSnFQLWFkckRlZ1XSAboBQVVfeXFMTWdJNlFOa1RuejF5bWY0aXVFWElHZnVUYjdNaEYtY2NvWW1hY1ZwYnJ0LTRFcHUzU0JGRmt0bzJEaVZPWlZ1M3EwTXB0QUpHR0l4OEhXLVJhbDNqRjlCQ29hNVA2ZDRRVThhNFZBYW5hbjl1TFhwckVtVGRlTHhWSmJDYWhPRFotWERJSElfcTZURGxLZEpESWNhMEEtN1NRNWRoWUNvdnV0c05tRml5LUxTSWI3U0lmTjJR?oc=5</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -821,17 +821,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cargo ship to be towed to shore after engine room fire - BBC</t>
+          <t>EU Considers Sanctions on Georgia’s Kulevi Port Over Russian Oil Links - Organized Crime and Corruption Reporting Project | OCCRP</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 07:32:05 GMT</t>
+          <t>Tue, 10 Feb 2026 23:28:27 GMT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE1JdjZkYVdxc0tLMlhXcUFxUDBFd09BYVFGVkYwRU9VSXJoMVh2NWhpSDJXZnlmb1NHZURtWTdaQXd2XzZsN050VGVVZXgwajB2Uk41ZVVJeDc3RDBy?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOOVBUS2Q1MGNTdnZHN3FCcDFqNUpBNU1aeWVJNi1JN1lzdFFNMURJSW5LNWRDSHdpV1BEeGRHUXMzOWdmbzJjMEF2WkhwVEpOcVJqeVNkLXVLbnpBdVNxTVpySVR4Mm5xTUsxSW1fc2lsSGdjZnJlNlBwbG1lTzBtcFpQNEk1bURYT3NSQWsxU1dEby1ELUpsNWg0Z2NJbzNk?oc=5</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -851,17 +851,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>In 2026, contract logistics is set to grow again - Trans.INFO</t>
+          <t>Yorkshire logistics firm invests in new facility with HSBC UK backing - Insider Media Ltd</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 04:07:19 GMT</t>
+          <t>Wed, 11 Feb 2026 06:03:04 GMT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiYkFVX3lxTE5hS09jREZ1MEZwck5KX1NvRlpMMi1aSDB3RGR0cVg4R0JLM3huZ1lRczlFd3BWNTM4TFJ6SkVtVll1Z3pjcFoyTWw3Z21pVmd6UzhUM0ZrVUprMzFFb1BUSzlR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQdTlBYkh2Nk04aGRoRXlFel9hNDV6VU5iR05wQW43bWZTem1tRnhKMXhZQ2Z4emt0MWpLZlNxcTRSMDR3QWFWeXQ2bmx4R1VtN1lXc0NYTElncm9NV3JrbkJXbmRveGJMZklWcVZDcEZ2bm1TVXhDbE9qZWtoRHRZQm0zOVQ2V2EzSHJMVm9BRzJldmwzeFQzZEpjRkpEOEhMLWQxZFpHdzlEVTVVSFYzRlVUaw?oc=5</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -881,17 +881,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Match Officials | Port Vale (A) - Stockport County</t>
+          <t>What Does the Descartes Shipping Report Reveal About Trade? - Supply Chain Digital Magazine</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 17:18:08 GMT</t>
+          <t>Tue, 10 Feb 2026 17:31:51 GMT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNaXlGRzh0QUt2d1NKdGM1ZU5IbmZJYVZnOVJ0SU5jX2QtZ1hYbkRPREVadGZabG9xRkgzbFF5eDFrNmgtRGJsWnJoaWFCck1vUVRkeVhQb0p4YUtvMDA5bzBTZWNGdzVPcEpJYXl1NHVaT1FEdVUyNGc2UjlMbDdGcXpreHQ3QXotdlo2ekwyOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE02NF9uM3ZIMGNyb0ZXNnFJbVlSY2RVd0lPaGJTVktsd3ZHYVZEODhUd0FpbENVWTVSYTUwRkptcWJkbmZyT1FEU0VTY1dFampOZG9ENWQ5bmdCY2tid1hrMDBHeFhfdlZ3d2VmUmlBaWlzZEJNOWc?oc=5</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -911,17 +911,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Grant Ward is a Valiant! - Port Vale Football Club</t>
+          <t>Broadband social tariffs – how you can save £220 a year - thecanary.co</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 15:54:38 GMT</t>
+          <t>Tue, 10 Feb 2026 18:10:00 GMT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE1DZE1lMlpmTkRXVl9FZ2VhZnhzaDhCMHEyTFNxRGFfd2N4MUNWN0NlLUU1eHZ2RUtlU0lCdWZkdVdQT3RBeVVkX0JQT0xOQlljeXVDaFdGX0FqaEhCODE1Qw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPeGNoX0hSSUhKUU85SVJNX3d5UG80MEgxaGt4TEczUk80bUVuWFNBeWd5Y2haY1BpckVfc2ljMC1WNzQzLS1yekE1VWFYZm45REY2cWFaaU5mLXozZnM3MWZ4d0tXclE3Zi1ISmNyYW8zLUZvVG9SOTdvYnpvREs2M3Fkc05TQUg4TjQwMDRWMmV1WXpzMGZGei1oRUhoUQ?oc=5</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>RLAM's 1m sq ft Leicester logistics scheme to be approved - Green Street News</t>
+          <t>US giant buys €65m Milan logistics hub - Green Street News</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 07:12:32 GMT</t>
+          <t>Wed, 11 Feb 2026 07:47:47 GMT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNX1pkamVkSlRCUWJZSFJvbGFmcUVkRUFsaWtaT1VuenpmOXBHVDJBOTNQOXR1d25CaUxLYV9fZkUtd0FHTW9jeHliOVhKSTRkUXlhZHZWSkNWbXNYOUREdS1FaUlDUVBVeldKblNqaXBZdk00bFo3ejk4WjU5eTdKb3R3YktjMkp1VkZFWjB4OWc0UHFuUXNvQg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNenB2UXFwQWVCVGgyTzFBV25DNW9NZm5jcU9jc0VOVHJTNjQtUXp6VkdDQVpfbFhhVU92SDBBM1dRdUdBSUhaanVYOS1zNmdJa1E4Qmowa1hqVVoyNWZ4UkRnM0pjWG44NFgyTFB5SU5pTUtJbkdKYm5BdGtRQUVrUw?oc=5</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -971,17 +971,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hiring delays worse than economic instability - The Global Recruiter</t>
+          <t>Why Haven’t Tariffs Trashed the Global Economy? Explaining the ‘Global Resilience Puzzle’ - NIESR</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 07:47:40 GMT</t>
+          <t>Tue, 10 Feb 2026 09:05:49 GMT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQemUydWYycU1rZUxUZGpvcVdPSWdPeEdjNXh2LU5xVVU4T2hUQkg2VUpuTUpQWkRQYnhOb0dQc2dGbmNkYkJLRHBxSWJobUJFSnZnTXRtdlBmVGllWnV5RVd2dkhrQVVSRHJFV0Jxd0Mzc3RmWWx3VE9WNkhKM0ZxZTFLNTY4UFlX?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE0tXzRKOXNVekVwYVRBOFZpamJleGRjUGNlMUJ5NU5XR1ltODdwVVl6eEFXc3hmdXpHWTJORGN4SnpHZUFlRnp3ODdkSEdfUUxUbDJRekpXTURSdm9jLThYbUJHSkhNVXRQT3RFeXNQZURTWFJh?oc=5</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>How Buy With Prime is Transforming Logistics and Fulfilment - Supply Chain Digital Magazine</t>
+          <t>Full Fibre ISP Hyperoptic Add Faster and Cheaper UK Broadband Social Tariffs - ISPreview UK</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 16:01:13 GMT</t>
+          <t>Wed, 11 Feb 2026 07:38:00 GMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOUktNZW53RmJzQ0RUZG50SndmTEhOT0d5X0ZoQkR3NENELTNqUDJUMFhSR2QwaDQ2VkV1dHJCb24xbTI0Z1ZxX2I1WVhnZVVaSjhIdnZmS2JhWm1kQWJqVWh6bmsyREVtbEczcG95Tnd1RlE1TmJBUHk4a0JUZmx3QUdMMmFQaXVUdXoyUlZUQV90QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNcnE4RTdYOFZCWl9sX29sdmI0WXp3ZHhqSHNKQU1JWUJ3bjA3TVlTZGJHb2hvMzIwYlNMU1VlX3pCSHhBVzBDa1VxS1dldkU2RVJOQXNhZlE4cEREUEwxNkNTZXpDVFB2dWJvb3hfSXlUblBlUXNsYk5jbEl1RUhYc0lCQzZwdVN1UEx4UkdyMUszMXpYZnZyc1FQaUMzZmNuTVVaQm5HMHFBWWNmTWxpQVJSUGdhVkxfYjNleEhFNUFRQk9UQXc?oc=5</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1031,17 +1031,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Shipping giants have learned the right lessons from past storms - Financial Times</t>
+          <t>EU seeks to ban all Russian crypto transactions - Financial Times</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 13:48:40 GMT</t>
+          <t>Tue, 10 Feb 2026 14:02:22 GMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE9SMGpTQ2M4Q3NuRTZDRVdqNFFHSGhqTUstSGM0WVdPamdKMnBfbXlIY2ZHUnNJYjVSekdDSGtmU2owVWdwYkkzLVRFRlNoQ3VDOUtLNGFLcEZkeTIwZnZlVWlrZFV6dUp2aDk0SkdqOXQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE4tOFVKeFFXc0tFSUszczJrTzlwU2p6bmJUc0d6dDh5M3dvLWxFSXNKNDUxcjdWN290TWZsdHRqSDVZLWVvUzJVOTAzWmh6c0Z6cmMwSzZGZkRMTnFlOTFXRnRVT1VDd2hPRlo4NkpkREk?oc=5</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1061,17 +1061,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Shipping giant MSC facilitates trade from Israeli settlements through EU - Al Jazeera</t>
+          <t>US imposes new Hezbollah sanctions targeting gold exchange firm - Al Jazeera</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 10:02:46 GMT</t>
+          <t>Wed, 11 Feb 2026 01:14:02 GMT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOdXd5S1R0TS1hWW43U2ExSnpGcU9wWWxsMFFTbHlPT29oSWRzLWlyQjE2MDZ2ZjlLbXpqaXFfN2dESzRkWGNfVFZSaWlnMzhQbjRRZkJvdkRlQldnc3o1S3hfRHo0WHQybVcwaDFMdHVxT0dzeEo0VGtTMlFFak5JOVdqT0xSbTU3WjRObTlHODdJd19yN0FlYWx4WjRmZ1VUVF9ZaVNPSGw4TDZVVUpBM3VR0gG3AUFVX3lxTE8xaUpIZlg1T2hfU1BDOG9UakJWaGR1VVpNcVltbGxGUkVhTjE4OVFqNzVqbDVmdU10ZzN6Y0QxaUZhLXhka21CUmRYSkpoQmpLM1ZGRDl6UlBCMDBtekthb1NjaFIxTjF0cnpOcmFYWjlvWVFicUFQZzVaMGZaUzVERERISGRHUFVRblg0TTgzbElqWWN0WjdOM2llQ3Zyd2NhM2xPRk4yV0sydFVYT1g1eUx2WURTQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQZWZDeVNLNFlvSkF2bmw3RWF6Rjg0WXNRM3NGcHlkOTNLR3dTLVNJVUo0eld1ODQxT1ljWFRxTnFYLVlpcWVpR3dZTUhocHpOaDBDeEFmZGNvRXRWSDNrUDRodXlJVVJHcFl1ZFNma01RUDROWXhyNGRQekotNGxac2xINl9YMHlOdmVwXzY0dWZCeDFrYTR5T2p3MlVlNHZvNEt3Wk1KVdIBrAFBVV95cUxQenRYVmlrVjhmLVpBSFdPYUlZZDNqd1U2Y2ZhbnBXcmtKSXNPcm03ak5RM1ctc3ZTUENucnRjUFJhYjROdHVzWHpja3g3bU9IMUdaOVFQM0RFVmZkM19tNFZ3S3lXbGR5czdiMy1qTzNfc0xpemVpOUs3Nk0xQUtISm9TMk1haTRLcWVuZVhzVUwtdHYwdnZodHNNbVBqVnpNaEhxRDcwWGpKVWpT?oc=5</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>EU proposes sanctions on Georgian, Indonesian ports for handling Russian oil - Reuters</t>
+          <t>Trump plans to spare Amazon, Google and Microsoft from next wave of chip tariffs - Financial Times</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 16:59:37 GMT</t>
+          <t>Tue, 10 Feb 2026 14:00:02 GMT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQSmF0YlpISU1LNm9adUVUOXdaemlFbG9hTzFHUnUxX3N4Rm5PYURNc1FSLVVHTm95bE9BSHlsZVJLZE9HazVWVG1CTk81NGh2eFpKeDh5bTdiYWtlRDh2ZjBfZ2JZcTV0ZDVGV2NOdU0wRG1HdzJ4WXBhRER0REZQMm5WSVdPSVlhbkRRa0p1ZUV0c0NXdnBaaDQ1cnpwVWxjejZ2ZkhHbThPSTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5ScHJRUU1zZEEzUm8tMC0zZkFydFBmWjZ4SU5WQ1hDcmhvdlpScGdMLW1XMzdHb1U4QzkzMHBiT0MtTGZlS25lWGFycjgwYWR1SzlVdHlrZFkwdWItVnNSczA4N1ZPLV95dE8yeW5rQTE?oc=5</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1121,17 +1121,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Campaign to help tenants saw Port St Mary rent arrears fall 47% - BBC</t>
+          <t>EU financial VAT exemption questioned in European Parliament report - Global VAT Compliance</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 06:39:08 GMT</t>
+          <t>Wed, 11 Feb 2026 07:04:58 GMT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxOaVFYLXJXVU9sX0I4N3JHbVFObzFhTmJTYWxVcFJ6M2NrczRvd3hlRnFzUkhIellBMlFZOGp3YlR3RXpUQzFPSlVVV0ZQRExLMmZSZjlZSVY3ckpmYkx1czd0X2Y2TTV3YkFaSEFTNDBwbXFnd01VU0VoMW5ZQVU5Z0F0UXZFVktpM3Y5UUZrMlFENnpxN2tSb056NGoxaDlHN2xCUjdpRkx6ZkxDWUdsRjRFaUU0M1dzcnl2dWUwZ1pkV2N4a2RkVjJ2aENNVU8tQ0FESS1RRmFfZkJIMEF5TEJn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPNGVzbmZMcGlmMUF0dzFyd2RFWXBrNzVsMnM3Y3pibFRFdldRQUpacnh3Ylc1X0NXTUJlWXI3V0NyY3cxRFF2U29mQ2xqekxkc2ZtdmR5YjRaM21NMDhVaGNmamV1RWpUV2NtWUhzWWdxZUZ1UFhVVkpUZnVsaVE5RlR2VQ?oc=5</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>More people travelling to and from Jersey, say ports - BBC</t>
+          <t>Businesses with Payroll Urged to Prepare for April 6 ‘R-Day’ Compliance Changes - Business News Wales</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 06:17:17 GMT</t>
+          <t>Tue, 10 Feb 2026 17:47:52 GMT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTFBhWnVueEQyajRWRU9Xd09HM29jSVhOeGZXdU5uZVZlVndfYkFoeGVrYWR0RXlmWm9rT196bTRpdFRVdHNMclE3ZDdqeUhtUkljN1IxemtEa0hMVDB40gFiQVVfeXFMTzJTdHNBWFA1NU1EQ0NMZmM1MGVyYmxlalB4c1dpZFZGRjhlekQzU2ozcVYtNmNhblBwY2tuZmVkYzd3QVYyX3BaZXRoNkU3ZllxM2lvdVU4dmJQclJrbmxtN0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQOVFaaGJzMXFiX1F5RGthNlBvZE9XNzJiQnhOYlNfdEdTSnZrdXE5T21rTy1JSXJMdm9wRU9yNDFGcHFKSkZpclRNTkFCS1JscnE4WUIyUE8zS3NRaGtHR2QzbGpURUJ6cy0teGt0dUFRclpmSlcyRU9McVdIWXhQaUx1cllKcS1odDlHWHN4VXMwQzVhcE9ZVlNrUFZ4VktpTU9BRzZUYzBUN0pJ?oc=5</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Oil exports have been a cash cow for Russia. But revenues are dwindling, thanks to sanctions - The Independent</t>
+          <t>Neath Port Talbot parent support scheme to expand across Wales - Wales 247</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 05:05:00 GMT</t>
+          <t>Wed, 11 Feb 2026 06:43:47 GMT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPd1BtSzFYSHRlLUJwX215Tkw1NG1rN1RfSjZodW1ZVENxSHJRWkloWFlNT3M5bUhQX3JlamhDYndFUmNGaF81dVV5SGItMjVVdFl3OTQzckVmWG50WUpMak5HX0pXQ2pGTHBpQS1PTVNfYjN4MnBXYWM1OVNkbFZST1lxeUhqdkhWem9zOWV5WG03RlRnYUxwMWpMOGlTUXkxYkRFTXhzRDJmdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOUWhxT3czV29JMldHRWNxVjUyMzBXamgydlJLVUE2Q0l1UXFubExFNk5VZnlZS2ZHYnFOSTFHWDAxTVhELW42RTdpYTRaUC1nR2lQek9JaVhxU1VQa0hDeENvTGFZSHFQX2V0YjlWQmtGbVdzbGRYTHpYODlocXdTajNWWVpQbkZMRVpIb3dUdXpMbkE?oc=5</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1211,17 +1211,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Port Vale MatchWornShirt auction now live! - AFC Wimbledon</t>
+          <t>Port of Liverpool receives record ADM Shipment - Container News</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 18:06:11 GMT</t>
+          <t>Wed, 11 Feb 2026 05:32:05 GMT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPSmRDM1hpZVBoVVRWVTN3ajYwQ2sxOGRMR1QyRS0yUXpubFI5MkcyVzZLbEU5NkNWQ2NuZjc0amFuODVyLUNCR050WE5SUlJvZTN2ZWNyNS1LTEI4MlNwdE5ZS2RMVGpJcDhQS3VkQ2ZUbGhxU2FBR29yYmo1NG1EMmQyRUtYUTF5cVY2NG9OT2ZReE9heTBXM01xRlJyMHFzU1I4dmgzUTludy1MREE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFBkRHZoMmVfSXNWTXdpZjU1aU5vRFFIN0xpZGF0N2xHUC1fTlFYV3lDX1VsOUl4V2pDeE95RnFNMzFHM21tR1RIUmF6SFJQc3FoWUhGSjFkR0hRXzhfYUJ3N1pVTGV1ekJadmdqcnlOMTlBM1JVVmtla2NIWldhdms?oc=5</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1241,17 +1241,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Iran suggests it could dilute highly enriched uranium for sanctions relief - Al Jazeera</t>
+          <t>Canadian pension giant halts deals with DP World over chief’s Jeffrey Epstein ties - Financial Times</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 17:12:31 GMT</t>
+          <t>Tue, 10 Feb 2026 20:48:54 GMT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQX0VYZ3JhZk9rUW80RmR3clZlQXFFVGtwcmtvUnZjN25MN1ZjWVQxRnBvSi1sT2E3SWhfQjFJWlNWQWV3cTNXenVFRmlwbjVycVZibTRpRm5sR3JyTzBMSERXcUY1VUxxOF9yRzdEMHowMjkyTldUUGtjeW1Ub25MLVAxUnhfTUk0aE0xU1RBbWRXbEJYaHctMWs4NFJNREZwX2NTeWlzcWRMOXlGTE5SVUs0YkHSAboBQVVfeXFMTlBYaTdfay1YY1JiMEJ0cllidTVFUmltY0c1SHNaNlpQM2JqdkNZeE5TMDlqUDN0WG13NjFTWlBUN09JVDh1TmVlOHdUbjdnLVc3MU10b2pJekFBSVBscVhNSTZhVDlfRTlzejdHUzFZeGhoZkRBZ080ckFabXVHRVFzMnVZVWhHWjhweU5pYjFodzMzQ3d5SW1KX2tQYnlGNm1nYzRiTjhORkFuVm9xcTBtWGlfX0pCM2dn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1sb29DZlNPY2dXbHAxUVZLQ0xfaFIxREpuT2F1YTRFTlViWl9ZSkpLNmN6dHNfZS1jbDMzSjFSdXNlM0xHWlVTODREeHB4YmVCV2MyZ3pRN1FqSVdIWFhBek0wWEhEbEcxNnYxcS1reGg?oc=5</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Council set to approve shipping containers despite emergency service fears - Nwemail.co.uk</t>
+          <t>Trump Tariffs Face Rebuke as Johnson Fails to Block Votes - Bloomberg.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 05:00:00 GMT</t>
+          <t>Wed, 11 Feb 2026 03:46:00 GMT</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOdGxXVUtrRGpGSnIxWmE2dFRJa1VqT3cyam5UX3NoQXBReVdySjFwTE1fUU5fbFlRMlNKUEZWNl9RaUFoREhuQXZ6bjY0eEJ5QW0wNVkxLVA2LXNrMEp3VnhPYVRWako3UmFLOGhYSnYydXFaWk5ySjVnZlVsUnBmRDR5M3Nta3ZISDNMLXUxc1FlbmxKUFhmRVRvR0RuQmJQSFpfUUVn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQRHFBZGFWMVJiM19UcHU3eVVRQ01GUjBNajA3eTB4OXVfM3BjT3NYV0dmY3FEUlVubXlLbFd3YXJUWWhGQmF0bDgtTXF6aGRiVEoxTG9oWjR0dm96Nnl2bzRDNXUxdzB5SDFsVjU4WXY4V1dKZ09DMTFZOTltT3M0TTZldjVrNWRKX002UzdfSUxQUUc3dktfTjd3amlVSG9jNXJkR3B6a29DUS1MVVRYT2tLTUM?oc=5</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>House Republicans Move to Keep Putting Off Vote on Trump Tariffs - bloomberg.com</t>
+          <t>‘Cash rain’ coming for Himalaya Shipping shareholders as bulker rates rise, analyst says - Tradewinds News</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 00:53:00 GMT</t>
+          <t>Wed, 11 Feb 2026 07:14:50 GMT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPYWJaVE00N3A4N3hHME5KTE0tQUF5MlRsRk9VX2UwSmpVRGZSRmRRNTB6YVdVQzlNQ2ZBVDBiNE5YRDJGTXRzZTFsb3NPTFVUVkJoeHhYWXRNUEx6WEJRczNBeThQbFJaTzd3MGhDQmxuYm1tNElBN2plWkp3SVFweWJqZHExSVQwSDlGWHZxeDRLeEJpX0xRd3BzRU5McWN5dkhxbXNRQWZ3cGJHRTE3bnhNa2JDdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNWDRaY242b0VQRnJwUFlJRDgzMmRoVTJiMzBzTjBVVEthNGFlM2h1aWVvVjRxdVRnQVJzSnJ1aXFkdGJWU196dXJyQXBreC1ZeW1kdTVZbGl2d1lRcHpXUmljdWF4a0FQQ3N0UGNEbGdwM1did2pKUF9BZVNUQm1KUEtVTGpHV2M0QTFpWUs1S2lWeWF0M2xxRXZiQ3V2XzlIY1l1VkFaTlFheFRiaFZVWUNmQi13dThCQlZfRWprZW9hVS1CamRhckpmemNQZXNFdi1R?oc=5</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1331,17 +1331,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BoE’s Mann says US Trump tariffs are pushing Chinese export prices higher for UK - investingLive</t>
+          <t>Bespoke tariffs backed to boost community energy schemes - Utility Week</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 02:47:24 GMT</t>
+          <t>Tue, 10 Feb 2026 17:45:25 GMT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPX1lGMHVKZXJoS1p4RWlMLU1UU2RwcFhJU2hNRHZsS211Z1NreTlFemhTN19pRFhqYVh3ZWVZbmZELXRqZTY2M3c5ekVBV2wxN0UzZTV0ZUw1RllMd2FlYjRkQWxsaFA2amJBU0dpVFpMbWh6ejdHR0poMjRVUDUyY3NPVmZUbWUxejVETjJSc2xIcHJrTjhpN0JYMGc5cjZrTm44UHBYY2RxbVJJUzVHZTN0a19kVkh3eW45UUZ0QV9YTHVXcGfSAcsBQVVfeXFMT012VzJLVl9fNlI5d0xqRndUaUFZdkVQaExuNmIyaTM3Tlg1ME1fTnJHTU15bFJqRUxFVVVxbmRPa1F5aFc5cjdqLVRPc1ZkR2djQ0I5SmZPbnBuSFM3R2tOc0RqR1cyQWlielNSX1RwN0lvdDI4d28zb1dSRjN2cHQwNngtV2VjMi1lR2tndlVmX2NOWTlpYThHQkhzcS10Z0JWS01oMzF6VmZTMm1rTFhEclctTmprSllXNDFIS1hJUkVzY3dFMldqU1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQNmV1c3FsaTY2SFJsTDFrYURIeHlnT2h5cEhVUW8zVzJIQnNiejRkcVFrNDA1RmdzMDNlcXpMSEVCaUlLM3RBZlhXaDRucmRzSmVxMVRfZlJ6ZmNKTmZZTEJRY1d3Y0xZRXhZX09iYmdJZXp3ZUlaWHBVa2YzVWgtYTNjc3hUQV84bF9N0gGXAUFVX3lxTE9XNjF3S29RMTVGcm14Uk1pakZHUXhuTUtRd09NblZoOHJ1aE5Ia2lGbXphNmdPdW1WRG11RWNSWmkySEdHRGFYNGpObnR1bVdyM0pGQTVIZ015LVFWcWJkeUZEYUNFbXZ2V3dGNmNiY0Iza3lXd3hhbG9UTEc5QmtHMGFzcHRoX3pGeExnSTF5UkdqUDFkMVk?oc=5</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US tariffs pushed French cosmetics exports into rare 2025 decline - Cosmetics Design Europe</t>
+          <t>EFL Trophy: Stockport, Northampton and Doncaster reach semi-finals - BBC</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 18:25:22 GMT</t>
+          <t>Tue, 10 Feb 2026 23:09:17 GMT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNVXR2bjlnaU9IODJJVGt0UDQ5UEFhMTZ0ZnN6ZXRVemQwdHY3NkNWUzJ1eXBoNS1kTElkVDhwdDhHT0J0NWROVkhub2RwcEp6OHlFRkVoVEFaSzJaNDJ0ZEJDWlhDUnlJVFhNWmF1TllYTk9KZEowU2p6bjBTYmY1di1xU0pMY0ZnRUpsZzJXTEpxTHRfQkNNLXRxd1NLbnpTX1hKeGFLbnIwbUhaUWVDbGZzZkZQV0x5THVIUGtHUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE01LW14c1UyS0Nrbkh1OEtoMmswYW9qNXEwbTV0Uktsd0JOM2tuTzZnTTZ5OXlna2QwMDZaalhEUDZaRjV3RkZHN3BHRktpMDE4VDB0bzdxQ2ZGY2xzUDRKbmdnOXhoakU?oc=5</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1391,17 +1391,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>International compliance firm acquires VAT specialist SimplyVAT - Yahoo News UK</t>
+          <t>Sanctions Force Russia’s Foreign Trade Down to Soviet-Era Lows - UNITED24 Media</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 05:00:00 GMT</t>
+          <t>Tue, 10 Feb 2026 20:01:56 GMT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxPbVhsVmN6RXBtZlA4My1VQXZVb2FlT0pjQzRMN1pTOXBEd2pOLUR5Q0FkUElkRFl5X0lENUx6d3JYR3pHYUpLY0NJQno1OUR2SzNQaS04dXFXcWMzeGRic0JMSXVqWWFUY2s4R2h6OUhudk9iWHVmNk55LTB6UlBEUUd5d1g2MW9xZENJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNdkptR0liX09lUHNmUUpNQU82MHpnR3lBdWpEV0NNTTFoaFl1akM5amkyMjZ4WjhHaG44Ynp6aWpmOE40eVROSW5CeElFLUhJOHBoUjRZbUUzYTFoMi1Sc1hJYTQtNXAwWlBXbHV5Um92VW9TbXlhNzdETnNPUlNkTnpwNkdtOVFGQXU4RzYxa3hEYXBGdEFVeDFFRERhSnNTajMxNEV0OS0?oc=5</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1421,17 +1421,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Logistics firm will run major Swindon factory - Yahoo News UK</t>
+          <t>Man who was found to be dealing drugs appears at court for sentencing - East Lothian Courier</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 05:00:00 GMT</t>
+          <t>Wed, 11 Feb 2026 07:06:06 GMT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9KdGloTGV0NmpMbUdtUDMzY3FIR05qZUJSODJXR3lHVW10X0F3SUljYkRSNk51UExPaTJ3Mm85UW1IWElaVC1Ta1NJVlJZSFFwX1VVaGZ5SXFIZ3J6R1lyWXFkNVkyNnpwTl9jY2l0Y1NTMnJUeDE4RFpBMkhVZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOcGRObFpXU0dRY25CTE55dnZFU2hGQ3ZDY1ZHZDFIdDlHUmJISldhQXQzeUlaUW5mVUVQc3lDbWpKR19iYzV5Zl9iM0tOcXlVdXdZZnhVbWF2NXJuZUQxcEpyTEU2RktXeDNnNUl5SkdkYnlIZnlOM2sxYzN2NTNTN0tGUHNSMzhya3BsREVEMFBqU091TFFvcEd0UkxDQUJwNkRKQkZHbw?oc=5</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1451,17 +1451,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Top-Rated Logistics Software Development Companies Driving Efficiency in 2026 - Impakter</t>
+          <t>Syria’s Future Between Fragmentation and Rival Reconstruction - Manara Magazine</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 22:45:08 GMT</t>
+          <t>Wed, 11 Feb 2026 00:39:40 GMT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE9pTzU2eXhCRjhLUEYwdDhxVzVKMFFJMWd6c1hrdUlvWlpWd1ExNU9VZHFaT2hTSEc5Q3NNdUZZQU1odGlJV3NJTURLMUtGcDRRWFhMLXJZR2JEbHNtbkxLbnM4WC1NUjdzWm4tSWpkVnRXeXE2ZmxtZEJEYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFB0VF9DMWxhR2tkWFViNi1EV0xJSzhtZ0VZSDBZQjF0YkVJY281UTZuMnZ5ZndzdU95UXpoeGN2ckxLQ1FzSGhXeUNXbGZvYXVSU0xlM1BhR2YzeDhzWUZEa2Vod2NHUnN1V0djeEpRSWR0T240aXZaT2NhTDRwSEU?oc=5</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Pembrokeshire student cadets receive boost from port - Yahoo News UK</t>
+          <t>25 wonderful old photos of Fleetwood - port, town and seafont through the years - Blackpool Gazette</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 06:00:00 GMT</t>
+          <t>Wed, 11 Feb 2026 06:00:00 GMT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOX0JXR0J1UnZEcF9RX2NrcVVtUklLUjh2b29GdnNlaWloT2JBb1l0TGZjcHFXT2RscWRPOU1zTWRLTUV6X0VzWkJ0VkNjMHdSNld5d0JvejNiUFRpUUR1Rk1mdkpaNTdjMmlzZDdXZlFoOVU5ZFdLS1JRUUZneTNFOV9HcFdJM2tGc1lR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxONmN4RjFsUFRtOWZzVjZkQkxsX2F2UjVjWkdTdWZQVXlxb0xDOUxIOTJ3Y0NwT0NGS3dtSktHemRZSVZLbHdHa3Z1S3lUWGR3VTVGSEZiX0hsWlVRN3h3OVJBSGx5R1l2RWZwNUFkWEp1ZnY0Tm1qTTdiWGNrTExiUzNtcFJCV1lJcUF5R1BrUTdGU0xQMkNjdERsOF9jZnFTemRrNGJPaEJHREhvdWlBYzZOSTZXZmJwbkNjSTVnb0RMWjA?oc=5</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1511,17 +1511,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Himalaya Shipping reports ‘strong’ trading performance in January - Tradewinds News</t>
+          <t>Gabriel Makhlouf sticks to ECB line on rates as US tariffs help keep inflation anchored - The Irish Times</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 07:59:54 GMT</t>
+          <t>Wed, 11 Feb 2026 06:00:55 GMT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPQkxsOHAwa1EteDR3OV9mWE1HYUVGVW4yWmphSzg1aUhLT2JLTVJfMnY4a0duTHBFN0dpS01weTFjbXFZS2hzRjUwdEVkX0YwUVFneFh1ZmtxY2d0ZlY1ZURkd25pLUQtSzcxc1B5VjFyTW5sN1lSVkY4bmNKeXlaZ1gyYV9DTDF0bEtpUXRtXzd5TEJxaXFnTmk5blNrRWZXZVJMQlV5SlFhZTQtdjVLZUQ5S2E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQQUVrbmpWYTRHSnZreEJmRGFkcjJBQV9iY0lXMWdnUDZ2WE9Td2F5U0g3elNNbG8xMVA2M01SYTliMlJyWE9RYkJjcGF3eUhxem5uMTJYVS1jV1dWa0I0MEdaWW5pUG9jQm90YVBpZ1JzbFlDb0QzY2o0eTR6RmZLZm02ZjJxa3pHbWtoM3ljS182QUtUZWI5Rl9GY3RaazJkV0I2QkpHQTdabW1lUmxtaU1kREhzOXQwdENHa3JsR19ZM181YVZlRGNCMTdEUzh4?oc=5</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1541,17 +1541,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Boeing sees aerospace aftermarket recovering from supply chain pressures - FlightGlobal</t>
+          <t>VW’s Cupra Tavascan first EV to dodge EU’s China tariffs - Automotive World</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 04:49:40 GMT</t>
+          <t>Wed, 11 Feb 2026 06:30:07 GMT</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOZDd4UGNSWWlRMGdtbGpNOVpwSGVyV1RCY2p6VFhmNVhnX2FZdlhTWFp0eEM1SDc1cnB3M3JBcVZ5eGw5LVZWb0lsRzZHbFZ5NTRDelBHa2VLdHJ0ckhHdW5iMWh3Z0wyZjRuRFZQelI1cm04QkE0NkU1ZUw2M2xFMVZTQkI2cXJmaW9JRUZBZ0hJQmJ3VURuS1otZXBrTHRJUk1RVnpQMUtja2RPbklDb2h0Mk5sN2tUUGxBcnQ0b3VHOUls?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOOEd1dGJ0Y3ZhT1lHZUQ4SmFQSU15ZVY4QXFpb2RkaG9Ra0pXSlNEdmxqT2VmdXloMlh3MnJRR25aNnJhRjF3SGtWdEpKQjRuRHlRRWoyVWlaMEJRZTN6dG9qaTRCTTZXOUxsMTV4VjR4S3hVdUtvYi1RczRsdEh0RF80WUpwbjJDUGRfNDcyVWkxMVkxQUxZ?oc=5</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Changes to school funding could affect thousands of local parents - southwalesguardian.co.uk</t>
+          <t>Ukraine Hits Russian Drone Nerve Centers and Logistics Networks - UNITED24 Media</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 06:00:00 GMT</t>
+          <t>Tue, 10 Feb 2026 16:14:01 GMT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQT0lfaG5fR3FPUUVCUGlINHFhbWNHMUNobzZNWk5MaGNxaVNPT1d0OUR6dHlldnQzZnYxa3ZnMnBBWW5Ka0MwVk5DYy0xQjBGWlF2TlhFbVRPOTc5SUNwaTRsWER1WDZnbHRfcThvZldORFVpVkFNU2JNMHY5Qm83SjVXVnZ2cThGR0pOQ2FPV2NzN09qdklZbGpQVWVFWnZ5VG9jWW5YRHlRanM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNSE1FdEVRaXkxd1ozVUxMX21kNi1PM3lMcFA5QWZmU3VmZC1fd2ZaY1ZqcExJa0dveUU3RlE0aVMybW95X0tVRS1Meml4R05sX0xWQk5TT3UwOE5vYjQ2Rk0yUVpNeENkaEdrVUJtekctRDZqUkN4OUEtdjhZdmxMYTJHcjJJalJSazJIYmprMms3aWFJUFJJNUluWW41ZV9TMXlTbk9mcmdvQU0?oc=5</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -1601,17 +1601,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Residents warned of drone activity around Radlett rail freight site - Herts Advertiser</t>
+          <t>SeaLead plummets in shipping line rankings - Seatrade Maritime News</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 06:01:00 GMT</t>
+          <t>Wed, 11 Feb 2026 05:54:57 GMT</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQcDF6X19MUEt0S3U4YmY1ZVBaMEhGUlJ3SnFoUmFDMlBUSW1fM0lvZXRFMW9wb0diSmRtT0ZoUUtKU3JtdVc4bTFzdXBMT2Vna3RUUFQtLXo0RWZCb1loUjB5MG1oeTFSQzVobTBrTHpjblk2RUh0SnFBOVltOWd5dzlZdVE0V0xGdEVKMmpUMkxDS0NmOFBGZA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxObUh3d3FvVThxUl90ZmV2czZldWE3THJsQTBQT29LWUZyZ2hFdmhCdEpNcmNNTGItc0tFdDg1cHJBUWtjSUdnMW1IVkxuZlpNeHNOSWZCQXRfMHRDYUpqcUYtVFhMbWVUcFZIVjZpa2RQcU9CTGdIT1I5WjFmejkxcTNVZ1FhQlAySTlkdlNKNXI?oc=5</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Northfleet Hope – Gravesend Reach – Port of Tilbury: Dredging Operations - DredgeWire</t>
+          <t>How AI collaboration transforms governance and compliance - Thomson Reuters Legal Solutions</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 00:26:59 GMT</t>
+          <t>Tue, 10 Feb 2026 21:13:48 GMT</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQZWFMM2Q2aUVpUURUTFFpYlJwTEMtQ2w5UnRKT01rSWptNGZNcVZNSmN2c3NFVWk2NkZOcnhmX2hLSGNLX0xFaGRXOEktcTdVZ1J4TFpaLWEwQmNYaXFwbVdvamtXVFEtZHB5NG1TTlpZczMtODlqOURQUGx4YnIwVnZFY01QQ0h0MTBoT3czbVlUb0RmRUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPSG9mcmdjeEFJNU9heTYyMHdzdHIyYlB3S0hJSndwU1pTcnVkOV9XTTJaVmZXMHZPcVUwOUNoQVlJU0w4SHpkM19NZUdCSjE3WjZZYzl2Uml3SE9UQm53YVlMXzh0ODZMY2ZaZF9EdmRjZEl0ekNudEFZRkt0S0JIMDdfMHJzSElFMXNQLTM2bHdXZUJhclBuaXJLQzZMWE8yZm9kcmxsa0otbVY3dGV1T1ZGNDFRUWc?oc=5</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1661,17 +1661,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>How do CTV ad teams handle Pharma compliance? - Advanced Television</t>
+          <t>German Oil Refinery Sounds Alarm Over U.S. Sanctions Risk - Crude Oil Prices Today | OilPrice.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 22:57:23 GMT</t>
+          <t>Tue, 10 Feb 2026 21:30:00 GMT</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQbWdITTBWMVcxd2pPeHliUlUwYi1ma3Q5SkxxMVcwLXUzMFZXRTZDaFQ3bEJFNnJhSUE5Z0k5SDVMMmV2R0lHb2Jib0xJM2x2WjFnX3hNX2dSZVF6WDJZNzNON0lneW9sV0FRdTVUeHRqaVNLcFYyVUxXMEZpaHpVWk9WaDQ1ZWZMVmg0a2FVMnoybWJIeTZr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPRVBocnlscUNIOG01T3hEcU4xczcyVlhiUlVLMzFXd0J3YmdveTR5Ri02NklLVUFoZ3REQ29CSkxrekpoeEtaYkZYX2lUUkFqRFFSY3podWRSN0VGQkNiTTFIWlRZcmNnWng4aDlROEJ3QjBTNVZFendRTm1qclhZN3g1dC1EV09DYm5tOEtjV2pndHRveVVKZTJVY0dfdk4yYUVsU3NrMEZ0SkFjYTRwZdIBtgFBVV95cUxNOGdNSjJTQ29XVnFuNnVSLUdmNmRPYWdDNzE4M25URXNiS3Y2T09Qam55SFRqeHJOSE0yNFk5aHJKUGNNcFBYel84UUtfWG1LTVp5ZWFZUUJORW01SklNSmk2aTR1MkU5bGlrejZ1cHl4TWFNOXIxdm01Sy1rcmtTcXVYT2pYWTdCTDI0NklNMzFvcW9rZ0p6c3R1YVJ2UkFmbFlsTVVTSWV3TENNYkN1ZDNJRTVkQQ?oc=5</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1681,27 +1681,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Port expansion would have ‘extremely significant’ impact on historic fort - Inverness Courier</t>
+          <t>Woman, 69, in hospital with broken vertebrae after police allegedly pushed her to the ground at Sydney Herzog protest - The Guardian</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 17:00:00 GMT</t>
+          <t>Wed, 11 Feb 2026 02:15:00 GMT</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOa2x0VTVJenF6RlhlVm82MUsxNDFHNlBKdUtWc0ZHZDBSb19nRWxYV1plbUROTUZPRV9UNjFHN3I2RGo1V19ZN2Vxdm9BZm1RX1BZSnpYTkt4RmhIZzBhbVJKNGFvY0s1cUtPekZnNDRBOUJvUGtKSTI4SWZaTWFPVlhOc1J6amE2a0RlMmExTEItOUR3eENJU3I5TFZmYjdxWEVIQ09renBHdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQYnFCY3FhWHY5OU9pdnNRUDJMc1YyaG1iLUxzUHgwQkh3ZUJya2d2SjBpWDU5UXNyMUN6UWlJc3ZFMnhVREJCVTZYSFQ5eUhPQ251Y2tRNm1ONmZqMk1UT2hkNDBhRHNVSk42Nk9VSWxreGlpWVlrYlp3X052b05NWHIwdEdWTW8tbWwtWVpmck83LUE2MGV2SEhENmt4UFBwZnFRTVktYUdSM255b1d6STRJdGx0UnZJODk5bmF5cUl0Zw?oc=5</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1711,27 +1711,27 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>INTERVIEW: UAE’s AML chief Hamid AlZaabi reveals plans to maximize compliance effectiveness - AML Intelligence</t>
+          <t>Epping: Man in court over alleged racial abuse at protest - essex.police.uk</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 02:04:19 GMT</t>
+          <t>Tue, 10 Feb 2026 17:44:00 GMT</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQSjVQTDhWUmlJN1NsS0laT2VhUWxtTDgwUS1vcG1RWFlXVWd6cXNIdF80M3NqUmpKMG1FRVp0RVdkVFZyUFRoeFc4QjZtX25pcUJuWTA5LU81UWdpZEdPY3NzUWp2RkZfblk4TlFCRmNHckYzN1dsRDctZ0xOWDFaSFhXOTFVZWd3MGY3NDlNdVBJT0xIVS1iTk9XUzU3YlUxQVlOTFc4MmRDdExuMGFZVmJlSTNRbGZGcldDMEp3cDJJelFxTWpablZ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxOSVFCc2RNS2pkYkRkNTRhWkFrU3loYnV6ODF0X2V6Zmg1QThrdmV4Tkk3eWZOQTFlejFEZXZLV1hyd1cxdnMxa0VSeXFFU2gyVjhRRGxRdFluREhSR2FZYzhBXzd6RzFKMnhBS001LVMwcXVfQlZsSlhJQ1lNR2RicHZDUldUdHBwLUlVSU50ZloxSi1BRnBqNFNUNnlmYmJVUm51V3NuV3FqNkoyU3dSUXpVSncyVUJ5c2NTNkpPQ0U3U19oQmZpajBBOG9aY1g1RGpZNmVtMEptbmxq?oc=5</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 04:19:50 GMT</t>
+          <t>Tue, 10 Feb 2026 09:34:33 GMT</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Australia politics live: Ley allies demand Taylor backers put their names to spill petition; rally at Sydney police station after alleged brutality at Herzog protest - The Guardian</t>
+          <t>Day 45 the Protests: Nighttime Chants and Intensified Police Presence - Hrana</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 07:16:00 GMT</t>
+          <t>Tue, 10 Feb 2026 22:00:15 GMT</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AJBVV95cUxOSmxaQUQxYks4b09OSVh3LTE5OWk4eTIydEZQUk5pZnphYUJ6SHF2d0NJSUVRSlJDakNhLU9sQXdpc2trMnprdkFqX0pSUXNkc3p2bEo1bXhZb2hGU28wWU5XeV93cUJabVhIWmxQSTNHX2xUWFZZM3pOTVNYZWdXMnNBbGl3VHVsZ0oySERDMzNCOE5YNW9ya05tVndyS1dCYWY5MEZFcWs5VXRtZjdEZWVOUXZwOUNiLXA5N2dNNnA2em0wUjlKb0dLU0VENW9pVzZxTEhadUVDMk1qRUZ2dGx0MzdpTDI3b0k2VDBaVTFCMlZOWk5iUjlWMWp0Z3phdmd3aU13QmJJVmVyemRzYi1UdHBaMmlndng5NWlTUnN5S1JSZTFURVdxdzhBbFk5Y0ZOZlVtYU5LQWo0akR3UWFPLWMxRzB4VTdHR1laTUpKSkZKZG9FbEZVNmEyd1c2?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQTEJ1ZUszLTBIUGVOTWdBV2Y2eVMyZWZfMVlnYnVHMERtV1h4MTFUdGFQTkpOVDNVaFo2WVhOLWJhWTdRYUZHOU40Zkx4ek8wUGNKbVRieU12RVczNlhlUjBRNXdsd2tDeFhIWjY1eTZJUWdIM3JMRDFjOHIxcEtYNmU4NnhQOXU3TWtfRFZJSTNfNzhVajlGWnlB?oc=5</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1811,17 +1811,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Haredi protesters block highway, clash with police after suspected draft dodgers arrested - The Times of Israel</t>
+          <t>Eyewitness: London protests converge on the Iranian embassy once again - Police Oracle</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 20:05:00 GMT</t>
+          <t>Tue, 10 Feb 2026 12:07:35 GMT</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOWWhoc1UteGE5TEVEUG5YOWV1aTAzenFITHBUMkZVcm1jREp5cno3OFJjbklpcDk3VEc0SVJZcFQ3dlhOWFk0OHpieUxYZkZGVTkydUFMc2lWcnNiWDAxTDI1QS16eU53elpERXV0ZWVESGN1eDdkcVkyZDdma1pHWXQzTzFNME4yX0tRcmpJVE1mRU9uNTJZank1YThfUWtxdURCX1A0bzNKU0k4VmZuSTlKcXlMNVp0ajhv0gHAAUFVX3lxTE9oSWZRbUZKWE1wNTBuM3FYdkVNSzVRNXQ5WjFYR0JkS29kTS02eDJDWEtNTVlYMEZTa2FDZ2NBYWh5dVFYazF5U3JFdG1CczlwY3dfNTJPQ1RMV2NxeHkySGtZOGw5ZjZrZFlWLXc2bldGdUtUVjlZSzNqUWVtbE40eUNuTVdoZkdzNFhLTXR6U01DWTFtN0JQVDJHT0Jxc2p6S3EyYVVZWlY5UXBqb0xKM09ETVBSS1ZTQklJRUNFeg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPR0p4RXhFQjdmY1ZSZmhpWVNSLUpYSXJvcEFuT3JqaGxraVNlNVZmWnJGSXVTZWFBdTQ5VnBXR0t3ZGJjb2FFbXpKQ243d0RDZnVxUmRacTVhY0RHNnl3bnRBRDRGV0RBN01Ob21MVjl5Y0FvaHVmZWpIOTZWSl9veDdnV081M2x3R1o1N1VBZE9HNDFSUnJ0MzZpZ2EyU0dtX0xsTkJjTGlNUHNtTXZLX0tOY2xWZw?oc=5</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -1841,17 +1841,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Police update after rumours of 'man threatening people with belt' - Cambs Times</t>
+          <t>Antigovernment protests in Albania turn violent, at least 13 arrested - Al Jazeera</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 13:00:00 GMT</t>
+          <t>Wed, 11 Feb 2026 04:17:00 GMT</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPemxoenFFcUN2YVFRQThSYzEyS1BtUDlmWnBGelNlWXhlNk0tVVhPaFdTcnZUOEFyTmpDUWhRdUZpTGFzMWhFY0N4V0hJYmZKQkRWUDh5d1hfdEZxRUZfTnl2ajNOQmZxR1BMYm5KVjQ0blp6UDNpVUtJenNGSGFmWnFXbFU0NE5pYllrTm1vNHJwQ0FNMlBtNTBrblA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQcmFnaUJZWDY5Q2RObUltcjVpdjBoOFFhZHlubkFhaE5qY0phWHNUNGJNaFJKa29VanVMbnY1OXVZM0VlbkhSc3BpN0R6UjJFQkhJWDc0dVpkTDJJbUNYM004c21yenZtN0tFUVNOVkZjOUU0WkZYNzNaMGJ3eFROWUwwcWYybkdsQjg0YXkyYmdmdGIySkFZSlJvSkFNalpfR2FCc0p1U2xGRXNfOEHSAbMBQVVfeXFMTnVUbzhsUkhMOUNqYUlWaHpac2VpX3Q5b2UzczIxYlVrT0JyR1RqbmxUUmh4YXp3Tzd4UUJWbmNOYUNQSk0xcGs1NzQwZnlMbmtNLTNmMDVhY0ZpTUo0LVU0aG1LMnBQOHZvaUx5cnpKZDBrRlVTZ3plWWgxQXdwQlA4NE1aM0pMOXI1TDlxd0Q0MUtQcFNnb0RQOTYtMmNYTFJQZnpPV2g0ei1qWVphVWxlOGc?oc=5</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -1871,17 +1871,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Latest News - NSW Police</t>
+          <t>Labor group voices ‘distress and disgust’ at police response to anti-Herzog protests - The Guardian</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 03:54:43 GMT</t>
+          <t>Tue, 10 Feb 2026 22:18:00 GMT</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxPQXQ3ZDc5MnpSYml4WG5Lc2JfUlFXcGdsZ29ITmdJOWFueVptR1dPN0wwOUZmNU52Y2tZazlCYkdDZUhEZFVTdjZidmE4akw1MTNqVWIxWlVlZUZkUFlhMGlkMmduS1U1Y01CV2xFc1psT3pjQjNmeGpZTk4tS2pBYXIxa1ZkZjd0SkdEWXhCaDZlbUpTSDFVdkJicFRwZ3h1blE4cC1IemlXeTl4Qkt1RVlKZGZrWF9SSzhWcW1rUldicFl5OWt0cU5GSGpmeElrX2s5X2dRNnlfX1JrbWM2UHZ3bjJvZmpGZUpkbg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOYU15V3RDMTJyNEdxZVRvYThsMHVyZTQwek5hOXlsLURjdTd5dUYxODdDdGluZFJLYXZHeFZNRTllNnJZcXhVcGhtbVgyb1F6SkxvcDI1dTVjZ0Rjby14TlBGTDF0UWlrd2g5ZjJwVUp5V3MwbFEwdXI1YjczMlBjVXhVRXlGTUtUcmtNLXFSV19ZSkozejR2RjI2b1dTVmhYWTRQTktyM1Jad1ExR3lrN0tJelRENFd5Ym5GeVNSSQ?oc=5</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -1901,17 +1901,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Significant police response ready for expected protests - ACT Policing</t>
+          <t>Australia politics live: Angus Taylor expected to quit shadow cabinet and launch leadership challenge against Sussan Ley tonight - The Guardian</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 00:29:15 GMT</t>
+          <t>Wed, 11 Feb 2026 07:01:00 GMT</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOYkEtSWFWQVkta05IaXBJN3BLTGM5MUNLblpZSXc0ekhxYnpMRm5oaXQzUnhuNk9WTmZ1SE1wcm1ueTlXSlBGMy11MFJnaFpIV0ZXWXRncWJBbzBKY0haMEpnSlpROWVUSjU3WWNwbFRiNlowM0haMGw2UE9TOENpX0I0STJaUmhUVzhZU3VxMTRUV2FRSmVHbU9yNjcyS0prdVoteU5Cajd3UGJUc190cEhPR3BoUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxOLUt0Y2hrdDRkSElsTkc3UnlnRmtJbExLMFdOVDdHSEs1VlRsTm9VaWRZOGZjNmJlZjVfWmlrbE1vNXhwWEFUMVY1X01QUGNFOTdxZHdKSDdrdExVV2JaTWlGR2pVaHdqSnZJOEg3dWhTLUhJZGsxR0VOSDdjWHo3aUJPamRVTlNOMXRSSzQzREtPNlRkdUhnamRCQmpKZEF1QU02elB2NGR1UEtDNUMxUGFZWnpidVFxemxDNHhLcklmajduSEJ5dkI3LUVZQVYxaEppYnppM2VaU28tMDktVERLNDhGNkJ2YWNCcDB6UHR5VTdBdXFnMkVKaGg0R1JJ?oc=5</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -1921,27 +1921,27 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Focus on AI and cyber attacks at business event - BBC</t>
+          <t>Police chief orders watch on groups over post-election protests - Nation Thailand</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 06:25:45 GMT</t>
+          <t>Tue, 10 Feb 2026 09:43:00 GMT</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE9SaXhSTzNIaDN2UzBYU1h6NURyYVFUZzhZWWk4eE5ySUJoWkxoVjl4ZnNCVG5VX1dvTGtueGJhVGxaeTlmNmVlV3g3enpvcERpVmoybzFQblpWQVNX?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYkFVX3lxTFBzQy1WQ1lpNG1aV0hXa0hkY3Q3Wm5zSVplR1loX1d4UW9TLUozZ2J6VWttOEpjOXBfcE9hdUtiNDhuLUNtWVVmVVNEdmw5RXNQYkVMOEQwMHRzSW8tcTVMRUZn?oc=5</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -1951,27 +1951,27 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Investors pour billions into Europe’s AI and defence start-ups - Financial Times</t>
+          <t>Despite police crisis and protests, Unión, Colón and Copa go ahead - OneFootball</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 05:00:17 GMT</t>
+          <t>Tue, 10 Feb 2026 17:01:09 GMT</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5lS0NTQS1aNEdWbXJ0TzZCck4yU24yYkdIVEtoQ3hUSjJGTE8tbmxhVW1OSzk0a3g5UTJLaHNqSTRIa2JOZ1NkSUpXWkdPbmgyMHpYUDhyVTJYNV80N3F1NG9NMlJQc3lKWGE3SzVmTi0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPRDFRaWVYRFZRRmpLZ3YzTXhFZ01uSk0xam9obzdUZS1XODBDaS1Sbl9kYml2NjBWN1ZoY0V0UnlYd2VXSVlCTW5HODBmNGtNZjFGRVQ5VEwtRmt1SElPVWJtLU43bVZLY2Faek90dmZJbXJqZE9MbVhDOE4wSll5R3o5bVhKTmhlWkVnNHY4LXBMb0IyRVN1WEJtLThzWGJiOWdScnJNdDc?oc=5</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -1981,27 +1981,27 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New National Cancer Plan with AI and robotics focus - UKAuthority</t>
+          <t>‘Like a pack of wild dogs’: Protester injured in Town Hall clashes calls for officers to be charged - SMH.com.au</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 06:01:26 GMT</t>
+          <t>Tue, 10 Feb 2026 21:20:24 GMT</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPSGtUOGliT2gyd1FIdEQ3YXBOaGJnWk5MbWFNSTk3WURxWjE3SVBnS3Z0ckVORlNvMFVEVnU3TkdLV0EwLU1pbU9BeUg5cTJnXzNqai01SEFiQjZZZDVpNU11Nm0xakxzOWlwbjNZVE44X0dZMFBJTWQ2X3ZVbFlxY2NQcFJXOGZodm1iYXJESmpaZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOLW82YkxUdVhjdTBFRlRvYU1jcmM4UjhGbmV1LVQzVEZDcTY3NDliWjdDbk9ZQlExZTFNcVVFNTZDcnlUd21rX1Aza1RmNjIwWmJRVWZ4SWZLVVhVSUJ6WHctOEVBbnB1S2VZRkRkZTBTb2hfMzluMFpKUFM2dndBV05vbklETkRSd1JhOHpvamtnMkdWeHJDelRldGY2RGwwUlRzVVA5eUJOX0N5TDNFYUZ3VXNtVHlQR0NPM2VGZ2lVMzUtOEo0QlptMA?oc=5</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2011,27 +2011,27 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AI In Robotics - New Position Paper - IFR International Federation of Robotics</t>
+          <t>Rather than promote social cohesion, Minns’ laws have led to concerns about police brutality - SMH.com.au</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 06:10:49 GMT</t>
+          <t>Wed, 11 Feb 2026 07:29:47 GMT</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1xNmVSVWNmVUV0cUZUeWF5c2llWVA4X2w3NG14NkNETm9xNkRoU1hySnlnTkdBQWNCSzJ5MXN2eUU2bWpZUU9iUjZFdTZEVHhBc0hULS1QYUJQcnJ0U3dvSElHSkxOeE9NR1pNMXlfaTE4VEhWa1VWbTF0QWJBdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOMk85MWo1MVVkalVtYVR4VzUyaFVEUGpXWk9FSDBQRzVrLWlId0ZwU0Q4alFlYVlkWFBkTW9qTWprd1kyZFNOOEx0dlBxM0l3bHY5dk9BX3oxd29ta1B6eGFNbHJtY1ZqdlZ5bzlGa0NBSUstTEtYdWdka1ZvTnFQeFotZnZRdk1mY0JzS1lyR2huVmVxNjU2T05iSzFfZTJjbzVoZkVuY3ZaeWJfZWVUSnVaa1AxdllDM3FwdktMZ0k?oc=5</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2051,17 +2051,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Addison Lee partners with Multiverse to build AI and data capability across workforce - taxi-point.co.uk</t>
+          <t>Durham philosopher brings ethical thinking on AI and democracy to global stage - Durham University</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 07:09:05 GMT</t>
+          <t>Tue, 10 Feb 2026 11:16:16 GMT</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNNWszTkZqS2t5a0s4X3V4VkpROHNYQ0ZpU2d1UkZjTEpoaGlyREtDNFhCTHFieGlkaDBxWklyQlpWNmpEcG1JTEVrZW5mNk9Oa0ZEZHNOWmZlRHlXcjBleFlsQ1VvUGV3akY2cW44THlVZnlNNW1jSkhteFA0RW5wYzNIeV9uOWs3TmNFNWs3Zk1DaDZ5bmQ4R2xpTUxka1NKcjM5QmZoZEZmZ1haRUR2bU1rUDA3QU1VZWx3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQbF9EZ3B4TnBNWmw5dnBZZ0pPVkZjbzFaVmVOeXVpUVpxVU9MSFkzbFFuOVhuZng1NEdkWkd0MEt3eG1qeW5Lb2FfYjI4eGREU2x3eVhYU0VxSm1ibWNRdm9uSmlyNFRxU19ISVFvVXE5bnpFUU53amFISGFhd0R4WVd0cVVPY1paUFZiUlFnQ0taNklMZHRIUHBSUkh0VktCYlpZMkZpQ2NRRU9KbEtjUkVlMjVPeXBGdEdxcWMtdGRld3MxdHVLTGF2NEhYN0xOT3c?oc=5</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2081,17 +2081,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AI and the future of professional services - benews.co.uk</t>
+          <t>Escape the rain and discover the world of robotics and AI at Aberdeen Science Centre this half term - Aberdeen &amp; Grampian Chamber of Commerce</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 20:38:47 GMT</t>
+          <t>Tue, 10 Feb 2026 14:13:42 GMT</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE1Ya2FKbzlFemJrOFpLMURsUGlJb25iMXh2cnVQeXo2ZnRWUXpVMlZWMFVMUUhQNGFLZkkxOXVtemRyU3p0UkVjZHBuQ1dpbkhIR1lyQU5qWHhpNk8wRk0yRHA3Tk9KSl9lSExtYl82TEpteWFlS0FocWdMRmk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQWnJuUzI2RXhza0dBajFXZU1CT3g0OHh0YkNpWmZQLWNEYnhXNnUxeE54Q2xvM0h0c3ZOU2tNOGtESlVHNFRDSjM4a19DS25pOTF1RWZGLVhGRG5oeUsxaHdxX3FNTkY1OFRWMXRqVzNDTjNyVXlVTTY5dzF5RjltdXFFTGhLU3J1V1NIdWxSVjBZUmxvSU9LREZRelZhUDBSSm5LQW0tTGFYcUU1NEF3Wk03bDllVnFmSFo4LTNjcHA4ZEVVdFROMFVfcGtucHhx?oc=5</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2111,17 +2111,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Australian tribunal decision helps shape how businesses use facial recognition technology - Pinsent Masons</t>
+          <t>Silicon In Focus Podcast: Building Inclusive Tech Teams: Skills, AI, and the Future of Work - Silicon UK</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 00:59:31 GMT</t>
+          <t>Tue, 10 Feb 2026 12:27:10 GMT</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTFAtTEc3RnRJT2hHOEQ1ZGN5bHJmY243OEEzNGR3eThKdGVGUGw5Nm03UmY0NG9xRnNFZmo5SFBzOU9UeWVQTlRRbUJFd2ExZ3VJR3F6Z3RsR2wwZlA3M29Kd25BTmgzaDhKd1J1TU5saEtpM2FySEZQWVFuRjk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOT2FQc25wdGNXNzJjWEI3RFY1VkVkN0Nvb1M5ZlZQMTh1YVJ0WVhuMWpCNC1iV1o2dXdrSnI0YjZBQ0R0dWxPV0EydVpkSndRdExrek1rblp4SFAzTXJ3OW1SU1paME53LTFGN2hjamIwQXlNQmVDY1VjM3pzN1Q2ejVBd1E5ODN2N3VYQlFnVFh6Qkt3R0Fad3hZMGVLR1BuZFBLR2NyX0xRTl8wb1BxSFpiY25TSXNya0tJQ1YySzIwSzBVSzl1VmN5endpZmNDc042bGFyY9IB3AFBVV95cUxNZ0lyQktSSWR6QWdDRTJLY2xQOWlNYjZ5VkRyRUF5Zm1leFJ3MDdvMmpGS243YjUyNzNST3c5Mjdjc0VKbFNsbEdwaVVhOEFlYnlfejBTM2VES0JLUWZXMURFSE5NSkxLTTdFSnBMZmtjX2VmSFZ4dVJzeTB4a0YwT3k2a0l4SnJVVjRQTDdDNmdneTk1WnZ1RE0zOWVPWnRxdXVnclN5cVN2bjRPMkkxbHk4X0FHa1ZkMkRIR2ZmMzhGaXptZkNkWEplZVVMZkUtM2JRRlBhSFZLdndO?oc=5</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ABB Robotics brings AI-driven automation to life at SLAS 2026 - Drug Target Review</t>
+          <t>NEWS: AI Partnership Aims to Speed Up Discovery of New Medicines - Practice Business</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 18:45:37 GMT</t>
+          <t>Wed, 11 Feb 2026 06:29:01 GMT</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQZkRCbDgxMGVRNXE4WGJ6aTdwR180NGFyWVR4SGxYQ3hlVFlLVnVfTjhqTDdpc3duSERyb2oxQ2xCNTVDcU93UnduSkw3MGVxaF9MdHFVY29oS0k5NEpJRW9tWUlNLUE3bHFPZXJrdE9USlV1RjdMd0hBYTB5VVN3bEg5RFNzMGpLSVYydjl0R2JxMGVBT3dIaDN6WGgtSUhTZ2NjNHBtUVBZNkk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQYzUyNXlaeTJ3LTFZb2RhS05tbkQwU0tqTWdPeUpIbVJlSkFOa2JRQmhnV1ViejBNSmRrQTFINjJ0MFpKN1RxNFN4cGhtNUM1XzhFQ0I2R3BqWVNDNHlRdUs2M2lvWTkyRGlJYXFmUElrXzlfT2VVZm9WdVBSVERDNWNKQlRGSHBFX3dybUU0ckhNak9Oc2ZaUzlB?oc=5</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2171,17 +2171,17 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Should you believe the AI hype? Probably not - The London School of Economics and Political Science</t>
+          <t>Announcing the shortlist for the AI &amp; Software Development Awards 2026 - Computing UK</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 18:33:40 GMT</t>
+          <t>Tue, 10 Feb 2026 14:41:58 GMT</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxObTlrQ2lBMzVjbnF6SUU4dmVpZUwydVZpbk1JWG5CQ2Y1NV9GQlhpY2NuZ09COFpzaUxxTDJjNGFfeGtNLWs4aS12aHlVS3pwUTdocVhrb01Ma0E3YnlHejNBYXR3YVdIQ0M1YlFXQURxd2JFTnNSQk1tbnFibjB4bDRlQmxGcmdodng0VHdiNTJROEVaemVSRnhaWHJ2enVnQ2NV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPSDVzNXFfdDltRGFLRDQwWTRyMnZxSXhKOURMQ2VOOUc5RlNkN19PXzVuNU52NTBNTGJlZDU5SnRwY1RkdHdHUlpDNS1samVIQnUwakM3VS1sZUkwZC1vNmctTnJqN2MxTGpHMzdsNjFwOWd6X2RTRXpvY1RNcVNMbm85NUZfMHNTOFRsZg?oc=5</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2201,17 +2201,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Mainland China’s cloud infrastructure market accelerates to 24% growth in Q3 2025 - Omdia</t>
+          <t>CreaTech Network 2026: Exploring Creativity &amp; AI in Entertainment, Heritage, and Open Tools - The University of Manchester</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 06:51:46 GMT</t>
+          <t>Tue, 10 Feb 2026 15:48:14 GMT</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQOXpOUWI3UVUwSDRzdGRLOTZfdHJTdF9XUFctNVNnc25QaXBURWVoQ1gzckhkSzRtQlhrdEl4dDhrWWNudUJac1BNWkpaLUN1NTgtMGlKczBfVzVlblRaN2d0cUM2X0h5RWR2b2k3UFVEQXNvb2VqRXpzS2dpUVdDbXktdUNtVFo5TzU2VzR6U2pKaUgwQkFnTWVlVjdXcFNtQkY2QXptU3FJOUZxSkhmOU4wR0RleWRsek45Q3hyWVdMeTVUY0Q4Tw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPaHMyWTdfQTNFNzNKcS1zeGIzcW1Pc1RhS3JZV0ZXOV9TMXZvd2l4V2h6aXZSLVYzbmJfd3U5VTloRDk5NW5BaHRyV0NsTnQxeWd5Wld2WFBRMlF2b2c1bGJidGlZWGlFTGQzdzhWc2RtdTZHTEVkYi16UHhyVDZsMWROODZLb3BRRExfTzBURXFLdl9ncm5KM3RrLWxaSzNMMUExYkQ1QW1YV0NNaDlCbTF4TmtCSUZhZmJGRm9rdEMydkFYU1lR?oc=5</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2231,17 +2231,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Industrial Automation Market is Projected to Reach US$ 326.48 Billion by 2032, Driven by Smart Manufacturing and Predictive Maintenance, According to Maximize Market Research - prnewswire.co.uk</t>
+          <t>Former Daily Mail editor tells hacking trial allegations are 'preposterous' - BBC</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 05:31:00 GMT</t>
+          <t>Tue, 10 Feb 2026 19:30:14 GMT</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwJBVV95cUxQanlHeEJQYlVqN0ZwQ2ZqeGJOMksxMlRsUlh5SEllOFhmX0NCLUpnMHFsWEV5dEZEeEI2VWZ1NU0zOGM1RVZweU1tcHkxQ2JSdGFHcmtWdUtLS05JdTBFcGpVU2Nzd3RnU0ZLTEVQSE9wYkNROHMzUmp3QzdGN1k1TDVjX01aZkdJeGdtWnZRdjZEZld1NDZiMHlsUmtiTHJfWFRYQklmaDNLb1VxTk9NRmpieWswWFlaM0djdVRNV05SemE2NnV0OWdPRTBneDdHYW5UVUVUWk93VkVLd3c1NTAyX2dyNUFQeXB6aGR6LTdLUWNEcGhjVG50ekFKZFhJenByQ053RGxUV1lCbkQxMGFtUGlFenZ4SVFrcEh0SzVjR192aXFsWjFILVhoOGgwX2NQZTFfbURhSEJOMFFzTmJVLXFQNGplT1lzM0RqUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5Kelhub0J1VVQ3NHY4a3Uxb3RiS1piWVczSTZWeDBwMnNlMGIwQnRnQTJmdjl1OEZ4V2R3LThRdExnc0lGV2w5M3BGUVA1MzhNZTVLTTRZTC1uQQ?oc=5</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2261,17 +2261,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>How AI and automation are redefining legal practice - Today's Conveyancer</t>
+          <t>Broadcom Wi Fi 8 Launch Extends AI Networking Story Into Enterprises - Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 16:32:34 GMT</t>
+          <t>Wed, 11 Feb 2026 07:09:00 GMT</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE5iSkhWdkxyZFNLeXQwTDlfbUk2MExjbFNfRktUUjhSU2tCWGZpd1NQVjhHMVU5eW5JQ2VTWEptOEs2dDdsUDR2a3JocENDR1ZhRUl6MHpkY005TGhpeEFONU5vaEJfNWdQbHBWb0pLamc5eWczQ3Vybnp6WTU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE9fbUhucEo2a1Fqcl8wQmJiZDgzZWRwU2dtSWc1c3doVV81LUYtZm1PejlpZDA2RWRnQU5DbE02UWhWcHo1OGo2LURQY1VVeDVHRFpKTDR1S2I0TEVkc1RwZGlXTjlEU1dyZ3N6NzdiRTlsSktLcVVxZ1k0SW4?oc=5</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2291,17 +2291,17 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>EU risks losing AI and space computing sovereignty amid Musk's plans - Euronews.com</t>
+          <t>Hospitality Tech360 puts leadership, AI and people at the heart of hospitality tech - The Caterer</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 05:30:26 GMT</t>
+          <t>Tue, 10 Feb 2026 14:21:04 GMT</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPN0FmN2NhWXJUUENlZVRDUWdJUVZwckszRDNBZEVlQzV2TGlxb2JGQ0ZqT1ExUFdpMlhKbzlXakhXMmtPZjVHS2JIQXpiXzhJSUhOaHFpQ2lFc2FZYnpjVHM5MnRXYk1ET0FfVmJKNDQyQUNWYjVrMV9uWmRxbG1vaDBDVzQ5QThOMVhETzZLVVozQ2RueXlfVHVVOEhQWGQ3UXFHWlBhRVpfTnRSek15Um44RlFJbE1neVZGcU5sTXhNWnhPVVloMDI1TQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQVUJLWlFobVJVY1hZSHFobVJaZEZVNXEyUkh6RlpHX2l6emgzbGhHbF9kWmtGLW5QU0k5dm1UcEdyX2dqTXVoamU1TmlhU2tFWmJoZ3Q5aGd6VE1SNlRnZE1QT1JPVkpTVWFiMFNnWWtQQzU0SXRHNkR0LWdENUVjLUZ1VmZfQ1d5MXMtLXg3c3ZkSGJudHdNY3lPUUVmQzl1akgwZ2pBVlV2T1RRTGNnbTU5bzIzUFlX?oc=5</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2321,17 +2321,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Council using AI technology to predict flooding and save social workers’ time - Hexham Courant</t>
+          <t>AI and the future - Atlantic Council</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 05:00:00 GMT</t>
+          <t>Tue, 10 Feb 2026 11:01:20 GMT</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPMnhoay1PT3J2bkZDYlJ6YzkteC1lNVlOTno5YmRvOGh6VjlWUTViQnZmNXlIbmdiNnNhYUpVTjczUlNOanhLN2ljekZVMlM3aWxJUWdoRWxVa1JyTFVPUXBJVlFEVmwya2Uzc0hTT0IwNmZ3VEp6dVMwalNPaDM4SlRkV3hwN1VKcmxLMGFEOEdJTmJaWG1TdmttZVZHTy12OHdJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQRzhpY0tmc21xVjAyVUJnVHB1MUQydmRNRGVpZUhsWDlkb3BqY3dzOC1PZTUxM0hiVjJmWGxJN2ZBVVU2LVI5aEJmMW1Zb0ZWQ194cmxnMlRFOU1wWndWRGVVTHVBa0dZckdhOVVYQUZmZUU5dlVodlpoenVRa0I2elVORk9aUVZoU0J1ZGJfemhwMnVNX25VeVZ3ZXRjMGhORGdqUnF5TQ?oc=5</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -2351,17 +2351,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Technology and older people: bridging the digital divide with empathy, innovation and purpose - telefonica.com</t>
+          <t>Microsoft Confirms Saudi Arabia Datacenter Region Available for Customers to Run Cloud Workloads from Q4 2026 - Microsoft Source</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 16:30:00 GMT</t>
+          <t>Tue, 10 Feb 2026 17:35:19 GMT</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOSUxhWnJGSm5lTTVxZEszelg4NTlOYWdXYXBDLUxYWW1PUUZXN1A5UW9DV2JlbGRRQ3h5aDlHMDlmSXY2SElzS1JwZjJmRW4tSy1HMEt2X2QtMFFfcnBsLXY5WDFFMUdveUt3UW5RWW5qc21LUnNZWEZLd1dzZjJaejBNZzA2dktHbjFfQnhkQzRNTDNaOWNEN1Iyc2FzTWFYWHp0UmUtYWRfZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxNTTNSejlUVVk4aWRpRG5YNDJzRzhVbHhHNHJfVlNQNEphQ0J3RTJ5WHJwMngzWlRqS1RDdnFzdldkb1VTemhmUDV6d19FYXdocHFoODdUTTNiUDZBbS1nVUFiS2FHQi1TU09ocWVkNXdCLS1mYkl6d1YwMGoxSGNwbmFEUG9GSnN1am9sMVR4bFBKY2VzNVdvWmhlMl9xaDVwOHRacnBGV0NCaGFCS0hfUnFJblNBb1BpbTlVSERXbUxZem9OOUFQT1FENmN3UXhXTzRNbHoxQVFrT2VJdTRDMEQxaHVONGZmWGYxR2RR?oc=5</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -2381,17 +2381,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Students deliver AI, automation and digital tools to SMEs - Machinery Market</t>
+          <t>Drive for AI and data to push tech spend over $6trillion - DecisionMarketing</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 11:15:32 GMT</t>
+          <t>Tue, 10 Feb 2026 11:30:00 GMT</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPMG81OW9FeHBYQzVobXB0VDZyaUlQWDlNWEI2M0VGbUVaZmNUR1NZS0pQNEhYSWZWYkdpU0EzYkk0REF1MjVhcGV5SEtYbjI2MUtBYXUwdWZFWnduMGlfSUVxREd3TTdDcm1xcW1pY1FJdWsyS19uZGV2U3d0aHdKVGp1cUo4VnFXa1lmTVFCSVA0YXhSQ3c0ZlViR2FaeXlEYVlMMQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOSFNGcm5xUFVCMS12M1pUWG0zZmpxV2ZjZktGRm9WdFhhMnpnQVhoSzE3ZzJDOFktYkpaYVNPRWpKbjBwZEpGQWxCclZZTWtQQ0lVVWs1RXc5MWVQcnJkYjRXY2xGNUtrXzNnbHAyVjdHVXZ1Y1c0RmcxZGVSSHZBV0t6MDVScndqUGV5OFo4aTZDNnd4MEh1d0FpNF8?oc=5</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -2411,17 +2411,17 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AI, edge and colo: Nokia’s Neutral Host Index redraws telecom’s $200bn shared-infra map - TelcoTitans.com</t>
+          <t>AI’s New Bottleneck: Power Supply, Not Chips – Asian Chemical Connections - ICIS</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 05:03:47 GMT</t>
+          <t>Wed, 11 Feb 2026 05:37:57 GMT</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOY0VjT243eU5FNXF5aUExcDlfR3lhRGd4NWxjbWRzbTZ4MWFuMk90TXpBb0s2SWs4UlNNNGxvczRYeW5qNDhYbnVyZFl1cXVkTXdhTktOZklVVlBscVJDY1lSU20yUjhKZ3h6eUVUUVhETm9xc1NlY2kxSUZBU29mMWZPaVlFT1o3UUdYVktjRFE5enR5cG4wdVF3cVdPUmFvS1JLTW5TWnF1bXdhT3JBeUVJQUlDalQyTmd2R2o2VDBzeFpLUGt5amltTEdxT0tn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPMXFXbEVuWlBpNjh2dmJENkRPeTVpUVFVdVU5NW91WXJxaV9sQ1FYNXYyUXdlTHJ3WkxxajZpVWNrYWMwS2hmeEo4SnlDbUZpTGl3Skpyd1NNTHlLd2ZUQTNNVnV5ZHNYSkpUYmtEX05mRzhySTRRRFp6UVVuZ2V1YjV6RlFjck5IUWhjNHpjVW42UTlrcWZTLVhJdG9iNnc?oc=5</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>STMicroelectronics introduces the first automotive microcontroller with AI acceleration for edge intelligence - Yahoo Finance UK</t>
+          <t>BBC set to launch AI Unpacked Week in March - BBC</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 07:00:00 GMT</t>
+          <t>Tue, 10 Feb 2026 09:00:00 GMT</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNMHVKaUo1Y0Q0TUVhMWZtZ3Q3bkJteUlPbFF0Smd1RktaZDVZb1dfOXR3Z0V1RnRmVjllb1k5SEI5dHp3N2ZSNlFJOUg4YVhwTG5vb3JfY1B3NXotZEZ4ai1KbkpMMUVESHFIX2VFYlBaYzRXYUw5WTNEeWxyb3pZNVFwVkhnMENWQUdGNWVuRkJmNXZwMF9zRmRNdHYyQkNiZVF0aFlsaUp5YWNOZGZJTg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTFBZVjlQN3g4Si02WTdkcEswUGxNOUFhd1Y1djNXMFh4N1QzdW1rVG1ZaHg3MlFaRFQycXFCMFpxaF8yd3pFMk9zTXhUcmJyUDlGRWpRNnJjemZJWTZyajNteTlCX3hBdjdDMV9NQnVDbjJCZw?oc=5</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -2471,17 +2471,17 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>The AI Divide - Foreign Affairs</t>
+          <t>Cadence introduces ChipStack AI tool to automate chip design and verification - New Electronics</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 05:00:00 GMT</t>
+          <t>Tue, 10 Feb 2026 22:55:09 GMT</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTFAtd1A2ekhhSC11Ym9WZ3g4N1VhR0JSQ0h1Rk15ME5IYzh3MmVoQWl1THFhX2FuY1pUWDM1bDJUZVFZLVJtQ2F1dzB2akJxRVA0elVZSW9Yd3B3ajRVX3VXZmV5YjY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQdTRjV2plWTlqb3phX1V0cC1vZm1kWHROTWdWdW11X28tcE9JWUQ0UXNnTzhuU2E2dVlkRjZSaXhLTXRrQVEtZTJTOURaNXZHNG9rcXFLRmZzTURzNTFQcHdYNVV6WEFmM1ZfVDlrbmI3MThBb0tybzF6MUVEdkZoUEMxOXFLcmRNM04xVHpaeWZQeS1jMy1GdGFPUFNzdnF0R3k0LWJwWmV2bnI2bHEwbzBnV2xGTUJiQmUyRjQzWU8?oc=5</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -2501,17 +2501,17 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AI experts warn of ‘zombie algorithm phenomenon’ impacting imaging - Radiology Business</t>
+          <t>GitLab pushes agentic AI to orchestrate software delivery - IT Brief UK</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 06:05:29 GMT</t>
+          <t>Tue, 10 Feb 2026 23:05:00 GMT</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPOGFvMWNiTkRHcTR4UHNmaHRSWWlxb0pZcUpwVW16RG5aMjlhYnpCd29WS1NZQm8tdjQtTGNtSkZHYVlZLWVONjNia3BFWVF3a1lNN2Q5TUIwNVNTZjZ6ZFlQb1FRU3VpeDBSX3VjWVZrbTRoemwtMnJqVFM3UGVsc0MyUDZiY3JnelRiTDBnWlNfeWZ0eURTVmtwS3BJU1VRcUpyakpERG5rR0dkZHBxWVk4RFJ0eUtoZ3h3YmRYOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOTlA2QTdwVUdWcy1VNGxCMG9EZGJqM0tZVnJBbU1JRWpGX0RxeEFHZnd4VWpvS3Rob3NGNlNUM3pDaXhhcGtDVnV1S19XSndqNzB3NEoxVHM1YnNVdHNrYkpTLUJYS2FlQzZRZWd3TXVoc3lrYmUxTm9qd3ItTm9iVm5oaUZwTFJBRnBNNHZ3?oc=5</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -2531,17 +2531,17 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Google Cloud and Liberty Global sign 5 year deal - rcrwireless.com</t>
+          <t>The Real Cost of the UK’s ‘Free AI Training for All’ is Democracy - Tech Policy Press</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 18:37:10 GMT</t>
+          <t>Tue, 10 Feb 2026 21:46:08 GMT</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE9jRU54VVcweFpiSTlaMkJlWERhSERQeFhuM05jQkl3Vnl3Z25FR2xOdk1vVXNrWmNLaWNBOE1MS3FRdEdBN0R0VjFFQXpOU1EzVkY3TUQxYlZFcmltYXQ5U0ViNjh4ZEg3VWY4eVJFRnVQUTIwVEdVRGs2dHU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNSV9sWF9hdE9uTjVQWEJMZllsZjhtS2JKTHhLaHNERXpVR0ZFQnVCVHQwUmVva0JUcDZrZGJlTWEzbW1ERUdPaEF1bHhTT3BTT3Q0X3laWWVOOWloUk9MaUx1OFBJdHFMeERXZGg5UTk0cG9nSHJONEJzV2JETFRaOFRCeTZnaGozSFFvUXpta1I?oc=5</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -2561,17 +2561,17 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AI model accelerates antibody production and clone selection - News-Medical</t>
+          <t>Exclusive-ByteDance developing AI chip, in manufacturing talks with Samsung, sources say - Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 03:41:00 GMT</t>
+          <t>Wed, 11 Feb 2026 04:47:00 GMT</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNSlFXdTNWVktnZm5MWVBRcm5oaHMxc2l0U2ZwVTEwZGR1elctR0ViZ3p4dnQwcmp3MDdlN0FhcmE3SE95WkpQMk9sNHk1dVE3UVFaemNmUUJWSWNfVi1KM2RyUVpyVE1Ia2cwd3Fkb2hXZGs2c282b2FGc294WnluMTNzM19NcGszOHBHT1JKUllXcy1nTnowaV81OThnVzQtd1JocUJpRjFiNEhr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOSm83V3o3YXRmRkduOXRCbkV4a3FHeWpPbnJhc25OekNHQ2ZmdWdqZ24xa2stVTVwei0yTVg1b0kzR244MWR4NG9jUTFMYjFMYkgwNWtDZ2x3V3YwRDNzYVZvSGtQZlBueUh5UFpESUd5eUFjR1FaQ1czVzBSQnNzRGlPc1NaUXJRNy12ZGtxVDM?oc=5</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -2591,17 +2591,17 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Special Issue: The World of Fluid Technology and Moving People - openDemocracy</t>
+          <t>Disciplined Autonomy: How AI and sUAS Will Redefine Security, Safety, Emergency Response, and Military Operations - Small Wars Journal</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 11:35:13 GMT</t>
+          <t>Wed, 11 Feb 2026 06:05:12 GMT</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE91SDYwWUFyN19MUmY3cXM1eWNkeUlhSnE4Y0U4ZGV5aF9FbW1JMjBOUlhDMjU2WlRxckticHFuZTVoZWRPaUxXaTFJWWwxcVY4RnQ4a0FjeURFa0hxTjdQX2RSckNkYk9KRGNQSkVIR3JEQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE1aVlpiQzZqRXpqNjNjRG0tekRpOE85ZlhzelNHVGFIcGw1aE5RSDJYRWZTWU5JUXhkTmpNeUFIX3FIWlAydWh6T1JlQzA5S0dEM0U5NV9WcVIyRFlKQ2xubW55U3BBVVdCNmVrWUNn?oc=5</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AI literacy and competency: The key to workforce readiness - Relocate magazine</t>
+          <t>World Defense Show Day 3: Saudis eye AI, and a local defense giant transforms - Breaking Defense</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 15:02:04 GMT</t>
+          <t>Tue, 10 Feb 2026 20:07:25 GMT</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQbEhZTGlqWktJNXBSd2dsTDJfSWhLOWJDbnpUcngteE15RUxDTklOTTJPNFNUVEhPT2pMYldVdE1feUhNVlhfWnRETzEtRk9PNTFENktTU2ZKSVBlMmY2WWNKZFk0UVZsRlR4VURQX3ZLemotLV91bEpQc2lSV21fUnlJQXJqYkU4bi1VVHdhejZxYzQwQXplS3VXaldIYTBOTTlBc0pKU1NkQ3JnakxkeXlyRHY5TEpQT1RtZzlTRUk0VUFNVVNTSg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE1WQ0lTOW9fbVhrOFk2ZW1jdUZpU1VJM25MUEVlbDlTZ3hiXzAzd0tFWTZTYzVGWXRxT29fRnd4dGZma1FNZkpXSU1za1pnVmFibGsySmhzLXNYc0t0RnlCbEM1azcwaXlkZVJobXpxNXBpSjdN?oc=5</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -2651,17 +2651,17 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Majority of young people worry AI will be used to make inappropriate images of them - The Independent</t>
+          <t>'Introduction to AI and ChatGPT' workshop in Haverfordwest - The Western Telegraph</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 00:03:00 GMT</t>
+          <t>Wed, 11 Feb 2026 06:00:00 GMT</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNZ3hhUXE3allXQkhlN0hOR2kzNXNIRnMwX3Bqczh4c1JuYm1vR1hkb2hxVEZXc3FoaGZQU01nM0ZySTExMFVqVHhOZkgwbnhqNV9KZFNCcVQ3alFuVXFkWkV6aS1lTFRFdC0xc0dnVlJPMmF4ajBMQ0Z5MU5yUnlNWUw4X3p1X3pNS2FyRjZSN2ZqSEZmV3FDNVo2VFZmUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPbHVBanRLX3dTQnNiM3M1SWRSM2tsSy1YRWhHbjdhV3Q3RDBwMHZGQ1ZJcmlTNWVRbnhqX0wzZXpuQ2dRMWZZcmNNNFN0a3k0TUJGTXJIRDF1VGgtSkx0ZERCOWtuWG5FQmxvNU9ubDFCUm55NVpWRDB0Uko3R2F0eVVoNks5czFNXzdRcU1qdkMya3Jtb3JEMW9kWGlIU0drV2xNdlVn?oc=5</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Looking At The Alibaba Group Holding (NYSE:BABA) Narrative After Mixed Cloud And Retail Signals - Yahoo Finance UK</t>
+          <t>Airlines' tentative approach to AI - PhocusWire</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 01:11:00 GMT</t>
+          <t>Wed, 11 Feb 2026 06:04:02 GMT</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQUG1ja2ZsRG9ZVDU4eklNTng2Unhna196ZDFheW9PVm9YQ3lBbmlDVXdQTkVaQloweGk2V0RJaERBdUM1dWFYa3pOYkI4eF9TR1VuOG9kNGExV3MwM0kzTlB5czJnODZaVVFMTnNyNEZvYnZQZkpySUtQXzV1djdRNmdEUG90b0RGbHNN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE15Q0Q0VVZhY3hXMHcxSzR5REt2dEsycGY3X3d1R1VHRnBCOE1sNDlMRllJX05DYzFCQWZWYmFvRUs3Y0M1QlRqTGF6X0pNcWF0WFNfakUxTzlIZ3Mx?oc=5</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -2711,17 +2711,17 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AI chatbots and competition law: A look into the Meta WhatsApp antitrust investigations | Insights - TLT LLP</t>
+          <t>Brandwatch and Blackbird.AI to deliver advanced IEAC to NATO - ADS Advance</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 11:56:19 GMT</t>
+          <t>Tue, 10 Feb 2026 15:46:00 GMT</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPb2h2MFQwRHpQS3NuZG9ra1BZWVJtSEtXWGo1SVBaRFlzbWlGOURBZWxNYWNZMEdHZW9EMzRBU0FqTHBFRjB5T0xsTWhfQTJsZFFaVDdrekVSUUpwNGVxZ0JOQnpWWjAzY0x1UFgtM0RDNVBXT2NlRXF1Nl81c0JEZGNMTWJPWEZWTDVOR1ZGRkZUSXYtQVVRUXJFbU9VbEUtckNQbHQzT0NTQlU3cUR2VW85ay1wREVmOGljNC1oTkp6YW5zVEwxYkRDZVNFTjA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPVkFNd3ViOGV3QnRsZXJFbm1nNkJtQzNQVURwOUxMUlJxWGRCZFRmcmZxMERUOC01UU9OY29vMzJfQ1Ftal9obXRzVEVvV3gtSUhGYVpOS3NVd3IwRjUtU1NpbW9tWlpfRFpKX1MtcE9lMHNNMldNYmVCNFh4aWJEVXlnNDNIbXU5ZTNiLWRLcHpWR2U4NVhqLThn?oc=5</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -2741,17 +2741,17 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>’AI can be helpful for learning if it’s used in a safe way’ - The Mirror</t>
+          <t>Spotify eyes AI ‘derivatives’ as new revenue stream for artists – says its tech to let fans make remixes and covers is ready - Music Business Worldwide</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 06:00:00 GMT</t>
+          <t>Tue, 10 Feb 2026 20:17:54 GMT</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxQMUFqZEVsTFFwUHZXdFlJTklQUnRDUTFQc0pMMWFESWxzLUxtMkFyTmVfS2cwNjJnUVVrN05taW5taFpWRnVCMWU4eUNMbXhfbmRBVmdTbExvRmFLVEFlWXkySW1UdzBIRDk1T3pkTFpINGdQc1h6TG9vUWVaMW9FZHJQQVrSAYoBQVVfeXFMUDRjU19CQXdSczhFY05JTGFxNjUydG1iSzRuNjlJOEp3WTlYWXhXUzl2al9VSUE4UTI0VGRNNmQ3OHctWmZvOEhMSURGX29GRUZYTVJXZ2NZYlR1ZXBuX2QxOHNEa1V1Nmd4Ui14NTczNlZWWGgxekZvMmd2RUVSVHJaUWVNRVduY3pB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxNRWVIcGREN0dDODV5N2gwUGZlVGR0elIzLS15TWJuTkZ4VmxrcTE4eVNRNDhCVzh6XzAyaHFvOHRIWXlQUE1RQkZjOEtyU0xGU0s3azhIYnR6d1ctbXhMMnVZZFNodTFxU3RIcGRhOGVwRFpKN3JKQ1VnWVp5Q2FMWTMtZENnUVdwTTgyeEJNMENaaXFZWXp2d0cyb19SVDNudVA1OERmbGFLT3EteXR3QzJaOHNwMGxVR3BTdU44TTgxXzVMMUZyamFEUUdjd2Uxbks3dGZvaDVQeUpmY3hkYVJSRkt1Ymc1UTQtM2QxN0lNZw?oc=5</t>
         </is>
       </c>
       <c r="F78" t="n">
@@ -2771,17 +2771,17 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026 CreaTech Network Series: Creativity and AI - The University of Manchester</t>
+          <t>How the use of AI and 'deepfakes' plays a role in the search for Nancy Guthrie - NPR</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 10:41:31 GMT</t>
+          <t>Tue, 10 Feb 2026 10:00:00 GMT</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNeU5KWkxMT3h1MUxUUThXd292MElQcktjUDhNODh1RWl5V0JBM0R1bVlXQk9TZC1vSktuNHV3QzZqMjJuRUpNVWJLWjU1dlRISC1oV292ZXpDaVJicFRQaVBUYmI0NmVYUEE5aUZtOUNsODdFb2xGcGtVMXh3Y1lVWXprbWN4V2JBZ2Q1WXZldkc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTFBaVWdvUkFSRWF2V3VKalFvX0x2UDVvT2tVaU5qQ19ZVEFTRV9CQWtNSzdGWV9uZDdZWGhYLXY2NHNYdlJvM0FfN1pXSUNleWdpSE9XVGRSbWx3bDFpc3ZLOF9lUlhHQTJPY2ZtVVFkdEZUc3JSUFB6QW54TQ?oc=5</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -2801,17 +2801,17 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AI, homework and friendship: Why more children are opening up to chatbots - ITVX</t>
+          <t>Experts urge Ofcom to probe AI’s role in fake news after major incidents - The Independent</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 17:00:53 GMT</t>
+          <t>Wed, 11 Feb 2026 00:01:00 GMT</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQTU5BVUZ3dDNqNXBNN3ZjNmtDTXFQWXFYQ0M5X2NEdTEzVXlaR1BOdGZxLVlYX1N4eXI0aEJudzhHcTF0NVQ2WlFqR0RLQVNEbnlEeGR0OWFBVGI3QzRnQTh1dzBzZU9zcllzTm1rbDNySDJwNnR0b1V5MVFJY2dhMmF2RndnZW1PdjFzbnRUODNKRExpcF9nNVJWMGR5UnQ2WkEybEJTMUNBLVU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOdTlKQ0hmQzFqSEE1NU9fM1IwQi1GcHI2d3JtSkVCWGpmYXZXalJVeE44THVUeVlEc19md3FXblpVRnAyUG9neDNTQklLUkJURGliNVpvaUdXZFpYb0JOTHZySmpNNWRtZW5Nak02c2RSZ090Wld5UHdfWWxlWEV3Tl85enZPNXZub2ZVUmpsTlY?oc=5</t>
         </is>
       </c>
       <c r="F80" t="n">
@@ -2831,17 +2831,17 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Academics moving away from outright bans of AI, study finds - Times Higher Education</t>
+          <t>Is AI getting smarter or just getting better at faking it? - Psychology Today</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 00:35:17 GMT</t>
+          <t>Tue, 10 Feb 2026 10:58:25 GMT</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPMzB1YzVsTUhjUzl6b2M5cC03TWlyRWdCaVhxeUJhZ1VuV1BjNlNET0VxU1dtUXdmR1dFNGJSeGVWZlNuOXV3MHBrbExzaGV1UWoySjBtYlFjQXF3TUpTLVRYTWFxTm9YRkNudGx6UEQ1cWxJTl9QbUF5RVhBdXd4SkdWTnB5b19hR1NQREh5M1QyM19lSEc4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOMmZOQXhWQldBVXA4Tmg3OWgzekRseW43cmlZbFFuVUhCTXFnTkFDTGNEYlVyZWdtakZzUlRGUV9OUjN6ZzlCd0JmaW9GNTh4QUlEdXhUSFR4WndVdnZ2SmljZXVQX3ctdlVhc1dmWlpFeC1HLVh5bzgzR3RBcG9YZzJFMWZQSE9aSlFPWXJaamFfSW9WVm5aNW90M0V6ZHdlTHFQUktuaFVSSC050gGyAUFVX3lxTE1LcUZETWdkOW9FUEhIYi0wak1DY3Bncy1XTV9qZVBFejlER1I2MFVyRl9MNUhXUnhndmYxWnJBODFsWnhPZVhFNDFRcUpGVVNEeXVycW5MYVc5cmFDNG9leHZCRVR4SWI1ZHlCUjhQZ2ctUElpX1I4cjZJOEdCYjh4d19Xcmh5TGg1LWR0NE44a1ZxZWhQQS1zZEZ4dXIxeG4yZ3Z3blNHQ0FNWFprNFBhMkE?oc=5</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -2861,17 +2861,17 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>From Quantum Threat to AI Exposure: Why Security Is Converging Faster Than Enterprises Expect - The Quantum Insider</t>
+          <t>Empower launches embedded silicon capacitors for next-generation AI and HPC chips - New Electronics</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 13:36:09 GMT</t>
+          <t>Tue, 10 Feb 2026 22:44:07 GMT</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPeDJUSjh3RUhVOGc3eXhGRm1nbEVMRWMwNl94LXlKRkh0NjFDNmNOdHNySDBfUHg1MmRMOFBOVFBYRGVpU1Y3RGhWOXNvcVpvU29tVFZfblBjeXFBUXA1MWlTSTF1ZXVZUEJ2akNDNEYzNTZzbmJ6clMxaTVyYWw0a05Zb1hCU1k1cGNaWFR3d0dFVmJ5ZllmOWlNcEo2TktDVTJaNmpNOTZjSU1nd0YzNHVSTnpxT3VUdk5mT1h5NXQ1YUhWY0JFR0tSRkZUWFU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxOQ283d3MwOEE0eDFleTFIM082VVlCS2FWZFNLeExqS1NWNU9MY0FETnpEd2V6ZnAyRTNDSnlxSXVuYVRMbV9fZnp1Vmc3X1dfcTNJUVZ2R1czYnFNVVE2b25OZVpvb2VVdGk2VkZTT01MWnUyRUJUU2JmOS1lT1p0bGREV0pNRzdtVkpEZGtUVjBlaTl2SUZsMjBzeDJxQlFkbk0wNHJLa1JjemlHdnpuYVJ6c0V3c294MlRidTZZRjl3OXJ5OU9lLUw5NmN5RnV6UFVad3VR?oc=5</t>
         </is>
       </c>
       <c r="F82" t="n">
@@ -2891,17 +2891,17 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Datavault AI Sets Bold Revenue Targets With US$150m AI And Web3 Plan - Yahoo Finance</t>
+          <t>No, the human-robot singularity isn’t here. But we must take action to govern AI | Samuel Woolley - The Guardian</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 04:28:00 GMT</t>
+          <t>Tue, 10 Feb 2026 16:17:00 GMT</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxOTVlKRjBLWi1nc1pPazNBX3lIUHBRT3kwNHZRQmEzYVBxUGFjTGhKbWZubkNFVnVxYlNEZFZ1U1VhZ0JaS3R6eHRNTDZuUjF2NjQ3SlJfc1JQMUcyNDJ1YV8yWS1tdjVmamhNdWpLZ3hVclhYSDk0eDJ1UGpRMnM1YllR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQeTlqM19rUXVLZHE4Y2RzNVVSUl8zRDBvN2lSWWlHZEJTNW1OQWR0dHp4bVBVZWVpaWpuOU8xemxSOVpZNTV4dXhsZUJKTTZvT282a1FGWlBRZHloNmdrWmtpblliSnpEald1VExmWDFfUUVLdl9ZWXg3M2pWSkxCTURTX3pZSUItdXlLZjJHQl8?oc=5</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>US software stocks tumble sparks concerns that AI trade is reshaping markets - Reuters</t>
+          <t>A Silent Arsenal: State Hacking and the Emerging Digital Order - ISPI - Istituto per gli Studi di Politica Internazionale</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 11:03:16 GMT</t>
+          <t>Tue, 10 Feb 2026 10:08:38 GMT</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQNWU2VDZkT1E5TmdpMXF5MkRqdU0yZ2VqN29iZ0dQRUlQZFRCMjVWTktEOU9kM3dhSDJUeFQ4NVZ3aGZrQ2RtSkRZYUE0MkJleEcxbnRQTDFFN0FCdEtJUTY1eUlKY3JFd2pJcmhHRjZ1N3c5aVJoRlI1LXF2RkNkaWQyc290X0tSMHpmQVlKbDZNZ1dISDRrcmZaSW01OTZYSmQ2SjZyamV4RFV5dkRYZ3lhMUFKbkp6Q3UzTDZzNmlUazZWYU9Ra29UZGoyamp6?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNZGc5ZFZSZUpBcnk1aEFMaTdvVmhoSklrUVlwY2tGUTU1ZU01UTI4X3BDQ05CSjlId3VmZnQwVk0weEhWNEZRUERsUndERTR1Rno0aFJEVFhEdHROZ0lvbnZDZ01oTkdZc1B0d0huMHpKd19oSHUyZC0xdmVXdDZoczJtUFJiTWpqbE1FUm9xQ0pxbWNEYTlzZmVHbHBUNnR4MXV2b0libmZ2TEd5UXc?oc=5</t>
         </is>
       </c>
       <c r="F84" t="n">
@@ -2951,17 +2951,17 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>£10 million expansion to Milton Keynes data centre to support AI and advanced computing - Milton Keynes Citizen</t>
+          <t>The Atlantic’s March Cover: Josh Tyrangiel on AI and the Future of Work—“What’s the Worst That Could Happen?” - The Atlantic</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 09:00:00 GMT</t>
+          <t>Tue, 10 Feb 2026 13:24:16 GMT</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPb3VqWks2ME96azdCVEdFVTVQbFpGU0hMMzliVEhiSEo5ZmZiOHJhdTBQZzBadEt2eURkcW5OQkR2TFA1Q2tHOUF2TWh6Vld2blFTQVRxUzB6OHFpNUFZUENqZnphaTlpQmQ2UE9GTjdDR3RyZzR1X1dna1JFdkJZVDdzTTFaWlRvNFM3ajFoU3J4NGJ6NElhc1VMRVpjekpTWGVIOEZEek1hTUM5cGo4NXVMeTI2Zjh3UkYzYVdFWTktSTJOMGVlRGRXbGdMa25ja0FVM19R?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQa09QUGtfZUZPX3hOOWFkZzU0dkVXeDE1YmY3dGhmV0pMVmlxUnphM2FaajJodXJTOGZzYkstaFhteTg2VmZ6bjJsel82TmEtVUdkLU03dnRrOUJoYnlidW1xczI3eHpaVFRsaUtYTUZDOWV1N0I1ZXlYSHpvYXA2dW1vem50am5jaS10VW9BaWFFVTJmZ2lQeVh0aXhyS3RRbVhj?oc=5</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Science Minister says AI can bring stronger North East communities and renewed pride of place - Chronicle Live</t>
+          <t>AI changes forecasting — But governance still wins - Wolters Kluwer</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 01:08:00 GMT</t>
+          <t>Wed, 11 Feb 2026 05:17:51 GMT</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNTVVFMDJWRVJKNG80cW1pX1FJSWFxZ1FqRlUwMmxoclhqQWJETjZTOGJ4dml0NUFya0hYcEtJcnRHV3JuQUVFMHU4ZkZhUWdXTFJhQUdhVlhqU19iMUwwZ0ZNZlhPNU9NcWM0TnFmbnNMdEpMVXctSS1IUFhVcU8ydGxvMnZva3ljWWlvc1h6aFBtRW050gGaAUFVX3lxTE1IQ3dSejV6V3h6eTZJQzl6MDlXVG8tckZ0bV84Z2ktNE1IUjFyU2gwSXhMLThGS2xadElDYlJ3VDV1d2xkYklKbGhyT0haWGtYalR0ak1XelB6X3BkUXI2TE9mZ09BZ2tPdWkxZ0s0UHVkQ3ZtUHJfc0xJTVlSRGNhaVJTNVdUbkJOUF94cEFpUlpMY0JHVDNTWVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNRnF1SVU0ZEZ3LWk2RVE5eWhteGI1X3lXRG5qb0dxSmVTY1lHSDhPaGNiY2lXeGEwSk5TZUR4cllmYkhSelY5cGpHMDhycTlvOEhJWmpRTkxDLVBDdHhzUGwyUHI5dWY1VlRjR0JLcGQtZVRfRFI5ZWJqczZKd1FLNFVfRkdrX2VtZnRBZTZmRHg2c3hjQUZIZ2ZxTjhQdw?oc=5</t>
         </is>
       </c>
       <c r="F86" t="n">
@@ -3011,17 +3011,17 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Experian caught in the AI crossfire, but fundamentals still standing, says UBS - Yahoo Finance UK</t>
+          <t>AI will boost games not break them, says ‘Clash of Clans’ maker - Financial Times</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 14:12:00 GMT</t>
+          <t>Tue, 10 Feb 2026 10:00:06 GMT</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOTTJiQXQxY2RlcXdfSi1WdXVUVUpiV2I2czhyOVdFNktZWjVpLXdDd1lReFhINEFTMGFXYk5naHZzQXdTSDgzN0k5N0tRRGdBYmV3czc5T2VEQ1o0TWE5WXpDblBITHNmel9LNU5iQTl3ZnJRTEFIb0hteUg4X2llbWlGTUl4TkZLUnFPNUlwa2NORmd1?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE9lWDk2MVhfY0JLM1ZwWkVhOHFrY1ZlS3J3RmxZNjBPRG45MS14SHE5eUxnNUs2TGpKNWxjNUF2X1Vha1hFZFFtSS1xY2t5UTh2b1prSHAzVEZsbGhxZUxaNXdqeXY1WlhfZ2d0bDYyeWI?oc=5</t>
         </is>
       </c>
       <c r="F87" t="n">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>As AI enters the operating room, reports arise of botched surgeries and misidentified body parts - Reuters</t>
+          <t>Startup Stage: Altek AI wants to use AI to improve hotel guest communications - PhocusWire</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 11:30:00 GMT</t>
+          <t>Wed, 11 Feb 2026 07:04:12 GMT</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxPb0EwdkM3R2tVX2RwczFRZFRnUGFBYlRoWG1Yb0d1Ul9XVHNvRUZzVnU5VThqZ1ZUVDFhc05SWG0zWTBDa1ZKLW04TXA2M1JHOGs1elZISTBhaHhvd1pGR05xaldGQ0xtRzNZUElvZk9IU1BIOWlLVDBIV0FZZnZ3V0lickNVbWZ1TWtPcjJtMHpFQV92QjhoNk9jUWFRcWIzZjFmV1cwYmRZRGRFR3Y2TU5CXy1STmZ5SkU5LVpyUDNCbzk5?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE9NeHU4UzZmTTZaVGhua1FGcE1OaVY0YTJ3RDVEUE9oTGdtQk1JTlBMLWRkNW1pVWd0bEowbjA3LXpxY1NXRHJxc2RxNFQ3eUNhd1ROb05JaFpKLVU1MFE?oc=5</t>
         </is>
       </c>
       <c r="F88" t="n">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Intel’s AI And GPU Pivot Puts Valuation And Momentum In Focus - Yahoo Finance</t>
+          <t>Are video game developers using AI? Players want to know, but the rules are patchy - The Conversation</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 03:10:00 GMT</t>
+          <t>Tue, 10 Feb 2026 23:19:16 GMT</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1oUWF5Ny1CX2ZvVE9ldUZzal9ZRlc5dDFhTUowaUp5NUFyVVIyRXhyd280QmlwU3htbnBsMDJqM3RzRzZWZ21zQ215SU50NmZzOEtWODVYNFZhUlY5TGhGZ3YyNDdxVmd4OENuaEZwczFPUVg2dUNjQg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNY3RRVGdBMHJDRWlkRkk5NGlVbXk0SlFPZTNWVFVmSEZ5S0VRN3RzODhqT2FqdUxvS2RTcUxkcEcyVHFYYVczUFpvYlpPUVY2Rm4xckFZZnZOOWZBcUdlTmFobVlRODB2TE1nQVZILW9pRVNhZkVrdDJLSk9YaURkVms2RmhJX3B5LXJZTU4yb1hWYUtyVkxBQ1BsQlNmWnoxMFpPR3lwSk1GeWNQbmFhRzdkeXB5QQ?oc=5</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -3091,27 +3091,27 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>The Modern Insider Threat: Shadow IT, BYOD, and Trade Secrets - Seyfarth Shaw</t>
+          <t>University Seminars Explore AI, and Also the Medieval World - Dartmouth</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 20:21:58 GMT</t>
+          <t>Tue, 10 Feb 2026 15:34:27 GMT</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQVXpXMVN1NDdoTk1QcldHSFlsWFVPa21BZ3JqeUltQVRzdDU4NlBGUlNLUk5EdEp3UWtJYjZDbVY3UE1CSVp3YTNqZzZiZWVIQ003NFNOcXZiMTlFZnRNUWxKdkJya1g5S09XeW1US09sWDl2cFpwenJHc3Vzb0F0NVBWMnFaWXF5cDNjV1Fnb1RHQUltYjhnZWdqU2ZGUFl0TnN1UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPQ0JIaktHa2FDbFJuNTIxd1d6WXpQYkZsVkxaX1R3c0NwX2dERkwzaHJhdFd2R05MMGpmcEctNjNxVGNoWEx6Vk1YX0VDcXdxUkd0dXdIcnNmaGtYdlhrSTBwTVZJbDBvWmluQU5MOWNUd3ljWHAtWVV2ZndDY1VYeDNrVTZrcTZUQUZ2ek9xd29paVBheVFjWldR?oc=5</t>
         </is>
       </c>
       <c r="F90" t="n">
@@ -3121,27 +3121,27 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Inside employee misconduct rings: closing blind spots on fraud and theft - hcamag.com</t>
+          <t>Why the OpenClaw AI agent is a ‘privacy nightmare’ - Northeastern Global News</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 20:41:28 GMT</t>
+          <t>Tue, 10 Feb 2026 20:18:26 GMT</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQRUdUM0FQWkpUVnBkbE4wbzJGZzRCSlNrTDNfN05vZjE2RUktWWtVZ1VzTkhXODl5UnZzQUpObEllWVFDY1FQWGJOSzlzT1B4NExmWlFNSmhpZjVqNzRfU1BiUXQzZVZYNVhYNTRNSV94VTlTUTQwYlk3T05WMW1YQlN1VVM1SEhFTGJYNjA2ZG1ud05TSDRVak01Nm5HLVJfM0NZcXFrNnZLLWNia2pWZTd0MUh1OXliak5qTEZ3M2NyNjdmMlRMNDFIeVg3ZkU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE1LVENWSG5FZElMZzNVUXplWFIzVmRwdU0xSnBvdFFiWEJfbXJHNDVzLWtXRkREZ1J3RHVwVkdkdDl0UDcyMk96OU5sNnI0Y2dNTTZlSWN0c2hIaFZRb3pBUl9wYnNIdHFHUE1URFBLaE02QQ?oc=5</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -3151,27 +3151,27 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>SD Public Integrity Unit fields 47 complaints, 4 criminal charges - aberdeennews.com</t>
+          <t>'Just working towards her pension' - woman settles discrimination case - BBC</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 09:01:00 GMT</t>
+          <t>Tue, 10 Feb 2026 15:28:20 GMT</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxOZ0o1WjdvUzZQV2YtWTZDc2JMU3RjVWtPUVhvOTlKYUEtY0FzUHJXWUV0eFdtYlZzcTJXSzFNeEJiZjNHQTFvVEZyTkNFa1BVWUlSd2lOa2dkMW1OSUdaSU8zQnItSlk5dXN4T0FJb04zd1ozWHRXdENzTGcxTVp5cWo4MnFZbkxiLWpMc3pMbktGdXZLWVhFc2Q3bUkwc0tHQUE4WV9ZTHoybTFRLXBPaHVkbFVubUlnS09mam9ndEZwOE1fMnBUd180M19YbGZteS1IRGFjN1ZkMlVVOHA3SzhzcDJxa2pieFNYV2dsZVdTQTBfeEIwOF9zaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE96ZmdRbS1uS0tSMVVlZHhZX09Cang2QkNIZEJlaUlrNFBEZXVoM21DQ2VoLS1JVUFYUkxKM2J2cWJtSTBMa3I3V2pFZ0ZuTWMwME1QQkdOZ0d3QQ?oc=5</t>
         </is>
       </c>
       <c r="F92" t="n">
@@ -3181,27 +3181,27 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>NEWS: Social media giants made €32m from scam ads aimed at Irish users - AML Intelligence</t>
+          <t>Ransomware hackers say NO to Data Exfiltration and YES to Encryption - Cybersecurity Insiders</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 01:59:17 GMT</t>
+          <t>Wed, 11 Feb 2026 06:39:52 GMT</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQMWNXbExxZUxfTlJ3SmlYVzVvcVRqMWNjbVV1N2F5bTJRdzZ6ZTBiY04wWHJhcjJkMVlqN1dDaC11eWxFekgyZmVCS2pSZ0dWeENMWngtYXZDYWY0WkhhQ0pPOGp3dUJxNnVpQ1oyZUk1YmNla2dxdUh1TzRQeDE5UUtvdHE5c24xSU5lNU9jX1NsNFp4RkFES2RlaG1lc3F0VXFvSV8zY2taMnBWN0Nr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOZWdaZ2E3Tng1VnBVN01EWnVweTNBQ3lpUk5EYXJvRWIyRWN6T2twWUM4dnZraEEzUW9OejdFN3hYLVczb05zYk9wU3ByaVZ6YU1mR2tuVDBiS3Q4YlR3RnVMVmozSUF5dWtzLXZJUmY2dG82STA1aV9YWUNEN3hrZW1DNkFDeTNTMkJBLThJOWt2b3NXcmhjNFhBcERFSVdYM0l1SVozSk0ySGlL?oc=5</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -3211,27 +3211,27 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ESET Threat Report H2 2025: Phishing and Social Engineering pose biggest cybersecurity risks for South African organisations - ZAWYA</t>
+          <t>When Employee Misconduct Becomes Marketplace Deception: Court Clarifies Chapter 93A’s Reach - The National Law Review</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Mon, 09 Feb 2026 10:50:43 GMT</t>
+          <t>Tue, 10 Feb 2026 22:17:46 GMT</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxOdlRIOHdKYXA3V0l4SWJCNXQyQmVYSUF5WXZmWG52cTRNcTI2cXJwQVoxMzNXd09VQzJYNzBUTldaVEd4cjhuX1cxRVlxM2VhckRINUp5a3JkSmExZXd2bUp4NzNxcEVRQnJ1VG8tblg3NDRGSnNscEc2NlJ1eUg3dFVLcF9wWklpVnVrRTlCa0NDczBveEQtSEk3c2xNSFdvT3VwVHRKU3RQanFpdEx2a1FOOGFhZE9VbnBtcHhLYmpMN29wajQ0UzZYYjVlZW1yZi1wUk1LSUpzclc4OHhkckF3TE9QcWtnaUJDRG9URm1aYmJHSVVZZWZtSHNIOFF0TWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPWFdfZWZYMFQ5RlQwdVZfR3h2Ty1JYlNqenR4ZS02ZVBsQlMySjJTb01zdzJaUFBKcFdVTTI5LXRjeGVrNVB6aTZyYnVuQkJBZGhJSFlDN205S3E2SjlLbHZNUEN3eFByVVR5TzEzRkxRQnVwWWI4dVFlS1ZOd2R2azhvZ2xrdW5IcE1ZUHI0NE03SjF0ZTU1dUdPMFNSRGp2VzhpVVMxcUdEWFUydTNKTXNKZVFmM2PSAbwBQVVfeXFMTWlLdDQ1TDY4RVA4MWMzTExqb3NmSG5sV1ZiMEx6YnJvengyRjI5V3NDb2taX0lrbFdvY0pBN1UzdDI5NVlFV0pSVi02M1BlMmNNLUxBaDNWYnlLT2ZETE4zRW9jWlFxWG1SZTdad2I3NFlvTHhPS3JqeVBzcDMwYWR5cldpblpLZGRXSEcyT0lOV180VWxEb18zeGtwZmktbDN5bFQ0MlJIcktma3RqeENad0N1R3hkQTNEX2g?oc=5</t>
         </is>
       </c>
       <c r="F94" t="n">
@@ -3251,20 +3251,200 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Hidalgo County warns of social media scam involving vehicle registration renewals - KRGV</t>
+          <t>Revealed: 95 billion scam adverts shown to Britons on social media last year - Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 04:40:03 GMT</t>
+          <t>Tue, 10 Feb 2026 15:21:26 GMT</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQRVpvaFJKRlE5VjFOSC1PRUliTndNSkM0dVdudThnOFpYTkZkVERXcWpGVm5KdDR0LWVVUWhKS2ltSldLbGI4VS1XRGhDZGNGTjBlLXhWYWhNd1kwdVl2VWtUTE11ZVNvXzNhLS16OXFjSnJ5WThXbEg3ZzNkU0R4Q2w5Wk5KRUpkQjNsTWRLeGdNUVJEQzVNNGtCYk5wX3U4ZUZBbWpiUWszQ2No?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQcFFPNXRBc3UydUZ4c1BqN1pPRVlaZWliNEV4amhiUEwzRlNYM0xac21GUkVjaV81b2ItWEw3VHlPdFZtM2RtbmI4eW5IVVRmZGNvaGNRMmdkRlhXeE9TYzc2aWJhLVoyVUZQSkxaZmRJNl95MWxoNHl5Ti1sWkZ6TVNQZ0ZsTkIy?oc=5</t>
         </is>
       </c>
       <c r="F95" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Fact Check: Social media posts misstate UK costs of asylum, fraud and tax - Reuters</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Tue, 10 Feb 2026 16:09:18 GMT</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNU3pNSUUxZkhySnBMQ3c2YkFIRlU0dTdtZk1ZblVsUENJalM4a212czdVREVIYlhUMTFQNnpTVjJ3WUdMYWdqV0hjM0ZFV01KSUxwa2ZNODg5Mm1wZ1FZbVVNVHFlMng0REFuUEhWSUVtMTczZDdDSjJuWkxMbDZxTURsaXlXalNhVDNUbWFDNTdneExsWnVnYUQ1U0RSMW5SX2c?oc=5</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Don't fall for this scam on social media about a deceased Charlotte County deputy - Gulf Coast News and Weather</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Tue, 10 Feb 2026 23:04:00 GMT</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOMGlibF8zWHo0aFFZaTVkanVybG5MYm9uNHBJRjVnWDlBREh2X21Pb1B5d3c5T0FZRmVPQ0tvNTFzN1RTMTVtRmFvUWdaang3V3RFQ1ItRWxmZzVhVkF1U3pnV3FtVWdqcVJTQjhxOFY1YXpMYXpHcXVRTDRLWHpzcGJXenBHZENyR0NPMmd5Yms2ZEJpWDIybGRDR051c0R5QWlv?oc=5</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>New scam spotted that uses a calendar invite, deepfakes of CEOs, and a troubleshooting program to create backdoors and data miners - PC Gamer</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Tue, 10 Feb 2026 12:37:21 GMT</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwJBVV95cUxNNFJYLXNNVU1lOTRNU3FqcGFidUw1Z0R5ZUtaenE4NEJaLWI0QzFkR3pQOGVSR2t4QzhOckRjWDh4a01jcFF0bXFib2xGejFVWlZkUHZPalVqbEpnQ2hGd25RUVBTVVk0WFItZ2hwQXV0MXpqRzFrMDAxNmR4MHRuUTBkdGpKQlg0Qlp2ZUpUUl81SURydjcxSXRwVjBmWGZrdk50d0JDeDlPaWZqYUhzTWFFZ3ItNUxfbEZaczJxS3NQdTBuMzBlQW5HUkRHdVVfZzBXYV9JNVE4LWplZzRVT0VoR2hwWXE1SV90TUE2MmxMbjVGSDFNNXhtTmZoYWtKQ0IzRUQ2Rlc3WENFNlBhekw0SXYzR3JJZHNWY0ttWVl6YWxwbXZjSTdYZHRJcUE?oc=5</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>The anatomy of a small-town scam: How glib talk, social media reels &amp; smalltown dreams fuelled a big scam in UP - The Indian Express</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Wed, 11 Feb 2026 02:39:14 GMT</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPYnpYSDdLYmZ0Wno3aHc5QVJpWmF4Vzgzc2tJTzE5QmNERE96VWNBVXFPQUdNQWxaaWRsU0N5cDZMYVhsaUpCRDB1a2lrNDhaNTNIUUVKSHBCZlVmNkRqRGhZUkRVYUE0UFB0NTNROXFmLXZaVlRfV3hjbXZqbk9CQkM2LXlZUkN0UWZGd1JHczlsTERNRGU0REpQMWIyUkEyZGdiekNNbWdOdkhwakNsTUtFb0dqOVM5cUtyV1A0Nk1KemtxWjBtc0VmbFZ4c185VlhlV24zbjBDc3c5djF3Tzd30gHoAUFVX3lxTE1RUGJJeDBXajEtQ1VmX1ctcTdrZ1BXMzhTX0RDNGQwR0xRVUwxdTEyWklxRlNFTGppb1I5bWwwZWhwYzdTZWVSRkd0YWd1ZFZUNngzaVF1bXJlaHdEdjg2cnFPWk1QYS15ZWJRN2gyYUJ4TU9UbFN3TGxMMnB1anJaYWY4MDJxeGhGN0ZoZ1ExMEozcllUTm11bUhNX25pbV9yNzlteS0zNGlOYXdvNG84UUUwa0Rtc0FpaDBVbllIZDBaa0JOamdISV9HN1AyZ211RUdVelVKZDdxeHlJU1FlZHRKck9UMVU?oc=5</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>As Minnesota cracks down on fraud, some lawful social service providers struggle to survive - Star Tribune</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Tue, 10 Feb 2026 12:06:39 GMT</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE9wQUJFY1MxblY2bEN0aG10RVZ1S0RCekpBbTZ0RWIxTnVZY0xZbFdrYWVpZThvV2ZfYjkzVms4Vjg0Y2pkbE91X0ptLWs4NWFSTHhKbXB0VXpXeEMta28zLUNmd2NWUjcyS0RoMlFBdm11Q1FuUjlycGVRSQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Hamirpur Judge Falls for Social Media Investment Scam, Loses ₹6 Lakh; Police Register FIR - The420.in</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Wed, 11 Feb 2026 05:34:33 GMT</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE5yQUF2ejV0dG1MOWF1SXoxeXA3bUh0bmJodmh2bVRwaUVMT2s5YVNNcnpQRENRWG1pemJNMHpxOFBfRzEzN2xESUJ0b0lMZXlBQ2RacDdPN3ZzMnVETVd2V0w0cXRSa2tCMUFhaUlfbWQ1Y1ZJ?oc=5</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
         <v>1</v>
       </c>
     </row>

--- a/data/daily/topic_feeds_daily.xlsx
+++ b/data/daily/topic_feeds_daily.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F101"/>
+  <dimension ref="A1:F82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,17 +461,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>I got a copy of the Beveridge Report for my 80th birthday. Every government minister should read it - Big Issue</t>
+          <t>Update on the procurement for Digital Gilt Instrument (DIGIT) Pilot - GOV.UK</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 04:03:31 GMT</t>
+          <t>Thu, 12 Feb 2026 07:04:42 GMT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxNRTNGMzYxRFl6cVJCZXNhbWlPQ0ptbFhpdXpHSWJFMDVDTXlRcnZ2MlEta1l2c0poMG5od19neGJURDE3enVKVUdqdHdnUmthMjJ5dVUyWXQ1aExHeHlqMUxDb25QYnYxRFBFb0JjU2kzbFRhdXdydV9GamZCd0VieHpBSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxONVJYV240Z0lDTHRISG1pM2tXMjdyWmtTSGFMdDFxRzBYNFBQa05BUkp4cmhZd1JJU2xDQTg0UVp6S3pjdzVsSFBlV3VaOGhORy1WaXhEeDE1MXAzZk9HZ25ablNxV0tqWlBwOHZPUkU0OVJZLW40RmFCOUZadlE3Q01XTXZmWldqdE9zXzh6REl6aElxaEJicXZGeVhHN1NvRWc?oc=5</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -491,17 +491,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Policy report: Mapping the EU's long-term budget - The Parliament Magazine</t>
+          <t>Government and prosecutors respond to JCNSS report on Cash/Berry spy case - UK Parliament</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 16:54:05 GMT</t>
+          <t>Thu, 12 Feb 2026 00:17:40 GMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNMGZ6b1RSQVkwOUVLQUFlYk5xM2wwMXA0ZXpqb3lTNm1hSm9jVUlqZDBSVmk0UVlpNXlxeFVEZ1A0WHlfTGdVU1JVVUlmdUtZRFdoWngtU0pnZmNXelJTRklfemVCbzRrNzRVT0tXMzJwcVJuNmw1YnRSaGVkcWtycmdValByeHNybWhVTEpGWE1qU1dib1o5TldkZ0tsVkU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxPWU1rSTJsRWNiNHNmX2xWbzJ3NGpHXzNXQmtDVXFHenE2MUNhMmk4TUpvLWlHNE15Qm1kQXlNT0puaVR0bUtIckdlcGtLelFEelBuckRfaVpOcWUweXNpWnAtVllLblBuUEVNcmozWUFuVXIwQzVpN1FkdGwwdHU4b0s0bnNDV2QtakVLdWNKcmthaWlNRmtOME12RDdyeldEaFY0eGhFdjFxOUlvR29rTDgxQTdTQ2NoYkRVZnNkRjlhTEJESEhSLTlQaVQ0ZVBaUXZBaXBJclNhckRldHlmbGtwakMzekZkQ0pLRlBZaHFOVUJSZFJiVy12MnNLUVdmdkFVSk9n?oc=5</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -521,17 +521,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Situational Analysis Report for children in conflict with the law in Egypt - ReliefWeb</t>
+          <t>From Rates to Ruin - Policy Exchange</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 12:03:47 GMT</t>
+          <t>Wed, 11 Feb 2026 22:03:43 GMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOOG9HemJ4S244MjBJYm81WG9WUlZyU0lMME5qNzBOMHZ3dVBtSHhfRnhLcGF6b1ZVa3ZnSjMxZ0p5Qml2MkV5MFY1TDBQdW5nWFpTdDVBenhvRFNHazl3UE5hU0J4YUJXZHVQelJTZmxBTkk4SmpVNmZPOEhicFE4R0U1LWdOaUpuZ3VfVWdqSzVMUVdW?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE0yOHFzQ190bmtpdzFfX0xKV0J1bmxYUDRYWnE1Y1AtZ2NmdkNBaFZQY29ycXZ5MFpOMEs0ZlViNUVlNVNONUZKekVGSnB3TTdXckVkdVJvUl8yWEhHOEc3OE5zOGZrSmVvTUxYVG5n?oc=5</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -551,17 +551,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Internal DOE Documents Confirm Climate Report Was Created to Justify Administration Policy - The Equation - Union of Concerned Scientists</t>
+          <t>Firearms Legislation Update: Surrender of Prohibited Blank Fires - Equity</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 14:18:01 GMT</t>
+          <t>Wed, 11 Feb 2026 16:52:42 GMT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOTEVzMVN1MXlMSldHTkdWMnBvV0p5MkhuNXd5MU1aZ1R0c3QyenhYWm9CRFp3THdYYU5XXzJnV2I3S25tRWVfZk5jZmlvRXdfSTRsUThZcHRrUmtkVU9BMTVYenhmcE9mdWljaFBRM3hraC1VSTlZMmRZbWoyaTd1ZU1KN0lSM01hQXhlV2VIcFNUQjZ4NGpjaVFwdlhLSzNJVFZaM3V5QUpOSktad2g4UmpORk80bEMtSkkyNWNXYmgxZ0FtRkJB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOdWROS3FNQk5RaWpVdDc2QlpRa0VpV254ZjlYMk9zZlRPMF9xWFJvRGFnRTRacmlsTHNRSEQwdGFWTHBqQnJfWm94Ti14d3lxa3QxMzFaSUdwbmdVQXQ1U2locUpsR1djMmttVk1HYnlrdDM5WmlNblNZSlFOYXQtclBuMTBTbmVEZnEwYmw5OXRJcmpxT3FQNk5SUlhTZ0RJ?oc=5</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -581,17 +581,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ICYMI - PBOC pledges loose policy, ample liquidity in Q4 report - investingLive</t>
+          <t>February Monthly Terrorism Update - Pool Reinsurance</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 00:27:01 GMT</t>
+          <t>Wed, 11 Feb 2026 15:04:54 GMT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQV1Vvakx4ZHRXUlo2eUZScFhzNjl6emNQZGZoanNaOWZDbXl6Q0cwZzYxbUZGZEF4QUJnNWRUNjVURF9GVW9qSTBsbWs3QURyWWhPaXlWbUlDNGZ5blV1ZVM3SGI1MDF2NXo2dGFIZmoxRExoczBGUWVBUzk3QUJJWVo3cVo0a2Z5enBMM0oxVnRjSzJwU0FqLXNDN1Z5WGtaYzRKNjctYWI3M1Bw0gGyAUFVX3lxTE1nS0w5TVc3R0l4WV9MMDdjdEdzTTVNMjFIeC1DZHp1cWs5REdvdTRVSWxrczhzOWlPQ0VUdm11Q1VKanNINjBPcmJGdWZmZ0xfcUZTTWNqT0k5RnNOWmpaQ2czZFBnTnJZZjAxZ202eUI2Z01vRWZnMGFfRWY3SGJOUnIwU1hxUTlJd0VQUGlmUXg2UW9BM0JkVFJJSG50NXpSemJkdTd5ZjFvSDhZMWU3QWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPd0J1ODBkbTQxVU5fNzZRMVA5OWRwRVV3ajNLQl9abkd1X1NlU0RMYUg4OHlmVFV3Y2ZuMmpCT19rUmU3TlhPV2NoaWpCVFJvU3hPZk92VEJTS0xpaU9odEhmc01SWi1OSXNSLTdGVUl3NVY3bFVJM2R5Uzd3M2F5TjM0ZWplbThRTW1xVlg3c3FDSHlKV3c?oc=5</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -611,17 +611,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>OpenAI policy head exits after discrimination allegation: Report - Storyboard18</t>
+          <t>Kyrgyzstan - Migration situation report (July - December 2025) [EN/KY] - ReliefWeb</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 03:22:38 GMT</t>
+          <t>Thu, 12 Feb 2026 01:33:32 GMT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPN2ZxVTVMR25DTWhUYy1xQTdhNkFJUFRMYWxaeElsWXhFMHd5X0VqekhrS3IyQWdYQ3RkS1NZX3FhdFM0ZkdsdlJlT2RjejBKdUdPamh3M3lhX2lxMFJvTDVQcDFjRU5vZEl4NUFpTFVJLS04WnF0dVFMdEZUdmpXVExENlJUZm9tS2w4NWZCN2VzSjJ2NXR1cUFRa0hhcWVpUnRkendxb05BZkZkQUhR0gG0AUFVX3lxTE43S19McW4xTWF4OXMwZG5LVUZtS0d4UGtDQ0ZOSHR6SjRFWERKSnpZbnVVb1paWUpjNTF3TndkUXVnV2otQUxuMWx1MzlObVZFbllGekdldXJuWXczRGFHUFJ6OW1mTDlCSUNWYnUwOHYtTm5KY2QtdjAyRmVIdE5YdE45VW41aTUzN25Bc0t0WE5Od1k3amRWS2xSaC1id1dUejRXM3lQdXpNNDY4eWtKbWdoWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOeHEzRFN0ZENUT1duN0U3Slc3cm1vSEJNSEdxeTdyU3gyMEl1YUtOWnVIMzZuaHpPeHMxWjFlelZYd1I0UzhLdnJBbTZFa1RwalBzd0plRW9MeHpnNnF1bkp2YXNHaGI4LWNoaVd2TEVXOGsyR0tCc1UwcVVRSTBuV1F6M0g2WXRJcWVfbTRPV1pFRmhEVnloVlE1U056UHlXUTVj?oc=5</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -641,17 +641,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Euna Solutions Releases “State of AI in the Public Sector” Report, Revealing Where Government Agencies Are Finding Real, Measurable Value from AI - Business Wire</t>
+          <t>UK economy ends 2025 ‘in the slow lane’ after growing just 0.1% in Q4 – business live - The Guardian</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 15:54:00 GMT</t>
+          <t>Thu, 12 Feb 2026 06:32:00 GMT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAJBVV95cUxNZFU4aHNKcDBXZDI2aTRQSGswZG1mdFRKM25xVDdqV1lyb2wtdXBVSkZuT2lWRjltY3VBT0ZaRE8xY0lKem5zRlh6Z1g5cF9VbFRORndCSVlRQXhXZUVKRFB1V2ttcF9DbG9NR29YSC1LTVFKTkg0eS11bkRfcTJSc253ZlM2Vjg4X3dhOVFRV3lTQmZERTYxUUdDeE15bXBrV3BQZHdaMnpmeVZjWXQtR1Z2aVF6T2V4OGpUN2JQWjd5aE5mcENwU3U4QjIwcE1aT2NrSE12WUlOX0wwUWl5Z2Y4ZWhvQWJjaFNXYm41M0huR1MxeVl5TVpBckVxRTVDMTZGd1F3RDhnM240a3FKbHFsS2N5X1BCNW5LTVBheXM2RHVH?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQYkY3Mzh5Z3NoWExjOGhwa0Qydk1MTW9NeGFERHYtamVRS1U1LW5JSEJ2SkxsYTlTem5QWFY4V1BMT09hX2x3c2F4QWNXWnZEcmNFZU44NzlCaFd0Wk1DNWlxd1l5MFBWTXZSMEhzeU5oa0w2RWJFaHBIMlV2aHpsRXF3X3dRUmxwTF9TZ1B6a2Q1M0lCS2dIdTZRd0w5bmpaNmhuc2R2Wm5lMGJ2QlExODF3QlBZRHRaTkV2ZWhtdHJOS0JKRUFCWUZaS1ozUQ?oc=5</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Sudan: Conflict in Jonglei State - Flash Update No.6 (as of 10 February 2026) - ReliefWeb</t>
+          <t>Polesie/Verity report published - GOV.UK</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 15:50:57 GMT</t>
+          <t>Wed, 11 Feb 2026 10:05:46 GMT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPLWFMYzUzOEt3a19BVzRLQThYZFZYM3FNVDZKelBweUhlbTFCcnl2aXkzcTltc3p5TjM1Ym5lWFFsbXJTbjc5Wl9rVThORm1NeGt6MmRCUXpzY3lhRkxEWDZEd0Vpa2FYYmFvYTBqWUxzbHFIa25ZZGxGeGMzOEtLUEFuN3ZxSUQxMzc4bHdqSXVBZDVuRFlHejRvS01oTDVwX3MtRFJFbktnbTROQkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE5QMzdsb0VZcmNwaktacFZqYTZJZEZpVU9jM2N6dDhPcG5scWF3MzkyemE2NGR5VzRRemNTa1NiYzRSbEpSaXhIenVPZmwwaVNqNk9jb2ViY191aDJGekJrWlNKbHQ4cUVidlh3OGNHNlNfT00?oc=5</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -691,27 +691,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sanctions-busting shadow ships are increasing - the big question is what to do about them - BBC</t>
+          <t>Jobs Report Live Updates: U.S. Hiring Starts the Year at a Strong Pace - The New York Times</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 00:17:37 GMT</t>
+          <t>Thu, 12 Feb 2026 04:17:00 GMT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE8tYnJWQ2piRzNBWlg0WUZQZ2NCWnM5VTMzNXJaSFowbUEycXZySGhmMElwSC11SThYU2FLdUxtaFRteFlsM01YTVZMOUtUVVgxX0s0Skkxd056Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE4zU2VjSUs0WkZoeXFwcms2NkJaSkVBRkVTOXFMc2hydnMtZnRBcnJ3dnJIYUpBSGZyYVNnQXVpSkhfSkJjNDIwV0lJNXpPeEVCVWpwdmh6U0ViR21qbXZ3VVVva1FJcjlDbWNkSTJXRGt1RjliaFlV?oc=5</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -721,27 +721,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tariffs and falling demand leave Scotch distillers under pressure - Business Matters</t>
+          <t>ACAPS Briefing Note: Sudan - Conflict-induced displacement in North and South Kordofan (11 February 2026) - ReliefWeb</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 07:13:24 GMT</t>
+          <t>Wed, 11 Feb 2026 14:03:08 GMT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOVkYxY0JNREhERW5tdEo4U1FVS1ktUFJHMGZvRFlBLVU2cXpmLUxka0dncjM3MEpoMWdHZ3UyM0I4SE56R0N0TWZBb2xqWUE0NFdXWHFja21CTFdobUR2ZWJyOXU0bEhaWEhYcWQtR2tyeEVKWGZkX29UUW9UTUQ5NnFZaG1MdVpYY3BScDRMamV5dmsxZzNZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPQ0lpaGkzZFpkcVRxOWhaUkdhaW1TNGdoWnJrRmRQOXN3Zy1oLVhpQThKeDZTYnJ0SV9jdmFXaHUwZVBXNi1PMjJOTTJfTGZQRGo3MEEtVWZKTDZMb29SaWlRdmxNQ0pzWmI1azh1RUxRc2JtX0oyam92QXR3SmkyYTZjRUt4U2NhQUhCWDg3YkxPUjU5R2Jnam5BSm5UXzUtMFhHSkRvV0cxYU9qbkJCRGNHSXc0ZHN4Rk9uRFhCaVpJUEgwQzVTZUwzUjc?oc=5</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -751,27 +751,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>An Invitation Into the world of elevated luxury logistics - Air Cargo Week</t>
+          <t>KPMG report: Public consultation on Amount B under Pillar One - KPMG</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 07:30:23 GMT</t>
+          <t>Wed, 11 Feb 2026 10:00:14 GMT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQWEtnY1F2bFNudGFMZ1I5WHJ6M195MXI5U1dSekxlcDREa2tDaDFiWkhaMEpfOGM0ZV9aNGVyd2NKajlYZC1heU5nRUF4TzdMZG1tOWlrcG5HS0ZiOGJTRkxYc2ZQWW9oeG1odVF4MlRlQTFlMklmbl9RaUJMNEFTakpSam9wRk9aeE9B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNaTlYbUwyUFRnbmF2UXN2ak5qZE9yUWx0OFYzMGdCYWJuaExIdVI3Zk5GcFpxOWZVN2NMNGs4NkRwYTN1NDRwaUN5RWFITXlBZmp4clZYeE9IeGpEZFZxeWlrRy1aMk1ldDR1ZkdySlNMRFpERkZCTFM0SzVkUjdWRlhNNzVyRmdsOHlSbTJFMUpaNFlvUEVCd3BsamRobXB5cG5LcWFZT2x6Y0Q4dmpBWFJUWGlGZHNscHZJUnkyVHVUWDJ4WENRMll4a0tKX2dROElPaw?oc=5</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -791,17 +791,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US sanctions officials from Marshall Islands and Palau, citing China fears - Al Jazeera</t>
+          <t>US House of Representatives votes to overturn Donald Trump’s tariffs on Canada - Financial Times</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 02:44:59 GMT</t>
+          <t>Thu, 12 Feb 2026 00:15:12 GMT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOZ09FUDJUdmZSc3dPc21lenByX3lSaTZicGZFMkdmMXRWSzE1WV9lQ05NMUotZVRKVUpKLWtpSEhsV21DaURxVEJxT2RVcnhNUlRCM3VGc0tyeUs5WENOSVR0NjNrc2dobmFiRVRZSDZkVFM3V2h0U3ZkdjBKbUZnUzlGMnBVaVJ2TGlPMEhQUlVqYjAtamZ3RUROa0U0bk40dS0xWkxaRVhJSnFQLWFkckRlZ1XSAboBQVVfeXFMTWdJNlFOa1RuejF5bWY0aXVFWElHZnVUYjdNaEYtY2NvWW1hY1ZwYnJ0LTRFcHUzU0JGRmt0bzJEaVZPWlZ1M3EwTXB0QUpHR0l4OEhXLVJhbDNqRjlCQ29hNVA2ZDRRVThhNFZBYW5hbjl1TFhwckVtVGRlTHhWSmJDYWhPRFotWERJSElfcTZURGxLZEpESWNhMEEtN1NRNWRoWUNvdnV0c05tRml5LUxTSWI3U0lmTjJR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5acnFCcThjWl91alJsdkRjTE02ZThyazA1eVU5VC1nMmdkRnpES3VBRE02dmlabUZLN3VBQnZJdldPZV9oTFVaVjZmdTM2ZjRsMFRfaWFjNlJkaUE1b0JMWHpfeF9LWlgxWmlEbEQ5U0I?oc=5</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -821,17 +821,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>EU Considers Sanctions on Georgia’s Kulevi Port Over Russian Oil Links - Organized Crime and Corruption Reporting Project | OCCRP</t>
+          <t>A year into Trump tariffs, Chinese factories and ports are buzzing with activity - CNBC</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 23:28:27 GMT</t>
+          <t>Thu, 12 Feb 2026 03:38:00 GMT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOOVBUS2Q1MGNTdnZHN3FCcDFqNUpBNU1aeWVJNi1JN1lzdFFNMURJSW5LNWRDSHdpV1BEeGRHUXMzOWdmbzJjMEF2WkhwVEpOcVJqeVNkLXVLbnpBdVNxTVpySVR4Mm5xTUsxSW1fc2lsSGdjZnJlNlBwbG1lTzBtcFpQNEk1bURYT3NSQWsxU1dEby1ELUpsNWg0Z2NJbzNk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOd2xOeXFTLW9KWmMwY0lRQ0YyMUg0WTB0UXRLbTlTNlNHc3dhb1hza3dTUU5MQnNNQzhLcXNmUVh3eWVFbWtJMXdnZHpRUnI3ZGhUeEVFSmwtWG44dUpXUFlHRkhVc3JLbGF3OG9iRTFxakF5TkRNRDVRMUJIS1hlZGF3eHFJdWxzeHN4WWZ2N2xHa1RQNGoyWmJkZlRiNnA4amVyTlJUTVBsTmNP0gGyAUFVX3lxTE5CNy1tbEhIbVRteEU4SElDX2tXc1ZXYTdfYm1xR192UzVZelo4TzlnVDc1VlduZWluVElpOW5RYVpQeWtfV2JXWUFoWkM2NnFVN1dkQ0N6WXhYVUo3V0FRWkRSaEY0RC1zanJMNEdRYlh3cHd1MXlxSlBVMExSX3dZNzJuYUZXLUQ3M0Q3c1R4dUtiTWZGSV94SEVzalZlY0dCSndjRlZuaFI3MWhpQlh0X2c?oc=5</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -851,17 +851,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Yorkshire logistics firm invests in new facility with HSBC UK backing - Insider Media Ltd</t>
+          <t>Co-op Group extends logistics deal with haulier Buffaload - Co-operative News</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 06:03:04 GMT</t>
+          <t>Thu, 12 Feb 2026 06:52:49 GMT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQdTlBYkh2Nk04aGRoRXlFel9hNDV6VU5iR05wQW43bWZTem1tRnhKMXhZQ2Z4emt0MWpLZlNxcTRSMDR3QWFWeXQ2bmx4R1VtN1lXc0NYTElncm9NV3JrbkJXbmRveGJMZklWcVZDcEZ2bm1TVXhDbE9qZWtoRHRZQm0zOVQ2V2EzSHJMVm9BRzJldmwzeFQzZEpjRkpEOEhMLWQxZFpHdzlEVTVVSFYzRlVUaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQVnU5RlFnLXhCemdwWkJJeXV1TUFyR29ILUJzenNhQnVaXzN4X1VEck9lcjRFd2lNNldpVWlLYkxCd1VSZXZzYVB1SFRVcmZlYTdlMlBCanJLbWlIZEZkMm03WnpSTHFuM2JUTHFaaDFnbXZCNl9LX1gzLVk5VzB1WDZpTEFoLVhadU40?oc=5</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -881,17 +881,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>What Does the Descartes Shipping Report Reveal About Trade? - Supply Chain Digital Magazine</t>
+          <t>Effect of geopolitics on shipping poised to escalate, so ‘buckle up’ - Lloyd's List</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 17:31:51 GMT</t>
+          <t>Thu, 12 Feb 2026 00:11:44 GMT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE02NF9uM3ZIMGNyb0ZXNnFJbVlSY2RVd0lPaGJTVktsd3ZHYVZEODhUd0FpbENVWTVSYTUwRkptcWJkbmZyT1FEU0VTY1dFampOZG9ENWQ5bmdCY2tid1hrMDBHeFhfdlZ3d2VmUmlBaWlzZEJNOWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNVlpSb0ZjdW1ZNEpOOE5NbV9HeklPWVFCT0dvLVBxTzJRZkI2SzBBRnVmME5LTFl3UTFuYmtNd0xKaElrWU9tRllKYWpiTnhFbzVCNmlXQVduZVBsUkQxWFd3eTBYb1B3MDF4N1dqeXhwLUlhVHJRQmpBQWNodUExeW5DMGhIU081bFR1bk5zZkpFb3hJaklPZ1oxWGRFMl96QzAwTw?oc=5</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -911,17 +911,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Broadband social tariffs – how you can save £220 a year - thecanary.co</t>
+          <t>Vestas back buying again with €120m Polish logistics deal - Green Street News</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 18:10:00 GMT</t>
+          <t>Thu, 12 Feb 2026 07:45:16 GMT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPeGNoX0hSSUhKUU85SVJNX3d5UG80MEgxaGt4TEczUk80bUVuWFNBeWd5Y2haY1BpckVfc2ljMC1WNzQzLS1yekE1VWFYZm45REY2cWFaaU5mLXozZnM3MWZ4d0tXclE3Zi1ISmNyYW8zLUZvVG9SOTdvYnpvREs2M3Fkc05TQUg4TjQwMDRWMmV1WXpzMGZGei1oRUhoUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNejhQakVnV2ZtVUZ5Q0NxdG1Ia1FsTkJhMFRVUlFyTkZ5dUtHeG9DZHJMYk9Gbk95ZkF6ZnY2NW9hVk1GamNMbEkzTmwtdjRkdzd2X01BR2F5YXUzeXRZSUlHQmhhbXFuRWk3WDJXaWY0RGNJeWVUVVNJQWprSlFXS01TOXZ6eVRwdnhXREY4ZFhndGFCMXZTcGZR?oc=5</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US giant buys €65m Milan logistics hub - Green Street News</t>
+          <t>McGregor issued compliance notice over stout posts - Belfast Telegraph</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 07:47:47 GMT</t>
+          <t>Thu, 12 Feb 2026 06:47:21 GMT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNenB2UXFwQWVCVGgyTzFBV25DNW9NZm5jcU9jc0VOVHJTNjQtUXp6VkdDQVpfbFhhVU92SDBBM1dRdUdBSUhaanVYOS1zNmdJa1E4Qmowa1hqVVoyNWZ4UkRnM0pjWG44NFgyTFB5SU5pTUtJbkdKYm5BdGtRQUVrUw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQeHkzeDVqM3psZkxzeEJXSHMzbVBhMUlRbmotamhaSFFpbzZEcVplZmZ2Rkc5TWE3SENUS1I4bk5ydUlYeXc2a192azhqWklCbWpEeWUxU0JWV0pCZjRJR0s0NXZhcWw5cl9DaEJHRzk5empnakhTMDBXYThsTHhpUnRobmR2bnBld1h6YmpyTEt3eXJWbjRBZDdxLXJ2SUdhSzMwRk5xLWRRNjJPczNyV01UaXMyUE41alVDY19qZHVUWUtCMmc?oc=5</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -971,17 +971,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Why Haven’t Tariffs Trashed the Global Economy? Explaining the ‘Global Resilience Puzzle’ - NIESR</t>
+          <t>Sanctions, Ship Seizures and Low Prices Squeeze Russia’s Oil Industry - WSJ - The Wall Street Journal</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 09:05:49 GMT</t>
+          <t>Thu, 12 Feb 2026 04:00:00 GMT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE0tXzRKOXNVekVwYVRBOFZpamJleGRjUGNlMUJ5NU5XR1ltODdwVVl6eEFXc3hmdXpHWTJORGN4SnpHZUFlRnp3ODdkSEdfUUxUbDJRekpXTURSdm9jLThYbUJHSkhNVXRQT3RFeXNQZURTWFJh?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwNBVV95cUxQakJKaFNDTzB4M2c0V05RUV9KYnBnczN6SjNoTG1FMGZ1N2ZlcmVwQ3l0R3I4RkdjYVRUWWkzWkY5VndDcXNZUmI4bjZFU3hGZHNPaGxncDcyajV1R25nbF9BMVkwbEZveWNlQ2R1dVRfenVJVTB1NGQwd3A3ZlF2UVdjbGNZSTJNdy1XcXVKRS0wb29TMHR3cHZQYjlDT0FxRTdBcGozRVktWDJJSWwyVU1UcS1tVktIS2t6Yi1rbEU3ZkpuV1BZVnJvb2pPdEZzTm1wd2tMRUE1LUNtXzhsb0NuN0RGRTc4TUFEbkZ1alk5WDZtNnpFM3JFdUo2ZzU0MHpzUXluUVJNdGI4SVpiNEl2RUx2SUpKaFoxTjc4RjY1REctSUFINm82Wkp0ZThMaGM0ajlDRF9Wb2VqczYwcm84d08wVVZWVE9hUXJhVFQ1eEpVaDhVTjdmNTlIV0tQYWkzNmNLbG1PcWJQS3RlbC0yRzBIYUdNcHpjcUo4eHFod3VSM3RBWHlfaXlEZHlSTkRUSXJVNTZyTFZ3T3ZzakxKQ005clhxLU5ZOFVUUTl6ZjV1ZE43a0Q1UVRZZ2pCZjl2X1YyOA?oc=5</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Full Fibre ISP Hyperoptic Add Faster and Cheaper UK Broadband Social Tariffs - ISPreview UK</t>
+          <t>Powerful cyclone kills at least 31 as it tears through Madagascar port - BBC</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 07:38:00 GMT</t>
+          <t>Wed, 11 Feb 2026 18:48:49 GMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNcnE4RTdYOFZCWl9sX29sdmI0WXp3ZHhqSHNKQU1JWUJ3bjA3TVlTZGJHb2hvMzIwYlNMU1VlX3pCSHhBVzBDa1VxS1dldkU2RVJOQXNhZlE4cEREUEwxNkNTZXpDVFB2dWJvb3hfSXlUblBlUXNsYk5jbEl1RUhYc0lCQzZwdVN1UEx4UkdyMUszMXpYZnZyc1FQaUMzZmNuTVVaQm5HMHFBWWNmTWxpQVJSUGdhVkxfYjNleEhFNUFRQk9UQXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBjNnhjWXRJZVNaQmlTbW5IeEpmNXpXRzlJbFRBaGxPd0VqRTU2ZmRtNjlPMXdIUUh4YkktdlE2Q2lRTERIdl9HSV9mdlFnb2J0RFQwdXVRUlFDdw?oc=5</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1031,17 +1031,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>EU seeks to ban all Russian crypto transactions - Financial Times</t>
+          <t>The Real Cost of Waiting: The Hidden Toll of Outdated Mobile Compliance - FinTech Weekly</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 14:02:22 GMT</t>
+          <t>Thu, 12 Feb 2026 07:09:00 GMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE4tOFVKeFFXc0tFSUszczJrTzlwU2p6bmJUc0d6dDh5M3dvLWxFSXNKNDUxcjdWN290TWZsdHRqSDVZLWVvUzJVOTAzWmh6c0Z6cmMwSzZGZkRMTnFlOTFXRnRVT1VDd2hPRlo4NkpkREk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPNVNXaVVhS1ByMFZEMlE3Y3FmVVAtU2dJdTZEZW9wRDhmRmtHRHkzOUZuM3BKaDZ4ZlEzWEZKbHNOX1pvcE1GeWxHT3VaMUhFaUQ4UnppaDNZVVpjRjBpVFp1ZktNUTNJWlh5SVliN3VZS28yUjQ2ZUNYbTNnYWlKT1c4ZW5jQUc4M09kUGVVNnd4U2dSQXFoa05pckJMdw?oc=5</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1061,17 +1061,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US imposes new Hezbollah sanctions targeting gold exchange firm - Al Jazeera</t>
+          <t>Europe’s CBAM raises supply chain carbon risks for South Korean technology industries - Institute for Energy Economics and Financial Analysis (IEEFA)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 01:14:02 GMT</t>
+          <t>Thu, 12 Feb 2026 02:07:49 GMT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQZWZDeVNLNFlvSkF2bmw3RWF6Rjg0WXNRM3NGcHlkOTNLR3dTLVNJVUo0eld1ODQxT1ljWFRxTnFYLVlpcWVpR3dZTUhocHpOaDBDeEFmZGNvRXRWSDNrUDRodXlJVVJHcFl1ZFNma01RUDROWXhyNGRQekotNGxac2xINl9YMHlOdmVwXzY0dWZCeDFrYTR5T2p3MlVlNHZvNEt3Wk1KVdIBrAFBVV95cUxQenRYVmlrVjhmLVpBSFdPYUlZZDNqd1U2Y2ZhbnBXcmtKSXNPcm03ak5RM1ctc3ZTUENucnRjUFJhYjROdHVzWHpja3g3bU9IMUdaOVFQM0RFVmZkM19tNFZ3S3lXbGR5czdiMy1qTzNfc0xpemVpOUs3Nk0xQUtISm9TMk1haTRLcWVuZVhzVUwtdHYwdnZodHNNbVBqVnpNaEhxRDcwWGpKVWpT?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOOHM1aTAyYWx4RU9mMXFTQTM2eUkxUlVLSUFuaG03NUFIcG54cGQ1dEh0ckJCZm9OVjRCQkZHcWZIYkNOV21BNktMenlwcGhyR1lIUmNmUUFHV0l3SHZUNGFzRGJVTTBFMGZMR2YyT000cjNwcHBDVkJvVDF5UTVabElmaW1qeG05Ymd4NXROdGRkWFU5T3hHQTFsaFZOUm01VWdwdF9rb1J6cV9l?oc=5</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Trump plans to spare Amazon, Google and Microsoft from next wave of chip tariffs - Financial Times</t>
+          <t>The Current Immigration Reality for Academic Institutions: Compliance, Cost, and Continuity - Mayer Brown</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 14:00:02 GMT</t>
+          <t>Thu, 12 Feb 2026 06:05:29 GMT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5ScHJRUU1zZEEzUm8tMC0zZkFydFBmWjZ4SU5WQ1hDcmhvdlpScGdMLW1XMzdHb1U4QzkzMHBiT0MtTGZlS25lWGFycjgwYWR1SzlVdHlrZFkwdWItVnNSczA4N1ZPLV95dE8yeW5rQTE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxNc0tOYnZYdFZlLTJpY2xsdDhoVHliRGdMTGloNGZWbzhuOU9zM0xBRXg1TkdCelV3OUw2RUROYWJBa2xNZWtvTlQyNE5IcktVUUlKcFIwbjk1SU5BMkVaMzFuYTFhRzFQNFBoUjdIa2YtSlpoNlhGaXBLNDlwakFSLU5pLUxORGxYVVVEWnVVZmdxdnlvYU5rdHBTM2l4V0J6V0RyRGl4c3FKMFRCd1hsUHNKX0NVZXY2dTBCVmpRZXRIeGdZekpDNTdndHl0aDJ3a2psQWhKYjhQQURKdnRvREJB?oc=5</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1121,17 +1121,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>EU financial VAT exemption questioned in European Parliament report - Global VAT Compliance</t>
+          <t>ABP submit plans submitted to demolish port building on West Quay Road - Daily Echo</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 07:04:58 GMT</t>
+          <t>Thu, 12 Feb 2026 03:30:00 GMT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPNGVzbmZMcGlmMUF0dzFyd2RFWXBrNzVsMnM3Y3pibFRFdldRQUpacnh3Ylc1X0NXTUJlWXI3V0NyY3cxRFF2U29mQ2xqekxkc2ZtdmR5YjRaM21NMDhVaGNmamV1RWpUV2NtWUhzWWdxZUZ1UFhVVkpUZnVsaVE5RlR2VQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPRG5lUEJsQ0duTDVXWGNJMkgtMUMtTGlrSjJORDJYM3ZjTUNtT0tqX2lDRDl5ZHRJUDRPcVQ5b0N1elI3eVhKLXQxTXV1R201dzBEcDlMRTcyY01MdVFVVHNhSTYxTmtlR3REeE5qeWQ3dGdiVzNmX0NjNS00S3BBYVZ2X05JNjNBY0ZTdTFaOUJoNHdZV0tJ?oc=5</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Businesses with Payroll Urged to Prepare for April 6 ‘R-Day’ Compliance Changes - Business News Wales</t>
+          <t>Port Glasgow man held 'large piece of pipe' behind his back during neighbourhood row - Greenock Telegraph</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 17:47:52 GMT</t>
+          <t>Thu, 12 Feb 2026 06:30:00 GMT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQOVFaaGJzMXFiX1F5RGthNlBvZE9XNzJiQnhOYlNfdEdTSnZrdXE5T21rTy1JSXJMdm9wRU9yNDFGcHFKSkZpclRNTkFCS1JscnE4WUIyUE8zS3NRaGtHR2QzbGpURUJ6cy0teGt0dUFRclpmSlcyRU9McVdIWXhQaUx1cllKcS1odDlHWHN4VXMwQzVhcE9ZVlNrUFZ4VktpTU9BRzZUYzBUN0pJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOMXlmR1ZRNlhQSmVmTk51VkhFVVFLTWVvYk11NjUzbmM2SzdoUDZPQlJNNkJvaGdUaXFLdzhkdkFfelhJcm5XdWhwVDZnb1FNNmh0SDJJLWVCTUh1ZFVjV3IyOFgxNFNORVZfTFg5bjZydk0xZ1Fzbk9YN2QxSHZUU2syb1E4OWhmRkk5Z2R2azRIOUlub3l6NzcxSWs4a3ZHMnVN?oc=5</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Neath Port Talbot parent support scheme to expand across Wales - Wales 247</t>
+          <t>Nation-State Actors Exploit Notepad++ Supply Chain - Unit 42</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 06:43:47 GMT</t>
+          <t>Wed, 11 Feb 2026 23:04:23 GMT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOUWhxT3czV29JMldHRWNxVjUyMzBXamgydlJLVUE2Q0l1UXFubExFNk5VZnlZS2ZHYnFOSTFHWDAxTVhELW42RTdpYTRaUC1nR2lQek9JaVhxU1VQa0hDeENvTGFZSHFQX2V0YjlWQmtGbVdzbGRYTHpYODlocXdTajNWWVpQbkZMRVpIb3dUdXpMbkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTFBGY0Z4dVpmMG9PbG80ZFZMSEFodDZXRnBmYUtBdnV0NkxFdmdoSDZIY0ktc25lVTdDUkVOY1piLWF1UzVVcmpYakhWVjh1ZldNUXFuSWZ1aXp1T25WaFpLc0dSWkhwY0tyc0szaERQUE9IMjZfSlFNY253?oc=5</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1211,17 +1211,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Port of Liverpool receives record ADM Shipment - Container News</t>
+          <t>Compliance Becomes the New Gatekeeper for Space Startups - news.satnews.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 05:32:05 GMT</t>
+          <t>Thu, 12 Feb 2026 02:27:48 GMT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFBkRHZoMmVfSXNWTXdpZjU1aU5vRFFIN0xpZGF0N2xHUC1fTlFYV3lDX1VsOUl4V2pDeE95RnFNMzFHM21tR1RIUmF6SFJQc3FoWUhGSjFkR0hRXzhfYUJ3N1pVTGV1ekJadmdqcnlOMTlBM1JVVmtla2NIWldhdms?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQNk1KdWxkMHN4MDVKRkV5NGU4d1BBdGVKV1lPbXZCWmxXQUYzTkNqeEs4QUV0ajRaLTBQMW5ONk9UZGhOdlU4MGppZ1ZnRV85RmJ6aHRyazZLaWZ0b1o1eU9CZm8xSUNVbHJvNmRQZUxKa1RxcDctZk95TEFiNlNtRVMtUkVJbUplanYwYlBPVTVfeW9XV3d5Qg?oc=5</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1241,17 +1241,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Canadian pension giant halts deals with DP World over chief’s Jeffrey Epstein ties - Financial Times</t>
+          <t>'Nowhere near good enough' - Brady on Trophy exit - BBC</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 20:48:54 GMT</t>
+          <t>Wed, 11 Feb 2026 14:37:36 GMT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1sb29DZlNPY2dXbHAxUVZLQ0xfaFIxREpuT2F1YTRFTlViWl9ZSkpLNmN6dHNfZS1jbDMzSjFSdXNlM0xHWlVTODREeHB4YmVCV2MyZ3pRN1FqSVdIWFhBek0wWEhEbEcxNnYxcS1reGg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE5iNUdlanVyTWFDWlhwN2xyUV80UHhHLThoVFVvZE1sQzR0YnB1SHJIQzQxX2tOMnRyR1BGaHZhMFRCUGtXenppc0hOR05SeFpBS3k0RFdnLUc4cVhrTkZfbHRhVnREcTA?oc=5</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Trump Tariffs Face Rebuke as Johnson Fails to Block Votes - Bloomberg.com</t>
+          <t>Thousands of foreign cars sold to Russia through China, circumventing sanctions - The Japan Times</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 03:46:00 GMT</t>
+          <t>Thu, 12 Feb 2026 06:35:00 GMT</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQRHFBZGFWMVJiM19UcHU3eVVRQ01GUjBNajA3eTB4OXVfM3BjT3NYV0dmY3FEUlVubXlLbFd3YXJUWWhGQmF0bDgtTXF6aGRiVEoxTG9oWjR0dm96Nnl2bzRDNXUxdzB5SDFsVjU4WXY4V1dKZ09DMTFZOTltT3M0TTZldjVrNWRKX002UzdfSUxQUUc3dktfTjd3amlVSG9jNXJkR3B6a29DUS1MVVRYT2tLTUM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOZ2FQc3cwT0F3NkFqZGZYTUJraEJpNmFta2hqc09mbTJKVEZQNTRjYWpid0F4U2M4NmlvbGU5RVJ2V3Zfd2hiSTRJWVBjZkxaWENhNU5ESkdPWm5xWG42QjZ1N1Z6X0dTX3RCX2lCYzY5RW00VE5PVml5NW9MSzlpUWNIckMzZGNWaXg2TWdab2JDRHFULUtWaw?oc=5</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>‘Cash rain’ coming for Himalaya Shipping shareholders as bulker rates rise, analyst says - Tradewinds News</t>
+          <t>Boeing sees significant supply chain quality gains - Reuters</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 07:14:50 GMT</t>
+          <t>Thu, 12 Feb 2026 00:35:00 GMT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNWDRaY242b0VQRnJwUFlJRDgzMmRoVTJiMzBzTjBVVEthNGFlM2h1aWVvVjRxdVRnQVJzSnJ1aXFkdGJWU196dXJyQXBreC1ZeW1kdTVZbGl2d1lRcHpXUmljdWF4a0FQQ3N0UGNEbGdwM1did2pKUF9BZVNUQm1KUEtVTGpHV2M0QTFpWUs1S2lWeWF0M2xxRXZiQ3V2XzlIY1l1VkFaTlFheFRiaFZVWUNmQi13dThCQlZfRWprZW9hVS1CamRhckpmemNQZXNFdi1R?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOVmR0UFhBUkRRVHA4czc0eF9KLUN4bmZqR2JpcG1VTVZlMnRKWHZQQmgxRFpVTVN4MXpsSEd4aWNKd1FXZDNqbHRkbGFseVhKOVlreW9RNHpUc1RUOWI5R2FWN3hmaFJGdW1RM0xQdENSQ1hGM05ZdkxsbUF4aWp4UHdheDh5RU9NS3FseVpqUFJSbmpXbVMxSnVFVVoyTWRkMHRiMGRvWlZocmJhWXdTUFFQZw?oc=5</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1331,17 +1331,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bespoke tariffs backed to boost community energy schemes - Utility Week</t>
+          <t>Shanghai Releases Draft Plan to Become Leading Int’l Shipping Center in Five Years - Yicai Global</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 17:45:25 GMT</t>
+          <t>Thu, 12 Feb 2026 06:44:47 GMT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQNmV1c3FsaTY2SFJsTDFrYURIeHlnT2h5cEhVUW8zVzJIQnNiejRkcVFrNDA1RmdzMDNlcXpMSEVCaUlLM3RBZlhXaDRucmRzSmVxMVRfZlJ6ZmNKTmZZTEJRY1d3Y0xZRXhZX09iYmdJZXp3ZUlaWHBVa2YzVWgtYTNjc3hUQV84bF9N0gGXAUFVX3lxTE9XNjF3S29RMTVGcm14Uk1pakZHUXhuTUtRd09NblZoOHJ1aE5Ia2lGbXphNmdPdW1WRG11RWNSWmkySEdHRGFYNGpObnR1bVdyM0pGQTVIZ015LVFWcWJkeUZEYUNFbXZ2V3dGNmNiY0Iza3lXd3hhbG9UTEc5QmtHMGFzcHRoX3pGeExnSTF5UkdqUDFkMVk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQNGVuMGY2QmFNSDVCdDdjTk1Sd3FyS1RJcExETHMxcmdYZjZFTVNmTWt6d2tsLVk5ekI1N1RkXzVYcl9hNmVtYV84ZVpVd29IX0hjdlhlR1pCelNHWkFFX3FLVkpEbDM0QXRicVNsa3RSRVVPR1BybHp0bTNQUDMxS2pWZVJOQThwZEhwYTE3TFBHRE5pajVTT3NrRUJoSHVxR1NpOXdaNU9jb3lINDRkazNXOFY?oc=5</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>EFL Trophy: Stockport, Northampton and Doncaster reach semi-finals - BBC</t>
+          <t>EU tariffs on imports of China-made EVs - Reuters</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 23:09:17 GMT</t>
+          <t>Wed, 11 Feb 2026 11:50:45 GMT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE01LW14c1UyS0Nrbkh1OEtoMmswYW9qNXEwbTV0Uktsd0JOM2tuTzZnTTZ5OXlna2QwMDZaalhEUDZaRjV3RkZHN3BHRktpMDE4VDB0bzdxQ2ZGY2xzUDRKbmdnOXhoakU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQczBmbGEtS0tDaGMyNWd1cHA0S3FWRVV6S2h4U3lvMVkwUEtDQmoxQURxeHU4OWJyelBxVnlOaUJSNkRrQlc1RDcwUmVGVkNMS3RiOHNBZXdseFpOb09hX0dudk9KcE9qV3R2NE84Zm9PODBhZWtFUjg0VUtxeTdhT0hZdjBPNi1D?oc=5</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1391,17 +1391,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sanctions Force Russia’s Foreign Trade Down to Soviet-Era Lows - UNITED24 Media</t>
+          <t>Scottish port 'UK's most affordable city for first-time house buyers' - Yahoo News UK</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 20:01:56 GMT</t>
+          <t>Thu, 12 Feb 2026 06:55:00 GMT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNdkptR0liX09lUHNmUUpNQU82MHpnR3lBdWpEV0NNTTFoaFl1akM5amkyMjZ4WjhHaG44Ynp6aWpmOE40eVROSW5CeElFLUhJOHBoUjRZbUUzYTFoMi1Sc1hJYTQtNXAwWlBXbHV5Um92VW9TbXlhNzdETnNPUlNkTnpwNkdtOVFGQXU4RzYxa3hEYXBGdEFVeDFFRERhSnNTajMxNEV0OS0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9hMVdVV0FPYWVUOXJVbWxUWWFiNjhxWXBQVTR4Ulh0N2Jaa0ZWT1FUUEdfaW84Y0hlMk84bmItSFRQaG45Uzk5RXJZOExqZGNfanhLbTBoN01abVFXNzdYMGZBRlJDcnBxdTFZWm82ZzN4cXRHS3N4TmhISUlNOTQ?oc=5</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1421,17 +1421,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Man who was found to be dealing drugs appears at court for sentencing - East Lothian Courier</t>
+          <t>“Responding to Global Supply Chain Risks Through AI Analytics and Data-Driven Decision-Making,” Samsung SDS Unveils Global Digital Logistics Solution at Manifest 2026| News - Samsung SDS</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 07:06:06 GMT</t>
+          <t>Thu, 12 Feb 2026 07:10:28 GMT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOcGRObFpXU0dRY25CTE55dnZFU2hGQ3ZDY1ZHZDFIdDlHUmJISldhQXQzeUlaUW5mVUVQc3lDbWpKR19iYzV5Zl9iM0tOcXlVdXdZZnhVbWF2NXJuZUQxcEpyTEU2RktXeDNnNUl5SkdkYnlIZnlOM2sxYzN2NTNTN0tGUHNSMzhya3BsREVEMFBqU091TFFvcEd0UkxDQUJwNkRKQkZHbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE16bFF0T0UxMDNKTThqNk1FU011dk5SdU4xaFdlUjRXaGc3eEZRREJBcHJ2dzZEaFV2a1Frd0RMWWNGa19CWUFDRGwyQ1dDb0ZoT05Fd0RScEN1TTItNVdBVXJLWVg?oc=5</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1441,27 +1441,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Syria’s Future Between Fragmentation and Rival Reconstruction - Manara Magazine</t>
+          <t>NSW premier won’t apologise to Muslims after police grab men praying at rally against Isaac Herzog - The Guardian</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 00:39:40 GMT</t>
+          <t>Thu, 12 Feb 2026 02:30:00 GMT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFB0VF9DMWxhR2tkWFViNi1EV0xJSzhtZ0VZSDBZQjF0YkVJY281UTZuMnZ5ZndzdU95UXpoeGN2ckxLQ1FzSGhXeUNXbGZvYXVSU0xlM1BhR2YzeDhzWUZEa2Vod2NHUnN1V0djeEpRSWR0T240aXZaT2NhTDRwSEU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxORjh2MXZhMGRZc2xHNHZMNTdnR0d1TXZsUVVyWGZqOG9Da19kMnJJcVliRUItMksxeUVsT2ZwQkhlNG1MQlc2bkw5OFVTODFPUF8xZ0w1SFpwMDRFX0x2ZlBRaHBxTktrelp4Y2pDMG9ib0ROaGs2MjVYOXNtTkwxSTFzbjBqdnQ4YlBxWFhUV180WFJwUjNralI1bmN1Tnlud0lpMC1Vb05XbjMxZzVsTW5tR2taSkZGNXUtMWdsTEFZVDQ?oc=5</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1471,27 +1471,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>25 wonderful old photos of Fleetwood - port, town and seafont through the years - Blackpool Gazette</t>
+          <t>Protesters clash with police over bid to restrict Argentina’s labour rights - Al Jazeera</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 06:00:00 GMT</t>
+          <t>Thu, 12 Feb 2026 00:53:21 GMT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxONmN4RjFsUFRtOWZzVjZkQkxsX2F2UjVjWkdTdWZQVXlxb0xDOUxIOTJ3Y0NwT0NGS3dtSktHemRZSVZLbHdHa3Z1S3lUWGR3VTVGSEZiX0hsWlVRN3h3OVJBSGx5R1l2RWZwNUFkWEp1ZnY0Tm1qTTdiWGNrTExiUzNtcFJCV1lJcUF5R1BrUTdGU0xQMkNjdERsOF9jZnFTemRrNGJPaEJHREhvdWlBYzZOSTZXZmJwbkNjSTVnb0RMWjA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPalVaa2VqTGdTNHp5cUw3eWhFOUNKQXZtYV9WMExiSDRaY2o2Ync4aUdqaFN5bjBlbDhqa1BrdzZHV1dyOHZYenZDT3RTWkE0S3l1djN3RV9IclJqX3UxREFpRjNQV1V4WEV6dG1nenU5NWlRSXpNNVdzS3NDT2UxSTJZeGZ6R2h2aXNydTBFYjNCUUoxR0c1RkJMcEdGSjdaT19wcjRDQlJfdHF2MUZ5WjhxSXVxd1hXY0HSAb8BQVVfeXFMUHBlbWxnT09ORTF4T3pMMWhLQS1XYWFic0NNM1lmbGRzV0J1bXB0ZXFLR2w3aGNIZjdMd0g4czZESHI4ZHFueGZUUmhBb3VYU25oQ2FqWkU4T0JSa1dDNENjVDdfdmJDYmdybE1oMmx3S1ZjbW00VW9IdjdEd3dyUVdjSl9VLUw3N1p5VFhHT0s2OGxBYllaNWJhTllNbXZZdU8zUE9jamFocmhtMllaSUtoUEt6NW1OU3VYQmpqaEU?oc=5</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1501,27 +1501,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Gabriel Makhlouf sticks to ECB line on rates as US tariffs help keep inflation anchored - The Irish Times</t>
+          <t>Amnesty International Australia calls for independent investigation of police violence towards peaceful protestors - Amnesty International Australia</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 06:00:55 GMT</t>
+          <t>Thu, 12 Feb 2026 02:38:39 GMT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQQUVrbmpWYTRHSnZreEJmRGFkcjJBQV9iY0lXMWdnUDZ2WE9Td2F5U0g3elNNbG8xMVA2M01SYTliMlJyWE9RYkJjcGF3eUhxem5uMTJYVS1jV1dWa0I0MEdaWW5pUG9jQm90YVBpZ1JzbFlDb0QzY2o0eTR6RmZLZm02ZjJxa3pHbWtoM3ljS182QUtUZWI5Rl9GY3RaazJkV0I2QkpHQTdabW1lUmxtaU1kREhzOXQwdENHa3JsR19ZM181YVZlRGNCMTdEUzh4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxNbFJ5dXlYVFdITm1KelBGSHJaYlJhVW1TY0dYT3B2ZkxTSXA1WHJFbDNSOTFOZ2VtNE5naFdrVWpMUHdLQ3RNZnA5eHFISUNablRuX1hNUS0zaktCdVlBZGp2aGk1T1lELXNQSnc0eHBYb2xHX3htTG1vQWxsU1AtemU2Z1MxZURsME8xZ2hsRDZXdFpMamF3YXEtSGFxMnZ2UkUybmxocThvU25fMkcwWXVCeF9DWElRY0VPeUc3aTdPZllSM1hxazBnV3VzNUpobl9sd2JtbldsUQ?oc=5</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1531,27 +1531,27 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>VW’s Cupra Tavascan first EV to dodge EU’s China tariffs - Automotive World</t>
+          <t>Police fire tear gas as Albania opposition protest turns violent - Euronews.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 06:30:07 GMT</t>
+          <t>Wed, 11 Feb 2026 09:08:53 GMT</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOOEd1dGJ0Y3ZhT1lHZUQ4SmFQSU15ZVY4QXFpb2RkaG9Ra0pXSlNEdmxqT2VmdXloMlh3MnJRR25aNnJhRjF3SGtWdEpKQjRuRHlRRWoyVWlaMEJRZTN6dG9qaTRCTTZXOUxsMTV4VjR4S3hVdUtvYi1RczRsdEh0RF80WUpwbjJDUGRfNDcyVWkxMVkxQUxZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOU25vVVZFbWpZN3dQM2VLQnpxdXNWNGVVM3loOEFnMXRqRjNXcjdQQW9oempKZTZJbXMway1LaG84YkZTM3NlTUhBZF9vVm5CeGlvRHhZSlRHXzFzSWt1d0xtenR6WHo4UjRiYXRiUEJXR25VQTcwbHZyWDF3ZFpsY1lfcXI3WjU0dDZUTFFkcmMxaVRyZFNrNUhXdVdtQk5UVmc?oc=5</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1561,27 +1561,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ukraine Hits Russian Drone Nerve Centers and Logistics Networks - UNITED24 Media</t>
+          <t>Protests dog Israeli president's last day in Australia - Reuters</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 16:14:01 GMT</t>
+          <t>Thu, 12 Feb 2026 03:47:00 GMT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNSE1FdEVRaXkxd1ozVUxMX21kNi1PM3lMcFA5QWZmU3VmZC1fd2ZaY1ZqcExJa0dveUU3RlE0aVMybW95X0tVRS1Meml4R05sX0xWQk5TT3UwOE5vYjQ2Rk0yUVpNeENkaEdrVUJtekctRDZqUkN4OUEtdjhZdmxMYTJHcjJJalJSazJIYmprMms3aWFJUFJJNUluWW41ZV9TMXlTbk9mcmdvQU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOUjN0OHFsdEtiV01BVF9hb0tPQU9STDhpNi1XNXNXLUF0WWRIanBWQTlVY3loYjA1czVoeFdhVlZyb1dzbm42cTRMeWpkb1dJWUw0TzIzcTJJS281dEZOb25PNDhfM1ZyRlJtSVZwSmNRZU9kM3BBdWNHdnE2SEdlc09rTDl1bFp3Tm96d1hKdGVnejFHUGp6RnhGVmhuSFJlVFNienlRUU5kVGI1eWFrbVhoaFBvQ0Rn?oc=5</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -1591,27 +1591,27 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SeaLead plummets in shipping line rankings - Seatrade Maritime News</t>
+          <t>Protesters, police clash at protest over Milei labor reform - RFI</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 05:54:57 GMT</t>
+          <t>Thu, 12 Feb 2026 01:04:14 GMT</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxObUh3d3FvVThxUl90ZmV2czZldWE3THJsQTBQT29LWUZyZ2hFdmhCdEpNcmNNTGItc0tFdDg1cHJBUWtjSUdnMW1IVkxuZlpNeHNOSWZCQXRfMHRDYUpqcUYtVFhMbWVUcFZIVjZpa2RQcU9CTGdIT1I5WjFmejkxcTNVZ1FhQlAySTlkdlNKNXI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNUVhQS3BEN2tBTUZ6TnBnYU5FdzY3YS1POXY2NEJybnZKRnI3cHFnUG1yRHFIbXBBVW4wMkE5bmJJUE8xQWxRWFd5ZC1pcFBsUFpqemx3YzZucDZxcDZUczZicXRZdThLY1FpRVdURzBXYnFGMmhjeExxR2V6ZTkwT2dqQ2xUYWpDVzVHQlo5Ni1tSDdSNFp3b1hBd3REVHF3eGtFaEc3c3NHc2xD?oc=5</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1621,27 +1621,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>How AI collaboration transforms governance and compliance - Thomson Reuters Legal Solutions</t>
+          <t>Lee Mark Chang Defends UDP Protest Amid Police Warning - Greater Belize Media</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 21:13:48 GMT</t>
+          <t>Thu, 12 Feb 2026 02:43:49 GMT</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPSG9mcmdjeEFJNU9heTYyMHdzdHIyYlB3S0hJSndwU1pTcnVkOV9XTTJaVmZXMHZPcVUwOUNoQVlJU0w4SHpkM19NZUdCSjE3WjZZYzl2Uml3SE9UQm53YVlMXzh0ODZMY2ZaZF9EdmRjZEl0ekNudEFZRkt0S0JIMDdfMHJzSElFMXNQLTM2bHdXZUJhclBuaXJLQzZMWE8yZm9kcmxsa0otbVY3dGV1T1ZGNDFRUWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOUGxzaUxtWnpkczJGd2lRSFlfQ255YXFVOGlfZTg2STVUS2FBVmUwNk9ja2dHSjF4MEh1M05MeGR6TEZQeC1Rb01pd0l6N2VuQTR2aDNodTVKdTRWeXczWWJuVF9zU3R0LXZ6UWQ1b0pqbWxJRWlQRW5NeHJuMU1ZbW1keTdZZlIyQVR0b0tB?oc=5</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1651,27 +1651,27 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>German Oil Refinery Sounds Alarm Over U.S. Sanctions Risk - Crude Oil Prices Today | OilPrice.com</t>
+          <t>Spokane police use dialogue team to manage protests peacefully - KXLY.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 21:30:00 GMT</t>
+          <t>Thu, 12 Feb 2026 03:08:55 GMT</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPRVBocnlscUNIOG01T3hEcU4xczcyVlhiUlVLMzFXd0J3YmdveTR5Ri02NklLVUFoZ3REQ29CSkxrekpoeEtaYkZYX2lUUkFqRFFSY3podWRSN0VGQkNiTTFIWlRZcmNnWng4aDlROEJ3QjBTNVZFendRTm1qclhZN3g1dC1EV09DYm5tOEtjV2pndHRveVVKZTJVY0dfdk4yYUVsU3NrMEZ0SkFjYTRwZdIBtgFBVV95cUxNOGdNSjJTQ29XVnFuNnVSLUdmNmRPYWdDNzE4M25URXNiS3Y2T09Qam55SFRqeHJOSE0yNFk5aHJKUGNNcFBYel84UUtfWG1LTVp5ZWFZUUJORW01SklNSmk2aTR1MkU5bGlrejZ1cHl4TWFNOXIxdm01Sy1rcmtTcXVYT2pYWTdCTDI0NklNMzFvcW9rZ0p6c3R1YVJ2UkFmbFlsTVVTSWV3TENNYkN1ZDNJRTVkQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNRG5HLWRLUkRRbjFYa2hnV2dHYVpnSG8zLVh6R2xLaFBJQXZkX0R4TE9sY0M5YkF2MWZLZlBMSGtMWlpzMFdFNGh0S3V3LURiaWRHVmMwNVZnZmdjWHZfeDJvdmNXVXJ3Y0hiU3UzMW9xU283OUNPLTR0cW85dlN6WWl6ai1FMVFOTE5oZEl6ZmJKSXYxT2hNNG44RWQ3bW9tSk5xaVFwWGVFQWpvR1FGWGR5T01IWDlaZTVta2Q5MlVfNFpBbkNhbW9QQTI5UmRsSjZRcA?oc=5</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1691,17 +1691,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Woman, 69, in hospital with broken vertebrae after police allegedly pushed her to the ground at Sydney Herzog protest - The Guardian</t>
+          <t>YouTuber charged with racially abusing police officer at hotel protest - Devon Live</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 02:15:00 GMT</t>
+          <t>Wed, 11 Feb 2026 10:32:12 GMT</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQYnFCY3FhWHY5OU9pdnNRUDJMc1YyaG1iLUxzUHgwQkh3ZUJya2d2SjBpWDU5UXNyMUN6UWlJc3ZFMnhVREJCVTZYSFQ5eUhPQ251Y2tRNm1ONmZqMk1UT2hkNDBhRHNVSk42Nk9VSWxreGlpWVlrYlp3X052b05NWHIwdEdWTW8tbWwtWVpmck83LUE2MGV2SEhENmt4UFBwZnFRTVktYUdSM255b1d6STRJdGx0UnZJODk5bmF5cUl0Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPYkJHbEhjbVhjTU9OM1l4YVFQRUE5aDB5aFJ3cHZIak0wX2trOWVLa2JWVmV1czA4MXFrMjFsdmRocUhibzVfdkFJQW5PdklYdXJTZ0NVUlVZUURmVDM1STNpclU1YnNjb0FuTHJVZlhsUjZuVFVvQlphOGczZXJ5NFF2YWN6dWNLc1BDczFPRHZvRklRNTJmNlhR0gGfAUFVX3lxTE1Ra0tIVnRhUEhqM0JxZGxzRi12d0lGb2V1cDBKYlNrTzctYjNQUXJxb0JpSzA4c2h0QTdFankyWVRiZk5RejQ3c3ozYjdqWTFCSjFLNFhUOElhaHdYZjBfclFtZzVhRW5ibk5URXpxR2ZzMFk0MUdNdVZ3OUlSREgzT3ZCTzEtZXh3V283Z3h4MTlNRnlpV1lndVVRZENkVQ?oc=5</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1721,17 +1721,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Epping: Man in court over alleged racial abuse at protest - essex.police.uk</t>
+          <t>Aurora Police Department responds after video shows officers, students clashing at anti-ICE protest at East Aurora High School - ABC7 Chicago</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 17:44:00 GMT</t>
+          <t>Thu, 12 Feb 2026 04:35:25 GMT</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxOSVFCc2RNS2pkYkRkNTRhWkFrU3loYnV6ODF0X2V6Zmg1QThrdmV4Tkk3eWZOQTFlejFEZXZLV1hyd1cxdnMxa0VSeXFFU2gyVjhRRGxRdFluREhSR2FZYzhBXzd6RzFKMnhBS001LVMwcXVfQlZsSlhJQ1lNR2RicHZDUldUdHBwLUlVSU50ZloxSi1BRnBqNFNUNnlmYmJVUm51V3NuV3FqNkoyU3dSUXpVSncyVUJ5c2NTNkpPQ0U3U19oQmZpajBBOG9aY1g1RGpZNmVtMEptbmxq?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNYTRSeHdCWDZ1RExFS3AxRGpFMzBLMEt3U2NvTGxBakpaNGpkR3Q3S1lURVBRVHR3R19rb3Z6RU9GQTg4SEFNWmM3UU56TjFRWTJiUWhPemRibTNkSFNNWlVYVm5OY3V2TG81cGU1dW1RTjhXQVV5UTBxTDJlalphMExCMHpfazZ6UmpnYi1KVDhQQU5IdVlsVUpkc0ROWlpLeEl4STF5TXZLeTIwemdvRzhCQW5SaFg0UTZncXMtVUhKUlBJWldDdUJLeXRqSERlOGt2bTdCdHFmT1hibUHSAeMBQVVfeXFMUHVMWXcxajZ6TGRBQldjU2Y2dVJaWVV1WURvd2EwVVk1Z2k2N0RqamZ3X0NUWWJ0SXpsMFJURXBmYm1MQVZGZWU1WG5LZkVBZnR5aDRfbXU0T0FCdTRCY3hsUDRMR3gtRjd1Y2dZMWs5WWx3S1FJdFZCcG9FYjZsNkdhNHRvZnRDUmlBS1hWdEF5YmM1Y3d4QjlyRFgxelU3Q1VaY0xzcnc1eTlOUUhRREFadTNLMWo4VEFWb2FQUWNYQ2p4UHk5LXJDbm0zM3BTMUJmZVkwLTg2R2xnMmtYbjhYQUU?oc=5</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1741,27 +1741,27 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Australia police defend actions after violence at protest over Israeli president visit - BBC</t>
+          <t>How AI and automation are redefining legal practice - Legal Futures</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 09:34:33 GMT</t>
+          <t>Wed, 11 Feb 2026 14:52:21 GMT</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE55X3pEekVVX2xLYkhnZjg4VmdvLUlPRFFOUkMxekVsc0ptSXEyMDA0ZkNzS0pNM2lEeGVubWs2Q3JoU2Z6YU1qZzB1cGVVRXViSS1sdW96XzRadw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOeDB1cDdVeENYbDM3VmRoLWJGdHhQQk9WeUhlc3hiUW5BWkltc2l5NnpIYzhyZlFydUdTUnl3Mnp0RERfQ2ZMTXdsWHFLVHFveUhrdEZNejRBVC1ERXpFWW1WNTdYcEZCVFhFX1hsLXhxbW5oLTkwTE1JWFo4R1lEend6alIyRE9NWWxtWXNsbXlWYnRCOXpiLTlFY0lldw?oc=5</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1771,27 +1771,27 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Day 45 the Protests: Nighttime Chants and Intensified Police Presence - Hrana</t>
+          <t>AI threatens to eat business software – and it could change the way we work - The Conversation</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 22:00:15 GMT</t>
+          <t>Thu, 12 Feb 2026 04:23:00 GMT</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQTEJ1ZUszLTBIUGVOTWdBV2Y2eVMyZWZfMVlnYnVHMERtV1h4MTFUdGFQTkpOVDNVaFo2WVhOLWJhWTdRYUZHOU40Zkx4ek8wUGNKbVRieU12RVczNlhlUjBRNXdsd2tDeFhIWjY1eTZJUWdIM3JMRDFjOHIxcEtYNmU4NnhQOXU3TWtfRFZJSTNfNzhVajlGWnlB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOZDR4ekdxRFctaFhmSFpFY0hOOTFXOTRidDAzRDdQLTJIQ1RfcWVWSDhLeTlsT3pDS0dDQW9rclAzVDhUSmpWdVV3YU5OLXVlOUJoUzE4a1JJbjVMRmxLb1d1cFl5S1hGdlRteEJDcHVHbjdwbVdzdHJmc0VzdzFrMlZIcmlVdkJYcjVvQVR3UU9Dc29DWXBORXNFZWZtZkItZkFqY1pvQ0lhaVZT?oc=5</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1801,27 +1801,27 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Eyewitness: London protests converge on the Iranian embassy once again - Police Oracle</t>
+          <t>NHS launches AI and robot pilot to spot lung cancer - Healthcare Today</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 12:07:35 GMT</t>
+          <t>Thu, 12 Feb 2026 03:35:24 GMT</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPR0p4RXhFQjdmY1ZSZmhpWVNSLUpYSXJvcEFuT3JqaGxraVNlNVZmWnJGSXVTZWFBdTQ5VnBXR0t3ZGJjb2FFbXpKQ243d0RDZnVxUmRacTVhY0RHNnl3bnRBRDRGV0RBN01Ob21MVjl5Y0FvaHVmZWpIOTZWSl9veDdnV081M2x3R1o1N1VBZE9HNDFSUnJ0MzZpZ2EyU0dtX0xsTkJjTGlNUHNtTXZLX0tOY2xWZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNMUF3bkNPdmxpZEZDeEI3ZGM1ZmFaSVpUNlZHNWZIMWZVVEhXR24wRzVNNkZuRWZTcmluV0VQUlJYOUwwdnlWWnlCdE1wOGg5ejlMc3Zvb0luNThXcXM2MExZdDhLOUxJM3hOdGdmSUxuNGd2c0oxdnQ1V3NSYWVyWGtXVWxmZmp2UG1TWXJQZ2M?oc=5</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -1831,27 +1831,27 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Antigovernment protests in Albania turn violent, at least 13 arrested - Al Jazeera</t>
+          <t>Reaping the benefits of collaboration on technology and innovation piece by piece - The MJ</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 04:17:00 GMT</t>
+          <t>Wed, 11 Feb 2026 16:47:20 GMT</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQcmFnaUJZWDY5Q2RObUltcjVpdjBoOFFhZHlubkFhaE5qY0phWHNUNGJNaFJKa29VanVMbnY1OXVZM0VlbkhSc3BpN0R6UjJFQkhJWDc0dVpkTDJJbUNYM004c21yenZtN0tFUVNOVkZjOUU0WkZYNzNaMGJ3eFROWUwwcWYybkdsQjg0YXkyYmdmdGIySkFZSlJvSkFNalpfR2FCc0p1U2xGRXNfOEHSAbMBQVVfeXFMTnVUbzhsUkhMOUNqYUlWaHpac2VpX3Q5b2UzczIxYlVrT0JyR1RqbmxUUmh4YXp3Tzd4UUJWbmNOYUNQSk0xcGs1NzQwZnlMbmtNLTNmMDVhY0ZpTUo0LVU0aG1LMnBQOHZvaUx5cnpKZDBrRlVTZ3plWWgxQXdwQlA4NE1aM0pMOXI1TDlxd0Q0MUtQcFNnb0RQOTYtMmNYTFJQZnpPV2g0ei1qWVphVWxlOGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOOTFUdW5HcGVxNXk0TnVLWGFFbGNBWE5UdnBGYU5sQXg1TkEyT3dQbmkwRE5HTjdRRG1KcTR1cFBQTnd3V1UybHo4REV4VkY0QzRBdHZZemllYkR4bGpWZlBPVGx6RWpGM1AzUXpyX29NMEFtNExSakdNQmVrS1JSZHNweEJzLVFPNC1JdXo1UnRFQQ?oc=5</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -1861,27 +1861,27 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Labor group voices ‘distress and disgust’ at police response to anti-Herzog protests - The Guardian</t>
+          <t>AI could rebalance power between people and the services they use - The University of Manchester</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 22:18:00 GMT</t>
+          <t>Wed, 11 Feb 2026 16:39:53 GMT</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOYU15V3RDMTJyNEdxZVRvYThsMHVyZTQwek5hOXlsLURjdTd5dUYxODdDdGluZFJLYXZHeFZNRTllNnJZcXhVcGhtbVgyb1F6SkxvcDI1dTVjZ0Rjby14TlBGTDF0UWlrd2g5ZjJwVUp5V3MwbFEwdXI1YjczMlBjVXhVRXlGTUtUcmtNLXFSV19ZSkozejR2RjI2b1dTVmhYWTRQTktyM1Jad1ExR3lrN0tJelRENFd5Ym5GeVNSSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNOGhma2ZXQUFnclNMV2twTGdIbHQ1end2X3RCMzIyNkRLV21HZkVXT244V1NMTzFqZ1JRal9Gd3QtX2RvYTVZNUdWamtwdkNjZVRfaGluSGJBQmxyMm1ieHhRb3RzZTRtYVFSWFktZE45OFVOS1lBdkxZQWRIWGg1azkzTWh3MnFCU0VjUnpGZFU4Vk9jSWp4WQ?oc=5</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -1891,27 +1891,27 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Australia politics live: Angus Taylor expected to quit shadow cabinet and launch leadership challenge against Sussan Ley tonight - The Guardian</t>
+          <t>AI (artificial intelligence) - The Guardian</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 07:01:00 GMT</t>
+          <t>Thu, 12 Feb 2026 05:10:33 GMT</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxOLUt0Y2hrdDRkSElsTkc3UnlnRmtJbExLMFdOVDdHSEs1VlRsTm9VaWRZOGZjNmJlZjVfWmlrbE1vNXhwWEFUMVY1X01QUGNFOTdxZHdKSDdrdExVV2JaTWlGR2pVaHdqSnZJOEg3dWhTLUhJZGsxR0VOSDdjWHo3aUJPamRVTlNOMXRSSzQzREtPNlRkdUhnamRCQmpKZEF1QU02elB2NGR1UEtDNUMxUGFZWnpidVFxemxDNHhLcklmajduSEJ5dkI3LUVZQVYxaEppYnppM2VaU28tMDktVERLNDhGNkJ2YWNCcDB6UHR5VTdBdXFnMkVKaGg0R1JJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNWHl5RUc2Z1pZVVk2Y3VmUTlXOFFiZ2ZUc01kcm0xTEI3WE1KYzN1d1drQ1l4NDhFa0VIX3ZQdEtYSzFNanlIamRRV0xpdThHZEhXX280TDdIdFVZeWVHeGpnMTJhd24xNEF0a3BhaEZ6VVZsTWlvZE5NdURtUW1Dalc2UjItdw?oc=5</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -1921,27 +1921,27 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Police chief orders watch on groups over post-election protests - Nation Thailand</t>
+          <t>Why UK CFOs are Trading Ad Spend for AI and T&amp;E - The CFO</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 09:43:00 GMT</t>
+          <t>Wed, 11 Feb 2026 18:01:29 GMT</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiYkFVX3lxTFBzQy1WQ1lpNG1aV0hXa0hkY3Q3Wm5zSVplR1loX1d4UW9TLUozZ2J6VWttOEpjOXBfcE9hdUtiNDhuLUNtWVVmVVNEdmw5RXNQYkVMOEQwMHRzSW8tcTVMRUZn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1odXhTN3NodUIzZ1g2UkhYYlpja3ZJdFZEU1FWWkFGWXhkcmgybW42a3hZODEzbFFyUXVGM3l6UDNxb3dpWmY5T1llUG5DalFHUTZ1NFRPWlpOWGM2N1RPc3A4NEpiQWp2cmJfbndvOF9IaU80X20zQ3QyS3lzZw?oc=5</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -1951,27 +1951,27 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Despite police crisis and protests, Unión, Colón and Copa go ahead - OneFootball</t>
+          <t>Accelerating science with AI and simulations - MIT News</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 17:01:09 GMT</t>
+          <t>Thu, 12 Feb 2026 05:00:00 GMT</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPRDFRaWVYRFZRRmpLZ3YzTXhFZ01uSk0xam9obzdUZS1XODBDaS1Sbl9kYml2NjBWN1ZoY0V0UnlYd2VXSVlCTW5HODBmNGtNZjFGRVQ5VEwtRmt1SElPVWJtLU43bVZLY2Faek90dmZJbXJqZE9MbVhDOE4wSll5R3o5bVhKTmhlWkVnNHY4LXBMb0IyRVN1WEJtLThzWGJiOWdScnJNdDc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQazZiTUl4M0w3TGJ5YVpfOWpwc3pqQjlRUVZacWl4dGxidk9XajAzWmtYeFNrYjFQVG4ybGxfSmVWMnY1SXd5bWFraXRVZFh6cm9udlZfMDc4NzFtVmt0akNST055eGxJODd2OTlvZkxpX2NMWFFoeGtDSnJ3UFVwamlZbkJQQW5fcnNqMFluR2FEYlhwRlZPM2xB?oc=5</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -1981,27 +1981,27 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>‘Like a pack of wild dogs’: Protester injured in Town Hall clashes calls for officers to be charged - SMH.com.au</t>
+          <t>Siri Delay Tests Apple’s AI Ambitions And Investor Patience - Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 21:20:24 GMT</t>
+          <t>Thu, 12 Feb 2026 06:11:00 GMT</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOLW82YkxUdVhjdTBFRlRvYU1jcmM4UjhGbmV1LVQzVEZDcTY3NDliWjdDbk9ZQlExZTFNcVVFNTZDcnlUd21rX1Aza1RmNjIwWmJRVWZ4SWZLVVhVSUJ6WHctOEVBbnB1S2VZRkRkZTBTb2hfMzluMFpKUFM2dndBV05vbklETkRSd1JhOHpvamtnMkdWeHJDelRldGY2RGwwUlRzVVA5eUJOX0N5TDNFYUZ3VXNtVHlQR0NPM2VGZ2lVMzUtOEo0QlptMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFBvTjREblg0c01oR1I1NFdncWRIekJtemJ3UzZkUzN1ZVdjSlRHRXZRUlZyb1dyZVpORC1sWlVSUkF2dHYwMUxzSGVRQ2ZFZzcydFpobXI2ZTFzNU5fSVliaU9fMGF3SlRVa0JlYVRrWjN3eF9tS2ltRVVGcjV4WXM?oc=5</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2011,27 +2011,27 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Rather than promote social cohesion, Minns’ laws have led to concerns about police brutality - SMH.com.au</t>
+          <t>[Webinar] AI and You Series: Common and Uncommon Ways to Leverage AI in E-Discovery - JD Supra</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 07:29:47 GMT</t>
+          <t>Wed, 11 Feb 2026 19:44:01 GMT</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOMk85MWo1MVVkalVtYVR4VzUyaFVEUGpXWk9FSDBQRzVrLWlId0ZwU0Q4alFlYVlkWFBkTW9qTWprd1kyZFNOOEx0dlBxM0l3bHY5dk9BX3oxd29ta1B6eGFNbHJtY1ZqdlZ5bzlGa0NBSUstTEtYdWdka1ZvTnFQeFotZnZRdk1mY0JzS1lyR2huVmVxNjU2T05iSzFfZTJjbzVoZkVuY3ZaeWJfZWVUSnVaa1AxdllDM3FwdktMZ0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPb3pvOG5kb1U4bU1ubGplVDVWbm9aOUdFRUtYQ0JYdVIzV25vWl9zWXJRdjdDXzNQY01nazVBblJNUTNEeHVVSmIyRnpnT1V2YjB2ZkFicWhUNWxrWXBJQlVub1ljZHFheTZzY0NBQ1lPSHBFM3dfOE9ncVVxRmNrbS10Q09Edw?oc=5</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2051,17 +2051,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Durham philosopher brings ethical thinking on AI and democracy to global stage - Durham University</t>
+          <t>US activist Elliott builds stake in LSEG as it reels from the threat of AI and the exodus of firms from the UK market - This is Money</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 11:16:16 GMT</t>
+          <t>Wed, 11 Feb 2026 22:01:25 GMT</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQbF9EZ3B4TnBNWmw5dnBZZ0pPVkZjbzFaVmVOeXVpUVpxVU9MSFkzbFFuOVhuZng1NEdkWkd0MEt3eG1qeW5Lb2FfYjI4eGREU2x3eVhYU0VxSm1ibWNRdm9uSmlyNFRxU19ISVFvVXE5bnpFUU53amFISGFhd0R4WVd0cVVPY1paUFZiUlFnQ0taNklMZHRIUHBSUkh0VktCYlpZMkZpQ2NRRU9KbEtjUkVlMjVPeXBGdEdxcWMtdGRld3MxdHVLTGF2NEhYN0xOT3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPVkx2c3JwVmc4WHAxLVA0blUyaEh5Y3RUTjNqdng3ajNWLWY0Ym5vNkJPc19YUkJySDJ2MXNTRUhGVVRBQnBuN09VMzEyVG85Y2xMVnVyenBvTmdhY3hSWHZBeFJzSnZ0VzhrTXNsUDBiOUhGcDJxOTFfSzgzV3NpX3p2TWZ6X1k1eVpIejlRNzFPdWc2bkh2Yk41dV9Ydm1HSnh5YVhyYzJaYzFNNG9mWmxiUG5hV0ZreDQxczJrcDUyZ1BQVXhNbmF2S0JDZDNTMm5YaW9OcnF4UQ?oc=5</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2081,17 +2081,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Escape the rain and discover the world of robotics and AI at Aberdeen Science Centre this half term - Aberdeen &amp; Grampian Chamber of Commerce</t>
+          <t>Software and copyright: key takeaways from Edozo v Valos - Mishcon de Reya LLP</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 14:13:42 GMT</t>
+          <t>Wed, 11 Feb 2026 09:17:05 GMT</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQWnJuUzI2RXhza0dBajFXZU1CT3g0OHh0YkNpWmZQLWNEYnhXNnUxeE54Q2xvM0h0c3ZOU2tNOGtESlVHNFRDSjM4a19DS25pOTF1RWZGLVhGRG5oeUsxaHdxX3FNTkY1OFRWMXRqVzNDTjNyVXlVTTY5dzF5RjltdXFFTGhLU3J1V1NIdWxSVjBZUmxvSU9LREZRelZhUDBSSm5LQW0tTGFYcUU1NEF3Wk03bDllVnFmSFo4LTNjcHA4ZEVVdFROMFVfcGtucHhx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNUFk5cGR5U1k4UGUxR19BYmJEWVlrbVdCdTVncmx0SlQ1TkdrSnl1dktYckZzN2tkTmxyaVBYaVpmWkZjVGNNMjUzeElBT085SWpVa09rM2xqMVNtZGpmbWNGTHhGUEJjYUJVOTJ4WjljQk9LUWtoTENjQXdDY21lbUotd1U1bS1GbUQxVQ?oc=5</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2111,17 +2111,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Silicon In Focus Podcast: Building Inclusive Tech Teams: Skills, AI, and the Future of Work - Silicon UK</t>
+          <t>New analysis shows AI could slash public sector admin task time by over a third in Scotland - FutureScot</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 12:27:10 GMT</t>
+          <t>Wed, 11 Feb 2026 14:26:07 GMT</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOT2FQc25wdGNXNzJjWEI3RFY1VkVkN0Nvb1M5ZlZQMTh1YVJ0WVhuMWpCNC1iV1o2dXdrSnI0YjZBQ0R0dWxPV0EydVpkSndRdExrek1rblp4SFAzTXJ3OW1SU1paME53LTFGN2hjamIwQXlNQmVDY1VjM3pzN1Q2ejVBd1E5ODN2N3VYQlFnVFh6Qkt3R0Fad3hZMGVLR1BuZFBLR2NyX0xRTl8wb1BxSFpiY25TSXNya0tJQ1YySzIwSzBVSzl1VmN5endpZmNDc042bGFyY9IB3AFBVV95cUxNZ0lyQktSSWR6QWdDRTJLY2xQOWlNYjZ5VkRyRUF5Zm1leFJ3MDdvMmpGS243YjUyNzNST3c5Mjdjc0VKbFNsbEdwaVVhOEFlYnlfejBTM2VES0JLUWZXMURFSE5NSkxLTTdFSnBMZmtjX2VmSFZ4dVJzeTB4a0YwT3k2a0l4SnJVVjRQTDdDNmdneTk1WnZ1RE0zOWVPWnRxdXVnclN5cVN2bjRPMkkxbHk4X0FHa1ZkMkRIR2ZmMzhGaXptZkNkWEplZVVMZkUtM2JRRlBhSFZLdndO?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPWW5aTDd5T2lGWTh1NHp1SnY3a3Y1cjFhU1RaYUNjbHVvQk1wWkQ5TVhGS25wM1dOTEQzdnNRZUJqVE5JUW1NYmRlX3EyLWQ5R3NraTVIRE12SEhSS3hLOV9vMWpxZUQwOGpzdl9yUnZoV2dhMlpQLThQYldNT2MyMWRZNjBZdDNWd0ZrYkd6aXFoWUhQMzhSenZ0ZWxsVEpaS2lRY0dMRkthcG5YaFdycNIBtgFBVV95cUxONGphZ0UxVkN4emtDNllZelAzR2ktOElUcWJtZFFLc0d1UWVrX2ZYT3ZxQVRzMXZSZi1jS2lJOGl3QmlQYW9NdnViSVZwa25XQ3ZkSkJQZDg5VXBHTGpTbWFFekV2OHlPNmViQzhPQ2hudk11M0s0WGlVUnJBOTZnOVF3ZWxFZGF1LXkyNTlhQWRMc0dqZGdTMjlOVkt1N0t0alhQTzE4cXRzTDhJSmw3Q2ZmX1drdw?oc=5</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>NEWS: AI Partnership Aims to Speed Up Discovery of New Medicines - Practice Business</t>
+          <t>Shares in UK wealth managers hit as AI contagion spreads - Financial Times</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 06:29:01 GMT</t>
+          <t>Wed, 11 Feb 2026 11:16:09 GMT</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQYzUyNXlaeTJ3LTFZb2RhS05tbkQwU0tqTWdPeUpIbVJlSkFOa2JRQmhnV1ViejBNSmRrQTFINjJ0MFpKN1RxNFN4cGhtNUM1XzhFQ0I2R3BqWVNDNHlRdUs2M2lvWTkyRGlJYXFmUElrXzlfT2VVZm9WdVBSVERDNWNKQlRGSHBFX3dybUU0ckhNak9Oc2ZaUzlB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE9DV3FGMlVWLVJMcEp2ckFRT1RTSUhtNkJ4eTFJQThTNEVTcHRDV3NNOE90NHdweVNPcm5uQ3ljbWM0R0d1VmIxY2d0ZlBBeVZ3WTBHV0tyX2tTVHFwejZmdTZveUpwMHB1NmJYY0NWNTI?oc=5</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2171,17 +2171,17 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Announcing the shortlist for the AI &amp; Software Development Awards 2026 - Computing UK</t>
+          <t>The big AI job swap: why white-collar workers are ditching their careers | AI (artificial intelligence) - The Guardian</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 14:41:58 GMT</t>
+          <t>Wed, 11 Feb 2026 14:10:00 GMT</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPSDVzNXFfdDltRGFLRDQwWTRyMnZxSXhKOURMQ2VOOUc5RlNkN19PXzVuNU52NTBNTGJlZDU5SnRwY1RkdHdHUlpDNS1samVIQnUwakM3VS1sZUkwZC1vNmctTnJqN2MxTGpHMzdsNjFwOWd6X2RTRXpvY1RNcVNMbm85NUZfMHNTOFRsZg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNaDEwbEgyRXBzVktxS1dMR2pHWE5VOTg5MXk1OFUtV3RBcUwtenRORDNxQWhTSkQycFpqWFNJb0RQaV9NOEJrenZGYjJhbENVNktzQWRnOXhKdVAyd2E5aFI4NHJHRUw0NFRuQkE4Nld4RDBBNGxMTGppVXZnOVA0VmFlMHlnM05jazhZQ21GSVNDS2h4ZDJwM3FuOTBTRk05dDFZeEJoSlBOMWRsck5J?oc=5</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2201,17 +2201,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CreaTech Network 2026: Exploring Creativity &amp; AI in Entertainment, Heritage, and Open Tools - The University of Manchester</t>
+          <t>Okta, Inc. (OKTA): Expanding Identity Security With AI and Global Growth - Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 15:48:14 GMT</t>
+          <t>Wed, 11 Feb 2026 17:18:29 GMT</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPaHMyWTdfQTNFNzNKcS1zeGIzcW1Pc1RhS3JZV0ZXOV9TMXZvd2l4V2h6aXZSLVYzbmJfd3U5VTloRDk5NW5BaHRyV0NsTnQxeWd5Wld2WFBRMlF2b2c1bGJidGlZWGlFTGQzdzhWc2RtdTZHTEVkYi16UHhyVDZsMWROODZLb3BRRExfTzBURXFLdl9ncm5KM3RrLWxaSzNMMUExYkQ1QW1YV0NNaDlCbTF4TmtCSUZhZmJGRm9rdEMydkFYU1lR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPZ0VRSWo3S2RSY180cG1QMGp0V3JkTzhSZkxrbGpHSWVUeEV0Mk1UZGo4dGRGSThNT2FuX2RiTXFHaVhjRG14aWwzZE55LVZ5OTEwQnBsellNcXFOTUpuVDl3WUZkMHZ6aWRWM21NN3hDbU05bWZJMXI1YVpQRUx1NWdHV1VLVHVS?oc=5</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2231,17 +2231,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Former Daily Mail editor tells hacking trial allegations are 'preposterous' - BBC</t>
+          <t>Something big is happening in AI — and most people will be blindsided - Fortune</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 19:30:14 GMT</t>
+          <t>Wed, 11 Feb 2026 14:22:00 GMT</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5Kelhub0J1VVQ3NHY4a3Uxb3RiS1piWVczSTZWeDBwMnNlMGIwQnRnQTJmdjl1OEZ4V2R3LThRdExnc0lGV2w5M3BGUVA1MzhNZTVLTTRZTC1uQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQUGFOV2RVWFhDV1drd2lpT2ZrZk1QXzI2emI3Y0pLTFhocDNFZEkwZGxadmx1VTd3N2pJX1lYNHZRQXVuWUZDM2V0dG9fLTlHc0dWSDhDajR6SFpxQTNJZ3dsZnAxUGZPWGdKVkNsVFRFTVZ1TmtKVnh4Rk95RG9aRjhCRHVpQkZNQ0hSUHFxeGRmbGVLNW16eW93?oc=5</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2261,17 +2261,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Broadcom Wi Fi 8 Launch Extends AI Networking Story Into Enterprises - Yahoo Finance UK</t>
+          <t>UK Supreme Court Issues Milestone Judgment for AI and Software Patentability - IPWatchdog.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 07:09:00 GMT</t>
+          <t>Wed, 11 Feb 2026 21:03:10 GMT</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE9fbUhucEo2a1Fqcl8wQmJiZDgzZWRwU2dtSWc1c3doVV81LUYtZm1PejlpZDA2RWRnQU5DbE02UWhWcHo1OGo2LURQY1VVeDVHRFpKTDR1S2I0TEVkc1RwZGlXTjlEU1dyZ3N6NzdiRTlsSktLcVVxZ1k0SW4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQaG9yNUtuNXZLZWNDTkhwQnJvMExyR0phUmZqZ1Y2Y0stSzdVUXB1T0ZiSHkzRnI5aXVYSktIcERrWERYU1d0Ui1FN0x1Q1hkTzBibjU0OThrYVJJMUNPUW5RcnZHMzNuV0JtV1MzU2hpelc4V2ZqN1V3Z0p3UXVac3RsdEJWOU9peGI3TndEd0JBUTZPZFpya04zNUJuWUMxVEQ0Vmdn?oc=5</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2291,17 +2291,17 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Hospitality Tech360 puts leadership, AI and people at the heart of hospitality tech - The Caterer</t>
+          <t>Five charts showing why AI is here to stay - Trustnet</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 14:21:04 GMT</t>
+          <t>Wed, 11 Feb 2026 15:05:58 GMT</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQVUJLWlFobVJVY1hZSHFobVJaZEZVNXEyUkh6RlpHX2l6emgzbGhHbF9kWmtGLW5QU0k5dm1UcEdyX2dqTXVoamU1TmlhU2tFWmJoZ3Q5aGd6VE1SNlRnZE1QT1JPVkpTVWFiMFNnWWtQQzU0SXRHNkR0LWdENUVjLUZ1VmZfQ1d5MXMtLXg3c3ZkSGJudHdNY3lPUUVmQzl1akgwZ2pBVlV2T1RRTGNnbTU5bzIzUFlX?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPZTZmOUJudEhHRXFEeWxiZ1ptSmpKRzBRR0FvendaMlNiWXhWRnVqZjg5bGlPQktaV05zbmRkVngyLTY1c2c1V1l5TFJRV25HdHM3bV9PYU1VMXlfTFJJQmFXZHJheDlpQno1MjhvWU16MTNNMXE3VUpKS3NvLU5GeGx5bDRWNldZ?oc=5</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2321,17 +2321,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AI and the future - Atlantic Council</t>
+          <t>NEUROssance And Universum Labs Establish Global Learning Consortium For Quantum and AI - The Quantum Insider</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 11:01:20 GMT</t>
+          <t>Wed, 11 Feb 2026 12:32:05 GMT</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQRzhpY0tmc21xVjAyVUJnVHB1MUQydmRNRGVpZUhsWDlkb3BqY3dzOC1PZTUxM0hiVjJmWGxJN2ZBVVU2LVI5aEJmMW1Zb0ZWQ194cmxnMlRFOU1wWndWRGVVTHVBa0dZckdhOVVYQUZmZUU5dlVodlpoenVRa0I2elVORk9aUVZoU0J1ZGJfemhwMnVNX25VeVZ3ZXRjMGhORGdqUnF5TQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOVWhSRERESHFnaUtQNV9jaEFhMGZJdEhNcExzQndscEM2a0t4TDdtb2ZhZ0RuRUl5M3BReWlmeU5WeGdiY2o4djc1S296YzI3ZnpTVDZVWFZJb0RoemZwSURqMElVOVNGZ0h0azNvcGVYcDZBVVNyLWhKX2NCUjRNemhkYU41YmpOVHpLS19QRmZLbFVhMkRYZEtGR21POUdnWXJ0cGcydVk3dGVUUUVqR3VTd2k0X2ZEalpSTVM5dEU5ajVHd2hZ?oc=5</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -2351,17 +2351,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Microsoft Confirms Saudi Arabia Datacenter Region Available for Customers to Run Cloud Workloads from Q4 2026 - Microsoft Source</t>
+          <t>Enterprise AI &amp; Analytics Insights | Strategy Blog - Strategy</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 17:35:19 GMT</t>
+          <t>Wed, 11 Feb 2026 19:11:02 GMT</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxNTTNSejlUVVk4aWRpRG5YNDJzRzhVbHhHNHJfVlNQNEphQ0J3RTJ5WHJwMngzWlRqS1RDdnFzdldkb1VTemhmUDV6d19FYXdocHFoODdUTTNiUDZBbS1nVUFiS2FHQi1TU09ocWVkNXdCLS1mYkl6d1YwMGoxSGNwbmFEUG9GSnN1am9sMVR4bFBKY2VzNVdvWmhlMl9xaDVwOHRacnBGV0NCaGFCS0hfUnFJblNBb1BpbTlVSERXbUxZem9OOUFQT1FENmN3UXhXTzRNbHoxQVFrT2VJdTRDMEQxaHVONGZmWGYxR2RR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE5XNmpjeUZhNHdwalJYaDR3bWRlTjM2ajM3MXVFN1Y3aTNCX1FhUjJaR3lvazQ4QXlITFBVTGx4bHVDMU51ZU40aHNsbEJpb0k?oc=5</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -2381,17 +2381,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Drive for AI and data to push tech spend over $6trillion - DecisionMarketing</t>
+          <t>AI partnership aims to 'futureproof' North East manufacturing business - The Northern Echo</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 11:30:00 GMT</t>
+          <t>Thu, 12 Feb 2026 05:00:00 GMT</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOSFNGcm5xUFVCMS12M1pUWG0zZmpxV2ZjZktGRm9WdFhhMnpnQVhoSzE3ZzJDOFktYkpaYVNPRWpKbjBwZEpGQWxCclZZTWtQQ0lVVWs1RXc5MWVQcnJkYjRXY2xGNUtrXzNnbHAyVjdHVXZ1Y1c0RmcxZGVSSHZBV0t6MDVScndqUGV5OFo4aTZDNnd4MEh1d0FpNF8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQZ0xBOVpiaUtVS1FRSkxwbkNPMmVCV3pwMzZkdDl5TmUycndUdUlzRVVpRkJHVWc1RG0xUTVBMGg5UXFBRFktdzdxUWdZcmd2UldCNkppRFFHaHM0QWdTTm4yanRUNHk0cl9WYndJangyclJZR3doSVF6a3FnUHBTRGt1UldXLUp2VEJZTng2U19CVGJHazUtYURNbHkweGs?oc=5</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -2411,17 +2411,17 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AI’s New Bottleneck: Power Supply, Not Chips – Asian Chemical Connections - ICIS</t>
+          <t>RegFi Episode 86: Agentic AI and the Future of Consumer Financial Guidance - orrick.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 05:37:57 GMT</t>
+          <t>Wed, 11 Feb 2026 19:39:06 GMT</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPMXFXbEVuWlBpNjh2dmJENkRPeTVpUVFVdVU5NW91WXJxaV9sQ1FYNXYyUXdlTHJ3WkxxajZpVWNrYWMwS2hmeEo4SnlDbUZpTGl3Skpyd1NNTHlLd2ZUQTNNVnV5ZHNYSkpUYmtEX05mRzhySTRRRFp6UVVuZ2V1YjV6RlFjck5IUWhjNHpjVW42UTlrcWZTLVhJdG9iNnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOZVdKU3NESUlhY29oLTBfZjZkUExRYnZZQ0JhdHE2STN3MFVfUGNVTUFldk9pS0JYSU9nUFdSRjE1dWl2NjMtQWlWUkgxUGJmaUFPQ1cwZEdQWk5CM010amtOVldhbHM5cGFLV2FNNm5jd0tGZXBXV1pCZUFjYzhTMEpIRzl6em9rSHpzY1k3Z3VPck01NGgzQ2dDTEo5ZVYzNEFicVh1Q3VZUUhK?oc=5</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>BBC set to launch AI Unpacked Week in March - BBC</t>
+          <t>Building an inclusive future with AI and education: IDWGIS 2026 - Anglo American</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 09:00:00 GMT</t>
+          <t>Wed, 11 Feb 2026 14:42:49 GMT</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTFBZVjlQN3g4Si02WTdkcEswUGxNOUFhd1Y1djNXMFh4N1QzdW1rVG1ZaHg3MlFaRFQycXFCMFpxaF8yd3pFMk9zTXhUcmJyUDlGRWpRNnJjemZJWTZyajNteTlCX3hBdjdDMV9NQnVDbjJCZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxORFFwWWRCYU1pS1l1OElDbEItdG1iQS1Hb1hnUVEyd0NwQmIzS254TmJqZ2VFaVhFSWxHaWl2Wkkyc3p3eTJSMzZLdDJWZVRxSWppOXIwWXdhMXpweTZwZjRHdmFrcElrVkZKYWpnYWFZb0VpWGlkcFFMZjM0T3J0aS12NnlYaFpZQVlkRGR4UzhVblEzZ1ZBSExtUHBGV0FranlLREV2MFQwRXpTbFVram5SMkl5QQ?oc=5</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -2471,17 +2471,17 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Cadence introduces ChipStack AI tool to automate chip design and verification - New Electronics</t>
+          <t>Create Music Group appoints Mitchell Shymansky as chief data &amp; technology officer - Music Week</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 22:55:09 GMT</t>
+          <t>Wed, 11 Feb 2026 15:18:00 GMT</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQdTRjV2plWTlqb3phX1V0cC1vZm1kWHROTWdWdW11X28tcE9JWUQ0UXNnTzhuU2E2dVlkRjZSaXhLTXRrQVEtZTJTOURaNXZHNG9rcXFLRmZzTURzNTFQcHdYNVV6WEFmM1ZfVDlrbmI3MThBb0tybzF6MUVEdkZoUEMxOXFLcmRNM04xVHpaeWZQeS1jMy1GdGFPUFNzdnF0R3k0LWJwWmV2bnI2bHEwbzBnV2xGTUJiQmUyRjQzWU8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNR0dCUUFHcGNBeEhzRDl6aDZXVVFyaXJQZjhHaldqVEJkQUZ6a2kwV01iSTRCZ01pX2FYd0FwdnBEZGFWM3lhRmtwY3JkT1ZNbUF6blRTTDlUV2d2cWhlMUt1Y0hMM1BxWm9ybjhWREtoTGJmOWxocTZCUXdWMVpYVXZ2aktsdlQxc2lsOFB0VjRRaU5WdkdCZjlTQVdKYkRBS1N1UjFUWUUtV1VQOXFvaGNldXJ6akRTX0wxSU8zY2lrQQ?oc=5</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -2501,17 +2501,17 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>GitLab pushes agentic AI to orchestrate software delivery - IT Brief UK</t>
+          <t>DSIT launches procurement for UK’s AI cloud compute capacity expansion - UKAuthority</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 23:05:00 GMT</t>
+          <t>Wed, 11 Feb 2026 17:15:47 GMT</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOTlA2QTdwVUdWcy1VNGxCMG9EZGJqM0tZVnJBbU1JRWpGX0RxeEFHZnd4VWpvS3Rob3NGNlNUM3pDaXhhcGtDVnV1S19XSndqNzB3NEoxVHM1YnNVdHNrYkpTLUJYS2FlQzZRZWd3TXVoc3lrYmUxTm9qd3ItTm9iVm5oaUZwTFJBRnBNNHZ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPUG9iMFkzOVNQeXg2VV9WMmZtZ0tJc0pFVk5DWXNGMjU4a0laSFFTTDdQM0d6ZF9MV2V4Xzc5aFpocFNMeV9KOV8yaDNyOGp6eTEtdkxZa3cyNWc2UnY0RVktYUtHVGM3bHk5VGo4MW5tZEotWVN5YWlCWG1mUURyMnY5RjkwLURwa2pub1ptVDNNUjlGa2cyckhDZEtzaFdTNjVxX1ZpQjkxZzQ?oc=5</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -2531,17 +2531,17 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>The Real Cost of the UK’s ‘Free AI Training for All’ is Democracy - Tech Policy Press</t>
+          <t>Chaucer and Armilla AI introduce Vanguard AI to streamline cyber, technology and AI liability protection - Reinsurance News</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 21:46:08 GMT</t>
+          <t>Wed, 11 Feb 2026 08:34:46 GMT</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNSV9sWF9hdE9uTjVQWEJMZllsZjhtS2JKTHhLaHNERXpVR0ZFQnVCVHQwUmVva0JUcDZrZGJlTWEzbW1ERUdPaEF1bHhTT3BTT3Q0X3laWWVOOWloUk9MaUx1OFBJdHFMeERXZGg5UTk0cG9nSHJONEJzV2JETFRaOFRCeTZnaGozSFFvUXpta1I?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxNb1A4NFNrZUg3SnhyYlAyb01xcmg2X0MwYVZmbXRvXzlLLWN4ZlZHS2tmZ2thZXFSbkVJVnBuMnBKTU1oQ21WdXFVUVF0aEU4SkVFX2owQUNHYkVuQzBzeWs1STdKdXE4aHR1UFNsX1V5MGhONGQ5QzNOX0F2M2xfbWZ0SzA1bFFfUzBQeEJibWhNTXJkRm5WWGRFR3Y0aDJEdFB6aVNDeHQ3a3JTbU9oX3FfS0pDZklxeXVlLWJrdzRPRzBWZDdfM0tyeGE5dw?oc=5</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -2561,17 +2561,17 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Exclusive-ByteDance developing AI chip, in manufacturing talks with Samsung, sources say - Yahoo Finance UK</t>
+          <t>Report: Knowledge maturity identified as key differentiator in AI success - Legal IT Insider</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 04:47:00 GMT</t>
+          <t>Wed, 11 Feb 2026 15:01:30 GMT</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOSm83V3o3YXRmRkduOXRCbkV4a3FHeWpPbnJhc25OekNHQ2ZmdWdqZ24xa2stVTVwei0yTVg1b0kzR244MWR4NG9jUTFMYjFMYkgwNWtDZ2x3V3YwRDNzYVZvSGtQZlBueUh5UFpESUd5eUFjR1FaQ1czVzBSQnNzRGlPc1NaUXJRNy12ZGtxVDM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPNWo5enotZjNqQjBQREVlMUZXTmo5eC16T2tLU2gyS0d1TFVsWWZTMExOT0hDWm1NYzBqX2x6RW9xTmFPOENsbzdlVWJ3MkJySE91VmpKXzZRX0ZzR0lEYmJraGl3SVZzYlZONnJsX2NSR3BnWTlxWnl6N3k0cUdtSmVnOXFlVE1seFNlMUtpSjR0WUhNZkp4X0g1WnlxNFMtbnoxX2RyZU1oWnBtLWF5T1Bn?oc=5</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -2591,17 +2591,17 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Disciplined Autonomy: How AI and sUAS Will Redefine Security, Safety, Emergency Response, and Military Operations - Small Wars Journal</t>
+          <t>I Loved My OpenClaw AI Agent—Until It Turned on Me - WIRED</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 06:05:12 GMT</t>
+          <t>Wed, 11 Feb 2026 19:00:00 GMT</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE1aVlpiQzZqRXpqNjNjRG0tekRpOE85ZlhzelNHVGFIcGw1aE5RSDJYRWZTWU5JUXhkTmpNeUFIX3FIWlAydWh6T1JlQzA5S0dEM0U5NV9WcVIyRFlKQ2xubW55U3BBVVdCNmVrWUNn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE8wRWx6c2otLXdyc1Q4YU96b3hRMDFoa1dNMnBSQ2JtSXRxTndrdThIeVg5S1pDMW13ekJOSmxVbWphWGxWMEFReXZCUl9yOGU4Q3RSUFY0Y19WRHpqQjVfbWJmek15aEo4WTJsdFJfLXA1Wjlm?oc=5</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>World Defense Show Day 3: Saudis eye AI, and a local defense giant transforms - Breaking Defense</t>
+          <t>PRIMARY-AI: outcomes-based standards to safeguard primary care in the AI era - Nature</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 20:07:25 GMT</t>
+          <t>Thu, 12 Feb 2026 00:05:13 GMT</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE1WQ0lTOW9fbVhrOFk2ZW1jdUZpU1VJM25MUEVlbDlTZ3hiXzAzd0tFWTZTYzVGWXRxT29fRnd4dGZma1FNZkpXSU1za1pnVmFibGsySmhzLXNYc0t0RnlCbEM1azcwaXlkZVJobXpxNXBpSjdN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE50V09wY1lTODF2R1VmWmg1eU5wdm95cEZtVERPWVJya0RsdmpRZVNLeE1BWklKd3ZDWUx3Y3NZYUR4NFBxeTBFYVhkZFJzYkJtTmZ5aGFDTklEV052d3k0?oc=5</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -2651,17 +2651,17 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>'Introduction to AI and ChatGPT' workshop in Haverfordwest - The Western Telegraph</t>
+          <t>AI Impact Summit 2026: AI Governance at the Edge of Democratic Backsliding - Center for the Study of Organized Hate (CSOH)</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 06:00:00 GMT</t>
+          <t>Thu, 12 Feb 2026 03:39:48 GMT</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPbHVBanRLX3dTQnNiM3M1SWRSM2tsSy1YRWhHbjdhV3Q3RDBwMHZGQ1ZJcmlTNWVRbnhqX0wzZXpuQ2dRMWZZcmNNNFN0a3k0TUJGTXJIRDF1VGgtSkx0ZERCOWtuWG5FQmxvNU9ubDFCUm55NVpWRDB0Uko3R2F0eVVoNks5czFNXzdRcU1qdkMya3Jtb3JEMW9kWGlIU0drV2xNdlVn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE80dnQ5bGdvc3VaRkpoZWtzVmxsQUU1YWtxR1hQRkdZQnV5MWdZMl9PWG5KUHBubmxHWGJuWVlzYlBxRXRQUEEydm5aN3VKTTFtVThRX0lfZnRzTzMyNTlqaWhRbndWQ2xB?oc=5</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Airlines' tentative approach to AI - PhocusWire</t>
+          <t>How AI can boost defenders , from defense in depth to the cyber kill chain (Q&amp;A) - Google Cloud</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 06:04:02 GMT</t>
+          <t>Wed, 11 Feb 2026 20:42:06 GMT</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE15Q0Q0VVZhY3hXMHcxSzR5REt2dEsycGY3X3d1R1VHRnBCOE1sNDlMRllJX05DYzFCQWZWYmFvRUs3Y0M1QlRqTGF6X0pNcWF0WFNfakUxTzlIZ3Mx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQdVR4VXM1cDFseXMxVVMtZ1dGQnhCZU1NbWFiMXNGTW9VaVh5ZXNwRXpET050TlZiRlFEN0N4dnpoMGlIbU0yZEJ4V19HZTJ0VVJQMzdLZ1pCQ0FaSUlxMWwwWnVmQjhfVnhNdUp3WEMwUk1ST0RySFBheFVnczZsaHZqcElUZmphSFBTYkVYbk8tN0I4bk9TSU1ZWV9XVU1TS3Z0WGdpbjlmZw?oc=5</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -2711,17 +2711,17 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Brandwatch and Blackbird.AI to deliver advanced IEAC to NATO - ADS Advance</t>
+          <t>New computing curriculum will teach AI awareness and digital literacy - Wired-Gov</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 15:46:00 GMT</t>
+          <t>Wed, 11 Feb 2026 12:04:50 GMT</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPVkFNd3ViOGV3QnRsZXJFbm1nNkJtQzNQVURwOUxMUlJxWGRCZFRmcmZxMERUOC01UU9OY29vMzJfQ1Ftal9obXRzVEVvV3gtSUhGYVpOS3NVd3IwRjUtU1NpbW9tWlpfRFpKX1MtcE9lMHNNMldNYmVCNFh4aWJEVXlnNDNIbXU5ZTNiLWRLcHpWR2U4NVhqLThn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNMENzV0tFb3NUYlFSMzhxcW13N3oxaDRvVGQ1NFZIblBubHFtYTZkcGZIN3lNNndEdUU5VE03Ymhnc1BmUm5RTVFSRjFMWU1YSl82Y2RPeFBDWmVRNmZmZmVYUDlWYXBsMG5PZFBHM2FnUzdoRU9lTkdjSXFNb0paYjF5Q3QyQ2dxVFJRWk9HWmZVMGt5YnFJMy1TT2pfbWV5clVfcGFkYkM3cXE1QXJVSXk2cGdMbHhsWHphSEpMVjh5S1NSSm8xcUtKQjJYYU5CRVE?oc=5</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -2741,17 +2741,17 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spotify eyes AI ‘derivatives’ as new revenue stream for artists – says its tech to let fans make remixes and covers is ready - Music Business Worldwide</t>
+          <t>OpenText (OTEX) Delivers Cloud Growth While Shedding Non-Core Assets - Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 20:17:54 GMT</t>
+          <t>Wed, 11 Feb 2026 17:20:16 GMT</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxNRWVIcGREN0dDODV5N2gwUGZlVGR0elIzLS15TWJuTkZ4VmxrcTE4eVNRNDhCVzh6XzAyaHFvOHRIWXlQUE1RQkZjOEtyU0xGU0s3azhIYnR6d1ctbXhMMnVZZFNodTFxU3RIcGRhOGVwRFpKN3JKQ1VnWVp5Q2FMWTMtZENnUVdwTTgyeEJNMENaaXFZWXp2d0cyb19SVDNudVA1OERmbGFLT3EteXR3QzJaOHNwMGxVR3BTdU44TTgxXzVMMUZyamFEUUdjd2Uxbks3dGZvaDVQeUpmY3hkYVJSRkt1Ymc1UTQtM2QxN0lNZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPTFdEbFBtQUxOakZINkV1bHhfLTEzemswQUFCc040LWxOVzBsWkQ3Snl5RU93SmZCWkZYTy1MeWh5ZXNjSmpWbXlsekl5MU42dmRSZnRiVEwyMmhGR1NkeGQwVEF3SGhuaWNiSjBJOC1pYkdVV08xZWh4blhDV0FnNzlLdjZTWllwcTY3bQ?oc=5</t>
         </is>
       </c>
       <c r="F78" t="n">
@@ -2771,17 +2771,17 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>How the use of AI and 'deepfakes' plays a role in the search for Nancy Guthrie - NPR</t>
+          <t>Moltbook, agentic AI, and data privacy, explained - Mashable</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 10:00:00 GMT</t>
+          <t>Wed, 11 Feb 2026 12:47:01 GMT</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTFBaVWdvUkFSRWF2V3VKalFvX0x2UDVvT2tVaU5qQ19ZVEFTRV9CQWtNSzdGWV9uZDdZWGhYLXY2NHNYdlJvM0FfN1pXSUNleWdpSE9XVGRSbWx3bDFpc3ZLOF9lUlhHQTJPY2ZtVVFkdEZUc3JSUFB6QW54TQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE9McEZwbzVYbDJTRVhWZVNjNm95UkVaNUVLMC1UM2paamlkVmgzbHhPcF9rN2dMbHhMX2FCYWZSWVVZRy1pRW9jQWtQSmhySnFXWWtKQVFkTVlhZHFG?oc=5</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -2791,27 +2791,27 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Experts urge Ofcom to probe AI’s role in fake news after major incidents - The Independent</t>
+          <t>How to spot fake concert tickets on social media as scam victims lose hundreds of pounds - The Mirror</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 00:01:00 GMT</t>
+          <t>Wed, 11 Feb 2026 09:55:00 GMT</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOdTlKQ0hmQzFqSEE1NU9fM1IwQi1GcHI2d3JtSkVCWGpmYXZXalJVeE44THVUeVlEc19md3FXblpVRnAyUG9neDNTQklLUkJURGliNVpvaUdXZFpYb0JOTHZySmpNNWRtZW5Nak02c2RSZ090Wld5UHdfWWxlWEV3Tl85enZPNXZub2ZVUmpsTlY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE5RVDFyOTVZdzZJTXR3RHhXNV9TSVdWMXkyUjhiSU95VHV5OTBMODdfU3FZRnhyWkswVzNweXBJcmwyYTJGcU04Mlh4Um9PWnZtWEJOeEFET1d1cng3dTA3NWxLMlV0ZDV6YnlGSEhXU1FRVVlSNDlDZtIBfkFVX3lxTE05QnA2ZVFleTJHbXJ2M0o1R3V3R0dnYVczdTRWSm43VF9RZmFadDhkX0ZqRzlBQ0pWMTFjX2ZmcXkzVnFFUURRZlNiUG0ybm0wX1dWVi1HTmVKYUpCVy16SHE0SThzaWxfUjRrUml4Qng2SFBSd1VMLVJOczI2dw?oc=5</t>
         </is>
       </c>
       <c r="F80" t="n">
@@ -2821,27 +2821,27 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Is AI getting smarter or just getting better at faking it? - Psychology Today</t>
+          <t>Canadians lost $43 million to spear phishing in 2025: Here’s how scammers use social media to target you - Inside Halton</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 10:58:25 GMT</t>
+          <t>Wed, 11 Feb 2026 20:30:00 GMT</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOMmZOQXhWQldBVXA4Tmg3OWgzekRseW43cmlZbFFuVUhCTXFnTkFDTGNEYlVyZWdtakZzUlRGUV9OUjN6ZzlCd0JmaW9GNTh4QUlEdXhUSFR4WndVdnZ2SmljZXVQX3ctdlVhc1dmWlpFeC1HLVh5bzgzR3RBcG9YZzJFMWZQSE9aSlFPWXJaamFfSW9WVm5aNW90M0V6ZHdlTHFQUktuaFVSSC050gGyAUFVX3lxTE1LcUZETWdkOW9FUEhIYi0wak1DY3Bncy1XTV9qZVBFejlER1I2MFVyRl9MNUhXUnhndmYxWnJBODFsWnhPZVhFNDFRcUpGVVNEeXVycW5MYVc5cmFDNG9leHZCRVR4SWI1ZHlCUjhQZ2ctUElpX1I4cjZJOEdCYjh4d19Xcmh5TGg1LWR0NE44a1ZxZWhQQS1zZEZ4dXIxeG4yZ3Z3blNHQ0FNWFprNFBhMkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQWUVpX3VudnBBYmUyR25fS3R1SGwtNFRZenh6MTNic3BYdi1kc1pxekp6c0JLSVF6Z01ZNllpVi1fZGRiSTdjVS1yWWtMTlVmRWZVLTRXNWNYWjExWFZscEoyUktpdk9uakxkVnpMNG0tMXdQbDExT2c5S0h2NFR5Yk9STFhCUVJRalF0ellod0F6bVJVT2NLWEotbURUOTZ3MDJPV3FvUnZSUXRCNnhxUTliZHc1OF94TDdRUWZBbw?oc=5</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -2851,600 +2851,30 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Empower launches embedded silicon capacitors for next-generation AI and HPC chips - New Electronics</t>
+          <t>The anatomy of a small-town scam: How glib talk, social media reels &amp; smalltown dreams fuelled a big scam in UP - The Indian Express</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Tue, 10 Feb 2026 22:44:07 GMT</t>
+          <t>Wed, 11 Feb 2026 15:46:00 GMT</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxOQ283d3MwOEE0eDFleTFIM082VVlCS2FWZFNLeExqS1NWNU9MY0FETnpEd2V6ZnAyRTNDSnlxSXVuYVRMbV9fZnp1Vmc3X1dfcTNJUVZ2R1czYnFNVVE2b25OZVpvb2VVdGk2VkZTT01MWnUyRUJUU2JmOS1lT1p0bGREV0pNRzdtVkpEZGtUVjBlaTl2SUZsMjBzeDJxQlFkbk0wNHJLa1JjemlHdnpuYVJ6c0V3c294MlRidTZZRjl3OXJ5OU9lLUw5NmN5RnV6UFVad3VR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPYnpYSDdLYmZ0Wno3aHc5QVJpWmF4Vzgzc2tJTzE5QmNERE96VWNBVXFPQUdNQWxaaWRsU0N5cDZMYVhsaUpCRDB1a2lrNDhaNTNIUUVKSHBCZlVmNkRqRGhZUkRVYUE0UFB0NTNROXFmLXZaVlRfV3hjbXZqbk9CQkM2LXlZUkN0UWZGd1JHczlsTERNRGU0REpQMWIyUkEyZGdiekNNbWdOdkhwakNsTUtFb0dqOVM5cUtyV1A0Nk1KemtxWjBtc0VmbFZ4c185VlhlV24zbjBDc3c5djF3Tzd30gHoAUFVX3lxTE1RUGJJeDBXajEtQ1VmX1ctcTdrZ1BXMzhTX0RDNGQwR0xRVUwxdTEyWklxRlNFTGppb1I5bWwwZWhwYzdTZWVSRkd0YWd1ZFZUNngzaVF1bXJlaHdEdjg2cnFPWk1QYS15ZWJRN2gyYUJ4TU9UbFN3TGxMMnB1anJaYWY4MDJxeGhGN0ZoZ1ExMEozcllUTm11bUhNX25pbV9yNzlteS0zNGlOYXdvNG84UUUwa0Rtc0FpaDBVbllIZDBaa0JOamdISV9HN1AyZ211RUdVelVKZDdxeHlJU1FlZHRKck9UMVU?oc=5</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>No, the human-robot singularity isn’t here. But we must take action to govern AI | Samuel Woolley - The Guardian</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Tue, 10 Feb 2026 16:17:00 GMT</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQeTlqM19rUXVLZHE4Y2RzNVVSUl8zRDBvN2lSWWlHZEJTNW1OQWR0dHp4bVBVZWVpaWpuOU8xemxSOVpZNTV4dXhsZUJKTTZvT282a1FGWlBRZHloNmdrWmtpblliSnpEald1VExmWDFfUUVLdl9ZWXg3M2pWSkxCTURTX3pZSUItdXlLZjJHQl8?oc=5</t>
-        </is>
-      </c>
-      <c r="F83" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>A Silent Arsenal: State Hacking and the Emerging Digital Order - ISPI - Istituto per gli Studi di Politica Internazionale</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Tue, 10 Feb 2026 10:08:38 GMT</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNZGc5ZFZSZUpBcnk1aEFMaTdvVmhoSklrUVlwY2tGUTU1ZU01UTI4X3BDQ05CSjlId3VmZnQwVk0weEhWNEZRUERsUndERTR1Rno0aFJEVFhEdHROZ0lvbnZDZ01oTkdZc1B0d0huMHpKd19oSHUyZC0xdmVXdDZoczJtUFJiTWpqbE1FUm9xQ0pxbWNEYTlzZmVHbHBUNnR4MXV2b0libmZ2TEd5UXc?oc=5</t>
-        </is>
-      </c>
-      <c r="F84" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>The Atlantic’s March Cover: Josh Tyrangiel on AI and the Future of Work—“What’s the Worst That Could Happen?” - The Atlantic</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Tue, 10 Feb 2026 13:24:16 GMT</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQa09QUGtfZUZPX3hOOWFkZzU0dkVXeDE1YmY3dGhmV0pMVmlxUnphM2FaajJodXJTOGZzYkstaFhteTg2VmZ6bjJsel82TmEtVUdkLU03dnRrOUJoYnlidW1xczI3eHpaVFRsaUtYTUZDOWV1N0I1ZXlYSHpvYXA2dW1vem50am5jaS10VW9BaWFFVTJmZ2lQeVh0aXhyS3RRbVhj?oc=5</t>
-        </is>
-      </c>
-      <c r="F85" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>AI changes forecasting — But governance still wins - Wolters Kluwer</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Wed, 11 Feb 2026 05:17:51 GMT</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNRnF1SVU0ZEZ3LWk2RVE5eWhteGI1X3lXRG5qb0dxSmVTY1lHSDhPaGNiY2lXeGEwSk5TZUR4cllmYkhSelY5cGpHMDhycTlvOEhJWmpRTkxDLVBDdHhzUGwyUHI5dWY1VlRjR0JLcGQtZVRfRFI5ZWJqczZKd1FLNFVfRkdrX2VtZnRBZTZmRHg2c3hjQUZIZ2ZxTjhQdw?oc=5</t>
-        </is>
-      </c>
-      <c r="F86" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>AI will boost games not break them, says ‘Clash of Clans’ maker - Financial Times</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Tue, 10 Feb 2026 10:00:06 GMT</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE9lWDk2MVhfY0JLM1ZwWkVhOHFrY1ZlS3J3RmxZNjBPRG45MS14SHE5eUxnNUs2TGpKNWxjNUF2X1Vha1hFZFFtSS1xY2t5UTh2b1prSHAzVEZsbGhxZUxaNXdqeXY1WlhfZ2d0bDYyeWI?oc=5</t>
-        </is>
-      </c>
-      <c r="F87" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Startup Stage: Altek AI wants to use AI to improve hotel guest communications - PhocusWire</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Wed, 11 Feb 2026 07:04:12 GMT</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE9NeHU4UzZmTTZaVGhua1FGcE1OaVY0YTJ3RDVEUE9oTGdtQk1JTlBMLWRkNW1pVWd0bEowbjA3LXpxY1NXRHJxc2RxNFQ3eUNhd1ROb05JaFpKLVU1MFE?oc=5</t>
-        </is>
-      </c>
-      <c r="F88" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Are video game developers using AI? Players want to know, but the rules are patchy - The Conversation</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Tue, 10 Feb 2026 23:19:16 GMT</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNY3RRVGdBMHJDRWlkRkk5NGlVbXk0SlFPZTNWVFVmSEZ5S0VRN3RzODhqT2FqdUxvS2RTcUxkcEcyVHFYYVczUFpvYlpPUVY2Rm4xckFZZnZOOWZBcUdlTmFobVlRODB2TE1nQVZILW9pRVNhZkVrdDJLSk9YaURkVms2RmhJX3B5LXJZTU4yb1hWYUtyVkxBQ1BsQlNmWnoxMFpPR3lwSk1GeWNQbmFhRzdkeXB5QQ?oc=5</t>
-        </is>
-      </c>
-      <c r="F89" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>University Seminars Explore AI, and Also the Medieval World - Dartmouth</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Tue, 10 Feb 2026 15:34:27 GMT</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPQ0JIaktHa2FDbFJuNTIxd1d6WXpQYkZsVkxaX1R3c0NwX2dERkwzaHJhdFd2R05MMGpmcEctNjNxVGNoWEx6Vk1YX0VDcXdxUkd0dXdIcnNmaGtYdlhrSTBwTVZJbDBvWmluQU5MOWNUd3ljWHAtWVV2ZndDY1VYeDNrVTZrcTZUQUZ2ek9xd29paVBheVFjWldR?oc=5</t>
-        </is>
-      </c>
-      <c r="F90" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Why the OpenClaw AI agent is a ‘privacy nightmare’ - Northeastern Global News</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Tue, 10 Feb 2026 20:18:26 GMT</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE1LVENWSG5FZElMZzNVUXplWFIzVmRwdU0xSnBvdFFiWEJfbXJHNDVzLWtXRkREZ1J3RHVwVkdkdDl0UDcyMk96OU5sNnI0Y2dNTTZlSWN0c2hIaFZRb3pBUl9wYnNIdHFHUE1URFBLaE02QQ?oc=5</t>
-        </is>
-      </c>
-      <c r="F91" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>'Just working towards her pension' - woman settles discrimination case - BBC</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Tue, 10 Feb 2026 15:28:20 GMT</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE96ZmdRbS1uS0tSMVVlZHhZX09Cang2QkNIZEJlaUlrNFBEZXVoM21DQ2VoLS1JVUFYUkxKM2J2cWJtSTBMa3I3V2pFZ0ZuTWMwME1QQkdOZ0d3QQ?oc=5</t>
-        </is>
-      </c>
-      <c r="F92" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Insider_Risk</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Ransomware hackers say NO to Data Exfiltration and YES to Encryption - Cybersecurity Insiders</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Wed, 11 Feb 2026 06:39:52 GMT</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOZWdaZ2E3Tng1VnBVN01EWnVweTNBQ3lpUk5EYXJvRWIyRWN6T2twWUM4dnZraEEzUW9OejdFN3hYLVczb05zYk9wU3ByaVZ6YU1mR2tuVDBiS3Q4YlR3RnVMVmozSUF5dWtzLXZJUmY2dG82STA1aV9YWUNEN3hrZW1DNkFDeTNTMkJBLThJOWt2b3NXcmhjNFhBcERFSVdYM0l1SVozSk0ySGlL?oc=5</t>
-        </is>
-      </c>
-      <c r="F93" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Insider_Risk</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>When Employee Misconduct Becomes Marketplace Deception: Court Clarifies Chapter 93A’s Reach - The National Law Review</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Tue, 10 Feb 2026 22:17:46 GMT</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPWFdfZWZYMFQ5RlQwdVZfR3h2Ty1JYlNqenR4ZS02ZVBsQlMySjJTb01zdzJaUFBKcFdVTTI5LXRjeGVrNVB6aTZyYnVuQkJBZGhJSFlDN205S3E2SjlLbHZNUEN3eFByVVR5TzEzRkxRQnVwWWI4dVFlS1ZOd2R2azhvZ2xrdW5IcE1ZUHI0NE03SjF0ZTU1dUdPMFNSRGp2VzhpVVMxcUdEWFUydTNKTXNKZVFmM2PSAbwBQVVfeXFMTWlLdDQ1TDY4RVA4MWMzTExqb3NmSG5sV1ZiMEx6YnJvengyRjI5V3NDb2taX0lrbFdvY0pBN1UzdDI5NVlFV0pSVi02M1BlMmNNLUxBaDNWYnlLT2ZETE4zRW9jWlFxWG1SZTdad2I3NFlvTHhPS3JqeVBzcDMwYWR5cldpblpLZGRXSEcyT0lOV180VWxEb18zeGtwZmktbDN5bFQ0MlJIcktma3RqeENad0N1R3hkQTNEX2g?oc=5</t>
-        </is>
-      </c>
-      <c r="F94" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Fraud_Scam</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Revealed: 95 billion scam adverts shown to Britons on social media last year - Yahoo Finance UK</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Tue, 10 Feb 2026 15:21:26 GMT</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQcFFPNXRBc3UydUZ4c1BqN1pPRVlaZWliNEV4amhiUEwzRlNYM0xac21GUkVjaV81b2ItWEw3VHlPdFZtM2RtbmI4eW5IVVRmZGNvaGNRMmdkRlhXeE9TYzc2aWJhLVoyVUZQSkxaZmRJNl95MWxoNHl5Ti1sWkZ6TVNQZ0ZsTkIy?oc=5</t>
-        </is>
-      </c>
-      <c r="F95" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Fraud_Scam</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Fact Check: Social media posts misstate UK costs of asylum, fraud and tax - Reuters</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Tue, 10 Feb 2026 16:09:18 GMT</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNU3pNSUUxZkhySnBMQ3c2YkFIRlU0dTdtZk1ZblVsUENJalM4a212czdVREVIYlhUMTFQNnpTVjJ3WUdMYWdqV0hjM0ZFV01KSUxwa2ZNODg5Mm1wZ1FZbVVNVHFlMng0REFuUEhWSUVtMTczZDdDSjJuWkxMbDZxTURsaXlXalNhVDNUbWFDNTdneExsWnVnYUQ1U0RSMW5SX2c?oc=5</t>
-        </is>
-      </c>
-      <c r="F96" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Fraud_Scam</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Don't fall for this scam on social media about a deceased Charlotte County deputy - Gulf Coast News and Weather</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Tue, 10 Feb 2026 23:04:00 GMT</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOMGlibF8zWHo0aFFZaTVkanVybG5MYm9uNHBJRjVnWDlBREh2X21Pb1B5d3c5T0FZRmVPQ0tvNTFzN1RTMTVtRmFvUWdaang3V3RFQ1ItRWxmZzVhVkF1U3pnV3FtVWdqcVJTQjhxOFY1YXpMYXpHcXVRTDRLWHpzcGJXenBHZENyR0NPMmd5Yms2ZEJpWDIybGRDR051c0R5QWlv?oc=5</t>
-        </is>
-      </c>
-      <c r="F97" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Fraud_Scam</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>New scam spotted that uses a calendar invite, deepfakes of CEOs, and a troubleshooting program to create backdoors and data miners - PC Gamer</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Tue, 10 Feb 2026 12:37:21 GMT</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirwJBVV95cUxNNFJYLXNNVU1lOTRNU3FqcGFidUw1Z0R5ZUtaenE4NEJaLWI0QzFkR3pQOGVSR2t4QzhOckRjWDh4a01jcFF0bXFib2xGejFVWlZkUHZPalVqbEpnQ2hGd25RUVBTVVk0WFItZ2hwQXV0MXpqRzFrMDAxNmR4MHRuUTBkdGpKQlg0Qlp2ZUpUUl81SURydjcxSXRwVjBmWGZrdk50d0JDeDlPaWZqYUhzTWFFZ3ItNUxfbEZaczJxS3NQdTBuMzBlQW5HUkRHdVVfZzBXYV9JNVE4LWplZzRVT0VoR2hwWXE1SV90TUE2MmxMbjVGSDFNNXhtTmZoYWtKQ0IzRUQ2Rlc3WENFNlBhekw0SXYzR3JJZHNWY0ttWVl6YWxwbXZjSTdYZHRJcUE?oc=5</t>
-        </is>
-      </c>
-      <c r="F98" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Fraud_Scam</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>The anatomy of a small-town scam: How glib talk, social media reels &amp; smalltown dreams fuelled a big scam in UP - The Indian Express</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Wed, 11 Feb 2026 02:39:14 GMT</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPYnpYSDdLYmZ0Wno3aHc5QVJpWmF4Vzgzc2tJTzE5QmNERE96VWNBVXFPQUdNQWxaaWRsU0N5cDZMYVhsaUpCRDB1a2lrNDhaNTNIUUVKSHBCZlVmNkRqRGhZUkRVYUE0UFB0NTNROXFmLXZaVlRfV3hjbXZqbk9CQkM2LXlZUkN0UWZGd1JHczlsTERNRGU0REpQMWIyUkEyZGdiekNNbWdOdkhwakNsTUtFb0dqOVM5cUtyV1A0Nk1KemtxWjBtc0VmbFZ4c185VlhlV24zbjBDc3c5djF3Tzd30gHoAUFVX3lxTE1RUGJJeDBXajEtQ1VmX1ctcTdrZ1BXMzhTX0RDNGQwR0xRVUwxdTEyWklxRlNFTGppb1I5bWwwZWhwYzdTZWVSRkd0YWd1ZFZUNngzaVF1bXJlaHdEdjg2cnFPWk1QYS15ZWJRN2gyYUJ4TU9UbFN3TGxMMnB1anJaYWY4MDJxeGhGN0ZoZ1ExMEozcllUTm11bUhNX25pbV9yNzlteS0zNGlOYXdvNG84UUUwa0Rtc0FpaDBVbllIZDBaa0JOamdISV9HN1AyZ211RUdVelVKZDdxeHlJU1FlZHRKck9UMVU?oc=5</t>
-        </is>
-      </c>
-      <c r="F99" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Fraud_Scam</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>As Minnesota cracks down on fraud, some lawful social service providers struggle to survive - Star Tribune</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>Tue, 10 Feb 2026 12:06:39 GMT</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE9wQUJFY1MxblY2bEN0aG10RVZ1S0RCekpBbTZ0RWIxTnVZY0xZbFdrYWVpZThvV2ZfYjkzVms4Vjg0Y2pkbE91X0ptLWs4NWFSTHhKbXB0VXpXeEMta28zLUNmd2NWUjcyS0RoMlFBdm11Q1FuUjlycGVRSQ?oc=5</t>
-        </is>
-      </c>
-      <c r="F100" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Fraud_Scam</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Hamirpur Judge Falls for Social Media Investment Scam, Loses ₹6 Lakh; Police Register FIR - The420.in</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Wed, 11 Feb 2026 05:34:33 GMT</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE5yQUF2ejV0dG1MOWF1SXoxeXA3bUh0bmJodmh2bVRwaUVMT2s5YVNNcnpQRENRWG1pemJNMHpxOFBfRzEzN2xESUJ0b0lMZXlBQ2RacDdPN3ZzMnVETVd2V0w0cXRSa2tCMUFhaUlfbWQ1Y1ZJ?oc=5</t>
-        </is>
-      </c>
-      <c r="F101" t="n">
         <v>1</v>
       </c>
     </row>

--- a/data/daily/topic_feeds_daily.xlsx
+++ b/data/daily/topic_feeds_daily.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:F98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,17 +461,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Update on the procurement for Digital Gilt Instrument (DIGIT) Pilot - GOV.UK</t>
+          <t>Scottish Government Spinouts report sets out integral role of universities in national research ecosystem - Universities Scotland</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 07:04:42 GMT</t>
+          <t>Thu, 12 Feb 2026 19:21:50 GMT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxONVJYV240Z0lDTHRISG1pM2tXMjdyWmtTSGFMdDFxRzBYNFBQa05BUkp4cmhZd1JJU2xDQTg0UVp6S3pjdzVsSFBlV3VaOGhORy1WaXhEeDE1MXAzZk9HZ25ablNxV0tqWlBwOHZPUkU0OVJZLW40RmFCOUZadlE3Q01XTXZmWldqdE9zXzh6REl6aElxaEJicXZGeVhHN1NvRWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE5FMHlsQ1NydER2N0hyZ1FSUjZqUVh3ZV8tSGlwX2tSbTdkaGxiMjFYVFlRTTdHQnctZUd0TXI2dnJYam5JYzlTNTREYmpmSzg2Uk5JaHBvVi1SWUlWbDg0elAtMHlLYjl0VGdRc2xTdHRvdHM?oc=5</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -491,17 +491,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Government and prosecutors respond to JCNSS report on Cash/Berry spy case - UK Parliament</t>
+          <t>The Government’s new approach to addressing the legacy of the past in Northern Ireland: NIAC publishes response to report - UK Parliament</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 00:17:40 GMT</t>
+          <t>Thu, 12 Feb 2026 14:20:53 GMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxPWU1rSTJsRWNiNHNmX2xWbzJ3NGpHXzNXQmtDVXFHenE2MUNhMmk4TUpvLWlHNE15Qm1kQXlNT0puaVR0bUtIckdlcGtLelFEelBuckRfaVpOcWUweXNpWnAtVllLblBuUEVNcmozWUFuVXIwQzVpN1FkdGwwdHU4b0s0bnNDV2QtakVLdWNKcmthaWlNRmtOME12RDdyeldEaFY0eGhFdjFxOUlvR29rTDgxQTdTQ2NoYkRVZnNkRjlhTEJESEhSLTlQaVQ0ZVBaUXZBaXBJclNhckRldHlmbGtwakMzekZkQ0pLRlBZaHFOVUJSZFJiVy12MnNLUVdmdkFVSk9n?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugJBVV95cUxQc0MtYzVyVlZESWtXdnZTM2R4ZENNcEIyYUN4OXJrQnh1RVhGZ3FMYzBIcGFnYk05a05RQlJGTEFHb2dPSFFTc3FIa3RTTFZRRmdPcVBPUmVvUXF2QUZlZUo0N1lFM2ZHT3VxZlRUZHJ5Wm5oSnVURzZ2MUNseDlRaGxkWTJudzRlV3h6X2NPeXg1WkdHRXNZV2Z1RE95UXBBdHV6SmtBbTRnaVhyZmhxLVIzWlZRQS1mWXdvN0ZQNVhGUjdFYVRZdGloa2VnRUZDb2pQR3RCYTcxZW1kNGZwNktGWWFTTW1ZUGNiUVVVNXJIWTRkYVNaMDZFZUdXQjNvdlVSa3lTOF94U1NXQklDNmlwam5wRk5xRWhmTFZpdUZmcGFkLUIwOXhmREVGSC1Uc3ltcWVNNXFXZw?oc=5</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -521,17 +521,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>From Rates to Ruin - Policy Exchange</t>
+          <t>Franchise market needs reform and accountability, warns new UK government report - Pinsent Masons</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 22:03:43 GMT</t>
+          <t>Thu, 12 Feb 2026 15:30:17 GMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE0yOHFzQ190bmtpdzFfX0xKV0J1bmxYUDRYWnE1Y1AtZ2NmdkNBaFZQY29ycXZ5MFpOMEs0ZlViNUVlNVNONUZKekVGSnB3TTdXckVkdVJvUl8yWEhHOEc3OE5zOGZrSmVvTUxYVG5n?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNbjl1bVlwNUUyQmxjX3hSdFVLbmJqbUs1SzRKWlJhblNyNmRIN1hlSEI4Ym11Skxma2NIQjlOYU9icjVyOWt5YlZWWGZSUVRfRV9EaFlxNnFUM000MTE1Q1pMYmlKd0F6SXZlcVVzb2wzc0VLSlFNb3FPTXVKWXdyTmw4X1RjaEVvZGtPdmtZc0V1UDRqbnc?oc=5</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -551,17 +551,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Firearms Legislation Update: Surrender of Prohibited Blank Fires - Equity</t>
+          <t>Grid upgrade could add £194bn to UK economy - Arup-led report - The Engineer</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 16:52:42 GMT</t>
+          <t>Fri, 13 Feb 2026 07:05:06 GMT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOdWROS3FNQk5RaWpVdDc2QlpRa0VpV254ZjlYMk9zZlRPMF9xWFJvRGFnRTRacmlsTHNRSEQwdGFWTHBqQnJfWm94Ti14d3lxa3QxMzFaSUdwbmdVQXQ1U2locUpsR1djMmttVk1HYnlrdDM5WmlNblNZSlFOYXQtclBuMTBTbmVEZnEwYmw5OXRJcmpxT3FQNk5SUlhTZ0RJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNQjFVVHpMdGJkZlAwSmM5eFZBNmYzTllXbEcwLUtOSjJTTHJ3a2tuQXpOWkQyZjZfUFNobENOZmU1aVJzNGdkSEp4OUdJOU16b2xjZWxrcTBtWmRoLTl3S3hpcUx5RHZSeVpHOTVybldSVFVBdXI1Zmotb0tBSjhOWmpRWktjWWxNMjI0WmZEdDF6VTFrbjBV?oc=5</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -581,17 +581,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>February Monthly Terrorism Update - Pool Reinsurance</t>
+          <t>"Strengthening Regional Policy Dialogue and Partnerships on Solutions" - Regional Socio-Economic Update, Bulletin Volume 2 - ReliefWeb</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 15:04:54 GMT</t>
+          <t>Thu, 12 Feb 2026 09:03:18 GMT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPd0J1ODBkbTQxVU5fNzZRMVA5OWRwRVV3ajNLQl9abkd1X1NlU0RMYUg4OHlmVFV3Y2ZuMmpCT19rUmU3TlhPV2NoaWpCVFJvU3hPZk92VEJTS0xpaU9odEhmc01SWi1OSXNSLTdGVUl3NVY3bFVJM2R5Uzd3M2F5TjM0ZWplbThRTW1xVlg3c3FDSHlKV3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxQazM0WDBKSWZicjdEY1Y3VlA1WUdiMEZncTRHRkd5LVFHVk9ya2VIOTZubDI1c1BFOHI0WGdxelI0bjhSanZXbm5BWWdoaEJEblRRcURYWkhCaEtSYkhBTElvdUFUNWFid19hQmJwUmxvUGFETlMyWWw2TjFLRm4waDluTkhzbzl3dlAzV29iSUY2N25Ia1czZXBoYTRIX1gyb2NYM05RX2Z4cG5hcEl4ZjdSc2tZOVlQaS1aTUZVTnA5VHJaUm1wTUpfUEttYnM0dFNKYWVUQmRqTmdfcm9IOUw4SlQ?oc=5</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -611,17 +611,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kyrgyzstan - Migration situation report (July - December 2025) [EN/KY] - ReliefWeb</t>
+          <t>The January CPI inflation report is due out Friday morning. Here's what it's expected to show - CNBC</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 01:33:32 GMT</t>
+          <t>Thu, 12 Feb 2026 19:55:30 GMT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOeHEzRFN0ZENUT1duN0U3Slc3cm1vSEJNSEdxeTdyU3gyMEl1YUtOWnVIMzZuaHpPeHMxWjFlelZYd1I0UzhLdnJBbTZFa1RwalBzd0plRW9MeHpnNnF1bkp2YXNHaGI4LWNoaVd2TEVXOGsyR0tCc1UwcVVRSTBuV1F6M0g2WXRJcWVfbTRPV1pFRmhEVnloVlE1U056UHlXUTVj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQdGdjVDluVHJZWmdtektHT2FicldYR1ota2w0N3NhcDJwTWpaX2ZSOHlCODBZbTF6VFZnOVVNY1JORjJIWlVRaGZOT1NXOGMwSkdTU19IaGJxWkUxWm5wam1rUmxnOUV3cEpyV3BRNGdFSTdDM2Y5Z19LOWxsNHd2bFpuMXdTLWRnWV9jLW1LaFk0Y0pTeWg5Zk80T2pUVkdqQ1NuWWlOTVNWd1o0ckRkUEE1MklkVDVnenZ5V2FCZk4tejJlN0HSAcsBQVVfeXFMTm9zU3ZLOE5PWDZUbDVpMDdFTC03RC1IckYtYTNRaUc3R1RDV3JucDdDLTk1Q0VqMEF1Z25pXzc3YkRWNkY3UG9GZVVsalEyQmFOb1E1TWgteDI5X09xbXdacWJ3Z2FsaHNOclhqVXlRWEItOUVQN3QxeGhreE8wcU1mUmxVUDVHSjc0U0c0dXgtZy1fZUNIYXp6Zk1NSDcwOUdCYmJKdEc2UV9JcG9LdU5qRl96V0FrYTU4RGVCQWQ1TVh5anNzbWlGcFk?oc=5</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -641,17 +641,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>UK economy ends 2025 ‘in the slow lane’ after growing just 0.1% in Q4 – business live - The Guardian</t>
+          <t>Government issues update after hundreds of thousands sign by-election petition - Manchester Evening News</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 06:32:00 GMT</t>
+          <t>Thu, 12 Feb 2026 19:55:00 GMT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQYkY3Mzh5Z3NoWExjOGhwa0Qydk1MTW9NeGFERHYtamVRS1U1LW5JSEJ2SkxsYTlTem5QWFY4V1BMT09hX2x3c2F4QWNXWnZEcmNFZU44NzlCaFd0Wk1DNWlxd1l5MFBWTXZSMEhzeU5oa0w2RWJFaHBIMlV2aHpsRXF3X3dRUmxwTF9TZ1B6a2Q1M0lCS2dIdTZRd0w5bmpaNmhuc2R2Wm5lMGJ2QlExODF3QlBZRHRaTkV2ZWhtdHJOS0JKRUFCWUZaS1ozUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOTHNqek4tTS1mLUcyOGI0czZpUGpRR0lWeEM4ZkJlSTJheEJhYW91alVPNjhoQXc4U09nUmlKVU5VSmJPWHdlOF9zYktIRkc1S2o3NXUxNTRXOS1paFJubVBVd1BxVGlKWlpsYmo1NkFtV1d3emZqYkY1NHd3SU1SVVhTWFhlRVFNbXZYTVhvc1NRTEFzZDNuai15aUd3Q05mVmJr0gGoAUFVX3lxTE1ERVZucmNPSkh3STJXZ3N4RjJzWU5KMUNGRXN4QVFhOWtDV3B3cUZ4eUtzQVE1d1N6U1ZybnRlVVZzaTEzTWJWdzRHZE52S2FVQU1jb0pBUW13bDA3NXc2R2xCd1d4UE5fVkVQOU5OYzdMakQxUzV0S1VNZ2o2NXB3Xy1LT18wWFk2TDdOUkdDQl9YZUNJREoyVTdtWDNkU1RrM0ZQaWdVag?oc=5</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Polesie/Verity report published - GOV.UK</t>
+          <t>Migration system needs reform to effectively sustain workforce and public services – report - The Irish Times</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 10:05:46 GMT</t>
+          <t>Thu, 12 Feb 2026 12:44:53 GMT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE5QMzdsb0VZcmNwaktacFZqYTZJZEZpVU9jM2N6dDhPcG5scWF3MzkyemE2NGR5VzRRemNTa1NiYzRSbEpSaXhIenVPZmwwaVNqNk9jb2ViY191aDJGekJrWlNKbHQ4cUVidlh3OGNHNlNfT00?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxNWWRlc2t0aWNkbUJNR0pzcGhCTW4zSzFkRV93UTAxRVZZc2Q4c0w0RTlsX0JBckN1ZGlKSXdySkRzb1BKanV2RXVIUkRkLWd5blhVQVNiYS1wM0FMcFdlYnRCUGk2Sk4zc3BnYUhNTHZ4NjRsY0JoMjh0T3FEczV2elo2X3B0X0cyVllOaGxQdUhXa3pVUjYwWnBrZE9aa0ZVTFl3ZVJJd0NScDhfenNZakxIalZ2ZWFIazlTQ3RQYnNCZ0pReFduMFpmWlpiTXhPSHc4dlpEa3dDZw?oc=5</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -701,17 +701,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jobs Report Live Updates: U.S. Hiring Starts the Year at a Strong Pace - The New York Times</t>
+          <t>Ranking Member Robert Garcia Releases Report on DOGE: “Breaking Government: How DOGE and Trump Cost Taxpayers, Federal Workers, and Public Services” - House Oversight Democrats (.gov)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 04:17:00 GMT</t>
+          <t>Thu, 12 Feb 2026 16:48:14 GMT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE4zU2VjSUs0WkZoeXFwcms2NkJaSkVBRkVTOXFMc2hydnMtZnRBcnJ3dnJIYUpBSGZyYVNnQXVpSkhfSkJjNDIwV0lJNXpPeEVCVWpwdmh6U0ViR21qbXZ3VVVva1FJcjlDbWNkSTJXRGt1RjliaFlV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgJBVV95cUxNTzB0R2JIMWtaN0x5cXVWRThTLW13OTRheDZoMXRRcVQtenRWWV9wb3A0ZG5EcVdvaHN3RUlyam83Y202R1NTR2pSbWVBN3NpRm4wZVNCZ3JnaF9WbXlWamUwNWdQU3pYY20tOUc2Unl3VHE5cjhBek5yWDRrQjhxeFJsNnVlRDdHamR3eXlfWlRIN2p0bmkzRTZRZk9sa0dNanpKTlhnV0lGV1BKSHhfUy1MQ0FwMHVGeGNHd29GaFpCczAtLWtfZTJUUS1vVktQNHZwSlR6emNIcHBoZzJzTXNQLUxtXzN5QnI5VnN1UlFhZk9aQVNPUHEtb2dNOHo4cEJEeTJOd1M2REgtaHpjaXJhRjJFSm0zaE02aGwyWDlfS0RQTkE?oc=5</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -731,17 +731,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ACAPS Briefing Note: Sudan - Conflict-induced displacement in North and South Kordofan (11 February 2026) - ReliefWeb</t>
+          <t>Solicitors Regulation Authority offer update on intervention into PM Law group - Yahoo News UK</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 14:03:08 GMT</t>
+          <t>Thu, 12 Feb 2026 13:00:00 GMT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPQ0lpaGkzZFpkcVRxOWhaUkdhaW1TNGdoWnJrRmRQOXN3Zy1oLVhpQThKeDZTYnJ0SV9jdmFXaHUwZVBXNi1PMjJOTTJfTGZQRGo3MEEtVWZKTDZMb29SaWlRdmxNQ0pzWmI1azh1RUxRc2JtX0oyam92QXR3SmkyYTZjRUt4U2NhQUhCWDg3YkxPUjU5R2Jnam5BSm5UXzUtMFhHSkRvV0cxYU9qbkJCRGNHSXc0ZHN4Rk9uRFhCaVpJUEgwQzVTZUwzUjc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNMl9yZ0piaVVvWE55eGFlWmk3ZVhDR1B2Nk1iZEFUbVpwdDJKeDI2YWFwc0VWaXpTRktFdUo3UjkxY19BdkwyT2lyczY2NUFHSFZTUjdKVEc2NXlqakJnUWxfRXREdGsySTVwUEg4MjduVURWTEUyNFZpY3ZJWDljTlctOWpvZkwxdmFURUNwY0Vka2JNR3c?oc=5</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -761,17 +761,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>KPMG report: Public consultation on Amount B under Pillar One - KPMG</t>
+          <t>Mikhail Mishustin’s meeting with deputies of the LDPR faction in the State Duma - Правительство России</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 10:00:14 GMT</t>
+          <t>Thu, 12 Feb 2026 17:52:41 GMT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNaTlYbUwyUFRnbmF2UXN2ak5qZE9yUWx0OFYzMGdCYWJuaExIdVI3Zk5GcFpxOWZVN2NMNGs4NkRwYTN1NDRwaUN5RWFITXlBZmp4clZYeE9IeGpEZFZxeWlrRy1aMk1ldDR1ZkdySlNMRFpERkZCTFM0SzVkUjdWRlhNNzVyRmdsOHlSbTJFMUpaNFlvUEVCd3BsamRobXB5cG5LcWFZT2x6Y0Q4dmpBWFJUWGlGZHNscHZJUnkyVHVUWDJ4WENRMll4a0tKX2dROElPaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiS0FVX3lxTE91d1B5Vm9ERkpBU2pFLWZDVDJOeDlYalFaZHNnTkVhZVk1MHNoR0N1eHRkLU5pcXVvX1oxOHB4bmFQcTNONTJ2ZE56MA?oc=5</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -781,27 +781,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US House of Representatives votes to overturn Donald Trump’s tariffs on Canada - Financial Times</t>
+          <t>Government issues update on plans to extend voting rights to 16-year-olds - Manchester Evening News</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 00:15:12 GMT</t>
+          <t>Thu, 12 Feb 2026 11:58:00 GMT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5acnFCcThjWl91alJsdkRjTE02ZThyazA1eVU5VC1nMmdkRnpES3VBRE02dmlabUZLN3VBQnZJdldPZV9oTFVaVjZmdTM2ZjRsMFRfaWFjNlJkaUE1b0JMWHpfeF9LWlgxWmlEbEQ5U0I?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNTnZpQWRueFZiSzhlekl0VmxYakRHTy1SaTFrcDlQZFJGdXFrWGFORW4zYTJ5bUNhSHp6NVF3VHRlQ0wtSUNqbzFFYXRERjA1NUotSkFrb3U1QWRycmJzdFR5N1lFdENPUktVbktQZVRpUmJlRm1uRTM5YjlSb2dmMTZVNGhnVGI3ak5FSzluQVFMVWM3SHhrYTNmaVVDZnFT0gGmAUFVX3lxTE5WYlEtbDV3NHpHQUVPM3VfS0hZWTZTSG9pYnFOQk5nTzVCWVpkaTBrbml3alk3amt2RVk5Z1pLWUU0ZkIyRnVDbDJpM1NiUjRiSVkzOWZ2SklNLXRVMTVBNW84OGZzdWl0MEtxelBXc1pkSzM0eGx2OEVra09YWlRZaFV6MV80dTVlS054V2FaTmVwVG9TbVkyYmI4R1hYSHItYzAwN3c?oc=5</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -811,27 +811,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>A year into Trump tariffs, Chinese factories and ports are buzzing with activity - CNBC</t>
+          <t>63 Poets Navigate Migration in "From Here To There", the Second Africa Migration Report Anthology - Brittle Paper</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 03:38:00 GMT</t>
+          <t>Thu, 12 Feb 2026 21:55:42 GMT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOd2xOeXFTLW9KWmMwY0lRQ0YyMUg0WTB0UXRLbTlTNlNHc3dhb1hza3dTUU5MQnNNQzhLcXNmUVh3eWVFbWtJMXdnZHpRUnI3ZGhUeEVFSmwtWG44dUpXUFlHRkhVc3JLbGF3OG9iRTFxakF5TkRNRDVRMUJIS1hlZGF3eHFJdWxzeHN4WWZ2N2xHa1RQNGoyWmJkZlRiNnA4amVyTlJUTVBsTmNP0gGyAUFVX3lxTE5CNy1tbEhIbVRteEU4SElDX2tXc1ZXYTdfYm1xR192UzVZelo4TzlnVDc1VlduZWluVElpOW5RYVpQeWtfV2JXWUFoWkM2NnFVN1dkQ0N6WXhYVUo3V0FRWkRSaEY0RC1zanJMNEdRYlh3cHd1MXlxSlBVMExSX3dZNzJuYUZXLUQ3M0Q3c1R4dUtiTWZGSV94SEVzalZlY0dCSndjRlZuaFI3MWhpQlh0X2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPbi1YMmZ1cmZvQXRfYlhud1ZuM3JfVUIzUW1TU1lpcy1YQkV1azAtSVU2NkpOeG1rd2drTU1fYjhiQXRmTVo3RVl4aG5YRWlFRk5kaU1YcWRzQWl3dnRDdkJHS1JNczN0QlJJZzA2d2g5d3dCeWFLYmVGc2RScG4xRDV5ZVkyd2VVOU90WGFBNDFfeE5tRUVlcno0SVVFSWJkSWRrNjdMbG5hN2dQM2poLTV0aXdROUg3YnV0dncydFpHOGpmZUVF?oc=5</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -841,27 +841,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Co-op Group extends logistics deal with haulier Buffaload - Co-operative News</t>
+          <t>2025 Idaho Policy Institute Annual Report - Boise State University</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 06:52:49 GMT</t>
+          <t>Thu, 12 Feb 2026 18:25:03 GMT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQVnU5RlFnLXhCemdwWkJJeXV1TUFyR29ILUJzenNhQnVaXzN4X1VEck9lcjRFd2lNNldpVWlLYkxCd1VSZXZzYVB1SFRVcmZlYTdlMlBCanJLbWlIZEZkMm03WnpSTHFuM2JUTHFaaDFnbXZCNl9LX1gzLVk5VzB1WDZpTEFoLVhadU40?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPVTJTcy1oLTlneE9hZVBkT0dYQkZLTzdZQVBPeVducmtDZ0dIcTRVbjRKVmRVcUdjNUVocmRTbTQ1VGNLZHdCNUloODZMMTl1Mlh2SndjYlE2a000clB3T2JLRWFvUWNkT2hTSkxJZ3pENEVubzdUcGxBeG5QSE9Qbk1wcw?oc=5</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -881,17 +881,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Effect of geopolitics on shipping poised to escalate, so ‘buckle up’ - Lloyd's List</t>
+          <t>Trump plans to roll back tariffs on metal and aluminium goods - Financial Times</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 00:11:44 GMT</t>
+          <t>Fri, 13 Feb 2026 05:00:54 GMT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNVlpSb0ZjdW1ZNEpOOE5NbV9HeklPWVFCT0dvLVBxTzJRZkI2SzBBRnVmME5LTFl3UTFuYmtNd0xKaElrWU9tRllKYWpiTnhFbzVCNmlXQVduZVBsUkQxWFd3eTBYb1B3MDF4N1dqeXhwLUlhVHJRQmpBQWNodUExeW5DMGhIU081bFR1bk5zZkpFb3hJaklPZ1oxWGRFMl96QzAwTw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBxemx4UjlSMGRnb3p3UVV6T2FiT0I4RDk2MEF0UlQ5TDl3Nm45cnIwMXN1WTlPQ2gzWnRxdnhOb2pkZUo3ZkRhYzJuZ1lKLTRiT2U2UWxSOXZ3SnNiY0ZSYVdOQTlYblZEV3BKcjU0YXI?oc=5</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -911,17 +911,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Vestas back buying again with €120m Polish logistics deal - Green Street News</t>
+          <t>Who Is Paying for the 2025 U.S. Tariffs? - Liberty Street Economics</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 07:45:16 GMT</t>
+          <t>Thu, 12 Feb 2026 22:19:08 GMT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNejhQakVnV2ZtVUZ5Q0NxdG1Ia1FsTkJhMFRVUlFyTkZ5dUtHeG9DZHJMYk9Gbk95ZkF6ZnY2NW9hVk1GamNMbEkzTmwtdjRkdzd2X01BR2F5YXUzeXRZSUlHQmhhbXFuRWk3WDJXaWY0RGNJeWVUVVNJQWprSlFXS01TOXZ6eVRwdnhXREY4ZFhndGFCMXZTcGZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOeFdvMVVjZC1HY3p3ZDNOVm5EZEFQNmNRUDU0OTVSVkVlNXlJN1VMY2xVRk5teHpST25CR1Z4bm9TaDlPaDdDYzE2a09FTVpyWjM1LUZJaG0yN0pHcGNhSnM3eTFqTTdWSC0zenVTekdHaEpZVGxqa2JkZ3l6WVRlR3JVOGNfeGdSR1huOWRMTGh4cXMyWklxdA?oc=5</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>McGregor issued compliance notice over stout posts - Belfast Telegraph</t>
+          <t>Costs from Trump's tariffs paid mainly by US firms and consumers, NY Fed says - BBC</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 06:47:21 GMT</t>
+          <t>Fri, 13 Feb 2026 01:07:59 GMT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQeHkzeDVqM3psZkxzeEJXSHMzbVBhMUlRbmotamhaSFFpbzZEcVplZmZ2Rkc5TWE3SENUS1I4bk5ydUlYeXc2a192azhqWklCbWpEeWUxU0JWV0pCZjRJR0s0NXZhcWw5cl9DaEJHRzk5empnakhTMDBXYThsTHhpUnRobmR2bnBld1h6YmpyTEt3eXJWbjRBZDdxLXJ2SUdhSzMwRk5xLWRRNjJPczNyV01UaXMyUE41alVDY19qZHVUWUtCMmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFB6WnR1Mi1xLWo1Qy0wa3kyX0JZejk0TnFybjR3bWVfbXpSNzZnNnZZbTRiT3Jwc3BGblVWaFUtOXQ2cGpaT1NjRlJhRGQ3ZE1XS1hkWXdpcUk3dw?oc=5</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -971,17 +971,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sanctions, Ship Seizures and Low Prices Squeeze Russia’s Oil Industry - WSJ - The Wall Street Journal</t>
+          <t>US and Taiwan sign ‘pivotal’ deal to cut tariffs - Al Jazeera</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 04:00:00 GMT</t>
+          <t>Fri, 13 Feb 2026 02:44:04 GMT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwNBVV95cUxQakJKaFNDTzB4M2c0V05RUV9KYnBnczN6SjNoTG1FMGZ1N2ZlcmVwQ3l0R3I4RkdjYVRUWWkzWkY5VndDcXNZUmI4bjZFU3hGZHNPaGxncDcyajV1R25nbF9BMVkwbEZveWNlQ2R1dVRfenVJVTB1NGQwd3A3ZlF2UVdjbGNZSTJNdy1XcXVKRS0wb29TMHR3cHZQYjlDT0FxRTdBcGozRVktWDJJSWwyVU1UcS1tVktIS2t6Yi1rbEU3ZkpuV1BZVnJvb2pPdEZzTm1wd2tMRUE1LUNtXzhsb0NuN0RGRTc4TUFEbkZ1alk5WDZtNnpFM3JFdUo2ZzU0MHpzUXluUVJNdGI4SVpiNEl2RUx2SUpKaFoxTjc4RjY1REctSUFINm82Wkp0ZThMaGM0ajlDRF9Wb2VqczYwcm84d08wVVZWVE9hUXJhVFQ1eEpVaDhVTjdmNTlIV0tQYWkzNmNLbG1PcWJQS3RlbC0yRzBIYUdNcHpjcUo4eHFod3VSM3RBWHlfaXlEZHlSTkRUSXJVNTZyTFZ3T3ZzakxKQ005clhxLU5ZOFVUUTl6ZjV1ZE43a0Q1UVRZZ2pCZjl2X1YyOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQUmRqRE5VYzRkcFdWSVBFWUlhai01Tm5wUWozdXJFMzFlSnNFRHBjOXM5TlVaNElicFM4a3ZlR2s3ZXk2MFBvT3lRSm5jWnQ1TkJmbjVTa1QycDdhUjlPeG0zNW9HZzlTZzFrdHhESHVtb2Z4cl9iX3JNb2dHVXlzeHJZajBQcWRXS3NzUXlwSlExclpESXBZV1N1Sm3SAaIBQVVfeXFMTjJDdDU2SEZVSmFOOEphQkdDeVBwbF9hWXNXdENTWWRIT0lScnRxNUE1MUJPZFlkZjZlZC1wLS1XZ1pRZzlNWW9sREhlZ2E2OHdXQldPTWxNUG9CRldrcTQ2VWZFdzk5eFhOMERLSVpxOUUxMjlLVGw4YXRyNWhNYU42R2VPamRtaHVDZldQV1dzQ3FlX3dDSkZfRkpITW9jREV3?oc=5</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Powerful cyclone kills at least 31 as it tears through Madagascar port - BBC</t>
+          <t>Future of Freight – European Executive Brief - Deloitte</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 18:48:49 GMT</t>
+          <t>Fri, 13 Feb 2026 03:04:24 GMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBjNnhjWXRJZVNaQmlTbW5IeEpmNXpXRzlJbFRBaGxPd0VqRTU2ZmRtNjlPMXdIUUh4YkktdlE2Q2lRTERIdl9HSV9mdlFnb2J0RFQwdXVRUlFDdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQUWVnMXBLdW5tX0JET0kyXzRaQWU0M29yLWx2SC1WNTFVbVliODJKNGlFX1lIbW9NWU9hUUNkVGhmMTlKUVBrWkxITVloN0dCbENnSGVoQl9TTkgxSnBNVnpOcU5LU2lHTHJpV0d0REFyc004VnBJdXlpcnlEaUVpN0VyRTJTdTc3RzBWUkt1Z0dqOXBRaG1UTHF4elNyTV84Ti0zMzlmSDFza242NHVvcV9XRUl3T29Z?oc=5</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1031,17 +1031,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>The Real Cost of Waiting: The Hidden Toll of Outdated Mobile Compliance - FinTech Weekly</t>
+          <t>EBRD to exit Giurgiulesti International Free Port (GIFP) - EBRD</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 07:09:00 GMT</t>
+          <t>Thu, 12 Feb 2026 12:40:42 GMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPNVNXaVVhS1ByMFZEMlE3Y3FmVVAtU2dJdTZEZW9wRDhmRmtHRHkzOUZuM3BKaDZ4ZlEzWEZKbHNOX1pvcE1GeWxHT3VaMUhFaUQ4UnppaDNZVVpjRjBpVFp1ZktNUTNJWlh5SVliN3VZS28yUjQ2ZUNYbTNnYWlKT1c4ZW5jQUc4M09kUGVVNnd4U2dSQXFoa05pckJMdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNSjVsbFJ5Rm1SOWI0R2lpaWpnVEZxOU5aR0pEdmwtbWxCb012SjNpTkItcXAteklqd1RQOF9BWkxLN04zTmtzSkxoLXFuczdnQU40aDlna2ZyWm9ZUGJpX0JOUG1OYlBQRmx0aFo4WmtsNGh5VjdkRS04Y1R5eEl2RlE3b19McnVYZnJwWldYRWZtX0d0eUQyRl9MSlNpeHRQUVF0c29odDhpdlNUdEd4UThWbw?oc=5</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1061,17 +1061,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Europe’s CBAM raises supply chain carbon risks for South Korean technology industries - Institute for Energy Economics and Financial Analysis (IEEFA)</t>
+          <t>Northern Ireland exports to US slump as Donald Trump’s tariffs begin to kick in - The Irish News</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 02:07:49 GMT</t>
+          <t>Fri, 13 Feb 2026 06:00:01 GMT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOOHM1aTAyYWx4RU9mMXFTQTM2eUkxUlVLSUFuaG03NUFIcG54cGQ1dEh0ckJCZm9OVjRCQkZHcWZIYkNOV21BNktMenlwcGhyR1lIUmNmUUFHV0l3SHZUNGFzRGJVTTBFMGZMR2YyT000cjNwcHBDVkJvVDF5UTVabElmaW1qeG05Ymd4NXROdGRkWFU5T3hHQTFsaFZOUm01VWdwdF9rb1J6cV9l?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPQlI5N1ZhT0pxQ3JnZnl3MFB2YXBlWlVFY1M0UW1yUGM4OWpOaTlkOWdEb1U5a1VqSDFmd2xJajJYdlVPVEZiNm1DQVFGYVRCa0hSdlZqTUNNeElBUzhHYU53MGZvMVZrMHVEVTNKenhZOHdQbTU1eUVYekNIZktlZDBON3ZaR3d5alRHOHY2aFdGRmp0QVMzRnpIYmZKQV8xSk5ONVhCbWlHU1hwVGh6V216TjlmNXdHVThpQ2owRnF6aTFxTmZuVkdPUWhFMEJkSGh5Ukh2aEdteldQTzZYbw?oc=5</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>The Current Immigration Reality for Academic Institutions: Compliance, Cost, and Continuity - Mayer Brown</t>
+          <t>Agri co-op giant CHS completes upgrade to deep water port - Co-operative News</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 06:05:29 GMT</t>
+          <t>Fri, 13 Feb 2026 07:02:53 GMT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxNc0tOYnZYdFZlLTJpY2xsdDhoVHliRGdMTGloNGZWbzhuOU9zM0xBRXg1TkdCelV3OUw2RUROYWJBa2xNZWtvTlQyNE5IcktVUUlKcFIwbjk1SU5BMkVaMzFuYTFhRzFQNFBoUjdIa2YtSlpoNlhGaXBLNDlwakFSLU5pLUxORGxYVVVEWnVVZmdxdnlvYU5rdHBTM2l4V0J6V0RyRGl4c3FKMFRCd1hsUHNKX0NVZXY2dTBCVmpRZXRIeGdZekpDNTdndHl0aDJ3a2psQWhKYjhQQURKdnRvREJB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOTnFnbHViQzkzTmRMbm15RHMyVkJncDA0ZjFZeU8wb19DSV9FYUt0VTRpQ3p1aUU5U2FEaFdpSW5QNGdPaG1yOU5Dc1FrVTY0bDE2WVJqS2NIT1RJVUFJSFRsTzlKUVhnS0lHQU5jcnJvOVI5ZUlsRGVVVW0zS1ZYYU5uSk44dm81aGlv?oc=5</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1121,17 +1121,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ABP submit plans submitted to demolish port building on West Quay Road - Daily Echo</t>
+          <t>The LR supply wave: can freight stay on its feet? - Vortexa</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 03:30:00 GMT</t>
+          <t>Thu, 12 Feb 2026 16:00:00 GMT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPRG5lUEJsQ0duTDVXWGNJMkgtMUMtTGlrSjJORDJYM3ZjTUNtT0tqX2lDRDl5ZHRJUDRPcVQ5b0N1elI3eVhKLXQxTXV1R201dzBEcDlMRTcyY01MdVFVVHNhSTYxTmtlR3REeE5qeWQ3dGdiVzNmX0NjNS00S3BBYVZ2X05JNjNBY0ZTdTFaOUJoNHdZV0tJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE8yRGNxeVJYRG5FVEY4NFhPMzBjR01YQlB5NjY2anA4QVdGTXcxN1BsNVlvLW1hQ0ZJVnlQTGFYQnA0OC1nanR4TDdJMFZiSnBlRDNFU29nNkZOeDQ?oc=5</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Port Glasgow man held 'large piece of pipe' behind his back during neighbourhood row - Greenock Telegraph</t>
+          <t>ECJ joint VAT liability ruling in Bulgarian supplier case - Global VAT Compliance</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 06:30:00 GMT</t>
+          <t>Fri, 13 Feb 2026 07:02:28 GMT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOMXlmR1ZRNlhQSmVmTk51VkhFVVFLTWVvYk11NjUzbmM2SzdoUDZPQlJNNkJvaGdUaXFLdzhkdkFfelhJcm5XdWhwVDZnb1FNNmh0SDJJLWVCTUh1ZFVjV3IyOFgxNFNORVZfTFg5bjZydk0xZ1Fzbk9YN2QxSHZUU2syb1E4OWhmRkk5Z2R2azRIOUlub3l6NzcxSWs4a3ZHMnVN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxPSFdDVGdPZjlMcHJZeXU0OFE0aXBTTWh4TldRNFd6bHktSENHMmlvMFczQkJhbzNpYnNrUVFjX1p1WEJkVkg2UnJBZnZsbzRyMDJBd3dvUXozZGdBN25SZW1qOG9VX1J0cUtHSU1lNlpZVmR0MThGRHVmZ25UR19tTy1BVWxHVk5nLWxV?oc=5</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Nation-State Actors Exploit Notepad++ Supply Chain - Unit 42</t>
+          <t>Scotch whisky exports to the US drop 15% after Trump’s tariffs - Financial Times</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 23:04:23 GMT</t>
+          <t>Thu, 12 Feb 2026 16:24:41 GMT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTFBGY0Z4dVpmMG9PbG80ZFZMSEFodDZXRnBmYUtBdnV0NkxFdmdoSDZIY0ktc25lVTdDUkVOY1piLWF1UzVVcmpYakhWVjh1ZldNUXFuSWZ1aXp1T25WaFpLc0dSWkhwY0tyc0szaERQUE9IMjZfSlFNY253?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1IMk1LVEcwME15MjJ3aXRMVktIM2daTFlFaDFIVlZuOTdYOUVJdFlHU0p6cUhsSkM5T3JMRkx4U0piS1ZYdmVRUTJOOFpnS2c0YXF5Z3FCTHBsbWgyR3ZiQ3J5VXdkalhOanhBOVA5Ylg?oc=5</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1211,17 +1211,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Compliance Becomes the New Gatekeeper for Space Startups - news.satnews.com</t>
+          <t>Port city in ruins as storm rips through Madagascar and on towards Mozambique - BBC</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 02:27:48 GMT</t>
+          <t>Thu, 12 Feb 2026 14:01:04 GMT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQNk1KdWxkMHN4MDVKRkV5NGU4d1BBdGVKV1lPbXZCWmxXQUYzTkNqeEs4QUV0ajRaLTBQMW5ONk9UZGhOdlU4MGppZ1ZnRV85RmJ6aHRyazZLaWZ0b1o1eU9CZm8xSUNVbHJvNmRQZUxKa1RxcDctZk95TEFiNlNtRVMtUkVJbUplanYwYlBPVTVfeW9XV3d5Qg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBjNnhjWXRJZVNaQmlTbW5IeEpmNXpXRzlJbFRBaGxPd0VqRTU2ZmRtNjlPMXdIUUh4YkktdlE2Q2lRTERIdl9HSV9mdlFnb2J0RFQwdXVRUlFDdw?oc=5</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1241,17 +1241,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>'Nowhere near good enough' - Brady on Trophy exit - BBC</t>
+          <t>Global shipping industry sticks with green investments, despite carbon price delay - Reuters</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 14:37:36 GMT</t>
+          <t>Thu, 12 Feb 2026 11:26:08 GMT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE5iNUdlanVyTWFDWlhwN2xyUV80UHhHLThoVFVvZE1sQzR0YnB1SHJIQzQxX2tOMnRyR1BGaHZhMFRCUGtXenppc0hOR05SeFpBS3k0RFdnLUc4cVhrTkZfbHRhVnREcTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPM0tXc19DLVBDM2FsVlVOd2JaU09VU1plODY0amRlV0JfWFNhc1Vac29aZ0JfQXdsRXJTYVQyWllCcmJWLVlSUU1POVg4Z0t0U1BoUE81d0xEaHB4SHlORERRbHhVMmxDV1M0d2o5SUc3azc3LUl0bjJTYV9ZdWJ1OFZJaU4xZlhGbHc5M2xkMFBNcUhTSXVWeXhKZ0ljeDUwYS0tZl9ubF85ckF6LWpfalhab3hPNW50b1ZfVUdmTk02QXpOMnhsUVRWM1BUcFU0Q1JWVEhfVTE?oc=5</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Thousands of foreign cars sold to Russia through China, circumventing sanctions - The Japan Times</t>
+          <t>Project finance veterans target new shipping deals with investment company - Tradewinds News</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 06:35:00 GMT</t>
+          <t>Fri, 13 Feb 2026 07:18:51 GMT</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOZ2FQc3cwT0F3NkFqZGZYTUJraEJpNmFta2hqc09mbTJKVEZQNTRjYWpid0F4U2M4NmlvbGU5RVJ2V3Zfd2hiSTRJWVBjZkxaWENhNU5ESkdPWm5xWG42QjZ1N1Z6X0dTX3RCX2lCYzY5RW00VE5PVml5NW9MSzlpUWNIckMzZGNWaXg2TWdab2JDRHFULUtWaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQajhOZm5aekdXMjE4b0duclB6TXMyNVdWQ1pER19EM01UeWY2SkxzcmR1ZTc3aDNaVE9SVWM5YlFXNEE2d0Y5LTg2RndkLXo3WEUtdHVQbWdnS2VZMzdhMllTOHYyb193Ti1OaDZQZmhnQXZJRkg5aDVFTVVtZFdReGY5MmVoTXdsVkJBQUZmblNNZTl0aGhpRndqZExzem1RRGQ1bVRWZ0IwTm5ER0UtU0MxNUhwRC1QNTF5ZWlmc195TW8?oc=5</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Boeing sees significant supply chain quality gains - Reuters</t>
+          <t>US and North Macedonia reach framework deal on tariffs, LNG purchases - eKathimerini.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 00:35:00 GMT</t>
+          <t>Fri, 13 Feb 2026 06:37:45 GMT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOVmR0UFhBUkRRVHA4czc0eF9KLUN4bmZqR2JpcG1VTVZlMnRKWHZQQmgxRFpVTVN4MXpsSEd4aWNKd1FXZDNqbHRkbGFseVhKOVlreW9RNHpUc1RUOWI5R2FWN3hmaFJGdW1RM0xQdENSQ1hGM05ZdkxsbUF4aWp4UHdheDh5RU9NS3FseVpqUFJSbmpXbVMxSnVFVVoyTWRkMHRiMGRvWlZocmJhWXdTUFFQZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOZmFrOG01U29xdURvaXRQNFIzdWJYbGRlbkdHblZhdThEaFRWenQzZ1VlM1pOR2Q4T1J0akpITUR1MlBWOW14UE9TNHZNNkJ2a0FFbGRyNkFlTm4yQzFTMm5qUFl3bWwxMXc1OWxWVGJkTWxFLUpfdjczZmo0N2RDeXlOYUZNMzNJdnI2R2FBdUxvQWQwN2dtUHRYZmx0czFReGljVE54aE5qRDZiQVZZeDRHOXA?oc=5</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1331,17 +1331,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Shanghai Releases Draft Plan to Become Leading Int’l Shipping Center in Five Years - Yicai Global</t>
+          <t>One killed, six hurt in Russian air attack on port in Ukraine's Odessa region: official - TRT World</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 06:44:47 GMT</t>
+          <t>Fri, 13 Feb 2026 07:31:18 GMT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQNGVuMGY2QmFNSDVCdDdjTk1Sd3FyS1RJcExETHMxcmdYZjZFTVNmTWt6d2tsLVk5ekI1N1RkXzVYcl9hNmVtYV84ZVpVd29IX0hjdlhlR1pCelNHWkFFX3FLVkpEbDM0QXRicVNsa3RSRVVPR1BybHp0bTNQUDMxS2pWZVJOQThwZEhwYTE3TFBHRE5pajVTT3NrRUJoSHVxR1NpOXdaNU9jb3lINDRkazNXOFY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFB1aGp4bWxfZGRPUHRtSjhKNGVtQ1Y3UTlVdVIzXzh0R0ZJRWx1VUd2c2FTRzc4RkJ0TmJHMkY3V1hLdk41R0ZqaFFyWDhOdl8zUG04eG9YZnXSAV5BVV95cUxOSU9rOG1CeUptSlZfSUpQQTNoN3h2WjlFcktMZFlFNmdfcjUzaWczR1RYNTJsOWFkMkwzTnMtNlpFX1JKXzVIWGt0RVljeG5qZzd0U3YyQktvZGpCNmd3?oc=5</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>EU tariffs on imports of China-made EVs - Reuters</t>
+          <t>Taiwanese owner Simosa Shipping exits LR2s in $86m sale to Greek buyers - Tradewinds News</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 11:50:45 GMT</t>
+          <t>Fri, 13 Feb 2026 01:42:40 GMT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQczBmbGEtS0tDaGMyNWd1cHA0S3FWRVV6S2h4U3lvMVkwUEtDQmoxQURxeHU4OWJyelBxVnlOaUJSNkRrQlc1RDcwUmVGVkNMS3RiOHNBZXdseFpOb09hX0dudk9KcE9qV3R2NE84Zm9PODBhZWtFUjg0VUtxeTdhT0hZdjBPNi1D?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOLWxlRElZWnVIcFVyZ09pQUktRGFLYldVSnY4M0FILW5ybnhNbE5vVGV3ZVZzREd0REYzaG5PMkNPQlZhTUE3MWRDX3M3bndqYk5LMkphdjhMS3RkeTZVVHJZY1Uxb2FabU5ZQnlTY2Q1aEphYW9fQ0hzckd5RGtGNElmQ1lwSTBvdWRPcnRPa0lvb2FmT0w1b19ONkl3Nm9qQXpjYjRBeTQzNzhOSk8tZ2UzT1J2bUwyM21uQnZ3?oc=5</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1391,17 +1391,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Scottish port 'UK's most affordable city for first-time house buyers' - Yahoo News UK</t>
+          <t>Welshpool transport company co-chief recognised by industry - County Times</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 06:55:00 GMT</t>
+          <t>Fri, 13 Feb 2026 05:00:00 GMT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9hMVdVV0FPYWVUOXJVbWxUWWFiNjhxWXBQVTR4Ulh0N2Jaa0ZWT1FUUEdfaW84Y0hlMk84bmItSFRQaG45Uzk5RXJZOExqZGNfanhLbTBoN01abVFXNzdYMGZBRlJDcnBxdTFZWm82ZzN4cXRHS3N4TmhISUlNOTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQQ0lwdlN2TWRZRW5LT0NtZE55eWNOQW9QYVpBbHRxUEJWNkk0d0MycktqUVdKWGF0SHBUMDVVRmJMUEIxR3NvY2c2SlI4N2tvc0hyaU9JaUFOTUQxOWFDM19MWDh6NF82YS1DYmd2d2xJY2dlaF94VmczcXA1ejhveXJzZVN3MWVxbTlFeV9nckVzcHNJY0VKN2lPUnJuWDJURU1oQQ?oc=5</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1421,17 +1421,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>“Responding to Global Supply Chain Risks Through AI Analytics and Data-Driven Decision-Making,” Samsung SDS Unveils Global Digital Logistics Solution at Manifest 2026| News - Samsung SDS</t>
+          <t>Young woman launches career through supply chain apprenticeship in York - Yahoo News UK</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 07:10:28 GMT</t>
+          <t>Fri, 13 Feb 2026 05:00:00 GMT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE16bFF0T0UxMDNKTThqNk1FU011dk5SdU4xaFdlUjRXaGc3eEZRREJBcHJ2dzZEaFV2a1Frd0RMWWNGa19CWUFDRGwyQ1dDb0ZoT05Fd0RScEN1TTItNVdBVXJLWVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxOSmVHRklMTFRTam05ZEFVSmFlaHQweDdCLS1nQzNHaU91OUdnWGp1SzlNQnhNa2hKT0FlTEZUUTNwR3phYThtbW16UGphUjV0LWRTY2NzUC0wb1JnT01QM3hjWWY2T3JaUHBxV01wUE52SWoyLVluT1A4WEtqVHJETA?oc=5</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1441,27 +1441,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NSW premier won’t apologise to Muslims after police grab men praying at rally against Isaac Herzog - The Guardian</t>
+          <t>Hormel Foods Names Will Bonifant Group Vice President and Chief Supply Chain Officer – Company Announcement - Financial Times</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 02:30:00 GMT</t>
+          <t>Thu, 12 Feb 2026 22:00:00 GMT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxORjh2MXZhMGRZc2xHNHZMNTdnR0d1TXZsUVVyWGZqOG9Da19kMnJJcVliRUItMksxeUVsT2ZwQkhlNG1MQlc2bkw5OFVTODFPUF8xZ0w1SFpwMDRFX0x2ZlBRaHBxTktrelp4Y2pDMG9ib0ROaGs2MjVYOXNtTkwxSTFzbjBqdnQ4YlBxWFhUV180WFJwUjNralI1bmN1Tnlud0lpMC1Vb05XbjMxZzVsTW5tR2taSkZGNXUtMWdsTEFZVDQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQVk94Y1NBWURtZncyLUU4YkdvWnE3YlJXWVFpeTFCb3dIbGxvejhzbFRIbGJiY3J4am9tbFJjazR1THVsYVNSM3dtYWg3czA4aHZVcE5oek5FTks2c09xU3RMYjVwd2l5LUduemRKcEdPQWMtOTRCWjVPRXpOTXJCd0FleXVFdnpJUFNSVXJEeVA4Q0ZNcW9Pcw?oc=5</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1471,27 +1471,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Protesters clash with police over bid to restrict Argentina’s labour rights - Al Jazeera</t>
+          <t>Oil Trading Giants Say Western Sanctions Driving Up Prices - Energy Connects</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 00:53:21 GMT</t>
+          <t>Fri, 13 Feb 2026 05:19:55 GMT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPalVaa2VqTGdTNHp5cUw3eWhFOUNKQXZtYV9WMExiSDRaY2o2Ync4aUdqaFN5bjBlbDhqa1BrdzZHV1dyOHZYenZDT3RTWkE0S3l1djN3RV9IclJqX3UxREFpRjNQV1V4WEV6dG1nenU5NWlRSXpNNVdzS3NDT2UxSTJZeGZ6R2h2aXNydTBFYjNCUUoxR0c1RkJMcEdGSjdaT19wcjRDQlJfdHF2MUZ5WjhxSXVxd1hXY0HSAb8BQVVfeXFMUHBlbWxnT09ORTF4T3pMMWhLQS1XYWFic0NNM1lmbGRzV0J1bXB0ZXFLR2w3aGNIZjdMd0g4czZESHI4ZHFueGZUUmhBb3VYU25oQ2FqWkU4T0JSa1dDNENjVDdfdmJDYmdybE1oMmx3S1ZjbW00VW9IdjdEd3dyUVdjSl9VLUw3N1p5VFhHT0s2OGxBYllaNWJhTllNbXZZdU8zUE9jamFocmhtMllaSUtoUEt6NW1OU3VYQmpqaEU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPcTg4eWZZUTQ5ZjdXdy1ONkR1MVNDQkJXckY5NThNODZwei10MEhnUUM5UHJROHplZ01XRS1PNEhmNXluYlcxZFJielN1c2R4YnQyWEFxbG1jQjU2MTFHSWhqcnJwVWlsRHgzVFU1d1BFTkFabkJERzRncDlIRFp2cUtBRDl4blpRMnI2bGJxTEVXVTBJb1IwdFg5Q3l5b3ZrNE9nUzluUVZEQmVjUmV0dE93dw?oc=5</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1501,27 +1501,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Amnesty International Australia calls for independent investigation of police violence towards peaceful protestors - Amnesty International Australia</t>
+          <t>New US Sanctions Bill Aims To Choke Off Kremlin Oil Revenue - Radio Free Europe/Radio Liberty</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 02:38:39 GMT</t>
+          <t>Thu, 12 Feb 2026 19:36:48 GMT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxNbFJ5dXlYVFdITm1KelBGSHJaYlJhVW1TY0dYT3B2ZkxTSXA1WHJFbDNSOTFOZ2VtNE5naFdrVWpMUHdLQ3RNZnA5eHFISUNablRuX1hNUS0zaktCdVlBZGp2aGk1T1lELXNQSnc0eHBYb2xHX3htTG1vQWxsU1AtemU2Z1MxZURsME8xZ2hsRDZXdFpMamF3YXEtSGFxMnZ2UkUybmxocThvU25fMkcwWXVCeF9DWElRY0VPeUc3aTdPZllSM1hxazBnV3VzNUpobl9sd2JtbldsUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNVW9WeXpCN3ZGQTI1X1lTZUd5RjlUZEpPeEVtbUhEa1A3WW1SNVVZRUo5RkM4TzI3TmJiSS1YQnp6QkpySXB1cXBGeFZvZEtoZHBja1BjTjRnemhxVlNTLUNMSnhrV0htVVN1bkJjaEZueTVmTENvZEZYV3hEN0hjQW9zN2NQLTFlWXfSAYwBQVVfeXFMTkhra1hoSmo1TE5IeTZTaHVxYllHcWcwNjJmeDJWTHZaTWNWckotZU0yQ081MUd2Vlh5ZVVNMHNWNm5CSHdfREw4TkZSSGV5dkZyZEJhYlpTdlF6N2V5Z1ptV2FWWmlPVDA5alhqNlhBYWQ0MUtlS2YxaGZHMGFmdHI0Z2VpRFVEb096cjU?oc=5</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1531,27 +1531,27 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Police fire tear gas as Albania opposition protest turns violent - Euronews.com</t>
+          <t>Trucking and logistics stocks drop on release of AI freight scaling tool - CNBC</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 09:08:53 GMT</t>
+          <t>Thu, 12 Feb 2026 18:11:10 GMT</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOU25vVVZFbWpZN3dQM2VLQnpxdXNWNGVVM3loOEFnMXRqRjNXcjdQQW9oempKZTZJbXMway1LaG84YkZTM3NlTUhBZF9vVm5CeGlvRHhZSlRHXzFzSWt1d0xtenR6WHo4UjRiYXRiUEJXR25VQTcwbHZyWDF3ZFpsY1lfcXI3WjU0dDZUTFFkcmMxaVRyZFNrNUhXdVdtQk5UVmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNbzBqaWpJbF9OVUN6VFY3M3duWGZwbmNFbXc5ZVV3dzRYWjJxVmhPSzZzZHFURjFvYzQ5SE9Qb2pyLWdWT3JRSG5XQXNQVWJ5ZzdabXJDTzB5M19xNXZRQmZKSmtDenYwRHB3TXh0MFJvRzZzeFdQNnhfZnpweXNzRGZnYmp3NWtXa3FBc2lFYl8wTGpIYkl5RHlFTzVpN250d3M2TE1QODJuVHRkT3Q2V9IBtgFBVV95cUxPWUk3VlRXNkJobjROSTdQdldwM0lUcjV6anVNTVdFNHhsbFlzT3p5dTVibE1sQW55OFFjUkpxaU44VEdRbWlKR1JXWW81OWVxQ3NyX2ZmdlJuSmw0ZXk4Zm9VMDlkaG1ZSEdHSmRrNHdFRXc5bjEzQlhjUkttVmtFeEpGbzUzNmlnWUR4OUlpVjBfUzBrRFc4NTJyUHhQQWpxdG5oT0pfaFVvT01FTk5LSjlTV3daQQ?oc=5</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1561,27 +1561,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Protests dog Israeli president's last day in Australia - Reuters</t>
+          <t>Six Republicans Break Ranks With Trump Over Canada Tariffs - Time Magazine</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 03:47:00 GMT</t>
+          <t>Thu, 12 Feb 2026 21:52:44 GMT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOUjN0OHFsdEtiV01BVF9hb0tPQU9STDhpNi1XNXNXLUF0WWRIanBWQTlVY3loYjA1czVoeFdhVlZyb1dzbm42cTRMeWpkb1dJWUw0TzIzcTJJS281dEZOb25PNDhfM1ZyRlJtSVZwSmNRZU9kM3BBdWNHdnE2SEdlc09rTDl1bFp3Tm96d1hKdGVnejFHUGp6RnhGVmhuSFJlVFNienlRUU5kVGI1eWFrbVhoaFBvQ0Rn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQZXNEUFI0QldRdkw5SFA0cU1MR190RHNhajlTNHQ5cnhLX3U1TzRVSFlLUHdwX0t1eWNmdk1YMFcxZVF3bkFGQ0JhUjRvWjh3emo0d1oxRnlpRUhyekxmV0dqaWh3YXNLdS12a0FMOG9IZlQ3NGowbElZRDliNTQ0cDZSaW5WQ1Fk?oc=5</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -1591,27 +1591,27 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Protesters, police clash at protest over Milei labor reform - RFI</t>
+          <t>Compliance notices for McGregor, Jackson for social posts - RTE.ie</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 01:04:14 GMT</t>
+          <t>Thu, 12 Feb 2026 12:42:38 GMT</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNUVhQS3BEN2tBTUZ6TnBnYU5FdzY3YS1POXY2NEJybnZKRnI3cHFnUG1yRHFIbXBBVW4wMkE5bmJJUE8xQWxRWFd5ZC1pcFBsUFpqemx3YzZucDZxcDZUczZicXRZdThLY1FpRVdURzBXYnFGMmhjeExxR2V6ZTkwT2dqQ2xUYWpDVzVHQlo5Ni1tSDdSNFp3b1hBd3REVHF3eGtFaEc3c3NHc2xD?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE54VUxUS2pCXzdOblEwX1hpZ1RDRXdnZWRob1d6cDlvaWhEamdBVWNyY01YMjl6aUpEWXZDcHdWRTFZVms2RWh6ZGR1eG5NdGtkRmFHN0pRQTJBWnlSeS1YQ3ZjZ014emgydUVTa1E1bGhTWmhSV1pB?oc=5</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1621,27 +1621,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Lee Mark Chang Defends UDP Protest Amid Police Warning - Greater Belize Media</t>
+          <t>"Compliance is one of the biggest challenges landlords face, and platforms are playing a critical role in supporting this." - Property Reporter</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 02:43:49 GMT</t>
+          <t>Fri, 13 Feb 2026 07:35:13 GMT</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOUGxzaUxtWnpkczJGd2lRSFlfQ255YXFVOGlfZTg2STVUS2FBVmUwNk9ja2dHSjF4MEh1M05MeGR6TEZQeC1Rb01pd0l6N2VuQTR2aDNodTVKdTRWeXczWWJuVF9zU3R0LXZ6UWQ1b0pqbWxJRWlQRW5NeHJuMU1ZbW1keTdZZlIyQVR0b0tB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxPOVY4OERWVXRHcmcySGM0SW1MT29ieC1ZSFZIdUFLLTB6WTR2MjE2TFNHb05lNUVUMnNnYTM0eFN2ay11NDVSek1OeXBESlFoRC1JY2lSV0ZWcnVhMGV5UjloY3lIYlF2RVE5MXg2X2lqVlJGOFEtLVFJTDh0Z1dsY05VZlBDYVk3Q1JVamFRRUZtb2FFN2phR0o4Qmtza2hnSVNOSHZMUDNERWdhRkJDdTlIUnNzc0FOaGxleTlhNzhJZVJOLU1odGdMdkpnbmMxZ1A3WkpmcDJpZlI3S1BOb0Mzc0laYnMzQkJwNFF2Z0s?oc=5</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1661,17 +1661,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spokane police use dialogue team to manage protests peacefully - KXLY.com</t>
+          <t>Sydney police to be investigated by watchdog after anti-Herzog protest violence - BBC</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 03:08:55 GMT</t>
+          <t>Fri, 13 Feb 2026 05:09:53 GMT</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNRG5HLWRLUkRRbjFYa2hnV2dHYVpnSG8zLVh6R2xLaFBJQXZkX0R4TE9sY0M5YkF2MWZLZlBMSGtMWlpzMFdFNGh0S3V3LURiaWRHVmMwNVZnZmdjWHZfeDJvdmNXVXJ3Y0hiU3UzMW9xU283OUNPLTR0cW85dlN6WWl6ai1FMVFOTE5oZEl6ZmJKSXYxT2hNNG44RWQ3bW9tSk5xaVFwWGVFQWpvR1FGWGR5T01IWDlaZTVta2Q5MlVfNFpBbkNhbW9QQTI5UmRsSjZRcA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5OXzFkVTl1S1RlU3h2RXdMTENxMXFlMVhHMS1PRVlOclFLSmV2SHRqcTBfVlJ4RU1lZUs5d3VRZThaVlhkLTdvYzVVZjZweWV4aU5LZWFWTnRCdw?oc=5</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1691,17 +1691,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>YouTuber charged with racially abusing police officer at hotel protest - Devon Live</t>
+          <t>Protest restrictions – why talk to the police if it makes protesters less safe? - netpol.org</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 10:32:12 GMT</t>
+          <t>Thu, 12 Feb 2026 20:08:14 GMT</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPYkJHbEhjbVhjTU9OM1l4YVFQRUE5aDB5aFJ3cHZIak0wX2trOWVLa2JWVmV1czA4MXFrMjFsdmRocUhibzVfdkFJQW5PdklYdXJTZ0NVUlVZUURmVDM1STNpclU1YnNjb0FuTHJVZlhsUjZuVFVvQlphOGczZXJ5NFF2YWN6dWNLc1BDczFPRHZvRklRNTJmNlhR0gGfAUFVX3lxTE1Ra0tIVnRhUEhqM0JxZGxzRi12d0lGb2V1cDBKYlNrTzctYjNQUXJxb0JpSzA4c2h0QTdFankyWVRiZk5RejQ3c3ozYjdqWTFCSjFLNFhUOElhaHdYZjBfclFtZzVhRW5ibk5URXpxR2ZzMFk0MUdNdVZ3OUlSREgzT3ZCTzEtZXh3V283Z3h4MTlNRnlpV1lndVVRZENkVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNYS1vTFl5UmVIQmxLOWNpLXd6c1h0eW5XRmp5NWJaYXNjYVFMd2FRUkFIV3JKYzBJdGhxd1NTdVlmRURwOWVobHlWNU9HM053MUo3dktnN1F2TXZxZ1ZFb20yUzJWUDlkT2ctNHd3TVR3dWRsczR2X3BVVVkxRHJRczBKd3YwODhRbnNyRXdVZ2ZmV2k5UjJvQ19xY29iTERZbDdUR3B6eGQ5NUk?oc=5</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1721,17 +1721,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Aurora Police Department responds after video shows officers, students clashing at anti-ICE protest at East Aurora High School - ABC7 Chicago</t>
+          <t>EU eyes plan to deepen single market in March, accelerate capital markets union - Reuters</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 04:35:25 GMT</t>
+          <t>Thu, 12 Feb 2026 18:32:34 GMT</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNYTRSeHdCWDZ1RExFS3AxRGpFMzBLMEt3U2NvTGxBakpaNGpkR3Q3S1lURVBRVHR3R19rb3Z6RU9GQTg4SEFNWmM3UU56TjFRWTJiUWhPemRibTNkSFNNWlVYVm5OY3V2TG81cGU1dW1RTjhXQVV5UTBxTDJlalphMExCMHpfazZ6UmpnYi1KVDhQQU5IdVlsVUpkc0ROWlpLeEl4STF5TXZLeTIwemdvRzhCQW5SaFg0UTZncXMtVUhKUlBJWldDdUJLeXRqSERlOGt2bTdCdHFmT1hibUHSAeMBQVVfeXFMUHVMWXcxajZ6TGRBQldjU2Y2dVJaWVV1WURvd2EwVVk1Z2k2N0RqamZ3X0NUWWJ0SXpsMFJURXBmYm1MQVZGZWU1WG5LZkVBZnR5aDRfbXU0T0FCdTRCY3hsUDRMR3gtRjd1Y2dZMWs5WWx3S1FJdFZCcG9FYjZsNkdhNHRvZnRDUmlBS1hWdEF5YmM1Y3d4QjlyRFgxelU3Q1VaY0xzcnc1eTlOUUhRREFadTNLMWo4VEFWb2FQUWNYQ2p4UHk5LXJDbm0zM3BTMUJmZVkwLTg2R2xnMmtYbjhYQUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPcUMxTmVDNHVhVzc3Wi1QdUJtVjVtX0RkdzVKdjdZZFoxZ2g5a1NoZlhkYVkzb09QZlpXc0tDdklCMF85NDVGaXJ3VF82QWdCaUhwaU8yM0Z1MHhUX1JRUUFQRjN5YlJoV0NNUlFUTlBnVkVYLUZDWHpxY21zbHp5YjJKZDNrdTVZdF9CTERham1Hd3oyMGVLLXk2NlNwSlBkX2Mxa3cxa3dNclZ1Zk54Z0ZBbFhXVjN6T0xWRWc1OHpKaFk?oc=5</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1741,27 +1741,27 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>How AI and automation are redefining legal practice - Legal Futures</t>
+          <t>NSW premier won’t apologise to Muslims after police grab men praying at rally against Isaac Herzog - The Guardian</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 14:52:21 GMT</t>
+          <t>Fri, 13 Feb 2026 00:35:00 GMT</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOeDB1cDdVeENYbDM3VmRoLWJGdHhQQk9WeUhlc3hiUW5BWkltc2l5NnpIYzhyZlFydUdTUnl3Mnp0RERfQ2ZMTXdsWHFLVHFveUhrdEZNejRBVC1ERXpFWW1WNTdYcEZCVFhFX1hsLXhxbW5oLTkwTE1JWFo4R1lEend6alIyRE9NWWxtWXNsbXlWYnRCOXpiLTlFY0lldw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxORjh2MXZhMGRZc2xHNHZMNTdnR0d1TXZsUVVyWGZqOG9Da19kMnJJcVliRUItMksxeUVsT2ZwQkhlNG1MQlc2bkw5OFVTODFPUF8xZ0w1SFpwMDRFX0x2ZlBRaHBxTktrelp4Y2pDMG9ib0ROaGs2MjVYOXNtTkwxSTFzbjBqdnQ4YlBxWFhUV180WFJwUjNralI1bmN1Tnlud0lpMC1Vb05XbjMxZzVsTW5tR2taSkZGNXUtMWdsTEFZVDQ?oc=5</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1771,27 +1771,27 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>AI threatens to eat business software – and it could change the way we work - The Conversation</t>
+          <t>Huge protests against Israeli president’s Australia visit - 5Pillars</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 04:23:00 GMT</t>
+          <t>Thu, 12 Feb 2026 14:37:46 GMT</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOZDR4ekdxRFctaFhmSFpFY0hOOTFXOTRidDAzRDdQLTJIQ1RfcWVWSDhLeTlsT3pDS0dDQW9rclAzVDhUSmpWdVV3YU5OLXVlOUJoUzE4a1JJbjVMRmxLb1d1cFl5S1hGdlRteEJDcHVHbjdwbVdzdHJmc0VzdzFrMlZIcmlVdkJYcjVvQVR3UU9Dc29DWXBORXNFZWZtZkItZkFqY1pvQ0lhaVZT?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQQjJFaUpWRV85NldNMUlNd3NHNnp1dEFEZldDRXEycEkwcTNCQmNwZ29URlJyODd3cFFLNzZVMW01WjdZUU1xcV91T2hhMTVWMENXeVpXTWd1ZXUtc2tVaERTd05UTEdES3NMUFRvWXRJQm41eHJmWTRRUy0yeS1RbUJLRWZ3OS1oeHo0dWJEQUM0dTZyQnc?oc=5</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1801,27 +1801,27 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>NHS launches AI and robot pilot to spot lung cancer - Healthcare Today</t>
+          <t>I’ve worked alongside good police, but what my daughter saw this week shocked me - SMH.com.au</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 03:35:24 GMT</t>
+          <t>Fri, 13 Feb 2026 04:30:00 GMT</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNMUF3bkNPdmxpZEZDeEI3ZGM1ZmFaSVpUNlZHNWZIMWZVVEhXR24wRzVNNkZuRWZTcmluV0VQUlJYOUwwdnlWWnlCdE1wOGg5ejlMc3Zvb0luNThXcXM2MExZdDhLOUxJM3hOdGdmSUxuNGd2c0oxdnQ1V3NSYWVyWGtXVWxmZmp2UG1TWXJQZ2M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNT0Izb3IxV0NCSDc2aW1jT0NIa1hzTmdPWTZzUUdQSkprZmM1M0RMQTM5NlVaMmtHcmhuY2hMNm1Ma3RqeXRqTFBXUGpCaTVrcmhiLWR2TjFlRnRCVGE0QTNCaEpBTWlTZFBwNmZWV3ZJWUVSTDFma2pxamN5bWdHaktSQ0lPemNrM1VwSnBiTHBFSDdONmxLd19Ia2lSTEFlbHVNdEFkcHdPUzk1eVZIOXJGNmtFS3QxSnZLb0swY2UySVVjSjVhY0NqY3M?oc=5</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -1831,27 +1831,27 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Reaping the benefits of collaboration on technology and innovation piece by piece - The MJ</t>
+          <t>Police investigating threatening social media comments following CHS protest - Cville Right Now</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 16:47:20 GMT</t>
+          <t>Thu, 12 Feb 2026 23:18:40 GMT</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOOTFUdW5HcGVxNXk0TnVLWGFFbGNBWE5UdnBGYU5sQXg1TkEyT3dQbmkwRE5HTjdRRG1KcTR1cFBQTnd3V1UybHo4REV4VkY0QzRBdHZZemllYkR4bGpWZlBPVGx6RWpGM1AzUXpyX29NMEFtNExSakdNQmVrS1JSZHNweEJzLVFPNC1JdXo1UnRFQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPelk1WWlNLW55bURrRXB3ekVuNXFKQ2s4SXBqX1ZHZk4zaHc4Qm83cEpRSS1tQjdsSm1qeF9qTGtYTGFwWFhlSWNXQVZFQmp0ZEZHYnA5bXBXMGpmZThCR2RfLTNYZ21VUXQ3SkZLMVk5a3F1LWhWbzQxT180cEtfSll2UkFsTVVNRTBxUVl2eEdFMGc2QUNpSlFlVlZPbjhqZUhsRjJOeEZUUXJVeUJPNXN4akRwdlU?oc=5</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -1861,27 +1861,27 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AI could rebalance power between people and the services they use - The University of Manchester</t>
+          <t>Eat Out Edinburgh! campaign in March proves city is still the capital of good taste - The Herald</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 16:39:53 GMT</t>
+          <t>Thu, 12 Feb 2026 11:25:43 GMT</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNOGhma2ZXQUFnclNMV2twTGdIbHQ1end2X3RCMzIyNkRLV21HZkVXT244V1NMTzFqZ1JRal9Gd3QtX2RvYTVZNUdWamtwdkNjZVRfaGluSGJBQmxyMm1ieHhRb3RzZTRtYVFSWFktZE45OFVOS1lBdkxZQWRIWGg1azkzTWh3MnFCU0VjUnpGZFU4Vk9jSWp4WQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNVUFLUlRSR09WYk5EX2MwVlpJbWFYZmpKaWFIWWZ2WWMyRGVMc1BsWkpFX2FkaVJvYTJudU93WmFobk5SUkRIM2VfcGZ2TWRCTDVvVVo4aDJqVTFteTk2Y25OYkZpb0pxbTBUVGlXRmptV19FYVFkcUR6aTM4dkctX3BES2RRLWl4RUxZVThTa0hnejh4R0poc0x4UWk?oc=5</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -1891,27 +1891,27 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AI (artificial intelligence) - The Guardian</t>
+          <t>Clovis Police says adults helped organize student walkouts, face charges - ABC30 Fresno</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 05:10:33 GMT</t>
+          <t>Thu, 12 Feb 2026 20:29:53 GMT</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNWHl5RUc2Z1pZVVk2Y3VmUTlXOFFiZ2ZUc01kcm0xTEI3WE1KYzN1d1drQ1l4NDhFa0VIX3ZQdEtYSzFNanlIamRRV0xpdThHZEhXX280TDdIdFVZeWVHeGpnMTJhd24xNEF0a3BhaEZ6VVZsTWlvZE5NdURtUW1Dalc2UjItdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNT1c1T19RTFU5d2h1YjVNVFBIUnBhYTJwaDYtdE5WWjRTV0VJNEVpa0s1aVYtVWdkOVlrcVZyRm1aNFFFWFFlZjd1OXNmcU81NkF1XzNRVHFnTzd0b250MkU1ZnY1ZFhXRVlCRURuVFBBMWkwTUktMVZTZ0VSdk4wbng1WWUwcEVZYVNfOC13YW1EQVhLM0dqUXFSRG15Q0dJX3gwWHVQWGbSAa4BQVVfeXFMUGRIZGNSMmxRR2VEQWp3T1JPM1BzT1NtM2pZQVhqRU5nWG1zNTlEMWFtcEFHNlpWaWZTNHphb3dpOU9ITE8yMWI1aU0tM1JPSmJYYjRLakl0cndYc0VfM0NGSUV4d2l0eFpVZndXQ0thbWxMN1VrVDl5aG5uNlBBcEdzM3MwcU1Od3c5RlRKZVhfN0xNbUFtZmVaM1ozcU93VnItVXhCbVRpUEtpU1pR?oc=5</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -1921,27 +1921,27 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Why UK CFOs are Trading Ad Spend for AI and T&amp;E - The CFO</t>
+          <t>Connecticut State Police agree to allow highway overpass demonstrations - Connecticut Public</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 18:01:29 GMT</t>
+          <t>Fri, 13 Feb 2026 01:12:00 GMT</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1odXhTN3NodUIzZ1g2UkhYYlpja3ZJdFZEU1FWWkFGWXhkcmgybW42a3hZODEzbFFyUXVGM3l6UDNxb3dpWmY5T1llUG5DalFHUTZ1NFRPWlpOWGM2N1RPc3A4NEpiQWp2cmJfbndvOF9IaU80X20zQ3QyS3lzZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNOGcwSXV2X1c3NzdkcXZuZDhMbGlOSVBhNTBSMDRuRVJzUHBJOF9Kc2Jnc29rcjlsUU9tUVo1T1NPTmlTOHk4SVdSQ0xfRVp6SllqWG80ZUV4SWNsOFRxbWtieGpjYTBqVFlnamNuZHN5OFl4a1Nsd3gyMDFWek55RXpEbzBTVDFLb0FHZkVtT2dtMTBlR3VBRWg1UElybDZaT3BKVXE5emQ1V2ljRjIzWXNXRDFVekhVQU4yMVZMcnZfdDZC?oc=5</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -1951,27 +1951,27 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Accelerating science with AI and simulations - MIT News</t>
+          <t>Lancaster man punches, strikes person with baseball bat: police - local21news.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 05:00:00 GMT</t>
+          <t>Fri, 13 Feb 2026 06:20:53 GMT</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQazZiTUl4M0w3TGJ5YVpfOWpwc3pqQjlRUVZacWl4dGxidk9XajAzWmtYeFNrYjFQVG4ybGxfSmVWMnY1SXd5bWFraXRVZFh6cm9udlZfMDc4NzFtVmt0akNST055eGxJODd2OTlvZkxpX2NMWFFoeGtDSnJ3UFVwamlZbkJQQW5fcnNqMFluR2FEYlhwRlZPM2xB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxObTZWQ0VQNXNnUzhhdnFSbmU2aVFvLWtscFdBWWI3eFZnUmtzdV9obWtJMm11VlRHZ3MxVnhxQkNna0FFWEtZLTZCZjZldnU2MXdqQ0NUY3pUT2ZVRU9DU3dwaFFLRC1aM0lCOWdzLThoaHltNmZzZFNVVEtnb085VURDQTU2UEExSmhoLTlEWjVXcW5tLTc3Qk8wenI?oc=5</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Siri Delay Tests Apple’s AI Ambitions And Investor Patience - Yahoo Finance UK</t>
+          <t>Anthropic AI safety researcher quits with 'world in peril' warning - BBC</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 06:11:00 GMT</t>
+          <t>Fri, 13 Feb 2026 04:37:44 GMT</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFBvTjREblg0c01oR1I1NFdncWRIekJtemJ3UzZkUzN1ZVdjSlRHRXZRUlZyb1dyZVpORC1sWlVSUkF2dHYwMUxzSGVRQ2ZFZzcydFpobXI2ZTFzNU5fSVliaU9fMGF3SlRVa0JlYVRrWjN3eF9tS2ltRVVGcjV4WXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1TUXJWZzZGczJLRXUzQTdvMFZnYTEtOE11UnJlSW04VkpYek84dWRYM2MwYkIzemlLb1huZVo3MWMzZUp2NVVoVVg5NFVienlRV08zbmNEaUFUdw?oc=5</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2021,17 +2021,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>[Webinar] AI and You Series: Common and Uncommon Ways to Leverage AI in E-Discovery - JD Supra</t>
+          <t>Ricoh acquires leading process automation and document management technology company ValueTech in Chile - Ricoh</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 19:44:01 GMT</t>
+          <t>Fri, 13 Feb 2026 00:04:22 GMT</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPb3pvOG5kb1U4bU1ubGplVDVWbm9aOUdFRUtYQ0JYdVIzV25vWl9zWXJRdjdDXzNQY01nazVBblJNUTNEeHVVSmIyRnpnT1V2YjB2ZkFicWhUNWxrWXBJQlVub1ljZHFheTZzY0NBQ1lPSHBFM3dfOE9ncVVxRmNrbS10Q09Edw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE1mTlJCc3dfMkR6c3dpSUhKNHNVWlpJeV96eTY0Y0hFOVdKdzZSU1pXQlRGZmRJeURXREppYWR2MVdDc0dISkhNVTNNSVZMZ043a1lz?oc=5</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2051,17 +2051,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US activist Elliott builds stake in LSEG as it reels from the threat of AI and the exodus of firms from the UK market - This is Money</t>
+          <t>Rightmove launches latest phase of AI-powered property search - Estate Agent Today</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 22:01:25 GMT</t>
+          <t>Fri, 13 Feb 2026 02:34:43 GMT</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPVkx2c3JwVmc4WHAxLVA0blUyaEh5Y3RUTjNqdng3ajNWLWY0Ym5vNkJPc19YUkJySDJ2MXNTRUhGVVRBQnBuN09VMzEyVG85Y2xMVnVyenBvTmdhY3hSWHZBeFJzSnZ0VzhrTXNsUDBiOUhGcDJxOTFfSzgzV3NpX3p2TWZ6X1k1eVpIejlRNzFPdWc2bkh2Yk41dV9Ydm1HSnh5YVhyYzJaYzFNNG9mWmxiUG5hV0ZreDQxczJrcDUyZ1BQVXhNbmF2S0JDZDNTMm5YaW9OcnF4UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQSUVJYVVURURyRl9ob1k5aUJZY1NJZExGUGpvTGVtZHlMV29LU3dsSGVoTHFhTXpCVlR4WXlycUFtN21sQldZRXFrMVowUmVRa2ZwTFVPOHZoYmozRVBMaXVzNGJXVlNTamprbzhRMGxlQUdIeGpJLTlubVN2eDlJSUxQa09UTkFwVUo1d2F4UUpLWFAxUDJyN3QxbVRndTdUeEJ5cHZVTVBwZzl0ZjVWS2oyMnhaRGhGaVpR?oc=5</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2081,17 +2081,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Software and copyright: key takeaways from Edozo v Valos - Mishcon de Reya LLP</t>
+          <t>Stanhope AI closes seed funding, sets sights on AI revolution. - Calibre Defence</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 09:17:05 GMT</t>
+          <t>Fri, 13 Feb 2026 07:19:58 GMT</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNUFk5cGR5U1k4UGUxR19BYmJEWVlrbVdCdTVncmx0SlQ1TkdrSnl1dktYckZzN2tkTmxyaVBYaVpmWkZjVGNNMjUzeElBT085SWpVa09rM2xqMVNtZGpmbWNGTHhGUEJjYUJVOTJ4WjljQk9LUWtoTENjQXdDY21lbUotd1U1bS1GbUQxVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOYjFmZUdrM2JtQVhCdVF0QUdEQ2syQlVkS1ZuRFY3eFh4N3FpLUpQQU5oZUVVTzRIb3NXcjRYMHBudVRsZ3NxaFJ2Q3ltTDhMOTVyaGVJaEx2bFFOSUpBM2Y3T2dfWmRTOW1YLXVKaDRrTnZyemJGS3M3Q24zLTExUFNDMGtnQ1p5SEhzQl9kWEJOMWVZLWZqbFNBYmVRWHUzU0otLUdGa1QzM3hnd3JSSEZn?oc=5</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2111,17 +2111,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>New analysis shows AI could slash public sector admin task time by over a third in Scotland - FutureScot</t>
+          <t>Telefónica hosts the VII Conference on Habeas Data and Artificial Intelligence - telefonica.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 14:26:07 GMT</t>
+          <t>Thu, 12 Feb 2026 15:58:44 GMT</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPWW5aTDd5T2lGWTh1NHp1SnY3a3Y1cjFhU1RaYUNjbHVvQk1wWkQ5TVhGS25wM1dOTEQzdnNRZUJqVE5JUW1NYmRlX3EyLWQ5R3NraTVIRE12SEhSS3hLOV9vMWpxZUQwOGpzdl9yUnZoV2dhMlpQLThQYldNT2MyMWRZNjBZdDNWd0ZrYkd6aXFoWUhQMzhSenZ0ZWxsVEpaS2lRY0dMRkthcG5YaFdycNIBtgFBVV95cUxONGphZ0UxVkN4emtDNllZelAzR2ktOElUcWJtZFFLc0d1UWVrX2ZYT3ZxQVRzMXZSZi1jS2lJOGl3QmlQYW9NdnViSVZwa25XQ3ZkSkJQZDg5VXBHTGpTbWFFekV2OHlPNmViQzhPQ2hudk11M0s0WGlVUnJBOTZnOVF3ZWxFZGF1LXkyNTlhQWRMc0dqZGdTMjlOVkt1N0t0alhQTzE4cXRzTDhJSmw3Q2ZmX1drdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOekRONnRNNHVBYWFDS1NkMjgtaHU3anh3bG01LWgtUjEtbGJONkFLUDZzV0ZHdFdTM2UxWWxyYUxsOFVqLWF3Y2VYY0xHcW9qSWFqSUI0YUxUSk92LXZnTUtxYmJvajl6SXZnbW94c01WS3BCVHdxZ0g5SmM5NHUyVElNT3pNaldMancweXJib3g1bFk4OFM3bXpkdFBZZEZnX1Eyc251akptb2t0am56RXVmT3ZIMGJYZFRPYmpXQ2NJeXc2YnJB?oc=5</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Shares in UK wealth managers hit as AI contagion spreads - Financial Times</t>
+          <t>What do I need to know to prepare for Quantum? - Association of British Insurers</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 11:16:09 GMT</t>
+          <t>Thu, 12 Feb 2026 11:29:31 GMT</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE9DV3FGMlVWLVJMcEp2ckFRT1RTSUhtNkJ4eTFJQThTNEVTcHRDV3NNOE90NHdweVNPcm5uQ3ljbWM0R0d1VmIxY2d0ZlBBeVZ3WTBHV0tyX2tTVHFwejZmdTZveUpwMHB1NmJYY0NWNTI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPbzEwMEh5cFY0akNSYU11RC1yWU9HZF9vNHFxNWQ3cWdsNE1adk44TEdGeGhlQjY1dWE1Y2tZUG1nVEstODhuZURPZmZvVGdvZTdDOUZUb2ZxX1NBR1l4WFVvZ2JsTGFzWmxnd3d6RExDRlFQLVBfX3ZaRmhHNnBmUTlRaFNqdnhYQlNTUk1XYy1CWXhCdFN1MDdRYw?oc=5</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2171,17 +2171,17 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>The big AI job swap: why white-collar workers are ditching their careers | AI (artificial intelligence) - The Guardian</t>
+          <t>Is Europe’s digital backbone ready for the AI supercycle? - Euronews.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 14:10:00 GMT</t>
+          <t>Fri, 13 Feb 2026 06:00:08 GMT</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNaDEwbEgyRXBzVktxS1dMR2pHWE5VOTg5MXk1OFUtV3RBcUwtenRORDNxQWhTSkQycFpqWFNJb0RQaV9NOEJrenZGYjJhbENVNktzQWRnOXhKdVAyd2E5aFI4NHJHRUw0NFRuQkE4Nld4RDBBNGxMTGppVXZnOVA0VmFlMHlnM05jazhZQ21GSVNDS2h4ZDJwM3FuOTBTRk05dDFZeEJoSlBOMWRsck5J?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQel9mQlNqWDhRcmh3aEFXeXE2dWJ3djBIaDhzZEZwQkpxODQ4dzUyLWVRcHRmTmhfLU1sYVJGU3p1WGtBVE1XSkdhWUtWWF83T3d0TDZURllXcllTanNSdEFhREpjbk1XOHN4S1FweldMWXpRMm5jcGdGd3Y5TFVnRzZYMVBpdmt0SFVySnJLMA?oc=5</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2201,17 +2201,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Okta, Inc. (OKTA): Expanding Identity Security With AI and Global Growth - Yahoo Finance UK</t>
+          <t>Supreme Court issues “bombshell” ruling in AI patent dispute - The Lawyer</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 17:18:29 GMT</t>
+          <t>Thu, 12 Feb 2026 17:47:10 GMT</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPZ0VRSWo3S2RSY180cG1QMGp0V3JkTzhSZkxrbGpHSWVUeEV0Mk1UZGo4dGRGSThNT2FuX2RiTXFHaVhjRG14aWwzZE55LVZ5OTEwQnBsellNcXFOTUpuVDl3WUZkMHZ6aWRWM21NN3hDbU05bWZJMXI1YVpQRUx1NWdHV1VLVHVS?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxONElkb21jSzk4ekhycEpHY1VSYmFMTG04bW0yX0dMV1ZhYjdHd0dQdk9wUlU3UmVEbDlHMFFvN3NBNTdydnA4UkFVaDNmeUotVEItYk81QXlsUGI5SWVYcGZGYktYTUdKR2FUVmRYR1JLdEZpMmtsUGdDN2U2YlJoYzB3a29hVXNiS1dYM1ln?oc=5</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2231,17 +2231,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Something big is happening in AI — and most people will be blindsided - Fortune</t>
+          <t>Unions call for strong AI guardrails to protect workers - International Trade Union Confederation</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 14:22:00 GMT</t>
+          <t>Thu, 12 Feb 2026 11:35:31 GMT</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQUGFOV2RVWFhDV1drd2lpT2ZrZk1QXzI2emI3Y0pLTFhocDNFZEkwZGxadmx1VTd3N2pJX1lYNHZRQXVuWUZDM2V0dG9fLTlHc0dWSDhDajR6SFpxQTNJZ3dsZnAxUGZPWGdKVkNsVFRFTVZ1TmtKVnh4Rk95RG9aRjhCRHVpQkZNQ0hSUHFxeGRmbGVLNW16eW93?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxOLTlRNUJxUDl6bGtpRDhidlFBOTB5anFkZktkaVlmVHFPUzFjb25BX0lGMFgzSHYzRnFUWnNPTEtNT0pjcl9yY3hnOXlxTWloMEFqZGlUcFE4elBFQjdha0NUeXRLUExnenRZa0hVbXNMejZVcVhnbmhFWXhfN3ZOMlFYWF9zdWs?oc=5</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2261,17 +2261,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>UK Supreme Court Issues Milestone Judgment for AI and Software Patentability - IPWatchdog.com</t>
+          <t>Building an AI manifesto - Wonkhe</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 21:03:10 GMT</t>
+          <t>Thu, 12 Feb 2026 18:09:19 GMT</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQaG9yNUtuNXZLZWNDTkhwQnJvMExyR0phUmZqZ1Y2Y0stSzdVUXB1T0ZiSHkzRnI5aXVYSktIcERrWERYU1d0Ui1FN0x1Q1hkTzBibjU0OThrYVJJMUNPUW5RcnZHMzNuV0JtV1MzU2hpelc4V2ZqN1V3Z0p3UXVac3RsdEJWOU9peGI3TndEd0JBUTZPZFpya04zNUJuWUMxVEQ0Vmdn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE51S2JjYUZGVHRzOThfYkVsWmF3cWYwOXZNTmotOVQtQ3hRbnFoc29QM0NzQ1JmLXVMZUdSaV9aZDROaUZuTmZCLTI3MEx3M2szU0hzRlk1THY2YjIxdEwxZTY5YVY?oc=5</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2291,17 +2291,17 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Five charts showing why AI is here to stay - Trustnet</t>
+          <t>International AI Safety Report 2026 Examines AI Capabilities, Risks, and Safeguards - Inside Privacy</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 15:05:58 GMT</t>
+          <t>Thu, 12 Feb 2026 16:24:54 GMT</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPZTZmOUJudEhHRXFEeWxiZ1ptSmpKRzBRR0FvendaMlNiWXhWRnVqZjg5bGlPQktaV05zbmRkVngyLTY1c2c1V1l5TFJRV25HdHM3bV9PYU1VMXlfTFJJQmFXZHJheDlpQno1MjhvWU16MTNNMXE3VUpKS3NvLU5GeGx5bDRWNldZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNUzVfYnVLek15dlUzX3Z4ZnByUnoxNnNTZmdaTXJWa2g4Z05KVW9WOEtXV0hLNGd3dTAtVk03bS00b2JpZV9SVGowRWlXM3dneGUwM3hBY1BLdklEb1hvQ0MzUVJVOTRFb19QXzdpN0FsTHJKUFBEMVNLSFZFOFdidDdtM3Q0SHFBa3pMcDlWV1pQd3FUMFkxekF3LWtnSFJjejhwZTBkQUVEMnpKak43aVowQl9aN2dERVRQNmQ3amVzN2U3QThjSU5yQ2lRZDFqZnc?oc=5</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2321,17 +2321,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>NEUROssance And Universum Labs Establish Global Learning Consortium For Quantum and AI - The Quantum Insider</t>
+          <t>Quantum Untangled is extended! - King's College London</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 12:32:05 GMT</t>
+          <t>Thu, 12 Feb 2026 15:53:28 GMT</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOVWhSRERESHFnaUtQNV9jaEFhMGZJdEhNcExzQndscEM2a0t4TDdtb2ZhZ0RuRUl5M3BReWlmeU5WeGdiY2o4djc1S296YzI3ZnpTVDZVWFZJb0RoemZwSURqMElVOVNGZ0h0azNvcGVYcDZBVVNyLWhKX2NCUjRNemhkYU41YmpOVHpLS19QRmZLbFVhMkRYZEtGR21POUdnWXJ0cGcydVk3dGVUUUVqR3VTd2k0X2ZEalpSTVM5dEU5ajVHd2hZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTFA0cFJjS2c4Q1NwOTJ5aTZxN0tkanI4T2k3RVdpZl9LemdhbVNJWGxYbjNuLVgzdHhhRUYxNTQzUWtFMy1ndWdQS1FudkVkLVhOS09KN1dfRkVYb0IyNWZjZ0pPV1ctRkk?oc=5</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -2351,17 +2351,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Enterprise AI &amp; Analytics Insights | Strategy Blog - Strategy</t>
+          <t>AI and cloud reshape Olympic broadcasting at Milano Cortina 2026 - Broadcast</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 19:11:02 GMT</t>
+          <t>Thu, 12 Feb 2026 12:06:17 GMT</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE5XNmpjeUZhNHdwalJYaDR3bWRlTjM2ajM3MXVFN1Y3aTNCX1FhUjJaR3lvazQ4QXlITFBVTGx4bHVDMU51ZU40aHNsbEJpb0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPampxUmx3SE1sblpsZkRZNUhhYzc5NHlOdVRLTDY0ZWY0UlV5TC14NU1vY0pTSF80eVhxeHRzelZZa3RVT0wzdVdWeklYRkRKX212a0tCbGZZNjhTZUg5VjV3LURZanZ5ZjhMSGNTQkl0Q2VaY2Y2NlhlV0tCZFBEbVppRDFVVTZ4cjJrQkRhZENpM3RqRkg5a3UxZjBMUlpSUm9RVFJ0RVpIbDBqaGhrQm9jcU4yWV80VGYyamVwaHpza0F3YVE?oc=5</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -2381,17 +2381,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AI partnership aims to 'futureproof' North East manufacturing business - The Northern Echo</t>
+          <t>Conference spotlights region’s AI potential - Bdaily</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 05:00:00 GMT</t>
+          <t>Thu, 12 Feb 2026 20:27:56 GMT</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQZ0xBOVpiaUtVS1FRSkxwbkNPMmVCV3pwMzZkdDl5TmUycndUdUlzRVVpRkJHVWc1RG0xUTVBMGg5UXFBRFktdzdxUWdZcmd2UldCNkppRFFHaHM0QWdTTm4yanRUNHk0cl9WYndJangyclJZR3doSVF6a3FnUHBTRGt1UldXLUp2VEJZTng2U19CVGJHazUtYURNbHkweGs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxPOUZOdVdjMjBXUjJwZ283NFhSOGZSYXFpU3YtNFBGUnBybGpUSndlTE80Wmp4TV9IVndoTzVyb1BPYWVkX3J6N0FoUEdodWFZMGd5bEpjdVdtODh2Z2V6NVNzc3ZkUlZLdC1NWWdCREQ4VjZCWFVEOU1jcWFleGI3MDZyOFdacFhLTlcw?oc=5</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -2411,17 +2411,17 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>RegFi Episode 86: Agentic AI and the Future of Consumer Financial Guidance - orrick.com</t>
+          <t>Digital love: The AI next door - Trustnet</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 19:39:06 GMT</t>
+          <t>Thu, 12 Feb 2026 15:00:41 GMT</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOZVdKU3NESUlhY29oLTBfZjZkUExRYnZZQ0JhdHE2STN3MFVfUGNVTUFldk9pS0JYSU9nUFdSRjE1dWl2NjMtQWlWUkgxUGJmaUFPQ1cwZEdQWk5CM010amtOVldhbHM5cGFLV2FNNm5jd0tGZXBXV1pCZUFjYzhTMEpIRzl6em9rSHpzY1k3Z3VPck01NGgzQ2dDTEo5ZVYzNEFicVh1Q3VZUUhK?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTFBacWY0UnJ2bXJCbm9GMm9nZWQyUHFodDVzUV9zRGR1cHlxMXlaZTI4ejl4TFZHaGdqb0hWdlM5THdqdnZrOVdPYVVvMHVUekNuelR1ZE8yUllVNnVtQm9NTWhfVEdFNHEtMWdZZGt4SmU0akI4ZHB3?oc=5</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Building an inclusive future with AI and education: IDWGIS 2026 - Anglo American</t>
+          <t>Get a grip: Robotics firms struggle to develop hands - BBC</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 14:42:49 GMT</t>
+          <t>Fri, 13 Feb 2026 00:04:16 GMT</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxORFFwWWRCYU1pS1l1OElDbEItdG1iQS1Hb1hnUVEyd0NwQmIzS254TmJqZ2VFaVhFSWxHaWl2Wkkyc3p3eTJSMzZLdDJWZVRxSWppOXIwWXdhMXpweTZwZjRHdmFrcElrVkZKYWpnYWFZb0VpWGlkcFFMZjM0T3J0aS12NnlYaFpZQVlkRGR4UzhVblEzZ1ZBSExtUHBGV0FranlLREV2MFQwRXpTbFVram5SMkl5QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1kdzlrd2FHdXRqYUR4YjZ4NEpqbC1NY1RuSmFWeWdrZXE2TVZObTlwcFBtTUtMUHgyS2I1VVJMdVF1alRDVXNDWlgzbkVzQzNXTFVvZlE1M1ZBUQ?oc=5</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -2471,17 +2471,17 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Create Music Group appoints Mitchell Shymansky as chief data &amp; technology officer - Music Week</t>
+          <t>The software sell-off (part one) - Financial Times</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 15:18:00 GMT</t>
+          <t>Fri, 13 Feb 2026 06:31:43 GMT</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNR0dCUUFHcGNBeEhzRDl6aDZXVVFyaXJQZjhHaldqVEJkQUZ6a2kwV01iSTRCZ01pX2FYd0FwdnBEZGFWM3lhRmtwY3JkT1ZNbUF6blRTTDlUV2d2cWhlMUt1Y0hMM1BxWm9ybjhWREtoTGJmOWxocTZCUXdWMVpYVXZ2aktsdlQxc2lsOFB0VjRRaU5WdkdCZjlTQVdKYkRBS1N1UjFUWUUtV1VQOXFvaGNldXJ6akRTX0wxSU8zY2lrQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE0yY3JsSWt5N19aVEQ0aEFmazktMGJNNTNuWmY2QkdkeUphcmJWSVdRQlo2Z29ETTFyVFVrSmZCNDktc1I4V2JjQmI1Zlg5Y0x2M3NEOXhFNGZKZVZLZ3M1eDAtUHMyT01XYTdyemd5Vmg?oc=5</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -2501,17 +2501,17 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>DSIT launches procurement for UK’s AI cloud compute capacity expansion - UKAuthority</t>
+          <t>Creativity and Learning with AI - MacArthur Foundation</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 17:15:47 GMT</t>
+          <t>Fri, 13 Feb 2026 07:41:15 GMT</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPUG9iMFkzOVNQeXg2VV9WMmZtZ0tJc0pFVk5DWXNGMjU4a0laSFFTTDdQM0d6ZF9MV2V4Xzc5aFpocFNMeV9KOV8yaDNyOGp6eTEtdkxZa3cyNWc2UnY0RVktYUtHVGM3bHk5VGo4MW5tZEotWVN5YWlCWG1mUURyMnY5RjkwLURwa2pub1ptVDNNUjlGa2cyckhDZEtzaFdTNjVxX1ZpQjkxZzQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxORW9yZHIzZ2dGS3QzbGg0cV9EbGd0N3QtdkNhaGhaR3djNkMtZzBXYXFqZkIyZFh6ZDJfN21EWll5S3VtbnNXbDBwQmhOTWJGQTJYeUMzbnFDQ3VsUUpKRm0tV0Q0N1RadGFaejJ2RFhZSVFQR2ZfTHM4dDVfRTQtVg?oc=5</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -2531,17 +2531,17 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chaucer and Armilla AI introduce Vanguard AI to streamline cyber, technology and AI liability protection - Reinsurance News</t>
+          <t>Data and AI Are Reshaping the Next Generation of Connected Compressors - The Engineer</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 08:34:46 GMT</t>
+          <t>Thu, 12 Feb 2026 12:42:47 GMT</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxNb1A4NFNrZUg3SnhyYlAyb01xcmg2X0MwYVZmbXRvXzlLLWN4ZlZHS2tmZ2thZXFSbkVJVnBuMnBKTU1oQ21WdXFVUVF0aEU4SkVFX2owQUNHYkVuQzBzeWs1STdKdXE4aHR1UFNsX1V5MGhONGQ5QzNOX0F2M2xfbWZ0SzA1bFFfUzBQeEJibWhNTXJkRm5WWGRFR3Y0aDJEdFB6aVNDeHQ3a3JTbU9oX3FfS0pDZklxeXVlLWJrdzRPRzBWZDdfM0tyeGE5dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQQm16SkRETWQ4VzNfaWVqdEI5VzhmRGktdFoxTDE0WkNBVFhrSUVjNnMxNm1FTTQwSlVJRGVsZmd0UGNmSWlYUTQ0cDE4Z3hIZEVzZEdORzhfa25JUk5nNTZXMFFOdEdXMC1ONlhTQzNRN3J3T3VidnB4TzNSZWs4R3oyZzdFOFM0eWFHNThrZHpZcDgtZWlxRXd5ZzJxMENLRWxJM0RPNkgyMF9uY0dlcXJSWlBmd1k?oc=5</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -2561,17 +2561,17 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Report: Knowledge maturity identified as key differentiator in AI success - Legal IT Insider</t>
+          <t>Gloucestershire HR expert is helping businesses get on top of 'shadow AI' with free online guide and roundtable events - SoGlos</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 15:01:30 GMT</t>
+          <t>Thu, 12 Feb 2026 10:21:25 GMT</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPNWo5enotZjNqQjBQREVlMUZXTmo5eC16T2tLU2gyS0d1TFVsWWZTMExOT0hDWm1NYzBqX2x6RW9xTmFPOENsbzdlVWJ3MkJySE91VmpKXzZRX0ZzR0lEYmJraGl3SVZzYlZONnJsX2NSR3BnWTlxWnl6N3k0cUdtSmVnOXFlVE1seFNlMUtpSjR0WUhNZkp4X0g1WnlxNFMtbnoxX2RyZU1oWnBtLWF5T1Bn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxOZ1k3ZXlHRDBoRFVPR2o0YjgyRnktMDFBMG0tdWdIMTVHakx6R2FzdUVfZmltbXhtbkROdk9CNFZRNkR2N2F2bF9VSTlQam5GYUc3dFlzWUFiWUZPVzRYbXV4UjhPdDBodS01am9vWE1IS2JTUnVHc1FrRTVPR3BmaU1TcXdaQmVuZjlJRThLZ0tLeko0R1FTZjR2VVBPMF92bm1fcmMwOVp2LVRydUFhRDVhWjQtcUlrN2QwdTFRc09mcDh6VDcxR2RKSTE0aDlYSGVxQUhOaW9kbXQ3VHNacktlN2lXakhadnpfQktydHlUZw?oc=5</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -2591,17 +2591,17 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>I Loved My OpenClaw AI Agent—Until It Turned on Me - WIRED</t>
+          <t>The Ultimate ‘GPT’: Is AI Game-Changing for the Macro Picture? - Neuberger Berman</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 19:00:00 GMT</t>
+          <t>Thu, 12 Feb 2026 14:49:31 GMT</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE8wRWx6c2otLXdyc1Q4YU96b3hRMDFoa1dNMnBSQ2JtSXRxTndrdThIeVg5S1pDMW13ekJOSmxVbWphWGxWMEFReXZCUl9yOGU4Q3RSUFY0Y19WRHpqQjVfbWJmek15aEo4WTJsdFJfLXA1Wjlm?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNQkkwU0hLMmNaQVQySUhHdnR5b1kxYUM0YkpvbUJvMWlsZmQ1RlBVMVdPQ0ZWb0FZeVQwTlFTaFE4VDVRVWYwNW1mWUNlR2U3azhlX25FSGNtcmI1Si11dWduOVdyT3hOWldqNUM0cDl5YmdCS0d3bHd6b0kyM1hLLXV0U0UyOVFqSHAxd3FOVjZldktYVmFwSzhmR2g2Y0xya0hyTzNKUkowZTVrX011Tg?oc=5</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>PRIMARY-AI: outcomes-based standards to safeguard primary care in the AI era - Nature</t>
+          <t>Transforming work in an AI world: Reflections from Davos 2026 - Mercer</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 00:05:13 GMT</t>
+          <t>Thu, 12 Feb 2026 16:31:55 GMT</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE50V09wY1lTODF2R1VmWmg1eU5wdm95cEZtVERPWVJya0RsdmpRZVNLeE1BWklKd3ZDWUx3Y3NZYUR4NFBxeTBFYVhkZFJzYkJtTmZ5aGFDTklEV052d3k0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQLTJGZzc1Szhxcm1qbDBMQk92OEt2N202XzFGMS1WckVfcF9tX3I4UUxPUHJ3NUVxUHdyVm1fNkdFWC1uZnBiWjlSU2o1Zzgxd2psNjNFMDBMSjZQWEpWYmRrV082dEhhMU1Ud0o3V2wzX1p1QVlGd2NZOVlHSW1DZHljb0tCenlrVzlpMF9rNzZVcENlUmc1R0FRcjBwV0h4bG12VlVRRjRRV1d1RTBuTURCUmdma0JTTHB4Y1p4bzN2WG84NkE?oc=5</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -2651,17 +2651,17 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AI Impact Summit 2026: AI Governance at the Edge of Democratic Backsliding - Center for the Study of Organized Hate (CSOH)</t>
+          <t>How China became fixated on cloud seeding - BBC</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 03:39:48 GMT</t>
+          <t>Thu, 12 Feb 2026 10:00:00 GMT</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE80dnQ5bGdvc3VaRkpoZWtzVmxsQUU1YWtxR1hQRkdZQnV5MWdZMl9PWG5KUHBubmxHWGJuWVlzYlBxRXRQUEEydm5aN3VKTTFtVThRX0lfZnRzTzMyNTlqaWhRbndWQ2xB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOeFY2VVBoLVJzYzdqUDdRNnQwZ3RMbzBEVUdwM0preGxlUi1NVXBVdG9TUkNtNzluSlRCVkZsc21SNVpCVktBb3BGUWlLc2w5OXN4VUdYSXpXVHdoejJRUGVEeGM0X2x6emNRRmIzalhqUFpkcDhIM2lmd3VGdC1uX0UzdHE3eXBtcGJpeHdQaEVrUGhCQXoyNzZza2thUQ?oc=5</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>How AI can boost defenders , from defense in depth to the cyber kill chain (Q&amp;A) - Google Cloud</t>
+          <t>Why CPUs sit at the center of AI infrastructure: Five takeaways from Futurum’s latest report - Arm Newsroom</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 20:42:06 GMT</t>
+          <t>Thu, 12 Feb 2026 20:52:39 GMT</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQdVR4VXM1cDFseXMxVVMtZ1dGQnhCZU1NbWFiMXNGTW9VaVh5ZXNwRXpET050TlZiRlFEN0N4dnpoMGlIbU0yZEJ4V19HZTJ0VVJQMzdLZ1pCQ0FaSUlxMWwwWnVmQjhfVnhNdUp3WEMwUk1ST0RySFBheFVnczZsaHZqcElUZmphSFBTYkVYbk8tN0I4bk9TSU1ZWV9XVU1TS3Z0WGdpbjlmZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxQWGJEZm1YV2dGSERUSFpvV196RkJya0MxVWVKLXRsRGpEZWlkb3lYaGxLaGpxcHA5T2RORFMzbXhFRlBnOUl4d290TkRJZHluMjc2cjMyZW1HR29LS0JwLTlfTHZBVllHX2JuMnEwX2FudEZoVVRSam0yelhlcHVrWlhmcXo?oc=5</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -2711,17 +2711,17 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>New computing curriculum will teach AI awareness and digital literacy - Wired-Gov</t>
+          <t>Hertfordshire officials warn of AI and deep fakes ahead of Valentine's Day - Hemel Today</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 12:04:50 GMT</t>
+          <t>Thu, 12 Feb 2026 15:07:00 GMT</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNMENzV0tFb3NUYlFSMzhxcW13N3oxaDRvVGQ1NFZIblBubHFtYTZkcGZIN3lNNndEdUU5VE03Ymhnc1BmUm5RTVFSRjFMWU1YSl82Y2RPeFBDWmVRNmZmZmVYUDlWYXBsMG5PZFBHM2FnUzdoRU9lTkdjSXFNb0paYjF5Q3QyQ2dxVFJRWk9HWmZVMGt5YnFJMy1TT2pfbWV5clVfcGFkYkM3cXE1QXJVSXk2cGdMbHhsWHphSEpMVjh5S1NSSm8xcUtKQjJYYU5CRVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOU21hWmZTb1dseXRpNmRvNGEyYW1FWTJNNVZ6Zm5GalBoN0VvbUUzMGMxRzdwRnl1cUdURVZaUEJqWld3U25DTmpxVW1lTndzWmpSd0VwbTFqQTNCVUEtNlpRT0JoWlN2UFk2NWdMVXdjZGZYOWxJaW0zWnZ6OE1jaERLTmJnNjU4UW85NDBMTlMwRnctdDJBNXlrd29EMlBlU0EzQ0VyZXJlTS12TEdkeW9YOGRwdGRHZlhTLW5n?oc=5</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -2741,17 +2741,17 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>OpenText (OTEX) Delivers Cloud Growth While Shedding Non-Core Assets - Yahoo Finance UK</t>
+          <t>Operant AI Launches Comprehensive Channel Partner Program to Lead AI and Agentic Security Revolution in 2026 - AI Magazine</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 17:20:16 GMT</t>
+          <t>Fri, 13 Feb 2026 00:52:06 GMT</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPTFdEbFBtQUxOakZINkV1bHhfLTEzemswQUFCc040LWxOVzBsWkQ3Snl5RU93SmZCWkZYTy1MeWh5ZXNjSmpWbXlsekl5MU42dmRSZnRiVEwyMmhGR1NkeGQwVEF3SGhuaWNiSjBJOC1pYkdVV08xZWh4blhDV0FnNzlLdjZTWllwcTY3bQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE9MbUFNTkN1U0ZNRXNKdVdTZGVvN0VNUHN4NGFjTll0X0FSWGJScjJnTEViTU5vMWVVb2s5a1F4cnhlVEVTMFNIM3RmY1g1TEgzVGRnYU1qaw?oc=5</t>
         </is>
       </c>
       <c r="F78" t="n">
@@ -2771,17 +2771,17 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Moltbook, agentic AI, and data privacy, explained - Mashable</t>
+          <t>Aramco signs MoU with Microsoft to help advance industrial AI and digital talent transformation - Aramco</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 12:47:01 GMT</t>
+          <t>Thu, 12 Feb 2026 17:45:00 GMT</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE9McEZwbzVYbDJTRVhWZVNjNm95UkVaNUVLMC1UM2paamlkVmgzbHhPcF9rN2dMbHhMX2FCYWZSWVVZRy1pRW9jQWtQSmhySnFXWWtKQVFkTVlhZHFG?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOY0xzeEtxN21ibEg2Q0ZkOUJ6ckNEaDVQbGhFd2NxZ1daTDFYRDduR2xrdGd1UDZ3WjBQVkM1Yk1Qd0lLd0JiWkhEbDJ4NXAzSHJnblA0RC0zRURZWkxmVHF3c0d4OFBzOFFYTHBfa3RQM200SFRvZE5jWHNmYXJTUmZFZHh0OUVWQlMxUUxOSHlxZUtGcnlYR0plRHJsUjhJZXNidDRlVlREcklhNmx2Q2xMMFhHTldFWnlrQUVMRnFqenpnbHhqYkNVODNqUkNKTmtiTmdaUWVmZw?oc=5</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -2791,27 +2791,27 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>How to spot fake concert tickets on social media as scam victims lose hundreds of pounds - The Mirror</t>
+          <t>Can Southeast Asia extend its AI data centre advantage into Space? - Lowy Institute</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 09:55:00 GMT</t>
+          <t>Fri, 13 Feb 2026 03:04:16 GMT</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE5RVDFyOTVZdzZJTXR3RHhXNV9TSVdWMXkyUjhiSU95VHV5OTBMODdfU3FZRnhyWkswVzNweXBJcmwyYTJGcU04Mlh4Um9PWnZtWEJOeEFET1d1cng3dTA3NWxLMlV0ZDV6YnlGSEhXU1FRVVlSNDlDZtIBfkFVX3lxTE05QnA2ZVFleTJHbXJ2M0o1R3V3R0dnYVczdTRWSm43VF9RZmFadDhkX0ZqRzlBQ0pWMTFjX2ZmcXkzVnFFUURRZlNiUG0ybm0wX1dWVi1HTmVKYUpCVy16SHE0SThzaWxfUjRrUml4Qng2SFBSd1VMLVJOczI2dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOYnZsdVNxQWduYThyX3pRVmt6STV5V1RBalNvRV9zcUIzZ09yenNsa1J6SEZwR2libUhnZ2ZCdGYyWE1tMGxuV0xlOVZjLUhOMjdOZl9wTHVuLU5rY2Jpb25jU1FFZFYzaHBOOFJkYmpwZVRXSi01MmU1X2t3X045OEVEcHczWVFzSFpCVFNTVDZIblQwNzlqcmY1RGpmOXRtVEJDX1pxdEpKdw?oc=5</t>
         </is>
       </c>
       <c r="F80" t="n">
@@ -2821,27 +2821,27 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Canadians lost $43 million to spear phishing in 2025: Here’s how scammers use social media to target you - Inside Halton</t>
+          <t>EuroHPC Deploys Euro-Q-Exa Quantum Computer in Germany - The Quantum Insider</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Wed, 11 Feb 2026 20:30:00 GMT</t>
+          <t>Thu, 12 Feb 2026 20:47:42 GMT</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQWUVpX3VudnBBYmUyR25fS3R1SGwtNFRZenh6MTNic3BYdi1kc1pxekp6c0JLSVF6Z01ZNllpVi1fZGRiSTdjVS1yWWtMTlVmRWZVLTRXNWNYWjExWFZscEoyUktpdk9uakxkVnpMNG0tMXdQbDExT2c5S0h2NFR5Yk9STFhCUVJRalF0ellod0F6bVJVT2NLWEotbURUOTZ3MDJPV3FvUnZSUXRCNnhxUTliZHc1OF94TDdRUWZBbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNQndvQUV2d1duZVVQTGtySmktZFJBQTIzMXIxVVQ0OG90bFZCVVhLUzRObFQySDZhMVRscXRDcUdCYVdmSkFzUy15ZmZTenZkMC1OVXUyWEZib2pEeVBVcWR4bGdPUFN1ZXQzT21Ka2UzNUhOS0hnLUlNQ0ZOQU1UbnBSUDN5NFBuVnFucDBBSjltRXN5X2g3RQ?oc=5</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -2851,30 +2851,510 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Video: Opinion | Is A.I. Coming for Your Job? - The New York Times</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Thu, 12 Feb 2026 22:08:20 GMT</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOMGE0dE1vSlhiT3g3SXBzX0pURXRydFpTdklXY0EySGF2ME94STZTVE5RQjMyNVYxaTUxWWs1UlhoZWdyLTVub2dmV1B3Ni1wRlVIb2doYUJ4QlVkd2tEMXlZRmV0LXlkMUZDdzNESGFBcnU4TW9BZ0JtQ2xYamphWE83bWpSaXN6WVVtSw?oc=5</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>AI and robotics researchers at ASU work to keep people safe, healthy - ASU News</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Thu, 12 Feb 2026 20:45:18 GMT</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQOXBrdXc0Q2FMeWU2N3kwUHhCaE1iaUsxUVJWSkE0REpkNTNhbGExUEgxZEhudVVwcGNfbHJuamIzV1pmcDFtR3RuZDJBdk1EMnJZdXUtcEQycklSUzRoT01CV0cwblJQaWRYS084Y3piUFVtZV9Ha001UDlzSnFaR1lCcktfZjlpTXRsZ1c5Q3lvQ2V1Uml4NVVyZTRxWXhDaW03bl9WMjFaWGdQZHZyZnlGVTI?oc=5</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>HENSOLDT and Helsing join forces for CA-1 Europa autonomous combat aircraft - hensoldt</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Thu, 12 Feb 2026 13:15:02 GMT</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOOU83TUMzcUVhR0FaMFZZTWM3YnBxNEFlTDRkS3lETGZwd21EZHBKOW9FeUhNQWtKV21FVUpfVXRiVmdYQmNJVXAyY00yUTBsTFhmT2lud1g0Q2x5a0h6X294ZHZmOTZuSDB3N2cyMUVTYllqX3VWdWYzZS1TTEowQ2RpcnowRHJ5aldsX05jUHl2bXNVcWtzU3gydG95WDRZWGUwTV9maVU?oc=5</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Microsoft AI Chief Sets Two-Year Timeline for AI to Automate Most White Collar Jobs - Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Thu, 12 Feb 2026 23:57:39 GMT</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9BT1BnaUNvNjlaSGluX1c3V0VTR1JEd2tteW9DTkxtSUJraFVsbjk0eXYxazlGTDNTYUtxZGpaMlFJSWh5Tl9veWF5ZGlycGZyajE3c2I4UVB0RFVnUU44WWhHcGQ5dElQcXdNTnI0M0t6MTVfSkduejFOV2Y4dw?oc=5</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Opinion | Anthropic’s Chief on A.I.: ‘We Don’t Know if the Models Are Conscious’ - The New York Times</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Thu, 12 Feb 2026 10:06:28 GMT</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNOWhTaVhtLXZNSW9JcHRqd242aC0xNWNZSlZPczJSR2dNNS13RDFzR0FMMk4wcUJjUkt4alltTFhhQk5VbWdKT2RzdzVpa0EzbzFycVNiTWhsTC1Zb2t3RkNEZW8weVY5bkNDVkhtMDMzNVA5aVBQdVZ6Y3phazNEbXVQUnFGWGJMUk1zaGYwYjVqQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>HOK Expands Leadership in Healthcare, Science + Technology and Sustainable Design - hok.com</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Thu, 12 Feb 2026 14:39:31 GMT</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPXzgyY0liN3pCSG5DUVk3YUNlWm5JWFdWSVZtSXlDV1VqYlEzMkxtaWZfdHN0TkNLWUtJbm9ZazIxT2kxcFNPN0d5VWtWeVhFQ1pyOGl0MldrdzhvZWI2U0hqc2hyZlY0c3Fpb2lhQUlncjIxd0JQN3pYY1ZGQmtKT3liRjFRSTFYVU1QdWwzd3FIVUtGTG16cTB5WHFkQ3phc09FanhwNERlOU5ORFlaMVJn?oc=5</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Opinion | A.I. Companies Are Eating Higher Education - The New York Times</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Thu, 12 Feb 2026 20:00:07 GMT</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxOejlvMzB3NnlBUE44aVc0VmhMOWdrU0JMc2JuakhoOXFybUlqM1pzV2k1R1U3RnJuY3J6elA2RnRncUk4SE5uOVhtc2lPUDF6d2V0VWY2VHhtTy1ISGR5M2xVZmtoQms0Vzh0cERFUzJLbmRCZlA3UnJxSmpDdWRjaWtjbw?oc=5</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Insider_Risk</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Cybersecurity and insider threat risks - Nixon Peabody</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Fri, 13 Feb 2026 02:43:12 GMT</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNOGRJSldlcFBxR2s4bzg0SjJTanZVRV9BSnUzaWtxaTVkc1BvbUhmMThnUHRyTEYxYzhrQmZiSGxYcUIzSWV2eGxsQ3VCZ05SRG1kSHNJRXBVZ244VTRhYXE4VVJtQnVKWUpENFV3QVlVOEhXNGl3bkp1OWVsLWRHbUw3WjROdkJkSkx1N3oxQXNyeld3Skhjelpn?oc=5</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Insider_Risk</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Fraud: Crazy Stories of the Often-Forgotten Insider Risk - MSDynamicsWorld.com</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Thu, 12 Feb 2026 22:51:02 GMT</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNNUxkNmNpcUo0NGNDUWpDMTFrZ1ZTaXNhWHFnaUwtYzhGenZxWWE3dEdCeTE4eWw3QXZ4VlRORkxRaXRXeXhFSzF5U1pLYXZxS0hJWUpZU1NOcVVxTzljQS1yeldHbFFSdW9Oa3JFMjVlMFNOY3BwTEZiNHJDQVRRNUtfZXBQQlI5Y2c?oc=5</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Insider_Risk</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Data Exfiltration Market Size to Hit USD 47.26 Billion by 2035 - Precedence Research</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Thu, 12 Feb 2026 15:27:40 GMT</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE01eVhuYXVSaG45cVNqbURtMXlEMzhQZ0hKRGNyVWpoTG5PX1R1SGRtNW1IVUlMeFBwbk8ta1VkS3NrYkNzTmJxZ0o5ZkItZ3VXVmRMWHk5bXp5UTJtTGxfV1FqSi1IZXFXWk13?oc=5</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Insider_Risk</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Shadow AI: The Invisible Insider Threat - Security Magazine</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Thu, 12 Feb 2026 09:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNeV80bTF1aFhfNjdfTmhjMFZ5VGN6cW5YOVZQRHhVMUZaZWlKQ05qQV8xVDVwQVdFZVI0dl9QLVZMUmxCTkJQT1RNN2tfNWtwdUdhQjBaZXI2eGRpTU5BRWVmbWhidmpFbkUtbTRTb3pHVFplSU1TUjFVQzVkVTNILWVaYVF5UjVqSDVrVDZSUDNNYTVKTjlSSW1VLUgxa2xmSXJXSHRwUnJGZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
           <t>Fraud_Scam</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>The anatomy of a small-town scam: How glib talk, social media reels &amp; smalltown dreams fuelled a big scam in UP - The Indian Express</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Wed, 11 Feb 2026 15:46:00 GMT</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPYnpYSDdLYmZ0Wno3aHc5QVJpWmF4Vzgzc2tJTzE5QmNERE96VWNBVXFPQUdNQWxaaWRsU0N5cDZMYVhsaUpCRDB1a2lrNDhaNTNIUUVKSHBCZlVmNkRqRGhZUkRVYUE0UFB0NTNROXFmLXZaVlRfV3hjbXZqbk9CQkM2LXlZUkN0UWZGd1JHczlsTERNRGU0REpQMWIyUkEyZGdiekNNbWdOdkhwakNsTUtFb0dqOVM5cUtyV1A0Nk1KemtxWjBtc0VmbFZ4c185VlhlV24zbjBDc3c5djF3Tzd30gHoAUFVX3lxTE1RUGJJeDBXajEtQ1VmX1ctcTdrZ1BXMzhTX0RDNGQwR0xRVUwxdTEyWklxRlNFTGppb1I5bWwwZWhwYzdTZWVSRkd0YWd1ZFZUNngzaVF1bXJlaHdEdjg2cnFPWk1QYS15ZWJRN2gyYUJ4TU9UbFN3TGxMMnB1anJaYWY4MDJxeGhGN0ZoZ1ExMEozcllUTm11bUhNX25pbV9yNzlteS0zNGlOYXdvNG84UUUwa0Rtc0FpaDBVbllIZDBaa0JOamdISV9HN1AyZ211RUdVelVKZDdxeHlJU1FlZHRKck9UMVU?oc=5</t>
-        </is>
-      </c>
-      <c r="F82" t="n">
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Social media platforms now make nearly £4bn a year from scam adverts - This is Money</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Thu, 12 Feb 2026 15:59:20 GMT</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNZTFLQWVHUk4yOC10QTVDZm9GUmxRdjB1SEE5OS1MZUlhWk53ZW1SMjZHUkJ4WU1hZ1AyTHRpdnpIZEdORi1DU3h5azVEUTIxWEphSUQwakhxWFVCdFdOdEFoZ0tjMkN6NXZaVG9fRHVMNlBHaUsxbDl3VmwxXzJLXzhUTkhoYldjSmZxenM0TElyT3FrV2ZVblAweUlRSDFxR1ZlNDNKZkhWS3NOUkFENWE1OEd2TEV6NkRRVmVObloxbVBmTl94V0NR0gHPAUFVX3lxTE84SXZCczhLaHZrSUM5a2EzX2lWdm4yUFRnMVkxYS0wMUltNEUyWGRRMVVjZWE5Vk1HZDYtaHE2U1FsTTF2X2JpN0pPbUJibWozR1FRSEpDMWU1OGJ3Q1BLRUNxdTdwbTdtWXVTelIxSHdTNVE5SmRnT1FHSk42RGt6bzAzQ0daeGYyWXZlcWlYVkRXM09WUjBDOTF5WjN3V3ZHcFliWVoybG1GNF91aDVLY05BanlzRERnT2FxSXlPUkZWSjlnbkUtZUYxd3BTSQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Google Says That Scam Tactics Are Evolving Through AI Usage - Social Media Today</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Thu, 12 Feb 2026 17:51:50 GMT</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPVlhwZUxLLWZDZW4za1BlZzJLaW1KTlAyd012WGEtb2pGeXZGUUl6RF9rZUtyeG5OS0hNWFI4VVBBOHpjN2RHVFpxNnpnUUhXVFhWOXRsMzlRYzhwYjZpNkZyQzQ3bWxuRTNhaERIcko3cFFsX28xVVpZeW9pcm40Z0FMbkFNT1d1VTBUWWt4Qy1DVW4wT0lqSmRIRTNIVElmYWlaUTczMnY?oc=5</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Payroll fraud: social engineering and identity theft target employee paychecks - SC Media</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Fri, 13 Feb 2026 00:17:10 GMT</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNRDg0TFo2VkhXMTNRWGRSWFV2TEdQeng1QXFONGdvNzhobXBUa1o5a0ExeDFvUi1IUnBHVG1SczRSeUVTZk5pWm0ta2lHVHlLQ08wRlBGZ2JtY2FNUmIwUUlUU3RYNGgtWHctaVdMZmltQVNDWmUxTW52UkZZaHo1MktWQ3BQRGM1aVM2Uy01UG53bDU5ZGE5RWljSElubnpBc3NCS01QVkRSTWs?oc=5</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Japan crime rate surges as fraud losses hit record 324.1 billion yen - 朝日新聞</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Fri, 13 Feb 2026 07:21:00 GMT</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE5Eb0FCOFFZd2tQZ3o0UFZDVWhQZmd4aFJKcEowTUMzWjBkSHBnX045ekx3R1JTSzY3QncxS2ZuMjN2WWN2U0N2ZWhsejJHSHlhTWgzQ2Vn?oc=5</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Bipartisan Bill Targets Scam Ads On Social Media Platforms - Law360</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Fri, 13 Feb 2026 00:58:00 GMT</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOaGpCRUtIb1RleFlCVDZJQzFueDF4VkVPS3V5dmtJSWtqV2VVRW1ON1U3OFBaSXh0M3BoczRlRnA3OFd4aXVNSnFFamhIWHU5Z2R1SnU0R3ZwSm05MU1fWm9qR3o0V2RWWDFpYzZ0MVJDWDZ5M0lOck83TENvWjk0eXdQeF83R2lmc3o3WFBsMGN5ay0yOHROclgxTVlsSGk20gFWQVVfeXFMTnVXTldxXzdENjJZV1cwLUx3a1B2NDhtUHBTZFFLelY0dHNzVExQRlBNUGgtV25mMWJjUHVyRmhmMEYwTVZsbzBLNHBucFlmdUNZay1NU1E?oc=5</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Ramstad: With $1B vulnerable to social services fraud, Minnesota needs solutions, not noise - Star Tribune</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Thu, 12 Feb 2026 17:55:29 GMT</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNckJMVXhCSHJzQ0w5SUxmdG1FZm1lS29pbmo5czdzT3hpbzVVOWo5TFF5ZXAydWJzSDFFV2pBRDMzRjY0cXJLaGVSOER1TThuZlM4cUhUNkxCOGVfb0xkZS11OVBPNWdyc3djZ1UxQ24xYzhldURiR19pMUoyTDhhR3pnYjRIQXVGRVZoN0lxaHQ5a0U0N1FKNkMzcVpISGNaVWZWTlc4dzJPbDJQbFhjeWFna1BKUEdRR3h6SUZFSlZyNzA?oc=5</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
         <v>1</v>
       </c>
     </row>

--- a/data/daily/topic_feeds_daily.xlsx
+++ b/data/daily/topic_feeds_daily.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F98"/>
+  <dimension ref="A1:F89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,17 +461,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Scottish Government Spinouts report sets out integral role of universities in national research ecosystem - Universities Scotland</t>
+          <t>UK: Analysis - High Court ruling that the Government’s terror proscription was unlawful is a significant victory for human rights - Amnesty International UK</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 19:21:50 GMT</t>
+          <t>Fri, 13 Feb 2026 17:05:20 GMT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE5FMHlsQ1NydER2N0hyZ1FSUjZqUVh3ZV8tSGlwX2tSbTdkaGxiMjFYVFlRTTdHQnctZUd0TXI2dnJYam5JYzlTNTREYmpmSzg2Uk5JaHBvVi1SWUlWbDg0elAtMHlLYjl0VGdRc2xTdHRvdHM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxPTF9yOExzZ0I5aU1LcERYWUpGNGxWRWw5RU1RYm4walpYMXZrU243alhHQ1JEaGhKODF3c2J5b01IWEF1Y05GZWVqSnN6TlB1WVB6LVlXaEtiRFJxeWFrLTlQQlJGNW5nQ0ktYktaZzJqakFqUHhmUTVpa1o3S3lPZjNlczhxNW5LM1ZIaEtRUjNTcDhmMnE5RmRqY0pzVVgzWUU5YUxsNjBLaVprdU5fWkZlMUtYR0ctXzk1XzFMT0NvcXh0N2tOQ2FnbHJzSVRpellsTWNjQ3dFUk12am1nVHc4VHhaTGlnR1NlN1Fya0hnUQ?oc=5</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -491,17 +491,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>The Government’s new approach to addressing the legacy of the past in Northern Ireland: NIAC publishes response to report - UK Parliament</t>
+          <t>Ruling against Palestine Action ban is embarrassing defeat for the government - The Guardian</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 14:20:53 GMT</t>
+          <t>Fri, 13 Feb 2026 15:40:00 GMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugJBVV95cUxQc0MtYzVyVlZESWtXdnZTM2R4ZENNcEIyYUN4OXJrQnh1RVhGZ3FMYzBIcGFnYk05a05RQlJGTEFHb2dPSFFTc3FIa3RTTFZRRmdPcVBPUmVvUXF2QUZlZUo0N1lFM2ZHT3VxZlRUZHJ5Wm5oSnVURzZ2MUNseDlRaGxkWTJudzRlV3h6X2NPeXg1WkdHRXNZV2Z1RE95UXBBdHV6SmtBbTRnaVhyZmhxLVIzWlZRQS1mWXdvN0ZQNVhGUjdFYVRZdGloa2VnRUZDb2pQR3RCYTcxZW1kNGZwNktGWWFTTW1ZUGNiUVVVNXJIWTRkYVNaMDZFZUdXQjNvdlVSa3lTOF94U1NXQklDNmlwam5wRk5xRWhmTFZpdUZmcGFkLUIwOXhmREVGSC1Uc3ltcWVNNXFXZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQLWt3WlZ5bjV2bjN4eEdzTXVKMjdJOFZOM3JmR01HRV85WEdwMHZZRGFYbnA1YTJ6ckhnQ01BUEpzS0pXQWE4VHkxekh3dEtBaTdSUnE5bnFaQWlHYVM4S3drSk9EaGU1TU14TDN6ZGVqcm53anFEVGRXUm5Hb19rY0VvQnZGNG4zbHp6MEVKbUEzQmkwWURSN2RBSmdSMUR1?oc=5</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -521,17 +521,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Franchise market needs reform and accountability, warns new UK government report - Pinsent Masons</t>
+          <t>Tony Blair’s thinktank accuses Ed Miliband of driving up energy prices - The Guardian</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 15:30:17 GMT</t>
+          <t>Fri, 13 Feb 2026 08:31:00 GMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNbjl1bVlwNUUyQmxjX3hSdFVLbmJqbUs1SzRKWlJhblNyNmRIN1hlSEI4Ym11Skxma2NIQjlOYU9icjVyOWt5YlZWWGZSUVRfRV9EaFlxNnFUM000MTE1Q1pMYmlKd0F6SXZlcVVzb2wzc0VLSlFNb3FPTXVKWXdyTmw4X1RjaEVvZGtPdmtZc0V1UDRqbnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQYmpldzZiZWhtelBsM2g1bnE3c1daS0lqdTdEdW9pWmkzMHoyXzFrM1RrX2ZVWXBpMXE3M2Z1NzNaeW95MDhuTlFNT0puaXU3TkVnUU83R2xBOEdoOUtISDhIalJ2TEpIOUgxOVA5OXFzLW1sdFRqUmZKT1RhODk5MlQ4RldpZk9QSzlzbEI3WmFlOWRmdWhEbzVlaUhCNUM4SXU1WjJFX21sejJu?oc=5</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -551,17 +551,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Grid upgrade could add £194bn to UK economy - Arup-led report - The Engineer</t>
+          <t>AI Legislative Update: Feb. 13, 2026 - Transparency Coalition</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Fri, 13 Feb 2026 07:05:06 GMT</t>
+          <t>Fri, 13 Feb 2026 21:39:38 GMT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNQjFVVHpMdGJkZlAwSmM5eFZBNmYzTllXbEcwLUtOSjJTTHJ3a2tuQXpOWkQyZjZfUFNobENOZmU1aVJzNGdkSEp4OUdJOU16b2xjZWxrcTBtWmRoLTl3S3hpcUx5RHZSeVpHOTVybldSVFVBdXI1Zmotb0tBSjhOWmpRWktjWWxNMjI0WmZEdDF6VTFrbjBV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE5Xc0NCeTFHbGtTQjJQNTJYRzFSOUpoRWF0N0ZzQ0JNY1p0Z3MyVk9fRFJEcC1GZDZwejh6aUVtNGg2VndMS3FFZjZUQVJpLTlsVEhNRmVUTnBWam5RbUNjd0xZeUhtTDJMa245cG5yYlBLeWd3N1ByLU93V2dTbmM?oc=5</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -581,17 +581,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>"Strengthening Regional Policy Dialogue and Partnerships on Solutions" - Regional Socio-Economic Update, Bulletin Volume 2 - ReliefWeb</t>
+          <t>Implementation of Government’s Equality Statement progressing – interim report presents outcomes and impacts to date - Valtioneuvosto</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 09:03:18 GMT</t>
+          <t>Fri, 13 Feb 2026 09:05:02 GMT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxQazM0WDBKSWZicjdEY1Y3VlA1WUdiMEZncTRHRkd5LVFHVk9ya2VIOTZubDI1c1BFOHI0WGdxelI0bjhSanZXbm5BWWdoaEJEblRRcURYWkhCaEtSYkhBTElvdUFUNWFid19hQmJwUmxvUGFETlMyWWw2TjFLRm4waDluTkhzbzl3dlAzV29iSUY2N25Ia1czZXBoYTRIX1gyb2NYM05RX2Z4cG5hcEl4ZjdSc2tZOVlQaS1aTUZVTnA5VHJaUm1wTUpfUEttYnM0dFNKYWVUQmRqTmdfcm9IOUw4SlQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxOajZVZkhOZUZ1V09vREplaFRpRnpEaXNhZF9WNnF5VTdXeWJpelU3dmdhWnhINlAzVWx6NEVVMnV5WGh3UVNoekhrSkMydXNlQVdHQkpYNVExUWtlYkxSallfMkZmWHMxbGhnMU82Z1JhTGk0SGM5V2RqdWoyUE8xSVpmMXlhMzlRM3dIWkdXUUJsT1A0WXFUVDNsdWNHc2NkU2tLaEJNWnk0U2RFaWFXd0dIYnR4U3VEakZBUzg5WVpEencyWDZDaDZHNXViNm9tc0dhLXNjRV9Zb1hVSnc?oc=5</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -601,27 +601,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Current_Affairs</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>The January CPI inflation report is due out Friday morning. Here's what it's expected to show - CNBC</t>
+          <t>Donald Trump plans to roll back tariffs on metal and aluminium goods - Financial Times</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 19:55:30 GMT</t>
+          <t>Fri, 13 Feb 2026 16:16:28 GMT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQdGdjVDluVHJZWmdtektHT2FicldYR1ota2w0N3NhcDJwTWpaX2ZSOHlCODBZbTF6VFZnOVVNY1JORjJIWlVRaGZOT1NXOGMwSkdTU19IaGJxWkUxWm5wam1rUmxnOUV3cEpyV3BRNGdFSTdDM2Y5Z19LOWxsNHd2bFpuMXdTLWRnWV9jLW1LaFk0Y0pTeWg5Zk80T2pUVkdqQ1NuWWlOTVNWd1o0ckRkUEE1MklkVDVnenZ5V2FCZk4tejJlN0HSAcsBQVVfeXFMTm9zU3ZLOE5PWDZUbDVpMDdFTC03RC1IckYtYTNRaUc3R1RDV3JucDdDLTk1Q0VqMEF1Z25pXzc3YkRWNkY3UG9GZVVsalEyQmFOb1E1TWgteDI5X09xbXdacWJ3Z2FsaHNOclhqVXlRWEItOUVQN3QxeGhreE8wcU1mUmxVUDVHSjc0U0c0dXgtZy1fZUNIYXp6Zk1NSDcwOUdCYmJKdEc2UV9JcG9LdU5qRl96V0FrYTU4RGVCQWQ1TVh5anNzbWlGcFk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBxemx4UjlSMGRnb3p3UVV6T2FiT0I4RDk2MEF0UlQ5TDl3Nm45cnIwMXN1WTlPQ2gzWnRxdnhOb2pkZUo3ZkRhYzJuZ1lKLTRiT2U2UWxSOXZ3SnNiY0ZSYVdOQTlYblZEV3BKcjU0YXI?oc=5</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -631,27 +631,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Current_Affairs</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Government issues update after hundreds of thousands sign by-election petition - Manchester Evening News</t>
+          <t>Shares in trucking and logistics firms plunge after AI freight tool launch - The Guardian</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 19:55:00 GMT</t>
+          <t>Fri, 13 Feb 2026 10:26:00 GMT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOTHNqek4tTS1mLUcyOGI0czZpUGpRR0lWeEM4ZkJlSTJheEJhYW91alVPNjhoQXc4U09nUmlKVU5VSmJPWHdlOF9zYktIRkc1S2o3NXUxNTRXOS1paFJubVBVd1BxVGlKWlpsYmo1NkFtV1d3emZqYkY1NHd3SU1SVVhTWFhlRVFNbXZYTVhvc1NRTEFzZDNuai15aUd3Q05mVmJr0gGoAUFVX3lxTE1ERVZucmNPSkh3STJXZ3N4RjJzWU5KMUNGRXN4QVFhOWtDV3B3cUZ4eUtzQVE1d1N6U1ZybnRlVVZzaTEzTWJWdzRHZE52S2FVQU1jb0pBUW13bDA3NXc2R2xCd1d4UE5fVkVQOU5OYzdMakQxUzV0S1VNZ2o2NXB3Xy1LT18wWFk2TDdOUkdDQl9YZUNJREoyVTdtWDNkU1RrM0ZQaWdVag?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOUS1ZcWYyVTFBNzl5MHhZMXRBaUtFbDcxcEg3elFISE4tUFhWeS15MlZJQ3RDVVdZY25MN0J1aUhndlh0LWlOVkktYW1aUk01X0MzbzRQQVVEWHRrYW4wTHJFaHVDTzc5T3pmMXNfd2RBRXBFb0tpbERuMk1md0ZnejhGRlY4aWN6MWswZEFiTlBJdzB1OEVyOUVMX3B0M2IxczFzLWU0aWVoY1AyNV9qRFMtVkFkWDA?oc=5</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -661,27 +661,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Current_Affairs</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Migration system needs reform to effectively sustain workforce and public services – report - The Irish Times</t>
+          <t>Port Vale v Bristol City FA Cup tie postponed - BBC</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 12:44:53 GMT</t>
+          <t>Fri, 13 Feb 2026 11:14:38 GMT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxNWWRlc2t0aWNkbUJNR0pzcGhCTW4zSzFkRV93UTAxRVZZc2Q4c0w0RTlsX0JBckN1ZGlKSXdySkRzb1BKanV2RXVIUkRkLWd5blhVQVNiYS1wM0FMcFdlYnRCUGk2Sk4zc3BnYUhNTHZ4NjRsY0JoMjh0T3FEczV2elo2X3B0X0cyVllOaGxQdUhXa3pVUjYwWnBrZE9aa0ZVTFl3ZVJJd0NScDhfenNZakxIalZ2ZWFIazlTQ3RQYnNCZ0pReFduMFpmWlpiTXhPSHc4dlpEa3dDZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE96QXZYSnRuWlJxX3pzQk5RYXYwTVJQcVhqNFN6dU1mT1JxVlRtVXAwcDBiMXdGQkp6MVVxRndSeEVYcTN0R0xXWC03MnJ5ZkNMQy1tWWRCeUFCZE1uZ3ZFLXBMOUtyUWM?oc=5</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -691,27 +691,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Current_Affairs</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ranking Member Robert Garcia Releases Report on DOGE: “Breaking Government: How DOGE and Trump Cost Taxpayers, Federal Workers, and Public Services” - House Oversight Democrats (.gov)</t>
+          <t>The cost of Trump’s tariffs Workers feel betrayed - UnHerd</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 16:48:14 GMT</t>
+          <t>Sat, 14 Feb 2026 00:59:16 GMT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgJBVV95cUxNTzB0R2JIMWtaN0x5cXVWRThTLW13OTRheDZoMXRRcVQtenRWWV9wb3A0ZG5EcVdvaHN3RUlyam83Y202R1NTR2pSbWVBN3NpRm4wZVNCZ3JnaF9WbXlWamUwNWdQU3pYY20tOUc2Unl3VHE5cjhBek5yWDRrQjhxeFJsNnVlRDdHamR3eXlfWlRIN2p0bmkzRTZRZk9sa0dNanpKTlhnV0lGV1BKSHhfUy1MQ0FwMHVGeGNHd29GaFpCczAtLWtfZTJUUS1vVktQNHZwSlR6emNIcHBoZzJzTXNQLUxtXzN5QnI5VnN1UlFhZk9aQVNPUHEtb2dNOHo4cEJEeTJOd1M2REgtaHpjaXJhRjJFSm0zaE02aGwyWDlfS0RQTkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE5jd0V2LXRmN2RiVjZEWms1WGh1WnZpY0ltVjZGb1dOTHlvNXNnY2pEcGNGVG5udHdpbHlQTkZiR2lsSUQ3b2tIdVl3MzJsWl96Q2pUWEwxZmJRSXFaXzEtSzZyUFc?oc=5</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -721,27 +721,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Current_Affairs</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Solicitors Regulation Authority offer update on intervention into PM Law group - Yahoo News UK</t>
+          <t>Fire service acts to help increase compliance - the Fire Protection Association.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 13:00:00 GMT</t>
+          <t>Sat, 14 Feb 2026 00:04:47 GMT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNMl9yZ0piaVVvWE55eGFlWmk3ZVhDR1B2Nk1iZEFUbVpwdDJKeDI2YWFwc0VWaXpTRktFdUo3UjkxY19BdkwyT2lyczY2NUFHSFZTUjdKVEc2NXlqakJnUWxfRXREdGsySTVwUEg4MjduVURWTEUyNFZpY3ZJWDljTlctOWpvZkwxdmFURUNwY0Vka2JNR3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNVE93dk94TlJEREVpb09JSVc5TUlCM2V0U1FPcWRYcThsdzh6Nzh6WFFjRGxGQkxWWFAwb2l4TDk4ZDZWNlpUaFVfaTU3bnpneXlxazZBRmNEc1VDN0U0VFdOWnZ2TDBsZ2taZVZWWlpyZUJtdHR2c2p3OG5fMlNIOA?oc=5</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -751,27 +751,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Current_Affairs</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mikhail Mishustin’s meeting with deputies of the LDPR faction in the State Duma - Правительство России</t>
+          <t>From property management to property compliance - Estate Agent Today</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 17:52:41 GMT</t>
+          <t>Sat, 14 Feb 2026 00:06:01 GMT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiS0FVX3lxTE91d1B5Vm9ERkpBU2pFLWZDVDJOeDlYalFaZHNnTkVhZVk1MHNoR0N1eHRkLU5pcXVvX1oxOHB4bmFQcTNONTJ2ZE56MA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNN1MtOXFEcW1QdFZ6NHBIY2RUV2plT2k5VDVhcHZHZ3p0VDBFUGo3Mmg0aTA4RV9FdTNCTG5BQ2czVWZ3M0gtU1RmUWVyZWhTTzh6QjZKWU1VRFEyQ09UeTJlM2NvZFJGQXNmOXZyYmRGSVVzQjV5d01WR0NVbl9vMEc2VkNBejQzbFMwZVdtaW0zLTBDTzJ1bERQVTc3eGFuTllIZQ?oc=5</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -781,27 +781,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Current_Affairs</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Government issues update on plans to extend voting rights to 16-year-olds - Manchester Evening News</t>
+          <t>Which Companies Shine in the Gartner Supply Chain Awards? - Supply Chain Digital</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 11:58:00 GMT</t>
+          <t>Fri, 13 Feb 2026 16:26:33 GMT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNTnZpQWRueFZiSzhlekl0VmxYakRHTy1SaTFrcDlQZFJGdXFrWGFORW4zYTJ5bUNhSHp6NVF3VHRlQ0wtSUNqbzFFYXRERjA1NUotSkFrb3U1QWRycmJzdFR5N1lFdENPUktVbktQZVRpUmJlRm1uRTM5YjlSb2dmMTZVNGhnVGI3ak5FSzluQVFMVWM3SHhrYTNmaVVDZnFT0gGmAUFVX3lxTE5WYlEtbDV3NHpHQUVPM3VfS0hZWTZTSG9pYnFOQk5nTzVCWVpkaTBrbml3alk3amt2RVk5Z1pLWUU0ZkIyRnVDbDJpM1NiUjRiSVkzOWZ2SklNLXRVMTVBNW84OGZzdWl0MEtxelBXc1pkSzM0eGx2OEVra09YWlRZaFV6MV80dTVlS054V2FaTmVwVG9TbVkyYmI4R1hYSHItYzAwN3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTFBnXzNxMEQ0T05TT3VoTGVMWWkzZXg3Wm5QVk1wMUp3dWhBOHY0SlY4blNDdmlINDl4Y3JqLVpBOGJMdi1wZkNUSmtMWnFRMFNqOFZmdVJ4OTJjWUhoMTdjQWlQRGRNVzlZa3BvMnBZVnExaFRlX1czdF8tYw?oc=5</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -811,27 +811,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Current_Affairs</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>63 Poets Navigate Migration in "From Here To There", the Second Africa Migration Report Anthology - Brittle Paper</t>
+          <t>Rusal affiliate’s sanctions defence fails on appeal in Jersey - Global Arbitration Review</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 21:55:42 GMT</t>
+          <t>Sat, 14 Feb 2026 00:48:28 GMT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPbi1YMmZ1cmZvQXRfYlhud1ZuM3JfVUIzUW1TU1lpcy1YQkV1azAtSVU2NkpOeG1rd2drTU1fYjhiQXRmTVo3RVl4aG5YRWlFRk5kaU1YcWRzQWl3dnRDdkJHS1JNczN0QlJJZzA2d2g5d3dCeWFLYmVGc2RScG4xRDV5ZVkyd2VVOU90WGFBNDFfeE5tRUVlcno0SVVFSWJkSWRrNjdMbG5hN2dQM2poLTV0aXdROUg3YnV0dncydFpHOGpmZUVF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxObVE3blFueGtpQjdsWXRyb1ByN2U0S2NOWm1pd0dGeW1WeWZHVTZFWDZpdFlKMmxCRmROQlg2ZEFQbU5wQmNJVUtyWk94SUN5akhabEoyT0I0MG5zczA0V3RvX2k2XzFqd2hGanFJeTcyVXFVOEU5dEtwSEd2ZVY5VHJwY2xsc2JDd1FrSUVXaWpxdGhEZGl4UTN5Q3p5VGpzOU1j?oc=5</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -841,27 +841,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Current_Affairs</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2025 Idaho Policy Institute Annual Report - Boise State University</t>
+          <t>Head of Dubai-based ports giant quits after Epstein links revealed - BBC</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 18:25:03 GMT</t>
+          <t>Fri, 13 Feb 2026 16:04:32 GMT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPVTJTcy1oLTlneE9hZVBkT0dYQkZLTzdZQVBPeVducmtDZ0dIcTRVbjRKVmRVcUdjNUVocmRTbTQ1VGNLZHdCNUloODZMMTl1Mlh2SndjYlE2a000clB3T2JLRWFvUWNkT2hTSkxJZ3pENEVubzdUcGxBeG5QSE9Qbk1wcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE04LUdOSDZzUDRKWGRLLVlyOUU5WXVHR2xQdTBpWmNZVUZGSjE4elM5X0dSSzVRSXNqTUNZdk5JTVpTUG9KQXBTbmF2cllwcGdfVjNjZl9yN2Zzbjd1?oc=5</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -881,17 +881,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Trump plans to roll back tariffs on metal and aluminium goods - Financial Times</t>
+          <t>Supreme Court set February 20 as next opinion day on Trump’s tariffs - Investing.com UK</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Fri, 13 Feb 2026 05:00:54 GMT</t>
+          <t>Fri, 13 Feb 2026 16:42:00 GMT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBxemx4UjlSMGRnb3p3UVV6T2FiT0I4RDk2MEF0UlQ5TDl3Nm45cnIwMXN1WTlPQ2gzWnRxdnhOb2pkZUo3ZkRhYzJuZ1lKLTRiT2U2UWxSOXZ3SnNiY0ZSYVdOQTlYblZEV3BKcjU0YXI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOTl96SDUxbTN4SDMxbkxNaW1KdUpXSmF5Yk5JMHd5dDY3WFo2SW1rM2tsdjJvRkltLVZId0JuSUpOTjl2ZVZTZXZHTGY2VFBXS1dVdXlhdGtuSWRkUTFPb18taEkxRzVVeDlYRHdRZkRmNnN0WXJ1SUJlcEx4Qzc1b1FtcTRQbTlXWUluWllNSkJzb3FLNi1HNnF1bjZJRWpRMDhYVDNJeVAxcWQ2OXJFb3ZaNGpBZGJlMXlSdlk1Nmw?oc=5</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -911,17 +911,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Who Is Paying for the 2025 U.S. Tariffs? - Liberty Street Economics</t>
+          <t>Logistics hub passed by thousands each day in Reading nearing completion - Reading Chronicle</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 22:19:08 GMT</t>
+          <t>Sat, 14 Feb 2026 05:00:00 GMT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOeFdvMVVjZC1HY3p3ZDNOVm5EZEFQNmNRUDU0OTVSVkVlNXlJN1VMY2xVRk5teHpST25CR1Z4bm9TaDlPaDdDYzE2a09FTVpyWjM1LUZJaG0yN0pHcGNhSnM3eTFqTTdWSC0zenVTekdHaEpZVGxqa2JkZ3l6WVRlR3JVOGNfeGdSR1huOWRMTGh4cXMyWklxdA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOUlNCTEs3RDRWMDdqQTNSbFFXaXB5VnVBZ2hNSEpkdkpORldSdlpPNnV5bDlFckxLd1FwZVdhTVpVZi1LbXpTVEFfSVlTVnNSNkNONzBzdzFQYmtkQmpPLVlhTUY4Zk1XTTJkZ3NMLXdBYVhVV1ZOanZod0RSemdIRkM0dThaMG1BUjdpUzZHeWdKTWNDZ0ZXVGFkQy1saUJSZXlxTw?oc=5</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Costs from Trump's tariffs paid mainly by US firms and consumers, NY Fed says - BBC</t>
+          <t>Swansea Researchers Help Strengthen Cybersecurity Across Semiconductor Supply Chain - Business News Wales</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Fri, 13 Feb 2026 01:07:59 GMT</t>
+          <t>Fri, 13 Feb 2026 16:41:37 GMT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFB6WnR1Mi1xLWo1Qy0wa3kyX0JZejk0TnFybjR3bWVfbXpSNzZnNnZZbTRiT3Jwc3BGblVWaFUtOXQ2cGpaT1NjRlJhRGQ3ZE1XS1hkWXdpcUk3dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQYnVZV1VWRFEwczR5bUFqZXBlTFpnbFBDTTJab2JsX3NpalZIT3JqLUlBUGRtUThXV3Z4X2tudTZOazJrb1NvTTJaZjZRVWVUTTY4eHhlMnZ4SnMtX2VLMjJCS0wtNVdmNURydnQ3ZGtKX0JHOEZ3dnNxbEFMcE5lU0FTeUc4UlhlbWhjSmhuU2M5WWhTT3AxcU4yc2I0NzhLY1Z3Uk5jSmVBVG1tbHZSeU1wLW4?oc=5</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -971,17 +971,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US and Taiwan sign ‘pivotal’ deal to cut tariffs - Al Jazeera</t>
+          <t>US inflation falls to 2.4% in January after Trump’s tariffs led to price fluctuations - The Guardian</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Fri, 13 Feb 2026 02:44:04 GMT</t>
+          <t>Fri, 13 Feb 2026 16:37:00 GMT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQUmRqRE5VYzRkcFdWSVBFWUlhai01Tm5wUWozdXJFMzFlSnNFRHBjOXM5TlVaNElicFM4a3ZlR2s3ZXk2MFBvT3lRSm5jWnQ1TkJmbjVTa1QycDdhUjlPeG0zNW9HZzlTZzFrdHhESHVtb2Z4cl9iX3JNb2dHVXlzeHJZajBQcWRXS3NzUXlwSlExclpESXBZV1N1Sm3SAaIBQVVfeXFMTjJDdDU2SEZVSmFOOEphQkdDeVBwbF9hWXNXdENTWWRIT0lScnRxNUE1MUJPZFlkZjZlZC1wLS1XZ1pRZzlNWW9sREhlZ2E2OHdXQldPTWxNUG9CRldrcTQ2VWZFdzk5eFhOMERLSVpxOUUxMjlLVGw4YXRyNWhNYU42R2VPamRtaHVDZldQV1dzQ3FlX3dDSkZfRkpITW9jREV3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPSEVyU19hdks3VGk4a3hDRDd2Y29tM1RtOHhFaTZtSmNpWDNHRGE2YXBXSlR4b3N0ZG9ldlFwRWx4T2xKTndoRnFON05fdnZqMVdtdFl0WEtTcGhxQ1ZPdFJXei1CeUJuSGI0dnZ3NEx0U0VZQWpSWmRvc0RYYlVhVEFnY2Rodnc?oc=5</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Future of Freight – European Executive Brief - Deloitte</t>
+          <t>Webinar: How SAP is Reimagining Supply Chain Planning - Supply Chain Digital</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Fri, 13 Feb 2026 03:04:24 GMT</t>
+          <t>Fri, 13 Feb 2026 13:44:38 GMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQUWVnMXBLdW5tX0JET0kyXzRaQWU0M29yLWx2SC1WNTFVbVliODJKNGlFX1lIbW9NWU9hUUNkVGhmMTlKUVBrWkxITVloN0dCbENnSGVoQl9TTkgxSnBNVnpOcU5LU2lHTHJpV0d0REFyc004VnBJdXlpcnlEaUVpN0VyRTJTdTc3RzBWUkt1Z0dqOXBRaG1UTHF4elNyTV84Ti0zMzlmSDFza242NHVvcV9XRUl3T29Z?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPUHRucGFfMExjX0pZSHlOZG1lVGxYT1IxLXhEODFqWHUzUjBkNkpYZy1VZFI4TVBBTWZBc0dHMWIza2xyV1JWOHhjeThwbkJxSExMSkhJQ1JrdzgzUzhLbHJMR3I3U25zcUxBMEdHUnB3UnNRMlpjQURTT1pndTBDTGVuUGF3U3RZbW5GeWVGSnF2VnM?oc=5</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1031,17 +1031,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>EBRD to exit Giurgiulesti International Free Port (GIFP) - EBRD</t>
+          <t>A big week for young people to see opportunities ahead, with port and council taking leading roles - Thurrock Nub News</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 12:40:42 GMT</t>
+          <t>Sat, 14 Feb 2026 00:38:04 GMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNSjVsbFJ5Rm1SOWI0R2lpaWpnVEZxOU5aR0pEdmwtbWxCb012SjNpTkItcXAteklqd1RQOF9BWkxLN04zTmtzSkxoLXFuczdnQU40aDlna2ZyWm9ZUGJpX0JOUG1OYlBQRmx0aFo4WmtsNGh5VjdkRS04Y1R5eEl2RlE3b19McnVYZnJwWldYRWZtX0d0eUQyRl9MSlNpeHRQUVF0c29odDhpdlNUdEd4UThWbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxORVZNSlJzRDlmS0w1bnZWTXU5WTdPZk83LUp2SHYtMWszbF9qaTVuejJnSV9tU0NBQU5CMFlIcDBUd1ZILXpZQ21JM1FkTzAyS2lJX2ltVktDNkV6Tm1DQnBkWFViTXNOWkFCOFlaMmtETmwyZW9QSjF3bGRNM2V2bGFabXlwa0lFTWZsMjQyYmx4bVM0ZmJVcUVsak01WUpILUtkUUJ6LWlabENxTER3TGlaZXBuNHdmSkFKNmQ5MmJsNWw0SXZmMm5UdC1fWnlWYnBjS1djMzAxTUctNnpXdmdGWmhXT1Y4?oc=5</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1061,17 +1061,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Northern Ireland exports to US slump as Donald Trump’s tariffs begin to kick in - The Irish News</t>
+          <t>Five steps to effective cryptocurrency sanctions compliance in 2026 - Elliptic</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Fri, 13 Feb 2026 06:00:01 GMT</t>
+          <t>Fri, 13 Feb 2026 15:09:36 GMT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPQlI5N1ZhT0pxQ3JnZnl3MFB2YXBlWlVFY1M0UW1yUGM4OWpOaTlkOWdEb1U5a1VqSDFmd2xJajJYdlVPVEZiNm1DQVFGYVRCa0hSdlZqTUNNeElBUzhHYU53MGZvMVZrMHVEVTNKenhZOHdQbTU1eUVYekNIZktlZDBON3ZaR3d5alRHOHY2aFdGRmp0QVMzRnpIYmZKQV8xSk5ONVhCbWlHU1hwVGh6V216TjlmNXdHVThpQ2owRnF6aTFxTmZuVkdPUWhFMEJkSGh5Ukh2aEdteldQTzZYbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNdXdwbzUzQ2RUSFNuaS1zWUwtZ2lHREdsU05jU3Rpdm02cVpoSDZEZ3FpdDlXVUl2U3ByemFZNDJ6WndjTU4zOWJURlA3M2g1SWpwSmNxRmNCaFZ5bmN3MWZDaHpvbFgxYk9PcHRqdGVkZmZTOFZMZ0tUNmpzX2JQQ0U3VDB1aHU5cW12QVloRlpEOWZBbnNnemdlemY?oc=5</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Agri co-op giant CHS completes upgrade to deep water port - Co-operative News</t>
+          <t>Exclusive: Binance fires top investigators who claim to have uncovered evidence of Iranian sanctions violations - Fortune</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Fri, 13 Feb 2026 07:02:53 GMT</t>
+          <t>Fri, 13 Feb 2026 16:36:00 GMT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOTnFnbHViQzkzTmRMbm15RHMyVkJncDA0ZjFZeU8wb19DSV9FYUt0VTRpQ3p1aUU5U2FEaFdpSW5QNGdPaG1yOU5Dc1FrVTY0bDE2WVJqS2NIT1RJVUFJSFRsTzlKUVhnS0lHQU5jcnJvOVI5ZUlsRGVVVW0zS1ZYYU5uSk44dm81aGlv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPeTgyeGpNUTlMWEVERGUzWXR5N1BJLXZTTzFsLVZBazdwMmVNZE1jeHNCUFRva21id0s1eWFzSE9nYndIMVY5Z0NWN1FwS2E5cWoyblMzX1ZwWVpFUDYtVVdSYWdxeG1zVDdLWS1lVzZYdXhPRU5GZmNKamNHTDNPXzQ5ejc5dUFrX0VkYmIxXzd5Y0xzZy1aUkpvNA?oc=5</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1121,17 +1121,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>The LR supply wave: can freight stay on its feet? - Vortexa</t>
+          <t>US eases sanctions to give oil majors broad scope to operate in Venezuela - Reuters</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 16:00:00 GMT</t>
+          <t>Fri, 13 Feb 2026 15:14:40 GMT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE8yRGNxeVJYRG5FVEY4NFhPMzBjR01YQlB5NjY2anA4QVdGTXcxN1BsNVlvLW1hQ0ZJVnlQTGFYQnA0OC1nanR4TDdJMFZiSnBlRDNFU29nNkZOeDQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNWXAxX1JoREhpWXNuMGJkeW5LdE0yZXp4MkVZal9LSlVFcnVKY2tOYXlBbW1KM28za3F1VkxVaTljVXRVaWpyMVhLNE5uTHI4Uzk3aHFmeDhLMXNVdl9rYUs2bS1PdlFHcVlRU0FqYXAydmFwSV9qT3RMRGRMb0ExdFdTdWFiZUpwekRlV3pMX1lQbzdaazVxSnpVQ2F3VEZmYTNGUFJYT0FPQmplZVg2ZWE5YjNzblhLWnY1eF90S0RWc0k?oc=5</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ECJ joint VAT liability ruling in Bulgarian supplier case - Global VAT Compliance</t>
+          <t>Tariffs, supplier fire continue to batter Ford - Supply Chain Dive</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Fri, 13 Feb 2026 07:02:28 GMT</t>
+          <t>Fri, 13 Feb 2026 19:45:09 GMT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxPSFdDVGdPZjlMcHJZeXU0OFE0aXBTTWh4TldRNFd6bHktSENHMmlvMFczQkJhbzNpYnNrUVFjX1p1WEJkVkg2UnJBZnZsbzRyMDJBd3dvUXozZGdBN25SZW1qOG9VX1J0cUtHSU1lNlpZVmR0MThGRHVmZ25UR19tTy1BVWxHVk5nLWxV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQQ1BQQWRNM19wMlBOUmR1M0hab3ZJeDNfSzYzX25fZkZNT1pJZlNhNDZsbDZuLU53dGpzZnJZeHNwM2FRS2VtczN4YU01anBsYnVJZDZxZUlDYmRlbFhRdWxoakg4Q05FZXhxT0xKU2Q1Yjh3RS1ZSWFuU3lZajhmLXBvbWJZWWVJNzNsYW5Cc05CWHNRMGc4SUpB?oc=5</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Scotch whisky exports to the US drop 15% after Trump’s tariffs - Financial Times</t>
+          <t>Ukraine Sanctions 91 Russian Shadow Fleet Vessels Over Oil Smuggling - UNITED24 Media</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 16:24:41 GMT</t>
+          <t>Fri, 13 Feb 2026 16:02:38 GMT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1IMk1LVEcwME15MjJ3aXRMVktIM2daTFlFaDFIVlZuOTdYOUVJdFlHU0p6cUhsSkM5T3JMRkx4U0piS1ZYdmVRUTJOOFpnS2c0YXF5Z3FCTHBsbWgyR3ZiQ3J5VXdkalhOanhBOVA5Ylg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxQOVNjMi1LZHJXTS1MLTAySmJKZFJDQVNrVHEzT2p0SWs5aVRKTndxYzRENzRub3ZPYkZxZkgxcnp4amdHaTFYZFFnMGpvb0JCNlFRSWprMVBFR25Hc0hFUEdlNWpEYi1tN1BIR2ZzZXE0MXZjbWlhY0ZLQndodnE3a2tMR2l0SWNielFuZ0xjTUZFT2Fyb0xNakpjQ2dFSmJ5WVptZ3pVcnpSVVJDcE56eE9n?oc=5</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1211,17 +1211,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Port city in ruins as storm rips through Madagascar and on towards Mozambique - BBC</t>
+          <t>FedEx Enters Hedera Network Council With Eye on Supply Chain Transformation - Decrypt</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 14:01:04 GMT</t>
+          <t>Fri, 13 Feb 2026 15:30:38 GMT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBjNnhjWXRJZVNaQmlTbW5IeEpmNXpXRzlJbFRBaGxPd0VqRTU2ZmRtNjlPMXdIUUh4YkktdlE2Q2lRTERIdl9HSV9mdlFnb2J0RFQwdXVRUlFDdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPMGVoSkczb0k3RjFaVEc3aHI2ekExN1NGa0JrazRMa2dacnc5Z05qenY2Q2hyOHJ6ZklhaXhyYi1sRVNNNi1YNFpQYUM1eEctYUtzeEp3Nmo0QVlGZHZ3Ql9CUWNmRXpwbkR3M1BBRzhPUFBkMkZBUkFnV1JyZXpIWHJUVkQ4QXRfR0HSAZIBQVVfeXFMUFFkWHNJU0FMNGpNeEdUNFVfeVoxbjhuU19zU3p1dXJXaTZEZEFib1M3VTVxYUh0aVdNdU1Ub3UwWThwb2gxRF9jdkJBcHRrMGJvUzd5ck5tYmt0NU1qWVA0NUMyeDF2TW5TMU9mSVZvXzhDQnE2dVg1Q3dIajJtakVCMHVkZkwtYVMtTmJtT25DQ2c?oc=5</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1241,17 +1241,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Global shipping industry sticks with green investments, despite carbon price delay - Reuters</t>
+          <t>Traffic easing on M56 near Ellesmere Port following crash - Chester Standard</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 11:26:08 GMT</t>
+          <t>Fri, 13 Feb 2026 15:51:57 GMT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPM0tXc19DLVBDM2FsVlVOd2JaU09VU1plODY0amRlV0JfWFNhc1Vac29aZ0JfQXdsRXJTYVQyWllCcmJWLVlSUU1POVg4Z0t0U1BoUE81d0xEaHB4SHlORERRbHhVMmxDV1M0d2o5SUc3azc3LUl0bjJTYV9ZdWJ1OFZJaU4xZlhGbHc5M2xkMFBNcUhTSXVWeXhKZ0ljeDUwYS0tZl9ubF85ckF6LWpfalhab3hPNW50b1ZfVUdmTk02QXpOMnhsUVRWM1BUcFU0Q1JWVEhfVTE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQYm4zWXpTaVlEN2V0Szg5dEc0dENMU0dJbHpGNVhKZW42dmktTm9rcjNEaE50a2huRTNCdkdhRkF6MV9aRjYyM2NiMjJRMU5RWXZQS2FpV2UzNTdidE1fNEF4UDVhX2pvc3A1enJPLXgzMFJtcGlLLU8wTXc1T3U1M05Mb0ktM2lsaVRLVko2U3dHVnBnZGFaUA?oc=5</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Project finance veterans target new shipping deals with investment company - Tradewinds News</t>
+          <t>Goldman Sachs enlists Anthropic for accounting and compliance AI agents - Finextra Research</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Fri, 13 Feb 2026 07:18:51 GMT</t>
+          <t>Fri, 13 Feb 2026 15:58:00 GMT</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQajhOZm5aekdXMjE4b0duclB6TXMyNVdWQ1pER19EM01UeWY2SkxzcmR1ZTc3aDNaVE9SVWM5YlFXNEE2d0Y5LTg2RndkLXo3WEUtdHVQbWdnS2VZMzdhMllTOHYyb193Ti1OaDZQZmhnQXZJRkg5aDVFTVVtZFdReGY5MmVoTXdsVkJBQUZmblNNZTl0aGhpRndqZExzem1RRGQ1bVRWZ0IwTm5ER0UtU0MxNUhwRC1QNTF5ZWlmc195TW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPSy0yR1ZyRElBZkdMM1JRdE16ZEprVTRIVHVmNTR6cHE1Z2Y4cjZiV3R3TFlnNVVRZ1BkVUdnUFhrTEVlR0JHWG1HZXlFQ0JIb1M4TnJBTjlMdXkxdmlZbTk3aEppa0NBZ0t4LVJGVHlWckVPM3kwd0REWjVJTU1tTXZHaFJvdThjcHN5QkI5MWJxd0xYYVlISGV5S1o1dURkWDBXYUZYNUxLdVpHdmZTR1VrcEE?oc=5</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US and North Macedonia reach framework deal on tariffs, LNG purchases - eKathimerini.com</t>
+          <t>JD.com rolls out logistics service JoyExpress across Europe to support its JoyBuy platform - FashionNetwork - The World's Fashion Business News</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Fri, 13 Feb 2026 06:37:45 GMT</t>
+          <t>Fri, 13 Feb 2026 17:05:53 GMT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOZmFrOG01U29xdURvaXRQNFIzdWJYbGRlbkdHblZhdThEaFRWenQzZ1VlM1pOR2Q4T1J0akpITUR1MlBWOW14UE9TNHZNNkJ2a0FFbGRyNkFlTm4yQzFTMm5qUFl3bWwxMXc1OWxWVGJkTWxFLUpfdjczZmo0N2RDeXlOYUZNMzNJdnI2R2FBdUxvQWQwN2dtUHRYZmx0czFReGljVE54aE5qRDZiQVZZeDRHOXA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPT2JIcW4xd2NMWGpJcDdMUlYxS3czMTF2TnBIVVBiTXZnSUJqbFN4dkJENjBaUFdoR3lJRG15eU4tSVdJbEZ2eGI3S1lXaDhDWTZDcWZ5YXdOaVBuVXI4WUhOWTVDNkl2MEljNDliZ29mTHdyZGp1cVp2dXA0N1lLMHFvZTh5NnpFX2ZobV94VDhGRndaZ053Q3NlcDhhVzNFV05fekZGbXhEWFowMjViUmVZdjlWY196NC1JcTdUUldUNHVoSjQtSlFfSlpyTVRERXpBTg?oc=5</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1331,17 +1331,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>One killed, six hurt in Russian air attack on port in Ukraine's Odessa region: official - TRT World</t>
+          <t>ECB fines Crédit Agricole over non-compliance on climate-related risk - Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Fri, 13 Feb 2026 07:31:18 GMT</t>
+          <t>Fri, 13 Feb 2026 17:13:18 GMT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFB1aGp4bWxfZGRPUHRtSjhKNGVtQ1Y3UTlVdVIzXzh0R0ZJRWx1VUd2c2FTRzc4RkJ0TmJHMkY3V1hLdk41R0ZqaFFyWDhOdl8zUG04eG9YZnXSAV5BVV95cUxOSU9rOG1CeUptSlZfSUpQQTNoN3h2WjlFcktMZFlFNmdfcjUzaWczR1RYNTJsOWFkMkwzTnMtNlpFX1JKXzVIWGt0RVljeG5qZzd0U3YyQktvZGpCNmd3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE05Mk0yZGVaZ0Q5TXFhbzQ3Q1B2NXNyeUc4bzR6amZid3VVOGw2LW9DU19sdS1jMEJLM3dPREVoN1hSTkkxcy1aVWhHRTZ0UkVJUFZDandiLXRFLTYwT1FZR0NjcTAtcFQtbXk2Zk9BUzlDbGQzdnJpb2lzRHFNODg?oc=5</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Taiwanese owner Simosa Shipping exits LR2s in $86m sale to Greek buyers - Tradewinds News</t>
+          <t>EU Exempts Chinese-made SUV from Tariffs, Ministry of Commerce: Supports Automakers on Price Undertaking Negotiations - Gasgoo</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Fri, 13 Feb 2026 01:42:40 GMT</t>
+          <t>Sat, 14 Feb 2026 07:00:29 GMT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOLWxlRElZWnVIcFVyZ09pQUktRGFLYldVSnY4M0FILW5ybnhNbE5vVGV3ZVZzREd0REYzaG5PMkNPQlZhTUE3MWRDX3M3bndqYk5LMkphdjhMS3RkeTZVVHJZY1Uxb2FabU5ZQnlTY2Q1aEphYW9fQ0hzckd5RGtGNElmQ1lwSTBvdWRPcnRPa0lvb2FmT0w1b19ONkl3Nm9qQXpjYjRBeTQzNzhOSk8tZ2UzT1J2bUwyM21uQnZ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxOWXJOWF9ZMEFKU0JmNFRLaUsyR0hBZlRSdlJsaUllYjE2NWpCZFE3WHBWMHRWal9wMHJmLWdlR2x1dDZYZXVORXlEOUZvVElRVGlYR1pGbk40Y2NIWDJXbVZQZ19EWGltNzhIRDg0cnJmZzR3MEpxaTNTRE5obGU4VUhuc05yc0UzcWJaTy1rNzBPeVBrTkoza2xuQzJLS2xLSzlsREtPU25VcEl3WTJmS1lhc1NHNDl2YW1oeU5uUlZGOURtcFEwcElFQVZZcEpSSHdaUjM1X2ZsY2o5QWFQUXkyb1V4TUFGMnNHNURMeUZiczJ4eUtzazZyTk8tM0Q2NGtYWUhBVno?oc=5</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1391,17 +1391,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Welshpool transport company co-chief recognised by industry - County Times</t>
+          <t>The massively underrated northeastern port city that is one of the UK’s most unmissable places to visit in 2026 - Time Out Worldwide</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Fri, 13 Feb 2026 05:00:00 GMT</t>
+          <t>Fri, 13 Feb 2026 15:52:01 GMT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQQ0lwdlN2TWRZRW5LT0NtZE55eWNOQW9QYVpBbHRxUEJWNkk0d0MycktqUVdKWGF0SHBUMDVVRmJMUEIxR3NvY2c2SlI4N2tvc0hyaU9JaUFOTUQxOWFDM19MWDh6NF82YS1DYmd2d2xJY2dlaF94VmczcXA1ejhveXJzZVN3MWVxbTlFeV9nckVzcHNJY0VKN2lPUnJuWDJURU1oQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxNd25mY1F3NWdpZGFDaVNVdUc5VnZjbklzaFVlRU9scHNzNnh3bEJ3aVJiVGt0R1NlVlZYNnJoa3Z5bWNFc3l3cHc1VTFId3dJNVJrVFp6ZXROeEhvVVZkeXNCU2owWmJHMTVUZk5yLVpXWW9ySldxeGpCeXFFWTJMM3RRcS1LUm5ILXZwQ1ZvaG5nUjlHbDdQX0dXY1llV05jZTVwZE9uTC1BdGNEeDJzZ3VDOXJ4Y1dnYjcxUmRrNlVSQUk1ejRTT1V4UWY4RER3UUhOcGp6UUJ6RzcySzRmUnI1VQ?oc=5</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1421,17 +1421,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Young woman launches career through supply chain apprenticeship in York - Yahoo News UK</t>
+          <t>EU proposes extending Russian oil sanctions to maritime services - The Jakarta Post</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Fri, 13 Feb 2026 05:00:00 GMT</t>
+          <t>Fri, 13 Feb 2026 23:49:38 GMT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxOSmVHRklMTFRTam05ZEFVSmFlaHQweDdCLS1nQzNHaU91OUdnWGp1SzlNQnhNa2hKT0FlTEZUUTNwR3phYThtbW16UGphUjV0LWRTY2NzUC0wb1JnT01QM3hjWWY2T3JaUHBxV01wUE52SWoyLVluT1A4WEtqVHJETA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQZFp0ZF9Ca2loN1NNdXpuUnhGN0h2d3VKYUpSeEEyVVpRX2FRZXFGcngyTHIzS05iR1lRNlJCMnVWVmU4Ui1pbUlnTnMxbDNWUklrcmpOY0N3ZUlmaWNMeG5tSTBZR1BCOWYxSmsyLW1YZHdJa1Q3SFFROXhNN0JxUG5WVDJRQkVjVU5BUW5GaTJLUUNTaEk1N2JjZUZGQmktRkNzWkh0RU9Falp6UUJqb3R0dEh1Uk9FalNyRg?oc=5</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1451,17 +1451,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hormel Foods Names Will Bonifant Group Vice President and Chief Supply Chain Officer – Company Announcement - Financial Times</t>
+          <t>PORT AIM FOR FIFTH SUCCESSIVE VICTORY IF WEATHER ALLOWS - Island Echo</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 22:00:00 GMT</t>
+          <t>Sat, 14 Feb 2026 05:53:50 GMT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQVk94Y1NBWURtZncyLUU4YkdvWnE3YlJXWVFpeTFCb3dIbGxvejhzbFRIbGJiY3J4am9tbFJjazR1THVsYVNSM3dtYWg3czA4aHZVcE5oek5FTks2c09xU3RMYjVwd2l5LUduemRKcEdPQWMtOTRCWjVPRXpOTXJCd0FleXVFdnpJUFNSVXJEeVA4Q0ZNcW9Pcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQVVl4WERicVcxd0N4MFN4R0N4SnU1V3FXejdLZ0V3Z0pBYmNMQTRhSTlEOU1rMi1YTUR4VGl6cmFSYXJfNHA5WUN2NVJoaEFjcHlncGZQcUU3d0JfMXB0bHVFLTF6eV9zT0J0aFNyaUVHVWNiUk90Q09tR3dTRlZCOTg3SWJtSkExRmZYSUpR?oc=5</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Oil Trading Giants Say Western Sanctions Driving Up Prices - Energy Connects</t>
+          <t>OPG and Port Hope to collaborate on 10 GW new nuclear plan - World Nuclear News</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Fri, 13 Feb 2026 05:19:55 GMT</t>
+          <t>Fri, 13 Feb 2026 19:04:47 GMT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPcTg4eWZZUTQ5ZjdXdy1ONkR1MVNDQkJXckY5NThNODZwei10MEhnUUM5UHJROHplZ01XRS1PNEhmNXluYlcxZFJielN1c2R4YnQyWEFxbG1jQjU2MTFHSWhqcnJwVWlsRHgzVFU1d1BFTkFabkJERzRncDlIRFp2cUtBRDl4blpRMnI2bGJxTEVXVTBJb1IwdFg5Q3l5b3ZrNE9nUzluUVZEQmVjUmV0dE93dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPQlFPNGZPUnVxUERlempaalNZLUNRb1dQb1ZBS1NESUFTRnFEekdrRzBtMkR2MFFmbmloWk80MERwUUdPMzVHSkpnS1VsNE80a09NTmxmWGR0aUgyT2d2bE9UbVlPSFBSN2ZQYktad19YX1FmbEtyckdlWVZTRGtuNEFrWmEtYVMtNUhVNkZ5TXFwcnQtTjZnUGh4dUxPLU0?oc=5</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1511,17 +1511,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New US Sanctions Bill Aims To Choke Off Kremlin Oil Revenue - Radio Free Europe/Radio Liberty</t>
+          <t>How packaging and logistics companies are automating their warehouses - CNBC</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 19:36:48 GMT</t>
+          <t>Fri, 13 Feb 2026 12:30:01 GMT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNVW9WeXpCN3ZGQTI1X1lTZUd5RjlUZEpPeEVtbUhEa1A3WW1SNVVZRUo5RkM4TzI3TmJiSS1YQnp6QkpySXB1cXBGeFZvZEtoZHBja1BjTjRnemhxVlNTLUNMSnhrV0htVVN1bkJjaEZueTVmTENvZEZYV3hEN0hjQW9zN2NQLTFlWXfSAYwBQVVfeXFMTkhra1hoSmo1TE5IeTZTaHVxYllHcWcwNjJmeDJWTHZaTWNWckotZU0yQ081MUd2Vlh5ZVVNMHNWNm5CSHdfREw4TkZSSGV5dkZyZEJhYlpTdlF6N2V5Z1ptV2FWWmlPVDA5alhqNlhBYWQ0MUtlS2YxaGZHMGFmdHI0Z2VpRFVEb096cjU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE54dUpmVUdsMlhSQ1BEeGpad2tZWjJwSi1qc3JwaXFVaDhsY0dVTEtTck1aZHgzTUI1WEY2YllibnlzY0hMU1VISGhuN2RhM3pUODV5eWVtbTRFMXNmbDNxMElqUzI1ZlJ6ZVlqRm5kYTRVUEo0bFk2U0lMa0PSAYIBQVVfeXFMUEdySHRicW9xUDJBbGp3QXNmXzhwOEVnZ1dtQlNqX2Fnd1VObVg2TUJ1Ym5naDhvVVVoRmJNUjE4UjFxdzl2anhCQUkxRmxwZ3c1WHh6MGNoSU11M1htdEJ2LUZOaXV3YmpKdWlfb0VZUC1COHRTR2lreEtha3BfalMxUQ?oc=5</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1541,17 +1541,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Trucking and logistics stocks drop on release of AI freight scaling tool - CNBC</t>
+          <t>As U.S. House votes to end Canadian tariffs, Alaska’s Begich seeks to extend them - Alaska Beacon</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 18:11:10 GMT</t>
+          <t>Fri, 13 Feb 2026 14:29:05 GMT</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNbzBqaWpJbF9OVUN6VFY3M3duWGZwbmNFbXc5ZVV3dzRYWjJxVmhPSzZzZHFURjFvYzQ5SE9Qb2pyLWdWT3JRSG5XQXNQVWJ5ZzdabXJDTzB5M19xNXZRQmZKSmtDenYwRHB3TXh0MFJvRzZzeFdQNnhfZnpweXNzRGZnYmp3NWtXa3FBc2lFYl8wTGpIYkl5RHlFTzVpN250d3M2TE1QODJuVHRkT3Q2V9IBtgFBVV95cUxPWUk3VlRXNkJobjROSTdQdldwM0lUcjV6anVNTVdFNHhsbFlzT3p5dTVibE1sQW55OFFjUkpxaU44VEdRbWlKR1JXWW81OWVxQ3NyX2ZmdlJuSmw0ZXk4Zm9VMDlkaG1ZSEdHSmRrNHdFRXc5bjEzQlhjUkttVmtFeEpGbzUzNmlnWUR4OUlpVjBfUzBrRFc4NTJyUHhQQWpxdG5oT0pfaFVvT01FTk5LSjlTV3daQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxORDJIWWpmdFlBbEZpbzhRZC1qUEFvNzc0VE1BaW0xa0duS1ZYdHQwOHptVW51R3hxODRoZ29WZU1uTVJkTzZ5TkRtQ1pXT3lvZzZlbkJxdHFvUGNubjRubUszaGZ1QXZkUnhpWjZ4OU9uU1JmU3p6clpFSmE3R0FRR0JsanM3TDFOT3lPWXlOaUhSUDNMekRUQkxuaUlBT2dKZGMzQXBLUnRrd0tSUjNxdQ?oc=5</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1561,27 +1561,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Six Republicans Break Ranks With Trump Over Canada Tariffs - Time Magazine</t>
+          <t>Police will not investigate activists going door-to-door asking people to stop buying Israeli products - Sky News</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 21:52:44 GMT</t>
+          <t>Sat, 14 Feb 2026 05:23:13 GMT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQZXNEUFI0QldRdkw5SFA0cU1MR190RHNhajlTNHQ5cnhLX3U1TzRVSFlLUHdwX0t1eWNmdk1YMFcxZVF3bkFGQ0JhUjRvWjh3emo0d1oxRnlpRUhyekxmV0dqaWh3YXNLdS12a0FMOG9IZlQ3NGowbElZRDliNTQ0cDZSaW5WQ1Fk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPSlNEdjN5ZFNCeUNrT3A3U3QxVlNNUi1GTnVyWEd4N00xLTNmOFlUeWFhdFUzdWVoQ0swTWVSV0ZRd3FIS09YZFl6OXFTUnlFaDFrZjB0ZnJRM05GTGV1M3VOUkw4dzdYLVIza1prSzdfakhmclNrcFZkb2I5c3RZX1h3OTVKbHZJNUIzaDI0WjRwQ2xBMlF4ZTVVX1BOTG4zUDJZTENnVmMycHpnLTdKT0R5VjFxZlV2T2hpU1JkSm4wUk5IbXF4SjlZZFdMSG9aZXBGUQ?oc=5</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -1591,27 +1591,27 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Compliance notices for McGregor, Jackson for social posts - RTE.ie</t>
+          <t>An ‘impossible’ situation or ‘unhinged’ police? Inside the chaos at Sydney’s anti-Herzog protest - The Guardian</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 12:42:38 GMT</t>
+          <t>Fri, 13 Feb 2026 14:00:00 GMT</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE54VUxUS2pCXzdOblEwX1hpZ1RDRXdnZWRob1d6cDlvaWhEamdBVWNyY01YMjl6aUpEWXZDcHdWRTFZVms2RWh6ZGR1eG5NdGtkRmFHN0pRQTJBWnlSeS1YQ3ZjZ014emgydUVTa1E1bGhTWmhSV1pB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOZHNuTlgtaXpDWUJBZVdQeFc0WDZiTnluX1EyT1dsVE9Xb3dWMTJRRVZsWWpOREU1cXhXUk1DSno0Q0VieVhQN1E1TXY0TlVXemRTekQ1N0hxUHQwNFU1ekV4SnVnZEgwcHV6V0NxaWV5YjJ5bkVNX3hSME9feEVMWG1qLU5EMnVnQ0VqUmloWm5BODFiSkhyQ21vUktuaFo4ZG5JVUJaS1h0N0ct?oc=5</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1621,27 +1621,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>"Compliance is one of the biggest challenges landlords face, and platforms are playing a critical role in supporting this." - Property Reporter</t>
+          <t>The George Floyd Effect: How Protests and Public Scrutiny Changed Police Behavior - - Political Science Now</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Fri, 13 Feb 2026 07:35:13 GMT</t>
+          <t>Fri, 13 Feb 2026 15:04:11 GMT</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxPOVY4OERWVXRHcmcySGM0SW1MT29ieC1ZSFZIdUFLLTB6WTR2MjE2TFNHb05lNUVUMnNnYTM0eFN2ay11NDVSek1OeXBESlFoRC1JY2lSV0ZWcnVhMGV5UjloY3lIYlF2RVE5MXg2X2lqVlJGOFEtLVFJTDh0Z1dsY05VZlBDYVk3Q1JVamFRRUZtb2FFN2phR0o4Qmtza2hnSVNOSHZMUDNERWdhRkJDdTlIUnNzc0FOaGxleTlhNzhJZVJOLU1odGdMdkpnbmMxZ1A3WkpmcDJpZlI3S1BOb0Mzc0laYnMzQkJwNFF2Z0s?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPOVg5aE1EV2hmVFVGelNGZUU5Wm0xNUMxclRYWjhjdXZCalpaaWVINDgtR2lnQnRNMzFIcWZ0cTdrRm5lWmpmUkd1bGJDaGdnYmIwOEhaNnFndWRlYnl2OXNpWl9BNlRzWEFTaVFfbllqS0lxejJZZVIzYUhyRFlLbUx3ZUJqYnpKTHl2aXdaQy05QTZOY0w5ODJKS2E2VExVTnJLN3hCaTN0MHlPb3BKaUFSMA?oc=5</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1661,17 +1661,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sydney police to be investigated by watchdog after anti-Herzog protest violence - BBC</t>
+          <t>Thieves strike at Wargrave property – police urgently seek CCTV footage - Wokingham.Today</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Fri, 13 Feb 2026 05:09:53 GMT</t>
+          <t>Fri, 13 Feb 2026 18:43:50 GMT</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5OXzFkVTl1S1RlU3h2RXdMTENxMXFlMVhHMS1PRVlOclFLSmV2SHRqcTBfVlJ4RU1lZUs5d3VRZThaVlhkLTdvYzVVZjZweWV4aU5LZWFWTnRCdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPMmdRZnVJYzFiN2pKSmMtTUdCREp1X1RwX2ZQOUE4aXJfR21lOXRLSjBUTkU3VVNSamV0UjZ4TnpJc3VkMklSMXNyTzRBVDFlSlpBeFA5NkxkMVZRcE9PU0YxczM3QU5xdmRfVDRNdnM0N1JLY3FnZnVFMlBGRHNGMjhDbkF4YTA3OTBaN1NONTFDdVM3NHNwMGpB?oc=5</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1691,17 +1691,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Protest restrictions – why talk to the police if it makes protesters less safe? - netpol.org</t>
+          <t>Australia police watchdog to investigate complaints of brutality at protests against Israeli president - AOL.co.uk</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 20:08:14 GMT</t>
+          <t>Fri, 13 Feb 2026 10:52:21 GMT</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNYS1vTFl5UmVIQmxLOWNpLXd6c1h0eW5XRmp5NWJaYXNjYVFMd2FRUkFIV3JKYzBJdGhxd1NTdVlmRURwOWVobHlWNU9HM053MUo3dktnN1F2TXZxZ1ZFb20yUzJWUDlkT2ctNHd3TVR3dWRsczR2X3BVVVkxRHJRczBKd3YwODhRbnNyRXdVZ2ZmV2k5UjJvQ19xY29iTERZbDdUR3B6eGQ5NUk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPWEp2Ul95aEV5VEVTUWZ1a2ZOTmtRZEpUS1dBNnByemZyLUpwaWp3YmdqbkNvSjBYcDVLckJ1anVfOGcxOVdWYVlvaFhrQjVlWXU1TTl5OGNVZXE0ajNhWmc3SUY3TDRLeDJwVW0yb0Zuc25PeXpnQmdFRlJRTWNBV3AyWXhid3d0N2JEOWFKZXZMbG5xYk14ZnBn?oc=5</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1721,17 +1721,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>EU eyes plan to deepen single market in March, accelerate capital markets union - Reuters</t>
+          <t>Ahead of armed protest, police stress respect for constitutional rights - IndyStar</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 18:32:34 GMT</t>
+          <t>Sat, 14 Feb 2026 01:27:00 GMT</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPcUMxTmVDNHVhVzc3Wi1QdUJtVjVtX0RkdzVKdjdZZFoxZ2g5a1NoZlhkYVkzb09QZlpXc0tDdklCMF85NDVGaXJ3VF82QWdCaUhwaU8yM0Z1MHhUX1JRUUFQRjN5YlJoV0NNUlFUTlBnVkVYLUZDWHpxY21zbHp5YjJKZDNrdTVZdF9CTERham1Hd3oyMGVLLXk2NlNwSlBkX2Mxa3cxa3dNclZ1Zk54Z0ZBbFhXVjN6T0xWRWc1OHpKaFk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOX1hGMFlMdS1DY3d4OVhkT0pWQVNxZ3ZMbmdVZU1JQkF3QVVqNWdHc1o2SU9ENFI4YUFVNTdzdHdvbGxTM3MyZ29XM0QxNWFvYm1PMTY2Q0NBd0RpOU5WNWxJcGpjY3hfMnJDZ0t3cnBJMUxOLTBZd1Vwank5UE5QQlVacWVoRHc3Tjk0bldQbzJmVzNNTy10b29aLTM2YmxXNFRqYXF1cGNrbmxPbUN1RHdoQTI5WG9PekxXcExiYkhmeUE?oc=5</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1751,17 +1751,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NSW premier won’t apologise to Muslims after police grab men praying at rally against Isaac Herzog - The Guardian</t>
+          <t>NeuroSense Therapeutics Calls March 10, 2026 Special Meeting to Approve Share Capital Increase - TipRanks</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Fri, 13 Feb 2026 00:35:00 GMT</t>
+          <t>Fri, 13 Feb 2026 21:59:44 GMT</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxORjh2MXZhMGRZc2xHNHZMNTdnR0d1TXZsUVVyWGZqOG9Da19kMnJJcVliRUItMksxeUVsT2ZwQkhlNG1MQlc2bkw5OFVTODFPUF8xZ0w1SFpwMDRFX0x2ZlBRaHBxTktrelp4Y2pDMG9ib0ROaGs2MjVYOXNtTkwxSTFzbjBqdnQ4YlBxWFhUV180WFJwUjNralI1bmN1Tnlud0lpMC1Vb05XbjMxZzVsTW5tR2taSkZGNXUtMWdsTEFZVDQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxOWFNibHZ3ZjVoZXRTWmRvbnpwVGd4NWlScEp6cHRPR05lZ0dORWZ5MDB2R2hldzJ1aWNYT0FMNnJDUlZROEV3OVpOYjE1bG5ORzMwS3ZTYWZtekpWSm55dDROZ0dyQ1RSdF91SHI4UzJhVE56YU14bENzZmpfZFE0V0sxamVTMmZ0ZC1tX1ZYcHpLU2hzVENVdFFXbF9MS003S0xqRVlVSjNsYnZMeGprVFk1MXpseV9QbHNnT19XWUEyY09sZ2ZJOFdXam84ZVpvRnQ3UENsRUhsLW1GTGc?oc=5</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Huge protests against Israeli president’s Australia visit - 5Pillars</t>
+          <t>Federal agent injured in downtown Los Angeles amid protest, police say - NBC Los Angeles</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 14:37:46 GMT</t>
+          <t>Fri, 13 Feb 2026 22:03:01 GMT</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQQjJFaUpWRV85NldNMUlNd3NHNnp1dEFEZldDRXEycEkwcTNCQmNwZ29URlJyODd3cFFLNzZVMW01WjdZUU1xcV91T2hhMTVWMENXeVpXTWd1ZXUtc2tVaERTd05UTEdES3NMUFRvWXRJQm41eHJmWTRRUy0yeS1RbUJLRWZ3OS1oeHo0dWJEQUM0dTZyQnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQR2FZRktuSkw5RU1jcVdId28zSlRwMFBsRlMtTmVVdDJvN1lQenpPWEplRXhaX0Nsb0RJVm1lTTNpVnU1R0pBT0ZYcWZNdkFrNVA2cjg5bnZ4VW9SeHdKVXZDZnk3eFBYTWlGcTBNMld4dXR3NkxCSU5KR3Y5aE9nYzFyREpJUHRoUFVfVUFGNlNvTTZVQjV4RtIBoAFBVV95cUxNYm04NzcxYmR2cUh4UUI2RnE4Z3dUdEhIQVNzbFE1Slhhd3Y0MERXNGZvekp5eVcxZGJQTWlUTjFWMzZwcE8xNmZCMjgyN2M2NndCZVVhRHlUbVJTRFVkRHhaWWdOTFpScDVWUE0xajdhTkFfZ3pmUE13TVBXczFRUk80eXRRY3E4SnJzRFRVQVkxUHk2ZmloMWxBYU4yd2l4?oc=5</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1811,17 +1811,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>I’ve worked alongside good police, but what my daughter saw this week shocked me - SMH.com.au</t>
+          <t>Who will police Gaza, and how? - NPR</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Fri, 13 Feb 2026 04:30:00 GMT</t>
+          <t>Fri, 13 Feb 2026 10:01:00 GMT</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNT0Izb3IxV0NCSDc2aW1jT0NIa1hzTmdPWTZzUUdQSkprZmM1M0RMQTM5NlVaMmtHcmhuY2hMNm1Ma3RqeXRqTFBXUGpCaTVrcmhiLWR2TjFlRnRCVGE0QTNCaEpBTWlTZFBwNmZWV3ZJWUVSTDFma2pxamN5bWdHaktSQ0lPemNrM1VwSnBiTHBFSDdONmxLd19Ia2lSTEFlbHVNdEFkcHdPUzk1eVZIOXJGNmtFS3QxSnZLb0swY2UySVVjSjVhY0NqY3M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTFAyWnhFMDl3SmMyMU00Z1h3aDV3V1lpTUJhaU5sNXVwUkFPLUlyN21JaEN5c2I0S0dFbnNORkVreHpaaUEta3JxdU56Ukxjd0M4M2ZoUXRqVFJkWWgxWjI0VGN2TXdFa0FkelZsbmZ3?oc=5</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -1841,17 +1841,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Police investigating threatening social media comments following CHS protest - Cville Right Now</t>
+          <t>Linkage Global Calls March 6 EGM to Reshape Share Capital and Consider Reverse Split - TipRanks</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 23:18:40 GMT</t>
+          <t>Fri, 13 Feb 2026 21:29:28 GMT</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPelk1WWlNLW55bURrRXB3ekVuNXFKQ2s4SXBqX1ZHZk4zaHc4Qm83cEpRSS1tQjdsSm1qeF9qTGtYTGFwWFhlSWNXQVZFQmp0ZEZHYnA5bXBXMGpmZThCR2RfLTNYZ21VUXQ3SkZLMVk5a3F1LWhWbzQxT180cEtfSll2UkFsTVVNRTBxUVl2eEdFMGc2QUNpSlFlVlZPbjhqZUhsRjJOeEZUUXJVeUJPNXN4akRwdlU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQSTRlQU9TUzNPeDFHQjdna0FqenBOQjMwejBaV2l2ZUhZOWFjLXFUV0s1NEoxdGN2Q3c0V3VadW9hZnU4WWc5YklYWnVHM2JEWGVRREZsM0txYUdhZ2oxWlM4ODNKVk5tM0RHRGtEMndkLTFHa3NUNktHYkF2RmNvMC1XX01HYlJCM2QycjBxampVQnNUUVhBNnBsTGlEWm5XcGdIQi1QVjVEZXRmM3ZIT1ZXbWlMOFY2T0tZQUF3NnlOdE00bFBMajk5YkxQS0J1NHc?oc=5</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -1871,17 +1871,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Eat Out Edinburgh! campaign in March proves city is still the capital of good taste - The Herald</t>
+          <t>BBVA Sets March AGM to Seek Expanded Capital and Buyback Powers - TipRanks</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 11:25:43 GMT</t>
+          <t>Fri, 13 Feb 2026 15:37:59 GMT</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNVUFLUlRSR09WYk5EX2MwVlpJbWFYZmpKaWFIWWZ2WWMyRGVMc1BsWkpFX2FkaVJvYTJudU93WmFobk5SUkRIM2VfcGZ2TWRCTDVvVVo4aDJqVTFteTk2Y25OYkZpb0pxbTBUVGlXRmptV19FYVFkcUR6aTM4dkctX3BES2RRLWl4RUxZVThTa0hnejh4R0poc0x4UWk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOWklEaEtpQUdpaEUxOHBWRVMxWWNHSTBhRFZqd3o2WDVSazhyb0hmaFVCc25QTFBSN0kxZXZDazUyLTNWcFpkcG00NHBOVW5pZ2tmdkVuNGRpeW9yQnY0a3JOX2EtcW96TWh4VFAwQVZIblBfQmtCc0xhLUpSM3VwZU56cDAyQlg4VVpDQzRGNGRCMHFQN3gtc2E3SlFQTXhSQm5FU3oyZGNucGZpRDRVVEk1N0VyQQ?oc=5</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -1901,17 +1901,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Clovis Police says adults helped organize student walkouts, face charges - ABC30 Fresno</t>
+          <t>Omaha Police Officers Association raises concerns about March staffing levels - WOWT</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 20:29:53 GMT</t>
+          <t>Fri, 13 Feb 2026 23:27:00 GMT</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNT1c1T19RTFU5d2h1YjVNVFBIUnBhYTJwaDYtdE5WWjRTV0VJNEVpa0s1aVYtVWdkOVlrcVZyRm1aNFFFWFFlZjd1OXNmcU81NkF1XzNRVHFnTzd0b250MkU1ZnY1ZFhXRVlCRURuVFBBMWkwTUktMVZTZ0VSdk4wbng1WWUwcEVZYVNfOC13YW1EQVhLM0dqUXFSRG15Q0dJX3gwWHVQWGbSAa4BQVVfeXFMUGRIZGNSMmxRR2VEQWp3T1JPM1BzT1NtM2pZQVhqRU5nWG1zNTlEMWFtcEFHNlpWaWZTNHphb3dpOU9ITE8yMWI1aU0tM1JPSmJYYjRLakl0cndYc0VfM0NGSUV4d2l0eFpVZndXQ0thbWxMN1VrVDl5aG5uNlBBcEdzM3MwcU1Od3c5RlRKZVhfN0xNbUFtZmVaM1ozcU93VnItVXhCbVRpUEtpU1pR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOMHZyUWJyR09OREZQcE1Sb1Z2dkZhdkhmRmxDQm02UzNJSExpS0FLRVhIM2JMZ21WcnZLSTJiSkUwX3QzamdnQ0oxYTA2MTJPR1JKcVV6YlZXMkFKamdZVnpGdzlINVlGdzR6VUJ4ZkNnemswWHZOV1FxZ29aR2pjQmNDQTZCYmRJX1lha01maXZlS1BWMXpkWFYwWlVqajFnQU52ajdLSDVVOUlqeExF0gHDAUFVX3lxTFA2bVJiZG80dG15cmI4MGZaZnJRS2hIdHh1NGJuOHRRU2tyMGh6MlBOdFNtS2Z2SXdqNkx1dUktYzY0RmkxSllGQnNkdzl5SW43V2J3OXQ5T3dyTm11UWtjcEFIbE9naGNab1EwWm1mVVJxTkNnbHVLYWFoeEZ0aVJLRTdPc2Z3azEydU04Y1BjMHliazBvd0RVMHVJeC00cm9uZFJ2Ymd2eVJkeGFuMTdzaDFXUVY4eFprY3hSUDhlUXctZw?oc=5</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -1931,17 +1931,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Connecticut State Police agree to allow highway overpass demonstrations - Connecticut Public</t>
+          <t>Clovis Police use surveillance car to pursue charges for student ICE protest - Fresno Bee</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Fri, 13 Feb 2026 01:12:00 GMT</t>
+          <t>Fri, 13 Feb 2026 22:28:00 GMT</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNOGcwSXV2X1c3NzdkcXZuZDhMbGlOSVBhNTBSMDRuRVJzUHBJOF9Kc2Jnc29rcjlsUU9tUVo1T1NPTmlTOHk4SVdSQ0xfRVp6SllqWG80ZUV4SWNsOFRxbWtieGpjYTBqVFlnamNuZHN5OFl4a1Nsd3gyMDFWek55RXpEbzBTVDFLb0FHZkVtT2dtMTBlR3VBRWg1UElybDZaT3BKVXE5emQ1V2ljRjIzWXNXRDFVekhVQU4yMVZMcnZfdDZC?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE1CaEtWTkt3TVBDZ196SjdaSlc1TFh4THJEYlpzcGdReFBLelFtbUxKMVRqS05BdlhMbHQzRC02aGRPblVGUXNmYUg3aHpuaXphS3ktLUlqX1czYUpmLUwwMTRKQUxwQ0R0dEHSAWpBVV95cUxNa2kzMlBXckROMHZURktGWVVUbnlSTEF5TUd0a1k1SlJyYWk0dWVJMElCWFZlblFrOUppR2xIZ1k3Q0NlX1VvWXpaQXFOODdLek9Bem5WNkdvVmk3dlJHcHBERFlPRjU5OVln?oc=5</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -1961,17 +1961,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Lancaster man punches, strikes person with baseball bat: police - local21news.com</t>
+          <t>Police find threat not credible, students walk out in protest of ICE - TMJ4 News</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Fri, 13 Feb 2026 06:20:53 GMT</t>
+          <t>Sat, 14 Feb 2026 01:10:19 GMT</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxObTZWQ0VQNXNnUzhhdnFSbmU2aVFvLWtscFdBWWI3eFZnUmtzdV9obWtJMm11VlRHZ3MxVnhxQkNna0FFWEtZLTZCZjZldnU2MXdqQ0NUY3pUT2ZVRU9DU3dwaFFLRC1aM0lCOWdzLThoaHltNmZzZFNVVEtnb085VURDQTU2UEExSmhoLTlEWjVXcW5tLTc3Qk8wenI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOLUNSVnNtbDhBZzRTTEt0V2hKV1pVcG9sWFBhZGlVM2xkMkFKQkszV0U5cUQ2eGhLNHhDNXZ3VTZxNG1kVGJDdi1yZG1kZk4xVzVLc1VhRzBLSVl4dXRmUTRYUzZ4VEtIVy1ZekpscWF3RE1fWFlkeGY2eHhHTmh2LUtWcGp3S3k2eE9MbFA0WVBFVllHalJublQwWlBOMzVmYzZQMkdaWF8tWGJZdFE?oc=5</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Anthropic AI safety researcher quits with 'world in peril' warning - BBC</t>
+          <t>How Nomad Foods is preparing for the future of robotics and AI - Logistics Manager</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Fri, 13 Feb 2026 04:37:44 GMT</t>
+          <t>Fri, 13 Feb 2026 16:58:35 GMT</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1TUXJWZzZGczJLRXUzQTdvMFZnYTEtOE11UnJlSW04VkpYek84dWRYM2MwYkIzemlLb1huZVo3MWMzZUp2NVVoVVg5NFVienlRV08zbmNEaUFUdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPeDFTM2QwME1pM2VkSHBOSlRBekpYM1psLTdwTlo4YWx6VHFXajA5UGFTNVZybmJEcWlyUFRsMnM2Y1VmZ01PZzZjSDZ1NDRKeTZqSmtrc0ZzUWVqOTlGQ1BOQlY0eWx2Tnl4NXFkWDNyVGwxZWZ4eGItU0NiYzU4RXQ3QzhtaHdDcVhZVUx2RURLWTNJNWJDanJjRnc?oc=5</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2021,17 +2021,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ricoh acquires leading process automation and document management technology company ValueTech in Chile - Ricoh</t>
+          <t>Events - Securing applications and APIs with AI-powered security tools - teiss</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Fri, 13 Feb 2026 00:04:22 GMT</t>
+          <t>Fri, 13 Feb 2026 18:59:08 GMT</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE1mTlJCc3dfMkR6c3dpSUhKNHNVWlpJeV96eTY0Y0hFOVdKdzZSU1pXQlRGZmRJeURXREppYWR2MVdDc0dISkhNVTNNSVZMZ043a1lz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxObnMtcV91ZjNWa2ZmTFZwZWRsbGYtZWVRWjZYZ3pxRGxwSDFacTRHRVlsM2RJVldBVm1tVW8tendPMldaaGo0bkpMVUhQZm9BS2szZ2dnUTVpV2I3MTdTYUV1THV4VEdFXzJpT0hteDIzVDJKTUtDSnpyLWtXV2ZDVmlwM3FZUnFvdHN2QmIzV1NuNEphdng4?oc=5</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2051,17 +2051,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Rightmove launches latest phase of AI-powered property search - Estate Agent Today</t>
+          <t>Tesla Leadership Shakeup Highlights Higher AI And Robotaxi Execution Risks - Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Fri, 13 Feb 2026 02:34:43 GMT</t>
+          <t>Fri, 13 Feb 2026 21:14:59 GMT</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQSUVJYVVURURyRl9ob1k5aUJZY1NJZExGUGpvTGVtZHlMV29LU3dsSGVoTHFhTXpCVlR4WXlycUFtN21sQldZRXFrMVowUmVRa2ZwTFVPOHZoYmozRVBMaXVzNGJXVlNTamprbzhRMGxlQUdIeGpJLTlubVN2eDlJSUxQa09UTkFwVUo1d2F4UUpLWFAxUDJyN3QxbVRndTdUeEJ5cHZVTVBwZzl0ZjVWS2oyMnhaRGhGaVpR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPWW1MQlhuMGppZmtRdzdtdGxwbEhkRktCQlpmY2xWQUFfLXk2MmsybE5qdFJINVdTam5La1RURHpSR2tGNDVEcVNXblNjbU5CblkwVlVQWVVaSlE4VVlpMldQNk5EbGh1NXJnOXplS2xzODZrUTBnS0VCR0F0MFJ0cm9uRG9LVl9HWll6OFZDOEZSTURvcWc?oc=5</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2081,17 +2081,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Stanhope AI closes seed funding, sets sights on AI revolution. - Calibre Defence</t>
+          <t>Cambridge academic appointed to new UN panel on AI - University of Cambridge</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Fri, 13 Feb 2026 07:19:58 GMT</t>
+          <t>Fri, 13 Feb 2026 09:53:11 GMT</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOYjFmZUdrM2JtQVhCdVF0QUdEQ2syQlVkS1ZuRFY3eFh4N3FpLUpQQU5oZUVVTzRIb3NXcjRYMHBudVRsZ3NxaFJ2Q3ltTDhMOTVyaGVJaEx2bFFOSUpBM2Y3T2dfWmRTOW1YLXVKaDRrTnZyemJGS3M3Q24zLTExUFNDMGtnQ1p5SEhzQl9kWEJOMWVZLWZqbFNBYmVRWHUzU0otLUdGa1QzM3hnd3JSSEZn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxOcGFRdkZiYjhyS0ZjbFRENHJ4Q2tVX3ZEYzFneEFWR3QwbDlid25uN0doWHlFeU9VNmcxaERuV0N4c29GSWU5V3ZXMmg2RWlwUFI1R0w0eGJ2ZlpoMjVsSmpsTGpjV0RfaTFOZFB3UEdKb2FKUWRFTGlxQTJuZHdURjBYZw?oc=5</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2111,17 +2111,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Telefónica hosts the VII Conference on Habeas Data and Artificial Intelligence - telefonica.com</t>
+          <t>Platforms, AI and Concentration - FTI Consulting</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 15:58:44 GMT</t>
+          <t>Fri, 13 Feb 2026 17:27:18 GMT</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOekRONnRNNHVBYWFDS1NkMjgtaHU3anh3bG01LWgtUjEtbGJONkFLUDZzV0ZHdFdTM2UxWWxyYUxsOFVqLWF3Y2VYY0xHcW9qSWFqSUI0YUxUSk92LXZnTUtxYmJvajl6SXZnbW94c01WS3BCVHdxZ0g5SmM5NHUyVElNT3pNaldMancweXJib3g1bFk4OFM3bXpkdFBZZEZnX1Eyc251akptb2t0am56RXVmT3ZIMGJYZFRPYmpXQ2NJeXc2YnJB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE13ZEgtNjRvVUliSGFkMXJQQ0pJeFM1aTZPTklBQzFyNU1hRU81WWtRQVR5MElFSFFScTNOaHlpVU5wckJjOGMtZTZ0cHJHNTE0ekxrWHJfVGh1emJXRXl6ajQzLWZDU29YTVhMY2lvY1pTV2RSeGRlNXZ2TEdlUmM?oc=5</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>What do I need to know to prepare for Quantum? - Association of British Insurers</t>
+          <t>NSF Launches $100 Million National Quantum And Nanotechnology Research Infrastructure program - The Quantum Insider</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 11:29:31 GMT</t>
+          <t>Fri, 13 Feb 2026 21:46:44 GMT</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPbzEwMEh5cFY0akNSYU11RC1yWU9HZF9vNHFxNWQ3cWdsNE1adk44TEdGeGhlQjY1dWE1Y2tZUG1nVEstODhuZURPZmZvVGdvZTdDOUZUb2ZxX1NBR1l4WFVvZ2JsTGFzWmxnd3d6RExDRlFQLVBfX3ZaRmhHNnBmUTlRaFNqdnhYQlNTUk1XYy1CWXhCdFN1MDdRYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOQWFDY0c2aFNKVVhfNnVSc2lsLWhKQXFPTTRkcDl3R2FCRmJORUdfajZGWGdmOW9nSGlPT2pYeGFTZmpWaU5UUHAzU1A5VkYtX2FJT1B0RVBBYThWNXI4VVZWTUxWcUFJQWFEb09PajZIUnpfY3FlbFhZV3RvbTdjXzVaTW5QWjhQMjNvZEp0bzhJUElsa3FKUWlkUndaRUFFQW1MT0F6MFZFYUx3ZUVBc3lWMTA3c18xNU90d3ByOUtTTDNoREs2aDhvdWU4MXM?oc=5</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2171,17 +2171,17 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Is Europe’s digital backbone ready for the AI supercycle? - Euronews.com</t>
+          <t>Claude, the ChatGPT rival shaking up AI and software: What it is and why it matters - EL PAÍS English</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Fri, 13 Feb 2026 06:00:08 GMT</t>
+          <t>Sat, 14 Feb 2026 04:00:00 GMT</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQel9mQlNqWDhRcmh3aEFXeXE2dWJ3djBIaDhzZEZwQkpxODQ4dzUyLWVRcHRmTmhfLU1sYVJGU3p1WGtBVE1XSkdhWUtWWF83T3d0TDZURllXcllTanNSdEFhREpjbk1XOHN4S1FweldMWXpRMm5jcGdGd3Y5TFVnRzZYMVBpdmt0SFVySnJLMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxPcVhoRXpoTnBGT1ZwbjJKY3pPWEJuaTFoRkFsN1lzRXFQdW9OME5RYThhRC1Pa3pUVnBfWTlvRWluLU1JQ0gxTVNHWWpvSGh0aTBMVFBLZzB4b3VFXzdwTzRPS21tdlJVMVRPOXhmWGJZdnRsLTFMRkVZYjVFR182djRYMldub1d1Zm44RVhmMFk1TEhvSDdpY1VOTVJYbjNDZ3VtTDI0YU5rX1MyVUtPR0ZlN0RmRTVGY2MyUWVQQ3J5UWcwdzEzREJuTkI5TWJURXZXVi1IMjNnY05WV0HSAfIBQVVfeXFMTXlTdDhrMTFiMFNZSFRoVzNnVmNLblgwRGJpMW1teW9ieGthZHNaMGFkRUhITzNwUXAyTGJndUN0VVU2Mnp1cDdlQzN6RFRNVHQ0NGs5c1RsWWRZRXNzRjIxek42QlhuUHZWcFJPc2tPT3pfVnpLdWVZUTg5cy1HQnp1ajRTMnZTTUt1d2R6eEhKYnFwQ3RrbDRSSjhHczBCVFkzR3pablFuZnNOcXRFTkQ5MjBpczhoaDVua0FhX2d2U1ZfX0xjNzFKeXRPVThSUW5lUVBTZzNkQWhReGxTanJzU1htTFoxRi1BclFXTTliZGc?oc=5</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2201,17 +2201,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Supreme Court issues “bombshell” ruling in AI patent dispute - The Lawyer</t>
+          <t>Building students for an AI-driven workforce - Relocate magazine</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 17:47:10 GMT</t>
+          <t>Sat, 14 Feb 2026 03:43:08 GMT</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxONElkb21jSzk4ekhycEpHY1VSYmFMTG04bW0yX0dMV1ZhYjdHd0dQdk9wUlU3UmVEbDlHMFFvN3NBNTdydnA4UkFVaDNmeUotVEItYk81QXlsUGI5SWVYcGZGYktYTUdKR2FUVmRYR1JLdEZpMmtsUGdDN2U2YlJoYzB3a29hVXNiS1dYM1ln?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOeUFST2RDd0R2RTVTQ3lQZmNHbG43YXRYWmhEMXFaQmszLWt5b3ZfUjY4YkRJVnExaEVnai1uZTdmRmdCSml6WF9DOFhZMjNaTnh1Sl9ZbWl2MVN2UEFQWmN0V0hTRGMyNzVVRHprVEFLbkNBYXhKb3FwWlNVWDhtbzBqcWducHRSN3dpMEN2TFkwSkhYVktLdXdGUzVWQW8zeGM4WFFuMzlSdm5B?oc=5</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2231,17 +2231,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Unions call for strong AI guardrails to protect workers - International Trade Union Confederation</t>
+          <t>UK ad agencies undergo their biggest exodus of staff as AI threatens industry - The Guardian</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 11:35:31 GMT</t>
+          <t>Fri, 13 Feb 2026 17:02:00 GMT</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxOLTlRNUJxUDl6bGtpRDhidlFBOTB5anFkZktkaVlmVHFPUzFjb25BX0lGMFgzSHYzRnFUWnNPTEtNT0pjcl9yY3hnOXlxTWloMEFqZGlUcFE4elBFQjdha0NUeXRLUExnenRZa0hVbXNMejZVcVhnbmhFWXhfN3ZOMlFYWF9zdWs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQYkExNXR1aHhOaEQ0MjMyVklqVFFfZWNCUk1YT0xBeU81Z2EzV1hLeUc2ZkZLWklkRFAzQW14WlItTmpHcGFDQ1hQdm5vYnVjUjNRSmZaMGtzcGE0OEhnOE5aeC02WFpDX1VZeFpZSHVrTkI5N0hLTmg4QnVXak05cUxKc3BIcWlvYTFfVVMxcjhLWm41QjA1T0JsREF0ZzhNWlVpZ0VjaVNYbVdUSUpXX3VvTQ?oc=5</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2261,17 +2261,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Building an AI manifesto - Wonkhe</t>
+          <t>NHS waiting list in the South East reaches its lowest since May as new tech speeds up care - Rayo</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 18:09:19 GMT</t>
+          <t>Sat, 14 Feb 2026 05:32:01 GMT</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE51S2JjYUZGVHRzOThfYkVsWmF3cWYwOXZNTmotOVQtQ3hRbnFoc29QM0NzQ1JmLXVMZUdSaV9aZDROaUZuTmZCLTI3MEx3M2szU0hzRlk1THY2YjIxdEwxZTY5YVY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUW5OSHNSS1ZvMmZGMnFVNWJ5YjM3bXllTHJ4Z3BaQUJUc0hKdTloWmlSRE5PN2RhRU5IVmc4Z0hKdlByaC1lYlFHd3BiSGNxVWJzY3RTZzlHS1MwMDhidnJNWFdLZE9GTGVnekI2NUExQVZiQVp5ZU44RF8wa0FpNThBZUd5NjdPOHg5LUdELVIzZjZlVDVLRGxCQ1FHLUht?oc=5</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2291,17 +2291,17 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>International AI Safety Report 2026 Examines AI Capabilities, Risks, and Safeguards - Inside Privacy</t>
+          <t>Why ads are coming to your AI chatbot - Financial Times</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 16:24:54 GMT</t>
+          <t>Fri, 13 Feb 2026 19:02:28 GMT</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNUzVfYnVLek15dlUzX3Z4ZnByUnoxNnNTZmdaTXJWa2g4Z05KVW9WOEtXV0hLNGd3dTAtVk03bS00b2JpZV9SVGowRWlXM3dneGUwM3hBY1BLdklEb1hvQ0MzUVJVOTRFb19QXzdpN0FsTHJKUFBEMVNLSFZFOFdidDdtM3Q0SHFBa3pMcDlWV1pQd3FUMFkxekF3LWtnSFJjejhwZTBkQUVEMnpKak43aVowQl9aN2dERVRQNmQ3amVzN2U3QThjSU5yQ2lRZDFqZnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1LMktZeVdWY3dhdllhNE1ickZMYjNLUjE1Y1Y5TzFpRFVhS0R0dnk4SmVtbmdZZURJWTVKQ0FyaTJPZ1d6ZlRUWHBwSU03UW9mYUxycXdnRk0zekR2eVowc0xHRktGS1BGNmpKUUxOaFA?oc=5</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2321,17 +2321,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Quantum Untangled is extended! - King's College London</t>
+          <t>World Radio Day 2026: Trust, Technology and the Human Voice - Radiodays Europe</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 15:53:28 GMT</t>
+          <t>Fri, 13 Feb 2026 12:57:55 GMT</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTFA0cFJjS2c4Q1NwOTJ5aTZxN0tkanI4T2k3RVdpZl9LemdhbVNJWGxYbjNuLVgzdHhhRUYxNTQzUWtFMy1ndWdQS1FudkVkLVhOS09KN1dfRkVYb0IyNWZjZ0pPV1ctRkk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOdDFBbDFLOGlERmM2MlE2YVd3d0E3dlpmeHNsdHBDdGxxeDJuUFFuUmtramowcHdGNkRnU0p6U3pmMVNSZjFOR2VySlZIa0lQY3QzelpfaV9ySXhsUzE5eDN0YzB2WUZUZHQ1WkNQZG1JQ3lQc253ajVkU3RxX0NadVE4MF8ybF9KMndDZDhVXzU3LUxHVFE?oc=5</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -2351,17 +2351,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AI and cloud reshape Olympic broadcasting at Milano Cortina 2026 - Broadcast</t>
+          <t>Siemens raises 2026 outlook, driven by AI and data center demand - Manufacturing Dive</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 12:06:17 GMT</t>
+          <t>Fri, 13 Feb 2026 16:47:04 GMT</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPampxUmx3SE1sblpsZkRZNUhhYzc5NHlOdVRLTDY0ZWY0UlV5TC14NU1vY0pTSF80eVhxeHRzelZZa3RVT0wzdVdWeklYRkRKX212a0tCbGZZNjhTZUg5VjV3LURZanZ5ZjhMSGNTQkl0Q2VaY2Y2NlhlV0tCZFBEbVppRDFVVTZ4cjJrQkRhZENpM3RqRkg5a3UxZjBMUlpSUm9RVFJ0RVpIbDBqaGhrQm9jcU4yWV80VGYyamVwaHpza0F3YVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOV1NKNTZUR1JqTmQ3cFZHNGcybmJmT19SWkdaXy1pTnQ2Q1E1WVg1ODRXRnp6aXBYMklmeElfWG0tSzhZMV92X1M0NHZCODlrTUN1VzhYZ1hZd2wzdUt5RkplNWVGLWVQSWtiV2F6MDNPQWVPZkpmUHR1ZU9CNTVmd2NkMGFfdTRmOE9CTUtQVTlHRzdrTzBuLWdUcDNfb0NM?oc=5</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -2381,17 +2381,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Conference spotlights region’s AI potential - Bdaily</t>
+          <t>Legal framework for AI-based vehicle systems and software - Taylor Wessing</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 20:27:56 GMT</t>
+          <t>Fri, 13 Feb 2026 10:42:15 GMT</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxPOUZOdVdjMjBXUjJwZ283NFhSOGZSYXFpU3YtNFBGUnBybGpUSndlTE80Wmp4TV9IVndoTzVyb1BPYWVkX3J6N0FoUEdodWFZMGd5bEpjdVdtODh2Z2V6NVNzc3ZkUlZLdC1NWWdCREQ4VjZCWFVEOU1jcWFleGI3MDZyOFdacFhLTlcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNSGJKVkRLTmduR2YwOHdqZm1JaXc2SnFLd2JhSG9GTENMb0JoMEluVFlGaGFJM1UtZmszUmUwQ0dVQkoydGRYNDFPcEtHS3JEWHZtZzZzZWFod3lUckt0Z21DWkxmQ3hWRXBuUU1BdFpmcEVGTjkxLXg2SWpURS1vci1TYVMwNDFiMFdCTGZpdXRvbzA?oc=5</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -2411,17 +2411,17 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Digital love: The AI next door - Trustnet</t>
+          <t>What is the one piece of technology or innovation that you would like to see as routine in practices in five years’ time? - Association of Optometrists (AOP)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 15:00:41 GMT</t>
+          <t>Fri, 13 Feb 2026 15:35:25 GMT</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTFBacWY0UnJ2bXJCbm9GMm9nZWQyUHFodDVzUV9zRGR1cHlxMXlaZTI4ejl4TFZHaGdqb0hWdlM5THdqdnZrOVdPYVVvMHVUekNuelR1ZE8yUllVNnVtQm9NTWhfVEdFNHEtMWdZZGt4SmU0akI4ZHB3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxQUTBUbktIN1JCRnJHaWF6cjd4QzFmM0pMV1ZEUFE0RFNFWWVUTlZfbDBUUTY2Wl9kTUszWTZOVmR2N0FzbDdqRzB3Z3NqbzUyOXM5YjdOSFhmSU80WjV1YThEdkJjU3FwWUlweVE4bzNXMzVBbl90Sl9oMF8tV29DQjRXR2N2OXNPX3l0anhReTFQM000OEVlNThFWEEzVGVfbG45N29Lc0VYZ1M4S21IRUszNndMeXAyZEw5UzREbUxNN0pDZkJybTlMWjM3MEw0YVk4LUxMM0liVEotbU1j?oc=5</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Get a grip: Robotics firms struggle to develop hands - BBC</t>
+          <t>The Editor’s Post: Are you struggling with the ethics of AI? Our Good Experts are here to help - Pioneers Post</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Fri, 13 Feb 2026 00:04:16 GMT</t>
+          <t>Fri, 13 Feb 2026 12:17:00 GMT</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1kdzlrd2FHdXRqYUR4YjZ4NEpqbC1NY1RuSmFWeWdrZXE2TVZObTlwcFBtTUtMUHgyS2I1VVJMdVF1alRDVXNDWlgzbkVzQzNXTFVvZlE1M1ZBUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQZXhYSVpGVkdiWlF6c0NJeVdiSEotV0tQeDhpU3NCQU1VZ2o3X3lZdFlUdTVjaERKWnZKU3NOT2NNM1JyQWlZRmdpS01TUVN0UDlRN28xTkR3YkFDOVQwUUFtWm9UZW1IbWtzQnFEWVhJWXNHc3oxbUdjVjVkZUlPdHIyM2pHelpUUHVxUjdReENXcE9XeFlBZ3NKRWJnV1c4aFh5b0VlQXduNjNlZXlVWlhGMUVJUlppVzhSRm9RdVctMTZuN3BZ?oc=5</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -2471,17 +2471,17 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>The software sell-off (part one) - Financial Times</t>
+          <t>UK–Southeast Asia Tech Week 2026 Highlights Expanding UK–Malaysia Digital and Technology Partnership - GOV.UK</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Fri, 13 Feb 2026 06:31:43 GMT</t>
+          <t>Fri, 13 Feb 2026 08:11:07 GMT</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE0yY3JsSWt5N19aVEQ0aEFmazktMGJNNTNuWmY2QkdkeUphcmJWSVdRQlo2Z29ETTFyVFVrSmZCNDktc1I4V2JjQmI1Zlg5Y0x2M3NEOXhFNGZKZVZLZ3M1eDAtUHMyT01XYTdyemd5Vmg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQdmRxM1p4bDhMWUJuV1luUmFsQXhOZU5nOFJRSzF0ZmZhOUswNFd0Qm41bDc1OWRieGY3NEJlc2M4VTRwdzJRV2h4RnZ0amFtZ0xSX2stMWhYa3lIMDVlYWRoT2NtelBLbUtqM2FuOUpSTnBOcXhZUi1haUczZ2VUeUhaeVcxMDRabC1uVVlnaXN6bVpMdGh0T2h3WU8ycHlwY3J6T0E0eEt5MGJQZXNXTzZfYzZTZEVLemFoY0xqQTlPYWY0WmxnXzctVWhRQVNv?oc=5</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -2501,17 +2501,17 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Creativity and Learning with AI - MacArthur Foundation</t>
+          <t>Amey invests in Skills for Life with new AI training for apprentices - Rail Business Daily</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Fri, 13 Feb 2026 07:41:15 GMT</t>
+          <t>Fri, 13 Feb 2026 10:44:36 GMT</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxORW9yZHIzZ2dGS3QzbGg0cV9EbGd0N3QtdkNhaGhaR3djNkMtZzBXYXFqZkIyZFh6ZDJfN21EWll5S3VtbnNXbDBwQmhOTWJGQTJYeUMzbnFDQ3VsUUpKRm0tV0Q0N1RadGFaejJ2RFhZSVFQR2ZfTHM4dDVfRTQtVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPb1VVRjdQb2pYQU80c2Y5bmNRdE5rUUtoa3c4cUJfTGUxY3hYb3ZOVU5fXzYwcGV2enF5QUt6VzBYSlJGSV9uei1INlE2TW5ITlhZQU5tSTNCMmVSTW5ab3o2QnpBanU2R0hDMjBuMDkzci1vc2tWMFp2VEhlNlRibWQ1cDJrc1lkSXpWS1RYM080czc2ZjVpNWlta2lkZm5rM2FrRHJXTQ?oc=5</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -2531,17 +2531,17 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Data and AI Are Reshaping the Next Generation of Connected Compressors - The Engineer</t>
+          <t>Marvell Expands AI And Cloud Role With Celestial AI And XConn Deals - Yahoo Finance</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 12:42:47 GMT</t>
+          <t>Sat, 14 Feb 2026 04:25:00 GMT</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQQm16SkRETWQ4VzNfaWVqdEI5VzhmRGktdFoxTDE0WkNBVFhrSUVjNnMxNm1FTTQwSlVJRGVsZmd0UGNmSWlYUTQ0cDE4Z3hIZEVzZEdORzhfa25JUk5nNTZXMFFOdEdXMC1ONlhTQzNRN3J3T3VidnB4TzNSZWs4R3oyZzdFOFM0eWFHNThrZHpZcDgtZWlxRXd5ZzJxMENLRWxJM0RPNkgyMF9uY0dlcXJSWlBmd1k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNYThUZ3NmcDFldUdiYUxtby1Td3otLWd4clhLT1ZjVHE2Z1MwbGEyLTVNbEl5WXRYZTNQMzM0c3pLLXNlVFRlVndYc2JqdXVEQUQwV3o2WlJLZGpOU1VESWNjWnhOUHJDY2hpSC0wcl9jdllGNlkyeVNYU0VXblU2Tg?oc=5</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -2561,17 +2561,17 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Gloucestershire HR expert is helping businesses get on top of 'shadow AI' with free online guide and roundtable events - SoGlos</t>
+          <t>Making the Business Case Amidst the Rapid Proliferation of Advanced Fleet Technology and Digital Innovations - Transport Topics</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 10:21:25 GMT</t>
+          <t>Fri, 13 Feb 2026 19:34:19 GMT</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxOZ1k3ZXlHRDBoRFVPR2o0YjgyRnktMDFBMG0tdWdIMTVHakx6R2FzdUVfZmltbXhtbkROdk9CNFZRNkR2N2F2bF9VSTlQam5GYUc3dFlzWUFiWUZPVzRYbXV4UjhPdDBodS01am9vWE1IS2JTUnVHc1FrRTVPR3BmaU1TcXdaQmVuZjlJRThLZ0tLeko0R1FTZjR2VVBPMF92bm1fcmMwOVp2LVRydUFhRDVhWjQtcUlrN2QwdTFRc09mcDh6VDcxR2RKSTE0aDlYSGVxQUhOaW9kbXQ3VHNacktlN2lXakhadnpfQktydHlUZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOc256d1NWTGdFQlpJdDM3clhFTDRicmk1WGhOeTdEdWVzQVBOUVlOcjZCb3lEbEJBWV84bzgtOGc3MUQ3dUw0RW1uazFKX2JmNGd6QXREU1hfOG1rMV9lUUJtejJmWmFMX2RvQVZTV3lUc0Jta2Jrb1hNdkx0MEVGUV92YW1UU1paUFpsazR2cEFic0xtOUpnb1ZfdVVWdG55WFFMbVpfVjRxVmlSTUtmektQSGVISlJt?oc=5</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -2591,17 +2591,17 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>The Ultimate ‘GPT’: Is AI Game-Changing for the Macro Picture? - Neuberger Berman</t>
+          <t>It's been a big — but rocky — week for AI models from China. Here's what's happened - CNBC</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 14:49:31 GMT</t>
+          <t>Sat, 14 Feb 2026 06:47:34 GMT</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNQkkwU0hLMmNaQVQySUhHdnR5b1kxYUM0YkpvbUJvMWlsZmQ1RlBVMVdPQ0ZWb0FZeVQwTlFTaFE4VDVRVWYwNW1mWUNlR2U3azhlX25FSGNtcmI1Si11dWduOVdyT3hOWldqNUM0cDl5YmdCS0d3bHd6b0kyM1hLLXV0U0UyOVFqSHAxd3FOVjZldktYVmFwSzhmR2g2Y0xya0hyTzNKUkowZTVrX011Tg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxObFFiaWg0c1d2eWNQaV9MMmJNbFBDS2hINFVqZTlTMDVhMzVFVllwcHFWN1ZpMTdlMXdRQmdraGFTUkJCTkIzYUZTT1lob1N4T05xaTNPWjNIUVpZLWdzUldod2RLU1A1WmE2cHRJUTJJQ0VsTTktUXFoeG51dVlpQmIwMDZ3VUlLVV9mb2V2MFNFcUc3TUhVLTlyMEx2S1HSAaQBQVVfeXFMT0xHZVZCQnp6ak1WamxqWmlROUxua3BWSDJTb1l1U3JxQ2xQTUZZSXBLMEtVS1phYVhoNjJ5VlNmbnZWdE9FSVRhTXA4Sm5tSjJhdGM0LU1DM01SOFptQ2JLa2djTW9SVXdETFpWSTVuYkhrU04tUjRWcEN6YlBXRDVSellHTWo2LVRVbWVNd3hJLXhJa3NydEY1RG1HNGFVTXJGU3Q?oc=5</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Transforming work in an AI world: Reflections from Davos 2026 - Mercer</t>
+          <t>Why is the EU struggling to scale artificial intelligence? - EUobserver</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 16:31:55 GMT</t>
+          <t>Fri, 13 Feb 2026 15:23:39 GMT</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQLTJGZzc1Szhxcm1qbDBMQk92OEt2N202XzFGMS1WckVfcF9tX3I4UUxPUHJ3NUVxUHdyVm1fNkdFWC1uZnBiWjlSU2o1Zzgxd2psNjNFMDBMSjZQWEpWYmRrV082dEhhMU1Ud0o3V2wzX1p1QVlGd2NZOVlHSW1DZHljb0tCenlrVzlpMF9rNzZVcENlUmc1R0FRcjBwV0h4bG12VlVRRjRRV1d1RTBuTURCUmdma0JTTHB4Y1p4bzN2WG84NkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNcEptSjV0X2YwN0F2ZEd0aDY0RlNDUEt4UUxUM0lDcHpHRXpCUHNOU3Jlel9kMDh2RENZRzlwLTJicmloMEdVQWVyYl9YNEZGcXhkUS1ZSXN4ZmF0VFFuWXhTdFJLSkxacGpCeGdYMThBNHA3OU5fYlNxQjJGTUktMmdUS0s3LVMzMEtmdHZmYXB3Zw?oc=5</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -2651,17 +2651,17 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>How China became fixated on cloud seeding - BBC</t>
+          <t>All-in on AI: what TikTok creator ByteDance did next - The Japan Times</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 10:00:00 GMT</t>
+          <t>Sat, 14 Feb 2026 03:14:00 GMT</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOeFY2VVBoLVJzYzdqUDdRNnQwZ3RMbzBEVUdwM0preGxlUi1NVXBVdG9TUkNtNzluSlRCVkZsc21SNVpCVktBb3BGUWlLc2w5OXN4VUdYSXpXVHdoejJRUGVEeGM0X2x6emNRRmIzalhqUFpkcDhIM2lmd3VGdC1uX0UzdHE3eXBtcGJpeHdQaEVrUGhCQXoyNzZza2thUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTFB2Y0Vjai1HcFBrLXpHRlBrQzVxUU1jaUdCVS11RG1pQTF4Um1qR2lBZHBQbXR0WnFIc0xpY3Q0dHZ0dnJvZlZ4Z1NaT2d0b0hveFdQMVVtVWhMYWRlT3luYlo1c1dnSEw4NGpheU15MzRXV0tjZ1M1OE9ObEM2UQ?oc=5</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Why CPUs sit at the center of AI infrastructure: Five takeaways from Futurum’s latest report - Arm Newsroom</t>
+          <t>South-South AI Collaboration: Advancing Practical Pathways - Carnegie Endowment for International Peace</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 20:52:39 GMT</t>
+          <t>Fri, 13 Feb 2026 16:34:11 GMT</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxQWGJEZm1YV2dGSERUSFpvV196RkJya0MxVWVKLXRsRGpEZWlkb3lYaGxLaGpxcHA5T2RORFMzbXhFRlBnOUl4d290TkRJZHluMjc2cjMyZW1HR29LS0JwLTlfTHZBVllHX2JuMnEwX2FudEZoVVRSam0yelhlcHVrWlhmcXo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQVEhFZURWX1piVWZucHNVX19aSGdLbWZ2RkE1MVNtMUpDbU95eE1fcURiZi1UdGNDOGpOdFFHVjEwVWF6eTB1TDg1NTlfMlFqQlpRckFycXlSX1ppTXdXRXdlSXhLaVlLeU91MW9OSEh1VWE3UVhnRDc1OFozOWMzZHdTWTZhMnQzMVEzR0V6enh1VE5Hb1JMVlVmYXJQZFd2ck1EdDM0SQ?oc=5</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -2711,17 +2711,17 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Hertfordshire officials warn of AI and deep fakes ahead of Valentine's Day - Hemel Today</t>
+          <t>New Book! How AI and Quantum Impact Cyber Threats and Defenses - KnowBe4 blog</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 15:07:00 GMT</t>
+          <t>Fri, 13 Feb 2026 16:25:30 GMT</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOU21hWmZTb1dseXRpNmRvNGEyYW1FWTJNNVZ6Zm5GalBoN0VvbUUzMGMxRzdwRnl1cUdURVZaUEJqWld3U25DTmpxVW1lTndzWmpSd0VwbTFqQTNCVUEtNlpRT0JoWlN2UFk2NWdMVXdjZGZYOWxJaW0zWnZ6OE1jaERLTmJnNjU4UW85NDBMTlMwRnctdDJBNXlrd29EMlBlU0EzQ0VyZXJlTS12TEdkeW9YOGRwdGRHZlhTLW5n?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxObVBLNm96NFhGeFI4OF9ISGFvWlQxVHhNVFVQUUZFaUh1Qi0wWGI0bjA5NGtMSTNJVGduTFE3aGF4SmVEdTVqeWc5YXRVWVRqZVZQVWxfcG9SUWk3WHdCbm1jM2FHUzFfdENudzVDb1VjMHZpVFdKb3VQOFpmNFpLSThJVHV4WWlpV1l5dGxkdw?oc=5</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -2741,17 +2741,17 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Operant AI Launches Comprehensive Channel Partner Program to Lead AI and Agentic Security Revolution in 2026 - AI Magazine</t>
+          <t>AI disruption could spark a ‘shock to the system’ in credit markets, UBS analyst says - CNBC</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Fri, 13 Feb 2026 00:52:06 GMT</t>
+          <t>Fri, 13 Feb 2026 17:34:21 GMT</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE9MbUFNTkN1U0ZNRXNKdVdTZGVvN0VNUHN4NGFjTll0X0FSWGJScjJnTEViTU5vMWVVb2s5a1F4cnhlVEVTMFNIM3RmY1g1TEgzVGRnYU1qaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE5LbGtSdzBqOHRsdGJycFZGQkM1aGFLeUdpeFdmMnZfZDdIN0hSYWt1M2lqNEpmd19yM2kxM2V5QzNtam5OYzJnTzUtSGtsSi1iVmpzNFl0ZkFDLVpFUDFuZVdiZDXSAWpBVV95cUxPbjFaeE5Id1ItWlcyOVdLQ3FROHdFNDdBY1dKYTd3Ujl5Sm1uWkxTU0ZyVlRmOHV2U3J6Ym9LQ21VOXZwNm1jWjFtc0N3Nm92dkludVRST0N5UFpWZjRTSDRQamhZTmJvZHR3?oc=5</t>
         </is>
       </c>
       <c r="F78" t="n">
@@ -2771,17 +2771,17 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Aramco signs MoU with Microsoft to help advance industrial AI and digital talent transformation - Aramco</t>
+          <t>Hybrid AI could reshape robotics and defence - Digital Watch Observatory</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 17:45:00 GMT</t>
+          <t>Fri, 13 Feb 2026 09:00:00 GMT</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOY0xzeEtxN21ibEg2Q0ZkOUJ6ckNEaDVQbGhFd2NxZ1daTDFYRDduR2xrdGd1UDZ3WjBQVkM1Yk1Qd0lLd0JiWkhEbDJ4NXAzSHJnblA0RC0zRURZWkxmVHF3c0d4OFBzOFFYTHBfa3RQM200SFRvZE5jWHNmYXJTUmZFZHh0OUVWQlMxUUxOSHlxZUtGcnlYR0plRHJsUjhJZXNidDRlVlREcklhNmx2Q2xMMFhHTldFWnlrQUVMRnFqenpnbHhqYkNVODNqUkNKTmtiTmdaUWVmZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE1RWlVBR3BGNS03dHFWTzNTdlR1STJDOS0yREd1M0VkaUYxX0luWDhQUU5TdkJFMGtXc3gtNGZQNkpKNkhWb2NENEQ4RzRiTFRwMExUMFRhRWNreUQ2SEtWdFVhdGFyZXRpMm1fSHFuZ1VWNDdlc200ZFNB?oc=5</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -2801,17 +2801,17 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Can Southeast Asia extend its AI data centre advantage into Space? - Lowy Institute</t>
+          <t>Global Mining Automation Market Poised for Strong Growth as Digital Transformation and Operational Efficiency Imperatives Accelerate Adoption: Verified Market Research® - PR Newswire UK</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Fri, 13 Feb 2026 03:04:16 GMT</t>
+          <t>Fri, 13 Feb 2026 16:15:00 GMT</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOYnZsdVNxQWduYThyX3pRVmt6STV5V1RBalNvRV9zcUIzZ09yenNsa1J6SEZwR2libUhnZ2ZCdGYyWE1tMGxuV0xlOVZjLUhOMjdOZl9wTHVuLU5rY2Jpb25jU1FFZFYzaHBOOFJkYmpwZVRXSi01MmU1X2t3X045OEVEcHczWVFzSFpCVFNTVDZIblQwNzlqcmY1RGpmOXRtVEJDX1pxdEpKdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwJBVV95cUxOTnNSR2U1SW1XRmtJaHFfRkM0ZHZnb3VGVWxCSEFWX1lnanZQelZ6RUplMXkyQUVkODFIdVc1UEpzSkNUaVdLdHgzdGV0UHdJZ05ya3c0M2dJb1kzeS02LTlHQnBNODlheHRLZ1RPV291c1R6eUxrcDNIeFNuQTU2OHBReElJR280UnpGMEVUTm9TQVZDYllWSmtNTTZjcGFjYzYtQkdOcmRObGM4XzY2UnBYU1dCbTZ1UDhBcnZPcUxrSjgzeEJKWVF2V3dQbUtFUlllUUxobUhmbWFuU1lnSlZzdEo2ckthd19NOGRvUi1NVGFnYnY3eWhZZ09BbE9Tb1Q3a0xyTlE0S1NrVHZhWjNJNmVkNXlYNFVWb0JSN3ZHVnd6blBNekkyc1JQOHNKdlVYclI2cUF6TGZLVTU5Z01SNW5mUlE?oc=5</t>
         </is>
       </c>
       <c r="F80" t="n">
@@ -2831,17 +2831,17 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>EuroHPC Deploys Euro-Q-Exa Quantum Computer in Germany - The Quantum Insider</t>
+          <t>Is it time to log off from old-school software firms? - This is Money</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 20:47:42 GMT</t>
+          <t>Fri, 13 Feb 2026 21:50:19 GMT</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNQndvQUV2d1duZVVQTGtySmktZFJBQTIzMXIxVVQ0OG90bFZCVVhLUzRObFQySDZhMVRscXRDcUdCYVdmSkFzUy15ZmZTenZkMC1OVXUyWEZib2pEeVBVcWR4bGdPUFN1ZXQzT21Ka2UzNUhOS0hnLUlNQ0ZOQU1UbnBSUDN5NFBuVnFucDBBSjltRXN5X2g3RQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPZ1RZWTNGVTFRanRqWjl1MDRqMDhWMkdaQ2txOTYwcVI0OTV5RXhkV0pIN3QxSlJVVFlMNkJ3aE91Mmh5cTdpWktKYjVMRXp6dTZJaXFPTXFiU25KRXhZY0c5Zm1JbXJuLUNyalNic1psWUhBMlhkUUI1LVB2dGJ6RzJiRWhPMkVxbER0TDM2TGdMT2VuQWE2UDE4N1pUc0pjV1U5VFA5MW_SAa4BQVVfeXFMTTJ6TUZmYnNmMEF4Ymt5YnhnX0xOWm9iX2p6RE5jS2tXdEFmSkFoSTFobmNDV0h3d2xmb0VIcUFpZER0cWl6OGFIcENJRW5RdEVLTXM1T1pNYlpPZVZRbjFVM0RsQnpWREp5YlRSSHdXRlBTUTlvWWNkWHFZNDB2NU1oYVg2QTBvdEJheW9BYVFjNjZLTHNfaFBxUDluc3hicnVvbl8xNmd3SWpUcE93?oc=5</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -2861,17 +2861,17 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Video: Opinion | Is A.I. Coming for Your Job? - The New York Times</t>
+          <t>The AI dilemma: Can social enterprises innovate without compromising their values? - Pioneers Post</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 22:08:20 GMT</t>
+          <t>Fri, 13 Feb 2026 09:30:00 GMT</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOMGE0dE1vSlhiT3g3SXBzX0pURXRydFpTdklXY0EySGF2ME94STZTVE5RQjMyNVYxaTUxWWs1UlhoZWdyLTVub2dmV1B3Ni1wRlVIb2doYUJ4QlVkd2tEMXlZRmV0LXlkMUZDdzNESGFBcnU4TW9BZ0JtQ2xYamphWE83bWpSaXN6WVVtSw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOMlRLTW9jSERXUzNicHZhTWVtdGZScGRUZU02d3VHcE9fRTlYYTBKNDhNaXIyN0J2V1NyRTgtd3F3dDZkYmYxQmd0S1hLeXE5OUt0SXZnYWxiWmZBTnNiT0tXYXpkQUt0NEgzcFd1Y2s2YXlIQS1USDh6SlN3SHRPcDBUQ2tENDlVMXNmcUthZ2YwRTRoVkp0NW5Yc2xST1pqX0FJWEV5d0RjUktDWTVlYWxjdEhPUldVSmdmLVNuZWY4SEU?oc=5</t>
         </is>
       </c>
       <c r="F82" t="n">
@@ -2891,17 +2891,17 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AI and robotics researchers at ASU work to keep people safe, healthy - ASU News</t>
+          <t>BMC &amp; AWS deepen Control-M cloud AI orchestration deal - IT Brief UK</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 20:45:18 GMT</t>
+          <t>Fri, 13 Feb 2026 11:46:00 GMT</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQOXBrdXc0Q2FMeWU2N3kwUHhCaE1iaUsxUVJWSkE0REpkNTNhbGExUEgxZEhudVVwcGNfbHJuamIzV1pmcDFtR3RuZDJBdk1EMnJZdXUtcEQycklSUzRoT01CV0cwblJQaWRYS084Y3piUFVtZV9Ha001UDlzSnFaR1lCcktfZjlpTXRsZ1c5Q3lvQ2V1Uml4NVVyZTRxWXhDaW03bl9WMjFaWGdQZHZyZnlGVTI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQUEMwc1BQWm55cnNSMHB6YjlGUUlWMG1CbTRaeWlMcnNCYkx6Y1dMMXZzbnFmZ2RWXzNtSlNDN2JpNzUtQVRLc3BHRzk5aVFHdE1nMGgxU0lfbVVYOWJLdWROLWxQbzBWVmVLb1l6SDVCeWFBcnJGeWRobXk4cEN3X0FtVG5EUXM?oc=5</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>HENSOLDT and Helsing join forces for CA-1 Europa autonomous combat aircraft - hensoldt</t>
+          <t>Radio and the challenge of artificial intelligence - Vatican News</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 13:15:02 GMT</t>
+          <t>Sat, 14 Feb 2026 05:23:38 GMT</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOOU83TUMzcUVhR0FaMFZZTWM3YnBxNEFlTDRkS3lETGZwd21EZHBKOW9FeUhNQWtKV21FVUpfVXRiVmdYQmNJVXAyY00yUTBsTFhmT2lud1g0Q2x5a0h6X294ZHZmOTZuSDB3N2cyMUVTYllqX3VWdWYzZS1TTEowQ2RpcnowRHJ5aldsX05jUHl2bXNVcWtzU3gydG95WDRZWGUwTV9maVU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPXzVIQnZVZ1RuTEJHWktwYlFYS3psZFIxcDQwMXR6MVJRSVJUT2hPWlRQLTU1eEhzbng5S1FFSmd6aWVVa1ltci1hQWl2OEdwYTYtUEg5OHNSVjB2a1R4c29KdVEtQzY4QWlJY2d5SjVpYWcxNUZnRm5qZzZiN0ZJUC1rUDVqcTd1clY5LWpXQ3pvVTlPQmx1T0lmYnI2SldpY1M4QkNnRE1halAtbnhkSS1n?oc=5</t>
         </is>
       </c>
       <c r="F84" t="n">
@@ -2951,17 +2951,17 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Microsoft AI Chief Sets Two-Year Timeline for AI to Automate Most White Collar Jobs - Yahoo Finance</t>
+          <t>Global technology leaders launch Trusted Tech Alliance - Nokia</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 23:57:39 GMT</t>
+          <t>Fri, 13 Feb 2026 17:43:34 GMT</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9BT1BnaUNvNjlaSGluX1c3V0VTR1JEd2tteW9DTkxtSUJraFVsbjk0eXYxazlGTDNTYUtxZGpaMlFJSWh5Tl9veWF5ZGlycGZyajE3c2I4UVB0RFVnUU44WWhHcGQ5dElQcXdNTnI0M0t6MTVfSkduejFOV2Y4dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNUjItaFhrNTB6TG42UjF5dW5adlhERVk4V3RqRUh5NkxuNTZkQzAzOXpfdWF6Mm5EY3d1NFhCTGQyWW9qd1JVclhfR3dJOGxacFpmVFlOVnBZS3psaG04c3pVUnNGRDZxdlMwMngwNndES0NucmEwNU5kLWVKNUNMckVucXpXMmEtTDBKVzlsNA?oc=5</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Opinion | Anthropic’s Chief on A.I.: ‘We Don’t Know if the Models Are Conscious’ - The New York Times</t>
+          <t>Wolters Kluwer Health pushes deeper into agentic AI to tackle medication workflows - Fierce Healthcare</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 10:06:28 GMT</t>
+          <t>Fri, 13 Feb 2026 14:15:00 GMT</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNOWhTaVhtLXZNSW9JcHRqd242aC0xNWNZSlZPczJSR2dNNS13RDFzR0FMMk4wcUJjUkt4alltTFhhQk5VbWdKT2RzdzVpa0EzbzFycVNiTWhsTC1Zb2t3RkNEZW8weVY5bkNDVkhtMDMzNVA5aVBQdVZ6Y3phazNEbXVQUnFGWGJMUk1zaGYwYjVqQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQX3VnUmZ5LTlZbmpGX0g4VTFUMHdSZ1RFaUNySGxTZzBXR0h5Z1FSWFNfdmlUUHRWSXcyV2VzaWZNZ1hjMm1GZldaSGNQOVJvYV8zVWlJZlVTNmdUR0FkcFY1LXdVaXprYjkwTlM5S0RJVUtoQWRsVDk3WmMtUkMxSV9JTE04Ynl6V2txVVdZWV8zUzh5dmdsYkx0YWdmV1dpRTFxZjhaLVB1cmRiMS1ScnBmN0lmdkJBSVFybkQwVnlzT1k1Y3VSNnlLcw?oc=5</t>
         </is>
       </c>
       <c r="F86" t="n">
@@ -3001,27 +3001,27 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>HOK Expands Leadership in Healthcare, Science + Technology and Sustainable Design - hok.com</t>
+          <t>Suffolk social worker fraudster handed suspended sentence - BBC</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 14:39:31 GMT</t>
+          <t>Fri, 13 Feb 2026 15:48:29 GMT</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPXzgyY0liN3pCSG5DUVk3YUNlWm5JWFdWSVZtSXlDV1VqYlEzMkxtaWZfdHN0TkNLWUtJbm9ZazIxT2kxcFNPN0d5VWtWeVhFQ1pyOGl0MldrdzhvZWI2U0hqc2hyZlY0c3Fpb2lhQUlncjIxd0JQN3pYY1ZGQmtKT3liRjFRSTFYVU1QdWwzd3FIVUtGTG16cTB5WHFkQ3phc09FanhwNERlOU5ORFlaMVJn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE42dkdjbnhPZ2M5VVk2Y2d4ZDYzckhka1B3dHB1MV8wcXItdmJTQlliQnI2UTYzWGJtSjZqTWxZanh6QVVZY3hfLThlVEtOM1JZTWUyWkpSQmhiSGty?oc=5</t>
         </is>
       </c>
       <c r="F87" t="n">
@@ -3031,27 +3031,27 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Opinion | A.I. Companies Are Eating Higher Education - The New York Times</t>
+          <t>Social media scam ads generate 140 mln euro in Bulgaria, Romania in 2025 - Revolut - SeeNews</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Thu, 12 Feb 2026 20:00:07 GMT</t>
+          <t>Fri, 13 Feb 2026 15:43:44 GMT</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxOejlvMzB3NnlBUE44aVc0VmhMOWdrU0JMc2JuakhoOXFybUlqM1pzV2k1R1U3RnJuY3J6elA2RnRncUk4SE5uOVhtc2lPUDF6d2V0VWY2VHhtTy1ISGR5M2xVZmtoQms0Vzh0cERFUzJLbmRCZlA3UnJxSmpDdWRjaWtjbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxQWTNKM092S05nd21odG1tN3BPenVNU0c2dGlhSV9wOVhlRWRGYUJCRFFkT3QtdmtXcjA3dWVLQTVGUkdubDQwZHNMeHk4VkhEczZlSkJ4Sm1ZcVFJME1fdnBRQXV3dW9KX3E4VnRUTUhHR2lqRFVMV0pYYjBwOXYxMmNhbXdZUFQwYmx0UlpHX2tmVk9fMFBwUHlEbDJIRmo1S2NqSHROeTJFSHhrVmJjU0xn?oc=5</t>
         </is>
       </c>
       <c r="F88" t="n">
@@ -3061,300 +3061,30 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Cybersecurity and insider threat risks - Nixon Peabody</t>
+          <t>Why is Minnesota so vulnerable to Medicaid fraud? - Star Tribune</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Fri, 13 Feb 2026 02:43:12 GMT</t>
+          <t>Fri, 13 Feb 2026 12:08:18 GMT</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNOGRJSldlcFBxR2s4bzg0SjJTanZVRV9BSnUzaWtxaTVkc1BvbUhmMThnUHRyTEYxYzhrQmZiSGxYcUIzSWV2eGxsQ3VCZ05SRG1kSHNJRXBVZ244VTRhYXE4VVJtQnVKWUpENFV3QVlVOEhXNGl3bkp1OWVsLWRHbUw3WjROdkJkSkx1N3oxQXNyeld3Skhjelpn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNNTJIcmYtVW4zWXkzVHJkZnFMc3lKWGtlSXpxbWxEMk9UeS1uM1pXcHhKOGpOYjdUYTQyLWZiMW9GX3lFMXFqTzE5OE42cVVCNnllRTdIVU1zVlJId29yLUJZQ24tX2lneFVxdWpJdlowWjBBdE9ORXNVS21OX2FKM1hUX19OQWxqVTFYR3JuMA?oc=5</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Insider_Risk</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Fraud: Crazy Stories of the Often-Forgotten Insider Risk - MSDynamicsWorld.com</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Thu, 12 Feb 2026 22:51:02 GMT</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNNUxkNmNpcUo0NGNDUWpDMTFrZ1ZTaXNhWHFnaUwtYzhGenZxWWE3dEdCeTE4eWw3QXZ4VlRORkxRaXRXeXhFSzF5U1pLYXZxS0hJWUpZU1NOcVVxTzljQS1yeldHbFFSdW9Oa3JFMjVlMFNOY3BwTEZiNHJDQVRRNUtfZXBQQlI5Y2c?oc=5</t>
-        </is>
-      </c>
-      <c r="F90" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Insider_Risk</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Data Exfiltration Market Size to Hit USD 47.26 Billion by 2035 - Precedence Research</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Thu, 12 Feb 2026 15:27:40 GMT</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE01eVhuYXVSaG45cVNqbURtMXlEMzhQZ0hKRGNyVWpoTG5PX1R1SGRtNW1IVUlMeFBwbk8ta1VkS3NrYkNzTmJxZ0o5ZkItZ3VXVmRMWHk5bXp5UTJtTGxfV1FqSi1IZXFXWk13?oc=5</t>
-        </is>
-      </c>
-      <c r="F91" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Insider_Risk</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Shadow AI: The Invisible Insider Threat - Security Magazine</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Thu, 12 Feb 2026 09:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNeV80bTF1aFhfNjdfTmhjMFZ5VGN6cW5YOVZQRHhVMUZaZWlKQ05qQV8xVDVwQVdFZVI0dl9QLVZMUmxCTkJQT1RNN2tfNWtwdUdhQjBaZXI2eGRpTU5BRWVmbWhidmpFbkUtbTRTb3pHVFplSU1TUjFVQzVkVTNILWVaYVF5UjVqSDVrVDZSUDNNYTVKTjlSSW1VLUgxa2xmSXJXSHRwUnJGZw?oc=5</t>
-        </is>
-      </c>
-      <c r="F92" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Fraud_Scam</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Social media platforms now make nearly £4bn a year from scam adverts - This is Money</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Thu, 12 Feb 2026 15:59:20 GMT</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNZTFLQWVHUk4yOC10QTVDZm9GUmxRdjB1SEE5OS1MZUlhWk53ZW1SMjZHUkJ4WU1hZ1AyTHRpdnpIZEdORi1DU3h5azVEUTIxWEphSUQwakhxWFVCdFdOdEFoZ0tjMkN6NXZaVG9fRHVMNlBHaUsxbDl3VmwxXzJLXzhUTkhoYldjSmZxenM0TElyT3FrV2ZVblAweUlRSDFxR1ZlNDNKZkhWS3NOUkFENWE1OEd2TEV6NkRRVmVObloxbVBmTl94V0NR0gHPAUFVX3lxTE84SXZCczhLaHZrSUM5a2EzX2lWdm4yUFRnMVkxYS0wMUltNEUyWGRRMVVjZWE5Vk1HZDYtaHE2U1FsTTF2X2JpN0pPbUJibWozR1FRSEpDMWU1OGJ3Q1BLRUNxdTdwbTdtWXVTelIxSHdTNVE5SmRnT1FHSk42RGt6bzAzQ0daeGYyWXZlcWlYVkRXM09WUjBDOTF5WjN3V3ZHcFliWVoybG1GNF91aDVLY05BanlzRERnT2FxSXlPUkZWSjlnbkUtZUYxd3BTSQ?oc=5</t>
-        </is>
-      </c>
-      <c r="F93" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Fraud_Scam</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Google Says That Scam Tactics Are Evolving Through AI Usage - Social Media Today</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Thu, 12 Feb 2026 17:51:50 GMT</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPVlhwZUxLLWZDZW4za1BlZzJLaW1KTlAyd012WGEtb2pGeXZGUUl6RF9rZUtyeG5OS0hNWFI4VVBBOHpjN2RHVFpxNnpnUUhXVFhWOXRsMzlRYzhwYjZpNkZyQzQ3bWxuRTNhaERIcko3cFFsX28xVVpZeW9pcm40Z0FMbkFNT1d1VTBUWWt4Qy1DVW4wT0lqSmRIRTNIVElmYWlaUTczMnY?oc=5</t>
-        </is>
-      </c>
-      <c r="F94" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Fraud_Scam</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Payroll fraud: social engineering and identity theft target employee paychecks - SC Media</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Fri, 13 Feb 2026 00:17:10 GMT</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNRDg0TFo2VkhXMTNRWGRSWFV2TEdQeng1QXFONGdvNzhobXBUa1o5a0ExeDFvUi1IUnBHVG1SczRSeUVTZk5pWm0ta2lHVHlLQ08wRlBGZ2JtY2FNUmIwUUlUU3RYNGgtWHctaVdMZmltQVNDWmUxTW52UkZZaHo1MktWQ3BQRGM1aVM2Uy01UG53bDU5ZGE5RWljSElubnpBc3NCS01QVkRSTWs?oc=5</t>
-        </is>
-      </c>
-      <c r="F95" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Fraud_Scam</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Japan crime rate surges as fraud losses hit record 324.1 billion yen - 朝日新聞</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Fri, 13 Feb 2026 07:21:00 GMT</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE5Eb0FCOFFZd2tQZ3o0UFZDVWhQZmd4aFJKcEowTUMzWjBkSHBnX045ekx3R1JTSzY3QncxS2ZuMjN2WWN2U0N2ZWhsejJHSHlhTWgzQ2Vn?oc=5</t>
-        </is>
-      </c>
-      <c r="F96" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Fraud_Scam</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Bipartisan Bill Targets Scam Ads On Social Media Platforms - Law360</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Fri, 13 Feb 2026 00:58:00 GMT</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOaGpCRUtIb1RleFlCVDZJQzFueDF4VkVPS3V5dmtJSWtqV2VVRW1ON1U3OFBaSXh0M3BoczRlRnA3OFd4aXVNSnFFamhIWHU5Z2R1SnU0R3ZwSm05MU1fWm9qR3o0V2RWWDFpYzZ0MVJDWDZ5M0lOck83TENvWjk0eXdQeF83R2lmc3o3WFBsMGN5ay0yOHROclgxTVlsSGk20gFWQVVfeXFMTnVXTldxXzdENjJZV1cwLUx3a1B2NDhtUHBTZFFLelY0dHNzVExQRlBNUGgtV25mMWJjUHVyRmhmMEYwTVZsbzBLNHBucFlmdUNZay1NU1E?oc=5</t>
-        </is>
-      </c>
-      <c r="F97" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Fraud_Scam</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Ramstad: With $1B vulnerable to social services fraud, Minnesota needs solutions, not noise - Star Tribune</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Thu, 12 Feb 2026 17:55:29 GMT</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNckJMVXhCSHJzQ0w5SUxmdG1FZm1lS29pbmo5czdzT3hpbzVVOWo5TFF5ZXAydWJzSDFFV2pBRDMzRjY0cXJLaGVSOER1TThuZlM4cUhUNkxCOGVfb0xkZS11OVBPNWdyc3djZ1UxQ24xYzhldURiR19pMUoyTDhhR3pnYjRIQXVGRVZoN0lxaHQ5a0U0N1FKNkMzcVpISGNaVWZWTlc4dzJPbDJQbFhjeWFna1BKUEdRR3h6SUZFSlZyNzA?oc=5</t>
-        </is>
-      </c>
-      <c r="F98" t="n">
         <v>1</v>
       </c>
     </row>

--- a/data/daily/topic_feeds_daily.xlsx
+++ b/data/daily/topic_feeds_daily.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,17 +461,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>The Goldilocks economy, if you don't look too close - Axios</t>
+          <t>IMF calls for tax shakeup as federal budget looms - CommBank</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Sat, 14 Feb 2026 15:09:43 GMT</t>
+          <t>Mon, 16 Feb 2026 04:22:09 GMT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE9HcHZ6a3FlNWlQdUJILUdZeHJ1NEgyWlRZOEJLd2dlcVVidUxjaWc0ekZGUlFaRGJVaHktUWFKWWNfX012WHh6YWgyX01WWHNjRGtPTWVOUmNMVEhMVTNiX09Ob3FSUEVOb3BjNVEwdTE4aHVMdW00?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPOEtzRUhHS0xHenFKZ0FuOGZKdldZeXhLUm55WkZoQk90ZnMxTGM3MmxJZkZPQ1I3Z2xISnp6MTlGVURGVFRCR1RDeFV5QVhMcFdNdDdxTEFyVGhmdDdfMkRFanYxWUotN1lENHpCblpvbUZ4NHRUdFI1azMydzgzQkFsbHFpZFJqVU55Q3BBYTdqcllkREp1ZUNxeElWTENTODhFU0xoM1dQMEU?oc=5</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -481,27 +481,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Navigating Compliance Innovation Amid Geopolitical Change - LexisNexis</t>
+          <t>Trump claims victory on affordability as public anxieties persist - The Washington Post</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sat, 14 Feb 2026 17:35:24 GMT</t>
+          <t>Sun, 15 Feb 2026 18:00:12 GMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQOXFqdWl4TW1CNUNCYmlpRmxzQXZHZzJBcHV4RVN5TGNlWHB3aFAwbUZ6azhfZ0lvWVdvV25qNlFRSzZobkNlcFlsd0JCTjEzVHFKS0k0NEZzTmZHcE5GS3djdm1pYVpyMFZWQmtzNmFGUmwwRmRwNHB3TXdqZGNDTXpXN1U3SkU0NG1OTFd4RTVJd0NC?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxQbkQ1ZHVhWkpUZHpyN040S05SWU5MRElaNFpfaGJkUGtDai1fRHZ5WnFzamtwU2VHWFJxbmlzRm82SFpOLV90Y2NaSkg0VmphbTRvVzdjWHNCX3dxYmoxa1lWRV81NjJLT0IxczRuc1FTTGNZRGhvT3E1YXRPbTBVS0V6d2xseU82VFE?oc=5</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -521,17 +521,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Powering Valentine’s Day with end-to-end supply chain orchestration - Air Cargo Week</t>
+          <t>UK considers new Russia sanctions after Navalny frog toxin finding - The Guardian</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sat, 14 Feb 2026 20:00:50 GMT</t>
+          <t>Sun, 15 Feb 2026 16:29:00 GMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQaEoyZ0ozUFQ4TFdhd2RleDJEZnNGbm1WS1l1RnBHcm1SYzl4NHFESnVYUlBybDRaVTVta3doeFhjc1VkR3lzdl9HSlR3b29xQ2xVM3VJTG1ZU2QxbUZhWFFkZUZ1a09mX1lZdmZGVzBiUUUyQ0hhcnBwMVJXVFdiNUNIX2tVMFlqd2NkSXBrNFc2SWZOR1NV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNR1VtVzZXT285VzAzUHJtbzB6Vk1iaFl1UG9TZnJKdWw3NDVvUFUtVXluQmZCNFZPcWV3WXFKNldKNXFpbXBQMW5IaTlrLVlYRlpVMlc4a2ZFbWttU1czWnU5c1NXNThhRFlFREtFVTZ4M296cnpKX3FNVWJqY285TkxGM28tQkRtNXNZcEdLdWs4YXQydzhfZ1ZOMnhFaFNwYm1z?oc=5</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -551,17 +551,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Get tickets now for Stevenage vs Port Vale on Tuesday night - Stevenage FC</t>
+          <t>Tehran’s oil lifeline shows signs of strain under tightening sanctions - ایران اینترنشنال</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sat, 14 Feb 2026 18:08:02 GMT</t>
+          <t>Mon, 16 Feb 2026 01:00:00 GMT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPNlJGaVpuWV9OWklEWjlyNG41R1kxcjY4Qmtxa2d3dU1fdjRqUGp5RVdPSUtib2NoRi1ad0tBdktMTloxVlIwZHpJLTVFemI3cDJHb3E0WFJNcHRubzdlNlNFQVdBcVhTcVIteWVVdkxOemx6emtTM2h6c2tYT0o1QlZsR1dnRk5xbnZURXhTTjhmYkZtcXh5bDBsUnk4TktKQ2tJTENrZTluMFdqXzRJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUkFVX3lxTE1sTG82UDFJV0x2RVAwbDVYUzA1ZzZfdXVZVy1lUWd2SVhMZ1dWZHBROGNoamZCUHhpTnJ1YnJvSG9tMWRHZTg3SlgySjhDQTVDbXc?oc=5</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -581,17 +581,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Take trip down memory lane with Port Glasgow harbour photo taken almost 50 years ago - Yahoo News UK</t>
+          <t>UK's Courtsdesk Shutdown Creates Compliance Headache - WealthBriefing</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sun, 15 Feb 2026 06:30:00 GMT</t>
+          <t>Mon, 16 Feb 2026 07:44:24 GMT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE9qMGx1cVFVMmcwOVJ0VE1uR29oN3NRT1ltay1hTHZia0NWaUcxZFZxclpSZW4wejk3MzZXaVY5aVZyWnBfS0tsVk5CMlJ3SFd1NXlxaTFtblNzRzBrdjNaUDUzak95a0NxMDJFbzduNmJ1dzRNYnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQaExRR19CV0paZGdUb1pFdERsZ3o2Um4yOWdBREJUSFF3SDltdXBGVVNIOUhhUGJIX0xBREREX01HZ183QmJSUHVxekhvSlpIVjBXb19HZjZic2N4RGJUdkFlY01acS1jYXdlaC1iMHlNbTFKVTFzNjA2eWlQU1lRblFYeENUc3Q2bkNUbUMzT3NFcTBUUG54RWZuTFVkbTVtMTRVcA?oc=5</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -611,17 +611,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ramos Pinto Late Bottled Vintage (LBV) Port Wine – 75cl Bottle, Full-Bodied Fortified Wine, Gift Box - umlconnector.com</t>
+          <t>Log-hub introduces Supply Chain Agent - FleetPoint</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sun, 15 Feb 2026 01:17:12 GMT</t>
+          <t>Mon, 16 Feb 2026 07:20:08 GMT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOaS1wcGNESW9MRnVVQXJYeHIwTFZrMk94MDdQOUtGVkZRY2ZsamphdzhlaE5zdkVNTG1ZVm9RUUtGVlktQjZjdC1wTm9HZWpvR0hFZWF4VWFvVk51RVA1OXlTQ1MyRHlIbkZIbENTTHBOY2pyY2I3Wmo4cEQ4bFBZN2pRQzhsQkRPU21yclhKaExxVU1fVzRz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNNHd4RkJDUFZYeEd6ODJGay1vMW5UQkFUcWZjZ2MtNHdfMmZXbUtnWlczcURiUnpIR0EySVlHcTBJOVpNX0ltUndYbHAxdW9oX1puUUxxSFZfek4tdFB4R1NXNUNydjQwUE9UU3dXNzMzbFZXbzdSemVWLUt3emwtUWFXMFBfR0dUZkNaMnVNZnI?oc=5</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -641,17 +641,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hapag-Lloyd and FIMI to acquire Zim for over $3.5 billion - CTech</t>
+          <t>World rail freight news round-up - Railway Gazette International</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Sun, 15 Feb 2026 04:54:00 GMT</t>
+          <t>Mon, 16 Feb 2026 04:49:18 GMT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTFBvdXB6RG44NFJqOTc0RE5QRGFnWGhTd05RcHRZWm05a2tpWVBSNUVtTnNnVUVQM0t6cW8wT19sdm9ZUld4QlEwXzhSRWczYjVtckg0X0dEOFBIWnZTYjR5bkdUdGVrbEpJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOa0FzMUplUC1ZRzJfbGZXbkdRamJIVzNGN0xoOVBGVGt0bnRzTUhBRE5rZGE2T1FKSDkwcV9LRXRaVWV4OGw5Ymdka0hRNk1WUk1vSzRHNC05Vy1MSDhKN2VQTE0xcklCaFpiQ1NZdzdWRHZKakRjenh0OHlIT1A5bUdXbDRQNm55U1JsX2dB?oc=5</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ofsted hails 'welcoming' Ellesmere Port school with 'happy' pupils - Cheshire Live</t>
+          <t>Container shipping scheduling collapses in 2025 - Seatrade Maritime News</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Sun, 15 Feb 2026 06:00:00 GMT</t>
+          <t>Mon, 16 Feb 2026 01:48:16 GMT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNUUE4V01yRVQzMmpsS09wUUlERUU3ZUtaa2Jma0RDTHlEdTRfNDRONzAtVVA1RjRBbGQ2a3VocGl1YWxLZ0N2RDNJU3k3eHNIS05aanF3SkVFQ3hDNE90dVE5WmFHRmx4cWJGdWtSMXpOUDQxRmFja0hHcW40SFZUNG1UQVQzaWNwUW5OUWN3VVdlY21nbkNJTEtsUE1uYTRGV1JKd0lrVHDSAa4BQVVfeXFMTzVGQktwVjJ4Tm55TUVJTWhwUDdTck9hZW1qMWh5OFlGTnRrdlVjdGo0X3EwT2lwZkpDSEd1M24zMGFDcEUteV9ERlg0VlcyLUpGX2dyTkFncVl6bW1abjNaeFI2WHpoZW1PSGQ2NVRJS18wc3NoZERYUlN4XzkyX0dLNDVuMnE3VUduY1VsbFRtTXJuY1FIT1g5dzVnSUF0OUt3MWkzM2Q0RXpvWWN3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNSXRWNVZCUXN6OWlKWlFGMHAyMGhCSHl2aXI0UXJvVl94ZE9QNzU4d1ZuZC1iZkREelMyMFZFLTktVmZYNE1neU1Wa2loLVl6dmxpWmJVWG1CZ1hDZjAwci1Ja2tmMERmS0o1R0g3OXI0SUpwcENZX0ZkaFZhZTNzbVBLQWltbGlEUEs2TVFVV0g3ZGg3SnJ3?oc=5</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -701,17 +701,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Red eyes and black beaches: How one of the worst environmental disasters left its mark - BBC</t>
+          <t>adidas taps project44 tech with focus on how AI transforming supply chain over next decade - Retail Technology Innovation Hub</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Sat, 14 Feb 2026 21:49:18 GMT</t>
+          <t>Mon, 16 Feb 2026 07:01:44 GMT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE14SWtmZFMwQWVkZ0pnRHlnbWctR3lJdm1vYzJsTjB4eEVacG92VlM4eXA4eGxqNHdaT1htY1JOYmp1cWJmN1RLR2syMU9GbzJWNjVhU3dFUFVrZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQZ185WHQzQ3FVUk5BZTdfb1VlOTAyTGswUEx6aUVsWkNZWU1yRkNIZFQwNkF0Z05QRVdaeHdrWUtPZVBMbXJlYmtxNU9HdnFabDNtbXJFVWJHckRkOEZQUDVnb0V1NlZ2ekttUlZqTFN0dXV2dGxJZDNXUl95Yjl6djR0cGo1R21GZGdYazhXR1JnNGhSM2RBMUhVekVYWm1ROEJfNzljaWtZSU1ndHR4RHpGTGliV2w1QXlOU19Na2YzN2VubThVY1lXSGJEdWpwRE94eHIxSE8?oc=5</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -731,17 +731,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>COP30 Shipping article - Norton Rose Fulbright</t>
+          <t>AI fears rattle Wall Street as logistics stocks slide - Trans.INFO</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Sat, 14 Feb 2026 08:28:42 GMT</t>
+          <t>Mon, 16 Feb 2026 04:08:06 GMT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOVXljbFIwZS1WRUs5NHFqMjJja0xkYW04RkVHS3g0b1o0TmpUQ1RHS0QzV3pkMUZpRndmemM3R2J4eUYwYTZVWFB0Yk1mRndnVmI0TnJsNWJHTWR3STZzbWJ5d3psVHVwbzFZa2pKSlRQOXVqeXQwMEZYLU40RVhMQXZLeFd2QkVlVWJRUnUwdmVrejVUeTNNMg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUkFVX3lxTE1rWHgtZHlWdEVsby1STFdPMkdSVThWYmVSbHZab1BaSk1GdEozLVdSclJhUzJObThfSGt1WW94TWJpRWFPWFZwREthSDZPMnRzX0E?oc=5</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -761,17 +761,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Trump’s Maritime Action Plan seeks to resurrect US port fees - Lloyd's List</t>
+          <t>Trump Sanctions Chief Poised to Leave After Bessent Tension - Bloomberg</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sat, 14 Feb 2026 21:00:48 GMT</t>
+          <t>Sun, 15 Feb 2026 18:27:55 GMT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOZl9BM3otMmRlNk45SjItLUhrbHZrSnVuNGQtWVFVQ1I1bVU2VmpHSnRmaWxKcVlCd1haRWlnc3VPcmlOenlFekd1TVBoWGdBODNUU2hiWUlGU0Jjd3lGRGluR2tkYUozdVRFb1BZNkR5Z1FZSW14VGVJLVZRWTZqLXo5RkdoOTFpLWw3dnpIdVBETjVhRlBvVTljZlhWUjNPZGtvaFJidFA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPazhJdkw1cHBJaTFETkk1aUFnQ3U5RkV5MVJncTdONmxHY3JVNWJEY0JKWGtRcElwbnFXcFQwRlVQTWRxV3QwM3lmVlFQZXI3QjZaWFB3aHRHMEk0OGN0bllWdThLM1E1Z2dmSlNkcFdOTnJxQzVESTRsMlNiZW1EMzFyNl9TTV9kemJuY0pGeTdCMFhFa0hSanVrRE1XWm4wWDl2cG9uM05QVXMyYWhNVEgydG9pZw?oc=5</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -791,17 +791,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Oxfordshire businesses warned to 'act now' ahead of new EU parcel tariffs - Oxford Mail</t>
+          <t>Latest SRA fines for AML non-compliance - Today's Conveyancer</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Sat, 14 Feb 2026 13:00:00 GMT</t>
+          <t>Mon, 16 Feb 2026 05:07:29 GMT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOZzlqZW00a3lqcEtqS2R2a2pkcVRnQXhvS2NkLTFIM2tuSjVNQ2FIQi1nSXJwTXNGQjcxd29CenlYUUlSaVV1NThQVUJid2dWaVJMdGJ2UG5seU1aNk5DdGRkSjdzQXpRbmtsQldkQmFCXzJzZkdTbE5RczlWQ0QwbGRScnpiRkFhTGptdEJDWGg1dFBBdzZqNg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTFA3cnZvQVNFRV9STFM5OGxVTnVObnJRMXMzaE1mRlhPYUxiajRmLXBXYmNTYjNrd21fcUdVS0Z3Q002ZDcyclBpaHRqOHVwMXFuaGNxNmh3cWhreGc2Ui0tX2JocmFPdzVQRXhyZTVGQzZSMEZYUjhR?oc=5</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -821,17 +821,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>How TOMRA is Unlocking Supply Chain Value From Mining Waste - Supply Chain Digital Magazine</t>
+          <t>VIDEO: Hydrogen Strategy delays ‘risk losing’ the supply chain - Energy Voice</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Sat, 14 Feb 2026 09:02:32 GMT</t>
+          <t>Mon, 16 Feb 2026 07:02:58 GMT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTFAycnZCbHZGUmNtUDdKZkgzczN4RHQ1bnlIMDFYcEFIVFc5WXg4ZGxIaDNXc1pUNXhJY05CMk84ckdRTjlyV2RveVZySC1KeEJGRGp5dXBsSGJYaUo3MzRyMHR3RTRCRFZneXd6UVd3YUZSUEViazBlS2NCOERWQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxORE16NzNkY0lRX1k3Q1k2eVBvbXFSTUh4TFljT3hUTnpFdkthZFNvZWlGbC1HdXhHMTBEc2R1QVNYa2IzUVRBWU5WMy1xSFJfeURNaXQzeVNibEl3N0Q5OG5NWVlSRkh2akxZT2lkXzFCdmVCNThTLUxUdUVKWW5KZlJDQmtYOWJIaDR0TkREOU5QVk5Icm5GNlFxM3hRX1hWbW1iMHdRcVMyb3BwdW1jM0ZNeEprNklCSmd2S2FUcFhpUVE?oc=5</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -851,17 +851,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Live: Russia says Ukrainian drones struck Black Sea port, Rubio to visit eastern Europe - Yahoo News UK</t>
+          <t>Trump’s Maritime Action Plan revives threat of port fees - Splash247</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Sun, 15 Feb 2026 07:26:57 GMT</t>
+          <t>Mon, 16 Feb 2026 07:28:09 GMT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE4xMWlWVzZfR2pyYUJ1dWNzam5zSDdwTXlCNEk0MjBvWEJfTEdIeHMwMDRrRXByOXZpOFBlZzNJMnZyMUNVcC1HSnF1SXVqVC1reHg3RXhZQ0w0RVVQR3Y2Y290N2ZlTXppcDJjOGJ5eUlia3hSbWoxeFZoWXg4MFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNVTBtNHNfd19MNldRMXVrS0U1Tk1XTm5Db3FMdzNWUmJka2g5TjV2ZjUtOVFMSEdYSklsNldvMXRhSVdKQTVWWnRRT1R6cGNIUGxoRmhHQzI5elpaU0wwUzJsbWhTd2o4Y2w1aVJOQ0ExQ3pvNmJwLVNBWHhOd2JCTlh2RDQ?oc=5</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -881,17 +881,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Analysis: US Treasury sanctions Hezbollah front designed to insulate terror group’s gold reserves - Long War Journal</t>
+          <t>Be Port of the crowd - Cliftonville Football Club</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sat, 14 Feb 2026 13:01:50 GMT</t>
+          <t>Sun, 15 Feb 2026 16:19:52 GMT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxNOWpLUlAtNGxmc0pvRldYRTFzb1BkNDRkZlNFR3ZJcUhTOHluV0QzVU45d0FhSVZQbE1BbHlJZUlGbnZ5aGl4NUFscWEyREZCX3ZZa3I2dW5QU3lZTXhuRDhmcGJfWEpHNWxtRmNKVENhVVlVYm5MSDhFZDhsYnJnTUF3dVVhQzVjbjRfSnFMTjQxbW9FbzVqdnFuWVg2LTNKOTVYV3lseGVRR0RFVmMyaEMwTzI3M3U1SkRJRllzQ3lvVk15MC14STVXYkxuUnF5bGNjc1BaQXFaNzlncGhaTw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE8tQlJlUFgwd1BrSHh0SzFsdkIxXzV4NGI1ME1ydi1WX09pWEl0T1pvWVdmalZqcGlhWG1qeUc2TENfQjJBVnJvSWFmWTVYZ1Ywekh4cDRuTXdHTU9weVVCbzlBb2lNSXo4MHpr?oc=5</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -911,17 +911,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China to Scrap Tariffs for Most of Africa from May - Asharq Al-awsat - English</t>
+          <t>Man's years of domestic abuse included throwing partner's belongings into the street - East Lothian Courier</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sat, 14 Feb 2026 10:01:27 GMT</t>
+          <t>Mon, 16 Feb 2026 07:03:46 GMT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNN0xIeHBsSUQwdU5Nd25TR3FvMFNZSDJWcDl3ZnBOYjktR0ZnNTMwNkhrUEozVllzeVRodm1sSXN4VVVac2VtdkZEWFpma3hId29zY0M2Z2hCQW9wTWxaTHhXWjBKc1Z6bmtXU3F4emxjVmlub2E3ajNRVzVUY0QwZlNtX2YtQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPVVpOVWFPUzNyR3c4YXVCQVRpXy1OTGtyQXJqZ1NSR3U3U1VIX0JjX0VHalMyczI0Vl9HcFNCNEJEdnp5OUZpVWxpTU4tVF9YS0dnZHF4aW9FVDFRbWlTYWpVcEYxX0VER0NBbmo1SUFCSV9aUUdpV0lKeWdoUG44WVdXWk5KQVJyTXd3LTd5Tkp0R3ItUFhIOExoVmxrTURp?oc=5</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US passes Hong Kong Autonomy Act - opening potential for sanctions on persons involved in Chinese government "crackdown" in Hong Kong - Ropes &amp; Gray LLP</t>
+          <t>German shipping giant in talks to buy Israel’s Zim for up to $3.5B; workers go on strike - The Times of Israel</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sat, 14 Feb 2026 12:48:54 GMT</t>
+          <t>Sun, 15 Feb 2026 16:42:00 GMT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxOUnBIZXJ4VGxXdGVZbE5UTU1lMzIzZXFXNi1helhncjFjem12cHg3Ym9SaFU1NUdyckdtNDhuZElZYkRpUzZZWFRGNF9ZNjdFWnRyUHF2dllVaGdnX3hvNWtGZkE0bTFYWlpGNzlRT184ejVrRHJvRHdzUkZ0d3BERElGSkEyVzdGYjJuZEdJVmR6cHR5VHdnTWwtcUVVNEl4QmNPSlFaeFdGcEFFNGgxNVFFazllb1pFZUo1ZHJ3MGpxeVlxVzRJZ3B3Q3RJeV9PUmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOSjZ3dWJVU2czNlhiU3pmOTBuQmRXSGd3NkZka1JqRXpLcE5SMFhBMFM3MFZWMTVpS0NaSC1IbWIweEZ3Mi1rZm94RzBndEVJTURLQW94RTJWdFI2QWFtSnRXV2pwLWNFN2QyUzZvazRaVGR5OURteUs2bXlES1hjcTBjRXZmU01laVBnZ09wZWtrY3hyN2xzVWZuWm1iUXJ5VzRYNWF4UHUzb1J5UEsydlluSHpSZ9IBuwFBVV95cUxORktMODhUVndXY2E2NENXT0ViWkY0bEhkMGItbFYzbzlJZllBM0FoNVlZakkwS1VySHROV1BCSjhjWU1pQnJ5WllwUTFBQXI1bmJIXzVwYkVGUXJCRUF3emtPYWpmS3pCSlFvaThtUTUyVHlMcThqZTRHZTN6YkRuOThOaVg4VnBrb1p1RGltNEcwUGxudWt6eE5xN25Xa1FjLXdYY2s2X0I4SlFoWV9pZTJ2M3hRdVJzVUFn?oc=5</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -971,17 +971,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>UAE deepens Africa investment push with focus on renewables and logistics - thenationalnews.com</t>
+          <t>Ukrainian drones hit key Russian oil port, local governor says - politico.eu</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Sun, 15 Feb 2026 04:41:15 GMT</t>
+          <t>Sun, 15 Feb 2026 11:47:00 GMT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOek15VW9XVWNOVGR5NkFMRmRBSE5VZkRHRVdTVE5IRE56ckZPc2hnYVhUcEowWXU2d3VKeFhJUDc0NWdzalcwSExNdFpJSmJ3QVl5blUyT2o0NVRaVDZHQjB0aThnbWwyQks2OTJ0Zll3dVpUR2hLVTBmdFc5SU5lQVhQVUJpNi1aWHFHeWxvVGRyazZnb1d6X21LaHJ6SWstSi01QXpUbEYtQWJZOTRrMk12am56cDRVV0xyV3pYM2NlVVY3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPSzFCZUxPNFFhRGNYWkY1NG9leWpnNHdjREVkV3ZkSXViRDRTT1ljQ1doRTJ0bVZsR0QwcmJsS3V5Rlp6VERkY1BOUGMydVZWRExWS0ZjeDI1M3NiVnNQV3RCMW1CMGhYRmJtQ2M0QXpBNlBDc0VMYkQ5S1JfVW9Bajk1dVlGYjhiVjhrTjFuUTBldEM5UTBSaTh3?oc=5</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Iran will consider nuclear compromises if sanctions on table: ‘Ball is in America’s court’ - The Times of Israel</t>
+          <t>Fragmentation, Governance, and the Limits of Political Settlement and Peacebuilding in Libya - Peace News Network</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Sun, 15 Feb 2026 07:11:50 GMT</t>
+          <t>Mon, 16 Feb 2026 05:00:00 GMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOTHVUZEo2UEJ1QzBjRnlZZ2dHajNiTVpsYkNfQjVqc2VPR20zSzdrWGl4SExNdU1laDFOTEFRVUFVQ1ZDZzllMDdnVTl1OS1IOFZIOXVYNkhZSXY3UEJ6ckNIWWEzRjhFbXBmTkI1RVZ2S1FuSjJiNUtiV0ljd0JzN1FhT0hwRzdxUF92N1ZZaVNuWXNsQkZUWkpacTY0OHZwOXJnWnZnNjB0Z3hVM25VR0RUSi1HVnpBYjFpTWhEaDIyWVczUDVMWmRxSnI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQcU90WERqQXgzaWVlY1lCb2RrSE5ieHhteE5OTHhsdGNqNXB2TUxfUFVlUGNFUVlHd1pVT0daTFpGYmhZcWZxX3NMV2I2Mi1nTHBvdFIxWUE3V1RfcmhtUXB1ZEx5NjFDakVWT05NQ3VMWWpzMzlNN2RIRXg2RG1QZndWd05ad2dCRFJHeU5hR2hmM1hqQWw0U1R0bHJYUzl3RGdpdkduM2ZfUVFDdWFaUVdWaw?oc=5</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1031,17 +1031,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>24‑hour gym approved for former Wilko unit in Port Talbot’s Aberafan Shopping Centre - Swansea Bay News</t>
+          <t>Op-Ed: LNG is the Future of Shipping's Energy Transition - The Maritime Executive</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Sat, 14 Feb 2026 15:08:54 GMT</t>
+          <t>Mon, 16 Feb 2026 00:35:00 GMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNNW0xMXo2TzdCWEpid2Z2U3c5WDAxR3NqNDFuNjhIZDVCajhzS1YzWkx3X0hZSkpLR0RMM2NYUGVZZWtSTW9vSUpSLUdqT2FSeWJpTFVkSTVSck1sclUzT0tDMXZOV2FXak9HVGJHVnJ4OFNpNU4zelJrODBLSExQTUczZEgtaVJ1TmhhTHcyd0RYUm9VTkJHeVlOVHdjV2RzOHQ4QmliZHU3LUNnekgteA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQcHZHaWFOUUptTXl3ekRlcFZOZGs1emVpSW1ObVU2V0tKWC1xZlVub2JQZHpqSlVoX1p4YmU3WHdiSkVfYzVTS21IdGRXc0YtM0tIV0FONDdUcXB2QWxveHVlYWJyMzNJb0xhcUZuMWNTM1RiUGR3WmpxWHJ6MjFOdXVOVWZyd3FIWDNybGZkSG9vOXZ6ZHc4NVVkTFBGdw?oc=5</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1061,17 +1061,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>PORT PROVE TOO SWEET FOR JAM BOYS AS WINNING RUN CONTINUES - Island Echo</t>
+          <t>How NHS Supply Chain is turning Scope 3 commitments into operational decarbonisation - GetTransport.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Sat, 14 Feb 2026 20:50:07 GMT</t>
+          <t>Mon, 16 Feb 2026 06:42:08 GMT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPNXZpczFBUU1Tam1nRENfYy0tQkZuWWprb0txUWNiWGJrcTItbkJpWmNYVF9vSnpvLWo1NlRtbnM5U0pRa1QtTFlfcmx0ME9JdWpTTkFQZHVvS1RRV1hTSFhWRThyRHM0cV9RcjJacGcyVklKaHoyd2FaeVZVY25qc291dXhYaVNsbjJ2WU9ldGkzUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9CX0RxVXF6eWdja3FrWTJUNmtiQVZGMDVKUmNNb1J0aHpiUXJ2cEJKU0M1X3ZoSnY4bEl2cjg1Qkdwa0o2Q3Y1OTg1Q0lYS05OWGpSSTUtQnEwTVFvdzhpblZGcFBfSXo4eHJYWEFOYWoyaFpYOFk0R1VZZ0Jjdw?oc=5</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Assessing the Acceptance of and Compliance With Centchroman Usage, a Non-hormonal Contraceptive Pill, Among Postpartum Women: A Cross-Sectional Study at a Tertiary Care Centre in North India - Cureus</t>
+          <t>How Fluor’s Procurement Powers Nuclear Supply Chain - Procurement Magazine</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Sun, 15 Feb 2026 01:47:45 GMT</t>
+          <t>Mon, 16 Feb 2026 07:33:57 GMT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygJBVV95cUxQVjhGV0ljYW96d011amVJUmNUMlc3UFB4alA4dTdhaDhoeWdCZ0F0eXNrbTdBUmFrWktWbEJhVERXNHBCYW5rbjFScXl1U1E1dTNHbkhKQUt3NFFmR0xCbU5qUmdzazloOTQ2YWE5R2ZRNUJYRzQ2NUlsbTJhNERrM2p0Zk52QUp3R3Zka3RwN3V4eVZ0LUdTaVhZMEpxQ0NJbFF0NEVlNEdqZDNCdEVVbGdpUk4weWxTSExjVHUwRnNHZ0p0UDV2MHRQczE0U0Z5XzBiYkxFUU1TMEZPUXFWS0R5czRfOGc5U0d1NFlWanpqaTBxaUpWeWpQRUJDRk44WWJMOWdiSUx1Tjh3SGxMMmVaTEVFUTZDVTg1Umk2Z1FEaVg0SzFDQ21fMjlyczh1aGRpUV9oVkNjXzVFekJRZnV6VnJxbXQyZUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNT0FGVXNYRzlqMnk3WEt2TDZBZHpFYUg3RGoyRmYyUFl6YW51dGV4eURaSW5aeHJ2b0ViaDROT1ZRRXk5NXQtM3N1Vnp6OXU2Sm9kT2lmSXJpOXNibUxvMm14SGJtSG52MHMtdEtmeHZyX2RSbGU4OTRHM19VTVhkS0pINVE?oc=5</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1121,17 +1121,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Celtic’s £24m reality check and where a year of instability leaves this football club - The Celtic Way</t>
+          <t>China sanctions - Table.Briefings</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Sat, 14 Feb 2026 15:26:00 GMT</t>
+          <t>Sun, 15 Feb 2026 21:27:19 GMT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxORjFTV3F4SDYyNE5QakxQcTVnTHB5SldBekJ2R3dPTjhndERRZGVDWFQ1RXVwYk5GTmtaYUhBTm5IdlJjWEdpUk56UjN0VmNDNlpfUlZfWm5fcUFweGRYdWFNdUtmb1k2YUxhNW4xMThYZXh0T2s2SXhrckRiM05GdEJ6S1pXcUFfT0ZLQ1FfdlJfd1FJVlFZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTE1iMG9jUXRWRklnaXJka0hYZi1GWXFiTkZTN3AwXzNRQjJRWnZjM0UwZlJhWlZhZDQ3YVNQdjM3VWNUWDNCQXV1TEgtWmxpeHBzQklJNQ?oc=5</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1141,27 +1141,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>About 200,000 join Iran demonstration in Munich: police - France 24</t>
+          <t>Iran says ready for nuclear compromise if US sanctions lifted - Le Monde.fr</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Sat, 14 Feb 2026 14:15:17 GMT</t>
+          <t>Sun, 15 Feb 2026 12:03:21 GMT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQTERZaEplQXpZZVVpakp6QkJ3ZWNEM2h5T041bFZxR3BnYkRVVlBNd1pHZlJBeUpJSUp4bUlRWkZOX21CdWdmbGtjWmNVd1pGWTc5OTBBVUw4aWl1eHRNcXYyeERLVzlUY0xqWHdGaWthWTZORVdQd09GcFBoWEFlRnE3anRKSWRucno5UEtZeW43dzFMVk5MWkNqVE96UDZSenAxd1Rn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOVm95c2Z6V2J5QjNJTzdwZm9FdFRKd19QVFliNmZLTjhNeC14LWFWVzktNnNfaWEzMjF3czRucE9MNUQ0eEdSVFpXQ3l2dU1KUHYyQndzZnJpSEpJRFRmaEFFRUI4MktOMEZTN1dSS05NVE5ZbTdycGFUZHpDS3JNM3hZR2FwZ3djclJXU09SWFZXbWh2bnhNQlhhZ2lWbkV4RjRueFUxX1k5RGVnaVdqV1FnVHlwMzlDemNRQXRVWERCaEZFRlVCN2Utdw?oc=5</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1171,27 +1171,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>The right to protest and reasonable police response is under scrutiny - Australian Broadcasting Corporation</t>
+          <t>'Port Glasgow parking bedlam is forcing me to push my baby's pram along a busy road' - Greenock Telegraph</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Sat, 14 Feb 2026 18:00:00 GMT</t>
+          <t>Mon, 16 Feb 2026 06:30:00 GMT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQUGdEVnhkelA0WVZYUnMtdU9IaHJNeG4tU0hORFF5eDhaa01Ic2Vqd1FrcVU2bV9CZm5hVjRTU3V4Y1IxcWVXdnV1ZkxseElDQnVwRFJCNzFzVTFyZEdkRWxTSVJUaHpZRHVDYUYycWhVVlpZX19ibjQ5eXNSRHBYOEtSYVp3UmVXcUhLQ3R0Vm9VX05ZaEZ1MnNPZDNXM2Ru?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOLW54cEFhM2toUXA1X09RSjdkMERzeGVGT3pHSlZFZ3M4ZVRYYjFvVGh6ZmYtQmM0MDdTdkNHTy1BMElTWl94dmo5bmJFcGdVcDZCR1pObFc5SmVIcjJmWGQyeFNaWW5XakNHMjdJTktuanNScUZrUGY4ZU54RV9BR056NUxrSXNyZHpJM05xcUJPZFkxZXg4ejlhSjRucVNa?oc=5</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1201,27 +1201,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>An estimated 350,000 people march in Toronto in support of Iran protests, police say - CBC</t>
+          <t>Tariffs Popped 500% — Of Which We Paid 90%. So How Did Inflation Drop? - Forbes</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Sat, 14 Feb 2026 16:54:00 GMT</t>
+          <t>Sun, 15 Feb 2026 16:12:12 GMT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQWmFUaXVwRHpOVWJLWEZuaERpVHFfM2FqOERyMkVTSDNXWnpKZWItdXpfWk5JdE85cFZ4QkgwR0RNd2JyN2lDWnMzUWo5dXl1NnFZTkZtcnRRSjAxMjU1Zlk5bkdlMWJ2Wk9mcVdyYkZqUmFBaGcyX2VwQ0k5czdMZFUweklyei11eWJvUUt0ZWZWR1E0V0dz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNMlh0RVBZYTJ5MHVQdlZfcE5BT04tajlHbnFmLVhjNi1rX01XYjJULWszZXBFb3QxckxxSllhUldXVEhpLS1QS0hqcFJQdU5saXN2YmpHUmJuUXo5ZjRROC1fbDRkWHFIRVJ6SDcxWkJCdFg4S3dPd3AwdWpJY0YzcWJRSjFSY2VfbmZablRZQmtsVDZxdnExbGhFTlppOXdXaWNwTlE5YWNRT25WWWhsOVowaFU2WFhGeWc?oc=5</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1231,27 +1231,27 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Air China to Launch Beijing Capital–Brussels Route on March 24 - TRAICY Global</t>
+          <t>GXO Logistics Extends Automotive And Defense Reach With BMW Deal - simplywall.st</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Sun, 15 Feb 2026 07:19:26 GMT</t>
+          <t>Mon, 16 Feb 2026 03:47:01 GMT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTE9yRFdpc0Nmb3hJUXRmdkp5NlBzakFjSlFjV1k3REtpaTlkTW5NZFNkM1dZMTFWSHA2VExaQ2E0bkR5djYyU2xkZ056cE9nQnpFdk9iUA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNUHhweVJmQXF3Q0FkUGZ3Nm9hZHVKT2F2YjVQa1NualZOVi1VSTh5a1R0RmpYX19aclR0Zk1JaG1UZ1EtV3VBNzhKZ3pFMWowelQ5Rk5FZGxaTlJRUUxoS085aW8tc3lDX3lIYUZ2WnJQeUE2QUkzdTBhNXo1QU5aeDY3LU01ZUFXTGhBVThjdXdOaGI0SWJQZmZPcWJiUkt4SndOUFltbVZQOUcwUm10eVJXdHo0LU5pVEFZUjN2ZGRPZEl6ZmVlSnRoMWRrZGs?oc=5</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1261,27 +1261,27 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>India seeks to broker consensus on global ‘AI commons’ - Financial Times</t>
+          <t>Oil producer Maurel &amp; Prom welcomes easing of US sanctions in Venezuela - TradingView</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sun, 15 Feb 2026 02:00:05 GMT</t>
+          <t>Mon, 16 Feb 2026 06:57:00 GMT</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFAxb2VqUzlQWHZRRy1RY3VQZkplX0szRVJQRkhmVFlYOFBCVGI5VzZEZnhmYUt3MzM5MzhUbG54LTVFamJDbTZSVVMyZWFfaDNEejROWER6U1dFcmhZQmx6d1ZhOEFNdFgtd3k3RkxFSm8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQeDRmV09VUzR0aHJoSG5pRy14bFR6eDRCLXR5UXFjVkNtbWFvMUsySGNDY0o4ZUF5Si1GUWZiekJUY0pCYXB4UlJKMkpfM3VhMXV3VmZZSUhfMERPQncwRVJET0lCR05ZS254WWxUV0VRdkYzXzNDRXFNcFdLTDZoVzBQVzl1N0xYTXAtWF9XbjZZNXI1T3JpdHR1NzVUSng3NHd5OHZyb3h3aXVPdzN6Nk1lRURJOGhtR3lEX2J6NXVVTE9hb0oxdmtwMzlneXVsejM5djRR?oc=5</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1291,27 +1291,27 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>No swiping involved: the AI dating apps promising to find your soulmate - The Guardian</t>
+          <t>Seoul races to avert Trump's proposed 25% tariffs - upi.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sun, 15 Feb 2026 07:00:00 GMT</t>
+          <t>Mon, 16 Feb 2026 02:30:51 GMT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPV1Zod2NZMU1vM3k0dTR6UVJBWUk0M0RVb2d5MVc4elAwN3pzNGlhVnMxLVZTMS1QMkk4ZFVOVEJiajZzdTRCbXhOVmVWci1wXzRsNDRESnhpVy1HckljUndHMndydU1EY0RVMGZoLWR3S29sQ3MyczRodnpJQ0MybU5ocG8xRmhpX0twR3JKOXE4YUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQc25sd185dk5GbGkwaF96SFJkeFBiYkF2MV9FQV9VMUxTRmZGVWd5cElWZS1FNEszWHlXNWRValA2Z0ZteHZscktybllscXZIb0NJbHJGbTNFNHNZTXJsMU9Zc0RTRWc1ZVZfSm9fSzZOb1pGMngtbGtQZWxOLUJIVW5JT1NXeFg5MkVCaTAzLXZET0JmX3ptM19IdTNadlVnd0HSAacBQVVfeXFMUHdsR3NXTVZhYlpkV1pzaC0wRlZXcGwwV2JZeHMtWElMeHE0WHVGZDJPX1F1dkdoUGgwVE9FTFhHeV9OdF93bVBlNzlRcm5LOWtUbExaRzdvV202X19idGplZHNoaVNtZjg0dGdYUlFIbUVSQlJLQllLNnpBamhiRkc2UFlpeWlETkZFNEZMWXBVQm9wTDc5YlFQWF9BRk1oczB0d3c1Tmc?oc=5</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1321,27 +1321,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Will A.I. Kill Translation Jobs? - The New York Times</t>
+          <t>CK Hutchison warns Maersk over Panama’s Balboa, Cristobal terminals - Shipping Telegraph</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Sun, 15 Feb 2026 05:01:06 GMT</t>
+          <t>Mon, 16 Feb 2026 01:58:31 GMT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPX0M3cjA5Zi1DRFMwMUtGS0k2cFBwQy1PYnQ0TDQ1ekRUbVUwdXg3VVQ4TExWX0VnY1hFLVUzZE45c25BZkJqQkNiMlBMZ2NjSU8tZW03aEsyc3A4ZTVXOXVZUlczMERKeVVLRmhJbGVSaV9Fc3M4QTNhLWEwNlZfMm93UmYwbkVWUTJYMTducGVwTkhjTEtGbE1RZlM4dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQTFZEODlEcjdvNmx0c1Q1YkNsYmo5QUh3blA1UXd2LXBJalhvU1duT01IMVZqLVBqS1Z2T09IZ3pyOWNYNGw3TjNhYU5qQ0xOQy02NmRiSGpiVUhFYXRrTTNRVnE3dGtNU3NvZG1RVmdpM05fTm54NXBOWTJqOWlUNWVmMm5lNjhyS19raEYtcVF0dENBS3lhdlZZTWUyajRtX0tUdzJpZWd0QQ?oc=5</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1351,27 +1351,27 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Interpol backroom warriors fight cyber criminals 'weaponising' AI - France 24</t>
+          <t>Memory crunch tightens CIS capacity, pressures smartphone supply chain - digitimes</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Sun, 15 Feb 2026 03:45:22 GMT</t>
+          <t>Mon, 16 Feb 2026 07:24:07 GMT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQUjZFek9GelIwRTI1Qk00SXRydHhGa3daMnVpQ1ZTckFfME5YeVp5YnpnbmlHbDhSaFNDM3JOTzdBcmxETFZLZnZRRUtZeDE1eDBmdVVNdVBySDJIOGVOckVmdDVvbDBNVlZFNzl2OHZnZldWMWRVQkk1UG5PRDBKV2psMENqcGJqVXI0V2lwanB3aWtzZzdQdUw2cnAzZmliaEJIeEplZjFlWDFJRS1z?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNdFdfZjdiVnRtaEl1eFBRNzRuSzFxZnRXamFHeEtQTjl5ZHlzclQyWDV2WXZPbGNBRTV1Y3VsRDhoVWgyT2tsZ3lESUkwaGR6OG1wR0xCUUw4cHk3Nk1fSU1wdEhvcHA3eFM2dzczVVdmTmdRM281aUozV3VMVGpDTWhtR1RvT09sU1FpZVZQN05Ed1RENms4dg?oc=5</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1381,27 +1381,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>UK focus groups find support for sharing health data for AI is conditional - Medical Xpress</t>
+          <t>Port of Aarhus sets record container volumes in 2025 - Container News</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Sat, 14 Feb 2026 23:00:02 GMT</t>
+          <t>Mon, 16 Feb 2026 07:17:28 GMT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1tLUJYNjEwN29ybVhxY1p2QWZoNzRWeEJoLTJLUmJYQ0d2YWFIS0ZPODY5QjNvRjc0N1JjS3hNbEFKb2pWdko0RnlDN2FQTzVQdFFMaEhBX2F3V1FleGNGVENFR3FDcTlTa3VreEY5RTNhbEJjN1pLTw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxNbWcyQVY5U1FOSlZZRVFJTXo5Rk43WGdhZmNVLTQzMktjOVhMRUVIaW5LSVN6RVFiVnNfaHdaRTNuMjY2eS1DY2lfU0FKbXN0azRFQnB5cGtpOENOczNkYkczNUdXNWplUlJzNzBrVnN2N1ZPUEk4YnltSHZNVng3d0gwNHdwZmc?oc=5</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1411,27 +1411,27 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bernie Sanders Questions Jeff Bezos' Motives Over Amazon's $200 Billion AI Spending: 'What A Surprise' - Yahoo Finance UK</t>
+          <t>Gale-force winds paralyse parts of Catalonia, disrupting flights, roads and freight corridors - VisaHQ</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Sat, 14 Feb 2026 16:01:19 GMT</t>
+          <t>Sun, 15 Feb 2026 23:25:53 GMT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNVWdmMHZtVjZOdVMzZzNsaHJGMW5XSzhpSWVhb01pQW5VeGNWN3JwSlUtaHotYVlyRF92WXBUZElmdXZ0TmFEMkFPQW5jcWZZV3EtOGRoSThxNzcwWmlWdW5kMnhkNGs5algxMDVReHVKV1ZLa2hVR0ZuSktKSEYwU2NXaGt0c1plWmxZXw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQTEVpTzVadm41RGljeU9sWV8xMVRET293YmFqeFB5azlhamtZUjBLYzNKekozOEc0NjJ1Y0VabjFxQ2Z2OW9COGx5Sm5pZ3ZuMWs3bm1ZTWNIQ3JZOFE2ZGpucWRKZE5FWkw1M1ZFcG56emZnYkEzNzdnNWFLcDM1TEdaeWRhdXFrTmpnX28xYWFZOXY3b0ZsLTFWQV9Rdk81VzBVa2daeW5ienMtT0NMVDJOdUpyWkxRNXAwYk1LbXZjanJrT3hDRThFZE9adDA?oc=5</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1441,27 +1441,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>HTX and AINFT Collaborate to Build New Web3 AI Gateway, Offering Free Access to Leading AI Models and 40,000 USDT Prize Pool - PR Newswire UK</t>
+          <t>Americans, not other countries, paid Trump's tariffs in 2025 - USA Today</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Sat, 14 Feb 2026 16:41:00 GMT</t>
+          <t>Sun, 15 Feb 2026 19:42:00 GMT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgJBVV95cUxQWHdZVmYzNHMtMUs0LU1fcUlmbDdlVjJIMHMzbGxSQ1oycDR1aUhUTmE3STVUVm44dk5odzRGNkpxYkdGZkVINTRZSWJpUmotQUtKbGVRTlZ2WE5oUzczVE5oRktMZlZfYWVSbnRRRDVVT1dHOVZiMVNNSTYtbzdZdWhKNmVodDFSMG1KN2hadWpXdWc0UzdGT19ObXlBMUlOMEdWXzc3dDBaaVBOVGNybDFZZG9Damxra2dPak04cVJHUVlhN1MxQ0NicTExRml4RWxubENkSFhxcXBwSTN6elFPNzBQanNaT0lrWkZHR2lqSlpmYWhyN1ljVlJncXpsQkJiU2xScXZKdFlkT2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNbzVnQUJKOTg0NHdCT0dPcjg0VGlCS2JrT0xJYWF4d3pLa1F1OTNNUi03X2RHdjdCOFJyTUtsOUFIOHljN1hHSmhpRDhsYlJ1ZmRHcEJINUdpNDBYbTZEQVltRzNDV2sxMllBWFZtRkx5d2xoQzdJSTh1cE5NbDR1Q0FYRHByekZOUkVEQk0yTWh2RXVMTk53b3UzdjJjUGhPU2hGRHdySQ?oc=5</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1471,27 +1471,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Pupils lead the way in AI lessons thanks to their cutting-edge technology - The Worcester News</t>
+          <t>Pepper spray and threat of 'sonic weapons' at protests alarm rights groups - Australian Broadcasting Corporation</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Sun, 15 Feb 2026 05:00:00 GMT</t>
+          <t>Mon, 16 Feb 2026 02:12:40 GMT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQRTRXNF9GUXh2Zm1aNF9FNGJYeVJ5QWw2VUNCWUVjOEVVQ0NCVzJPWjVYenNia2xuWVJscWFyMlVkRlR0MVd0V0VyTFBBOW5mNTZWT2Uxck1xSFJWYUUzSTZENmRrVS1fQmpDR0JrcXZrbWhXSGVHaW14Q05vdm1kVjRTSTd0X2w3TWM0UFAxanptVnRRaUVKRHQ5eDVZSDA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPbjhXUHI3YW9KbUNObzdvVnhSSnlhUmdwemVRQksxOEhOdXFwcUpJd0JlNzlPSnoyWUNjMUZseXYyYWV6Tk5qcjJ2S0xuUkFSOXRDTjloS1RRZDVaSWNiZ1l4UEJHT2xXQ0liN1RSSWVjY3lYTjk2RUxHMjJtcXRMWXBOMk9uV1BRSEY1YWVpZm1YTFZEcGI5cE56aGloRDZPeTVn?oc=5</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1501,27 +1501,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Opinion | How Fast Can A.I. Change the Workplace? - The New York Times</t>
+          <t>An estimated 350,000 people rally in Toronto in support of Iran protests, police say - CBC</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Sat, 14 Feb 2026 12:00:12 GMT</t>
+          <t>Sun, 15 Feb 2026 20:50:35 GMT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE9va2FURnB6a19yaVBCZlhleUFqeDkwVDExQ2syc2tEZTRjcjRYY0hDWDZMV2FPZ2JFTUZ6eXpKOXB6MDdCeEdnY2JpNnFjQThZb1dDMHRaekxNNl9lRktKcVNCbUtwQXFlR0Q3VlpzZHV1bV9y?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE0yelB6NVNDWVRJS3JPZS1PTGxsd01uQUJpWmx5eHRYcHRmZlNjX045SlpSYUprdERfQm9zSUNJRDJ6YnFtTy1RXy0xVlFmUTZJa2RrRlpFTDVHUQ?oc=5</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1531,27 +1531,27 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Global AI Battle Turbocharged by 50% Power Demand Surge - Bloomberg.com</t>
+          <t>‘Awful to see that much hatred’: Anti-Israel protest fallout deepens - dailytelegraph.com.au</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Sat, 14 Feb 2026 23:47:50 GMT</t>
+          <t>Mon, 16 Feb 2026 05:07:07 GMT</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNTUQ5RWh1OHRCbjBnRzNpNXY0d1JsWUtrVm03c3ZDUTdNLU1oMnpCblN6TEdMYnJndDdzWkJFY00tYUZuZWdRaG5EeUFSVE9oT3ZzOEVWTWxCd0xsQWdnNXlzSWkyWHFxMVNrdmFocG9pVS1CMkZSa3Z6ZGVJNy1sS1oyUTFRc1ZsZ3p1VndNellUNGJTOVpjdlNsTEZ4SWFDX1NHaG52S3dxTVNseWdxZUlHaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAJBVV95cUxQTEFtZFN6Q2wxQWNNUlNvZ0lVa09KODdVZWhsQ05yX1FrV2ZlbG54UTBMTTBJUWswVEZ1MDhEdUZITzBxaHJlV002X1ZXTndVQlpKS1YxdVViOFY3aDFGQ3MzQzJWQ1paZ3Q0cXJLcmdYNTRLZ3R4dGNoN09SM2VoQWZVYXFTUWVTNW9BalF5MUJHS0h6eDVQdWNZRjZpTy1sSGRnQkRJSVI4eDgxZXdGRWhJZFVEb1RZTWFMWFdGbGlGVV9mR0ROdFNlSXYtdUQ3c3pXV3ZiWWhrQzlqR3hpb1RCUFBfRmE3Q2xQTzE4eWdsMEhiMDdIVWxRSU42dktzaHo5NGh5MktjUXkwdGFKcjhhRVrSAZoCQVVfeXFMTVJPcjRhamxlS1NFTnRQOVh0X3ZmTGtjbUFQMmNxb1UyR3RUcGk2b0lEZ0FZQ3NpZDVoQ2tNZWhtMndLSF9LUC1IcDhvbU1RVVlHU2lSRWtoSWlMMUJ3X0U1OFNKUEo3cjRtMlBFVWVNems5WjRGcml0UmszQUhKbDV1ZnFCRU1kUlUwZXFid3A5R09FeVFLaDFIQ3pJdGFGYjJ6UUlIeGl2UWVtVElXMEcyMmhKZHFETkZnUW1ZTVBxQ09rOUp1cGtpVlJjazJEb1lzSzRRc2pWQW9xVXdWQ01pRUtsakY1Q2lpVGZVTXhNaWhYUkVDNm83RHNUTW9hTHB6Ykk3cUN0RjdjYUNTUFlJS21STlJTYjBR?oc=5</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1561,27 +1561,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tesla’s Executive Shake Up Tests High Cost Pivot To AI And Energy - Yahoo Finance</t>
+          <t>New Protests scheduled for Today in BiH’s Capital - Sarajevo Times</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Sat, 14 Feb 2026 23:09:01 GMT</t>
+          <t>Sun, 15 Feb 2026 11:30:14 GMT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNOGp5RGtMM1ZwR3BYa3RhMWlrSU5oWHlsa0w0QWl2OVhvOHlncXBlMzNtYXNQbTJMem52MWJJa0ZwcE1Kc2U0SW1fSXBYUV9jcWdnaENncWpzY3JzbGs1dWxkMFVyb3oxLWVyTHJKWHROOFJHYUc5cEZldmhOR1k4Rlh5dEU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPcmhuLTZpZmJ3VEFUNFZveklqekpLU25oLXFvaE5JczlTVWdBcFB4LU5sRlViOFpPbkUzRk9zWnktT29uQmh4UmxmWXZ2YlBhcy13b0gtdFptRTdYN2Q3dUQ0eWkycDFKRW5SM3lGZzBVTnQxUWJjV2tacWFzWkoxUtIBgAFBVV95cUxPcmhuLTZpZmJ3VEFUNFZveklqekpLU25oLXFvaE5JczlTVWdBcFB4LU5sRlViOFpPbkUzRk9zWnktT29uQmh4UmxmWXZ2YlBhcy13b0gtdFptRTdYN2Q3dUQ0eWkycDFKRW5SM3lGZzBVTnQxUWJjV2tacWFzWkoxUg?oc=5</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -1591,27 +1591,27 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Solus Launch Puts Expro Subsea Technology And Growth Prospects In Focus - Yahoo Finance</t>
+          <t>Fahmi: Rafizi ‘has the right’ to attend Azam Baki rally, police report no unrest - Malay Mail</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Sat, 14 Feb 2026 12:12:17 GMT</t>
+          <t>Mon, 16 Feb 2026 05:39:26 GMT</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxNUXJubklabHdiMEdTMXBVdEZsWGE4dVZyVEludmQ3VVBqVmI5aFc2WDJvYkJpbVZYUENfNGNlaHdqZUl3dk5UaUItZVZBRnpTVmwtRV94MnJMdkI5MTJGdGNVS2pnclA3QjVMc2hMVDRPSnJjdnJWV2ZIZ2VwRjBmUnVB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOdkt5NkpYbjQwcFBjZ2lfVnB6VUFjSHFuaERVOU5lSUJBOUxvaWVyMjNEcmZMa29XNldiY0FMdldvSzhscDVZMGU5SWNxY0dTNGdudEV0TjdlQVhYSE5BQ3poWFBRT3BhUE1RRks2emdBRVFUNVBzNnIzQUNpcVh3OU82R2hFYzBhLWZ6ZW5vczhrTEhYUDBJZV83T1R4RGJlNFpmd2w0c1A4eGNjM3o4Z1EwdVUyS0RVTl9MU245ai1HVFNoTmFrZko5QWlXR2vSAdQBQVVfeXFMT0RQZ24zRTRRNkM3dnhUMzM5TnVuTmRGZTBsR3lKRGU2ZWxsaWZHbVJoR0ZNZmxZdTJlbEM0elRpeGtsdFFCa1FVS1FNN3cxa3NGWGlpZVpCUlZ4bnc5aHlJVFBuOG1MNzRVeUpCOXhBVU0wLVZzOWUwMjR4bzFXZmRkQkR3dnRhTU5vcjhKaUhTaTlpOXdHX0syYmhsZjRaTWUxZ2k0WjNhMzFSbXdXR0ZmdjZPY0h6eHdjQm1aUVNEcDZEQVBBLThnT0RMSFZnRVBvV0w?oc=5</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1621,27 +1621,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Oracle Lawsuits Put AI Spending Disclosures And New Contracts In Focus - Yahoo Finance Singapore</t>
+          <t>Careless driving charge expected after vehicle strikes building - Sarnia Police Service</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Sun, 15 Feb 2026 04:20:00 GMT</t>
+          <t>Sun, 15 Feb 2026 15:02:29 GMT</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPTU1pVVFRUFYwalBoNkRuekhKYWVoVnF4dVRpYXdDbGdfVlZ1T2tGNEo3UmhYaU9aZG95c3NEd0xkOXBYQWVWb1JvSnhNbEs4R250YjVaRjJCWEY0TXAxQkFaaVFtZ0tSSV9OamRGZ2I4eWl4N0Etcy1jcGcyWU8wSmRYVzRmbzg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOb0R4TnZSZ2gyMmNJRXVBNmlaOFlsTWlzZWllSDJuLURob0lOdnpUR1hXN09rRWZQTHhrcXJ1Y1FydkVUdklocWUxbUNHeFpVcV9rc1dYN09ENEFKRWViZ0N4dXRBNy1KS2V3SDQtTElSdTc3aE91OXVZempOeGoxRlNGS0kweURoWEdoeEozSnozWE9UMzd0MjlzSlBIZjBVc3dr?oc=5</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1651,27 +1651,27 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New scam scheme: fraudsters pose as couriers from relatives and ask for a code from SMS - Первый технический</t>
+          <t>Barclays warns motor insurers - especially Aviva - of 'slow-burn' AI and autonomy squeeze - Insurance Business</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Sun, 15 Feb 2026 04:55:38 GMT</t>
+          <t>Mon, 16 Feb 2026 06:22:32 GMT</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOS2Z5VklnZzh5Z3pnMTlzUVAyYWJqdDR6Tk1WVU1fTXFsTnZweVNXc0xhSUVlUmstWmQtb1dxaFg5ZFpfZHJYYjdybUtVTExLMzJoMHRRaGd5YnVNODd1V0x0RS10R3NJZFdtVDBnU1NUS0dzeWhjZ2o4SjVNejJTNEsxajV1TXNaa1VLZUlQQVBVQ3ctYUlxMTI5R1BPeFN3bkVRT2ZpTEZXU2RaYXh1Q1M3enNtVGhuN3hEcVNsdFhaYWNuY1FDZ3FVMXlNVGfSAdQBQVVfeXFMTTA3TzhtbU5jajBudTdza0ZFcEwyck5PbXVuNlhLM19iTHVERjF3Q1ZXTjhEel80YmtHVHRucHFnR2RhcC1yNThUNDI0WUNIVW1pOGlobmNtUXk2dVdKVVVNNGExZmFOc0lnT0RBbDN0YnNSdnFZWUhLNU9rTV90enRVTERwc19jaU0talhyX0x5c3ZxZmtkaDVOMnZEcjlndDZTS3B3aUt5bWFQQ0VGOWtDUHpkWGVtcDN3YWctNURkZHZMeGQyWFMwZTBNV0NqaFNtMF8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxOdm9Wc1JXT3NadV80Y3dnY1hMMEstZ0tRZ18wLVN1VGl1RjMtc1ZuYmJpdTN5LThlNTg1UlMxb0pCS0ZEX29yWXV3X21SSTh0U3dHalhtMkhtcFRxZnF2cWE3M3NrbGw0RmFBUXNyM09uMnFtTy13amVvNGItNGNDMUpLd2VTSjROYjExQWs5Y3lpdVpqc0NUYjZleDM0Tk1waVVPb1pNTl9wRXBsNFlhN2FSMEJEYktWM1M2YlkzMEoxN1dCRVhlcHV0WTk1QWRyM09talVYMkxOSVZ5M3FsQ1BCT1hQaU0?oc=5</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1681,30 +1681,780 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>UK’s Starmer announces crackdown on AI chatbots in child safety push - Al Jazeera</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Mon, 16 Feb 2026 06:53:56 GMT</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOcHhNdWVCT1JtUzF5dlRqOVNyYzR4dERmUng3R2piNllDUElwWFBHUDhKMEFPOFlBeXR0aFZtYlhoOWM4cDhwRlNrUE5oWWh6TnhubHBrSzk2aUdDRGtleUVRQk45ejFJc2ZwR211VlFrTzFXaTlScmdfU0I3ZlNwS1B5Q0xqelVMYlhtaml0VHUtaU5DVU8yelZxUUxzQVRfb19TaFZLdjlHNlVx0gGyAUFVX3lxTFBmaTFnaHEwbzRFaDVYMWl5NDNBTWRnQ2lORVlRVlpTU0dfbmZPNlhGQ0N2X2hHcUdiNWRsR1VQbl9EOTd1bEtqT3V4bXpVcWdERWlSMHRxcXBCUzRGYzJFVmliM29zZGt3UHByaDdoTnJFX3ZuRmVkaGlLZzZka2JyYksxQTI4cWtQWGNLdWZrbVhpNU1HaEVLUGU2UkxncGtyNHI5b1RqWlFRQUIwUTdzekE?oc=5</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>First ASIC penalty for cybersecurity failures: Federal Court imposes $2.5m penalty on FIIG - Herbert Smith Freehills Kramer</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Mon, 16 Feb 2026 07:26:27 GMT</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQOXNwREM1MWpSRVNPZFA3cld5X1d1eVRQTFRJWVRXT3RQMW8yNjhORHZOUEE1VDZfaGRmR3l2eE55akV2M0JBRFU0cDc4M0JUNzc5NjZDdkhBdXZHZ3NvUkRZNEgwQzNYbXNIdHU1eF8xRU4yT0tndjRubHVCQk8tZXU3RU9fNHEyZzlLVHVHR1JMd24zMC05eG55OE9WaEV1SGZSbUJ0RmpPNE1DYVFRTE9ZejI2a182Y05zeVpVTXVvdnFIenVYMlJXdEJVRmRXUDEzbE1rWFV3QlZ2ZzZpWFlmODgyRm4t?oc=5</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>AI in Markets: Embedded, but not Autonomous - The Full FX</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Mon, 16 Feb 2026 05:55:31 GMT</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE4zcHYzcERfVC1SVmtBZVFRZ20zdTFZVGVMMnl0WXFKSDBRb0Z1WkoxQU9NRDhaaHUxZ1NzbVlLVFo0YWdMamhjX2FId0drYjFfTm1TaHR2X3BFNU9yMEFlXzV4bFd2SW04RDFhMnJuQ1o4UQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Leaders gather for New Delhi AI summit as warnings grow over societal risks - France 24</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Mon, 16 Feb 2026 02:09:52 GMT</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE5MWl9WaERHMXBZaTRBVnZISDY2ekdSREtiV3pxUGYwMGNFdXF5OFd3a3RuVFRrZDRSX3JtaDNQM0RQVXlYaDdZZjRFX0RlYUZmR0MzVGNTT212UWpkWW5qTmJUcDN4Zjk0Vk9ndXNWTjVWdndFT0xmc0szcw?oc=5</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Google puts users at risk by downplaying health disclaimers under AI Overviews - The Guardian</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Mon, 16 Feb 2026 07:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQS3p1YV9xWTJHS0pILUpUbnY1VVE2VGlNcTkwaVV2YjRBMC1yYkUxWl9rVDV2R0s0ZVIxTjJjUS1GT1FtTnBVZjNyVHVYVlpPRTV3cVVVT1UzUDRscHFKNWJzN0Q0djJOSW5aNmZqcFduQmVVRlpldGNUMkk5OFZFTHRTXzl6Tzg4OFRsa0w4eUxXZnZfdWtTUzNsdFZ5cS1LUFEtT0hlT1o2UFVnQlREbFdSZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Technology for Change Asia 2026 to decode innovation for business growth - PR Newswire UK</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Mon, 16 Feb 2026 01:05:00 GMT</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQX0tEXy1ZWU5DdzZCYm5ndC1UMmhiYTRya19kZjZCa1pmMHl2R1hRbXZXbXlxUFVWNmJNX08wdWtxZEVkZnlhcU1ZVmJ6dHlDRFlnM25iSjlZMUlBSUE5c2dOalROR1pIM1Bxc0l5Q19wLWlrVDZJaGR4YTQzVmhZVERxV1l3eTY1cHl4UWVZT0lwREl1WE9TUENsM3hrNWxOTWxBck96ci16ckI5WlpnZWdQb1Q0RHVadEFQZ3FYVjZCUG1RQ2hPbkJn?oc=5</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Neurophet bags 510(k) for Alzheimer's imaging AI and more briefs - MobiHealthNews</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Mon, 16 Feb 2026 05:03:34 GMT</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxObTlzaV9nTXZQVkI0OWIwSVpQQmlYTHV5aWVSSjlpSnVNTTc5cUVWV3BfSXVWYWUzSG5INkVaY1pSMTYwQzU3c2Fudk9nUXo3SDhmczJSc0VrNHRNZ1RyOGl6Sm5VT3c0TXZ2bDFhTXhOR2VKQ1Z5NUgzVDFBM1ZnYWtMQzFPTDVnZmZsUzZQbVV1RDFWQ2tXQ1A5YXN0dWc?oc=5</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Rethinking human connection under the influence of AI. - Psychology Today</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Sun, 15 Feb 2026 22:24:29 GMT</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQdnI4LW9vNEs0OE85N3V3NWlrYmpNcHFvdy0yUEFHYmdqWjMtV1Jva3czdHFpTG9ETUwxVHp1ZUlLcWpCZTNfSFJnZkFOVGNaOHhYYzlxanhGTGFaSUlsTl9yaFg5Q2lYS1p6UUhlR3Rsbzhna3F4NWtCOVpzUnhGTUFLVHllRHB2VFlmdUk2X21TcWg0WjZZ0gGcAUFVX3lxTE1kUF9rMG1pd2RCVWttRlRUaHFha2J1UFpFbHVKUE9KSkZUUXloTkcySzBrNzQ5cnBMMmRhSzJrY0xMWnMwRWllbGZpaWctMFVsT3p2QVduaEtHb3c2Nlc1VTNLR1hjSmFESEFEbGZRTmdmT3lMMVhlX19PTmQ1bzlrYS1ZOEx1RllFWTlDWEpqZnJ0NE9XNWxNYi1OTw?oc=5</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Tom Lee Says AI Killed Software And Job Losses Are 'Soon To Follow' - Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Sun, 15 Feb 2026 23:01:55 GMT</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE10QXRncnZWXzJXWE5Jbks3R29jQlB6UkRKWFB1WHZFU2VmRUtWa2g4dGtHY3BZVkljWnhlVTk5UUNfZjhQRFVfWGt6SEZVVXMxUEFyZ2pScHdHTi1kYkV2SDNzQ1plS2RKQ1UxbThuVFZQRDZCMUkw?oc=5</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>What is AI’s extreme impact on the young people of today’s society? - The Bolton News</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Mon, 16 Feb 2026 05:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQMEpQZzZreTNiMW5NejhFbzM2ZzVwb0JReGRvX1JYVGtJS0pISVBLT0ttMVprbUxMZGlqTm0tQnFISXJSR0kwWExhVHVQVnNxS0lqd293NHdCTnJCZjJjaUhnTFk1LWpmN3dSZGFSNUlka0pnc3VyNUgyVE9kbjJnZVM2NWpnU3FJMkNVY1Rtb2JSVE5udW41eQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Generali creates new group technology unit to support insurance platform rollout - Insurance Business</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Mon, 16 Feb 2026 03:34:05 GMT</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxOZlNiZkNGenhKTlo4QzhZTGV0V1ZCbk8wNGNtQllOQkpQaVdWQk5lWkhna09qZWlQS2tMQVBGOVZwS1BXTUJmdFp3ZnowdnVkMVRHVF85bjZ0MllJaFYxTENPS3liX1h6bDdBcV9XNy1qbDZ3cWJXMVJEUnFpOGNfU3JZSXJCZll3RVFoNEJ2SXEyTUdQOWxacy05MEo5eEoybWNLMlJVczRyNVdKaG0xVXNFUzd5VVRiUVF1ZlJiX0RacE1Eb1phQy0wbFlnbWktV0JZQ3E5OTR5cl9vbm5wQXItOTdDQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>No swiping involved: the AI dating apps promising to find your soulmate | AI (artificial intelligence) - The Guardian</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Sun, 15 Feb 2026 08:59:00 GMT</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPV1Zod2NZMU1vM3k0dTR6UVJBWUk0M0RVb2d5MVc4elAwN3pzNGlhVnMxLVZTMS1QMkk4ZFVOVEJiajZzdTRCbXhOVmVWci1wXzRsNDRESnhpVy1HckljUndHMndydU1EY0RVMGZoLWR3S29sQ3MyczRodnpJQ0MybU5ocG8xRmhpX0twR3JKOXE4YUU?oc=5</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>UK IT departments most confident on AI future-readiness - IT Brief UK</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Sun, 15 Feb 2026 09:15:00 GMT</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNamNzc0RLTS11blg3VG9iZTBZb0xIT2hMUWFSdkpfU1VqRFp4NktzSHRhdDFnSFYtNmtpZ2lpaU5uZkdaQlZfY2EzVFJvS0lzS3NNRC10bmx0UkxlRmFDLWdOLWNNLVdZVWJJdDM1VFBPWk5mc29Gd3lqOWJ1eU1Rd1hqeHNjVS04c3NV?oc=5</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>How to Regulate, or Not Regulate, AI - The Regulatory Review</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Mon, 16 Feb 2026 05:11:20 GMT</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQYlJpZG8wb0hoZjZJRTJsVWZkdEZDbXFWV1pCSXo3MDdSNmV5SmRuZjAxYUJ2RUVzMWNqMWtsWmpBWURtZXR4T1hTLTZVcWRfRnFTaTMxMl9VQm00VWdGTGJVbUgtY3F2TG9LeW5yLVRxRDU0VldmcmFLWHNKMXlFbFRkQ2xFaDNUa3kxSndaeXBmQUVYdFViUF9RdFZtaWlhUEE?oc=5</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>UK scale-up founders fear AI could trigger job cuts - IT Brief UK</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Sun, 15 Feb 2026 08:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOYndzSWxXbzlKMjMzYVM4VVY1eENMdm51MFVOOGRzME41aW5LaW9RaTk5WWVHUGpqdUJVNUZ0bVBKaWZ2ZU5aWHh6a0VtNVVRUEl3a2JEZlpTTkM1NkFiNFpaV0w4WWQ1U3kzNjhyTlV3djlKNHFMMnFFdHhSOFZOdkt5VG84QQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>AI and Copyright: How Lessons from Litigation Can Pave the Way to Licensing - IPWatchdog.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Sun, 15 Feb 2026 17:26:53 GMT</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNNG9ncHFOb2M5SVhPRy05a0VCdDZ2cEMtQThxeTBjS3ZCT2pLb2JKLXAwNzZuM3EwYm9HOEx2eDFySEZteE9jcWpMQXBYLVE2clNQVVZUUmoweWhGVmNndmVZNWlHcEhXeWhmMjFOU2laLU1Kcm9tcDkzQ2FUVEtTZl9STnFjMExJeU55Z3NhQmxNc00?oc=5</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>India's Fractal Analytics drops 5% in trading debut as AI jitters keep investors cautious - Reuters</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Mon, 16 Feb 2026 05:14:00 GMT</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNb0otek5maEhfSjQwZFkyUXNETUNDOUZVQnQzUjZwQTNGekRTcjl0TTRaUkNUM1ZNN3d0OTlxbUV2djVFQUl1WlVTYlAxbm05RmtVYmZ2TjJiWjFDVnY5eTNnWWp0WE56alJtZU5GTHVpcGJOZlAzMzRWUTQ1ekJfNG5XYVpiX3g5a0NveW9hSjFhUkdaLWoyakllb0Ezd0NBRzQya3k1cEkzTkFUQ05fWVFR?oc=5</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Why are experts sounding the alarm on AI risks? - Al Jazeera</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Sun, 15 Feb 2026 11:37:19 GMT</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQdGlWWHY2VWJqeFAxTGY1ZG1JVkZkeXRleEctZWR1WGVCbHlBSXF5aDk4ZzdsdXFBX0hsZE1aUVFiemJwSWJRNzduQTFXQlhlaUVQcEN2MVhGOC1Yb2pfX2hHOUp5a2NOdjNRUUZfWklwMW1rNldVOU5lTVAwNXdISEVWNE9kbVFxMmZWV0dENTfSAZYBQVVfeXFMTmViTDVOUjU2Yl8zVEtfZXFDT19wLTFURlBPTjUwTE1JWmJvYUxESjhrR3BCaDB0TS1ubXpwdlZxR2hCR2xlVTNZZGtvOVUyenZuWGVha1BES2s5d29QWjhTckZIeldCVXc5VTRkWlBvbFdNWTk1RDg4WXlMREFPWjJjaDFvZV9DV2MwdWROVEJQb0MtU1JB?oc=5</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ICYMI: The Cost and Promise of AI and what it could mean for the future of Western Kentucky - WPSD Local 6</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Mon, 16 Feb 2026 01:40:54 GMT</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxQa2lnTElFdmdCNnZ0a2ZONzdTRFFBNS1OdUtXakl2WGlMTkpWLS1ZajFqRDZSNHU0Tks4S0Z4NDZwOG9seXVkOG1EQXBjTWZBSkJuYi1FWWhybm0zYnI4cEVkX0Z0SWxaSnY1MUxaOTRka1piV1lNcWNDSUI0Uy1vdDVzd1dtaWRPLVRfZnlkZTRucW8yYTY1SUdMeVRVOXFJS2ZnTkR5eDA3bGpqQmx5clVuWlczbVhXazVyUmtqVVNjM3dHcmU0YU9aTjE2UzFnbXRaclhjdnJ4a2x3SWduWW8xWXBiREE?oc=5</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Lumentum’s AI Optics Contract Puts Earnings Quality And Risks In Focus - Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Mon, 16 Feb 2026 06:07:00 GMT</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxPWlV0b08xS00tU19MWDZGZ3BJd3RkVTg3VGR0WmVsVXppWmd2NEhXSkZNWXg3QU0xZ1UtWkx4am9CZ2xsOHJ4aDF3YzlSUlpkS3RwdkNfYnk0Q19TUnZ0NkJZWkREWFNMMWs0R2k0Sm8zQVZjdF9WT3pwd1dHNk5JandkdkQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>AI Redefines the Role of Writers and Editors - ARCweb.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Mon, 16 Feb 2026 06:41:02 GMT</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE9TNUNrdjV4cml0OF9TSE5TMVVMbG45Z25Zc2x6ZXFGRVFVSUxvSnR3LTg2QXhhQjc5ZXBWMHRWN2pEU0s4RVRGNFRENDB4a1BhNWZhMGlyeG81WnE3Sk02R1dXUHNpSC1MY0xEWGR3?oc=5</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Elon Musk Envisions a Future of 'Zero Scarcity' with AI and Robotics - International Business Times UK</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Sun, 15 Feb 2026 22:53:00 GMT</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE5EYmY0WWhhYnMtZGtEeGRFa0lUOHRLSnJKNlI5Y3NraUxNcUI3dTNqNEVnS2FuUWlXMTBuNS1SczFnN1ZwVEtwelVKVXo3NUNIVUlHMV9ITERmeDNsUHRuSTBDeXFTWUhGWlNueS1Sc1Frc3BSRDUybw?oc=5</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>AI, automation and weight-loss drugs: 3 thematic investment trends analysts say are worth watching in 2026 - Yahoo! Finance Canada</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Sun, 15 Feb 2026 12:35:00 GMT</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxOUFM5M2QxSkdGSFctVFBCb09FZ2RudDRrcS15YURyWmpJcFk2MUpIcnJsWUV3YjBlTWY2T3RDMHFJYVNPX2ZuS0RldHNQbzB5NG44WDJHY2prQmt6RVNkVkUtNm1FaTM4Q3hBN3hxRHJHZlZhNXA2Nks0OEJnU0RxYXFBZWN1NDQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
           <t>Fraud_Scam</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Social worker held in Rs 22L fraud case - orissapost.com</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Sun, 15 Feb 2026 04:36:27 GMT</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE1fTHU4b28yenM2V0s4T3NDN3FHUmthQ0lhY1BGemU2ejlFa0FTZnoyT2xwYmdicVpFWlZQZ0V3aTdmMjBUSWJLeUNlanFJcUNNZFhIQnMzWjZtcUM5TjlZd043enlZM0FaZ0lRdnNhQV9vY2VJN3fSAXZBVV95cUxNX0x1OG9vMnpzNldLOE9zQzdxR1JrYUNJYWNQRnplNno5RWtBU2Z6Mk9scGJnYnFaRVpWUGdFd2k3ZjIwVEliS3lDZWpxSXFDTWRYSEJzM1o2bXFDOU45WXdON3p5WTNBWmdJUXZzYUFfb2NlSTd3?oc=5</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>‘Fake Flex’ Trend Raises Alarm Over AI-Driven Fraud and Social Media Illusions - Koreabizwire</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Mon, 16 Feb 2026 03:37:14 GMT</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxONGF1eUN5eU9EZzg4U04tXzViQlVYUjk4Q3d3TzZha1lPRWJQd0VLd3ViSC10OGQ2VG1Xc1JGdVFDTk1tNFJRNVN2aE9ySjdaWThtSDdUaGtmZHRBYUstdzlQdVpSUDFUaC1mY3ppM2hva3NfQnkwU0E5ekhKYkhLMmlJbENDd2otcWs2NjZSejFMNnluMkl3aGNjMENzak1sOVdBV1BGenZUZ0k?oc=5</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Egypt arrests woman over alleged Hajj visa scam - Gulf News</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Sun, 15 Feb 2026 12:46:30 GMT</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPSFdvWExQTGR0LWljZEdBZ0ZiUkw2MFQ0OVdQeU9wNmxzR0lBMm1vMkZCQnRZMVJwSUc3RUpqZ2ZFMzdPTlJodjBQOENodmNsMG0yT0NLYmJld1JOU2t3Qkp3d2lPeC1aempuV2x4Nk9pb1JvWHdBSlMwYkszZ2FtZlNwZ0s4cGJHZWMwa3J5bVBESkI5M0HSAagBQVVfeXFMTXdmczVEOU01RW05YUdNdHpsRVU0WnRuOGoydmNwdVFEYkkzSThhREdTOW5KUF9HdlZyd3dHNlJ4b3pzR0xScDVrdnBQOXVvelB3WmFqT1ZmVFpXUGdxQzNodmlsR080YnJFaWNqUEQ3dDRYUHd5WTdlbVltUHVtYm1taHJMTG1hZzEtamp0NmViLVljR0JTcklqSlZ2bUZmRGZkN1pROURt?oc=5</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>How a Social Media Tip Turned into a ₹45 Lakh Online Fraud - Open Magazine</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Sun, 15 Feb 2026 11:34:08 GMT</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPZlcyellrSDRMb21hUXVVc2xEQWxDY3AwTENkNk5uN0dYa1RfRlMydFJBUU80cHpxcXVXcS13ZXN3cVdjX2tBeEdLbnQ3Q3JBQTJSaS00Y1hIcFNrZ0FsVXVjT0VwY3FVN1BMZ3JLSGxRTWlad2pmU3FCX05OZVV6Vl9kRHlRNGhOVWVERjBiTDFTMlJWb0E?oc=5</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
         <v>1</v>
       </c>
     </row>

--- a/data/daily/topic_feeds_daily.xlsx
+++ b/data/daily/topic_feeds_daily.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,17 +461,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>IMF calls for tax shakeup as federal budget looms - CommBank</t>
+          <t>Update on May 2026 local authority elections - GOV.UK blogs</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 04:22:09 GMT</t>
+          <t>Mon, 16 Feb 2026 14:54:23 GMT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPOEtzRUhHS0xHenFKZ0FuOGZKdldZeXhLUm55WkZoQk90ZnMxTGM3MmxJZkZPQ1I3Z2xISnp6MTlGVURGVFRCR1RDeFV5QVhMcFdNdDdxTEFyVGhmdDdfMkRFanYxWUotN1lENHpCblpvbUZ4NHRUdFI1azMydzgzQkFsbHFpZFJqVU55Q3BBYTdqcllkREp1ZUNxeElWTENTODhFU0xoM1dQMEU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQRWh5VEc5ZDJuVTd0QVc5RVpYbUFISXlmSEtzazBtT1YxX282b256TWw3ZU5VQ2Nmd21zTGhYR0N4S1R1RTZZOUtneWMxVkxVLWczRS0xYU1XOGw5cUVLdjRudEpGOE1kVmtueUxFdk8waEdnVGZFN2hLNmd3elM1OWtHVWZTSzdBOVNhbnBDY08?oc=5</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -491,17 +491,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Trump claims victory on affordability as public anxieties persist - The Washington Post</t>
+          <t>“We are seeing free parties rise, mid-tier venues disappear… extraordinary resilience, but resilience is not a policy”: New report into UK electronic music brings mixed news - musicradar.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sun, 15 Feb 2026 18:00:12 GMT</t>
+          <t>Mon, 16 Feb 2026 15:25:04 GMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxQbkQ1ZHVhWkpUZHpyN040S05SWU5MRElaNFpfaGJkUGtDai1fRHZ5WnFzamtwU2VHWFJxbmlzRm82SFpOLV90Y2NaSkg0VmphbTRvVzdjWHNCX3dxYmoxa1lWRV81NjJLT0IxczRuc1FTTGNZRGhvT3E1YXRPbTBVS0V6d2xseU82VFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwJBVV95cUxNVTZJR3p1T0kzd25TcEx4ZXV6ZWpUNi1EQzVsSE92N1ZRSExYYzNZRTNrMmluUE9IbUt6bnhIaFFZb2FJQjZ5UTduQXQ2bk04Z1N3bnJrZ1lfOE5FbWxJN2Y4RmxmWWswcFRSMlo1NGlNblJmS3JqSFRqaUxpMWlHVWpCLVpLOUUxWUc1YXVmMTdMa2JFMlllMnlrR0h5cWFDNGlYQnZkTXlKdV80bWJnN3JnNXh4MjBaUDRxZ25WMG93eVlpeUp3MEpNWHlYcUxWU2xtdHFsejVLdU9jMnpHeWZubW1vd3ZxTjBDc3hfYnZvNFRNdl8zenZ6dWtsd1d5b1V5VDhMZHBPVXBxcDdBSElralBWZ1BFS05fRjVkMmhNZGtROXU1d3BMV25Oc2NfMVd3RkZjczFGX3ZUeWxV?oc=5</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -511,27 +511,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>UK considers new Russia sanctions after Navalny frog toxin finding - The Guardian</t>
+          <t>Labor approves 4.41% increase for health insurance premiums – as it happened - The Guardian</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sun, 15 Feb 2026 16:29:00 GMT</t>
+          <t>Tue, 17 Feb 2026 07:15:09 GMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNR1VtVzZXT285VzAzUHJtbzB6Vk1iaFl1UG9TZnJKdWw3NDVvUFUtVXluQmZCNFZPcWV3WXFKNldKNXFpbXBQMW5IaTlrLVlYRlpVMlc4a2ZFbWttU1czWnU5c1NXNThhRFlFREtFVTZ4M296cnpKX3FNVWJqY285TkxGM28tQkRtNXNZcEdLdWs4YXQydzhfZ1ZOMnhFaFNwYm1z?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxNZ2dOemh6MUh2cTFBNHNlLU5JTF92T0FBY0ZzRThjX09oeE5POWp4ZXB5TkVMcTlPYjBCMjl1UTZlNlFwRlUxRDdQLXhqLWxmdVM1dURqeEI1cmNaT1RxZVNGWFppQ19mOXgyXzlzbFJ2STNEN3FQczFpUDQ5a0pfYy1OWFRUdF84M0lRdkczbGFSQkpxTmk3MGpxb00xaHF5eHVQTFU2TURYUE1nT1BLdUVYbW1GeHJBZnYyOENpTDBnS3JHandJdGJsWWJIUGdweWU3WENZcWxFUmJMdnRFWU5vUWlmbFpBLU1hZF9GaFRMZk40WlF4a1FQUXQtRktBczhuM1hwWQ?oc=5</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -541,27 +541,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tehran’s oil lifeline shows signs of strain under tightening sanctions - ایران اینترنشنال</t>
+          <t>Japan narrowly avoids a technical recession in 2025, report shows - Euronews.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 01:00:00 GMT</t>
+          <t>Mon, 16 Feb 2026 11:22:22 GMT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUkFVX3lxTE1sTG82UDFJV0x2RVAwbDVYUzA1ZzZfdXVZVy1lUWd2SVhMZ1dWZHBROGNoamZCUHhpTnJ1YnJvSG9tMWRHZTg3SlgySjhDQTVDbXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNSkVFalJIOUNidnBMWE5QcFJNOXlxSGVMWnhPMEhPTUZOenJIbks2dkxuNFplQWRJVGRRNEZWenhfdDBDeE1oY0Vqd2h1R2NpT1VObGZBdkhCV2FXemR5RWZFNTd2d3pPbWgwOU5jWDlOY29sSk1XcXNRbk5abUVXa3BZNkpoa2cwQ2g1SEtINEd2MFNUWnlDcFM5aU9TY1FrMGxqMXI3ZjYyVVNaZlFXa0hhY1hOeEstMmZCcA?oc=5</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -571,27 +571,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>UK's Courtsdesk Shutdown Creates Compliance Headache - WealthBriefing</t>
+          <t>Legal analysis: What Project Vault means for critical minerals regulation - Mining.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 07:44:24 GMT</t>
+          <t>Mon, 16 Feb 2026 19:16:30 GMT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQaExRR19CV0paZGdUb1pFdERsZ3o2Um4yOWdBREJUSFF3SDltdXBGVVNIOUhhUGJIX0xBREREX01HZ183QmJSUHVxekhvSlpIVjBXb19HZjZic2N4RGJUdkFlY01acS1jYXdlaC1iMHlNbTFKVTFzNjA2eWlQU1lRblFYeENUc3Q2bkNUbUMzT3NFcTBUUG54RWZuTFVkbTVtMTRVcA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPNUpoMHF1SkljaUlNMTRBYlVIWEN4RGNURE1UMEQwS3doNVBHXzl4REFhc2hsU1dVS1Z2R2RVWk5lQXM4eWw4Ql9SS0dLclRWa3NwaFFoYjFPMVJNeXUtYWZCV3RxVUw1RjFpUkNKSEdzWEdtSlM2TWZlemFJMjJtOElvWkllU0U1OVdHUUFURHNnc09ORFFucnRyU04?oc=5</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -601,27 +601,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Log-hub introduces Supply Chain Agent - FleetPoint</t>
+          <t>Offshore wind could help support space-based solar, UK government report suggests - Recharge News</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 07:20:08 GMT</t>
+          <t>Mon, 16 Feb 2026 13:19:01 GMT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNNHd4RkJDUFZYeEd6ODJGay1vMW5UQkFUcWZjZ2MtNHdfMmZXbUtnWlczcURiUnpIR0EySVlHcTBJOVpNX0ltUndYbHAxdW9oX1puUUxxSFZfek4tdFB4R1NXNUNydjQwUE9UU3dXNzMzbFZXbzdSemVWLUt3emwtUWFXMFBfR0dUZkNaMnVNZnI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQb01lc0E5ZEhZemV3aUIwZDN3U01TdzdsQW9YTk1CbzlyMnIxTnVraVlEcWQ2WTZVb1NVYVZWQlNEbGlNSm9NWXlsdFFpTldrRXNxU04yQWJDSWNqenpnYVpJSHRDTS1PRmxEdnY5QVl0RUhqRmpkcFBnNF9MMUkza2UxU0RsWWtVSmhEUE1pRGh5ZWpqVkRqbnZQa3pWNGoyX0ZJZlFReGIxaWhDa3RIeENHMmR5WjM4RGFJSGxsRENQZXhKRUE?oc=5</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -631,27 +631,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>World rail freight news round-up - Railway Gazette International</t>
+          <t>Party of Pakistan’s Imran Khan rejects government medical report, seeks independent eye exam - Arab News PK</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 04:49:18 GMT</t>
+          <t>Tue, 17 Feb 2026 04:39:07 GMT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOa0FzMUplUC1ZRzJfbGZXbkdRamJIVzNGN0xoOVBGVGt0bnRzTUhBRE5rZGE2T1FKSDkwcV9LRXRaVWV4OGw5Ymdka0hRNk1WUk1vSzRHNC05Vy1MSDhKN2VQTE0xcklCaFpiQ1NZdzdWRHZKakRjenh0OHlIT1A5bUdXbDRQNm55U1JsX2dB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE9iLVFTbEVud0FVWXlnVzZQR0hsRFh5QXhMVXprbFdhODlDaGZYOG91NHdsV3NpZW8zS1BYNmhpbGZsRlYzcmliRjVNWTZvS3dEcWl3a1FXRlo?oc=5</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -661,27 +661,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Container shipping scheduling collapses in 2025 - Seatrade Maritime News</t>
+          <t>UK government asked not to release Mandelson emails on Epstein: Report - PressTV</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 01:48:16 GMT</t>
+          <t>Mon, 16 Feb 2026 19:15:00 GMT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNSXRWNVZCUXN6OWlKWlFGMHAyMGhCSHl2aXI0UXJvVl94ZE9QNzU4d1ZuZC1iZkREelMyMFZFLTktVmZYNE1neU1Wa2loLVl6dmxpWmJVWG1CZ1hDZjAwci1Ja2tmMERmS0o1R0g3OXI0SUpwcENZX0ZkaFZhZTNzbVBLQWltbGlEUEs2TVFVV0g3ZGg3SnJ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQb0N5UDNFZjNpdjdobWpOdU5fREVXSzJodTF6ZHEyZFM5NUw4OEpGaWRuVXp0TkFxcFJsNjZYek9qUDFqMWlDVVM2WEdaeXFMaERNWEkzeVpKelAzcHI3S1kxUjFzbDRpQl8tMU5wX3JPOU40TWMtSjg2OU12bmc0Tg?oc=5</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -701,17 +701,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>adidas taps project44 tech with focus on how AI transforming supply chain over next decade - Retail Technology Innovation Hub</t>
+          <t>Portsmouth Port fears £24m plug-in power system may not be used - BBC</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 07:01:44 GMT</t>
+          <t>Tue, 17 Feb 2026 06:16:46 GMT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQZ185WHQzQ3FVUk5BZTdfb1VlOTAyTGswUEx6aUVsWkNZWU1yRkNIZFQwNkF0Z05QRVdaeHdrWUtPZVBMbXJlYmtxNU9HdnFabDNtbXJFVWJHckRkOEZQUDVnb0V1NlZ2ekttUlZqTFN0dXV2dGxJZDNXUl95Yjl6djR0cGo1R21GZGdYazhXR1JnNGhSM2RBMUhVekVYWm1ROEJfNzljaWtZSU1ndHR4RHpGTGliV2w1QXlOU19Na2YzN2VubThVY1lXSGJEdWpwRE94eHIxSE8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE5hSHJyWUp1bDNWdE9ER0owN2NCclBoS1dyZjhxZENTMGJtaFhaM3pDX2hVbE00LVF3bWdfWE05ZmRIQnhDSXVmRG9ET016bEFncFZOWW5RdW1yTWI4?oc=5</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -731,17 +731,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AI fears rattle Wall Street as logistics stocks slide - Trans.INFO</t>
+          <t>CILT(UK) launches Women in Supply Chain &amp; Transport event - FleetPoint</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 04:08:06 GMT</t>
+          <t>Tue, 17 Feb 2026 05:44:42 GMT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUkFVX3lxTE1rWHgtZHlWdEVsby1STFdPMkdSVThWYmVSbHZab1BaSk1GdEozLVdSclJhUzJObThfSGt1WW94TWJpRWFPWFZwREthSDZPMnRzX0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQVjRObUFoZFJnN2hmNEJYZ3VhYWJCOUdSNTU3SzBzR1FwUXE1eUtncU12elNvalpYZnhoMHA3VkFHNmdfbFQxenNfYjZmbWZEWWJTS2c1T25DbEtXSnBSVUZfRGJpSDdrWEdKUktHVTFUbVFHY2RhTnV0alZ1dzJyRFRBZWxjV2NlLVZUSld4TjRVeHpFUWNNTmtWcjZEdEIxVndJN3ctQks?oc=5</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -761,17 +761,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Trump Sanctions Chief Poised to Leave After Bessent Tension - Bloomberg</t>
+          <t>Sunderland to face Port Vale or Bristol City in FA Cup fifth round - Sunderland AFC</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sun, 15 Feb 2026 18:27:55 GMT</t>
+          <t>Mon, 16 Feb 2026 21:04:22 GMT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPazhJdkw1cHBJaTFETkk1aUFnQ3U5RkV5MVJncTdONmxHY3JVNWJEY0JKWGtRcElwbnFXcFQwRlVQTWRxV3QwM3lmVlFQZXI3QjZaWFB3aHRHMEk0OGN0bllWdThLM1E1Z2dmSlNkcFdOTnJxQzVESTRsMlNiZW1EMzFyNl9TTV9kemJuY0pGeTdCMFhFa0hSanVrRE1XWm4wWDl2cG9uM05QVXMyYWhNVEgydG9pZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNdm54eGl1XzlLSGsyM1Z3d0JZcWV1WXFSRDFPbUROMDdEdkxWYXNzOU5BaWxXRkJ2YzEtMkdVRnUzZWJrbnlCRmR0aFN5ZjQyT3U5S2FOdWhibnJ2V2hSSHpBMmtqVVB6dFFJdXIyT01YdExJTE1iZUs1Zm1BTlNzY25Mc1dyT2g0Z085VjZYZW50SEtzMXRycWpiWUxQYl9aQUplUXFOcjRHSXVPZ2cw?oc=5</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -791,17 +791,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Latest SRA fines for AML non-compliance - Today's Conveyancer</t>
+          <t>‘Economic fighters’: the volunteers helping direct sanctions against Russia - The Guardian</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 05:07:29 GMT</t>
+          <t>Tue, 17 Feb 2026 05:00:00 GMT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTFA3cnZvQVNFRV9STFM5OGxVTnVObnJRMXMzaE1mRlhPYUxiajRmLXBXYmNTYjNrd21fcUdVS0Z3Q002ZDcyclBpaHRqOHVwMXFuaGNxNmh3cWhreGc2Ui0tX2JocmFPdzVQRXhyZTVGQzZSMEZYUjhR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPX0ZkYmsyOElfU2tuVzcxMTFieWhWMG1lVXl3SmtGbzVUSElWbzE0c29qMEJpdnFnc1Vfb2kxYmRhU1I4aUVPWUJ1bzRyWDF0LVhaUE5PZE5tcnFBOS1yUGhLb2dObFNzLTdfN01VYk5DM2h1VmFZN0NINHBxQl9VQUVkeEI2RndQc1hxdUZadUlCV19GNWtnbFhndGE?oc=5</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -821,17 +821,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>VIDEO: Hydrogen Strategy delays ‘risk losing’ the supply chain - Energy Voice</t>
+          <t>Sailing the shipping forecast: Unlocking the secrets of the Thames - Yachting Monthly</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 07:02:58 GMT</t>
+          <t>Tue, 17 Feb 2026 06:59:22 GMT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxORE16NzNkY0lRX1k3Q1k2eVBvbXFSTUh4TFljT3hUTnpFdkthZFNvZWlGbC1HdXhHMTBEc2R1QVNYa2IzUVRBWU5WMy1xSFJfeURNaXQzeVNibEl3N0Q5OG5NWVlSRkh2akxZT2lkXzFCdmVCNThTLUxUdUVKWW5KZlJDQmtYOWJIaDR0TkREOU5QVk5Icm5GNlFxM3hRX1hWbW1iMHdRcVMyb3BwdW1jM0ZNeEprNklCSmd2S2FUcFhpUVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPN1RmQm9yU3VpS3prYjhfZS0yWGZFUTN6OV9USkZuY0dyWTd1dW9UR0FDM2NZeWhIN1A5M21XWXJIUW55V0IzN2k3VXNiSEpiZVlVN05WcW1NSHBGZlp2dTRHM3l0UndSYlFMTUNHNHlCOXNOSGFSNzdvWENhQ0V1UU1RXzlxR0RFWGt5R2NSeW5wODBMTElwZVFHNWdnbGFSNE10WjlkVUZoNlFCQ0JMbzczQkVrVGVrYVIzNA?oc=5</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -851,17 +851,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Trump’s Maritime Action Plan revives threat of port fees - Splash247</t>
+          <t>The Chilled Hub - Logistics Business</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 07:28:09 GMT</t>
+          <t>Tue, 17 Feb 2026 02:17:59 GMT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNVTBtNHNfd19MNldRMXVrS0U1Tk1XTm5Db3FMdzNWUmJka2g5TjV2ZjUtOVFMSEdYSklsNldvMXRhSVdKQTVWWnRRT1R6cGNIUGxoRmhHQzI5elpaU0wwUzJsbWhTd2o4Y2w1aVJOQ0ExQ3pvNmJwLVNBWHhOd2JCTlh2RDQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPVmV6VU9sUDNEcG5zaXMyenoyNlFhc2hoWHBrTjhCN0Fabm0tMkJ6ZTd1ZmtzSVRtdXNpVXNHZnl5ZlpUcTN5YmJWbTF0UlI1TzdQVFhhSURQdDVJSXE4c0tobEhoMUJOQnRwTVFiTURTZVFFanlEVEwxN08tNlNHTlpOSkJGbkJHVUdOY283d1I?oc=5</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -881,17 +881,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Be Port of the crowd - Cliftonville Football Club</t>
+          <t>Godby Shipping orders two new RoRo vessels at CIMC Raffles - Shippax</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sun, 15 Feb 2026 16:19:52 GMT</t>
+          <t>Tue, 17 Feb 2026 07:26:52 GMT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE8tQlJlUFgwd1BrSHh0SzFsdkIxXzV4NGI1ME1ydi1WX09pWEl0T1pvWVdmalZqcGlhWG1qeUc2TENfQjJBVnJvSWFmWTVYZ1Ywekh4cDRuTXdHTU9weVVCbzlBb2lNSXo4MHpr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNaUJMYmJnZTF5ZVdrRmtWM3NyUlJ4X21RWFZiMlVzcTVhS2pBRTlXdFpaVzZXWUtWRGU2VGw2ZUxTcFY3YTctZExwcEdUekhhckI0al84UWptMjZyRWtBVXBSejZyWTc3a3phS0x2Y0Z6Yi1FbFI5T2kzbERRRF9HLUlfem9vdXY5ZXZfZlhvQ21HUXlyRXB2N2ZaZw?oc=5</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -911,17 +911,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Man's years of domestic abuse included throwing partner's belongings into the street - East Lothian Courier</t>
+          <t>Bashing Trump’s tariffs is slowly becoming a bipartisan sport - Financial Times</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 07:03:46 GMT</t>
+          <t>Mon, 16 Feb 2026 12:31:04 GMT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPVVpOVWFPUzNyR3c4YXVCQVRpXy1OTGtyQXJqZ1NSR3U3U1VIX0JjX0VHalMyczI0Vl9HcFNCNEJEdnp5OUZpVWxpTU4tVF9YS0dnZHF4aW9FVDFRbWlTYWpVcEYxX0VER0NBbmo1SUFCSV9aUUdpV0lKeWdoUG44WVdXWk5KQVJyTXd3LTd5Tkp0R3ItUFhIOExoVmxrTURp?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5GNzVjWmt1cHAtSllkM0dVZFVoNHZRRTBTTDZ5MWtuRjlWN0xpbmJ4b2Zydjkwb3hwUzJrTjBESmg3WW9IbmlER3lhaHVHNC1OcUZGVnpIUmd2RTVULUlralUzRjF4ay1sZE9Xd3Iwd3o?oc=5</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>German shipping giant in talks to buy Israel’s Zim for up to $3.5B; workers go on strike - The Times of Israel</t>
+          <t>Rethinking sustainable freight on NYC’s waterfront - Buro Happold</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sun, 15 Feb 2026 16:42:00 GMT</t>
+          <t>Mon, 16 Feb 2026 22:29:05 GMT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOSjZ3dWJVU2czNlhiU3pmOTBuQmRXSGd3NkZka1JqRXpLcE5SMFhBMFM3MFZWMTVpS0NaSC1IbWIweEZ3Mi1rZm94RzBndEVJTURLQW94RTJWdFI2QWFtSnRXV2pwLWNFN2QyUzZvazRaVGR5OURteUs2bXlES1hjcTBjRXZmU01laVBnZ09wZWtrY3hyN2xzVWZuWm1iUXJ5VzRYNWF4UHUzb1J5UEsydlluSHpSZ9IBuwFBVV95cUxORktMODhUVndXY2E2NENXT0ViWkY0bEhkMGItbFYzbzlJZllBM0FoNVlZakkwS1VySHROV1BCSjhjWU1pQnJ5WllwUTFBQXI1bmJIXzVwYkVGUXJCRUF3emtPYWpmS3pCSlFvaThtUTUyVHlMcThqZTRHZTN6YkRuOThOaVg4VnBrb1p1RGltNEcwUGxudWt6eE5xN25Xa1FjLXdYY2s2X0I4SlFoWV9pZTJ2M3hRdVJzVUFn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOUWM3dmZVSi13X0xMeVRUMGhmT1ZaWVo1akt6Z3I2M1p4ZWRpMXJUV2l6LVFlOTItWUlaV2p2aW54SGNKNkNKdE41WkZ2V2szVWl5X0FYU2F6eUZ2ejFDTGN5b284M1FqR1FyU3E5RzQ3VDlybnY3MjgyZE5SdXVoNW13SDZoRnVhYi1VTFIycGo?oc=5</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -971,17 +971,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ukrainian drones hit key Russian oil port, local governor says - politico.eu</t>
+          <t>Regulatory uncertainty: Why port readiness for alternative fuels is stalling - wtwco.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Sun, 15 Feb 2026 11:47:00 GMT</t>
+          <t>Tue, 17 Feb 2026 01:52:30 GMT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPSzFCZUxPNFFhRGNYWkY1NG9leWpnNHdjREVkV3ZkSXViRDRTT1ljQ1doRTJ0bVZsR0QwcmJsS3V5Rlp6VERkY1BOUGMydVZWRExWS0ZjeDI1M3NiVnNQV3RCMW1CMGhYRmJtQ2M0QXpBNlBDc0VMYkQ5S1JfVW9Bajk1dVlGYjhiVjhrTjFuUTBldEM5UTBSaTh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNdThadDRsSDY5UHE2eW80ME1Sd0JDNHNVY3YwTHVmTDhCUWFSN0ZHQklOQTA4NVRxdUFBWGF3dzF6TGJnY1dVanA4TVo5b1UyN2J2enRzR2YzR0tCNUhCU3cwWURidEU3OE9qQ3RySThFVFRoRDhpU1R4Z1R1TzlGdW1FMHZZRkZfc3hNUG9uS0tWQnRpNjRZNzRtSlVxV0lXRDRPUThBODhLZDJiNXZHX25LYTdOdnJOY3VBTw?oc=5</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Fragmentation, Governance, and the Limits of Political Settlement and Peacebuilding in Libya - Peace News Network</t>
+          <t>Jersey minister says ferry deal protected food supply chain - BBC</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 05:00:00 GMT</t>
+          <t>Mon, 16 Feb 2026 14:25:34 GMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQcU90WERqQXgzaWVlY1lCb2RrSE5ieHhteE5OTHhsdGNqNXB2TUxfUFVlUGNFUVlHd1pVT0daTFpGYmhZcWZxX3NMV2I2Mi1nTHBvdFIxWUE3V1RfcmhtUXB1ZEx5NjFDakVWT05NQ3VMWWpzMzlNN2RIRXg2RG1QZndWd05ad2dCRFJHeU5hR2hmM1hqQWw0U1R0bHJYUzl3RGdpdkduM2ZfUVFDdWFaUVdWaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1JZ0JmNlRsUDIxVlpGQUlKbXd6bndtMElUOTVybHJiQXlNZkw1Q2pGR2JndVlQYzJyaWRnVVAtcGlVbF91MVlmNERUQU1jMXdMdk1meGdLN2RvUdIBX0FVX3lxTFBReVBUOWNMLVJzV1pTU2pIS3VORkhldGVYMHFyMHFZMEFMeDlWZU9NV3JRUTNqT2k4djhVejF6aDlTN28zSmU5cTRxVkFOZDYtNi1MVUltLUJYc3JkOURZ?oc=5</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1031,17 +1031,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Op-Ed: LNG is the Future of Shipping's Energy Transition - The Maritime Executive</t>
+          <t>Just Mortgages unveils new quality and compliance supervision team - The Intermediary</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 00:35:00 GMT</t>
+          <t>Tue, 17 Feb 2026 00:01:00 GMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQcHZHaWFOUUptTXl3ekRlcFZOZGs1emVpSW1ObVU2V0tKWC1xZlVub2JQZHpqSlVoX1p4YmU3WHdiSkVfYzVTS21IdGRXc0YtM0tIV0FONDdUcXB2QWxveHVlYWJyMzNJb0xhcUZuMWNTM1RiUGR3WmpxWHJ6MjFOdXVOVWZyd3FIWDNybGZkSG9vOXZ6ZHc4NVVkTFBGdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOZ1ZXN0VDMG1xeV93ZXFyQ3ZtZGU0TXVHUC1lSGotVWdyRW83Ym1kS2dEZW5ublEzYWdxUDhTTDU1OTNLWFF2LVpqTGwxWkVVemJST3JaVmowcTA5YzVKYnV0d0k0M2JKai0tQlRvLXQyU25CVExyeG9HYUhKSWMtREEtdWIxaFdtbTdpU24zU0Z3UmVMSmRibkM5QXRHLXZUOEZEVTJIcEM?oc=5</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1061,17 +1061,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>How NHS Supply Chain is turning Scope 3 commitments into operational decarbonisation - GetTransport.com</t>
+          <t>Is this the New Leadership Vision for DP World’s Future? - Supply Chain Digital Magazine</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 06:42:08 GMT</t>
+          <t>Mon, 16 Feb 2026 17:27:52 GMT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9CX0RxVXF6eWdja3FrWTJUNmtiQVZGMDVKUmNNb1J0aHpiUXJ2cEJKU0M1X3ZoSnY4bEl2cjg1Qkdwa0o2Q3Y1OTg1Q0lYS05OWGpSSTUtQnEwTVFvdzhpblZGcFBfSXo4eHJYWEFOYWoyaFpYOFk0R1VZZ0Jjdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTFBGMlcwSGVsRVF0YmFZUFlid0ZGRXhmYUJBWFhURXVSZjZLaVZZNmo5X25fSTZPUU1XNW1OVXlJUmpJUVREcHJrNFVHWEhLX19CVXdmdWZVREprbXRWeU5uSXhYMlJhcno4bkY3Vm9kVUR0eFpIUU5kdUgwQ3o1UQ?oc=5</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>How Fluor’s Procurement Powers Nuclear Supply Chain - Procurement Magazine</t>
+          <t>Celnor strikes deal for health, safety and compliance services specialist - Insider Media Ltd</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 07:33:57 GMT</t>
+          <t>Tue, 17 Feb 2026 05:35:12 GMT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNT0FGVXNYRzlqMnk3WEt2TDZBZHpFYUg3RGoyRmYyUFl6YW51dGV4eURaSW5aeHJ2b0ViaDROT1ZRRXk5NXQtM3N1Vnp6OXU2Sm9kT2lmSXJpOXNibUxvMm14SGJtSG52MHMtdEtmeHZyX2RSbGU4OTRHM19VTVhkS0pINVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOOFVOUzF5d0RDdkxxQk9UU2h2eVAtc0ZIYkVyQVZzdFgzczdTeFZlNW02VERCUmdnTGJFbGZQZHZNc3RlMzd3WjEwZk91Rm8yaWcwaUZOWFBrMG5Kb29xbm5JNmluaG1TUjVCcTh1cHdDeFBzYXB5M2QzekVMcGk1eC1ZSUM3NTFScUZzVDdIcVQ4OC1YU0lua2xhZXphOWVHb1ljVTVCZWVvc2w4WlNYRWVPR1FUdw?oc=5</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1121,17 +1121,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>China sanctions - Table.Briefings</t>
+          <t>Shipping lobby warns US against port fee plan that could spark reprisal - Splash247</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Sun, 15 Feb 2026 21:27:19 GMT</t>
+          <t>Tue, 17 Feb 2026 07:23:10 GMT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTE1iMG9jUXRWRklnaXJka0hYZi1GWXFiTkZTN3AwXzNRQjJRWnZjM0UwZlJhWlZhZDQ3YVNQdjM3VWNUWDNCQXV1TEgtWmxpeHBzQklJNQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPUXBSN0xBMWtBcEpoZmRJRFRkTkZxSW1GVGppUjNSamRLVnEzcFN6MzhrWDFiUjJTUm9NN09mZnRMQktCd2dMY29fOHc2NjItOVh5eTd6c0k0a0VXSFJRX0pmaGhyLVd3RTdRX3lSX2RiLVFvdHZ3a3N3SWpQNXRZdlFxWlZtazBadXh0eWduV2dwdUVQNDg4cmZ3?oc=5</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Iran says ready for nuclear compromise if US sanctions lifted - Le Monde.fr</t>
+          <t>Hapag-Lloyd to buy Israel’s Zim in $4.2bn shipping deal - Financial Times</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Sun, 15 Feb 2026 12:03:21 GMT</t>
+          <t>Mon, 16 Feb 2026 17:57:32 GMT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOVm95c2Z6V2J5QjNJTzdwZm9FdFRKd19QVFliNmZLTjhNeC14LWFWVzktNnNfaWEzMjF3czRucE9MNUQ0eEdSVFpXQ3l2dU1KUHYyQndzZnJpSEpJRFRmaEFFRUI4MktOMEZTN1dSS05NVE5ZbTdycGFUZHpDS3JNM3hZR2FwZ3djclJXU09SWFZXbWh2bnhNQlhhZ2lWbkV4RjRueFUxX1k5RGVnaVdqV1FnVHlwMzlDemNRQXRVWERCaEZFRlVCN2Utdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBsM212Q0hOSV9GaWhuUTY4REJLQ1NrcTVCN3RyYkxuMFpwa3hrTEdsTUt3TlRrZ21veXhpalh0OFVuSUY2bWk0WW1ZMEsyVXU5RVpBRHlyVHg0SEhpcllMbXo3SmJta0V1WkVBci1Tc3I?oc=5</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>'Port Glasgow parking bedlam is forcing me to push my baby's pram along a busy road' - Greenock Telegraph</t>
+          <t>AI agents: the next step in supply chain automation - Trans.INFO</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 06:30:00 GMT</t>
+          <t>Tue, 17 Feb 2026 04:04:22 GMT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOLW54cEFhM2toUXA1X09RSjdkMERzeGVGT3pHSlZFZ3M4ZVRYYjFvVGh6ZmYtQmM0MDdTdkNHTy1BMElTWl94dmo5bmJFcGdVcDZCR1pObFc5SmVIcjJmWGQyeFNaWW5XakNHMjdJTktuanNScUZrUGY4ZU54RV9BR056NUxrSXNyZHpJM05xcUJPZFkxZXg4ejlhSjRucVNa?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE0xRWl0UVlWSmRmeGNEaFBWQ08yVVJBc1FVdmM1c29mZ1RXYmxjcVRHT3U2MEtHVDgxMVZ3ZVBvbDBqMHgzWndPQ3RMdFU3NTJiQmNOYzBGQjY0LVVG?oc=5</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1211,17 +1211,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tariffs Popped 500% — Of Which We Paid 90%. So How Did Inflation Drop? - Forbes</t>
+          <t>UK Emissions Trading Scheme expansion concerns shipping industry - IOM3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Sun, 15 Feb 2026 16:12:12 GMT</t>
+          <t>Mon, 16 Feb 2026 13:54:35 GMT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNMlh0RVBZYTJ5MHVQdlZfcE5BT04tajlHbnFmLVhjNi1rX01XYjJULWszZXBFb3QxckxxSllhUldXVEhpLS1QS0hqcFJQdU5saXN2YmpHUmJuUXo5ZjRROC1fbDRkWHFIRVJ6SDcxWkJCdFg4S3dPd3AwdWpJY0YzcWJRSjFSY2VfbmZablRZQmtsVDZxdnExbGhFTlppOXdXaWNwTlE5YWNRT25WWWhsOVowaFU2WFhGeWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOWnAzSWFmcnNiZjdfQXlMalBvRC1sQ2JrUmRlTWtxaVlkMWR4RmtDWjVEd0pMRFZIeTlxanJEMGUxR0hxTXJQRktQX1lja08zMkRReDMtMWd6UjRDa0NVTDNKMUF5U2VXNVl0WUJhN0xncHFRS2QzUUVnNUhtMzFLaUtWbGNoRmhaX1Nj?oc=5</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1241,17 +1241,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>GXO Logistics Extends Automotive And Defense Reach With BMW Deal - simplywall.st</t>
+          <t>DP World to operate new Czech logistics facility for BMW Group - Automotive Logistics</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 03:47:01 GMT</t>
+          <t>Mon, 16 Feb 2026 14:32:20 GMT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNUHhweVJmQXF3Q0FkUGZ3Nm9hZHVKT2F2YjVQa1NualZOVi1VSTh5a1R0RmpYX19aclR0Zk1JaG1UZ1EtV3VBNzhKZ3pFMWowelQ5Rk5FZGxaTlJRUUxoS085aW8tc3lDX3lIYUZ2WnJQeUE2QUkzdTBhNXo1QU5aeDY3LU01ZUFXTGhBVThjdXdOaGI0SWJQZmZPcWJiUkt4SndOUFltbVZQOUcwUm10eVJXdHo0LU5pVEFZUjN2ZGRPZEl6ZmVlSnRoMWRrZGs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxOMUNkU0lkNmZnR0dLWXhjaHM4bzRldS1JOC1TaGV5U3FLSTNHdmZtQzRSR2RUT2J1dDVETHl6eHhLSUpqbENIMHhLYWxfUjJPa0pkSkE2OGtIdmY3dnd0TG5qU1RpZDNnNXJYc1lIZWM3alMxVFV5RW4ydU5UWk9LdDd4cUlINUxfTDNFYmlTcEM0aV9VeFpJcXhWbjlWY0VPdUtCU05HVXpMV19fR3hHRkxsd1h6bUpQQXFxZTdjSEVlN2RCelFZZ1lKQ3dzN1hzeHktS3FB?oc=5</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Oil producer Maurel &amp; Prom welcomes easing of US sanctions in Venezuela - TradingView</t>
+          <t>Performance Shipping - businessfocusmagazine.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 06:57:00 GMT</t>
+          <t>Mon, 16 Feb 2026 14:54:55 GMT</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQeDRmV09VUzR0aHJoSG5pRy14bFR6eDRCLXR5UXFjVkNtbWFvMUsySGNDY0o4ZUF5Si1GUWZiekJUY0pCYXB4UlJKMkpfM3VhMXV3VmZZSUhfMERPQncwRVJET0lCR05ZS254WWxUV0VRdkYzXzNDRXFNcFdLTDZoVzBQVzl1N0xYTXAtWF9XbjZZNXI1T3JpdHR1NzVUSng3NHd5OHZyb3h3aXVPdzN6Nk1lRURJOGhtR3lEX2J6NXVVTE9hb0oxdmtwMzlneXVsejM5djRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQSVdjWXBTZVgyaXNIOEpHdzdGdXM5NXBzSnVFbmdzVnBFUk5SaFpZYUhrVzFFMFlWMXdGSFpQUjM5VGw3bGZ4NC1ZNnhmUV9OU0dJN08xTzBCVmpZci0wSThBWDdaSzVHejZTNGVGX3lPOVJTRGRRV29vcVV0Q0ZobEU1dlJWZkNvR1hzVUNjTERudmtBSnNQUVZhRGNxbldZS3FpaDRKZDEzT3lsWURqLUlocTQxUlF1STNJM3Z6a3EtLXItMkE?oc=5</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Seoul races to avert Trump's proposed 25% tariffs - upi.com</t>
+          <t>Schroder AsianTR Inv - Compliance with the Market Abuse Regulation - Research Tree</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 02:30:51 GMT</t>
+          <t>Tue, 17 Feb 2026 07:12:32 GMT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQc25sd185dk5GbGkwaF96SFJkeFBiYkF2MV9FQV9VMUxTRmZGVWd5cElWZS1FNEszWHlXNWRValA2Z0ZteHZscktybllscXZIb0NJbHJGbTNFNHNZTXJsMU9Zc0RTRWc1ZVZfSm9fSzZOb1pGMngtbGtQZWxOLUJIVW5JT1NXeFg5MkVCaTAzLXZET0JmX3ptM19IdTNadlVnd0HSAacBQVVfeXFMUHdsR3NXTVZhYlpkV1pzaC0wRlZXcGwwV2JZeHMtWElMeHE0WHVGZDJPX1F1dkdoUGgwVE9FTFhHeV9OdF93bVBlNzlRcm5LOWtUbExaRzdvV202X19idGplZHNoaVNtZjg0dGdYUlFIbUVSQlJLQllLNnpBamhiRkc2UFlpeWlETkZFNEZMWXBVQm9wTDc5YlFQWF9BRk1oczB0d3c1Tmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNMlI1ai03eHBFWTFpTFpvOVZtemVPR1dRM3BZS2NYWUtrTF8xSWFDMHFGQWcwMmZueGdfVW5hZ2paVUxmdXJ1NElDTDljSUZwSF9JYkx5ODY5VE94Q0pZazhCVlJXMnZKaHFzeGtYeWxwX1FLRjFLbkJOV2xpeklRZUVTWWpDN2lVM0tVOHRhdXk4VG9oelMtQ0Z2ajlCT1VaTWZFRHBwMEtWMzdEUFQ5SlJBSGpGa1pVTnIw?oc=5</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1331,17 +1331,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CK Hutchison warns Maersk over Panama’s Balboa, Cristobal terminals - Shipping Telegraph</t>
+          <t>ICS opposes proposed US port fees on foreign-built vessels - Seatrade Maritime News</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 01:58:31 GMT</t>
+          <t>Tue, 17 Feb 2026 05:14:45 GMT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQTFZEODlEcjdvNmx0c1Q1YkNsYmo5QUh3blA1UXd2LXBJalhvU1duT01IMVZqLVBqS1Z2T09IZ3pyOWNYNGw3TjNhYU5qQ0xOQy02NmRiSGpiVUhFYXRrTTNRVnE3dGtNU3NvZG1RVmdpM05fTm54NXBOWTJqOWlUNWVmMm5lNjhyS19raEYtcVF0dENBS3lhdlZZTWUyajRtX0tUdzJpZWd0QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPMVBWZFZORG1CeXRFeHNRMllYaG9mdS05b2hYeHU5SE5QN3RKVVNKdW5pSlA4cXEwVThzUkNEbVhtLVFpclhjVzhIZ2otZW8tSTFaZmk4QmphY09yeER2dFR1eV9hTHlsN3A1VDJxdU03OThFd1RjYnVtYmlKdk9DLXRWM0IxeTh5aFFOeVhnRWJsci1JNlhXb2RnN0J5X2ZwQ1NhMWhoWQ?oc=5</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Memory crunch tightens CIS capacity, pressures smartphone supply chain - digitimes</t>
+          <t>The hidden cost of poor compliance reconciliation - FinTech Global</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 07:24:07 GMT</t>
+          <t>Mon, 16 Feb 2026 12:17:11 GMT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNdFdfZjdiVnRtaEl1eFBRNzRuSzFxZnRXamFHeEtQTjl5ZHlzclQyWDV2WXZPbGNBRTV1Y3VsRDhoVWgyT2tsZ3lESUkwaGR6OG1wR0xCUUw4cHk3Nk1fSU1wdEhvcHA3eFM2dzczVVdmTmdRM281aUozV3VMVGpDTWhtR1RvT09sU1FpZVZQN05Ed1RENms4dg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOVmdSeWh2WkV5UE1uTlQwbHpzcC1qZDdEVzBOYkprMEpubXluSWo1aXQ3bFRVbHN5NGlHbXpkY1hfb1JMS0IwVmk2SXdWTjBmRWJxeGxNZHN5WFFoMVItZXJ4c3hEV2d6MEF6N3c4ZEt0NkJScVY4cnAtU0daUE9rdDVEamZiTnJRVEFXeA?oc=5</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1391,17 +1391,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Port of Aarhus sets record container volumes in 2025 - Container News</t>
+          <t>Work begins on new Welsh medium primary school in Port Talbot - Wales 247</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 07:17:28 GMT</t>
+          <t>Tue, 17 Feb 2026 05:57:04 GMT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxNbWcyQVY5U1FOSlZZRVFJTXo5Rk43WGdhZmNVLTQzMktjOVhMRUVIaW5LSVN6RVFiVnNfaHdaRTNuMjY2eS1DY2lfU0FKbXN0azRFQnB5cGtpOENOczNkYkczNUdXNWplUlJzNzBrVnN2N1ZPUEk4YnltSHZNVng3d0gwNHdwZmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOdUJ2UFJyWHh0SVVYalZ4bk5iQk5PRkpkU0gxQ2JNajFwV1ZGbWJkeV9tMkJWNU1TbjJuOEU4ak5pZnA2cGlvNlU4Z2xhUzJmOGtUZWpFX1dMeHFkYk1TZUxtODhEcXVuNmZobi1qdE1rVFN1OGhodFo1YzlmRmFtX0xZZDY5YTNYb0Zvbk1BdEJ2dw?oc=5</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1421,17 +1421,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Gale-force winds paralyse parts of Catalonia, disrupting flights, roads and freight corridors - VisaHQ</t>
+          <t>Fears of contractor ‘instability’ mount amid gateway three delays - Construction News</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Sun, 15 Feb 2026 23:25:53 GMT</t>
+          <t>Mon, 16 Feb 2026 12:50:29 GMT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQTEVpTzVadm41RGljeU9sWV8xMVRET293YmFqeFB5azlhamtZUjBLYzNKekozOEc0NjJ1Y0VabjFxQ2Z2OW9COGx5Sm5pZ3ZuMWs3bm1ZTWNIQ3JZOFE2ZGpucWRKZE5FWkw1M1ZFcG56emZnYkEzNzdnNWFLcDM1TEdaeWRhdXFrTmpnX28xYWFZOXY3b0ZsLTFWQV9Rdk81VzBVa2daeW5ienMtT0NMVDJOdUpyWkxRNXAwYk1LbXZjanJrT3hDRThFZE9adDA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQSTg0ZFRkMkdNYzFvN0tjMF9Ydlo4MzZReWpBZmxKbGdDQTJnSGVDU1JOYzZSTWdfNUVkaFpTTEVUWTZ6bUJYSmZ2OFlCYkxuekdReDd2a096OWhOdmVvQmhLNTcyVDVnbDllUUJJblZXLXpiQTR0Q29aV1M1NEFsdHBXNG8wTUNIMmdiRjZocFNlRV9BMUgycUI1RmpzWDJFZG5rLU1NY3NOOEpqek8zc2ZUdXF0OGpDT0REQmhZdm5HRzhEX05CSVd0QmxfbDY5ckE?oc=5</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1451,17 +1451,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Americans, not other countries, paid Trump's tariffs in 2025 - USA Today</t>
+          <t>Police seize huge £53 MILLION cocaine haul at port then arrest man in Manchester - Manchester Evening News</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Sun, 15 Feb 2026 19:42:00 GMT</t>
+          <t>Tue, 17 Feb 2026 06:52:00 GMT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNbzVnQUJKOTg0NHdCT0dPcjg0VGlCS2JrT0xJYWF4d3pLa1F1OTNNUi03X2RHdjdCOFJyTUtsOUFIOHljN1hHSmhpRDhsYlJ1ZmRHcEJINUdpNDBYbTZEQVltRzNDV2sxMllBWFZtRkx5d2xoQzdJSTh1cE5NbDR1Q0FYRHByekZOUkVEQk0yTWh2RXVMTk53b3UzdjJjUGhPU2hGRHdySQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNMGloU2Vvb0g4RUFXYXNpMzdpMGEtaFNlbmVUNlRTd1dDVEpWanhnbmtrcHlrZWUtTjRtdFlUbS01T2JPcHd2Ym50QTdNWnp5eXVSMVBydmF6eFVHbEVJSDdVMkk3ZDktNk9UaGw4TzJxOEo3MHdZMTh3NjdGcW5NYm4wNDVPeUl4eE5pbFF4TENHOHZ0M0lSeGpYMklfNF9sSlRWUkluVVd4d9IBrwFBVV95cUxPSE1XYnE5dFp4VW8zSjNNMUFQMTJfX2hLV3hEaE9JWXdKMFE3MzlKQ1U3Wm5ISURKRlFjMTNoam9XVkRPQzNfS3dCVi1CMDZBMFN2YnJJQzU2aHU3YnFxY0pRSzgza0VlazJNWVk1MUhwRFUtZ3dRZDFIZkVabUlOcnhGTG1ZenJlSFlLVG9icE1TNldTS1ROUkRBMkVrbi1fOXotOEpncjZTYWljb3Q0?oc=5</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1471,27 +1471,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Pepper spray and threat of 'sonic weapons' at protests alarm rights groups - Australian Broadcasting Corporation</t>
+          <t>ESG round-up: ECB fines Crédit Agricole over non-compliance on climate risks - Responsible Investor</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 02:12:40 GMT</t>
+          <t>Mon, 16 Feb 2026 16:06:20 GMT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPbjhXUHI3YW9KbUNObzdvVnhSSnlhUmdwemVRQksxOEhOdXFwcUpJd0JlNzlPSnoyWUNjMUZseXYyYWV6Tk5qcjJ2S0xuUkFSOXRDTjloS1RRZDVaSWNiZ1l4UEJHT2xXQ0liN1RSSWVjY3lYTjk2RUxHMjJtcXRMWXBOMk9uV1BRSEY1YWVpZm1YTFZEcGI5cE56aGloRDZPeTVn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPTUxyTWkxVk9fUHRDekplbTNHcmZtcnh4MUJ6VVB4V0ZoMDZrSTJuMDhGcnFKUDBkUUYzLVg5aGpFVnpuXzYweXVzNmlScU8teU5VdlNrMGZjeDFlZlNlZGdZblljRGQ1X0tneHNPeEFuWW9FWll0aTdmRE1nWFNsUzVPN0d1TzNKNEtPczFyMnNWRjBoRzJBVTBKb0g5Y0k2eU13WkZERDdUblNXaGdMbldVdw?oc=5</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1501,27 +1501,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>An estimated 350,000 people rally in Toronto in support of Iran protests, police say - CBC</t>
+          <t>Apple's Bengaluru Education Hub: Solving the India Premium - Supply Chain Digital Magazine</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Sun, 15 Feb 2026 20:50:35 GMT</t>
+          <t>Mon, 16 Feb 2026 14:51:06 GMT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE0yelB6NVNDWVRJS3JPZS1PTGxsd01uQUJpWmx5eHRYcHRmZlNjX045SlpSYUprdERfQm9zSUNJRDJ6YnFtTy1RXy0xVlFmUTZJa2RrRlpFTDVHUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOS0hLYzFQR0tuT0F0OXlwTHQxeXdQVndPVC1RbVFzc2xMYWdaMF92QU1ZX0ZWOWhhNGpPVVhIMzQzM29Gek1Fcld0RWpfa1BWay1CaDBrZDJHdUQwcDA5WDdrWHRQUDEwVTdLQlB4eEdpcU50VHFCc3RmTlB2Y1paSjFCenJpNmdvWnlidDlLUFM?oc=5</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1531,27 +1531,27 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>‘Awful to see that much hatred’: Anti-Israel protest fallout deepens - dailytelegraph.com.au</t>
+          <t>Another acquisition for Celnor Group in construction compliance sector - Construction Wave</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 05:07:07 GMT</t>
+          <t>Mon, 16 Feb 2026 14:39:26 GMT</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAJBVV95cUxQTEFtZFN6Q2wxQWNNUlNvZ0lVa09KODdVZWhsQ05yX1FrV2ZlbG54UTBMTTBJUWswVEZ1MDhEdUZITzBxaHJlV002X1ZXTndVQlpKS1YxdVViOFY3aDFGQ3MzQzJWQ1paZ3Q0cXJLcmdYNTRLZ3R4dGNoN09SM2VoQWZVYXFTUWVTNW9BalF5MUJHS0h6eDVQdWNZRjZpTy1sSGRnQkRJSVI4eDgxZXdGRWhJZFVEb1RZTWFMWFdGbGlGVV9mR0ROdFNlSXYtdUQ3c3pXV3ZiWWhrQzlqR3hpb1RCUFBfRmE3Q2xQTzE4eWdsMEhiMDdIVWxRSU42dktzaHo5NGh5MktjUXkwdGFKcjhhRVrSAZoCQVVfeXFMTVJPcjRhamxlS1NFTnRQOVh0X3ZmTGtjbUFQMmNxb1UyR3RUcGk2b0lEZ0FZQ3NpZDVoQ2tNZWhtMndLSF9LUC1IcDhvbU1RVVlHU2lSRWtoSWlMMUJ3X0U1OFNKUEo3cjRtMlBFVWVNems5WjRGcml0UmszQUhKbDV1ZnFCRU1kUlUwZXFid3A5R09FeVFLaDFIQ3pJdGFGYjJ6UUlIeGl2UWVtVElXMEcyMmhKZHFETkZnUW1ZTVBxQ09rOUp1cGtpVlJjazJEb1lzSzRRc2pWQW9xVXdWQ01pRUtsakY1Q2lpVGZVTXhNaWhYUkVDNm83RHNUTW9hTHB6Ykk3cUN0RjdjYUNTUFlJS21STlJTYjBR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNaV9hNzBrRmZqWXJpSEtKaE5Xek0ycG5iSFZfNzdVVzFQY1hWUVFnQU5EbFZRWlNzcjhfalc5M19MdVFBUUNTSG9lV0FVUTNpeUJYY2MxREw0cXBMbWEzN19YN0k5akw0d25ESUpva2pVd3VOMVN1OU9RWDNrS05mWWJsMlM2X2xfU0pucUx6dFdXNzQ1d1djb0JvMno4UlVJVEFqME5oYjBZNzFzLTFPSG5BZw?oc=5</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1561,27 +1561,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New Protests scheduled for Today in BiH’s Capital - Sarajevo Times</t>
+          <t>AI at Kraken Compliance: automating the routine, elevating the critical - Kraken Blog</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Sun, 15 Feb 2026 11:30:14 GMT</t>
+          <t>Mon, 16 Feb 2026 17:48:41 GMT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPcmhuLTZpZmJ3VEFUNFZveklqekpLU25oLXFvaE5JczlTVWdBcFB4LU5sRlViOFpPbkUzRk9zWnktT29uQmh4UmxmWXZ2YlBhcy13b0gtdFptRTdYN2Q3dUQ0eWkycDFKRW5SM3lGZzBVTnQxUWJjV2tacWFzWkoxUtIBgAFBVV95cUxPcmhuLTZpZmJ3VEFUNFZveklqekpLU25oLXFvaE5JczlTVWdBcFB4LU5sRlViOFpPbkUzRk9zWnktT29uQmh4UmxmWXZ2YlBhcy13b0gtdFptRTdYN2Q3dUQ0eWkycDFKRW5SM3lGZzBVTnQxUWJjV2tacWFzWkoxUg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE1aOEVkb0QzZjloN016N09DOE43Z3ZkY0NzbEJHRzROQ2ExekZaMEZ0SHdNUUxjUU10OTZlQUNzcmJHdzBkZklteGxhVGxLTE43dFRqeEtleWVPVGtHWGlzQ0toQmh4MnpibUE?oc=5</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -1591,27 +1591,27 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Fahmi: Rafizi ‘has the right’ to attend Azam Baki rally, police report no unrest - Malay Mail</t>
+          <t>Hoshyar Zebari: US warns Iraq of potential sanctions targeting key institutions - Iraqi News</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 05:39:26 GMT</t>
+          <t>Tue, 17 Feb 2026 05:41:03 GMT</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOdkt5NkpYbjQwcFBjZ2lfVnB6VUFjSHFuaERVOU5lSUJBOUxvaWVyMjNEcmZMa29XNldiY0FMdldvSzhscDVZMGU5SWNxY0dTNGdudEV0TjdlQVhYSE5BQ3poWFBRT3BhUE1RRks2emdBRVFUNVBzNnIzQUNpcVh3OU82R2hFYzBhLWZ6ZW5vczhrTEhYUDBJZV83T1R4RGJlNFpmd2w0c1A4eGNjM3o4Z1EwdVUyS0RVTl9MU245ai1HVFNoTmFrZko5QWlXR2vSAdQBQVVfeXFMT0RQZ24zRTRRNkM3dnhUMzM5TnVuTmRGZTBsR3lKRGU2ZWxsaWZHbVJoR0ZNZmxZdTJlbEM0elRpeGtsdFFCa1FVS1FNN3cxa3NGWGlpZVpCUlZ4bnc5aHlJVFBuOG1MNzRVeUpCOXhBVU0wLVZzOWUwMjR4bzFXZmRkQkR3dnRhTU5vcjhKaUhTaTlpOXdHX0syYmhsZjRaTWUxZ2k0WjNhMzFSbXdXR0ZmdjZPY0h6eHdjQm1aUVNEcDZEQVBBLThnT0RMSFZnRVBvV0w?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE5jMXY1aGtOZHNnS1Q0eXVMeEwtb2ljTHlRRGpwZ1Fyb0Rua0FYOGo0bmtsVTFhN0J3OE1LYWZBdzF2SDNLMjFjREVxSFNUSFJnN2o5RUI2M1BieU9aai1fUlNWVFlaQzdEajVCWmNqQW1PM1VPWlh2X00telM4UQ?oc=5</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1621,27 +1621,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Careless driving charge expected after vehicle strikes building - Sarnia Police Service</t>
+          <t>Why Intelligent Workforce Compliance Depends on Context, Not Alerts - ADP</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Sun, 15 Feb 2026 15:02:29 GMT</t>
+          <t>Tue, 17 Feb 2026 07:20:56 GMT</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOb0R4TnZSZ2gyMmNJRXVBNmlaOFlsTWlzZWllSDJuLURob0lOdnpUR1hXN09rRWZQTHhrcXJ1Y1FydkVUdklocWUxbUNHeFpVcV9rc1dYN09ENEFKRWViZ0N4dXRBNy1KS2V3SDQtTElSdTc3aE91OXVZempOeGoxRlNGS0kweURoWEdoeEozSnozWE9UMzd0MjlzSlBIZjBVc3dr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNYzVZVmlsVUgzYW0zU21YTHE0Y1M2azA5XzA1am1GLVZHUm9EZmVrZTBHclJyd1J3RHVHZUN2clVfMGsyQ0trMFZtVW16U2gtUXRZNFlJYkVncHJ3a1NnTkNiMThldlBudnkwVHVQRWtDY0JFZXBwR1gyLVR3Q21ORmphVS1xNFpLdE5KWmFOY1dpSmlBM1A5aXJrcFplR0lEenF1T1p1QXJUb0lHSVJ2MWcwRzk?oc=5</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1651,27 +1651,27 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Barclays warns motor insurers - especially Aviva - of 'slow-burn' AI and autonomy squeeze - Insurance Business</t>
+          <t>How shipping company MSC facilitates trade from Israeli settlements through - Al Jazeera</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 06:22:32 GMT</t>
+          <t>Mon, 16 Feb 2026 14:08:42 GMT</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxOdm9Wc1JXT3NadV80Y3dnY1hMMEstZ0tRZ18wLVN1VGl1RjMtc1ZuYmJpdTN5LThlNTg1UlMxb0pCS0ZEX29yWXV3X21SSTh0U3dHalhtMkhtcFRxZnF2cWE3M3NrbGw0RmFBUXNyM09uMnFtTy13amVvNGItNGNDMUpLd2VTSjROYjExQWs5Y3lpdVpqc0NUYjZleDM0Tk1waVVPb1pNTl9wRXBsNFlhN2FSMEJEYktWM1M2YlkzMEoxN1dCRVhlcHV0WTk1QWRyM09talVYMkxOSVZ5M3FsQ1BCT1hQaU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOd3ROZHhjeUZGLVN1bFNxcHdaTzVFMVJpeHloYlVsWE1lRnJSa1dDc1h3T2JPZVVibk5YT3Fod0pDMlRUTWNqYlBMa2lCTVRtQlBadXhBQ0dOdVVyRVRHMkU3Y3Q2MV9yZXphVm1MX2lhYmhxaUpUbVNZXzZvdWZmVkNYdl82bTc1RWsyNlNObUZSMi1GbzJTNnhqblZrQzJTZ3laT1ZWUEo0N0lqajcwbGtJNmVuLTg1R092ZUpDUjQtQkRx0gHKAUFVX3lxTFBYbnBZNEkwaU9XYUNDVlRrdGZIQzlGbnFjU3dyelVOenBqTmE0eFJ6QUM2d2pKY01iNThiV2FLQ3EyRWV4VUhQY2czSWhTa0JnRklyaEl4RFdzZ3l1V3ZKN0ZHOHZvekZGMGpIdmV1MFdwdnZSVENXekhhV2oxQWl1Vkk5QmxCcUtXSTJpM3BsbWtJbmRGaDRWbXRaR2IzcHFnSEdFNncyUU43YldTQUdiZGdJRGNoekVlN19wYmlpaXZFa3hfWDJScUE?oc=5</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1681,27 +1681,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>UK’s Starmer announces crackdown on AI chatbots in child safety push - Al Jazeera</t>
+          <t>News Content Hub - The hidden geography of LNG shipping risk - rivieramm.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 06:53:56 GMT</t>
+          <t>Mon, 16 Feb 2026 12:00:42 GMT</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOcHhNdWVCT1JtUzF5dlRqOVNyYzR4dERmUng3R2piNllDUElwWFBHUDhKMEFPOFlBeXR0aFZtYlhoOWM4cDhwRlNrUE5oWWh6TnhubHBrSzk2aUdDRGtleUVRQk45ejFJc2ZwR211VlFrTzFXaTlScmdfU0I3ZlNwS1B5Q0xqelVMYlhtaml0VHUtaU5DVU8yelZxUUxzQVRfb19TaFZLdjlHNlVx0gGyAUFVX3lxTFBmaTFnaHEwbzRFaDVYMWl5NDNBTWRnQ2lORVlRVlpTU0dfbmZPNlhGQ0N2X2hHcUdiNWRsR1VQbl9EOTd1bEtqT3V4bXpVcWdERWlSMHRxcXBCUzRGYzJFVmliM29zZGt3UHByaDdoTnJFX3ZuRmVkaGlLZzZka2JyYksxQTI4cWtQWGNLdWZrbVhpNU1HaEVLUGU2UkxncGtyNHI5b1RqWlFRQUIwUTdzekE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNX1BTWURNWDJJN2E0M1drWHZtbTVMTklHVTc4cTlKVmdCZFZFX2pzV1BYV3c2YmYtNWJFdXpoNDRyN2tOcVVWWVVGeTRSOGtJRE96U19iemY4TFB3Z0NYZnFwNVp3NE9VWS0tMGljWURNamJLOGdOMUMwS3VsZ1lnZGM5M3Uxek43VHN4Qm00TmlfcENG?oc=5</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1711,27 +1711,27 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>First ASIC penalty for cybersecurity failures: Federal Court imposes $2.5m penalty on FIIG - Herbert Smith Freehills Kramer</t>
+          <t>Man who left ex 'scared' after 'loitering' outside her work hit with fine - Greenock Telegraph</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 07:26:27 GMT</t>
+          <t>Tue, 17 Feb 2026 06:30:00 GMT</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQOXNwREM1MWpSRVNPZFA3cld5X1d1eVRQTFRJWVRXT3RQMW8yNjhORHZOUEE1VDZfaGRmR3l2eE55akV2M0JBRFU0cDc4M0JUNzc5NjZDdkhBdXZHZ3NvUkRZNEgwQzNYbXNIdHU1eF8xRU4yT0tndjRubHVCQk8tZXU3RU9fNHEyZzlLVHVHR1JMd24zMC05eG55OE9WaEV1SGZSbUJ0RmpPNE1DYVFRTE9ZejI2a182Y05zeVpVTXVvdnFIenVYMlJXdEJVRmRXUDEzbE1rWFV3QlZ2ZzZpWFlmODgyRm4t?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOSkVxVEhycDFTcXpwRHNzbjVaOWIyNFp6WlczYU1qRWRCU0NxT21LSjFDYjBqNDhxUjBoNHMxeXhjRXZJNjkydWgzR2lLaDFUNjBjeTlFU0JNMDdOQUtWTV9sTDhCcU5VbldkS1VIS3kwM2E0SzFKQ2JpRS1mTHk4dkhWZXg3Ym8wTG9NWWtDSFQ3Ni0tU0I3cUdubF9WMmpsN2c?oc=5</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1741,27 +1741,27 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AI in Markets: Embedded, but not Autonomous - The Full FX</t>
+          <t>Sweden's Gothenburg Port fined for illegal terminal concession - Baird Maritime</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 05:55:31 GMT</t>
+          <t>Tue, 17 Feb 2026 02:38:01 GMT</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE4zcHYzcERfVC1SVmtBZVFRZ20zdTFZVGVMMnl0WXFKSDBRb0Z1WkoxQU9NRDhaaHUxZ1NzbVlLVFo0YWdMamhjX2FId0drYjFfTm1TaHR2X3BFNU9yMEFlXzV4bFd2SW04RDFhMnJuQ1o4UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNcVBYMWV2UDlRNU5YWjJWcVVvMXVyc1had3NoVXhkV0VKTEdkN0I4UnFUMFhJeXV2aldqcnpDR0JOTGZJc0l0cHc5VFlhNUJkS3RnSUNsMTI2RGtDek9NWFM1bDNMT1c4aE5MRjdBaWkxTHdjdlZzZlF2MHJvRURVeU9ZbnYxSWRfYlVHOEV6WkdmZHg1TFh6cksyWVFBRGZ3dy1lcTRXZGc0d9IBtwFBVV95cUxOTDIyWXdMcU9GSU42YmJiLUN2TjVraWtVNnMwR0tLOEkxd2xOMGxQbVVNd0haNmF6cDFlaHRRT2Z1S21vNVZ4bU9zUERpQm94WWlzb01halA4VUpWbWNyaE82YjRsX1E1d0ZaQUhkXzVJXzhTTy1tS1R1VjlBcmRaZkJLUHMzVlN5eS1ZN1llUzFnY3Q5NGo1TVQxNWpaNXNlR2xpSndyb2VONUVlM0VLQkpMYWxpUk0?oc=5</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1771,27 +1771,27 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Leaders gather for New Delhi AI summit as warnings grow over societal risks - France 24</t>
+          <t>Macquarie Agrees to Buy Australian Ports and Logistics Company Qube - The Maritime Executive</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 02:09:52 GMT</t>
+          <t>Tue, 17 Feb 2026 00:19:28 GMT</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE5MWl9WaERHMXBZaTRBVnZISDY2ekdSREtiV3pxUGYwMGNFdXF5OFd3a3RuVFRrZDRSX3JtaDNQM0RQVXlYaDdZZjRFX0RlYUZmR0MzVGNTT212UWpkWW5qTmJUcDN4Zjk0Vk9ndXNWTjVWdndFT0xmc0szcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNU1pJeHZOSC1nZDltTHF6TjcwUzItakNFV3VxZXVoUHlRUXRPaDJ3S0FnbWdMUkppWXJVY0tzYjZ4SEV2RTM0TXlyamFyM0ltdGV2cmtfVnl3SEhWRkFNc3V5Y0RlQW1OcXZvMUdQNV9hZlhCMlhoMlNxUk5aVDFQRVNnVmt1TkFOY0JxeURlTmE0Wko2eG1kZDJxa1dtRkhvZ1JRSEJlMTVGUQ?oc=5</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1801,27 +1801,27 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Google puts users at risk by downplaying health disclaimers under AI Overviews - The Guardian</t>
+          <t>Arrest made after officer assaulted at Warwick protest - Warwickshire Police</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 07:30:00 GMT</t>
+          <t>Mon, 16 Feb 2026 15:45:00 GMT</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQS3p1YV9xWTJHS0pILUpUbnY1VVE2VGlNcTkwaVV2YjRBMC1yYkUxWl9rVDV2R0s0ZVIxTjJjUS1GT1FtTnBVZjNyVHVYVlpPRTV3cVVVT1UzUDRscHFKNWJzN0Q0djJOSW5aNmZqcFduQmVVRlpldGNUMkk5OFZFTHRTXzl6Tzg4OFRsa0w4eUxXZnZfdWtTUzNsdFZ5cS1LUFEtT0hlT1o2UFVnQlREbFdSZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNSG5sSW9TenItckIzVkpWNHpKMUpQUkZMaERQQVNfcmNaNE51QVJEQUViaWFBc01XT1lTNUQycFhhQ0xIYW4xR3NpR2ZVVUVWR1lhNFBHcUhsNUZ3OE94Y0RLMWx2c0ZsZXNEb0dTRk94YzlZa0g4OUhBczlYYjNDUEhOazZxUk95NjkwdEcteEx4QnhZSVBHVEc0NDIyWk9nY2l2YlZqNGlIM0xWcGd1ZDNCQW9saFpPd1hDVkstRjVnTWQxZmc?oc=5</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -1831,27 +1831,27 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Technology for Change Asia 2026 to decode innovation for business growth - PR Newswire UK</t>
+          <t>‘It was terrifying’: Australia faces reckoning over brutal police crackdown on pro-Palestine protests - The Independent</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 01:05:00 GMT</t>
+          <t>Tue, 17 Feb 2026 05:25:00 GMT</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQX0tEXy1ZWU5DdzZCYm5ndC1UMmhiYTRya19kZjZCa1pmMHl2R1hRbXZXbXlxUFVWNmJNX08wdWtxZEVkZnlhcU1ZVmJ6dHlDRFlnM25iSjlZMUlBSUE5c2dOalROR1pIM1Bxc0l5Q19wLWlrVDZJaGR4YTQzVmhZVERxV1l3eTY1cHl4UWVZT0lwREl1WE9TUENsM3hrNWxOTWxBck96ci16ckI5WlpnZWdQb1Q0RHVadEFQZ3FYVjZCUG1RQ2hPbkJn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPTy0wZ1RhcWs1Ny1iVm5lQUJaeWc0X0VwWmNVVTdNcGl1cmVkd3JpRUtEeWlNRzBjVmdYbkZYNXp1bGZLbGlCZUZjNGk4bGplZWRRZEhZQXpPRVN2dm4zR2p1TW9kV1BGZ09WZmNuVWRWQV9tVDgxQVdmYzhZNUZSemlMUm15YndZWW1rajRrY2o2dFNzMFd6SVVzX0dGcXNBN2swbVZwakg0U1E1enJiOVFmSjBSdw?oc=5</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -1861,27 +1861,27 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Neurophet bags 510(k) for Alzheimer's imaging AI and more briefs - MobiHealthNews</t>
+          <t>Sydney's post-Bondi attack protest restrictions come to an end - Australian Broadcasting Corporation</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 05:03:34 GMT</t>
+          <t>Mon, 16 Feb 2026 23:22:53 GMT</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxObTlzaV9nTXZQVkI0OWIwSVpQQmlYTHV5aWVSSjlpSnVNTTc5cUVWV3BfSXVWYWUzSG5INkVaY1pSMTYwQzU3c2Fudk9nUXo3SDhmczJSc0VrNHRNZ1RyOGl6Sm5VT3c0TXZ2bDFhTXhOR2VKQ1Z5NUgzVDFBM1ZnYWtMQzFPTDVnZmZsUzZQbVV1RDFWQ2tXQ1A5YXN0dWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPbE5YbTFGVEt4bmdrRXh3eHFTS25HV0ZQclVYOEd2WTdXdFJxZ0VaYVkyd01hcEpGX2xzXzY2YnZfMHFDeFlGcjFvZ2FDRVdhRlBmaFZ3N29kaDRSRmFKZktvcnFpdjdTQkpfM01ZUUVqTnY0cGthZEhCQkxrQVdSRGFDWmdNcUhNWXJRMWxnUGxjaWducUtPVGR6Ml82NWNPZ3NaMmtQM3BPSms?oc=5</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -1891,27 +1891,27 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Rethinking human connection under the influence of AI. - Psychology Today</t>
+          <t>Arion Bank Sets March AGM to Vote on Dividend, Capital Cut and Share Buybacks - TipRanks</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Sun, 15 Feb 2026 22:24:29 GMT</t>
+          <t>Mon, 16 Feb 2026 20:05:23 GMT</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQdnI4LW9vNEs0OE85N3V3NWlrYmpNcHFvdy0yUEFHYmdqWjMtV1Jva3czdHFpTG9ETUwxVHp1ZUlLcWpCZTNfSFJnZkFOVGNaOHhYYzlxanhGTGFaSUlsTl9yaFg5Q2lYS1p6UUhlR3Rsbzhna3F4NWtCOVpzUnhGTUFLVHllRHB2VFlmdUk2X21TcWg0WjZZ0gGcAUFVX3lxTE1kUF9rMG1pd2RCVWttRlRUaHFha2J1UFpFbHVKUE9KSkZUUXloTkcySzBrNzQ5cnBMMmRhSzJrY0xMWnMwRWllbGZpaWctMFVsT3p2QVduaEtHb3c2Nlc1VTNLR1hjSmFESEFEbGZRTmdmT3lMMVhlX19PTmQ1bzlrYS1ZOEx1RllFWTlDWEpqZnJ0NE9XNWxNYi1OTw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNY2xOUXVIVFNZaEV1SDQ2ejlReVp1SF9TMTFCU09LWkNZYUpLVExCX3NTRWJrUUtJOUZVT2Q0bXFVNEU3WDZ3RXExTWZQdjBrTkFiQmk1TFRRdXJGbXc5SElZUExhTDVyNkNUVVk3SlVhOUtqMVNrYS1POWRSQ01JcTJGT3Y5ekdEeVRUVE9jUzhPcFBONHdwSG5NTnZLWlNaeDVEZTNRSktKZ3cyUUZsREVMX05QODd3dEgzOVI4S2NGYUxJRWR3?oc=5</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -1921,27 +1921,27 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Tom Lee Says AI Killed Software And Job Losses Are 'Soon To Follow' - Yahoo Finance</t>
+          <t>Today in History: March 3, Rodney King beaten by Los Angeles police - Norwalk Hour</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Sun, 15 Feb 2026 23:01:55 GMT</t>
+          <t>Mon, 16 Feb 2026 20:40:39 GMT</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE10QXRncnZWXzJXWE5Jbks3R29jQlB6UkRKWFB1WHZFU2VmRUtWa2g4dGtHY3BZVkljWnhlVTk5UUNfZjhQRFVfWGt6SEZVVXMxUEFyZ2pScHdHTi1kYkV2SDNzQ1plS2RKQ1UxbThuVFZQRDZCMUkw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPU2JpTGxDek5qMi1ZZV9NWWp2MWVadjJhTUdKbXNXSDNiLVZ3RXVzbk8weU43LUs3Sk1MY2pMY0FxM3ZUbTdlUGVHWWFxS1lEZ2dfTVNzQWUtVHhzWHY1Rmt2M2pUelVGZVRfYW1CcHNhNmt0Y3BNREhlVVpzenU2YWx0S1dHY0x4d28yNWJ5bldycTJNaTRmRDFhRzU?oc=5</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -1951,27 +1951,27 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>What is AI’s extreme impact on the young people of today’s society? - The Bolton News</t>
+          <t>Protest marches can return to city, eastern suburbs, police declare - SMH.com.au</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 05:00:00 GMT</t>
+          <t>Tue, 17 Feb 2026 00:39:30 GMT</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQMEpQZzZreTNiMW5NejhFbzM2ZzVwb0JReGRvX1JYVGtJS0pISVBLT0ttMVprbUxMZGlqTm0tQnFISXJSR0kwWExhVHVQVnNxS0lqd293NHdCTnJCZjJjaUhnTFk1LWpmN3dSZGFSNUlka0pnc3VyNUgyVE9kbjJnZVM2NWpnU3FJMkNVY1Rtb2JSVE5udW41eQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQcEYxUGxtLXpZWjFiMDlCN2hld1BxYVgycFdFNV9oekdCSVVabGVJZXNXczFLTWpLeW1tamxPbmZQcU5BaFN4ZzFfNXNUeWhLQTh2azZHVDRlakc3WV90cmNLYUNyeDRodncwOG5pSkxRUHZHOGxndXM1RXBZelVCVFBfQkRQMkZoN2t1S0REckh2Zi16OGF6SzVqbW9FdWdEMjlCSWhlXzM4OU5IVXlQbWZhRl8wZUQ4LTYyb19DQQ?oc=5</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -1981,27 +1981,27 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Generali creates new group technology unit to support insurance platform rollout - Insurance Business</t>
+          <t>Toronto police make 2 arrests related to weekend rally to support Iran protests - Global News</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 03:34:05 GMT</t>
+          <t>Mon, 16 Feb 2026 16:08:27 GMT</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxOZlNiZkNGenhKTlo4QzhZTGV0V1ZCbk8wNGNtQllOQkpQaVdWQk5lWkhna09qZWlQS2tMQVBGOVZwS1BXTUJmdFp3ZnowdnVkMVRHVF85bjZ0MllJaFYxTENPS3liX1h6bDdBcV9XNy1qbDZ3cWJXMVJEUnFpOGNfU3JZSXJCZll3RVFoNEJ2SXEyTUdQOWxacy05MEo5eEoybWNLMlJVczRyNVdKaG0xVXNFUzd5VVRiUVF1ZlJiX0RacE1Eb1phQy0wbFlnbWktV0JZQ3E5OTR5cl9vbm5wQXItOTdDQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBnS2FiSFNTdTdBRWRPRWJFQmRuVHZLalhjcVRPcHdTamtxUXBpUHZwRm9OeXlMZ3lVNG9KWGRYa241ZXNMUWg0cm5pc2h6VUszVHhIRjFPcTMtcC0tRi1SaDdjcS1SMVBYRGhDcW5DYmw?oc=5</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2011,27 +2011,27 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>No swiping involved: the AI dating apps promising to find your soulmate | AI (artificial intelligence) - The Guardian</t>
+          <t>‘Excessive and disproportionate’: Police criticize feds’ tear gas tactics at Portland ICE protests - OregonLive.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Sun, 15 Feb 2026 08:59:00 GMT</t>
+          <t>Tue, 17 Feb 2026 01:59:00 GMT</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPV1Zod2NZMU1vM3k0dTR6UVJBWUk0M0RVb2d5MVc4elAwN3pzNGlhVnMxLVZTMS1QMkk4ZFVOVEJiajZzdTRCbXhOVmVWci1wXzRsNDRESnhpVy1HckljUndHMndydU1EY0RVMGZoLWR3S29sQ3MyczRodnpJQ0MybU5ocG8xRmhpX0twR3JKOXE4YUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQQWlNdExvelZ6cGpvcW1WVGtKa1djdFRfWmRqZGl4RVAyR0FLR24xQ3BNWVB0YjI0b2ZBbks5UHdJaXZ5NUxqXzNzTVhveVZkYkhrbnJGYXRHeXJTbzhKbGhBWjV4Zk1uaEtqOElQd0ltT2U5eDdKMkV4Njl4RjBzRXFmZV9qRUdubFFaQkJPNUwyUlh4bjNxbnRRN0Y0LXJpSkJiS3B6LXJuTEk1NG1GSEE5d1VaaTZfVXBkbnpYMWY0Q2hzRGY4VkpRcU80SEh2NS1xdktNNNIB6wFBVV95cUxNY3p2RlZISG1IdlhwWGJubTdESVo0TWFnVXp5aW1YWnY4bldFSWJ2YXdUeERUVWV2UXpEWE9lVGxCXzZ4LXIyYkhQeWtkdUtVZmJiZndBd2hhVFVDMjdSaHczNVRJamJIM0M5N242VTJIWk5MMkdWYzEtc21mT2ZubXZSNzU4WnV4V1JIXzNsRmxST1NoNWNBUXE4RHQxU3RORjhsWEpzZ3FpN09oZWRhMGc1UEJ4Qk1LSDdiZjExT0pQQnk5Y01MVEJBQVIyWVAxUVFnRnFUdTJMeFVvZm9wSGs5SXBWQ1ZMM1ZN?oc=5</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2041,27 +2041,27 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>UK IT departments most confident on AI future-readiness - IT Brief UK</t>
+          <t>Grand Island police arrest one, cite juvenile after ‘GISH’ walk-out incident - KSNB</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Sun, 15 Feb 2026 09:15:00 GMT</t>
+          <t>Tue, 17 Feb 2026 00:20:00 GMT</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNamNzc0RLTS11blg3VG9iZTBZb0xIT2hMUWFSdkpfU1VqRFp4NktzSHRhdDFnSFYtNmtpZ2lpaU5uZkdaQlZfY2EzVFJvS0lzS3NNRC10bmx0UkxlRmFDLWdOLWNNLVdZVWJJdDM1VFBPWk5mc29Gd3lqOWJ1eU1Rd1hqeHNjVS04c3NV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPV3l1VWdJcmtfZGMwR1N4ekphc2JZSGhHUk10RWNxMEVLT1Ntd3NjNVhCVlY3TkpfaU16LUNfbzdYNEMzaExSdzRxb2lWY1d3YW5JWWZ5VFZmWHd0Vjk1ajFBU1R6VlhHYUpMVk1KX2RIRU95NUQzd2xVWDR6bVZNcmtHbDVUUGhrNk13RW1fOWJtS2JnYmVEa19Cd0hqTHZFNE53YjVkV1ZFMzZUSVlmZHpR0gHGAUFVX3lxTE1SZWlVQVcya3U0ZWVJTU9nOXBhX1RmcG9Xc1RPbzNCeUJCVnRnMHRBWHByRzAxc3lRdFk3eGNCSWJYX3gyREhIVjdXR0hzaURsS0ViZTFTZktkeDlaRTU4YkRSRk1tRDU2cDA1NDBRSGlXTG9kZUFsYnNQUUNBS09NSGlON05EYjBDN05JYVBISFNUQzdMdVBzdGFSYkRpM05qQzRyVkRMcldmcGtjMjZxVV9nNWNvdDhvZG9jYmJ1ZUNhWmF2dw?oc=5</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2071,27 +2071,27 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>How to Regulate, or Not Regulate, AI - The Regulatory Review</t>
+          <t>POLICE LOG: Loyalty points used for lavish purchases; backhoe strikes cruiser during storm cleanup - Marblehead Current</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 05:11:20 GMT</t>
+          <t>Mon, 16 Feb 2026 14:45:40 GMT</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQYlJpZG8wb0hoZjZJRTJsVWZkdEZDbXFWV1pCSXo3MDdSNmV5SmRuZjAxYUJ2RUVzMWNqMWtsWmpBWURtZXR4T1hTLTZVcWRfRnFTaTMxMl9VQm00VWdGTGJVbUgtY3F2TG9LeW5yLVRxRDU0VldmcmFLWHNKMXlFbFRkQ2xFaDNUa3kxSndaeXBmQUVYdFViUF9RdFZtaWlhUEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPLTN2UDAxazE4b2Myc1V0aldHOVBJMENtd3ZZY0xJeWxRRmZpUHhxUjNKMEcybE5yQ2JGVkN3bU1DOXZmSWlIN3pncXBXQWEteEdMaG5SSWtGbkpZdThwazF4bTNYM2xuN1BHd3N5OV9yemxaTVg2bE5KdjlDdXNsaV96VzJ0TWZWYUttTXh2eGtKQnRuT2xwWi1iYzJWSHFqeVQ2OTFyNnlodkNxVmxrX0dUMW9fZEZIZkZIR1RCekRlaHlQY1h3bW90QWNwbms5VXBvQw?oc=5</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2111,17 +2111,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>UK scale-up founders fear AI could trigger job cuts - IT Brief UK</t>
+          <t>The Future Of Artificial Intelligence: Physical AI and Humanoid Robotics Are The Next Industrial Frontier - FII Institute</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Sun, 15 Feb 2026 08:30:00 GMT</t>
+          <t>Tue, 17 Feb 2026 07:35:09 GMT</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOYndzSWxXbzlKMjMzYVM4VVY1eENMdm51MFVOOGRzME41aW5LaW9RaTk5WWVHUGpqdUJVNUZ0bVBKaWZ2ZU5aWHh6a0VtNVVRUEl3a2JEZlpTTkM1NkFiNFpaV0w4WWQ1U3kzNjhyTlV3djlKNHFMMnFFdHhSOFZOdkt5VG84QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPZjI0SWR2NTJER3NDT29KRmZuenZ0QTZGWm5Mdy1BWGNKTjd5T21iNHpPY3BJeTRIWEtWcFlLYVgzczUyb29CRkMzNFpsR2tKUTBpOTlJc3JLUHM2YXp4eU9LRkhFdEZFTVhueXhkUy05bGZXNnBZRk1WZDdRR0loVV9xaGR5eGFVTlp1Q1NvdFFVWjdxbGVDVkxxWmtlS3ZidlBJeTJMVTRYanlwMFVTWkxZR3AwSWd1UFRseGxDWkZsTFJSLWNCZjN4TENXS29JMTMweGFTemVQUQ?oc=5</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AI and Copyright: How Lessons from Litigation Can Pave the Way to Licensing - IPWatchdog.com</t>
+          <t>Could India challenge tech boss power at Delhi AI Impact Summit? - BBC</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Sun, 15 Feb 2026 17:26:53 GMT</t>
+          <t>Tue, 17 Feb 2026 00:12:58 GMT</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNNG9ncHFOb2M5SVhPRy05a0VCdDZ2cEMtQThxeTBjS3ZCT2pLb2JKLXAwNzZuM3EwYm9HOEx2eDFySEZteE9jcWpMQXBYLVE2clNQVVZUUmoweWhGVmNndmVZNWlHcEhXeWhmMjFOU2laLU1Kcm9tcDkzQ2FUVEtTZl9STnFjMExJeU55Z3NhQmxNc00?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBPSEtXQ0trd3o5V1lQbDF0NFhZN0NNdjRBNWo1U2RkcWhiV1E0bVZNa0Rmb1lxNkhkNExfMU5NOUUzNV9xWlFpbzIzU3g4WmIzYnh0NUl2S1dmdw?oc=5</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2171,17 +2171,17 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>India's Fractal Analytics drops 5% in trading debut as AI jitters keep investors cautious - Reuters</t>
+          <t>AI and Uncertainty Are Gnawing at the Edges of the Job Market - FE News</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 05:14:00 GMT</t>
+          <t>Tue, 17 Feb 2026 04:04:20 GMT</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNb0otek5maEhfSjQwZFkyUXNETUNDOUZVQnQzUjZwQTNGekRTcjl0TTRaUkNUM1ZNN3d0OTlxbUV2djVFQUl1WlVTYlAxbm05RmtVYmZ2TjJiWjFDVnY5eTNnWWp0WE56alJtZU5GTHVpcGJOZlAzMzRWUTQ1ekJfNG5XYVpiX3g5a0NveW9hSjFhUkdaLWoyakllb0Ezd0NBRzQya3k1cEkzTkFUQ05fWVFR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOTW9MMVd3b2Y0cTZFR0FpS0hOTzA4RzNqVFFKMnhDQTV2dE5xRzFqWFdQZ3BhMGp6VmFlT1hVbjUwVXBmUUItNHpLQUNBTXQzTzBzeUJUNF9kT2I1Uk5ZdFNvTFd5N3g4NW43M1FUaE8xWHpLQzJ5WVVJV3FEUE9fbkJpZWxNOGpSaGZVZjVzaWRIZXZGaUNRZnZ6dm5rdw?oc=5</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2201,17 +2201,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Why are experts sounding the alarm on AI risks? - Al Jazeera</t>
+          <t>Docs &amp; Dialogue II: AI, Love &amp; Loneliness - University College London</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Sun, 15 Feb 2026 11:37:19 GMT</t>
+          <t>Tue, 17 Feb 2026 06:05:04 GMT</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQdGlWWHY2VWJqeFAxTGY1ZG1JVkZkeXRleEctZWR1WGVCbHlBSXF5aDk4ZzdsdXFBX0hsZE1aUVFiemJwSWJRNzduQTFXQlhlaUVQcEN2MVhGOC1Yb2pfX2hHOUp5a2NOdjNRUUZfWklwMW1rNldVOU5lTVAwNXdISEVWNE9kbVFxMmZWV0dENTfSAZYBQVVfeXFMTmViTDVOUjU2Yl8zVEtfZXFDT19wLTFURlBPTjUwTE1JWmJvYUxESjhrR3BCaDB0TS1ubXpwdlZxR2hCR2xlVTNZZGtvOVUyenZuWGVha1BES2s5d29QWjhTckZIeldCVXc5VTRkWlBvbFdNWTk1RDg4WXlMREFPWjJjaDFvZV9DV2MwdWROVEJQb0MtU1JB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxOb1RTT3pqbFN1WjFrdkZSaEsxa3hSUndIR1luRXVjejVYNVJ2Rkg1X0V3d1JQUTNpWjA3MXhHaFoyaWFOZ1F2UVU5eklrSU55UWY2WlM3aEN2dnlpQjFfeVBGX1RzUzRJV3J4RnMtTGR1bHJtV2JqXzlMcTR5TGZYQmhDYVZaOUdNTjV3bmVKcHpHTUttaUVSS1huOU12dVBxdF9SNVJKT0xNRnA4QUtuQjZKYXNxZXBzMThNbnNkck9ldlFoemt5NUNFdWxfcXB5bWVJTUQwX0ZvMTNuT1pyaVVWSjRxOFJpeG5JVg?oc=5</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2231,17 +2231,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ICYMI: The Cost and Promise of AI and what it could mean for the future of Western Kentucky - WPSD Local 6</t>
+          <t>Claims that AI can help fix climate dismissed as greenwashing - The Guardian</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 01:40:54 GMT</t>
+          <t>Tue, 17 Feb 2026 05:00:00 GMT</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxQa2lnTElFdmdCNnZ0a2ZONzdTRFFBNS1OdUtXakl2WGlMTkpWLS1ZajFqRDZSNHU0Tks4S0Z4NDZwOG9seXVkOG1EQXBjTWZBSkJuYi1FWWhybm0zYnI4cEVkX0Z0SWxaSnY1MUxaOTRka1piV1lNcWNDSUI0Uy1vdDVzd1dtaWRPLVRfZnlkZTRucW8yYTY1SUdMeVRVOXFJS2ZnTkR5eDA3bGpqQmx5clVuWlczbVhXazVyUmtqVVNjM3dHcmU0YU9aTjE2UzFnbXRaclhjdnJ4a2x3SWduWW8xWXBiREE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNVkhjWktRSVpwRmxYa05yZ3FYU2x3OFRkR1BWZWpoWDdncHczMWE2NzEydjZmMGo0eTRTQWtXRWpOQkpTWTVRQVU1ZVNQX0x0YTBuUnNzN1Nmell5R1JxellLSkx6aWRrb3d6MjF1VWlRN3hNUHZlMFNzZDhCWlBWMG5IUEgydVNvd1FpS2RQODhBSTdwU09VelBobFRNbEVaZzRaaDlRRWlhc2RkNHJYZG54ckZ4NFE?oc=5</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2261,17 +2261,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Lumentum’s AI Optics Contract Puts Earnings Quality And Risks In Focus - Yahoo Finance</t>
+          <t>2026 will be the year local AI emerges in AEC - Planning, Building &amp; Construction Today</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 06:07:00 GMT</t>
+          <t>Tue, 17 Feb 2026 06:48:04 GMT</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxPWlV0b08xS00tU19MWDZGZ3BJd3RkVTg3VGR0WmVsVXppWmd2NEhXSkZNWXg3QU0xZ1UtWkx4am9CZ2xsOHJ4aDF3YzlSUlpkS3RwdkNfYnk0Q19TUnZ0NkJZWkREWFNMMWs0R2k0Sm8zQVZjdF9WT3pwd1dHNk5JandkdkQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOTHM3V3ZiZUNKWDE1Sl9NTXN3ZmVlOFdFOXVGeVpvNnU0UlpJS09NeWRJblZZaWlWVUVxTG9QVFF4MWlQeHVmczZ4NFpwMUxFd2VHSWRsSld3TXNFa1c0V2FuOFlkd1ZDeEFGYmNLREdaQTNEOVNTeUU1anVIeVltUlE3UDJ5a0dla2tsbkdPTDNRR1pzVEhXbngyYm50QnRWMFYtQnNGU0xGR2lmN05WOVZHeHRhNm9nQnU5bmdFeWVILVhtTDE4c05uZ1JzenA0WnpRdldMNA?oc=5</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2291,17 +2291,17 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AI Redefines the Role of Writers and Editors - ARCweb.com</t>
+          <t>RIBA 2026 AI Summit - Royal Institute of British Architects Journal</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 06:41:02 GMT</t>
+          <t>Tue, 17 Feb 2026 07:02:39 GMT</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE9TNUNrdjV4cml0OF9TSE5TMVVMbG45Z25Zc2x6ZXFGRVFVSUxvSnR3LTg2QXhhQjc5ZXBWMHRWN2pEU0s4RVRGNFRENDB4a1BhNWZhMGlyeG81WnE3Sk02R1dXUHNpSC1MY0xEWGR3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxPbHB6STQzWkhZTkRtM000eTdPT2lSd21wZHl5bDFLTWRDZ18zaFFNWnRCSC1EVi1nZU9hMlpTUEpFMmpiSnRlTWYwaWg2Rk9VODh5UDd6TkZyOUNTTmg1UzdVaGRQU3J6YnVxeGQ3Q3d0M1VfOWR5NGUzWVVuaG9Oc0xSSHc?oc=5</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2321,17 +2321,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Elon Musk Envisions a Future of 'Zero Scarcity' with AI and Robotics - International Business Times UK</t>
+          <t>Infosys and Anthropic Announce Collaboration to Unlock AI Value across Complex, Regulated Industries - PR Newswire UK</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Sun, 15 Feb 2026 22:53:00 GMT</t>
+          <t>Tue, 17 Feb 2026 04:38:00 GMT</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE5EYmY0WWhhYnMtZGtEeGRFa0lUOHRLSnJKNlI5Y3NraUxNcUI3dTNqNEVnS2FuUWlXMTBuNS1SczFnN1ZwVEtwelVKVXo3NUNIVUlHMV9ITERmeDNsUHRuSTBDeXFTWUhGWlNueS1Sc1Frc3BSRDUybw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxOSG55SEtjY1lyYUVlVmNfaFhkV1F1RGtHY3JUZ0RlWEYyWUlVMVlvNW83R0ZRbDk2VXJ3NmRzV1ZKNDdBWUNQdnBqNTdkZEh2Sl9yNnZUenNlN1dQRC15NmdiSFRhZThqMXZqcS0xRFVFSmNVanhDaDl6OEVZRVh5bzJSOWI3OXN3ZDdiRDhZZ3BDdUhGN21DSlJ2bExGVXJ3aGJHaDdUZ2ZQOUNUajY0NnhpdHNJUW9rbGNfUkd4STR2bDF4azVLNUx4dkREdmlzdTdURFZZWkVNa1p1UWdDanZoRnQ4ZFU0ZlduUzZ3?oc=5</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -2351,17 +2351,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AI, automation and weight-loss drugs: 3 thematic investment trends analysts say are worth watching in 2026 - Yahoo! Finance Canada</t>
+          <t>Energy software development companies: Top providers compared - businesscloud.co.uk</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Sun, 15 Feb 2026 12:35:00 GMT</t>
+          <t>Tue, 17 Feb 2026 06:52:52 GMT</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxOUFM5M2QxSkdGSFctVFBCb09FZ2RudDRrcS15YURyWmpJcFk2MUpIcnJsWUV3YjBlTWY2T3RDMHFJYVNPX2ZuS0RldHNQbzB5NG44WDJHY2prQmt6RVNkVkUtNm1FaTM4Q3hBN3hxRHJHZlZhNXA2Nks0OEJnU0RxYXFBZWN1NDQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOWDB0eUhkdjZXYkVHbm9YcDQtVGVoc1FRWGl5dHNQcm1Ua2h2ZHA2SmFfNHYtZDl3ZG8xM2ZJMkZUNzR3OEFOYlZjLVBDLXlIRXEzOW9zQ242akdPZWVDS2NDUWJkdEMydEFHMVhBZFZoeUU0YWo1QmhOWWxTSUs3R29OajhxaGtuNEZUbzM2MHJWXzNCNl9Zb3l1b25WTjZmV1BPMmZ3QWF3WjFWVktTQQ?oc=5</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -2371,27 +2371,27 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>‘Fake Flex’ Trend Raises Alarm Over AI-Driven Fraud and Social Media Illusions - Koreabizwire</t>
+          <t>AI and Cybersecurity: Powering the next frontier of business resilience - EY</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Mon, 16 Feb 2026 03:37:14 GMT</t>
+          <t>Tue, 17 Feb 2026 04:42:02 GMT</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxONGF1eUN5eU9EZzg4U04tXzViQlVYUjk4Q3d3TzZha1lPRWJQd0VLd3ViSC10OGQ2VG1Xc1JGdVFDTk1tNFJRNVN2aE9ySjdaWThtSDdUaGtmZHRBYUstdzlQdVpSUDFUaC1mY3ppM2hva3NfQnkwU0E5ekhKYkhLMmlJbENDd2otcWs2NjZSejFMNnluMkl3aGNjMENzak1sOVdBV1BGenZUZ0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNbUZVbzZCZXVnTTVaVURYMHJmNU5pSlplT2Q5ZHNWTkhsbjNpTWJ6UXZ6TGYzLTlaMGtmdHl3dEpCSVp1ekJkbTVJam14Z08tUkhSQ0dZUTZRRGd5TlcwQnpWZEVwdnNyLXVRUFMwUHd1UEJSTUptVEJqQjJnMHZJR2JmU0FWUHlCaktnc0ZVZWVZQzg4YWtxMGJJdWtwZkpVUlBTWndLMHNsbDFFTXp6SldPZDRaRkwtbkdoaUtR?oc=5</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -2401,27 +2401,27 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Egypt arrests woman over alleged Hajj visa scam - Gulf News</t>
+          <t>Guest Post — 2026 Global Strategy Briefing For Boards on Quantum And AI - The Quantum Insider</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Sun, 15 Feb 2026 12:46:30 GMT</t>
+          <t>Mon, 16 Feb 2026 09:18:20 GMT</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPSFdvWExQTGR0LWljZEdBZ0ZiUkw2MFQ0OVdQeU9wNmxzR0lBMm1vMkZCQnRZMVJwSUc3RUpqZ2ZFMzdPTlJodjBQOENodmNsMG0yT0NLYmJld1JOU2t3Qkp3d2lPeC1aempuV2x4Nk9pb1JvWHdBSlMwYkszZ2FtZlNwZ0s4cGJHZWMwa3J5bVBESkI5M0HSAagBQVVfeXFMTXdmczVEOU01RW05YUdNdHpsRVU0WnRuOGoydmNwdVFEYkkzSThhREdTOW5KUF9HdlZyd3dHNlJ4b3pzR0xScDVrdnBQOXVvelB3WmFqT1ZmVFpXUGdxQzNodmlsR080YnJFaWNqUEQ3dDRYUHd5WTdlbVltUHVtYm1taHJMTG1hZzEtamp0NmViLVljR0JTcklqSlZ2bUZmRGZkN1pROURt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNNG5vdXE5VHNLZ3BtYUZqc0ZLbXlITjNjMU5EN1VOcFhnekk3bjVZRkdLR0NZMW5aeUZpQV9FVkVCVzhmUFJYdDRuNU91cHMwd21lMUYtbk00anIxMzk4R0UyM3pEczRwZmwyZlVVMmxxSm1wdVNHdWJmNjR1aE9rb2o1cENLWUF3ZnlSNFBObDFiMlFHRkh1dmN5QldodEQ3cmpJdlRhbmV2bk4zTXpVZg?oc=5</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -2431,30 +2431,1080 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>How AI is affecting productivity and jobs in Europe - CEPR</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Tue, 17 Feb 2026 00:01:49 GMT</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxNdll5X3ljSHVYTHB2aHMxOXctRTRjWW43VHpWQzRXRkFoZjFQbW5BLWZIX2VtazR2Q0t0R2VLcHVFSDNXQWlHMklpY0h0aDNxS2tDNFJsWVE3bWRpdkN2R2ctclZZby1FTExnUUF2Ny1BazNINllMbFhsNFJYdnFjelRn?oc=5</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Chief AI officer or CTO? Travel’s evolving executive playbook - PhocusWire</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Tue, 17 Feb 2026 06:03:42 GMT</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPUENOWlhqcElkUGNJZEdXNmI4R2ZCai1IVXdYbElvaHBkeTdLeWE3MldWT3pFQnowMUhGc2ptR1VGNlJzTXVzWEdsTGt3UWIwVGVRa0xya3QwQXlyY1dJam1OdWw0dGs5ZXFNWDZoQkdjUzN2WE9jYlAyQ25PdUluYm5Cc2d0QWVIZWRnV3BreE9YY2M?oc=5</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Dutch Data Protection Authority Warns OpenClaw AI Agents Pose Major Cybersecurity and Privacy Risks - BABL AI</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Tue, 17 Feb 2026 01:40:03 GMT</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPN3dyalhqb1BlRVA4d002cmY0U2F3YVdNb29KOWZqc1JlcVRJMHFuRU1hNVNRU0ZqU3R6S2UwVS01SV9nTzk4Y252WVM4N19MQXEtMGVLSTZyRkxiSkI2SEx4cXhVYzBjSGE3X2F5QXNNN18wakowa2RnQVA1MmI3RE50bHRoS0Q4OFVJekFCSnRwN0ZRN1NfdkVlQ3lQQTctUFJQajBGdnU1TXdUOTJFbTVDbmxwWnM?oc=5</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>What is the future of Artificial Intelligence regulation? - telefonica.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Mon, 16 Feb 2026 16:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNTm9xd3k5eTN